--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,13 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D543"/>
+  <dimension ref="A1:E543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -438,10 +439,15 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>price_00:15</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -457,11 +463,14 @@
         <v>71818.39999999999</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>71818.39999999999</v>
+        <v>71663.39999999999</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>71818.39999999999</v>
       </c>
+      <c r="E2" s="1" t="n">
+        <v>71663.39999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -473,11 +482,14 @@
         <v>2127.37</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>2127.37</v>
+        <v>2126.71</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>2127.37</v>
       </c>
+      <c r="E3" s="1" t="n">
+        <v>2126.71</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -489,9 +501,12 @@
         <v>89.45</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>89.45</v>
+        <v>89.59</v>
       </c>
       <c r="D4" s="1" t="n">
+        <v>89.59</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>89.45</v>
       </c>
     </row>
@@ -505,9 +520,12 @@
         <v>3.77</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>3.77</v>
+        <v>3.861</v>
       </c>
       <c r="D5" s="1" t="n">
+        <v>3.861</v>
+      </c>
+      <c r="E5" s="1" t="n">
         <v>3.77</v>
       </c>
     </row>
@@ -521,9 +539,12 @@
         <v>1.4082</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>1.4082</v>
+        <v>1.4085</v>
       </c>
       <c r="D6" s="1" t="n">
+        <v>1.4085</v>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>1.4082</v>
       </c>
     </row>
@@ -537,9 +558,12 @@
         <v>0.09796000000000001</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.09796000000000001</v>
+        <v>0.09828000000000001</v>
       </c>
       <c r="D7" s="1" t="n">
+        <v>0.09828000000000001</v>
+      </c>
+      <c r="E7" s="1" t="n">
         <v>0.09796000000000001</v>
       </c>
     </row>
@@ -553,11 +577,14 @@
         <v>0.014568</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>0.014568</v>
+        <v>0.014478</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>0.014568</v>
       </c>
+      <c r="E8" s="1" t="n">
+        <v>0.014478</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -569,11 +596,14 @@
         <v>662.61</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>662.61</v>
+        <v>660.9299999999999</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>662.61</v>
       </c>
+      <c r="E9" s="1" t="n">
+        <v>660.9299999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -585,9 +615,12 @@
         <v>18.938</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>18.938</v>
+        <v>19.415</v>
       </c>
       <c r="D10" s="1" t="n">
+        <v>19.415</v>
+      </c>
+      <c r="E10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -601,11 +634,14 @@
         <v>0.0034782</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>0.0034782</v>
+        <v>0.0034747</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>0.0034782</v>
       </c>
+      <c r="E11" s="1" t="n">
+        <v>0.0034747</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -617,9 +653,12 @@
         <v>36.244</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>36.244</v>
+        <v>36.304</v>
       </c>
       <c r="D12" s="1" t="n">
+        <v>36.304</v>
+      </c>
+      <c r="E12" s="1" t="n">
         <v>36.244</v>
       </c>
     </row>
@@ -633,9 +672,12 @@
         <v>213.2</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>213.2</v>
+        <v>213.55</v>
       </c>
       <c r="D13" s="1" t="n">
+        <v>213.55</v>
+      </c>
+      <c r="E13" s="1" t="n">
         <v>213.2</v>
       </c>
     </row>
@@ -649,11 +691,14 @@
         <v>0.0011389</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>0.0011389</v>
+        <v>0.0011346</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>0.0011389</v>
       </c>
+      <c r="E14" s="1" t="n">
+        <v>0.0011346</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -665,11 +710,14 @@
         <v>0.29276</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>0.29276</v>
+        <v>0.28578</v>
       </c>
       <c r="D15" s="1" t="n">
         <v>0.29276</v>
       </c>
+      <c r="E15" s="1" t="n">
+        <v>0.28578</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -681,9 +729,12 @@
         <v>230.3</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>230.3</v>
+        <v>234.41</v>
       </c>
       <c r="D16" s="1" t="n">
+        <v>234.41</v>
+      </c>
+      <c r="E16" s="1" t="n">
         <v>230.3</v>
       </c>
     </row>
@@ -697,11 +748,14 @@
         <v>1.0137</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>1.0137</v>
+        <v>1.0133</v>
       </c>
       <c r="D17" s="1" t="n">
         <v>1.0137</v>
       </c>
+      <c r="E17" s="1" t="n">
+        <v>1.0133</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -713,9 +767,12 @@
         <v>0.2714</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>0.2714</v>
+        <v>0.2717</v>
       </c>
       <c r="D18" s="1" t="n">
+        <v>0.2717</v>
+      </c>
+      <c r="E18" s="1" t="n">
         <v>0.2714</v>
       </c>
     </row>
@@ -729,11 +786,14 @@
         <v>9.893000000000001</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>9.893000000000001</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="D19" s="1" t="n">
         <v>9.893000000000001</v>
       </c>
+      <c r="E19" s="1" t="n">
+        <v>9.890000000000001</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -745,11 +805,14 @@
         <v>5035.65</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>5035.65</v>
+        <v>5033.31</v>
       </c>
       <c r="D20" s="1" t="n">
         <v>5035.65</v>
       </c>
+      <c r="E20" s="1" t="n">
+        <v>5033.31</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -761,11 +824,14 @@
         <v>463.29</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>463.29</v>
+        <v>462.57</v>
       </c>
       <c r="D21" s="1" t="n">
         <v>463.29</v>
       </c>
+      <c r="E21" s="1" t="n">
+        <v>462.57</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -777,9 +843,12 @@
         <v>1.4185</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>1.4185</v>
+        <v>1.4248</v>
       </c>
       <c r="D22" s="1" t="n">
+        <v>1.4248</v>
+      </c>
+      <c r="E22" s="1" t="n">
         <v>1.4185</v>
       </c>
     </row>
@@ -793,9 +862,12 @@
         <v>1.1298</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>1.1298</v>
+        <v>1.1445</v>
       </c>
       <c r="D23" s="1" t="n">
+        <v>1.1445</v>
+      </c>
+      <c r="E23" s="1" t="n">
         <v>1.1298</v>
       </c>
     </row>
@@ -809,9 +881,12 @@
         <v>1.351</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>1.351</v>
+        <v>1.36</v>
       </c>
       <c r="D24" s="1" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E24" s="1" t="n">
         <v>1.351</v>
       </c>
     </row>
@@ -825,11 +900,14 @@
         <v>9.260999999999999</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>9.260999999999999</v>
+        <v>9.257</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>9.260999999999999</v>
       </c>
+      <c r="E25" s="1" t="n">
+        <v>9.257</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -841,11 +919,14 @@
         <v>0.3749</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>0.3749</v>
+        <v>0.3714</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>0.3749</v>
       </c>
+      <c r="E26" s="1" t="n">
+        <v>0.3714</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -862,6 +943,9 @@
       <c r="D27" s="1" t="n">
         <v>0.887</v>
       </c>
+      <c r="E27" s="1" t="n">
+        <v>0.887</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -873,9 +957,12 @@
         <v>1.798</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>1.798</v>
+        <v>1.803</v>
       </c>
       <c r="D28" s="1" t="n">
+        <v>1.803</v>
+      </c>
+      <c r="E28" s="1" t="n">
         <v>1.798</v>
       </c>
     </row>
@@ -889,11 +976,14 @@
         <v>0.112</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>0.112</v>
+        <v>0.1115</v>
       </c>
       <c r="D29" s="1" t="n">
         <v>0.112</v>
       </c>
+      <c r="E29" s="1" t="n">
+        <v>0.1115</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -905,9 +995,12 @@
         <v>0.002058</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>0.002058</v>
+        <v>0.002059</v>
       </c>
       <c r="D30" s="1" t="n">
+        <v>0.002059</v>
+      </c>
+      <c r="E30" s="1" t="n">
         <v>0.002058</v>
       </c>
     </row>
@@ -921,11 +1014,14 @@
         <v>1.506</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>1.506</v>
+        <v>1.504</v>
       </c>
       <c r="D31" s="1" t="n">
         <v>1.506</v>
       </c>
+      <c r="E31" s="1" t="n">
+        <v>1.504</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -937,11 +1033,14 @@
         <v>0.1792</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>0.1792</v>
+        <v>0.178</v>
       </c>
       <c r="D32" s="1" t="n">
         <v>0.1792</v>
       </c>
+      <c r="E32" s="1" t="n">
+        <v>0.178</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -953,9 +1052,12 @@
         <v>0.1048</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>0.1048</v>
+        <v>0.1049</v>
       </c>
       <c r="D33" s="1" t="n">
+        <v>0.1049</v>
+      </c>
+      <c r="E33" s="1" t="n">
         <v>0.1048</v>
       </c>
     </row>
@@ -969,11 +1071,14 @@
         <v>113.97</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>113.97</v>
+        <v>113.94</v>
       </c>
       <c r="D34" s="1" t="n">
         <v>113.97</v>
       </c>
+      <c r="E34" s="1" t="n">
+        <v>113.94</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -985,11 +1090,14 @@
         <v>6.893</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>6.893</v>
+        <v>6.776</v>
       </c>
       <c r="D35" s="1" t="n">
         <v>6.893</v>
       </c>
+      <c r="E35" s="1" t="n">
+        <v>6.776</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1001,9 +1109,12 @@
         <v>0.017313</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>0.017313</v>
+        <v>0.017384</v>
       </c>
       <c r="D36" s="1" t="n">
+        <v>0.017384</v>
+      </c>
+      <c r="E36" s="1" t="n">
         <v>0.017313</v>
       </c>
     </row>
@@ -1017,9 +1128,12 @@
         <v>0.3666</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>0.3666</v>
+        <v>0.3667</v>
       </c>
       <c r="D37" s="1" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="E37" s="1" t="n">
         <v>0.3666</v>
       </c>
     </row>
@@ -1033,9 +1147,12 @@
         <v>55.3</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>55.3</v>
+        <v>55.42</v>
       </c>
       <c r="D38" s="1" t="n">
+        <v>55.42</v>
+      </c>
+      <c r="E38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -1049,11 +1166,14 @@
         <v>0.58963</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>0.58963</v>
+        <v>0.58131</v>
       </c>
       <c r="D39" s="1" t="n">
         <v>0.58963</v>
       </c>
+      <c r="E39" s="1" t="n">
+        <v>0.58131</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1065,11 +1185,14 @@
         <v>4.064</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>4.064</v>
+        <v>4.057</v>
       </c>
       <c r="D40" s="1" t="n">
         <v>4.064</v>
       </c>
+      <c r="E40" s="1" t="n">
+        <v>4.057</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1081,11 +1204,14 @@
         <v>0.04938</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>0.04938</v>
+        <v>0.04927</v>
       </c>
       <c r="D41" s="1" t="n">
         <v>0.04938</v>
       </c>
+      <c r="E41" s="1" t="n">
+        <v>0.04927</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1097,11 +1223,14 @@
         <v>0.7056</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>0.7056</v>
+        <v>0.7034</v>
       </c>
       <c r="D42" s="1" t="n">
         <v>0.7056</v>
       </c>
+      <c r="E42" s="1" t="n">
+        <v>0.7034</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1113,9 +1242,12 @@
         <v>0.23323</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>0.23323</v>
+        <v>0.23341</v>
       </c>
       <c r="D43" s="1" t="n">
+        <v>0.23341</v>
+      </c>
+      <c r="E43" s="1" t="n">
         <v>0.23323</v>
       </c>
     </row>
@@ -1129,9 +1261,12 @@
         <v>0.35391</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>0.35391</v>
+        <v>0.35392</v>
       </c>
       <c r="D44" s="1" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="E44" s="1" t="n">
         <v>0.35391</v>
       </c>
     </row>
@@ -1145,11 +1280,14 @@
         <v>0.1731</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>0.1731</v>
+        <v>0.1714</v>
       </c>
       <c r="D45" s="1" t="n">
         <v>0.1731</v>
       </c>
+      <c r="E45" s="1" t="n">
+        <v>0.1714</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1161,11 +1299,14 @@
         <v>0.0266</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>0.0266</v>
+        <v>0.0264</v>
       </c>
       <c r="D46" s="1" t="n">
         <v>0.0266</v>
       </c>
+      <c r="E46" s="1" t="n">
+        <v>0.0264</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1177,11 +1318,14 @@
         <v>0.00605</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>0.00605</v>
+        <v>0.006043</v>
       </c>
       <c r="D47" s="1" t="n">
         <v>0.00605</v>
       </c>
+      <c r="E47" s="1" t="n">
+        <v>0.006043</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1193,11 +1337,14 @@
         <v>0.007515</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>0.007515</v>
+        <v>0.007513</v>
       </c>
       <c r="D48" s="1" t="n">
         <v>0.007515</v>
       </c>
+      <c r="E48" s="1" t="n">
+        <v>0.007513</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1209,11 +1356,14 @@
         <v>0.1111</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>0.1111</v>
+        <v>0.1108</v>
       </c>
       <c r="D49" s="1" t="n">
         <v>0.1111</v>
       </c>
+      <c r="E49" s="1" t="n">
+        <v>0.1108</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1225,11 +1375,14 @@
         <v>0.04046</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>0.04046</v>
+        <v>0.04033</v>
       </c>
       <c r="D50" s="1" t="n">
         <v>0.04046</v>
       </c>
+      <c r="E50" s="1" t="n">
+        <v>0.04033</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1241,11 +1394,14 @@
         <v>0.1671</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>0.1671</v>
+        <v>0.1659</v>
       </c>
       <c r="D51" s="1" t="n">
         <v>0.1671</v>
       </c>
+      <c r="E51" s="1" t="n">
+        <v>0.1659</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1257,9 +1413,12 @@
         <v>0.00354</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>0.00354</v>
+        <v>0.00355</v>
       </c>
       <c r="D52" s="1" t="n">
+        <v>0.00355</v>
+      </c>
+      <c r="E52" s="1" t="n">
         <v>0.00354</v>
       </c>
     </row>
@@ -1273,11 +1432,14 @@
         <v>2.665</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>2.665</v>
+        <v>2.662</v>
       </c>
       <c r="D53" s="1" t="n">
         <v>2.665</v>
       </c>
+      <c r="E53" s="1" t="n">
+        <v>2.662</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1289,11 +1451,14 @@
         <v>0.006298</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>0.006298</v>
+        <v>0.006277</v>
       </c>
       <c r="D54" s="1" t="n">
         <v>0.006298</v>
       </c>
+      <c r="E54" s="1" t="n">
+        <v>0.006277</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1305,11 +1470,14 @@
         <v>0.03019</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>0.03019</v>
+        <v>0.02989</v>
       </c>
       <c r="D55" s="1" t="n">
         <v>0.03019</v>
       </c>
+      <c r="E55" s="1" t="n">
+        <v>0.02989</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1321,11 +1489,14 @@
         <v>0.7463</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>0.7463</v>
+        <v>0.7443</v>
       </c>
       <c r="D56" s="1" t="n">
         <v>0.7463</v>
       </c>
+      <c r="E56" s="1" t="n">
+        <v>0.7443</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1337,11 +1508,14 @@
         <v>0.105</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>0.105</v>
+        <v>0.1048</v>
       </c>
       <c r="D57" s="1" t="n">
         <v>0.105</v>
       </c>
+      <c r="E57" s="1" t="n">
+        <v>0.1048</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1353,11 +1527,14 @@
         <v>0.9622000000000001</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9523</v>
       </c>
       <c r="D58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
+      <c r="E58" s="1" t="n">
+        <v>0.9523</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1369,9 +1546,12 @@
         <v>0.08381</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>0.08381</v>
+        <v>0.08391</v>
       </c>
       <c r="D59" s="1" t="n">
+        <v>0.08391</v>
+      </c>
+      <c r="E59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -1385,11 +1565,14 @@
         <v>0.07001</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>0.07001</v>
+        <v>0.06947</v>
       </c>
       <c r="D60" s="1" t="n">
         <v>0.07001</v>
       </c>
+      <c r="E60" s="1" t="n">
+        <v>0.06947</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1401,9 +1584,12 @@
         <v>0.05469</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>0.05469</v>
+        <v>0.05482</v>
       </c>
       <c r="D61" s="1" t="n">
+        <v>0.05482</v>
+      </c>
+      <c r="E61" s="1" t="n">
         <v>0.05469</v>
       </c>
     </row>
@@ -1417,9 +1603,12 @@
         <v>0.009535999999999999</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>0.009535999999999999</v>
+        <v>0.009571</v>
       </c>
       <c r="D62" s="1" t="n">
+        <v>0.009571</v>
+      </c>
+      <c r="E62" s="1" t="n">
         <v>0.009535999999999999</v>
       </c>
     </row>
@@ -1433,9 +1622,12 @@
         <v>0.28945</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>0.28945</v>
+        <v>0.28956</v>
       </c>
       <c r="D63" s="1" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="E63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -1449,9 +1641,12 @@
         <v>0.06894</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>0.06894</v>
+        <v>0.07034</v>
       </c>
       <c r="D64" s="1" t="n">
+        <v>0.07034</v>
+      </c>
+      <c r="E64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -1465,11 +1660,14 @@
         <v>0.3073</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>0.3073</v>
+        <v>0.3068</v>
       </c>
       <c r="D65" s="1" t="n">
         <v>0.3073</v>
       </c>
+      <c r="E65" s="1" t="n">
+        <v>0.3068</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1481,9 +1679,12 @@
         <v>0.16346</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>0.16346</v>
+        <v>0.1636</v>
       </c>
       <c r="D66" s="1" t="n">
+        <v>0.1636</v>
+      </c>
+      <c r="E66" s="1" t="n">
         <v>0.16346</v>
       </c>
     </row>
@@ -1497,9 +1698,12 @@
         <v>0.11934</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>0.11934</v>
+        <v>0.11988</v>
       </c>
       <c r="D67" s="1" t="n">
+        <v>0.11988</v>
+      </c>
+      <c r="E67" s="1" t="n">
         <v>0.11934</v>
       </c>
     </row>
@@ -1513,11 +1717,14 @@
         <v>0.09734</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>0.09734</v>
+        <v>0.09712</v>
       </c>
       <c r="D68" s="1" t="n">
         <v>0.09734</v>
       </c>
+      <c r="E68" s="1" t="n">
+        <v>0.09712</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1529,11 +1736,14 @@
         <v>0.1259</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>0.1259</v>
+        <v>0.1254</v>
       </c>
       <c r="D69" s="1" t="n">
         <v>0.1259</v>
       </c>
+      <c r="E69" s="1" t="n">
+        <v>0.1254</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1545,9 +1755,12 @@
         <v>8.567</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>8.567</v>
+        <v>8.582000000000001</v>
       </c>
       <c r="D70" s="1" t="n">
+        <v>8.582000000000001</v>
+      </c>
+      <c r="E70" s="1" t="n">
         <v>8.567</v>
       </c>
     </row>
@@ -1566,6 +1779,9 @@
       <c r="D71" s="1" t="n">
         <v>0.24</v>
       </c>
+      <c r="E71" s="1" t="n">
+        <v>0.24</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1577,11 +1793,14 @@
         <v>0.05179</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>0.05179</v>
+        <v>0.05163</v>
       </c>
       <c r="D72" s="1" t="n">
         <v>0.05179</v>
       </c>
+      <c r="E72" s="1" t="n">
+        <v>0.05163</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1593,9 +1812,12 @@
         <v>0.05039</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>0.05039</v>
+        <v>0.05059</v>
       </c>
       <c r="D73" s="1" t="n">
+        <v>0.05059</v>
+      </c>
+      <c r="E73" s="1" t="n">
         <v>0.05039</v>
       </c>
     </row>
@@ -1609,11 +1831,14 @@
         <v>0.1253</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>0.1253</v>
+        <v>0.1252</v>
       </c>
       <c r="D74" s="1" t="n">
         <v>0.1253</v>
       </c>
+      <c r="E74" s="1" t="n">
+        <v>0.1252</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1625,11 +1850,14 @@
         <v>0.04726</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>0.04726</v>
+        <v>0.04688</v>
       </c>
       <c r="D75" s="1" t="n">
         <v>0.04726</v>
       </c>
+      <c r="E75" s="1" t="n">
+        <v>0.04688</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1641,9 +1869,12 @@
         <v>0.06758</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>0.06758</v>
+        <v>0.06786</v>
       </c>
       <c r="D76" s="1" t="n">
+        <v>0.06786</v>
+      </c>
+      <c r="E76" s="1" t="n">
         <v>0.06758</v>
       </c>
     </row>
@@ -1657,9 +1888,12 @@
         <v>0.12685</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>0.12685</v>
+        <v>0.12881</v>
       </c>
       <c r="D77" s="1" t="n">
+        <v>0.12881</v>
+      </c>
+      <c r="E77" s="1" t="n">
         <v>0.12685</v>
       </c>
     </row>
@@ -1673,11 +1907,14 @@
         <v>0.1653</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>0.1653</v>
+        <v>0.1646</v>
       </c>
       <c r="D78" s="1" t="n">
         <v>0.1653</v>
       </c>
+      <c r="E78" s="1" t="n">
+        <v>0.1646</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1689,11 +1926,14 @@
         <v>0.02738</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>0.02738</v>
+        <v>0.0272</v>
       </c>
       <c r="D79" s="1" t="n">
         <v>0.02738</v>
       </c>
+      <c r="E79" s="1" t="n">
+        <v>0.0272</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1705,11 +1945,14 @@
         <v>354.5</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>354.5</v>
+        <v>354.29</v>
       </c>
       <c r="D80" s="1" t="n">
         <v>354.5</v>
       </c>
+      <c r="E80" s="1" t="n">
+        <v>354.29</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1721,11 +1964,14 @@
         <v>7.249000000000001e-05</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>7.249000000000001e-05</v>
+        <v>7.211999999999999e-05</v>
       </c>
       <c r="D81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
+      <c r="E81" s="1" t="n">
+        <v>7.211999999999999e-05</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1737,11 +1983,14 @@
         <v>0.2681</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>0.2681</v>
+        <v>0.2676</v>
       </c>
       <c r="D82" s="1" t="n">
         <v>0.2681</v>
       </c>
+      <c r="E82" s="1" t="n">
+        <v>0.2676</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1753,11 +2002,14 @@
         <v>1.1447</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>1.1447</v>
+        <v>1.1408</v>
       </c>
       <c r="D83" s="1" t="n">
         <v>1.1447</v>
       </c>
+      <c r="E83" s="1" t="n">
+        <v>1.1408</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1769,11 +2021,14 @@
         <v>0.3592</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>0.3592</v>
+        <v>0.3591</v>
       </c>
       <c r="D84" s="1" t="n">
         <v>0.3592</v>
       </c>
+      <c r="E84" s="1" t="n">
+        <v>0.3591</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1785,11 +2040,14 @@
         <v>2.0181</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>2.0181</v>
+        <v>2.0067</v>
       </c>
       <c r="D85" s="1" t="n">
         <v>2.0181</v>
       </c>
+      <c r="E85" s="1" t="n">
+        <v>2.0067</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1801,11 +2059,14 @@
         <v>1.3167</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>1.3167</v>
+        <v>1.3126</v>
       </c>
       <c r="D86" s="1" t="n">
         <v>1.3167</v>
       </c>
+      <c r="E86" s="1" t="n">
+        <v>1.3126</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1817,9 +2078,12 @@
         <v>32.97</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>32.97</v>
+        <v>33.01</v>
       </c>
       <c r="D87" s="1" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="E87" s="1" t="n">
         <v>32.97</v>
       </c>
     </row>
@@ -1833,9 +2097,12 @@
         <v>0.01046</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>0.01046</v>
+        <v>0.01071</v>
       </c>
       <c r="D88" s="1" t="n">
+        <v>0.01071</v>
+      </c>
+      <c r="E88" s="1" t="n">
         <v>0.01046</v>
       </c>
     </row>
@@ -1849,11 +2116,14 @@
         <v>0.01835</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>0.01835</v>
+        <v>0.01832</v>
       </c>
       <c r="D89" s="1" t="n">
         <v>0.01835</v>
       </c>
+      <c r="E89" s="1" t="n">
+        <v>0.01832</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1865,9 +2135,12 @@
         <v>0.03571</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>0.03571</v>
+        <v>0.03619</v>
       </c>
       <c r="D90" s="1" t="n">
+        <v>0.03619</v>
+      </c>
+      <c r="E90" s="1" t="n">
         <v>0.03571</v>
       </c>
     </row>
@@ -1881,11 +2154,14 @@
         <v>0.01202</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>0.01202</v>
+        <v>0.01194</v>
       </c>
       <c r="D91" s="1" t="n">
         <v>0.01202</v>
       </c>
+      <c r="E91" s="1" t="n">
+        <v>0.01194</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1897,11 +2173,14 @@
         <v>3.12</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>3.12</v>
+        <v>3.118</v>
       </c>
       <c r="D92" s="1" t="n">
         <v>3.12</v>
       </c>
+      <c r="E92" s="1" t="n">
+        <v>3.118</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1913,9 +2192,12 @@
         <v>0.005638</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>0.005638</v>
+        <v>0.00564</v>
       </c>
       <c r="D93" s="1" t="n">
+        <v>0.00564</v>
+      </c>
+      <c r="E93" s="1" t="n">
         <v>0.005638</v>
       </c>
     </row>
@@ -1929,9 +2211,12 @@
         <v>0.094</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>0.094</v>
+        <v>0.0945</v>
       </c>
       <c r="D94" s="1" t="n">
+        <v>0.0945</v>
+      </c>
+      <c r="E94" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -1945,9 +2230,12 @@
         <v>0.6006</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>0.6006</v>
+        <v>0.6028</v>
       </c>
       <c r="D95" s="1" t="n">
+        <v>0.6028</v>
+      </c>
+      <c r="E95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -1961,11 +2249,14 @@
         <v>1.3e-05</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>1.3e-05</v>
+        <v>1.29e-05</v>
       </c>
       <c r="D96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
+      <c r="E96" s="1" t="n">
+        <v>1.29e-05</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1977,9 +2268,12 @@
         <v>1.136</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>1.136</v>
+        <v>1.143</v>
       </c>
       <c r="D97" s="1" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="E97" s="1" t="n">
         <v>1.136</v>
       </c>
     </row>
@@ -1993,11 +2287,14 @@
         <v>0.26116</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>0.26116</v>
+        <v>0.25933</v>
       </c>
       <c r="D98" s="1" t="n">
         <v>0.26116</v>
       </c>
+      <c r="E98" s="1" t="n">
+        <v>0.25933</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2009,11 +2306,14 @@
         <v>1.151</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>1.151</v>
+        <v>1.15</v>
       </c>
       <c r="D99" s="1" t="n">
         <v>1.151</v>
       </c>
+      <c r="E99" s="1" t="n">
+        <v>1.15</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2025,11 +2325,14 @@
         <v>1.866</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>1.866</v>
+        <v>1.864</v>
       </c>
       <c r="D100" s="1" t="n">
         <v>1.866</v>
       </c>
+      <c r="E100" s="1" t="n">
+        <v>1.864</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2041,9 +2344,12 @@
         <v>0.01597</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>0.01597</v>
+        <v>0.01599</v>
       </c>
       <c r="D101" s="1" t="n">
+        <v>0.01599</v>
+      </c>
+      <c r="E101" s="1" t="n">
         <v>0.01597</v>
       </c>
     </row>
@@ -2057,11 +2363,14 @@
         <v>0.10417</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>0.10417</v>
+        <v>0.10377</v>
       </c>
       <c r="D102" s="1" t="n">
         <v>0.10417</v>
       </c>
+      <c r="E102" s="1" t="n">
+        <v>0.10377</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2073,11 +2382,14 @@
         <v>0.0006065000000000001</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>0.0006065000000000001</v>
+        <v>0.0006053</v>
       </c>
       <c r="D103" s="1" t="n">
         <v>0.0006065000000000001</v>
       </c>
+      <c r="E103" s="1" t="n">
+        <v>0.0006053</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2089,11 +2401,14 @@
         <v>0.0005594</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>0.0005594</v>
+        <v>0.0005566</v>
       </c>
       <c r="D104" s="1" t="n">
         <v>0.0005594</v>
       </c>
+      <c r="E104" s="1" t="n">
+        <v>0.0005566</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2110,6 +2425,9 @@
       <c r="D105" s="1" t="n">
         <v>0.003257</v>
       </c>
+      <c r="E105" s="1" t="n">
+        <v>0.003257</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2121,11 +2439,14 @@
         <v>2.638</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>2.638</v>
+        <v>2.623</v>
       </c>
       <c r="D106" s="1" t="n">
         <v>2.638</v>
       </c>
+      <c r="E106" s="1" t="n">
+        <v>2.623</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2137,9 +2458,12 @@
         <v>0.1671</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>0.1671</v>
+        <v>0.1674</v>
       </c>
       <c r="D107" s="1" t="n">
+        <v>0.1674</v>
+      </c>
+      <c r="E107" s="1" t="n">
         <v>0.1671</v>
       </c>
     </row>
@@ -2153,11 +2477,14 @@
         <v>0.09814000000000001</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>0.09814000000000001</v>
+        <v>0.09742000000000001</v>
       </c>
       <c r="D108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
+      <c r="E108" s="1" t="n">
+        <v>0.09742000000000001</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2169,9 +2496,12 @@
         <v>0.02236</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>0.02236</v>
+        <v>0.02242</v>
       </c>
       <c r="D109" s="1" t="n">
+        <v>0.02242</v>
+      </c>
+      <c r="E109" s="1" t="n">
         <v>0.02236</v>
       </c>
     </row>
@@ -2185,9 +2515,12 @@
         <v>0.2913</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>0.2913</v>
+        <v>0.292</v>
       </c>
       <c r="D110" s="1" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="E110" s="1" t="n">
         <v>0.2913</v>
       </c>
     </row>
@@ -2201,9 +2534,12 @@
         <v>0.05684</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>0.05684</v>
+        <v>0.05697</v>
       </c>
       <c r="D111" s="1" t="n">
+        <v>0.05697</v>
+      </c>
+      <c r="E111" s="1" t="n">
         <v>0.05684</v>
       </c>
     </row>
@@ -2217,11 +2553,14 @@
         <v>0.3057</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>0.3057</v>
+        <v>0.3047</v>
       </c>
       <c r="D112" s="1" t="n">
         <v>0.3057</v>
       </c>
+      <c r="E112" s="1" t="n">
+        <v>0.3047</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2233,9 +2572,12 @@
         <v>18.62</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>18.62</v>
+        <v>18.67</v>
       </c>
       <c r="D113" s="1" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="E113" s="1" t="n">
         <v>18.62</v>
       </c>
     </row>
@@ -2249,11 +2591,14 @@
         <v>0.13365</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>0.13365</v>
+        <v>0.13225</v>
       </c>
       <c r="D114" s="1" t="n">
         <v>0.13365</v>
       </c>
+      <c r="E114" s="1" t="n">
+        <v>0.13225</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2265,11 +2610,14 @@
         <v>0.01583</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>0.01583</v>
+        <v>0.01538</v>
       </c>
       <c r="D115" s="1" t="n">
         <v>0.01583</v>
       </c>
+      <c r="E115" s="1" t="n">
+        <v>0.01538</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2281,11 +2629,14 @@
         <v>0.08558</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>0.08558</v>
+        <v>0.08545999999999999</v>
       </c>
       <c r="D116" s="1" t="n">
         <v>0.08558</v>
       </c>
+      <c r="E116" s="1" t="n">
+        <v>0.08545999999999999</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2297,11 +2648,14 @@
         <v>0.04998</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>0.04998</v>
+        <v>0.04921</v>
       </c>
       <c r="D117" s="1" t="n">
         <v>0.04998</v>
       </c>
+      <c r="E117" s="1" t="n">
+        <v>0.04921</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2313,11 +2667,14 @@
         <v>0.04844</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>0.04844</v>
+        <v>0.04824</v>
       </c>
       <c r="D118" s="1" t="n">
         <v>0.04844</v>
       </c>
+      <c r="E118" s="1" t="n">
+        <v>0.04824</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2329,9 +2686,12 @@
         <v>0.04109</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>0.04109</v>
+        <v>0.04116</v>
       </c>
       <c r="D119" s="1" t="n">
+        <v>0.04116</v>
+      </c>
+      <c r="E119" s="1" t="n">
         <v>0.04109</v>
       </c>
     </row>
@@ -2345,9 +2705,12 @@
         <v>0.14499</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>0.14499</v>
+        <v>0.14654</v>
       </c>
       <c r="D120" s="1" t="n">
+        <v>0.14654</v>
+      </c>
+      <c r="E120" s="1" t="n">
         <v>0.14499</v>
       </c>
     </row>
@@ -2361,11 +2724,14 @@
         <v>0.1279</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>0.1279</v>
+        <v>0.1272</v>
       </c>
       <c r="D121" s="1" t="n">
         <v>0.1279</v>
       </c>
+      <c r="E121" s="1" t="n">
+        <v>0.1272</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2377,11 +2743,14 @@
         <v>1.893</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>1.893</v>
+        <v>1.887</v>
       </c>
       <c r="D122" s="1" t="n">
         <v>1.893</v>
       </c>
+      <c r="E122" s="1" t="n">
+        <v>1.887</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2393,11 +2762,14 @@
         <v>0.03049</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>0.03049</v>
+        <v>0.03048</v>
       </c>
       <c r="D123" s="1" t="n">
         <v>0.03049</v>
       </c>
+      <c r="E123" s="1" t="n">
+        <v>0.03048</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2409,11 +2781,14 @@
         <v>0.13309</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>0.13309</v>
+        <v>0.13288</v>
       </c>
       <c r="D124" s="1" t="n">
         <v>0.13309</v>
       </c>
+      <c r="E124" s="1" t="n">
+        <v>0.13288</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2425,11 +2800,14 @@
         <v>0.04187</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>0.04187</v>
+        <v>0.04143</v>
       </c>
       <c r="D125" s="1" t="n">
         <v>0.04187</v>
       </c>
+      <c r="E125" s="1" t="n">
+        <v>0.04143</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2441,11 +2819,14 @@
         <v>0.1165</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>0.1165</v>
+        <v>0.1154</v>
       </c>
       <c r="D126" s="1" t="n">
         <v>0.1165</v>
       </c>
+      <c r="E126" s="1" t="n">
+        <v>0.1154</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2457,9 +2838,12 @@
         <v>0.4957</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>0.4957</v>
+        <v>0.497</v>
       </c>
       <c r="D127" s="1" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="E127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -2473,11 +2857,14 @@
         <v>0.03797</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>0.03797</v>
+        <v>0.03795</v>
       </c>
       <c r="D128" s="1" t="n">
         <v>0.03797</v>
       </c>
+      <c r="E128" s="1" t="n">
+        <v>0.03795</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2489,11 +2876,14 @@
         <v>0.797</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>0.797</v>
+        <v>0.796</v>
       </c>
       <c r="D129" s="1" t="n">
         <v>0.797</v>
       </c>
+      <c r="E129" s="1" t="n">
+        <v>0.796</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2505,9 +2895,12 @@
         <v>0.03439</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>0.03439</v>
+        <v>0.03458</v>
       </c>
       <c r="D130" s="1" t="n">
+        <v>0.03458</v>
+      </c>
+      <c r="E130" s="1" t="n">
         <v>0.03439</v>
       </c>
     </row>
@@ -2521,9 +2914,12 @@
         <v>0.4149</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>0.4149</v>
+        <v>0.4183</v>
       </c>
       <c r="D131" s="1" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="E131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -2537,11 +2933,14 @@
         <v>0.04409</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>0.04409</v>
+        <v>0.04405</v>
       </c>
       <c r="D132" s="1" t="n">
         <v>0.04409</v>
       </c>
+      <c r="E132" s="1" t="n">
+        <v>0.04405</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2553,11 +2952,14 @@
         <v>1.2946</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>1.2946</v>
+        <v>1.2941</v>
       </c>
       <c r="D133" s="1" t="n">
         <v>1.2946</v>
       </c>
+      <c r="E133" s="1" t="n">
+        <v>1.2941</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2569,9 +2971,12 @@
         <v>0.02208</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>0.02208</v>
+        <v>0.02215</v>
       </c>
       <c r="D134" s="1" t="n">
+        <v>0.02215</v>
+      </c>
+      <c r="E134" s="1" t="n">
         <v>0.02208</v>
       </c>
     </row>
@@ -2585,11 +2990,14 @@
         <v>0.0004716</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>0.0004716</v>
+        <v>0.0004699</v>
       </c>
       <c r="D135" s="1" t="n">
         <v>0.0004716</v>
       </c>
+      <c r="E135" s="1" t="n">
+        <v>0.0004699</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2601,11 +3009,14 @@
         <v>0.001918</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>0.001918</v>
+        <v>0.001913</v>
       </c>
       <c r="D136" s="1" t="n">
         <v>0.001918</v>
       </c>
+      <c r="E136" s="1" t="n">
+        <v>0.001913</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2617,11 +3028,14 @@
         <v>0.3227</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>0.3227</v>
+        <v>0.3221</v>
       </c>
       <c r="D137" s="1" t="n">
         <v>0.3227</v>
       </c>
+      <c r="E137" s="1" t="n">
+        <v>0.3221</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2633,11 +3047,14 @@
         <v>0.5717</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>0.5717</v>
+        <v>0.5705</v>
       </c>
       <c r="D138" s="1" t="n">
         <v>0.5717</v>
       </c>
+      <c r="E138" s="1" t="n">
+        <v>0.5705</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2649,9 +3066,12 @@
         <v>0.02145</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>0.02145</v>
+        <v>0.02148</v>
       </c>
       <c r="D139" s="1" t="n">
+        <v>0.02148</v>
+      </c>
+      <c r="E139" s="1" t="n">
         <v>0.02145</v>
       </c>
     </row>
@@ -2665,11 +3085,14 @@
         <v>0.08092000000000001</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>0.08092000000000001</v>
+        <v>0.08081000000000001</v>
       </c>
       <c r="D140" s="1" t="n">
         <v>0.08092000000000001</v>
       </c>
+      <c r="E140" s="1" t="n">
+        <v>0.08081000000000001</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2681,9 +3104,12 @@
         <v>0.001616</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>0.001616</v>
+        <v>0.00163</v>
       </c>
       <c r="D141" s="1" t="n">
+        <v>0.00163</v>
+      </c>
+      <c r="E141" s="1" t="n">
         <v>0.001616</v>
       </c>
     </row>
@@ -2697,9 +3123,12 @@
         <v>0.4218</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>0.4218</v>
+        <v>0.4256</v>
       </c>
       <c r="D142" s="1" t="n">
+        <v>0.4256</v>
+      </c>
+      <c r="E142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -2713,9 +3142,12 @@
         <v>0.030377</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>0.030377</v>
+        <v>0.030655</v>
       </c>
       <c r="D143" s="1" t="n">
+        <v>0.030655</v>
+      </c>
+      <c r="E143" s="1" t="n">
         <v>0.030377</v>
       </c>
     </row>
@@ -2729,9 +3161,12 @@
         <v>0.000223</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>0.000223</v>
+        <v>0.000225</v>
       </c>
       <c r="D144" s="1" t="n">
+        <v>0.000225</v>
+      </c>
+      <c r="E144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -2745,9 +3180,12 @@
         <v>0.03178</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>0.03178</v>
+        <v>0.03197</v>
       </c>
       <c r="D145" s="1" t="n">
+        <v>0.03197</v>
+      </c>
+      <c r="E145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -2761,9 +3199,12 @@
         <v>0.11518</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>0.11518</v>
+        <v>0.11584</v>
       </c>
       <c r="D146" s="1" t="n">
+        <v>0.11584</v>
+      </c>
+      <c r="E146" s="1" t="n">
         <v>0.11518</v>
       </c>
     </row>
@@ -2777,9 +3218,12 @@
         <v>0.02171</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>0.02171</v>
+        <v>0.02185</v>
       </c>
       <c r="D147" s="1" t="n">
+        <v>0.02185</v>
+      </c>
+      <c r="E147" s="1" t="n">
         <v>0.02171</v>
       </c>
     </row>
@@ -2793,11 +3237,14 @@
         <v>1.4234</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>1.4234</v>
+        <v>1.4191</v>
       </c>
       <c r="D148" s="1" t="n">
         <v>1.4234</v>
       </c>
+      <c r="E148" s="1" t="n">
+        <v>1.4191</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2809,9 +3256,12 @@
         <v>1.8594</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>1.8594</v>
+        <v>1.8715</v>
       </c>
       <c r="D149" s="1" t="n">
+        <v>1.8715</v>
+      </c>
+      <c r="E149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -2825,11 +3275,14 @@
         <v>0.101</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>0.101</v>
+        <v>0.1</v>
       </c>
       <c r="D150" s="1" t="n">
         <v>0.101</v>
       </c>
+      <c r="E150" s="1" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2841,9 +3294,12 @@
         <v>4.488</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>4.488</v>
+        <v>4.521</v>
       </c>
       <c r="D151" s="1" t="n">
+        <v>4.521</v>
+      </c>
+      <c r="E151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -2857,11 +3313,14 @@
         <v>5.561</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>5.561</v>
+        <v>5.55</v>
       </c>
       <c r="D152" s="1" t="n">
         <v>5.561</v>
       </c>
+      <c r="E152" s="1" t="n">
+        <v>5.55</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2873,9 +3332,12 @@
         <v>0.3178</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>0.3178</v>
+        <v>0.3205</v>
       </c>
       <c r="D153" s="1" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="E153" s="1" t="n">
         <v>0.3178</v>
       </c>
     </row>
@@ -2889,11 +3351,14 @@
         <v>0.5901999999999999</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5901</v>
       </c>
       <c r="D154" s="1" t="n">
         <v>0.5901999999999999</v>
       </c>
+      <c r="E154" s="1" t="n">
+        <v>0.5901</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2910,6 +3375,9 @@
       <c r="D155" s="1" t="n">
         <v>0.01267</v>
       </c>
+      <c r="E155" s="1" t="n">
+        <v>0.01267</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2921,11 +3389,14 @@
         <v>0.1002</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>0.1002</v>
+        <v>0.1001</v>
       </c>
       <c r="D156" s="1" t="n">
         <v>0.1002</v>
       </c>
+      <c r="E156" s="1" t="n">
+        <v>0.1001</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2937,11 +3408,14 @@
         <v>16.596</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>16.596</v>
+        <v>16.588</v>
       </c>
       <c r="D157" s="1" t="n">
         <v>16.596</v>
       </c>
+      <c r="E157" s="1" t="n">
+        <v>16.588</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2953,9 +3427,12 @@
         <v>0.05477</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>0.05477</v>
+        <v>0.05548</v>
       </c>
       <c r="D158" s="1" t="n">
+        <v>0.05548</v>
+      </c>
+      <c r="E158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -2969,11 +3446,14 @@
         <v>29.04</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>29.04</v>
+        <v>28.92</v>
       </c>
       <c r="D159" s="1" t="n">
         <v>29.04</v>
       </c>
+      <c r="E159" s="1" t="n">
+        <v>28.92</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2985,11 +3465,14 @@
         <v>0.02132</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>0.02132</v>
+        <v>0.02124</v>
       </c>
       <c r="D160" s="1" t="n">
         <v>0.02132</v>
       </c>
+      <c r="E160" s="1" t="n">
+        <v>0.02124</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3001,11 +3484,14 @@
         <v>0.0006619</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>0.0006619</v>
+        <v>0.0006608</v>
       </c>
       <c r="D161" s="1" t="n">
         <v>0.0006619</v>
       </c>
+      <c r="E161" s="1" t="n">
+        <v>0.0006608</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3017,9 +3503,12 @@
         <v>0.3936</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>0.3936</v>
+        <v>0.3968</v>
       </c>
       <c r="D162" s="1" t="n">
+        <v>0.3968</v>
+      </c>
+      <c r="E162" s="1" t="n">
         <v>0.3936</v>
       </c>
     </row>
@@ -3033,11 +3522,14 @@
         <v>0.1939</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>0.1939</v>
+        <v>0.1934</v>
       </c>
       <c r="D163" s="1" t="n">
         <v>0.1939</v>
       </c>
+      <c r="E163" s="1" t="n">
+        <v>0.1934</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3049,11 +3541,14 @@
         <v>0.321</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>0.321</v>
+        <v>0.32</v>
       </c>
       <c r="D164" s="1" t="n">
         <v>0.321</v>
       </c>
+      <c r="E164" s="1" t="n">
+        <v>0.32</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3065,11 +3560,14 @@
         <v>0.377</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>0.377</v>
+        <v>0.376</v>
       </c>
       <c r="D165" s="1" t="n">
         <v>0.377</v>
       </c>
+      <c r="E165" s="1" t="n">
+        <v>0.376</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3081,11 +3579,14 @@
         <v>0.02276</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>0.02276</v>
+        <v>0.02274</v>
       </c>
       <c r="D166" s="1" t="n">
         <v>0.02276</v>
       </c>
+      <c r="E166" s="1" t="n">
+        <v>0.02274</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3097,11 +3598,14 @@
         <v>0.007385</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>0.007385</v>
+        <v>0.007366</v>
       </c>
       <c r="D167" s="1" t="n">
         <v>0.007385</v>
       </c>
+      <c r="E167" s="1" t="n">
+        <v>0.007366</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3118,6 +3622,9 @@
       <c r="D168" s="1" t="n">
         <v>0.01397</v>
       </c>
+      <c r="E168" s="1" t="n">
+        <v>0.01397</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3129,11 +3636,14 @@
         <v>0.26035</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>0.26035</v>
+        <v>0.25715</v>
       </c>
       <c r="D169" s="1" t="n">
         <v>0.26035</v>
       </c>
+      <c r="E169" s="1" t="n">
+        <v>0.25715</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3145,11 +3655,14 @@
         <v>0.02193</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>0.02193</v>
+        <v>0.02143</v>
       </c>
       <c r="D170" s="1" t="n">
         <v>0.02193</v>
       </c>
+      <c r="E170" s="1" t="n">
+        <v>0.02143</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3161,9 +3674,12 @@
         <v>0.1733</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>0.1733</v>
+        <v>0.1741</v>
       </c>
       <c r="D171" s="1" t="n">
+        <v>0.1741</v>
+      </c>
+      <c r="E171" s="1" t="n">
         <v>0.1733</v>
       </c>
     </row>
@@ -3182,6 +3698,9 @@
       <c r="D172" s="1" t="n">
         <v>0.09</v>
       </c>
+      <c r="E172" s="1" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3193,11 +3712,14 @@
         <v>0.004729</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>0.004729</v>
+        <v>0.004722</v>
       </c>
       <c r="D173" s="1" t="n">
         <v>0.004729</v>
       </c>
+      <c r="E173" s="1" t="n">
+        <v>0.004722</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3209,9 +3731,12 @@
         <v>0.4373</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>0.4373</v>
+        <v>0.4382</v>
       </c>
       <c r="D174" s="1" t="n">
+        <v>0.4382</v>
+      </c>
+      <c r="E174" s="1" t="n">
         <v>0.4373</v>
       </c>
     </row>
@@ -3225,9 +3750,12 @@
         <v>0.08966</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>0.08966</v>
+        <v>0.09001000000000001</v>
       </c>
       <c r="D175" s="1" t="n">
+        <v>0.09001000000000001</v>
+      </c>
+      <c r="E175" s="1" t="n">
         <v>0.08966</v>
       </c>
     </row>
@@ -3241,11 +3769,14 @@
         <v>0.2475</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>0.2475</v>
+        <v>0.2453</v>
       </c>
       <c r="D176" s="1" t="n">
         <v>0.2475</v>
       </c>
+      <c r="E176" s="1" t="n">
+        <v>0.2453</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3257,11 +3788,14 @@
         <v>0.01925</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>0.01925</v>
+        <v>0.01918</v>
       </c>
       <c r="D177" s="1" t="n">
         <v>0.01925</v>
       </c>
+      <c r="E177" s="1" t="n">
+        <v>0.01918</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3273,9 +3807,12 @@
         <v>6.195</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>6.195</v>
+        <v>6.196</v>
       </c>
       <c r="D178" s="1" t="n">
+        <v>6.196</v>
+      </c>
+      <c r="E178" s="1" t="n">
         <v>6.195</v>
       </c>
     </row>
@@ -3289,11 +3826,14 @@
         <v>0.1383</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>0.1383</v>
+        <v>0.1364</v>
       </c>
       <c r="D179" s="1" t="n">
         <v>0.1383</v>
       </c>
+      <c r="E179" s="1" t="n">
+        <v>0.1364</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3305,11 +3845,14 @@
         <v>0.004923</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>0.004923</v>
+        <v>0.004848</v>
       </c>
       <c r="D180" s="1" t="n">
         <v>0.004923</v>
       </c>
+      <c r="E180" s="1" t="n">
+        <v>0.004848</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -3326,6 +3869,9 @@
       <c r="D181" s="1" t="n">
         <v>0.01191</v>
       </c>
+      <c r="E181" s="1" t="n">
+        <v>0.01191</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3337,9 +3883,12 @@
         <v>0.007295</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>0.007295</v>
+        <v>0.007524</v>
       </c>
       <c r="D182" s="1" t="n">
+        <v>0.007524</v>
+      </c>
+      <c r="E182" s="1" t="n">
         <v>0.007295</v>
       </c>
     </row>
@@ -3353,9 +3902,12 @@
         <v>0.13194</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>0.13194</v>
+        <v>0.13206</v>
       </c>
       <c r="D183" s="1" t="n">
+        <v>0.13206</v>
+      </c>
+      <c r="E183" s="1" t="n">
         <v>0.13194</v>
       </c>
     </row>
@@ -3369,9 +3921,12 @@
         <v>0.09587</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>0.09587</v>
+        <v>0.09626</v>
       </c>
       <c r="D184" s="1" t="n">
+        <v>0.09626</v>
+      </c>
+      <c r="E184" s="1" t="n">
         <v>0.09587</v>
       </c>
     </row>
@@ -3385,11 +3940,14 @@
         <v>0.00761</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>0.00761</v>
+        <v>0.00758</v>
       </c>
       <c r="D185" s="1" t="n">
         <v>0.00761</v>
       </c>
+      <c r="E185" s="1" t="n">
+        <v>0.00758</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -3401,11 +3959,14 @@
         <v>0.04933</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>0.04933</v>
+        <v>0.04914</v>
       </c>
       <c r="D186" s="1" t="n">
         <v>0.04933</v>
       </c>
+      <c r="E186" s="1" t="n">
+        <v>0.04914</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3417,9 +3978,12 @@
         <v>0.02686</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>0.02686</v>
+        <v>0.02695</v>
       </c>
       <c r="D187" s="1" t="n">
+        <v>0.02695</v>
+      </c>
+      <c r="E187" s="1" t="n">
         <v>0.02686</v>
       </c>
     </row>
@@ -3433,11 +3997,14 @@
         <v>0.00334</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>0.00334</v>
+        <v>0.003333</v>
       </c>
       <c r="D188" s="1" t="n">
         <v>0.00334</v>
       </c>
+      <c r="E188" s="1" t="n">
+        <v>0.003333</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -3449,9 +4016,12 @@
         <v>0.2875</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>0.2875</v>
+        <v>0.2888</v>
       </c>
       <c r="D189" s="1" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="E189" s="1" t="n">
         <v>0.2875</v>
       </c>
     </row>
@@ -3465,11 +4035,14 @@
         <v>0.01822</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>0.01822</v>
+        <v>0.01821</v>
       </c>
       <c r="D190" s="1" t="n">
         <v>0.01822</v>
       </c>
+      <c r="E190" s="1" t="n">
+        <v>0.01821</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -3486,6 +4059,9 @@
       <c r="D191" s="1" t="n">
         <v>0.2617</v>
       </c>
+      <c r="E191" s="1" t="n">
+        <v>0.2617</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -3497,11 +4073,14 @@
         <v>0.03981</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>0.03981</v>
+        <v>0.03946</v>
       </c>
       <c r="D192" s="1" t="n">
         <v>0.03981</v>
       </c>
+      <c r="E192" s="1" t="n">
+        <v>0.03946</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -3513,11 +4092,14 @@
         <v>0.000221</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>0.000221</v>
+        <v>0.0002205</v>
       </c>
       <c r="D193" s="1" t="n">
         <v>0.000221</v>
       </c>
+      <c r="E193" s="1" t="n">
+        <v>0.0002205</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -3529,11 +4111,14 @@
         <v>4.196</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>4.196</v>
+        <v>4.169</v>
       </c>
       <c r="D194" s="1" t="n">
         <v>4.196</v>
       </c>
+      <c r="E194" s="1" t="n">
+        <v>4.169</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -3545,11 +4130,14 @@
         <v>0.999341</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>0.999341</v>
+        <v>0.99934</v>
       </c>
       <c r="D195" s="1" t="n">
         <v>0.999341</v>
       </c>
+      <c r="E195" s="1" t="n">
+        <v>0.99934</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -3561,11 +4149,14 @@
         <v>4.316</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>4.316</v>
+        <v>4.302</v>
       </c>
       <c r="D196" s="1" t="n">
         <v>4.316</v>
       </c>
+      <c r="E196" s="1" t="n">
+        <v>4.302</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -3577,11 +4168,14 @@
         <v>0.15012</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>0.15012</v>
+        <v>0.15006</v>
       </c>
       <c r="D197" s="1" t="n">
         <v>0.15012</v>
       </c>
+      <c r="E197" s="1" t="n">
+        <v>0.15006</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -3593,9 +4187,12 @@
         <v>0.007413</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>0.007413</v>
+        <v>0.007586</v>
       </c>
       <c r="D198" s="1" t="n">
+        <v>0.007586</v>
+      </c>
+      <c r="E198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -3609,11 +4206,14 @@
         <v>0.4503</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>0.4503</v>
+        <v>0.4502</v>
       </c>
       <c r="D199" s="1" t="n">
         <v>0.4503</v>
       </c>
+      <c r="E199" s="1" t="n">
+        <v>0.4502</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -3625,11 +4225,14 @@
         <v>0.5731000000000001</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5715</v>
       </c>
       <c r="D200" s="1" t="n">
         <v>0.5731000000000001</v>
       </c>
+      <c r="E200" s="1" t="n">
+        <v>0.5715</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -3641,11 +4244,14 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.094</v>
       </c>
       <c r="D201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
+      <c r="E201" s="1" t="n">
+        <v>0.094</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -3657,11 +4263,14 @@
         <v>0.06068</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>0.06068</v>
+        <v>0.06063</v>
       </c>
       <c r="D202" s="1" t="n">
         <v>0.06068</v>
       </c>
+      <c r="E202" s="1" t="n">
+        <v>0.06063</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -3673,9 +4282,12 @@
         <v>0.008359999999999999</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>0.008359999999999999</v>
+        <v>0.00847</v>
       </c>
       <c r="D203" s="1" t="n">
+        <v>0.00847</v>
+      </c>
+      <c r="E203" s="1" t="n">
         <v>0.008359999999999999</v>
       </c>
     </row>
@@ -3694,6 +4306,9 @@
       <c r="D204" s="1" t="n">
         <v>0.00422</v>
       </c>
+      <c r="E204" s="1" t="n">
+        <v>0.00422</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -3705,9 +4320,12 @@
         <v>0.009239000000000001</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>0.009239000000000001</v>
+        <v>0.009318</v>
       </c>
       <c r="D205" s="1" t="n">
+        <v>0.009318</v>
+      </c>
+      <c r="E205" s="1" t="n">
         <v>0.009239000000000001</v>
       </c>
     </row>
@@ -3721,11 +4339,14 @@
         <v>0.2362</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>0.2362</v>
+        <v>0.2356</v>
       </c>
       <c r="D206" s="1" t="n">
         <v>0.2362</v>
       </c>
+      <c r="E206" s="1" t="n">
+        <v>0.2356</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -3737,9 +4358,12 @@
         <v>0.02128</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>0.02128</v>
+        <v>0.02163</v>
       </c>
       <c r="D207" s="1" t="n">
+        <v>0.02163</v>
+      </c>
+      <c r="E207" s="1" t="n">
         <v>0.02128</v>
       </c>
     </row>
@@ -3753,11 +4377,14 @@
         <v>0.2392</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>0.2392</v>
+        <v>0.2376</v>
       </c>
       <c r="D208" s="1" t="n">
         <v>0.2392</v>
       </c>
+      <c r="E208" s="1" t="n">
+        <v>0.2376</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -3769,11 +4396,14 @@
         <v>0.3638</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>0.3638</v>
+        <v>0.3616</v>
       </c>
       <c r="D209" s="1" t="n">
         <v>0.3638</v>
       </c>
+      <c r="E209" s="1" t="n">
+        <v>0.3616</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -3785,11 +4415,14 @@
         <v>0.04311</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>0.04311</v>
+        <v>0.04302</v>
       </c>
       <c r="D210" s="1" t="n">
         <v>0.04311</v>
       </c>
+      <c r="E210" s="1" t="n">
+        <v>0.04302</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -3801,11 +4434,14 @@
         <v>0.0004307</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>0.0004307</v>
+        <v>0.0004303</v>
       </c>
       <c r="D211" s="1" t="n">
         <v>0.0004307</v>
       </c>
+      <c r="E211" s="1" t="n">
+        <v>0.0004303</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -3817,9 +4453,12 @@
         <v>0.0217</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>0.0217</v>
+        <v>0.02171</v>
       </c>
       <c r="D212" s="1" t="n">
+        <v>0.02171</v>
+      </c>
+      <c r="E212" s="1" t="n">
         <v>0.0217</v>
       </c>
     </row>
@@ -3833,11 +4472,14 @@
         <v>0.1165</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>0.1165</v>
+        <v>0.1151</v>
       </c>
       <c r="D213" s="1" t="n">
         <v>0.1165</v>
       </c>
+      <c r="E213" s="1" t="n">
+        <v>0.1151</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -3849,11 +4491,14 @@
         <v>0.04204</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>0.04204</v>
+        <v>0.04199</v>
       </c>
       <c r="D214" s="1" t="n">
         <v>0.04204</v>
       </c>
+      <c r="E214" s="1" t="n">
+        <v>0.04199</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -3865,9 +4510,12 @@
         <v>0.009896</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>0.009896</v>
+        <v>0.010028</v>
       </c>
       <c r="D215" s="1" t="n">
+        <v>0.010028</v>
+      </c>
+      <c r="E215" s="1" t="n">
         <v>0.009896</v>
       </c>
     </row>
@@ -3886,6 +4534,9 @@
       <c r="D216" s="1" t="n">
         <v>0.064</v>
       </c>
+      <c r="E216" s="1" t="n">
+        <v>0.064</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -3897,11 +4548,14 @@
         <v>0.004186</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>0.004186</v>
+        <v>0.004184</v>
       </c>
       <c r="D217" s="1" t="n">
         <v>0.004186</v>
       </c>
+      <c r="E217" s="1" t="n">
+        <v>0.004184</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -3913,11 +4567,14 @@
         <v>0.01085</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>0.01085</v>
+        <v>0.01062</v>
       </c>
       <c r="D218" s="1" t="n">
         <v>0.01085</v>
       </c>
+      <c r="E218" s="1" t="n">
+        <v>0.01062</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -3929,9 +4586,12 @@
         <v>0.03127</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>0.03127</v>
+        <v>0.03134</v>
       </c>
       <c r="D219" s="1" t="n">
+        <v>0.03134</v>
+      </c>
+      <c r="E219" s="1" t="n">
         <v>0.03127</v>
       </c>
     </row>
@@ -3945,11 +4605,14 @@
         <v>2.306</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>2.306</v>
+        <v>2.305</v>
       </c>
       <c r="D220" s="1" t="n">
         <v>2.306</v>
       </c>
+      <c r="E220" s="1" t="n">
+        <v>2.305</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -3961,9 +4624,12 @@
         <v>0.023052</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>0.023052</v>
+        <v>0.023068</v>
       </c>
       <c r="D221" s="1" t="n">
+        <v>0.023068</v>
+      </c>
+      <c r="E221" s="1" t="n">
         <v>0.023052</v>
       </c>
     </row>
@@ -3977,11 +4643,14 @@
         <v>0.0372</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>0.0372</v>
+        <v>0.0371</v>
       </c>
       <c r="D222" s="1" t="n">
         <v>0.0372</v>
       </c>
+      <c r="E222" s="1" t="n">
+        <v>0.0371</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -3993,9 +4662,12 @@
         <v>0.2943</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>0.2943</v>
+        <v>0.2946</v>
       </c>
       <c r="D223" s="1" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="E223" s="1" t="n">
         <v>0.2943</v>
       </c>
     </row>
@@ -4009,11 +4681,14 @@
         <v>0.01549</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>0.01549</v>
+        <v>0.01537</v>
       </c>
       <c r="D224" s="1" t="n">
         <v>0.01549</v>
       </c>
+      <c r="E224" s="1" t="n">
+        <v>0.01537</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4025,11 +4700,14 @@
         <v>0.0004135</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>0.0004135</v>
+        <v>0.0004125</v>
       </c>
       <c r="D225" s="1" t="n">
         <v>0.0004135</v>
       </c>
+      <c r="E225" s="1" t="n">
+        <v>0.0004125</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4041,11 +4719,14 @@
         <v>0.08766</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>0.08766</v>
+        <v>0.08731999999999999</v>
       </c>
       <c r="D226" s="1" t="n">
         <v>0.08766</v>
       </c>
+      <c r="E226" s="1" t="n">
+        <v>0.08731999999999999</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4062,6 +4743,9 @@
       <c r="D227" s="1" t="n">
         <v>0.945</v>
       </c>
+      <c r="E227" s="1" t="n">
+        <v>0.945</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -4073,11 +4757,14 @@
         <v>0.05614</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>0.05614</v>
+        <v>0.0558</v>
       </c>
       <c r="D228" s="1" t="n">
         <v>0.05614</v>
       </c>
+      <c r="E228" s="1" t="n">
+        <v>0.0558</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -4089,11 +4776,14 @@
         <v>0.002026</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>0.002026</v>
+        <v>0.002022</v>
       </c>
       <c r="D229" s="1" t="n">
         <v>0.002026</v>
       </c>
+      <c r="E229" s="1" t="n">
+        <v>0.002022</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -4105,9 +4795,12 @@
         <v>0.022659</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>0.022659</v>
+        <v>0.022734</v>
       </c>
       <c r="D230" s="1" t="n">
+        <v>0.022734</v>
+      </c>
+      <c r="E230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -4121,9 +4814,12 @@
         <v>0.05471</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>0.05471</v>
+        <v>0.05499</v>
       </c>
       <c r="D231" s="1" t="n">
+        <v>0.05499</v>
+      </c>
+      <c r="E231" s="1" t="n">
         <v>0.05471</v>
       </c>
     </row>
@@ -4137,11 +4833,14 @@
         <v>0.0595</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>0.0595</v>
+        <v>0.0594</v>
       </c>
       <c r="D232" s="1" t="n">
         <v>0.0595</v>
       </c>
+      <c r="E232" s="1" t="n">
+        <v>0.0594</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -4153,11 +4852,14 @@
         <v>0.001689</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>0.001689</v>
+        <v>0.001687</v>
       </c>
       <c r="D233" s="1" t="n">
         <v>0.001689</v>
       </c>
+      <c r="E233" s="1" t="n">
+        <v>0.001687</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -4169,9 +4871,12 @@
         <v>0.005784</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>0.005784</v>
+        <v>0.005788</v>
       </c>
       <c r="D234" s="1" t="n">
+        <v>0.005788</v>
+      </c>
+      <c r="E234" s="1" t="n">
         <v>0.005784</v>
       </c>
     </row>
@@ -4185,9 +4890,12 @@
         <v>0.12453</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>0.12453</v>
+        <v>0.1256</v>
       </c>
       <c r="D235" s="1" t="n">
+        <v>0.1256</v>
+      </c>
+      <c r="E235" s="1" t="n">
         <v>0.12453</v>
       </c>
     </row>
@@ -4201,11 +4909,14 @@
         <v>65.36</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>65.36</v>
+        <v>64.86</v>
       </c>
       <c r="D236" s="1" t="n">
         <v>65.36</v>
       </c>
+      <c r="E236" s="1" t="n">
+        <v>64.86</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -4217,11 +4928,14 @@
         <v>0.1028</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>0.1028</v>
+        <v>0.1024</v>
       </c>
       <c r="D237" s="1" t="n">
         <v>0.1028</v>
       </c>
+      <c r="E237" s="1" t="n">
+        <v>0.1024</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -4233,11 +4947,14 @@
         <v>0.003951</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>0.003951</v>
+        <v>0.003944</v>
       </c>
       <c r="D238" s="1" t="n">
         <v>0.003951</v>
       </c>
+      <c r="E238" s="1" t="n">
+        <v>0.003944</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -4249,9 +4966,12 @@
         <v>0.01533</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>0.01533</v>
+        <v>0.01541</v>
       </c>
       <c r="D239" s="1" t="n">
+        <v>0.01541</v>
+      </c>
+      <c r="E239" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -4265,11 +4985,14 @@
         <v>0.05631</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>0.05631</v>
+        <v>0.05621</v>
       </c>
       <c r="D240" s="1" t="n">
         <v>0.05631</v>
       </c>
+      <c r="E240" s="1" t="n">
+        <v>0.05621</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -4281,11 +5004,14 @@
         <v>0.0116</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>0.0116</v>
+        <v>0.0115</v>
       </c>
       <c r="D241" s="1" t="n">
         <v>0.0116</v>
       </c>
+      <c r="E241" s="1" t="n">
+        <v>0.0115</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -4297,11 +5023,14 @@
         <v>0.3372</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>0.3372</v>
+        <v>0.3368</v>
       </c>
       <c r="D242" s="1" t="n">
         <v>0.3372</v>
       </c>
+      <c r="E242" s="1" t="n">
+        <v>0.3368</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -4313,11 +5042,14 @@
         <v>0.01247</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>0.01247</v>
+        <v>0.01243</v>
       </c>
       <c r="D243" s="1" t="n">
         <v>0.01247</v>
       </c>
+      <c r="E243" s="1" t="n">
+        <v>0.01243</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -4329,11 +5061,14 @@
         <v>0.08051999999999999</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>0.08051999999999999</v>
+        <v>0.08032</v>
       </c>
       <c r="D244" s="1" t="n">
         <v>0.08051999999999999</v>
       </c>
+      <c r="E244" s="1" t="n">
+        <v>0.08032</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -4345,9 +5080,12 @@
         <v>0.008</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>0.008</v>
+        <v>0.008052</v>
       </c>
       <c r="D245" s="1" t="n">
+        <v>0.008052</v>
+      </c>
+      <c r="E245" s="1" t="n">
         <v>0.008</v>
       </c>
     </row>
@@ -4361,9 +5099,12 @@
         <v>0.03056</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>0.03056</v>
+        <v>0.03059</v>
       </c>
       <c r="D246" s="1" t="n">
+        <v>0.03059</v>
+      </c>
+      <c r="E246" s="1" t="n">
         <v>0.03056</v>
       </c>
     </row>
@@ -4377,11 +5118,14 @@
         <v>0.1813</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>0.1813</v>
+        <v>0.1808</v>
       </c>
       <c r="D247" s="1" t="n">
         <v>0.1813</v>
       </c>
+      <c r="E247" s="1" t="n">
+        <v>0.1808</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -4393,9 +5137,12 @@
         <v>0.05925</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>0.05925</v>
+        <v>0.05929</v>
       </c>
       <c r="D248" s="1" t="n">
+        <v>0.05929</v>
+      </c>
+      <c r="E248" s="1" t="n">
         <v>0.05925</v>
       </c>
     </row>
@@ -4409,11 +5156,14 @@
         <v>0.1676</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>0.1676</v>
+        <v>0.1669</v>
       </c>
       <c r="D249" s="1" t="n">
         <v>0.1676</v>
       </c>
+      <c r="E249" s="1" t="n">
+        <v>0.1669</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -4425,11 +5175,14 @@
         <v>0.01947</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>0.01947</v>
+        <v>0.01946</v>
       </c>
       <c r="D250" s="1" t="n">
         <v>0.01947</v>
       </c>
+      <c r="E250" s="1" t="n">
+        <v>0.01946</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -4441,9 +5194,12 @@
         <v>0.02304</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>0.02304</v>
+        <v>0.02312</v>
       </c>
       <c r="D251" s="1" t="n">
+        <v>0.02312</v>
+      </c>
+      <c r="E251" s="1" t="n">
         <v>0.02304</v>
       </c>
     </row>
@@ -4457,9 +5213,12 @@
         <v>0.2993</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>0.2993</v>
+        <v>0.30027</v>
       </c>
       <c r="D252" s="1" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="E252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -4473,11 +5232,14 @@
         <v>0.006106</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>0.006106</v>
+        <v>0.006074</v>
       </c>
       <c r="D253" s="1" t="n">
         <v>0.006106</v>
       </c>
+      <c r="E253" s="1" t="n">
+        <v>0.006074</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -4489,11 +5251,14 @@
         <v>0.6167</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>0.6167</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="D254" s="1" t="n">
         <v>0.6167</v>
       </c>
+      <c r="E254" s="1" t="n">
+        <v>0.6163999999999999</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -4505,9 +5270,12 @@
         <v>0.10807</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>0.10807</v>
+        <v>0.10811</v>
       </c>
       <c r="D255" s="1" t="n">
+        <v>0.10811</v>
+      </c>
+      <c r="E255" s="1" t="n">
         <v>0.10807</v>
       </c>
     </row>
@@ -4521,9 +5289,12 @@
         <v>0.0901</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>0.0901</v>
+        <v>0.0907</v>
       </c>
       <c r="D256" s="1" t="n">
+        <v>0.0907</v>
+      </c>
+      <c r="E256" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -4537,11 +5308,14 @@
         <v>0.01433</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>0.01433</v>
+        <v>0.01421</v>
       </c>
       <c r="D257" s="1" t="n">
         <v>0.01433</v>
       </c>
+      <c r="E257" s="1" t="n">
+        <v>0.01421</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -4553,11 +5327,14 @@
         <v>0.0514</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>0.0514</v>
+        <v>0.0511</v>
       </c>
       <c r="D258" s="1" t="n">
         <v>0.0514</v>
       </c>
+      <c r="E258" s="1" t="n">
+        <v>0.0511</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -4569,11 +5346,14 @@
         <v>0.008319999999999999</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>0.008319999999999999</v>
+        <v>0.00827</v>
       </c>
       <c r="D259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
+      <c r="E259" s="1" t="n">
+        <v>0.00827</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -4585,9 +5365,12 @@
         <v>0.1904</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>0.1904</v>
+        <v>0.1907</v>
       </c>
       <c r="D260" s="1" t="n">
+        <v>0.1907</v>
+      </c>
+      <c r="E260" s="1" t="n">
         <v>0.1904</v>
       </c>
     </row>
@@ -4601,11 +5384,14 @@
         <v>0.0993</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>0.0993</v>
+        <v>0.0989</v>
       </c>
       <c r="D261" s="1" t="n">
         <v>0.0993</v>
       </c>
+      <c r="E261" s="1" t="n">
+        <v>0.0989</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -4617,11 +5403,14 @@
         <v>0.2138</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>0.2138</v>
+        <v>0.2129</v>
       </c>
       <c r="D262" s="1" t="n">
         <v>0.2138</v>
       </c>
+      <c r="E262" s="1" t="n">
+        <v>0.2129</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -4633,9 +5422,12 @@
         <v>0.008366</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>0.008366</v>
+        <v>0.008384000000000001</v>
       </c>
       <c r="D263" s="1" t="n">
+        <v>0.008384000000000001</v>
+      </c>
+      <c r="E263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -4649,11 +5441,14 @@
         <v>2.651</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>2.651</v>
+        <v>2.648</v>
       </c>
       <c r="D264" s="1" t="n">
         <v>2.651</v>
       </c>
+      <c r="E264" s="1" t="n">
+        <v>2.648</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -4665,11 +5460,14 @@
         <v>0.01907</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>0.01907</v>
+        <v>0.01889</v>
       </c>
       <c r="D265" s="1" t="n">
         <v>0.01907</v>
       </c>
+      <c r="E265" s="1" t="n">
+        <v>0.01889</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -4681,11 +5479,14 @@
         <v>0.3602</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>0.3602</v>
+        <v>0.3595</v>
       </c>
       <c r="D266" s="1" t="n">
         <v>0.3602</v>
       </c>
+      <c r="E266" s="1" t="n">
+        <v>0.3595</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -4697,11 +5498,14 @@
         <v>0.03464</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>0.03464</v>
+        <v>0.03441</v>
       </c>
       <c r="D267" s="1" t="n">
         <v>0.03464</v>
       </c>
+      <c r="E267" s="1" t="n">
+        <v>0.03441</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -4713,11 +5517,14 @@
         <v>0.121</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>0.121</v>
+        <v>0.12</v>
       </c>
       <c r="D268" s="1" t="n">
         <v>0.121</v>
       </c>
+      <c r="E268" s="1" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -4729,9 +5536,12 @@
         <v>0.08082</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>0.08082</v>
+        <v>0.0809</v>
       </c>
       <c r="D269" s="1" t="n">
+        <v>0.0809</v>
+      </c>
+      <c r="E269" s="1" t="n">
         <v>0.08082</v>
       </c>
     </row>
@@ -4745,11 +5555,14 @@
         <v>0.01402</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>0.01402</v>
+        <v>0.01398</v>
       </c>
       <c r="D270" s="1" t="n">
         <v>0.01402</v>
       </c>
+      <c r="E270" s="1" t="n">
+        <v>0.01398</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -4766,6 +5579,9 @@
       <c r="D271" s="1" t="n">
         <v>0.007659</v>
       </c>
+      <c r="E271" s="1" t="n">
+        <v>0.007659</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -4777,11 +5593,14 @@
         <v>0.07452</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>0.07452</v>
+        <v>0.07432999999999999</v>
       </c>
       <c r="D272" s="1" t="n">
         <v>0.07452</v>
       </c>
+      <c r="E272" s="1" t="n">
+        <v>0.07432999999999999</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -4798,6 +5617,9 @@
       <c r="D273" s="1" t="n">
         <v>3.13e-05</v>
       </c>
+      <c r="E273" s="1" t="n">
+        <v>3.13e-05</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -4809,11 +5631,14 @@
         <v>0.005646</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>0.005646</v>
+        <v>0.00559</v>
       </c>
       <c r="D274" s="1" t="n">
         <v>0.005646</v>
       </c>
+      <c r="E274" s="1" t="n">
+        <v>0.00559</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -4830,6 +5655,9 @@
       <c r="D275" s="1" t="n">
         <v>0.1804</v>
       </c>
+      <c r="E275" s="1" t="n">
+        <v>0.1804</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -4841,11 +5669,14 @@
         <v>0.006919</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>0.006919</v>
+        <v>0.006876</v>
       </c>
       <c r="D276" s="1" t="n">
         <v>0.006919</v>
       </c>
+      <c r="E276" s="1" t="n">
+        <v>0.006876</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -4857,11 +5688,14 @@
         <v>0.1319</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>0.1319</v>
+        <v>0.1317</v>
       </c>
       <c r="D277" s="1" t="n">
         <v>0.1319</v>
       </c>
+      <c r="E277" s="1" t="n">
+        <v>0.1317</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -4873,11 +5707,14 @@
         <v>0.0237</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>0.0237</v>
+        <v>0.02354</v>
       </c>
       <c r="D278" s="1" t="n">
         <v>0.0237</v>
       </c>
+      <c r="E278" s="1" t="n">
+        <v>0.02354</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -4894,6 +5731,9 @@
       <c r="D279" s="1" t="n">
         <v>0.01818</v>
       </c>
+      <c r="E279" s="1" t="n">
+        <v>0.01818</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -4905,11 +5745,14 @@
         <v>0.03802</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>0.03802</v>
+        <v>0.03761</v>
       </c>
       <c r="D280" s="1" t="n">
         <v>0.03802</v>
       </c>
+      <c r="E280" s="1" t="n">
+        <v>0.03761</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -4921,11 +5764,14 @@
         <v>0.03994</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>0.03994</v>
+        <v>0.03988</v>
       </c>
       <c r="D281" s="1" t="n">
         <v>0.03994</v>
       </c>
+      <c r="E281" s="1" t="n">
+        <v>0.03988</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -4937,11 +5783,14 @@
         <v>0.3053</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>0.3053</v>
+        <v>0.3045</v>
       </c>
       <c r="D282" s="1" t="n">
         <v>0.3053</v>
       </c>
+      <c r="E282" s="1" t="n">
+        <v>0.3045</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -4953,11 +5802,14 @@
         <v>0.01131</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>0.01131</v>
+        <v>0.01127</v>
       </c>
       <c r="D283" s="1" t="n">
         <v>0.01131</v>
       </c>
+      <c r="E283" s="1" t="n">
+        <v>0.01127</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -4969,9 +5821,12 @@
         <v>9.500000000000001e-06</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>9.500000000000001e-06</v>
+        <v>9.7e-06</v>
       </c>
       <c r="D284" s="1" t="n">
+        <v>9.7e-06</v>
+      </c>
+      <c r="E284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -4985,11 +5840,14 @@
         <v>0.1159</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>0.1159</v>
+        <v>0.1154</v>
       </c>
       <c r="D285" s="1" t="n">
         <v>0.1159</v>
       </c>
+      <c r="E285" s="1" t="n">
+        <v>0.1154</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -5001,11 +5859,14 @@
         <v>0.003453</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>0.003453</v>
+        <v>0.00345</v>
       </c>
       <c r="D286" s="1" t="n">
         <v>0.003453</v>
       </c>
+      <c r="E286" s="1" t="n">
+        <v>0.00345</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -5017,9 +5878,12 @@
         <v>0.08558</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>0.08558</v>
+        <v>0.08563999999999999</v>
       </c>
       <c r="D287" s="1" t="n">
+        <v>0.08563999999999999</v>
+      </c>
+      <c r="E287" s="1" t="n">
         <v>0.08558</v>
       </c>
     </row>
@@ -5033,11 +5897,14 @@
         <v>0.1001</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>0.1001</v>
+        <v>0.09889000000000001</v>
       </c>
       <c r="D288" s="1" t="n">
         <v>0.1001</v>
       </c>
+      <c r="E288" s="1" t="n">
+        <v>0.09889000000000001</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -5049,11 +5916,14 @@
         <v>0.4327</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>0.4327</v>
+        <v>0.4308</v>
       </c>
       <c r="D289" s="1" t="n">
         <v>0.4327</v>
       </c>
+      <c r="E289" s="1" t="n">
+        <v>0.4308</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -5065,11 +5935,14 @@
         <v>0.03958</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>0.03958</v>
+        <v>0.03928</v>
       </c>
       <c r="D290" s="1" t="n">
         <v>0.03958</v>
       </c>
+      <c r="E290" s="1" t="n">
+        <v>0.03928</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -5081,11 +5954,14 @@
         <v>0.2474</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>0.2474</v>
+        <v>0.2433</v>
       </c>
       <c r="D291" s="1" t="n">
         <v>0.2474</v>
       </c>
+      <c r="E291" s="1" t="n">
+        <v>0.2433</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -5097,9 +5973,12 @@
         <v>0.28496</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>0.28496</v>
+        <v>0.28533</v>
       </c>
       <c r="D292" s="1" t="n">
+        <v>0.28533</v>
+      </c>
+      <c r="E292" s="1" t="n">
         <v>0.28496</v>
       </c>
     </row>
@@ -5113,11 +5992,14 @@
         <v>0.1515</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>0.1515</v>
+        <v>0.1512</v>
       </c>
       <c r="D293" s="1" t="n">
         <v>0.1515</v>
       </c>
+      <c r="E293" s="1" t="n">
+        <v>0.1512</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -5129,11 +6011,14 @@
         <v>4.254</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>4.254</v>
+        <v>4.238</v>
       </c>
       <c r="D294" s="1" t="n">
         <v>4.254</v>
       </c>
+      <c r="E294" s="1" t="n">
+        <v>4.238</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -5145,9 +6030,12 @@
         <v>0.03212</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>0.03212</v>
+        <v>0.03219</v>
       </c>
       <c r="D295" s="1" t="n">
+        <v>0.03219</v>
+      </c>
+      <c r="E295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -5161,9 +6049,12 @@
         <v>0.00098</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>0.00098</v>
+        <v>0.0009890000000000001</v>
       </c>
       <c r="D296" s="1" t="n">
+        <v>0.0009890000000000001</v>
+      </c>
+      <c r="E296" s="1" t="n">
         <v>0.00098</v>
       </c>
     </row>
@@ -5177,11 +6068,14 @@
         <v>0.08255999999999999</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>0.08255999999999999</v>
+        <v>0.08252</v>
       </c>
       <c r="D297" s="1" t="n">
         <v>0.08255999999999999</v>
       </c>
+      <c r="E297" s="1" t="n">
+        <v>0.08252</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -5193,11 +6087,14 @@
         <v>0.05792</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>0.05792</v>
+        <v>0.05763</v>
       </c>
       <c r="D298" s="1" t="n">
         <v>0.05792</v>
       </c>
+      <c r="E298" s="1" t="n">
+        <v>0.05763</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -5209,11 +6106,14 @@
         <v>0.09109</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>0.09109</v>
+        <v>0.09082</v>
       </c>
       <c r="D299" s="1" t="n">
         <v>0.09109</v>
       </c>
+      <c r="E299" s="1" t="n">
+        <v>0.09082</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -5225,11 +6125,14 @@
         <v>0.02792</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>0.02792</v>
+        <v>0.02774</v>
       </c>
       <c r="D300" s="1" t="n">
         <v>0.02792</v>
       </c>
+      <c r="E300" s="1" t="n">
+        <v>0.02774</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -5241,11 +6144,14 @@
         <v>0.06623999999999999</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>0.06623999999999999</v>
+        <v>0.06605999999999999</v>
       </c>
       <c r="D301" s="1" t="n">
         <v>0.06623999999999999</v>
       </c>
+      <c r="E301" s="1" t="n">
+        <v>0.06605999999999999</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -5257,9 +6163,12 @@
         <v>0.051794</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>0.051794</v>
+        <v>0.052263</v>
       </c>
       <c r="D302" s="1" t="n">
+        <v>0.052263</v>
+      </c>
+      <c r="E302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -5273,11 +6182,14 @@
         <v>5172.3</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>5172.3</v>
+        <v>5163.3</v>
       </c>
       <c r="D303" s="1" t="n">
         <v>5172.3</v>
       </c>
+      <c r="E303" s="1" t="n">
+        <v>5163.3</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -5289,9 +6201,12 @@
         <v>15.01</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>15.01</v>
+        <v>15.02</v>
       </c>
       <c r="D304" s="1" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="E304" s="1" t="n">
         <v>15.01</v>
       </c>
     </row>
@@ -5305,11 +6220,14 @@
         <v>0.00379</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>0.00379</v>
+        <v>0.003771</v>
       </c>
       <c r="D305" s="1" t="n">
         <v>0.00379</v>
       </c>
+      <c r="E305" s="1" t="n">
+        <v>0.003771</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -5321,11 +6239,14 @@
         <v>0.4602</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>0.4602</v>
+        <v>0.4573</v>
       </c>
       <c r="D306" s="1" t="n">
         <v>0.4602</v>
       </c>
+      <c r="E306" s="1" t="n">
+        <v>0.4573</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -5337,11 +6258,14 @@
         <v>0.04745</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>0.04745</v>
+        <v>0.04732</v>
       </c>
       <c r="D307" s="1" t="n">
         <v>0.04745</v>
       </c>
+      <c r="E307" s="1" t="n">
+        <v>0.04732</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -5353,9 +6277,12 @@
         <v>1.4598</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>1.4598</v>
+        <v>1.4627</v>
       </c>
       <c r="D308" s="1" t="n">
+        <v>1.4627</v>
+      </c>
+      <c r="E308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -5369,11 +6296,14 @@
         <v>0.0008101</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>0.0008101</v>
+        <v>0.0008068</v>
       </c>
       <c r="D309" s="1" t="n">
         <v>0.0008101</v>
       </c>
+      <c r="E309" s="1" t="n">
+        <v>0.0008068</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -5390,6 +6320,9 @@
       <c r="D310" s="1" t="n">
         <v>4.699</v>
       </c>
+      <c r="E310" s="1" t="n">
+        <v>4.699</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -5401,11 +6334,14 @@
         <v>4.784</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>4.784</v>
+        <v>4.778</v>
       </c>
       <c r="D311" s="1" t="n">
         <v>4.784</v>
       </c>
+      <c r="E311" s="1" t="n">
+        <v>4.778</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -5417,9 +6353,12 @@
         <v>0.08098</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>0.08098</v>
+        <v>0.08121</v>
       </c>
       <c r="D312" s="1" t="n">
+        <v>0.08121</v>
+      </c>
+      <c r="E312" s="1" t="n">
         <v>0.08098</v>
       </c>
     </row>
@@ -5433,11 +6372,14 @@
         <v>2.05</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>2.05</v>
+        <v>2.048</v>
       </c>
       <c r="D313" s="1" t="n">
         <v>2.05</v>
       </c>
+      <c r="E313" s="1" t="n">
+        <v>2.048</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -5449,9 +6391,12 @@
         <v>0.06802</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>0.06802</v>
+        <v>0.06839000000000001</v>
       </c>
       <c r="D314" s="1" t="n">
+        <v>0.06839000000000001</v>
+      </c>
+      <c r="E314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -5465,11 +6410,14 @@
         <v>0.97</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>0.97</v>
+        <v>0.959</v>
       </c>
       <c r="D315" s="1" t="n">
         <v>0.97</v>
       </c>
+      <c r="E315" s="1" t="n">
+        <v>0.959</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -5481,11 +6429,14 @@
         <v>0.1308</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>0.1308</v>
+        <v>0.1307</v>
       </c>
       <c r="D316" s="1" t="n">
         <v>0.1308</v>
       </c>
+      <c r="E316" s="1" t="n">
+        <v>0.1307</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -5497,9 +6448,12 @@
         <v>0.1761</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>0.1761</v>
+        <v>0.18</v>
       </c>
       <c r="D317" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -5513,9 +6467,12 @@
         <v>0.01661</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>0.01661</v>
+        <v>0.01666</v>
       </c>
       <c r="D318" s="1" t="n">
+        <v>0.01666</v>
+      </c>
+      <c r="E318" s="1" t="n">
         <v>0.01661</v>
       </c>
     </row>
@@ -5529,11 +6486,14 @@
         <v>0.08409</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>0.08409</v>
+        <v>0.08395</v>
       </c>
       <c r="D319" s="1" t="n">
         <v>0.08409</v>
       </c>
+      <c r="E319" s="1" t="n">
+        <v>0.08395</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -5545,11 +6505,14 @@
         <v>0.007659</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>0.007659</v>
+        <v>0.007618</v>
       </c>
       <c r="D320" s="1" t="n">
         <v>0.007659</v>
       </c>
+      <c r="E320" s="1" t="n">
+        <v>0.007618</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -5561,11 +6524,14 @@
         <v>0.05463</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>0.05463</v>
+        <v>0.05452</v>
       </c>
       <c r="D321" s="1" t="n">
         <v>0.05463</v>
       </c>
+      <c r="E321" s="1" t="n">
+        <v>0.05452</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -5577,11 +6543,14 @@
         <v>0.5513</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>0.5513</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="D322" s="1" t="n">
         <v>0.5513</v>
       </c>
+      <c r="E322" s="1" t="n">
+        <v>0.5489000000000001</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -5593,11 +6562,14 @@
         <v>0.07593</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>0.07593</v>
+        <v>0.07525</v>
       </c>
       <c r="D323" s="1" t="n">
         <v>0.07593</v>
       </c>
+      <c r="E323" s="1" t="n">
+        <v>0.07525</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -5609,9 +6581,12 @@
         <v>0.012745</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>0.012745</v>
+        <v>0.012753</v>
       </c>
       <c r="D324" s="1" t="n">
+        <v>0.012753</v>
+      </c>
+      <c r="E324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -5625,11 +6600,14 @@
         <v>0.0998</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>0.0998</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="D325" s="1" t="n">
         <v>0.0998</v>
       </c>
+      <c r="E325" s="1" t="n">
+        <v>0.09950000000000001</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -5641,11 +6619,14 @@
         <v>0.01756</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>0.01756</v>
+        <v>0.01753</v>
       </c>
       <c r="D326" s="1" t="n">
         <v>0.01756</v>
       </c>
+      <c r="E326" s="1" t="n">
+        <v>0.01753</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -5657,11 +6638,14 @@
         <v>0.06401999999999999</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>0.06401999999999999</v>
+        <v>0.06393</v>
       </c>
       <c r="D327" s="1" t="n">
         <v>0.06401999999999999</v>
       </c>
+      <c r="E327" s="1" t="n">
+        <v>0.06393</v>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -5673,11 +6657,14 @@
         <v>0.2696</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>0.2696</v>
+        <v>0.2681</v>
       </c>
       <c r="D328" s="1" t="n">
         <v>0.2696</v>
       </c>
+      <c r="E328" s="1" t="n">
+        <v>0.2681</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -5689,9 +6676,12 @@
         <v>0.17172</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>0.17172</v>
+        <v>0.17224</v>
       </c>
       <c r="D329" s="1" t="n">
+        <v>0.17224</v>
+      </c>
+      <c r="E329" s="1" t="n">
         <v>0.17172</v>
       </c>
     </row>
@@ -5705,9 +6695,12 @@
         <v>2.043</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>2.043</v>
+        <v>2.064</v>
       </c>
       <c r="D330" s="1" t="n">
+        <v>2.064</v>
+      </c>
+      <c r="E330" s="1" t="n">
         <v>2.043</v>
       </c>
     </row>
@@ -5721,11 +6714,14 @@
         <v>0.028</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>0.028</v>
+        <v>0.0278</v>
       </c>
       <c r="D331" s="1" t="n">
         <v>0.028</v>
       </c>
+      <c r="E331" s="1" t="n">
+        <v>0.0278</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -5737,9 +6733,12 @@
         <v>0.005927</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>0.005927</v>
+        <v>0.005932</v>
       </c>
       <c r="D332" s="1" t="n">
+        <v>0.005932</v>
+      </c>
+      <c r="E332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -5753,11 +6752,14 @@
         <v>0.00355</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>0.00355</v>
+        <v>0.003531</v>
       </c>
       <c r="D333" s="1" t="n">
         <v>0.00355</v>
       </c>
+      <c r="E333" s="1" t="n">
+        <v>0.003531</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -5769,11 +6771,14 @@
         <v>0.01417</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>0.01417</v>
+        <v>0.01409</v>
       </c>
       <c r="D334" s="1" t="n">
         <v>0.01417</v>
       </c>
+      <c r="E334" s="1" t="n">
+        <v>0.01409</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -5785,11 +6790,14 @@
         <v>1.125</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>1.125</v>
+        <v>1.12</v>
       </c>
       <c r="D335" s="1" t="n">
         <v>1.125</v>
       </c>
+      <c r="E335" s="1" t="n">
+        <v>1.12</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -5801,11 +6809,14 @@
         <v>0.011326</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>0.011326</v>
+        <v>0.011273</v>
       </c>
       <c r="D336" s="1" t="n">
         <v>0.011326</v>
       </c>
+      <c r="E336" s="1" t="n">
+        <v>0.011273</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -5817,9 +6828,12 @@
         <v>2.913</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>2.913</v>
+        <v>2.914</v>
       </c>
       <c r="D337" s="1" t="n">
+        <v>2.914</v>
+      </c>
+      <c r="E337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -5833,11 +6847,14 @@
         <v>0.01884</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>0.01884</v>
+        <v>0.01874</v>
       </c>
       <c r="D338" s="1" t="n">
         <v>0.01884</v>
       </c>
+      <c r="E338" s="1" t="n">
+        <v>0.01874</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -5849,9 +6866,12 @@
         <v>0.07689</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>0.07689</v>
+        <v>0.07691000000000001</v>
       </c>
       <c r="D339" s="1" t="n">
+        <v>0.07691000000000001</v>
+      </c>
+      <c r="E339" s="1" t="n">
         <v>0.07689</v>
       </c>
     </row>
@@ -5870,6 +6890,9 @@
       <c r="D340" s="1" t="n">
         <v>0.077</v>
       </c>
+      <c r="E340" s="1" t="n">
+        <v>0.077</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -5881,9 +6904,12 @@
         <v>0.0362</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>0.0362</v>
+        <v>0.03628</v>
       </c>
       <c r="D341" s="1" t="n">
+        <v>0.03628</v>
+      </c>
+      <c r="E341" s="1" t="n">
         <v>0.0362</v>
       </c>
     </row>
@@ -5897,9 +6923,12 @@
         <v>2623</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>2623</v>
+        <v>2635</v>
       </c>
       <c r="D342" s="1" t="n">
+        <v>2635</v>
+      </c>
+      <c r="E342" s="1" t="n">
         <v>2623</v>
       </c>
     </row>
@@ -5913,11 +6942,14 @@
         <v>0.000198</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>0.000198</v>
+        <v>0.0001965</v>
       </c>
       <c r="D343" s="1" t="n">
         <v>0.000198</v>
       </c>
+      <c r="E343" s="1" t="n">
+        <v>0.0001965</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -5929,11 +6961,14 @@
         <v>0.07993</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>0.07993</v>
+        <v>0.07989</v>
       </c>
       <c r="D344" s="1" t="n">
         <v>0.07993</v>
       </c>
+      <c r="E344" s="1" t="n">
+        <v>0.07989</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -5945,11 +6980,14 @@
         <v>0.01645</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>0.01645</v>
+        <v>0.0164</v>
       </c>
       <c r="D345" s="1" t="n">
         <v>0.01645</v>
       </c>
+      <c r="E345" s="1" t="n">
+        <v>0.0164</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -5961,11 +6999,14 @@
         <v>2.794</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>2.794</v>
+        <v>2.773</v>
       </c>
       <c r="D346" s="1" t="n">
         <v>2.794</v>
       </c>
+      <c r="E346" s="1" t="n">
+        <v>2.773</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -5977,11 +7018,14 @@
         <v>0.01647</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>0.01647</v>
+        <v>0.01643</v>
       </c>
       <c r="D347" s="1" t="n">
         <v>0.01647</v>
       </c>
+      <c r="E347" s="1" t="n">
+        <v>0.01643</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -5993,9 +7037,12 @@
         <v>0.03812</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>0.03812</v>
+        <v>0.03829</v>
       </c>
       <c r="D348" s="1" t="n">
+        <v>0.03829</v>
+      </c>
+      <c r="E348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -6009,11 +7056,14 @@
         <v>0.3065</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>0.3065</v>
+        <v>0.305</v>
       </c>
       <c r="D349" s="1" t="n">
         <v>0.3065</v>
       </c>
+      <c r="E349" s="1" t="n">
+        <v>0.305</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -6025,11 +7075,14 @@
         <v>0.005155</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>0.005155</v>
+        <v>0.005095</v>
       </c>
       <c r="D350" s="1" t="n">
         <v>0.005155</v>
       </c>
+      <c r="E350" s="1" t="n">
+        <v>0.005095</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -6041,11 +7094,14 @@
         <v>0.005171</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>0.005171</v>
+        <v>0.005145</v>
       </c>
       <c r="D351" s="1" t="n">
         <v>0.005171</v>
       </c>
+      <c r="E351" s="1" t="n">
+        <v>0.005145</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -6057,11 +7113,14 @@
         <v>0.004397</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>0.004397</v>
+        <v>0.004394</v>
       </c>
       <c r="D352" s="1" t="n">
         <v>0.004397</v>
       </c>
+      <c r="E352" s="1" t="n">
+        <v>0.004394</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -6073,11 +7132,14 @@
         <v>0.08211</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>0.08211</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="D353" s="1" t="n">
         <v>0.08211</v>
       </c>
+      <c r="E353" s="1" t="n">
+        <v>0.08210000000000001</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -6089,9 +7151,12 @@
         <v>1.283</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>1.283</v>
+        <v>1.291</v>
       </c>
       <c r="D354" s="1" t="n">
+        <v>1.291</v>
+      </c>
+      <c r="E354" s="1" t="n">
         <v>1.283</v>
       </c>
     </row>
@@ -6105,11 +7170,14 @@
         <v>7.771</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>7.771</v>
+        <v>7.744</v>
       </c>
       <c r="D355" s="1" t="n">
         <v>7.771</v>
       </c>
+      <c r="E355" s="1" t="n">
+        <v>7.744</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -6121,11 +7189,14 @@
         <v>0.007990000000000001</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>0.007990000000000001</v>
+        <v>0.007889999999999999</v>
       </c>
       <c r="D356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
+      <c r="E356" s="1" t="n">
+        <v>0.007889999999999999</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -6137,11 +7208,14 @@
         <v>0.005738</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>0.005738</v>
+        <v>0.00573</v>
       </c>
       <c r="D357" s="1" t="n">
         <v>0.005738</v>
       </c>
+      <c r="E357" s="1" t="n">
+        <v>0.00573</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -6153,11 +7227,14 @@
         <v>0.01582</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>0.01582</v>
+        <v>0.01577</v>
       </c>
       <c r="D358" s="1" t="n">
         <v>0.01582</v>
       </c>
+      <c r="E358" s="1" t="n">
+        <v>0.01577</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -6169,11 +7246,14 @@
         <v>3.655</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>3.655</v>
+        <v>3.654</v>
       </c>
       <c r="D359" s="1" t="n">
         <v>3.655</v>
       </c>
+      <c r="E359" s="1" t="n">
+        <v>3.654</v>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -6185,11 +7265,14 @@
         <v>0.1503</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>0.1503</v>
+        <v>0.1499</v>
       </c>
       <c r="D360" s="1" t="n">
         <v>0.1503</v>
       </c>
+      <c r="E360" s="1" t="n">
+        <v>0.1499</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -6201,11 +7284,14 @@
         <v>0.07093000000000001</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>0.07093000000000001</v>
+        <v>0.07069</v>
       </c>
       <c r="D361" s="1" t="n">
         <v>0.07093000000000001</v>
       </c>
+      <c r="E361" s="1" t="n">
+        <v>0.07069</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -6217,11 +7303,14 @@
         <v>0.01796</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>0.01796</v>
+        <v>0.01795</v>
       </c>
       <c r="D362" s="1" t="n">
         <v>0.01796</v>
       </c>
+      <c r="E362" s="1" t="n">
+        <v>0.01795</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -6233,11 +7322,14 @@
         <v>0.02278</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>0.02278</v>
+        <v>0.02262</v>
       </c>
       <c r="D363" s="1" t="n">
         <v>0.02278</v>
       </c>
+      <c r="E363" s="1" t="n">
+        <v>0.02262</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -6249,11 +7341,14 @@
         <v>0.01283</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>0.01283</v>
+        <v>0.01277</v>
       </c>
       <c r="D364" s="1" t="n">
         <v>0.01283</v>
       </c>
+      <c r="E364" s="1" t="n">
+        <v>0.01277</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -6270,6 +7365,9 @@
       <c r="D365" s="1" t="n">
         <v>0.0919</v>
       </c>
+      <c r="E365" s="1" t="n">
+        <v>0.0919</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -6281,11 +7379,14 @@
         <v>0.04257</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>0.04257</v>
+        <v>0.04245</v>
       </c>
       <c r="D366" s="1" t="n">
         <v>0.04257</v>
       </c>
+      <c r="E366" s="1" t="n">
+        <v>0.04245</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -6297,11 +7398,14 @@
         <v>0.03163</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>0.03163</v>
+        <v>0.03154</v>
       </c>
       <c r="D367" s="1" t="n">
         <v>0.03163</v>
       </c>
+      <c r="E367" s="1" t="n">
+        <v>0.03154</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -6313,11 +7417,14 @@
         <v>0.02405</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>0.02405</v>
+        <v>0.0236</v>
       </c>
       <c r="D368" s="1" t="n">
         <v>0.02405</v>
       </c>
+      <c r="E368" s="1" t="n">
+        <v>0.0236</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -6329,11 +7436,14 @@
         <v>0.03128</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>0.03128</v>
+        <v>0.03113</v>
       </c>
       <c r="D369" s="1" t="n">
         <v>0.03128</v>
       </c>
+      <c r="E369" s="1" t="n">
+        <v>0.03113</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -6345,11 +7455,14 @@
         <v>0.07784000000000001</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>0.07784000000000001</v>
+        <v>0.07741000000000001</v>
       </c>
       <c r="D370" s="1" t="n">
         <v>0.07784000000000001</v>
       </c>
+      <c r="E370" s="1" t="n">
+        <v>0.07741000000000001</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -6361,9 +7474,12 @@
         <v>0.1074</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>0.1074</v>
+        <v>0.1078</v>
       </c>
       <c r="D371" s="1" t="n">
+        <v>0.1078</v>
+      </c>
+      <c r="E371" s="1" t="n">
         <v>0.1074</v>
       </c>
     </row>
@@ -6377,9 +7493,12 @@
         <v>0.007057</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>0.007057</v>
+        <v>0.007108</v>
       </c>
       <c r="D372" s="1" t="n">
+        <v>0.007108</v>
+      </c>
+      <c r="E372" s="1" t="n">
         <v>0.007057</v>
       </c>
     </row>
@@ -6393,9 +7512,12 @@
         <v>0.09710000000000001</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="D373" s="1" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="E373" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
     </row>
@@ -6409,11 +7531,14 @@
         <v>0.05852</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>0.05852</v>
+        <v>0.0583</v>
       </c>
       <c r="D374" s="1" t="n">
         <v>0.05852</v>
       </c>
+      <c r="E374" s="1" t="n">
+        <v>0.0583</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -6425,9 +7550,12 @@
         <v>0.3197</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>0.3197</v>
+        <v>0.3207</v>
       </c>
       <c r="D375" s="1" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="E375" s="1" t="n">
         <v>0.3197</v>
       </c>
     </row>
@@ -6441,11 +7569,14 @@
         <v>0.02004</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>0.02004</v>
+        <v>0.01996</v>
       </c>
       <c r="D376" s="1" t="n">
         <v>0.02004</v>
       </c>
+      <c r="E376" s="1" t="n">
+        <v>0.01996</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -6457,11 +7588,14 @@
         <v>0.06926</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>0.06926</v>
+        <v>0.06888</v>
       </c>
       <c r="D377" s="1" t="n">
         <v>0.06926</v>
       </c>
+      <c r="E377" s="1" t="n">
+        <v>0.06888</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -6473,11 +7607,14 @@
         <v>0.15365</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>0.15365</v>
+        <v>0.15347</v>
       </c>
       <c r="D378" s="1" t="n">
         <v>0.15365</v>
       </c>
+      <c r="E378" s="1" t="n">
+        <v>0.15347</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -6489,11 +7626,14 @@
         <v>0.0006091</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>0.0006091</v>
+        <v>0.0006049</v>
       </c>
       <c r="D379" s="1" t="n">
         <v>0.0006091</v>
       </c>
+      <c r="E379" s="1" t="n">
+        <v>0.0006049</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -6505,11 +7645,14 @@
         <v>0.01019</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>0.01019</v>
+        <v>0.01016</v>
       </c>
       <c r="D380" s="1" t="n">
         <v>0.01019</v>
       </c>
+      <c r="E380" s="1" t="n">
+        <v>0.01016</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -6521,11 +7664,14 @@
         <v>0.0259</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>0.0259</v>
+        <v>0.02553</v>
       </c>
       <c r="D381" s="1" t="n">
         <v>0.0259</v>
       </c>
+      <c r="E381" s="1" t="n">
+        <v>0.02553</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -6537,9 +7683,12 @@
         <v>0.18936</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>0.18936</v>
+        <v>0.19064</v>
       </c>
       <c r="D382" s="1" t="n">
+        <v>0.19064</v>
+      </c>
+      <c r="E382" s="1" t="n">
         <v>0.18936</v>
       </c>
     </row>
@@ -6553,9 +7702,12 @@
         <v>0.09372999999999999</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>0.09372999999999999</v>
+        <v>0.09406</v>
       </c>
       <c r="D383" s="1" t="n">
+        <v>0.09406</v>
+      </c>
+      <c r="E383" s="1" t="n">
         <v>0.09372999999999999</v>
       </c>
     </row>
@@ -6569,9 +7721,12 @@
         <v>0.03194</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>0.03194</v>
+        <v>0.03206</v>
       </c>
       <c r="D384" s="1" t="n">
+        <v>0.03206</v>
+      </c>
+      <c r="E384" s="1" t="n">
         <v>0.03194</v>
       </c>
     </row>
@@ -6585,11 +7740,14 @@
         <v>0.01126</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>0.01126</v>
+        <v>0.0112</v>
       </c>
       <c r="D385" s="1" t="n">
         <v>0.01126</v>
       </c>
+      <c r="E385" s="1" t="n">
+        <v>0.0112</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -6601,11 +7759,14 @@
         <v>0.05101</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>0.05101</v>
+        <v>0.051</v>
       </c>
       <c r="D386" s="1" t="n">
         <v>0.05101</v>
       </c>
+      <c r="E386" s="1" t="n">
+        <v>0.051</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -6617,11 +7778,14 @@
         <v>0.02504</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>0.02504</v>
+        <v>0.02494</v>
       </c>
       <c r="D387" s="1" t="n">
         <v>0.02504</v>
       </c>
+      <c r="E387" s="1" t="n">
+        <v>0.02494</v>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -6633,9 +7797,12 @@
         <v>0.007344</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>0.007344</v>
+        <v>0.007365</v>
       </c>
       <c r="D388" s="1" t="n">
+        <v>0.007365</v>
+      </c>
+      <c r="E388" s="1" t="n">
         <v>0.007344</v>
       </c>
     </row>
@@ -6649,11 +7816,14 @@
         <v>0.0102</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>0.0102</v>
+        <v>0.01016</v>
       </c>
       <c r="D389" s="1" t="n">
         <v>0.0102</v>
       </c>
+      <c r="E389" s="1" t="n">
+        <v>0.01016</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -6665,9 +7835,12 @@
         <v>0.08304</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>0.08304</v>
+        <v>0.0833</v>
       </c>
       <c r="D390" s="1" t="n">
+        <v>0.0833</v>
+      </c>
+      <c r="E390" s="1" t="n">
         <v>0.08304</v>
       </c>
     </row>
@@ -6681,11 +7854,14 @@
         <v>0.5027</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>0.5027</v>
+        <v>0.5019</v>
       </c>
       <c r="D391" s="1" t="n">
         <v>0.5027</v>
       </c>
+      <c r="E391" s="1" t="n">
+        <v>0.5019</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -6697,11 +7873,14 @@
         <v>0.1174</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>0.1174</v>
+        <v>0.1172</v>
       </c>
       <c r="D392" s="1" t="n">
         <v>0.1174</v>
       </c>
+      <c r="E392" s="1" t="n">
+        <v>0.1172</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -6713,11 +7892,14 @@
         <v>0.00254</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>0.00254</v>
+        <v>0.00251</v>
       </c>
       <c r="D393" s="1" t="n">
         <v>0.00254</v>
       </c>
+      <c r="E393" s="1" t="n">
+        <v>0.00251</v>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -6734,6 +7916,9 @@
       <c r="D394" s="1" t="n">
         <v>0.02163</v>
       </c>
+      <c r="E394" s="1" t="n">
+        <v>0.02163</v>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -6745,9 +7930,12 @@
         <v>0.0162</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>0.0162</v>
+        <v>0.0163</v>
       </c>
       <c r="D395" s="1" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="E395" s="1" t="n">
         <v>0.0162</v>
       </c>
     </row>
@@ -6761,9 +7949,12 @@
         <v>0.1358</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>0.1358</v>
+        <v>0.1362</v>
       </c>
       <c r="D396" s="1" t="n">
+        <v>0.1362</v>
+      </c>
+      <c r="E396" s="1" t="n">
         <v>0.1358</v>
       </c>
     </row>
@@ -6777,11 +7968,14 @@
         <v>0.01486</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>0.01486</v>
+        <v>0.01482</v>
       </c>
       <c r="D397" s="1" t="n">
         <v>0.01486</v>
       </c>
+      <c r="E397" s="1" t="n">
+        <v>0.01482</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -6793,11 +7987,14 @@
         <v>6.755</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>6.755</v>
+        <v>6.725</v>
       </c>
       <c r="D398" s="1" t="n">
         <v>6.755</v>
       </c>
+      <c r="E398" s="1" t="n">
+        <v>6.725</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -6809,11 +8006,14 @@
         <v>0.009509999999999999</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>0.009509999999999999</v>
+        <v>0.009506000000000001</v>
       </c>
       <c r="D399" s="1" t="n">
         <v>0.009509999999999999</v>
       </c>
+      <c r="E399" s="1" t="n">
+        <v>0.009506000000000001</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -6825,9 +8025,12 @@
         <v>0.001287</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>0.001287</v>
+        <v>0.001291</v>
       </c>
       <c r="D400" s="1" t="n">
+        <v>0.001291</v>
+      </c>
+      <c r="E400" s="1" t="n">
         <v>0.001287</v>
       </c>
     </row>
@@ -6841,11 +8044,14 @@
         <v>0.01861</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>0.01861</v>
+        <v>0.01849</v>
       </c>
       <c r="D401" s="1" t="n">
         <v>0.01861</v>
       </c>
+      <c r="E401" s="1" t="n">
+        <v>0.01849</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -6857,9 +8063,12 @@
         <v>0.08563999999999999</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>0.08563999999999999</v>
+        <v>0.08577</v>
       </c>
       <c r="D402" s="1" t="n">
+        <v>0.08577</v>
+      </c>
+      <c r="E402" s="1" t="n">
         <v>0.08563999999999999</v>
       </c>
     </row>
@@ -6878,6 +8087,9 @@
       <c r="D403" s="1" t="n">
         <v>0.00553</v>
       </c>
+      <c r="E403" s="1" t="n">
+        <v>0.00553</v>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -6889,9 +8101,12 @@
         <v>0.0437</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>0.0437</v>
+        <v>0.04381</v>
       </c>
       <c r="D404" s="1" t="n">
+        <v>0.04381</v>
+      </c>
+      <c r="E404" s="1" t="n">
         <v>0.0437</v>
       </c>
     </row>
@@ -6905,11 +8120,14 @@
         <v>0.05876</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>0.05876</v>
+        <v>0.05871</v>
       </c>
       <c r="D405" s="1" t="n">
         <v>0.05876</v>
       </c>
+      <c r="E405" s="1" t="n">
+        <v>0.05871</v>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -6921,11 +8139,14 @@
         <v>0.01689</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>0.01689</v>
+        <v>0.01659</v>
       </c>
       <c r="D406" s="1" t="n">
         <v>0.01689</v>
       </c>
+      <c r="E406" s="1" t="n">
+        <v>0.01659</v>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -6937,11 +8158,14 @@
         <v>0.0428</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>0.0428</v>
+        <v>0.0426</v>
       </c>
       <c r="D407" s="1" t="n">
         <v>0.0428</v>
       </c>
+      <c r="E407" s="1" t="n">
+        <v>0.0426</v>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -6953,11 +8177,14 @@
         <v>0.0195</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>0.0195</v>
+        <v>0.01945</v>
       </c>
       <c r="D408" s="1" t="n">
         <v>0.0195</v>
       </c>
+      <c r="E408" s="1" t="n">
+        <v>0.01945</v>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -6969,9 +8196,12 @@
         <v>0.4427</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>0.4427</v>
+        <v>0.4439</v>
       </c>
       <c r="D409" s="1" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="E409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -6985,11 +8215,14 @@
         <v>0.04437</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>0.04437</v>
+        <v>0.04433</v>
       </c>
       <c r="D410" s="1" t="n">
         <v>0.04437</v>
       </c>
+      <c r="E410" s="1" t="n">
+        <v>0.04433</v>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -7001,11 +8234,14 @@
         <v>26.84</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>26.84</v>
+        <v>26.8</v>
       </c>
       <c r="D411" s="1" t="n">
         <v>26.84</v>
       </c>
+      <c r="E411" s="1" t="n">
+        <v>26.8</v>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -7017,11 +8253,14 @@
         <v>0.03561</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>0.03561</v>
+        <v>0.03527</v>
       </c>
       <c r="D412" s="1" t="n">
         <v>0.03561</v>
       </c>
+      <c r="E412" s="1" t="n">
+        <v>0.03527</v>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -7033,11 +8272,14 @@
         <v>0.003429</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>0.003429</v>
+        <v>0.003425</v>
       </c>
       <c r="D413" s="1" t="n">
         <v>0.003429</v>
       </c>
+      <c r="E413" s="1" t="n">
+        <v>0.003425</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -7049,11 +8291,14 @@
         <v>0.1531</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>0.1531</v>
+        <v>0.1527</v>
       </c>
       <c r="D414" s="1" t="n">
         <v>0.1531</v>
       </c>
+      <c r="E414" s="1" t="n">
+        <v>0.1527</v>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -7065,11 +8310,14 @@
         <v>0.05263</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>0.05263</v>
+        <v>0.05258</v>
       </c>
       <c r="D415" s="1" t="n">
         <v>0.05263</v>
       </c>
+      <c r="E415" s="1" t="n">
+        <v>0.05258</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -7081,11 +8329,14 @@
         <v>0.00668</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>0.00668</v>
+        <v>0.00664</v>
       </c>
       <c r="D416" s="1" t="n">
         <v>0.00668</v>
       </c>
+      <c r="E416" s="1" t="n">
+        <v>0.00664</v>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -7097,9 +8348,12 @@
         <v>0.06086</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>0.06086</v>
+        <v>0.06091</v>
       </c>
       <c r="D417" s="1" t="n">
+        <v>0.06091</v>
+      </c>
+      <c r="E417" s="1" t="n">
         <v>0.06086</v>
       </c>
     </row>
@@ -7113,11 +8367,14 @@
         <v>0.008241</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>0.008241</v>
+        <v>0.008199</v>
       </c>
       <c r="D418" s="1" t="n">
         <v>0.008241</v>
       </c>
+      <c r="E418" s="1" t="n">
+        <v>0.008199</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -7129,11 +8386,14 @@
         <v>0.07466</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>0.07466</v>
+        <v>0.07459</v>
       </c>
       <c r="D419" s="1" t="n">
         <v>0.07466</v>
       </c>
+      <c r="E419" s="1" t="n">
+        <v>0.07459</v>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -7145,11 +8405,14 @@
         <v>0.02145</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>0.02145</v>
+        <v>0.02135</v>
       </c>
       <c r="D420" s="1" t="n">
         <v>0.02145</v>
       </c>
+      <c r="E420" s="1" t="n">
+        <v>0.02135</v>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -7161,11 +8424,14 @@
         <v>0.06984</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>0.06984</v>
+        <v>0.06938999999999999</v>
       </c>
       <c r="D421" s="1" t="n">
         <v>0.06984</v>
       </c>
+      <c r="E421" s="1" t="n">
+        <v>0.06938999999999999</v>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -7177,11 +8443,14 @@
         <v>0.01527</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>0.01527</v>
+        <v>0.01524</v>
       </c>
       <c r="D422" s="1" t="n">
         <v>0.01527</v>
       </c>
+      <c r="E422" s="1" t="n">
+        <v>0.01524</v>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -7193,11 +8462,14 @@
         <v>0.006699</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>0.006699</v>
+        <v>0.006689</v>
       </c>
       <c r="D423" s="1" t="n">
         <v>0.006699</v>
       </c>
+      <c r="E423" s="1" t="n">
+        <v>0.006689</v>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -7209,11 +8481,14 @@
         <v>0.92</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>0.92</v>
+        <v>0.919</v>
       </c>
       <c r="D424" s="1" t="n">
         <v>0.92</v>
       </c>
+      <c r="E424" s="1" t="n">
+        <v>0.919</v>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -7225,11 +8500,14 @@
         <v>0.03561</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>0.03561</v>
+        <v>0.03555</v>
       </c>
       <c r="D425" s="1" t="n">
         <v>0.03561</v>
       </c>
+      <c r="E425" s="1" t="n">
+        <v>0.03555</v>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -7241,11 +8519,14 @@
         <v>1.781</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>1.781</v>
+        <v>1.778</v>
       </c>
       <c r="D426" s="1" t="n">
         <v>1.781</v>
       </c>
+      <c r="E426" s="1" t="n">
+        <v>1.778</v>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -7257,11 +8538,14 @@
         <v>0.12793</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>0.12793</v>
+        <v>0.12781</v>
       </c>
       <c r="D427" s="1" t="n">
         <v>0.12793</v>
       </c>
+      <c r="E427" s="1" t="n">
+        <v>0.12781</v>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -7273,9 +8557,12 @@
         <v>0.05354</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>0.05354</v>
+        <v>0.05359</v>
       </c>
       <c r="D428" s="1" t="n">
+        <v>0.05359</v>
+      </c>
+      <c r="E428" s="1" t="n">
         <v>0.05354</v>
       </c>
     </row>
@@ -7289,11 +8576,14 @@
         <v>1.333</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>1.333</v>
+        <v>1.317</v>
       </c>
       <c r="D429" s="1" t="n">
         <v>1.333</v>
       </c>
+      <c r="E429" s="1" t="n">
+        <v>1.317</v>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -7305,9 +8595,12 @@
         <v>0.07563</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>0.07563</v>
+        <v>0.07566000000000001</v>
       </c>
       <c r="D430" s="1" t="n">
+        <v>0.07566000000000001</v>
+      </c>
+      <c r="E430" s="1" t="n">
         <v>0.07563</v>
       </c>
     </row>
@@ -7321,11 +8614,14 @@
         <v>0.1652</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>0.1652</v>
+        <v>0.1641</v>
       </c>
       <c r="D431" s="1" t="n">
         <v>0.1652</v>
       </c>
+      <c r="E431" s="1" t="n">
+        <v>0.1641</v>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -7337,11 +8633,14 @@
         <v>1.457</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>1.457</v>
+        <v>1.456</v>
       </c>
       <c r="D432" s="1" t="n">
         <v>1.457</v>
       </c>
+      <c r="E432" s="1" t="n">
+        <v>1.456</v>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -7353,11 +8652,14 @@
         <v>3.316</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>3.316</v>
+        <v>3.306</v>
       </c>
       <c r="D433" s="1" t="n">
         <v>3.316</v>
       </c>
+      <c r="E433" s="1" t="n">
+        <v>3.306</v>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -7369,11 +8671,14 @@
         <v>0.1802</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>0.1802</v>
+        <v>0.1796</v>
       </c>
       <c r="D434" s="1" t="n">
         <v>0.1802</v>
       </c>
+      <c r="E434" s="1" t="n">
+        <v>0.1796</v>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -7385,11 +8690,14 @@
         <v>0.008717000000000001</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>0.008717000000000001</v>
+        <v>0.008688</v>
       </c>
       <c r="D435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
+      <c r="E435" s="1" t="n">
+        <v>0.008688</v>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -7401,11 +8709,14 @@
         <v>0.2881</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>0.2881</v>
+        <v>0.2841</v>
       </c>
       <c r="D436" s="1" t="n">
         <v>0.2881</v>
       </c>
+      <c r="E436" s="1" t="n">
+        <v>0.2841</v>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -7422,6 +8733,9 @@
       <c r="D437" s="1" t="n">
         <v>0.03814</v>
       </c>
+      <c r="E437" s="1" t="n">
+        <v>0.03814</v>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -7433,11 +8747,14 @@
         <v>0.02474</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>0.02474</v>
+        <v>0.02452</v>
       </c>
       <c r="D438" s="1" t="n">
         <v>0.02474</v>
       </c>
+      <c r="E438" s="1" t="n">
+        <v>0.02452</v>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -7449,11 +8766,14 @@
         <v>0.04418</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>0.04418</v>
+        <v>0.0441</v>
       </c>
       <c r="D439" s="1" t="n">
         <v>0.04418</v>
       </c>
+      <c r="E439" s="1" t="n">
+        <v>0.0441</v>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -7465,11 +8785,14 @@
         <v>0.0005258</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>0.0005258</v>
+        <v>0.0005232</v>
       </c>
       <c r="D440" s="1" t="n">
         <v>0.0005258</v>
       </c>
+      <c r="E440" s="1" t="n">
+        <v>0.0005232</v>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -7481,11 +8804,14 @@
         <v>0.04428</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>0.04428</v>
+        <v>0.04406</v>
       </c>
       <c r="D441" s="1" t="n">
         <v>0.04428</v>
       </c>
+      <c r="E441" s="1" t="n">
+        <v>0.04406</v>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -7497,11 +8823,14 @@
         <v>0.000416</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>0.000416</v>
+        <v>0.000415</v>
       </c>
       <c r="D442" s="1" t="n">
         <v>0.000416</v>
       </c>
+      <c r="E442" s="1" t="n">
+        <v>0.000415</v>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -7513,9 +8842,12 @@
         <v>0.09737</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>0.09737</v>
+        <v>0.09789</v>
       </c>
       <c r="D443" s="1" t="n">
+        <v>0.09789</v>
+      </c>
+      <c r="E443" s="1" t="n">
         <v>0.09737</v>
       </c>
     </row>
@@ -7529,11 +8861,14 @@
         <v>2.321</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>2.321</v>
+        <v>2.298</v>
       </c>
       <c r="D444" s="1" t="n">
         <v>2.321</v>
       </c>
+      <c r="E444" s="1" t="n">
+        <v>2.298</v>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -7545,9 +8880,12 @@
         <v>0.2661</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>0.2661</v>
+        <v>0.2671</v>
       </c>
       <c r="D445" s="1" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="E445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -7561,11 +8899,14 @@
         <v>0.0007577</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>0.0007577</v>
+        <v>0.0007548</v>
       </c>
       <c r="D446" s="1" t="n">
         <v>0.0007577</v>
       </c>
+      <c r="E446" s="1" t="n">
+        <v>0.0007548</v>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -7577,11 +8918,14 @@
         <v>0.03904</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>0.03904</v>
+        <v>0.03901</v>
       </c>
       <c r="D447" s="1" t="n">
         <v>0.03904</v>
       </c>
+      <c r="E447" s="1" t="n">
+        <v>0.03901</v>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -7593,11 +8937,14 @@
         <v>0.1756</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>0.1756</v>
+        <v>0.1755</v>
       </c>
       <c r="D448" s="1" t="n">
         <v>0.1756</v>
       </c>
+      <c r="E448" s="1" t="n">
+        <v>0.1755</v>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -7609,11 +8956,14 @@
         <v>0.04301</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>0.04301</v>
+        <v>0.04287</v>
       </c>
       <c r="D449" s="1" t="n">
         <v>0.04301</v>
       </c>
+      <c r="E449" s="1" t="n">
+        <v>0.04287</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -7625,11 +8975,14 @@
         <v>0.0001654</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>0.0001654</v>
+        <v>0.0001643</v>
       </c>
       <c r="D450" s="1" t="n">
         <v>0.0001654</v>
       </c>
+      <c r="E450" s="1" t="n">
+        <v>0.0001643</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -7641,11 +8994,14 @@
         <v>0.03784</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>0.03784</v>
+        <v>0.03779</v>
       </c>
       <c r="D451" s="1" t="n">
         <v>0.03784</v>
       </c>
+      <c r="E451" s="1" t="n">
+        <v>0.03779</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -7657,9 +9013,12 @@
         <v>0.00996</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>0.00996</v>
+        <v>0.01</v>
       </c>
       <c r="D452" s="1" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E452" s="1" t="n">
         <v>0.00996</v>
       </c>
     </row>
@@ -7673,11 +9032,14 @@
         <v>0.06798999999999999</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>0.06798999999999999</v>
+        <v>0.06796000000000001</v>
       </c>
       <c r="D453" s="1" t="n">
         <v>0.06798999999999999</v>
       </c>
+      <c r="E453" s="1" t="n">
+        <v>0.06796000000000001</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -7689,11 +9051,14 @@
         <v>0.007613</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>0.007613</v>
+        <v>0.007554</v>
       </c>
       <c r="D454" s="1" t="n">
         <v>0.007613</v>
       </c>
+      <c r="E454" s="1" t="n">
+        <v>0.007554</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -7705,9 +9070,12 @@
         <v>0.00337</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>0.00337</v>
+        <v>0.003377</v>
       </c>
       <c r="D455" s="1" t="n">
+        <v>0.003377</v>
+      </c>
+      <c r="E455" s="1" t="n">
         <v>0.00337</v>
       </c>
     </row>
@@ -7721,11 +9089,14 @@
         <v>0.001864</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>0.001864</v>
+        <v>0.001859</v>
       </c>
       <c r="D456" s="1" t="n">
         <v>0.001864</v>
       </c>
+      <c r="E456" s="1" t="n">
+        <v>0.001859</v>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -7737,9 +9108,12 @@
         <v>0.0001762</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>0.0001762</v>
+        <v>0.0001763</v>
       </c>
       <c r="D457" s="1" t="n">
+        <v>0.0001763</v>
+      </c>
+      <c r="E457" s="1" t="n">
         <v>0.0001762</v>
       </c>
     </row>
@@ -7753,11 +9127,14 @@
         <v>0.0003878</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>0.0003878</v>
+        <v>0.0003873</v>
       </c>
       <c r="D458" s="1" t="n">
         <v>0.0003878</v>
       </c>
+      <c r="E458" s="1" t="n">
+        <v>0.0003873</v>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -7769,11 +9146,14 @@
         <v>0.01406</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>0.01406</v>
+        <v>0.01404</v>
       </c>
       <c r="D459" s="1" t="n">
         <v>0.01406</v>
       </c>
+      <c r="E459" s="1" t="n">
+        <v>0.01404</v>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -7785,9 +9165,12 @@
         <v>0.04518</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>0.04518</v>
+        <v>0.04532</v>
       </c>
       <c r="D460" s="1" t="n">
+        <v>0.04532</v>
+      </c>
+      <c r="E460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -7801,11 +9184,14 @@
         <v>0.283</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>0.283</v>
+        <v>0.2823</v>
       </c>
       <c r="D461" s="1" t="n">
         <v>0.283</v>
       </c>
+      <c r="E461" s="1" t="n">
+        <v>0.2823</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -7817,11 +9203,14 @@
         <v>0.006279</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>0.006279</v>
+        <v>0.00622</v>
       </c>
       <c r="D462" s="1" t="n">
         <v>0.006279</v>
       </c>
+      <c r="E462" s="1" t="n">
+        <v>0.00622</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -7833,11 +9222,14 @@
         <v>0.007056</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>0.007056</v>
+        <v>0.007052</v>
       </c>
       <c r="D463" s="1" t="n">
         <v>0.007056</v>
       </c>
+      <c r="E463" s="1" t="n">
+        <v>0.007052</v>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -7849,9 +9241,12 @@
         <v>0.2853</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>0.2853</v>
+        <v>0.2864</v>
       </c>
       <c r="D464" s="1" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="E464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -7865,11 +9260,14 @@
         <v>0.08134</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>0.08134</v>
+        <v>0.08082</v>
       </c>
       <c r="D465" s="1" t="n">
         <v>0.08134</v>
       </c>
+      <c r="E465" s="1" t="n">
+        <v>0.08082</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -7881,11 +9279,14 @@
         <v>0.6343</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>0.6343</v>
+        <v>0.6338</v>
       </c>
       <c r="D466" s="1" t="n">
         <v>0.6343</v>
       </c>
+      <c r="E466" s="1" t="n">
+        <v>0.6338</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -7897,9 +9298,12 @@
         <v>0.0147</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>0.0147</v>
+        <v>0.01471</v>
       </c>
       <c r="D467" s="1" t="n">
+        <v>0.01471</v>
+      </c>
+      <c r="E467" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -7913,11 +9317,14 @@
         <v>0.03462</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>0.03462</v>
+        <v>0.03458</v>
       </c>
       <c r="D468" s="1" t="n">
         <v>0.03462</v>
       </c>
+      <c r="E468" s="1" t="n">
+        <v>0.03458</v>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -7929,11 +9336,14 @@
         <v>0.1652</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>0.1652</v>
+        <v>0.1645</v>
       </c>
       <c r="D469" s="1" t="n">
         <v>0.1652</v>
       </c>
+      <c r="E469" s="1" t="n">
+        <v>0.1645</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -7945,9 +9355,12 @@
         <v>0.4137</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>0.4137</v>
+        <v>0.4139</v>
       </c>
       <c r="D470" s="1" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="E470" s="1" t="n">
         <v>0.4137</v>
       </c>
     </row>
@@ -7961,11 +9374,14 @@
         <v>0.07015</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>0.07015</v>
+        <v>0.06988</v>
       </c>
       <c r="D471" s="1" t="n">
         <v>0.07015</v>
       </c>
+      <c r="E471" s="1" t="n">
+        <v>0.06988</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -7977,11 +9393,14 @@
         <v>0.06773999999999999</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>0.06773999999999999</v>
+        <v>0.06701</v>
       </c>
       <c r="D472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
+      <c r="E472" s="1" t="n">
+        <v>0.06701</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -7993,11 +9412,14 @@
         <v>0.01647</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>0.01647</v>
+        <v>0.01643</v>
       </c>
       <c r="D473" s="1" t="n">
         <v>0.01647</v>
       </c>
+      <c r="E473" s="1" t="n">
+        <v>0.01643</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -8009,11 +9431,14 @@
         <v>0.2124</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>0.2124</v>
+        <v>0.2108</v>
       </c>
       <c r="D474" s="1" t="n">
         <v>0.2124</v>
       </c>
+      <c r="E474" s="1" t="n">
+        <v>0.2108</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -8025,11 +9450,14 @@
         <v>0.04289</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>0.04289</v>
+        <v>0.04219</v>
       </c>
       <c r="D475" s="1" t="n">
         <v>0.04289</v>
       </c>
+      <c r="E475" s="1" t="n">
+        <v>0.04219</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -8041,9 +9469,12 @@
         <v>1.571</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>1.571</v>
+        <v>1.572</v>
       </c>
       <c r="D476" s="1" t="n">
+        <v>1.572</v>
+      </c>
+      <c r="E476" s="1" t="n">
         <v>1.571</v>
       </c>
     </row>
@@ -8057,11 +9488,14 @@
         <v>0.1019</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>0.1019</v>
+        <v>0.1015</v>
       </c>
       <c r="D477" s="1" t="n">
         <v>0.1019</v>
       </c>
+      <c r="E477" s="1" t="n">
+        <v>0.1015</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -8073,11 +9507,14 @@
         <v>0.001162</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>0.001162</v>
+        <v>0.001159</v>
       </c>
       <c r="D478" s="1" t="n">
         <v>0.001162</v>
       </c>
+      <c r="E478" s="1" t="n">
+        <v>0.001159</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -8089,11 +9526,14 @@
         <v>0.1473</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>0.1473</v>
+        <v>0.1466</v>
       </c>
       <c r="D479" s="1" t="n">
         <v>0.1473</v>
       </c>
+      <c r="E479" s="1" t="n">
+        <v>0.1466</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -8105,11 +9545,14 @@
         <v>0.00173</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>0.00173</v>
+        <v>0.001728</v>
       </c>
       <c r="D480" s="1" t="n">
         <v>0.00173</v>
       </c>
+      <c r="E480" s="1" t="n">
+        <v>0.001728</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -8121,11 +9564,14 @@
         <v>0.925</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>0.925</v>
+        <v>0.923</v>
       </c>
       <c r="D481" s="1" t="n">
         <v>0.925</v>
       </c>
+      <c r="E481" s="1" t="n">
+        <v>0.923</v>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -8137,11 +9583,14 @@
         <v>0.13673</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>0.13673</v>
+        <v>0.13437</v>
       </c>
       <c r="D482" s="1" t="n">
         <v>0.13673</v>
       </c>
+      <c r="E482" s="1" t="n">
+        <v>0.13437</v>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -8153,9 +9602,12 @@
         <v>0.04048</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>0.04048</v>
+        <v>0.04056</v>
       </c>
       <c r="D483" s="1" t="n">
+        <v>0.04056</v>
+      </c>
+      <c r="E483" s="1" t="n">
         <v>0.04048</v>
       </c>
     </row>
@@ -8169,9 +9621,12 @@
         <v>0.3001</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>0.3001</v>
+        <v>0.3137</v>
       </c>
       <c r="D484" s="1" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="E484" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -8185,9 +9640,12 @@
         <v>0.05633</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>0.05633</v>
+        <v>0.05671</v>
       </c>
       <c r="D485" s="1" t="n">
+        <v>0.05671</v>
+      </c>
+      <c r="E485" s="1" t="n">
         <v>0.05633</v>
       </c>
     </row>
@@ -8206,6 +9664,9 @@
       <c r="D486" s="1" t="n">
         <v>0.001572</v>
       </c>
+      <c r="E486" s="1" t="n">
+        <v>0.001572</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -8217,11 +9678,14 @@
         <v>0.06738</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>0.06738</v>
+        <v>0.06722</v>
       </c>
       <c r="D487" s="1" t="n">
         <v>0.06738</v>
       </c>
+      <c r="E487" s="1" t="n">
+        <v>0.06722</v>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -8233,11 +9697,14 @@
         <v>0.1942</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>0.1942</v>
+        <v>0.194</v>
       </c>
       <c r="D488" s="1" t="n">
         <v>0.1942</v>
       </c>
+      <c r="E488" s="1" t="n">
+        <v>0.194</v>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -8249,9 +9716,12 @@
         <v>0.04815</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>0.04815</v>
+        <v>0.04817</v>
       </c>
       <c r="D489" s="1" t="n">
+        <v>0.04817</v>
+      </c>
+      <c r="E489" s="1" t="n">
         <v>0.04815</v>
       </c>
     </row>
@@ -8270,6 +9740,9 @@
       <c r="D490" s="1" t="n">
         <v>0.1395</v>
       </c>
+      <c r="E490" s="1" t="n">
+        <v>0.1395</v>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -8281,11 +9754,14 @@
         <v>0.02281</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>0.02281</v>
+        <v>0.02243</v>
       </c>
       <c r="D491" s="1" t="n">
         <v>0.02281</v>
       </c>
+      <c r="E491" s="1" t="n">
+        <v>0.02243</v>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -8297,11 +9773,14 @@
         <v>0.007929</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>0.007929</v>
+        <v>0.007856</v>
       </c>
       <c r="D492" s="1" t="n">
         <v>0.007929</v>
       </c>
+      <c r="E492" s="1" t="n">
+        <v>0.007856</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -8313,11 +9792,14 @@
         <v>0.0005967</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>0.0005967</v>
+        <v>0.0005966</v>
       </c>
       <c r="D493" s="1" t="n">
         <v>0.0005967</v>
       </c>
+      <c r="E493" s="1" t="n">
+        <v>0.0005966</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -8329,11 +9811,14 @@
         <v>3.038</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>3.038</v>
+        <v>3.029</v>
       </c>
       <c r="D494" s="1" t="n">
         <v>3.038</v>
       </c>
+      <c r="E494" s="1" t="n">
+        <v>3.029</v>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -8345,9 +9830,12 @@
         <v>0.05102</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>0.05102</v>
+        <v>0.05103</v>
       </c>
       <c r="D495" s="1" t="n">
+        <v>0.05103</v>
+      </c>
+      <c r="E495" s="1" t="n">
         <v>0.05102</v>
       </c>
     </row>
@@ -8366,6 +9854,9 @@
       <c r="D496" s="1" t="n">
         <v>0.006886</v>
       </c>
+      <c r="E496" s="1" t="n">
+        <v>0.006886</v>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -8377,9 +9868,12 @@
         <v>1.3</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>1.3</v>
+        <v>1.302</v>
       </c>
       <c r="D497" s="1" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="E497" s="1" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -8393,11 +9887,14 @@
         <v>0.04018</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>0.04018</v>
+        <v>0.04015</v>
       </c>
       <c r="D498" s="1" t="n">
         <v>0.04018</v>
       </c>
+      <c r="E498" s="1" t="n">
+        <v>0.04015</v>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -8409,11 +9906,14 @@
         <v>0.04206</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>0.04206</v>
+        <v>0.04204</v>
       </c>
       <c r="D499" s="1" t="n">
         <v>0.04206</v>
       </c>
+      <c r="E499" s="1" t="n">
+        <v>0.04204</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -8425,11 +9925,14 @@
         <v>0.0054</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>0.0054</v>
+        <v>0.00538</v>
       </c>
       <c r="D500" s="1" t="n">
         <v>0.0054</v>
       </c>
+      <c r="E500" s="1" t="n">
+        <v>0.00538</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -8441,9 +9944,12 @@
         <v>0.03628</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>0.03628</v>
+        <v>0.03638</v>
       </c>
       <c r="D501" s="1" t="n">
+        <v>0.03638</v>
+      </c>
+      <c r="E501" s="1" t="n">
         <v>0.03628</v>
       </c>
     </row>
@@ -8457,11 +9963,14 @@
         <v>0.07335999999999999</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>0.07335999999999999</v>
+        <v>0.07321</v>
       </c>
       <c r="D502" s="1" t="n">
         <v>0.07335999999999999</v>
       </c>
+      <c r="E502" s="1" t="n">
+        <v>0.07321</v>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -8473,11 +9982,14 @@
         <v>0.0007543</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>0.0007543</v>
+        <v>0.0007531</v>
       </c>
       <c r="D503" s="1" t="n">
         <v>0.0007543</v>
       </c>
+      <c r="E503" s="1" t="n">
+        <v>0.0007531</v>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -8489,11 +10001,14 @@
         <v>0.015956</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>0.015956</v>
+        <v>0.015946</v>
       </c>
       <c r="D504" s="1" t="n">
         <v>0.015956</v>
       </c>
+      <c r="E504" s="1" t="n">
+        <v>0.015946</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -8510,6 +10025,9 @@
       <c r="D505" s="1" t="n">
         <v>0.00709</v>
       </c>
+      <c r="E505" s="1" t="n">
+        <v>0.00709</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -8526,6 +10044,9 @@
       <c r="D506" s="1" t="n">
         <v>0.0257</v>
       </c>
+      <c r="E506" s="1" t="n">
+        <v>0.0257</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -8537,9 +10058,12 @@
         <v>0.00135</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>0.00135</v>
+        <v>0.001351</v>
       </c>
       <c r="D507" s="1" t="n">
+        <v>0.001351</v>
+      </c>
+      <c r="E507" s="1" t="n">
         <v>0.00135</v>
       </c>
     </row>
@@ -8553,11 +10077,14 @@
         <v>0.2837</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>0.2837</v>
+        <v>0.2831</v>
       </c>
       <c r="D508" s="1" t="n">
         <v>0.2837</v>
       </c>
+      <c r="E508" s="1" t="n">
+        <v>0.2831</v>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -8569,11 +10096,14 @@
         <v>0.1324</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>0.1324</v>
+        <v>0.1323</v>
       </c>
       <c r="D509" s="1" t="n">
         <v>0.1324</v>
       </c>
+      <c r="E509" s="1" t="n">
+        <v>0.1323</v>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -8585,11 +10115,14 @@
         <v>0.04949</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>0.04949</v>
+        <v>0.04932</v>
       </c>
       <c r="D510" s="1" t="n">
         <v>0.04949</v>
       </c>
+      <c r="E510" s="1" t="n">
+        <v>0.04932</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -8601,11 +10134,14 @@
         <v>0.00277</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>0.00277</v>
+        <v>0.00276</v>
       </c>
       <c r="D511" s="1" t="n">
         <v>0.00277</v>
       </c>
+      <c r="E511" s="1" t="n">
+        <v>0.00276</v>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -8617,11 +10153,14 @@
         <v>0.015434</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>0.015434</v>
+        <v>0.015402</v>
       </c>
       <c r="D512" s="1" t="n">
         <v>0.015434</v>
       </c>
+      <c r="E512" s="1" t="n">
+        <v>0.015402</v>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -8633,9 +10172,12 @@
         <v>0.6938</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>0.6938</v>
+        <v>0.6948</v>
       </c>
       <c r="D513" s="1" t="n">
+        <v>0.6948</v>
+      </c>
+      <c r="E513" s="1" t="n">
         <v>0.6938</v>
       </c>
     </row>
@@ -8649,11 +10191,14 @@
         <v>0.004561</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>0.004561</v>
+        <v>0.004534</v>
       </c>
       <c r="D514" s="1" t="n">
         <v>0.004561</v>
       </c>
+      <c r="E514" s="1" t="n">
+        <v>0.004534</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
@@ -8670,6 +10215,9 @@
       <c r="D515" s="1" t="n">
         <v>0.005048</v>
       </c>
+      <c r="E515" s="1" t="n">
+        <v>0.005048</v>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
@@ -8681,11 +10229,14 @@
         <v>0.06385</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>0.06385</v>
+        <v>0.06372999999999999</v>
       </c>
       <c r="D516" s="1" t="n">
         <v>0.06385</v>
       </c>
+      <c r="E516" s="1" t="n">
+        <v>0.06372999999999999</v>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
@@ -8697,11 +10248,14 @@
         <v>0.06401999999999999</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>0.06401999999999999</v>
+        <v>0.06401</v>
       </c>
       <c r="D517" s="1" t="n">
         <v>0.06401999999999999</v>
       </c>
+      <c r="E517" s="1" t="n">
+        <v>0.06401</v>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
@@ -8713,11 +10267,14 @@
         <v>0.01216</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>0.01216</v>
+        <v>0.01214</v>
       </c>
       <c r="D518" s="1" t="n">
         <v>0.01216</v>
       </c>
+      <c r="E518" s="1" t="n">
+        <v>0.01214</v>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
@@ -8729,11 +10286,14 @@
         <v>0.04794</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>0.04794</v>
+        <v>0.04768</v>
       </c>
       <c r="D519" s="1" t="n">
         <v>0.04794</v>
       </c>
+      <c r="E519" s="1" t="n">
+        <v>0.04768</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
@@ -8745,11 +10305,14 @@
         <v>0.04396</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>0.04396</v>
+        <v>0.04394</v>
       </c>
       <c r="D520" s="1" t="n">
         <v>0.04396</v>
       </c>
+      <c r="E520" s="1" t="n">
+        <v>0.04394</v>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
@@ -8761,9 +10324,12 @@
         <v>0.008557</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>0.008557</v>
+        <v>0.008560999999999999</v>
       </c>
       <c r="D521" s="1" t="n">
+        <v>0.008560999999999999</v>
+      </c>
+      <c r="E521" s="1" t="n">
         <v>0.008557</v>
       </c>
     </row>
@@ -8777,11 +10343,14 @@
         <v>0.08992</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>0.08992</v>
+        <v>0.08969000000000001</v>
       </c>
       <c r="D522" s="1" t="n">
         <v>0.08992</v>
       </c>
+      <c r="E522" s="1" t="n">
+        <v>0.08969000000000001</v>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
@@ -8793,9 +10362,12 @@
         <v>0.00646</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>0.00646</v>
+        <v>0.006466</v>
       </c>
       <c r="D523" s="1" t="n">
+        <v>0.006466</v>
+      </c>
+      <c r="E523" s="1" t="n">
         <v>0.00646</v>
       </c>
     </row>
@@ -8809,11 +10381,14 @@
         <v>0.01671</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>0.01671</v>
+        <v>0.01663</v>
       </c>
       <c r="D524" s="1" t="n">
         <v>0.01671</v>
       </c>
+      <c r="E524" s="1" t="n">
+        <v>0.01663</v>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
@@ -8830,6 +10405,9 @@
       <c r="D525" s="1" t="n">
         <v>0.01808</v>
       </c>
+      <c r="E525" s="1" t="n">
+        <v>0.01808</v>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -8841,11 +10419,14 @@
         <v>0.07938000000000001</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>0.07938000000000001</v>
+        <v>0.07917</v>
       </c>
       <c r="D526" s="1" t="n">
         <v>0.07938000000000001</v>
       </c>
+      <c r="E526" s="1" t="n">
+        <v>0.07917</v>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -8857,11 +10438,14 @@
         <v>0.01652</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>0.01652</v>
+        <v>0.01641</v>
       </c>
       <c r="D527" s="1" t="n">
         <v>0.01652</v>
       </c>
+      <c r="E527" s="1" t="n">
+        <v>0.01641</v>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
@@ -8873,11 +10457,14 @@
         <v>0.004198</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>0.004198</v>
+        <v>0.004183</v>
       </c>
       <c r="D528" s="1" t="n">
         <v>0.004198</v>
       </c>
+      <c r="E528" s="1" t="n">
+        <v>0.004183</v>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
@@ -8889,9 +10476,12 @@
         <v>0.003698</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>0.003698</v>
+        <v>0.003713</v>
       </c>
       <c r="D529" s="1" t="n">
+        <v>0.003713</v>
+      </c>
+      <c r="E529" s="1" t="n">
         <v>0.003698</v>
       </c>
     </row>
@@ -8905,11 +10495,14 @@
         <v>1.332</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>1.332</v>
+        <v>1.328</v>
       </c>
       <c r="D530" s="1" t="n">
         <v>1.332</v>
       </c>
+      <c r="E530" s="1" t="n">
+        <v>1.328</v>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -8921,9 +10514,12 @@
         <v>0.4919</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>0.4919</v>
+        <v>0.4922</v>
       </c>
       <c r="D531" s="1" t="n">
+        <v>0.4922</v>
+      </c>
+      <c r="E531" s="1" t="n">
         <v>0.4919</v>
       </c>
     </row>
@@ -8937,9 +10533,12 @@
         <v>0.03058</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>0.03058</v>
+        <v>0.03061</v>
       </c>
       <c r="D532" s="1" t="n">
+        <v>0.03061</v>
+      </c>
+      <c r="E532" s="1" t="n">
         <v>0.03058</v>
       </c>
     </row>
@@ -8953,9 +10552,12 @@
         <v>0.1533</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>0.1533</v>
+        <v>0.1535</v>
       </c>
       <c r="D533" s="1" t="n">
+        <v>0.1535</v>
+      </c>
+      <c r="E533" s="1" t="n">
         <v>0.1533</v>
       </c>
     </row>
@@ -8969,11 +10571,14 @@
         <v>0.05421</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>0.05421</v>
+        <v>0.05404</v>
       </c>
       <c r="D534" s="1" t="n">
         <v>0.05421</v>
       </c>
+      <c r="E534" s="1" t="n">
+        <v>0.05404</v>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -8985,11 +10590,14 @@
         <v>0.01516</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>0.01516</v>
+        <v>0.01507</v>
       </c>
       <c r="D535" s="1" t="n">
         <v>0.01516</v>
       </c>
+      <c r="E535" s="1" t="n">
+        <v>0.01507</v>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -9001,9 +10609,12 @@
         <v>0.0581</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>0.0581</v>
+        <v>0.05833</v>
       </c>
       <c r="D536" s="1" t="n">
+        <v>0.05833</v>
+      </c>
+      <c r="E536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -9017,9 +10628,12 @@
         <v>0.05499</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>0.05499</v>
+        <v>0.05508</v>
       </c>
       <c r="D537" s="1" t="n">
+        <v>0.05508</v>
+      </c>
+      <c r="E537" s="1" t="n">
         <v>0.05499</v>
       </c>
     </row>
@@ -9033,9 +10647,12 @@
         <v>0.1058</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>0.1058</v>
+        <v>0.1065</v>
       </c>
       <c r="D538" s="1" t="n">
+        <v>0.1065</v>
+      </c>
+      <c r="E538" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -9049,11 +10666,14 @@
         <v>0.01296</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>0.01296</v>
+        <v>0.0129</v>
       </c>
       <c r="D539" s="1" t="n">
         <v>0.01296</v>
       </c>
+      <c r="E539" s="1" t="n">
+        <v>0.0129</v>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -9065,11 +10685,14 @@
         <v>0.1753</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>0.1753</v>
+        <v>0.1751</v>
       </c>
       <c r="D540" s="1" t="n">
         <v>0.1753</v>
       </c>
+      <c r="E540" s="1" t="n">
+        <v>0.1751</v>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -9081,9 +10704,12 @@
         <v>0.1231</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>0.1231</v>
+        <v>0.1235</v>
       </c>
       <c r="D541" s="1" t="n">
+        <v>0.1235</v>
+      </c>
+      <c r="E541" s="1" t="n">
         <v>0.1231</v>
       </c>
     </row>
@@ -9097,11 +10723,14 @@
         <v>0.02509</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>0.02509</v>
+        <v>0.02496</v>
       </c>
       <c r="D542" s="1" t="n">
         <v>0.02509</v>
       </c>
+      <c r="E542" s="1" t="n">
+        <v>0.02496</v>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -9113,9 +10742,12 @@
         <v>0.05852</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>0.05852</v>
+        <v>0.05891</v>
       </c>
       <c r="D543" s="1" t="n">
+        <v>0.05891</v>
+      </c>
+      <c r="E543" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,15 +416,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F543"/>
+  <dimension ref="A1:G543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -450,10 +451,15 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>price_00:45</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -475,9 +481,12 @@
         <v>71323.7</v>
       </c>
       <c r="E2" s="1" t="n">
+        <v>71796.5</v>
+      </c>
+      <c r="F2" s="1" t="n">
         <v>71818.39999999999</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="G2" s="1" t="n">
         <v>71323.7</v>
       </c>
     </row>
@@ -497,9 +506,12 @@
         <v>2118.6</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>2127.37</v>
+        <v>2131.78</v>
       </c>
       <c r="F3" s="1" t="n">
+        <v>2131.78</v>
+      </c>
+      <c r="G3" s="1" t="n">
         <v>2118.6</v>
       </c>
     </row>
@@ -519,9 +531,12 @@
         <v>89.23</v>
       </c>
       <c r="E4" s="1" t="n">
+        <v>89.58</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>89.59</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="G4" s="1" t="n">
         <v>89.23</v>
       </c>
     </row>
@@ -541,9 +556,12 @@
         <v>3.857</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>3.861</v>
+        <v>3.887</v>
       </c>
       <c r="F5" s="1" t="n">
+        <v>3.887</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>3.77</v>
       </c>
     </row>
@@ -563,9 +581,12 @@
         <v>1.4035</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>1.4085</v>
+        <v>1.4097</v>
       </c>
       <c r="F6" s="1" t="n">
+        <v>1.4097</v>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>1.4035</v>
       </c>
     </row>
@@ -585,9 +606,12 @@
         <v>0.09765</v>
       </c>
       <c r="E7" s="1" t="n">
+        <v>0.09811</v>
+      </c>
+      <c r="F7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.09765</v>
       </c>
     </row>
@@ -607,9 +631,12 @@
         <v>0.014158</v>
       </c>
       <c r="E8" s="1" t="n">
+        <v>0.014341</v>
+      </c>
+      <c r="F8" s="1" t="n">
         <v>0.014568</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="G8" s="1" t="n">
         <v>0.014158</v>
       </c>
     </row>
@@ -629,9 +656,12 @@
         <v>659.95</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>662.61</v>
+        <v>663.25</v>
       </c>
       <c r="F9" s="1" t="n">
+        <v>663.25</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>659.95</v>
       </c>
     </row>
@@ -651,9 +681,12 @@
         <v>19.149</v>
       </c>
       <c r="E10" s="1" t="n">
+        <v>19.036</v>
+      </c>
+      <c r="F10" s="1" t="n">
         <v>19.415</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="G10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -673,9 +706,12 @@
         <v>0.0034668</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>0.0034782</v>
+        <v>0.0034884</v>
       </c>
       <c r="F11" s="1" t="n">
+        <v>0.0034884</v>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>0.0034668</v>
       </c>
     </row>
@@ -695,9 +731,12 @@
         <v>36.163</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>36.304</v>
+        <v>36.352</v>
       </c>
       <c r="F12" s="1" t="n">
+        <v>36.352</v>
+      </c>
+      <c r="G12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -717,9 +756,12 @@
         <v>213.78</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>213.78</v>
+        <v>214.83</v>
       </c>
       <c r="F13" s="1" t="n">
+        <v>214.83</v>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>213.2</v>
       </c>
     </row>
@@ -739,9 +781,12 @@
         <v>0.0011277</v>
       </c>
       <c r="E14" s="1" t="n">
+        <v>0.0011374</v>
+      </c>
+      <c r="F14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="G14" s="1" t="n">
         <v>0.0011277</v>
       </c>
     </row>
@@ -761,9 +806,12 @@
         <v>0.28871</v>
       </c>
       <c r="E15" s="1" t="n">
+        <v>0.28887</v>
+      </c>
+      <c r="F15" s="1" t="n">
         <v>0.29276</v>
       </c>
-      <c r="F15" s="1" t="n">
+      <c r="G15" s="1" t="n">
         <v>0.28578</v>
       </c>
     </row>
@@ -783,9 +831,12 @@
         <v>233.01</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>234.41</v>
+        <v>236.4</v>
       </c>
       <c r="F16" s="1" t="n">
+        <v>236.4</v>
+      </c>
+      <c r="G16" s="1" t="n">
         <v>230.3</v>
       </c>
     </row>
@@ -805,9 +856,12 @@
         <v>1.012</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>1.0137</v>
+        <v>1.0151</v>
       </c>
       <c r="F17" s="1" t="n">
+        <v>1.0151</v>
+      </c>
+      <c r="G17" s="1" t="n">
         <v>1.012</v>
       </c>
     </row>
@@ -827,9 +881,12 @@
         <v>0.2713</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>0.2717</v>
+        <v>0.2725</v>
       </c>
       <c r="F18" s="1" t="n">
+        <v>0.2725</v>
+      </c>
+      <c r="G18" s="1" t="n">
         <v>0.2713</v>
       </c>
     </row>
@@ -849,9 +906,12 @@
         <v>9.859</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>9.893000000000001</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="F19" s="1" t="n">
+        <v>9.906000000000001</v>
+      </c>
+      <c r="G19" s="1" t="n">
         <v>9.859</v>
       </c>
     </row>
@@ -871,9 +931,12 @@
         <v>5042.6</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>5042.6</v>
+        <v>5044.75</v>
       </c>
       <c r="F20" s="1" t="n">
+        <v>5044.75</v>
+      </c>
+      <c r="G20" s="1" t="n">
         <v>5033.31</v>
       </c>
     </row>
@@ -893,9 +956,12 @@
         <v>462.95</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>463.29</v>
+        <v>464.61</v>
       </c>
       <c r="F21" s="1" t="n">
+        <v>464.61</v>
+      </c>
+      <c r="G21" s="1" t="n">
         <v>462.57</v>
       </c>
     </row>
@@ -915,9 +981,12 @@
         <v>1.4336</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>1.4336</v>
+        <v>1.4544</v>
       </c>
       <c r="F22" s="1" t="n">
+        <v>1.4544</v>
+      </c>
+      <c r="G22" s="1" t="n">
         <v>1.4185</v>
       </c>
     </row>
@@ -937,9 +1006,12 @@
         <v>1.132</v>
       </c>
       <c r="E23" s="1" t="n">
+        <v>1.1304</v>
+      </c>
+      <c r="F23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="F23" s="1" t="n">
+      <c r="G23" s="1" t="n">
         <v>1.1298</v>
       </c>
     </row>
@@ -959,9 +1031,12 @@
         <v>1.354</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>1.36</v>
+        <v>1.363</v>
       </c>
       <c r="F24" s="1" t="n">
+        <v>1.363</v>
+      </c>
+      <c r="G24" s="1" t="n">
         <v>1.351</v>
       </c>
     </row>
@@ -981,9 +1056,12 @@
         <v>9.246</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>9.260999999999999</v>
+        <v>9.297000000000001</v>
       </c>
       <c r="F25" s="1" t="n">
+        <v>9.297000000000001</v>
+      </c>
+      <c r="G25" s="1" t="n">
         <v>9.246</v>
       </c>
     </row>
@@ -1003,9 +1081,12 @@
         <v>0.368</v>
       </c>
       <c r="E26" s="1" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="F26" s="1" t="n">
         <v>0.3749</v>
       </c>
-      <c r="F26" s="1" t="n">
+      <c r="G26" s="1" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -1025,9 +1106,12 @@
         <v>0.889</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>0.889</v>
+        <v>0.897</v>
       </c>
       <c r="F27" s="1" t="n">
+        <v>0.897</v>
+      </c>
+      <c r="G27" s="1" t="n">
         <v>0.887</v>
       </c>
     </row>
@@ -1047,9 +1131,12 @@
         <v>1.787</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>1.803</v>
+        <v>1.816</v>
       </c>
       <c r="F28" s="1" t="n">
+        <v>1.816</v>
+      </c>
+      <c r="G28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -1069,9 +1156,12 @@
         <v>0.1115</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>0.112</v>
+        <v>0.1121</v>
       </c>
       <c r="F29" s="1" t="n">
+        <v>0.1121</v>
+      </c>
+      <c r="G29" s="1" t="n">
         <v>0.1115</v>
       </c>
     </row>
@@ -1091,9 +1181,12 @@
         <v>0.002054</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>0.002059</v>
+        <v>0.002063</v>
       </c>
       <c r="F30" s="1" t="n">
+        <v>0.002063</v>
+      </c>
+      <c r="G30" s="1" t="n">
         <v>0.002054</v>
       </c>
     </row>
@@ -1113,9 +1206,12 @@
         <v>1.499</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>1.506</v>
+        <v>1.511</v>
       </c>
       <c r="F31" s="1" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="G31" s="1" t="n">
         <v>1.499</v>
       </c>
     </row>
@@ -1135,9 +1231,12 @@
         <v>0.177</v>
       </c>
       <c r="E32" s="1" t="n">
+        <v>0.1776</v>
+      </c>
+      <c r="F32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="F32" s="1" t="n">
+      <c r="G32" s="1" t="n">
         <v>0.177</v>
       </c>
     </row>
@@ -1157,9 +1256,12 @@
         <v>0.1045</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>0.1049</v>
+        <v>0.1056</v>
       </c>
       <c r="F33" s="1" t="n">
+        <v>0.1056</v>
+      </c>
+      <c r="G33" s="1" t="n">
         <v>0.1045</v>
       </c>
     </row>
@@ -1179,9 +1281,12 @@
         <v>113.65</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>113.97</v>
+        <v>114.54</v>
       </c>
       <c r="F34" s="1" t="n">
+        <v>114.54</v>
+      </c>
+      <c r="G34" s="1" t="n">
         <v>113.65</v>
       </c>
     </row>
@@ -1201,9 +1306,12 @@
         <v>6.772</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>6.893</v>
+        <v>6.936</v>
       </c>
       <c r="F35" s="1" t="n">
+        <v>6.936</v>
+      </c>
+      <c r="G35" s="1" t="n">
         <v>6.772</v>
       </c>
     </row>
@@ -1223,9 +1331,12 @@
         <v>0.017415</v>
       </c>
       <c r="E36" s="1" t="n">
+        <v>0.017409</v>
+      </c>
+      <c r="F36" s="1" t="n">
         <v>0.017415</v>
       </c>
-      <c r="F36" s="1" t="n">
+      <c r="G36" s="1" t="n">
         <v>0.017313</v>
       </c>
     </row>
@@ -1245,9 +1356,12 @@
         <v>0.3656</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>0.3667</v>
+        <v>0.3687</v>
       </c>
       <c r="F37" s="1" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="G37" s="1" t="n">
         <v>0.3656</v>
       </c>
     </row>
@@ -1267,9 +1381,12 @@
         <v>55.34</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>55.42</v>
+        <v>55.72</v>
       </c>
       <c r="F38" s="1" t="n">
+        <v>55.72</v>
+      </c>
+      <c r="G38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -1289,9 +1406,12 @@
         <v>0.5914700000000001</v>
       </c>
       <c r="E39" s="1" t="n">
+        <v>0.58919</v>
+      </c>
+      <c r="F39" s="1" t="n">
         <v>0.5914700000000001</v>
       </c>
-      <c r="F39" s="1" t="n">
+      <c r="G39" s="1" t="n">
         <v>0.58131</v>
       </c>
     </row>
@@ -1311,9 +1431,12 @@
         <v>4.051</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>4.064</v>
+        <v>4.092</v>
       </c>
       <c r="F40" s="1" t="n">
+        <v>4.092</v>
+      </c>
+      <c r="G40" s="1" t="n">
         <v>4.051</v>
       </c>
     </row>
@@ -1333,9 +1456,12 @@
         <v>0.04957</v>
       </c>
       <c r="E41" s="1" t="n">
+        <v>0.04943</v>
+      </c>
+      <c r="F41" s="1" t="n">
         <v>0.04957</v>
       </c>
-      <c r="F41" s="1" t="n">
+      <c r="G41" s="1" t="n">
         <v>0.04927</v>
       </c>
     </row>
@@ -1355,9 +1481,12 @@
         <v>0.7017</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>0.7056</v>
+        <v>0.7066</v>
       </c>
       <c r="F42" s="1" t="n">
+        <v>0.7066</v>
+      </c>
+      <c r="G42" s="1" t="n">
         <v>0.7017</v>
       </c>
     </row>
@@ -1377,9 +1506,12 @@
         <v>0.23491</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>0.23491</v>
+        <v>0.2383</v>
       </c>
       <c r="F43" s="1" t="n">
+        <v>0.2383</v>
+      </c>
+      <c r="G43" s="1" t="n">
         <v>0.23323</v>
       </c>
     </row>
@@ -1399,9 +1531,12 @@
         <v>0.35261</v>
       </c>
       <c r="E44" s="1" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="F44" s="1" t="n">
         <v>0.35392</v>
       </c>
-      <c r="F44" s="1" t="n">
+      <c r="G44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -1421,9 +1556,12 @@
         <v>0.1715</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>0.1731</v>
+        <v>0.1734</v>
       </c>
       <c r="F45" s="1" t="n">
+        <v>0.1734</v>
+      </c>
+      <c r="G45" s="1" t="n">
         <v>0.1714</v>
       </c>
     </row>
@@ -1443,9 +1581,12 @@
         <v>0.0264</v>
       </c>
       <c r="E46" s="1" t="n">
+        <v>0.0264</v>
+      </c>
+      <c r="F46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="F46" s="1" t="n">
+      <c r="G46" s="1" t="n">
         <v>0.0264</v>
       </c>
     </row>
@@ -1465,9 +1606,12 @@
         <v>0.006032</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>0.00605</v>
+        <v>0.006059</v>
       </c>
       <c r="F47" s="1" t="n">
+        <v>0.006059</v>
+      </c>
+      <c r="G47" s="1" t="n">
         <v>0.006032</v>
       </c>
     </row>
@@ -1487,9 +1631,12 @@
         <v>0.007479</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>0.007515</v>
+        <v>0.007521</v>
       </c>
       <c r="F48" s="1" t="n">
+        <v>0.007521</v>
+      </c>
+      <c r="G48" s="1" t="n">
         <v>0.007479</v>
       </c>
     </row>
@@ -1509,9 +1656,12 @@
         <v>0.1105</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>0.1111</v>
+        <v>0.1115</v>
       </c>
       <c r="F49" s="1" t="n">
+        <v>0.1115</v>
+      </c>
+      <c r="G49" s="1" t="n">
         <v>0.1105</v>
       </c>
     </row>
@@ -1534,6 +1684,9 @@
         <v>0.04046</v>
       </c>
       <c r="F50" s="1" t="n">
+        <v>0.04046</v>
+      </c>
+      <c r="G50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -1553,9 +1706,12 @@
         <v>0.1658</v>
       </c>
       <c r="E51" s="1" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="F51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="F51" s="1" t="n">
+      <c r="G51" s="1" t="n">
         <v>0.1658</v>
       </c>
     </row>
@@ -1575,9 +1731,12 @@
         <v>0.00354</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>0.00355</v>
+        <v>0.00357</v>
       </c>
       <c r="F52" s="1" t="n">
+        <v>0.00357</v>
+      </c>
+      <c r="G52" s="1" t="n">
         <v>0.00354</v>
       </c>
     </row>
@@ -1597,9 +1756,12 @@
         <v>2.645</v>
       </c>
       <c r="E53" s="1" t="n">
+        <v>2.662</v>
+      </c>
+      <c r="F53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="F53" s="1" t="n">
+      <c r="G53" s="1" t="n">
         <v>2.645</v>
       </c>
     </row>
@@ -1619,9 +1781,12 @@
         <v>0.006263</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>0.006298</v>
+        <v>0.006309</v>
       </c>
       <c r="F54" s="1" t="n">
+        <v>0.006309</v>
+      </c>
+      <c r="G54" s="1" t="n">
         <v>0.006263</v>
       </c>
     </row>
@@ -1641,9 +1806,12 @@
         <v>0.02927</v>
       </c>
       <c r="E55" s="1" t="n">
+        <v>0.02943</v>
+      </c>
+      <c r="F55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="F55" s="1" t="n">
+      <c r="G55" s="1" t="n">
         <v>0.02927</v>
       </c>
     </row>
@@ -1663,9 +1831,12 @@
         <v>0.7433999999999999</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>0.7463</v>
+        <v>0.7513</v>
       </c>
       <c r="F56" s="1" t="n">
+        <v>0.7513</v>
+      </c>
+      <c r="G56" s="1" t="n">
         <v>0.7433999999999999</v>
       </c>
     </row>
@@ -1688,6 +1859,9 @@
         <v>0.105</v>
       </c>
       <c r="F57" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="G57" s="1" t="n">
         <v>0.104</v>
       </c>
     </row>
@@ -1707,9 +1881,12 @@
         <v>0.9505</v>
       </c>
       <c r="E58" s="1" t="n">
+        <v>0.9574</v>
+      </c>
+      <c r="F58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="F58" s="1" t="n">
+      <c r="G58" s="1" t="n">
         <v>0.9505</v>
       </c>
     </row>
@@ -1729,9 +1906,12 @@
         <v>0.08542</v>
       </c>
       <c r="E59" s="1" t="n">
+        <v>0.08448</v>
+      </c>
+      <c r="F59" s="1" t="n">
         <v>0.08542</v>
       </c>
-      <c r="F59" s="1" t="n">
+      <c r="G59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -1751,9 +1931,12 @@
         <v>0.06924</v>
       </c>
       <c r="E60" s="1" t="n">
+        <v>0.06976</v>
+      </c>
+      <c r="F60" s="1" t="n">
         <v>0.07001</v>
       </c>
-      <c r="F60" s="1" t="n">
+      <c r="G60" s="1" t="n">
         <v>0.06924</v>
       </c>
     </row>
@@ -1773,9 +1956,12 @@
         <v>0.05479</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>0.05482</v>
+        <v>0.05523</v>
       </c>
       <c r="F61" s="1" t="n">
+        <v>0.05523</v>
+      </c>
+      <c r="G61" s="1" t="n">
         <v>0.05469</v>
       </c>
     </row>
@@ -1795,9 +1981,12 @@
         <v>0.009769</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>0.009769</v>
+        <v>0.010194</v>
       </c>
       <c r="F62" s="1" t="n">
+        <v>0.010194</v>
+      </c>
+      <c r="G62" s="1" t="n">
         <v>0.009535999999999999</v>
       </c>
     </row>
@@ -1817,9 +2006,12 @@
         <v>0.2896</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>0.2896</v>
+        <v>0.28965</v>
       </c>
       <c r="F63" s="1" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="G63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -1839,9 +2031,12 @@
         <v>0.07234</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>0.07234</v>
+        <v>0.07310999999999999</v>
       </c>
       <c r="F64" s="1" t="n">
+        <v>0.07310999999999999</v>
+      </c>
+      <c r="G64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -1861,9 +2056,12 @@
         <v>0.31</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>0.31</v>
+        <v>0.3106</v>
       </c>
       <c r="F65" s="1" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="G65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -1883,9 +2081,12 @@
         <v>0.16337</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>0.1636</v>
+        <v>0.16461</v>
       </c>
       <c r="F66" s="1" t="n">
+        <v>0.16461</v>
+      </c>
+      <c r="G66" s="1" t="n">
         <v>0.16337</v>
       </c>
     </row>
@@ -1905,9 +2106,12 @@
         <v>0.11997</v>
       </c>
       <c r="E67" s="1" t="n">
+        <v>0.11978</v>
+      </c>
+      <c r="F67" s="1" t="n">
         <v>0.11997</v>
       </c>
-      <c r="F67" s="1" t="n">
+      <c r="G67" s="1" t="n">
         <v>0.11934</v>
       </c>
     </row>
@@ -1927,9 +2131,12 @@
         <v>0.09666</v>
       </c>
       <c r="E68" s="1" t="n">
+        <v>0.09730999999999999</v>
+      </c>
+      <c r="F68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="F68" s="1" t="n">
+      <c r="G68" s="1" t="n">
         <v>0.09666</v>
       </c>
     </row>
@@ -1952,6 +2159,9 @@
         <v>0.1259</v>
       </c>
       <c r="F69" s="1" t="n">
+        <v>0.1259</v>
+      </c>
+      <c r="G69" s="1" t="n">
         <v>0.1247</v>
       </c>
     </row>
@@ -1971,9 +2181,12 @@
         <v>8.550000000000001</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>8.582000000000001</v>
+        <v>8.621</v>
       </c>
       <c r="F70" s="1" t="n">
+        <v>8.621</v>
+      </c>
+      <c r="G70" s="1" t="n">
         <v>8.550000000000001</v>
       </c>
     </row>
@@ -1993,9 +2206,12 @@
         <v>0.239</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>0.24</v>
+        <v>0.241</v>
       </c>
       <c r="F71" s="1" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="G71" s="1" t="n">
         <v>0.239</v>
       </c>
     </row>
@@ -2015,10 +2231,13 @@
         <v>0.05164</v>
       </c>
       <c r="E72" s="1" t="n">
+        <v>0.05156</v>
+      </c>
+      <c r="F72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="F72" s="1" t="n">
-        <v>0.05163</v>
+      <c r="G72" s="1" t="n">
+        <v>0.05156</v>
       </c>
     </row>
     <row r="73">
@@ -2037,9 +2256,12 @@
         <v>0.05013</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>0.05059</v>
+        <v>0.05076</v>
       </c>
       <c r="F73" s="1" t="n">
+        <v>0.05076</v>
+      </c>
+      <c r="G73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -2059,9 +2281,12 @@
         <v>0.1257</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>0.1257</v>
+        <v>0.1266</v>
       </c>
       <c r="F74" s="1" t="n">
+        <v>0.1266</v>
+      </c>
+      <c r="G74" s="1" t="n">
         <v>0.1252</v>
       </c>
     </row>
@@ -2081,9 +2306,12 @@
         <v>0.04697</v>
       </c>
       <c r="E75" s="1" t="n">
+        <v>0.04712</v>
+      </c>
+      <c r="F75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="F75" s="1" t="n">
+      <c r="G75" s="1" t="n">
         <v>0.04688</v>
       </c>
     </row>
@@ -2103,9 +2331,12 @@
         <v>0.06743</v>
       </c>
       <c r="E76" s="1" t="n">
+        <v>0.0677</v>
+      </c>
+      <c r="F76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="F76" s="1" t="n">
+      <c r="G76" s="1" t="n">
         <v>0.06743</v>
       </c>
     </row>
@@ -2125,9 +2356,12 @@
         <v>0.12796</v>
       </c>
       <c r="E77" s="1" t="n">
+        <v>0.12772</v>
+      </c>
+      <c r="F77" s="1" t="n">
         <v>0.12881</v>
       </c>
-      <c r="F77" s="1" t="n">
+      <c r="G77" s="1" t="n">
         <v>0.12685</v>
       </c>
     </row>
@@ -2147,9 +2381,12 @@
         <v>0.1624</v>
       </c>
       <c r="E78" s="1" t="n">
+        <v>0.1636</v>
+      </c>
+      <c r="F78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="F78" s="1" t="n">
+      <c r="G78" s="1" t="n">
         <v>0.1624</v>
       </c>
     </row>
@@ -2169,9 +2406,12 @@
         <v>0.02725</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>0.02738</v>
+        <v>0.02753</v>
       </c>
       <c r="F79" s="1" t="n">
+        <v>0.02753</v>
+      </c>
+      <c r="G79" s="1" t="n">
         <v>0.0272</v>
       </c>
     </row>
@@ -2191,9 +2431,12 @@
         <v>354.1</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>354.5</v>
+        <v>356.25</v>
       </c>
       <c r="F80" s="1" t="n">
+        <v>356.25</v>
+      </c>
+      <c r="G80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -2213,9 +2456,12 @@
         <v>7.196e-05</v>
       </c>
       <c r="E81" s="1" t="n">
+        <v>7.248e-05</v>
+      </c>
+      <c r="F81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="F81" s="1" t="n">
+      <c r="G81" s="1" t="n">
         <v>7.196e-05</v>
       </c>
     </row>
@@ -2235,9 +2481,12 @@
         <v>0.2672</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>0.2681</v>
+        <v>0.2687</v>
       </c>
       <c r="F82" s="1" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="G82" s="1" t="n">
         <v>0.2672</v>
       </c>
     </row>
@@ -2257,9 +2506,12 @@
         <v>1.1418</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>1.1447</v>
+        <v>1.1461</v>
       </c>
       <c r="F83" s="1" t="n">
+        <v>1.1461</v>
+      </c>
+      <c r="G83" s="1" t="n">
         <v>1.1408</v>
       </c>
     </row>
@@ -2279,9 +2531,12 @@
         <v>0.3569</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>0.3592</v>
+        <v>0.3622</v>
       </c>
       <c r="F84" s="1" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="G84" s="1" t="n">
         <v>0.3569</v>
       </c>
     </row>
@@ -2301,9 +2556,12 @@
         <v>2.0118</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>2.0181</v>
+        <v>2.0238</v>
       </c>
       <c r="F85" s="1" t="n">
+        <v>2.0238</v>
+      </c>
+      <c r="G85" s="1" t="n">
         <v>2.0067</v>
       </c>
     </row>
@@ -2323,9 +2581,12 @@
         <v>1.3103</v>
       </c>
       <c r="E86" s="1" t="n">
+        <v>1.3145</v>
+      </c>
+      <c r="F86" s="1" t="n">
         <v>1.3167</v>
       </c>
-      <c r="F86" s="1" t="n">
+      <c r="G86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -2345,9 +2606,12 @@
         <v>33.01</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>33.01</v>
+        <v>33.17</v>
       </c>
       <c r="F87" s="1" t="n">
+        <v>33.17</v>
+      </c>
+      <c r="G87" s="1" t="n">
         <v>32.97</v>
       </c>
     </row>
@@ -2367,9 +2631,12 @@
         <v>0.01074</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>0.01074</v>
+        <v>0.01128</v>
       </c>
       <c r="F88" s="1" t="n">
+        <v>0.01128</v>
+      </c>
+      <c r="G88" s="1" t="n">
         <v>0.01046</v>
       </c>
     </row>
@@ -2389,9 +2656,12 @@
         <v>0.01828</v>
       </c>
       <c r="E89" s="1" t="n">
+        <v>0.01829</v>
+      </c>
+      <c r="F89" s="1" t="n">
         <v>0.01835</v>
       </c>
-      <c r="F89" s="1" t="n">
+      <c r="G89" s="1" t="n">
         <v>0.01828</v>
       </c>
     </row>
@@ -2411,9 +2681,12 @@
         <v>0.03586</v>
       </c>
       <c r="E90" s="1" t="n">
+        <v>0.03601</v>
+      </c>
+      <c r="F90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="F90" s="1" t="n">
+      <c r="G90" s="1" t="n">
         <v>0.03571</v>
       </c>
     </row>
@@ -2436,6 +2709,9 @@
         <v>0.01202</v>
       </c>
       <c r="F91" s="1" t="n">
+        <v>0.01202</v>
+      </c>
+      <c r="G91" s="1" t="n">
         <v>0.01192</v>
       </c>
     </row>
@@ -2455,9 +2731,12 @@
         <v>3.111</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>3.12</v>
+        <v>3.136</v>
       </c>
       <c r="F92" s="1" t="n">
+        <v>3.136</v>
+      </c>
+      <c r="G92" s="1" t="n">
         <v>3.111</v>
       </c>
     </row>
@@ -2477,9 +2756,12 @@
         <v>0.005635</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>0.00564</v>
+        <v>0.005656</v>
       </c>
       <c r="F93" s="1" t="n">
+        <v>0.005656</v>
+      </c>
+      <c r="G93" s="1" t="n">
         <v>0.005635</v>
       </c>
     </row>
@@ -2499,9 +2781,12 @@
         <v>0.094</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>0.0945</v>
+        <v>0.0946</v>
       </c>
       <c r="F94" s="1" t="n">
+        <v>0.0946</v>
+      </c>
+      <c r="G94" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -2521,9 +2806,12 @@
         <v>0.6025</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>0.6028</v>
+        <v>0.6058</v>
       </c>
       <c r="F95" s="1" t="n">
+        <v>0.6058</v>
+      </c>
+      <c r="G95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -2543,9 +2831,12 @@
         <v>1.28e-05</v>
       </c>
       <c r="E96" s="1" t="n">
+        <v>1.29e-05</v>
+      </c>
+      <c r="F96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="F96" s="1" t="n">
+      <c r="G96" s="1" t="n">
         <v>1.28e-05</v>
       </c>
     </row>
@@ -2565,9 +2856,12 @@
         <v>1.138</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>1.143</v>
+        <v>1.15</v>
       </c>
       <c r="F97" s="1" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G97" s="1" t="n">
         <v>1.136</v>
       </c>
     </row>
@@ -2587,10 +2881,13 @@
         <v>0.25703</v>
       </c>
       <c r="E98" s="1" t="n">
+        <v>0.25616</v>
+      </c>
+      <c r="F98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="F98" s="1" t="n">
-        <v>0.25703</v>
+      <c r="G98" s="1" t="n">
+        <v>0.25616</v>
       </c>
     </row>
     <row r="99">
@@ -2609,9 +2906,12 @@
         <v>1.146</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>1.151</v>
+        <v>1.155</v>
       </c>
       <c r="F99" s="1" t="n">
+        <v>1.155</v>
+      </c>
+      <c r="G99" s="1" t="n">
         <v>1.146</v>
       </c>
     </row>
@@ -2631,9 +2931,12 @@
         <v>1.862</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>1.866</v>
+        <v>1.873</v>
       </c>
       <c r="F100" s="1" t="n">
+        <v>1.873</v>
+      </c>
+      <c r="G100" s="1" t="n">
         <v>1.862</v>
       </c>
     </row>
@@ -2656,6 +2959,9 @@
         <v>0.01599</v>
       </c>
       <c r="F101" s="1" t="n">
+        <v>0.01599</v>
+      </c>
+      <c r="G101" s="1" t="n">
         <v>0.01597</v>
       </c>
     </row>
@@ -2675,9 +2981,12 @@
         <v>0.10353</v>
       </c>
       <c r="E102" s="1" t="n">
+        <v>0.10381</v>
+      </c>
+      <c r="F102" s="1" t="n">
         <v>0.10417</v>
       </c>
-      <c r="F102" s="1" t="n">
+      <c r="G102" s="1" t="n">
         <v>0.10353</v>
       </c>
     </row>
@@ -2697,9 +3006,12 @@
         <v>0.000605</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>0.0006065000000000001</v>
+        <v>0.0006089</v>
       </c>
       <c r="F103" s="1" t="n">
+        <v>0.0006089</v>
+      </c>
+      <c r="G103" s="1" t="n">
         <v>0.000605</v>
       </c>
     </row>
@@ -2719,9 +3031,12 @@
         <v>0.00056</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>0.00056</v>
+        <v>0.0005731999999999999</v>
       </c>
       <c r="F104" s="1" t="n">
+        <v>0.0005731999999999999</v>
+      </c>
+      <c r="G104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -2741,10 +3056,13 @@
         <v>0.003244</v>
       </c>
       <c r="E105" s="1" t="n">
+        <v>0.003241</v>
+      </c>
+      <c r="F105" s="1" t="n">
         <v>0.003257</v>
       </c>
-      <c r="F105" s="1" t="n">
-        <v>0.003244</v>
+      <c r="G105" s="1" t="n">
+        <v>0.003241</v>
       </c>
     </row>
     <row r="106">
@@ -2763,9 +3081,12 @@
         <v>2.617</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>2.638</v>
+        <v>2.647</v>
       </c>
       <c r="F106" s="1" t="n">
+        <v>2.647</v>
+      </c>
+      <c r="G106" s="1" t="n">
         <v>2.617</v>
       </c>
     </row>
@@ -2785,9 +3106,12 @@
         <v>0.167</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>0.1674</v>
+        <v>0.1681</v>
       </c>
       <c r="F107" s="1" t="n">
+        <v>0.1681</v>
+      </c>
+      <c r="G107" s="1" t="n">
         <v>0.167</v>
       </c>
     </row>
@@ -2807,9 +3131,12 @@
         <v>0.09744</v>
       </c>
       <c r="E108" s="1" t="n">
+        <v>0.09787</v>
+      </c>
+      <c r="F108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="F108" s="1" t="n">
+      <c r="G108" s="1" t="n">
         <v>0.09742000000000001</v>
       </c>
     </row>
@@ -2829,9 +3156,12 @@
         <v>0.02229</v>
       </c>
       <c r="E109" s="1" t="n">
+        <v>0.02237</v>
+      </c>
+      <c r="F109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="F109" s="1" t="n">
+      <c r="G109" s="1" t="n">
         <v>0.02229</v>
       </c>
     </row>
@@ -2851,9 +3181,12 @@
         <v>0.2937</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>0.2937</v>
+        <v>0.2948</v>
       </c>
       <c r="F110" s="1" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="G110" s="1" t="n">
         <v>0.2913</v>
       </c>
     </row>
@@ -2873,9 +3206,12 @@
         <v>0.05688</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>0.05697</v>
+        <v>0.05721</v>
       </c>
       <c r="F111" s="1" t="n">
+        <v>0.05721</v>
+      </c>
+      <c r="G111" s="1" t="n">
         <v>0.05684</v>
       </c>
     </row>
@@ -2895,9 +3231,12 @@
         <v>0.3039</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>0.3057</v>
+        <v>0.3064</v>
       </c>
       <c r="F112" s="1" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="G112" s="1" t="n">
         <v>0.3039</v>
       </c>
     </row>
@@ -2917,9 +3256,12 @@
         <v>18.62</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>18.67</v>
+        <v>18.73</v>
       </c>
       <c r="F113" s="1" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="G113" s="1" t="n">
         <v>18.62</v>
       </c>
     </row>
@@ -2939,9 +3281,12 @@
         <v>0.13373</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>0.13373</v>
+        <v>0.13604</v>
       </c>
       <c r="F114" s="1" t="n">
+        <v>0.13604</v>
+      </c>
+      <c r="G114" s="1" t="n">
         <v>0.13225</v>
       </c>
     </row>
@@ -2961,9 +3306,12 @@
         <v>0.01554</v>
       </c>
       <c r="E115" s="1" t="n">
+        <v>0.01575</v>
+      </c>
+      <c r="F115" s="1" t="n">
         <v>0.01583</v>
       </c>
-      <c r="F115" s="1" t="n">
+      <c r="G115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -2983,9 +3331,12 @@
         <v>0.08527</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>0.08558</v>
+        <v>0.08609</v>
       </c>
       <c r="F116" s="1" t="n">
+        <v>0.08609</v>
+      </c>
+      <c r="G116" s="1" t="n">
         <v>0.08527</v>
       </c>
     </row>
@@ -3005,10 +3356,13 @@
         <v>0.049196</v>
       </c>
       <c r="E117" s="1" t="n">
+        <v>0.04873</v>
+      </c>
+      <c r="F117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="F117" s="1" t="n">
-        <v>0.049196</v>
+      <c r="G117" s="1" t="n">
+        <v>0.04873</v>
       </c>
     </row>
     <row r="118">
@@ -3027,9 +3381,12 @@
         <v>0.04807</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>0.04844</v>
+        <v>0.04849</v>
       </c>
       <c r="F118" s="1" t="n">
+        <v>0.04849</v>
+      </c>
+      <c r="G118" s="1" t="n">
         <v>0.04807</v>
       </c>
     </row>
@@ -3049,9 +3406,12 @@
         <v>0.04167</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>0.04167</v>
+        <v>0.04271</v>
       </c>
       <c r="F119" s="1" t="n">
+        <v>0.04271</v>
+      </c>
+      <c r="G119" s="1" t="n">
         <v>0.04109</v>
       </c>
     </row>
@@ -3071,9 +3431,12 @@
         <v>0.14662</v>
       </c>
       <c r="E120" s="1" t="n">
+        <v>0.14629</v>
+      </c>
+      <c r="F120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="F120" s="1" t="n">
+      <c r="G120" s="1" t="n">
         <v>0.14499</v>
       </c>
     </row>
@@ -3093,9 +3456,12 @@
         <v>0.1276</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>0.1279</v>
+        <v>0.1284</v>
       </c>
       <c r="F121" s="1" t="n">
+        <v>0.1284</v>
+      </c>
+      <c r="G121" s="1" t="n">
         <v>0.1272</v>
       </c>
     </row>
@@ -3115,9 +3481,12 @@
         <v>1.887</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>1.893</v>
+        <v>1.903</v>
       </c>
       <c r="F122" s="1" t="n">
+        <v>1.903</v>
+      </c>
+      <c r="G122" s="1" t="n">
         <v>1.887</v>
       </c>
     </row>
@@ -3137,9 +3506,12 @@
         <v>0.03041</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>0.03049</v>
+        <v>0.03064</v>
       </c>
       <c r="F123" s="1" t="n">
+        <v>0.03064</v>
+      </c>
+      <c r="G123" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -3159,9 +3531,12 @@
         <v>0.13346</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>0.13346</v>
+        <v>0.13401</v>
       </c>
       <c r="F124" s="1" t="n">
+        <v>0.13401</v>
+      </c>
+      <c r="G124" s="1" t="n">
         <v>0.13288</v>
       </c>
     </row>
@@ -3181,9 +3556,12 @@
         <v>0.04139</v>
       </c>
       <c r="E125" s="1" t="n">
+        <v>0.04143</v>
+      </c>
+      <c r="F125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="F125" s="1" t="n">
+      <c r="G125" s="1" t="n">
         <v>0.04139</v>
       </c>
     </row>
@@ -3203,9 +3581,12 @@
         <v>0.1156</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>0.1165</v>
+        <v>0.1166</v>
       </c>
       <c r="F126" s="1" t="n">
+        <v>0.1166</v>
+      </c>
+      <c r="G126" s="1" t="n">
         <v>0.1154</v>
       </c>
     </row>
@@ -3225,9 +3606,12 @@
         <v>0.4979</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>0.4979</v>
+        <v>0.5013</v>
       </c>
       <c r="F127" s="1" t="n">
+        <v>0.5013</v>
+      </c>
+      <c r="G127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -3247,9 +3631,12 @@
         <v>0.03787</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>0.03797</v>
+        <v>0.03838</v>
       </c>
       <c r="F128" s="1" t="n">
+        <v>0.03838</v>
+      </c>
+      <c r="G128" s="1" t="n">
         <v>0.03787</v>
       </c>
     </row>
@@ -3269,9 +3656,12 @@
         <v>0.796</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>0.797</v>
+        <v>0.798</v>
       </c>
       <c r="F129" s="1" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="G129" s="1" t="n">
         <v>0.796</v>
       </c>
     </row>
@@ -3291,9 +3681,12 @@
         <v>0.03452</v>
       </c>
       <c r="E130" s="1" t="n">
+        <v>0.03441</v>
+      </c>
+      <c r="F130" s="1" t="n">
         <v>0.03458</v>
       </c>
-      <c r="F130" s="1" t="n">
+      <c r="G130" s="1" t="n">
         <v>0.03439</v>
       </c>
     </row>
@@ -3313,9 +3706,12 @@
         <v>0.4279</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>0.4279</v>
+        <v>0.4316</v>
       </c>
       <c r="F131" s="1" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="G131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -3335,10 +3731,13 @@
         <v>0.04375</v>
       </c>
       <c r="E132" s="1" t="n">
+        <v>0.04361</v>
+      </c>
+      <c r="F132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="F132" s="1" t="n">
-        <v>0.04375</v>
+      <c r="G132" s="1" t="n">
+        <v>0.04361</v>
       </c>
     </row>
     <row r="133">
@@ -3357,9 +3756,12 @@
         <v>1.2958</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>1.2958</v>
+        <v>1.3057</v>
       </c>
       <c r="F133" s="1" t="n">
+        <v>1.3057</v>
+      </c>
+      <c r="G133" s="1" t="n">
         <v>1.2941</v>
       </c>
     </row>
@@ -3379,9 +3781,12 @@
         <v>0.0222</v>
       </c>
       <c r="E134" s="1" t="n">
+        <v>0.02214</v>
+      </c>
+      <c r="F134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="F134" s="1" t="n">
+      <c r="G134" s="1" t="n">
         <v>0.02208</v>
       </c>
     </row>
@@ -3401,9 +3806,12 @@
         <v>0.0004706</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>0.0004716</v>
+        <v>0.0004731</v>
       </c>
       <c r="F135" s="1" t="n">
+        <v>0.0004731</v>
+      </c>
+      <c r="G135" s="1" t="n">
         <v>0.0004699</v>
       </c>
     </row>
@@ -3423,9 +3831,12 @@
         <v>0.00195</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>0.00195</v>
+        <v>0.001966</v>
       </c>
       <c r="F136" s="1" t="n">
+        <v>0.001966</v>
+      </c>
+      <c r="G136" s="1" t="n">
         <v>0.001913</v>
       </c>
     </row>
@@ -3445,9 +3856,12 @@
         <v>0.3204</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>0.3227</v>
+        <v>0.3239</v>
       </c>
       <c r="F137" s="1" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="G137" s="1" t="n">
         <v>0.3204</v>
       </c>
     </row>
@@ -3467,9 +3881,12 @@
         <v>0.5713</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>0.5717</v>
+        <v>0.5759</v>
       </c>
       <c r="F138" s="1" t="n">
+        <v>0.5759</v>
+      </c>
+      <c r="G138" s="1" t="n">
         <v>0.5705</v>
       </c>
     </row>
@@ -3489,9 +3906,12 @@
         <v>0.0215</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>0.0215</v>
+        <v>0.02161</v>
       </c>
       <c r="F139" s="1" t="n">
+        <v>0.02161</v>
+      </c>
+      <c r="G139" s="1" t="n">
         <v>0.02145</v>
       </c>
     </row>
@@ -3511,9 +3931,12 @@
         <v>0.08082</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>0.08092000000000001</v>
+        <v>0.08103</v>
       </c>
       <c r="F140" s="1" t="n">
+        <v>0.08103</v>
+      </c>
+      <c r="G140" s="1" t="n">
         <v>0.08081000000000001</v>
       </c>
     </row>
@@ -3533,9 +3956,12 @@
         <v>0.001632</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>0.001632</v>
+        <v>0.001642</v>
       </c>
       <c r="F141" s="1" t="n">
+        <v>0.001642</v>
+      </c>
+      <c r="G141" s="1" t="n">
         <v>0.001616</v>
       </c>
     </row>
@@ -3555,9 +3981,12 @@
         <v>0.4269</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>0.4269</v>
+        <v>0.4274</v>
       </c>
       <c r="F142" s="1" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="G142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -3577,9 +4006,12 @@
         <v>0.030681</v>
       </c>
       <c r="E143" s="1" t="n">
+        <v>0.030559</v>
+      </c>
+      <c r="F143" s="1" t="n">
         <v>0.030681</v>
       </c>
-      <c r="F143" s="1" t="n">
+      <c r="G143" s="1" t="n">
         <v>0.030377</v>
       </c>
     </row>
@@ -3599,9 +4031,12 @@
         <v>0.000223</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>0.000225</v>
+        <v>0.000226</v>
       </c>
       <c r="F144" s="1" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="G144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -3621,9 +4056,12 @@
         <v>0.0319</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>0.03197</v>
+        <v>0.03225</v>
       </c>
       <c r="F145" s="1" t="n">
+        <v>0.03225</v>
+      </c>
+      <c r="G145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -3643,9 +4081,12 @@
         <v>0.11596</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>0.11596</v>
+        <v>0.116</v>
       </c>
       <c r="F146" s="1" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="G146" s="1" t="n">
         <v>0.11518</v>
       </c>
     </row>
@@ -3665,9 +4106,12 @@
         <v>0.02181</v>
       </c>
       <c r="E147" s="1" t="n">
+        <v>0.02181</v>
+      </c>
+      <c r="F147" s="1" t="n">
         <v>0.02185</v>
       </c>
-      <c r="F147" s="1" t="n">
+      <c r="G147" s="1" t="n">
         <v>0.02171</v>
       </c>
     </row>
@@ -3687,9 +4131,12 @@
         <v>1.4154</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>1.4234</v>
+        <v>1.4256</v>
       </c>
       <c r="F148" s="1" t="n">
+        <v>1.4256</v>
+      </c>
+      <c r="G148" s="1" t="n">
         <v>1.4154</v>
       </c>
     </row>
@@ -3709,9 +4156,12 @@
         <v>1.865</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>1.8715</v>
+        <v>1.8771</v>
       </c>
       <c r="F149" s="1" t="n">
+        <v>1.8771</v>
+      </c>
+      <c r="G149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -3731,9 +4181,12 @@
         <v>0.1</v>
       </c>
       <c r="E150" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="F150" s="1" t="n">
+      <c r="G150" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3753,9 +4206,12 @@
         <v>4.553</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>4.553</v>
+        <v>4.609</v>
       </c>
       <c r="F151" s="1" t="n">
+        <v>4.609</v>
+      </c>
+      <c r="G151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -3775,9 +4231,12 @@
         <v>5.552</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>5.561</v>
+        <v>5.593</v>
       </c>
       <c r="F152" s="1" t="n">
+        <v>5.593</v>
+      </c>
+      <c r="G152" s="1" t="n">
         <v>5.55</v>
       </c>
     </row>
@@ -3797,9 +4256,12 @@
         <v>0.3201</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>0.3205</v>
+        <v>0.3263</v>
       </c>
       <c r="F153" s="1" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="G153" s="1" t="n">
         <v>0.3178</v>
       </c>
     </row>
@@ -3819,9 +4281,12 @@
         <v>0.5891999999999999</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="F154" s="1" t="n">
+        <v>0.5921999999999999</v>
+      </c>
+      <c r="G154" s="1" t="n">
         <v>0.5891999999999999</v>
       </c>
     </row>
@@ -3841,9 +4306,12 @@
         <v>0.01269</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>0.01269</v>
+        <v>0.01278</v>
       </c>
       <c r="F155" s="1" t="n">
+        <v>0.01278</v>
+      </c>
+      <c r="G155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -3863,9 +4331,12 @@
         <v>0.0997</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>0.1002</v>
+        <v>0.1005</v>
       </c>
       <c r="F156" s="1" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="G156" s="1" t="n">
         <v>0.0997</v>
       </c>
     </row>
@@ -3885,9 +4356,12 @@
         <v>16.563</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>16.596</v>
+        <v>16.755</v>
       </c>
       <c r="F157" s="1" t="n">
+        <v>16.755</v>
+      </c>
+      <c r="G157" s="1" t="n">
         <v>16.563</v>
       </c>
     </row>
@@ -3907,9 +4381,12 @@
         <v>0.05539</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>0.05548</v>
+        <v>0.05593</v>
       </c>
       <c r="F158" s="1" t="n">
+        <v>0.05593</v>
+      </c>
+      <c r="G158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -3929,9 +4406,12 @@
         <v>28.87</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>29.04</v>
+        <v>29.14</v>
       </c>
       <c r="F159" s="1" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="G159" s="1" t="n">
         <v>28.87</v>
       </c>
     </row>
@@ -3951,9 +4431,12 @@
         <v>0.02121</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>0.02132</v>
+        <v>0.02141</v>
       </c>
       <c r="F160" s="1" t="n">
+        <v>0.02141</v>
+      </c>
+      <c r="G160" s="1" t="n">
         <v>0.02121</v>
       </c>
     </row>
@@ -3973,9 +4456,12 @@
         <v>0.0006601000000000001</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>0.0006619</v>
+        <v>0.0006655</v>
       </c>
       <c r="F161" s="1" t="n">
+        <v>0.0006655</v>
+      </c>
+      <c r="G161" s="1" t="n">
         <v>0.0006601000000000001</v>
       </c>
     </row>
@@ -3995,9 +4481,12 @@
         <v>0.4016</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>0.4016</v>
+        <v>0.4053</v>
       </c>
       <c r="F162" s="1" t="n">
+        <v>0.4053</v>
+      </c>
+      <c r="G162" s="1" t="n">
         <v>0.3936</v>
       </c>
     </row>
@@ -4017,9 +4506,12 @@
         <v>0.1931</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>0.1939</v>
+        <v>0.1952</v>
       </c>
       <c r="F163" s="1" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="G163" s="1" t="n">
         <v>0.1931</v>
       </c>
     </row>
@@ -4042,6 +4534,9 @@
         <v>0.321</v>
       </c>
       <c r="F164" s="1" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="G164" s="1" t="n">
         <v>0.32</v>
       </c>
     </row>
@@ -4064,6 +4559,9 @@
         <v>0.377</v>
       </c>
       <c r="F165" s="1" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="G165" s="1" t="n">
         <v>0.375</v>
       </c>
     </row>
@@ -4083,9 +4581,12 @@
         <v>0.02271</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>0.02276</v>
+        <v>0.02286</v>
       </c>
       <c r="F166" s="1" t="n">
+        <v>0.02286</v>
+      </c>
+      <c r="G166" s="1" t="n">
         <v>0.02271</v>
       </c>
     </row>
@@ -4105,9 +4606,12 @@
         <v>0.007348</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>0.007385</v>
+        <v>0.0074</v>
       </c>
       <c r="F167" s="1" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="G167" s="1" t="n">
         <v>0.007348</v>
       </c>
     </row>
@@ -4127,10 +4631,13 @@
         <v>0.01395</v>
       </c>
       <c r="E168" s="1" t="n">
+        <v>0.01394</v>
+      </c>
+      <c r="F168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="F168" s="1" t="n">
-        <v>0.01395</v>
+      <c r="G168" s="1" t="n">
+        <v>0.01394</v>
       </c>
     </row>
     <row r="169">
@@ -4149,9 +4656,12 @@
         <v>0.25376</v>
       </c>
       <c r="E169" s="1" t="n">
+        <v>0.25629</v>
+      </c>
+      <c r="F169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="F169" s="1" t="n">
+      <c r="G169" s="1" t="n">
         <v>0.25376</v>
       </c>
     </row>
@@ -4171,9 +4681,12 @@
         <v>0.0215</v>
       </c>
       <c r="E170" s="1" t="n">
+        <v>0.02158</v>
+      </c>
+      <c r="F170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="F170" s="1" t="n">
+      <c r="G170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -4193,9 +4706,12 @@
         <v>0.1748</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>0.1748</v>
+        <v>0.1756</v>
       </c>
       <c r="F171" s="1" t="n">
+        <v>0.1756</v>
+      </c>
+      <c r="G171" s="1" t="n">
         <v>0.1733</v>
       </c>
     </row>
@@ -4218,6 +4734,9 @@
         <v>0.09</v>
       </c>
       <c r="F172" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -4237,9 +4756,12 @@
         <v>0.004719</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>0.004729</v>
+        <v>0.004732</v>
       </c>
       <c r="F173" s="1" t="n">
+        <v>0.004732</v>
+      </c>
+      <c r="G173" s="1" t="n">
         <v>0.004719</v>
       </c>
     </row>
@@ -4259,9 +4781,12 @@
         <v>0.4368</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>0.4382</v>
+        <v>0.4401</v>
       </c>
       <c r="F174" s="1" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="G174" s="1" t="n">
         <v>0.4368</v>
       </c>
     </row>
@@ -4281,9 +4806,12 @@
         <v>0.0895</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>0.09001000000000001</v>
+        <v>0.09011</v>
       </c>
       <c r="F175" s="1" t="n">
+        <v>0.09011</v>
+      </c>
+      <c r="G175" s="1" t="n">
         <v>0.0895</v>
       </c>
     </row>
@@ -4303,9 +4831,12 @@
         <v>0.2454</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>0.2475</v>
+        <v>0.2476</v>
       </c>
       <c r="F176" s="1" t="n">
+        <v>0.2476</v>
+      </c>
+      <c r="G176" s="1" t="n">
         <v>0.2453</v>
       </c>
     </row>
@@ -4325,9 +4856,12 @@
         <v>0.01917</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>0.01925</v>
+        <v>0.01935</v>
       </c>
       <c r="F177" s="1" t="n">
+        <v>0.01935</v>
+      </c>
+      <c r="G177" s="1" t="n">
         <v>0.01917</v>
       </c>
     </row>
@@ -4347,9 +4881,12 @@
         <v>6.18</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>6.196</v>
+        <v>6.24</v>
       </c>
       <c r="F178" s="1" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="G178" s="1" t="n">
         <v>6.18</v>
       </c>
     </row>
@@ -4369,9 +4906,12 @@
         <v>0.1364</v>
       </c>
       <c r="E179" s="1" t="n">
+        <v>0.1369</v>
+      </c>
+      <c r="F179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="F179" s="1" t="n">
+      <c r="G179" s="1" t="n">
         <v>0.1364</v>
       </c>
     </row>
@@ -4391,9 +4931,12 @@
         <v>0.004943</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>0.004943</v>
+        <v>0.005052</v>
       </c>
       <c r="F180" s="1" t="n">
+        <v>0.005052</v>
+      </c>
+      <c r="G180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -4413,9 +4956,12 @@
         <v>0.01189</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>0.01191</v>
+        <v>0.01203</v>
       </c>
       <c r="F181" s="1" t="n">
+        <v>0.01203</v>
+      </c>
+      <c r="G181" s="1" t="n">
         <v>0.01189</v>
       </c>
     </row>
@@ -4435,9 +4981,12 @@
         <v>0.007538</v>
       </c>
       <c r="E182" s="1" t="n">
+        <v>0.007442</v>
+      </c>
+      <c r="F182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="F182" s="1" t="n">
+      <c r="G182" s="1" t="n">
         <v>0.007295</v>
       </c>
     </row>
@@ -4457,10 +5006,13 @@
         <v>0.13155</v>
       </c>
       <c r="E183" s="1" t="n">
+        <v>0.12964</v>
+      </c>
+      <c r="F183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="F183" s="1" t="n">
-        <v>0.13155</v>
+      <c r="G183" s="1" t="n">
+        <v>0.12964</v>
       </c>
     </row>
     <row r="184">
@@ -4479,9 +5031,12 @@
         <v>0.09635000000000001</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>0.09635000000000001</v>
+        <v>0.09673</v>
       </c>
       <c r="F184" s="1" t="n">
+        <v>0.09673</v>
+      </c>
+      <c r="G184" s="1" t="n">
         <v>0.09587</v>
       </c>
     </row>
@@ -4501,9 +5056,12 @@
         <v>0.00759</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>0.00761</v>
+        <v>0.00763</v>
       </c>
       <c r="F185" s="1" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="G185" s="1" t="n">
         <v>0.00758</v>
       </c>
     </row>
@@ -4523,9 +5081,12 @@
         <v>0.04915</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>0.04933</v>
+        <v>0.04951</v>
       </c>
       <c r="F186" s="1" t="n">
+        <v>0.04951</v>
+      </c>
+      <c r="G186" s="1" t="n">
         <v>0.04914</v>
       </c>
     </row>
@@ -4545,9 +5106,12 @@
         <v>0.02699</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>0.02699</v>
+        <v>0.0272</v>
       </c>
       <c r="F187" s="1" t="n">
+        <v>0.0272</v>
+      </c>
+      <c r="G187" s="1" t="n">
         <v>0.02686</v>
       </c>
     </row>
@@ -4567,9 +5131,12 @@
         <v>0.003323</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>0.00334</v>
+        <v>0.00335</v>
       </c>
       <c r="F188" s="1" t="n">
+        <v>0.00335</v>
+      </c>
+      <c r="G188" s="1" t="n">
         <v>0.003323</v>
       </c>
     </row>
@@ -4589,9 +5156,12 @@
         <v>0.2885</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>0.2888</v>
+        <v>0.29</v>
       </c>
       <c r="F189" s="1" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G189" s="1" t="n">
         <v>0.2875</v>
       </c>
     </row>
@@ -4611,9 +5181,12 @@
         <v>0.01819</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>0.01822</v>
+        <v>0.01837</v>
       </c>
       <c r="F190" s="1" t="n">
+        <v>0.01837</v>
+      </c>
+      <c r="G190" s="1" t="n">
         <v>0.01819</v>
       </c>
     </row>
@@ -4633,9 +5206,12 @@
         <v>0.2606</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>0.2617</v>
+        <v>0.262</v>
       </c>
       <c r="F191" s="1" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="G191" s="1" t="n">
         <v>0.2606</v>
       </c>
     </row>
@@ -4655,9 +5231,12 @@
         <v>0.03914</v>
       </c>
       <c r="E192" s="1" t="n">
+        <v>0.03962</v>
+      </c>
+      <c r="F192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="F192" s="1" t="n">
+      <c r="G192" s="1" t="n">
         <v>0.03914</v>
       </c>
     </row>
@@ -4677,9 +5256,12 @@
         <v>0.0002208</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>0.000221</v>
+        <v>0.0002228</v>
       </c>
       <c r="F193" s="1" t="n">
+        <v>0.0002228</v>
+      </c>
+      <c r="G193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -4699,9 +5281,12 @@
         <v>4.154</v>
       </c>
       <c r="E194" s="1" t="n">
+        <v>4.173</v>
+      </c>
+      <c r="F194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="F194" s="1" t="n">
+      <c r="G194" s="1" t="n">
         <v>4.154</v>
       </c>
     </row>
@@ -4724,6 +5309,9 @@
         <v>0.999341</v>
       </c>
       <c r="F195" s="1" t="n">
+        <v>0.999341</v>
+      </c>
+      <c r="G195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -4743,9 +5331,12 @@
         <v>4.304</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>4.316</v>
+        <v>4.347</v>
       </c>
       <c r="F196" s="1" t="n">
+        <v>4.347</v>
+      </c>
+      <c r="G196" s="1" t="n">
         <v>4.302</v>
       </c>
     </row>
@@ -4765,9 +5356,12 @@
         <v>0.14981</v>
       </c>
       <c r="E197" s="1" t="n">
+        <v>0.15011</v>
+      </c>
+      <c r="F197" s="1" t="n">
         <v>0.15012</v>
       </c>
-      <c r="F197" s="1" t="n">
+      <c r="G197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -4787,9 +5381,12 @@
         <v>0.007485</v>
       </c>
       <c r="E198" s="1" t="n">
+        <v>0.007508</v>
+      </c>
+      <c r="F198" s="1" t="n">
         <v>0.007586</v>
       </c>
-      <c r="F198" s="1" t="n">
+      <c r="G198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -4809,9 +5406,12 @@
         <v>0.4483</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>0.4503</v>
+        <v>0.4524</v>
       </c>
       <c r="F199" s="1" t="n">
+        <v>0.4524</v>
+      </c>
+      <c r="G199" s="1" t="n">
         <v>0.4483</v>
       </c>
     </row>
@@ -4834,6 +5434,9 @@
         <v>0.5777</v>
       </c>
       <c r="F200" s="1" t="n">
+        <v>0.5777</v>
+      </c>
+      <c r="G200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -4856,6 +5459,9 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="F201" s="1" t="n">
+        <v>0.09429999999999999</v>
+      </c>
+      <c r="G201" s="1" t="n">
         <v>0.09379999999999999</v>
       </c>
     </row>
@@ -4875,9 +5481,12 @@
         <v>0.06069</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>0.06069</v>
+        <v>0.06118</v>
       </c>
       <c r="F202" s="1" t="n">
+        <v>0.06118</v>
+      </c>
+      <c r="G202" s="1" t="n">
         <v>0.06063</v>
       </c>
     </row>
@@ -4897,9 +5506,12 @@
         <v>0.00851</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>0.00851</v>
+        <v>0.008580000000000001</v>
       </c>
       <c r="F203" s="1" t="n">
+        <v>0.008580000000000001</v>
+      </c>
+      <c r="G203" s="1" t="n">
         <v>0.008359999999999999</v>
       </c>
     </row>
@@ -4919,9 +5531,12 @@
         <v>0.00421</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>0.00422</v>
+        <v>0.00423</v>
       </c>
       <c r="F204" s="1" t="n">
+        <v>0.00423</v>
+      </c>
+      <c r="G204" s="1" t="n">
         <v>0.00421</v>
       </c>
     </row>
@@ -4941,10 +5556,13 @@
         <v>0.009283</v>
       </c>
       <c r="E205" s="1" t="n">
+        <v>0.009176999999999999</v>
+      </c>
+      <c r="F205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="F205" s="1" t="n">
-        <v>0.009239000000000001</v>
+      <c r="G205" s="1" t="n">
+        <v>0.009176999999999999</v>
       </c>
     </row>
     <row r="206">
@@ -4963,9 +5581,12 @@
         <v>0.2366</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>0.2366</v>
+        <v>0.2399</v>
       </c>
       <c r="F206" s="1" t="n">
+        <v>0.2399</v>
+      </c>
+      <c r="G206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -4985,9 +5606,12 @@
         <v>0.0215</v>
       </c>
       <c r="E207" s="1" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="F207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="F207" s="1" t="n">
+      <c r="G207" s="1" t="n">
         <v>0.02128</v>
       </c>
     </row>
@@ -5007,9 +5631,12 @@
         <v>0.2366</v>
       </c>
       <c r="E208" s="1" t="n">
+        <v>0.2386</v>
+      </c>
+      <c r="F208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="F208" s="1" t="n">
+      <c r="G208" s="1" t="n">
         <v>0.2366</v>
       </c>
     </row>
@@ -5029,9 +5656,12 @@
         <v>0.3624</v>
       </c>
       <c r="E209" s="1" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="F209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="F209" s="1" t="n">
+      <c r="G209" s="1" t="n">
         <v>0.3616</v>
       </c>
     </row>
@@ -5051,9 +5681,12 @@
         <v>0.04286</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>0.04311</v>
+        <v>0.04318</v>
       </c>
       <c r="F210" s="1" t="n">
+        <v>0.04318</v>
+      </c>
+      <c r="G210" s="1" t="n">
         <v>0.04286</v>
       </c>
     </row>
@@ -5073,9 +5706,12 @@
         <v>0.0004282</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>0.0004307</v>
+        <v>0.0004327</v>
       </c>
       <c r="F211" s="1" t="n">
+        <v>0.0004327</v>
+      </c>
+      <c r="G211" s="1" t="n">
         <v>0.0004282</v>
       </c>
     </row>
@@ -5095,9 +5731,12 @@
         <v>0.0216</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>0.02171</v>
+        <v>0.02177</v>
       </c>
       <c r="F212" s="1" t="n">
+        <v>0.02177</v>
+      </c>
+      <c r="G212" s="1" t="n">
         <v>0.0216</v>
       </c>
     </row>
@@ -5117,9 +5756,12 @@
         <v>0.1154</v>
       </c>
       <c r="E213" s="1" t="n">
+        <v>0.1156</v>
+      </c>
+      <c r="F213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="F213" s="1" t="n">
+      <c r="G213" s="1" t="n">
         <v>0.1151</v>
       </c>
     </row>
@@ -5139,9 +5781,12 @@
         <v>0.04188</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>0.04204</v>
+        <v>0.04206</v>
       </c>
       <c r="F214" s="1" t="n">
+        <v>0.04206</v>
+      </c>
+      <c r="G214" s="1" t="n">
         <v>0.04188</v>
       </c>
     </row>
@@ -5161,9 +5806,12 @@
         <v>0.010039</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>0.010039</v>
+        <v>0.010079</v>
       </c>
       <c r="F215" s="1" t="n">
+        <v>0.010079</v>
+      </c>
+      <c r="G215" s="1" t="n">
         <v>0.009896</v>
       </c>
     </row>
@@ -5183,9 +5831,12 @@
         <v>0.0634</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>0.064</v>
+        <v>0.0643</v>
       </c>
       <c r="F216" s="1" t="n">
+        <v>0.0643</v>
+      </c>
+      <c r="G216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -5205,9 +5856,12 @@
         <v>0.004177</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>0.004186</v>
+        <v>0.004216</v>
       </c>
       <c r="F217" s="1" t="n">
+        <v>0.004216</v>
+      </c>
+      <c r="G217" s="1" t="n">
         <v>0.004177</v>
       </c>
     </row>
@@ -5227,9 +5881,12 @@
         <v>0.01065</v>
       </c>
       <c r="E218" s="1" t="n">
+        <v>0.01079</v>
+      </c>
+      <c r="F218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="F218" s="1" t="n">
+      <c r="G218" s="1" t="n">
         <v>0.01062</v>
       </c>
     </row>
@@ -5249,9 +5906,12 @@
         <v>0.03054</v>
       </c>
       <c r="E219" s="1" t="n">
+        <v>0.03068</v>
+      </c>
+      <c r="F219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="F219" s="1" t="n">
+      <c r="G219" s="1" t="n">
         <v>0.03054</v>
       </c>
     </row>
@@ -5271,9 +5931,12 @@
         <v>2.296</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>2.306</v>
+        <v>2.315</v>
       </c>
       <c r="F220" s="1" t="n">
+        <v>2.315</v>
+      </c>
+      <c r="G220" s="1" t="n">
         <v>2.296</v>
       </c>
     </row>
@@ -5293,9 +5956,12 @@
         <v>0.023027</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>0.023068</v>
+        <v>0.023224</v>
       </c>
       <c r="F221" s="1" t="n">
+        <v>0.023224</v>
+      </c>
+      <c r="G221" s="1" t="n">
         <v>0.023027</v>
       </c>
     </row>
@@ -5318,6 +5984,9 @@
         <v>0.0372</v>
       </c>
       <c r="F222" s="1" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="G222" s="1" t="n">
         <v>0.037</v>
       </c>
     </row>
@@ -5337,9 +6006,12 @@
         <v>0.294</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>0.2946</v>
+        <v>0.295</v>
       </c>
       <c r="F223" s="1" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="G223" s="1" t="n">
         <v>0.294</v>
       </c>
     </row>
@@ -5359,9 +6031,12 @@
         <v>0.01537</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>0.01549</v>
+        <v>0.01576</v>
       </c>
       <c r="F224" s="1" t="n">
+        <v>0.01576</v>
+      </c>
+      <c r="G224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -5381,9 +6056,12 @@
         <v>0.0004112</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>0.0004135</v>
+        <v>0.0004153</v>
       </c>
       <c r="F225" s="1" t="n">
+        <v>0.0004153</v>
+      </c>
+      <c r="G225" s="1" t="n">
         <v>0.0004112</v>
       </c>
     </row>
@@ -5403,9 +6081,12 @@
         <v>0.08765000000000001</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>0.08766</v>
+        <v>0.0881</v>
       </c>
       <c r="F226" s="1" t="n">
+        <v>0.0881</v>
+      </c>
+      <c r="G226" s="1" t="n">
         <v>0.08731999999999999</v>
       </c>
     </row>
@@ -5425,9 +6106,12 @@
         <v>0.949</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>0.949</v>
+        <v>0.956</v>
       </c>
       <c r="F227" s="1" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="G227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -5447,9 +6131,12 @@
         <v>0.0563</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>0.0563</v>
+        <v>0.05641</v>
       </c>
       <c r="F228" s="1" t="n">
+        <v>0.05641</v>
+      </c>
+      <c r="G228" s="1" t="n">
         <v>0.0558</v>
       </c>
     </row>
@@ -5469,9 +6156,12 @@
         <v>0.002017</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>0.002026</v>
+        <v>0.002035</v>
       </c>
       <c r="F229" s="1" t="n">
+        <v>0.002035</v>
+      </c>
+      <c r="G229" s="1" t="n">
         <v>0.002017</v>
       </c>
     </row>
@@ -5491,9 +6181,12 @@
         <v>0.022714</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>0.022734</v>
+        <v>0.022893</v>
       </c>
       <c r="F230" s="1" t="n">
+        <v>0.022893</v>
+      </c>
+      <c r="G230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -5513,9 +6206,12 @@
         <v>0.05471</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>0.05499</v>
+        <v>0.05507</v>
       </c>
       <c r="F231" s="1" t="n">
+        <v>0.05507</v>
+      </c>
+      <c r="G231" s="1" t="n">
         <v>0.05471</v>
       </c>
     </row>
@@ -5535,9 +6231,12 @@
         <v>0.0591</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>0.0595</v>
+        <v>0.0597</v>
       </c>
       <c r="F232" s="1" t="n">
+        <v>0.0597</v>
+      </c>
+      <c r="G232" s="1" t="n">
         <v>0.0591</v>
       </c>
     </row>
@@ -5557,9 +6256,12 @@
         <v>0.001678</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>0.001689</v>
+        <v>0.001701</v>
       </c>
       <c r="F233" s="1" t="n">
+        <v>0.001701</v>
+      </c>
+      <c r="G233" s="1" t="n">
         <v>0.001678</v>
       </c>
     </row>
@@ -5579,9 +6281,12 @@
         <v>0.005796</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>0.005796</v>
+        <v>0.005837</v>
       </c>
       <c r="F234" s="1" t="n">
+        <v>0.005837</v>
+      </c>
+      <c r="G234" s="1" t="n">
         <v>0.005784</v>
       </c>
     </row>
@@ -5601,9 +6306,12 @@
         <v>0.12568</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>0.12568</v>
+        <v>0.1264</v>
       </c>
       <c r="F235" s="1" t="n">
+        <v>0.1264</v>
+      </c>
+      <c r="G235" s="1" t="n">
         <v>0.12453</v>
       </c>
     </row>
@@ -5623,9 +6331,12 @@
         <v>64.78</v>
       </c>
       <c r="E236" s="1" t="n">
+        <v>65.23</v>
+      </c>
+      <c r="F236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="F236" s="1" t="n">
+      <c r="G236" s="1" t="n">
         <v>64.78</v>
       </c>
     </row>
@@ -5645,9 +6356,12 @@
         <v>0.1021</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>0.1028</v>
+        <v>0.1032</v>
       </c>
       <c r="F237" s="1" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="G237" s="1" t="n">
         <v>0.1021</v>
       </c>
     </row>
@@ -5667,9 +6381,12 @@
         <v>0.003925</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>0.003951</v>
+        <v>0.003989</v>
       </c>
       <c r="F238" s="1" t="n">
+        <v>0.003989</v>
+      </c>
+      <c r="G238" s="1" t="n">
         <v>0.003925</v>
       </c>
     </row>
@@ -5689,9 +6406,12 @@
         <v>0.01532</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>0.01541</v>
+        <v>0.01556</v>
       </c>
       <c r="F239" s="1" t="n">
+        <v>0.01556</v>
+      </c>
+      <c r="G239" s="1" t="n">
         <v>0.01532</v>
       </c>
     </row>
@@ -5711,9 +6431,12 @@
         <v>0.05624</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>0.05631</v>
+        <v>0.05673</v>
       </c>
       <c r="F240" s="1" t="n">
+        <v>0.05673</v>
+      </c>
+      <c r="G240" s="1" t="n">
         <v>0.05621</v>
       </c>
     </row>
@@ -5733,9 +6456,12 @@
         <v>0.0114</v>
       </c>
       <c r="E241" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="F241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="F241" s="1" t="n">
+      <c r="G241" s="1" t="n">
         <v>0.0114</v>
       </c>
     </row>
@@ -5755,9 +6481,12 @@
         <v>0.336</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>0.3372</v>
+        <v>0.3388</v>
       </c>
       <c r="F242" s="1" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="G242" s="1" t="n">
         <v>0.336</v>
       </c>
     </row>
@@ -5777,9 +6506,12 @@
         <v>0.01241</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>0.01247</v>
+        <v>0.01249</v>
       </c>
       <c r="F243" s="1" t="n">
+        <v>0.01249</v>
+      </c>
+      <c r="G243" s="1" t="n">
         <v>0.01241</v>
       </c>
     </row>
@@ -5799,9 +6531,12 @@
         <v>0.07997</v>
       </c>
       <c r="E244" s="1" t="n">
+        <v>0.08043</v>
+      </c>
+      <c r="F244" s="1" t="n">
         <v>0.08051999999999999</v>
       </c>
-      <c r="F244" s="1" t="n">
+      <c r="G244" s="1" t="n">
         <v>0.07997</v>
       </c>
     </row>
@@ -5821,10 +6556,13 @@
         <v>0.008022</v>
       </c>
       <c r="E245" s="1" t="n">
+        <v>0.007972999999999999</v>
+      </c>
+      <c r="F245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="F245" s="1" t="n">
-        <v>0.008</v>
+      <c r="G245" s="1" t="n">
+        <v>0.007972999999999999</v>
       </c>
     </row>
     <row r="246">
@@ -5843,9 +6581,12 @@
         <v>0.03059</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>0.03059</v>
+        <v>0.03071</v>
       </c>
       <c r="F246" s="1" t="n">
+        <v>0.03071</v>
+      </c>
+      <c r="G246" s="1" t="n">
         <v>0.03056</v>
       </c>
     </row>
@@ -5865,9 +6606,12 @@
         <v>0.1808</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>0.1813</v>
+        <v>0.1823</v>
       </c>
       <c r="F247" s="1" t="n">
+        <v>0.1823</v>
+      </c>
+      <c r="G247" s="1" t="n">
         <v>0.1808</v>
       </c>
     </row>
@@ -5887,9 +6631,12 @@
         <v>0.05915</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>0.05929</v>
+        <v>0.05956</v>
       </c>
       <c r="F248" s="1" t="n">
+        <v>0.05956</v>
+      </c>
+      <c r="G248" s="1" t="n">
         <v>0.05915</v>
       </c>
     </row>
@@ -5909,9 +6656,12 @@
         <v>0.1664</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>0.1676</v>
+        <v>0.1682</v>
       </c>
       <c r="F249" s="1" t="n">
+        <v>0.1682</v>
+      </c>
+      <c r="G249" s="1" t="n">
         <v>0.1664</v>
       </c>
     </row>
@@ -5931,9 +6681,12 @@
         <v>0.01938</v>
       </c>
       <c r="E250" s="1" t="n">
+        <v>0.01944</v>
+      </c>
+      <c r="F250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="F250" s="1" t="n">
+      <c r="G250" s="1" t="n">
         <v>0.01938</v>
       </c>
     </row>
@@ -5953,9 +6706,12 @@
         <v>0.02309</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>0.02312</v>
+        <v>0.02318</v>
       </c>
       <c r="F251" s="1" t="n">
+        <v>0.02318</v>
+      </c>
+      <c r="G251" s="1" t="n">
         <v>0.02304</v>
       </c>
     </row>
@@ -5975,9 +6731,12 @@
         <v>0.30199</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>0.30199</v>
+        <v>0.30378</v>
       </c>
       <c r="F252" s="1" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="G252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -5997,9 +6756,12 @@
         <v>0.00607</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>0.006106</v>
+        <v>0.006143</v>
       </c>
       <c r="F253" s="1" t="n">
+        <v>0.006143</v>
+      </c>
+      <c r="G253" s="1" t="n">
         <v>0.00607</v>
       </c>
     </row>
@@ -6019,9 +6781,12 @@
         <v>0.6141</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>0.6167</v>
+        <v>0.6193</v>
       </c>
       <c r="F254" s="1" t="n">
+        <v>0.6193</v>
+      </c>
+      <c r="G254" s="1" t="n">
         <v>0.6141</v>
       </c>
     </row>
@@ -6041,9 +6806,12 @@
         <v>0.10785</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>0.10811</v>
+        <v>0.10823</v>
       </c>
       <c r="F255" s="1" t="n">
+        <v>0.10823</v>
+      </c>
+      <c r="G255" s="1" t="n">
         <v>0.10785</v>
       </c>
     </row>
@@ -6063,9 +6831,12 @@
         <v>0.0902</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>0.0907</v>
+        <v>0.0911</v>
       </c>
       <c r="F256" s="1" t="n">
+        <v>0.0911</v>
+      </c>
+      <c r="G256" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -6085,9 +6856,12 @@
         <v>0.01417</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>0.01433</v>
+        <v>0.01454</v>
       </c>
       <c r="F257" s="1" t="n">
+        <v>0.01454</v>
+      </c>
+      <c r="G257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -6107,9 +6881,12 @@
         <v>0.05124</v>
       </c>
       <c r="E258" s="1" t="n">
+        <v>0.05122</v>
+      </c>
+      <c r="F258" s="1" t="n">
         <v>0.0514</v>
       </c>
-      <c r="F258" s="1" t="n">
+      <c r="G258" s="1" t="n">
         <v>0.0511</v>
       </c>
     </row>
@@ -6129,9 +6906,12 @@
         <v>0.008240000000000001</v>
       </c>
       <c r="E259" s="1" t="n">
+        <v>0.00829</v>
+      </c>
+      <c r="F259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="F259" s="1" t="n">
+      <c r="G259" s="1" t="n">
         <v>0.008240000000000001</v>
       </c>
     </row>
@@ -6151,9 +6931,12 @@
         <v>0.1902</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>0.1907</v>
+        <v>0.1914</v>
       </c>
       <c r="F260" s="1" t="n">
+        <v>0.1914</v>
+      </c>
+      <c r="G260" s="1" t="n">
         <v>0.1902</v>
       </c>
     </row>
@@ -6176,6 +6959,9 @@
         <v>0.0993</v>
       </c>
       <c r="F261" s="1" t="n">
+        <v>0.0993</v>
+      </c>
+      <c r="G261" s="1" t="n">
         <v>0.09859999999999999</v>
       </c>
     </row>
@@ -6195,9 +6981,12 @@
         <v>0.2128</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>0.2138</v>
+        <v>0.2144</v>
       </c>
       <c r="F262" s="1" t="n">
+        <v>0.2144</v>
+      </c>
+      <c r="G262" s="1" t="n">
         <v>0.2128</v>
       </c>
     </row>
@@ -6217,9 +7006,12 @@
         <v>0.008394</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>0.008394</v>
+        <v>0.008451999999999999</v>
       </c>
       <c r="F263" s="1" t="n">
+        <v>0.008451999999999999</v>
+      </c>
+      <c r="G263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -6239,9 +7031,12 @@
         <v>2.647</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>2.651</v>
+        <v>2.658</v>
       </c>
       <c r="F264" s="1" t="n">
+        <v>2.658</v>
+      </c>
+      <c r="G264" s="1" t="n">
         <v>2.647</v>
       </c>
     </row>
@@ -6261,9 +7056,12 @@
         <v>0.01847</v>
       </c>
       <c r="E265" s="1" t="n">
+        <v>0.0186</v>
+      </c>
+      <c r="F265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="F265" s="1" t="n">
+      <c r="G265" s="1" t="n">
         <v>0.01847</v>
       </c>
     </row>
@@ -6283,9 +7081,12 @@
         <v>0.3604</v>
       </c>
       <c r="E266" s="1" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="F266" s="1" t="n">
         <v>0.3604</v>
       </c>
-      <c r="F266" s="1" t="n">
+      <c r="G266" s="1" t="n">
         <v>0.3595</v>
       </c>
     </row>
@@ -6305,9 +7106,12 @@
         <v>0.03429</v>
       </c>
       <c r="E267" s="1" t="n">
+        <v>0.03446</v>
+      </c>
+      <c r="F267" s="1" t="n">
         <v>0.03464</v>
       </c>
-      <c r="F267" s="1" t="n">
+      <c r="G267" s="1" t="n">
         <v>0.03429</v>
       </c>
     </row>
@@ -6327,10 +7131,13 @@
         <v>0.12</v>
       </c>
       <c r="E268" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="F268" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="F268" s="1" t="n">
-        <v>0.12</v>
+      <c r="G268" s="1" t="n">
+        <v>0.119</v>
       </c>
     </row>
     <row r="269">
@@ -6349,9 +7156,12 @@
         <v>0.08053</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>0.0809</v>
+        <v>0.08105</v>
       </c>
       <c r="F269" s="1" t="n">
+        <v>0.08105</v>
+      </c>
+      <c r="G269" s="1" t="n">
         <v>0.08053</v>
       </c>
     </row>
@@ -6374,6 +7184,9 @@
         <v>0.01402</v>
       </c>
       <c r="F270" s="1" t="n">
+        <v>0.01402</v>
+      </c>
+      <c r="G270" s="1" t="n">
         <v>0.01397</v>
       </c>
     </row>
@@ -6393,9 +7206,12 @@
         <v>0.007654</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>0.007659</v>
+        <v>0.007707</v>
       </c>
       <c r="F271" s="1" t="n">
+        <v>0.007707</v>
+      </c>
+      <c r="G271" s="1" t="n">
         <v>0.007654</v>
       </c>
     </row>
@@ -6415,9 +7231,12 @@
         <v>0.07425</v>
       </c>
       <c r="E272" s="1" t="n">
+        <v>0.07439</v>
+      </c>
+      <c r="F272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="F272" s="1" t="n">
+      <c r="G272" s="1" t="n">
         <v>0.07425</v>
       </c>
     </row>
@@ -6437,9 +7256,12 @@
         <v>3.11e-05</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>3.13e-05</v>
+        <v>3.16e-05</v>
       </c>
       <c r="F273" s="1" t="n">
+        <v>3.16e-05</v>
+      </c>
+      <c r="G273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -6459,10 +7281,13 @@
         <v>0.005586</v>
       </c>
       <c r="E274" s="1" t="n">
+        <v>0.005576</v>
+      </c>
+      <c r="F274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="F274" s="1" t="n">
-        <v>0.005586</v>
+      <c r="G274" s="1" t="n">
+        <v>0.005576</v>
       </c>
     </row>
     <row r="275">
@@ -6481,9 +7306,12 @@
         <v>0.1802</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>0.1804</v>
+        <v>0.1817</v>
       </c>
       <c r="F275" s="1" t="n">
+        <v>0.1817</v>
+      </c>
+      <c r="G275" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -6503,9 +7331,12 @@
         <v>0.006878</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>0.006919</v>
+        <v>0.006933</v>
       </c>
       <c r="F276" s="1" t="n">
+        <v>0.006933</v>
+      </c>
+      <c r="G276" s="1" t="n">
         <v>0.006876</v>
       </c>
     </row>
@@ -6525,9 +7356,12 @@
         <v>0.1316</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>0.1319</v>
+        <v>0.1332</v>
       </c>
       <c r="F277" s="1" t="n">
+        <v>0.1332</v>
+      </c>
+      <c r="G277" s="1" t="n">
         <v>0.1316</v>
       </c>
     </row>
@@ -6547,9 +7381,12 @@
         <v>0.02335</v>
       </c>
       <c r="E278" s="1" t="n">
+        <v>0.02355</v>
+      </c>
+      <c r="F278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="F278" s="1" t="n">
+      <c r="G278" s="1" t="n">
         <v>0.02335</v>
       </c>
     </row>
@@ -6569,9 +7406,12 @@
         <v>0.01817</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>0.01818</v>
+        <v>0.01827</v>
       </c>
       <c r="F279" s="1" t="n">
+        <v>0.01827</v>
+      </c>
+      <c r="G279" s="1" t="n">
         <v>0.01817</v>
       </c>
     </row>
@@ -6591,9 +7431,12 @@
         <v>0.03755</v>
       </c>
       <c r="E280" s="1" t="n">
+        <v>0.03773</v>
+      </c>
+      <c r="F280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="F280" s="1" t="n">
+      <c r="G280" s="1" t="n">
         <v>0.03755</v>
       </c>
     </row>
@@ -6613,9 +7456,12 @@
         <v>0.03981</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>0.03994</v>
+        <v>0.0401</v>
       </c>
       <c r="F281" s="1" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="G281" s="1" t="n">
         <v>0.03981</v>
       </c>
     </row>
@@ -6635,9 +7481,12 @@
         <v>0.3025</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>0.3053</v>
+        <v>0.3059</v>
       </c>
       <c r="F282" s="1" t="n">
+        <v>0.3059</v>
+      </c>
+      <c r="G282" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -6657,9 +7506,12 @@
         <v>0.01124</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>0.01131</v>
+        <v>0.01133</v>
       </c>
       <c r="F283" s="1" t="n">
+        <v>0.01133</v>
+      </c>
+      <c r="G283" s="1" t="n">
         <v>0.01124</v>
       </c>
     </row>
@@ -6679,9 +7531,12 @@
         <v>9.6e-06</v>
       </c>
       <c r="E284" s="1" t="n">
+        <v>9.500000000000001e-06</v>
+      </c>
+      <c r="F284" s="1" t="n">
         <v>9.7e-06</v>
       </c>
-      <c r="F284" s="1" t="n">
+      <c r="G284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -6701,9 +7556,12 @@
         <v>0.1153</v>
       </c>
       <c r="E285" s="1" t="n">
+        <v>0.1157</v>
+      </c>
+      <c r="F285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="F285" s="1" t="n">
+      <c r="G285" s="1" t="n">
         <v>0.1153</v>
       </c>
     </row>
@@ -6723,9 +7581,12 @@
         <v>0.003442</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>0.003453</v>
+        <v>0.003466</v>
       </c>
       <c r="F286" s="1" t="n">
+        <v>0.003466</v>
+      </c>
+      <c r="G286" s="1" t="n">
         <v>0.003442</v>
       </c>
     </row>
@@ -6745,9 +7606,12 @@
         <v>0.08545999999999999</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>0.08563999999999999</v>
+        <v>0.08568000000000001</v>
       </c>
       <c r="F287" s="1" t="n">
+        <v>0.08568000000000001</v>
+      </c>
+      <c r="G287" s="1" t="n">
         <v>0.08545999999999999</v>
       </c>
     </row>
@@ -6767,9 +7631,12 @@
         <v>0.09962</v>
       </c>
       <c r="E288" s="1" t="n">
+        <v>0.09895</v>
+      </c>
+      <c r="F288" s="1" t="n">
         <v>0.1001</v>
       </c>
-      <c r="F288" s="1" t="n">
+      <c r="G288" s="1" t="n">
         <v>0.09889000000000001</v>
       </c>
     </row>
@@ -6789,9 +7656,12 @@
         <v>0.4307</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>0.4327</v>
+        <v>0.434</v>
       </c>
       <c r="F289" s="1" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="G289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -6811,9 +7681,12 @@
         <v>0.03921</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>0.03958</v>
+        <v>0.03966</v>
       </c>
       <c r="F290" s="1" t="n">
+        <v>0.03966</v>
+      </c>
+      <c r="G290" s="1" t="n">
         <v>0.03921</v>
       </c>
     </row>
@@ -6833,9 +7706,12 @@
         <v>0.2416</v>
       </c>
       <c r="E291" s="1" t="n">
+        <v>0.2447</v>
+      </c>
+      <c r="F291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="F291" s="1" t="n">
+      <c r="G291" s="1" t="n">
         <v>0.2416</v>
       </c>
     </row>
@@ -6855,10 +7731,13 @@
         <v>0.28375</v>
       </c>
       <c r="E292" s="1" t="n">
+        <v>0.28275</v>
+      </c>
+      <c r="F292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="F292" s="1" t="n">
-        <v>0.28375</v>
+      <c r="G292" s="1" t="n">
+        <v>0.28275</v>
       </c>
     </row>
     <row r="293">
@@ -6877,9 +7756,12 @@
         <v>0.1498</v>
       </c>
       <c r="E293" s="1" t="n">
+        <v>0.1505</v>
+      </c>
+      <c r="F293" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="F293" s="1" t="n">
+      <c r="G293" s="1" t="n">
         <v>0.1498</v>
       </c>
     </row>
@@ -6899,9 +7781,12 @@
         <v>4.243</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>4.254</v>
+        <v>4.269</v>
       </c>
       <c r="F294" s="1" t="n">
+        <v>4.269</v>
+      </c>
+      <c r="G294" s="1" t="n">
         <v>4.238</v>
       </c>
     </row>
@@ -6921,9 +7806,12 @@
         <v>0.03223</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>0.03223</v>
+        <v>0.03267</v>
       </c>
       <c r="F295" s="1" t="n">
+        <v>0.03267</v>
+      </c>
+      <c r="G295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -6943,9 +7831,12 @@
         <v>0.0009829999999999999</v>
       </c>
       <c r="E296" s="1" t="n">
+        <v>0.000987</v>
+      </c>
+      <c r="F296" s="1" t="n">
         <v>0.0009890000000000001</v>
       </c>
-      <c r="F296" s="1" t="n">
+      <c r="G296" s="1" t="n">
         <v>0.00098</v>
       </c>
     </row>
@@ -6965,9 +7856,12 @@
         <v>0.08209</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>0.08255999999999999</v>
+        <v>0.08259</v>
       </c>
       <c r="F297" s="1" t="n">
+        <v>0.08259</v>
+      </c>
+      <c r="G297" s="1" t="n">
         <v>0.08209</v>
       </c>
     </row>
@@ -6987,9 +7881,12 @@
         <v>0.05771</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>0.05792</v>
+        <v>0.05815</v>
       </c>
       <c r="F298" s="1" t="n">
+        <v>0.05815</v>
+      </c>
+      <c r="G298" s="1" t="n">
         <v>0.05763</v>
       </c>
     </row>
@@ -7009,9 +7906,12 @@
         <v>0.09066</v>
       </c>
       <c r="E299" s="1" t="n">
+        <v>0.09102</v>
+      </c>
+      <c r="F299" s="1" t="n">
         <v>0.09109</v>
       </c>
-      <c r="F299" s="1" t="n">
+      <c r="G299" s="1" t="n">
         <v>0.09066</v>
       </c>
     </row>
@@ -7031,9 +7931,12 @@
         <v>0.02764</v>
       </c>
       <c r="E300" s="1" t="n">
+        <v>0.02781</v>
+      </c>
+      <c r="F300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="F300" s="1" t="n">
+      <c r="G300" s="1" t="n">
         <v>0.02764</v>
       </c>
     </row>
@@ -7053,9 +7956,12 @@
         <v>0.06603000000000001</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>0.06623999999999999</v>
+        <v>0.06634</v>
       </c>
       <c r="F301" s="1" t="n">
+        <v>0.06634</v>
+      </c>
+      <c r="G301" s="1" t="n">
         <v>0.06603000000000001</v>
       </c>
     </row>
@@ -7075,9 +7981,12 @@
         <v>0.052337</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>0.052337</v>
+        <v>0.052584</v>
       </c>
       <c r="F302" s="1" t="n">
+        <v>0.052584</v>
+      </c>
+      <c r="G302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -7097,9 +8006,12 @@
         <v>5156.4</v>
       </c>
       <c r="E303" s="1" t="n">
+        <v>5162</v>
+      </c>
+      <c r="F303" s="1" t="n">
         <v>5172.3</v>
       </c>
-      <c r="F303" s="1" t="n">
+      <c r="G303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -7119,9 +8031,12 @@
         <v>14.99</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>15.02</v>
+        <v>15.09</v>
       </c>
       <c r="F304" s="1" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="G304" s="1" t="n">
         <v>14.99</v>
       </c>
     </row>
@@ -7141,9 +8056,12 @@
         <v>0.003722</v>
       </c>
       <c r="E305" s="1" t="n">
+        <v>0.003736</v>
+      </c>
+      <c r="F305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="F305" s="1" t="n">
+      <c r="G305" s="1" t="n">
         <v>0.003722</v>
       </c>
     </row>
@@ -7163,9 +8081,12 @@
         <v>0.4574</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>0.4602</v>
+        <v>0.4607</v>
       </c>
       <c r="F306" s="1" t="n">
+        <v>0.4607</v>
+      </c>
+      <c r="G306" s="1" t="n">
         <v>0.4573</v>
       </c>
     </row>
@@ -7185,9 +8106,12 @@
         <v>0.04732</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>0.04745</v>
+        <v>0.04753</v>
       </c>
       <c r="F307" s="1" t="n">
+        <v>0.04753</v>
+      </c>
+      <c r="G307" s="1" t="n">
         <v>0.04732</v>
       </c>
     </row>
@@ -7207,9 +8131,12 @@
         <v>1.4784</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>1.4784</v>
+        <v>1.4857</v>
       </c>
       <c r="F308" s="1" t="n">
+        <v>1.4857</v>
+      </c>
+      <c r="G308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -7229,9 +8156,12 @@
         <v>0.000807</v>
       </c>
       <c r="E309" s="1" t="n">
+        <v>0.0008099</v>
+      </c>
+      <c r="F309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="F309" s="1" t="n">
+      <c r="G309" s="1" t="n">
         <v>0.0008068</v>
       </c>
     </row>
@@ -7251,9 +8181,12 @@
         <v>4.692</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>4.699</v>
+        <v>4.721</v>
       </c>
       <c r="F310" s="1" t="n">
+        <v>4.721</v>
+      </c>
+      <c r="G310" s="1" t="n">
         <v>4.692</v>
       </c>
     </row>
@@ -7273,9 +8206,12 @@
         <v>4.765</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>4.784</v>
+        <v>4.805</v>
       </c>
       <c r="F311" s="1" t="n">
+        <v>4.805</v>
+      </c>
+      <c r="G311" s="1" t="n">
         <v>4.765</v>
       </c>
     </row>
@@ -7295,9 +8231,12 @@
         <v>0.08133</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>0.08133</v>
+        <v>0.08141</v>
       </c>
       <c r="F312" s="1" t="n">
+        <v>0.08141</v>
+      </c>
+      <c r="G312" s="1" t="n">
         <v>0.08098</v>
       </c>
     </row>
@@ -7317,9 +8256,12 @@
         <v>2.037</v>
       </c>
       <c r="E313" s="1" t="n">
+        <v>2.041</v>
+      </c>
+      <c r="F313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="F313" s="1" t="n">
+      <c r="G313" s="1" t="n">
         <v>2.037</v>
       </c>
     </row>
@@ -7339,9 +8281,12 @@
         <v>0.06886</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>0.06886</v>
+        <v>0.07025000000000001</v>
       </c>
       <c r="F314" s="1" t="n">
+        <v>0.07025000000000001</v>
+      </c>
+      <c r="G314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -7361,9 +8306,12 @@
         <v>0.959</v>
       </c>
       <c r="E315" s="1" t="n">
+        <v>0.961</v>
+      </c>
+      <c r="F315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="F315" s="1" t="n">
+      <c r="G315" s="1" t="n">
         <v>0.959</v>
       </c>
     </row>
@@ -7383,9 +8331,12 @@
         <v>0.1305</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>0.1308</v>
+        <v>0.1313</v>
       </c>
       <c r="F316" s="1" t="n">
+        <v>0.1313</v>
+      </c>
+      <c r="G316" s="1" t="n">
         <v>0.1305</v>
       </c>
     </row>
@@ -7405,9 +8356,12 @@
         <v>0.1814</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>0.1814</v>
+        <v>0.1859</v>
       </c>
       <c r="F317" s="1" t="n">
+        <v>0.1859</v>
+      </c>
+      <c r="G317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -7427,9 +8381,12 @@
         <v>0.01666</v>
       </c>
       <c r="E318" s="1" t="n">
+        <v>0.01662</v>
+      </c>
+      <c r="F318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="F318" s="1" t="n">
+      <c r="G318" s="1" t="n">
         <v>0.01661</v>
       </c>
     </row>
@@ -7449,9 +8406,12 @@
         <v>0.08399</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>0.08409</v>
+        <v>0.08445999999999999</v>
       </c>
       <c r="F319" s="1" t="n">
+        <v>0.08445999999999999</v>
+      </c>
+      <c r="G319" s="1" t="n">
         <v>0.08395</v>
       </c>
     </row>
@@ -7471,9 +8431,12 @@
         <v>0.007597</v>
       </c>
       <c r="E320" s="1" t="n">
+        <v>0.007647</v>
+      </c>
+      <c r="F320" s="1" t="n">
         <v>0.007659</v>
       </c>
-      <c r="F320" s="1" t="n">
+      <c r="G320" s="1" t="n">
         <v>0.007597</v>
       </c>
     </row>
@@ -7493,9 +8456,12 @@
         <v>0.05453</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>0.05463</v>
+        <v>0.05505</v>
       </c>
       <c r="F321" s="1" t="n">
+        <v>0.05505</v>
+      </c>
+      <c r="G321" s="1" t="n">
         <v>0.05452</v>
       </c>
     </row>
@@ -7515,9 +8481,12 @@
         <v>0.5483</v>
       </c>
       <c r="E322" s="1" t="n">
+        <v>0.5508999999999999</v>
+      </c>
+      <c r="F322" s="1" t="n">
         <v>0.5513</v>
       </c>
-      <c r="F322" s="1" t="n">
+      <c r="G322" s="1" t="n">
         <v>0.5483</v>
       </c>
     </row>
@@ -7537,9 +8506,12 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="E323" s="1" t="n">
+        <v>0.07565</v>
+      </c>
+      <c r="F323" s="1" t="n">
         <v>0.07593</v>
       </c>
-      <c r="F323" s="1" t="n">
+      <c r="G323" s="1" t="n">
         <v>0.07525</v>
       </c>
     </row>
@@ -7559,9 +8531,12 @@
         <v>0.012807</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>0.012807</v>
+        <v>0.012885</v>
       </c>
       <c r="F324" s="1" t="n">
+        <v>0.012885</v>
+      </c>
+      <c r="G324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -7581,9 +8556,12 @@
         <v>0.0993</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>0.0998</v>
+        <v>0.0999</v>
       </c>
       <c r="F325" s="1" t="n">
+        <v>0.0999</v>
+      </c>
+      <c r="G325" s="1" t="n">
         <v>0.0993</v>
       </c>
     </row>
@@ -7603,9 +8581,12 @@
         <v>0.01752</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>0.01756</v>
+        <v>0.01765</v>
       </c>
       <c r="F326" s="1" t="n">
+        <v>0.01765</v>
+      </c>
+      <c r="G326" s="1" t="n">
         <v>0.01752</v>
       </c>
     </row>
@@ -7625,9 +8606,12 @@
         <v>0.06392</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>0.06401999999999999</v>
+        <v>0.06435</v>
       </c>
       <c r="F327" s="1" t="n">
+        <v>0.06435</v>
+      </c>
+      <c r="G327" s="1" t="n">
         <v>0.06392</v>
       </c>
     </row>
@@ -7647,9 +8631,12 @@
         <v>0.2675</v>
       </c>
       <c r="E328" s="1" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="F328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="F328" s="1" t="n">
+      <c r="G328" s="1" t="n">
         <v>0.2675</v>
       </c>
     </row>
@@ -7669,9 +8656,12 @@
         <v>0.17286</v>
       </c>
       <c r="E329" s="1" t="n">
+        <v>0.1725</v>
+      </c>
+      <c r="F329" s="1" t="n">
         <v>0.17286</v>
       </c>
-      <c r="F329" s="1" t="n">
+      <c r="G329" s="1" t="n">
         <v>0.17172</v>
       </c>
     </row>
@@ -7691,9 +8681,12 @@
         <v>2.071</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>2.071</v>
+        <v>2.072</v>
       </c>
       <c r="F330" s="1" t="n">
+        <v>2.072</v>
+      </c>
+      <c r="G330" s="1" t="n">
         <v>2.043</v>
       </c>
     </row>
@@ -7716,6 +8709,9 @@
         <v>0.028</v>
       </c>
       <c r="F331" s="1" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="G331" s="1" t="n">
         <v>0.0278</v>
       </c>
     </row>
@@ -7735,9 +8731,12 @@
         <v>0.005981</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>0.005981</v>
+        <v>0.00602</v>
       </c>
       <c r="F332" s="1" t="n">
+        <v>0.00602</v>
+      </c>
+      <c r="G332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -7757,9 +8756,12 @@
         <v>0.003548</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>0.00355</v>
+        <v>0.003558</v>
       </c>
       <c r="F333" s="1" t="n">
+        <v>0.003558</v>
+      </c>
+      <c r="G333" s="1" t="n">
         <v>0.003531</v>
       </c>
     </row>
@@ -7779,9 +8781,12 @@
         <v>0.01399</v>
       </c>
       <c r="E334" s="1" t="n">
+        <v>0.01406</v>
+      </c>
+      <c r="F334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="F334" s="1" t="n">
+      <c r="G334" s="1" t="n">
         <v>0.01399</v>
       </c>
     </row>
@@ -7801,9 +8806,12 @@
         <v>1.12</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>1.125</v>
+        <v>1.128</v>
       </c>
       <c r="F335" s="1" t="n">
+        <v>1.128</v>
+      </c>
+      <c r="G335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -7823,9 +8831,12 @@
         <v>0.011253</v>
       </c>
       <c r="E336" s="1" t="n">
+        <v>0.011286</v>
+      </c>
+      <c r="F336" s="1" t="n">
         <v>0.011326</v>
       </c>
-      <c r="F336" s="1" t="n">
+      <c r="G336" s="1" t="n">
         <v>0.011253</v>
       </c>
     </row>
@@ -7845,9 +8856,12 @@
         <v>2.918</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>2.918</v>
+        <v>2.974</v>
       </c>
       <c r="F337" s="1" t="n">
+        <v>2.974</v>
+      </c>
+      <c r="G337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -7867,9 +8881,12 @@
         <v>0.01861</v>
       </c>
       <c r="E338" s="1" t="n">
+        <v>0.01882</v>
+      </c>
+      <c r="F338" s="1" t="n">
         <v>0.01884</v>
       </c>
-      <c r="F338" s="1" t="n">
+      <c r="G338" s="1" t="n">
         <v>0.01861</v>
       </c>
     </row>
@@ -7889,9 +8906,12 @@
         <v>0.07691000000000001</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>0.07691000000000001</v>
+        <v>0.07781</v>
       </c>
       <c r="F339" s="1" t="n">
+        <v>0.07781</v>
+      </c>
+      <c r="G339" s="1" t="n">
         <v>0.07689</v>
       </c>
     </row>
@@ -7911,9 +8931,12 @@
         <v>0.076</v>
       </c>
       <c r="E340" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="F340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="F340" s="1" t="n">
+      <c r="G340" s="1" t="n">
         <v>0.076</v>
       </c>
     </row>
@@ -7933,9 +8956,12 @@
         <v>0.03623</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>0.03628</v>
+        <v>0.03638</v>
       </c>
       <c r="F341" s="1" t="n">
+        <v>0.03638</v>
+      </c>
+      <c r="G341" s="1" t="n">
         <v>0.0362</v>
       </c>
     </row>
@@ -7955,9 +8981,12 @@
         <v>2620</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>2635</v>
+        <v>2643</v>
       </c>
       <c r="F342" s="1" t="n">
+        <v>2643</v>
+      </c>
+      <c r="G342" s="1" t="n">
         <v>2620</v>
       </c>
     </row>
@@ -7977,9 +9006,12 @@
         <v>0.0001959</v>
       </c>
       <c r="E343" s="1" t="n">
+        <v>0.0001978</v>
+      </c>
+      <c r="F343" s="1" t="n">
         <v>0.000198</v>
       </c>
-      <c r="F343" s="1" t="n">
+      <c r="G343" s="1" t="n">
         <v>0.0001959</v>
       </c>
     </row>
@@ -7999,9 +9031,12 @@
         <v>0.07987</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>0.07993</v>
+        <v>0.08032</v>
       </c>
       <c r="F344" s="1" t="n">
+        <v>0.08032</v>
+      </c>
+      <c r="G344" s="1" t="n">
         <v>0.07987</v>
       </c>
     </row>
@@ -8021,9 +9056,12 @@
         <v>0.01632</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>0.01645</v>
+        <v>0.01654</v>
       </c>
       <c r="F345" s="1" t="n">
+        <v>0.01654</v>
+      </c>
+      <c r="G345" s="1" t="n">
         <v>0.01632</v>
       </c>
     </row>
@@ -8043,9 +9081,12 @@
         <v>2.773</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>2.794</v>
+        <v>2.798</v>
       </c>
       <c r="F346" s="1" t="n">
+        <v>2.798</v>
+      </c>
+      <c r="G346" s="1" t="n">
         <v>2.773</v>
       </c>
     </row>
@@ -8068,6 +9109,9 @@
         <v>0.01647</v>
       </c>
       <c r="F347" s="1" t="n">
+        <v>0.01647</v>
+      </c>
+      <c r="G347" s="1" t="n">
         <v>0.01639</v>
       </c>
     </row>
@@ -8087,9 +9131,12 @@
         <v>0.03877</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>0.03877</v>
+        <v>0.03897</v>
       </c>
       <c r="F348" s="1" t="n">
+        <v>0.03897</v>
+      </c>
+      <c r="G348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -8109,9 +9156,12 @@
         <v>0.3037</v>
       </c>
       <c r="E349" s="1" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="F349" s="1" t="n">
         <v>0.3065</v>
       </c>
-      <c r="F349" s="1" t="n">
+      <c r="G349" s="1" t="n">
         <v>0.3037</v>
       </c>
     </row>
@@ -8131,9 +9181,12 @@
         <v>0.005039</v>
       </c>
       <c r="E350" s="1" t="n">
+        <v>0.005082</v>
+      </c>
+      <c r="F350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="F350" s="1" t="n">
+      <c r="G350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -8153,9 +9206,12 @@
         <v>0.00512</v>
       </c>
       <c r="E351" s="1" t="n">
+        <v>0.005145</v>
+      </c>
+      <c r="F351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="F351" s="1" t="n">
+      <c r="G351" s="1" t="n">
         <v>0.00512</v>
       </c>
     </row>
@@ -8175,9 +9231,12 @@
         <v>0.004387</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>0.004397</v>
+        <v>0.004413</v>
       </c>
       <c r="F352" s="1" t="n">
+        <v>0.004413</v>
+      </c>
+      <c r="G352" s="1" t="n">
         <v>0.004387</v>
       </c>
     </row>
@@ -8197,9 +9256,12 @@
         <v>0.08172</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>0.08211</v>
+        <v>0.08214</v>
       </c>
       <c r="F353" s="1" t="n">
+        <v>0.08214</v>
+      </c>
+      <c r="G353" s="1" t="n">
         <v>0.08172</v>
       </c>
     </row>
@@ -8219,9 +9281,12 @@
         <v>1.292</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>1.292</v>
+        <v>1.312</v>
       </c>
       <c r="F354" s="1" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="G354" s="1" t="n">
         <v>1.283</v>
       </c>
     </row>
@@ -8241,9 +9306,12 @@
         <v>7.745</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>7.771</v>
+        <v>7.775</v>
       </c>
       <c r="F355" s="1" t="n">
+        <v>7.775</v>
+      </c>
+      <c r="G355" s="1" t="n">
         <v>7.744</v>
       </c>
     </row>
@@ -8263,9 +9331,12 @@
         <v>0.007849999999999999</v>
       </c>
       <c r="E356" s="1" t="n">
+        <v>0.007889999999999999</v>
+      </c>
+      <c r="F356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="F356" s="1" t="n">
+      <c r="G356" s="1" t="n">
         <v>0.007849999999999999</v>
       </c>
     </row>
@@ -8285,9 +9356,12 @@
         <v>0.005696</v>
       </c>
       <c r="E357" s="1" t="n">
+        <v>0.005726</v>
+      </c>
+      <c r="F357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="F357" s="1" t="n">
+      <c r="G357" s="1" t="n">
         <v>0.005696</v>
       </c>
     </row>
@@ -8307,9 +9381,12 @@
         <v>0.01567</v>
       </c>
       <c r="E358" s="1" t="n">
+        <v>0.01576</v>
+      </c>
+      <c r="F358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="F358" s="1" t="n">
+      <c r="G358" s="1" t="n">
         <v>0.01567</v>
       </c>
     </row>
@@ -8329,9 +9406,12 @@
         <v>3.65</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>3.655</v>
+        <v>3.67</v>
       </c>
       <c r="F359" s="1" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="G359" s="1" t="n">
         <v>3.65</v>
       </c>
     </row>
@@ -8351,9 +9431,12 @@
         <v>0.1501</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>0.1503</v>
+        <v>0.1506</v>
       </c>
       <c r="F360" s="1" t="n">
+        <v>0.1506</v>
+      </c>
+      <c r="G360" s="1" t="n">
         <v>0.1499</v>
       </c>
     </row>
@@ -8373,9 +9456,12 @@
         <v>0.0708</v>
       </c>
       <c r="E361" s="1" t="n">
+        <v>0.07072000000000001</v>
+      </c>
+      <c r="F361" s="1" t="n">
         <v>0.07093000000000001</v>
       </c>
-      <c r="F361" s="1" t="n">
+      <c r="G361" s="1" t="n">
         <v>0.07069</v>
       </c>
     </row>
@@ -8395,9 +9481,12 @@
         <v>0.01786</v>
       </c>
       <c r="E362" s="1" t="n">
+        <v>0.01795</v>
+      </c>
+      <c r="F362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="F362" s="1" t="n">
+      <c r="G362" s="1" t="n">
         <v>0.01786</v>
       </c>
     </row>
@@ -8417,9 +9506,12 @@
         <v>0.02263</v>
       </c>
       <c r="E363" s="1" t="n">
+        <v>0.02262</v>
+      </c>
+      <c r="F363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="F363" s="1" t="n">
+      <c r="G363" s="1" t="n">
         <v>0.02262</v>
       </c>
     </row>
@@ -8439,9 +9531,12 @@
         <v>0.01271</v>
       </c>
       <c r="E364" s="1" t="n">
+        <v>0.01275</v>
+      </c>
+      <c r="F364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="F364" s="1" t="n">
+      <c r="G364" s="1" t="n">
         <v>0.01271</v>
       </c>
     </row>
@@ -8461,9 +9556,12 @@
         <v>0.0919</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>0.0919</v>
+        <v>0.0925</v>
       </c>
       <c r="F365" s="1" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="G365" s="1" t="n">
         <v>0.0919</v>
       </c>
     </row>
@@ -8483,9 +9581,12 @@
         <v>0.04244</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>0.04257</v>
+        <v>0.04261</v>
       </c>
       <c r="F366" s="1" t="n">
+        <v>0.04261</v>
+      </c>
+      <c r="G366" s="1" t="n">
         <v>0.04244</v>
       </c>
     </row>
@@ -8505,9 +9606,12 @@
         <v>0.03145</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>0.03163</v>
+        <v>0.03164</v>
       </c>
       <c r="F367" s="1" t="n">
+        <v>0.03164</v>
+      </c>
+      <c r="G367" s="1" t="n">
         <v>0.03145</v>
       </c>
     </row>
@@ -8527,9 +9631,12 @@
         <v>0.02373</v>
       </c>
       <c r="E368" s="1" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="F368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="F368" s="1" t="n">
+      <c r="G368" s="1" t="n">
         <v>0.0236</v>
       </c>
     </row>
@@ -8549,9 +9656,12 @@
         <v>0.03114</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>0.03128</v>
+        <v>0.0313</v>
       </c>
       <c r="F369" s="1" t="n">
+        <v>0.0313</v>
+      </c>
+      <c r="G369" s="1" t="n">
         <v>0.03113</v>
       </c>
     </row>
@@ -8571,9 +9681,12 @@
         <v>0.07751</v>
       </c>
       <c r="E370" s="1" t="n">
+        <v>0.07745</v>
+      </c>
+      <c r="F370" s="1" t="n">
         <v>0.07784000000000001</v>
       </c>
-      <c r="F370" s="1" t="n">
+      <c r="G370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -8593,9 +9706,12 @@
         <v>0.1085</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>0.1085</v>
+        <v>0.1087</v>
       </c>
       <c r="F371" s="1" t="n">
+        <v>0.1087</v>
+      </c>
+      <c r="G371" s="1" t="n">
         <v>0.1074</v>
       </c>
     </row>
@@ -8615,9 +9731,12 @@
         <v>0.007084</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>0.007108</v>
+        <v>0.007206</v>
       </c>
       <c r="F372" s="1" t="n">
+        <v>0.007206</v>
+      </c>
+      <c r="G372" s="1" t="n">
         <v>0.007057</v>
       </c>
     </row>
@@ -8637,9 +9756,12 @@
         <v>0.0965</v>
       </c>
       <c r="E373" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="F373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="F373" s="1" t="n">
+      <c r="G373" s="1" t="n">
         <v>0.0965</v>
       </c>
     </row>
@@ -8659,9 +9781,12 @@
         <v>0.05831</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>0.05852</v>
+        <v>0.05881</v>
       </c>
       <c r="F374" s="1" t="n">
+        <v>0.05881</v>
+      </c>
+      <c r="G374" s="1" t="n">
         <v>0.0583</v>
       </c>
     </row>
@@ -8681,9 +9806,12 @@
         <v>0.3193</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>0.3207</v>
+        <v>0.3234</v>
       </c>
       <c r="F375" s="1" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="G375" s="1" t="n">
         <v>0.3193</v>
       </c>
     </row>
@@ -8703,9 +9831,12 @@
         <v>0.01988</v>
       </c>
       <c r="E376" s="1" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="F376" s="1" t="n">
+      <c r="G376" s="1" t="n">
         <v>0.01988</v>
       </c>
     </row>
@@ -8725,9 +9856,12 @@
         <v>0.06877</v>
       </c>
       <c r="E377" s="1" t="n">
+        <v>0.06909999999999999</v>
+      </c>
+      <c r="F377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="F377" s="1" t="n">
+      <c r="G377" s="1" t="n">
         <v>0.06877</v>
       </c>
     </row>
@@ -8747,9 +9881,12 @@
         <v>0.15387</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>0.15387</v>
+        <v>0.15583</v>
       </c>
       <c r="F378" s="1" t="n">
+        <v>0.15583</v>
+      </c>
+      <c r="G378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -8769,9 +9906,12 @@
         <v>0.0006028</v>
       </c>
       <c r="E379" s="1" t="n">
+        <v>0.0006059</v>
+      </c>
+      <c r="F379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="F379" s="1" t="n">
+      <c r="G379" s="1" t="n">
         <v>0.0006028</v>
       </c>
     </row>
@@ -8791,9 +9931,12 @@
         <v>0.01016</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>0.01019</v>
+        <v>0.01021</v>
       </c>
       <c r="F380" s="1" t="n">
+        <v>0.01021</v>
+      </c>
+      <c r="G380" s="1" t="n">
         <v>0.01016</v>
       </c>
     </row>
@@ -8813,9 +9956,12 @@
         <v>0.02555</v>
       </c>
       <c r="E381" s="1" t="n">
+        <v>0.02571</v>
+      </c>
+      <c r="F381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="F381" s="1" t="n">
+      <c r="G381" s="1" t="n">
         <v>0.02553</v>
       </c>
     </row>
@@ -8835,9 +9981,12 @@
         <v>0.19096</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>0.19096</v>
+        <v>0.19263</v>
       </c>
       <c r="F382" s="1" t="n">
+        <v>0.19263</v>
+      </c>
+      <c r="G382" s="1" t="n">
         <v>0.18936</v>
       </c>
     </row>
@@ -8857,9 +10006,12 @@
         <v>0.09433</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>0.09433</v>
+        <v>0.09479</v>
       </c>
       <c r="F383" s="1" t="n">
+        <v>0.09479</v>
+      </c>
+      <c r="G383" s="1" t="n">
         <v>0.09372999999999999</v>
       </c>
     </row>
@@ -8879,9 +10031,12 @@
         <v>0.03208</v>
       </c>
       <c r="E384" s="1" t="n">
+        <v>0.03198</v>
+      </c>
+      <c r="F384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="F384" s="1" t="n">
+      <c r="G384" s="1" t="n">
         <v>0.03194</v>
       </c>
     </row>
@@ -8901,9 +10056,12 @@
         <v>0.01115</v>
       </c>
       <c r="E385" s="1" t="n">
+        <v>0.01123</v>
+      </c>
+      <c r="F385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="F385" s="1" t="n">
+      <c r="G385" s="1" t="n">
         <v>0.01115</v>
       </c>
     </row>
@@ -8923,9 +10081,12 @@
         <v>0.05087</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>0.05101</v>
+        <v>0.05131</v>
       </c>
       <c r="F386" s="1" t="n">
+        <v>0.05131</v>
+      </c>
+      <c r="G386" s="1" t="n">
         <v>0.05087</v>
       </c>
     </row>
@@ -8945,9 +10106,12 @@
         <v>0.02483</v>
       </c>
       <c r="E387" s="1" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="F387" s="1" t="n">
         <v>0.02504</v>
       </c>
-      <c r="F387" s="1" t="n">
+      <c r="G387" s="1" t="n">
         <v>0.02483</v>
       </c>
     </row>
@@ -8967,9 +10131,12 @@
         <v>0.007381</v>
       </c>
       <c r="E388" s="1" t="n">
+        <v>0.00738</v>
+      </c>
+      <c r="F388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="F388" s="1" t="n">
+      <c r="G388" s="1" t="n">
         <v>0.007344</v>
       </c>
     </row>
@@ -8989,9 +10156,12 @@
         <v>0.01016</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>0.0102</v>
+        <v>0.01024</v>
       </c>
       <c r="F389" s="1" t="n">
+        <v>0.01024</v>
+      </c>
+      <c r="G389" s="1" t="n">
         <v>0.01016</v>
       </c>
     </row>
@@ -9011,9 +10181,12 @@
         <v>0.08312</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>0.0833</v>
+        <v>0.08369</v>
       </c>
       <c r="F390" s="1" t="n">
+        <v>0.08369</v>
+      </c>
+      <c r="G390" s="1" t="n">
         <v>0.08304</v>
       </c>
     </row>
@@ -9033,9 +10206,12 @@
         <v>0.5017</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>0.5027</v>
+        <v>0.5061</v>
       </c>
       <c r="F391" s="1" t="n">
+        <v>0.5061</v>
+      </c>
+      <c r="G391" s="1" t="n">
         <v>0.5017</v>
       </c>
     </row>
@@ -9055,9 +10231,12 @@
         <v>0.1171</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>0.1174</v>
+        <v>0.118</v>
       </c>
       <c r="F392" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="G392" s="1" t="n">
         <v>0.1171</v>
       </c>
     </row>
@@ -9077,9 +10256,12 @@
         <v>0.0025</v>
       </c>
       <c r="E393" s="1" t="n">
+        <v>0.00251</v>
+      </c>
+      <c r="F393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="F393" s="1" t="n">
+      <c r="G393" s="1" t="n">
         <v>0.0025</v>
       </c>
     </row>
@@ -9099,9 +10281,12 @@
         <v>0.02146</v>
       </c>
       <c r="E394" s="1" t="n">
+        <v>0.02155</v>
+      </c>
+      <c r="F394" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="F394" s="1" t="n">
+      <c r="G394" s="1" t="n">
         <v>0.02146</v>
       </c>
     </row>
@@ -9124,6 +10309,9 @@
         <v>0.0163</v>
       </c>
       <c r="F395" s="1" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="G395" s="1" t="n">
         <v>0.0162</v>
       </c>
     </row>
@@ -9143,9 +10331,12 @@
         <v>0.1359</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>0.1362</v>
+        <v>0.1364</v>
       </c>
       <c r="F396" s="1" t="n">
+        <v>0.1364</v>
+      </c>
+      <c r="G396" s="1" t="n">
         <v>0.1358</v>
       </c>
     </row>
@@ -9165,9 +10356,12 @@
         <v>0.01475</v>
       </c>
       <c r="E397" s="1" t="n">
+        <v>0.01482</v>
+      </c>
+      <c r="F397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="F397" s="1" t="n">
+      <c r="G397" s="1" t="n">
         <v>0.01475</v>
       </c>
     </row>
@@ -9187,9 +10381,12 @@
         <v>6.725</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>6.755</v>
+        <v>6.807</v>
       </c>
       <c r="F398" s="1" t="n">
+        <v>6.807</v>
+      </c>
+      <c r="G398" s="1" t="n">
         <v>6.725</v>
       </c>
     </row>
@@ -9209,10 +10406,13 @@
         <v>0.009473000000000001</v>
       </c>
       <c r="E399" s="1" t="n">
+        <v>0.009471</v>
+      </c>
+      <c r="F399" s="1" t="n">
         <v>0.009509999999999999</v>
       </c>
-      <c r="F399" s="1" t="n">
-        <v>0.009473000000000001</v>
+      <c r="G399" s="1" t="n">
+        <v>0.009471</v>
       </c>
     </row>
     <row r="400">
@@ -9231,9 +10431,12 @@
         <v>0.001269</v>
       </c>
       <c r="E400" s="1" t="n">
+        <v>0.001272</v>
+      </c>
+      <c r="F400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="F400" s="1" t="n">
+      <c r="G400" s="1" t="n">
         <v>0.001269</v>
       </c>
     </row>
@@ -9253,9 +10456,12 @@
         <v>0.01841</v>
       </c>
       <c r="E401" s="1" t="n">
+        <v>0.01844</v>
+      </c>
+      <c r="F401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="F401" s="1" t="n">
+      <c r="G401" s="1" t="n">
         <v>0.01841</v>
       </c>
     </row>
@@ -9275,9 +10481,12 @@
         <v>0.08587</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>0.08587</v>
+        <v>0.08595999999999999</v>
       </c>
       <c r="F402" s="1" t="n">
+        <v>0.08595999999999999</v>
+      </c>
+      <c r="G402" s="1" t="n">
         <v>0.08563999999999999</v>
       </c>
     </row>
@@ -9297,9 +10506,12 @@
         <v>0.00553</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>0.00553</v>
+        <v>0.00555</v>
       </c>
       <c r="F403" s="1" t="n">
+        <v>0.00555</v>
+      </c>
+      <c r="G403" s="1" t="n">
         <v>0.00553</v>
       </c>
     </row>
@@ -9319,10 +10531,13 @@
         <v>0.04369</v>
       </c>
       <c r="E404" s="1" t="n">
+        <v>0.04366</v>
+      </c>
+      <c r="F404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="F404" s="1" t="n">
-        <v>0.04369</v>
+      <c r="G404" s="1" t="n">
+        <v>0.04366</v>
       </c>
     </row>
     <row r="405">
@@ -9341,9 +10556,12 @@
         <v>0.05873</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>0.05876</v>
+        <v>0.05915</v>
       </c>
       <c r="F405" s="1" t="n">
+        <v>0.05915</v>
+      </c>
+      <c r="G405" s="1" t="n">
         <v>0.05871</v>
       </c>
     </row>
@@ -9363,9 +10581,12 @@
         <v>0.01658</v>
       </c>
       <c r="E406" s="1" t="n">
+        <v>0.01674</v>
+      </c>
+      <c r="F406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="F406" s="1" t="n">
+      <c r="G406" s="1" t="n">
         <v>0.01658</v>
       </c>
     </row>
@@ -9388,6 +10609,9 @@
         <v>0.0428</v>
       </c>
       <c r="F407" s="1" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="G407" s="1" t="n">
         <v>0.0425</v>
       </c>
     </row>
@@ -9407,9 +10631,12 @@
         <v>0.01938</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>0.0195</v>
+        <v>0.01951</v>
       </c>
       <c r="F408" s="1" t="n">
+        <v>0.01951</v>
+      </c>
+      <c r="G408" s="1" t="n">
         <v>0.01938</v>
       </c>
     </row>
@@ -9429,9 +10656,12 @@
         <v>0.4436</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>0.4439</v>
+        <v>0.4466</v>
       </c>
       <c r="F409" s="1" t="n">
+        <v>0.4466</v>
+      </c>
+      <c r="G409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -9451,9 +10681,12 @@
         <v>0.04418</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>0.04437</v>
+        <v>0.04454</v>
       </c>
       <c r="F410" s="1" t="n">
+        <v>0.04454</v>
+      </c>
+      <c r="G410" s="1" t="n">
         <v>0.04418</v>
       </c>
     </row>
@@ -9473,9 +10706,12 @@
         <v>26.78</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>26.84</v>
+        <v>27.06</v>
       </c>
       <c r="F411" s="1" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="G411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -9495,9 +10731,12 @@
         <v>0.03515</v>
       </c>
       <c r="E412" s="1" t="n">
+        <v>0.03553</v>
+      </c>
+      <c r="F412" s="1" t="n">
         <v>0.03561</v>
       </c>
-      <c r="F412" s="1" t="n">
+      <c r="G412" s="1" t="n">
         <v>0.03515</v>
       </c>
     </row>
@@ -9517,9 +10756,12 @@
         <v>0.00341</v>
       </c>
       <c r="E413" s="1" t="n">
+        <v>0.003426</v>
+      </c>
+      <c r="F413" s="1" t="n">
         <v>0.003429</v>
       </c>
-      <c r="F413" s="1" t="n">
+      <c r="G413" s="1" t="n">
         <v>0.00341</v>
       </c>
     </row>
@@ -9539,9 +10781,12 @@
         <v>0.1528</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>0.1531</v>
+        <v>0.1537</v>
       </c>
       <c r="F414" s="1" t="n">
+        <v>0.1537</v>
+      </c>
+      <c r="G414" s="1" t="n">
         <v>0.1527</v>
       </c>
     </row>
@@ -9561,9 +10806,12 @@
         <v>0.05267</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>0.05267</v>
+        <v>0.05286</v>
       </c>
       <c r="F415" s="1" t="n">
+        <v>0.05286</v>
+      </c>
+      <c r="G415" s="1" t="n">
         <v>0.05258</v>
       </c>
     </row>
@@ -9583,9 +10831,12 @@
         <v>0.00664</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>0.00668</v>
+        <v>0.00669</v>
       </c>
       <c r="F416" s="1" t="n">
+        <v>0.00669</v>
+      </c>
+      <c r="G416" s="1" t="n">
         <v>0.00664</v>
       </c>
     </row>
@@ -9605,9 +10856,12 @@
         <v>0.0608</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>0.06091</v>
+        <v>0.06101</v>
       </c>
       <c r="F417" s="1" t="n">
+        <v>0.06101</v>
+      </c>
+      <c r="G417" s="1" t="n">
         <v>0.0608</v>
       </c>
     </row>
@@ -9627,9 +10881,12 @@
         <v>0.008156</v>
       </c>
       <c r="E418" s="1" t="n">
+        <v>0.008211</v>
+      </c>
+      <c r="F418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="F418" s="1" t="n">
+      <c r="G418" s="1" t="n">
         <v>0.008156</v>
       </c>
     </row>
@@ -9649,9 +10906,12 @@
         <v>0.07471</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>0.07471</v>
+        <v>0.07494000000000001</v>
       </c>
       <c r="F419" s="1" t="n">
+        <v>0.07494000000000001</v>
+      </c>
+      <c r="G419" s="1" t="n">
         <v>0.07459</v>
       </c>
     </row>
@@ -9671,9 +10931,12 @@
         <v>0.0213</v>
       </c>
       <c r="E420" s="1" t="n">
+        <v>0.02144</v>
+      </c>
+      <c r="F420" s="1" t="n">
         <v>0.02145</v>
       </c>
-      <c r="F420" s="1" t="n">
+      <c r="G420" s="1" t="n">
         <v>0.0213</v>
       </c>
     </row>
@@ -9693,9 +10956,12 @@
         <v>0.0696</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>0.06984</v>
+        <v>0.07011000000000001</v>
       </c>
       <c r="F421" s="1" t="n">
+        <v>0.07011000000000001</v>
+      </c>
+      <c r="G421" s="1" t="n">
         <v>0.06938999999999999</v>
       </c>
     </row>
@@ -9715,10 +10981,13 @@
         <v>0.01528</v>
       </c>
       <c r="E422" s="1" t="n">
+        <v>0.01522</v>
+      </c>
+      <c r="F422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="F422" s="1" t="n">
-        <v>0.01524</v>
+      <c r="G422" s="1" t="n">
+        <v>0.01522</v>
       </c>
     </row>
     <row r="423">
@@ -9737,9 +11006,12 @@
         <v>0.006677</v>
       </c>
       <c r="E423" s="1" t="n">
+        <v>0.006695</v>
+      </c>
+      <c r="F423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="F423" s="1" t="n">
+      <c r="G423" s="1" t="n">
         <v>0.006677</v>
       </c>
     </row>
@@ -9759,9 +11031,12 @@
         <v>0.915</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>0.92</v>
+        <v>0.921</v>
       </c>
       <c r="F424" s="1" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="G424" s="1" t="n">
         <v>0.915</v>
       </c>
     </row>
@@ -9781,9 +11056,12 @@
         <v>0.0356</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>0.03561</v>
+        <v>0.03577</v>
       </c>
       <c r="F425" s="1" t="n">
+        <v>0.03577</v>
+      </c>
+      <c r="G425" s="1" t="n">
         <v>0.03555</v>
       </c>
     </row>
@@ -9803,9 +11081,12 @@
         <v>1.78</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>1.781</v>
+        <v>1.785</v>
       </c>
       <c r="F426" s="1" t="n">
+        <v>1.785</v>
+      </c>
+      <c r="G426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -9825,9 +11106,12 @@
         <v>0.12771</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>0.12793</v>
+        <v>0.12835</v>
       </c>
       <c r="F427" s="1" t="n">
+        <v>0.12835</v>
+      </c>
+      <c r="G427" s="1" t="n">
         <v>0.12771</v>
       </c>
     </row>
@@ -9847,10 +11131,13 @@
         <v>0.05339</v>
       </c>
       <c r="E428" s="1" t="n">
+        <v>0.05325</v>
+      </c>
+      <c r="F428" s="1" t="n">
         <v>0.05359</v>
       </c>
-      <c r="F428" s="1" t="n">
-        <v>0.05339</v>
+      <c r="G428" s="1" t="n">
+        <v>0.05325</v>
       </c>
     </row>
     <row r="429">
@@ -9869,9 +11156,12 @@
         <v>1.309</v>
       </c>
       <c r="E429" s="1" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="F429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="F429" s="1" t="n">
+      <c r="G429" s="1" t="n">
         <v>1.309</v>
       </c>
     </row>
@@ -9891,9 +11181,12 @@
         <v>0.07547</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>0.07566000000000001</v>
+        <v>0.07618</v>
       </c>
       <c r="F430" s="1" t="n">
+        <v>0.07618</v>
+      </c>
+      <c r="G430" s="1" t="n">
         <v>0.07547</v>
       </c>
     </row>
@@ -9913,9 +11206,12 @@
         <v>0.1636</v>
       </c>
       <c r="E431" s="1" t="n">
+        <v>0.1638</v>
+      </c>
+      <c r="F431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="F431" s="1" t="n">
+      <c r="G431" s="1" t="n">
         <v>0.1636</v>
       </c>
     </row>
@@ -9935,9 +11231,12 @@
         <v>1.456</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>1.457</v>
+        <v>1.461</v>
       </c>
       <c r="F432" s="1" t="n">
+        <v>1.461</v>
+      </c>
+      <c r="G432" s="1" t="n">
         <v>1.456</v>
       </c>
     </row>
@@ -9957,9 +11256,12 @@
         <v>3.306</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>3.316</v>
+        <v>3.324</v>
       </c>
       <c r="F433" s="1" t="n">
+        <v>3.324</v>
+      </c>
+      <c r="G433" s="1" t="n">
         <v>3.306</v>
       </c>
     </row>
@@ -9979,9 +11281,12 @@
         <v>0.1792</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>0.1802</v>
+        <v>0.1803</v>
       </c>
       <c r="F434" s="1" t="n">
+        <v>0.1803</v>
+      </c>
+      <c r="G434" s="1" t="n">
         <v>0.1792</v>
       </c>
     </row>
@@ -10001,9 +11306,12 @@
         <v>0.00864</v>
       </c>
       <c r="E435" s="1" t="n">
+        <v>0.008665000000000001</v>
+      </c>
+      <c r="F435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="F435" s="1" t="n">
+      <c r="G435" s="1" t="n">
         <v>0.00864</v>
       </c>
     </row>
@@ -10023,9 +11331,12 @@
         <v>0.2852</v>
       </c>
       <c r="E436" s="1" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="F436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="F436" s="1" t="n">
+      <c r="G436" s="1" t="n">
         <v>0.2841</v>
       </c>
     </row>
@@ -10045,9 +11356,12 @@
         <v>0.03824</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>0.03824</v>
+        <v>0.0384</v>
       </c>
       <c r="F437" s="1" t="n">
+        <v>0.0384</v>
+      </c>
+      <c r="G437" s="1" t="n">
         <v>0.03814</v>
       </c>
     </row>
@@ -10067,10 +11381,13 @@
         <v>0.02455</v>
       </c>
       <c r="E438" s="1" t="n">
+        <v>0.02444</v>
+      </c>
+      <c r="F438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="F438" s="1" t="n">
-        <v>0.02452</v>
+      <c r="G438" s="1" t="n">
+        <v>0.02444</v>
       </c>
     </row>
     <row r="439">
@@ -10089,10 +11406,13 @@
         <v>0.04406</v>
       </c>
       <c r="E439" s="1" t="n">
+        <v>0.04405</v>
+      </c>
+      <c r="F439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="F439" s="1" t="n">
-        <v>0.04406</v>
+      <c r="G439" s="1" t="n">
+        <v>0.04405</v>
       </c>
     </row>
     <row r="440">
@@ -10111,9 +11431,12 @@
         <v>0.0005221</v>
       </c>
       <c r="E440" s="1" t="n">
+        <v>0.0005253</v>
+      </c>
+      <c r="F440" s="1" t="n">
         <v>0.0005258</v>
       </c>
-      <c r="F440" s="1" t="n">
+      <c r="G440" s="1" t="n">
         <v>0.0005221</v>
       </c>
     </row>
@@ -10136,6 +11459,9 @@
         <v>0.04428</v>
       </c>
       <c r="F441" s="1" t="n">
+        <v>0.04428</v>
+      </c>
+      <c r="G441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -10155,9 +11481,12 @@
         <v>0.000413</v>
       </c>
       <c r="E442" s="1" t="n">
+        <v>0.000415</v>
+      </c>
+      <c r="F442" s="1" t="n">
         <v>0.000416</v>
       </c>
-      <c r="F442" s="1" t="n">
+      <c r="G442" s="1" t="n">
         <v>0.000413</v>
       </c>
     </row>
@@ -10177,9 +11506,12 @@
         <v>0.09672</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>0.09789</v>
+        <v>0.09826</v>
       </c>
       <c r="F443" s="1" t="n">
+        <v>0.09826</v>
+      </c>
+      <c r="G443" s="1" t="n">
         <v>0.09672</v>
       </c>
     </row>
@@ -10199,9 +11531,12 @@
         <v>2.289</v>
       </c>
       <c r="E444" s="1" t="n">
+        <v>2.307</v>
+      </c>
+      <c r="F444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="F444" s="1" t="n">
+      <c r="G444" s="1" t="n">
         <v>2.289</v>
       </c>
     </row>
@@ -10221,9 +11556,12 @@
         <v>0.268</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>0.268</v>
+        <v>0.2695</v>
       </c>
       <c r="F445" s="1" t="n">
+        <v>0.2695</v>
+      </c>
+      <c r="G445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -10243,9 +11581,12 @@
         <v>0.0007521</v>
       </c>
       <c r="E446" s="1" t="n">
+        <v>0.000755</v>
+      </c>
+      <c r="F446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="F446" s="1" t="n">
+      <c r="G446" s="1" t="n">
         <v>0.0007521</v>
       </c>
     </row>
@@ -10268,6 +11609,9 @@
         <v>0.03904</v>
       </c>
       <c r="F447" s="1" t="n">
+        <v>0.03904</v>
+      </c>
+      <c r="G447" s="1" t="n">
         <v>0.03873</v>
       </c>
     </row>
@@ -10287,9 +11631,12 @@
         <v>0.1763</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>0.1763</v>
+        <v>0.1771</v>
       </c>
       <c r="F448" s="1" t="n">
+        <v>0.1771</v>
+      </c>
+      <c r="G448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -10309,9 +11656,12 @@
         <v>0.0427</v>
       </c>
       <c r="E449" s="1" t="n">
+        <v>0.04283</v>
+      </c>
+      <c r="F449" s="1" t="n">
         <v>0.04301</v>
       </c>
-      <c r="F449" s="1" t="n">
+      <c r="G449" s="1" t="n">
         <v>0.0427</v>
       </c>
     </row>
@@ -10334,6 +11684,9 @@
         <v>0.0001654</v>
       </c>
       <c r="F450" s="1" t="n">
+        <v>0.0001654</v>
+      </c>
+      <c r="G450" s="1" t="n">
         <v>0.0001641</v>
       </c>
     </row>
@@ -10353,9 +11706,12 @@
         <v>0.0376</v>
       </c>
       <c r="E451" s="1" t="n">
+        <v>0.03764</v>
+      </c>
+      <c r="F451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="F451" s="1" t="n">
+      <c r="G451" s="1" t="n">
         <v>0.0376</v>
       </c>
     </row>
@@ -10375,9 +11731,12 @@
         <v>0.009939999999999999</v>
       </c>
       <c r="E452" s="1" t="n">
+        <v>0.009990000000000001</v>
+      </c>
+      <c r="F452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="F452" s="1" t="n">
+      <c r="G452" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
     </row>
@@ -10397,9 +11756,12 @@
         <v>0.06793</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>0.06798999999999999</v>
+        <v>0.06805</v>
       </c>
       <c r="F453" s="1" t="n">
+        <v>0.06805</v>
+      </c>
+      <c r="G453" s="1" t="n">
         <v>0.06793</v>
       </c>
     </row>
@@ -10419,9 +11781,12 @@
         <v>0.007541</v>
       </c>
       <c r="E454" s="1" t="n">
+        <v>0.007608</v>
+      </c>
+      <c r="F454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="F454" s="1" t="n">
+      <c r="G454" s="1" t="n">
         <v>0.007541</v>
       </c>
     </row>
@@ -10441,9 +11806,12 @@
         <v>0.003362</v>
       </c>
       <c r="E455" s="1" t="n">
+        <v>0.003376</v>
+      </c>
+      <c r="F455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="F455" s="1" t="n">
+      <c r="G455" s="1" t="n">
         <v>0.003362</v>
       </c>
     </row>
@@ -10463,9 +11831,12 @@
         <v>0.001854</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>0.001864</v>
+        <v>0.001874</v>
       </c>
       <c r="F456" s="1" t="n">
+        <v>0.001874</v>
+      </c>
+      <c r="G456" s="1" t="n">
         <v>0.001854</v>
       </c>
     </row>
@@ -10485,9 +11856,12 @@
         <v>0.0001758</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>0.0001763</v>
+        <v>0.0001767</v>
       </c>
       <c r="F457" s="1" t="n">
+        <v>0.0001767</v>
+      </c>
+      <c r="G457" s="1" t="n">
         <v>0.0001758</v>
       </c>
     </row>
@@ -10507,9 +11881,12 @@
         <v>0.0003874</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>0.0003878</v>
+        <v>0.0003898</v>
       </c>
       <c r="F458" s="1" t="n">
+        <v>0.0003898</v>
+      </c>
+      <c r="G458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -10529,9 +11906,12 @@
         <v>0.01391</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>0.01406</v>
+        <v>0.01409</v>
       </c>
       <c r="F459" s="1" t="n">
+        <v>0.01409</v>
+      </c>
+      <c r="G459" s="1" t="n">
         <v>0.01391</v>
       </c>
     </row>
@@ -10551,9 +11931,12 @@
         <v>0.04533</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>0.04533</v>
+        <v>0.04556</v>
       </c>
       <c r="F460" s="1" t="n">
+        <v>0.04556</v>
+      </c>
+      <c r="G460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -10573,9 +11956,12 @@
         <v>0.2822</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>0.283</v>
+        <v>0.2839</v>
       </c>
       <c r="F461" s="1" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="G461" s="1" t="n">
         <v>0.2822</v>
       </c>
     </row>
@@ -10595,9 +11981,12 @@
         <v>0.006244</v>
       </c>
       <c r="E462" s="1" t="n">
+        <v>0.006278</v>
+      </c>
+      <c r="F462" s="1" t="n">
         <v>0.006279</v>
       </c>
-      <c r="F462" s="1" t="n">
+      <c r="G462" s="1" t="n">
         <v>0.00622</v>
       </c>
     </row>
@@ -10617,9 +12006,12 @@
         <v>0.00704</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>0.007056</v>
+        <v>0.007088</v>
       </c>
       <c r="F463" s="1" t="n">
+        <v>0.007088</v>
+      </c>
+      <c r="G463" s="1" t="n">
         <v>0.00704</v>
       </c>
     </row>
@@ -10639,9 +12031,12 @@
         <v>0.2878</v>
       </c>
       <c r="E464" s="1" t="n">
+        <v>0.2876</v>
+      </c>
+      <c r="F464" s="1" t="n">
         <v>0.2878</v>
       </c>
-      <c r="F464" s="1" t="n">
+      <c r="G464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -10664,6 +12059,9 @@
         <v>0.08134</v>
       </c>
       <c r="F465" s="1" t="n">
+        <v>0.08134</v>
+      </c>
+      <c r="G465" s="1" t="n">
         <v>0.08078</v>
       </c>
     </row>
@@ -10683,10 +12081,13 @@
         <v>0.6327</v>
       </c>
       <c r="E466" s="1" t="n">
+        <v>0.6318</v>
+      </c>
+      <c r="F466" s="1" t="n">
         <v>0.6343</v>
       </c>
-      <c r="F466" s="1" t="n">
-        <v>0.6327</v>
+      <c r="G466" s="1" t="n">
+        <v>0.6318</v>
       </c>
     </row>
     <row r="467">
@@ -10705,9 +12106,12 @@
         <v>0.01477</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>0.01477</v>
+        <v>0.01486</v>
       </c>
       <c r="F467" s="1" t="n">
+        <v>0.01486</v>
+      </c>
+      <c r="G467" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -10727,9 +12131,12 @@
         <v>0.03448</v>
       </c>
       <c r="E468" s="1" t="n">
+        <v>0.03455</v>
+      </c>
+      <c r="F468" s="1" t="n">
         <v>0.03462</v>
       </c>
-      <c r="F468" s="1" t="n">
+      <c r="G468" s="1" t="n">
         <v>0.03448</v>
       </c>
     </row>
@@ -10752,6 +12159,9 @@
         <v>0.1652</v>
       </c>
       <c r="F469" s="1" t="n">
+        <v>0.1652</v>
+      </c>
+      <c r="G469" s="1" t="n">
         <v>0.1644</v>
       </c>
     </row>
@@ -10771,9 +12181,12 @@
         <v>0.4123</v>
       </c>
       <c r="E470" s="1" t="n">
+        <v>0.4132</v>
+      </c>
+      <c r="F470" s="1" t="n">
         <v>0.4139</v>
       </c>
-      <c r="F470" s="1" t="n">
+      <c r="G470" s="1" t="n">
         <v>0.4123</v>
       </c>
     </row>
@@ -10793,9 +12206,12 @@
         <v>0.06975000000000001</v>
       </c>
       <c r="E471" s="1" t="n">
+        <v>0.07012</v>
+      </c>
+      <c r="F471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="F471" s="1" t="n">
+      <c r="G471" s="1" t="n">
         <v>0.06975000000000001</v>
       </c>
     </row>
@@ -10818,6 +12234,9 @@
         <v>0.06773999999999999</v>
       </c>
       <c r="F472" s="1" t="n">
+        <v>0.06773999999999999</v>
+      </c>
+      <c r="G472" s="1" t="n">
         <v>0.06688</v>
       </c>
     </row>
@@ -10840,6 +12259,9 @@
         <v>0.01647</v>
       </c>
       <c r="F473" s="1" t="n">
+        <v>0.01647</v>
+      </c>
+      <c r="G473" s="1" t="n">
         <v>0.0164</v>
       </c>
     </row>
@@ -10859,9 +12281,12 @@
         <v>0.2101</v>
       </c>
       <c r="E474" s="1" t="n">
+        <v>0.2106</v>
+      </c>
+      <c r="F474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="F474" s="1" t="n">
+      <c r="G474" s="1" t="n">
         <v>0.2101</v>
       </c>
     </row>
@@ -10881,9 +12306,12 @@
         <v>0.04202</v>
       </c>
       <c r="E475" s="1" t="n">
+        <v>0.04232</v>
+      </c>
+      <c r="F475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="F475" s="1" t="n">
+      <c r="G475" s="1" t="n">
         <v>0.04202</v>
       </c>
     </row>
@@ -10903,9 +12331,12 @@
         <v>1.57</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>1.572</v>
+        <v>1.578</v>
       </c>
       <c r="F476" s="1" t="n">
+        <v>1.578</v>
+      </c>
+      <c r="G476" s="1" t="n">
         <v>1.57</v>
       </c>
     </row>
@@ -10925,9 +12356,12 @@
         <v>0.1012</v>
       </c>
       <c r="E477" s="1" t="n">
+        <v>0.1014</v>
+      </c>
+      <c r="F477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="F477" s="1" t="n">
+      <c r="G477" s="1" t="n">
         <v>0.1012</v>
       </c>
     </row>
@@ -10947,9 +12381,12 @@
         <v>0.001155</v>
       </c>
       <c r="E478" s="1" t="n">
+        <v>0.001161</v>
+      </c>
+      <c r="F478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="F478" s="1" t="n">
+      <c r="G478" s="1" t="n">
         <v>0.001155</v>
       </c>
     </row>
@@ -10969,9 +12406,12 @@
         <v>0.1462</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>0.1473</v>
+        <v>0.148</v>
       </c>
       <c r="F479" s="1" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="G479" s="1" t="n">
         <v>0.1462</v>
       </c>
     </row>
@@ -10991,9 +12431,12 @@
         <v>0.001722</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>0.00173</v>
+        <v>0.001734</v>
       </c>
       <c r="F480" s="1" t="n">
+        <v>0.001734</v>
+      </c>
+      <c r="G480" s="1" t="n">
         <v>0.001722</v>
       </c>
     </row>
@@ -11013,9 +12456,12 @@
         <v>0.915</v>
       </c>
       <c r="E481" s="1" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="F481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="F481" s="1" t="n">
+      <c r="G481" s="1" t="n">
         <v>0.915</v>
       </c>
     </row>
@@ -11035,9 +12481,12 @@
         <v>0.13463</v>
       </c>
       <c r="E482" s="1" t="n">
+        <v>0.13479</v>
+      </c>
+      <c r="F482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="F482" s="1" t="n">
+      <c r="G482" s="1" t="n">
         <v>0.13437</v>
       </c>
     </row>
@@ -11057,9 +12506,12 @@
         <v>0.04053</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>0.04056</v>
+        <v>0.04062</v>
       </c>
       <c r="F483" s="1" t="n">
+        <v>0.04062</v>
+      </c>
+      <c r="G483" s="1" t="n">
         <v>0.04048</v>
       </c>
     </row>
@@ -11079,9 +12531,12 @@
         <v>0.3109</v>
       </c>
       <c r="E484" s="1" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="F484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="F484" s="1" t="n">
+      <c r="G484" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -11101,9 +12556,12 @@
         <v>0.0566</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>0.05671</v>
+        <v>0.057</v>
       </c>
       <c r="F485" s="1" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="G485" s="1" t="n">
         <v>0.05633</v>
       </c>
     </row>
@@ -11123,9 +12581,12 @@
         <v>0.001569</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>0.001572</v>
+        <v>0.001577</v>
       </c>
       <c r="F486" s="1" t="n">
+        <v>0.001577</v>
+      </c>
+      <c r="G486" s="1" t="n">
         <v>0.001569</v>
       </c>
     </row>
@@ -11145,9 +12606,12 @@
         <v>0.06716</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>0.06738</v>
+        <v>0.0675</v>
       </c>
       <c r="F487" s="1" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="G487" s="1" t="n">
         <v>0.06716</v>
       </c>
     </row>
@@ -11167,9 +12631,12 @@
         <v>0.1936</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>0.1942</v>
+        <v>0.195</v>
       </c>
       <c r="F488" s="1" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="G488" s="1" t="n">
         <v>0.1936</v>
       </c>
     </row>
@@ -11189,9 +12656,12 @@
         <v>0.04804</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>0.04817</v>
+        <v>0.04837</v>
       </c>
       <c r="F489" s="1" t="n">
+        <v>0.04837</v>
+      </c>
+      <c r="G489" s="1" t="n">
         <v>0.04804</v>
       </c>
     </row>
@@ -11211,9 +12681,12 @@
         <v>0.139</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>0.1395</v>
+        <v>0.1397</v>
       </c>
       <c r="F490" s="1" t="n">
+        <v>0.1397</v>
+      </c>
+      <c r="G490" s="1" t="n">
         <v>0.139</v>
       </c>
     </row>
@@ -11233,9 +12706,12 @@
         <v>0.02243</v>
       </c>
       <c r="E491" s="1" t="n">
+        <v>0.0227</v>
+      </c>
+      <c r="F491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="F491" s="1" t="n">
+      <c r="G491" s="1" t="n">
         <v>0.02243</v>
       </c>
     </row>
@@ -11255,9 +12731,12 @@
         <v>0.007825</v>
       </c>
       <c r="E492" s="1" t="n">
+        <v>0.007886000000000001</v>
+      </c>
+      <c r="F492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="F492" s="1" t="n">
+      <c r="G492" s="1" t="n">
         <v>0.007825</v>
       </c>
     </row>
@@ -11277,9 +12756,12 @@
         <v>0.0005952</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>0.0005967</v>
+        <v>0.0005984</v>
       </c>
       <c r="F493" s="1" t="n">
+        <v>0.0005984</v>
+      </c>
+      <c r="G493" s="1" t="n">
         <v>0.0005952</v>
       </c>
     </row>
@@ -11299,9 +12781,12 @@
         <v>2.999</v>
       </c>
       <c r="E494" s="1" t="n">
+        <v>3.033</v>
+      </c>
+      <c r="F494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="F494" s="1" t="n">
+      <c r="G494" s="1" t="n">
         <v>2.999</v>
       </c>
     </row>
@@ -11321,9 +12806,12 @@
         <v>0.05085</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>0.05103</v>
+        <v>0.05131</v>
       </c>
       <c r="F495" s="1" t="n">
+        <v>0.05131</v>
+      </c>
+      <c r="G495" s="1" t="n">
         <v>0.05085</v>
       </c>
     </row>
@@ -11343,9 +12831,12 @@
         <v>0.006839</v>
       </c>
       <c r="E496" s="1" t="n">
+        <v>0.006864</v>
+      </c>
+      <c r="F496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="F496" s="1" t="n">
+      <c r="G496" s="1" t="n">
         <v>0.006839</v>
       </c>
     </row>
@@ -11365,9 +12856,12 @@
         <v>1.299</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>1.302</v>
+        <v>1.31</v>
       </c>
       <c r="F497" s="1" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G497" s="1" t="n">
         <v>1.299</v>
       </c>
     </row>
@@ -11387,9 +12881,12 @@
         <v>0.03999</v>
       </c>
       <c r="E498" s="1" t="n">
+        <v>0.04005</v>
+      </c>
+      <c r="F498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="F498" s="1" t="n">
+      <c r="G498" s="1" t="n">
         <v>0.03999</v>
       </c>
     </row>
@@ -11409,9 +12906,12 @@
         <v>0.04186</v>
       </c>
       <c r="E499" s="1" t="n">
+        <v>0.04196</v>
+      </c>
+      <c r="F499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="F499" s="1" t="n">
+      <c r="G499" s="1" t="n">
         <v>0.04186</v>
       </c>
     </row>
@@ -11431,9 +12931,12 @@
         <v>0.00536</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>0.0054</v>
+        <v>0.00541</v>
       </c>
       <c r="F500" s="1" t="n">
+        <v>0.00541</v>
+      </c>
+      <c r="G500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -11453,9 +12956,12 @@
         <v>0.03625</v>
       </c>
       <c r="E501" s="1" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="F501" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="F501" s="1" t="n">
+      <c r="G501" s="1" t="n">
         <v>0.03625</v>
       </c>
     </row>
@@ -11475,9 +12981,12 @@
         <v>0.07324</v>
       </c>
       <c r="E502" s="1" t="n">
+        <v>0.0733</v>
+      </c>
+      <c r="F502" s="1" t="n">
         <v>0.07335999999999999</v>
       </c>
-      <c r="F502" s="1" t="n">
+      <c r="G502" s="1" t="n">
         <v>0.07321</v>
       </c>
     </row>
@@ -11497,9 +13006,12 @@
         <v>0.0007499</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>0.0007543</v>
+        <v>0.0007545</v>
       </c>
       <c r="F503" s="1" t="n">
+        <v>0.0007545</v>
+      </c>
+      <c r="G503" s="1" t="n">
         <v>0.0007499</v>
       </c>
     </row>
@@ -11519,9 +13031,12 @@
         <v>0.015945</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>0.015956</v>
+        <v>0.016003</v>
       </c>
       <c r="F504" s="1" t="n">
+        <v>0.016003</v>
+      </c>
+      <c r="G504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -11541,9 +13056,12 @@
         <v>0.00709</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>0.00709</v>
+        <v>0.00713</v>
       </c>
       <c r="F505" s="1" t="n">
+        <v>0.00713</v>
+      </c>
+      <c r="G505" s="1" t="n">
         <v>0.00709</v>
       </c>
     </row>
@@ -11563,11 +13081,14 @@
         <v>0.0257</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>0.0257</v>
+        <v>0.0256</v>
       </c>
       <c r="F506" s="1" t="n">
         <v>0.0257</v>
       </c>
+      <c r="G506" s="1" t="n">
+        <v>0.0256</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -11585,9 +13106,12 @@
         <v>0.001343</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>0.001351</v>
+        <v>0.001354</v>
       </c>
       <c r="F507" s="1" t="n">
+        <v>0.001354</v>
+      </c>
+      <c r="G507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -11607,9 +13131,12 @@
         <v>0.2821</v>
       </c>
       <c r="E508" s="1" t="n">
+        <v>0.2831</v>
+      </c>
+      <c r="F508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="F508" s="1" t="n">
+      <c r="G508" s="1" t="n">
         <v>0.2821</v>
       </c>
     </row>
@@ -11629,9 +13156,12 @@
         <v>0.1323</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>0.1324</v>
+        <v>0.133</v>
       </c>
       <c r="F509" s="1" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="G509" s="1" t="n">
         <v>0.1323</v>
       </c>
     </row>
@@ -11651,9 +13181,12 @@
         <v>0.04934</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>0.04949</v>
+        <v>0.04967</v>
       </c>
       <c r="F510" s="1" t="n">
+        <v>0.04967</v>
+      </c>
+      <c r="G510" s="1" t="n">
         <v>0.04932</v>
       </c>
     </row>
@@ -11676,6 +13209,9 @@
         <v>0.00277</v>
       </c>
       <c r="F511" s="1" t="n">
+        <v>0.00277</v>
+      </c>
+      <c r="G511" s="1" t="n">
         <v>0.00275</v>
       </c>
     </row>
@@ -11695,9 +13231,12 @@
         <v>0.015351</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>0.015434</v>
+        <v>0.015448</v>
       </c>
       <c r="F512" s="1" t="n">
+        <v>0.015448</v>
+      </c>
+      <c r="G512" s="1" t="n">
         <v>0.015351</v>
       </c>
     </row>
@@ -11717,9 +13256,12 @@
         <v>0.6933</v>
       </c>
       <c r="E513" s="1" t="n">
+        <v>0.6943</v>
+      </c>
+      <c r="F513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="F513" s="1" t="n">
+      <c r="G513" s="1" t="n">
         <v>0.6933</v>
       </c>
     </row>
@@ -11739,9 +13281,12 @@
         <v>0.004545</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>0.004561</v>
+        <v>0.004584</v>
       </c>
       <c r="F514" s="1" t="n">
+        <v>0.004584</v>
+      </c>
+      <c r="G514" s="1" t="n">
         <v>0.004534</v>
       </c>
     </row>
@@ -11761,9 +13306,12 @@
         <v>0.005037</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>0.005048</v>
+        <v>0.005066</v>
       </c>
       <c r="F515" s="1" t="n">
+        <v>0.005066</v>
+      </c>
+      <c r="G515" s="1" t="n">
         <v>0.005037</v>
       </c>
     </row>
@@ -11783,9 +13331,12 @@
         <v>0.06353</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>0.06385</v>
+        <v>0.06394</v>
       </c>
       <c r="F516" s="1" t="n">
+        <v>0.06394</v>
+      </c>
+      <c r="G516" s="1" t="n">
         <v>0.06353</v>
       </c>
     </row>
@@ -11805,9 +13356,12 @@
         <v>0.06438000000000001</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>0.06438000000000001</v>
+        <v>0.06566</v>
       </c>
       <c r="F517" s="1" t="n">
+        <v>0.06566</v>
+      </c>
+      <c r="G517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -11827,9 +13381,12 @@
         <v>0.0121</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>0.01216</v>
+        <v>0.01219</v>
       </c>
       <c r="F518" s="1" t="n">
+        <v>0.01219</v>
+      </c>
+      <c r="G518" s="1" t="n">
         <v>0.0121</v>
       </c>
     </row>
@@ -11849,9 +13406,12 @@
         <v>0.04743</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>0.04794</v>
+        <v>0.04795</v>
       </c>
       <c r="F519" s="1" t="n">
+        <v>0.04795</v>
+      </c>
+      <c r="G519" s="1" t="n">
         <v>0.04743</v>
       </c>
     </row>
@@ -11871,9 +13431,12 @@
         <v>0.04384</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>0.04396</v>
+        <v>0.04406</v>
       </c>
       <c r="F520" s="1" t="n">
+        <v>0.04406</v>
+      </c>
+      <c r="G520" s="1" t="n">
         <v>0.04384</v>
       </c>
     </row>
@@ -11893,9 +13456,12 @@
         <v>0.008552000000000001</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>0.008560999999999999</v>
+        <v>0.008609</v>
       </c>
       <c r="F521" s="1" t="n">
+        <v>0.008609</v>
+      </c>
+      <c r="G521" s="1" t="n">
         <v>0.008552000000000001</v>
       </c>
     </row>
@@ -11915,9 +13481,12 @@
         <v>0.0893</v>
       </c>
       <c r="E522" s="1" t="n">
+        <v>0.08933000000000001</v>
+      </c>
+      <c r="F522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="F522" s="1" t="n">
+      <c r="G522" s="1" t="n">
         <v>0.0893</v>
       </c>
     </row>
@@ -11937,9 +13506,12 @@
         <v>0.006462</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>0.006466</v>
+        <v>0.006492</v>
       </c>
       <c r="F523" s="1" t="n">
+        <v>0.006492</v>
+      </c>
+      <c r="G523" s="1" t="n">
         <v>0.00646</v>
       </c>
     </row>
@@ -11959,9 +13531,12 @@
         <v>0.01662</v>
       </c>
       <c r="E524" s="1" t="n">
+        <v>0.01668</v>
+      </c>
+      <c r="F524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="F524" s="1" t="n">
+      <c r="G524" s="1" t="n">
         <v>0.01662</v>
       </c>
     </row>
@@ -11981,9 +13556,12 @@
         <v>0.0181</v>
       </c>
       <c r="E525" s="1" t="n">
+        <v>0.01809</v>
+      </c>
+      <c r="F525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="F525" s="1" t="n">
+      <c r="G525" s="1" t="n">
         <v>0.01808</v>
       </c>
     </row>
@@ -12003,9 +13581,12 @@
         <v>0.07918</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>0.07938000000000001</v>
+        <v>0.07968</v>
       </c>
       <c r="F526" s="1" t="n">
+        <v>0.07968</v>
+      </c>
+      <c r="G526" s="1" t="n">
         <v>0.07917</v>
       </c>
     </row>
@@ -12025,9 +13606,12 @@
         <v>0.01634</v>
       </c>
       <c r="E527" s="1" t="n">
+        <v>0.01638</v>
+      </c>
+      <c r="F527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="F527" s="1" t="n">
+      <c r="G527" s="1" t="n">
         <v>0.01634</v>
       </c>
     </row>
@@ -12047,9 +13631,12 @@
         <v>0.004164</v>
       </c>
       <c r="E528" s="1" t="n">
+        <v>0.004177</v>
+      </c>
+      <c r="F528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="F528" s="1" t="n">
+      <c r="G528" s="1" t="n">
         <v>0.004164</v>
       </c>
     </row>
@@ -12069,9 +13656,12 @@
         <v>0.003698</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>0.003713</v>
+        <v>0.003753</v>
       </c>
       <c r="F529" s="1" t="n">
+        <v>0.003753</v>
+      </c>
+      <c r="G529" s="1" t="n">
         <v>0.003698</v>
       </c>
     </row>
@@ -12091,9 +13681,12 @@
         <v>1.316</v>
       </c>
       <c r="E530" s="1" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="F530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="F530" s="1" t="n">
+      <c r="G530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -12113,9 +13706,12 @@
         <v>0.4912</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>0.4922</v>
+        <v>0.4932</v>
       </c>
       <c r="F531" s="1" t="n">
+        <v>0.4932</v>
+      </c>
+      <c r="G531" s="1" t="n">
         <v>0.4912</v>
       </c>
     </row>
@@ -12135,9 +13731,12 @@
         <v>0.03071</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>0.03071</v>
+        <v>0.03087</v>
       </c>
       <c r="F532" s="1" t="n">
+        <v>0.03087</v>
+      </c>
+      <c r="G532" s="1" t="n">
         <v>0.03058</v>
       </c>
     </row>
@@ -12157,9 +13756,12 @@
         <v>0.1532</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>0.1535</v>
+        <v>0.154</v>
       </c>
       <c r="F533" s="1" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="G533" s="1" t="n">
         <v>0.1532</v>
       </c>
     </row>
@@ -12179,9 +13781,12 @@
         <v>0.05388</v>
       </c>
       <c r="E534" s="1" t="n">
+        <v>0.05418</v>
+      </c>
+      <c r="F534" s="1" t="n">
         <v>0.05421</v>
       </c>
-      <c r="F534" s="1" t="n">
+      <c r="G534" s="1" t="n">
         <v>0.05388</v>
       </c>
     </row>
@@ -12201,9 +13806,12 @@
         <v>0.01501</v>
       </c>
       <c r="E535" s="1" t="n">
+        <v>0.01515</v>
+      </c>
+      <c r="F535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="F535" s="1" t="n">
+      <c r="G535" s="1" t="n">
         <v>0.01501</v>
       </c>
     </row>
@@ -12223,9 +13831,12 @@
         <v>0.0585</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>0.0585</v>
+        <v>0.05863</v>
       </c>
       <c r="F536" s="1" t="n">
+        <v>0.05863</v>
+      </c>
+      <c r="G536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -12245,9 +13856,12 @@
         <v>0.05497</v>
       </c>
       <c r="E537" s="1" t="n">
+        <v>0.05499</v>
+      </c>
+      <c r="F537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="F537" s="1" t="n">
+      <c r="G537" s="1" t="n">
         <v>0.05497</v>
       </c>
     </row>
@@ -12267,9 +13881,12 @@
         <v>0.1067</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>0.1067</v>
+        <v>0.1071</v>
       </c>
       <c r="F538" s="1" t="n">
+        <v>0.1071</v>
+      </c>
+      <c r="G538" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -12289,9 +13906,12 @@
         <v>0.01284</v>
       </c>
       <c r="E539" s="1" t="n">
+        <v>0.01293</v>
+      </c>
+      <c r="F539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="F539" s="1" t="n">
+      <c r="G539" s="1" t="n">
         <v>0.01284</v>
       </c>
     </row>
@@ -12311,9 +13931,12 @@
         <v>0.175</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>0.1753</v>
+        <v>0.1765</v>
       </c>
       <c r="F540" s="1" t="n">
+        <v>0.1765</v>
+      </c>
+      <c r="G540" s="1" t="n">
         <v>0.175</v>
       </c>
     </row>
@@ -12333,9 +13956,12 @@
         <v>0.1236</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>0.1236</v>
+        <v>0.1238</v>
       </c>
       <c r="F541" s="1" t="n">
+        <v>0.1238</v>
+      </c>
+      <c r="G541" s="1" t="n">
         <v>0.1231</v>
       </c>
     </row>
@@ -12355,9 +13981,12 @@
         <v>0.02489</v>
       </c>
       <c r="E542" s="1" t="n">
+        <v>0.02506</v>
+      </c>
+      <c r="F542" s="1" t="n">
         <v>0.02509</v>
       </c>
-      <c r="F542" s="1" t="n">
+      <c r="G542" s="1" t="n">
         <v>0.02489</v>
       </c>
     </row>
@@ -12377,9 +14006,12 @@
         <v>0.05861</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>0.05891</v>
+        <v>0.05892</v>
       </c>
       <c r="F543" s="1" t="n">
+        <v>0.05892</v>
+      </c>
+      <c r="G543" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G543"/>
+  <dimension ref="A1:H543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -424,8 +424,9 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -456,10 +457,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>price_01:00</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -484,9 +490,12 @@
         <v>71796.5</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>71818.39999999999</v>
+        <v>71830.3</v>
       </c>
       <c r="G2" s="1" t="n">
+        <v>71830.3</v>
+      </c>
+      <c r="H2" s="1" t="n">
         <v>71323.7</v>
       </c>
     </row>
@@ -509,9 +518,12 @@
         <v>2131.78</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>2131.78</v>
+        <v>2132.9</v>
       </c>
       <c r="G3" s="1" t="n">
+        <v>2132.9</v>
+      </c>
+      <c r="H3" s="1" t="n">
         <v>2118.6</v>
       </c>
     </row>
@@ -534,9 +546,12 @@
         <v>89.58</v>
       </c>
       <c r="F4" s="1" t="n">
+        <v>89.55</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>89.59</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="H4" s="1" t="n">
         <v>89.23</v>
       </c>
     </row>
@@ -559,9 +574,12 @@
         <v>3.887</v>
       </c>
       <c r="F5" s="1" t="n">
+        <v>3.861</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>3.887</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="H5" s="1" t="n">
         <v>3.77</v>
       </c>
     </row>
@@ -584,9 +602,12 @@
         <v>1.4097</v>
       </c>
       <c r="F6" s="1" t="n">
+        <v>1.4091</v>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="H6" s="1" t="n">
         <v>1.4035</v>
       </c>
     </row>
@@ -609,9 +630,12 @@
         <v>0.09811</v>
       </c>
       <c r="F7" s="1" t="n">
+        <v>0.09765</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="H7" s="1" t="n">
         <v>0.09765</v>
       </c>
     </row>
@@ -634,9 +658,12 @@
         <v>0.014341</v>
       </c>
       <c r="F8" s="1" t="n">
+        <v>0.014278</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>0.014568</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="H8" s="1" t="n">
         <v>0.014158</v>
       </c>
     </row>
@@ -659,9 +686,12 @@
         <v>663.25</v>
       </c>
       <c r="F9" s="1" t="n">
+        <v>661.92</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="H9" s="1" t="n">
         <v>659.95</v>
       </c>
     </row>
@@ -684,9 +714,12 @@
         <v>19.036</v>
       </c>
       <c r="F10" s="1" t="n">
+        <v>19.278</v>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>19.415</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="H10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -709,9 +742,12 @@
         <v>0.0034884</v>
       </c>
       <c r="F11" s="1" t="n">
+        <v>0.0034773</v>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="H11" s="1" t="n">
         <v>0.0034668</v>
       </c>
     </row>
@@ -734,9 +770,12 @@
         <v>36.352</v>
       </c>
       <c r="F12" s="1" t="n">
+        <v>36.262</v>
+      </c>
+      <c r="G12" s="1" t="n">
         <v>36.352</v>
       </c>
-      <c r="G12" s="1" t="n">
+      <c r="H12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -759,10 +798,13 @@
         <v>214.83</v>
       </c>
       <c r="F13" s="1" t="n">
+        <v>212.79</v>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="G13" s="1" t="n">
-        <v>213.2</v>
+      <c r="H13" s="1" t="n">
+        <v>212.79</v>
       </c>
     </row>
     <row r="14">
@@ -784,9 +826,12 @@
         <v>0.0011374</v>
       </c>
       <c r="F14" s="1" t="n">
+        <v>0.0011384</v>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="G14" s="1" t="n">
+      <c r="H14" s="1" t="n">
         <v>0.0011277</v>
       </c>
     </row>
@@ -809,9 +854,12 @@
         <v>0.28887</v>
       </c>
       <c r="F15" s="1" t="n">
+        <v>0.28796</v>
+      </c>
+      <c r="G15" s="1" t="n">
         <v>0.29276</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="H15" s="1" t="n">
         <v>0.28578</v>
       </c>
     </row>
@@ -834,9 +882,12 @@
         <v>236.4</v>
       </c>
       <c r="F16" s="1" t="n">
+        <v>235.84</v>
+      </c>
+      <c r="G16" s="1" t="n">
         <v>236.4</v>
       </c>
-      <c r="G16" s="1" t="n">
+      <c r="H16" s="1" t="n">
         <v>230.3</v>
       </c>
     </row>
@@ -859,10 +910,13 @@
         <v>1.0151</v>
       </c>
       <c r="F17" s="1" t="n">
+        <v>1.0116</v>
+      </c>
+      <c r="G17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="G17" s="1" t="n">
-        <v>1.012</v>
+      <c r="H17" s="1" t="n">
+        <v>1.0116</v>
       </c>
     </row>
     <row r="18">
@@ -884,9 +938,12 @@
         <v>0.2725</v>
       </c>
       <c r="F18" s="1" t="n">
+        <v>0.2718</v>
+      </c>
+      <c r="G18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="G18" s="1" t="n">
+      <c r="H18" s="1" t="n">
         <v>0.2713</v>
       </c>
     </row>
@@ -909,9 +966,12 @@
         <v>9.906000000000001</v>
       </c>
       <c r="F19" s="1" t="n">
+        <v>9.891999999999999</v>
+      </c>
+      <c r="G19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="G19" s="1" t="n">
+      <c r="H19" s="1" t="n">
         <v>9.859</v>
       </c>
     </row>
@@ -934,9 +994,12 @@
         <v>5044.75</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>5044.75</v>
+        <v>5047.38</v>
       </c>
       <c r="G20" s="1" t="n">
+        <v>5047.38</v>
+      </c>
+      <c r="H20" s="1" t="n">
         <v>5033.31</v>
       </c>
     </row>
@@ -959,9 +1022,12 @@
         <v>464.61</v>
       </c>
       <c r="F21" s="1" t="n">
+        <v>464.39</v>
+      </c>
+      <c r="G21" s="1" t="n">
         <v>464.61</v>
       </c>
-      <c r="G21" s="1" t="n">
+      <c r="H21" s="1" t="n">
         <v>462.57</v>
       </c>
     </row>
@@ -984,9 +1050,12 @@
         <v>1.4544</v>
       </c>
       <c r="F22" s="1" t="n">
+        <v>1.4489</v>
+      </c>
+      <c r="G22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="G22" s="1" t="n">
+      <c r="H22" s="1" t="n">
         <v>1.4185</v>
       </c>
     </row>
@@ -1009,10 +1078,13 @@
         <v>1.1304</v>
       </c>
       <c r="F23" s="1" t="n">
+        <v>1.1257</v>
+      </c>
+      <c r="G23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="G23" s="1" t="n">
-        <v>1.1298</v>
+      <c r="H23" s="1" t="n">
+        <v>1.1257</v>
       </c>
     </row>
     <row r="24">
@@ -1034,9 +1106,12 @@
         <v>1.363</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>1.363</v>
+        <v>1.366</v>
       </c>
       <c r="G24" s="1" t="n">
+        <v>1.366</v>
+      </c>
+      <c r="H24" s="1" t="n">
         <v>1.351</v>
       </c>
     </row>
@@ -1059,9 +1134,12 @@
         <v>9.297000000000001</v>
       </c>
       <c r="F25" s="1" t="n">
+        <v>9.282</v>
+      </c>
+      <c r="G25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="G25" s="1" t="n">
+      <c r="H25" s="1" t="n">
         <v>9.246</v>
       </c>
     </row>
@@ -1084,9 +1162,12 @@
         <v>0.3696</v>
       </c>
       <c r="F26" s="1" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="G26" s="1" t="n">
         <v>0.3749</v>
       </c>
-      <c r="G26" s="1" t="n">
+      <c r="H26" s="1" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -1109,9 +1190,12 @@
         <v>0.897</v>
       </c>
       <c r="F27" s="1" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="G27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="G27" s="1" t="n">
+      <c r="H27" s="1" t="n">
         <v>0.887</v>
       </c>
     </row>
@@ -1134,9 +1218,12 @@
         <v>1.816</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>1.816</v>
+        <v>1.823</v>
       </c>
       <c r="G28" s="1" t="n">
+        <v>1.823</v>
+      </c>
+      <c r="H28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -1159,9 +1246,12 @@
         <v>0.1121</v>
       </c>
       <c r="F29" s="1" t="n">
+        <v>0.1118</v>
+      </c>
+      <c r="G29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="G29" s="1" t="n">
+      <c r="H29" s="1" t="n">
         <v>0.1115</v>
       </c>
     </row>
@@ -1184,9 +1274,12 @@
         <v>0.002063</v>
       </c>
       <c r="F30" s="1" t="n">
+        <v>0.002059</v>
+      </c>
+      <c r="G30" s="1" t="n">
         <v>0.002063</v>
       </c>
-      <c r="G30" s="1" t="n">
+      <c r="H30" s="1" t="n">
         <v>0.002054</v>
       </c>
     </row>
@@ -1209,9 +1302,12 @@
         <v>1.511</v>
       </c>
       <c r="F31" s="1" t="n">
+        <v>1.508</v>
+      </c>
+      <c r="G31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="G31" s="1" t="n">
+      <c r="H31" s="1" t="n">
         <v>1.499</v>
       </c>
     </row>
@@ -1234,9 +1330,12 @@
         <v>0.1776</v>
       </c>
       <c r="F32" s="1" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="G32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="G32" s="1" t="n">
+      <c r="H32" s="1" t="n">
         <v>0.177</v>
       </c>
     </row>
@@ -1259,9 +1358,12 @@
         <v>0.1056</v>
       </c>
       <c r="F33" s="1" t="n">
+        <v>0.1055</v>
+      </c>
+      <c r="G33" s="1" t="n">
         <v>0.1056</v>
       </c>
-      <c r="G33" s="1" t="n">
+      <c r="H33" s="1" t="n">
         <v>0.1045</v>
       </c>
     </row>
@@ -1284,9 +1386,12 @@
         <v>114.54</v>
       </c>
       <c r="F34" s="1" t="n">
+        <v>114.29</v>
+      </c>
+      <c r="G34" s="1" t="n">
         <v>114.54</v>
       </c>
-      <c r="G34" s="1" t="n">
+      <c r="H34" s="1" t="n">
         <v>113.65</v>
       </c>
     </row>
@@ -1309,9 +1414,12 @@
         <v>6.936</v>
       </c>
       <c r="F35" s="1" t="n">
+        <v>6.885</v>
+      </c>
+      <c r="G35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="G35" s="1" t="n">
+      <c r="H35" s="1" t="n">
         <v>6.772</v>
       </c>
     </row>
@@ -1334,9 +1442,12 @@
         <v>0.017409</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.017415</v>
+        <v>0.017421</v>
       </c>
       <c r="G36" s="1" t="n">
+        <v>0.017421</v>
+      </c>
+      <c r="H36" s="1" t="n">
         <v>0.017313</v>
       </c>
     </row>
@@ -1359,9 +1470,12 @@
         <v>0.3687</v>
       </c>
       <c r="F37" s="1" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="G37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="G37" s="1" t="n">
+      <c r="H37" s="1" t="n">
         <v>0.3656</v>
       </c>
     </row>
@@ -1384,9 +1498,12 @@
         <v>55.72</v>
       </c>
       <c r="F38" s="1" t="n">
+        <v>55.67</v>
+      </c>
+      <c r="G38" s="1" t="n">
         <v>55.72</v>
       </c>
-      <c r="G38" s="1" t="n">
+      <c r="H38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -1409,9 +1526,12 @@
         <v>0.58919</v>
       </c>
       <c r="F39" s="1" t="n">
+        <v>0.58924</v>
+      </c>
+      <c r="G39" s="1" t="n">
         <v>0.5914700000000001</v>
       </c>
-      <c r="G39" s="1" t="n">
+      <c r="H39" s="1" t="n">
         <v>0.58131</v>
       </c>
     </row>
@@ -1434,9 +1554,12 @@
         <v>4.092</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>4.092</v>
+        <v>4.096</v>
       </c>
       <c r="G40" s="1" t="n">
+        <v>4.096</v>
+      </c>
+      <c r="H40" s="1" t="n">
         <v>4.051</v>
       </c>
     </row>
@@ -1459,9 +1582,12 @@
         <v>0.04943</v>
       </c>
       <c r="F41" s="1" t="n">
+        <v>0.04928</v>
+      </c>
+      <c r="G41" s="1" t="n">
         <v>0.04957</v>
       </c>
-      <c r="G41" s="1" t="n">
+      <c r="H41" s="1" t="n">
         <v>0.04927</v>
       </c>
     </row>
@@ -1484,9 +1610,12 @@
         <v>0.7066</v>
       </c>
       <c r="F42" s="1" t="n">
+        <v>0.7039</v>
+      </c>
+      <c r="G42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="G42" s="1" t="n">
+      <c r="H42" s="1" t="n">
         <v>0.7017</v>
       </c>
     </row>
@@ -1509,9 +1638,12 @@
         <v>0.2383</v>
       </c>
       <c r="F43" s="1" t="n">
+        <v>0.23334</v>
+      </c>
+      <c r="G43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="G43" s="1" t="n">
+      <c r="H43" s="1" t="n">
         <v>0.23323</v>
       </c>
     </row>
@@ -1534,9 +1666,12 @@
         <v>0.3529</v>
       </c>
       <c r="F44" s="1" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="G44" s="1" t="n">
         <v>0.35392</v>
       </c>
-      <c r="G44" s="1" t="n">
+      <c r="H44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -1559,9 +1694,12 @@
         <v>0.1734</v>
       </c>
       <c r="F45" s="1" t="n">
+        <v>0.1725</v>
+      </c>
+      <c r="G45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="G45" s="1" t="n">
+      <c r="H45" s="1" t="n">
         <v>0.1714</v>
       </c>
     </row>
@@ -1584,9 +1722,12 @@
         <v>0.0264</v>
       </c>
       <c r="F46" s="1" t="n">
+        <v>0.0264</v>
+      </c>
+      <c r="G46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="G46" s="1" t="n">
+      <c r="H46" s="1" t="n">
         <v>0.0264</v>
       </c>
     </row>
@@ -1609,9 +1750,12 @@
         <v>0.006059</v>
       </c>
       <c r="F47" s="1" t="n">
+        <v>0.006041</v>
+      </c>
+      <c r="G47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="G47" s="1" t="n">
+      <c r="H47" s="1" t="n">
         <v>0.006032</v>
       </c>
     </row>
@@ -1634,9 +1778,12 @@
         <v>0.007521</v>
       </c>
       <c r="F48" s="1" t="n">
+        <v>0.007489</v>
+      </c>
+      <c r="G48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="G48" s="1" t="n">
+      <c r="H48" s="1" t="n">
         <v>0.007479</v>
       </c>
     </row>
@@ -1659,9 +1806,12 @@
         <v>0.1115</v>
       </c>
       <c r="F49" s="1" t="n">
+        <v>0.1113</v>
+      </c>
+      <c r="G49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="G49" s="1" t="n">
+      <c r="H49" s="1" t="n">
         <v>0.1105</v>
       </c>
     </row>
@@ -1684,9 +1834,12 @@
         <v>0.04046</v>
       </c>
       <c r="F50" s="1" t="n">
+        <v>0.0403</v>
+      </c>
+      <c r="G50" s="1" t="n">
         <v>0.04046</v>
       </c>
-      <c r="G50" s="1" t="n">
+      <c r="H50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -1709,10 +1862,13 @@
         <v>0.167</v>
       </c>
       <c r="F51" s="1" t="n">
+        <v>0.1655</v>
+      </c>
+      <c r="G51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="G51" s="1" t="n">
-        <v>0.1658</v>
+      <c r="H51" s="1" t="n">
+        <v>0.1655</v>
       </c>
     </row>
     <row r="52">
@@ -1734,9 +1890,12 @@
         <v>0.00357</v>
       </c>
       <c r="F52" s="1" t="n">
+        <v>0.00355</v>
+      </c>
+      <c r="G52" s="1" t="n">
         <v>0.00357</v>
       </c>
-      <c r="G52" s="1" t="n">
+      <c r="H52" s="1" t="n">
         <v>0.00354</v>
       </c>
     </row>
@@ -1759,9 +1918,12 @@
         <v>2.662</v>
       </c>
       <c r="F53" s="1" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="G53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="G53" s="1" t="n">
+      <c r="H53" s="1" t="n">
         <v>2.645</v>
       </c>
     </row>
@@ -1784,9 +1946,12 @@
         <v>0.006309</v>
       </c>
       <c r="F54" s="1" t="n">
+        <v>0.006287</v>
+      </c>
+      <c r="G54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="G54" s="1" t="n">
+      <c r="H54" s="1" t="n">
         <v>0.006263</v>
       </c>
     </row>
@@ -1809,10 +1974,13 @@
         <v>0.02943</v>
       </c>
       <c r="F55" s="1" t="n">
+        <v>0.02885</v>
+      </c>
+      <c r="G55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="G55" s="1" t="n">
-        <v>0.02927</v>
+      <c r="H55" s="1" t="n">
+        <v>0.02885</v>
       </c>
     </row>
     <row r="56">
@@ -1834,9 +2002,12 @@
         <v>0.7513</v>
       </c>
       <c r="F56" s="1" t="n">
+        <v>0.7488</v>
+      </c>
+      <c r="G56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="G56" s="1" t="n">
+      <c r="H56" s="1" t="n">
         <v>0.7433999999999999</v>
       </c>
     </row>
@@ -1859,9 +2030,12 @@
         <v>0.105</v>
       </c>
       <c r="F57" s="1" t="n">
+        <v>0.1048</v>
+      </c>
+      <c r="G57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="G57" s="1" t="n">
+      <c r="H57" s="1" t="n">
         <v>0.104</v>
       </c>
     </row>
@@ -1884,9 +2058,12 @@
         <v>0.9574</v>
       </c>
       <c r="F58" s="1" t="n">
+        <v>0.9536</v>
+      </c>
+      <c r="G58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="G58" s="1" t="n">
+      <c r="H58" s="1" t="n">
         <v>0.9505</v>
       </c>
     </row>
@@ -1909,9 +2086,12 @@
         <v>0.08448</v>
       </c>
       <c r="F59" s="1" t="n">
+        <v>0.08464000000000001</v>
+      </c>
+      <c r="G59" s="1" t="n">
         <v>0.08542</v>
       </c>
-      <c r="G59" s="1" t="n">
+      <c r="H59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -1934,9 +2114,12 @@
         <v>0.06976</v>
       </c>
       <c r="F60" s="1" t="n">
+        <v>0.06957000000000001</v>
+      </c>
+      <c r="G60" s="1" t="n">
         <v>0.07001</v>
       </c>
-      <c r="G60" s="1" t="n">
+      <c r="H60" s="1" t="n">
         <v>0.06924</v>
       </c>
     </row>
@@ -1959,9 +2142,12 @@
         <v>0.05523</v>
       </c>
       <c r="F61" s="1" t="n">
+        <v>0.0549</v>
+      </c>
+      <c r="G61" s="1" t="n">
         <v>0.05523</v>
       </c>
-      <c r="G61" s="1" t="n">
+      <c r="H61" s="1" t="n">
         <v>0.05469</v>
       </c>
     </row>
@@ -1984,9 +2170,12 @@
         <v>0.010194</v>
       </c>
       <c r="F62" s="1" t="n">
+        <v>0.010152</v>
+      </c>
+      <c r="G62" s="1" t="n">
         <v>0.010194</v>
       </c>
-      <c r="G62" s="1" t="n">
+      <c r="H62" s="1" t="n">
         <v>0.009535999999999999</v>
       </c>
     </row>
@@ -2009,9 +2198,12 @@
         <v>0.28965</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>0.28965</v>
+        <v>0.28984</v>
       </c>
       <c r="G63" s="1" t="n">
+        <v>0.28984</v>
+      </c>
+      <c r="H63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -2034,9 +2226,12 @@
         <v>0.07310999999999999</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>0.07310999999999999</v>
+        <v>0.0742</v>
       </c>
       <c r="G64" s="1" t="n">
+        <v>0.0742</v>
+      </c>
+      <c r="H64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -2059,9 +2254,12 @@
         <v>0.3106</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>0.3106</v>
+        <v>0.3108</v>
       </c>
       <c r="G65" s="1" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="H65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -2084,9 +2282,12 @@
         <v>0.16461</v>
       </c>
       <c r="F66" s="1" t="n">
+        <v>0.16433</v>
+      </c>
+      <c r="G66" s="1" t="n">
         <v>0.16461</v>
       </c>
-      <c r="G66" s="1" t="n">
+      <c r="H66" s="1" t="n">
         <v>0.16337</v>
       </c>
     </row>
@@ -2109,10 +2310,13 @@
         <v>0.11978</v>
       </c>
       <c r="F67" s="1" t="n">
+        <v>0.11926</v>
+      </c>
+      <c r="G67" s="1" t="n">
         <v>0.11997</v>
       </c>
-      <c r="G67" s="1" t="n">
-        <v>0.11934</v>
+      <c r="H67" s="1" t="n">
+        <v>0.11926</v>
       </c>
     </row>
     <row r="68">
@@ -2134,9 +2338,12 @@
         <v>0.09730999999999999</v>
       </c>
       <c r="F68" s="1" t="n">
+        <v>0.09716</v>
+      </c>
+      <c r="G68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="G68" s="1" t="n">
+      <c r="H68" s="1" t="n">
         <v>0.09666</v>
       </c>
     </row>
@@ -2159,9 +2366,12 @@
         <v>0.1259</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>0.1259</v>
+        <v>0.1262</v>
       </c>
       <c r="G69" s="1" t="n">
+        <v>0.1262</v>
+      </c>
+      <c r="H69" s="1" t="n">
         <v>0.1247</v>
       </c>
     </row>
@@ -2184,9 +2394,12 @@
         <v>8.621</v>
       </c>
       <c r="F70" s="1" t="n">
+        <v>8.602</v>
+      </c>
+      <c r="G70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="G70" s="1" t="n">
+      <c r="H70" s="1" t="n">
         <v>8.550000000000001</v>
       </c>
     </row>
@@ -2212,6 +2425,9 @@
         <v>0.241</v>
       </c>
       <c r="G71" s="1" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="H71" s="1" t="n">
         <v>0.239</v>
       </c>
     </row>
@@ -2234,10 +2450,13 @@
         <v>0.05156</v>
       </c>
       <c r="F72" s="1" t="n">
+        <v>0.05125</v>
+      </c>
+      <c r="G72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="G72" s="1" t="n">
-        <v>0.05156</v>
+      <c r="H72" s="1" t="n">
+        <v>0.05125</v>
       </c>
     </row>
     <row r="73">
@@ -2259,9 +2478,12 @@
         <v>0.05076</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>0.05076</v>
+        <v>0.05109</v>
       </c>
       <c r="G73" s="1" t="n">
+        <v>0.05109</v>
+      </c>
+      <c r="H73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -2284,9 +2506,12 @@
         <v>0.1266</v>
       </c>
       <c r="F74" s="1" t="n">
+        <v>0.1256</v>
+      </c>
+      <c r="G74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="G74" s="1" t="n">
+      <c r="H74" s="1" t="n">
         <v>0.1252</v>
       </c>
     </row>
@@ -2309,9 +2534,12 @@
         <v>0.04712</v>
       </c>
       <c r="F75" s="1" t="n">
+        <v>0.04696</v>
+      </c>
+      <c r="G75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="G75" s="1" t="n">
+      <c r="H75" s="1" t="n">
         <v>0.04688</v>
       </c>
     </row>
@@ -2334,9 +2562,12 @@
         <v>0.0677</v>
       </c>
       <c r="F76" s="1" t="n">
+        <v>0.06769</v>
+      </c>
+      <c r="G76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="G76" s="1" t="n">
+      <c r="H76" s="1" t="n">
         <v>0.06743</v>
       </c>
     </row>
@@ -2359,9 +2590,12 @@
         <v>0.12772</v>
       </c>
       <c r="F77" s="1" t="n">
+        <v>0.12707</v>
+      </c>
+      <c r="G77" s="1" t="n">
         <v>0.12881</v>
       </c>
-      <c r="G77" s="1" t="n">
+      <c r="H77" s="1" t="n">
         <v>0.12685</v>
       </c>
     </row>
@@ -2384,9 +2618,12 @@
         <v>0.1636</v>
       </c>
       <c r="F78" s="1" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="G78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="G78" s="1" t="n">
+      <c r="H78" s="1" t="n">
         <v>0.1624</v>
       </c>
     </row>
@@ -2409,9 +2646,12 @@
         <v>0.02753</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>0.02753</v>
+        <v>0.0276</v>
       </c>
       <c r="G79" s="1" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="H79" s="1" t="n">
         <v>0.0272</v>
       </c>
     </row>
@@ -2434,9 +2674,12 @@
         <v>356.25</v>
       </c>
       <c r="F80" s="1" t="n">
+        <v>356.02</v>
+      </c>
+      <c r="G80" s="1" t="n">
         <v>356.25</v>
       </c>
-      <c r="G80" s="1" t="n">
+      <c r="H80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -2459,9 +2702,12 @@
         <v>7.248e-05</v>
       </c>
       <c r="F81" s="1" t="n">
+        <v>7.224999999999999e-05</v>
+      </c>
+      <c r="G81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="G81" s="1" t="n">
+      <c r="H81" s="1" t="n">
         <v>7.196e-05</v>
       </c>
     </row>
@@ -2484,9 +2730,12 @@
         <v>0.2687</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>0.2687</v>
+        <v>0.2688</v>
       </c>
       <c r="G82" s="1" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="H82" s="1" t="n">
         <v>0.2672</v>
       </c>
     </row>
@@ -2509,9 +2758,12 @@
         <v>1.1461</v>
       </c>
       <c r="F83" s="1" t="n">
+        <v>1.1459</v>
+      </c>
+      <c r="G83" s="1" t="n">
         <v>1.1461</v>
       </c>
-      <c r="G83" s="1" t="n">
+      <c r="H83" s="1" t="n">
         <v>1.1408</v>
       </c>
     </row>
@@ -2534,9 +2786,12 @@
         <v>0.3622</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>0.3622</v>
+        <v>0.3623</v>
       </c>
       <c r="G84" s="1" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="H84" s="1" t="n">
         <v>0.3569</v>
       </c>
     </row>
@@ -2559,9 +2814,12 @@
         <v>2.0238</v>
       </c>
       <c r="F85" s="1" t="n">
+        <v>2.0144</v>
+      </c>
+      <c r="G85" s="1" t="n">
         <v>2.0238</v>
       </c>
-      <c r="G85" s="1" t="n">
+      <c r="H85" s="1" t="n">
         <v>2.0067</v>
       </c>
     </row>
@@ -2584,9 +2842,12 @@
         <v>1.3145</v>
       </c>
       <c r="F86" s="1" t="n">
+        <v>1.3106</v>
+      </c>
+      <c r="G86" s="1" t="n">
         <v>1.3167</v>
       </c>
-      <c r="G86" s="1" t="n">
+      <c r="H86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -2609,9 +2870,12 @@
         <v>33.17</v>
       </c>
       <c r="F87" s="1" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="G87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="G87" s="1" t="n">
+      <c r="H87" s="1" t="n">
         <v>32.97</v>
       </c>
     </row>
@@ -2634,9 +2898,12 @@
         <v>0.01128</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>0.01128</v>
+        <v>0.01147</v>
       </c>
       <c r="G88" s="1" t="n">
+        <v>0.01147</v>
+      </c>
+      <c r="H88" s="1" t="n">
         <v>0.01046</v>
       </c>
     </row>
@@ -2659,9 +2926,12 @@
         <v>0.01829</v>
       </c>
       <c r="F89" s="1" t="n">
+        <v>0.01833</v>
+      </c>
+      <c r="G89" s="1" t="n">
         <v>0.01835</v>
       </c>
-      <c r="G89" s="1" t="n">
+      <c r="H89" s="1" t="n">
         <v>0.01828</v>
       </c>
     </row>
@@ -2684,9 +2954,12 @@
         <v>0.03601</v>
       </c>
       <c r="F90" s="1" t="n">
+        <v>0.03613</v>
+      </c>
+      <c r="G90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="G90" s="1" t="n">
+      <c r="H90" s="1" t="n">
         <v>0.03571</v>
       </c>
     </row>
@@ -2709,9 +2982,12 @@
         <v>0.01202</v>
       </c>
       <c r="F91" s="1" t="n">
+        <v>0.01199</v>
+      </c>
+      <c r="G91" s="1" t="n">
         <v>0.01202</v>
       </c>
-      <c r="G91" s="1" t="n">
+      <c r="H91" s="1" t="n">
         <v>0.01192</v>
       </c>
     </row>
@@ -2734,9 +3010,12 @@
         <v>3.136</v>
       </c>
       <c r="F92" s="1" t="n">
+        <v>3.134</v>
+      </c>
+      <c r="G92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="G92" s="1" t="n">
+      <c r="H92" s="1" t="n">
         <v>3.111</v>
       </c>
     </row>
@@ -2759,9 +3038,12 @@
         <v>0.005656</v>
       </c>
       <c r="F93" s="1" t="n">
+        <v>0.005642</v>
+      </c>
+      <c r="G93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="G93" s="1" t="n">
+      <c r="H93" s="1" t="n">
         <v>0.005635</v>
       </c>
     </row>
@@ -2784,9 +3066,12 @@
         <v>0.0946</v>
       </c>
       <c r="F94" s="1" t="n">
+        <v>0.09420000000000001</v>
+      </c>
+      <c r="G94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="G94" s="1" t="n">
+      <c r="H94" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -2809,9 +3094,12 @@
         <v>0.6058</v>
       </c>
       <c r="F95" s="1" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="G95" s="1" t="n">
         <v>0.6058</v>
       </c>
-      <c r="G95" s="1" t="n">
+      <c r="H95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -2834,9 +3122,12 @@
         <v>1.29e-05</v>
       </c>
       <c r="F96" s="1" t="n">
+        <v>1.28e-05</v>
+      </c>
+      <c r="G96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="G96" s="1" t="n">
+      <c r="H96" s="1" t="n">
         <v>1.28e-05</v>
       </c>
     </row>
@@ -2859,9 +3150,12 @@
         <v>1.15</v>
       </c>
       <c r="F97" s="1" t="n">
+        <v>1.144</v>
+      </c>
+      <c r="G97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="G97" s="1" t="n">
+      <c r="H97" s="1" t="n">
         <v>1.136</v>
       </c>
     </row>
@@ -2884,9 +3178,12 @@
         <v>0.25616</v>
       </c>
       <c r="F98" s="1" t="n">
+        <v>0.25642</v>
+      </c>
+      <c r="G98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="G98" s="1" t="n">
+      <c r="H98" s="1" t="n">
         <v>0.25616</v>
       </c>
     </row>
@@ -2909,9 +3206,12 @@
         <v>1.155</v>
       </c>
       <c r="F99" s="1" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="G99" s="1" t="n">
         <v>1.155</v>
       </c>
-      <c r="G99" s="1" t="n">
+      <c r="H99" s="1" t="n">
         <v>1.146</v>
       </c>
     </row>
@@ -2934,9 +3234,12 @@
         <v>1.873</v>
       </c>
       <c r="F100" s="1" t="n">
+        <v>1.868</v>
+      </c>
+      <c r="G100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="G100" s="1" t="n">
+      <c r="H100" s="1" t="n">
         <v>1.862</v>
       </c>
     </row>
@@ -2959,10 +3262,13 @@
         <v>0.01599</v>
       </c>
       <c r="F101" s="1" t="n">
+        <v>0.01595</v>
+      </c>
+      <c r="G101" s="1" t="n">
         <v>0.01599</v>
       </c>
-      <c r="G101" s="1" t="n">
-        <v>0.01597</v>
+      <c r="H101" s="1" t="n">
+        <v>0.01595</v>
       </c>
     </row>
     <row r="102">
@@ -2984,9 +3290,12 @@
         <v>0.10381</v>
       </c>
       <c r="F102" s="1" t="n">
+        <v>0.10378</v>
+      </c>
+      <c r="G102" s="1" t="n">
         <v>0.10417</v>
       </c>
-      <c r="G102" s="1" t="n">
+      <c r="H102" s="1" t="n">
         <v>0.10353</v>
       </c>
     </row>
@@ -3009,10 +3318,13 @@
         <v>0.0006089</v>
       </c>
       <c r="F103" s="1" t="n">
+        <v>0.0006041</v>
+      </c>
+      <c r="G103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="G103" s="1" t="n">
-        <v>0.000605</v>
+      <c r="H103" s="1" t="n">
+        <v>0.0006041</v>
       </c>
     </row>
     <row r="104">
@@ -3034,9 +3346,12 @@
         <v>0.0005731999999999999</v>
       </c>
       <c r="F104" s="1" t="n">
+        <v>0.0005731</v>
+      </c>
+      <c r="G104" s="1" t="n">
         <v>0.0005731999999999999</v>
       </c>
-      <c r="G104" s="1" t="n">
+      <c r="H104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -3059,10 +3374,13 @@
         <v>0.003241</v>
       </c>
       <c r="F105" s="1" t="n">
+        <v>0.003229</v>
+      </c>
+      <c r="G105" s="1" t="n">
         <v>0.003257</v>
       </c>
-      <c r="G105" s="1" t="n">
-        <v>0.003241</v>
+      <c r="H105" s="1" t="n">
+        <v>0.003229</v>
       </c>
     </row>
     <row r="106">
@@ -3084,9 +3402,12 @@
         <v>2.647</v>
       </c>
       <c r="F106" s="1" t="n">
+        <v>2.633</v>
+      </c>
+      <c r="G106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="G106" s="1" t="n">
+      <c r="H106" s="1" t="n">
         <v>2.617</v>
       </c>
     </row>
@@ -3109,9 +3430,12 @@
         <v>0.1681</v>
       </c>
       <c r="F107" s="1" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="G107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="G107" s="1" t="n">
+      <c r="H107" s="1" t="n">
         <v>0.167</v>
       </c>
     </row>
@@ -3134,10 +3458,13 @@
         <v>0.09787</v>
       </c>
       <c r="F108" s="1" t="n">
+        <v>0.09727</v>
+      </c>
+      <c r="G108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="G108" s="1" t="n">
-        <v>0.09742000000000001</v>
+      <c r="H108" s="1" t="n">
+        <v>0.09727</v>
       </c>
     </row>
     <row r="109">
@@ -3159,10 +3486,13 @@
         <v>0.02237</v>
       </c>
       <c r="F109" s="1" t="n">
+        <v>0.02228</v>
+      </c>
+      <c r="G109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="G109" s="1" t="n">
-        <v>0.02229</v>
+      <c r="H109" s="1" t="n">
+        <v>0.02228</v>
       </c>
     </row>
     <row r="110">
@@ -3184,9 +3514,12 @@
         <v>0.2948</v>
       </c>
       <c r="F110" s="1" t="n">
-        <v>0.2948</v>
+        <v>0.2953</v>
       </c>
       <c r="G110" s="1" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="H110" s="1" t="n">
         <v>0.2913</v>
       </c>
     </row>
@@ -3209,9 +3542,12 @@
         <v>0.05721</v>
       </c>
       <c r="F111" s="1" t="n">
+        <v>0.05708</v>
+      </c>
+      <c r="G111" s="1" t="n">
         <v>0.05721</v>
       </c>
-      <c r="G111" s="1" t="n">
+      <c r="H111" s="1" t="n">
         <v>0.05684</v>
       </c>
     </row>
@@ -3234,9 +3570,12 @@
         <v>0.3064</v>
       </c>
       <c r="F112" s="1" t="n">
+        <v>0.3059</v>
+      </c>
+      <c r="G112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="G112" s="1" t="n">
+      <c r="H112" s="1" t="n">
         <v>0.3039</v>
       </c>
     </row>
@@ -3259,9 +3598,12 @@
         <v>18.73</v>
       </c>
       <c r="F113" s="1" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="G113" s="1" t="n">
+      <c r="H113" s="1" t="n">
         <v>18.62</v>
       </c>
     </row>
@@ -3284,9 +3626,12 @@
         <v>0.13604</v>
       </c>
       <c r="F114" s="1" t="n">
+        <v>0.13425</v>
+      </c>
+      <c r="G114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="G114" s="1" t="n">
+      <c r="H114" s="1" t="n">
         <v>0.13225</v>
       </c>
     </row>
@@ -3309,9 +3654,12 @@
         <v>0.01575</v>
       </c>
       <c r="F115" s="1" t="n">
+        <v>0.01545</v>
+      </c>
+      <c r="G115" s="1" t="n">
         <v>0.01583</v>
       </c>
-      <c r="G115" s="1" t="n">
+      <c r="H115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -3334,9 +3682,12 @@
         <v>0.08609</v>
       </c>
       <c r="F116" s="1" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="G116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="G116" s="1" t="n">
+      <c r="H116" s="1" t="n">
         <v>0.08527</v>
       </c>
     </row>
@@ -3359,10 +3710,13 @@
         <v>0.04873</v>
       </c>
       <c r="F117" s="1" t="n">
+        <v>0.048291</v>
+      </c>
+      <c r="G117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="G117" s="1" t="n">
-        <v>0.04873</v>
+      <c r="H117" s="1" t="n">
+        <v>0.048291</v>
       </c>
     </row>
     <row r="118">
@@ -3384,9 +3738,12 @@
         <v>0.04849</v>
       </c>
       <c r="F118" s="1" t="n">
+        <v>0.04823</v>
+      </c>
+      <c r="G118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="G118" s="1" t="n">
+      <c r="H118" s="1" t="n">
         <v>0.04807</v>
       </c>
     </row>
@@ -3409,9 +3766,12 @@
         <v>0.04271</v>
       </c>
       <c r="F119" s="1" t="n">
+        <v>0.04161</v>
+      </c>
+      <c r="G119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="G119" s="1" t="n">
+      <c r="H119" s="1" t="n">
         <v>0.04109</v>
       </c>
     </row>
@@ -3434,9 +3794,12 @@
         <v>0.14629</v>
       </c>
       <c r="F120" s="1" t="n">
+        <v>0.14552</v>
+      </c>
+      <c r="G120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="G120" s="1" t="n">
+      <c r="H120" s="1" t="n">
         <v>0.14499</v>
       </c>
     </row>
@@ -3462,6 +3825,9 @@
         <v>0.1284</v>
       </c>
       <c r="G121" s="1" t="n">
+        <v>0.1284</v>
+      </c>
+      <c r="H121" s="1" t="n">
         <v>0.1272</v>
       </c>
     </row>
@@ -3484,9 +3850,12 @@
         <v>1.903</v>
       </c>
       <c r="F122" s="1" t="n">
+        <v>1.893</v>
+      </c>
+      <c r="G122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="G122" s="1" t="n">
+      <c r="H122" s="1" t="n">
         <v>1.887</v>
       </c>
     </row>
@@ -3509,9 +3878,12 @@
         <v>0.03064</v>
       </c>
       <c r="F123" s="1" t="n">
+        <v>0.03058</v>
+      </c>
+      <c r="G123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="G123" s="1" t="n">
+      <c r="H123" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -3534,9 +3906,12 @@
         <v>0.13401</v>
       </c>
       <c r="F124" s="1" t="n">
+        <v>0.13351</v>
+      </c>
+      <c r="G124" s="1" t="n">
         <v>0.13401</v>
       </c>
-      <c r="G124" s="1" t="n">
+      <c r="H124" s="1" t="n">
         <v>0.13288</v>
       </c>
     </row>
@@ -3559,9 +3934,12 @@
         <v>0.04143</v>
       </c>
       <c r="F125" s="1" t="n">
+        <v>0.04139</v>
+      </c>
+      <c r="G125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="G125" s="1" t="n">
+      <c r="H125" s="1" t="n">
         <v>0.04139</v>
       </c>
     </row>
@@ -3584,9 +3962,12 @@
         <v>0.1166</v>
       </c>
       <c r="F126" s="1" t="n">
+        <v>0.1163</v>
+      </c>
+      <c r="G126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="G126" s="1" t="n">
+      <c r="H126" s="1" t="n">
         <v>0.1154</v>
       </c>
     </row>
@@ -3609,9 +3990,12 @@
         <v>0.5013</v>
       </c>
       <c r="F127" s="1" t="n">
-        <v>0.5013</v>
+        <v>0.5028</v>
       </c>
       <c r="G127" s="1" t="n">
+        <v>0.5028</v>
+      </c>
+      <c r="H127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -3634,9 +4018,12 @@
         <v>0.03838</v>
       </c>
       <c r="F128" s="1" t="n">
+        <v>0.0383</v>
+      </c>
+      <c r="G128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="G128" s="1" t="n">
+      <c r="H128" s="1" t="n">
         <v>0.03787</v>
       </c>
     </row>
@@ -3659,9 +4046,12 @@
         <v>0.798</v>
       </c>
       <c r="F129" s="1" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="G129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="G129" s="1" t="n">
+      <c r="H129" s="1" t="n">
         <v>0.796</v>
       </c>
     </row>
@@ -3687,6 +4077,9 @@
         <v>0.03458</v>
       </c>
       <c r="G130" s="1" t="n">
+        <v>0.03458</v>
+      </c>
+      <c r="H130" s="1" t="n">
         <v>0.03439</v>
       </c>
     </row>
@@ -3709,9 +4102,12 @@
         <v>0.4316</v>
       </c>
       <c r="F131" s="1" t="n">
+        <v>0.4295</v>
+      </c>
+      <c r="G131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="G131" s="1" t="n">
+      <c r="H131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -3734,9 +4130,12 @@
         <v>0.04361</v>
       </c>
       <c r="F132" s="1" t="n">
+        <v>0.04361</v>
+      </c>
+      <c r="G132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="G132" s="1" t="n">
+      <c r="H132" s="1" t="n">
         <v>0.04361</v>
       </c>
     </row>
@@ -3759,9 +4158,12 @@
         <v>1.3057</v>
       </c>
       <c r="F133" s="1" t="n">
+        <v>1.3017</v>
+      </c>
+      <c r="G133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="G133" s="1" t="n">
+      <c r="H133" s="1" t="n">
         <v>1.2941</v>
       </c>
     </row>
@@ -3784,9 +4186,12 @@
         <v>0.02214</v>
       </c>
       <c r="F134" s="1" t="n">
+        <v>0.02208</v>
+      </c>
+      <c r="G134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="G134" s="1" t="n">
+      <c r="H134" s="1" t="n">
         <v>0.02208</v>
       </c>
     </row>
@@ -3809,10 +4214,13 @@
         <v>0.0004731</v>
       </c>
       <c r="F135" s="1" t="n">
+        <v>0.0004694</v>
+      </c>
+      <c r="G135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="G135" s="1" t="n">
-        <v>0.0004699</v>
+      <c r="H135" s="1" t="n">
+        <v>0.0004694</v>
       </c>
     </row>
     <row r="136">
@@ -3834,9 +4242,12 @@
         <v>0.001966</v>
       </c>
       <c r="F136" s="1" t="n">
-        <v>0.001966</v>
+        <v>0.001976</v>
       </c>
       <c r="G136" s="1" t="n">
+        <v>0.001976</v>
+      </c>
+      <c r="H136" s="1" t="n">
         <v>0.001913</v>
       </c>
     </row>
@@ -3862,6 +4273,9 @@
         <v>0.3239</v>
       </c>
       <c r="G137" s="1" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="H137" s="1" t="n">
         <v>0.3204</v>
       </c>
     </row>
@@ -3884,9 +4298,12 @@
         <v>0.5759</v>
       </c>
       <c r="F138" s="1" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="G138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="G138" s="1" t="n">
+      <c r="H138" s="1" t="n">
         <v>0.5705</v>
       </c>
     </row>
@@ -3909,9 +4326,12 @@
         <v>0.02161</v>
       </c>
       <c r="F139" s="1" t="n">
+        <v>0.02151</v>
+      </c>
+      <c r="G139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="G139" s="1" t="n">
+      <c r="H139" s="1" t="n">
         <v>0.02145</v>
       </c>
     </row>
@@ -3934,10 +4354,13 @@
         <v>0.08103</v>
       </c>
       <c r="F140" s="1" t="n">
+        <v>0.08073</v>
+      </c>
+      <c r="G140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="G140" s="1" t="n">
-        <v>0.08081000000000001</v>
+      <c r="H140" s="1" t="n">
+        <v>0.08073</v>
       </c>
     </row>
     <row r="141">
@@ -3959,9 +4382,12 @@
         <v>0.001642</v>
       </c>
       <c r="F141" s="1" t="n">
-        <v>0.001642</v>
+        <v>0.001656</v>
       </c>
       <c r="G141" s="1" t="n">
+        <v>0.001656</v>
+      </c>
+      <c r="H141" s="1" t="n">
         <v>0.001616</v>
       </c>
     </row>
@@ -3984,9 +4410,12 @@
         <v>0.4274</v>
       </c>
       <c r="F142" s="1" t="n">
+        <v>0.4266</v>
+      </c>
+      <c r="G142" s="1" t="n">
         <v>0.4274</v>
       </c>
-      <c r="G142" s="1" t="n">
+      <c r="H142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -4009,10 +4438,13 @@
         <v>0.030559</v>
       </c>
       <c r="F143" s="1" t="n">
+        <v>0.030127</v>
+      </c>
+      <c r="G143" s="1" t="n">
         <v>0.030681</v>
       </c>
-      <c r="G143" s="1" t="n">
-        <v>0.030377</v>
+      <c r="H143" s="1" t="n">
+        <v>0.030127</v>
       </c>
     </row>
     <row r="144">
@@ -4037,6 +4469,9 @@
         <v>0.000226</v>
       </c>
       <c r="G144" s="1" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="H144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -4059,9 +4494,12 @@
         <v>0.03225</v>
       </c>
       <c r="F145" s="1" t="n">
-        <v>0.03225</v>
+        <v>0.03311</v>
       </c>
       <c r="G145" s="1" t="n">
+        <v>0.03311</v>
+      </c>
+      <c r="H145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -4084,9 +4522,12 @@
         <v>0.116</v>
       </c>
       <c r="F146" s="1" t="n">
+        <v>0.11573</v>
+      </c>
+      <c r="G146" s="1" t="n">
         <v>0.116</v>
       </c>
-      <c r="G146" s="1" t="n">
+      <c r="H146" s="1" t="n">
         <v>0.11518</v>
       </c>
     </row>
@@ -4109,10 +4550,13 @@
         <v>0.02181</v>
       </c>
       <c r="F147" s="1" t="n">
+        <v>0.02164</v>
+      </c>
+      <c r="G147" s="1" t="n">
         <v>0.02185</v>
       </c>
-      <c r="G147" s="1" t="n">
-        <v>0.02171</v>
+      <c r="H147" s="1" t="n">
+        <v>0.02164</v>
       </c>
     </row>
     <row r="148">
@@ -4134,9 +4578,12 @@
         <v>1.4256</v>
       </c>
       <c r="F148" s="1" t="n">
+        <v>1.4242</v>
+      </c>
+      <c r="G148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="G148" s="1" t="n">
+      <c r="H148" s="1" t="n">
         <v>1.4154</v>
       </c>
     </row>
@@ -4159,9 +4606,12 @@
         <v>1.8771</v>
       </c>
       <c r="F149" s="1" t="n">
+        <v>1.8742</v>
+      </c>
+      <c r="G149" s="1" t="n">
         <v>1.8771</v>
       </c>
-      <c r="G149" s="1" t="n">
+      <c r="H149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -4184,9 +4634,12 @@
         <v>0.1</v>
       </c>
       <c r="F150" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="G150" s="1" t="n">
+      <c r="H150" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4209,9 +4662,12 @@
         <v>4.609</v>
       </c>
       <c r="F151" s="1" t="n">
+        <v>4.605</v>
+      </c>
+      <c r="G151" s="1" t="n">
         <v>4.609</v>
       </c>
-      <c r="G151" s="1" t="n">
+      <c r="H151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -4234,9 +4690,12 @@
         <v>5.593</v>
       </c>
       <c r="F152" s="1" t="n">
+        <v>5.569</v>
+      </c>
+      <c r="G152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="G152" s="1" t="n">
+      <c r="H152" s="1" t="n">
         <v>5.55</v>
       </c>
     </row>
@@ -4259,9 +4718,12 @@
         <v>0.3263</v>
       </c>
       <c r="F153" s="1" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="G153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="G153" s="1" t="n">
+      <c r="H153" s="1" t="n">
         <v>0.3178</v>
       </c>
     </row>
@@ -4284,9 +4746,12 @@
         <v>0.5921999999999999</v>
       </c>
       <c r="F154" s="1" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="G154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="G154" s="1" t="n">
+      <c r="H154" s="1" t="n">
         <v>0.5891999999999999</v>
       </c>
     </row>
@@ -4309,9 +4774,12 @@
         <v>0.01278</v>
       </c>
       <c r="F155" s="1" t="n">
+        <v>0.01272</v>
+      </c>
+      <c r="G155" s="1" t="n">
         <v>0.01278</v>
       </c>
-      <c r="G155" s="1" t="n">
+      <c r="H155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -4334,9 +4802,12 @@
         <v>0.1005</v>
       </c>
       <c r="F156" s="1" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="G156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="G156" s="1" t="n">
+      <c r="H156" s="1" t="n">
         <v>0.0997</v>
       </c>
     </row>
@@ -4359,9 +4830,12 @@
         <v>16.755</v>
       </c>
       <c r="F157" s="1" t="n">
+        <v>16.739</v>
+      </c>
+      <c r="G157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="G157" s="1" t="n">
+      <c r="H157" s="1" t="n">
         <v>16.563</v>
       </c>
     </row>
@@ -4384,9 +4858,12 @@
         <v>0.05593</v>
       </c>
       <c r="F158" s="1" t="n">
+        <v>0.05579</v>
+      </c>
+      <c r="G158" s="1" t="n">
         <v>0.05593</v>
       </c>
-      <c r="G158" s="1" t="n">
+      <c r="H158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -4409,9 +4886,12 @@
         <v>29.14</v>
       </c>
       <c r="F159" s="1" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="G159" s="1" t="n">
         <v>29.14</v>
       </c>
-      <c r="G159" s="1" t="n">
+      <c r="H159" s="1" t="n">
         <v>28.87</v>
       </c>
     </row>
@@ -4434,9 +4914,12 @@
         <v>0.02141</v>
       </c>
       <c r="F160" s="1" t="n">
+        <v>0.02138</v>
+      </c>
+      <c r="G160" s="1" t="n">
         <v>0.02141</v>
       </c>
-      <c r="G160" s="1" t="n">
+      <c r="H160" s="1" t="n">
         <v>0.02121</v>
       </c>
     </row>
@@ -4459,9 +4942,12 @@
         <v>0.0006655</v>
       </c>
       <c r="F161" s="1" t="n">
+        <v>0.0006626</v>
+      </c>
+      <c r="G161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="G161" s="1" t="n">
+      <c r="H161" s="1" t="n">
         <v>0.0006601000000000001</v>
       </c>
     </row>
@@ -4484,9 +4970,12 @@
         <v>0.4053</v>
       </c>
       <c r="F162" s="1" t="n">
-        <v>0.4053</v>
+        <v>0.4068</v>
       </c>
       <c r="G162" s="1" t="n">
+        <v>0.4068</v>
+      </c>
+      <c r="H162" s="1" t="n">
         <v>0.3936</v>
       </c>
     </row>
@@ -4509,9 +4998,12 @@
         <v>0.1952</v>
       </c>
       <c r="F163" s="1" t="n">
+        <v>0.1946</v>
+      </c>
+      <c r="G163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="G163" s="1" t="n">
+      <c r="H163" s="1" t="n">
         <v>0.1931</v>
       </c>
     </row>
@@ -4534,9 +5026,12 @@
         <v>0.321</v>
       </c>
       <c r="F164" s="1" t="n">
-        <v>0.321</v>
+        <v>0.322</v>
       </c>
       <c r="G164" s="1" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="H164" s="1" t="n">
         <v>0.32</v>
       </c>
     </row>
@@ -4562,6 +5057,9 @@
         <v>0.377</v>
       </c>
       <c r="G165" s="1" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="H165" s="1" t="n">
         <v>0.375</v>
       </c>
     </row>
@@ -4584,9 +5082,12 @@
         <v>0.02286</v>
       </c>
       <c r="F166" s="1" t="n">
+        <v>0.02276</v>
+      </c>
+      <c r="G166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="G166" s="1" t="n">
+      <c r="H166" s="1" t="n">
         <v>0.02271</v>
       </c>
     </row>
@@ -4609,9 +5110,12 @@
         <v>0.0074</v>
       </c>
       <c r="F167" s="1" t="n">
+        <v>0.007387</v>
+      </c>
+      <c r="G167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="G167" s="1" t="n">
+      <c r="H167" s="1" t="n">
         <v>0.007348</v>
       </c>
     </row>
@@ -4634,10 +5138,13 @@
         <v>0.01394</v>
       </c>
       <c r="F168" s="1" t="n">
+        <v>0.01392</v>
+      </c>
+      <c r="G168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="G168" s="1" t="n">
-        <v>0.01394</v>
+      <c r="H168" s="1" t="n">
+        <v>0.01392</v>
       </c>
     </row>
     <row r="169">
@@ -4659,9 +5166,12 @@
         <v>0.25629</v>
       </c>
       <c r="F169" s="1" t="n">
+        <v>0.25673</v>
+      </c>
+      <c r="G169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="G169" s="1" t="n">
+      <c r="H169" s="1" t="n">
         <v>0.25376</v>
       </c>
     </row>
@@ -4684,9 +5194,12 @@
         <v>0.02158</v>
       </c>
       <c r="F170" s="1" t="n">
+        <v>0.02167</v>
+      </c>
+      <c r="G170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="G170" s="1" t="n">
+      <c r="H170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -4709,9 +5222,12 @@
         <v>0.1756</v>
       </c>
       <c r="F171" s="1" t="n">
+        <v>0.1742</v>
+      </c>
+      <c r="G171" s="1" t="n">
         <v>0.1756</v>
       </c>
-      <c r="G171" s="1" t="n">
+      <c r="H171" s="1" t="n">
         <v>0.1733</v>
       </c>
     </row>
@@ -4734,9 +5250,12 @@
         <v>0.09</v>
       </c>
       <c r="F172" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="G172" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="G172" s="1" t="n">
+      <c r="H172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -4759,9 +5278,12 @@
         <v>0.004732</v>
       </c>
       <c r="F173" s="1" t="n">
+        <v>0.004719</v>
+      </c>
+      <c r="G173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="G173" s="1" t="n">
+      <c r="H173" s="1" t="n">
         <v>0.004719</v>
       </c>
     </row>
@@ -4784,9 +5306,12 @@
         <v>0.4401</v>
       </c>
       <c r="F174" s="1" t="n">
-        <v>0.4401</v>
+        <v>0.4406</v>
       </c>
       <c r="G174" s="1" t="n">
+        <v>0.4406</v>
+      </c>
+      <c r="H174" s="1" t="n">
         <v>0.4368</v>
       </c>
     </row>
@@ -4809,9 +5334,12 @@
         <v>0.09011</v>
       </c>
       <c r="F175" s="1" t="n">
+        <v>0.08978999999999999</v>
+      </c>
+      <c r="G175" s="1" t="n">
         <v>0.09011</v>
       </c>
-      <c r="G175" s="1" t="n">
+      <c r="H175" s="1" t="n">
         <v>0.0895</v>
       </c>
     </row>
@@ -4834,9 +5362,12 @@
         <v>0.2476</v>
       </c>
       <c r="F176" s="1" t="n">
+        <v>0.2474</v>
+      </c>
+      <c r="G176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="G176" s="1" t="n">
+      <c r="H176" s="1" t="n">
         <v>0.2453</v>
       </c>
     </row>
@@ -4859,9 +5390,12 @@
         <v>0.01935</v>
       </c>
       <c r="F177" s="1" t="n">
+        <v>0.01931</v>
+      </c>
+      <c r="G177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="G177" s="1" t="n">
+      <c r="H177" s="1" t="n">
         <v>0.01917</v>
       </c>
     </row>
@@ -4884,9 +5418,12 @@
         <v>6.24</v>
       </c>
       <c r="F178" s="1" t="n">
+        <v>6.219</v>
+      </c>
+      <c r="G178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="G178" s="1" t="n">
+      <c r="H178" s="1" t="n">
         <v>6.18</v>
       </c>
     </row>
@@ -4909,10 +5446,13 @@
         <v>0.1369</v>
       </c>
       <c r="F179" s="1" t="n">
+        <v>0.1362</v>
+      </c>
+      <c r="G179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="G179" s="1" t="n">
-        <v>0.1364</v>
+      <c r="H179" s="1" t="n">
+        <v>0.1362</v>
       </c>
     </row>
     <row r="180">
@@ -4934,9 +5474,12 @@
         <v>0.005052</v>
       </c>
       <c r="F180" s="1" t="n">
-        <v>0.005052</v>
+        <v>0.005093</v>
       </c>
       <c r="G180" s="1" t="n">
+        <v>0.005093</v>
+      </c>
+      <c r="H180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -4959,9 +5502,12 @@
         <v>0.01203</v>
       </c>
       <c r="F181" s="1" t="n">
+        <v>0.01202</v>
+      </c>
+      <c r="G181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="G181" s="1" t="n">
+      <c r="H181" s="1" t="n">
         <v>0.01189</v>
       </c>
     </row>
@@ -4984,9 +5530,12 @@
         <v>0.007442</v>
       </c>
       <c r="F182" s="1" t="n">
+        <v>0.007408</v>
+      </c>
+      <c r="G182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="G182" s="1" t="n">
+      <c r="H182" s="1" t="n">
         <v>0.007295</v>
       </c>
     </row>
@@ -5009,9 +5558,12 @@
         <v>0.12964</v>
       </c>
       <c r="F183" s="1" t="n">
+        <v>0.12966</v>
+      </c>
+      <c r="G183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="G183" s="1" t="n">
+      <c r="H183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -5034,9 +5586,12 @@
         <v>0.09673</v>
       </c>
       <c r="F184" s="1" t="n">
+        <v>0.09658</v>
+      </c>
+      <c r="G184" s="1" t="n">
         <v>0.09673</v>
       </c>
-      <c r="G184" s="1" t="n">
+      <c r="H184" s="1" t="n">
         <v>0.09587</v>
       </c>
     </row>
@@ -5062,6 +5617,9 @@
         <v>0.00763</v>
       </c>
       <c r="G185" s="1" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="H185" s="1" t="n">
         <v>0.00758</v>
       </c>
     </row>
@@ -5084,9 +5642,12 @@
         <v>0.04951</v>
       </c>
       <c r="F186" s="1" t="n">
+        <v>0.04936</v>
+      </c>
+      <c r="G186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="G186" s="1" t="n">
+      <c r="H186" s="1" t="n">
         <v>0.04914</v>
       </c>
     </row>
@@ -5109,9 +5670,12 @@
         <v>0.0272</v>
       </c>
       <c r="F187" s="1" t="n">
+        <v>0.0271</v>
+      </c>
+      <c r="G187" s="1" t="n">
         <v>0.0272</v>
       </c>
-      <c r="G187" s="1" t="n">
+      <c r="H187" s="1" t="n">
         <v>0.02686</v>
       </c>
     </row>
@@ -5134,9 +5698,12 @@
         <v>0.00335</v>
       </c>
       <c r="F188" s="1" t="n">
+        <v>0.003341</v>
+      </c>
+      <c r="G188" s="1" t="n">
         <v>0.00335</v>
       </c>
-      <c r="G188" s="1" t="n">
+      <c r="H188" s="1" t="n">
         <v>0.003323</v>
       </c>
     </row>
@@ -5162,6 +5729,9 @@
         <v>0.29</v>
       </c>
       <c r="G189" s="1" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H189" s="1" t="n">
         <v>0.2875</v>
       </c>
     </row>
@@ -5184,9 +5754,12 @@
         <v>0.01837</v>
       </c>
       <c r="F190" s="1" t="n">
+        <v>0.01831</v>
+      </c>
+      <c r="G190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="G190" s="1" t="n">
+      <c r="H190" s="1" t="n">
         <v>0.01819</v>
       </c>
     </row>
@@ -5209,9 +5782,12 @@
         <v>0.262</v>
       </c>
       <c r="F191" s="1" t="n">
+        <v>0.2609</v>
+      </c>
+      <c r="G191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="G191" s="1" t="n">
+      <c r="H191" s="1" t="n">
         <v>0.2606</v>
       </c>
     </row>
@@ -5234,9 +5810,12 @@
         <v>0.03962</v>
       </c>
       <c r="F192" s="1" t="n">
+        <v>0.03943</v>
+      </c>
+      <c r="G192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="G192" s="1" t="n">
+      <c r="H192" s="1" t="n">
         <v>0.03914</v>
       </c>
     </row>
@@ -5259,9 +5838,12 @@
         <v>0.0002228</v>
       </c>
       <c r="F193" s="1" t="n">
-        <v>0.0002228</v>
+        <v>0.000223</v>
       </c>
       <c r="G193" s="1" t="n">
+        <v>0.000223</v>
+      </c>
+      <c r="H193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -5284,9 +5866,12 @@
         <v>4.173</v>
       </c>
       <c r="F194" s="1" t="n">
+        <v>4.164</v>
+      </c>
+      <c r="G194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="G194" s="1" t="n">
+      <c r="H194" s="1" t="n">
         <v>4.154</v>
       </c>
     </row>
@@ -5309,9 +5894,12 @@
         <v>0.999341</v>
       </c>
       <c r="F195" s="1" t="n">
+        <v>0.99934</v>
+      </c>
+      <c r="G195" s="1" t="n">
         <v>0.999341</v>
       </c>
-      <c r="G195" s="1" t="n">
+      <c r="H195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -5334,9 +5922,12 @@
         <v>4.347</v>
       </c>
       <c r="F196" s="1" t="n">
+        <v>4.324</v>
+      </c>
+      <c r="G196" s="1" t="n">
         <v>4.347</v>
       </c>
-      <c r="G196" s="1" t="n">
+      <c r="H196" s="1" t="n">
         <v>4.302</v>
       </c>
     </row>
@@ -5359,9 +5950,12 @@
         <v>0.15011</v>
       </c>
       <c r="F197" s="1" t="n">
-        <v>0.15012</v>
+        <v>0.15048</v>
       </c>
       <c r="G197" s="1" t="n">
+        <v>0.15048</v>
+      </c>
+      <c r="H197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -5384,9 +5978,12 @@
         <v>0.007508</v>
       </c>
       <c r="F198" s="1" t="n">
-        <v>0.007586</v>
+        <v>0.007661</v>
       </c>
       <c r="G198" s="1" t="n">
+        <v>0.007661</v>
+      </c>
+      <c r="H198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -5409,9 +6006,12 @@
         <v>0.4524</v>
       </c>
       <c r="F199" s="1" t="n">
-        <v>0.4524</v>
+        <v>0.4528</v>
       </c>
       <c r="G199" s="1" t="n">
+        <v>0.4528</v>
+      </c>
+      <c r="H199" s="1" t="n">
         <v>0.4483</v>
       </c>
     </row>
@@ -5434,9 +6034,12 @@
         <v>0.5777</v>
       </c>
       <c r="F200" s="1" t="n">
-        <v>0.5777</v>
+        <v>0.5857</v>
       </c>
       <c r="G200" s="1" t="n">
+        <v>0.5857</v>
+      </c>
+      <c r="H200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -5462,6 +6065,9 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="G201" s="1" t="n">
+        <v>0.09429999999999999</v>
+      </c>
+      <c r="H201" s="1" t="n">
         <v>0.09379999999999999</v>
       </c>
     </row>
@@ -5484,9 +6090,12 @@
         <v>0.06118</v>
       </c>
       <c r="F202" s="1" t="n">
-        <v>0.06118</v>
+        <v>0.0612</v>
       </c>
       <c r="G202" s="1" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="H202" s="1" t="n">
         <v>0.06063</v>
       </c>
     </row>
@@ -5509,9 +6118,12 @@
         <v>0.008580000000000001</v>
       </c>
       <c r="F203" s="1" t="n">
-        <v>0.008580000000000001</v>
+        <v>0.008619999999999999</v>
       </c>
       <c r="G203" s="1" t="n">
+        <v>0.008619999999999999</v>
+      </c>
+      <c r="H203" s="1" t="n">
         <v>0.008359999999999999</v>
       </c>
     </row>
@@ -5534,9 +6146,12 @@
         <v>0.00423</v>
       </c>
       <c r="F204" s="1" t="n">
+        <v>0.00422</v>
+      </c>
+      <c r="G204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="G204" s="1" t="n">
+      <c r="H204" s="1" t="n">
         <v>0.00421</v>
       </c>
     </row>
@@ -5559,10 +6174,13 @@
         <v>0.009176999999999999</v>
       </c>
       <c r="F205" s="1" t="n">
+        <v>0.009154000000000001</v>
+      </c>
+      <c r="G205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="G205" s="1" t="n">
-        <v>0.009176999999999999</v>
+      <c r="H205" s="1" t="n">
+        <v>0.009154000000000001</v>
       </c>
     </row>
     <row r="206">
@@ -5584,9 +6202,12 @@
         <v>0.2399</v>
       </c>
       <c r="F206" s="1" t="n">
+        <v>0.2391</v>
+      </c>
+      <c r="G206" s="1" t="n">
         <v>0.2399</v>
       </c>
-      <c r="G206" s="1" t="n">
+      <c r="H206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -5609,9 +6230,12 @@
         <v>0.0215</v>
       </c>
       <c r="F207" s="1" t="n">
+        <v>0.02133</v>
+      </c>
+      <c r="G207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="G207" s="1" t="n">
+      <c r="H207" s="1" t="n">
         <v>0.02128</v>
       </c>
     </row>
@@ -5634,9 +6258,12 @@
         <v>0.2386</v>
       </c>
       <c r="F208" s="1" t="n">
+        <v>0.2379</v>
+      </c>
+      <c r="G208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="G208" s="1" t="n">
+      <c r="H208" s="1" t="n">
         <v>0.2366</v>
       </c>
     </row>
@@ -5659,10 +6286,13 @@
         <v>0.3619</v>
       </c>
       <c r="F209" s="1" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="G209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="G209" s="1" t="n">
-        <v>0.3616</v>
+      <c r="H209" s="1" t="n">
+        <v>0.3613</v>
       </c>
     </row>
     <row r="210">
@@ -5684,9 +6314,12 @@
         <v>0.04318</v>
       </c>
       <c r="F210" s="1" t="n">
+        <v>0.04307</v>
+      </c>
+      <c r="G210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="G210" s="1" t="n">
+      <c r="H210" s="1" t="n">
         <v>0.04286</v>
       </c>
     </row>
@@ -5709,9 +6342,12 @@
         <v>0.0004327</v>
       </c>
       <c r="F211" s="1" t="n">
+        <v>0.0004318</v>
+      </c>
+      <c r="G211" s="1" t="n">
         <v>0.0004327</v>
       </c>
-      <c r="G211" s="1" t="n">
+      <c r="H211" s="1" t="n">
         <v>0.0004282</v>
       </c>
     </row>
@@ -5734,9 +6370,12 @@
         <v>0.02177</v>
       </c>
       <c r="F212" s="1" t="n">
+        <v>0.02173</v>
+      </c>
+      <c r="G212" s="1" t="n">
         <v>0.02177</v>
       </c>
-      <c r="G212" s="1" t="n">
+      <c r="H212" s="1" t="n">
         <v>0.0216</v>
       </c>
     </row>
@@ -5759,9 +6398,12 @@
         <v>0.1156</v>
       </c>
       <c r="F213" s="1" t="n">
+        <v>0.1154</v>
+      </c>
+      <c r="G213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="G213" s="1" t="n">
+      <c r="H213" s="1" t="n">
         <v>0.1151</v>
       </c>
     </row>
@@ -5784,9 +6426,12 @@
         <v>0.04206</v>
       </c>
       <c r="F214" s="1" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="G214" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="G214" s="1" t="n">
+      <c r="H214" s="1" t="n">
         <v>0.04188</v>
       </c>
     </row>
@@ -5809,9 +6454,12 @@
         <v>0.010079</v>
       </c>
       <c r="F215" s="1" t="n">
+        <v>0.010016</v>
+      </c>
+      <c r="G215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="G215" s="1" t="n">
+      <c r="H215" s="1" t="n">
         <v>0.009896</v>
       </c>
     </row>
@@ -5834,9 +6482,12 @@
         <v>0.0643</v>
       </c>
       <c r="F216" s="1" t="n">
-        <v>0.0643</v>
+        <v>0.0644</v>
       </c>
       <c r="G216" s="1" t="n">
+        <v>0.0644</v>
+      </c>
+      <c r="H216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -5859,9 +6510,12 @@
         <v>0.004216</v>
       </c>
       <c r="F217" s="1" t="n">
+        <v>0.004211</v>
+      </c>
+      <c r="G217" s="1" t="n">
         <v>0.004216</v>
       </c>
-      <c r="G217" s="1" t="n">
+      <c r="H217" s="1" t="n">
         <v>0.004177</v>
       </c>
     </row>
@@ -5884,10 +6538,13 @@
         <v>0.01079</v>
       </c>
       <c r="F218" s="1" t="n">
+        <v>0.01049</v>
+      </c>
+      <c r="G218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="G218" s="1" t="n">
-        <v>0.01062</v>
+      <c r="H218" s="1" t="n">
+        <v>0.01049</v>
       </c>
     </row>
     <row r="219">
@@ -5909,10 +6566,13 @@
         <v>0.03068</v>
       </c>
       <c r="F219" s="1" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="G219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="G219" s="1" t="n">
-        <v>0.03054</v>
+      <c r="H219" s="1" t="n">
+        <v>0.0303</v>
       </c>
     </row>
     <row r="220">
@@ -5934,9 +6594,12 @@
         <v>2.315</v>
       </c>
       <c r="F220" s="1" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="G220" s="1" t="n">
+      <c r="H220" s="1" t="n">
         <v>2.296</v>
       </c>
     </row>
@@ -5959,9 +6622,12 @@
         <v>0.023224</v>
       </c>
       <c r="F221" s="1" t="n">
+        <v>0.023132</v>
+      </c>
+      <c r="G221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="G221" s="1" t="n">
+      <c r="H221" s="1" t="n">
         <v>0.023027</v>
       </c>
     </row>
@@ -5984,9 +6650,12 @@
         <v>0.0372</v>
       </c>
       <c r="F222" s="1" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="G222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="G222" s="1" t="n">
+      <c r="H222" s="1" t="n">
         <v>0.037</v>
       </c>
     </row>
@@ -6009,9 +6678,12 @@
         <v>0.295</v>
       </c>
       <c r="F223" s="1" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="G223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="G223" s="1" t="n">
+      <c r="H223" s="1" t="n">
         <v>0.294</v>
       </c>
     </row>
@@ -6034,9 +6706,12 @@
         <v>0.01576</v>
       </c>
       <c r="F224" s="1" t="n">
-        <v>0.01576</v>
+        <v>0.01577</v>
       </c>
       <c r="G224" s="1" t="n">
+        <v>0.01577</v>
+      </c>
+      <c r="H224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -6059,9 +6734,12 @@
         <v>0.0004153</v>
       </c>
       <c r="F225" s="1" t="n">
+        <v>0.0004141</v>
+      </c>
+      <c r="G225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="G225" s="1" t="n">
+      <c r="H225" s="1" t="n">
         <v>0.0004112</v>
       </c>
     </row>
@@ -6084,9 +6762,12 @@
         <v>0.0881</v>
       </c>
       <c r="F226" s="1" t="n">
+        <v>0.08806</v>
+      </c>
+      <c r="G226" s="1" t="n">
         <v>0.0881</v>
       </c>
-      <c r="G226" s="1" t="n">
+      <c r="H226" s="1" t="n">
         <v>0.08731999999999999</v>
       </c>
     </row>
@@ -6109,9 +6790,12 @@
         <v>0.956</v>
       </c>
       <c r="F227" s="1" t="n">
+        <v>0.955</v>
+      </c>
+      <c r="G227" s="1" t="n">
         <v>0.956</v>
       </c>
-      <c r="G227" s="1" t="n">
+      <c r="H227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -6134,9 +6818,12 @@
         <v>0.05641</v>
       </c>
       <c r="F228" s="1" t="n">
+        <v>0.05634</v>
+      </c>
+      <c r="G228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="G228" s="1" t="n">
+      <c r="H228" s="1" t="n">
         <v>0.0558</v>
       </c>
     </row>
@@ -6159,9 +6846,12 @@
         <v>0.002035</v>
       </c>
       <c r="F229" s="1" t="n">
+        <v>0.002027</v>
+      </c>
+      <c r="G229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="G229" s="1" t="n">
+      <c r="H229" s="1" t="n">
         <v>0.002017</v>
       </c>
     </row>
@@ -6184,9 +6874,12 @@
         <v>0.022893</v>
       </c>
       <c r="F230" s="1" t="n">
+        <v>0.022865</v>
+      </c>
+      <c r="G230" s="1" t="n">
         <v>0.022893</v>
       </c>
-      <c r="G230" s="1" t="n">
+      <c r="H230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -6209,10 +6902,13 @@
         <v>0.05507</v>
       </c>
       <c r="F231" s="1" t="n">
+        <v>0.05459</v>
+      </c>
+      <c r="G231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="G231" s="1" t="n">
-        <v>0.05471</v>
+      <c r="H231" s="1" t="n">
+        <v>0.05459</v>
       </c>
     </row>
     <row r="232">
@@ -6234,9 +6930,12 @@
         <v>0.0597</v>
       </c>
       <c r="F232" s="1" t="n">
+        <v>0.0595</v>
+      </c>
+      <c r="G232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="G232" s="1" t="n">
+      <c r="H232" s="1" t="n">
         <v>0.0591</v>
       </c>
     </row>
@@ -6259,9 +6958,12 @@
         <v>0.001701</v>
       </c>
       <c r="F233" s="1" t="n">
+        <v>0.001697</v>
+      </c>
+      <c r="G233" s="1" t="n">
         <v>0.001701</v>
       </c>
-      <c r="G233" s="1" t="n">
+      <c r="H233" s="1" t="n">
         <v>0.001678</v>
       </c>
     </row>
@@ -6284,9 +6986,12 @@
         <v>0.005837</v>
       </c>
       <c r="F234" s="1" t="n">
+        <v>0.005836</v>
+      </c>
+      <c r="G234" s="1" t="n">
         <v>0.005837</v>
       </c>
-      <c r="G234" s="1" t="n">
+      <c r="H234" s="1" t="n">
         <v>0.005784</v>
       </c>
     </row>
@@ -6309,9 +7014,12 @@
         <v>0.1264</v>
       </c>
       <c r="F235" s="1" t="n">
+        <v>0.12599</v>
+      </c>
+      <c r="G235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="G235" s="1" t="n">
+      <c r="H235" s="1" t="n">
         <v>0.12453</v>
       </c>
     </row>
@@ -6334,9 +7042,12 @@
         <v>65.23</v>
       </c>
       <c r="F236" s="1" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="G236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="G236" s="1" t="n">
+      <c r="H236" s="1" t="n">
         <v>64.78</v>
       </c>
     </row>
@@ -6359,9 +7070,12 @@
         <v>0.1032</v>
       </c>
       <c r="F237" s="1" t="n">
+        <v>0.1026</v>
+      </c>
+      <c r="G237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="G237" s="1" t="n">
+      <c r="H237" s="1" t="n">
         <v>0.1021</v>
       </c>
     </row>
@@ -6384,9 +7098,12 @@
         <v>0.003989</v>
       </c>
       <c r="F238" s="1" t="n">
-        <v>0.003989</v>
+        <v>0.00399</v>
       </c>
       <c r="G238" s="1" t="n">
+        <v>0.00399</v>
+      </c>
+      <c r="H238" s="1" t="n">
         <v>0.003925</v>
       </c>
     </row>
@@ -6412,6 +7129,9 @@
         <v>0.01556</v>
       </c>
       <c r="G239" s="1" t="n">
+        <v>0.01556</v>
+      </c>
+      <c r="H239" s="1" t="n">
         <v>0.01532</v>
       </c>
     </row>
@@ -6434,9 +7154,12 @@
         <v>0.05673</v>
       </c>
       <c r="F240" s="1" t="n">
+        <v>0.05661</v>
+      </c>
+      <c r="G240" s="1" t="n">
         <v>0.05673</v>
       </c>
-      <c r="G240" s="1" t="n">
+      <c r="H240" s="1" t="n">
         <v>0.05621</v>
       </c>
     </row>
@@ -6462,6 +7185,9 @@
         <v>0.0116</v>
       </c>
       <c r="G241" s="1" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="H241" s="1" t="n">
         <v>0.0114</v>
       </c>
     </row>
@@ -6484,9 +7210,12 @@
         <v>0.3388</v>
       </c>
       <c r="F242" s="1" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="G242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="G242" s="1" t="n">
+      <c r="H242" s="1" t="n">
         <v>0.336</v>
       </c>
     </row>
@@ -6509,9 +7238,12 @@
         <v>0.01249</v>
       </c>
       <c r="F243" s="1" t="n">
+        <v>0.01246</v>
+      </c>
+      <c r="G243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="G243" s="1" t="n">
+      <c r="H243" s="1" t="n">
         <v>0.01241</v>
       </c>
     </row>
@@ -6534,9 +7266,12 @@
         <v>0.08043</v>
       </c>
       <c r="F244" s="1" t="n">
+        <v>0.08032</v>
+      </c>
+      <c r="G244" s="1" t="n">
         <v>0.08051999999999999</v>
       </c>
-      <c r="G244" s="1" t="n">
+      <c r="H244" s="1" t="n">
         <v>0.07997</v>
       </c>
     </row>
@@ -6559,10 +7294,13 @@
         <v>0.007972999999999999</v>
       </c>
       <c r="F245" s="1" t="n">
+        <v>0.007967999999999999</v>
+      </c>
+      <c r="G245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="G245" s="1" t="n">
-        <v>0.007972999999999999</v>
+      <c r="H245" s="1" t="n">
+        <v>0.007967999999999999</v>
       </c>
     </row>
     <row r="246">
@@ -6584,9 +7322,12 @@
         <v>0.03071</v>
       </c>
       <c r="F246" s="1" t="n">
+        <v>0.03065</v>
+      </c>
+      <c r="G246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="G246" s="1" t="n">
+      <c r="H246" s="1" t="n">
         <v>0.03056</v>
       </c>
     </row>
@@ -6609,9 +7350,12 @@
         <v>0.1823</v>
       </c>
       <c r="F247" s="1" t="n">
-        <v>0.1823</v>
+        <v>0.1826</v>
       </c>
       <c r="G247" s="1" t="n">
+        <v>0.1826</v>
+      </c>
+      <c r="H247" s="1" t="n">
         <v>0.1808</v>
       </c>
     </row>
@@ -6634,9 +7378,12 @@
         <v>0.05956</v>
       </c>
       <c r="F248" s="1" t="n">
+        <v>0.05952</v>
+      </c>
+      <c r="G248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="G248" s="1" t="n">
+      <c r="H248" s="1" t="n">
         <v>0.05915</v>
       </c>
     </row>
@@ -6659,9 +7406,12 @@
         <v>0.1682</v>
       </c>
       <c r="F249" s="1" t="n">
-        <v>0.1682</v>
+        <v>0.1683</v>
       </c>
       <c r="G249" s="1" t="n">
+        <v>0.1683</v>
+      </c>
+      <c r="H249" s="1" t="n">
         <v>0.1664</v>
       </c>
     </row>
@@ -6684,9 +7434,12 @@
         <v>0.01944</v>
       </c>
       <c r="F250" s="1" t="n">
+        <v>0.01944</v>
+      </c>
+      <c r="G250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="G250" s="1" t="n">
+      <c r="H250" s="1" t="n">
         <v>0.01938</v>
       </c>
     </row>
@@ -6709,9 +7462,12 @@
         <v>0.02318</v>
       </c>
       <c r="F251" s="1" t="n">
+        <v>0.02311</v>
+      </c>
+      <c r="G251" s="1" t="n">
         <v>0.02318</v>
       </c>
-      <c r="G251" s="1" t="n">
+      <c r="H251" s="1" t="n">
         <v>0.02304</v>
       </c>
     </row>
@@ -6734,9 +7490,12 @@
         <v>0.30378</v>
       </c>
       <c r="F252" s="1" t="n">
-        <v>0.30378</v>
+        <v>0.30577</v>
       </c>
       <c r="G252" s="1" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="H252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -6759,10 +7518,13 @@
         <v>0.006143</v>
       </c>
       <c r="F253" s="1" t="n">
+        <v>0.006063</v>
+      </c>
+      <c r="G253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="G253" s="1" t="n">
-        <v>0.00607</v>
+      <c r="H253" s="1" t="n">
+        <v>0.006063</v>
       </c>
     </row>
     <row r="254">
@@ -6784,9 +7546,12 @@
         <v>0.6193</v>
       </c>
       <c r="F254" s="1" t="n">
+        <v>0.6185</v>
+      </c>
+      <c r="G254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="G254" s="1" t="n">
+      <c r="H254" s="1" t="n">
         <v>0.6141</v>
       </c>
     </row>
@@ -6809,10 +7574,13 @@
         <v>0.10823</v>
       </c>
       <c r="F255" s="1" t="n">
+        <v>0.10726</v>
+      </c>
+      <c r="G255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="G255" s="1" t="n">
-        <v>0.10785</v>
+      <c r="H255" s="1" t="n">
+        <v>0.10726</v>
       </c>
     </row>
     <row r="256">
@@ -6834,9 +7602,12 @@
         <v>0.0911</v>
       </c>
       <c r="F256" s="1" t="n">
+        <v>0.0907</v>
+      </c>
+      <c r="G256" s="1" t="n">
         <v>0.0911</v>
       </c>
-      <c r="G256" s="1" t="n">
+      <c r="H256" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -6859,9 +7630,12 @@
         <v>0.01454</v>
       </c>
       <c r="F257" s="1" t="n">
+        <v>0.01446</v>
+      </c>
+      <c r="G257" s="1" t="n">
         <v>0.01454</v>
       </c>
-      <c r="G257" s="1" t="n">
+      <c r="H257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -6884,9 +7658,12 @@
         <v>0.05122</v>
       </c>
       <c r="F258" s="1" t="n">
-        <v>0.0514</v>
+        <v>0.05145</v>
       </c>
       <c r="G258" s="1" t="n">
+        <v>0.05145</v>
+      </c>
+      <c r="H258" s="1" t="n">
         <v>0.0511</v>
       </c>
     </row>
@@ -6909,9 +7686,12 @@
         <v>0.00829</v>
       </c>
       <c r="F259" s="1" t="n">
+        <v>0.00827</v>
+      </c>
+      <c r="G259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="G259" s="1" t="n">
+      <c r="H259" s="1" t="n">
         <v>0.008240000000000001</v>
       </c>
     </row>
@@ -6934,9 +7714,12 @@
         <v>0.1914</v>
       </c>
       <c r="F260" s="1" t="n">
-        <v>0.1914</v>
+        <v>0.1915</v>
       </c>
       <c r="G260" s="1" t="n">
+        <v>0.1915</v>
+      </c>
+      <c r="H260" s="1" t="n">
         <v>0.1902</v>
       </c>
     </row>
@@ -6959,9 +7742,12 @@
         <v>0.0993</v>
       </c>
       <c r="F261" s="1" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="G261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="G261" s="1" t="n">
+      <c r="H261" s="1" t="n">
         <v>0.09859999999999999</v>
       </c>
     </row>
@@ -6987,6 +7773,9 @@
         <v>0.2144</v>
       </c>
       <c r="G262" s="1" t="n">
+        <v>0.2144</v>
+      </c>
+      <c r="H262" s="1" t="n">
         <v>0.2128</v>
       </c>
     </row>
@@ -7009,9 +7798,12 @@
         <v>0.008451999999999999</v>
       </c>
       <c r="F263" s="1" t="n">
-        <v>0.008451999999999999</v>
+        <v>0.008510999999999999</v>
       </c>
       <c r="G263" s="1" t="n">
+        <v>0.008510999999999999</v>
+      </c>
+      <c r="H263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -7034,9 +7826,12 @@
         <v>2.658</v>
       </c>
       <c r="F264" s="1" t="n">
+        <v>2.652</v>
+      </c>
+      <c r="G264" s="1" t="n">
         <v>2.658</v>
       </c>
-      <c r="G264" s="1" t="n">
+      <c r="H264" s="1" t="n">
         <v>2.647</v>
       </c>
     </row>
@@ -7059,9 +7854,12 @@
         <v>0.0186</v>
       </c>
       <c r="F265" s="1" t="n">
+        <v>0.01877</v>
+      </c>
+      <c r="G265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="G265" s="1" t="n">
+      <c r="H265" s="1" t="n">
         <v>0.01847</v>
       </c>
     </row>
@@ -7084,10 +7882,13 @@
         <v>0.3603</v>
       </c>
       <c r="F266" s="1" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="G266" s="1" t="n">
         <v>0.3604</v>
       </c>
-      <c r="G266" s="1" t="n">
-        <v>0.3595</v>
+      <c r="H266" s="1" t="n">
+        <v>0.359</v>
       </c>
     </row>
     <row r="267">
@@ -7109,9 +7910,12 @@
         <v>0.03446</v>
       </c>
       <c r="F267" s="1" t="n">
+        <v>0.03441</v>
+      </c>
+      <c r="G267" s="1" t="n">
         <v>0.03464</v>
       </c>
-      <c r="G267" s="1" t="n">
+      <c r="H267" s="1" t="n">
         <v>0.03429</v>
       </c>
     </row>
@@ -7134,9 +7938,12 @@
         <v>0.119</v>
       </c>
       <c r="F268" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G268" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="G268" s="1" t="n">
+      <c r="H268" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -7159,9 +7966,12 @@
         <v>0.08105</v>
       </c>
       <c r="F269" s="1" t="n">
+        <v>0.08082</v>
+      </c>
+      <c r="G269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="G269" s="1" t="n">
+      <c r="H269" s="1" t="n">
         <v>0.08053</v>
       </c>
     </row>
@@ -7184,9 +7994,12 @@
         <v>0.01402</v>
       </c>
       <c r="F270" s="1" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="G270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="G270" s="1" t="n">
+      <c r="H270" s="1" t="n">
         <v>0.01397</v>
       </c>
     </row>
@@ -7209,9 +8022,12 @@
         <v>0.007707</v>
       </c>
       <c r="F271" s="1" t="n">
+        <v>0.007681</v>
+      </c>
+      <c r="G271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="G271" s="1" t="n">
+      <c r="H271" s="1" t="n">
         <v>0.007654</v>
       </c>
     </row>
@@ -7234,10 +8050,13 @@
         <v>0.07439</v>
       </c>
       <c r="F272" s="1" t="n">
+        <v>0.07414</v>
+      </c>
+      <c r="G272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="G272" s="1" t="n">
-        <v>0.07425</v>
+      <c r="H272" s="1" t="n">
+        <v>0.07414</v>
       </c>
     </row>
     <row r="273">
@@ -7262,6 +8081,9 @@
         <v>3.16e-05</v>
       </c>
       <c r="G273" s="1" t="n">
+        <v>3.16e-05</v>
+      </c>
+      <c r="H273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -7284,10 +8106,13 @@
         <v>0.005576</v>
       </c>
       <c r="F274" s="1" t="n">
+        <v>0.005556</v>
+      </c>
+      <c r="G274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="G274" s="1" t="n">
-        <v>0.005576</v>
+      <c r="H274" s="1" t="n">
+        <v>0.005556</v>
       </c>
     </row>
     <row r="275">
@@ -7309,9 +8134,12 @@
         <v>0.1817</v>
       </c>
       <c r="F275" s="1" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="G275" s="1" t="n">
         <v>0.1817</v>
       </c>
-      <c r="G275" s="1" t="n">
+      <c r="H275" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -7334,9 +8162,12 @@
         <v>0.006933</v>
       </c>
       <c r="F276" s="1" t="n">
+        <v>0.006917</v>
+      </c>
+      <c r="G276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="G276" s="1" t="n">
+      <c r="H276" s="1" t="n">
         <v>0.006876</v>
       </c>
     </row>
@@ -7359,9 +8190,12 @@
         <v>0.1332</v>
       </c>
       <c r="F277" s="1" t="n">
+        <v>0.1321</v>
+      </c>
+      <c r="G277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="G277" s="1" t="n">
+      <c r="H277" s="1" t="n">
         <v>0.1316</v>
       </c>
     </row>
@@ -7384,9 +8218,12 @@
         <v>0.02355</v>
       </c>
       <c r="F278" s="1" t="n">
+        <v>0.02343</v>
+      </c>
+      <c r="G278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="G278" s="1" t="n">
+      <c r="H278" s="1" t="n">
         <v>0.02335</v>
       </c>
     </row>
@@ -7409,9 +8246,12 @@
         <v>0.01827</v>
       </c>
       <c r="F279" s="1" t="n">
+        <v>0.01822</v>
+      </c>
+      <c r="G279" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="G279" s="1" t="n">
+      <c r="H279" s="1" t="n">
         <v>0.01817</v>
       </c>
     </row>
@@ -7434,9 +8274,12 @@
         <v>0.03773</v>
       </c>
       <c r="F280" s="1" t="n">
+        <v>0.03772</v>
+      </c>
+      <c r="G280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="G280" s="1" t="n">
+      <c r="H280" s="1" t="n">
         <v>0.03755</v>
       </c>
     </row>
@@ -7459,9 +8302,12 @@
         <v>0.0401</v>
       </c>
       <c r="F281" s="1" t="n">
+        <v>0.04005</v>
+      </c>
+      <c r="G281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="G281" s="1" t="n">
+      <c r="H281" s="1" t="n">
         <v>0.03981</v>
       </c>
     </row>
@@ -7484,9 +8330,12 @@
         <v>0.3059</v>
       </c>
       <c r="F282" s="1" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="G282" s="1" t="n">
         <v>0.3059</v>
       </c>
-      <c r="G282" s="1" t="n">
+      <c r="H282" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -7509,9 +8358,12 @@
         <v>0.01133</v>
       </c>
       <c r="F283" s="1" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="G283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="G283" s="1" t="n">
+      <c r="H283" s="1" t="n">
         <v>0.01124</v>
       </c>
     </row>
@@ -7534,9 +8386,12 @@
         <v>9.500000000000001e-06</v>
       </c>
       <c r="F284" s="1" t="n">
+        <v>9.6e-06</v>
+      </c>
+      <c r="G284" s="1" t="n">
         <v>9.7e-06</v>
       </c>
-      <c r="G284" s="1" t="n">
+      <c r="H284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -7559,9 +8414,12 @@
         <v>0.1157</v>
       </c>
       <c r="F285" s="1" t="n">
+        <v>0.1155</v>
+      </c>
+      <c r="G285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="G285" s="1" t="n">
+      <c r="H285" s="1" t="n">
         <v>0.1153</v>
       </c>
     </row>
@@ -7584,9 +8442,12 @@
         <v>0.003466</v>
       </c>
       <c r="F286" s="1" t="n">
+        <v>0.003465</v>
+      </c>
+      <c r="G286" s="1" t="n">
         <v>0.003466</v>
       </c>
-      <c r="G286" s="1" t="n">
+      <c r="H286" s="1" t="n">
         <v>0.003442</v>
       </c>
     </row>
@@ -7609,9 +8470,12 @@
         <v>0.08568000000000001</v>
       </c>
       <c r="F287" s="1" t="n">
-        <v>0.08568000000000001</v>
+        <v>0.08573</v>
       </c>
       <c r="G287" s="1" t="n">
+        <v>0.08573</v>
+      </c>
+      <c r="H287" s="1" t="n">
         <v>0.08545999999999999</v>
       </c>
     </row>
@@ -7634,9 +8498,12 @@
         <v>0.09895</v>
       </c>
       <c r="F288" s="1" t="n">
+        <v>0.09969</v>
+      </c>
+      <c r="G288" s="1" t="n">
         <v>0.1001</v>
       </c>
-      <c r="G288" s="1" t="n">
+      <c r="H288" s="1" t="n">
         <v>0.09889000000000001</v>
       </c>
     </row>
@@ -7659,9 +8526,12 @@
         <v>0.434</v>
       </c>
       <c r="F289" s="1" t="n">
+        <v>0.4334</v>
+      </c>
+      <c r="G289" s="1" t="n">
         <v>0.434</v>
       </c>
-      <c r="G289" s="1" t="n">
+      <c r="H289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -7684,9 +8554,12 @@
         <v>0.03966</v>
       </c>
       <c r="F290" s="1" t="n">
+        <v>0.03955</v>
+      </c>
+      <c r="G290" s="1" t="n">
         <v>0.03966</v>
       </c>
-      <c r="G290" s="1" t="n">
+      <c r="H290" s="1" t="n">
         <v>0.03921</v>
       </c>
     </row>
@@ -7709,9 +8582,12 @@
         <v>0.2447</v>
       </c>
       <c r="F291" s="1" t="n">
+        <v>0.2435</v>
+      </c>
+      <c r="G291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="G291" s="1" t="n">
+      <c r="H291" s="1" t="n">
         <v>0.2416</v>
       </c>
     </row>
@@ -7734,9 +8610,12 @@
         <v>0.28275</v>
       </c>
       <c r="F292" s="1" t="n">
+        <v>0.2831</v>
+      </c>
+      <c r="G292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="G292" s="1" t="n">
+      <c r="H292" s="1" t="n">
         <v>0.28275</v>
       </c>
     </row>
@@ -7759,9 +8638,12 @@
         <v>0.1505</v>
       </c>
       <c r="F293" s="1" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="G293" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="G293" s="1" t="n">
+      <c r="H293" s="1" t="n">
         <v>0.1498</v>
       </c>
     </row>
@@ -7784,9 +8666,12 @@
         <v>4.269</v>
       </c>
       <c r="F294" s="1" t="n">
+        <v>4.257</v>
+      </c>
+      <c r="G294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="G294" s="1" t="n">
+      <c r="H294" s="1" t="n">
         <v>4.238</v>
       </c>
     </row>
@@ -7809,9 +8694,12 @@
         <v>0.03267</v>
       </c>
       <c r="F295" s="1" t="n">
-        <v>0.03267</v>
+        <v>0.03292</v>
       </c>
       <c r="G295" s="1" t="n">
+        <v>0.03292</v>
+      </c>
+      <c r="H295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -7834,9 +8722,12 @@
         <v>0.000987</v>
       </c>
       <c r="F296" s="1" t="n">
-        <v>0.0009890000000000001</v>
+        <v>0.0009909999999999999</v>
       </c>
       <c r="G296" s="1" t="n">
+        <v>0.0009909999999999999</v>
+      </c>
+      <c r="H296" s="1" t="n">
         <v>0.00098</v>
       </c>
     </row>
@@ -7859,9 +8750,12 @@
         <v>0.08259</v>
       </c>
       <c r="F297" s="1" t="n">
+        <v>0.08236</v>
+      </c>
+      <c r="G297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="G297" s="1" t="n">
+      <c r="H297" s="1" t="n">
         <v>0.08209</v>
       </c>
     </row>
@@ -7884,9 +8778,12 @@
         <v>0.05815</v>
       </c>
       <c r="F298" s="1" t="n">
+        <v>0.05806</v>
+      </c>
+      <c r="G298" s="1" t="n">
         <v>0.05815</v>
       </c>
-      <c r="G298" s="1" t="n">
+      <c r="H298" s="1" t="n">
         <v>0.05763</v>
       </c>
     </row>
@@ -7909,9 +8806,12 @@
         <v>0.09102</v>
       </c>
       <c r="F299" s="1" t="n">
-        <v>0.09109</v>
+        <v>0.0917</v>
       </c>
       <c r="G299" s="1" t="n">
+        <v>0.0917</v>
+      </c>
+      <c r="H299" s="1" t="n">
         <v>0.09066</v>
       </c>
     </row>
@@ -7934,9 +8834,12 @@
         <v>0.02781</v>
       </c>
       <c r="F300" s="1" t="n">
+        <v>0.02771</v>
+      </c>
+      <c r="G300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="G300" s="1" t="n">
+      <c r="H300" s="1" t="n">
         <v>0.02764</v>
       </c>
     </row>
@@ -7959,9 +8862,12 @@
         <v>0.06634</v>
       </c>
       <c r="F301" s="1" t="n">
+        <v>0.06605999999999999</v>
+      </c>
+      <c r="G301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="G301" s="1" t="n">
+      <c r="H301" s="1" t="n">
         <v>0.06603000000000001</v>
       </c>
     </row>
@@ -7984,9 +8890,12 @@
         <v>0.052584</v>
       </c>
       <c r="F302" s="1" t="n">
+        <v>0.05232</v>
+      </c>
+      <c r="G302" s="1" t="n">
         <v>0.052584</v>
       </c>
-      <c r="G302" s="1" t="n">
+      <c r="H302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -8009,9 +8918,12 @@
         <v>5162</v>
       </c>
       <c r="F303" s="1" t="n">
+        <v>5165.7</v>
+      </c>
+      <c r="G303" s="1" t="n">
         <v>5172.3</v>
       </c>
-      <c r="G303" s="1" t="n">
+      <c r="H303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -8034,9 +8946,12 @@
         <v>15.09</v>
       </c>
       <c r="F304" s="1" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="G304" s="1" t="n">
         <v>15.09</v>
       </c>
-      <c r="G304" s="1" t="n">
+      <c r="H304" s="1" t="n">
         <v>14.99</v>
       </c>
     </row>
@@ -8059,9 +8974,12 @@
         <v>0.003736</v>
       </c>
       <c r="F305" s="1" t="n">
+        <v>0.003728</v>
+      </c>
+      <c r="G305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="G305" s="1" t="n">
+      <c r="H305" s="1" t="n">
         <v>0.003722</v>
       </c>
     </row>
@@ -8084,9 +9002,12 @@
         <v>0.4607</v>
       </c>
       <c r="F306" s="1" t="n">
+        <v>0.4596</v>
+      </c>
+      <c r="G306" s="1" t="n">
         <v>0.4607</v>
       </c>
-      <c r="G306" s="1" t="n">
+      <c r="H306" s="1" t="n">
         <v>0.4573</v>
       </c>
     </row>
@@ -8109,9 +9030,12 @@
         <v>0.04753</v>
       </c>
       <c r="F307" s="1" t="n">
+        <v>0.04734</v>
+      </c>
+      <c r="G307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="G307" s="1" t="n">
+      <c r="H307" s="1" t="n">
         <v>0.04732</v>
       </c>
     </row>
@@ -8134,9 +9058,12 @@
         <v>1.4857</v>
       </c>
       <c r="F308" s="1" t="n">
-        <v>1.4857</v>
+        <v>1.4891</v>
       </c>
       <c r="G308" s="1" t="n">
+        <v>1.4891</v>
+      </c>
+      <c r="H308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -8159,9 +9086,12 @@
         <v>0.0008099</v>
       </c>
       <c r="F309" s="1" t="n">
+        <v>0.0008092</v>
+      </c>
+      <c r="G309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="G309" s="1" t="n">
+      <c r="H309" s="1" t="n">
         <v>0.0008068</v>
       </c>
     </row>
@@ -8184,10 +9114,13 @@
         <v>4.721</v>
       </c>
       <c r="F310" s="1" t="n">
+        <v>4.687</v>
+      </c>
+      <c r="G310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="G310" s="1" t="n">
-        <v>4.692</v>
+      <c r="H310" s="1" t="n">
+        <v>4.687</v>
       </c>
     </row>
     <row r="311">
@@ -8209,9 +9142,12 @@
         <v>4.805</v>
       </c>
       <c r="F311" s="1" t="n">
+        <v>4.788</v>
+      </c>
+      <c r="G311" s="1" t="n">
         <v>4.805</v>
       </c>
-      <c r="G311" s="1" t="n">
+      <c r="H311" s="1" t="n">
         <v>4.765</v>
       </c>
     </row>
@@ -8234,9 +9170,12 @@
         <v>0.08141</v>
       </c>
       <c r="F312" s="1" t="n">
+        <v>0.08126</v>
+      </c>
+      <c r="G312" s="1" t="n">
         <v>0.08141</v>
       </c>
-      <c r="G312" s="1" t="n">
+      <c r="H312" s="1" t="n">
         <v>0.08098</v>
       </c>
     </row>
@@ -8259,9 +9198,12 @@
         <v>2.041</v>
       </c>
       <c r="F313" s="1" t="n">
+        <v>2.039</v>
+      </c>
+      <c r="G313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="G313" s="1" t="n">
+      <c r="H313" s="1" t="n">
         <v>2.037</v>
       </c>
     </row>
@@ -8284,9 +9226,12 @@
         <v>0.07025000000000001</v>
       </c>
       <c r="F314" s="1" t="n">
-        <v>0.07025000000000001</v>
+        <v>0.07056999999999999</v>
       </c>
       <c r="G314" s="1" t="n">
+        <v>0.07056999999999999</v>
+      </c>
+      <c r="H314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -8309,10 +9254,13 @@
         <v>0.961</v>
       </c>
       <c r="F315" s="1" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="G315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="G315" s="1" t="n">
-        <v>0.959</v>
+      <c r="H315" s="1" t="n">
+        <v>0.957</v>
       </c>
     </row>
     <row r="316">
@@ -8334,9 +9282,12 @@
         <v>0.1313</v>
       </c>
       <c r="F316" s="1" t="n">
+        <v>0.1311</v>
+      </c>
+      <c r="G316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="G316" s="1" t="n">
+      <c r="H316" s="1" t="n">
         <v>0.1305</v>
       </c>
     </row>
@@ -8359,9 +9310,12 @@
         <v>0.1859</v>
       </c>
       <c r="F317" s="1" t="n">
+        <v>0.1839</v>
+      </c>
+      <c r="G317" s="1" t="n">
         <v>0.1859</v>
       </c>
-      <c r="G317" s="1" t="n">
+      <c r="H317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -8384,10 +9338,13 @@
         <v>0.01662</v>
       </c>
       <c r="F318" s="1" t="n">
+        <v>0.01634</v>
+      </c>
+      <c r="G318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="G318" s="1" t="n">
-        <v>0.01661</v>
+      <c r="H318" s="1" t="n">
+        <v>0.01634</v>
       </c>
     </row>
     <row r="319">
@@ -8409,9 +9366,12 @@
         <v>0.08445999999999999</v>
       </c>
       <c r="F319" s="1" t="n">
+        <v>0.08422</v>
+      </c>
+      <c r="G319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="G319" s="1" t="n">
+      <c r="H319" s="1" t="n">
         <v>0.08395</v>
       </c>
     </row>
@@ -8434,9 +9394,12 @@
         <v>0.007647</v>
       </c>
       <c r="F320" s="1" t="n">
+        <v>0.007655</v>
+      </c>
+      <c r="G320" s="1" t="n">
         <v>0.007659</v>
       </c>
-      <c r="G320" s="1" t="n">
+      <c r="H320" s="1" t="n">
         <v>0.007597</v>
       </c>
     </row>
@@ -8459,9 +9422,12 @@
         <v>0.05505</v>
       </c>
       <c r="F321" s="1" t="n">
+        <v>0.05484</v>
+      </c>
+      <c r="G321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="G321" s="1" t="n">
+      <c r="H321" s="1" t="n">
         <v>0.05452</v>
       </c>
     </row>
@@ -8484,9 +9450,12 @@
         <v>0.5508999999999999</v>
       </c>
       <c r="F322" s="1" t="n">
+        <v>0.5501</v>
+      </c>
+      <c r="G322" s="1" t="n">
         <v>0.5513</v>
       </c>
-      <c r="G322" s="1" t="n">
+      <c r="H322" s="1" t="n">
         <v>0.5483</v>
       </c>
     </row>
@@ -8509,9 +9478,12 @@
         <v>0.07565</v>
       </c>
       <c r="F323" s="1" t="n">
+        <v>0.07572</v>
+      </c>
+      <c r="G323" s="1" t="n">
         <v>0.07593</v>
       </c>
-      <c r="G323" s="1" t="n">
+      <c r="H323" s="1" t="n">
         <v>0.07525</v>
       </c>
     </row>
@@ -8534,9 +9506,12 @@
         <v>0.012885</v>
       </c>
       <c r="F324" s="1" t="n">
+        <v>0.012833</v>
+      </c>
+      <c r="G324" s="1" t="n">
         <v>0.012885</v>
       </c>
-      <c r="G324" s="1" t="n">
+      <c r="H324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -8559,9 +9534,12 @@
         <v>0.0999</v>
       </c>
       <c r="F325" s="1" t="n">
+        <v>0.0997</v>
+      </c>
+      <c r="G325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="G325" s="1" t="n">
+      <c r="H325" s="1" t="n">
         <v>0.0993</v>
       </c>
     </row>
@@ -8584,9 +9562,12 @@
         <v>0.01765</v>
       </c>
       <c r="F326" s="1" t="n">
+        <v>0.01763</v>
+      </c>
+      <c r="G326" s="1" t="n">
         <v>0.01765</v>
       </c>
-      <c r="G326" s="1" t="n">
+      <c r="H326" s="1" t="n">
         <v>0.01752</v>
       </c>
     </row>
@@ -8609,9 +9590,12 @@
         <v>0.06435</v>
       </c>
       <c r="F327" s="1" t="n">
+        <v>0.06418</v>
+      </c>
+      <c r="G327" s="1" t="n">
         <v>0.06435</v>
       </c>
-      <c r="G327" s="1" t="n">
+      <c r="H327" s="1" t="n">
         <v>0.06392</v>
       </c>
     </row>
@@ -8634,10 +9618,13 @@
         <v>0.2693</v>
       </c>
       <c r="F328" s="1" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="G328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="G328" s="1" t="n">
-        <v>0.2675</v>
+      <c r="H328" s="1" t="n">
+        <v>0.2671</v>
       </c>
     </row>
     <row r="329">
@@ -8659,9 +9646,12 @@
         <v>0.1725</v>
       </c>
       <c r="F329" s="1" t="n">
+        <v>0.17196</v>
+      </c>
+      <c r="G329" s="1" t="n">
         <v>0.17286</v>
       </c>
-      <c r="G329" s="1" t="n">
+      <c r="H329" s="1" t="n">
         <v>0.17172</v>
       </c>
     </row>
@@ -8684,9 +9674,12 @@
         <v>2.072</v>
       </c>
       <c r="F330" s="1" t="n">
+        <v>2.071</v>
+      </c>
+      <c r="G330" s="1" t="n">
         <v>2.072</v>
       </c>
-      <c r="G330" s="1" t="n">
+      <c r="H330" s="1" t="n">
         <v>2.043</v>
       </c>
     </row>
@@ -8709,9 +9702,12 @@
         <v>0.028</v>
       </c>
       <c r="F331" s="1" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="G331" s="1" t="n">
         <v>0.028</v>
       </c>
-      <c r="G331" s="1" t="n">
+      <c r="H331" s="1" t="n">
         <v>0.0278</v>
       </c>
     </row>
@@ -8734,9 +9730,12 @@
         <v>0.00602</v>
       </c>
       <c r="F332" s="1" t="n">
+        <v>0.006004</v>
+      </c>
+      <c r="G332" s="1" t="n">
         <v>0.00602</v>
       </c>
-      <c r="G332" s="1" t="n">
+      <c r="H332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -8759,9 +9758,12 @@
         <v>0.003558</v>
       </c>
       <c r="F333" s="1" t="n">
-        <v>0.003558</v>
+        <v>0.003579</v>
       </c>
       <c r="G333" s="1" t="n">
+        <v>0.003579</v>
+      </c>
+      <c r="H333" s="1" t="n">
         <v>0.003531</v>
       </c>
     </row>
@@ -8784,9 +9786,12 @@
         <v>0.01406</v>
       </c>
       <c r="F334" s="1" t="n">
+        <v>0.01408</v>
+      </c>
+      <c r="G334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="G334" s="1" t="n">
+      <c r="H334" s="1" t="n">
         <v>0.01399</v>
       </c>
     </row>
@@ -8809,9 +9814,12 @@
         <v>1.128</v>
       </c>
       <c r="F335" s="1" t="n">
+        <v>1.126</v>
+      </c>
+      <c r="G335" s="1" t="n">
         <v>1.128</v>
       </c>
-      <c r="G335" s="1" t="n">
+      <c r="H335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -8834,9 +9842,12 @@
         <v>0.011286</v>
       </c>
       <c r="F336" s="1" t="n">
+        <v>0.011305</v>
+      </c>
+      <c r="G336" s="1" t="n">
         <v>0.011326</v>
       </c>
-      <c r="G336" s="1" t="n">
+      <c r="H336" s="1" t="n">
         <v>0.011253</v>
       </c>
     </row>
@@ -8859,9 +9870,12 @@
         <v>2.974</v>
       </c>
       <c r="F337" s="1" t="n">
-        <v>2.974</v>
+        <v>3.043</v>
       </c>
       <c r="G337" s="1" t="n">
+        <v>3.043</v>
+      </c>
+      <c r="H337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -8884,9 +9898,12 @@
         <v>0.01882</v>
       </c>
       <c r="F338" s="1" t="n">
+        <v>0.01879</v>
+      </c>
+      <c r="G338" s="1" t="n">
         <v>0.01884</v>
       </c>
-      <c r="G338" s="1" t="n">
+      <c r="H338" s="1" t="n">
         <v>0.01861</v>
       </c>
     </row>
@@ -8909,9 +9926,12 @@
         <v>0.07781</v>
       </c>
       <c r="F339" s="1" t="n">
+        <v>0.07766000000000001</v>
+      </c>
+      <c r="G339" s="1" t="n">
         <v>0.07781</v>
       </c>
-      <c r="G339" s="1" t="n">
+      <c r="H339" s="1" t="n">
         <v>0.07689</v>
       </c>
     </row>
@@ -8934,9 +9954,12 @@
         <v>0.076</v>
       </c>
       <c r="F340" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="G340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="G340" s="1" t="n">
+      <c r="H340" s="1" t="n">
         <v>0.076</v>
       </c>
     </row>
@@ -8962,6 +9985,9 @@
         <v>0.03638</v>
       </c>
       <c r="G341" s="1" t="n">
+        <v>0.03638</v>
+      </c>
+      <c r="H341" s="1" t="n">
         <v>0.0362</v>
       </c>
     </row>
@@ -8987,6 +10013,9 @@
         <v>2643</v>
       </c>
       <c r="G342" s="1" t="n">
+        <v>2643</v>
+      </c>
+      <c r="H342" s="1" t="n">
         <v>2620</v>
       </c>
     </row>
@@ -9012,6 +10041,9 @@
         <v>0.000198</v>
       </c>
       <c r="G343" s="1" t="n">
+        <v>0.000198</v>
+      </c>
+      <c r="H343" s="1" t="n">
         <v>0.0001959</v>
       </c>
     </row>
@@ -9034,9 +10066,12 @@
         <v>0.08032</v>
       </c>
       <c r="F344" s="1" t="n">
+        <v>0.08003</v>
+      </c>
+      <c r="G344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="G344" s="1" t="n">
+      <c r="H344" s="1" t="n">
         <v>0.07987</v>
       </c>
     </row>
@@ -9059,9 +10094,12 @@
         <v>0.01654</v>
       </c>
       <c r="F345" s="1" t="n">
-        <v>0.01654</v>
+        <v>0.01656</v>
       </c>
       <c r="G345" s="1" t="n">
+        <v>0.01656</v>
+      </c>
+      <c r="H345" s="1" t="n">
         <v>0.01632</v>
       </c>
     </row>
@@ -9084,9 +10122,12 @@
         <v>2.798</v>
       </c>
       <c r="F346" s="1" t="n">
+        <v>2.797</v>
+      </c>
+      <c r="G346" s="1" t="n">
         <v>2.798</v>
       </c>
-      <c r="G346" s="1" t="n">
+      <c r="H346" s="1" t="n">
         <v>2.773</v>
       </c>
     </row>
@@ -9109,9 +10150,12 @@
         <v>0.01647</v>
       </c>
       <c r="F347" s="1" t="n">
+        <v>0.01645</v>
+      </c>
+      <c r="G347" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="G347" s="1" t="n">
+      <c r="H347" s="1" t="n">
         <v>0.01639</v>
       </c>
     </row>
@@ -9134,9 +10178,12 @@
         <v>0.03897</v>
       </c>
       <c r="F348" s="1" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="G348" s="1" t="n">
         <v>0.03897</v>
       </c>
-      <c r="G348" s="1" t="n">
+      <c r="H348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -9159,9 +10206,12 @@
         <v>0.3058</v>
       </c>
       <c r="F349" s="1" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="G349" s="1" t="n">
         <v>0.3065</v>
       </c>
-      <c r="G349" s="1" t="n">
+      <c r="H349" s="1" t="n">
         <v>0.3037</v>
       </c>
     </row>
@@ -9184,9 +10234,12 @@
         <v>0.005082</v>
       </c>
       <c r="F350" s="1" t="n">
+        <v>0.005062</v>
+      </c>
+      <c r="G350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="G350" s="1" t="n">
+      <c r="H350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -9209,9 +10262,12 @@
         <v>0.005145</v>
       </c>
       <c r="F351" s="1" t="n">
+        <v>0.005128</v>
+      </c>
+      <c r="G351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="G351" s="1" t="n">
+      <c r="H351" s="1" t="n">
         <v>0.00512</v>
       </c>
     </row>
@@ -9234,9 +10290,12 @@
         <v>0.004413</v>
       </c>
       <c r="F352" s="1" t="n">
+        <v>0.004404</v>
+      </c>
+      <c r="G352" s="1" t="n">
         <v>0.004413</v>
       </c>
-      <c r="G352" s="1" t="n">
+      <c r="H352" s="1" t="n">
         <v>0.004387</v>
       </c>
     </row>
@@ -9259,10 +10318,13 @@
         <v>0.08214</v>
       </c>
       <c r="F353" s="1" t="n">
+        <v>0.08171</v>
+      </c>
+      <c r="G353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="G353" s="1" t="n">
-        <v>0.08172</v>
+      <c r="H353" s="1" t="n">
+        <v>0.08171</v>
       </c>
     </row>
     <row r="354">
@@ -9284,9 +10346,12 @@
         <v>1.312</v>
       </c>
       <c r="F354" s="1" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="G354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="G354" s="1" t="n">
+      <c r="H354" s="1" t="n">
         <v>1.283</v>
       </c>
     </row>
@@ -9309,9 +10374,12 @@
         <v>7.775</v>
       </c>
       <c r="F355" s="1" t="n">
+        <v>7.766</v>
+      </c>
+      <c r="G355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="G355" s="1" t="n">
+      <c r="H355" s="1" t="n">
         <v>7.744</v>
       </c>
     </row>
@@ -9334,9 +10402,12 @@
         <v>0.007889999999999999</v>
       </c>
       <c r="F356" s="1" t="n">
+        <v>0.007889999999999999</v>
+      </c>
+      <c r="G356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="G356" s="1" t="n">
+      <c r="H356" s="1" t="n">
         <v>0.007849999999999999</v>
       </c>
     </row>
@@ -9359,9 +10430,12 @@
         <v>0.005726</v>
       </c>
       <c r="F357" s="1" t="n">
+        <v>0.00573</v>
+      </c>
+      <c r="G357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="G357" s="1" t="n">
+      <c r="H357" s="1" t="n">
         <v>0.005696</v>
       </c>
     </row>
@@ -9384,9 +10458,12 @@
         <v>0.01576</v>
       </c>
       <c r="F358" s="1" t="n">
+        <v>0.01569</v>
+      </c>
+      <c r="G358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="G358" s="1" t="n">
+      <c r="H358" s="1" t="n">
         <v>0.01567</v>
       </c>
     </row>
@@ -9409,9 +10486,12 @@
         <v>3.67</v>
       </c>
       <c r="F359" s="1" t="n">
+        <v>3.661</v>
+      </c>
+      <c r="G359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="G359" s="1" t="n">
+      <c r="H359" s="1" t="n">
         <v>3.65</v>
       </c>
     </row>
@@ -9434,9 +10514,12 @@
         <v>0.1506</v>
       </c>
       <c r="F360" s="1" t="n">
-        <v>0.1506</v>
+        <v>0.1507</v>
       </c>
       <c r="G360" s="1" t="n">
+        <v>0.1507</v>
+      </c>
+      <c r="H360" s="1" t="n">
         <v>0.1499</v>
       </c>
     </row>
@@ -9459,9 +10542,12 @@
         <v>0.07072000000000001</v>
       </c>
       <c r="F361" s="1" t="n">
+        <v>0.07081999999999999</v>
+      </c>
+      <c r="G361" s="1" t="n">
         <v>0.07093000000000001</v>
       </c>
-      <c r="G361" s="1" t="n">
+      <c r="H361" s="1" t="n">
         <v>0.07069</v>
       </c>
     </row>
@@ -9484,9 +10570,12 @@
         <v>0.01795</v>
       </c>
       <c r="F362" s="1" t="n">
+        <v>0.01792</v>
+      </c>
+      <c r="G362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="G362" s="1" t="n">
+      <c r="H362" s="1" t="n">
         <v>0.01786</v>
       </c>
     </row>
@@ -9509,10 +10598,13 @@
         <v>0.02262</v>
       </c>
       <c r="F363" s="1" t="n">
+        <v>0.02256</v>
+      </c>
+      <c r="G363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="G363" s="1" t="n">
-        <v>0.02262</v>
+      <c r="H363" s="1" t="n">
+        <v>0.02256</v>
       </c>
     </row>
     <row r="364">
@@ -9534,9 +10626,12 @@
         <v>0.01275</v>
       </c>
       <c r="F364" s="1" t="n">
+        <v>0.01272</v>
+      </c>
+      <c r="G364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="G364" s="1" t="n">
+      <c r="H364" s="1" t="n">
         <v>0.01271</v>
       </c>
     </row>
@@ -9559,9 +10654,12 @@
         <v>0.0925</v>
       </c>
       <c r="F365" s="1" t="n">
+        <v>0.0924</v>
+      </c>
+      <c r="G365" s="1" t="n">
         <v>0.0925</v>
       </c>
-      <c r="G365" s="1" t="n">
+      <c r="H365" s="1" t="n">
         <v>0.0919</v>
       </c>
     </row>
@@ -9584,9 +10682,12 @@
         <v>0.04261</v>
       </c>
       <c r="F366" s="1" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="G366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="G366" s="1" t="n">
+      <c r="H366" s="1" t="n">
         <v>0.04244</v>
       </c>
     </row>
@@ -9609,9 +10710,12 @@
         <v>0.03164</v>
       </c>
       <c r="F367" s="1" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="G367" s="1" t="n">
         <v>0.03164</v>
       </c>
-      <c r="G367" s="1" t="n">
+      <c r="H367" s="1" t="n">
         <v>0.03145</v>
       </c>
     </row>
@@ -9634,9 +10738,12 @@
         <v>0.0237</v>
       </c>
       <c r="F368" s="1" t="n">
+        <v>0.02386</v>
+      </c>
+      <c r="G368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="G368" s="1" t="n">
+      <c r="H368" s="1" t="n">
         <v>0.0236</v>
       </c>
     </row>
@@ -9659,9 +10766,12 @@
         <v>0.0313</v>
       </c>
       <c r="F369" s="1" t="n">
+        <v>0.03124</v>
+      </c>
+      <c r="G369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="G369" s="1" t="n">
+      <c r="H369" s="1" t="n">
         <v>0.03113</v>
       </c>
     </row>
@@ -9684,9 +10794,12 @@
         <v>0.07745</v>
       </c>
       <c r="F370" s="1" t="n">
-        <v>0.07784000000000001</v>
+        <v>0.07836</v>
       </c>
       <c r="G370" s="1" t="n">
+        <v>0.07836</v>
+      </c>
+      <c r="H370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -9709,9 +10822,12 @@
         <v>0.1087</v>
       </c>
       <c r="F371" s="1" t="n">
-        <v>0.1087</v>
+        <v>0.1088</v>
       </c>
       <c r="G371" s="1" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="H371" s="1" t="n">
         <v>0.1074</v>
       </c>
     </row>
@@ -9734,9 +10850,12 @@
         <v>0.007206</v>
       </c>
       <c r="F372" s="1" t="n">
-        <v>0.007206</v>
+        <v>0.007209</v>
       </c>
       <c r="G372" s="1" t="n">
+        <v>0.007209</v>
+      </c>
+      <c r="H372" s="1" t="n">
         <v>0.007057</v>
       </c>
     </row>
@@ -9759,9 +10878,12 @@
         <v>0.097</v>
       </c>
       <c r="F373" s="1" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="G373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="G373" s="1" t="n">
+      <c r="H373" s="1" t="n">
         <v>0.0965</v>
       </c>
     </row>
@@ -9784,9 +10906,12 @@
         <v>0.05881</v>
       </c>
       <c r="F374" s="1" t="n">
+        <v>0.05855</v>
+      </c>
+      <c r="G374" s="1" t="n">
         <v>0.05881</v>
       </c>
-      <c r="G374" s="1" t="n">
+      <c r="H374" s="1" t="n">
         <v>0.0583</v>
       </c>
     </row>
@@ -9809,9 +10934,12 @@
         <v>0.3234</v>
       </c>
       <c r="F375" s="1" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="G375" s="1" t="n">
         <v>0.3234</v>
       </c>
-      <c r="G375" s="1" t="n">
+      <c r="H375" s="1" t="n">
         <v>0.3193</v>
       </c>
     </row>
@@ -9834,9 +10962,12 @@
         <v>0.02</v>
       </c>
       <c r="F376" s="1" t="n">
+        <v>0.01997</v>
+      </c>
+      <c r="G376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="G376" s="1" t="n">
+      <c r="H376" s="1" t="n">
         <v>0.01988</v>
       </c>
     </row>
@@ -9859,9 +10990,12 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="F377" s="1" t="n">
+        <v>0.06902</v>
+      </c>
+      <c r="G377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="G377" s="1" t="n">
+      <c r="H377" s="1" t="n">
         <v>0.06877</v>
       </c>
     </row>
@@ -9884,9 +11018,12 @@
         <v>0.15583</v>
       </c>
       <c r="F378" s="1" t="n">
+        <v>0.15483</v>
+      </c>
+      <c r="G378" s="1" t="n">
         <v>0.15583</v>
       </c>
-      <c r="G378" s="1" t="n">
+      <c r="H378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -9909,9 +11046,12 @@
         <v>0.0006059</v>
       </c>
       <c r="F379" s="1" t="n">
+        <v>0.0006047</v>
+      </c>
+      <c r="G379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="G379" s="1" t="n">
+      <c r="H379" s="1" t="n">
         <v>0.0006028</v>
       </c>
     </row>
@@ -9937,6 +11077,9 @@
         <v>0.01021</v>
       </c>
       <c r="G380" s="1" t="n">
+        <v>0.01021</v>
+      </c>
+      <c r="H380" s="1" t="n">
         <v>0.01016</v>
       </c>
     </row>
@@ -9959,9 +11102,12 @@
         <v>0.02571</v>
       </c>
       <c r="F381" s="1" t="n">
+        <v>0.02569</v>
+      </c>
+      <c r="G381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="G381" s="1" t="n">
+      <c r="H381" s="1" t="n">
         <v>0.02553</v>
       </c>
     </row>
@@ -9984,9 +11130,12 @@
         <v>0.19263</v>
       </c>
       <c r="F382" s="1" t="n">
+        <v>0.19215</v>
+      </c>
+      <c r="G382" s="1" t="n">
         <v>0.19263</v>
       </c>
-      <c r="G382" s="1" t="n">
+      <c r="H382" s="1" t="n">
         <v>0.18936</v>
       </c>
     </row>
@@ -10009,9 +11158,12 @@
         <v>0.09479</v>
       </c>
       <c r="F383" s="1" t="n">
+        <v>0.09384000000000001</v>
+      </c>
+      <c r="G383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="G383" s="1" t="n">
+      <c r="H383" s="1" t="n">
         <v>0.09372999999999999</v>
       </c>
     </row>
@@ -10034,10 +11186,13 @@
         <v>0.03198</v>
       </c>
       <c r="F384" s="1" t="n">
+        <v>0.03192</v>
+      </c>
+      <c r="G384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="G384" s="1" t="n">
-        <v>0.03194</v>
+      <c r="H384" s="1" t="n">
+        <v>0.03192</v>
       </c>
     </row>
     <row r="385">
@@ -10059,9 +11214,12 @@
         <v>0.01123</v>
       </c>
       <c r="F385" s="1" t="n">
+        <v>0.01122</v>
+      </c>
+      <c r="G385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="G385" s="1" t="n">
+      <c r="H385" s="1" t="n">
         <v>0.01115</v>
       </c>
     </row>
@@ -10084,9 +11242,12 @@
         <v>0.05131</v>
       </c>
       <c r="F386" s="1" t="n">
-        <v>0.05131</v>
+        <v>0.05135</v>
       </c>
       <c r="G386" s="1" t="n">
+        <v>0.05135</v>
+      </c>
+      <c r="H386" s="1" t="n">
         <v>0.05087</v>
       </c>
     </row>
@@ -10109,9 +11270,12 @@
         <v>0.0249</v>
       </c>
       <c r="F387" s="1" t="n">
-        <v>0.02504</v>
+        <v>0.02512</v>
       </c>
       <c r="G387" s="1" t="n">
+        <v>0.02512</v>
+      </c>
+      <c r="H387" s="1" t="n">
         <v>0.02483</v>
       </c>
     </row>
@@ -10134,9 +11298,12 @@
         <v>0.00738</v>
       </c>
       <c r="F388" s="1" t="n">
+        <v>0.007348</v>
+      </c>
+      <c r="G388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="G388" s="1" t="n">
+      <c r="H388" s="1" t="n">
         <v>0.007344</v>
       </c>
     </row>
@@ -10159,9 +11326,12 @@
         <v>0.01024</v>
       </c>
       <c r="F389" s="1" t="n">
+        <v>0.01021</v>
+      </c>
+      <c r="G389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="G389" s="1" t="n">
+      <c r="H389" s="1" t="n">
         <v>0.01016</v>
       </c>
     </row>
@@ -10184,9 +11354,12 @@
         <v>0.08369</v>
       </c>
       <c r="F390" s="1" t="n">
+        <v>0.08341999999999999</v>
+      </c>
+      <c r="G390" s="1" t="n">
         <v>0.08369</v>
       </c>
-      <c r="G390" s="1" t="n">
+      <c r="H390" s="1" t="n">
         <v>0.08304</v>
       </c>
     </row>
@@ -10209,9 +11382,12 @@
         <v>0.5061</v>
       </c>
       <c r="F391" s="1" t="n">
+        <v>0.5048</v>
+      </c>
+      <c r="G391" s="1" t="n">
         <v>0.5061</v>
       </c>
-      <c r="G391" s="1" t="n">
+      <c r="H391" s="1" t="n">
         <v>0.5017</v>
       </c>
     </row>
@@ -10234,9 +11410,12 @@
         <v>0.118</v>
       </c>
       <c r="F392" s="1" t="n">
+        <v>0.1179</v>
+      </c>
+      <c r="G392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="G392" s="1" t="n">
+      <c r="H392" s="1" t="n">
         <v>0.1171</v>
       </c>
     </row>
@@ -10259,9 +11438,12 @@
         <v>0.00251</v>
       </c>
       <c r="F393" s="1" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="G393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="G393" s="1" t="n">
+      <c r="H393" s="1" t="n">
         <v>0.0025</v>
       </c>
     </row>
@@ -10284,9 +11466,12 @@
         <v>0.02155</v>
       </c>
       <c r="F394" s="1" t="n">
+        <v>0.02157</v>
+      </c>
+      <c r="G394" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="G394" s="1" t="n">
+      <c r="H394" s="1" t="n">
         <v>0.02146</v>
       </c>
     </row>
@@ -10312,6 +11497,9 @@
         <v>0.0163</v>
       </c>
       <c r="G395" s="1" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="H395" s="1" t="n">
         <v>0.0162</v>
       </c>
     </row>
@@ -10334,9 +11522,12 @@
         <v>0.1364</v>
       </c>
       <c r="F396" s="1" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="G396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="G396" s="1" t="n">
+      <c r="H396" s="1" t="n">
         <v>0.1358</v>
       </c>
     </row>
@@ -10359,10 +11550,13 @@
         <v>0.01482</v>
       </c>
       <c r="F397" s="1" t="n">
+        <v>0.01473</v>
+      </c>
+      <c r="G397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="G397" s="1" t="n">
-        <v>0.01475</v>
+      <c r="H397" s="1" t="n">
+        <v>0.01473</v>
       </c>
     </row>
     <row r="398">
@@ -10384,9 +11578,12 @@
         <v>6.807</v>
       </c>
       <c r="F398" s="1" t="n">
-        <v>6.807</v>
+        <v>6.847</v>
       </c>
       <c r="G398" s="1" t="n">
+        <v>6.847</v>
+      </c>
+      <c r="H398" s="1" t="n">
         <v>6.725</v>
       </c>
     </row>
@@ -10409,10 +11606,13 @@
         <v>0.009471</v>
       </c>
       <c r="F399" s="1" t="n">
+        <v>0.009449000000000001</v>
+      </c>
+      <c r="G399" s="1" t="n">
         <v>0.009509999999999999</v>
       </c>
-      <c r="G399" s="1" t="n">
-        <v>0.009471</v>
+      <c r="H399" s="1" t="n">
+        <v>0.009449000000000001</v>
       </c>
     </row>
     <row r="400">
@@ -10434,10 +11634,13 @@
         <v>0.001272</v>
       </c>
       <c r="F400" s="1" t="n">
+        <v>0.001264</v>
+      </c>
+      <c r="G400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="G400" s="1" t="n">
-        <v>0.001269</v>
+      <c r="H400" s="1" t="n">
+        <v>0.001264</v>
       </c>
     </row>
     <row r="401">
@@ -10459,9 +11662,12 @@
         <v>0.01844</v>
       </c>
       <c r="F401" s="1" t="n">
+        <v>0.01841</v>
+      </c>
+      <c r="G401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="G401" s="1" t="n">
+      <c r="H401" s="1" t="n">
         <v>0.01841</v>
       </c>
     </row>
@@ -10484,9 +11690,12 @@
         <v>0.08595999999999999</v>
       </c>
       <c r="F402" s="1" t="n">
+        <v>0.08591</v>
+      </c>
+      <c r="G402" s="1" t="n">
         <v>0.08595999999999999</v>
       </c>
-      <c r="G402" s="1" t="n">
+      <c r="H402" s="1" t="n">
         <v>0.08563999999999999</v>
       </c>
     </row>
@@ -10512,6 +11721,9 @@
         <v>0.00555</v>
       </c>
       <c r="G403" s="1" t="n">
+        <v>0.00555</v>
+      </c>
+      <c r="H403" s="1" t="n">
         <v>0.00553</v>
       </c>
     </row>
@@ -10534,10 +11746,13 @@
         <v>0.04366</v>
       </c>
       <c r="F404" s="1" t="n">
+        <v>0.04362</v>
+      </c>
+      <c r="G404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="G404" s="1" t="n">
-        <v>0.04366</v>
+      <c r="H404" s="1" t="n">
+        <v>0.04362</v>
       </c>
     </row>
     <row r="405">
@@ -10559,9 +11774,12 @@
         <v>0.05915</v>
       </c>
       <c r="F405" s="1" t="n">
+        <v>0.05902</v>
+      </c>
+      <c r="G405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="G405" s="1" t="n">
+      <c r="H405" s="1" t="n">
         <v>0.05871</v>
       </c>
     </row>
@@ -10584,9 +11802,12 @@
         <v>0.01674</v>
       </c>
       <c r="F406" s="1" t="n">
+        <v>0.01665</v>
+      </c>
+      <c r="G406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="G406" s="1" t="n">
+      <c r="H406" s="1" t="n">
         <v>0.01658</v>
       </c>
     </row>
@@ -10609,9 +11830,12 @@
         <v>0.0428</v>
       </c>
       <c r="F407" s="1" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="G407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="G407" s="1" t="n">
+      <c r="H407" s="1" t="n">
         <v>0.0425</v>
       </c>
     </row>
@@ -10634,9 +11858,12 @@
         <v>0.01951</v>
       </c>
       <c r="F408" s="1" t="n">
+        <v>0.01945</v>
+      </c>
+      <c r="G408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="G408" s="1" t="n">
+      <c r="H408" s="1" t="n">
         <v>0.01938</v>
       </c>
     </row>
@@ -10659,9 +11886,12 @@
         <v>0.4466</v>
       </c>
       <c r="F409" s="1" t="n">
-        <v>0.4466</v>
+        <v>0.4475</v>
       </c>
       <c r="G409" s="1" t="n">
+        <v>0.4475</v>
+      </c>
+      <c r="H409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -10684,9 +11914,12 @@
         <v>0.04454</v>
       </c>
       <c r="F410" s="1" t="n">
+        <v>0.0445</v>
+      </c>
+      <c r="G410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="G410" s="1" t="n">
+      <c r="H410" s="1" t="n">
         <v>0.04418</v>
       </c>
     </row>
@@ -10709,9 +11942,12 @@
         <v>27.06</v>
       </c>
       <c r="F411" s="1" t="n">
+        <v>26.87</v>
+      </c>
+      <c r="G411" s="1" t="n">
         <v>27.06</v>
       </c>
-      <c r="G411" s="1" t="n">
+      <c r="H411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -10734,9 +11970,12 @@
         <v>0.03553</v>
       </c>
       <c r="F412" s="1" t="n">
+        <v>0.03549</v>
+      </c>
+      <c r="G412" s="1" t="n">
         <v>0.03561</v>
       </c>
-      <c r="G412" s="1" t="n">
+      <c r="H412" s="1" t="n">
         <v>0.03515</v>
       </c>
     </row>
@@ -10759,9 +11998,12 @@
         <v>0.003426</v>
       </c>
       <c r="F413" s="1" t="n">
-        <v>0.003429</v>
+        <v>0.00343</v>
       </c>
       <c r="G413" s="1" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="H413" s="1" t="n">
         <v>0.00341</v>
       </c>
     </row>
@@ -10784,9 +12026,12 @@
         <v>0.1537</v>
       </c>
       <c r="F414" s="1" t="n">
+        <v>0.1535</v>
+      </c>
+      <c r="G414" s="1" t="n">
         <v>0.1537</v>
       </c>
-      <c r="G414" s="1" t="n">
+      <c r="H414" s="1" t="n">
         <v>0.1527</v>
       </c>
     </row>
@@ -10809,9 +12054,12 @@
         <v>0.05286</v>
       </c>
       <c r="F415" s="1" t="n">
+        <v>0.05274</v>
+      </c>
+      <c r="G415" s="1" t="n">
         <v>0.05286</v>
       </c>
-      <c r="G415" s="1" t="n">
+      <c r="H415" s="1" t="n">
         <v>0.05258</v>
       </c>
     </row>
@@ -10837,6 +12085,9 @@
         <v>0.00669</v>
       </c>
       <c r="G416" s="1" t="n">
+        <v>0.00669</v>
+      </c>
+      <c r="H416" s="1" t="n">
         <v>0.00664</v>
       </c>
     </row>
@@ -10859,9 +12110,12 @@
         <v>0.06101</v>
       </c>
       <c r="F417" s="1" t="n">
+        <v>0.06091</v>
+      </c>
+      <c r="G417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="G417" s="1" t="n">
+      <c r="H417" s="1" t="n">
         <v>0.0608</v>
       </c>
     </row>
@@ -10884,9 +12138,12 @@
         <v>0.008211</v>
       </c>
       <c r="F418" s="1" t="n">
+        <v>0.008205</v>
+      </c>
+      <c r="G418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="G418" s="1" t="n">
+      <c r="H418" s="1" t="n">
         <v>0.008156</v>
       </c>
     </row>
@@ -10909,9 +12166,12 @@
         <v>0.07494000000000001</v>
       </c>
       <c r="F419" s="1" t="n">
+        <v>0.07473</v>
+      </c>
+      <c r="G419" s="1" t="n">
         <v>0.07494000000000001</v>
       </c>
-      <c r="G419" s="1" t="n">
+      <c r="H419" s="1" t="n">
         <v>0.07459</v>
       </c>
     </row>
@@ -10934,9 +12194,12 @@
         <v>0.02144</v>
       </c>
       <c r="F420" s="1" t="n">
+        <v>0.02144</v>
+      </c>
+      <c r="G420" s="1" t="n">
         <v>0.02145</v>
       </c>
-      <c r="G420" s="1" t="n">
+      <c r="H420" s="1" t="n">
         <v>0.0213</v>
       </c>
     </row>
@@ -10959,9 +12222,12 @@
         <v>0.07011000000000001</v>
       </c>
       <c r="F421" s="1" t="n">
+        <v>0.06981999999999999</v>
+      </c>
+      <c r="G421" s="1" t="n">
         <v>0.07011000000000001</v>
       </c>
-      <c r="G421" s="1" t="n">
+      <c r="H421" s="1" t="n">
         <v>0.06938999999999999</v>
       </c>
     </row>
@@ -10984,10 +12250,13 @@
         <v>0.01522</v>
       </c>
       <c r="F422" s="1" t="n">
+        <v>0.01519</v>
+      </c>
+      <c r="G422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="G422" s="1" t="n">
-        <v>0.01522</v>
+      <c r="H422" s="1" t="n">
+        <v>0.01519</v>
       </c>
     </row>
     <row r="423">
@@ -11009,9 +12278,12 @@
         <v>0.006695</v>
       </c>
       <c r="F423" s="1" t="n">
+        <v>0.006685</v>
+      </c>
+      <c r="G423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="G423" s="1" t="n">
+      <c r="H423" s="1" t="n">
         <v>0.006677</v>
       </c>
     </row>
@@ -11034,9 +12306,12 @@
         <v>0.921</v>
       </c>
       <c r="F424" s="1" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="G424" s="1" t="n">
+      <c r="H424" s="1" t="n">
         <v>0.915</v>
       </c>
     </row>
@@ -11059,9 +12334,12 @@
         <v>0.03577</v>
       </c>
       <c r="F425" s="1" t="n">
-        <v>0.03577</v>
+        <v>0.03596</v>
       </c>
       <c r="G425" s="1" t="n">
+        <v>0.03596</v>
+      </c>
+      <c r="H425" s="1" t="n">
         <v>0.03555</v>
       </c>
     </row>
@@ -11084,9 +12362,12 @@
         <v>1.785</v>
       </c>
       <c r="F426" s="1" t="n">
-        <v>1.785</v>
+        <v>1.795</v>
       </c>
       <c r="G426" s="1" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="H426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -11109,9 +12390,12 @@
         <v>0.12835</v>
       </c>
       <c r="F427" s="1" t="n">
+        <v>0.12816</v>
+      </c>
+      <c r="G427" s="1" t="n">
         <v>0.12835</v>
       </c>
-      <c r="G427" s="1" t="n">
+      <c r="H427" s="1" t="n">
         <v>0.12771</v>
       </c>
     </row>
@@ -11134,9 +12418,12 @@
         <v>0.05325</v>
       </c>
       <c r="F428" s="1" t="n">
+        <v>0.05341</v>
+      </c>
+      <c r="G428" s="1" t="n">
         <v>0.05359</v>
       </c>
-      <c r="G428" s="1" t="n">
+      <c r="H428" s="1" t="n">
         <v>0.05325</v>
       </c>
     </row>
@@ -11159,9 +12446,12 @@
         <v>1.316</v>
       </c>
       <c r="F429" s="1" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="G429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="G429" s="1" t="n">
+      <c r="H429" s="1" t="n">
         <v>1.309</v>
       </c>
     </row>
@@ -11184,9 +12474,12 @@
         <v>0.07618</v>
       </c>
       <c r="F430" s="1" t="n">
+        <v>0.07571</v>
+      </c>
+      <c r="G430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="G430" s="1" t="n">
+      <c r="H430" s="1" t="n">
         <v>0.07547</v>
       </c>
     </row>
@@ -11209,9 +12502,12 @@
         <v>0.1638</v>
       </c>
       <c r="F431" s="1" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="G431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="G431" s="1" t="n">
+      <c r="H431" s="1" t="n">
         <v>0.1636</v>
       </c>
     </row>
@@ -11234,9 +12530,12 @@
         <v>1.461</v>
       </c>
       <c r="F432" s="1" t="n">
+        <v>1.458</v>
+      </c>
+      <c r="G432" s="1" t="n">
         <v>1.461</v>
       </c>
-      <c r="G432" s="1" t="n">
+      <c r="H432" s="1" t="n">
         <v>1.456</v>
       </c>
     </row>
@@ -11259,9 +12558,12 @@
         <v>3.324</v>
       </c>
       <c r="F433" s="1" t="n">
+        <v>3.317</v>
+      </c>
+      <c r="G433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="G433" s="1" t="n">
+      <c r="H433" s="1" t="n">
         <v>3.306</v>
       </c>
     </row>
@@ -11284,9 +12586,12 @@
         <v>0.1803</v>
       </c>
       <c r="F434" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="G434" s="1" t="n">
+      <c r="H434" s="1" t="n">
         <v>0.1792</v>
       </c>
     </row>
@@ -11309,9 +12614,12 @@
         <v>0.008665000000000001</v>
       </c>
       <c r="F435" s="1" t="n">
+        <v>0.008645</v>
+      </c>
+      <c r="G435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="G435" s="1" t="n">
+      <c r="H435" s="1" t="n">
         <v>0.00864</v>
       </c>
     </row>
@@ -11334,9 +12642,12 @@
         <v>0.2866</v>
       </c>
       <c r="F436" s="1" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="G436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="G436" s="1" t="n">
+      <c r="H436" s="1" t="n">
         <v>0.2841</v>
       </c>
     </row>
@@ -11359,9 +12670,12 @@
         <v>0.0384</v>
       </c>
       <c r="F437" s="1" t="n">
+        <v>0.03822</v>
+      </c>
+      <c r="G437" s="1" t="n">
         <v>0.0384</v>
       </c>
-      <c r="G437" s="1" t="n">
+      <c r="H437" s="1" t="n">
         <v>0.03814</v>
       </c>
     </row>
@@ -11384,9 +12698,12 @@
         <v>0.02444</v>
       </c>
       <c r="F438" s="1" t="n">
+        <v>0.02459</v>
+      </c>
+      <c r="G438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="G438" s="1" t="n">
+      <c r="H438" s="1" t="n">
         <v>0.02444</v>
       </c>
     </row>
@@ -11409,9 +12726,12 @@
         <v>0.04405</v>
       </c>
       <c r="F439" s="1" t="n">
+        <v>0.04406</v>
+      </c>
+      <c r="G439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="G439" s="1" t="n">
+      <c r="H439" s="1" t="n">
         <v>0.04405</v>
       </c>
     </row>
@@ -11434,10 +12754,13 @@
         <v>0.0005253</v>
       </c>
       <c r="F440" s="1" t="n">
+        <v>0.0005212</v>
+      </c>
+      <c r="G440" s="1" t="n">
         <v>0.0005258</v>
       </c>
-      <c r="G440" s="1" t="n">
-        <v>0.0005221</v>
+      <c r="H440" s="1" t="n">
+        <v>0.0005212</v>
       </c>
     </row>
     <row r="441">
@@ -11459,9 +12782,12 @@
         <v>0.04428</v>
       </c>
       <c r="F441" s="1" t="n">
+        <v>0.04396</v>
+      </c>
+      <c r="G441" s="1" t="n">
         <v>0.04428</v>
       </c>
-      <c r="G441" s="1" t="n">
+      <c r="H441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -11484,9 +12810,12 @@
         <v>0.000415</v>
       </c>
       <c r="F442" s="1" t="n">
+        <v>0.000415</v>
+      </c>
+      <c r="G442" s="1" t="n">
         <v>0.000416</v>
       </c>
-      <c r="G442" s="1" t="n">
+      <c r="H442" s="1" t="n">
         <v>0.000413</v>
       </c>
     </row>
@@ -11509,10 +12838,13 @@
         <v>0.09826</v>
       </c>
       <c r="F443" s="1" t="n">
+        <v>0.0961</v>
+      </c>
+      <c r="G443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="G443" s="1" t="n">
-        <v>0.09672</v>
+      <c r="H443" s="1" t="n">
+        <v>0.0961</v>
       </c>
     </row>
     <row r="444">
@@ -11534,9 +12866,12 @@
         <v>2.307</v>
       </c>
       <c r="F444" s="1" t="n">
+        <v>2.308</v>
+      </c>
+      <c r="G444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="G444" s="1" t="n">
+      <c r="H444" s="1" t="n">
         <v>2.289</v>
       </c>
     </row>
@@ -11559,9 +12894,12 @@
         <v>0.2695</v>
       </c>
       <c r="F445" s="1" t="n">
-        <v>0.2695</v>
+        <v>0.2707</v>
       </c>
       <c r="G445" s="1" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="H445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -11584,9 +12922,12 @@
         <v>0.000755</v>
       </c>
       <c r="F446" s="1" t="n">
+        <v>0.0007534</v>
+      </c>
+      <c r="G446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="G446" s="1" t="n">
+      <c r="H446" s="1" t="n">
         <v>0.0007521</v>
       </c>
     </row>
@@ -11609,10 +12950,13 @@
         <v>0.03904</v>
       </c>
       <c r="F447" s="1" t="n">
+        <v>0.03869</v>
+      </c>
+      <c r="G447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="G447" s="1" t="n">
-        <v>0.03873</v>
+      <c r="H447" s="1" t="n">
+        <v>0.03869</v>
       </c>
     </row>
     <row r="448">
@@ -11634,9 +12978,12 @@
         <v>0.1771</v>
       </c>
       <c r="F448" s="1" t="n">
-        <v>0.1771</v>
+        <v>0.1773</v>
       </c>
       <c r="G448" s="1" t="n">
+        <v>0.1773</v>
+      </c>
+      <c r="H448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -11659,9 +13006,12 @@
         <v>0.04283</v>
       </c>
       <c r="F449" s="1" t="n">
+        <v>0.04284</v>
+      </c>
+      <c r="G449" s="1" t="n">
         <v>0.04301</v>
       </c>
-      <c r="G449" s="1" t="n">
+      <c r="H449" s="1" t="n">
         <v>0.0427</v>
       </c>
     </row>
@@ -11684,9 +13034,12 @@
         <v>0.0001654</v>
       </c>
       <c r="F450" s="1" t="n">
+        <v>0.000165</v>
+      </c>
+      <c r="G450" s="1" t="n">
         <v>0.0001654</v>
       </c>
-      <c r="G450" s="1" t="n">
+      <c r="H450" s="1" t="n">
         <v>0.0001641</v>
       </c>
     </row>
@@ -11709,10 +13062,13 @@
         <v>0.03764</v>
       </c>
       <c r="F451" s="1" t="n">
+        <v>0.03751</v>
+      </c>
+      <c r="G451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="G451" s="1" t="n">
-        <v>0.0376</v>
+      <c r="H451" s="1" t="n">
+        <v>0.03751</v>
       </c>
     </row>
     <row r="452">
@@ -11734,9 +13090,12 @@
         <v>0.009990000000000001</v>
       </c>
       <c r="F452" s="1" t="n">
+        <v>0.00997</v>
+      </c>
+      <c r="G452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="G452" s="1" t="n">
+      <c r="H452" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
     </row>
@@ -11759,9 +13118,12 @@
         <v>0.06805</v>
       </c>
       <c r="F453" s="1" t="n">
+        <v>0.06804</v>
+      </c>
+      <c r="G453" s="1" t="n">
         <v>0.06805</v>
       </c>
-      <c r="G453" s="1" t="n">
+      <c r="H453" s="1" t="n">
         <v>0.06793</v>
       </c>
     </row>
@@ -11784,9 +13146,12 @@
         <v>0.007608</v>
       </c>
       <c r="F454" s="1" t="n">
+        <v>0.007577</v>
+      </c>
+      <c r="G454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="G454" s="1" t="n">
+      <c r="H454" s="1" t="n">
         <v>0.007541</v>
       </c>
     </row>
@@ -11809,9 +13174,12 @@
         <v>0.003376</v>
       </c>
       <c r="F455" s="1" t="n">
+        <v>0.003373</v>
+      </c>
+      <c r="G455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="G455" s="1" t="n">
+      <c r="H455" s="1" t="n">
         <v>0.003362</v>
       </c>
     </row>
@@ -11834,9 +13202,12 @@
         <v>0.001874</v>
       </c>
       <c r="F456" s="1" t="n">
+        <v>0.001871</v>
+      </c>
+      <c r="G456" s="1" t="n">
         <v>0.001874</v>
       </c>
-      <c r="G456" s="1" t="n">
+      <c r="H456" s="1" t="n">
         <v>0.001854</v>
       </c>
     </row>
@@ -11859,9 +13230,12 @@
         <v>0.0001767</v>
       </c>
       <c r="F457" s="1" t="n">
+        <v>0.0001761</v>
+      </c>
+      <c r="G457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="G457" s="1" t="n">
+      <c r="H457" s="1" t="n">
         <v>0.0001758</v>
       </c>
     </row>
@@ -11884,9 +13258,12 @@
         <v>0.0003898</v>
       </c>
       <c r="F458" s="1" t="n">
-        <v>0.0003898</v>
+        <v>0.0003913</v>
       </c>
       <c r="G458" s="1" t="n">
+        <v>0.0003913</v>
+      </c>
+      <c r="H458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -11909,9 +13286,12 @@
         <v>0.01409</v>
       </c>
       <c r="F459" s="1" t="n">
+        <v>0.01404</v>
+      </c>
+      <c r="G459" s="1" t="n">
         <v>0.01409</v>
       </c>
-      <c r="G459" s="1" t="n">
+      <c r="H459" s="1" t="n">
         <v>0.01391</v>
       </c>
     </row>
@@ -11934,9 +13314,12 @@
         <v>0.04556</v>
       </c>
       <c r="F460" s="1" t="n">
-        <v>0.04556</v>
+        <v>0.04559</v>
       </c>
       <c r="G460" s="1" t="n">
+        <v>0.04559</v>
+      </c>
+      <c r="H460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -11959,9 +13342,12 @@
         <v>0.2839</v>
       </c>
       <c r="F461" s="1" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="G461" s="1" t="n">
         <v>0.2839</v>
       </c>
-      <c r="G461" s="1" t="n">
+      <c r="H461" s="1" t="n">
         <v>0.2822</v>
       </c>
     </row>
@@ -11984,9 +13370,12 @@
         <v>0.006278</v>
       </c>
       <c r="F462" s="1" t="n">
+        <v>0.00626</v>
+      </c>
+      <c r="G462" s="1" t="n">
         <v>0.006279</v>
       </c>
-      <c r="G462" s="1" t="n">
+      <c r="H462" s="1" t="n">
         <v>0.00622</v>
       </c>
     </row>
@@ -12009,9 +13398,12 @@
         <v>0.007088</v>
       </c>
       <c r="F463" s="1" t="n">
+        <v>0.007085</v>
+      </c>
+      <c r="G463" s="1" t="n">
         <v>0.007088</v>
       </c>
-      <c r="G463" s="1" t="n">
+      <c r="H463" s="1" t="n">
         <v>0.00704</v>
       </c>
     </row>
@@ -12034,9 +13426,12 @@
         <v>0.2876</v>
       </c>
       <c r="F464" s="1" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="G464" s="1" t="n">
         <v>0.2878</v>
       </c>
-      <c r="G464" s="1" t="n">
+      <c r="H464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -12059,9 +13454,12 @@
         <v>0.08134</v>
       </c>
       <c r="F465" s="1" t="n">
-        <v>0.08134</v>
+        <v>0.08177</v>
       </c>
       <c r="G465" s="1" t="n">
+        <v>0.08177</v>
+      </c>
+      <c r="H465" s="1" t="n">
         <v>0.08078</v>
       </c>
     </row>
@@ -12084,9 +13482,12 @@
         <v>0.6318</v>
       </c>
       <c r="F466" s="1" t="n">
-        <v>0.6343</v>
+        <v>0.635</v>
       </c>
       <c r="G466" s="1" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="H466" s="1" t="n">
         <v>0.6318</v>
       </c>
     </row>
@@ -12109,9 +13510,12 @@
         <v>0.01486</v>
       </c>
       <c r="F467" s="1" t="n">
-        <v>0.01486</v>
+        <v>0.01491</v>
       </c>
       <c r="G467" s="1" t="n">
+        <v>0.01491</v>
+      </c>
+      <c r="H467" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -12134,9 +13538,12 @@
         <v>0.03455</v>
       </c>
       <c r="F468" s="1" t="n">
-        <v>0.03462</v>
+        <v>0.03468</v>
       </c>
       <c r="G468" s="1" t="n">
+        <v>0.03468</v>
+      </c>
+      <c r="H468" s="1" t="n">
         <v>0.03448</v>
       </c>
     </row>
@@ -12159,9 +13566,12 @@
         <v>0.1652</v>
       </c>
       <c r="F469" s="1" t="n">
+        <v>0.1647</v>
+      </c>
+      <c r="G469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="G469" s="1" t="n">
+      <c r="H469" s="1" t="n">
         <v>0.1644</v>
       </c>
     </row>
@@ -12184,9 +13594,12 @@
         <v>0.4132</v>
       </c>
       <c r="F470" s="1" t="n">
-        <v>0.4139</v>
+        <v>0.4151</v>
       </c>
       <c r="G470" s="1" t="n">
+        <v>0.4151</v>
+      </c>
+      <c r="H470" s="1" t="n">
         <v>0.4123</v>
       </c>
     </row>
@@ -12209,9 +13622,12 @@
         <v>0.07012</v>
       </c>
       <c r="F471" s="1" t="n">
+        <v>0.06999</v>
+      </c>
+      <c r="G471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="G471" s="1" t="n">
+      <c r="H471" s="1" t="n">
         <v>0.06975000000000001</v>
       </c>
     </row>
@@ -12234,9 +13650,12 @@
         <v>0.06773999999999999</v>
       </c>
       <c r="F472" s="1" t="n">
+        <v>0.06734</v>
+      </c>
+      <c r="G472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="G472" s="1" t="n">
+      <c r="H472" s="1" t="n">
         <v>0.06688</v>
       </c>
     </row>
@@ -12259,9 +13678,12 @@
         <v>0.01647</v>
       </c>
       <c r="F473" s="1" t="n">
+        <v>0.01643</v>
+      </c>
+      <c r="G473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="G473" s="1" t="n">
+      <c r="H473" s="1" t="n">
         <v>0.0164</v>
       </c>
     </row>
@@ -12284,10 +13706,13 @@
         <v>0.2106</v>
       </c>
       <c r="F474" s="1" t="n">
+        <v>0.2092</v>
+      </c>
+      <c r="G474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="G474" s="1" t="n">
-        <v>0.2101</v>
+      <c r="H474" s="1" t="n">
+        <v>0.2092</v>
       </c>
     </row>
     <row r="475">
@@ -12309,9 +13734,12 @@
         <v>0.04232</v>
       </c>
       <c r="F475" s="1" t="n">
+        <v>0.04223</v>
+      </c>
+      <c r="G475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="G475" s="1" t="n">
+      <c r="H475" s="1" t="n">
         <v>0.04202</v>
       </c>
     </row>
@@ -12334,9 +13762,12 @@
         <v>1.578</v>
       </c>
       <c r="F476" s="1" t="n">
+        <v>1.574</v>
+      </c>
+      <c r="G476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="G476" s="1" t="n">
+      <c r="H476" s="1" t="n">
         <v>1.57</v>
       </c>
     </row>
@@ -12359,10 +13790,13 @@
         <v>0.1014</v>
       </c>
       <c r="F477" s="1" t="n">
+        <v>0.1011</v>
+      </c>
+      <c r="G477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="G477" s="1" t="n">
-        <v>0.1012</v>
+      <c r="H477" s="1" t="n">
+        <v>0.1011</v>
       </c>
     </row>
     <row r="478">
@@ -12384,9 +13818,12 @@
         <v>0.001161</v>
       </c>
       <c r="F478" s="1" t="n">
+        <v>0.001157</v>
+      </c>
+      <c r="G478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="G478" s="1" t="n">
+      <c r="H478" s="1" t="n">
         <v>0.001155</v>
       </c>
     </row>
@@ -12409,9 +13846,12 @@
         <v>0.148</v>
       </c>
       <c r="F479" s="1" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="G479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="G479" s="1" t="n">
+      <c r="H479" s="1" t="n">
         <v>0.1462</v>
       </c>
     </row>
@@ -12434,9 +13874,12 @@
         <v>0.001734</v>
       </c>
       <c r="F480" s="1" t="n">
+        <v>0.001732</v>
+      </c>
+      <c r="G480" s="1" t="n">
         <v>0.001734</v>
       </c>
-      <c r="G480" s="1" t="n">
+      <c r="H480" s="1" t="n">
         <v>0.001722</v>
       </c>
     </row>
@@ -12459,9 +13902,12 @@
         <v>0.923</v>
       </c>
       <c r="F481" s="1" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="G481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="G481" s="1" t="n">
+      <c r="H481" s="1" t="n">
         <v>0.915</v>
       </c>
     </row>
@@ -12484,9 +13930,12 @@
         <v>0.13479</v>
       </c>
       <c r="F482" s="1" t="n">
+        <v>0.13459</v>
+      </c>
+      <c r="G482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="G482" s="1" t="n">
+      <c r="H482" s="1" t="n">
         <v>0.13437</v>
       </c>
     </row>
@@ -12509,9 +13958,12 @@
         <v>0.04062</v>
       </c>
       <c r="F483" s="1" t="n">
+        <v>0.04057</v>
+      </c>
+      <c r="G483" s="1" t="n">
         <v>0.04062</v>
       </c>
-      <c r="G483" s="1" t="n">
+      <c r="H483" s="1" t="n">
         <v>0.04048</v>
       </c>
     </row>
@@ -12534,9 +13986,12 @@
         <v>0.3102</v>
       </c>
       <c r="F484" s="1" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="G484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="G484" s="1" t="n">
+      <c r="H484" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -12559,9 +14014,12 @@
         <v>0.057</v>
       </c>
       <c r="F485" s="1" t="n">
-        <v>0.057</v>
+        <v>0.05702</v>
       </c>
       <c r="G485" s="1" t="n">
+        <v>0.05702</v>
+      </c>
+      <c r="H485" s="1" t="n">
         <v>0.05633</v>
       </c>
     </row>
@@ -12584,9 +14042,12 @@
         <v>0.001577</v>
       </c>
       <c r="F486" s="1" t="n">
-        <v>0.001577</v>
+        <v>0.001578</v>
       </c>
       <c r="G486" s="1" t="n">
+        <v>0.001578</v>
+      </c>
+      <c r="H486" s="1" t="n">
         <v>0.001569</v>
       </c>
     </row>
@@ -12609,9 +14070,12 @@
         <v>0.0675</v>
       </c>
       <c r="F487" s="1" t="n">
-        <v>0.0675</v>
+        <v>0.06763</v>
       </c>
       <c r="G487" s="1" t="n">
+        <v>0.06763</v>
+      </c>
+      <c r="H487" s="1" t="n">
         <v>0.06716</v>
       </c>
     </row>
@@ -12634,9 +14098,12 @@
         <v>0.195</v>
       </c>
       <c r="F488" s="1" t="n">
-        <v>0.195</v>
+        <v>0.1953</v>
       </c>
       <c r="G488" s="1" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="H488" s="1" t="n">
         <v>0.1936</v>
       </c>
     </row>
@@ -12659,9 +14126,12 @@
         <v>0.04837</v>
       </c>
       <c r="F489" s="1" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="G489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="G489" s="1" t="n">
+      <c r="H489" s="1" t="n">
         <v>0.04804</v>
       </c>
     </row>
@@ -12684,9 +14154,12 @@
         <v>0.1397</v>
       </c>
       <c r="F490" s="1" t="n">
+        <v>0.1394</v>
+      </c>
+      <c r="G490" s="1" t="n">
         <v>0.1397</v>
       </c>
-      <c r="G490" s="1" t="n">
+      <c r="H490" s="1" t="n">
         <v>0.139</v>
       </c>
     </row>
@@ -12709,9 +14182,12 @@
         <v>0.0227</v>
       </c>
       <c r="F491" s="1" t="n">
+        <v>0.0226</v>
+      </c>
+      <c r="G491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="G491" s="1" t="n">
+      <c r="H491" s="1" t="n">
         <v>0.02243</v>
       </c>
     </row>
@@ -12734,9 +14210,12 @@
         <v>0.007886000000000001</v>
       </c>
       <c r="F492" s="1" t="n">
+        <v>0.007889</v>
+      </c>
+      <c r="G492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="G492" s="1" t="n">
+      <c r="H492" s="1" t="n">
         <v>0.007825</v>
       </c>
     </row>
@@ -12759,9 +14238,12 @@
         <v>0.0005984</v>
       </c>
       <c r="F493" s="1" t="n">
+        <v>0.000598</v>
+      </c>
+      <c r="G493" s="1" t="n">
         <v>0.0005984</v>
       </c>
-      <c r="G493" s="1" t="n">
+      <c r="H493" s="1" t="n">
         <v>0.0005952</v>
       </c>
     </row>
@@ -12784,9 +14266,12 @@
         <v>3.033</v>
       </c>
       <c r="F494" s="1" t="n">
+        <v>3.025</v>
+      </c>
+      <c r="G494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="G494" s="1" t="n">
+      <c r="H494" s="1" t="n">
         <v>2.999</v>
       </c>
     </row>
@@ -12809,9 +14294,12 @@
         <v>0.05131</v>
       </c>
       <c r="F495" s="1" t="n">
+        <v>0.05109</v>
+      </c>
+      <c r="G495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="G495" s="1" t="n">
+      <c r="H495" s="1" t="n">
         <v>0.05085</v>
       </c>
     </row>
@@ -12834,9 +14322,12 @@
         <v>0.006864</v>
       </c>
       <c r="F496" s="1" t="n">
+        <v>0.006855</v>
+      </c>
+      <c r="G496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="G496" s="1" t="n">
+      <c r="H496" s="1" t="n">
         <v>0.006839</v>
       </c>
     </row>
@@ -12862,6 +14353,9 @@
         <v>1.31</v>
       </c>
       <c r="G497" s="1" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="H497" s="1" t="n">
         <v>1.299</v>
       </c>
     </row>
@@ -12884,9 +14378,12 @@
         <v>0.04005</v>
       </c>
       <c r="F498" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="G498" s="1" t="n">
+      <c r="H498" s="1" t="n">
         <v>0.03999</v>
       </c>
     </row>
@@ -12909,9 +14406,12 @@
         <v>0.04196</v>
       </c>
       <c r="F499" s="1" t="n">
+        <v>0.04196</v>
+      </c>
+      <c r="G499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="G499" s="1" t="n">
+      <c r="H499" s="1" t="n">
         <v>0.04186</v>
       </c>
     </row>
@@ -12934,9 +14434,12 @@
         <v>0.00541</v>
       </c>
       <c r="F500" s="1" t="n">
-        <v>0.00541</v>
+        <v>0.00543</v>
       </c>
       <c r="G500" s="1" t="n">
+        <v>0.00543</v>
+      </c>
+      <c r="H500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -12959,9 +14462,12 @@
         <v>0.0363</v>
       </c>
       <c r="F501" s="1" t="n">
+        <v>0.03628</v>
+      </c>
+      <c r="G501" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="G501" s="1" t="n">
+      <c r="H501" s="1" t="n">
         <v>0.03625</v>
       </c>
     </row>
@@ -12984,9 +14490,12 @@
         <v>0.0733</v>
       </c>
       <c r="F502" s="1" t="n">
+        <v>0.0733</v>
+      </c>
+      <c r="G502" s="1" t="n">
         <v>0.07335999999999999</v>
       </c>
-      <c r="G502" s="1" t="n">
+      <c r="H502" s="1" t="n">
         <v>0.07321</v>
       </c>
     </row>
@@ -13009,9 +14518,12 @@
         <v>0.0007545</v>
       </c>
       <c r="F503" s="1" t="n">
-        <v>0.0007545</v>
+        <v>0.000755</v>
       </c>
       <c r="G503" s="1" t="n">
+        <v>0.000755</v>
+      </c>
+      <c r="H503" s="1" t="n">
         <v>0.0007499</v>
       </c>
     </row>
@@ -13034,9 +14546,12 @@
         <v>0.016003</v>
       </c>
       <c r="F504" s="1" t="n">
+        <v>0.015976</v>
+      </c>
+      <c r="G504" s="1" t="n">
         <v>0.016003</v>
       </c>
-      <c r="G504" s="1" t="n">
+      <c r="H504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -13059,9 +14574,12 @@
         <v>0.00713</v>
       </c>
       <c r="F505" s="1" t="n">
+        <v>0.00711</v>
+      </c>
+      <c r="G505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="G505" s="1" t="n">
+      <c r="H505" s="1" t="n">
         <v>0.00709</v>
       </c>
     </row>
@@ -13084,9 +14602,12 @@
         <v>0.0256</v>
       </c>
       <c r="F506" s="1" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="G506" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="G506" s="1" t="n">
+      <c r="H506" s="1" t="n">
         <v>0.0256</v>
       </c>
     </row>
@@ -13112,6 +14633,9 @@
         <v>0.001354</v>
       </c>
       <c r="G507" s="1" t="n">
+        <v>0.001354</v>
+      </c>
+      <c r="H507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -13134,9 +14658,12 @@
         <v>0.2831</v>
       </c>
       <c r="F508" s="1" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="G508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="G508" s="1" t="n">
+      <c r="H508" s="1" t="n">
         <v>0.2821</v>
       </c>
     </row>
@@ -13159,9 +14686,12 @@
         <v>0.133</v>
       </c>
       <c r="F509" s="1" t="n">
+        <v>0.1328</v>
+      </c>
+      <c r="G509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="G509" s="1" t="n">
+      <c r="H509" s="1" t="n">
         <v>0.1323</v>
       </c>
     </row>
@@ -13184,9 +14714,12 @@
         <v>0.04967</v>
       </c>
       <c r="F510" s="1" t="n">
-        <v>0.04967</v>
+        <v>0.04972</v>
       </c>
       <c r="G510" s="1" t="n">
+        <v>0.04972</v>
+      </c>
+      <c r="H510" s="1" t="n">
         <v>0.04932</v>
       </c>
     </row>
@@ -13209,9 +14742,12 @@
         <v>0.00277</v>
       </c>
       <c r="F511" s="1" t="n">
-        <v>0.00277</v>
+        <v>0.00278</v>
       </c>
       <c r="G511" s="1" t="n">
+        <v>0.00278</v>
+      </c>
+      <c r="H511" s="1" t="n">
         <v>0.00275</v>
       </c>
     </row>
@@ -13234,9 +14770,12 @@
         <v>0.015448</v>
       </c>
       <c r="F512" s="1" t="n">
-        <v>0.015448</v>
+        <v>0.015454</v>
       </c>
       <c r="G512" s="1" t="n">
+        <v>0.015454</v>
+      </c>
+      <c r="H512" s="1" t="n">
         <v>0.015351</v>
       </c>
     </row>
@@ -13259,9 +14798,12 @@
         <v>0.6943</v>
       </c>
       <c r="F513" s="1" t="n">
+        <v>0.6938</v>
+      </c>
+      <c r="G513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="G513" s="1" t="n">
+      <c r="H513" s="1" t="n">
         <v>0.6933</v>
       </c>
     </row>
@@ -13284,9 +14826,12 @@
         <v>0.004584</v>
       </c>
       <c r="F514" s="1" t="n">
-        <v>0.004584</v>
+        <v>0.004589</v>
       </c>
       <c r="G514" s="1" t="n">
+        <v>0.004589</v>
+      </c>
+      <c r="H514" s="1" t="n">
         <v>0.004534</v>
       </c>
     </row>
@@ -13309,9 +14854,12 @@
         <v>0.005066</v>
       </c>
       <c r="F515" s="1" t="n">
+        <v>0.005056</v>
+      </c>
+      <c r="G515" s="1" t="n">
         <v>0.005066</v>
       </c>
-      <c r="G515" s="1" t="n">
+      <c r="H515" s="1" t="n">
         <v>0.005037</v>
       </c>
     </row>
@@ -13334,9 +14882,12 @@
         <v>0.06394</v>
       </c>
       <c r="F516" s="1" t="n">
+        <v>0.06369</v>
+      </c>
+      <c r="G516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="G516" s="1" t="n">
+      <c r="H516" s="1" t="n">
         <v>0.06353</v>
       </c>
     </row>
@@ -13359,9 +14910,12 @@
         <v>0.06566</v>
       </c>
       <c r="F517" s="1" t="n">
+        <v>0.06531000000000001</v>
+      </c>
+      <c r="G517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="G517" s="1" t="n">
+      <c r="H517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -13387,6 +14941,9 @@
         <v>0.01219</v>
       </c>
       <c r="G518" s="1" t="n">
+        <v>0.01219</v>
+      </c>
+      <c r="H518" s="1" t="n">
         <v>0.0121</v>
       </c>
     </row>
@@ -13409,9 +14966,12 @@
         <v>0.04795</v>
       </c>
       <c r="F519" s="1" t="n">
+        <v>0.04793</v>
+      </c>
+      <c r="G519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="G519" s="1" t="n">
+      <c r="H519" s="1" t="n">
         <v>0.04743</v>
       </c>
     </row>
@@ -13434,9 +14994,12 @@
         <v>0.04406</v>
       </c>
       <c r="F520" s="1" t="n">
+        <v>0.04401</v>
+      </c>
+      <c r="G520" s="1" t="n">
         <v>0.04406</v>
       </c>
-      <c r="G520" s="1" t="n">
+      <c r="H520" s="1" t="n">
         <v>0.04384</v>
       </c>
     </row>
@@ -13459,9 +15022,12 @@
         <v>0.008609</v>
       </c>
       <c r="F521" s="1" t="n">
+        <v>0.008569</v>
+      </c>
+      <c r="G521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="G521" s="1" t="n">
+      <c r="H521" s="1" t="n">
         <v>0.008552000000000001</v>
       </c>
     </row>
@@ -13484,10 +15050,13 @@
         <v>0.08933000000000001</v>
       </c>
       <c r="F522" s="1" t="n">
+        <v>0.08912</v>
+      </c>
+      <c r="G522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="G522" s="1" t="n">
-        <v>0.0893</v>
+      <c r="H522" s="1" t="n">
+        <v>0.08912</v>
       </c>
     </row>
     <row r="523">
@@ -13509,9 +15078,12 @@
         <v>0.006492</v>
       </c>
       <c r="F523" s="1" t="n">
+        <v>0.006482</v>
+      </c>
+      <c r="G523" s="1" t="n">
         <v>0.006492</v>
       </c>
-      <c r="G523" s="1" t="n">
+      <c r="H523" s="1" t="n">
         <v>0.00646</v>
       </c>
     </row>
@@ -13534,9 +15106,12 @@
         <v>0.01668</v>
       </c>
       <c r="F524" s="1" t="n">
+        <v>0.01666</v>
+      </c>
+      <c r="G524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="G524" s="1" t="n">
+      <c r="H524" s="1" t="n">
         <v>0.01662</v>
       </c>
     </row>
@@ -13559,10 +15134,13 @@
         <v>0.01809</v>
       </c>
       <c r="F525" s="1" t="n">
+        <v>0.01807</v>
+      </c>
+      <c r="G525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="G525" s="1" t="n">
-        <v>0.01808</v>
+      <c r="H525" s="1" t="n">
+        <v>0.01807</v>
       </c>
     </row>
     <row r="526">
@@ -13584,9 +15162,12 @@
         <v>0.07968</v>
       </c>
       <c r="F526" s="1" t="n">
+        <v>0.07965</v>
+      </c>
+      <c r="G526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="G526" s="1" t="n">
+      <c r="H526" s="1" t="n">
         <v>0.07917</v>
       </c>
     </row>
@@ -13609,9 +15190,12 @@
         <v>0.01638</v>
       </c>
       <c r="F527" s="1" t="n">
+        <v>0.01634</v>
+      </c>
+      <c r="G527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="G527" s="1" t="n">
+      <c r="H527" s="1" t="n">
         <v>0.01634</v>
       </c>
     </row>
@@ -13634,9 +15218,12 @@
         <v>0.004177</v>
       </c>
       <c r="F528" s="1" t="n">
+        <v>0.004193</v>
+      </c>
+      <c r="G528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="G528" s="1" t="n">
+      <c r="H528" s="1" t="n">
         <v>0.004164</v>
       </c>
     </row>
@@ -13659,9 +15246,12 @@
         <v>0.003753</v>
       </c>
       <c r="F529" s="1" t="n">
+        <v>0.003739</v>
+      </c>
+      <c r="G529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="G529" s="1" t="n">
+      <c r="H529" s="1" t="n">
         <v>0.003698</v>
       </c>
     </row>
@@ -13684,9 +15274,12 @@
         <v>1.317</v>
       </c>
       <c r="F530" s="1" t="n">
+        <v>1.319</v>
+      </c>
+      <c r="G530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="G530" s="1" t="n">
+      <c r="H530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -13709,9 +15302,12 @@
         <v>0.4932</v>
       </c>
       <c r="F531" s="1" t="n">
-        <v>0.4932</v>
+        <v>0.4937</v>
       </c>
       <c r="G531" s="1" t="n">
+        <v>0.4937</v>
+      </c>
+      <c r="H531" s="1" t="n">
         <v>0.4912</v>
       </c>
     </row>
@@ -13734,9 +15330,12 @@
         <v>0.03087</v>
       </c>
       <c r="F532" s="1" t="n">
+        <v>0.03083</v>
+      </c>
+      <c r="G532" s="1" t="n">
         <v>0.03087</v>
       </c>
-      <c r="G532" s="1" t="n">
+      <c r="H532" s="1" t="n">
         <v>0.03058</v>
       </c>
     </row>
@@ -13759,9 +15358,12 @@
         <v>0.154</v>
       </c>
       <c r="F533" s="1" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="G533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="G533" s="1" t="n">
+      <c r="H533" s="1" t="n">
         <v>0.1532</v>
       </c>
     </row>
@@ -13784,9 +15386,12 @@
         <v>0.05418</v>
       </c>
       <c r="F534" s="1" t="n">
-        <v>0.05421</v>
+        <v>0.05424</v>
       </c>
       <c r="G534" s="1" t="n">
+        <v>0.05424</v>
+      </c>
+      <c r="H534" s="1" t="n">
         <v>0.05388</v>
       </c>
     </row>
@@ -13809,9 +15414,12 @@
         <v>0.01515</v>
       </c>
       <c r="F535" s="1" t="n">
+        <v>0.01514</v>
+      </c>
+      <c r="G535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="G535" s="1" t="n">
+      <c r="H535" s="1" t="n">
         <v>0.01501</v>
       </c>
     </row>
@@ -13834,9 +15442,12 @@
         <v>0.05863</v>
       </c>
       <c r="F536" s="1" t="n">
+        <v>0.05832</v>
+      </c>
+      <c r="G536" s="1" t="n">
         <v>0.05863</v>
       </c>
-      <c r="G536" s="1" t="n">
+      <c r="H536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -13859,10 +15470,13 @@
         <v>0.05499</v>
       </c>
       <c r="F537" s="1" t="n">
+        <v>0.05495</v>
+      </c>
+      <c r="G537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="G537" s="1" t="n">
-        <v>0.05497</v>
+      <c r="H537" s="1" t="n">
+        <v>0.05495</v>
       </c>
     </row>
     <row r="538">
@@ -13887,6 +15501,9 @@
         <v>0.1071</v>
       </c>
       <c r="G538" s="1" t="n">
+        <v>0.1071</v>
+      </c>
+      <c r="H538" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -13909,9 +15526,12 @@
         <v>0.01293</v>
       </c>
       <c r="F539" s="1" t="n">
+        <v>0.01293</v>
+      </c>
+      <c r="G539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="G539" s="1" t="n">
+      <c r="H539" s="1" t="n">
         <v>0.01284</v>
       </c>
     </row>
@@ -13934,9 +15554,12 @@
         <v>0.1765</v>
       </c>
       <c r="F540" s="1" t="n">
+        <v>0.1758</v>
+      </c>
+      <c r="G540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="G540" s="1" t="n">
+      <c r="H540" s="1" t="n">
         <v>0.175</v>
       </c>
     </row>
@@ -13959,9 +15582,12 @@
         <v>0.1238</v>
       </c>
       <c r="F541" s="1" t="n">
-        <v>0.1238</v>
+        <v>0.1239</v>
       </c>
       <c r="G541" s="1" t="n">
+        <v>0.1239</v>
+      </c>
+      <c r="H541" s="1" t="n">
         <v>0.1231</v>
       </c>
     </row>
@@ -13984,9 +15610,12 @@
         <v>0.02506</v>
       </c>
       <c r="F542" s="1" t="n">
-        <v>0.02509</v>
+        <v>0.0251</v>
       </c>
       <c r="G542" s="1" t="n">
+        <v>0.0251</v>
+      </c>
+      <c r="H542" s="1" t="n">
         <v>0.02489</v>
       </c>
     </row>
@@ -14009,9 +15638,12 @@
         <v>0.05892</v>
       </c>
       <c r="F543" s="1" t="n">
-        <v>0.05892</v>
+        <v>0.05894</v>
       </c>
       <c r="G543" s="1" t="n">
+        <v>0.05894</v>
+      </c>
+      <c r="H543" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H543"/>
+  <dimension ref="A1:I543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -425,8 +425,9 @@
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,10 +463,15 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>price_01:15</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -493,9 +499,12 @@
         <v>71830.3</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>71830.3</v>
+        <v>72052.5</v>
       </c>
       <c r="H2" s="1" t="n">
+        <v>72052.5</v>
+      </c>
+      <c r="I2" s="1" t="n">
         <v>71323.7</v>
       </c>
     </row>
@@ -521,9 +530,12 @@
         <v>2132.9</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>2132.9</v>
+        <v>2135.64</v>
       </c>
       <c r="H3" s="1" t="n">
+        <v>2135.64</v>
+      </c>
+      <c r="I3" s="1" t="n">
         <v>2118.6</v>
       </c>
     </row>
@@ -549,9 +561,12 @@
         <v>89.55</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>89.59</v>
+        <v>89.84</v>
       </c>
       <c r="H4" s="1" t="n">
+        <v>89.84</v>
+      </c>
+      <c r="I4" s="1" t="n">
         <v>89.23</v>
       </c>
     </row>
@@ -577,9 +592,12 @@
         <v>3.861</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>3.887</v>
+        <v>3.888</v>
       </c>
       <c r="H5" s="1" t="n">
+        <v>3.888</v>
+      </c>
+      <c r="I5" s="1" t="n">
         <v>3.77</v>
       </c>
     </row>
@@ -605,9 +623,12 @@
         <v>1.4091</v>
       </c>
       <c r="G6" s="1" t="n">
+        <v>1.4087</v>
+      </c>
+      <c r="H6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="I6" s="1" t="n">
         <v>1.4035</v>
       </c>
     </row>
@@ -633,10 +654,13 @@
         <v>0.09765</v>
       </c>
       <c r="G7" s="1" t="n">
+        <v>0.09744999999999999</v>
+      </c>
+      <c r="H7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="H7" s="1" t="n">
-        <v>0.09765</v>
+      <c r="I7" s="1" t="n">
+        <v>0.09744999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -661,9 +685,12 @@
         <v>0.014278</v>
       </c>
       <c r="G8" s="1" t="n">
+        <v>0.014219</v>
+      </c>
+      <c r="H8" s="1" t="n">
         <v>0.014568</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="I8" s="1" t="n">
         <v>0.014158</v>
       </c>
     </row>
@@ -689,9 +716,12 @@
         <v>661.92</v>
       </c>
       <c r="G9" s="1" t="n">
+        <v>662.78</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="I9" s="1" t="n">
         <v>659.95</v>
       </c>
     </row>
@@ -717,9 +747,12 @@
         <v>19.278</v>
       </c>
       <c r="G10" s="1" t="n">
+        <v>19.312</v>
+      </c>
+      <c r="H10" s="1" t="n">
         <v>19.415</v>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="I10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -745,9 +778,12 @@
         <v>0.0034773</v>
       </c>
       <c r="G11" s="1" t="n">
+        <v>0.0034688</v>
+      </c>
+      <c r="H11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="H11" s="1" t="n">
+      <c r="I11" s="1" t="n">
         <v>0.0034668</v>
       </c>
     </row>
@@ -773,9 +809,12 @@
         <v>36.262</v>
       </c>
       <c r="G12" s="1" t="n">
+        <v>36.34</v>
+      </c>
+      <c r="H12" s="1" t="n">
         <v>36.352</v>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="I12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -801,9 +840,12 @@
         <v>212.79</v>
       </c>
       <c r="G13" s="1" t="n">
+        <v>213.63</v>
+      </c>
+      <c r="H13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="H13" s="1" t="n">
+      <c r="I13" s="1" t="n">
         <v>212.79</v>
       </c>
     </row>
@@ -829,9 +871,12 @@
         <v>0.0011384</v>
       </c>
       <c r="G14" s="1" t="n">
+        <v>0.0011325</v>
+      </c>
+      <c r="H14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="H14" s="1" t="n">
+      <c r="I14" s="1" t="n">
         <v>0.0011277</v>
       </c>
     </row>
@@ -857,10 +902,13 @@
         <v>0.28796</v>
       </c>
       <c r="G15" s="1" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="H15" s="1" t="n">
         <v>0.29276</v>
       </c>
-      <c r="H15" s="1" t="n">
-        <v>0.28578</v>
+      <c r="I15" s="1" t="n">
+        <v>0.28505</v>
       </c>
     </row>
     <row r="16">
@@ -885,9 +933,12 @@
         <v>235.84</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>236.4</v>
+        <v>237.1</v>
       </c>
       <c r="H16" s="1" t="n">
+        <v>237.1</v>
+      </c>
+      <c r="I16" s="1" t="n">
         <v>230.3</v>
       </c>
     </row>
@@ -913,10 +964,13 @@
         <v>1.0116</v>
       </c>
       <c r="G17" s="1" t="n">
+        <v>1.0093</v>
+      </c>
+      <c r="H17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="H17" s="1" t="n">
-        <v>1.0116</v>
+      <c r="I17" s="1" t="n">
+        <v>1.0093</v>
       </c>
     </row>
     <row r="18">
@@ -941,9 +995,12 @@
         <v>0.2718</v>
       </c>
       <c r="G18" s="1" t="n">
+        <v>0.2717</v>
+      </c>
+      <c r="H18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="H18" s="1" t="n">
+      <c r="I18" s="1" t="n">
         <v>0.2713</v>
       </c>
     </row>
@@ -969,9 +1026,12 @@
         <v>9.891999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
+        <v>9.891</v>
+      </c>
+      <c r="H19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="H19" s="1" t="n">
+      <c r="I19" s="1" t="n">
         <v>9.859</v>
       </c>
     </row>
@@ -997,9 +1057,12 @@
         <v>5047.38</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>5047.38</v>
+        <v>5056.54</v>
       </c>
       <c r="H20" s="1" t="n">
+        <v>5056.54</v>
+      </c>
+      <c r="I20" s="1" t="n">
         <v>5033.31</v>
       </c>
     </row>
@@ -1025,9 +1088,12 @@
         <v>464.39</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>464.61</v>
+        <v>464.66</v>
       </c>
       <c r="H21" s="1" t="n">
+        <v>464.66</v>
+      </c>
+      <c r="I21" s="1" t="n">
         <v>462.57</v>
       </c>
     </row>
@@ -1053,9 +1119,12 @@
         <v>1.4489</v>
       </c>
       <c r="G22" s="1" t="n">
+        <v>1.4336</v>
+      </c>
+      <c r="H22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="H22" s="1" t="n">
+      <c r="I22" s="1" t="n">
         <v>1.4185</v>
       </c>
     </row>
@@ -1081,10 +1150,13 @@
         <v>1.1257</v>
       </c>
       <c r="G23" s="1" t="n">
+        <v>1.0926</v>
+      </c>
+      <c r="H23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="H23" s="1" t="n">
-        <v>1.1257</v>
+      <c r="I23" s="1" t="n">
+        <v>1.0926</v>
       </c>
     </row>
     <row r="24">
@@ -1109,9 +1181,12 @@
         <v>1.366</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>1.366</v>
+        <v>1.37</v>
       </c>
       <c r="H24" s="1" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I24" s="1" t="n">
         <v>1.351</v>
       </c>
     </row>
@@ -1137,9 +1212,12 @@
         <v>9.282</v>
       </c>
       <c r="G25" s="1" t="n">
+        <v>9.282</v>
+      </c>
+      <c r="H25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="H25" s="1" t="n">
+      <c r="I25" s="1" t="n">
         <v>9.246</v>
       </c>
     </row>
@@ -1165,9 +1243,12 @@
         <v>0.3741</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>0.3749</v>
+        <v>0.3776</v>
       </c>
       <c r="H26" s="1" t="n">
+        <v>0.3776</v>
+      </c>
+      <c r="I26" s="1" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -1193,9 +1274,12 @@
         <v>0.893</v>
       </c>
       <c r="G27" s="1" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="H27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="H27" s="1" t="n">
+      <c r="I27" s="1" t="n">
         <v>0.887</v>
       </c>
     </row>
@@ -1221,9 +1305,12 @@
         <v>1.823</v>
       </c>
       <c r="G28" s="1" t="n">
+        <v>1.814</v>
+      </c>
+      <c r="H28" s="1" t="n">
         <v>1.823</v>
       </c>
-      <c r="H28" s="1" t="n">
+      <c r="I28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -1249,9 +1336,12 @@
         <v>0.1118</v>
       </c>
       <c r="G29" s="1" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="H29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="H29" s="1" t="n">
+      <c r="I29" s="1" t="n">
         <v>0.1115</v>
       </c>
     </row>
@@ -1277,9 +1367,12 @@
         <v>0.002059</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>0.002063</v>
+        <v>0.002065</v>
       </c>
       <c r="H30" s="1" t="n">
+        <v>0.002065</v>
+      </c>
+      <c r="I30" s="1" t="n">
         <v>0.002054</v>
       </c>
     </row>
@@ -1305,9 +1398,12 @@
         <v>1.508</v>
       </c>
       <c r="G31" s="1" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="H31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="H31" s="1" t="n">
+      <c r="I31" s="1" t="n">
         <v>1.499</v>
       </c>
     </row>
@@ -1333,10 +1429,13 @@
         <v>0.177</v>
       </c>
       <c r="G32" s="1" t="n">
+        <v>0.1762</v>
+      </c>
+      <c r="H32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="H32" s="1" t="n">
-        <v>0.177</v>
+      <c r="I32" s="1" t="n">
+        <v>0.1762</v>
       </c>
     </row>
     <row r="33">
@@ -1361,9 +1460,12 @@
         <v>0.1055</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>0.1056</v>
+        <v>0.1058</v>
       </c>
       <c r="H33" s="1" t="n">
+        <v>0.1058</v>
+      </c>
+      <c r="I33" s="1" t="n">
         <v>0.1045</v>
       </c>
     </row>
@@ -1389,9 +1491,12 @@
         <v>114.29</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>114.54</v>
+        <v>114.6</v>
       </c>
       <c r="H34" s="1" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="I34" s="1" t="n">
         <v>113.65</v>
       </c>
     </row>
@@ -1417,9 +1522,12 @@
         <v>6.885</v>
       </c>
       <c r="G35" s="1" t="n">
+        <v>6.898</v>
+      </c>
+      <c r="H35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="H35" s="1" t="n">
+      <c r="I35" s="1" t="n">
         <v>6.772</v>
       </c>
     </row>
@@ -1445,9 +1553,12 @@
         <v>0.017421</v>
       </c>
       <c r="G36" s="1" t="n">
+        <v>0.017369</v>
+      </c>
+      <c r="H36" s="1" t="n">
         <v>0.017421</v>
       </c>
-      <c r="H36" s="1" t="n">
+      <c r="I36" s="1" t="n">
         <v>0.017313</v>
       </c>
     </row>
@@ -1473,9 +1584,12 @@
         <v>0.3675</v>
       </c>
       <c r="G37" s="1" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="H37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="H37" s="1" t="n">
+      <c r="I37" s="1" t="n">
         <v>0.3656</v>
       </c>
     </row>
@@ -1501,9 +1615,12 @@
         <v>55.67</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>55.72</v>
+        <v>55.79</v>
       </c>
       <c r="H38" s="1" t="n">
+        <v>55.79</v>
+      </c>
+      <c r="I38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -1529,9 +1646,12 @@
         <v>0.58924</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>0.5914700000000001</v>
+        <v>0.59815</v>
       </c>
       <c r="H39" s="1" t="n">
+        <v>0.59815</v>
+      </c>
+      <c r="I39" s="1" t="n">
         <v>0.58131</v>
       </c>
     </row>
@@ -1557,9 +1677,12 @@
         <v>4.096</v>
       </c>
       <c r="G40" s="1" t="n">
+        <v>4.092</v>
+      </c>
+      <c r="H40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="H40" s="1" t="n">
+      <c r="I40" s="1" t="n">
         <v>4.051</v>
       </c>
     </row>
@@ -1585,9 +1708,12 @@
         <v>0.04928</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>0.04957</v>
+        <v>0.04979</v>
       </c>
       <c r="H41" s="1" t="n">
+        <v>0.04979</v>
+      </c>
+      <c r="I41" s="1" t="n">
         <v>0.04927</v>
       </c>
     </row>
@@ -1613,9 +1739,12 @@
         <v>0.7039</v>
       </c>
       <c r="G42" s="1" t="n">
+        <v>0.7042</v>
+      </c>
+      <c r="H42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="H42" s="1" t="n">
+      <c r="I42" s="1" t="n">
         <v>0.7017</v>
       </c>
     </row>
@@ -1641,9 +1770,12 @@
         <v>0.23334</v>
       </c>
       <c r="G43" s="1" t="n">
+        <v>0.23597</v>
+      </c>
+      <c r="H43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="H43" s="1" t="n">
+      <c r="I43" s="1" t="n">
         <v>0.23323</v>
       </c>
     </row>
@@ -1669,9 +1801,12 @@
         <v>0.35352</v>
       </c>
       <c r="G44" s="1" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="H44" s="1" t="n">
         <v>0.35392</v>
       </c>
-      <c r="H44" s="1" t="n">
+      <c r="I44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -1697,9 +1832,12 @@
         <v>0.1725</v>
       </c>
       <c r="G45" s="1" t="n">
+        <v>0.1728</v>
+      </c>
+      <c r="H45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="H45" s="1" t="n">
+      <c r="I45" s="1" t="n">
         <v>0.1714</v>
       </c>
     </row>
@@ -1725,9 +1863,12 @@
         <v>0.0264</v>
       </c>
       <c r="G46" s="1" t="n">
+        <v>0.0265</v>
+      </c>
+      <c r="H46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="H46" s="1" t="n">
+      <c r="I46" s="1" t="n">
         <v>0.0264</v>
       </c>
     </row>
@@ -1753,10 +1894,13 @@
         <v>0.006041</v>
       </c>
       <c r="G47" s="1" t="n">
+        <v>0.006026</v>
+      </c>
+      <c r="H47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="H47" s="1" t="n">
-        <v>0.006032</v>
+      <c r="I47" s="1" t="n">
+        <v>0.006026</v>
       </c>
     </row>
     <row r="48">
@@ -1781,9 +1925,12 @@
         <v>0.007489</v>
       </c>
       <c r="G48" s="1" t="n">
+        <v>0.007499</v>
+      </c>
+      <c r="H48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="H48" s="1" t="n">
+      <c r="I48" s="1" t="n">
         <v>0.007479</v>
       </c>
     </row>
@@ -1809,9 +1956,12 @@
         <v>0.1113</v>
       </c>
       <c r="G49" s="1" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="H49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="H49" s="1" t="n">
+      <c r="I49" s="1" t="n">
         <v>0.1105</v>
       </c>
     </row>
@@ -1837,9 +1987,12 @@
         <v>0.0403</v>
       </c>
       <c r="G50" s="1" t="n">
+        <v>0.04038</v>
+      </c>
+      <c r="H50" s="1" t="n">
         <v>0.04046</v>
       </c>
-      <c r="H50" s="1" t="n">
+      <c r="I50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -1865,9 +2018,12 @@
         <v>0.1655</v>
       </c>
       <c r="G51" s="1" t="n">
+        <v>0.1656</v>
+      </c>
+      <c r="H51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="H51" s="1" t="n">
+      <c r="I51" s="1" t="n">
         <v>0.1655</v>
       </c>
     </row>
@@ -1893,9 +2049,12 @@
         <v>0.00355</v>
       </c>
       <c r="G52" s="1" t="n">
+        <v>0.00356</v>
+      </c>
+      <c r="H52" s="1" t="n">
         <v>0.00357</v>
       </c>
-      <c r="H52" s="1" t="n">
+      <c r="I52" s="1" t="n">
         <v>0.00354</v>
       </c>
     </row>
@@ -1921,9 +2080,12 @@
         <v>2.65</v>
       </c>
       <c r="G53" s="1" t="n">
+        <v>2.657</v>
+      </c>
+      <c r="H53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="H53" s="1" t="n">
+      <c r="I53" s="1" t="n">
         <v>2.645</v>
       </c>
     </row>
@@ -1949,9 +2111,12 @@
         <v>0.006287</v>
       </c>
       <c r="G54" s="1" t="n">
+        <v>0.006295</v>
+      </c>
+      <c r="H54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="H54" s="1" t="n">
+      <c r="I54" s="1" t="n">
         <v>0.006263</v>
       </c>
     </row>
@@ -1977,10 +2142,13 @@
         <v>0.02885</v>
       </c>
       <c r="G55" s="1" t="n">
+        <v>0.02882</v>
+      </c>
+      <c r="H55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="H55" s="1" t="n">
-        <v>0.02885</v>
+      <c r="I55" s="1" t="n">
+        <v>0.02882</v>
       </c>
     </row>
     <row r="56">
@@ -2005,9 +2173,12 @@
         <v>0.7488</v>
       </c>
       <c r="G56" s="1" t="n">
+        <v>0.7495000000000001</v>
+      </c>
+      <c r="H56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="H56" s="1" t="n">
+      <c r="I56" s="1" t="n">
         <v>0.7433999999999999</v>
       </c>
     </row>
@@ -2036,6 +2207,9 @@
         <v>0.105</v>
       </c>
       <c r="H57" s="1" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I57" s="1" t="n">
         <v>0.104</v>
       </c>
     </row>
@@ -2061,9 +2235,12 @@
         <v>0.9536</v>
       </c>
       <c r="G58" s="1" t="n">
+        <v>0.9574</v>
+      </c>
+      <c r="H58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="H58" s="1" t="n">
+      <c r="I58" s="1" t="n">
         <v>0.9505</v>
       </c>
     </row>
@@ -2089,9 +2266,12 @@
         <v>0.08464000000000001</v>
       </c>
       <c r="G59" s="1" t="n">
+        <v>0.08508</v>
+      </c>
+      <c r="H59" s="1" t="n">
         <v>0.08542</v>
       </c>
-      <c r="H59" s="1" t="n">
+      <c r="I59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -2117,9 +2297,12 @@
         <v>0.06957000000000001</v>
       </c>
       <c r="G60" s="1" t="n">
+        <v>0.06995999999999999</v>
+      </c>
+      <c r="H60" s="1" t="n">
         <v>0.07001</v>
       </c>
-      <c r="H60" s="1" t="n">
+      <c r="I60" s="1" t="n">
         <v>0.06924</v>
       </c>
     </row>
@@ -2145,9 +2328,12 @@
         <v>0.0549</v>
       </c>
       <c r="G61" s="1" t="n">
+        <v>0.05502</v>
+      </c>
+      <c r="H61" s="1" t="n">
         <v>0.05523</v>
       </c>
-      <c r="H61" s="1" t="n">
+      <c r="I61" s="1" t="n">
         <v>0.05469</v>
       </c>
     </row>
@@ -2173,9 +2359,12 @@
         <v>0.010152</v>
       </c>
       <c r="G62" s="1" t="n">
+        <v>0.009735000000000001</v>
+      </c>
+      <c r="H62" s="1" t="n">
         <v>0.010194</v>
       </c>
-      <c r="H62" s="1" t="n">
+      <c r="I62" s="1" t="n">
         <v>0.009535999999999999</v>
       </c>
     </row>
@@ -2201,9 +2390,12 @@
         <v>0.28984</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>0.28984</v>
+        <v>0.29028</v>
       </c>
       <c r="H63" s="1" t="n">
+        <v>0.29028</v>
+      </c>
+      <c r="I63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -2229,9 +2421,12 @@
         <v>0.0742</v>
       </c>
       <c r="G64" s="1" t="n">
+        <v>0.07378999999999999</v>
+      </c>
+      <c r="H64" s="1" t="n">
         <v>0.0742</v>
       </c>
-      <c r="H64" s="1" t="n">
+      <c r="I64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -2257,9 +2452,12 @@
         <v>0.3108</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>0.3108</v>
+        <v>0.3154</v>
       </c>
       <c r="H65" s="1" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="I65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -2285,9 +2483,12 @@
         <v>0.16433</v>
       </c>
       <c r="G66" s="1" t="n">
+        <v>0.16416</v>
+      </c>
+      <c r="H66" s="1" t="n">
         <v>0.16461</v>
       </c>
-      <c r="H66" s="1" t="n">
+      <c r="I66" s="1" t="n">
         <v>0.16337</v>
       </c>
     </row>
@@ -2313,9 +2514,12 @@
         <v>0.11926</v>
       </c>
       <c r="G67" s="1" t="n">
+        <v>0.11935</v>
+      </c>
+      <c r="H67" s="1" t="n">
         <v>0.11997</v>
       </c>
-      <c r="H67" s="1" t="n">
+      <c r="I67" s="1" t="n">
         <v>0.11926</v>
       </c>
     </row>
@@ -2341,9 +2545,12 @@
         <v>0.09716</v>
       </c>
       <c r="G68" s="1" t="n">
+        <v>0.09715</v>
+      </c>
+      <c r="H68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="H68" s="1" t="n">
+      <c r="I68" s="1" t="n">
         <v>0.09666</v>
       </c>
     </row>
@@ -2369,9 +2576,12 @@
         <v>0.1262</v>
       </c>
       <c r="G69" s="1" t="n">
+        <v>0.1261</v>
+      </c>
+      <c r="H69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="H69" s="1" t="n">
+      <c r="I69" s="1" t="n">
         <v>0.1247</v>
       </c>
     </row>
@@ -2397,9 +2607,12 @@
         <v>8.602</v>
       </c>
       <c r="G70" s="1" t="n">
+        <v>8.602</v>
+      </c>
+      <c r="H70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="H70" s="1" t="n">
+      <c r="I70" s="1" t="n">
         <v>8.550000000000001</v>
       </c>
     </row>
@@ -2428,6 +2641,9 @@
         <v>0.241</v>
       </c>
       <c r="H71" s="1" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="I71" s="1" t="n">
         <v>0.239</v>
       </c>
     </row>
@@ -2453,10 +2669,13 @@
         <v>0.05125</v>
       </c>
       <c r="G72" s="1" t="n">
+        <v>0.05078</v>
+      </c>
+      <c r="H72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="H72" s="1" t="n">
-        <v>0.05125</v>
+      <c r="I72" s="1" t="n">
+        <v>0.05078</v>
       </c>
     </row>
     <row r="73">
@@ -2481,9 +2700,12 @@
         <v>0.05109</v>
       </c>
       <c r="G73" s="1" t="n">
+        <v>0.05101</v>
+      </c>
+      <c r="H73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="H73" s="1" t="n">
+      <c r="I73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -2509,9 +2731,12 @@
         <v>0.1256</v>
       </c>
       <c r="G74" s="1" t="n">
+        <v>0.1257</v>
+      </c>
+      <c r="H74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="H74" s="1" t="n">
+      <c r="I74" s="1" t="n">
         <v>0.1252</v>
       </c>
     </row>
@@ -2537,9 +2762,12 @@
         <v>0.04696</v>
       </c>
       <c r="G75" s="1" t="n">
+        <v>0.04695</v>
+      </c>
+      <c r="H75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="H75" s="1" t="n">
+      <c r="I75" s="1" t="n">
         <v>0.04688</v>
       </c>
     </row>
@@ -2565,9 +2793,12 @@
         <v>0.06769</v>
       </c>
       <c r="G76" s="1" t="n">
+        <v>0.06781</v>
+      </c>
+      <c r="H76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="H76" s="1" t="n">
+      <c r="I76" s="1" t="n">
         <v>0.06743</v>
       </c>
     </row>
@@ -2593,9 +2824,12 @@
         <v>0.12707</v>
       </c>
       <c r="G77" s="1" t="n">
+        <v>0.12753</v>
+      </c>
+      <c r="H77" s="1" t="n">
         <v>0.12881</v>
       </c>
-      <c r="H77" s="1" t="n">
+      <c r="I77" s="1" t="n">
         <v>0.12685</v>
       </c>
     </row>
@@ -2621,9 +2855,12 @@
         <v>0.1637</v>
       </c>
       <c r="G78" s="1" t="n">
+        <v>0.1648</v>
+      </c>
+      <c r="H78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="H78" s="1" t="n">
+      <c r="I78" s="1" t="n">
         <v>0.1624</v>
       </c>
     </row>
@@ -2649,9 +2886,12 @@
         <v>0.0276</v>
       </c>
       <c r="G79" s="1" t="n">
+        <v>0.0275</v>
+      </c>
+      <c r="H79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="H79" s="1" t="n">
+      <c r="I79" s="1" t="n">
         <v>0.0272</v>
       </c>
     </row>
@@ -2677,9 +2917,12 @@
         <v>356.02</v>
       </c>
       <c r="G80" s="1" t="n">
+        <v>355.97</v>
+      </c>
+      <c r="H80" s="1" t="n">
         <v>356.25</v>
       </c>
-      <c r="H80" s="1" t="n">
+      <c r="I80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -2705,9 +2948,12 @@
         <v>7.224999999999999e-05</v>
       </c>
       <c r="G81" s="1" t="n">
+        <v>7.216e-05</v>
+      </c>
+      <c r="H81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="H81" s="1" t="n">
+      <c r="I81" s="1" t="n">
         <v>7.196e-05</v>
       </c>
     </row>
@@ -2733,9 +2979,12 @@
         <v>0.2688</v>
       </c>
       <c r="G82" s="1" t="n">
+        <v>0.2685</v>
+      </c>
+      <c r="H82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="H82" s="1" t="n">
+      <c r="I82" s="1" t="n">
         <v>0.2672</v>
       </c>
     </row>
@@ -2761,9 +3010,12 @@
         <v>1.1459</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>1.1461</v>
+        <v>1.1483</v>
       </c>
       <c r="H83" s="1" t="n">
+        <v>1.1483</v>
+      </c>
+      <c r="I83" s="1" t="n">
         <v>1.1408</v>
       </c>
     </row>
@@ -2789,9 +3041,12 @@
         <v>0.3623</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>0.3623</v>
+        <v>0.363</v>
       </c>
       <c r="H84" s="1" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="I84" s="1" t="n">
         <v>0.3569</v>
       </c>
     </row>
@@ -2817,9 +3072,12 @@
         <v>2.0144</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>2.0238</v>
+        <v>2.0327</v>
       </c>
       <c r="H85" s="1" t="n">
+        <v>2.0327</v>
+      </c>
+      <c r="I85" s="1" t="n">
         <v>2.0067</v>
       </c>
     </row>
@@ -2845,9 +3103,12 @@
         <v>1.3106</v>
       </c>
       <c r="G86" s="1" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="H86" s="1" t="n">
         <v>1.3167</v>
       </c>
-      <c r="H86" s="1" t="n">
+      <c r="I86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -2873,9 +3134,12 @@
         <v>33.01</v>
       </c>
       <c r="G87" s="1" t="n">
+        <v>33.15</v>
+      </c>
+      <c r="H87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="H87" s="1" t="n">
+      <c r="I87" s="1" t="n">
         <v>32.97</v>
       </c>
     </row>
@@ -2901,10 +3165,13 @@
         <v>0.01147</v>
       </c>
       <c r="G88" s="1" t="n">
+        <v>0.01037</v>
+      </c>
+      <c r="H88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="H88" s="1" t="n">
-        <v>0.01046</v>
+      <c r="I88" s="1" t="n">
+        <v>0.01037</v>
       </c>
     </row>
     <row r="89">
@@ -2929,9 +3196,12 @@
         <v>0.01833</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>0.01835</v>
+        <v>0.01843</v>
       </c>
       <c r="H89" s="1" t="n">
+        <v>0.01843</v>
+      </c>
+      <c r="I89" s="1" t="n">
         <v>0.01828</v>
       </c>
     </row>
@@ -2957,10 +3227,13 @@
         <v>0.03613</v>
       </c>
       <c r="G90" s="1" t="n">
+        <v>0.03566</v>
+      </c>
+      <c r="H90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="H90" s="1" t="n">
-        <v>0.03571</v>
+      <c r="I90" s="1" t="n">
+        <v>0.03566</v>
       </c>
     </row>
     <row r="91">
@@ -2985,9 +3258,12 @@
         <v>0.01199</v>
       </c>
       <c r="G91" s="1" t="n">
+        <v>0.01196</v>
+      </c>
+      <c r="H91" s="1" t="n">
         <v>0.01202</v>
       </c>
-      <c r="H91" s="1" t="n">
+      <c r="I91" s="1" t="n">
         <v>0.01192</v>
       </c>
     </row>
@@ -3016,6 +3292,9 @@
         <v>3.136</v>
       </c>
       <c r="H92" s="1" t="n">
+        <v>3.136</v>
+      </c>
+      <c r="I92" s="1" t="n">
         <v>3.111</v>
       </c>
     </row>
@@ -3041,9 +3320,12 @@
         <v>0.005642</v>
       </c>
       <c r="G93" s="1" t="n">
+        <v>0.005654</v>
+      </c>
+      <c r="H93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="H93" s="1" t="n">
+      <c r="I93" s="1" t="n">
         <v>0.005635</v>
       </c>
     </row>
@@ -3069,9 +3351,12 @@
         <v>0.09420000000000001</v>
       </c>
       <c r="G94" s="1" t="n">
+        <v>0.0941</v>
+      </c>
+      <c r="H94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="H94" s="1" t="n">
+      <c r="I94" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -3097,9 +3382,12 @@
         <v>0.605</v>
       </c>
       <c r="G95" s="1" t="n">
+        <v>0.6032</v>
+      </c>
+      <c r="H95" s="1" t="n">
         <v>0.6058</v>
       </c>
-      <c r="H95" s="1" t="n">
+      <c r="I95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -3125,9 +3413,12 @@
         <v>1.28e-05</v>
       </c>
       <c r="G96" s="1" t="n">
+        <v>1.28e-05</v>
+      </c>
+      <c r="H96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="H96" s="1" t="n">
+      <c r="I96" s="1" t="n">
         <v>1.28e-05</v>
       </c>
     </row>
@@ -3153,9 +3444,12 @@
         <v>1.144</v>
       </c>
       <c r="G97" s="1" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="H97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="H97" s="1" t="n">
+      <c r="I97" s="1" t="n">
         <v>1.136</v>
       </c>
     </row>
@@ -3181,10 +3475,13 @@
         <v>0.25642</v>
       </c>
       <c r="G98" s="1" t="n">
+        <v>0.25472</v>
+      </c>
+      <c r="H98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="H98" s="1" t="n">
-        <v>0.25616</v>
+      <c r="I98" s="1" t="n">
+        <v>0.25472</v>
       </c>
     </row>
     <row r="99">
@@ -3209,9 +3506,12 @@
         <v>1.152</v>
       </c>
       <c r="G99" s="1" t="n">
-        <v>1.155</v>
+        <v>1.156</v>
       </c>
       <c r="H99" s="1" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="I99" s="1" t="n">
         <v>1.146</v>
       </c>
     </row>
@@ -3237,9 +3537,12 @@
         <v>1.868</v>
       </c>
       <c r="G100" s="1" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="H100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="H100" s="1" t="n">
+      <c r="I100" s="1" t="n">
         <v>1.862</v>
       </c>
     </row>
@@ -3265,9 +3568,12 @@
         <v>0.01595</v>
       </c>
       <c r="G101" s="1" t="n">
-        <v>0.01599</v>
+        <v>0.01601</v>
       </c>
       <c r="H101" s="1" t="n">
+        <v>0.01601</v>
+      </c>
+      <c r="I101" s="1" t="n">
         <v>0.01595</v>
       </c>
     </row>
@@ -3293,9 +3599,12 @@
         <v>0.10378</v>
       </c>
       <c r="G102" s="1" t="n">
-        <v>0.10417</v>
+        <v>0.10431</v>
       </c>
       <c r="H102" s="1" t="n">
+        <v>0.10431</v>
+      </c>
+      <c r="I102" s="1" t="n">
         <v>0.10353</v>
       </c>
     </row>
@@ -3321,10 +3630,13 @@
         <v>0.0006041</v>
       </c>
       <c r="G103" s="1" t="n">
+        <v>0.0006039</v>
+      </c>
+      <c r="H103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="H103" s="1" t="n">
-        <v>0.0006041</v>
+      <c r="I103" s="1" t="n">
+        <v>0.0006039</v>
       </c>
     </row>
     <row r="104">
@@ -3349,9 +3661,12 @@
         <v>0.0005731</v>
       </c>
       <c r="G104" s="1" t="n">
-        <v>0.0005731999999999999</v>
+        <v>0.0005776000000000001</v>
       </c>
       <c r="H104" s="1" t="n">
+        <v>0.0005776000000000001</v>
+      </c>
+      <c r="I104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -3377,9 +3692,12 @@
         <v>0.003229</v>
       </c>
       <c r="G105" s="1" t="n">
+        <v>0.003253</v>
+      </c>
+      <c r="H105" s="1" t="n">
         <v>0.003257</v>
       </c>
-      <c r="H105" s="1" t="n">
+      <c r="I105" s="1" t="n">
         <v>0.003229</v>
       </c>
     </row>
@@ -3405,9 +3723,12 @@
         <v>2.633</v>
       </c>
       <c r="G106" s="1" t="n">
+        <v>2.637</v>
+      </c>
+      <c r="H106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="H106" s="1" t="n">
+      <c r="I106" s="1" t="n">
         <v>2.617</v>
       </c>
     </row>
@@ -3433,9 +3754,12 @@
         <v>0.168</v>
       </c>
       <c r="G107" s="1" t="n">
+        <v>0.1678</v>
+      </c>
+      <c r="H107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="H107" s="1" t="n">
+      <c r="I107" s="1" t="n">
         <v>0.167</v>
       </c>
     </row>
@@ -3461,10 +3785,13 @@
         <v>0.09727</v>
       </c>
       <c r="G108" s="1" t="n">
+        <v>0.09683</v>
+      </c>
+      <c r="H108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="H108" s="1" t="n">
-        <v>0.09727</v>
+      <c r="I108" s="1" t="n">
+        <v>0.09683</v>
       </c>
     </row>
     <row r="109">
@@ -3489,9 +3816,12 @@
         <v>0.02228</v>
       </c>
       <c r="G109" s="1" t="n">
+        <v>0.0223</v>
+      </c>
+      <c r="H109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="H109" s="1" t="n">
+      <c r="I109" s="1" t="n">
         <v>0.02228</v>
       </c>
     </row>
@@ -3517,9 +3847,12 @@
         <v>0.2953</v>
       </c>
       <c r="G110" s="1" t="n">
-        <v>0.2953</v>
+        <v>0.2971</v>
       </c>
       <c r="H110" s="1" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="I110" s="1" t="n">
         <v>0.2913</v>
       </c>
     </row>
@@ -3545,9 +3878,12 @@
         <v>0.05708</v>
       </c>
       <c r="G111" s="1" t="n">
-        <v>0.05721</v>
+        <v>0.05736</v>
       </c>
       <c r="H111" s="1" t="n">
+        <v>0.05736</v>
+      </c>
+      <c r="I111" s="1" t="n">
         <v>0.05684</v>
       </c>
     </row>
@@ -3573,9 +3909,12 @@
         <v>0.3059</v>
       </c>
       <c r="G112" s="1" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="H112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="H112" s="1" t="n">
+      <c r="I112" s="1" t="n">
         <v>0.3039</v>
       </c>
     </row>
@@ -3604,6 +3943,9 @@
         <v>18.73</v>
       </c>
       <c r="H113" s="1" t="n">
+        <v>18.73</v>
+      </c>
+      <c r="I113" s="1" t="n">
         <v>18.62</v>
       </c>
     </row>
@@ -3629,9 +3971,12 @@
         <v>0.13425</v>
       </c>
       <c r="G114" s="1" t="n">
+        <v>0.13294</v>
+      </c>
+      <c r="H114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="H114" s="1" t="n">
+      <c r="I114" s="1" t="n">
         <v>0.13225</v>
       </c>
     </row>
@@ -3657,9 +4002,12 @@
         <v>0.01545</v>
       </c>
       <c r="G115" s="1" t="n">
+        <v>0.01552</v>
+      </c>
+      <c r="H115" s="1" t="n">
         <v>0.01583</v>
       </c>
-      <c r="H115" s="1" t="n">
+      <c r="I115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -3685,9 +4033,12 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="G116" s="1" t="n">
+        <v>0.08597</v>
+      </c>
+      <c r="H116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="H116" s="1" t="n">
+      <c r="I116" s="1" t="n">
         <v>0.08527</v>
       </c>
     </row>
@@ -3713,10 +4064,13 @@
         <v>0.048291</v>
       </c>
       <c r="G117" s="1" t="n">
+        <v>0.047967</v>
+      </c>
+      <c r="H117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="H117" s="1" t="n">
-        <v>0.048291</v>
+      <c r="I117" s="1" t="n">
+        <v>0.047967</v>
       </c>
     </row>
     <row r="118">
@@ -3741,9 +4095,12 @@
         <v>0.04823</v>
       </c>
       <c r="G118" s="1" t="n">
+        <v>0.04813</v>
+      </c>
+      <c r="H118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="H118" s="1" t="n">
+      <c r="I118" s="1" t="n">
         <v>0.04807</v>
       </c>
     </row>
@@ -3769,9 +4126,12 @@
         <v>0.04161</v>
       </c>
       <c r="G119" s="1" t="n">
+        <v>0.04216</v>
+      </c>
+      <c r="H119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="H119" s="1" t="n">
+      <c r="I119" s="1" t="n">
         <v>0.04109</v>
       </c>
     </row>
@@ -3797,9 +4157,12 @@
         <v>0.14552</v>
       </c>
       <c r="G120" s="1" t="n">
+        <v>0.14562</v>
+      </c>
+      <c r="H120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="H120" s="1" t="n">
+      <c r="I120" s="1" t="n">
         <v>0.14499</v>
       </c>
     </row>
@@ -3825,9 +4188,12 @@
         <v>0.1284</v>
       </c>
       <c r="G121" s="1" t="n">
-        <v>0.1284</v>
+        <v>0.1287</v>
       </c>
       <c r="H121" s="1" t="n">
+        <v>0.1287</v>
+      </c>
+      <c r="I121" s="1" t="n">
         <v>0.1272</v>
       </c>
     </row>
@@ -3853,9 +4219,12 @@
         <v>1.893</v>
       </c>
       <c r="G122" s="1" t="n">
+        <v>1.894</v>
+      </c>
+      <c r="H122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="H122" s="1" t="n">
+      <c r="I122" s="1" t="n">
         <v>1.887</v>
       </c>
     </row>
@@ -3881,9 +4250,12 @@
         <v>0.03058</v>
       </c>
       <c r="G123" s="1" t="n">
+        <v>0.03049</v>
+      </c>
+      <c r="H123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="H123" s="1" t="n">
+      <c r="I123" s="1" t="n">
         <v>0.03041</v>
       </c>
     </row>
@@ -3909,9 +4281,12 @@
         <v>0.13351</v>
       </c>
       <c r="G124" s="1" t="n">
+        <v>0.13304</v>
+      </c>
+      <c r="H124" s="1" t="n">
         <v>0.13401</v>
       </c>
-      <c r="H124" s="1" t="n">
+      <c r="I124" s="1" t="n">
         <v>0.13288</v>
       </c>
     </row>
@@ -3937,9 +4312,12 @@
         <v>0.04139</v>
       </c>
       <c r="G125" s="1" t="n">
+        <v>0.04144</v>
+      </c>
+      <c r="H125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="H125" s="1" t="n">
+      <c r="I125" s="1" t="n">
         <v>0.04139</v>
       </c>
     </row>
@@ -3965,9 +4343,12 @@
         <v>0.1163</v>
       </c>
       <c r="G126" s="1" t="n">
+        <v>0.1165</v>
+      </c>
+      <c r="H126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="H126" s="1" t="n">
+      <c r="I126" s="1" t="n">
         <v>0.1154</v>
       </c>
     </row>
@@ -3993,9 +4374,12 @@
         <v>0.5028</v>
       </c>
       <c r="G127" s="1" t="n">
-        <v>0.5028</v>
+        <v>0.5046</v>
       </c>
       <c r="H127" s="1" t="n">
+        <v>0.5046</v>
+      </c>
+      <c r="I127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -4021,9 +4405,12 @@
         <v>0.0383</v>
       </c>
       <c r="G128" s="1" t="n">
+        <v>0.03819</v>
+      </c>
+      <c r="H128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="H128" s="1" t="n">
+      <c r="I128" s="1" t="n">
         <v>0.03787</v>
       </c>
     </row>
@@ -4052,6 +4439,9 @@
         <v>0.798</v>
       </c>
       <c r="H129" s="1" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="I129" s="1" t="n">
         <v>0.796</v>
       </c>
     </row>
@@ -4077,9 +4467,12 @@
         <v>0.03458</v>
       </c>
       <c r="G130" s="1" t="n">
+        <v>0.03447</v>
+      </c>
+      <c r="H130" s="1" t="n">
         <v>0.03458</v>
       </c>
-      <c r="H130" s="1" t="n">
+      <c r="I130" s="1" t="n">
         <v>0.03439</v>
       </c>
     </row>
@@ -4105,9 +4498,12 @@
         <v>0.4295</v>
       </c>
       <c r="G131" s="1" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="H131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="H131" s="1" t="n">
+      <c r="I131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -4133,9 +4529,12 @@
         <v>0.04361</v>
       </c>
       <c r="G132" s="1" t="n">
+        <v>0.04381</v>
+      </c>
+      <c r="H132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="H132" s="1" t="n">
+      <c r="I132" s="1" t="n">
         <v>0.04361</v>
       </c>
     </row>
@@ -4161,9 +4560,12 @@
         <v>1.3017</v>
       </c>
       <c r="G133" s="1" t="n">
+        <v>1.2987</v>
+      </c>
+      <c r="H133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="H133" s="1" t="n">
+      <c r="I133" s="1" t="n">
         <v>1.2941</v>
       </c>
     </row>
@@ -4189,9 +4591,12 @@
         <v>0.02208</v>
       </c>
       <c r="G134" s="1" t="n">
+        <v>0.02211</v>
+      </c>
+      <c r="H134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="H134" s="1" t="n">
+      <c r="I134" s="1" t="n">
         <v>0.02208</v>
       </c>
     </row>
@@ -4217,10 +4622,13 @@
         <v>0.0004694</v>
       </c>
       <c r="G135" s="1" t="n">
+        <v>0.0004675</v>
+      </c>
+      <c r="H135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="H135" s="1" t="n">
-        <v>0.0004694</v>
+      <c r="I135" s="1" t="n">
+        <v>0.0004675</v>
       </c>
     </row>
     <row r="136">
@@ -4245,9 +4653,12 @@
         <v>0.001976</v>
       </c>
       <c r="G136" s="1" t="n">
+        <v>0.001957</v>
+      </c>
+      <c r="H136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="H136" s="1" t="n">
+      <c r="I136" s="1" t="n">
         <v>0.001913</v>
       </c>
     </row>
@@ -4273,9 +4684,12 @@
         <v>0.3239</v>
       </c>
       <c r="G137" s="1" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="H137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="H137" s="1" t="n">
+      <c r="I137" s="1" t="n">
         <v>0.3204</v>
       </c>
     </row>
@@ -4301,9 +4715,12 @@
         <v>0.575</v>
       </c>
       <c r="G138" s="1" t="n">
+        <v>0.5747</v>
+      </c>
+      <c r="H138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="H138" s="1" t="n">
+      <c r="I138" s="1" t="n">
         <v>0.5705</v>
       </c>
     </row>
@@ -4329,9 +4746,12 @@
         <v>0.02151</v>
       </c>
       <c r="G139" s="1" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="H139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="H139" s="1" t="n">
+      <c r="I139" s="1" t="n">
         <v>0.02145</v>
       </c>
     </row>
@@ -4357,10 +4777,13 @@
         <v>0.08073</v>
       </c>
       <c r="G140" s="1" t="n">
+        <v>0.08071</v>
+      </c>
+      <c r="H140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="H140" s="1" t="n">
-        <v>0.08073</v>
+      <c r="I140" s="1" t="n">
+        <v>0.08071</v>
       </c>
     </row>
     <row r="141">
@@ -4388,6 +4811,9 @@
         <v>0.001656</v>
       </c>
       <c r="H141" s="1" t="n">
+        <v>0.001656</v>
+      </c>
+      <c r="I141" s="1" t="n">
         <v>0.001616</v>
       </c>
     </row>
@@ -4413,9 +4839,12 @@
         <v>0.4266</v>
       </c>
       <c r="G142" s="1" t="n">
-        <v>0.4274</v>
+        <v>0.4276</v>
       </c>
       <c r="H142" s="1" t="n">
+        <v>0.4276</v>
+      </c>
+      <c r="I142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -4441,10 +4870,13 @@
         <v>0.030127</v>
       </c>
       <c r="G143" s="1" t="n">
+        <v>0.030021</v>
+      </c>
+      <c r="H143" s="1" t="n">
         <v>0.030681</v>
       </c>
-      <c r="H143" s="1" t="n">
-        <v>0.030127</v>
+      <c r="I143" s="1" t="n">
+        <v>0.030021</v>
       </c>
     </row>
     <row r="144">
@@ -4469,9 +4901,12 @@
         <v>0.000226</v>
       </c>
       <c r="G144" s="1" t="n">
+        <v>0.000225</v>
+      </c>
+      <c r="H144" s="1" t="n">
         <v>0.000226</v>
       </c>
-      <c r="H144" s="1" t="n">
+      <c r="I144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -4497,9 +4932,12 @@
         <v>0.03311</v>
       </c>
       <c r="G145" s="1" t="n">
-        <v>0.03311</v>
+        <v>0.03529</v>
       </c>
       <c r="H145" s="1" t="n">
+        <v>0.03529</v>
+      </c>
+      <c r="I145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -4525,9 +4963,12 @@
         <v>0.11573</v>
       </c>
       <c r="G146" s="1" t="n">
+        <v>0.11546</v>
+      </c>
+      <c r="H146" s="1" t="n">
         <v>0.116</v>
       </c>
-      <c r="H146" s="1" t="n">
+      <c r="I146" s="1" t="n">
         <v>0.11518</v>
       </c>
     </row>
@@ -4553,9 +4994,12 @@
         <v>0.02164</v>
       </c>
       <c r="G147" s="1" t="n">
-        <v>0.02185</v>
+        <v>0.02198</v>
       </c>
       <c r="H147" s="1" t="n">
+        <v>0.02198</v>
+      </c>
+      <c r="I147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -4581,9 +5025,12 @@
         <v>1.4242</v>
       </c>
       <c r="G148" s="1" t="n">
+        <v>1.4234</v>
+      </c>
+      <c r="H148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="H148" s="1" t="n">
+      <c r="I148" s="1" t="n">
         <v>1.4154</v>
       </c>
     </row>
@@ -4609,9 +5056,12 @@
         <v>1.8742</v>
       </c>
       <c r="G149" s="1" t="n">
-        <v>1.8771</v>
+        <v>1.8868</v>
       </c>
       <c r="H149" s="1" t="n">
+        <v>1.8868</v>
+      </c>
+      <c r="I149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -4637,9 +5087,12 @@
         <v>0.1</v>
       </c>
       <c r="G150" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="H150" s="1" t="n">
+      <c r="I150" s="1" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4665,9 +5118,12 @@
         <v>4.605</v>
       </c>
       <c r="G151" s="1" t="n">
+        <v>4.593</v>
+      </c>
+      <c r="H151" s="1" t="n">
         <v>4.609</v>
       </c>
-      <c r="H151" s="1" t="n">
+      <c r="I151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -4693,9 +5149,12 @@
         <v>5.569</v>
       </c>
       <c r="G152" s="1" t="n">
+        <v>5.587</v>
+      </c>
+      <c r="H152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="H152" s="1" t="n">
+      <c r="I152" s="1" t="n">
         <v>5.55</v>
       </c>
     </row>
@@ -4721,9 +5180,12 @@
         <v>0.3227</v>
       </c>
       <c r="G153" s="1" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="H153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="H153" s="1" t="n">
+      <c r="I153" s="1" t="n">
         <v>0.3178</v>
       </c>
     </row>
@@ -4749,9 +5211,12 @@
         <v>0.5901999999999999</v>
       </c>
       <c r="G154" s="1" t="n">
+        <v>0.5911999999999999</v>
+      </c>
+      <c r="H154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="H154" s="1" t="n">
+      <c r="I154" s="1" t="n">
         <v>0.5891999999999999</v>
       </c>
     </row>
@@ -4777,9 +5242,12 @@
         <v>0.01272</v>
       </c>
       <c r="G155" s="1" t="n">
-        <v>0.01278</v>
+        <v>0.01279</v>
       </c>
       <c r="H155" s="1" t="n">
+        <v>0.01279</v>
+      </c>
+      <c r="I155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -4805,9 +5273,12 @@
         <v>0.1002</v>
       </c>
       <c r="G156" s="1" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="H156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="H156" s="1" t="n">
+      <c r="I156" s="1" t="n">
         <v>0.0997</v>
       </c>
     </row>
@@ -4833,9 +5304,12 @@
         <v>16.739</v>
       </c>
       <c r="G157" s="1" t="n">
+        <v>16.741</v>
+      </c>
+      <c r="H157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="H157" s="1" t="n">
+      <c r="I157" s="1" t="n">
         <v>16.563</v>
       </c>
     </row>
@@ -4861,9 +5335,12 @@
         <v>0.05579</v>
       </c>
       <c r="G158" s="1" t="n">
-        <v>0.05593</v>
+        <v>0.05615</v>
       </c>
       <c r="H158" s="1" t="n">
+        <v>0.05615</v>
+      </c>
+      <c r="I158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -4889,9 +5366,12 @@
         <v>29.1</v>
       </c>
       <c r="G159" s="1" t="n">
-        <v>29.14</v>
+        <v>29.22</v>
       </c>
       <c r="H159" s="1" t="n">
+        <v>29.22</v>
+      </c>
+      <c r="I159" s="1" t="n">
         <v>28.87</v>
       </c>
     </row>
@@ -4917,9 +5397,12 @@
         <v>0.02138</v>
       </c>
       <c r="G160" s="1" t="n">
+        <v>0.02138</v>
+      </c>
+      <c r="H160" s="1" t="n">
         <v>0.02141</v>
       </c>
-      <c r="H160" s="1" t="n">
+      <c r="I160" s="1" t="n">
         <v>0.02121</v>
       </c>
     </row>
@@ -4945,9 +5428,12 @@
         <v>0.0006626</v>
       </c>
       <c r="G161" s="1" t="n">
+        <v>0.0006636</v>
+      </c>
+      <c r="H161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="H161" s="1" t="n">
+      <c r="I161" s="1" t="n">
         <v>0.0006601000000000001</v>
       </c>
     </row>
@@ -4973,9 +5459,12 @@
         <v>0.4068</v>
       </c>
       <c r="G162" s="1" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="H162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="H162" s="1" t="n">
+      <c r="I162" s="1" t="n">
         <v>0.3936</v>
       </c>
     </row>
@@ -5001,9 +5490,12 @@
         <v>0.1946</v>
       </c>
       <c r="G163" s="1" t="n">
+        <v>0.1951</v>
+      </c>
+      <c r="H163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="H163" s="1" t="n">
+      <c r="I163" s="1" t="n">
         <v>0.1931</v>
       </c>
     </row>
@@ -5029,9 +5521,12 @@
         <v>0.322</v>
       </c>
       <c r="G164" s="1" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="H164" s="1" t="n">
+      <c r="I164" s="1" t="n">
         <v>0.32</v>
       </c>
     </row>
@@ -5060,6 +5555,9 @@
         <v>0.377</v>
       </c>
       <c r="H165" s="1" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="I165" s="1" t="n">
         <v>0.375</v>
       </c>
     </row>
@@ -5085,9 +5583,12 @@
         <v>0.02276</v>
       </c>
       <c r="G166" s="1" t="n">
+        <v>0.02276</v>
+      </c>
+      <c r="H166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="H166" s="1" t="n">
+      <c r="I166" s="1" t="n">
         <v>0.02271</v>
       </c>
     </row>
@@ -5113,9 +5614,12 @@
         <v>0.007387</v>
       </c>
       <c r="G167" s="1" t="n">
+        <v>0.007389</v>
+      </c>
+      <c r="H167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="H167" s="1" t="n">
+      <c r="I167" s="1" t="n">
         <v>0.007348</v>
       </c>
     </row>
@@ -5141,10 +5645,13 @@
         <v>0.01392</v>
       </c>
       <c r="G168" s="1" t="n">
+        <v>0.01391</v>
+      </c>
+      <c r="H168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="H168" s="1" t="n">
-        <v>0.01392</v>
+      <c r="I168" s="1" t="n">
+        <v>0.01391</v>
       </c>
     </row>
     <row r="169">
@@ -5169,9 +5676,12 @@
         <v>0.25673</v>
       </c>
       <c r="G169" s="1" t="n">
+        <v>0.25715</v>
+      </c>
+      <c r="H169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="H169" s="1" t="n">
+      <c r="I169" s="1" t="n">
         <v>0.25376</v>
       </c>
     </row>
@@ -5197,9 +5707,12 @@
         <v>0.02167</v>
       </c>
       <c r="G170" s="1" t="n">
+        <v>0.02174</v>
+      </c>
+      <c r="H170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="H170" s="1" t="n">
+      <c r="I170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -5225,9 +5738,12 @@
         <v>0.1742</v>
       </c>
       <c r="G171" s="1" t="n">
-        <v>0.1756</v>
+        <v>0.177</v>
       </c>
       <c r="H171" s="1" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="I171" s="1" t="n">
         <v>0.1733</v>
       </c>
     </row>
@@ -5256,6 +5772,9 @@
         <v>0.09</v>
       </c>
       <c r="H172" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -5281,9 +5800,12 @@
         <v>0.004719</v>
       </c>
       <c r="G173" s="1" t="n">
+        <v>0.004729</v>
+      </c>
+      <c r="H173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="H173" s="1" t="n">
+      <c r="I173" s="1" t="n">
         <v>0.004719</v>
       </c>
     </row>
@@ -5309,9 +5831,12 @@
         <v>0.4406</v>
       </c>
       <c r="G174" s="1" t="n">
-        <v>0.4406</v>
+        <v>0.4423</v>
       </c>
       <c r="H174" s="1" t="n">
+        <v>0.4423</v>
+      </c>
+      <c r="I174" s="1" t="n">
         <v>0.4368</v>
       </c>
     </row>
@@ -5337,9 +5862,12 @@
         <v>0.08978999999999999</v>
       </c>
       <c r="G175" s="1" t="n">
-        <v>0.09011</v>
+        <v>0.09021999999999999</v>
       </c>
       <c r="H175" s="1" t="n">
+        <v>0.09021999999999999</v>
+      </c>
+      <c r="I175" s="1" t="n">
         <v>0.0895</v>
       </c>
     </row>
@@ -5365,9 +5893,12 @@
         <v>0.2474</v>
       </c>
       <c r="G176" s="1" t="n">
+        <v>0.2475</v>
+      </c>
+      <c r="H176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="H176" s="1" t="n">
+      <c r="I176" s="1" t="n">
         <v>0.2453</v>
       </c>
     </row>
@@ -5393,9 +5924,12 @@
         <v>0.01931</v>
       </c>
       <c r="G177" s="1" t="n">
+        <v>0.01931</v>
+      </c>
+      <c r="H177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="H177" s="1" t="n">
+      <c r="I177" s="1" t="n">
         <v>0.01917</v>
       </c>
     </row>
@@ -5421,9 +5955,12 @@
         <v>6.219</v>
       </c>
       <c r="G178" s="1" t="n">
+        <v>6.216</v>
+      </c>
+      <c r="H178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="H178" s="1" t="n">
+      <c r="I178" s="1" t="n">
         <v>6.18</v>
       </c>
     </row>
@@ -5449,9 +5986,12 @@
         <v>0.1362</v>
       </c>
       <c r="G179" s="1" t="n">
+        <v>0.1371</v>
+      </c>
+      <c r="H179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="H179" s="1" t="n">
+      <c r="I179" s="1" t="n">
         <v>0.1362</v>
       </c>
     </row>
@@ -5477,9 +6017,12 @@
         <v>0.005093</v>
       </c>
       <c r="G180" s="1" t="n">
+        <v>0.005091</v>
+      </c>
+      <c r="H180" s="1" t="n">
         <v>0.005093</v>
       </c>
-      <c r="H180" s="1" t="n">
+      <c r="I180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -5505,9 +6048,12 @@
         <v>0.01202</v>
       </c>
       <c r="G181" s="1" t="n">
+        <v>0.01196</v>
+      </c>
+      <c r="H181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="H181" s="1" t="n">
+      <c r="I181" s="1" t="n">
         <v>0.01189</v>
       </c>
     </row>
@@ -5533,9 +6079,12 @@
         <v>0.007408</v>
       </c>
       <c r="G182" s="1" t="n">
+        <v>0.007408</v>
+      </c>
+      <c r="H182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="H182" s="1" t="n">
+      <c r="I182" s="1" t="n">
         <v>0.007295</v>
       </c>
     </row>
@@ -5561,9 +6110,12 @@
         <v>0.12966</v>
       </c>
       <c r="G183" s="1" t="n">
+        <v>0.13142</v>
+      </c>
+      <c r="H183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="H183" s="1" t="n">
+      <c r="I183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -5589,9 +6141,12 @@
         <v>0.09658</v>
       </c>
       <c r="G184" s="1" t="n">
-        <v>0.09673</v>
+        <v>0.09733</v>
       </c>
       <c r="H184" s="1" t="n">
+        <v>0.09733</v>
+      </c>
+      <c r="I184" s="1" t="n">
         <v>0.09587</v>
       </c>
     </row>
@@ -5617,9 +6172,12 @@
         <v>0.00763</v>
       </c>
       <c r="G185" s="1" t="n">
-        <v>0.00763</v>
+        <v>0.00764</v>
       </c>
       <c r="H185" s="1" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="I185" s="1" t="n">
         <v>0.00758</v>
       </c>
     </row>
@@ -5645,9 +6203,12 @@
         <v>0.04936</v>
       </c>
       <c r="G186" s="1" t="n">
+        <v>0.04928</v>
+      </c>
+      <c r="H186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="H186" s="1" t="n">
+      <c r="I186" s="1" t="n">
         <v>0.04914</v>
       </c>
     </row>
@@ -5673,9 +6234,12 @@
         <v>0.0271</v>
       </c>
       <c r="G187" s="1" t="n">
-        <v>0.0272</v>
+        <v>0.02725</v>
       </c>
       <c r="H187" s="1" t="n">
+        <v>0.02725</v>
+      </c>
+      <c r="I187" s="1" t="n">
         <v>0.02686</v>
       </c>
     </row>
@@ -5701,9 +6265,12 @@
         <v>0.003341</v>
       </c>
       <c r="G188" s="1" t="n">
-        <v>0.00335</v>
+        <v>0.003351</v>
       </c>
       <c r="H188" s="1" t="n">
+        <v>0.003351</v>
+      </c>
+      <c r="I188" s="1" t="n">
         <v>0.003323</v>
       </c>
     </row>
@@ -5729,9 +6296,12 @@
         <v>0.29</v>
       </c>
       <c r="G189" s="1" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="H189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="H189" s="1" t="n">
+      <c r="I189" s="1" t="n">
         <v>0.2875</v>
       </c>
     </row>
@@ -5757,9 +6327,12 @@
         <v>0.01831</v>
       </c>
       <c r="G190" s="1" t="n">
+        <v>0.01833</v>
+      </c>
+      <c r="H190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="H190" s="1" t="n">
+      <c r="I190" s="1" t="n">
         <v>0.01819</v>
       </c>
     </row>
@@ -5785,10 +6358,13 @@
         <v>0.2609</v>
       </c>
       <c r="G191" s="1" t="n">
+        <v>0.2604</v>
+      </c>
+      <c r="H191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="H191" s="1" t="n">
-        <v>0.2606</v>
+      <c r="I191" s="1" t="n">
+        <v>0.2604</v>
       </c>
     </row>
     <row r="192">
@@ -5813,9 +6389,12 @@
         <v>0.03943</v>
       </c>
       <c r="G192" s="1" t="n">
+        <v>0.03969</v>
+      </c>
+      <c r="H192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="H192" s="1" t="n">
+      <c r="I192" s="1" t="n">
         <v>0.03914</v>
       </c>
     </row>
@@ -5841,9 +6420,12 @@
         <v>0.000223</v>
       </c>
       <c r="G193" s="1" t="n">
-        <v>0.000223</v>
+        <v>0.0002232</v>
       </c>
       <c r="H193" s="1" t="n">
+        <v>0.0002232</v>
+      </c>
+      <c r="I193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -5869,9 +6451,12 @@
         <v>4.164</v>
       </c>
       <c r="G194" s="1" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="H194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="H194" s="1" t="n">
+      <c r="I194" s="1" t="n">
         <v>4.154</v>
       </c>
     </row>
@@ -5900,6 +6485,9 @@
         <v>0.999341</v>
       </c>
       <c r="H195" s="1" t="n">
+        <v>0.999341</v>
+      </c>
+      <c r="I195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -5925,9 +6513,12 @@
         <v>4.324</v>
       </c>
       <c r="G196" s="1" t="n">
+        <v>4.327</v>
+      </c>
+      <c r="H196" s="1" t="n">
         <v>4.347</v>
       </c>
-      <c r="H196" s="1" t="n">
+      <c r="I196" s="1" t="n">
         <v>4.302</v>
       </c>
     </row>
@@ -5953,9 +6544,12 @@
         <v>0.15048</v>
       </c>
       <c r="G197" s="1" t="n">
-        <v>0.15048</v>
+        <v>0.15105</v>
       </c>
       <c r="H197" s="1" t="n">
+        <v>0.15105</v>
+      </c>
+      <c r="I197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -5981,9 +6575,12 @@
         <v>0.007661</v>
       </c>
       <c r="G198" s="1" t="n">
-        <v>0.007661</v>
+        <v>0.0077</v>
       </c>
       <c r="H198" s="1" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="I198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -6009,9 +6606,12 @@
         <v>0.4528</v>
       </c>
       <c r="G199" s="1" t="n">
-        <v>0.4528</v>
+        <v>0.4533</v>
       </c>
       <c r="H199" s="1" t="n">
+        <v>0.4533</v>
+      </c>
+      <c r="I199" s="1" t="n">
         <v>0.4483</v>
       </c>
     </row>
@@ -6040,6 +6640,9 @@
         <v>0.5857</v>
       </c>
       <c r="H200" s="1" t="n">
+        <v>0.5857</v>
+      </c>
+      <c r="I200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -6065,9 +6668,12 @@
         <v>0.09429999999999999</v>
       </c>
       <c r="G201" s="1" t="n">
+        <v>0.0941</v>
+      </c>
+      <c r="H201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="H201" s="1" t="n">
+      <c r="I201" s="1" t="n">
         <v>0.09379999999999999</v>
       </c>
     </row>
@@ -6093,9 +6699,12 @@
         <v>0.0612</v>
       </c>
       <c r="G202" s="1" t="n">
+        <v>0.06103</v>
+      </c>
+      <c r="H202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="H202" s="1" t="n">
+      <c r="I202" s="1" t="n">
         <v>0.06063</v>
       </c>
     </row>
@@ -6121,10 +6730,13 @@
         <v>0.008619999999999999</v>
       </c>
       <c r="G203" s="1" t="n">
+        <v>0.00821</v>
+      </c>
+      <c r="H203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="H203" s="1" t="n">
-        <v>0.008359999999999999</v>
+      <c r="I203" s="1" t="n">
+        <v>0.00821</v>
       </c>
     </row>
     <row r="204">
@@ -6149,9 +6761,12 @@
         <v>0.00422</v>
       </c>
       <c r="G204" s="1" t="n">
+        <v>0.00421</v>
+      </c>
+      <c r="H204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="H204" s="1" t="n">
+      <c r="I204" s="1" t="n">
         <v>0.00421</v>
       </c>
     </row>
@@ -6177,9 +6792,12 @@
         <v>0.009154000000000001</v>
       </c>
       <c r="G205" s="1" t="n">
+        <v>0.009284000000000001</v>
+      </c>
+      <c r="H205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="H205" s="1" t="n">
+      <c r="I205" s="1" t="n">
         <v>0.009154000000000001</v>
       </c>
     </row>
@@ -6205,9 +6823,12 @@
         <v>0.2391</v>
       </c>
       <c r="G206" s="1" t="n">
+        <v>0.2384</v>
+      </c>
+      <c r="H206" s="1" t="n">
         <v>0.2399</v>
       </c>
-      <c r="H206" s="1" t="n">
+      <c r="I206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -6233,10 +6854,13 @@
         <v>0.02133</v>
       </c>
       <c r="G207" s="1" t="n">
+        <v>0.02112</v>
+      </c>
+      <c r="H207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="H207" s="1" t="n">
-        <v>0.02128</v>
+      <c r="I207" s="1" t="n">
+        <v>0.02112</v>
       </c>
     </row>
     <row r="208">
@@ -6261,9 +6885,12 @@
         <v>0.2379</v>
       </c>
       <c r="G208" s="1" t="n">
+        <v>0.2387</v>
+      </c>
+      <c r="H208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="H208" s="1" t="n">
+      <c r="I208" s="1" t="n">
         <v>0.2366</v>
       </c>
     </row>
@@ -6289,9 +6916,12 @@
         <v>0.3613</v>
       </c>
       <c r="G209" s="1" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="H209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="H209" s="1" t="n">
+      <c r="I209" s="1" t="n">
         <v>0.3613</v>
       </c>
     </row>
@@ -6317,9 +6947,12 @@
         <v>0.04307</v>
       </c>
       <c r="G210" s="1" t="n">
+        <v>0.04308</v>
+      </c>
+      <c r="H210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="H210" s="1" t="n">
+      <c r="I210" s="1" t="n">
         <v>0.04286</v>
       </c>
     </row>
@@ -6345,9 +6978,12 @@
         <v>0.0004318</v>
       </c>
       <c r="G211" s="1" t="n">
-        <v>0.0004327</v>
+        <v>0.0004329</v>
       </c>
       <c r="H211" s="1" t="n">
+        <v>0.0004329</v>
+      </c>
+      <c r="I211" s="1" t="n">
         <v>0.0004282</v>
       </c>
     </row>
@@ -6373,9 +7009,12 @@
         <v>0.02173</v>
       </c>
       <c r="G212" s="1" t="n">
-        <v>0.02177</v>
+        <v>0.02179</v>
       </c>
       <c r="H212" s="1" t="n">
+        <v>0.02179</v>
+      </c>
+      <c r="I212" s="1" t="n">
         <v>0.0216</v>
       </c>
     </row>
@@ -6401,9 +7040,12 @@
         <v>0.1154</v>
       </c>
       <c r="G213" s="1" t="n">
+        <v>0.1154</v>
+      </c>
+      <c r="H213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="H213" s="1" t="n">
+      <c r="I213" s="1" t="n">
         <v>0.1151</v>
       </c>
     </row>
@@ -6429,9 +7071,12 @@
         <v>0.042</v>
       </c>
       <c r="G214" s="1" t="n">
+        <v>0.04202</v>
+      </c>
+      <c r="H214" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="H214" s="1" t="n">
+      <c r="I214" s="1" t="n">
         <v>0.04188</v>
       </c>
     </row>
@@ -6457,9 +7102,12 @@
         <v>0.010016</v>
       </c>
       <c r="G215" s="1" t="n">
+        <v>0.010043</v>
+      </c>
+      <c r="H215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="H215" s="1" t="n">
+      <c r="I215" s="1" t="n">
         <v>0.009896</v>
       </c>
     </row>
@@ -6485,9 +7133,12 @@
         <v>0.0644</v>
       </c>
       <c r="G216" s="1" t="n">
-        <v>0.0644</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="H216" s="1" t="n">
+        <v>0.06469999999999999</v>
+      </c>
+      <c r="I216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -6513,9 +7164,12 @@
         <v>0.004211</v>
       </c>
       <c r="G217" s="1" t="n">
-        <v>0.004216</v>
+        <v>0.004231</v>
       </c>
       <c r="H217" s="1" t="n">
+        <v>0.004231</v>
+      </c>
+      <c r="I217" s="1" t="n">
         <v>0.004177</v>
       </c>
     </row>
@@ -6541,10 +7195,13 @@
         <v>0.01049</v>
       </c>
       <c r="G218" s="1" t="n">
+        <v>0.01024</v>
+      </c>
+      <c r="H218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="H218" s="1" t="n">
-        <v>0.01049</v>
+      <c r="I218" s="1" t="n">
+        <v>0.01024</v>
       </c>
     </row>
     <row r="219">
@@ -6569,10 +7226,13 @@
         <v>0.0303</v>
       </c>
       <c r="G219" s="1" t="n">
+        <v>0.02958</v>
+      </c>
+      <c r="H219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="H219" s="1" t="n">
-        <v>0.0303</v>
+      <c r="I219" s="1" t="n">
+        <v>0.02958</v>
       </c>
     </row>
     <row r="220">
@@ -6597,9 +7257,12 @@
         <v>2.31</v>
       </c>
       <c r="G220" s="1" t="n">
+        <v>2.312</v>
+      </c>
+      <c r="H220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="H220" s="1" t="n">
+      <c r="I220" s="1" t="n">
         <v>2.296</v>
       </c>
     </row>
@@ -6625,9 +7288,12 @@
         <v>0.023132</v>
       </c>
       <c r="G221" s="1" t="n">
+        <v>0.023038</v>
+      </c>
+      <c r="H221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="H221" s="1" t="n">
+      <c r="I221" s="1" t="n">
         <v>0.023027</v>
       </c>
     </row>
@@ -6656,6 +7322,9 @@
         <v>0.0372</v>
       </c>
       <c r="H222" s="1" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="I222" s="1" t="n">
         <v>0.037</v>
       </c>
     </row>
@@ -6681,9 +7350,12 @@
         <v>0.2944</v>
       </c>
       <c r="G223" s="1" t="n">
+        <v>0.2945</v>
+      </c>
+      <c r="H223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="H223" s="1" t="n">
+      <c r="I223" s="1" t="n">
         <v>0.294</v>
       </c>
     </row>
@@ -6709,9 +7381,12 @@
         <v>0.01577</v>
       </c>
       <c r="G224" s="1" t="n">
-        <v>0.01577</v>
+        <v>0.01582</v>
       </c>
       <c r="H224" s="1" t="n">
+        <v>0.01582</v>
+      </c>
+      <c r="I224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -6737,9 +7412,12 @@
         <v>0.0004141</v>
       </c>
       <c r="G225" s="1" t="n">
+        <v>0.0004136</v>
+      </c>
+      <c r="H225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="H225" s="1" t="n">
+      <c r="I225" s="1" t="n">
         <v>0.0004112</v>
       </c>
     </row>
@@ -6765,9 +7443,12 @@
         <v>0.08806</v>
       </c>
       <c r="G226" s="1" t="n">
-        <v>0.0881</v>
+        <v>0.08815000000000001</v>
       </c>
       <c r="H226" s="1" t="n">
+        <v>0.08815000000000001</v>
+      </c>
+      <c r="I226" s="1" t="n">
         <v>0.08731999999999999</v>
       </c>
     </row>
@@ -6793,9 +7474,12 @@
         <v>0.955</v>
       </c>
       <c r="G227" s="1" t="n">
-        <v>0.956</v>
+        <v>0.959</v>
       </c>
       <c r="H227" s="1" t="n">
+        <v>0.959</v>
+      </c>
+      <c r="I227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -6821,9 +7505,12 @@
         <v>0.05634</v>
       </c>
       <c r="G228" s="1" t="n">
+        <v>0.05622</v>
+      </c>
+      <c r="H228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="H228" s="1" t="n">
+      <c r="I228" s="1" t="n">
         <v>0.0558</v>
       </c>
     </row>
@@ -6849,9 +7536,12 @@
         <v>0.002027</v>
       </c>
       <c r="G229" s="1" t="n">
+        <v>0.002032</v>
+      </c>
+      <c r="H229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="H229" s="1" t="n">
+      <c r="I229" s="1" t="n">
         <v>0.002017</v>
       </c>
     </row>
@@ -6880,6 +7570,9 @@
         <v>0.022893</v>
       </c>
       <c r="H230" s="1" t="n">
+        <v>0.022893</v>
+      </c>
+      <c r="I230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -6905,10 +7598,13 @@
         <v>0.05459</v>
       </c>
       <c r="G231" s="1" t="n">
+        <v>0.05442</v>
+      </c>
+      <c r="H231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="H231" s="1" t="n">
-        <v>0.05459</v>
+      <c r="I231" s="1" t="n">
+        <v>0.05442</v>
       </c>
     </row>
     <row r="232">
@@ -6933,9 +7629,12 @@
         <v>0.0595</v>
       </c>
       <c r="G232" s="1" t="n">
+        <v>0.0596</v>
+      </c>
+      <c r="H232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="H232" s="1" t="n">
+      <c r="I232" s="1" t="n">
         <v>0.0591</v>
       </c>
     </row>
@@ -6961,9 +7660,12 @@
         <v>0.001697</v>
       </c>
       <c r="G233" s="1" t="n">
+        <v>0.001698</v>
+      </c>
+      <c r="H233" s="1" t="n">
         <v>0.001701</v>
       </c>
-      <c r="H233" s="1" t="n">
+      <c r="I233" s="1" t="n">
         <v>0.001678</v>
       </c>
     </row>
@@ -6989,9 +7691,12 @@
         <v>0.005836</v>
       </c>
       <c r="G234" s="1" t="n">
-        <v>0.005837</v>
+        <v>0.005854</v>
       </c>
       <c r="H234" s="1" t="n">
+        <v>0.005854</v>
+      </c>
+      <c r="I234" s="1" t="n">
         <v>0.005784</v>
       </c>
     </row>
@@ -7017,9 +7722,12 @@
         <v>0.12599</v>
       </c>
       <c r="G235" s="1" t="n">
+        <v>0.12578</v>
+      </c>
+      <c r="H235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="H235" s="1" t="n">
+      <c r="I235" s="1" t="n">
         <v>0.12453</v>
       </c>
     </row>
@@ -7045,9 +7753,12 @@
         <v>65.09999999999999</v>
       </c>
       <c r="G236" s="1" t="n">
+        <v>65.15000000000001</v>
+      </c>
+      <c r="H236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="H236" s="1" t="n">
+      <c r="I236" s="1" t="n">
         <v>64.78</v>
       </c>
     </row>
@@ -7073,9 +7784,12 @@
         <v>0.1026</v>
       </c>
       <c r="G237" s="1" t="n">
+        <v>0.1028</v>
+      </c>
+      <c r="H237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="H237" s="1" t="n">
+      <c r="I237" s="1" t="n">
         <v>0.1021</v>
       </c>
     </row>
@@ -7101,9 +7815,12 @@
         <v>0.00399</v>
       </c>
       <c r="G238" s="1" t="n">
-        <v>0.00399</v>
+        <v>0.003993</v>
       </c>
       <c r="H238" s="1" t="n">
+        <v>0.003993</v>
+      </c>
+      <c r="I238" s="1" t="n">
         <v>0.003925</v>
       </c>
     </row>
@@ -7129,9 +7846,12 @@
         <v>0.01556</v>
       </c>
       <c r="G239" s="1" t="n">
-        <v>0.01556</v>
+        <v>0.01562</v>
       </c>
       <c r="H239" s="1" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="I239" s="1" t="n">
         <v>0.01532</v>
       </c>
     </row>
@@ -7157,9 +7877,12 @@
         <v>0.05661</v>
       </c>
       <c r="G240" s="1" t="n">
-        <v>0.05673</v>
+        <v>0.0568</v>
       </c>
       <c r="H240" s="1" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="I240" s="1" t="n">
         <v>0.05621</v>
       </c>
     </row>
@@ -7185,9 +7908,12 @@
         <v>0.0116</v>
       </c>
       <c r="G241" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="H241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="H241" s="1" t="n">
+      <c r="I241" s="1" t="n">
         <v>0.0114</v>
       </c>
     </row>
@@ -7216,6 +7942,9 @@
         <v>0.3388</v>
       </c>
       <c r="H242" s="1" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="I242" s="1" t="n">
         <v>0.336</v>
       </c>
     </row>
@@ -7241,9 +7970,12 @@
         <v>0.01246</v>
       </c>
       <c r="G243" s="1" t="n">
+        <v>0.01242</v>
+      </c>
+      <c r="H243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="H243" s="1" t="n">
+      <c r="I243" s="1" t="n">
         <v>0.01241</v>
       </c>
     </row>
@@ -7269,9 +8001,12 @@
         <v>0.08032</v>
       </c>
       <c r="G244" s="1" t="n">
-        <v>0.08051999999999999</v>
+        <v>0.08067000000000001</v>
       </c>
       <c r="H244" s="1" t="n">
+        <v>0.08067000000000001</v>
+      </c>
+      <c r="I244" s="1" t="n">
         <v>0.07997</v>
       </c>
     </row>
@@ -7297,9 +8032,12 @@
         <v>0.007967999999999999</v>
       </c>
       <c r="G245" s="1" t="n">
+        <v>0.007969</v>
+      </c>
+      <c r="H245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="H245" s="1" t="n">
+      <c r="I245" s="1" t="n">
         <v>0.007967999999999999</v>
       </c>
     </row>
@@ -7325,9 +8063,12 @@
         <v>0.03065</v>
       </c>
       <c r="G246" s="1" t="n">
+        <v>0.03067</v>
+      </c>
+      <c r="H246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="H246" s="1" t="n">
+      <c r="I246" s="1" t="n">
         <v>0.03056</v>
       </c>
     </row>
@@ -7353,9 +8094,12 @@
         <v>0.1826</v>
       </c>
       <c r="G247" s="1" t="n">
-        <v>0.1826</v>
+        <v>0.1827</v>
       </c>
       <c r="H247" s="1" t="n">
+        <v>0.1827</v>
+      </c>
+      <c r="I247" s="1" t="n">
         <v>0.1808</v>
       </c>
     </row>
@@ -7381,9 +8125,12 @@
         <v>0.05952</v>
       </c>
       <c r="G248" s="1" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="H248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="H248" s="1" t="n">
+      <c r="I248" s="1" t="n">
         <v>0.05915</v>
       </c>
     </row>
@@ -7409,9 +8156,12 @@
         <v>0.1683</v>
       </c>
       <c r="G249" s="1" t="n">
-        <v>0.1683</v>
+        <v>0.1684</v>
       </c>
       <c r="H249" s="1" t="n">
+        <v>0.1684</v>
+      </c>
+      <c r="I249" s="1" t="n">
         <v>0.1664</v>
       </c>
     </row>
@@ -7437,9 +8187,12 @@
         <v>0.01944</v>
       </c>
       <c r="G250" s="1" t="n">
+        <v>0.01945</v>
+      </c>
+      <c r="H250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="H250" s="1" t="n">
+      <c r="I250" s="1" t="n">
         <v>0.01938</v>
       </c>
     </row>
@@ -7465,9 +8218,12 @@
         <v>0.02311</v>
       </c>
       <c r="G251" s="1" t="n">
+        <v>0.02304</v>
+      </c>
+      <c r="H251" s="1" t="n">
         <v>0.02318</v>
       </c>
-      <c r="H251" s="1" t="n">
+      <c r="I251" s="1" t="n">
         <v>0.02304</v>
       </c>
     </row>
@@ -7493,9 +8249,12 @@
         <v>0.30577</v>
       </c>
       <c r="G252" s="1" t="n">
-        <v>0.30577</v>
+        <v>0.31227</v>
       </c>
       <c r="H252" s="1" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="I252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -7521,9 +8280,12 @@
         <v>0.006063</v>
       </c>
       <c r="G253" s="1" t="n">
+        <v>0.006083</v>
+      </c>
+      <c r="H253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="H253" s="1" t="n">
+      <c r="I253" s="1" t="n">
         <v>0.006063</v>
       </c>
     </row>
@@ -7549,9 +8311,12 @@
         <v>0.6185</v>
       </c>
       <c r="G254" s="1" t="n">
+        <v>0.6186</v>
+      </c>
+      <c r="H254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="H254" s="1" t="n">
+      <c r="I254" s="1" t="n">
         <v>0.6141</v>
       </c>
     </row>
@@ -7577,9 +8342,12 @@
         <v>0.10726</v>
       </c>
       <c r="G255" s="1" t="n">
+        <v>0.10751</v>
+      </c>
+      <c r="H255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="H255" s="1" t="n">
+      <c r="I255" s="1" t="n">
         <v>0.10726</v>
       </c>
     </row>
@@ -7605,9 +8373,12 @@
         <v>0.0907</v>
       </c>
       <c r="G256" s="1" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="H256" s="1" t="n">
         <v>0.0911</v>
       </c>
-      <c r="H256" s="1" t="n">
+      <c r="I256" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -7633,9 +8404,12 @@
         <v>0.01446</v>
       </c>
       <c r="G257" s="1" t="n">
+        <v>0.01451</v>
+      </c>
+      <c r="H257" s="1" t="n">
         <v>0.01454</v>
       </c>
-      <c r="H257" s="1" t="n">
+      <c r="I257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -7661,9 +8435,12 @@
         <v>0.05145</v>
       </c>
       <c r="G258" s="1" t="n">
+        <v>0.05131</v>
+      </c>
+      <c r="H258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="H258" s="1" t="n">
+      <c r="I258" s="1" t="n">
         <v>0.0511</v>
       </c>
     </row>
@@ -7689,9 +8466,12 @@
         <v>0.00827</v>
       </c>
       <c r="G259" s="1" t="n">
+        <v>0.008279999999999999</v>
+      </c>
+      <c r="H259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="H259" s="1" t="n">
+      <c r="I259" s="1" t="n">
         <v>0.008240000000000001</v>
       </c>
     </row>
@@ -7717,9 +8497,12 @@
         <v>0.1915</v>
       </c>
       <c r="G260" s="1" t="n">
+        <v>0.1914</v>
+      </c>
+      <c r="H260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="H260" s="1" t="n">
+      <c r="I260" s="1" t="n">
         <v>0.1902</v>
       </c>
     </row>
@@ -7745,9 +8528,12 @@
         <v>0.0989</v>
       </c>
       <c r="G261" s="1" t="n">
+        <v>0.0992</v>
+      </c>
+      <c r="H261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="H261" s="1" t="n">
+      <c r="I261" s="1" t="n">
         <v>0.09859999999999999</v>
       </c>
     </row>
@@ -7773,9 +8559,12 @@
         <v>0.2144</v>
       </c>
       <c r="G262" s="1" t="n">
+        <v>0.2142</v>
+      </c>
+      <c r="H262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="H262" s="1" t="n">
+      <c r="I262" s="1" t="n">
         <v>0.2128</v>
       </c>
     </row>
@@ -7801,9 +8590,12 @@
         <v>0.008510999999999999</v>
       </c>
       <c r="G263" s="1" t="n">
-        <v>0.008510999999999999</v>
+        <v>0.008522999999999999</v>
       </c>
       <c r="H263" s="1" t="n">
+        <v>0.008522999999999999</v>
+      </c>
+      <c r="I263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -7829,9 +8621,12 @@
         <v>2.652</v>
       </c>
       <c r="G264" s="1" t="n">
-        <v>2.658</v>
+        <v>2.659</v>
       </c>
       <c r="H264" s="1" t="n">
+        <v>2.659</v>
+      </c>
+      <c r="I264" s="1" t="n">
         <v>2.647</v>
       </c>
     </row>
@@ -7857,9 +8652,12 @@
         <v>0.01877</v>
       </c>
       <c r="G265" s="1" t="n">
+        <v>0.01878</v>
+      </c>
+      <c r="H265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="H265" s="1" t="n">
+      <c r="I265" s="1" t="n">
         <v>0.01847</v>
       </c>
     </row>
@@ -7885,9 +8683,12 @@
         <v>0.359</v>
       </c>
       <c r="G266" s="1" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="H266" s="1" t="n">
         <v>0.3604</v>
       </c>
-      <c r="H266" s="1" t="n">
+      <c r="I266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -7913,9 +8714,12 @@
         <v>0.03441</v>
       </c>
       <c r="G267" s="1" t="n">
+        <v>0.0346</v>
+      </c>
+      <c r="H267" s="1" t="n">
         <v>0.03464</v>
       </c>
-      <c r="H267" s="1" t="n">
+      <c r="I267" s="1" t="n">
         <v>0.03429</v>
       </c>
     </row>
@@ -7941,9 +8745,12 @@
         <v>0.12</v>
       </c>
       <c r="G268" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H268" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="H268" s="1" t="n">
+      <c r="I268" s="1" t="n">
         <v>0.119</v>
       </c>
     </row>
@@ -7969,9 +8776,12 @@
         <v>0.08082</v>
       </c>
       <c r="G269" s="1" t="n">
+        <v>0.08091</v>
+      </c>
+      <c r="H269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="H269" s="1" t="n">
+      <c r="I269" s="1" t="n">
         <v>0.08053</v>
       </c>
     </row>
@@ -7997,9 +8807,12 @@
         <v>0.01397</v>
       </c>
       <c r="G270" s="1" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="H270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="H270" s="1" t="n">
+      <c r="I270" s="1" t="n">
         <v>0.01397</v>
       </c>
     </row>
@@ -8025,9 +8838,12 @@
         <v>0.007681</v>
       </c>
       <c r="G271" s="1" t="n">
+        <v>0.007685</v>
+      </c>
+      <c r="H271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="H271" s="1" t="n">
+      <c r="I271" s="1" t="n">
         <v>0.007654</v>
       </c>
     </row>
@@ -8053,9 +8869,12 @@
         <v>0.07414</v>
       </c>
       <c r="G272" s="1" t="n">
+        <v>0.07428</v>
+      </c>
+      <c r="H272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="H272" s="1" t="n">
+      <c r="I272" s="1" t="n">
         <v>0.07414</v>
       </c>
     </row>
@@ -8081,9 +8900,12 @@
         <v>3.16e-05</v>
       </c>
       <c r="G273" s="1" t="n">
+        <v>3.15e-05</v>
+      </c>
+      <c r="H273" s="1" t="n">
         <v>3.16e-05</v>
       </c>
-      <c r="H273" s="1" t="n">
+      <c r="I273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -8109,10 +8931,13 @@
         <v>0.005556</v>
       </c>
       <c r="G274" s="1" t="n">
+        <v>0.005553</v>
+      </c>
+      <c r="H274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="H274" s="1" t="n">
-        <v>0.005556</v>
+      <c r="I274" s="1" t="n">
+        <v>0.005553</v>
       </c>
     </row>
     <row r="275">
@@ -8137,9 +8962,12 @@
         <v>0.181</v>
       </c>
       <c r="G275" s="1" t="n">
-        <v>0.1817</v>
+        <v>0.1821</v>
       </c>
       <c r="H275" s="1" t="n">
+        <v>0.1821</v>
+      </c>
+      <c r="I275" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -8165,9 +8993,12 @@
         <v>0.006917</v>
       </c>
       <c r="G276" s="1" t="n">
+        <v>0.006922</v>
+      </c>
+      <c r="H276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="H276" s="1" t="n">
+      <c r="I276" s="1" t="n">
         <v>0.006876</v>
       </c>
     </row>
@@ -8193,9 +9024,12 @@
         <v>0.1321</v>
       </c>
       <c r="G277" s="1" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="H277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="H277" s="1" t="n">
+      <c r="I277" s="1" t="n">
         <v>0.1316</v>
       </c>
     </row>
@@ -8221,9 +9055,12 @@
         <v>0.02343</v>
       </c>
       <c r="G278" s="1" t="n">
+        <v>0.02344</v>
+      </c>
+      <c r="H278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="H278" s="1" t="n">
+      <c r="I278" s="1" t="n">
         <v>0.02335</v>
       </c>
     </row>
@@ -8252,6 +9089,9 @@
         <v>0.01827</v>
       </c>
       <c r="H279" s="1" t="n">
+        <v>0.01827</v>
+      </c>
+      <c r="I279" s="1" t="n">
         <v>0.01817</v>
       </c>
     </row>
@@ -8277,9 +9117,12 @@
         <v>0.03772</v>
       </c>
       <c r="G280" s="1" t="n">
+        <v>0.03783</v>
+      </c>
+      <c r="H280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="H280" s="1" t="n">
+      <c r="I280" s="1" t="n">
         <v>0.03755</v>
       </c>
     </row>
@@ -8305,9 +9148,12 @@
         <v>0.04005</v>
       </c>
       <c r="G281" s="1" t="n">
+        <v>0.04005</v>
+      </c>
+      <c r="H281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="H281" s="1" t="n">
+      <c r="I281" s="1" t="n">
         <v>0.03981</v>
       </c>
     </row>
@@ -8333,9 +9179,12 @@
         <v>0.3051</v>
       </c>
       <c r="G282" s="1" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="H282" s="1" t="n">
         <v>0.3059</v>
       </c>
-      <c r="H282" s="1" t="n">
+      <c r="I282" s="1" t="n">
         <v>0.3025</v>
       </c>
     </row>
@@ -8361,9 +9210,12 @@
         <v>0.0113</v>
       </c>
       <c r="G283" s="1" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="H283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="H283" s="1" t="n">
+      <c r="I283" s="1" t="n">
         <v>0.01124</v>
       </c>
     </row>
@@ -8392,6 +9244,9 @@
         <v>9.7e-06</v>
       </c>
       <c r="H284" s="1" t="n">
+        <v>9.7e-06</v>
+      </c>
+      <c r="I284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -8417,9 +9272,12 @@
         <v>0.1155</v>
       </c>
       <c r="G285" s="1" t="n">
+        <v>0.1157</v>
+      </c>
+      <c r="H285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="H285" s="1" t="n">
+      <c r="I285" s="1" t="n">
         <v>0.1153</v>
       </c>
     </row>
@@ -8445,9 +9303,12 @@
         <v>0.003465</v>
       </c>
       <c r="G286" s="1" t="n">
-        <v>0.003466</v>
+        <v>0.003485</v>
       </c>
       <c r="H286" s="1" t="n">
+        <v>0.003485</v>
+      </c>
+      <c r="I286" s="1" t="n">
         <v>0.003442</v>
       </c>
     </row>
@@ -8473,9 +9334,12 @@
         <v>0.08573</v>
       </c>
       <c r="G287" s="1" t="n">
+        <v>0.08570999999999999</v>
+      </c>
+      <c r="H287" s="1" t="n">
         <v>0.08573</v>
       </c>
-      <c r="H287" s="1" t="n">
+      <c r="I287" s="1" t="n">
         <v>0.08545999999999999</v>
       </c>
     </row>
@@ -8501,9 +9365,12 @@
         <v>0.09969</v>
       </c>
       <c r="G288" s="1" t="n">
+        <v>0.09926</v>
+      </c>
+      <c r="H288" s="1" t="n">
         <v>0.1001</v>
       </c>
-      <c r="H288" s="1" t="n">
+      <c r="I288" s="1" t="n">
         <v>0.09889000000000001</v>
       </c>
     </row>
@@ -8529,9 +9396,12 @@
         <v>0.4334</v>
       </c>
       <c r="G289" s="1" t="n">
-        <v>0.434</v>
+        <v>0.4358</v>
       </c>
       <c r="H289" s="1" t="n">
+        <v>0.4358</v>
+      </c>
+      <c r="I289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -8557,9 +9427,12 @@
         <v>0.03955</v>
       </c>
       <c r="G290" s="1" t="n">
+        <v>0.03928</v>
+      </c>
+      <c r="H290" s="1" t="n">
         <v>0.03966</v>
       </c>
-      <c r="H290" s="1" t="n">
+      <c r="I290" s="1" t="n">
         <v>0.03921</v>
       </c>
     </row>
@@ -8585,10 +9458,13 @@
         <v>0.2435</v>
       </c>
       <c r="G291" s="1" t="n">
+        <v>0.2409</v>
+      </c>
+      <c r="H291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="H291" s="1" t="n">
-        <v>0.2416</v>
+      <c r="I291" s="1" t="n">
+        <v>0.2409</v>
       </c>
     </row>
     <row r="292">
@@ -8613,9 +9489,12 @@
         <v>0.2831</v>
       </c>
       <c r="G292" s="1" t="n">
+        <v>0.28296</v>
+      </c>
+      <c r="H292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="H292" s="1" t="n">
+      <c r="I292" s="1" t="n">
         <v>0.28275</v>
       </c>
     </row>
@@ -8641,9 +9520,12 @@
         <v>0.1504</v>
       </c>
       <c r="G293" s="1" t="n">
+        <v>0.1503</v>
+      </c>
+      <c r="H293" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="H293" s="1" t="n">
+      <c r="I293" s="1" t="n">
         <v>0.1498</v>
       </c>
     </row>
@@ -8669,9 +9551,12 @@
         <v>4.257</v>
       </c>
       <c r="G294" s="1" t="n">
+        <v>4.262</v>
+      </c>
+      <c r="H294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="H294" s="1" t="n">
+      <c r="I294" s="1" t="n">
         <v>4.238</v>
       </c>
     </row>
@@ -8697,9 +9582,12 @@
         <v>0.03292</v>
       </c>
       <c r="G295" s="1" t="n">
-        <v>0.03292</v>
+        <v>0.03318</v>
       </c>
       <c r="H295" s="1" t="n">
+        <v>0.03318</v>
+      </c>
+      <c r="I295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -8725,10 +9613,13 @@
         <v>0.0009909999999999999</v>
       </c>
       <c r="G296" s="1" t="n">
+        <v>0.0009790000000000001</v>
+      </c>
+      <c r="H296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="H296" s="1" t="n">
-        <v>0.00098</v>
+      <c r="I296" s="1" t="n">
+        <v>0.0009790000000000001</v>
       </c>
     </row>
     <row r="297">
@@ -8753,9 +9644,12 @@
         <v>0.08236</v>
       </c>
       <c r="G297" s="1" t="n">
+        <v>0.08244</v>
+      </c>
+      <c r="H297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="H297" s="1" t="n">
+      <c r="I297" s="1" t="n">
         <v>0.08209</v>
       </c>
     </row>
@@ -8781,9 +9675,12 @@
         <v>0.05806</v>
       </c>
       <c r="G298" s="1" t="n">
-        <v>0.05815</v>
+        <v>0.05821</v>
       </c>
       <c r="H298" s="1" t="n">
+        <v>0.05821</v>
+      </c>
+      <c r="I298" s="1" t="n">
         <v>0.05763</v>
       </c>
     </row>
@@ -8812,6 +9709,9 @@
         <v>0.0917</v>
       </c>
       <c r="H299" s="1" t="n">
+        <v>0.0917</v>
+      </c>
+      <c r="I299" s="1" t="n">
         <v>0.09066</v>
       </c>
     </row>
@@ -8837,9 +9737,12 @@
         <v>0.02771</v>
       </c>
       <c r="G300" s="1" t="n">
+        <v>0.02783</v>
+      </c>
+      <c r="H300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="H300" s="1" t="n">
+      <c r="I300" s="1" t="n">
         <v>0.02764</v>
       </c>
     </row>
@@ -8865,9 +9768,12 @@
         <v>0.06605999999999999</v>
       </c>
       <c r="G301" s="1" t="n">
+        <v>0.06612999999999999</v>
+      </c>
+      <c r="H301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="H301" s="1" t="n">
+      <c r="I301" s="1" t="n">
         <v>0.06603000000000001</v>
       </c>
     </row>
@@ -8893,9 +9799,12 @@
         <v>0.05232</v>
       </c>
       <c r="G302" s="1" t="n">
-        <v>0.052584</v>
+        <v>0.052828</v>
       </c>
       <c r="H302" s="1" t="n">
+        <v>0.052828</v>
+      </c>
+      <c r="I302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -8921,9 +9830,12 @@
         <v>5165.7</v>
       </c>
       <c r="G303" s="1" t="n">
-        <v>5172.3</v>
+        <v>5177.6</v>
       </c>
       <c r="H303" s="1" t="n">
+        <v>5177.6</v>
+      </c>
+      <c r="I303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -8949,9 +9861,12 @@
         <v>15.07</v>
       </c>
       <c r="G304" s="1" t="n">
-        <v>15.09</v>
+        <v>15.1</v>
       </c>
       <c r="H304" s="1" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="I304" s="1" t="n">
         <v>14.99</v>
       </c>
     </row>
@@ -8977,9 +9892,12 @@
         <v>0.003728</v>
       </c>
       <c r="G305" s="1" t="n">
+        <v>0.003737</v>
+      </c>
+      <c r="H305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="H305" s="1" t="n">
+      <c r="I305" s="1" t="n">
         <v>0.003722</v>
       </c>
     </row>
@@ -9005,9 +9923,12 @@
         <v>0.4596</v>
       </c>
       <c r="G306" s="1" t="n">
-        <v>0.4607</v>
+        <v>0.4608</v>
       </c>
       <c r="H306" s="1" t="n">
+        <v>0.4608</v>
+      </c>
+      <c r="I306" s="1" t="n">
         <v>0.4573</v>
       </c>
     </row>
@@ -9033,9 +9954,12 @@
         <v>0.04734</v>
       </c>
       <c r="G307" s="1" t="n">
+        <v>0.04734</v>
+      </c>
+      <c r="H307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="H307" s="1" t="n">
+      <c r="I307" s="1" t="n">
         <v>0.04732</v>
       </c>
     </row>
@@ -9061,9 +9985,12 @@
         <v>1.4891</v>
       </c>
       <c r="G308" s="1" t="n">
+        <v>1.4853</v>
+      </c>
+      <c r="H308" s="1" t="n">
         <v>1.4891</v>
       </c>
-      <c r="H308" s="1" t="n">
+      <c r="I308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -9089,9 +10016,12 @@
         <v>0.0008092</v>
       </c>
       <c r="G309" s="1" t="n">
+        <v>0.0008073000000000001</v>
+      </c>
+      <c r="H309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="H309" s="1" t="n">
+      <c r="I309" s="1" t="n">
         <v>0.0008068</v>
       </c>
     </row>
@@ -9117,9 +10047,12 @@
         <v>4.687</v>
       </c>
       <c r="G310" s="1" t="n">
+        <v>4.687</v>
+      </c>
+      <c r="H310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="H310" s="1" t="n">
+      <c r="I310" s="1" t="n">
         <v>4.687</v>
       </c>
     </row>
@@ -9145,9 +10078,12 @@
         <v>4.788</v>
       </c>
       <c r="G311" s="1" t="n">
+        <v>4.801</v>
+      </c>
+      <c r="H311" s="1" t="n">
         <v>4.805</v>
       </c>
-      <c r="H311" s="1" t="n">
+      <c r="I311" s="1" t="n">
         <v>4.765</v>
       </c>
     </row>
@@ -9173,9 +10109,12 @@
         <v>0.08126</v>
       </c>
       <c r="G312" s="1" t="n">
-        <v>0.08141</v>
+        <v>0.08212</v>
       </c>
       <c r="H312" s="1" t="n">
+        <v>0.08212</v>
+      </c>
+      <c r="I312" s="1" t="n">
         <v>0.08098</v>
       </c>
     </row>
@@ -9201,9 +10140,12 @@
         <v>2.039</v>
       </c>
       <c r="G313" s="1" t="n">
+        <v>2.041</v>
+      </c>
+      <c r="H313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="H313" s="1" t="n">
+      <c r="I313" s="1" t="n">
         <v>2.037</v>
       </c>
     </row>
@@ -9229,9 +10171,12 @@
         <v>0.07056999999999999</v>
       </c>
       <c r="G314" s="1" t="n">
-        <v>0.07056999999999999</v>
+        <v>0.07104000000000001</v>
       </c>
       <c r="H314" s="1" t="n">
+        <v>0.07104000000000001</v>
+      </c>
+      <c r="I314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -9257,9 +10202,12 @@
         <v>0.957</v>
       </c>
       <c r="G315" s="1" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="H315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="H315" s="1" t="n">
+      <c r="I315" s="1" t="n">
         <v>0.957</v>
       </c>
     </row>
@@ -9288,6 +10236,9 @@
         <v>0.1313</v>
       </c>
       <c r="H316" s="1" t="n">
+        <v>0.1313</v>
+      </c>
+      <c r="I316" s="1" t="n">
         <v>0.1305</v>
       </c>
     </row>
@@ -9313,9 +10264,12 @@
         <v>0.1839</v>
       </c>
       <c r="G317" s="1" t="n">
-        <v>0.1859</v>
+        <v>0.186</v>
       </c>
       <c r="H317" s="1" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="I317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -9341,9 +10295,12 @@
         <v>0.01634</v>
       </c>
       <c r="G318" s="1" t="n">
+        <v>0.01644</v>
+      </c>
+      <c r="H318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="H318" s="1" t="n">
+      <c r="I318" s="1" t="n">
         <v>0.01634</v>
       </c>
     </row>
@@ -9369,9 +10326,12 @@
         <v>0.08422</v>
       </c>
       <c r="G319" s="1" t="n">
+        <v>0.0843</v>
+      </c>
+      <c r="H319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="H319" s="1" t="n">
+      <c r="I319" s="1" t="n">
         <v>0.08395</v>
       </c>
     </row>
@@ -9397,9 +10357,12 @@
         <v>0.007655</v>
       </c>
       <c r="G320" s="1" t="n">
-        <v>0.007659</v>
+        <v>0.007667</v>
       </c>
       <c r="H320" s="1" t="n">
+        <v>0.007667</v>
+      </c>
+      <c r="I320" s="1" t="n">
         <v>0.007597</v>
       </c>
     </row>
@@ -9425,9 +10388,12 @@
         <v>0.05484</v>
       </c>
       <c r="G321" s="1" t="n">
+        <v>0.05501</v>
+      </c>
+      <c r="H321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="H321" s="1" t="n">
+      <c r="I321" s="1" t="n">
         <v>0.05452</v>
       </c>
     </row>
@@ -9453,9 +10419,12 @@
         <v>0.5501</v>
       </c>
       <c r="G322" s="1" t="n">
-        <v>0.5513</v>
+        <v>0.5514</v>
       </c>
       <c r="H322" s="1" t="n">
+        <v>0.5514</v>
+      </c>
+      <c r="I322" s="1" t="n">
         <v>0.5483</v>
       </c>
     </row>
@@ -9481,9 +10450,12 @@
         <v>0.07572</v>
       </c>
       <c r="G323" s="1" t="n">
-        <v>0.07593</v>
+        <v>0.07611999999999999</v>
       </c>
       <c r="H323" s="1" t="n">
+        <v>0.07611999999999999</v>
+      </c>
+      <c r="I323" s="1" t="n">
         <v>0.07525</v>
       </c>
     </row>
@@ -9509,9 +10481,12 @@
         <v>0.012833</v>
       </c>
       <c r="G324" s="1" t="n">
-        <v>0.012885</v>
+        <v>0.012933</v>
       </c>
       <c r="H324" s="1" t="n">
+        <v>0.012933</v>
+      </c>
+      <c r="I324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -9537,9 +10512,12 @@
         <v>0.0997</v>
       </c>
       <c r="G325" s="1" t="n">
+        <v>0.0997</v>
+      </c>
+      <c r="H325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="H325" s="1" t="n">
+      <c r="I325" s="1" t="n">
         <v>0.0993</v>
       </c>
     </row>
@@ -9568,6 +10546,9 @@
         <v>0.01765</v>
       </c>
       <c r="H326" s="1" t="n">
+        <v>0.01765</v>
+      </c>
+      <c r="I326" s="1" t="n">
         <v>0.01752</v>
       </c>
     </row>
@@ -9593,9 +10574,12 @@
         <v>0.06418</v>
       </c>
       <c r="G327" s="1" t="n">
+        <v>0.06432</v>
+      </c>
+      <c r="H327" s="1" t="n">
         <v>0.06435</v>
       </c>
-      <c r="H327" s="1" t="n">
+      <c r="I327" s="1" t="n">
         <v>0.06392</v>
       </c>
     </row>
@@ -9621,9 +10605,12 @@
         <v>0.2671</v>
       </c>
       <c r="G328" s="1" t="n">
+        <v>0.2673</v>
+      </c>
+      <c r="H328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="H328" s="1" t="n">
+      <c r="I328" s="1" t="n">
         <v>0.2671</v>
       </c>
     </row>
@@ -9649,9 +10636,12 @@
         <v>0.17196</v>
       </c>
       <c r="G329" s="1" t="n">
-        <v>0.17286</v>
+        <v>0.17297</v>
       </c>
       <c r="H329" s="1" t="n">
+        <v>0.17297</v>
+      </c>
+      <c r="I329" s="1" t="n">
         <v>0.17172</v>
       </c>
     </row>
@@ -9677,9 +10667,12 @@
         <v>2.071</v>
       </c>
       <c r="G330" s="1" t="n">
-        <v>2.072</v>
+        <v>2.088</v>
       </c>
       <c r="H330" s="1" t="n">
+        <v>2.088</v>
+      </c>
+      <c r="I330" s="1" t="n">
         <v>2.043</v>
       </c>
     </row>
@@ -9705,10 +10698,13 @@
         <v>0.0278</v>
       </c>
       <c r="G331" s="1" t="n">
+        <v>0.0277</v>
+      </c>
+      <c r="H331" s="1" t="n">
         <v>0.028</v>
       </c>
-      <c r="H331" s="1" t="n">
-        <v>0.0278</v>
+      <c r="I331" s="1" t="n">
+        <v>0.0277</v>
       </c>
     </row>
     <row r="332">
@@ -9733,9 +10729,12 @@
         <v>0.006004</v>
       </c>
       <c r="G332" s="1" t="n">
-        <v>0.00602</v>
+        <v>0.006031</v>
       </c>
       <c r="H332" s="1" t="n">
+        <v>0.006031</v>
+      </c>
+      <c r="I332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -9761,9 +10760,12 @@
         <v>0.003579</v>
       </c>
       <c r="G333" s="1" t="n">
+        <v>0.003578</v>
+      </c>
+      <c r="H333" s="1" t="n">
         <v>0.003579</v>
       </c>
-      <c r="H333" s="1" t="n">
+      <c r="I333" s="1" t="n">
         <v>0.003531</v>
       </c>
     </row>
@@ -9789,9 +10791,12 @@
         <v>0.01408</v>
       </c>
       <c r="G334" s="1" t="n">
+        <v>0.01408</v>
+      </c>
+      <c r="H334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="H334" s="1" t="n">
+      <c r="I334" s="1" t="n">
         <v>0.01399</v>
       </c>
     </row>
@@ -9817,9 +10822,12 @@
         <v>1.126</v>
       </c>
       <c r="G335" s="1" t="n">
-        <v>1.128</v>
+        <v>1.13</v>
       </c>
       <c r="H335" s="1" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="I335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -9845,9 +10853,12 @@
         <v>0.011305</v>
       </c>
       <c r="G336" s="1" t="n">
+        <v>0.011298</v>
+      </c>
+      <c r="H336" s="1" t="n">
         <v>0.011326</v>
       </c>
-      <c r="H336" s="1" t="n">
+      <c r="I336" s="1" t="n">
         <v>0.011253</v>
       </c>
     </row>
@@ -9873,9 +10884,12 @@
         <v>3.043</v>
       </c>
       <c r="G337" s="1" t="n">
+        <v>2.964</v>
+      </c>
+      <c r="H337" s="1" t="n">
         <v>3.043</v>
       </c>
-      <c r="H337" s="1" t="n">
+      <c r="I337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -9901,9 +10915,12 @@
         <v>0.01879</v>
       </c>
       <c r="G338" s="1" t="n">
-        <v>0.01884</v>
+        <v>0.01885</v>
       </c>
       <c r="H338" s="1" t="n">
+        <v>0.01885</v>
+      </c>
+      <c r="I338" s="1" t="n">
         <v>0.01861</v>
       </c>
     </row>
@@ -9929,9 +10946,12 @@
         <v>0.07766000000000001</v>
       </c>
       <c r="G339" s="1" t="n">
-        <v>0.07781</v>
+        <v>0.07790999999999999</v>
       </c>
       <c r="H339" s="1" t="n">
+        <v>0.07790999999999999</v>
+      </c>
+      <c r="I339" s="1" t="n">
         <v>0.07689</v>
       </c>
     </row>
@@ -9957,9 +10977,12 @@
         <v>0.076</v>
       </c>
       <c r="G340" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="H340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="H340" s="1" t="n">
+      <c r="I340" s="1" t="n">
         <v>0.076</v>
       </c>
     </row>
@@ -9985,9 +11008,12 @@
         <v>0.03638</v>
       </c>
       <c r="G341" s="1" t="n">
+        <v>0.03637</v>
+      </c>
+      <c r="H341" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="H341" s="1" t="n">
+      <c r="I341" s="1" t="n">
         <v>0.0362</v>
       </c>
     </row>
@@ -10013,9 +11039,12 @@
         <v>2643</v>
       </c>
       <c r="G342" s="1" t="n">
-        <v>2643</v>
+        <v>2647</v>
       </c>
       <c r="H342" s="1" t="n">
+        <v>2647</v>
+      </c>
+      <c r="I342" s="1" t="n">
         <v>2620</v>
       </c>
     </row>
@@ -10041,9 +11070,12 @@
         <v>0.000198</v>
       </c>
       <c r="G343" s="1" t="n">
+        <v>0.0001972</v>
+      </c>
+      <c r="H343" s="1" t="n">
         <v>0.000198</v>
       </c>
-      <c r="H343" s="1" t="n">
+      <c r="I343" s="1" t="n">
         <v>0.0001959</v>
       </c>
     </row>
@@ -10069,9 +11101,12 @@
         <v>0.08003</v>
       </c>
       <c r="G344" s="1" t="n">
+        <v>0.08008999999999999</v>
+      </c>
+      <c r="H344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="H344" s="1" t="n">
+      <c r="I344" s="1" t="n">
         <v>0.07987</v>
       </c>
     </row>
@@ -10097,9 +11132,12 @@
         <v>0.01656</v>
       </c>
       <c r="G345" s="1" t="n">
+        <v>0.01651</v>
+      </c>
+      <c r="H345" s="1" t="n">
         <v>0.01656</v>
       </c>
-      <c r="H345" s="1" t="n">
+      <c r="I345" s="1" t="n">
         <v>0.01632</v>
       </c>
     </row>
@@ -10125,9 +11163,12 @@
         <v>2.797</v>
       </c>
       <c r="G346" s="1" t="n">
-        <v>2.798</v>
+        <v>2.799</v>
       </c>
       <c r="H346" s="1" t="n">
+        <v>2.799</v>
+      </c>
+      <c r="I346" s="1" t="n">
         <v>2.773</v>
       </c>
     </row>
@@ -10153,9 +11194,12 @@
         <v>0.01645</v>
       </c>
       <c r="G347" s="1" t="n">
-        <v>0.01647</v>
+        <v>0.0165</v>
       </c>
       <c r="H347" s="1" t="n">
+        <v>0.0165</v>
+      </c>
+      <c r="I347" s="1" t="n">
         <v>0.01639</v>
       </c>
     </row>
@@ -10181,9 +11225,12 @@
         <v>0.0388</v>
       </c>
       <c r="G348" s="1" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="H348" s="1" t="n">
         <v>0.03897</v>
       </c>
-      <c r="H348" s="1" t="n">
+      <c r="I348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -10209,9 +11256,12 @@
         <v>0.3047</v>
       </c>
       <c r="G349" s="1" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="H349" s="1" t="n">
         <v>0.3065</v>
       </c>
-      <c r="H349" s="1" t="n">
+      <c r="I349" s="1" t="n">
         <v>0.3037</v>
       </c>
     </row>
@@ -10237,9 +11287,12 @@
         <v>0.005062</v>
       </c>
       <c r="G350" s="1" t="n">
+        <v>0.005081</v>
+      </c>
+      <c r="H350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="H350" s="1" t="n">
+      <c r="I350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -10265,9 +11318,12 @@
         <v>0.005128</v>
       </c>
       <c r="G351" s="1" t="n">
+        <v>0.005135</v>
+      </c>
+      <c r="H351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="H351" s="1" t="n">
+      <c r="I351" s="1" t="n">
         <v>0.00512</v>
       </c>
     </row>
@@ -10293,9 +11349,12 @@
         <v>0.004404</v>
       </c>
       <c r="G352" s="1" t="n">
-        <v>0.004413</v>
+        <v>0.004419</v>
       </c>
       <c r="H352" s="1" t="n">
+        <v>0.004419</v>
+      </c>
+      <c r="I352" s="1" t="n">
         <v>0.004387</v>
       </c>
     </row>
@@ -10321,9 +11380,12 @@
         <v>0.08171</v>
       </c>
       <c r="G353" s="1" t="n">
+        <v>0.08172</v>
+      </c>
+      <c r="H353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="H353" s="1" t="n">
+      <c r="I353" s="1" t="n">
         <v>0.08171</v>
       </c>
     </row>
@@ -10349,9 +11411,12 @@
         <v>1.308</v>
       </c>
       <c r="G354" s="1" t="n">
+        <v>1.307</v>
+      </c>
+      <c r="H354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="H354" s="1" t="n">
+      <c r="I354" s="1" t="n">
         <v>1.283</v>
       </c>
     </row>
@@ -10377,9 +11442,12 @@
         <v>7.766</v>
       </c>
       <c r="G355" s="1" t="n">
+        <v>7.774</v>
+      </c>
+      <c r="H355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="H355" s="1" t="n">
+      <c r="I355" s="1" t="n">
         <v>7.744</v>
       </c>
     </row>
@@ -10405,9 +11473,12 @@
         <v>0.007889999999999999</v>
       </c>
       <c r="G356" s="1" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="H356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="H356" s="1" t="n">
+      <c r="I356" s="1" t="n">
         <v>0.007849999999999999</v>
       </c>
     </row>
@@ -10433,9 +11504,12 @@
         <v>0.00573</v>
       </c>
       <c r="G357" s="1" t="n">
+        <v>0.005728</v>
+      </c>
+      <c r="H357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="H357" s="1" t="n">
+      <c r="I357" s="1" t="n">
         <v>0.005696</v>
       </c>
     </row>
@@ -10461,9 +11535,12 @@
         <v>0.01569</v>
       </c>
       <c r="G358" s="1" t="n">
+        <v>0.01574</v>
+      </c>
+      <c r="H358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="H358" s="1" t="n">
+      <c r="I358" s="1" t="n">
         <v>0.01567</v>
       </c>
     </row>
@@ -10489,9 +11566,12 @@
         <v>3.661</v>
       </c>
       <c r="G359" s="1" t="n">
+        <v>3.666</v>
+      </c>
+      <c r="H359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="H359" s="1" t="n">
+      <c r="I359" s="1" t="n">
         <v>3.65</v>
       </c>
     </row>
@@ -10517,9 +11597,12 @@
         <v>0.1507</v>
       </c>
       <c r="G360" s="1" t="n">
-        <v>0.1507</v>
+        <v>0.1515</v>
       </c>
       <c r="H360" s="1" t="n">
+        <v>0.1515</v>
+      </c>
+      <c r="I360" s="1" t="n">
         <v>0.1499</v>
       </c>
     </row>
@@ -10545,9 +11628,12 @@
         <v>0.07081999999999999</v>
       </c>
       <c r="G361" s="1" t="n">
-        <v>0.07093000000000001</v>
+        <v>0.07104000000000001</v>
       </c>
       <c r="H361" s="1" t="n">
+        <v>0.07104000000000001</v>
+      </c>
+      <c r="I361" s="1" t="n">
         <v>0.07069</v>
       </c>
     </row>
@@ -10573,9 +11659,12 @@
         <v>0.01792</v>
       </c>
       <c r="G362" s="1" t="n">
+        <v>0.01795</v>
+      </c>
+      <c r="H362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="H362" s="1" t="n">
+      <c r="I362" s="1" t="n">
         <v>0.01786</v>
       </c>
     </row>
@@ -10601,10 +11690,13 @@
         <v>0.02256</v>
       </c>
       <c r="G363" s="1" t="n">
+        <v>0.02254</v>
+      </c>
+      <c r="H363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="H363" s="1" t="n">
-        <v>0.02256</v>
+      <c r="I363" s="1" t="n">
+        <v>0.02254</v>
       </c>
     </row>
     <row r="364">
@@ -10629,10 +11721,13 @@
         <v>0.01272</v>
       </c>
       <c r="G364" s="1" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="H364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="H364" s="1" t="n">
-        <v>0.01271</v>
+      <c r="I364" s="1" t="n">
+        <v>0.0127</v>
       </c>
     </row>
     <row r="365">
@@ -10657,9 +11752,12 @@
         <v>0.0924</v>
       </c>
       <c r="G365" s="1" t="n">
-        <v>0.0925</v>
+        <v>0.0926</v>
       </c>
       <c r="H365" s="1" t="n">
+        <v>0.0926</v>
+      </c>
+      <c r="I365" s="1" t="n">
         <v>0.0919</v>
       </c>
     </row>
@@ -10685,9 +11783,12 @@
         <v>0.0425</v>
       </c>
       <c r="G366" s="1" t="n">
+        <v>0.04255</v>
+      </c>
+      <c r="H366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="H366" s="1" t="n">
+      <c r="I366" s="1" t="n">
         <v>0.04244</v>
       </c>
     </row>
@@ -10713,9 +11814,12 @@
         <v>0.0315</v>
       </c>
       <c r="G367" s="1" t="n">
+        <v>0.03157</v>
+      </c>
+      <c r="H367" s="1" t="n">
         <v>0.03164</v>
       </c>
-      <c r="H367" s="1" t="n">
+      <c r="I367" s="1" t="n">
         <v>0.03145</v>
       </c>
     </row>
@@ -10741,10 +11845,13 @@
         <v>0.02386</v>
       </c>
       <c r="G368" s="1" t="n">
+        <v>0.02358</v>
+      </c>
+      <c r="H368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="H368" s="1" t="n">
-        <v>0.0236</v>
+      <c r="I368" s="1" t="n">
+        <v>0.02358</v>
       </c>
     </row>
     <row r="369">
@@ -10769,9 +11876,12 @@
         <v>0.03124</v>
       </c>
       <c r="G369" s="1" t="n">
+        <v>0.03118</v>
+      </c>
+      <c r="H369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="H369" s="1" t="n">
+      <c r="I369" s="1" t="n">
         <v>0.03113</v>
       </c>
     </row>
@@ -10797,9 +11907,12 @@
         <v>0.07836</v>
       </c>
       <c r="G370" s="1" t="n">
-        <v>0.07836</v>
+        <v>0.07890999999999999</v>
       </c>
       <c r="H370" s="1" t="n">
+        <v>0.07890999999999999</v>
+      </c>
+      <c r="I370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -10825,9 +11938,12 @@
         <v>0.1088</v>
       </c>
       <c r="G371" s="1" t="n">
-        <v>0.1088</v>
+        <v>0.1089</v>
       </c>
       <c r="H371" s="1" t="n">
+        <v>0.1089</v>
+      </c>
+      <c r="I371" s="1" t="n">
         <v>0.1074</v>
       </c>
     </row>
@@ -10853,9 +11969,12 @@
         <v>0.007209</v>
       </c>
       <c r="G372" s="1" t="n">
+        <v>0.007156</v>
+      </c>
+      <c r="H372" s="1" t="n">
         <v>0.007209</v>
       </c>
-      <c r="H372" s="1" t="n">
+      <c r="I372" s="1" t="n">
         <v>0.007057</v>
       </c>
     </row>
@@ -10884,6 +12003,9 @@
         <v>0.09719999999999999</v>
       </c>
       <c r="H373" s="1" t="n">
+        <v>0.09719999999999999</v>
+      </c>
+      <c r="I373" s="1" t="n">
         <v>0.0965</v>
       </c>
     </row>
@@ -10912,6 +12034,9 @@
         <v>0.05881</v>
       </c>
       <c r="H374" s="1" t="n">
+        <v>0.05881</v>
+      </c>
+      <c r="I374" s="1" t="n">
         <v>0.0583</v>
       </c>
     </row>
@@ -10937,9 +12062,12 @@
         <v>0.323</v>
       </c>
       <c r="G375" s="1" t="n">
-        <v>0.3234</v>
+        <v>0.3238</v>
       </c>
       <c r="H375" s="1" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="I375" s="1" t="n">
         <v>0.3193</v>
       </c>
     </row>
@@ -10965,9 +12093,12 @@
         <v>0.01997</v>
       </c>
       <c r="G376" s="1" t="n">
+        <v>0.01994</v>
+      </c>
+      <c r="H376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="H376" s="1" t="n">
+      <c r="I376" s="1" t="n">
         <v>0.01988</v>
       </c>
     </row>
@@ -10993,9 +12124,12 @@
         <v>0.06902</v>
       </c>
       <c r="G377" s="1" t="n">
+        <v>0.06915</v>
+      </c>
+      <c r="H377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="H377" s="1" t="n">
+      <c r="I377" s="1" t="n">
         <v>0.06877</v>
       </c>
     </row>
@@ -11021,9 +12155,12 @@
         <v>0.15483</v>
       </c>
       <c r="G378" s="1" t="n">
+        <v>0.15493</v>
+      </c>
+      <c r="H378" s="1" t="n">
         <v>0.15583</v>
       </c>
-      <c r="H378" s="1" t="n">
+      <c r="I378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -11049,9 +12186,12 @@
         <v>0.0006047</v>
       </c>
       <c r="G379" s="1" t="n">
+        <v>0.0006057</v>
+      </c>
+      <c r="H379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="H379" s="1" t="n">
+      <c r="I379" s="1" t="n">
         <v>0.0006028</v>
       </c>
     </row>
@@ -11077,9 +12217,12 @@
         <v>0.01021</v>
       </c>
       <c r="G380" s="1" t="n">
-        <v>0.01021</v>
+        <v>0.01024</v>
       </c>
       <c r="H380" s="1" t="n">
+        <v>0.01024</v>
+      </c>
+      <c r="I380" s="1" t="n">
         <v>0.01016</v>
       </c>
     </row>
@@ -11105,9 +12248,12 @@
         <v>0.02569</v>
       </c>
       <c r="G381" s="1" t="n">
+        <v>0.02561</v>
+      </c>
+      <c r="H381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="H381" s="1" t="n">
+      <c r="I381" s="1" t="n">
         <v>0.02553</v>
       </c>
     </row>
@@ -11133,9 +12279,12 @@
         <v>0.19215</v>
       </c>
       <c r="G382" s="1" t="n">
+        <v>0.19193</v>
+      </c>
+      <c r="H382" s="1" t="n">
         <v>0.19263</v>
       </c>
-      <c r="H382" s="1" t="n">
+      <c r="I382" s="1" t="n">
         <v>0.18936</v>
       </c>
     </row>
@@ -11161,10 +12310,13 @@
         <v>0.09384000000000001</v>
       </c>
       <c r="G383" s="1" t="n">
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="H383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="H383" s="1" t="n">
-        <v>0.09372999999999999</v>
+      <c r="I383" s="1" t="n">
+        <v>0.09329999999999999</v>
       </c>
     </row>
     <row r="384">
@@ -11189,10 +12341,13 @@
         <v>0.03192</v>
       </c>
       <c r="G384" s="1" t="n">
+        <v>0.03182</v>
+      </c>
+      <c r="H384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="H384" s="1" t="n">
-        <v>0.03192</v>
+      <c r="I384" s="1" t="n">
+        <v>0.03182</v>
       </c>
     </row>
     <row r="385">
@@ -11217,9 +12372,12 @@
         <v>0.01122</v>
       </c>
       <c r="G385" s="1" t="n">
+        <v>0.01118</v>
+      </c>
+      <c r="H385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="H385" s="1" t="n">
+      <c r="I385" s="1" t="n">
         <v>0.01115</v>
       </c>
     </row>
@@ -11245,9 +12403,12 @@
         <v>0.05135</v>
       </c>
       <c r="G386" s="1" t="n">
-        <v>0.05135</v>
+        <v>0.05156</v>
       </c>
       <c r="H386" s="1" t="n">
+        <v>0.05156</v>
+      </c>
+      <c r="I386" s="1" t="n">
         <v>0.05087</v>
       </c>
     </row>
@@ -11273,9 +12434,12 @@
         <v>0.02512</v>
       </c>
       <c r="G387" s="1" t="n">
-        <v>0.02512</v>
+        <v>0.02524</v>
       </c>
       <c r="H387" s="1" t="n">
+        <v>0.02524</v>
+      </c>
+      <c r="I387" s="1" t="n">
         <v>0.02483</v>
       </c>
     </row>
@@ -11301,9 +12465,12 @@
         <v>0.007348</v>
       </c>
       <c r="G388" s="1" t="n">
+        <v>0.007355</v>
+      </c>
+      <c r="H388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="H388" s="1" t="n">
+      <c r="I388" s="1" t="n">
         <v>0.007344</v>
       </c>
     </row>
@@ -11329,9 +12496,12 @@
         <v>0.01021</v>
       </c>
       <c r="G389" s="1" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="H389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="H389" s="1" t="n">
+      <c r="I389" s="1" t="n">
         <v>0.01016</v>
       </c>
     </row>
@@ -11357,9 +12527,12 @@
         <v>0.08341999999999999</v>
       </c>
       <c r="G390" s="1" t="n">
-        <v>0.08369</v>
+        <v>0.0839</v>
       </c>
       <c r="H390" s="1" t="n">
+        <v>0.0839</v>
+      </c>
+      <c r="I390" s="1" t="n">
         <v>0.08304</v>
       </c>
     </row>
@@ -11388,6 +12561,9 @@
         <v>0.5061</v>
       </c>
       <c r="H391" s="1" t="n">
+        <v>0.5061</v>
+      </c>
+      <c r="I391" s="1" t="n">
         <v>0.5017</v>
       </c>
     </row>
@@ -11413,9 +12589,12 @@
         <v>0.1179</v>
       </c>
       <c r="G392" s="1" t="n">
+        <v>0.1179</v>
+      </c>
+      <c r="H392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="H392" s="1" t="n">
+      <c r="I392" s="1" t="n">
         <v>0.1171</v>
       </c>
     </row>
@@ -11441,9 +12620,12 @@
         <v>0.0025</v>
       </c>
       <c r="G393" s="1" t="n">
+        <v>0.00251</v>
+      </c>
+      <c r="H393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="H393" s="1" t="n">
+      <c r="I393" s="1" t="n">
         <v>0.0025</v>
       </c>
     </row>
@@ -11469,10 +12651,13 @@
         <v>0.02157</v>
       </c>
       <c r="G394" s="1" t="n">
+        <v>0.02135</v>
+      </c>
+      <c r="H394" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="H394" s="1" t="n">
-        <v>0.02146</v>
+      <c r="I394" s="1" t="n">
+        <v>0.02135</v>
       </c>
     </row>
     <row r="395">
@@ -11500,6 +12685,9 @@
         <v>0.0163</v>
       </c>
       <c r="H395" s="1" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="I395" s="1" t="n">
         <v>0.0162</v>
       </c>
     </row>
@@ -11525,9 +12713,12 @@
         <v>0.136</v>
       </c>
       <c r="G396" s="1" t="n">
+        <v>0.1363</v>
+      </c>
+      <c r="H396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="H396" s="1" t="n">
+      <c r="I396" s="1" t="n">
         <v>0.1358</v>
       </c>
     </row>
@@ -11553,9 +12744,12 @@
         <v>0.01473</v>
       </c>
       <c r="G397" s="1" t="n">
+        <v>0.01476</v>
+      </c>
+      <c r="H397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="H397" s="1" t="n">
+      <c r="I397" s="1" t="n">
         <v>0.01473</v>
       </c>
     </row>
@@ -11581,9 +12775,12 @@
         <v>6.847</v>
       </c>
       <c r="G398" s="1" t="n">
-        <v>6.847</v>
+        <v>6.955</v>
       </c>
       <c r="H398" s="1" t="n">
+        <v>6.955</v>
+      </c>
+      <c r="I398" s="1" t="n">
         <v>6.725</v>
       </c>
     </row>
@@ -11609,10 +12806,13 @@
         <v>0.009449000000000001</v>
       </c>
       <c r="G399" s="1" t="n">
+        <v>0.009448</v>
+      </c>
+      <c r="H399" s="1" t="n">
         <v>0.009509999999999999</v>
       </c>
-      <c r="H399" s="1" t="n">
-        <v>0.009449000000000001</v>
+      <c r="I399" s="1" t="n">
+        <v>0.009448</v>
       </c>
     </row>
     <row r="400">
@@ -11637,9 +12837,12 @@
         <v>0.001264</v>
       </c>
       <c r="G400" s="1" t="n">
+        <v>0.001284</v>
+      </c>
+      <c r="H400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="H400" s="1" t="n">
+      <c r="I400" s="1" t="n">
         <v>0.001264</v>
       </c>
     </row>
@@ -11665,9 +12868,12 @@
         <v>0.01841</v>
       </c>
       <c r="G401" s="1" t="n">
+        <v>0.01859</v>
+      </c>
+      <c r="H401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="H401" s="1" t="n">
+      <c r="I401" s="1" t="n">
         <v>0.01841</v>
       </c>
     </row>
@@ -11693,9 +12899,12 @@
         <v>0.08591</v>
       </c>
       <c r="G402" s="1" t="n">
-        <v>0.08595999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H402" s="1" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="I402" s="1" t="n">
         <v>0.08563999999999999</v>
       </c>
     </row>
@@ -11721,9 +12930,12 @@
         <v>0.00555</v>
       </c>
       <c r="G403" s="1" t="n">
-        <v>0.00555</v>
+        <v>0.00556</v>
       </c>
       <c r="H403" s="1" t="n">
+        <v>0.00556</v>
+      </c>
+      <c r="I403" s="1" t="n">
         <v>0.00553</v>
       </c>
     </row>
@@ -11749,9 +12961,12 @@
         <v>0.04362</v>
       </c>
       <c r="G404" s="1" t="n">
+        <v>0.04379</v>
+      </c>
+      <c r="H404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="H404" s="1" t="n">
+      <c r="I404" s="1" t="n">
         <v>0.04362</v>
       </c>
     </row>
@@ -11777,9 +12992,12 @@
         <v>0.05902</v>
       </c>
       <c r="G405" s="1" t="n">
+        <v>0.05906</v>
+      </c>
+      <c r="H405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="H405" s="1" t="n">
+      <c r="I405" s="1" t="n">
         <v>0.05871</v>
       </c>
     </row>
@@ -11805,9 +13023,12 @@
         <v>0.01665</v>
       </c>
       <c r="G406" s="1" t="n">
+        <v>0.01663</v>
+      </c>
+      <c r="H406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="H406" s="1" t="n">
+      <c r="I406" s="1" t="n">
         <v>0.01658</v>
       </c>
     </row>
@@ -11836,6 +13057,9 @@
         <v>0.0428</v>
       </c>
       <c r="H407" s="1" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="I407" s="1" t="n">
         <v>0.0425</v>
       </c>
     </row>
@@ -11861,9 +13085,12 @@
         <v>0.01945</v>
       </c>
       <c r="G408" s="1" t="n">
+        <v>0.01947</v>
+      </c>
+      <c r="H408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="H408" s="1" t="n">
+      <c r="I408" s="1" t="n">
         <v>0.01938</v>
       </c>
     </row>
@@ -11889,9 +13116,12 @@
         <v>0.4475</v>
       </c>
       <c r="G409" s="1" t="n">
-        <v>0.4475</v>
+        <v>0.4484</v>
       </c>
       <c r="H409" s="1" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="I409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -11917,9 +13147,12 @@
         <v>0.0445</v>
       </c>
       <c r="G410" s="1" t="n">
+        <v>0.0445</v>
+      </c>
+      <c r="H410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="H410" s="1" t="n">
+      <c r="I410" s="1" t="n">
         <v>0.04418</v>
       </c>
     </row>
@@ -11945,9 +13178,12 @@
         <v>26.87</v>
       </c>
       <c r="G411" s="1" t="n">
-        <v>27.06</v>
+        <v>28</v>
       </c>
       <c r="H411" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="I411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -11973,9 +13209,12 @@
         <v>0.03549</v>
       </c>
       <c r="G412" s="1" t="n">
-        <v>0.03561</v>
+        <v>0.03564</v>
       </c>
       <c r="H412" s="1" t="n">
+        <v>0.03564</v>
+      </c>
+      <c r="I412" s="1" t="n">
         <v>0.03515</v>
       </c>
     </row>
@@ -12001,9 +13240,12 @@
         <v>0.00343</v>
       </c>
       <c r="G413" s="1" t="n">
-        <v>0.00343</v>
+        <v>0.003432</v>
       </c>
       <c r="H413" s="1" t="n">
+        <v>0.003432</v>
+      </c>
+      <c r="I413" s="1" t="n">
         <v>0.00341</v>
       </c>
     </row>
@@ -12029,9 +13271,12 @@
         <v>0.1535</v>
       </c>
       <c r="G414" s="1" t="n">
-        <v>0.1537</v>
+        <v>0.1538</v>
       </c>
       <c r="H414" s="1" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="I414" s="1" t="n">
         <v>0.1527</v>
       </c>
     </row>
@@ -12057,9 +13302,12 @@
         <v>0.05274</v>
       </c>
       <c r="G415" s="1" t="n">
-        <v>0.05286</v>
+        <v>0.05288</v>
       </c>
       <c r="H415" s="1" t="n">
+        <v>0.05288</v>
+      </c>
+      <c r="I415" s="1" t="n">
         <v>0.05258</v>
       </c>
     </row>
@@ -12085,9 +13333,12 @@
         <v>0.00669</v>
       </c>
       <c r="G416" s="1" t="n">
+        <v>0.00666</v>
+      </c>
+      <c r="H416" s="1" t="n">
         <v>0.00669</v>
       </c>
-      <c r="H416" s="1" t="n">
+      <c r="I416" s="1" t="n">
         <v>0.00664</v>
       </c>
     </row>
@@ -12113,9 +13364,12 @@
         <v>0.06091</v>
       </c>
       <c r="G417" s="1" t="n">
+        <v>0.06094</v>
+      </c>
+      <c r="H417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="H417" s="1" t="n">
+      <c r="I417" s="1" t="n">
         <v>0.0608</v>
       </c>
     </row>
@@ -12141,9 +13395,12 @@
         <v>0.008205</v>
       </c>
       <c r="G418" s="1" t="n">
+        <v>0.008203999999999999</v>
+      </c>
+      <c r="H418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="H418" s="1" t="n">
+      <c r="I418" s="1" t="n">
         <v>0.008156</v>
       </c>
     </row>
@@ -12169,9 +13426,12 @@
         <v>0.07473</v>
       </c>
       <c r="G419" s="1" t="n">
-        <v>0.07494000000000001</v>
+        <v>0.07524</v>
       </c>
       <c r="H419" s="1" t="n">
+        <v>0.07524</v>
+      </c>
+      <c r="I419" s="1" t="n">
         <v>0.07459</v>
       </c>
     </row>
@@ -12197,9 +13457,12 @@
         <v>0.02144</v>
       </c>
       <c r="G420" s="1" t="n">
-        <v>0.02145</v>
+        <v>0.02146</v>
       </c>
       <c r="H420" s="1" t="n">
+        <v>0.02146</v>
+      </c>
+      <c r="I420" s="1" t="n">
         <v>0.0213</v>
       </c>
     </row>
@@ -12225,9 +13488,12 @@
         <v>0.06981999999999999</v>
       </c>
       <c r="G421" s="1" t="n">
-        <v>0.07011000000000001</v>
+        <v>0.07038999999999999</v>
       </c>
       <c r="H421" s="1" t="n">
+        <v>0.07038999999999999</v>
+      </c>
+      <c r="I421" s="1" t="n">
         <v>0.06938999999999999</v>
       </c>
     </row>
@@ -12253,10 +13519,13 @@
         <v>0.01519</v>
       </c>
       <c r="G422" s="1" t="n">
+        <v>0.01514</v>
+      </c>
+      <c r="H422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="H422" s="1" t="n">
-        <v>0.01519</v>
+      <c r="I422" s="1" t="n">
+        <v>0.01514</v>
       </c>
     </row>
     <row r="423">
@@ -12281,9 +13550,12 @@
         <v>0.006685</v>
       </c>
       <c r="G423" s="1" t="n">
+        <v>0.006694</v>
+      </c>
+      <c r="H423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="H423" s="1" t="n">
+      <c r="I423" s="1" t="n">
         <v>0.006677</v>
       </c>
     </row>
@@ -12309,9 +13581,12 @@
         <v>0.92</v>
       </c>
       <c r="G424" s="1" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="H424" s="1" t="n">
+      <c r="I424" s="1" t="n">
         <v>0.915</v>
       </c>
     </row>
@@ -12337,9 +13612,12 @@
         <v>0.03596</v>
       </c>
       <c r="G425" s="1" t="n">
+        <v>0.03567</v>
+      </c>
+      <c r="H425" s="1" t="n">
         <v>0.03596</v>
       </c>
-      <c r="H425" s="1" t="n">
+      <c r="I425" s="1" t="n">
         <v>0.03555</v>
       </c>
     </row>
@@ -12365,9 +13643,12 @@
         <v>1.795</v>
       </c>
       <c r="G426" s="1" t="n">
-        <v>1.795</v>
+        <v>1.81</v>
       </c>
       <c r="H426" s="1" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -12393,9 +13674,12 @@
         <v>0.12816</v>
       </c>
       <c r="G427" s="1" t="n">
+        <v>0.12829</v>
+      </c>
+      <c r="H427" s="1" t="n">
         <v>0.12835</v>
       </c>
-      <c r="H427" s="1" t="n">
+      <c r="I427" s="1" t="n">
         <v>0.12771</v>
       </c>
     </row>
@@ -12421,9 +13705,12 @@
         <v>0.05341</v>
       </c>
       <c r="G428" s="1" t="n">
-        <v>0.05359</v>
+        <v>0.05362</v>
       </c>
       <c r="H428" s="1" t="n">
+        <v>0.05362</v>
+      </c>
+      <c r="I428" s="1" t="n">
         <v>0.05325</v>
       </c>
     </row>
@@ -12449,9 +13736,12 @@
         <v>1.315</v>
       </c>
       <c r="G429" s="1" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="H429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="H429" s="1" t="n">
+      <c r="I429" s="1" t="n">
         <v>1.309</v>
       </c>
     </row>
@@ -12477,9 +13767,12 @@
         <v>0.07571</v>
       </c>
       <c r="G430" s="1" t="n">
+        <v>0.07597</v>
+      </c>
+      <c r="H430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="H430" s="1" t="n">
+      <c r="I430" s="1" t="n">
         <v>0.07547</v>
       </c>
     </row>
@@ -12505,9 +13798,12 @@
         <v>0.1645</v>
       </c>
       <c r="G431" s="1" t="n">
+        <v>0.1637</v>
+      </c>
+      <c r="H431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="H431" s="1" t="n">
+      <c r="I431" s="1" t="n">
         <v>0.1636</v>
       </c>
     </row>
@@ -12536,6 +13832,9 @@
         <v>1.461</v>
       </c>
       <c r="H432" s="1" t="n">
+        <v>1.461</v>
+      </c>
+      <c r="I432" s="1" t="n">
         <v>1.456</v>
       </c>
     </row>
@@ -12561,9 +13860,12 @@
         <v>3.317</v>
       </c>
       <c r="G433" s="1" t="n">
+        <v>3.311</v>
+      </c>
+      <c r="H433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="H433" s="1" t="n">
+      <c r="I433" s="1" t="n">
         <v>3.306</v>
       </c>
     </row>
@@ -12589,9 +13891,12 @@
         <v>0.18</v>
       </c>
       <c r="G434" s="1" t="n">
+        <v>0.1802</v>
+      </c>
+      <c r="H434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="H434" s="1" t="n">
+      <c r="I434" s="1" t="n">
         <v>0.1792</v>
       </c>
     </row>
@@ -12617,9 +13922,12 @@
         <v>0.008645</v>
       </c>
       <c r="G435" s="1" t="n">
+        <v>0.008663000000000001</v>
+      </c>
+      <c r="H435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="H435" s="1" t="n">
+      <c r="I435" s="1" t="n">
         <v>0.00864</v>
       </c>
     </row>
@@ -12645,9 +13953,12 @@
         <v>0.2849</v>
       </c>
       <c r="G436" s="1" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="H436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="H436" s="1" t="n">
+      <c r="I436" s="1" t="n">
         <v>0.2841</v>
       </c>
     </row>
@@ -12673,9 +13984,12 @@
         <v>0.03822</v>
       </c>
       <c r="G437" s="1" t="n">
-        <v>0.0384</v>
+        <v>0.03873</v>
       </c>
       <c r="H437" s="1" t="n">
+        <v>0.03873</v>
+      </c>
+      <c r="I437" s="1" t="n">
         <v>0.03814</v>
       </c>
     </row>
@@ -12701,9 +14015,12 @@
         <v>0.02459</v>
       </c>
       <c r="G438" s="1" t="n">
+        <v>0.02464</v>
+      </c>
+      <c r="H438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="H438" s="1" t="n">
+      <c r="I438" s="1" t="n">
         <v>0.02444</v>
       </c>
     </row>
@@ -12729,9 +14046,12 @@
         <v>0.04406</v>
       </c>
       <c r="G439" s="1" t="n">
+        <v>0.04412</v>
+      </c>
+      <c r="H439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="H439" s="1" t="n">
+      <c r="I439" s="1" t="n">
         <v>0.04405</v>
       </c>
     </row>
@@ -12757,9 +14077,12 @@
         <v>0.0005212</v>
       </c>
       <c r="G440" s="1" t="n">
+        <v>0.0005231</v>
+      </c>
+      <c r="H440" s="1" t="n">
         <v>0.0005258</v>
       </c>
-      <c r="H440" s="1" t="n">
+      <c r="I440" s="1" t="n">
         <v>0.0005212</v>
       </c>
     </row>
@@ -12785,9 +14108,12 @@
         <v>0.04396</v>
       </c>
       <c r="G441" s="1" t="n">
+        <v>0.04403</v>
+      </c>
+      <c r="H441" s="1" t="n">
         <v>0.04428</v>
       </c>
-      <c r="H441" s="1" t="n">
+      <c r="I441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -12813,9 +14139,12 @@
         <v>0.000415</v>
       </c>
       <c r="G442" s="1" t="n">
+        <v>0.000413</v>
+      </c>
+      <c r="H442" s="1" t="n">
         <v>0.000416</v>
       </c>
-      <c r="H442" s="1" t="n">
+      <c r="I442" s="1" t="n">
         <v>0.000413</v>
       </c>
     </row>
@@ -12841,9 +14170,12 @@
         <v>0.0961</v>
       </c>
       <c r="G443" s="1" t="n">
+        <v>0.09689</v>
+      </c>
+      <c r="H443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="H443" s="1" t="n">
+      <c r="I443" s="1" t="n">
         <v>0.0961</v>
       </c>
     </row>
@@ -12869,9 +14201,12 @@
         <v>2.308</v>
       </c>
       <c r="G444" s="1" t="n">
+        <v>2.305</v>
+      </c>
+      <c r="H444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="H444" s="1" t="n">
+      <c r="I444" s="1" t="n">
         <v>2.289</v>
       </c>
     </row>
@@ -12897,9 +14232,12 @@
         <v>0.2707</v>
       </c>
       <c r="G445" s="1" t="n">
-        <v>0.2707</v>
+        <v>0.2741</v>
       </c>
       <c r="H445" s="1" t="n">
+        <v>0.2741</v>
+      </c>
+      <c r="I445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -12925,9 +14263,12 @@
         <v>0.0007534</v>
       </c>
       <c r="G446" s="1" t="n">
+        <v>0.0007526</v>
+      </c>
+      <c r="H446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="H446" s="1" t="n">
+      <c r="I446" s="1" t="n">
         <v>0.0007521</v>
       </c>
     </row>
@@ -12953,10 +14294,13 @@
         <v>0.03869</v>
       </c>
       <c r="G447" s="1" t="n">
+        <v>0.03838</v>
+      </c>
+      <c r="H447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="H447" s="1" t="n">
-        <v>0.03869</v>
+      <c r="I447" s="1" t="n">
+        <v>0.03838</v>
       </c>
     </row>
     <row r="448">
@@ -12981,9 +14325,12 @@
         <v>0.1773</v>
       </c>
       <c r="G448" s="1" t="n">
+        <v>0.1772</v>
+      </c>
+      <c r="H448" s="1" t="n">
         <v>0.1773</v>
       </c>
-      <c r="H448" s="1" t="n">
+      <c r="I448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -13009,9 +14356,12 @@
         <v>0.04284</v>
       </c>
       <c r="G449" s="1" t="n">
+        <v>0.04299</v>
+      </c>
+      <c r="H449" s="1" t="n">
         <v>0.04301</v>
       </c>
-      <c r="H449" s="1" t="n">
+      <c r="I449" s="1" t="n">
         <v>0.0427</v>
       </c>
     </row>
@@ -13037,9 +14387,12 @@
         <v>0.000165</v>
       </c>
       <c r="G450" s="1" t="n">
+        <v>0.000165</v>
+      </c>
+      <c r="H450" s="1" t="n">
         <v>0.0001654</v>
       </c>
-      <c r="H450" s="1" t="n">
+      <c r="I450" s="1" t="n">
         <v>0.0001641</v>
       </c>
     </row>
@@ -13065,9 +14418,12 @@
         <v>0.03751</v>
       </c>
       <c r="G451" s="1" t="n">
+        <v>0.03753</v>
+      </c>
+      <c r="H451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="H451" s="1" t="n">
+      <c r="I451" s="1" t="n">
         <v>0.03751</v>
       </c>
     </row>
@@ -13093,9 +14449,12 @@
         <v>0.00997</v>
       </c>
       <c r="G452" s="1" t="n">
+        <v>0.00996</v>
+      </c>
+      <c r="H452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="H452" s="1" t="n">
+      <c r="I452" s="1" t="n">
         <v>0.009939999999999999</v>
       </c>
     </row>
@@ -13121,9 +14480,12 @@
         <v>0.06804</v>
       </c>
       <c r="G453" s="1" t="n">
-        <v>0.06805</v>
+        <v>0.06816</v>
       </c>
       <c r="H453" s="1" t="n">
+        <v>0.06816</v>
+      </c>
+      <c r="I453" s="1" t="n">
         <v>0.06793</v>
       </c>
     </row>
@@ -13149,9 +14511,12 @@
         <v>0.007577</v>
       </c>
       <c r="G454" s="1" t="n">
+        <v>0.007586</v>
+      </c>
+      <c r="H454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="H454" s="1" t="n">
+      <c r="I454" s="1" t="n">
         <v>0.007541</v>
       </c>
     </row>
@@ -13177,9 +14542,12 @@
         <v>0.003373</v>
       </c>
       <c r="G455" s="1" t="n">
+        <v>0.00337</v>
+      </c>
+      <c r="H455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="H455" s="1" t="n">
+      <c r="I455" s="1" t="n">
         <v>0.003362</v>
       </c>
     </row>
@@ -13205,9 +14573,12 @@
         <v>0.001871</v>
       </c>
       <c r="G456" s="1" t="n">
-        <v>0.001874</v>
+        <v>0.001875</v>
       </c>
       <c r="H456" s="1" t="n">
+        <v>0.001875</v>
+      </c>
+      <c r="I456" s="1" t="n">
         <v>0.001854</v>
       </c>
     </row>
@@ -13233,9 +14604,12 @@
         <v>0.0001761</v>
       </c>
       <c r="G457" s="1" t="n">
+        <v>0.0001765</v>
+      </c>
+      <c r="H457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="H457" s="1" t="n">
+      <c r="I457" s="1" t="n">
         <v>0.0001758</v>
       </c>
     </row>
@@ -13261,9 +14635,12 @@
         <v>0.0003913</v>
       </c>
       <c r="G458" s="1" t="n">
-        <v>0.0003913</v>
+        <v>0.0003916</v>
       </c>
       <c r="H458" s="1" t="n">
+        <v>0.0003916</v>
+      </c>
+      <c r="I458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -13289,9 +14666,12 @@
         <v>0.01404</v>
       </c>
       <c r="G459" s="1" t="n">
-        <v>0.01409</v>
+        <v>0.01413</v>
       </c>
       <c r="H459" s="1" t="n">
+        <v>0.01413</v>
+      </c>
+      <c r="I459" s="1" t="n">
         <v>0.01391</v>
       </c>
     </row>
@@ -13317,9 +14697,12 @@
         <v>0.04559</v>
       </c>
       <c r="G460" s="1" t="n">
+        <v>0.04553</v>
+      </c>
+      <c r="H460" s="1" t="n">
         <v>0.04559</v>
       </c>
-      <c r="H460" s="1" t="n">
+      <c r="I460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -13348,6 +14731,9 @@
         <v>0.2839</v>
       </c>
       <c r="H461" s="1" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="I461" s="1" t="n">
         <v>0.2822</v>
       </c>
     </row>
@@ -13373,9 +14759,12 @@
         <v>0.00626</v>
       </c>
       <c r="G462" s="1" t="n">
-        <v>0.006279</v>
+        <v>0.006312</v>
       </c>
       <c r="H462" s="1" t="n">
+        <v>0.006312</v>
+      </c>
+      <c r="I462" s="1" t="n">
         <v>0.00622</v>
       </c>
     </row>
@@ -13401,9 +14790,12 @@
         <v>0.007085</v>
       </c>
       <c r="G463" s="1" t="n">
+        <v>0.007086</v>
+      </c>
+      <c r="H463" s="1" t="n">
         <v>0.007088</v>
       </c>
-      <c r="H463" s="1" t="n">
+      <c r="I463" s="1" t="n">
         <v>0.00704</v>
       </c>
     </row>
@@ -13429,9 +14821,12 @@
         <v>0.2871</v>
       </c>
       <c r="G464" s="1" t="n">
-        <v>0.2878</v>
+        <v>0.288</v>
       </c>
       <c r="H464" s="1" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="I464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -13457,9 +14852,12 @@
         <v>0.08177</v>
       </c>
       <c r="G465" s="1" t="n">
-        <v>0.08177</v>
+        <v>0.08183</v>
       </c>
       <c r="H465" s="1" t="n">
+        <v>0.08183</v>
+      </c>
+      <c r="I465" s="1" t="n">
         <v>0.08078</v>
       </c>
     </row>
@@ -13485,9 +14883,12 @@
         <v>0.635</v>
       </c>
       <c r="G466" s="1" t="n">
-        <v>0.635</v>
+        <v>0.6368</v>
       </c>
       <c r="H466" s="1" t="n">
+        <v>0.6368</v>
+      </c>
+      <c r="I466" s="1" t="n">
         <v>0.6318</v>
       </c>
     </row>
@@ -13513,9 +14914,12 @@
         <v>0.01491</v>
       </c>
       <c r="G467" s="1" t="n">
-        <v>0.01491</v>
+        <v>0.01499</v>
       </c>
       <c r="H467" s="1" t="n">
+        <v>0.01499</v>
+      </c>
+      <c r="I467" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -13541,9 +14945,12 @@
         <v>0.03468</v>
       </c>
       <c r="G468" s="1" t="n">
+        <v>0.03458</v>
+      </c>
+      <c r="H468" s="1" t="n">
         <v>0.03468</v>
       </c>
-      <c r="H468" s="1" t="n">
+      <c r="I468" s="1" t="n">
         <v>0.03448</v>
       </c>
     </row>
@@ -13569,9 +14976,12 @@
         <v>0.1647</v>
       </c>
       <c r="G469" s="1" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="H469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="H469" s="1" t="n">
+      <c r="I469" s="1" t="n">
         <v>0.1644</v>
       </c>
     </row>
@@ -13597,9 +15007,12 @@
         <v>0.4151</v>
       </c>
       <c r="G470" s="1" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="H470" s="1" t="n">
         <v>0.4151</v>
       </c>
-      <c r="H470" s="1" t="n">
+      <c r="I470" s="1" t="n">
         <v>0.4123</v>
       </c>
     </row>
@@ -13625,9 +15038,12 @@
         <v>0.06999</v>
       </c>
       <c r="G471" s="1" t="n">
+        <v>0.07004000000000001</v>
+      </c>
+      <c r="H471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="H471" s="1" t="n">
+      <c r="I471" s="1" t="n">
         <v>0.06975000000000001</v>
       </c>
     </row>
@@ -13653,9 +15069,12 @@
         <v>0.06734</v>
       </c>
       <c r="G472" s="1" t="n">
+        <v>0.06713</v>
+      </c>
+      <c r="H472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="H472" s="1" t="n">
+      <c r="I472" s="1" t="n">
         <v>0.06688</v>
       </c>
     </row>
@@ -13681,9 +15100,12 @@
         <v>0.01643</v>
       </c>
       <c r="G473" s="1" t="n">
+        <v>0.01645</v>
+      </c>
+      <c r="H473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="H473" s="1" t="n">
+      <c r="I473" s="1" t="n">
         <v>0.0164</v>
       </c>
     </row>
@@ -13709,10 +15131,13 @@
         <v>0.2092</v>
       </c>
       <c r="G474" s="1" t="n">
+        <v>0.2091</v>
+      </c>
+      <c r="H474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="H474" s="1" t="n">
-        <v>0.2092</v>
+      <c r="I474" s="1" t="n">
+        <v>0.2091</v>
       </c>
     </row>
     <row r="475">
@@ -13737,9 +15162,12 @@
         <v>0.04223</v>
       </c>
       <c r="G475" s="1" t="n">
+        <v>0.04241</v>
+      </c>
+      <c r="H475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="H475" s="1" t="n">
+      <c r="I475" s="1" t="n">
         <v>0.04202</v>
       </c>
     </row>
@@ -13765,9 +15193,12 @@
         <v>1.574</v>
       </c>
       <c r="G476" s="1" t="n">
+        <v>1.577</v>
+      </c>
+      <c r="H476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="H476" s="1" t="n">
+      <c r="I476" s="1" t="n">
         <v>1.57</v>
       </c>
     </row>
@@ -13793,10 +15224,13 @@
         <v>0.1011</v>
       </c>
       <c r="G477" s="1" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="H477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="H477" s="1" t="n">
-        <v>0.1011</v>
+      <c r="I477" s="1" t="n">
+        <v>0.1008</v>
       </c>
     </row>
     <row r="478">
@@ -13821,9 +15255,12 @@
         <v>0.001157</v>
       </c>
       <c r="G478" s="1" t="n">
+        <v>0.00116</v>
+      </c>
+      <c r="H478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="H478" s="1" t="n">
+      <c r="I478" s="1" t="n">
         <v>0.001155</v>
       </c>
     </row>
@@ -13849,9 +15286,12 @@
         <v>0.147</v>
       </c>
       <c r="G479" s="1" t="n">
+        <v>0.1473</v>
+      </c>
+      <c r="H479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="H479" s="1" t="n">
+      <c r="I479" s="1" t="n">
         <v>0.1462</v>
       </c>
     </row>
@@ -13877,9 +15317,12 @@
         <v>0.001732</v>
       </c>
       <c r="G480" s="1" t="n">
+        <v>0.001733</v>
+      </c>
+      <c r="H480" s="1" t="n">
         <v>0.001734</v>
       </c>
-      <c r="H480" s="1" t="n">
+      <c r="I480" s="1" t="n">
         <v>0.001722</v>
       </c>
     </row>
@@ -13905,9 +15348,12 @@
         <v>0.918</v>
       </c>
       <c r="G481" s="1" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="H481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="H481" s="1" t="n">
+      <c r="I481" s="1" t="n">
         <v>0.915</v>
       </c>
     </row>
@@ -13933,10 +15379,13 @@
         <v>0.13459</v>
       </c>
       <c r="G482" s="1" t="n">
+        <v>0.13419</v>
+      </c>
+      <c r="H482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="H482" s="1" t="n">
-        <v>0.13437</v>
+      <c r="I482" s="1" t="n">
+        <v>0.13419</v>
       </c>
     </row>
     <row r="483">
@@ -13961,9 +15410,12 @@
         <v>0.04057</v>
       </c>
       <c r="G483" s="1" t="n">
-        <v>0.04062</v>
+        <v>0.04063</v>
       </c>
       <c r="H483" s="1" t="n">
+        <v>0.04063</v>
+      </c>
+      <c r="I483" s="1" t="n">
         <v>0.04048</v>
       </c>
     </row>
@@ -13989,9 +15441,12 @@
         <v>0.3086</v>
       </c>
       <c r="G484" s="1" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="H484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="H484" s="1" t="n">
+      <c r="I484" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -14017,9 +15472,12 @@
         <v>0.05702</v>
       </c>
       <c r="G485" s="1" t="n">
-        <v>0.05702</v>
+        <v>0.05709</v>
       </c>
       <c r="H485" s="1" t="n">
+        <v>0.05709</v>
+      </c>
+      <c r="I485" s="1" t="n">
         <v>0.05633</v>
       </c>
     </row>
@@ -14045,9 +15503,12 @@
         <v>0.001578</v>
       </c>
       <c r="G486" s="1" t="n">
-        <v>0.001578</v>
+        <v>0.001579</v>
       </c>
       <c r="H486" s="1" t="n">
+        <v>0.001579</v>
+      </c>
+      <c r="I486" s="1" t="n">
         <v>0.001569</v>
       </c>
     </row>
@@ -14073,9 +15534,12 @@
         <v>0.06763</v>
       </c>
       <c r="G487" s="1" t="n">
-        <v>0.06763</v>
+        <v>0.06766999999999999</v>
       </c>
       <c r="H487" s="1" t="n">
+        <v>0.06766999999999999</v>
+      </c>
+      <c r="I487" s="1" t="n">
         <v>0.06716</v>
       </c>
     </row>
@@ -14101,9 +15565,12 @@
         <v>0.1953</v>
       </c>
       <c r="G488" s="1" t="n">
+        <v>0.1947</v>
+      </c>
+      <c r="H488" s="1" t="n">
         <v>0.1953</v>
       </c>
-      <c r="H488" s="1" t="n">
+      <c r="I488" s="1" t="n">
         <v>0.1936</v>
       </c>
     </row>
@@ -14129,9 +15596,12 @@
         <v>0.0482</v>
       </c>
       <c r="G489" s="1" t="n">
+        <v>0.04826</v>
+      </c>
+      <c r="H489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="H489" s="1" t="n">
+      <c r="I489" s="1" t="n">
         <v>0.04804</v>
       </c>
     </row>
@@ -14157,9 +15627,12 @@
         <v>0.1394</v>
       </c>
       <c r="G490" s="1" t="n">
-        <v>0.1397</v>
+        <v>0.1401</v>
       </c>
       <c r="H490" s="1" t="n">
+        <v>0.1401</v>
+      </c>
+      <c r="I490" s="1" t="n">
         <v>0.139</v>
       </c>
     </row>
@@ -14185,9 +15658,12 @@
         <v>0.0226</v>
       </c>
       <c r="G491" s="1" t="n">
+        <v>0.02261</v>
+      </c>
+      <c r="H491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="H491" s="1" t="n">
+      <c r="I491" s="1" t="n">
         <v>0.02243</v>
       </c>
     </row>
@@ -14213,9 +15689,12 @@
         <v>0.007889</v>
       </c>
       <c r="G492" s="1" t="n">
+        <v>0.007901999999999999</v>
+      </c>
+      <c r="H492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="H492" s="1" t="n">
+      <c r="I492" s="1" t="n">
         <v>0.007825</v>
       </c>
     </row>
@@ -14241,9 +15720,12 @@
         <v>0.000598</v>
       </c>
       <c r="G493" s="1" t="n">
-        <v>0.0005984</v>
+        <v>0.0005992</v>
       </c>
       <c r="H493" s="1" t="n">
+        <v>0.0005992</v>
+      </c>
+      <c r="I493" s="1" t="n">
         <v>0.0005952</v>
       </c>
     </row>
@@ -14269,9 +15751,12 @@
         <v>3.025</v>
       </c>
       <c r="G494" s="1" t="n">
+        <v>3.037</v>
+      </c>
+      <c r="H494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="H494" s="1" t="n">
+      <c r="I494" s="1" t="n">
         <v>2.999</v>
       </c>
     </row>
@@ -14297,9 +15782,12 @@
         <v>0.05109</v>
       </c>
       <c r="G495" s="1" t="n">
+        <v>0.05123</v>
+      </c>
+      <c r="H495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="H495" s="1" t="n">
+      <c r="I495" s="1" t="n">
         <v>0.05085</v>
       </c>
     </row>
@@ -14325,9 +15813,12 @@
         <v>0.006855</v>
       </c>
       <c r="G496" s="1" t="n">
+        <v>0.006854</v>
+      </c>
+      <c r="H496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="H496" s="1" t="n">
+      <c r="I496" s="1" t="n">
         <v>0.006839</v>
       </c>
     </row>
@@ -14353,9 +15844,12 @@
         <v>1.31</v>
       </c>
       <c r="G497" s="1" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="H497" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="H497" s="1" t="n">
+      <c r="I497" s="1" t="n">
         <v>1.299</v>
       </c>
     </row>
@@ -14381,10 +15875,13 @@
         <v>0.04</v>
       </c>
       <c r="G498" s="1" t="n">
+        <v>0.03984</v>
+      </c>
+      <c r="H498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="H498" s="1" t="n">
-        <v>0.03999</v>
+      <c r="I498" s="1" t="n">
+        <v>0.03984</v>
       </c>
     </row>
     <row r="499">
@@ -14409,9 +15906,12 @@
         <v>0.04196</v>
       </c>
       <c r="G499" s="1" t="n">
+        <v>0.04196</v>
+      </c>
+      <c r="H499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="H499" s="1" t="n">
+      <c r="I499" s="1" t="n">
         <v>0.04186</v>
       </c>
     </row>
@@ -14437,9 +15937,12 @@
         <v>0.00543</v>
       </c>
       <c r="G500" s="1" t="n">
-        <v>0.00543</v>
+        <v>0.00549</v>
       </c>
       <c r="H500" s="1" t="n">
+        <v>0.00549</v>
+      </c>
+      <c r="I500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -14465,9 +15968,12 @@
         <v>0.03628</v>
       </c>
       <c r="G501" s="1" t="n">
-        <v>0.03638</v>
+        <v>0.0364</v>
       </c>
       <c r="H501" s="1" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="I501" s="1" t="n">
         <v>0.03625</v>
       </c>
     </row>
@@ -14493,9 +15999,12 @@
         <v>0.0733</v>
       </c>
       <c r="G502" s="1" t="n">
-        <v>0.07335999999999999</v>
+        <v>0.07342</v>
       </c>
       <c r="H502" s="1" t="n">
+        <v>0.07342</v>
+      </c>
+      <c r="I502" s="1" t="n">
         <v>0.07321</v>
       </c>
     </row>
@@ -14521,9 +16030,12 @@
         <v>0.000755</v>
       </c>
       <c r="G503" s="1" t="n">
+        <v>0.0007548</v>
+      </c>
+      <c r="H503" s="1" t="n">
         <v>0.000755</v>
       </c>
-      <c r="H503" s="1" t="n">
+      <c r="I503" s="1" t="n">
         <v>0.0007499</v>
       </c>
     </row>
@@ -14549,9 +16061,12 @@
         <v>0.015976</v>
       </c>
       <c r="G504" s="1" t="n">
+        <v>0.015976</v>
+      </c>
+      <c r="H504" s="1" t="n">
         <v>0.016003</v>
       </c>
-      <c r="H504" s="1" t="n">
+      <c r="I504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -14577,9 +16092,12 @@
         <v>0.00711</v>
       </c>
       <c r="G505" s="1" t="n">
+        <v>0.00712</v>
+      </c>
+      <c r="H505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="H505" s="1" t="n">
+      <c r="I505" s="1" t="n">
         <v>0.00709</v>
       </c>
     </row>
@@ -14605,10 +16123,13 @@
         <v>0.0256</v>
       </c>
       <c r="G506" s="1" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="H506" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="H506" s="1" t="n">
-        <v>0.0256</v>
+      <c r="I506" s="1" t="n">
+        <v>0.0255</v>
       </c>
     </row>
     <row r="507">
@@ -14633,9 +16154,12 @@
         <v>0.001354</v>
       </c>
       <c r="G507" s="1" t="n">
-        <v>0.001354</v>
+        <v>0.001358</v>
       </c>
       <c r="H507" s="1" t="n">
+        <v>0.001358</v>
+      </c>
+      <c r="I507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -14661,9 +16185,12 @@
         <v>0.2827</v>
       </c>
       <c r="G508" s="1" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="H508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="H508" s="1" t="n">
+      <c r="I508" s="1" t="n">
         <v>0.2821</v>
       </c>
     </row>
@@ -14689,9 +16216,12 @@
         <v>0.1328</v>
       </c>
       <c r="G509" s="1" t="n">
+        <v>0.1329</v>
+      </c>
+      <c r="H509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="H509" s="1" t="n">
+      <c r="I509" s="1" t="n">
         <v>0.1323</v>
       </c>
     </row>
@@ -14720,6 +16250,9 @@
         <v>0.04972</v>
       </c>
       <c r="H510" s="1" t="n">
+        <v>0.04972</v>
+      </c>
+      <c r="I510" s="1" t="n">
         <v>0.04932</v>
       </c>
     </row>
@@ -14748,6 +16281,9 @@
         <v>0.00278</v>
       </c>
       <c r="H511" s="1" t="n">
+        <v>0.00278</v>
+      </c>
+      <c r="I511" s="1" t="n">
         <v>0.00275</v>
       </c>
     </row>
@@ -14773,9 +16309,12 @@
         <v>0.015454</v>
       </c>
       <c r="G512" s="1" t="n">
+        <v>0.015426</v>
+      </c>
+      <c r="H512" s="1" t="n">
         <v>0.015454</v>
       </c>
-      <c r="H512" s="1" t="n">
+      <c r="I512" s="1" t="n">
         <v>0.015351</v>
       </c>
     </row>
@@ -14804,6 +16343,9 @@
         <v>0.6948</v>
       </c>
       <c r="H513" s="1" t="n">
+        <v>0.6948</v>
+      </c>
+      <c r="I513" s="1" t="n">
         <v>0.6933</v>
       </c>
     </row>
@@ -14829,9 +16371,12 @@
         <v>0.004589</v>
       </c>
       <c r="G514" s="1" t="n">
+        <v>0.004578</v>
+      </c>
+      <c r="H514" s="1" t="n">
         <v>0.004589</v>
       </c>
-      <c r="H514" s="1" t="n">
+      <c r="I514" s="1" t="n">
         <v>0.004534</v>
       </c>
     </row>
@@ -14857,9 +16402,12 @@
         <v>0.005056</v>
       </c>
       <c r="G515" s="1" t="n">
+        <v>0.005057</v>
+      </c>
+      <c r="H515" s="1" t="n">
         <v>0.005066</v>
       </c>
-      <c r="H515" s="1" t="n">
+      <c r="I515" s="1" t="n">
         <v>0.005037</v>
       </c>
     </row>
@@ -14885,9 +16433,12 @@
         <v>0.06369</v>
       </c>
       <c r="G516" s="1" t="n">
+        <v>0.06356000000000001</v>
+      </c>
+      <c r="H516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="H516" s="1" t="n">
+      <c r="I516" s="1" t="n">
         <v>0.06353</v>
       </c>
     </row>
@@ -14913,9 +16464,12 @@
         <v>0.06531000000000001</v>
       </c>
       <c r="G517" s="1" t="n">
+        <v>0.06504</v>
+      </c>
+      <c r="H517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="H517" s="1" t="n">
+      <c r="I517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -14941,9 +16495,12 @@
         <v>0.01219</v>
       </c>
       <c r="G518" s="1" t="n">
+        <v>0.01216</v>
+      </c>
+      <c r="H518" s="1" t="n">
         <v>0.01219</v>
       </c>
-      <c r="H518" s="1" t="n">
+      <c r="I518" s="1" t="n">
         <v>0.0121</v>
       </c>
     </row>
@@ -14969,9 +16526,12 @@
         <v>0.04793</v>
       </c>
       <c r="G519" s="1" t="n">
+        <v>0.04781</v>
+      </c>
+      <c r="H519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="H519" s="1" t="n">
+      <c r="I519" s="1" t="n">
         <v>0.04743</v>
       </c>
     </row>
@@ -14997,9 +16557,12 @@
         <v>0.04401</v>
       </c>
       <c r="G520" s="1" t="n">
-        <v>0.04406</v>
+        <v>0.04411</v>
       </c>
       <c r="H520" s="1" t="n">
+        <v>0.04411</v>
+      </c>
+      <c r="I520" s="1" t="n">
         <v>0.04384</v>
       </c>
     </row>
@@ -15025,9 +16588,12 @@
         <v>0.008569</v>
       </c>
       <c r="G521" s="1" t="n">
+        <v>0.008598</v>
+      </c>
+      <c r="H521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="H521" s="1" t="n">
+      <c r="I521" s="1" t="n">
         <v>0.008552000000000001</v>
       </c>
     </row>
@@ -15053,10 +16619,13 @@
         <v>0.08912</v>
       </c>
       <c r="G522" s="1" t="n">
+        <v>0.08910999999999999</v>
+      </c>
+      <c r="H522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="H522" s="1" t="n">
-        <v>0.08912</v>
+      <c r="I522" s="1" t="n">
+        <v>0.08910999999999999</v>
       </c>
     </row>
     <row r="523">
@@ -15084,6 +16653,9 @@
         <v>0.006492</v>
       </c>
       <c r="H523" s="1" t="n">
+        <v>0.006492</v>
+      </c>
+      <c r="I523" s="1" t="n">
         <v>0.00646</v>
       </c>
     </row>
@@ -15109,9 +16681,12 @@
         <v>0.01666</v>
       </c>
       <c r="G524" s="1" t="n">
+        <v>0.01667</v>
+      </c>
+      <c r="H524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="H524" s="1" t="n">
+      <c r="I524" s="1" t="n">
         <v>0.01662</v>
       </c>
     </row>
@@ -15137,10 +16712,13 @@
         <v>0.01807</v>
       </c>
       <c r="G525" s="1" t="n">
+        <v>0.01801</v>
+      </c>
+      <c r="H525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="H525" s="1" t="n">
-        <v>0.01807</v>
+      <c r="I525" s="1" t="n">
+        <v>0.01801</v>
       </c>
     </row>
     <row r="526">
@@ -15165,9 +16743,12 @@
         <v>0.07965</v>
       </c>
       <c r="G526" s="1" t="n">
+        <v>0.07951999999999999</v>
+      </c>
+      <c r="H526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="H526" s="1" t="n">
+      <c r="I526" s="1" t="n">
         <v>0.07917</v>
       </c>
     </row>
@@ -15193,9 +16774,12 @@
         <v>0.01634</v>
       </c>
       <c r="G527" s="1" t="n">
+        <v>0.01636</v>
+      </c>
+      <c r="H527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="H527" s="1" t="n">
+      <c r="I527" s="1" t="n">
         <v>0.01634</v>
       </c>
     </row>
@@ -15221,9 +16805,12 @@
         <v>0.004193</v>
       </c>
       <c r="G528" s="1" t="n">
+        <v>0.004191</v>
+      </c>
+      <c r="H528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="H528" s="1" t="n">
+      <c r="I528" s="1" t="n">
         <v>0.004164</v>
       </c>
     </row>
@@ -15249,9 +16836,12 @@
         <v>0.003739</v>
       </c>
       <c r="G529" s="1" t="n">
+        <v>0.003739</v>
+      </c>
+      <c r="H529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="H529" s="1" t="n">
+      <c r="I529" s="1" t="n">
         <v>0.003698</v>
       </c>
     </row>
@@ -15277,9 +16867,12 @@
         <v>1.319</v>
       </c>
       <c r="G530" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="H530" s="1" t="n">
+      <c r="I530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -15305,9 +16898,12 @@
         <v>0.4937</v>
       </c>
       <c r="G531" s="1" t="n">
-        <v>0.4937</v>
+        <v>0.494</v>
       </c>
       <c r="H531" s="1" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="I531" s="1" t="n">
         <v>0.4912</v>
       </c>
     </row>
@@ -15333,9 +16929,12 @@
         <v>0.03083</v>
       </c>
       <c r="G532" s="1" t="n">
-        <v>0.03087</v>
+        <v>0.03091</v>
       </c>
       <c r="H532" s="1" t="n">
+        <v>0.03091</v>
+      </c>
+      <c r="I532" s="1" t="n">
         <v>0.03058</v>
       </c>
     </row>
@@ -15361,9 +16960,12 @@
         <v>0.1538</v>
       </c>
       <c r="G533" s="1" t="n">
+        <v>0.1536</v>
+      </c>
+      <c r="H533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="H533" s="1" t="n">
+      <c r="I533" s="1" t="n">
         <v>0.1532</v>
       </c>
     </row>
@@ -15389,9 +16991,12 @@
         <v>0.05424</v>
       </c>
       <c r="G534" s="1" t="n">
+        <v>0.05423</v>
+      </c>
+      <c r="H534" s="1" t="n">
         <v>0.05424</v>
       </c>
-      <c r="H534" s="1" t="n">
+      <c r="I534" s="1" t="n">
         <v>0.05388</v>
       </c>
     </row>
@@ -15417,9 +17022,12 @@
         <v>0.01514</v>
       </c>
       <c r="G535" s="1" t="n">
+        <v>0.01509</v>
+      </c>
+      <c r="H535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="H535" s="1" t="n">
+      <c r="I535" s="1" t="n">
         <v>0.01501</v>
       </c>
     </row>
@@ -15445,9 +17053,12 @@
         <v>0.05832</v>
       </c>
       <c r="G536" s="1" t="n">
-        <v>0.05863</v>
+        <v>0.05879</v>
       </c>
       <c r="H536" s="1" t="n">
+        <v>0.05879</v>
+      </c>
+      <c r="I536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -15473,9 +17084,12 @@
         <v>0.05495</v>
       </c>
       <c r="G537" s="1" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="H537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="H537" s="1" t="n">
+      <c r="I537" s="1" t="n">
         <v>0.05495</v>
       </c>
     </row>
@@ -15501,9 +17115,12 @@
         <v>0.1071</v>
       </c>
       <c r="G538" s="1" t="n">
-        <v>0.1071</v>
+        <v>0.1076</v>
       </c>
       <c r="H538" s="1" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="I538" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -15529,9 +17146,12 @@
         <v>0.01293</v>
       </c>
       <c r="G539" s="1" t="n">
+        <v>0.01294</v>
+      </c>
+      <c r="H539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="H539" s="1" t="n">
+      <c r="I539" s="1" t="n">
         <v>0.01284</v>
       </c>
     </row>
@@ -15557,9 +17177,12 @@
         <v>0.1758</v>
       </c>
       <c r="G540" s="1" t="n">
+        <v>0.1763</v>
+      </c>
+      <c r="H540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="H540" s="1" t="n">
+      <c r="I540" s="1" t="n">
         <v>0.175</v>
       </c>
     </row>
@@ -15585,9 +17208,12 @@
         <v>0.1239</v>
       </c>
       <c r="G541" s="1" t="n">
+        <v>0.1237</v>
+      </c>
+      <c r="H541" s="1" t="n">
         <v>0.1239</v>
       </c>
-      <c r="H541" s="1" t="n">
+      <c r="I541" s="1" t="n">
         <v>0.1231</v>
       </c>
     </row>
@@ -15613,9 +17239,12 @@
         <v>0.0251</v>
       </c>
       <c r="G542" s="1" t="n">
+        <v>0.02507</v>
+      </c>
+      <c r="H542" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="H542" s="1" t="n">
+      <c r="I542" s="1" t="n">
         <v>0.02489</v>
       </c>
     </row>
@@ -15641,9 +17270,12 @@
         <v>0.05894</v>
       </c>
       <c r="G543" s="1" t="n">
-        <v>0.05894</v>
+        <v>0.059</v>
       </c>
       <c r="H543" s="1" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="I543" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J543"/>
+  <dimension ref="A1:K543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -427,8 +427,9 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,10 +475,15 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>price_01:45</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -511,10 +517,13 @@
         <v>71637.3</v>
       </c>
       <c r="I2" s="1" t="n">
+        <v>71185.89999999999</v>
+      </c>
+      <c r="J2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="J2" s="1" t="n">
-        <v>71323.7</v>
+      <c r="K2" s="1" t="n">
+        <v>71185.89999999999</v>
       </c>
     </row>
     <row r="3">
@@ -545,10 +554,13 @@
         <v>2119.57</v>
       </c>
       <c r="I3" s="1" t="n">
+        <v>2105.84</v>
+      </c>
+      <c r="J3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="J3" s="1" t="n">
-        <v>2118.6</v>
+      <c r="K3" s="1" t="n">
+        <v>2105.84</v>
       </c>
     </row>
     <row r="4">
@@ -579,10 +591,13 @@
         <v>89.3</v>
       </c>
       <c r="I4" s="1" t="n">
+        <v>88.86</v>
+      </c>
+      <c r="J4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="J4" s="1" t="n">
-        <v>89.23</v>
+      <c r="K4" s="1" t="n">
+        <v>88.86</v>
       </c>
     </row>
     <row r="5">
@@ -613,9 +628,12 @@
         <v>3.851</v>
       </c>
       <c r="I5" s="1" t="n">
+        <v>3.845</v>
+      </c>
+      <c r="J5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="K5" s="1" t="n">
         <v>3.77</v>
       </c>
     </row>
@@ -647,10 +665,13 @@
         <v>1.402</v>
       </c>
       <c r="I6" s="1" t="n">
+        <v>1.3962</v>
+      </c>
+      <c r="J6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="J6" s="1" t="n">
-        <v>1.402</v>
+      <c r="K6" s="1" t="n">
+        <v>1.3962</v>
       </c>
     </row>
     <row r="7">
@@ -681,10 +702,13 @@
         <v>0.09683</v>
       </c>
       <c r="I7" s="1" t="n">
+        <v>0.09636</v>
+      </c>
+      <c r="J7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="J7" s="1" t="n">
-        <v>0.09683</v>
+      <c r="K7" s="1" t="n">
+        <v>0.09636</v>
       </c>
     </row>
     <row r="8">
@@ -715,9 +739,12 @@
         <v>0.014064</v>
       </c>
       <c r="I8" s="1" t="n">
+        <v>0.014164</v>
+      </c>
+      <c r="J8" s="1" t="n">
         <v>0.014568</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="K8" s="1" t="n">
         <v>0.014064</v>
       </c>
     </row>
@@ -749,10 +776,13 @@
         <v>660.08</v>
       </c>
       <c r="I9" s="1" t="n">
+        <v>656.64</v>
+      </c>
+      <c r="J9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="J9" s="1" t="n">
-        <v>659.95</v>
+      <c r="K9" s="1" t="n">
+        <v>656.64</v>
       </c>
     </row>
     <row r="10">
@@ -783,9 +813,12 @@
         <v>19.203</v>
       </c>
       <c r="I10" s="1" t="n">
-        <v>19.415</v>
+        <v>19.544</v>
       </c>
       <c r="J10" s="1" t="n">
+        <v>19.544</v>
+      </c>
+      <c r="K10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -817,10 +850,13 @@
         <v>0.003438</v>
       </c>
       <c r="I11" s="1" t="n">
+        <v>0.0034204</v>
+      </c>
+      <c r="J11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="J11" s="1" t="n">
-        <v>0.003438</v>
+      <c r="K11" s="1" t="n">
+        <v>0.0034204</v>
       </c>
     </row>
     <row r="12">
@@ -851,9 +887,12 @@
         <v>36.524</v>
       </c>
       <c r="I12" s="1" t="n">
-        <v>36.524</v>
+        <v>36.561</v>
       </c>
       <c r="J12" s="1" t="n">
+        <v>36.561</v>
+      </c>
+      <c r="K12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -885,10 +924,13 @@
         <v>213.29</v>
       </c>
       <c r="I13" s="1" t="n">
+        <v>212.33</v>
+      </c>
+      <c r="J13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="J13" s="1" t="n">
-        <v>212.79</v>
+      <c r="K13" s="1" t="n">
+        <v>212.33</v>
       </c>
     </row>
     <row r="14">
@@ -919,10 +961,13 @@
         <v>0.0011193</v>
       </c>
       <c r="I14" s="1" t="n">
+        <v>0.0011153</v>
+      </c>
+      <c r="J14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="J14" s="1" t="n">
-        <v>0.0011193</v>
+      <c r="K14" s="1" t="n">
+        <v>0.0011153</v>
       </c>
     </row>
     <row r="15">
@@ -953,9 +998,12 @@
         <v>0.28497</v>
       </c>
       <c r="I15" s="1" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="J15" s="1" t="n">
         <v>0.29276</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="K15" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -987,9 +1035,12 @@
         <v>234.49</v>
       </c>
       <c r="I16" s="1" t="n">
+        <v>233.64</v>
+      </c>
+      <c r="J16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="K16" s="1" t="n">
         <v>230.3</v>
       </c>
     </row>
@@ -1021,10 +1072,13 @@
         <v>1.0027</v>
       </c>
       <c r="I17" s="1" t="n">
+        <v>0.9963</v>
+      </c>
+      <c r="J17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="J17" s="1" t="n">
-        <v>1.0027</v>
+      <c r="K17" s="1" t="n">
+        <v>0.9963</v>
       </c>
     </row>
     <row r="18">
@@ -1055,10 +1109,13 @@
         <v>0.2697</v>
       </c>
       <c r="I18" s="1" t="n">
+        <v>0.2681</v>
+      </c>
+      <c r="J18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="J18" s="1" t="n">
-        <v>0.2697</v>
+      <c r="K18" s="1" t="n">
+        <v>0.2681</v>
       </c>
     </row>
     <row r="19">
@@ -1089,10 +1146,13 @@
         <v>9.834</v>
       </c>
       <c r="I19" s="1" t="n">
+        <v>9.773</v>
+      </c>
+      <c r="J19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="J19" s="1" t="n">
-        <v>9.834</v>
+      <c r="K19" s="1" t="n">
+        <v>9.773</v>
       </c>
     </row>
     <row r="20">
@@ -1123,9 +1183,12 @@
         <v>5059.14</v>
       </c>
       <c r="I20" s="1" t="n">
+        <v>5056.39</v>
+      </c>
+      <c r="J20" s="1" t="n">
         <v>5059.14</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="K20" s="1" t="n">
         <v>5033.31</v>
       </c>
     </row>
@@ -1157,10 +1220,13 @@
         <v>463.47</v>
       </c>
       <c r="I21" s="1" t="n">
+        <v>462.45</v>
+      </c>
+      <c r="J21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="J21" s="1" t="n">
-        <v>462.57</v>
+      <c r="K21" s="1" t="n">
+        <v>462.45</v>
       </c>
     </row>
     <row r="22">
@@ -1191,9 +1257,12 @@
         <v>1.4444</v>
       </c>
       <c r="I22" s="1" t="n">
+        <v>1.4445</v>
+      </c>
+      <c r="J22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="K22" s="1" t="n">
         <v>1.4185</v>
       </c>
     </row>
@@ -1225,9 +1294,12 @@
         <v>1.0691</v>
       </c>
       <c r="I23" s="1" t="n">
+        <v>1.0792</v>
+      </c>
+      <c r="J23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="K23" s="1" t="n">
         <v>1.0691</v>
       </c>
     </row>
@@ -1259,10 +1331,13 @@
         <v>1.36</v>
       </c>
       <c r="I24" s="1" t="n">
+        <v>1.349</v>
+      </c>
+      <c r="J24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="J24" s="1" t="n">
-        <v>1.351</v>
+      <c r="K24" s="1" t="n">
+        <v>1.349</v>
       </c>
     </row>
     <row r="25">
@@ -1293,10 +1368,13 @@
         <v>9.223000000000001</v>
       </c>
       <c r="I25" s="1" t="n">
+        <v>9.153</v>
+      </c>
+      <c r="J25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="J25" s="1" t="n">
-        <v>9.223000000000001</v>
+      <c r="K25" s="1" t="n">
+        <v>9.153</v>
       </c>
     </row>
     <row r="26">
@@ -1327,9 +1405,12 @@
         <v>0.3742</v>
       </c>
       <c r="I26" s="1" t="n">
+        <v>0.3734</v>
+      </c>
+      <c r="J26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="K26" s="1" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -1361,10 +1442,13 @@
         <v>0.887</v>
       </c>
       <c r="I27" s="1" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="J27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="J27" s="1" t="n">
-        <v>0.887</v>
+      <c r="K27" s="1" t="n">
+        <v>0.877</v>
       </c>
     </row>
     <row r="28">
@@ -1395,9 +1479,12 @@
         <v>1.807</v>
       </c>
       <c r="I28" s="1" t="n">
+        <v>1.796</v>
+      </c>
+      <c r="J28" s="1" t="n">
         <v>1.823</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="K28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -1429,10 +1516,13 @@
         <v>0.1111</v>
       </c>
       <c r="I29" s="1" t="n">
+        <v>0.1102</v>
+      </c>
+      <c r="J29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="J29" s="1" t="n">
-        <v>0.1111</v>
+      <c r="K29" s="1" t="n">
+        <v>0.1102</v>
       </c>
     </row>
     <row r="30">
@@ -1463,10 +1553,13 @@
         <v>0.002052</v>
       </c>
       <c r="I30" s="1" t="n">
+        <v>0.002045</v>
+      </c>
+      <c r="J30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="J30" s="1" t="n">
-        <v>0.002052</v>
+      <c r="K30" s="1" t="n">
+        <v>0.002045</v>
       </c>
     </row>
     <row r="31">
@@ -1497,10 +1590,13 @@
         <v>1.493</v>
       </c>
       <c r="I31" s="1" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="J31" s="1" t="n">
-        <v>1.493</v>
+      <c r="K31" s="1" t="n">
+        <v>1.48</v>
       </c>
     </row>
     <row r="32">
@@ -1531,10 +1627,13 @@
         <v>0.175</v>
       </c>
       <c r="I32" s="1" t="n">
+        <v>0.1739</v>
+      </c>
+      <c r="J32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="J32" s="1" t="n">
-        <v>0.175</v>
+      <c r="K32" s="1" t="n">
+        <v>0.1739</v>
       </c>
     </row>
     <row r="33">
@@ -1565,10 +1664,13 @@
         <v>0.1048</v>
       </c>
       <c r="I33" s="1" t="n">
+        <v>0.1042</v>
+      </c>
+      <c r="J33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="J33" s="1" t="n">
-        <v>0.1045</v>
+      <c r="K33" s="1" t="n">
+        <v>0.1042</v>
       </c>
     </row>
     <row r="34">
@@ -1599,10 +1701,13 @@
         <v>113.73</v>
       </c>
       <c r="I34" s="1" t="n">
+        <v>113.01</v>
+      </c>
+      <c r="J34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="J34" s="1" t="n">
-        <v>113.65</v>
+      <c r="K34" s="1" t="n">
+        <v>113.01</v>
       </c>
     </row>
     <row r="35">
@@ -1633,10 +1738,13 @@
         <v>6.766</v>
       </c>
       <c r="I35" s="1" t="n">
+        <v>6.764</v>
+      </c>
+      <c r="J35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="J35" s="1" t="n">
-        <v>6.766</v>
+      <c r="K35" s="1" t="n">
+        <v>6.764</v>
       </c>
     </row>
     <row r="36">
@@ -1667,10 +1775,13 @@
         <v>0.016866</v>
       </c>
       <c r="I36" s="1" t="n">
+        <v>0.016815</v>
+      </c>
+      <c r="J36" s="1" t="n">
         <v>0.017421</v>
       </c>
-      <c r="J36" s="1" t="n">
-        <v>0.016866</v>
+      <c r="K36" s="1" t="n">
+        <v>0.016815</v>
       </c>
     </row>
     <row r="37">
@@ -1701,10 +1812,13 @@
         <v>0.3638</v>
       </c>
       <c r="I37" s="1" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="J37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="J37" s="1" t="n">
-        <v>0.3638</v>
+      <c r="K37" s="1" t="n">
+        <v>0.361</v>
       </c>
     </row>
     <row r="38">
@@ -1735,9 +1849,12 @@
         <v>55.6</v>
       </c>
       <c r="I38" s="1" t="n">
+        <v>55.32</v>
+      </c>
+      <c r="J38" s="1" t="n">
         <v>55.79</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="K38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -1769,9 +1886,12 @@
         <v>0.59182</v>
       </c>
       <c r="I39" s="1" t="n">
-        <v>0.59815</v>
+        <v>0.59932</v>
       </c>
       <c r="J39" s="1" t="n">
+        <v>0.59932</v>
+      </c>
+      <c r="K39" s="1" t="n">
         <v>0.58131</v>
       </c>
     </row>
@@ -1803,10 +1923,13 @@
         <v>4.064</v>
       </c>
       <c r="I40" s="1" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="J40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="J40" s="1" t="n">
-        <v>4.051</v>
+      <c r="K40" s="1" t="n">
+        <v>4.038</v>
       </c>
     </row>
     <row r="41">
@@ -1837,9 +1960,12 @@
         <v>0.0499</v>
       </c>
       <c r="I41" s="1" t="n">
-        <v>0.0499</v>
+        <v>0.05015</v>
       </c>
       <c r="J41" s="1" t="n">
+        <v>0.05015</v>
+      </c>
+      <c r="K41" s="1" t="n">
         <v>0.04927</v>
       </c>
     </row>
@@ -1871,10 +1997,13 @@
         <v>0.7014</v>
       </c>
       <c r="I42" s="1" t="n">
+        <v>0.7006</v>
+      </c>
+      <c r="J42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="J42" s="1" t="n">
-        <v>0.7014</v>
+      <c r="K42" s="1" t="n">
+        <v>0.7006</v>
       </c>
     </row>
     <row r="43">
@@ -1905,10 +2034,13 @@
         <v>0.23357</v>
       </c>
       <c r="I43" s="1" t="n">
+        <v>0.23214</v>
+      </c>
+      <c r="J43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="J43" s="1" t="n">
-        <v>0.23323</v>
+      <c r="K43" s="1" t="n">
+        <v>0.23214</v>
       </c>
     </row>
     <row r="44">
@@ -1939,9 +2071,12 @@
         <v>0.35416</v>
       </c>
       <c r="I44" s="1" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="J44" s="1" t="n">
         <v>0.35416</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="K44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -1973,10 +2108,13 @@
         <v>0.1713</v>
       </c>
       <c r="I45" s="1" t="n">
+        <v>0.1699</v>
+      </c>
+      <c r="J45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="J45" s="1" t="n">
-        <v>0.1713</v>
+      <c r="K45" s="1" t="n">
+        <v>0.1699</v>
       </c>
     </row>
     <row r="46">
@@ -2007,9 +2145,12 @@
         <v>0.0262</v>
       </c>
       <c r="I46" s="1" t="n">
+        <v>0.0263</v>
+      </c>
+      <c r="J46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="K46" s="1" t="n">
         <v>0.0262</v>
       </c>
     </row>
@@ -2041,10 +2182,13 @@
         <v>0.005998</v>
       </c>
       <c r="I47" s="1" t="n">
+        <v>0.005968</v>
+      </c>
+      <c r="J47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="J47" s="1" t="n">
-        <v>0.005998</v>
+      <c r="K47" s="1" t="n">
+        <v>0.005968</v>
       </c>
     </row>
     <row r="48">
@@ -2075,10 +2219,13 @@
         <v>0.007417</v>
       </c>
       <c r="I48" s="1" t="n">
+        <v>0.007349</v>
+      </c>
+      <c r="J48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="J48" s="1" t="n">
-        <v>0.007417</v>
+      <c r="K48" s="1" t="n">
+        <v>0.007349</v>
       </c>
     </row>
     <row r="49">
@@ -2109,10 +2256,13 @@
         <v>0.1087</v>
       </c>
       <c r="I49" s="1" t="n">
+        <v>0.1078</v>
+      </c>
+      <c r="J49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="J49" s="1" t="n">
-        <v>0.1087</v>
+      <c r="K49" s="1" t="n">
+        <v>0.1078</v>
       </c>
     </row>
     <row r="50">
@@ -2143,9 +2293,12 @@
         <v>0.04048</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>0.04048</v>
+        <v>0.04068</v>
       </c>
       <c r="J50" s="1" t="n">
+        <v>0.04068</v>
+      </c>
+      <c r="K50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -2177,10 +2330,13 @@
         <v>0.1633</v>
       </c>
       <c r="I51" s="1" t="n">
+        <v>0.1617</v>
+      </c>
+      <c r="J51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="J51" s="1" t="n">
-        <v>0.1633</v>
+      <c r="K51" s="1" t="n">
+        <v>0.1617</v>
       </c>
     </row>
     <row r="52">
@@ -2211,10 +2367,13 @@
         <v>0.00353</v>
       </c>
       <c r="I52" s="1" t="n">
+        <v>0.00351</v>
+      </c>
+      <c r="J52" s="1" t="n">
         <v>0.00357</v>
       </c>
-      <c r="J52" s="1" t="n">
-        <v>0.00353</v>
+      <c r="K52" s="1" t="n">
+        <v>0.00351</v>
       </c>
     </row>
     <row r="53">
@@ -2245,10 +2404,13 @@
         <v>2.631</v>
       </c>
       <c r="I53" s="1" t="n">
+        <v>2.622</v>
+      </c>
+      <c r="J53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="J53" s="1" t="n">
-        <v>2.631</v>
+      <c r="K53" s="1" t="n">
+        <v>2.622</v>
       </c>
     </row>
     <row r="54">
@@ -2279,10 +2441,13 @@
         <v>0.006242</v>
       </c>
       <c r="I54" s="1" t="n">
+        <v>0.006191</v>
+      </c>
+      <c r="J54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="J54" s="1" t="n">
-        <v>0.006242</v>
+      <c r="K54" s="1" t="n">
+        <v>0.006191</v>
       </c>
     </row>
     <row r="55">
@@ -2313,9 +2478,12 @@
         <v>0.02879</v>
       </c>
       <c r="I55" s="1" t="n">
+        <v>0.02955</v>
+      </c>
+      <c r="J55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="K55" s="1" t="n">
         <v>0.02879</v>
       </c>
     </row>
@@ -2347,10 +2515,13 @@
         <v>0.7415</v>
       </c>
       <c r="I56" s="1" t="n">
+        <v>0.7352</v>
+      </c>
+      <c r="J56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="J56" s="1" t="n">
-        <v>0.7415</v>
+      <c r="K56" s="1" t="n">
+        <v>0.7352</v>
       </c>
     </row>
     <row r="57">
@@ -2381,10 +2552,13 @@
         <v>0.104</v>
       </c>
       <c r="I57" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="J57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="J57" s="1" t="n">
-        <v>0.104</v>
+      <c r="K57" s="1" t="n">
+        <v>0.1034</v>
       </c>
     </row>
     <row r="58">
@@ -2415,10 +2589,13 @@
         <v>0.9476</v>
       </c>
       <c r="I58" s="1" t="n">
+        <v>0.9374</v>
+      </c>
+      <c r="J58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="J58" s="1" t="n">
-        <v>0.9476</v>
+      <c r="K58" s="1" t="n">
+        <v>0.9374</v>
       </c>
     </row>
     <row r="59">
@@ -2449,9 +2626,12 @@
         <v>0.08704000000000001</v>
       </c>
       <c r="I59" s="1" t="n">
+        <v>0.08645</v>
+      </c>
+      <c r="J59" s="1" t="n">
         <v>0.08704000000000001</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="K59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -2483,9 +2663,12 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="I60" s="1" t="n">
+        <v>0.06929</v>
+      </c>
+      <c r="J60" s="1" t="n">
         <v>0.07001</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="K60" s="1" t="n">
         <v>0.06924</v>
       </c>
     </row>
@@ -2517,10 +2700,13 @@
         <v>0.05482</v>
       </c>
       <c r="I61" s="1" t="n">
+        <v>0.05445</v>
+      </c>
+      <c r="J61" s="1" t="n">
         <v>0.05523</v>
       </c>
-      <c r="J61" s="1" t="n">
-        <v>0.05469</v>
+      <c r="K61" s="1" t="n">
+        <v>0.05445</v>
       </c>
     </row>
     <row r="62">
@@ -2551,9 +2737,12 @@
         <v>0.009387</v>
       </c>
       <c r="I62" s="1" t="n">
+        <v>0.009516999999999999</v>
+      </c>
+      <c r="J62" s="1" t="n">
         <v>0.010194</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="K62" s="1" t="n">
         <v>0.009387</v>
       </c>
     </row>
@@ -2585,9 +2774,12 @@
         <v>0.29032</v>
       </c>
       <c r="I63" s="1" t="n">
+        <v>0.29028</v>
+      </c>
+      <c r="J63" s="1" t="n">
         <v>0.29032</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="K63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -2619,9 +2811,12 @@
         <v>0.07489</v>
       </c>
       <c r="I64" s="1" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="J64" s="1" t="n">
         <v>0.07489</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="K64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -2653,9 +2848,12 @@
         <v>0.3155</v>
       </c>
       <c r="I65" s="1" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="J65" s="1" t="n">
         <v>0.3155</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="K65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -2687,10 +2885,13 @@
         <v>0.16324</v>
       </c>
       <c r="I66" s="1" t="n">
+        <v>0.16242</v>
+      </c>
+      <c r="J66" s="1" t="n">
         <v>0.16461</v>
       </c>
-      <c r="J66" s="1" t="n">
-        <v>0.16324</v>
+      <c r="K66" s="1" t="n">
+        <v>0.16242</v>
       </c>
     </row>
     <row r="67">
@@ -2721,9 +2922,12 @@
         <v>0.11919</v>
       </c>
       <c r="I67" s="1" t="n">
-        <v>0.11997</v>
+        <v>0.11999</v>
       </c>
       <c r="J67" s="1" t="n">
+        <v>0.11999</v>
+      </c>
+      <c r="K67" s="1" t="n">
         <v>0.11919</v>
       </c>
     </row>
@@ -2755,10 +2959,13 @@
         <v>0.09637999999999999</v>
       </c>
       <c r="I68" s="1" t="n">
+        <v>0.09548</v>
+      </c>
+      <c r="J68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="J68" s="1" t="n">
-        <v>0.09637999999999999</v>
+      <c r="K68" s="1" t="n">
+        <v>0.09548</v>
       </c>
     </row>
     <row r="69">
@@ -2789,10 +2996,13 @@
         <v>0.1248</v>
       </c>
       <c r="I69" s="1" t="n">
+        <v>0.1239</v>
+      </c>
+      <c r="J69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="J69" s="1" t="n">
-        <v>0.1247</v>
+      <c r="K69" s="1" t="n">
+        <v>0.1239</v>
       </c>
     </row>
     <row r="70">
@@ -2823,10 +3033,13 @@
         <v>8.564</v>
       </c>
       <c r="I70" s="1" t="n">
+        <v>8.502000000000001</v>
+      </c>
+      <c r="J70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="J70" s="1" t="n">
-        <v>8.550000000000001</v>
+      <c r="K70" s="1" t="n">
+        <v>8.502000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -2857,9 +3070,12 @@
         <v>0.238</v>
       </c>
       <c r="I71" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="J71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="K71" s="1" t="n">
         <v>0.238</v>
       </c>
     </row>
@@ -2891,10 +3107,13 @@
         <v>0.05056</v>
       </c>
       <c r="I72" s="1" t="n">
+        <v>0.0504</v>
+      </c>
+      <c r="J72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="J72" s="1" t="n">
-        <v>0.05056</v>
+      <c r="K72" s="1" t="n">
+        <v>0.0504</v>
       </c>
     </row>
     <row r="73">
@@ -2925,9 +3144,12 @@
         <v>0.05089</v>
       </c>
       <c r="I73" s="1" t="n">
+        <v>0.05062</v>
+      </c>
+      <c r="J73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="K73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -2959,9 +3181,12 @@
         <v>0.1263</v>
       </c>
       <c r="I74" s="1" t="n">
+        <v>0.1253</v>
+      </c>
+      <c r="J74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="J74" s="1" t="n">
+      <c r="K74" s="1" t="n">
         <v>0.1252</v>
       </c>
     </row>
@@ -2993,10 +3218,13 @@
         <v>0.0465</v>
       </c>
       <c r="I75" s="1" t="n">
+        <v>0.04621</v>
+      </c>
+      <c r="J75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="J75" s="1" t="n">
-        <v>0.0465</v>
+      <c r="K75" s="1" t="n">
+        <v>0.04621</v>
       </c>
     </row>
     <row r="76">
@@ -3027,10 +3255,13 @@
         <v>0.06743</v>
       </c>
       <c r="I76" s="1" t="n">
+        <v>0.06741</v>
+      </c>
+      <c r="J76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="J76" s="1" t="n">
-        <v>0.06743</v>
+      <c r="K76" s="1" t="n">
+        <v>0.06741</v>
       </c>
     </row>
     <row r="77">
@@ -3061,10 +3292,13 @@
         <v>0.12766</v>
       </c>
       <c r="I77" s="1" t="n">
+        <v>0.12654</v>
+      </c>
+      <c r="J77" s="1" t="n">
         <v>0.12881</v>
       </c>
-      <c r="J77" s="1" t="n">
-        <v>0.12685</v>
+      <c r="K77" s="1" t="n">
+        <v>0.12654</v>
       </c>
     </row>
     <row r="78">
@@ -3095,10 +3329,13 @@
         <v>0.1629</v>
       </c>
       <c r="I78" s="1" t="n">
+        <v>0.1613</v>
+      </c>
+      <c r="J78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="J78" s="1" t="n">
-        <v>0.1624</v>
+      <c r="K78" s="1" t="n">
+        <v>0.1613</v>
       </c>
     </row>
     <row r="79">
@@ -3129,10 +3366,13 @@
         <v>0.02738</v>
       </c>
       <c r="I79" s="1" t="n">
+        <v>0.02719</v>
+      </c>
+      <c r="J79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="J79" s="1" t="n">
-        <v>0.0272</v>
+      <c r="K79" s="1" t="n">
+        <v>0.02719</v>
       </c>
     </row>
     <row r="80">
@@ -3163,9 +3403,12 @@
         <v>355.17</v>
       </c>
       <c r="I80" s="1" t="n">
-        <v>356.25</v>
+        <v>357.15</v>
       </c>
       <c r="J80" s="1" t="n">
+        <v>357.15</v>
+      </c>
+      <c r="K80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -3197,10 +3440,13 @@
         <v>7.142e-05</v>
       </c>
       <c r="I81" s="1" t="n">
+        <v>7.080999999999999e-05</v>
+      </c>
+      <c r="J81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="J81" s="1" t="n">
-        <v>7.142e-05</v>
+      <c r="K81" s="1" t="n">
+        <v>7.080999999999999e-05</v>
       </c>
     </row>
     <row r="82">
@@ -3231,10 +3477,13 @@
         <v>0.2668</v>
       </c>
       <c r="I82" s="1" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="J82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="J82" s="1" t="n">
-        <v>0.2668</v>
+      <c r="K82" s="1" t="n">
+        <v>0.2645</v>
       </c>
     </row>
     <row r="83">
@@ -3265,10 +3514,13 @@
         <v>1.1435</v>
       </c>
       <c r="I83" s="1" t="n">
+        <v>1.1379</v>
+      </c>
+      <c r="J83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="J83" s="1" t="n">
-        <v>1.1408</v>
+      <c r="K83" s="1" t="n">
+        <v>1.1379</v>
       </c>
     </row>
     <row r="84">
@@ -3299,10 +3551,13 @@
         <v>0.3587</v>
       </c>
       <c r="I84" s="1" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="J84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="J84" s="1" t="n">
-        <v>0.3569</v>
+      <c r="K84" s="1" t="n">
+        <v>0.3543</v>
       </c>
     </row>
     <row r="85">
@@ -3333,9 +3588,12 @@
         <v>2.0252</v>
       </c>
       <c r="I85" s="1" t="n">
+        <v>2.0149</v>
+      </c>
+      <c r="J85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="J85" s="1" t="n">
+      <c r="K85" s="1" t="n">
         <v>2.0067</v>
       </c>
     </row>
@@ -3367,9 +3625,12 @@
         <v>1.3132</v>
       </c>
       <c r="I86" s="1" t="n">
+        <v>1.3126</v>
+      </c>
+      <c r="J86" s="1" t="n">
         <v>1.3167</v>
       </c>
-      <c r="J86" s="1" t="n">
+      <c r="K86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -3401,10 +3662,13 @@
         <v>32.88</v>
       </c>
       <c r="I87" s="1" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="J87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="J87" s="1" t="n">
-        <v>32.88</v>
+      <c r="K87" s="1" t="n">
+        <v>32.73</v>
       </c>
     </row>
     <row r="88">
@@ -3435,10 +3699,13 @@
         <v>0.01002</v>
       </c>
       <c r="I88" s="1" t="n">
+        <v>0.009690000000000001</v>
+      </c>
+      <c r="J88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="J88" s="1" t="n">
-        <v>0.01002</v>
+      <c r="K88" s="1" t="n">
+        <v>0.009690000000000001</v>
       </c>
     </row>
     <row r="89">
@@ -3469,9 +3736,12 @@
         <v>0.0184</v>
       </c>
       <c r="I89" s="1" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="J89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="J89" s="1" t="n">
+      <c r="K89" s="1" t="n">
         <v>0.01828</v>
       </c>
     </row>
@@ -3503,10 +3773,13 @@
         <v>0.03577</v>
       </c>
       <c r="I90" s="1" t="n">
+        <v>0.03548</v>
+      </c>
+      <c r="J90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="J90" s="1" t="n">
-        <v>0.03566</v>
+      <c r="K90" s="1" t="n">
+        <v>0.03548</v>
       </c>
     </row>
     <row r="91">
@@ -3537,10 +3810,13 @@
         <v>0.01191</v>
       </c>
       <c r="I91" s="1" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="J91" s="1" t="n">
         <v>0.01202</v>
       </c>
-      <c r="J91" s="1" t="n">
-        <v>0.01191</v>
+      <c r="K91" s="1" t="n">
+        <v>0.0118</v>
       </c>
     </row>
     <row r="92">
@@ -3571,10 +3847,13 @@
         <v>3.119</v>
       </c>
       <c r="I92" s="1" t="n">
+        <v>3.097</v>
+      </c>
+      <c r="J92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="J92" s="1" t="n">
-        <v>3.111</v>
+      <c r="K92" s="1" t="n">
+        <v>3.097</v>
       </c>
     </row>
     <row r="93">
@@ -3605,10 +3884,13 @@
         <v>0.005635</v>
       </c>
       <c r="I93" s="1" t="n">
+        <v>0.005596</v>
+      </c>
+      <c r="J93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="J93" s="1" t="n">
-        <v>0.005635</v>
+      <c r="K93" s="1" t="n">
+        <v>0.005596</v>
       </c>
     </row>
     <row r="94">
@@ -3639,10 +3921,13 @@
         <v>0.0936</v>
       </c>
       <c r="I94" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="J94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="J94" s="1" t="n">
-        <v>0.0936</v>
+      <c r="K94" s="1" t="n">
+        <v>0.093</v>
       </c>
     </row>
     <row r="95">
@@ -3673,9 +3958,12 @@
         <v>0.6052999999999999</v>
       </c>
       <c r="I95" s="1" t="n">
+        <v>0.6054</v>
+      </c>
+      <c r="J95" s="1" t="n">
         <v>0.6058</v>
       </c>
-      <c r="J95" s="1" t="n">
+      <c r="K95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -3707,9 +3995,12 @@
         <v>1.28e-05</v>
       </c>
       <c r="I96" s="1" t="n">
+        <v>1.28e-05</v>
+      </c>
+      <c r="J96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="J96" s="1" t="n">
+      <c r="K96" s="1" t="n">
         <v>1.28e-05</v>
       </c>
     </row>
@@ -3741,10 +4032,13 @@
         <v>1.143</v>
       </c>
       <c r="I97" s="1" t="n">
+        <v>1.132</v>
+      </c>
+      <c r="J97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="J97" s="1" t="n">
-        <v>1.136</v>
+      <c r="K97" s="1" t="n">
+        <v>1.132</v>
       </c>
     </row>
     <row r="98">
@@ -3775,10 +4069,13 @@
         <v>0.25366</v>
       </c>
       <c r="I98" s="1" t="n">
+        <v>0.2523</v>
+      </c>
+      <c r="J98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="J98" s="1" t="n">
-        <v>0.25366</v>
+      <c r="K98" s="1" t="n">
+        <v>0.2523</v>
       </c>
     </row>
     <row r="99">
@@ -3809,9 +4106,12 @@
         <v>1.151</v>
       </c>
       <c r="I99" s="1" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="J99" s="1" t="n">
         <v>1.156</v>
       </c>
-      <c r="J99" s="1" t="n">
+      <c r="K99" s="1" t="n">
         <v>1.146</v>
       </c>
     </row>
@@ -3843,10 +4143,13 @@
         <v>1.863</v>
       </c>
       <c r="I100" s="1" t="n">
+        <v>1.852</v>
+      </c>
+      <c r="J100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="J100" s="1" t="n">
-        <v>1.862</v>
+      <c r="K100" s="1" t="n">
+        <v>1.852</v>
       </c>
     </row>
     <row r="101">
@@ -3877,10 +4180,13 @@
         <v>0.01593</v>
       </c>
       <c r="I101" s="1" t="n">
+        <v>0.01587</v>
+      </c>
+      <c r="J101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="J101" s="1" t="n">
-        <v>0.01593</v>
+      <c r="K101" s="1" t="n">
+        <v>0.01587</v>
       </c>
     </row>
     <row r="102">
@@ -3911,9 +4217,12 @@
         <v>0.10398</v>
       </c>
       <c r="I102" s="1" t="n">
+        <v>0.10392</v>
+      </c>
+      <c r="J102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="J102" s="1" t="n">
+      <c r="K102" s="1" t="n">
         <v>0.10353</v>
       </c>
     </row>
@@ -3945,10 +4254,13 @@
         <v>0.000602</v>
       </c>
       <c r="I103" s="1" t="n">
+        <v>0.0005972</v>
+      </c>
+      <c r="J103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="J103" s="1" t="n">
-        <v>0.000602</v>
+      <c r="K103" s="1" t="n">
+        <v>0.0005972</v>
       </c>
     </row>
     <row r="104">
@@ -3979,9 +4291,12 @@
         <v>0.0005743</v>
       </c>
       <c r="I104" s="1" t="n">
+        <v>0.0005734</v>
+      </c>
+      <c r="J104" s="1" t="n">
         <v>0.0005776000000000001</v>
       </c>
-      <c r="J104" s="1" t="n">
+      <c r="K104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -4013,9 +4328,12 @@
         <v>0.003239</v>
       </c>
       <c r="I105" s="1" t="n">
+        <v>0.003244</v>
+      </c>
+      <c r="J105" s="1" t="n">
         <v>0.003257</v>
       </c>
-      <c r="J105" s="1" t="n">
+      <c r="K105" s="1" t="n">
         <v>0.003229</v>
       </c>
     </row>
@@ -4047,10 +4365,13 @@
         <v>2.61</v>
       </c>
       <c r="I106" s="1" t="n">
+        <v>2.587</v>
+      </c>
+      <c r="J106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="J106" s="1" t="n">
-        <v>2.61</v>
+      <c r="K106" s="1" t="n">
+        <v>2.587</v>
       </c>
     </row>
     <row r="107">
@@ -4081,10 +4402,13 @@
         <v>0.1667</v>
       </c>
       <c r="I107" s="1" t="n">
+        <v>0.1654</v>
+      </c>
+      <c r="J107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="J107" s="1" t="n">
-        <v>0.1667</v>
+      <c r="K107" s="1" t="n">
+        <v>0.1654</v>
       </c>
     </row>
     <row r="108">
@@ -4115,10 +4439,13 @@
         <v>0.09607</v>
       </c>
       <c r="I108" s="1" t="n">
+        <v>0.0955</v>
+      </c>
+      <c r="J108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="J108" s="1" t="n">
-        <v>0.09607</v>
+      <c r="K108" s="1" t="n">
+        <v>0.0955</v>
       </c>
     </row>
     <row r="109">
@@ -4149,10 +4476,13 @@
         <v>0.02216</v>
       </c>
       <c r="I109" s="1" t="n">
+        <v>0.02204</v>
+      </c>
+      <c r="J109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="J109" s="1" t="n">
-        <v>0.02216</v>
+      <c r="K109" s="1" t="n">
+        <v>0.02204</v>
       </c>
     </row>
     <row r="110">
@@ -4183,9 +4513,12 @@
         <v>0.2949</v>
       </c>
       <c r="I110" s="1" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="J110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="J110" s="1" t="n">
+      <c r="K110" s="1" t="n">
         <v>0.2913</v>
       </c>
     </row>
@@ -4217,10 +4550,13 @@
         <v>0.05729</v>
       </c>
       <c r="I111" s="1" t="n">
+        <v>0.05665</v>
+      </c>
+      <c r="J111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="J111" s="1" t="n">
-        <v>0.05684</v>
+      <c r="K111" s="1" t="n">
+        <v>0.05665</v>
       </c>
     </row>
     <row r="112">
@@ -4251,10 +4587,13 @@
         <v>0.3026</v>
       </c>
       <c r="I112" s="1" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="J112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="J112" s="1" t="n">
-        <v>0.3026</v>
+      <c r="K112" s="1" t="n">
+        <v>0.3002</v>
       </c>
     </row>
     <row r="113">
@@ -4285,10 +4624,13 @@
         <v>18.71</v>
       </c>
       <c r="I113" s="1" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="J113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="J113" s="1" t="n">
-        <v>18.62</v>
+      <c r="K113" s="1" t="n">
+        <v>18.6</v>
       </c>
     </row>
     <row r="114">
@@ -4319,10 +4661,13 @@
         <v>0.13302</v>
       </c>
       <c r="I114" s="1" t="n">
+        <v>0.13035</v>
+      </c>
+      <c r="J114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="J114" s="1" t="n">
-        <v>0.13225</v>
+      <c r="K114" s="1" t="n">
+        <v>0.13035</v>
       </c>
     </row>
     <row r="115">
@@ -4353,9 +4698,12 @@
         <v>0.0155</v>
       </c>
       <c r="I115" s="1" t="n">
+        <v>0.01557</v>
+      </c>
+      <c r="J115" s="1" t="n">
         <v>0.01583</v>
       </c>
-      <c r="J115" s="1" t="n">
+      <c r="K115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -4387,10 +4735,13 @@
         <v>0.08529</v>
       </c>
       <c r="I116" s="1" t="n">
+        <v>0.08472</v>
+      </c>
+      <c r="J116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="J116" s="1" t="n">
-        <v>0.08527</v>
+      <c r="K116" s="1" t="n">
+        <v>0.08472</v>
       </c>
     </row>
     <row r="117">
@@ -4421,9 +4772,12 @@
         <v>0.047711</v>
       </c>
       <c r="I117" s="1" t="n">
+        <v>0.048525</v>
+      </c>
+      <c r="J117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="J117" s="1" t="n">
+      <c r="K117" s="1" t="n">
         <v>0.047711</v>
       </c>
     </row>
@@ -4455,10 +4809,13 @@
         <v>0.04771</v>
       </c>
       <c r="I118" s="1" t="n">
+        <v>0.04737</v>
+      </c>
+      <c r="J118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="J118" s="1" t="n">
-        <v>0.04771</v>
+      <c r="K118" s="1" t="n">
+        <v>0.04737</v>
       </c>
     </row>
     <row r="119">
@@ -4489,9 +4846,12 @@
         <v>0.04153</v>
       </c>
       <c r="I119" s="1" t="n">
+        <v>0.04175</v>
+      </c>
+      <c r="J119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="J119" s="1" t="n">
+      <c r="K119" s="1" t="n">
         <v>0.04109</v>
       </c>
     </row>
@@ -4523,9 +4883,12 @@
         <v>0.14658</v>
       </c>
       <c r="I120" s="1" t="n">
+        <v>0.14531</v>
+      </c>
+      <c r="J120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="J120" s="1" t="n">
+      <c r="K120" s="1" t="n">
         <v>0.14499</v>
       </c>
     </row>
@@ -4557,9 +4920,12 @@
         <v>0.1278</v>
       </c>
       <c r="I121" s="1" t="n">
+        <v>0.1274</v>
+      </c>
+      <c r="J121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="J121" s="1" t="n">
+      <c r="K121" s="1" t="n">
         <v>0.1272</v>
       </c>
     </row>
@@ -4591,10 +4957,13 @@
         <v>1.883</v>
       </c>
       <c r="I122" s="1" t="n">
+        <v>1.873</v>
+      </c>
+      <c r="J122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="J122" s="1" t="n">
-        <v>1.883</v>
+      <c r="K122" s="1" t="n">
+        <v>1.873</v>
       </c>
     </row>
     <row r="123">
@@ -4625,10 +4994,13 @@
         <v>0.03028</v>
       </c>
       <c r="I123" s="1" t="n">
+        <v>0.03013</v>
+      </c>
+      <c r="J123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="J123" s="1" t="n">
-        <v>0.03028</v>
+      <c r="K123" s="1" t="n">
+        <v>0.03013</v>
       </c>
     </row>
     <row r="124">
@@ -4659,10 +5031,13 @@
         <v>0.13279</v>
       </c>
       <c r="I124" s="1" t="n">
+        <v>0.13211</v>
+      </c>
+      <c r="J124" s="1" t="n">
         <v>0.13401</v>
       </c>
-      <c r="J124" s="1" t="n">
-        <v>0.13279</v>
+      <c r="K124" s="1" t="n">
+        <v>0.13211</v>
       </c>
     </row>
     <row r="125">
@@ -4693,10 +5068,13 @@
         <v>0.04121</v>
       </c>
       <c r="I125" s="1" t="n">
+        <v>0.04095</v>
+      </c>
+      <c r="J125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="J125" s="1" t="n">
-        <v>0.04121</v>
+      <c r="K125" s="1" t="n">
+        <v>0.04095</v>
       </c>
     </row>
     <row r="126">
@@ -4727,10 +5105,13 @@
         <v>0.1156</v>
       </c>
       <c r="I126" s="1" t="n">
+        <v>0.1151</v>
+      </c>
+      <c r="J126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="J126" s="1" t="n">
-        <v>0.1154</v>
+      <c r="K126" s="1" t="n">
+        <v>0.1151</v>
       </c>
     </row>
     <row r="127">
@@ -4761,9 +5142,12 @@
         <v>0.5026</v>
       </c>
       <c r="I127" s="1" t="n">
+        <v>0.5017</v>
+      </c>
+      <c r="J127" s="1" t="n">
         <v>0.5046</v>
       </c>
-      <c r="J127" s="1" t="n">
+      <c r="K127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -4795,9 +5179,12 @@
         <v>0.03804</v>
       </c>
       <c r="I128" s="1" t="n">
+        <v>0.03792</v>
+      </c>
+      <c r="J128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="J128" s="1" t="n">
+      <c r="K128" s="1" t="n">
         <v>0.03787</v>
       </c>
     </row>
@@ -4829,10 +5216,13 @@
         <v>0.795</v>
       </c>
       <c r="I129" s="1" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="J129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="J129" s="1" t="n">
-        <v>0.795</v>
+      <c r="K129" s="1" t="n">
+        <v>0.792</v>
       </c>
     </row>
     <row r="130">
@@ -4863,9 +5253,12 @@
         <v>0.03422</v>
       </c>
       <c r="I130" s="1" t="n">
+        <v>0.03423</v>
+      </c>
+      <c r="J130" s="1" t="n">
         <v>0.03458</v>
       </c>
-      <c r="J130" s="1" t="n">
+      <c r="K130" s="1" t="n">
         <v>0.03422</v>
       </c>
     </row>
@@ -4897,9 +5290,12 @@
         <v>0.4213</v>
       </c>
       <c r="I131" s="1" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="J131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="J131" s="1" t="n">
+      <c r="K131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -4931,10 +5327,13 @@
         <v>0.04379</v>
       </c>
       <c r="I132" s="1" t="n">
+        <v>0.04354</v>
+      </c>
+      <c r="J132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="J132" s="1" t="n">
-        <v>0.04361</v>
+      <c r="K132" s="1" t="n">
+        <v>0.04354</v>
       </c>
     </row>
     <row r="133">
@@ -4965,10 +5364,13 @@
         <v>1.2942</v>
       </c>
       <c r="I133" s="1" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="J133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="J133" s="1" t="n">
-        <v>1.2941</v>
+      <c r="K133" s="1" t="n">
+        <v>1.282</v>
       </c>
     </row>
     <row r="134">
@@ -4999,10 +5401,13 @@
         <v>0.02197</v>
       </c>
       <c r="I134" s="1" t="n">
+        <v>0.02184</v>
+      </c>
+      <c r="J134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="J134" s="1" t="n">
-        <v>0.02197</v>
+      <c r="K134" s="1" t="n">
+        <v>0.02184</v>
       </c>
     </row>
     <row r="135">
@@ -5033,10 +5438,13 @@
         <v>0.0004626</v>
       </c>
       <c r="I135" s="1" t="n">
+        <v>0.0004592</v>
+      </c>
+      <c r="J135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="J135" s="1" t="n">
-        <v>0.0004626</v>
+      <c r="K135" s="1" t="n">
+        <v>0.0004592</v>
       </c>
     </row>
     <row r="136">
@@ -5067,10 +5475,13 @@
         <v>0.001915</v>
       </c>
       <c r="I136" s="1" t="n">
+        <v>0.001908</v>
+      </c>
+      <c r="J136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="J136" s="1" t="n">
-        <v>0.001913</v>
+      <c r="K136" s="1" t="n">
+        <v>0.001908</v>
       </c>
     </row>
     <row r="137">
@@ -5101,10 +5512,13 @@
         <v>0.3208</v>
       </c>
       <c r="I137" s="1" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="J137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="J137" s="1" t="n">
-        <v>0.3204</v>
+      <c r="K137" s="1" t="n">
+        <v>0.3177</v>
       </c>
     </row>
     <row r="138">
@@ -5135,10 +5549,13 @@
         <v>0.5724</v>
       </c>
       <c r="I138" s="1" t="n">
+        <v>0.5703</v>
+      </c>
+      <c r="J138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="J138" s="1" t="n">
-        <v>0.5705</v>
+      <c r="K138" s="1" t="n">
+        <v>0.5703</v>
       </c>
     </row>
     <row r="139">
@@ -5169,10 +5586,13 @@
         <v>0.02142</v>
       </c>
       <c r="I139" s="1" t="n">
+        <v>0.02136</v>
+      </c>
+      <c r="J139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="J139" s="1" t="n">
-        <v>0.02142</v>
+      <c r="K139" s="1" t="n">
+        <v>0.02136</v>
       </c>
     </row>
     <row r="140">
@@ -5203,10 +5623,13 @@
         <v>0.08058</v>
       </c>
       <c r="I140" s="1" t="n">
+        <v>0.0805</v>
+      </c>
+      <c r="J140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="J140" s="1" t="n">
-        <v>0.08058</v>
+      <c r="K140" s="1" t="n">
+        <v>0.0805</v>
       </c>
     </row>
     <row r="141">
@@ -5237,9 +5660,12 @@
         <v>0.001656</v>
       </c>
       <c r="I141" s="1" t="n">
-        <v>0.001656</v>
+        <v>0.001672</v>
       </c>
       <c r="J141" s="1" t="n">
+        <v>0.001672</v>
+      </c>
+      <c r="K141" s="1" t="n">
         <v>0.001616</v>
       </c>
     </row>
@@ -5271,9 +5697,12 @@
         <v>0.4263</v>
       </c>
       <c r="I142" s="1" t="n">
-        <v>0.4276</v>
+        <v>0.4289</v>
       </c>
       <c r="J142" s="1" t="n">
+        <v>0.4289</v>
+      </c>
+      <c r="K142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -5305,9 +5734,12 @@
         <v>0.030184</v>
       </c>
       <c r="I143" s="1" t="n">
+        <v>0.030208</v>
+      </c>
+      <c r="J143" s="1" t="n">
         <v>0.030681</v>
       </c>
-      <c r="J143" s="1" t="n">
+      <c r="K143" s="1" t="n">
         <v>0.030021</v>
       </c>
     </row>
@@ -5339,9 +5771,12 @@
         <v>0.000224</v>
       </c>
       <c r="I144" s="1" t="n">
+        <v>0.000225</v>
+      </c>
+      <c r="J144" s="1" t="n">
         <v>0.000226</v>
       </c>
-      <c r="J144" s="1" t="n">
+      <c r="K144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -5373,9 +5808,12 @@
         <v>0.03675</v>
       </c>
       <c r="I145" s="1" t="n">
-        <v>0.03675</v>
+        <v>0.03696</v>
       </c>
       <c r="J145" s="1" t="n">
+        <v>0.03696</v>
+      </c>
+      <c r="K145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -5407,9 +5845,12 @@
         <v>0.11567</v>
       </c>
       <c r="I146" s="1" t="n">
+        <v>0.11531</v>
+      </c>
+      <c r="J146" s="1" t="n">
         <v>0.116</v>
       </c>
-      <c r="J146" s="1" t="n">
+      <c r="K146" s="1" t="n">
         <v>0.11518</v>
       </c>
     </row>
@@ -5441,9 +5882,12 @@
         <v>0.02181</v>
       </c>
       <c r="I147" s="1" t="n">
+        <v>0.02175</v>
+      </c>
+      <c r="J147" s="1" t="n">
         <v>0.02198</v>
       </c>
-      <c r="J147" s="1" t="n">
+      <c r="K147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -5475,10 +5919,13 @@
         <v>1.4166</v>
       </c>
       <c r="I148" s="1" t="n">
+        <v>1.4092</v>
+      </c>
+      <c r="J148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="J148" s="1" t="n">
-        <v>1.4154</v>
+      <c r="K148" s="1" t="n">
+        <v>1.4092</v>
       </c>
     </row>
     <row r="149">
@@ -5509,9 +5956,12 @@
         <v>1.8738</v>
       </c>
       <c r="I149" s="1" t="n">
+        <v>1.8656</v>
+      </c>
+      <c r="J149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="J149" s="1" t="n">
+      <c r="K149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -5543,10 +5993,13 @@
         <v>0.099</v>
       </c>
       <c r="I150" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="J150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="J150" s="1" t="n">
-        <v>0.099</v>
+      <c r="K150" s="1" t="n">
+        <v>0.097</v>
       </c>
     </row>
     <row r="151">
@@ -5577,9 +6030,12 @@
         <v>4.623</v>
       </c>
       <c r="I151" s="1" t="n">
+        <v>4.612</v>
+      </c>
+      <c r="J151" s="1" t="n">
         <v>4.623</v>
       </c>
-      <c r="J151" s="1" t="n">
+      <c r="K151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -5611,10 +6067,13 @@
         <v>5.553</v>
       </c>
       <c r="I152" s="1" t="n">
+        <v>5.527</v>
+      </c>
+      <c r="J152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="J152" s="1" t="n">
-        <v>5.55</v>
+      <c r="K152" s="1" t="n">
+        <v>5.527</v>
       </c>
     </row>
     <row r="153">
@@ -5645,10 +6104,13 @@
         <v>0.3212</v>
       </c>
       <c r="I153" s="1" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="J153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="J153" s="1" t="n">
-        <v>0.3178</v>
+      <c r="K153" s="1" t="n">
+        <v>0.3175</v>
       </c>
     </row>
     <row r="154">
@@ -5679,10 +6141,13 @@
         <v>0.5908</v>
       </c>
       <c r="I154" s="1" t="n">
+        <v>0.5877</v>
+      </c>
+      <c r="J154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="J154" s="1" t="n">
-        <v>0.5891999999999999</v>
+      <c r="K154" s="1" t="n">
+        <v>0.5877</v>
       </c>
     </row>
     <row r="155">
@@ -5713,9 +6178,12 @@
         <v>0.01292</v>
       </c>
       <c r="I155" s="1" t="n">
+        <v>0.01287</v>
+      </c>
+      <c r="J155" s="1" t="n">
         <v>0.01292</v>
       </c>
-      <c r="J155" s="1" t="n">
+      <c r="K155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -5747,10 +6215,13 @@
         <v>0.09950000000000001</v>
       </c>
       <c r="I156" s="1" t="n">
+        <v>0.0987</v>
+      </c>
+      <c r="J156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="J156" s="1" t="n">
-        <v>0.09950000000000001</v>
+      <c r="K156" s="1" t="n">
+        <v>0.0987</v>
       </c>
     </row>
     <row r="157">
@@ -5781,10 +6252,13 @@
         <v>16.698</v>
       </c>
       <c r="I157" s="1" t="n">
+        <v>16.538</v>
+      </c>
+      <c r="J157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="J157" s="1" t="n">
-        <v>16.563</v>
+      <c r="K157" s="1" t="n">
+        <v>16.538</v>
       </c>
     </row>
     <row r="158">
@@ -5815,9 +6289,12 @@
         <v>0.05592</v>
       </c>
       <c r="I158" s="1" t="n">
+        <v>0.05542</v>
+      </c>
+      <c r="J158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="J158" s="1" t="n">
+      <c r="K158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -5849,9 +6326,12 @@
         <v>29.13</v>
       </c>
       <c r="I159" s="1" t="n">
+        <v>28.93</v>
+      </c>
+      <c r="J159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="J159" s="1" t="n">
+      <c r="K159" s="1" t="n">
         <v>28.87</v>
       </c>
     </row>
@@ -5883,10 +6363,13 @@
         <v>0.0213</v>
       </c>
       <c r="I160" s="1" t="n">
+        <v>0.02117</v>
+      </c>
+      <c r="J160" s="1" t="n">
         <v>0.02141</v>
       </c>
-      <c r="J160" s="1" t="n">
-        <v>0.02121</v>
+      <c r="K160" s="1" t="n">
+        <v>0.02117</v>
       </c>
     </row>
     <row r="161">
@@ -5917,10 +6400,13 @@
         <v>0.000659</v>
       </c>
       <c r="I161" s="1" t="n">
+        <v>0.0006507</v>
+      </c>
+      <c r="J161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="J161" s="1" t="n">
-        <v>0.000659</v>
+      <c r="K161" s="1" t="n">
+        <v>0.0006507</v>
       </c>
     </row>
     <row r="162">
@@ -5951,10 +6437,13 @@
         <v>0.394</v>
       </c>
       <c r="I162" s="1" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="J162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="J162" s="1" t="n">
-        <v>0.3936</v>
+      <c r="K162" s="1" t="n">
+        <v>0.3922</v>
       </c>
     </row>
     <row r="163">
@@ -5985,10 +6474,13 @@
         <v>0.1945</v>
       </c>
       <c r="I163" s="1" t="n">
+        <v>0.1925</v>
+      </c>
+      <c r="J163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="J163" s="1" t="n">
-        <v>0.1931</v>
+      <c r="K163" s="1" t="n">
+        <v>0.1925</v>
       </c>
     </row>
     <row r="164">
@@ -6019,10 +6511,13 @@
         <v>0.319</v>
       </c>
       <c r="I164" s="1" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="J164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="J164" s="1" t="n">
-        <v>0.319</v>
+      <c r="K164" s="1" t="n">
+        <v>0.317</v>
       </c>
     </row>
     <row r="165">
@@ -6053,10 +6548,13 @@
         <v>0.375</v>
       </c>
       <c r="I165" s="1" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="J165" s="1" t="n">
         <v>0.377</v>
       </c>
-      <c r="J165" s="1" t="n">
-        <v>0.375</v>
+      <c r="K165" s="1" t="n">
+        <v>0.372</v>
       </c>
     </row>
     <row r="166">
@@ -6087,10 +6585,13 @@
         <v>0.02263</v>
       </c>
       <c r="I166" s="1" t="n">
+        <v>0.02258</v>
+      </c>
+      <c r="J166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="J166" s="1" t="n">
-        <v>0.02263</v>
+      <c r="K166" s="1" t="n">
+        <v>0.02258</v>
       </c>
     </row>
     <row r="167">
@@ -6121,10 +6622,13 @@
         <v>0.007343</v>
       </c>
       <c r="I167" s="1" t="n">
+        <v>0.007303</v>
+      </c>
+      <c r="J167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="J167" s="1" t="n">
-        <v>0.007343</v>
+      <c r="K167" s="1" t="n">
+        <v>0.007303</v>
       </c>
     </row>
     <row r="168">
@@ -6155,10 +6659,13 @@
         <v>0.01372</v>
       </c>
       <c r="I168" s="1" t="n">
+        <v>0.01362</v>
+      </c>
+      <c r="J168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="J168" s="1" t="n">
-        <v>0.01372</v>
+      <c r="K168" s="1" t="n">
+        <v>0.01362</v>
       </c>
     </row>
     <row r="169">
@@ -6189,10 +6696,13 @@
         <v>0.25531</v>
       </c>
       <c r="I169" s="1" t="n">
+        <v>0.25175</v>
+      </c>
+      <c r="J169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="J169" s="1" t="n">
-        <v>0.25376</v>
+      <c r="K169" s="1" t="n">
+        <v>0.25175</v>
       </c>
     </row>
     <row r="170">
@@ -6223,9 +6733,12 @@
         <v>0.02169</v>
       </c>
       <c r="I170" s="1" t="n">
+        <v>0.02174</v>
+      </c>
+      <c r="J170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="J170" s="1" t="n">
+      <c r="K170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -6257,10 +6770,13 @@
         <v>0.1758</v>
       </c>
       <c r="I171" s="1" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="J171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="J171" s="1" t="n">
-        <v>0.1733</v>
+      <c r="K171" s="1" t="n">
+        <v>0.1718</v>
       </c>
     </row>
     <row r="172">
@@ -6291,9 +6807,12 @@
         <v>0.089</v>
       </c>
       <c r="I172" s="1" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="J172" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="J172" s="1" t="n">
+      <c r="K172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -6325,10 +6844,13 @@
         <v>0.004706</v>
       </c>
       <c r="I173" s="1" t="n">
+        <v>0.004682</v>
+      </c>
+      <c r="J173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="J173" s="1" t="n">
-        <v>0.004706</v>
+      <c r="K173" s="1" t="n">
+        <v>0.004682</v>
       </c>
     </row>
     <row r="174">
@@ -6359,9 +6881,12 @@
         <v>0.4401</v>
       </c>
       <c r="I174" s="1" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="J174" s="1" t="n">
         <v>0.4423</v>
       </c>
-      <c r="J174" s="1" t="n">
+      <c r="K174" s="1" t="n">
         <v>0.4368</v>
       </c>
     </row>
@@ -6393,10 +6918,13 @@
         <v>0.08978</v>
       </c>
       <c r="I175" s="1" t="n">
+        <v>0.08935999999999999</v>
+      </c>
+      <c r="J175" s="1" t="n">
         <v>0.09021999999999999</v>
       </c>
-      <c r="J175" s="1" t="n">
-        <v>0.0895</v>
+      <c r="K175" s="1" t="n">
+        <v>0.08935999999999999</v>
       </c>
     </row>
     <row r="176">
@@ -6427,9 +6955,12 @@
         <v>0.2464</v>
       </c>
       <c r="I176" s="1" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="J176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="J176" s="1" t="n">
+      <c r="K176" s="1" t="n">
         <v>0.2453</v>
       </c>
     </row>
@@ -6461,10 +6992,13 @@
         <v>0.0192</v>
       </c>
       <c r="I177" s="1" t="n">
+        <v>0.01909</v>
+      </c>
+      <c r="J177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="J177" s="1" t="n">
-        <v>0.01917</v>
+      <c r="K177" s="1" t="n">
+        <v>0.01909</v>
       </c>
     </row>
     <row r="178">
@@ -6495,10 +7029,13 @@
         <v>6.18</v>
       </c>
       <c r="I178" s="1" t="n">
+        <v>6.138</v>
+      </c>
+      <c r="J178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="J178" s="1" t="n">
-        <v>6.18</v>
+      <c r="K178" s="1" t="n">
+        <v>6.138</v>
       </c>
     </row>
     <row r="179">
@@ -6529,9 +7066,12 @@
         <v>0.136</v>
       </c>
       <c r="I179" s="1" t="n">
+        <v>0.1362</v>
+      </c>
+      <c r="J179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="J179" s="1" t="n">
+      <c r="K179" s="1" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -6563,9 +7103,12 @@
         <v>0.005012</v>
       </c>
       <c r="I180" s="1" t="n">
-        <v>0.005093</v>
+        <v>0.005154</v>
       </c>
       <c r="J180" s="1" t="n">
+        <v>0.005154</v>
+      </c>
+      <c r="K180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -6597,9 +7140,12 @@
         <v>0.01194</v>
       </c>
       <c r="I181" s="1" t="n">
+        <v>0.01193</v>
+      </c>
+      <c r="J181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="J181" s="1" t="n">
+      <c r="K181" s="1" t="n">
         <v>0.01189</v>
       </c>
     </row>
@@ -6631,9 +7177,12 @@
         <v>0.00733</v>
       </c>
       <c r="I182" s="1" t="n">
+        <v>0.007353</v>
+      </c>
+      <c r="J182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="J182" s="1" t="n">
+      <c r="K182" s="1" t="n">
         <v>0.007295</v>
       </c>
     </row>
@@ -6665,9 +7214,12 @@
         <v>0.12988</v>
       </c>
       <c r="I183" s="1" t="n">
+        <v>0.12975</v>
+      </c>
+      <c r="J183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="J183" s="1" t="n">
+      <c r="K183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -6699,9 +7251,12 @@
         <v>0.09682</v>
       </c>
       <c r="I184" s="1" t="n">
+        <v>0.09649000000000001</v>
+      </c>
+      <c r="J184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="J184" s="1" t="n">
+      <c r="K184" s="1" t="n">
         <v>0.09587</v>
       </c>
     </row>
@@ -6733,10 +7288,13 @@
         <v>0.00758</v>
       </c>
       <c r="I185" s="1" t="n">
+        <v>0.00755</v>
+      </c>
+      <c r="J185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="J185" s="1" t="n">
-        <v>0.00758</v>
+      <c r="K185" s="1" t="n">
+        <v>0.00755</v>
       </c>
     </row>
     <row r="186">
@@ -6767,10 +7325,13 @@
         <v>0.04894</v>
       </c>
       <c r="I186" s="1" t="n">
+        <v>0.0486</v>
+      </c>
+      <c r="J186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="J186" s="1" t="n">
-        <v>0.04894</v>
+      <c r="K186" s="1" t="n">
+        <v>0.0486</v>
       </c>
     </row>
     <row r="187">
@@ -6801,10 +7362,13 @@
         <v>0.02694</v>
       </c>
       <c r="I187" s="1" t="n">
+        <v>0.02674</v>
+      </c>
+      <c r="J187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="J187" s="1" t="n">
-        <v>0.02686</v>
+      <c r="K187" s="1" t="n">
+        <v>0.02674</v>
       </c>
     </row>
     <row r="188">
@@ -6835,10 +7399,13 @@
         <v>0.00332</v>
       </c>
       <c r="I188" s="1" t="n">
+        <v>0.003303</v>
+      </c>
+      <c r="J188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="J188" s="1" t="n">
-        <v>0.00332</v>
+      <c r="K188" s="1" t="n">
+        <v>0.003303</v>
       </c>
     </row>
     <row r="189">
@@ -6869,10 +7436,13 @@
         <v>0.2869</v>
       </c>
       <c r="I189" s="1" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="J189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="J189" s="1" t="n">
-        <v>0.2869</v>
+      <c r="K189" s="1" t="n">
+        <v>0.286</v>
       </c>
     </row>
     <row r="190">
@@ -6903,10 +7473,13 @@
         <v>0.01817</v>
       </c>
       <c r="I190" s="1" t="n">
+        <v>0.01805</v>
+      </c>
+      <c r="J190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="J190" s="1" t="n">
-        <v>0.01817</v>
+      <c r="K190" s="1" t="n">
+        <v>0.01805</v>
       </c>
     </row>
     <row r="191">
@@ -6937,10 +7510,13 @@
         <v>0.259</v>
       </c>
       <c r="I191" s="1" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="J191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="J191" s="1" t="n">
-        <v>0.259</v>
+      <c r="K191" s="1" t="n">
+        <v>0.2574</v>
       </c>
     </row>
     <row r="192">
@@ -6971,10 +7547,13 @@
         <v>0.0387</v>
       </c>
       <c r="I192" s="1" t="n">
+        <v>0.03844</v>
+      </c>
+      <c r="J192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="J192" s="1" t="n">
-        <v>0.0387</v>
+      <c r="K192" s="1" t="n">
+        <v>0.03844</v>
       </c>
     </row>
     <row r="193">
@@ -7005,9 +7584,12 @@
         <v>0.0002234</v>
       </c>
       <c r="I193" s="1" t="n">
+        <v>0.0002226</v>
+      </c>
+      <c r="J193" s="1" t="n">
         <v>0.0002234</v>
       </c>
-      <c r="J193" s="1" t="n">
+      <c r="K193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -7039,10 +7621,13 @@
         <v>4.144</v>
       </c>
       <c r="I194" s="1" t="n">
+        <v>4.091</v>
+      </c>
+      <c r="J194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="J194" s="1" t="n">
-        <v>4.144</v>
+      <c r="K194" s="1" t="n">
+        <v>4.091</v>
       </c>
     </row>
     <row r="195">
@@ -7073,9 +7658,12 @@
         <v>0.999401</v>
       </c>
       <c r="I195" s="1" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="J195" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="J195" s="1" t="n">
+      <c r="K195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -7107,10 +7695,13 @@
         <v>4.298</v>
       </c>
       <c r="I196" s="1" t="n">
+        <v>4.276</v>
+      </c>
+      <c r="J196" s="1" t="n">
         <v>4.347</v>
       </c>
-      <c r="J196" s="1" t="n">
-        <v>4.298</v>
+      <c r="K196" s="1" t="n">
+        <v>4.276</v>
       </c>
     </row>
     <row r="197">
@@ -7141,9 +7732,12 @@
         <v>0.15118</v>
       </c>
       <c r="I197" s="1" t="n">
-        <v>0.15118</v>
+        <v>0.15151</v>
       </c>
       <c r="J197" s="1" t="n">
+        <v>0.15151</v>
+      </c>
+      <c r="K197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -7175,9 +7769,12 @@
         <v>0.007648</v>
       </c>
       <c r="I198" s="1" t="n">
+        <v>0.007514</v>
+      </c>
+      <c r="J198" s="1" t="n">
         <v>0.0077</v>
       </c>
-      <c r="J198" s="1" t="n">
+      <c r="K198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -7209,9 +7806,12 @@
         <v>0.4507</v>
       </c>
       <c r="I199" s="1" t="n">
+        <v>0.4483</v>
+      </c>
+      <c r="J199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="J199" s="1" t="n">
+      <c r="K199" s="1" t="n">
         <v>0.4483</v>
       </c>
     </row>
@@ -7243,9 +7843,12 @@
         <v>0.5787</v>
       </c>
       <c r="I200" s="1" t="n">
+        <v>0.5784</v>
+      </c>
+      <c r="J200" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="J200" s="1" t="n">
+      <c r="K200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -7277,10 +7880,13 @@
         <v>0.0936</v>
       </c>
       <c r="I201" s="1" t="n">
+        <v>0.0931</v>
+      </c>
+      <c r="J201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="J201" s="1" t="n">
-        <v>0.0936</v>
+      <c r="K201" s="1" t="n">
+        <v>0.0931</v>
       </c>
     </row>
     <row r="202">
@@ -7311,10 +7917,13 @@
         <v>0.06086</v>
       </c>
       <c r="I202" s="1" t="n">
+        <v>0.06044</v>
+      </c>
+      <c r="J202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="J202" s="1" t="n">
-        <v>0.06063</v>
+      <c r="K202" s="1" t="n">
+        <v>0.06044</v>
       </c>
     </row>
     <row r="203">
@@ -7345,9 +7954,12 @@
         <v>0.00804</v>
       </c>
       <c r="I203" s="1" t="n">
+        <v>0.00817</v>
+      </c>
+      <c r="J203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="J203" s="1" t="n">
+      <c r="K203" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -7379,10 +7991,13 @@
         <v>0.0042</v>
       </c>
       <c r="I204" s="1" t="n">
+        <v>0.00418</v>
+      </c>
+      <c r="J204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="J204" s="1" t="n">
-        <v>0.0042</v>
+      <c r="K204" s="1" t="n">
+        <v>0.00418</v>
       </c>
     </row>
     <row r="205">
@@ -7413,10 +8028,13 @@
         <v>0.009169</v>
       </c>
       <c r="I205" s="1" t="n">
+        <v>0.009136</v>
+      </c>
+      <c r="J205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="J205" s="1" t="n">
-        <v>0.009154000000000001</v>
+      <c r="K205" s="1" t="n">
+        <v>0.009136</v>
       </c>
     </row>
     <row r="206">
@@ -7447,9 +8065,12 @@
         <v>0.2413</v>
       </c>
       <c r="I206" s="1" t="n">
+        <v>0.2399</v>
+      </c>
+      <c r="J206" s="1" t="n">
         <v>0.2413</v>
       </c>
-      <c r="J206" s="1" t="n">
+      <c r="K206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -7481,10 +8102,13 @@
         <v>0.02111</v>
       </c>
       <c r="I207" s="1" t="n">
+        <v>0.02092</v>
+      </c>
+      <c r="J207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="J207" s="1" t="n">
-        <v>0.02111</v>
+      <c r="K207" s="1" t="n">
+        <v>0.02092</v>
       </c>
     </row>
     <row r="208">
@@ -7515,9 +8139,12 @@
         <v>0.2375</v>
       </c>
       <c r="I208" s="1" t="n">
+        <v>0.2368</v>
+      </c>
+      <c r="J208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="J208" s="1" t="n">
+      <c r="K208" s="1" t="n">
         <v>0.2366</v>
       </c>
     </row>
@@ -7549,10 +8176,13 @@
         <v>0.3601</v>
       </c>
       <c r="I209" s="1" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="J209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="J209" s="1" t="n">
-        <v>0.3601</v>
+      <c r="K209" s="1" t="n">
+        <v>0.3587</v>
       </c>
     </row>
     <row r="210">
@@ -7583,10 +8213,13 @@
         <v>0.04259</v>
       </c>
       <c r="I210" s="1" t="n">
+        <v>0.04249</v>
+      </c>
+      <c r="J210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="J210" s="1" t="n">
-        <v>0.04259</v>
+      <c r="K210" s="1" t="n">
+        <v>0.04249</v>
       </c>
     </row>
     <row r="211">
@@ -7617,10 +8250,13 @@
         <v>0.0004289</v>
       </c>
       <c r="I211" s="1" t="n">
+        <v>0.0004256</v>
+      </c>
+      <c r="J211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="J211" s="1" t="n">
-        <v>0.0004282</v>
+      <c r="K211" s="1" t="n">
+        <v>0.0004256</v>
       </c>
     </row>
     <row r="212">
@@ -7651,10 +8287,13 @@
         <v>0.02164</v>
       </c>
       <c r="I212" s="1" t="n">
+        <v>0.02151</v>
+      </c>
+      <c r="J212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="J212" s="1" t="n">
-        <v>0.0216</v>
+      <c r="K212" s="1" t="n">
+        <v>0.02151</v>
       </c>
     </row>
     <row r="213">
@@ -7685,10 +8324,13 @@
         <v>0.1149</v>
       </c>
       <c r="I213" s="1" t="n">
+        <v>0.1137</v>
+      </c>
+      <c r="J213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="J213" s="1" t="n">
-        <v>0.1149</v>
+      <c r="K213" s="1" t="n">
+        <v>0.1137</v>
       </c>
     </row>
     <row r="214">
@@ -7719,10 +8361,13 @@
         <v>0.04189</v>
       </c>
       <c r="I214" s="1" t="n">
+        <v>0.04174</v>
+      </c>
+      <c r="J214" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="J214" s="1" t="n">
-        <v>0.04188</v>
+      <c r="K214" s="1" t="n">
+        <v>0.04174</v>
       </c>
     </row>
     <row r="215">
@@ -7753,9 +8398,12 @@
         <v>0.010036</v>
       </c>
       <c r="I215" s="1" t="n">
+        <v>0.009991</v>
+      </c>
+      <c r="J215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="J215" s="1" t="n">
+      <c r="K215" s="1" t="n">
         <v>0.009896</v>
       </c>
     </row>
@@ -7787,9 +8435,12 @@
         <v>0.0643</v>
       </c>
       <c r="I216" s="1" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="J216" s="1" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="J216" s="1" t="n">
+      <c r="K216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -7821,9 +8472,12 @@
         <v>0.004209</v>
       </c>
       <c r="I217" s="1" t="n">
+        <v>0.004183</v>
+      </c>
+      <c r="J217" s="1" t="n">
         <v>0.004231</v>
       </c>
-      <c r="J217" s="1" t="n">
+      <c r="K217" s="1" t="n">
         <v>0.004177</v>
       </c>
     </row>
@@ -7855,9 +8509,12 @@
         <v>0.009820000000000001</v>
       </c>
       <c r="I218" s="1" t="n">
+        <v>0.01013</v>
+      </c>
+      <c r="J218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="J218" s="1" t="n">
+      <c r="K218" s="1" t="n">
         <v>0.009820000000000001</v>
       </c>
     </row>
@@ -7889,9 +8546,12 @@
         <v>0.02983</v>
       </c>
       <c r="I219" s="1" t="n">
+        <v>0.03001</v>
+      </c>
+      <c r="J219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="J219" s="1" t="n">
+      <c r="K219" s="1" t="n">
         <v>0.02958</v>
       </c>
     </row>
@@ -7923,10 +8583,13 @@
         <v>2.295</v>
       </c>
       <c r="I220" s="1" t="n">
+        <v>2.292</v>
+      </c>
+      <c r="J220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="J220" s="1" t="n">
-        <v>2.295</v>
+      <c r="K220" s="1" t="n">
+        <v>2.292</v>
       </c>
     </row>
     <row r="221">
@@ -7957,10 +8620,13 @@
         <v>0.022908</v>
       </c>
       <c r="I221" s="1" t="n">
+        <v>0.022886</v>
+      </c>
+      <c r="J221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="J221" s="1" t="n">
-        <v>0.022908</v>
+      <c r="K221" s="1" t="n">
+        <v>0.022886</v>
       </c>
     </row>
     <row r="222">
@@ -7991,9 +8657,12 @@
         <v>0.0369</v>
       </c>
       <c r="I222" s="1" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="J222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="J222" s="1" t="n">
+      <c r="K222" s="1" t="n">
         <v>0.0369</v>
       </c>
     </row>
@@ -8025,10 +8694,13 @@
         <v>0.2938</v>
       </c>
       <c r="I223" s="1" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="J223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="J223" s="1" t="n">
-        <v>0.2938</v>
+      <c r="K223" s="1" t="n">
+        <v>0.2918</v>
       </c>
     </row>
     <row r="224">
@@ -8059,9 +8731,12 @@
         <v>0.01564</v>
       </c>
       <c r="I224" s="1" t="n">
+        <v>0.01552</v>
+      </c>
+      <c r="J224" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="J224" s="1" t="n">
+      <c r="K224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -8093,10 +8768,13 @@
         <v>0.0004105</v>
       </c>
       <c r="I225" s="1" t="n">
+        <v>0.0004069</v>
+      </c>
+      <c r="J225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="J225" s="1" t="n">
-        <v>0.0004105</v>
+      <c r="K225" s="1" t="n">
+        <v>0.0004069</v>
       </c>
     </row>
     <row r="226">
@@ -8127,10 +8805,13 @@
         <v>0.08735999999999999</v>
       </c>
       <c r="I226" s="1" t="n">
+        <v>0.08654000000000001</v>
+      </c>
+      <c r="J226" s="1" t="n">
         <v>0.08815000000000001</v>
       </c>
-      <c r="J226" s="1" t="n">
-        <v>0.08731999999999999</v>
+      <c r="K226" s="1" t="n">
+        <v>0.08654000000000001</v>
       </c>
     </row>
     <row r="227">
@@ -8161,9 +8842,12 @@
         <v>0.953</v>
       </c>
       <c r="I227" s="1" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="J227" s="1" t="n">
         <v>0.959</v>
       </c>
-      <c r="J227" s="1" t="n">
+      <c r="K227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -8195,9 +8879,12 @@
         <v>0.05603</v>
       </c>
       <c r="I228" s="1" t="n">
+        <v>0.05581</v>
+      </c>
+      <c r="J228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="J228" s="1" t="n">
+      <c r="K228" s="1" t="n">
         <v>0.0558</v>
       </c>
     </row>
@@ -8229,10 +8916,13 @@
         <v>0.002019</v>
       </c>
       <c r="I229" s="1" t="n">
+        <v>0.002003</v>
+      </c>
+      <c r="J229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="J229" s="1" t="n">
-        <v>0.002017</v>
+      <c r="K229" s="1" t="n">
+        <v>0.002003</v>
       </c>
     </row>
     <row r="230">
@@ -8263,9 +8953,12 @@
         <v>0.022963</v>
       </c>
       <c r="I230" s="1" t="n">
-        <v>0.022963</v>
+        <v>0.023091</v>
       </c>
       <c r="J230" s="1" t="n">
+        <v>0.023091</v>
+      </c>
+      <c r="K230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -8297,10 +8990,13 @@
         <v>0.05407</v>
       </c>
       <c r="I231" s="1" t="n">
+        <v>0.0535</v>
+      </c>
+      <c r="J231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="J231" s="1" t="n">
-        <v>0.05407</v>
+      <c r="K231" s="1" t="n">
+        <v>0.0535</v>
       </c>
     </row>
     <row r="232">
@@ -8331,10 +9027,13 @@
         <v>0.0596</v>
       </c>
       <c r="I232" s="1" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="J232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="J232" s="1" t="n">
-        <v>0.0591</v>
+      <c r="K232" s="1" t="n">
+        <v>0.0588</v>
       </c>
     </row>
     <row r="233">
@@ -8365,9 +9064,12 @@
         <v>0.001688</v>
       </c>
       <c r="I233" s="1" t="n">
+        <v>0.001679</v>
+      </c>
+      <c r="J233" s="1" t="n">
         <v>0.001701</v>
       </c>
-      <c r="J233" s="1" t="n">
+      <c r="K233" s="1" t="n">
         <v>0.001678</v>
       </c>
     </row>
@@ -8399,10 +9101,13 @@
         <v>0.005794</v>
       </c>
       <c r="I234" s="1" t="n">
+        <v>0.005769</v>
+      </c>
+      <c r="J234" s="1" t="n">
         <v>0.005854</v>
       </c>
-      <c r="J234" s="1" t="n">
-        <v>0.005784</v>
+      <c r="K234" s="1" t="n">
+        <v>0.005769</v>
       </c>
     </row>
     <row r="235">
@@ -8433,9 +9138,12 @@
         <v>0.12575</v>
       </c>
       <c r="I235" s="1" t="n">
+        <v>0.12492</v>
+      </c>
+      <c r="J235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="J235" s="1" t="n">
+      <c r="K235" s="1" t="n">
         <v>0.12453</v>
       </c>
     </row>
@@ -8467,10 +9175,13 @@
         <v>64.73999999999999</v>
       </c>
       <c r="I236" s="1" t="n">
+        <v>64.73</v>
+      </c>
+      <c r="J236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="J236" s="1" t="n">
-        <v>64.73999999999999</v>
+      <c r="K236" s="1" t="n">
+        <v>64.73</v>
       </c>
     </row>
     <row r="237">
@@ -8501,10 +9212,13 @@
         <v>0.1021</v>
       </c>
       <c r="I237" s="1" t="n">
+        <v>0.1017</v>
+      </c>
+      <c r="J237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="J237" s="1" t="n">
-        <v>0.1021</v>
+      <c r="K237" s="1" t="n">
+        <v>0.1017</v>
       </c>
     </row>
     <row r="238">
@@ -8535,9 +9249,12 @@
         <v>0.003969</v>
       </c>
       <c r="I238" s="1" t="n">
+        <v>0.003952</v>
+      </c>
+      <c r="J238" s="1" t="n">
         <v>0.003993</v>
       </c>
-      <c r="J238" s="1" t="n">
+      <c r="K238" s="1" t="n">
         <v>0.003925</v>
       </c>
     </row>
@@ -8569,9 +9286,12 @@
         <v>0.01544</v>
       </c>
       <c r="I239" s="1" t="n">
+        <v>0.01551</v>
+      </c>
+      <c r="J239" s="1" t="n">
         <v>0.01562</v>
       </c>
-      <c r="J239" s="1" t="n">
+      <c r="K239" s="1" t="n">
         <v>0.01532</v>
       </c>
     </row>
@@ -8603,10 +9323,13 @@
         <v>0.05635</v>
       </c>
       <c r="I240" s="1" t="n">
+        <v>0.05598</v>
+      </c>
+      <c r="J240" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="J240" s="1" t="n">
-        <v>0.05621</v>
+      <c r="K240" s="1" t="n">
+        <v>0.05598</v>
       </c>
     </row>
     <row r="241">
@@ -8637,10 +9360,13 @@
         <v>0.0114</v>
       </c>
       <c r="I241" s="1" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="J241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="J241" s="1" t="n">
-        <v>0.0114</v>
+      <c r="K241" s="1" t="n">
+        <v>0.0113</v>
       </c>
     </row>
     <row r="242">
@@ -8671,10 +9397,13 @@
         <v>0.3368</v>
       </c>
       <c r="I242" s="1" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="J242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="J242" s="1" t="n">
-        <v>0.336</v>
+      <c r="K242" s="1" t="n">
+        <v>0.3334</v>
       </c>
     </row>
     <row r="243">
@@ -8705,10 +9434,13 @@
         <v>0.01235</v>
       </c>
       <c r="I243" s="1" t="n">
+        <v>0.01229</v>
+      </c>
+      <c r="J243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="J243" s="1" t="n">
-        <v>0.01235</v>
+      <c r="K243" s="1" t="n">
+        <v>0.01229</v>
       </c>
     </row>
     <row r="244">
@@ -8739,9 +9471,12 @@
         <v>0.08041</v>
       </c>
       <c r="I244" s="1" t="n">
+        <v>0.08006000000000001</v>
+      </c>
+      <c r="J244" s="1" t="n">
         <v>0.08067000000000001</v>
       </c>
-      <c r="J244" s="1" t="n">
+      <c r="K244" s="1" t="n">
         <v>0.07997</v>
       </c>
     </row>
@@ -8773,10 +9508,13 @@
         <v>0.007848000000000001</v>
       </c>
       <c r="I245" s="1" t="n">
+        <v>0.007769</v>
+      </c>
+      <c r="J245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="J245" s="1" t="n">
-        <v>0.007848000000000001</v>
+      <c r="K245" s="1" t="n">
+        <v>0.007769</v>
       </c>
     </row>
     <row r="246">
@@ -8807,10 +9545,13 @@
         <v>0.0305</v>
       </c>
       <c r="I246" s="1" t="n">
+        <v>0.03029</v>
+      </c>
+      <c r="J246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="J246" s="1" t="n">
-        <v>0.0305</v>
+      <c r="K246" s="1" t="n">
+        <v>0.03029</v>
       </c>
     </row>
     <row r="247">
@@ -8841,10 +9582,13 @@
         <v>0.1813</v>
       </c>
       <c r="I247" s="1" t="n">
+        <v>0.1801</v>
+      </c>
+      <c r="J247" s="1" t="n">
         <v>0.1827</v>
       </c>
-      <c r="J247" s="1" t="n">
-        <v>0.1808</v>
+      <c r="K247" s="1" t="n">
+        <v>0.1801</v>
       </c>
     </row>
     <row r="248">
@@ -8875,10 +9619,13 @@
         <v>0.0591</v>
       </c>
       <c r="I248" s="1" t="n">
+        <v>0.05886</v>
+      </c>
+      <c r="J248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="J248" s="1" t="n">
-        <v>0.0591</v>
+      <c r="K248" s="1" t="n">
+        <v>0.05886</v>
       </c>
     </row>
     <row r="249">
@@ -8909,9 +9656,12 @@
         <v>0.1673</v>
       </c>
       <c r="I249" s="1" t="n">
+        <v>0.1664</v>
+      </c>
+      <c r="J249" s="1" t="n">
         <v>0.1684</v>
       </c>
-      <c r="J249" s="1" t="n">
+      <c r="K249" s="1" t="n">
         <v>0.1664</v>
       </c>
     </row>
@@ -8943,10 +9693,13 @@
         <v>0.01931</v>
       </c>
       <c r="I250" s="1" t="n">
+        <v>0.01916</v>
+      </c>
+      <c r="J250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="J250" s="1" t="n">
-        <v>0.01931</v>
+      <c r="K250" s="1" t="n">
+        <v>0.01916</v>
       </c>
     </row>
     <row r="251">
@@ -8977,10 +9730,13 @@
         <v>0.02309</v>
       </c>
       <c r="I251" s="1" t="n">
+        <v>0.02295</v>
+      </c>
+      <c r="J251" s="1" t="n">
         <v>0.02318</v>
       </c>
-      <c r="J251" s="1" t="n">
-        <v>0.02304</v>
+      <c r="K251" s="1" t="n">
+        <v>0.02295</v>
       </c>
     </row>
     <row r="252">
@@ -9011,9 +9767,12 @@
         <v>0.31021</v>
       </c>
       <c r="I252" s="1" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="J252" s="1" t="n">
         <v>0.31227</v>
       </c>
-      <c r="J252" s="1" t="n">
+      <c r="K252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -9045,10 +9804,13 @@
         <v>0.006037</v>
       </c>
       <c r="I253" s="1" t="n">
+        <v>0.005971</v>
+      </c>
+      <c r="J253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="J253" s="1" t="n">
-        <v>0.006037</v>
+      <c r="K253" s="1" t="n">
+        <v>0.005971</v>
       </c>
     </row>
     <row r="254">
@@ -9079,10 +9841,13 @@
         <v>0.6142</v>
       </c>
       <c r="I254" s="1" t="n">
+        <v>0.6116</v>
+      </c>
+      <c r="J254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="J254" s="1" t="n">
-        <v>0.6141</v>
+      <c r="K254" s="1" t="n">
+        <v>0.6116</v>
       </c>
     </row>
     <row r="255">
@@ -9113,10 +9878,13 @@
         <v>0.10727</v>
       </c>
       <c r="I255" s="1" t="n">
+        <v>0.10612</v>
+      </c>
+      <c r="J255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="J255" s="1" t="n">
-        <v>0.10726</v>
+      <c r="K255" s="1" t="n">
+        <v>0.10612</v>
       </c>
     </row>
     <row r="256">
@@ -9147,9 +9915,12 @@
         <v>0.0907</v>
       </c>
       <c r="I256" s="1" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="J256" s="1" t="n">
         <v>0.0911</v>
       </c>
-      <c r="J256" s="1" t="n">
+      <c r="K256" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -9181,9 +9952,12 @@
         <v>0.01433</v>
       </c>
       <c r="I257" s="1" t="n">
+        <v>0.01421</v>
+      </c>
+      <c r="J257" s="1" t="n">
         <v>0.01454</v>
       </c>
-      <c r="J257" s="1" t="n">
+      <c r="K257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -9215,9 +9989,12 @@
         <v>0.05137</v>
       </c>
       <c r="I258" s="1" t="n">
+        <v>0.05125</v>
+      </c>
+      <c r="J258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="J258" s="1" t="n">
+      <c r="K258" s="1" t="n">
         <v>0.0511</v>
       </c>
     </row>
@@ -9249,10 +10026,13 @@
         <v>0.008240000000000001</v>
       </c>
       <c r="I259" s="1" t="n">
+        <v>0.008109999999999999</v>
+      </c>
+      <c r="J259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="J259" s="1" t="n">
-        <v>0.008240000000000001</v>
+      <c r="K259" s="1" t="n">
+        <v>0.008109999999999999</v>
       </c>
     </row>
     <row r="260">
@@ -9283,10 +10063,13 @@
         <v>0.1904</v>
       </c>
       <c r="I260" s="1" t="n">
+        <v>0.1894</v>
+      </c>
+      <c r="J260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="J260" s="1" t="n">
-        <v>0.1902</v>
+      <c r="K260" s="1" t="n">
+        <v>0.1894</v>
       </c>
     </row>
     <row r="261">
@@ -9317,10 +10100,13 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="I261" s="1" t="n">
+        <v>0.0983</v>
+      </c>
+      <c r="J261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="J261" s="1" t="n">
-        <v>0.09859999999999999</v>
+      <c r="K261" s="1" t="n">
+        <v>0.0983</v>
       </c>
     </row>
     <row r="262">
@@ -9351,10 +10137,13 @@
         <v>0.2127</v>
       </c>
       <c r="I262" s="1" t="n">
+        <v>0.2113</v>
+      </c>
+      <c r="J262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="J262" s="1" t="n">
-        <v>0.2127</v>
+      <c r="K262" s="1" t="n">
+        <v>0.2113</v>
       </c>
     </row>
     <row r="263">
@@ -9385,9 +10174,12 @@
         <v>0.008495000000000001</v>
       </c>
       <c r="I263" s="1" t="n">
+        <v>0.008465</v>
+      </c>
+      <c r="J263" s="1" t="n">
         <v>0.008522999999999999</v>
       </c>
-      <c r="J263" s="1" t="n">
+      <c r="K263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -9419,10 +10211,13 @@
         <v>2.645</v>
       </c>
       <c r="I264" s="1" t="n">
+        <v>2.632</v>
+      </c>
+      <c r="J264" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="J264" s="1" t="n">
-        <v>2.645</v>
+      <c r="K264" s="1" t="n">
+        <v>2.632</v>
       </c>
     </row>
     <row r="265">
@@ -9453,9 +10248,12 @@
         <v>0.01871</v>
       </c>
       <c r="I265" s="1" t="n">
+        <v>0.01855</v>
+      </c>
+      <c r="J265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="J265" s="1" t="n">
+      <c r="K265" s="1" t="n">
         <v>0.01847</v>
       </c>
     </row>
@@ -9487,9 +10285,12 @@
         <v>0.3593</v>
       </c>
       <c r="I266" s="1" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="J266" s="1" t="n">
         <v>0.3604</v>
       </c>
-      <c r="J266" s="1" t="n">
+      <c r="K266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -9521,10 +10322,13 @@
         <v>0.03431</v>
       </c>
       <c r="I267" s="1" t="n">
+        <v>0.03408</v>
+      </c>
+      <c r="J267" s="1" t="n">
         <v>0.03464</v>
       </c>
-      <c r="J267" s="1" t="n">
-        <v>0.03429</v>
+      <c r="K267" s="1" t="n">
+        <v>0.03408</v>
       </c>
     </row>
     <row r="268">
@@ -9555,9 +10359,12 @@
         <v>0.118</v>
       </c>
       <c r="I268" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="J268" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="J268" s="1" t="n">
+      <c r="K268" s="1" t="n">
         <v>0.118</v>
       </c>
     </row>
@@ -9589,10 +10396,13 @@
         <v>0.08019999999999999</v>
       </c>
       <c r="I269" s="1" t="n">
+        <v>0.07973</v>
+      </c>
+      <c r="J269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="J269" s="1" t="n">
-        <v>0.08019999999999999</v>
+      <c r="K269" s="1" t="n">
+        <v>0.07973</v>
       </c>
     </row>
     <row r="270">
@@ -9623,10 +10433,13 @@
         <v>0.01388</v>
       </c>
       <c r="I270" s="1" t="n">
+        <v>0.01382</v>
+      </c>
+      <c r="J270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="J270" s="1" t="n">
-        <v>0.01388</v>
+      <c r="K270" s="1" t="n">
+        <v>0.01382</v>
       </c>
     </row>
     <row r="271">
@@ -9657,10 +10470,13 @@
         <v>0.007625</v>
       </c>
       <c r="I271" s="1" t="n">
+        <v>0.007558</v>
+      </c>
+      <c r="J271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="J271" s="1" t="n">
-        <v>0.007625</v>
+      <c r="K271" s="1" t="n">
+        <v>0.007558</v>
       </c>
     </row>
     <row r="272">
@@ -9691,10 +10507,13 @@
         <v>0.0742</v>
       </c>
       <c r="I272" s="1" t="n">
+        <v>0.0741</v>
+      </c>
+      <c r="J272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="J272" s="1" t="n">
-        <v>0.07414</v>
+      <c r="K272" s="1" t="n">
+        <v>0.0741</v>
       </c>
     </row>
     <row r="273">
@@ -9728,6 +10547,9 @@
         <v>3.16e-05</v>
       </c>
       <c r="J273" s="1" t="n">
+        <v>3.16e-05</v>
+      </c>
+      <c r="K273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -9759,10 +10581,13 @@
         <v>0.005484</v>
       </c>
       <c r="I274" s="1" t="n">
+        <v>0.005469</v>
+      </c>
+      <c r="J274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="J274" s="1" t="n">
-        <v>0.005484</v>
+      <c r="K274" s="1" t="n">
+        <v>0.005469</v>
       </c>
     </row>
     <row r="275">
@@ -9793,9 +10618,12 @@
         <v>0.1818</v>
       </c>
       <c r="I275" s="1" t="n">
+        <v>0.1813</v>
+      </c>
+      <c r="J275" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="J275" s="1" t="n">
+      <c r="K275" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -9827,10 +10655,13 @@
         <v>0.006891</v>
       </c>
       <c r="I276" s="1" t="n">
+        <v>0.006844</v>
+      </c>
+      <c r="J276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="J276" s="1" t="n">
-        <v>0.006876</v>
+      <c r="K276" s="1" t="n">
+        <v>0.006844</v>
       </c>
     </row>
     <row r="277">
@@ -9861,10 +10692,13 @@
         <v>0.1309</v>
       </c>
       <c r="I277" s="1" t="n">
+        <v>0.1303</v>
+      </c>
+      <c r="J277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="J277" s="1" t="n">
-        <v>0.1309</v>
+      <c r="K277" s="1" t="n">
+        <v>0.1303</v>
       </c>
     </row>
     <row r="278">
@@ -9895,10 +10729,13 @@
         <v>0.02323</v>
       </c>
       <c r="I278" s="1" t="n">
+        <v>0.02308</v>
+      </c>
+      <c r="J278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="J278" s="1" t="n">
-        <v>0.02323</v>
+      <c r="K278" s="1" t="n">
+        <v>0.02308</v>
       </c>
     </row>
     <row r="279">
@@ -9929,10 +10766,13 @@
         <v>0.01815</v>
       </c>
       <c r="I279" s="1" t="n">
+        <v>0.01812</v>
+      </c>
+      <c r="J279" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="J279" s="1" t="n">
-        <v>0.01815</v>
+      <c r="K279" s="1" t="n">
+        <v>0.01812</v>
       </c>
     </row>
     <row r="280">
@@ -9963,10 +10803,13 @@
         <v>0.03755</v>
       </c>
       <c r="I280" s="1" t="n">
+        <v>0.03723</v>
+      </c>
+      <c r="J280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="J280" s="1" t="n">
-        <v>0.03755</v>
+      <c r="K280" s="1" t="n">
+        <v>0.03723</v>
       </c>
     </row>
     <row r="281">
@@ -9997,10 +10840,13 @@
         <v>0.03979</v>
       </c>
       <c r="I281" s="1" t="n">
+        <v>0.03953</v>
+      </c>
+      <c r="J281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="J281" s="1" t="n">
-        <v>0.03979</v>
+      <c r="K281" s="1" t="n">
+        <v>0.03953</v>
       </c>
     </row>
     <row r="282">
@@ -10031,10 +10877,13 @@
         <v>0.3021</v>
       </c>
       <c r="I282" s="1" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="J282" s="1" t="n">
         <v>0.3059</v>
       </c>
-      <c r="J282" s="1" t="n">
-        <v>0.3021</v>
+      <c r="K282" s="1" t="n">
+        <v>0.3007</v>
       </c>
     </row>
     <row r="283">
@@ -10065,10 +10914,13 @@
         <v>0.01124</v>
       </c>
       <c r="I283" s="1" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="J283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="J283" s="1" t="n">
-        <v>0.01124</v>
+      <c r="K283" s="1" t="n">
+        <v>0.0112</v>
       </c>
     </row>
     <row r="284">
@@ -10099,9 +10951,12 @@
         <v>9.6e-06</v>
       </c>
       <c r="I284" s="1" t="n">
+        <v>9.500000000000001e-06</v>
+      </c>
+      <c r="J284" s="1" t="n">
         <v>9.7e-06</v>
       </c>
-      <c r="J284" s="1" t="n">
+      <c r="K284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -10133,10 +10988,13 @@
         <v>0.1151</v>
       </c>
       <c r="I285" s="1" t="n">
+        <v>0.1141</v>
+      </c>
+      <c r="J285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="J285" s="1" t="n">
-        <v>0.1151</v>
+      <c r="K285" s="1" t="n">
+        <v>0.1141</v>
       </c>
     </row>
     <row r="286">
@@ -10167,10 +11025,13 @@
         <v>0.00348</v>
       </c>
       <c r="I286" s="1" t="n">
+        <v>0.003422</v>
+      </c>
+      <c r="J286" s="1" t="n">
         <v>0.003485</v>
       </c>
-      <c r="J286" s="1" t="n">
-        <v>0.003442</v>
+      <c r="K286" s="1" t="n">
+        <v>0.003422</v>
       </c>
     </row>
     <row r="287">
@@ -10201,10 +11062,13 @@
         <v>0.08522</v>
       </c>
       <c r="I287" s="1" t="n">
+        <v>0.08486</v>
+      </c>
+      <c r="J287" s="1" t="n">
         <v>0.08573</v>
       </c>
-      <c r="J287" s="1" t="n">
-        <v>0.08522</v>
+      <c r="K287" s="1" t="n">
+        <v>0.08486</v>
       </c>
     </row>
     <row r="288">
@@ -10235,10 +11099,13 @@
         <v>0.09921000000000001</v>
       </c>
       <c r="I288" s="1" t="n">
+        <v>0.09869</v>
+      </c>
+      <c r="J288" s="1" t="n">
         <v>0.1001</v>
       </c>
-      <c r="J288" s="1" t="n">
-        <v>0.09889000000000001</v>
+      <c r="K288" s="1" t="n">
+        <v>0.09869</v>
       </c>
     </row>
     <row r="289">
@@ -10269,9 +11136,12 @@
         <v>0.4359</v>
       </c>
       <c r="I289" s="1" t="n">
+        <v>0.4334</v>
+      </c>
+      <c r="J289" s="1" t="n">
         <v>0.4359</v>
       </c>
-      <c r="J289" s="1" t="n">
+      <c r="K289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -10303,10 +11173,13 @@
         <v>0.03897</v>
       </c>
       <c r="I290" s="1" t="n">
+        <v>0.03878</v>
+      </c>
+      <c r="J290" s="1" t="n">
         <v>0.03966</v>
       </c>
-      <c r="J290" s="1" t="n">
-        <v>0.03897</v>
+      <c r="K290" s="1" t="n">
+        <v>0.03878</v>
       </c>
     </row>
     <row r="291">
@@ -10337,10 +11210,13 @@
         <v>0.2394</v>
       </c>
       <c r="I291" s="1" t="n">
+        <v>0.2392</v>
+      </c>
+      <c r="J291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="J291" s="1" t="n">
-        <v>0.2394</v>
+      <c r="K291" s="1" t="n">
+        <v>0.2392</v>
       </c>
     </row>
     <row r="292">
@@ -10371,9 +11247,12 @@
         <v>0.28327</v>
       </c>
       <c r="I292" s="1" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="J292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="J292" s="1" t="n">
+      <c r="K292" s="1" t="n">
         <v>0.28275</v>
       </c>
     </row>
@@ -10405,10 +11284,13 @@
         <v>0.1494</v>
       </c>
       <c r="I293" s="1" t="n">
+        <v>0.1489</v>
+      </c>
+      <c r="J293" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="J293" s="1" t="n">
-        <v>0.1494</v>
+      <c r="K293" s="1" t="n">
+        <v>0.1489</v>
       </c>
     </row>
     <row r="294">
@@ -10439,10 +11321,13 @@
         <v>4.232</v>
       </c>
       <c r="I294" s="1" t="n">
+        <v>4.207</v>
+      </c>
+      <c r="J294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="J294" s="1" t="n">
-        <v>4.232</v>
+      <c r="K294" s="1" t="n">
+        <v>4.207</v>
       </c>
     </row>
     <row r="295">
@@ -10473,9 +11358,12 @@
         <v>0.03271</v>
       </c>
       <c r="I295" s="1" t="n">
-        <v>0.03318</v>
+        <v>0.03339</v>
       </c>
       <c r="J295" s="1" t="n">
+        <v>0.03339</v>
+      </c>
+      <c r="K295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -10507,10 +11395,13 @@
         <v>0.000985</v>
       </c>
       <c r="I296" s="1" t="n">
+        <v>0.000975</v>
+      </c>
+      <c r="J296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="J296" s="1" t="n">
-        <v>0.0009790000000000001</v>
+      <c r="K296" s="1" t="n">
+        <v>0.000975</v>
       </c>
     </row>
     <row r="297">
@@ -10541,10 +11432,13 @@
         <v>0.0818</v>
       </c>
       <c r="I297" s="1" t="n">
+        <v>0.08154</v>
+      </c>
+      <c r="J297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="J297" s="1" t="n">
-        <v>0.0818</v>
+      <c r="K297" s="1" t="n">
+        <v>0.08154</v>
       </c>
     </row>
     <row r="298">
@@ -10575,10 +11469,13 @@
         <v>0.05798</v>
       </c>
       <c r="I298" s="1" t="n">
+        <v>0.05745</v>
+      </c>
+      <c r="J298" s="1" t="n">
         <v>0.05821</v>
       </c>
-      <c r="J298" s="1" t="n">
-        <v>0.05763</v>
+      <c r="K298" s="1" t="n">
+        <v>0.05745</v>
       </c>
     </row>
     <row r="299">
@@ -10609,9 +11506,12 @@
         <v>0.09132999999999999</v>
       </c>
       <c r="I299" s="1" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="J299" s="1" t="n">
         <v>0.0917</v>
       </c>
-      <c r="J299" s="1" t="n">
+      <c r="K299" s="1" t="n">
         <v>0.09066</v>
       </c>
     </row>
@@ -10643,10 +11543,13 @@
         <v>0.0276</v>
       </c>
       <c r="I300" s="1" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="J300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="J300" s="1" t="n">
-        <v>0.0276</v>
+      <c r="K300" s="1" t="n">
+        <v>0.0274</v>
       </c>
     </row>
     <row r="301">
@@ -10677,10 +11580,13 @@
         <v>0.06576</v>
       </c>
       <c r="I301" s="1" t="n">
+        <v>0.06557</v>
+      </c>
+      <c r="J301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="J301" s="1" t="n">
-        <v>0.06576</v>
+      <c r="K301" s="1" t="n">
+        <v>0.06557</v>
       </c>
     </row>
     <row r="302">
@@ -10711,9 +11617,12 @@
         <v>0.052777</v>
       </c>
       <c r="I302" s="1" t="n">
-        <v>0.052828</v>
+        <v>0.052936</v>
       </c>
       <c r="J302" s="1" t="n">
+        <v>0.052936</v>
+      </c>
+      <c r="K302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -10745,9 +11654,12 @@
         <v>5175.3</v>
       </c>
       <c r="I303" s="1" t="n">
+        <v>5169.3</v>
+      </c>
+      <c r="J303" s="1" t="n">
         <v>5177.6</v>
       </c>
-      <c r="J303" s="1" t="n">
+      <c r="K303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -10779,10 +11691,13 @@
         <v>15.02</v>
       </c>
       <c r="I304" s="1" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="J304" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="J304" s="1" t="n">
-        <v>14.99</v>
+      <c r="K304" s="1" t="n">
+        <v>14.9</v>
       </c>
     </row>
     <row r="305">
@@ -10813,10 +11728,13 @@
         <v>0.003721</v>
       </c>
       <c r="I305" s="1" t="n">
+        <v>0.003695</v>
+      </c>
+      <c r="J305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="J305" s="1" t="n">
-        <v>0.003721</v>
+      <c r="K305" s="1" t="n">
+        <v>0.003695</v>
       </c>
     </row>
     <row r="306">
@@ -10847,10 +11765,13 @@
         <v>0.4588</v>
       </c>
       <c r="I306" s="1" t="n">
+        <v>0.4568</v>
+      </c>
+      <c r="J306" s="1" t="n">
         <v>0.4608</v>
       </c>
-      <c r="J306" s="1" t="n">
-        <v>0.4573</v>
+      <c r="K306" s="1" t="n">
+        <v>0.4568</v>
       </c>
     </row>
     <row r="307">
@@ -10881,10 +11802,13 @@
         <v>0.04718</v>
       </c>
       <c r="I307" s="1" t="n">
+        <v>0.04696</v>
+      </c>
+      <c r="J307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="J307" s="1" t="n">
-        <v>0.04718</v>
+      <c r="K307" s="1" t="n">
+        <v>0.04696</v>
       </c>
     </row>
     <row r="308">
@@ -10915,9 +11839,12 @@
         <v>1.4883</v>
       </c>
       <c r="I308" s="1" t="n">
+        <v>1.4876</v>
+      </c>
+      <c r="J308" s="1" t="n">
         <v>1.4891</v>
       </c>
-      <c r="J308" s="1" t="n">
+      <c r="K308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -10949,10 +11876,13 @@
         <v>0.0007948</v>
       </c>
       <c r="I309" s="1" t="n">
+        <v>0.0007937</v>
+      </c>
+      <c r="J309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="J309" s="1" t="n">
-        <v>0.0007948</v>
+      <c r="K309" s="1" t="n">
+        <v>0.0007937</v>
       </c>
     </row>
     <row r="310">
@@ -10983,10 +11913,13 @@
         <v>4.657</v>
       </c>
       <c r="I310" s="1" t="n">
+        <v>4.617</v>
+      </c>
+      <c r="J310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="J310" s="1" t="n">
-        <v>4.657</v>
+      <c r="K310" s="1" t="n">
+        <v>4.617</v>
       </c>
     </row>
     <row r="311">
@@ -11017,10 +11950,13 @@
         <v>4.775</v>
       </c>
       <c r="I311" s="1" t="n">
+        <v>4.761</v>
+      </c>
+      <c r="J311" s="1" t="n">
         <v>4.805</v>
       </c>
-      <c r="J311" s="1" t="n">
-        <v>4.765</v>
+      <c r="K311" s="1" t="n">
+        <v>4.761</v>
       </c>
     </row>
     <row r="312">
@@ -11051,9 +11987,12 @@
         <v>0.08134</v>
       </c>
       <c r="I312" s="1" t="n">
+        <v>0.08160000000000001</v>
+      </c>
+      <c r="J312" s="1" t="n">
         <v>0.08212</v>
       </c>
-      <c r="J312" s="1" t="n">
+      <c r="K312" s="1" t="n">
         <v>0.08098</v>
       </c>
     </row>
@@ -11085,10 +12024,13 @@
         <v>2.029</v>
       </c>
       <c r="I313" s="1" t="n">
+        <v>2.012</v>
+      </c>
+      <c r="J313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="J313" s="1" t="n">
-        <v>2.029</v>
+      <c r="K313" s="1" t="n">
+        <v>2.012</v>
       </c>
     </row>
     <row r="314">
@@ -11119,9 +12061,12 @@
         <v>0.07123</v>
       </c>
       <c r="I314" s="1" t="n">
+        <v>0.07053</v>
+      </c>
+      <c r="J314" s="1" t="n">
         <v>0.07123</v>
       </c>
-      <c r="J314" s="1" t="n">
+      <c r="K314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -11153,10 +12098,13 @@
         <v>0.955</v>
       </c>
       <c r="I315" s="1" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="J315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="J315" s="1" t="n">
-        <v>0.955</v>
+      <c r="K315" s="1" t="n">
+        <v>0.946</v>
       </c>
     </row>
     <row r="316">
@@ -11187,10 +12135,13 @@
         <v>0.1305</v>
       </c>
       <c r="I316" s="1" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="J316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="J316" s="1" t="n">
-        <v>0.1305</v>
+      <c r="K316" s="1" t="n">
+        <v>0.1299</v>
       </c>
     </row>
     <row r="317">
@@ -11221,9 +12172,12 @@
         <v>0.1845</v>
       </c>
       <c r="I317" s="1" t="n">
+        <v>0.1811</v>
+      </c>
+      <c r="J317" s="1" t="n">
         <v>0.186</v>
       </c>
-      <c r="J317" s="1" t="n">
+      <c r="K317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -11255,10 +12209,13 @@
         <v>0.01636</v>
       </c>
       <c r="I318" s="1" t="n">
+        <v>0.01626</v>
+      </c>
+      <c r="J318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="J318" s="1" t="n">
-        <v>0.01634</v>
+      <c r="K318" s="1" t="n">
+        <v>0.01626</v>
       </c>
     </row>
     <row r="319">
@@ -11289,10 +12246,13 @@
         <v>0.08404</v>
       </c>
       <c r="I319" s="1" t="n">
+        <v>0.08369</v>
+      </c>
+      <c r="J319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="J319" s="1" t="n">
-        <v>0.08395</v>
+      <c r="K319" s="1" t="n">
+        <v>0.08369</v>
       </c>
     </row>
     <row r="320">
@@ -11323,10 +12283,13 @@
         <v>0.00761</v>
       </c>
       <c r="I320" s="1" t="n">
+        <v>0.007571</v>
+      </c>
+      <c r="J320" s="1" t="n">
         <v>0.007667</v>
       </c>
-      <c r="J320" s="1" t="n">
-        <v>0.007597</v>
+      <c r="K320" s="1" t="n">
+        <v>0.007571</v>
       </c>
     </row>
     <row r="321">
@@ -11357,10 +12320,13 @@
         <v>0.05442</v>
       </c>
       <c r="I321" s="1" t="n">
+        <v>0.05406</v>
+      </c>
+      <c r="J321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="J321" s="1" t="n">
-        <v>0.05442</v>
+      <c r="K321" s="1" t="n">
+        <v>0.05406</v>
       </c>
     </row>
     <row r="322">
@@ -11391,10 +12357,13 @@
         <v>0.5483</v>
       </c>
       <c r="I322" s="1" t="n">
+        <v>0.5476</v>
+      </c>
+      <c r="J322" s="1" t="n">
         <v>0.5514</v>
       </c>
-      <c r="J322" s="1" t="n">
-        <v>0.5483</v>
+      <c r="K322" s="1" t="n">
+        <v>0.5476</v>
       </c>
     </row>
     <row r="323">
@@ -11425,9 +12394,12 @@
         <v>0.07568</v>
       </c>
       <c r="I323" s="1" t="n">
+        <v>0.07557</v>
+      </c>
+      <c r="J323" s="1" t="n">
         <v>0.07611999999999999</v>
       </c>
-      <c r="J323" s="1" t="n">
+      <c r="K323" s="1" t="n">
         <v>0.07525</v>
       </c>
     </row>
@@ -11459,9 +12431,12 @@
         <v>0.013001</v>
       </c>
       <c r="I324" s="1" t="n">
+        <v>0.012909</v>
+      </c>
+      <c r="J324" s="1" t="n">
         <v>0.013001</v>
       </c>
-      <c r="J324" s="1" t="n">
+      <c r="K324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -11493,10 +12468,13 @@
         <v>0.0993</v>
       </c>
       <c r="I325" s="1" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="J325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="J325" s="1" t="n">
-        <v>0.0993</v>
+      <c r="K325" s="1" t="n">
+        <v>0.0989</v>
       </c>
     </row>
     <row r="326">
@@ -11527,10 +12505,13 @@
         <v>0.01748</v>
       </c>
       <c r="I326" s="1" t="n">
+        <v>0.01735</v>
+      </c>
+      <c r="J326" s="1" t="n">
         <v>0.01765</v>
       </c>
-      <c r="J326" s="1" t="n">
-        <v>0.01748</v>
+      <c r="K326" s="1" t="n">
+        <v>0.01735</v>
       </c>
     </row>
     <row r="327">
@@ -11561,10 +12542,13 @@
         <v>0.06406000000000001</v>
       </c>
       <c r="I327" s="1" t="n">
+        <v>0.06382</v>
+      </c>
+      <c r="J327" s="1" t="n">
         <v>0.06435</v>
       </c>
-      <c r="J327" s="1" t="n">
-        <v>0.06392</v>
+      <c r="K327" s="1" t="n">
+        <v>0.06382</v>
       </c>
     </row>
     <row r="328">
@@ -11595,10 +12579,13 @@
         <v>0.2647</v>
       </c>
       <c r="I328" s="1" t="n">
+        <v>0.2627</v>
+      </c>
+      <c r="J328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="J328" s="1" t="n">
-        <v>0.2647</v>
+      <c r="K328" s="1" t="n">
+        <v>0.2627</v>
       </c>
     </row>
     <row r="329">
@@ -11629,9 +12616,12 @@
         <v>0.17145</v>
       </c>
       <c r="I329" s="1" t="n">
+        <v>0.17234</v>
+      </c>
+      <c r="J329" s="1" t="n">
         <v>0.17297</v>
       </c>
-      <c r="J329" s="1" t="n">
+      <c r="K329" s="1" t="n">
         <v>0.17145</v>
       </c>
     </row>
@@ -11663,9 +12653,12 @@
         <v>2.069</v>
       </c>
       <c r="I330" s="1" t="n">
+        <v>2.053</v>
+      </c>
+      <c r="J330" s="1" t="n">
         <v>2.088</v>
       </c>
-      <c r="J330" s="1" t="n">
+      <c r="K330" s="1" t="n">
         <v>2.043</v>
       </c>
     </row>
@@ -11697,9 +12690,12 @@
         <v>0.0279</v>
       </c>
       <c r="I331" s="1" t="n">
-        <v>0.028</v>
+        <v>0.0283</v>
       </c>
       <c r="J331" s="1" t="n">
+        <v>0.0283</v>
+      </c>
+      <c r="K331" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -11731,9 +12727,12 @@
         <v>0.006003</v>
       </c>
       <c r="I332" s="1" t="n">
+        <v>0.006026</v>
+      </c>
+      <c r="J332" s="1" t="n">
         <v>0.006031</v>
       </c>
-      <c r="J332" s="1" t="n">
+      <c r="K332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -11765,10 +12764,13 @@
         <v>0.003503</v>
       </c>
       <c r="I333" s="1" t="n">
+        <v>0.003497</v>
+      </c>
+      <c r="J333" s="1" t="n">
         <v>0.003579</v>
       </c>
-      <c r="J333" s="1" t="n">
-        <v>0.003503</v>
+      <c r="K333" s="1" t="n">
+        <v>0.003497</v>
       </c>
     </row>
     <row r="334">
@@ -11799,10 +12801,13 @@
         <v>0.01398</v>
       </c>
       <c r="I334" s="1" t="n">
+        <v>0.01395</v>
+      </c>
+      <c r="J334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="J334" s="1" t="n">
-        <v>0.01398</v>
+      <c r="K334" s="1" t="n">
+        <v>0.01395</v>
       </c>
     </row>
     <row r="335">
@@ -11833,9 +12838,12 @@
         <v>1.124</v>
       </c>
       <c r="I335" s="1" t="n">
+        <v>1.123</v>
+      </c>
+      <c r="J335" s="1" t="n">
         <v>1.13</v>
       </c>
-      <c r="J335" s="1" t="n">
+      <c r="K335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -11867,9 +12875,12 @@
         <v>0.011316</v>
       </c>
       <c r="I336" s="1" t="n">
+        <v>0.011297</v>
+      </c>
+      <c r="J336" s="1" t="n">
         <v>0.011326</v>
       </c>
-      <c r="J336" s="1" t="n">
+      <c r="K336" s="1" t="n">
         <v>0.011253</v>
       </c>
     </row>
@@ -11901,9 +12912,12 @@
         <v>2.961</v>
       </c>
       <c r="I337" s="1" t="n">
+        <v>2.965</v>
+      </c>
+      <c r="J337" s="1" t="n">
         <v>3.043</v>
       </c>
-      <c r="J337" s="1" t="n">
+      <c r="K337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -11935,10 +12949,13 @@
         <v>0.01871</v>
       </c>
       <c r="I338" s="1" t="n">
+        <v>0.01858</v>
+      </c>
+      <c r="J338" s="1" t="n">
         <v>0.01885</v>
       </c>
-      <c r="J338" s="1" t="n">
-        <v>0.01861</v>
+      <c r="K338" s="1" t="n">
+        <v>0.01858</v>
       </c>
     </row>
     <row r="339">
@@ -11969,9 +12986,12 @@
         <v>0.07758</v>
       </c>
       <c r="I339" s="1" t="n">
+        <v>0.07708</v>
+      </c>
+      <c r="J339" s="1" t="n">
         <v>0.07790999999999999</v>
       </c>
-      <c r="J339" s="1" t="n">
+      <c r="K339" s="1" t="n">
         <v>0.07689</v>
       </c>
     </row>
@@ -12003,10 +13023,13 @@
         <v>0.076</v>
       </c>
       <c r="I340" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="J340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="J340" s="1" t="n">
-        <v>0.076</v>
+      <c r="K340" s="1" t="n">
+        <v>0.075</v>
       </c>
     </row>
     <row r="341">
@@ -12037,10 +13060,13 @@
         <v>0.03618</v>
       </c>
       <c r="I341" s="1" t="n">
+        <v>0.03591</v>
+      </c>
+      <c r="J341" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="J341" s="1" t="n">
-        <v>0.03618</v>
+      <c r="K341" s="1" t="n">
+        <v>0.03591</v>
       </c>
     </row>
     <row r="342">
@@ -12071,10 +13097,13 @@
         <v>2630</v>
       </c>
       <c r="I342" s="1" t="n">
+        <v>2607</v>
+      </c>
+      <c r="J342" s="1" t="n">
         <v>2647</v>
       </c>
-      <c r="J342" s="1" t="n">
-        <v>2620</v>
+      <c r="K342" s="1" t="n">
+        <v>2607</v>
       </c>
     </row>
     <row r="343">
@@ -12105,9 +13134,12 @@
         <v>0.0001968</v>
       </c>
       <c r="I343" s="1" t="n">
+        <v>0.0001962</v>
+      </c>
+      <c r="J343" s="1" t="n">
         <v>0.000198</v>
       </c>
-      <c r="J343" s="1" t="n">
+      <c r="K343" s="1" t="n">
         <v>0.0001959</v>
       </c>
     </row>
@@ -12139,10 +13171,13 @@
         <v>0.07947</v>
       </c>
       <c r="I344" s="1" t="n">
+        <v>0.07925</v>
+      </c>
+      <c r="J344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="J344" s="1" t="n">
-        <v>0.07947</v>
+      <c r="K344" s="1" t="n">
+        <v>0.07925</v>
       </c>
     </row>
     <row r="345">
@@ -12173,10 +13208,13 @@
         <v>0.01635</v>
       </c>
       <c r="I345" s="1" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="J345" s="1" t="n">
         <v>0.01656</v>
       </c>
-      <c r="J345" s="1" t="n">
-        <v>0.01632</v>
+      <c r="K345" s="1" t="n">
+        <v>0.0163</v>
       </c>
     </row>
     <row r="346">
@@ -12207,10 +13245,13 @@
         <v>2.78</v>
       </c>
       <c r="I346" s="1" t="n">
+        <v>2.746</v>
+      </c>
+      <c r="J346" s="1" t="n">
         <v>2.799</v>
       </c>
-      <c r="J346" s="1" t="n">
-        <v>2.773</v>
+      <c r="K346" s="1" t="n">
+        <v>2.746</v>
       </c>
     </row>
     <row r="347">
@@ -12241,10 +13282,13 @@
         <v>0.01641</v>
       </c>
       <c r="I347" s="1" t="n">
+        <v>0.01631</v>
+      </c>
+      <c r="J347" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="J347" s="1" t="n">
-        <v>0.01639</v>
+      <c r="K347" s="1" t="n">
+        <v>0.01631</v>
       </c>
     </row>
     <row r="348">
@@ -12275,9 +13319,12 @@
         <v>0.03867</v>
       </c>
       <c r="I348" s="1" t="n">
+        <v>0.03863</v>
+      </c>
+      <c r="J348" s="1" t="n">
         <v>0.03897</v>
       </c>
-      <c r="J348" s="1" t="n">
+      <c r="K348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -12309,10 +13356,13 @@
         <v>0.3043</v>
       </c>
       <c r="I349" s="1" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="J349" s="1" t="n">
         <v>0.3065</v>
       </c>
-      <c r="J349" s="1" t="n">
-        <v>0.3037</v>
+      <c r="K349" s="1" t="n">
+        <v>0.3029</v>
       </c>
     </row>
     <row r="350">
@@ -12343,9 +13393,12 @@
         <v>0.005094</v>
       </c>
       <c r="I350" s="1" t="n">
+        <v>0.005076</v>
+      </c>
+      <c r="J350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="J350" s="1" t="n">
+      <c r="K350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -12377,10 +13430,13 @@
         <v>0.005096</v>
       </c>
       <c r="I351" s="1" t="n">
+        <v>0.005065</v>
+      </c>
+      <c r="J351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="J351" s="1" t="n">
-        <v>0.005096</v>
+      <c r="K351" s="1" t="n">
+        <v>0.005065</v>
       </c>
     </row>
     <row r="352">
@@ -12411,10 +13467,13 @@
         <v>0.004397</v>
       </c>
       <c r="I352" s="1" t="n">
+        <v>0.004384</v>
+      </c>
+      <c r="J352" s="1" t="n">
         <v>0.004419</v>
       </c>
-      <c r="J352" s="1" t="n">
-        <v>0.004387</v>
+      <c r="K352" s="1" t="n">
+        <v>0.004384</v>
       </c>
     </row>
     <row r="353">
@@ -12445,10 +13504,13 @@
         <v>0.08129</v>
       </c>
       <c r="I353" s="1" t="n">
+        <v>0.08062999999999999</v>
+      </c>
+      <c r="J353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="J353" s="1" t="n">
-        <v>0.08129</v>
+      <c r="K353" s="1" t="n">
+        <v>0.08062999999999999</v>
       </c>
     </row>
     <row r="354">
@@ -12479,9 +13541,12 @@
         <v>1.297</v>
       </c>
       <c r="I354" s="1" t="n">
+        <v>1.293</v>
+      </c>
+      <c r="J354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="J354" s="1" t="n">
+      <c r="K354" s="1" t="n">
         <v>1.283</v>
       </c>
     </row>
@@ -12513,10 +13578,13 @@
         <v>7.739</v>
       </c>
       <c r="I355" s="1" t="n">
+        <v>7.707</v>
+      </c>
+      <c r="J355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="J355" s="1" t="n">
-        <v>7.739</v>
+      <c r="K355" s="1" t="n">
+        <v>7.707</v>
       </c>
     </row>
     <row r="356">
@@ -12547,10 +13615,13 @@
         <v>0.00781</v>
       </c>
       <c r="I356" s="1" t="n">
+        <v>0.00778</v>
+      </c>
+      <c r="J356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="J356" s="1" t="n">
-        <v>0.00781</v>
+      <c r="K356" s="1" t="n">
+        <v>0.00778</v>
       </c>
     </row>
     <row r="357">
@@ -12581,9 +13652,12 @@
         <v>0.005722</v>
       </c>
       <c r="I357" s="1" t="n">
+        <v>0.005707</v>
+      </c>
+      <c r="J357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="J357" s="1" t="n">
+      <c r="K357" s="1" t="n">
         <v>0.005696</v>
       </c>
     </row>
@@ -12615,10 +13689,13 @@
         <v>0.01554</v>
       </c>
       <c r="I358" s="1" t="n">
+        <v>0.01551</v>
+      </c>
+      <c r="J358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="J358" s="1" t="n">
-        <v>0.01554</v>
+      <c r="K358" s="1" t="n">
+        <v>0.01551</v>
       </c>
     </row>
     <row r="359">
@@ -12649,10 +13726,13 @@
         <v>3.652</v>
       </c>
       <c r="I359" s="1" t="n">
+        <v>3.636</v>
+      </c>
+      <c r="J359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="J359" s="1" t="n">
-        <v>3.65</v>
+      <c r="K359" s="1" t="n">
+        <v>3.636</v>
       </c>
     </row>
     <row r="360">
@@ -12683,9 +13763,12 @@
         <v>0.1509</v>
       </c>
       <c r="I360" s="1" t="n">
+        <v>0.1502</v>
+      </c>
+      <c r="J360" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="J360" s="1" t="n">
+      <c r="K360" s="1" t="n">
         <v>0.1499</v>
       </c>
     </row>
@@ -12717,10 +13800,13 @@
         <v>0.07074</v>
       </c>
       <c r="I361" s="1" t="n">
+        <v>0.07019</v>
+      </c>
+      <c r="J361" s="1" t="n">
         <v>0.07104000000000001</v>
       </c>
-      <c r="J361" s="1" t="n">
-        <v>0.07069</v>
+      <c r="K361" s="1" t="n">
+        <v>0.07019</v>
       </c>
     </row>
     <row r="362">
@@ -12751,10 +13837,13 @@
         <v>0.01776</v>
       </c>
       <c r="I362" s="1" t="n">
+        <v>0.01761</v>
+      </c>
+      <c r="J362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="J362" s="1" t="n">
-        <v>0.01776</v>
+      <c r="K362" s="1" t="n">
+        <v>0.01761</v>
       </c>
     </row>
     <row r="363">
@@ -12785,10 +13874,13 @@
         <v>0.02243</v>
       </c>
       <c r="I363" s="1" t="n">
+        <v>0.02234</v>
+      </c>
+      <c r="J363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="J363" s="1" t="n">
-        <v>0.02243</v>
+      <c r="K363" s="1" t="n">
+        <v>0.02234</v>
       </c>
     </row>
     <row r="364">
@@ -12819,10 +13911,13 @@
         <v>0.01262</v>
       </c>
       <c r="I364" s="1" t="n">
+        <v>0.01249</v>
+      </c>
+      <c r="J364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="J364" s="1" t="n">
-        <v>0.01262</v>
+      <c r="K364" s="1" t="n">
+        <v>0.01249</v>
       </c>
     </row>
     <row r="365">
@@ -12853,10 +13948,13 @@
         <v>0.092</v>
       </c>
       <c r="I365" s="1" t="n">
+        <v>0.0916</v>
+      </c>
+      <c r="J365" s="1" t="n">
         <v>0.0926</v>
       </c>
-      <c r="J365" s="1" t="n">
-        <v>0.0919</v>
+      <c r="K365" s="1" t="n">
+        <v>0.0916</v>
       </c>
     </row>
     <row r="366">
@@ -12887,10 +13985,13 @@
         <v>0.04236</v>
       </c>
       <c r="I366" s="1" t="n">
+        <v>0.04224</v>
+      </c>
+      <c r="J366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="J366" s="1" t="n">
-        <v>0.04236</v>
+      <c r="K366" s="1" t="n">
+        <v>0.04224</v>
       </c>
     </row>
     <row r="367">
@@ -12921,10 +14022,13 @@
         <v>0.03148</v>
       </c>
       <c r="I367" s="1" t="n">
+        <v>0.03141</v>
+      </c>
+      <c r="J367" s="1" t="n">
         <v>0.03164</v>
       </c>
-      <c r="J367" s="1" t="n">
-        <v>0.03145</v>
+      <c r="K367" s="1" t="n">
+        <v>0.03141</v>
       </c>
     </row>
     <row r="368">
@@ -12955,10 +14059,13 @@
         <v>0.02342</v>
       </c>
       <c r="I368" s="1" t="n">
+        <v>0.02335</v>
+      </c>
+      <c r="J368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="J368" s="1" t="n">
-        <v>0.02342</v>
+      <c r="K368" s="1" t="n">
+        <v>0.02335</v>
       </c>
     </row>
     <row r="369">
@@ -12989,10 +14096,13 @@
         <v>0.03102</v>
       </c>
       <c r="I369" s="1" t="n">
+        <v>0.03089</v>
+      </c>
+      <c r="J369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="J369" s="1" t="n">
-        <v>0.03102</v>
+      <c r="K369" s="1" t="n">
+        <v>0.03089</v>
       </c>
     </row>
     <row r="370">
@@ -13023,9 +14133,12 @@
         <v>0.07932</v>
       </c>
       <c r="I370" s="1" t="n">
+        <v>0.07924</v>
+      </c>
+      <c r="J370" s="1" t="n">
         <v>0.07932</v>
       </c>
-      <c r="J370" s="1" t="n">
+      <c r="K370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -13057,9 +14170,12 @@
         <v>0.1083</v>
       </c>
       <c r="I371" s="1" t="n">
+        <v>0.1077</v>
+      </c>
+      <c r="J371" s="1" t="n">
         <v>0.1089</v>
       </c>
-      <c r="J371" s="1" t="n">
+      <c r="K371" s="1" t="n">
         <v>0.1074</v>
       </c>
     </row>
@@ -13091,10 +14207,13 @@
         <v>0.007105</v>
       </c>
       <c r="I372" s="1" t="n">
+        <v>0.007045</v>
+      </c>
+      <c r="J372" s="1" t="n">
         <v>0.007209</v>
       </c>
-      <c r="J372" s="1" t="n">
-        <v>0.007057</v>
+      <c r="K372" s="1" t="n">
+        <v>0.007045</v>
       </c>
     </row>
     <row r="373">
@@ -13125,10 +14244,13 @@
         <v>0.0963</v>
       </c>
       <c r="I373" s="1" t="n">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="J373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="J373" s="1" t="n">
-        <v>0.0963</v>
+      <c r="K373" s="1" t="n">
+        <v>0.09619999999999999</v>
       </c>
     </row>
     <row r="374">
@@ -13159,10 +14281,13 @@
         <v>0.05831</v>
       </c>
       <c r="I374" s="1" t="n">
+        <v>0.05804</v>
+      </c>
+      <c r="J374" s="1" t="n">
         <v>0.05881</v>
       </c>
-      <c r="J374" s="1" t="n">
-        <v>0.0583</v>
+      <c r="K374" s="1" t="n">
+        <v>0.05804</v>
       </c>
     </row>
     <row r="375">
@@ -13193,9 +14318,12 @@
         <v>0.3229</v>
       </c>
       <c r="I375" s="1" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="J375" s="1" t="n">
         <v>0.3238</v>
       </c>
-      <c r="J375" s="1" t="n">
+      <c r="K375" s="1" t="n">
         <v>0.3193</v>
       </c>
     </row>
@@ -13227,10 +14355,13 @@
         <v>0.01971</v>
       </c>
       <c r="I376" s="1" t="n">
+        <v>0.01958</v>
+      </c>
+      <c r="J376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="J376" s="1" t="n">
-        <v>0.01971</v>
+      <c r="K376" s="1" t="n">
+        <v>0.01958</v>
       </c>
     </row>
     <row r="377">
@@ -13261,10 +14392,13 @@
         <v>0.06872</v>
       </c>
       <c r="I377" s="1" t="n">
+        <v>0.06852999999999999</v>
+      </c>
+      <c r="J377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="J377" s="1" t="n">
-        <v>0.06872</v>
+      <c r="K377" s="1" t="n">
+        <v>0.06852999999999999</v>
       </c>
     </row>
     <row r="378">
@@ -13295,9 +14429,12 @@
         <v>0.15637</v>
       </c>
       <c r="I378" s="1" t="n">
-        <v>0.15637</v>
+        <v>0.1581</v>
       </c>
       <c r="J378" s="1" t="n">
+        <v>0.1581</v>
+      </c>
+      <c r="K378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -13329,10 +14466,13 @@
         <v>0.0006015</v>
       </c>
       <c r="I379" s="1" t="n">
+        <v>0.0005965</v>
+      </c>
+      <c r="J379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="J379" s="1" t="n">
-        <v>0.0006015</v>
+      <c r="K379" s="1" t="n">
+        <v>0.0005965</v>
       </c>
     </row>
     <row r="380">
@@ -13363,10 +14503,13 @@
         <v>0.0102</v>
       </c>
       <c r="I380" s="1" t="n">
+        <v>0.01015</v>
+      </c>
+      <c r="J380" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="J380" s="1" t="n">
-        <v>0.01016</v>
+      <c r="K380" s="1" t="n">
+        <v>0.01015</v>
       </c>
     </row>
     <row r="381">
@@ -13397,10 +14540,13 @@
         <v>0.02551</v>
       </c>
       <c r="I381" s="1" t="n">
+        <v>0.02547</v>
+      </c>
+      <c r="J381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="J381" s="1" t="n">
-        <v>0.02551</v>
+      <c r="K381" s="1" t="n">
+        <v>0.02547</v>
       </c>
     </row>
     <row r="382">
@@ -13431,9 +14577,12 @@
         <v>0.19145</v>
       </c>
       <c r="I382" s="1" t="n">
+        <v>0.19219</v>
+      </c>
+      <c r="J382" s="1" t="n">
         <v>0.19263</v>
       </c>
-      <c r="J382" s="1" t="n">
+      <c r="K382" s="1" t="n">
         <v>0.18936</v>
       </c>
     </row>
@@ -13465,10 +14614,13 @@
         <v>0.09325</v>
       </c>
       <c r="I383" s="1" t="n">
+        <v>0.09236</v>
+      </c>
+      <c r="J383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="J383" s="1" t="n">
-        <v>0.09325</v>
+      <c r="K383" s="1" t="n">
+        <v>0.09236</v>
       </c>
     </row>
     <row r="384">
@@ -13499,9 +14651,12 @@
         <v>0.03176</v>
       </c>
       <c r="I384" s="1" t="n">
+        <v>0.03179</v>
+      </c>
+      <c r="J384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="J384" s="1" t="n">
+      <c r="K384" s="1" t="n">
         <v>0.03176</v>
       </c>
     </row>
@@ -13533,10 +14688,13 @@
         <v>0.0111</v>
       </c>
       <c r="I385" s="1" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="J385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="J385" s="1" t="n">
-        <v>0.0111</v>
+      <c r="K385" s="1" t="n">
+        <v>0.011</v>
       </c>
     </row>
     <row r="386">
@@ -13567,9 +14725,12 @@
         <v>0.05218</v>
       </c>
       <c r="I386" s="1" t="n">
-        <v>0.05218</v>
+        <v>0.05224</v>
       </c>
       <c r="J386" s="1" t="n">
+        <v>0.05224</v>
+      </c>
+      <c r="K386" s="1" t="n">
         <v>0.05087</v>
       </c>
     </row>
@@ -13601,9 +14762,12 @@
         <v>0.02541</v>
       </c>
       <c r="I387" s="1" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="J387" s="1" t="n">
         <v>0.02541</v>
       </c>
-      <c r="J387" s="1" t="n">
+      <c r="K387" s="1" t="n">
         <v>0.02483</v>
       </c>
     </row>
@@ -13635,10 +14799,13 @@
         <v>0.007291</v>
       </c>
       <c r="I388" s="1" t="n">
+        <v>0.007267</v>
+      </c>
+      <c r="J388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="J388" s="1" t="n">
-        <v>0.007291</v>
+      <c r="K388" s="1" t="n">
+        <v>0.007267</v>
       </c>
     </row>
     <row r="389">
@@ -13669,10 +14836,13 @@
         <v>0.01015</v>
       </c>
       <c r="I389" s="1" t="n">
+        <v>0.01011</v>
+      </c>
+      <c r="J389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="J389" s="1" t="n">
-        <v>0.01015</v>
+      <c r="K389" s="1" t="n">
+        <v>0.01011</v>
       </c>
     </row>
     <row r="390">
@@ -13703,10 +14873,13 @@
         <v>0.08295</v>
       </c>
       <c r="I390" s="1" t="n">
+        <v>0.08233</v>
+      </c>
+      <c r="J390" s="1" t="n">
         <v>0.0839</v>
       </c>
-      <c r="J390" s="1" t="n">
-        <v>0.08295</v>
+      <c r="K390" s="1" t="n">
+        <v>0.08233</v>
       </c>
     </row>
     <row r="391">
@@ -13737,9 +14910,12 @@
         <v>0.5039</v>
       </c>
       <c r="I391" s="1" t="n">
+        <v>0.5021</v>
+      </c>
+      <c r="J391" s="1" t="n">
         <v>0.5061</v>
       </c>
-      <c r="J391" s="1" t="n">
+      <c r="K391" s="1" t="n">
         <v>0.5017</v>
       </c>
     </row>
@@ -13771,9 +14947,12 @@
         <v>0.1177</v>
       </c>
       <c r="I392" s="1" t="n">
+        <v>0.1171</v>
+      </c>
+      <c r="J392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="J392" s="1" t="n">
+      <c r="K392" s="1" t="n">
         <v>0.1171</v>
       </c>
     </row>
@@ -13805,10 +14984,13 @@
         <v>0.00248</v>
       </c>
       <c r="I393" s="1" t="n">
+        <v>0.00246</v>
+      </c>
+      <c r="J393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="J393" s="1" t="n">
-        <v>0.00248</v>
+      <c r="K393" s="1" t="n">
+        <v>0.00246</v>
       </c>
     </row>
     <row r="394">
@@ -13839,9 +15021,12 @@
         <v>0.02121</v>
       </c>
       <c r="I394" s="1" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="J394" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="J394" s="1" t="n">
+      <c r="K394" s="1" t="n">
         <v>0.02121</v>
       </c>
     </row>
@@ -13873,9 +15058,12 @@
         <v>0.0161</v>
       </c>
       <c r="I395" s="1" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="J395" s="1" t="n">
         <v>0.0163</v>
       </c>
-      <c r="J395" s="1" t="n">
+      <c r="K395" s="1" t="n">
         <v>0.0161</v>
       </c>
     </row>
@@ -13907,10 +15095,13 @@
         <v>0.1357</v>
       </c>
       <c r="I396" s="1" t="n">
+        <v>0.1356</v>
+      </c>
+      <c r="J396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="J396" s="1" t="n">
-        <v>0.1357</v>
+      <c r="K396" s="1" t="n">
+        <v>0.1356</v>
       </c>
     </row>
     <row r="397">
@@ -13941,10 +15132,13 @@
         <v>0.01468</v>
       </c>
       <c r="I397" s="1" t="n">
+        <v>0.01458</v>
+      </c>
+      <c r="J397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="J397" s="1" t="n">
-        <v>0.01468</v>
+      <c r="K397" s="1" t="n">
+        <v>0.01458</v>
       </c>
     </row>
     <row r="398">
@@ -13975,9 +15169,12 @@
         <v>6.901</v>
       </c>
       <c r="I398" s="1" t="n">
+        <v>6.813</v>
+      </c>
+      <c r="J398" s="1" t="n">
         <v>6.955</v>
       </c>
-      <c r="J398" s="1" t="n">
+      <c r="K398" s="1" t="n">
         <v>6.725</v>
       </c>
     </row>
@@ -14009,9 +15206,12 @@
         <v>0.009476</v>
       </c>
       <c r="I399" s="1" t="n">
+        <v>0.009471</v>
+      </c>
+      <c r="J399" s="1" t="n">
         <v>0.009509999999999999</v>
       </c>
-      <c r="J399" s="1" t="n">
+      <c r="K399" s="1" t="n">
         <v>0.009448</v>
       </c>
     </row>
@@ -14043,10 +15243,13 @@
         <v>0.001277</v>
       </c>
       <c r="I400" s="1" t="n">
+        <v>0.001256</v>
+      </c>
+      <c r="J400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="J400" s="1" t="n">
-        <v>0.001264</v>
+      <c r="K400" s="1" t="n">
+        <v>0.001256</v>
       </c>
     </row>
     <row r="401">
@@ -14077,9 +15280,12 @@
         <v>0.01846</v>
       </c>
       <c r="I401" s="1" t="n">
+        <v>0.01846</v>
+      </c>
+      <c r="J401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="J401" s="1" t="n">
+      <c r="K401" s="1" t="n">
         <v>0.01841</v>
       </c>
     </row>
@@ -14111,10 +15317,13 @@
         <v>0.08538999999999999</v>
       </c>
       <c r="I402" s="1" t="n">
+        <v>0.08488999999999999</v>
+      </c>
+      <c r="J402" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="J402" s="1" t="n">
-        <v>0.08538999999999999</v>
+      <c r="K402" s="1" t="n">
+        <v>0.08488999999999999</v>
       </c>
     </row>
     <row r="403">
@@ -14145,10 +15354,13 @@
         <v>0.00553</v>
       </c>
       <c r="I403" s="1" t="n">
+        <v>0.00552</v>
+      </c>
+      <c r="J403" s="1" t="n">
         <v>0.00556</v>
       </c>
-      <c r="J403" s="1" t="n">
-        <v>0.00553</v>
+      <c r="K403" s="1" t="n">
+        <v>0.00552</v>
       </c>
     </row>
     <row r="404">
@@ -14179,10 +15391,13 @@
         <v>0.0434</v>
       </c>
       <c r="I404" s="1" t="n">
+        <v>0.04302</v>
+      </c>
+      <c r="J404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="J404" s="1" t="n">
-        <v>0.0434</v>
+      <c r="K404" s="1" t="n">
+        <v>0.04302</v>
       </c>
     </row>
     <row r="405">
@@ -14213,10 +15428,13 @@
         <v>0.05857</v>
       </c>
       <c r="I405" s="1" t="n">
+        <v>0.05838</v>
+      </c>
+      <c r="J405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="J405" s="1" t="n">
-        <v>0.05857</v>
+      <c r="K405" s="1" t="n">
+        <v>0.05838</v>
       </c>
     </row>
     <row r="406">
@@ -14247,10 +15465,13 @@
         <v>0.01651</v>
       </c>
       <c r="I406" s="1" t="n">
+        <v>0.01647</v>
+      </c>
+      <c r="J406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="J406" s="1" t="n">
-        <v>0.01651</v>
+      <c r="K406" s="1" t="n">
+        <v>0.01647</v>
       </c>
     </row>
     <row r="407">
@@ -14281,10 +15502,13 @@
         <v>0.0426</v>
       </c>
       <c r="I407" s="1" t="n">
+        <v>0.0423</v>
+      </c>
+      <c r="J407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="J407" s="1" t="n">
-        <v>0.0425</v>
+      <c r="K407" s="1" t="n">
+        <v>0.0423</v>
       </c>
     </row>
     <row r="408">
@@ -14315,10 +15539,13 @@
         <v>0.01937</v>
       </c>
       <c r="I408" s="1" t="n">
+        <v>0.01927</v>
+      </c>
+      <c r="J408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="J408" s="1" t="n">
-        <v>0.01937</v>
+      <c r="K408" s="1" t="n">
+        <v>0.01927</v>
       </c>
     </row>
     <row r="409">
@@ -14349,9 +15576,12 @@
         <v>0.446</v>
       </c>
       <c r="I409" s="1" t="n">
+        <v>0.4441</v>
+      </c>
+      <c r="J409" s="1" t="n">
         <v>0.4484</v>
       </c>
-      <c r="J409" s="1" t="n">
+      <c r="K409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -14383,9 +15613,12 @@
         <v>0.04433</v>
       </c>
       <c r="I410" s="1" t="n">
+        <v>0.04419</v>
+      </c>
+      <c r="J410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="J410" s="1" t="n">
+      <c r="K410" s="1" t="n">
         <v>0.04418</v>
       </c>
     </row>
@@ -14417,9 +15650,12 @@
         <v>27.96</v>
       </c>
       <c r="I411" s="1" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="J411" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="J411" s="1" t="n">
+      <c r="K411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -14451,10 +15687,13 @@
         <v>0.03535</v>
       </c>
       <c r="I412" s="1" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="J412" s="1" t="n">
         <v>0.03564</v>
       </c>
-      <c r="J412" s="1" t="n">
-        <v>0.03515</v>
+      <c r="K412" s="1" t="n">
+        <v>0.0351</v>
       </c>
     </row>
     <row r="413">
@@ -14485,9 +15724,12 @@
         <v>0.003414</v>
       </c>
       <c r="I413" s="1" t="n">
+        <v>0.00341</v>
+      </c>
+      <c r="J413" s="1" t="n">
         <v>0.003432</v>
       </c>
-      <c r="J413" s="1" t="n">
+      <c r="K413" s="1" t="n">
         <v>0.00341</v>
       </c>
     </row>
@@ -14519,10 +15761,13 @@
         <v>0.1528</v>
       </c>
       <c r="I414" s="1" t="n">
+        <v>0.1526</v>
+      </c>
+      <c r="J414" s="1" t="n">
         <v>0.1538</v>
       </c>
-      <c r="J414" s="1" t="n">
-        <v>0.1527</v>
+      <c r="K414" s="1" t="n">
+        <v>0.1526</v>
       </c>
     </row>
     <row r="415">
@@ -14553,10 +15798,13 @@
         <v>0.05265</v>
       </c>
       <c r="I415" s="1" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="J415" s="1" t="n">
         <v>0.05288</v>
       </c>
-      <c r="J415" s="1" t="n">
-        <v>0.05258</v>
+      <c r="K415" s="1" t="n">
+        <v>0.0525</v>
       </c>
     </row>
     <row r="416">
@@ -14587,10 +15835,13 @@
         <v>0.00663</v>
       </c>
       <c r="I416" s="1" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="J416" s="1" t="n">
         <v>0.00669</v>
       </c>
-      <c r="J416" s="1" t="n">
-        <v>0.00663</v>
+      <c r="K416" s="1" t="n">
+        <v>0.0066</v>
       </c>
     </row>
     <row r="417">
@@ -14621,10 +15872,13 @@
         <v>0.06065</v>
       </c>
       <c r="I417" s="1" t="n">
+        <v>0.06053</v>
+      </c>
+      <c r="J417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="J417" s="1" t="n">
-        <v>0.06065</v>
+      <c r="K417" s="1" t="n">
+        <v>0.06053</v>
       </c>
     </row>
     <row r="418">
@@ -14655,10 +15909,13 @@
         <v>0.008127000000000001</v>
       </c>
       <c r="I418" s="1" t="n">
+        <v>0.008047</v>
+      </c>
+      <c r="J418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="J418" s="1" t="n">
-        <v>0.008127000000000001</v>
+      <c r="K418" s="1" t="n">
+        <v>0.008047</v>
       </c>
     </row>
     <row r="419">
@@ -14689,9 +15946,12 @@
         <v>0.07516</v>
       </c>
       <c r="I419" s="1" t="n">
+        <v>0.07474</v>
+      </c>
+      <c r="J419" s="1" t="n">
         <v>0.07524</v>
       </c>
-      <c r="J419" s="1" t="n">
+      <c r="K419" s="1" t="n">
         <v>0.07459</v>
       </c>
     </row>
@@ -14723,10 +15983,13 @@
         <v>0.02131</v>
       </c>
       <c r="I420" s="1" t="n">
+        <v>0.02105</v>
+      </c>
+      <c r="J420" s="1" t="n">
         <v>0.02146</v>
       </c>
-      <c r="J420" s="1" t="n">
-        <v>0.0213</v>
+      <c r="K420" s="1" t="n">
+        <v>0.02105</v>
       </c>
     </row>
     <row r="421">
@@ -14757,9 +16020,12 @@
         <v>0.06983</v>
       </c>
       <c r="I421" s="1" t="n">
+        <v>0.06977999999999999</v>
+      </c>
+      <c r="J421" s="1" t="n">
         <v>0.07038999999999999</v>
       </c>
-      <c r="J421" s="1" t="n">
+      <c r="K421" s="1" t="n">
         <v>0.06938999999999999</v>
       </c>
     </row>
@@ -14791,10 +16057,13 @@
         <v>0.01501</v>
       </c>
       <c r="I422" s="1" t="n">
+        <v>0.01493</v>
+      </c>
+      <c r="J422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="J422" s="1" t="n">
-        <v>0.01501</v>
+      <c r="K422" s="1" t="n">
+        <v>0.01493</v>
       </c>
     </row>
     <row r="423">
@@ -14825,10 +16094,13 @@
         <v>0.006662</v>
       </c>
       <c r="I423" s="1" t="n">
+        <v>0.006648</v>
+      </c>
+      <c r="J423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="J423" s="1" t="n">
-        <v>0.006662</v>
+      <c r="K423" s="1" t="n">
+        <v>0.006648</v>
       </c>
     </row>
     <row r="424">
@@ -14859,10 +16131,13 @@
         <v>0.913</v>
       </c>
       <c r="I424" s="1" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="J424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="J424" s="1" t="n">
-        <v>0.913</v>
+      <c r="K424" s="1" t="n">
+        <v>0.912</v>
       </c>
     </row>
     <row r="425">
@@ -14893,10 +16168,13 @@
         <v>0.03558</v>
       </c>
       <c r="I425" s="1" t="n">
+        <v>0.03546</v>
+      </c>
+      <c r="J425" s="1" t="n">
         <v>0.03596</v>
       </c>
-      <c r="J425" s="1" t="n">
-        <v>0.03555</v>
+      <c r="K425" s="1" t="n">
+        <v>0.03546</v>
       </c>
     </row>
     <row r="426">
@@ -14927,9 +16205,12 @@
         <v>1.8</v>
       </c>
       <c r="I426" s="1" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="J426" s="1" t="n">
         <v>1.81</v>
       </c>
-      <c r="J426" s="1" t="n">
+      <c r="K426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -14961,10 +16242,13 @@
         <v>0.12776</v>
       </c>
       <c r="I427" s="1" t="n">
+        <v>0.12736</v>
+      </c>
+      <c r="J427" s="1" t="n">
         <v>0.12835</v>
       </c>
-      <c r="J427" s="1" t="n">
-        <v>0.12771</v>
+      <c r="K427" s="1" t="n">
+        <v>0.12736</v>
       </c>
     </row>
     <row r="428">
@@ -14995,10 +16279,13 @@
         <v>0.05345</v>
       </c>
       <c r="I428" s="1" t="n">
+        <v>0.05297</v>
+      </c>
+      <c r="J428" s="1" t="n">
         <v>0.05362</v>
       </c>
-      <c r="J428" s="1" t="n">
-        <v>0.05325</v>
+      <c r="K428" s="1" t="n">
+        <v>0.05297</v>
       </c>
     </row>
     <row r="429">
@@ -15029,10 +16316,13 @@
         <v>1.3</v>
       </c>
       <c r="I429" s="1" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="J429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="J429" s="1" t="n">
-        <v>1.3</v>
+      <c r="K429" s="1" t="n">
+        <v>1.289</v>
       </c>
     </row>
     <row r="430">
@@ -15063,10 +16353,13 @@
         <v>0.07527</v>
       </c>
       <c r="I430" s="1" t="n">
+        <v>0.07482</v>
+      </c>
+      <c r="J430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="J430" s="1" t="n">
-        <v>0.07527</v>
+      <c r="K430" s="1" t="n">
+        <v>0.07482</v>
       </c>
     </row>
     <row r="431">
@@ -15097,10 +16390,13 @@
         <v>0.1614</v>
       </c>
       <c r="I431" s="1" t="n">
+        <v>0.1588</v>
+      </c>
+      <c r="J431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="J431" s="1" t="n">
-        <v>0.1614</v>
+      <c r="K431" s="1" t="n">
+        <v>0.1588</v>
       </c>
     </row>
     <row r="432">
@@ -15131,10 +16427,13 @@
         <v>1.453</v>
       </c>
       <c r="I432" s="1" t="n">
+        <v>1.445</v>
+      </c>
+      <c r="J432" s="1" t="n">
         <v>1.461</v>
       </c>
-      <c r="J432" s="1" t="n">
-        <v>1.453</v>
+      <c r="K432" s="1" t="n">
+        <v>1.445</v>
       </c>
     </row>
     <row r="433">
@@ -15165,10 +16464,13 @@
         <v>3.291</v>
       </c>
       <c r="I433" s="1" t="n">
+        <v>3.266</v>
+      </c>
+      <c r="J433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="J433" s="1" t="n">
-        <v>3.291</v>
+      <c r="K433" s="1" t="n">
+        <v>3.266</v>
       </c>
     </row>
     <row r="434">
@@ -15199,10 +16501,13 @@
         <v>0.1792</v>
       </c>
       <c r="I434" s="1" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="J434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="J434" s="1" t="n">
-        <v>0.1792</v>
+      <c r="K434" s="1" t="n">
+        <v>0.1783</v>
       </c>
     </row>
     <row r="435">
@@ -15233,10 +16538,13 @@
         <v>0.008616</v>
       </c>
       <c r="I435" s="1" t="n">
+        <v>0.008580000000000001</v>
+      </c>
+      <c r="J435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="J435" s="1" t="n">
-        <v>0.008616</v>
+      <c r="K435" s="1" t="n">
+        <v>0.008580000000000001</v>
       </c>
     </row>
     <row r="436">
@@ -15267,10 +16575,13 @@
         <v>0.2842</v>
       </c>
       <c r="I436" s="1" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="J436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="J436" s="1" t="n">
-        <v>0.2841</v>
+      <c r="K436" s="1" t="n">
+        <v>0.2826</v>
       </c>
     </row>
     <row r="437">
@@ -15301,9 +16612,12 @@
         <v>0.03905</v>
       </c>
       <c r="I437" s="1" t="n">
-        <v>0.03905</v>
+        <v>0.03906</v>
       </c>
       <c r="J437" s="1" t="n">
+        <v>0.03906</v>
+      </c>
+      <c r="K437" s="1" t="n">
         <v>0.03814</v>
       </c>
     </row>
@@ -15335,10 +16649,13 @@
         <v>0.02438</v>
       </c>
       <c r="I438" s="1" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="J438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="J438" s="1" t="n">
-        <v>0.02438</v>
+      <c r="K438" s="1" t="n">
+        <v>0.0242</v>
       </c>
     </row>
     <row r="439">
@@ -15369,9 +16686,12 @@
         <v>0.04409</v>
       </c>
       <c r="I439" s="1" t="n">
+        <v>0.04413</v>
+      </c>
+      <c r="J439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="J439" s="1" t="n">
+      <c r="K439" s="1" t="n">
         <v>0.04405</v>
       </c>
     </row>
@@ -15403,10 +16723,13 @@
         <v>0.0005233</v>
       </c>
       <c r="I440" s="1" t="n">
+        <v>0.0005192</v>
+      </c>
+      <c r="J440" s="1" t="n">
         <v>0.0005258</v>
       </c>
-      <c r="J440" s="1" t="n">
-        <v>0.0005212</v>
+      <c r="K440" s="1" t="n">
+        <v>0.0005192</v>
       </c>
     </row>
     <row r="441">
@@ -15437,9 +16760,12 @@
         <v>0.04405</v>
       </c>
       <c r="I441" s="1" t="n">
-        <v>0.04428</v>
+        <v>0.04451</v>
       </c>
       <c r="J441" s="1" t="n">
+        <v>0.04451</v>
+      </c>
+      <c r="K441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -15471,10 +16797,13 @@
         <v>0.000412</v>
       </c>
       <c r="I442" s="1" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="J442" s="1" t="n">
         <v>0.000416</v>
       </c>
-      <c r="J442" s="1" t="n">
-        <v>0.000412</v>
+      <c r="K442" s="1" t="n">
+        <v>0.00041</v>
       </c>
     </row>
     <row r="443">
@@ -15505,10 +16834,13 @@
         <v>0.09604</v>
       </c>
       <c r="I443" s="1" t="n">
+        <v>0.09528</v>
+      </c>
+      <c r="J443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="J443" s="1" t="n">
-        <v>0.09604</v>
+      <c r="K443" s="1" t="n">
+        <v>0.09528</v>
       </c>
     </row>
     <row r="444">
@@ -15539,9 +16871,12 @@
         <v>2.295</v>
       </c>
       <c r="I444" s="1" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="J444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="J444" s="1" t="n">
+      <c r="K444" s="1" t="n">
         <v>2.289</v>
       </c>
     </row>
@@ -15573,9 +16908,12 @@
         <v>0.2732</v>
       </c>
       <c r="I445" s="1" t="n">
+        <v>0.2715</v>
+      </c>
+      <c r="J445" s="1" t="n">
         <v>0.2741</v>
       </c>
-      <c r="J445" s="1" t="n">
+      <c r="K445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -15607,10 +16945,13 @@
         <v>0.000748</v>
       </c>
       <c r="I446" s="1" t="n">
+        <v>0.0007423</v>
+      </c>
+      <c r="J446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="J446" s="1" t="n">
-        <v>0.000748</v>
+      <c r="K446" s="1" t="n">
+        <v>0.0007423</v>
       </c>
     </row>
     <row r="447">
@@ -15641,10 +16982,13 @@
         <v>0.03835</v>
       </c>
       <c r="I447" s="1" t="n">
+        <v>0.03824</v>
+      </c>
+      <c r="J447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="J447" s="1" t="n">
-        <v>0.03835</v>
+      <c r="K447" s="1" t="n">
+        <v>0.03824</v>
       </c>
     </row>
     <row r="448">
@@ -15675,9 +17019,12 @@
         <v>0.1765</v>
       </c>
       <c r="I448" s="1" t="n">
+        <v>0.1769</v>
+      </c>
+      <c r="J448" s="1" t="n">
         <v>0.1773</v>
       </c>
-      <c r="J448" s="1" t="n">
+      <c r="K448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -15709,10 +17056,13 @@
         <v>0.0428</v>
       </c>
       <c r="I449" s="1" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="J449" s="1" t="n">
         <v>0.04301</v>
       </c>
-      <c r="J449" s="1" t="n">
-        <v>0.0427</v>
+      <c r="K449" s="1" t="n">
+        <v>0.0426</v>
       </c>
     </row>
     <row r="450">
@@ -15743,10 +17093,13 @@
         <v>0.000164</v>
       </c>
       <c r="I450" s="1" t="n">
+        <v>0.0001632</v>
+      </c>
+      <c r="J450" s="1" t="n">
         <v>0.0001654</v>
       </c>
-      <c r="J450" s="1" t="n">
-        <v>0.000164</v>
+      <c r="K450" s="1" t="n">
+        <v>0.0001632</v>
       </c>
     </row>
     <row r="451">
@@ -15777,10 +17130,13 @@
         <v>0.0375</v>
       </c>
       <c r="I451" s="1" t="n">
+        <v>0.03745</v>
+      </c>
+      <c r="J451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="J451" s="1" t="n">
-        <v>0.0375</v>
+      <c r="K451" s="1" t="n">
+        <v>0.03745</v>
       </c>
     </row>
     <row r="452">
@@ -15811,10 +17167,13 @@
         <v>0.009860000000000001</v>
       </c>
       <c r="I452" s="1" t="n">
+        <v>0.00976</v>
+      </c>
+      <c r="J452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="J452" s="1" t="n">
-        <v>0.009860000000000001</v>
+      <c r="K452" s="1" t="n">
+        <v>0.00976</v>
       </c>
     </row>
     <row r="453">
@@ -15845,10 +17204,13 @@
         <v>0.06793</v>
       </c>
       <c r="I453" s="1" t="n">
+        <v>0.06782000000000001</v>
+      </c>
+      <c r="J453" s="1" t="n">
         <v>0.06816</v>
       </c>
-      <c r="J453" s="1" t="n">
-        <v>0.06793</v>
+      <c r="K453" s="1" t="n">
+        <v>0.06782000000000001</v>
       </c>
     </row>
     <row r="454">
@@ -15879,10 +17241,13 @@
         <v>0.007524</v>
       </c>
       <c r="I454" s="1" t="n">
+        <v>0.007496</v>
+      </c>
+      <c r="J454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="J454" s="1" t="n">
-        <v>0.007524</v>
+      <c r="K454" s="1" t="n">
+        <v>0.007496</v>
       </c>
     </row>
     <row r="455">
@@ -15913,10 +17278,13 @@
         <v>0.003337</v>
       </c>
       <c r="I455" s="1" t="n">
+        <v>0.003314</v>
+      </c>
+      <c r="J455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="J455" s="1" t="n">
-        <v>0.003337</v>
+      <c r="K455" s="1" t="n">
+        <v>0.003314</v>
       </c>
     </row>
     <row r="456">
@@ -15947,10 +17315,13 @@
         <v>0.001858</v>
       </c>
       <c r="I456" s="1" t="n">
+        <v>0.001842</v>
+      </c>
+      <c r="J456" s="1" t="n">
         <v>0.001875</v>
       </c>
-      <c r="J456" s="1" t="n">
-        <v>0.001854</v>
+      <c r="K456" s="1" t="n">
+        <v>0.001842</v>
       </c>
     </row>
     <row r="457">
@@ -15981,10 +17352,13 @@
         <v>0.0001756</v>
       </c>
       <c r="I457" s="1" t="n">
+        <v>0.0001745</v>
+      </c>
+      <c r="J457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="J457" s="1" t="n">
-        <v>0.0001756</v>
+      <c r="K457" s="1" t="n">
+        <v>0.0001745</v>
       </c>
     </row>
     <row r="458">
@@ -16015,9 +17389,12 @@
         <v>0.0003915</v>
       </c>
       <c r="I458" s="1" t="n">
+        <v>0.0003889</v>
+      </c>
+      <c r="J458" s="1" t="n">
         <v>0.0003916</v>
       </c>
-      <c r="J458" s="1" t="n">
+      <c r="K458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -16049,9 +17426,12 @@
         <v>0.01406</v>
       </c>
       <c r="I459" s="1" t="n">
+        <v>0.01403</v>
+      </c>
+      <c r="J459" s="1" t="n">
         <v>0.01413</v>
       </c>
-      <c r="J459" s="1" t="n">
+      <c r="K459" s="1" t="n">
         <v>0.01391</v>
       </c>
     </row>
@@ -16083,9 +17463,12 @@
         <v>0.04546</v>
       </c>
       <c r="I460" s="1" t="n">
+        <v>0.04523</v>
+      </c>
+      <c r="J460" s="1" t="n">
         <v>0.04559</v>
       </c>
-      <c r="J460" s="1" t="n">
+      <c r="K460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -16117,10 +17500,13 @@
         <v>0.2825</v>
       </c>
       <c r="I461" s="1" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="J461" s="1" t="n">
         <v>0.2839</v>
       </c>
-      <c r="J461" s="1" t="n">
-        <v>0.2822</v>
+      <c r="K461" s="1" t="n">
+        <v>0.2809</v>
       </c>
     </row>
     <row r="462">
@@ -16151,9 +17537,12 @@
         <v>0.006273</v>
       </c>
       <c r="I462" s="1" t="n">
+        <v>0.006267</v>
+      </c>
+      <c r="J462" s="1" t="n">
         <v>0.006312</v>
       </c>
-      <c r="J462" s="1" t="n">
+      <c r="K462" s="1" t="n">
         <v>0.00622</v>
       </c>
     </row>
@@ -16185,10 +17574,13 @@
         <v>0.007047</v>
       </c>
       <c r="I463" s="1" t="n">
+        <v>0.007032</v>
+      </c>
+      <c r="J463" s="1" t="n">
         <v>0.007088</v>
       </c>
-      <c r="J463" s="1" t="n">
-        <v>0.00704</v>
+      <c r="K463" s="1" t="n">
+        <v>0.007032</v>
       </c>
     </row>
     <row r="464">
@@ -16219,9 +17611,12 @@
         <v>0.2871</v>
       </c>
       <c r="I464" s="1" t="n">
+        <v>0.2876</v>
+      </c>
+      <c r="J464" s="1" t="n">
         <v>0.288</v>
       </c>
-      <c r="J464" s="1" t="n">
+      <c r="K464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -16253,10 +17648,13 @@
         <v>0.08109</v>
       </c>
       <c r="I465" s="1" t="n">
+        <v>0.08076</v>
+      </c>
+      <c r="J465" s="1" t="n">
         <v>0.08183</v>
       </c>
-      <c r="J465" s="1" t="n">
-        <v>0.08078</v>
+      <c r="K465" s="1" t="n">
+        <v>0.08076</v>
       </c>
     </row>
     <row r="466">
@@ -16287,9 +17685,12 @@
         <v>0.6335</v>
       </c>
       <c r="I466" s="1" t="n">
+        <v>0.6321</v>
+      </c>
+      <c r="J466" s="1" t="n">
         <v>0.6368</v>
       </c>
-      <c r="J466" s="1" t="n">
+      <c r="K466" s="1" t="n">
         <v>0.6318</v>
       </c>
     </row>
@@ -16321,9 +17722,12 @@
         <v>0.01485</v>
       </c>
       <c r="I467" s="1" t="n">
+        <v>0.01481</v>
+      </c>
+      <c r="J467" s="1" t="n">
         <v>0.01499</v>
       </c>
-      <c r="J467" s="1" t="n">
+      <c r="K467" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -16355,10 +17759,13 @@
         <v>0.03439</v>
       </c>
       <c r="I468" s="1" t="n">
+        <v>0.03437</v>
+      </c>
+      <c r="J468" s="1" t="n">
         <v>0.03468</v>
       </c>
-      <c r="J468" s="1" t="n">
-        <v>0.03439</v>
+      <c r="K468" s="1" t="n">
+        <v>0.03437</v>
       </c>
     </row>
     <row r="469">
@@ -16389,10 +17796,13 @@
         <v>0.1637</v>
       </c>
       <c r="I469" s="1" t="n">
+        <v>0.1624</v>
+      </c>
+      <c r="J469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="J469" s="1" t="n">
-        <v>0.1637</v>
+      <c r="K469" s="1" t="n">
+        <v>0.1624</v>
       </c>
     </row>
     <row r="470">
@@ -16423,10 +17833,13 @@
         <v>0.4121</v>
       </c>
       <c r="I470" s="1" t="n">
+        <v>0.4091</v>
+      </c>
+      <c r="J470" s="1" t="n">
         <v>0.4151</v>
       </c>
-      <c r="J470" s="1" t="n">
-        <v>0.4121</v>
+      <c r="K470" s="1" t="n">
+        <v>0.4091</v>
       </c>
     </row>
     <row r="471">
@@ -16457,10 +17870,13 @@
         <v>0.06965</v>
       </c>
       <c r="I471" s="1" t="n">
+        <v>0.06947</v>
+      </c>
+      <c r="J471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="J471" s="1" t="n">
-        <v>0.06965</v>
+      <c r="K471" s="1" t="n">
+        <v>0.06947</v>
       </c>
     </row>
     <row r="472">
@@ -16491,10 +17907,13 @@
         <v>0.06721000000000001</v>
       </c>
       <c r="I472" s="1" t="n">
+        <v>0.06641</v>
+      </c>
+      <c r="J472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="J472" s="1" t="n">
-        <v>0.06688</v>
+      <c r="K472" s="1" t="n">
+        <v>0.06641</v>
       </c>
     </row>
     <row r="473">
@@ -16525,10 +17944,13 @@
         <v>0.01632</v>
       </c>
       <c r="I473" s="1" t="n">
+        <v>0.01621</v>
+      </c>
+      <c r="J473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="J473" s="1" t="n">
-        <v>0.01632</v>
+      <c r="K473" s="1" t="n">
+        <v>0.01621</v>
       </c>
     </row>
     <row r="474">
@@ -16559,10 +17981,13 @@
         <v>0.2075</v>
       </c>
       <c r="I474" s="1" t="n">
+        <v>0.2066</v>
+      </c>
+      <c r="J474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="J474" s="1" t="n">
-        <v>0.2075</v>
+      <c r="K474" s="1" t="n">
+        <v>0.2066</v>
       </c>
     </row>
     <row r="475">
@@ -16593,9 +18018,12 @@
         <v>0.04229</v>
       </c>
       <c r="I475" s="1" t="n">
+        <v>0.04222</v>
+      </c>
+      <c r="J475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="J475" s="1" t="n">
+      <c r="K475" s="1" t="n">
         <v>0.04202</v>
       </c>
     </row>
@@ -16627,10 +18055,13 @@
         <v>1.568</v>
       </c>
       <c r="I476" s="1" t="n">
+        <v>1.563</v>
+      </c>
+      <c r="J476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="J476" s="1" t="n">
-        <v>1.568</v>
+      <c r="K476" s="1" t="n">
+        <v>1.563</v>
       </c>
     </row>
     <row r="477">
@@ -16661,10 +18092,13 @@
         <v>0.101</v>
       </c>
       <c r="I477" s="1" t="n">
+        <v>0.1004</v>
+      </c>
+      <c r="J477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="J477" s="1" t="n">
-        <v>0.1008</v>
+      <c r="K477" s="1" t="n">
+        <v>0.1004</v>
       </c>
     </row>
     <row r="478">
@@ -16695,10 +18129,13 @@
         <v>0.001154</v>
       </c>
       <c r="I478" s="1" t="n">
+        <v>0.00115</v>
+      </c>
+      <c r="J478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="J478" s="1" t="n">
-        <v>0.001154</v>
+      <c r="K478" s="1" t="n">
+        <v>0.00115</v>
       </c>
     </row>
     <row r="479">
@@ -16729,9 +18166,12 @@
         <v>0.147</v>
       </c>
       <c r="I479" s="1" t="n">
+        <v>0.1473</v>
+      </c>
+      <c r="J479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="J479" s="1" t="n">
+      <c r="K479" s="1" t="n">
         <v>0.1462</v>
       </c>
     </row>
@@ -16763,10 +18203,13 @@
         <v>0.001725</v>
       </c>
       <c r="I480" s="1" t="n">
+        <v>0.001719</v>
+      </c>
+      <c r="J480" s="1" t="n">
         <v>0.001734</v>
       </c>
-      <c r="J480" s="1" t="n">
-        <v>0.001722</v>
+      <c r="K480" s="1" t="n">
+        <v>0.001719</v>
       </c>
     </row>
     <row r="481">
@@ -16797,10 +18240,13 @@
         <v>0.913</v>
       </c>
       <c r="I481" s="1" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="J481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="J481" s="1" t="n">
-        <v>0.913</v>
+      <c r="K481" s="1" t="n">
+        <v>0.909</v>
       </c>
     </row>
     <row r="482">
@@ -16831,10 +18277,13 @@
         <v>0.13367</v>
       </c>
       <c r="I482" s="1" t="n">
+        <v>0.13336</v>
+      </c>
+      <c r="J482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="J482" s="1" t="n">
-        <v>0.13367</v>
+      <c r="K482" s="1" t="n">
+        <v>0.13336</v>
       </c>
     </row>
     <row r="483">
@@ -16865,10 +18314,13 @@
         <v>0.04035</v>
       </c>
       <c r="I483" s="1" t="n">
+        <v>0.04024</v>
+      </c>
+      <c r="J483" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="J483" s="1" t="n">
-        <v>0.04035</v>
+      <c r="K483" s="1" t="n">
+        <v>0.04024</v>
       </c>
     </row>
     <row r="484">
@@ -16899,9 +18351,12 @@
         <v>0.3046</v>
       </c>
       <c r="I484" s="1" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="J484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="J484" s="1" t="n">
+      <c r="K484" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -16933,9 +18388,12 @@
         <v>0.05692</v>
       </c>
       <c r="I485" s="1" t="n">
+        <v>0.05646</v>
+      </c>
+      <c r="J485" s="1" t="n">
         <v>0.05709</v>
       </c>
-      <c r="J485" s="1" t="n">
+      <c r="K485" s="1" t="n">
         <v>0.05633</v>
       </c>
     </row>
@@ -16967,10 +18425,13 @@
         <v>0.001569</v>
       </c>
       <c r="I486" s="1" t="n">
+        <v>0.001564</v>
+      </c>
+      <c r="J486" s="1" t="n">
         <v>0.001579</v>
       </c>
-      <c r="J486" s="1" t="n">
-        <v>0.001569</v>
+      <c r="K486" s="1" t="n">
+        <v>0.001564</v>
       </c>
     </row>
     <row r="487">
@@ -17001,10 +18462,13 @@
         <v>0.06741</v>
       </c>
       <c r="I487" s="1" t="n">
+        <v>0.06705999999999999</v>
+      </c>
+      <c r="J487" s="1" t="n">
         <v>0.06766999999999999</v>
       </c>
-      <c r="J487" s="1" t="n">
-        <v>0.06716</v>
+      <c r="K487" s="1" t="n">
+        <v>0.06705999999999999</v>
       </c>
     </row>
     <row r="488">
@@ -17035,10 +18499,13 @@
         <v>0.1935</v>
       </c>
       <c r="I488" s="1" t="n">
+        <v>0.1929</v>
+      </c>
+      <c r="J488" s="1" t="n">
         <v>0.1953</v>
       </c>
-      <c r="J488" s="1" t="n">
-        <v>0.1935</v>
+      <c r="K488" s="1" t="n">
+        <v>0.1929</v>
       </c>
     </row>
     <row r="489">
@@ -17069,10 +18536,13 @@
         <v>0.04792</v>
       </c>
       <c r="I489" s="1" t="n">
+        <v>0.04779</v>
+      </c>
+      <c r="J489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="J489" s="1" t="n">
-        <v>0.04792</v>
+      <c r="K489" s="1" t="n">
+        <v>0.04779</v>
       </c>
     </row>
     <row r="490">
@@ -17103,10 +18573,13 @@
         <v>0.1394</v>
       </c>
       <c r="I490" s="1" t="n">
+        <v>0.1389</v>
+      </c>
+      <c r="J490" s="1" t="n">
         <v>0.1401</v>
       </c>
-      <c r="J490" s="1" t="n">
-        <v>0.139</v>
+      <c r="K490" s="1" t="n">
+        <v>0.1389</v>
       </c>
     </row>
     <row r="491">
@@ -17137,9 +18610,12 @@
         <v>0.02246</v>
       </c>
       <c r="I491" s="1" t="n">
+        <v>0.02245</v>
+      </c>
+      <c r="J491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="J491" s="1" t="n">
+      <c r="K491" s="1" t="n">
         <v>0.02243</v>
       </c>
     </row>
@@ -17171,10 +18647,13 @@
         <v>0.00787</v>
       </c>
       <c r="I492" s="1" t="n">
+        <v>0.007761</v>
+      </c>
+      <c r="J492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="J492" s="1" t="n">
-        <v>0.007825</v>
+      <c r="K492" s="1" t="n">
+        <v>0.007761</v>
       </c>
     </row>
     <row r="493">
@@ -17205,10 +18684,13 @@
         <v>0.0005949</v>
       </c>
       <c r="I493" s="1" t="n">
+        <v>0.0005932</v>
+      </c>
+      <c r="J493" s="1" t="n">
         <v>0.0005992</v>
       </c>
-      <c r="J493" s="1" t="n">
-        <v>0.0005949</v>
+      <c r="K493" s="1" t="n">
+        <v>0.0005932</v>
       </c>
     </row>
     <row r="494">
@@ -17239,9 +18721,12 @@
         <v>3.023</v>
       </c>
       <c r="I494" s="1" t="n">
+        <v>3.014</v>
+      </c>
+      <c r="J494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="J494" s="1" t="n">
+      <c r="K494" s="1" t="n">
         <v>2.999</v>
       </c>
     </row>
@@ -17273,10 +18758,13 @@
         <v>0.05082</v>
       </c>
       <c r="I495" s="1" t="n">
+        <v>0.05042</v>
+      </c>
+      <c r="J495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="J495" s="1" t="n">
-        <v>0.05082</v>
+      <c r="K495" s="1" t="n">
+        <v>0.05042</v>
       </c>
     </row>
     <row r="496">
@@ -17307,10 +18795,13 @@
         <v>0.006802</v>
       </c>
       <c r="I496" s="1" t="n">
+        <v>0.00677</v>
+      </c>
+      <c r="J496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="J496" s="1" t="n">
-        <v>0.006802</v>
+      <c r="K496" s="1" t="n">
+        <v>0.00677</v>
       </c>
     </row>
     <row r="497">
@@ -17341,9 +18832,12 @@
         <v>1.302</v>
       </c>
       <c r="I497" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J497" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="J497" s="1" t="n">
+      <c r="K497" s="1" t="n">
         <v>1.299</v>
       </c>
     </row>
@@ -17375,10 +18869,13 @@
         <v>0.03964</v>
       </c>
       <c r="I498" s="1" t="n">
+        <v>0.03957</v>
+      </c>
+      <c r="J498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="J498" s="1" t="n">
-        <v>0.03964</v>
+      <c r="K498" s="1" t="n">
+        <v>0.03957</v>
       </c>
     </row>
     <row r="499">
@@ -17409,10 +18906,13 @@
         <v>0.04166</v>
       </c>
       <c r="I499" s="1" t="n">
+        <v>0.04145</v>
+      </c>
+      <c r="J499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="J499" s="1" t="n">
-        <v>0.04166</v>
+      <c r="K499" s="1" t="n">
+        <v>0.04145</v>
       </c>
     </row>
     <row r="500">
@@ -17443,9 +18943,12 @@
         <v>0.00547</v>
       </c>
       <c r="I500" s="1" t="n">
+        <v>0.00544</v>
+      </c>
+      <c r="J500" s="1" t="n">
         <v>0.00549</v>
       </c>
-      <c r="J500" s="1" t="n">
+      <c r="K500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -17477,10 +18980,13 @@
         <v>0.03617</v>
       </c>
       <c r="I501" s="1" t="n">
+        <v>0.03572</v>
+      </c>
+      <c r="J501" s="1" t="n">
         <v>0.0364</v>
       </c>
-      <c r="J501" s="1" t="n">
-        <v>0.03617</v>
+      <c r="K501" s="1" t="n">
+        <v>0.03572</v>
       </c>
     </row>
     <row r="502">
@@ -17511,10 +19017,13 @@
         <v>0.07321999999999999</v>
       </c>
       <c r="I502" s="1" t="n">
+        <v>0.07288</v>
+      </c>
+      <c r="J502" s="1" t="n">
         <v>0.07342</v>
       </c>
-      <c r="J502" s="1" t="n">
-        <v>0.07321</v>
+      <c r="K502" s="1" t="n">
+        <v>0.07288</v>
       </c>
     </row>
     <row r="503">
@@ -17545,10 +19054,13 @@
         <v>0.0007497</v>
       </c>
       <c r="I503" s="1" t="n">
+        <v>0.0007422</v>
+      </c>
+      <c r="J503" s="1" t="n">
         <v>0.000755</v>
       </c>
-      <c r="J503" s="1" t="n">
-        <v>0.0007497</v>
+      <c r="K503" s="1" t="n">
+        <v>0.0007422</v>
       </c>
     </row>
     <row r="504">
@@ -17579,9 +19091,12 @@
         <v>0.015977</v>
       </c>
       <c r="I504" s="1" t="n">
+        <v>0.015968</v>
+      </c>
+      <c r="J504" s="1" t="n">
         <v>0.016003</v>
       </c>
-      <c r="J504" s="1" t="n">
+      <c r="K504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -17613,10 +19128,13 @@
         <v>0.00707</v>
       </c>
       <c r="I505" s="1" t="n">
+        <v>0.00703</v>
+      </c>
+      <c r="J505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="J505" s="1" t="n">
-        <v>0.00707</v>
+      <c r="K505" s="1" t="n">
+        <v>0.00703</v>
       </c>
     </row>
     <row r="506">
@@ -17647,9 +19165,12 @@
         <v>0.0255</v>
       </c>
       <c r="I506" s="1" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="J506" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="J506" s="1" t="n">
+      <c r="K506" s="1" t="n">
         <v>0.0255</v>
       </c>
     </row>
@@ -17681,9 +19202,12 @@
         <v>0.001357</v>
       </c>
       <c r="I507" s="1" t="n">
+        <v>0.001351</v>
+      </c>
+      <c r="J507" s="1" t="n">
         <v>0.001358</v>
       </c>
-      <c r="J507" s="1" t="n">
+      <c r="K507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -17715,10 +19239,13 @@
         <v>0.2816</v>
       </c>
       <c r="I508" s="1" t="n">
+        <v>0.2805</v>
+      </c>
+      <c r="J508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="J508" s="1" t="n">
-        <v>0.2816</v>
+      <c r="K508" s="1" t="n">
+        <v>0.2805</v>
       </c>
     </row>
     <row r="509">
@@ -17749,10 +19276,13 @@
         <v>0.132</v>
       </c>
       <c r="I509" s="1" t="n">
+        <v>0.1317</v>
+      </c>
+      <c r="J509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="J509" s="1" t="n">
-        <v>0.132</v>
+      <c r="K509" s="1" t="n">
+        <v>0.1317</v>
       </c>
     </row>
     <row r="510">
@@ -17783,10 +19313,13 @@
         <v>0.04934</v>
       </c>
       <c r="I510" s="1" t="n">
+        <v>0.04896</v>
+      </c>
+      <c r="J510" s="1" t="n">
         <v>0.04972</v>
       </c>
-      <c r="J510" s="1" t="n">
-        <v>0.04932</v>
+      <c r="K510" s="1" t="n">
+        <v>0.04896</v>
       </c>
     </row>
     <row r="511">
@@ -17817,10 +19350,13 @@
         <v>0.00275</v>
       </c>
       <c r="I511" s="1" t="n">
+        <v>0.00274</v>
+      </c>
+      <c r="J511" s="1" t="n">
         <v>0.00278</v>
       </c>
-      <c r="J511" s="1" t="n">
-        <v>0.00275</v>
+      <c r="K511" s="1" t="n">
+        <v>0.00274</v>
       </c>
     </row>
     <row r="512">
@@ -17851,10 +19387,13 @@
         <v>0.01538</v>
       </c>
       <c r="I512" s="1" t="n">
+        <v>0.015285</v>
+      </c>
+      <c r="J512" s="1" t="n">
         <v>0.015454</v>
       </c>
-      <c r="J512" s="1" t="n">
-        <v>0.015351</v>
+      <c r="K512" s="1" t="n">
+        <v>0.015285</v>
       </c>
     </row>
     <row r="513">
@@ -17885,10 +19424,13 @@
         <v>0.6925</v>
       </c>
       <c r="I513" s="1" t="n">
+        <v>0.6918</v>
+      </c>
+      <c r="J513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="J513" s="1" t="n">
-        <v>0.6925</v>
+      <c r="K513" s="1" t="n">
+        <v>0.6918</v>
       </c>
     </row>
     <row r="514">
@@ -17919,9 +19461,12 @@
         <v>0.00456</v>
       </c>
       <c r="I514" s="1" t="n">
+        <v>0.004538</v>
+      </c>
+      <c r="J514" s="1" t="n">
         <v>0.004589</v>
       </c>
-      <c r="J514" s="1" t="n">
+      <c r="K514" s="1" t="n">
         <v>0.004534</v>
       </c>
     </row>
@@ -17953,10 +19498,13 @@
         <v>0.005037</v>
       </c>
       <c r="I515" s="1" t="n">
+        <v>0.005008</v>
+      </c>
+      <c r="J515" s="1" t="n">
         <v>0.005066</v>
       </c>
-      <c r="J515" s="1" t="n">
-        <v>0.005037</v>
+      <c r="K515" s="1" t="n">
+        <v>0.005008</v>
       </c>
     </row>
     <row r="516">
@@ -17987,10 +19535,13 @@
         <v>0.06340999999999999</v>
       </c>
       <c r="I516" s="1" t="n">
+        <v>0.06321</v>
+      </c>
+      <c r="J516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="J516" s="1" t="n">
-        <v>0.06340999999999999</v>
+      <c r="K516" s="1" t="n">
+        <v>0.06321</v>
       </c>
     </row>
     <row r="517">
@@ -18021,9 +19572,12 @@
         <v>0.06476999999999999</v>
       </c>
       <c r="I517" s="1" t="n">
+        <v>0.06458</v>
+      </c>
+      <c r="J517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="J517" s="1" t="n">
+      <c r="K517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -18055,10 +19609,13 @@
         <v>0.01206</v>
       </c>
       <c r="I518" s="1" t="n">
+        <v>0.01199</v>
+      </c>
+      <c r="J518" s="1" t="n">
         <v>0.01219</v>
       </c>
-      <c r="J518" s="1" t="n">
-        <v>0.01206</v>
+      <c r="K518" s="1" t="n">
+        <v>0.01199</v>
       </c>
     </row>
     <row r="519">
@@ -18089,9 +19646,12 @@
         <v>0.04772</v>
       </c>
       <c r="I519" s="1" t="n">
+        <v>0.04749</v>
+      </c>
+      <c r="J519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="J519" s="1" t="n">
+      <c r="K519" s="1" t="n">
         <v>0.04743</v>
       </c>
     </row>
@@ -18123,10 +19683,13 @@
         <v>0.0439</v>
       </c>
       <c r="I520" s="1" t="n">
+        <v>0.04349</v>
+      </c>
+      <c r="J520" s="1" t="n">
         <v>0.04411</v>
       </c>
-      <c r="J520" s="1" t="n">
-        <v>0.04384</v>
+      <c r="K520" s="1" t="n">
+        <v>0.04349</v>
       </c>
     </row>
     <row r="521">
@@ -18157,10 +19720,13 @@
         <v>0.00851</v>
       </c>
       <c r="I521" s="1" t="n">
+        <v>0.008461</v>
+      </c>
+      <c r="J521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="J521" s="1" t="n">
-        <v>0.00851</v>
+      <c r="K521" s="1" t="n">
+        <v>0.008461</v>
       </c>
     </row>
     <row r="522">
@@ -18191,9 +19757,12 @@
         <v>0.08906</v>
       </c>
       <c r="I522" s="1" t="n">
+        <v>0.08908000000000001</v>
+      </c>
+      <c r="J522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="J522" s="1" t="n">
+      <c r="K522" s="1" t="n">
         <v>0.08906</v>
       </c>
     </row>
@@ -18225,10 +19794,13 @@
         <v>0.006453</v>
       </c>
       <c r="I523" s="1" t="n">
+        <v>0.006433</v>
+      </c>
+      <c r="J523" s="1" t="n">
         <v>0.006492</v>
       </c>
-      <c r="J523" s="1" t="n">
-        <v>0.006453</v>
+      <c r="K523" s="1" t="n">
+        <v>0.006433</v>
       </c>
     </row>
     <row r="524">
@@ -18259,10 +19831,13 @@
         <v>0.01656</v>
       </c>
       <c r="I524" s="1" t="n">
+        <v>0.01646</v>
+      </c>
+      <c r="J524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="J524" s="1" t="n">
-        <v>0.01656</v>
+      <c r="K524" s="1" t="n">
+        <v>0.01646</v>
       </c>
     </row>
     <row r="525">
@@ -18293,9 +19868,12 @@
         <v>0.01787</v>
       </c>
       <c r="I525" s="1" t="n">
+        <v>0.01787</v>
+      </c>
+      <c r="J525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="J525" s="1" t="n">
+      <c r="K525" s="1" t="n">
         <v>0.01787</v>
       </c>
     </row>
@@ -18327,10 +19905,13 @@
         <v>0.07913000000000001</v>
       </c>
       <c r="I526" s="1" t="n">
+        <v>0.07883</v>
+      </c>
+      <c r="J526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="J526" s="1" t="n">
-        <v>0.07913000000000001</v>
+      <c r="K526" s="1" t="n">
+        <v>0.07883</v>
       </c>
     </row>
     <row r="527">
@@ -18361,10 +19942,13 @@
         <v>0.01618</v>
       </c>
       <c r="I527" s="1" t="n">
+        <v>0.01611</v>
+      </c>
+      <c r="J527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="J527" s="1" t="n">
-        <v>0.01618</v>
+      <c r="K527" s="1" t="n">
+        <v>0.01611</v>
       </c>
     </row>
     <row r="528">
@@ -18395,9 +19979,12 @@
         <v>0.00418</v>
       </c>
       <c r="I528" s="1" t="n">
+        <v>0.004183</v>
+      </c>
+      <c r="J528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="J528" s="1" t="n">
+      <c r="K528" s="1" t="n">
         <v>0.004164</v>
       </c>
     </row>
@@ -18429,10 +20016,13 @@
         <v>0.003705</v>
       </c>
       <c r="I529" s="1" t="n">
+        <v>0.003694</v>
+      </c>
+      <c r="J529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="J529" s="1" t="n">
-        <v>0.003698</v>
+      <c r="K529" s="1" t="n">
+        <v>0.003694</v>
       </c>
     </row>
     <row r="530">
@@ -18463,9 +20053,12 @@
         <v>1.318</v>
       </c>
       <c r="I530" s="1" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="J530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="J530" s="1" t="n">
+      <c r="K530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -18497,10 +20090,13 @@
         <v>0.4917</v>
       </c>
       <c r="I531" s="1" t="n">
+        <v>0.4896</v>
+      </c>
+      <c r="J531" s="1" t="n">
         <v>0.494</v>
       </c>
-      <c r="J531" s="1" t="n">
-        <v>0.4912</v>
+      <c r="K531" s="1" t="n">
+        <v>0.4896</v>
       </c>
     </row>
     <row r="532">
@@ -18531,9 +20127,12 @@
         <v>0.03074</v>
       </c>
       <c r="I532" s="1" t="n">
+        <v>0.03065</v>
+      </c>
+      <c r="J532" s="1" t="n">
         <v>0.03091</v>
       </c>
-      <c r="J532" s="1" t="n">
+      <c r="K532" s="1" t="n">
         <v>0.03058</v>
       </c>
     </row>
@@ -18565,9 +20164,12 @@
         <v>0.153</v>
       </c>
       <c r="I533" s="1" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="J533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="J533" s="1" t="n">
+      <c r="K533" s="1" t="n">
         <v>0.153</v>
       </c>
     </row>
@@ -18599,9 +20201,12 @@
         <v>0.054</v>
       </c>
       <c r="I534" s="1" t="n">
+        <v>0.05393</v>
+      </c>
+      <c r="J534" s="1" t="n">
         <v>0.05424</v>
       </c>
-      <c r="J534" s="1" t="n">
+      <c r="K534" s="1" t="n">
         <v>0.05388</v>
       </c>
     </row>
@@ -18633,10 +20238,13 @@
         <v>0.01503</v>
       </c>
       <c r="I535" s="1" t="n">
+        <v>0.01498</v>
+      </c>
+      <c r="J535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="J535" s="1" t="n">
-        <v>0.01501</v>
+      <c r="K535" s="1" t="n">
+        <v>0.01498</v>
       </c>
     </row>
     <row r="536">
@@ -18667,9 +20275,12 @@
         <v>0.05865</v>
       </c>
       <c r="I536" s="1" t="n">
+        <v>0.05832</v>
+      </c>
+      <c r="J536" s="1" t="n">
         <v>0.05879</v>
       </c>
-      <c r="J536" s="1" t="n">
+      <c r="K536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -18701,10 +20312,13 @@
         <v>0.05488</v>
       </c>
       <c r="I537" s="1" t="n">
+        <v>0.05481</v>
+      </c>
+      <c r="J537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="J537" s="1" t="n">
-        <v>0.05488</v>
+      <c r="K537" s="1" t="n">
+        <v>0.05481</v>
       </c>
     </row>
     <row r="538">
@@ -18735,9 +20349,12 @@
         <v>0.1068</v>
       </c>
       <c r="I538" s="1" t="n">
+        <v>0.1059</v>
+      </c>
+      <c r="J538" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="J538" s="1" t="n">
+      <c r="K538" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -18769,10 +20386,13 @@
         <v>0.01281</v>
       </c>
       <c r="I539" s="1" t="n">
+        <v>0.01278</v>
+      </c>
+      <c r="J539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="J539" s="1" t="n">
-        <v>0.01281</v>
+      <c r="K539" s="1" t="n">
+        <v>0.01278</v>
       </c>
     </row>
     <row r="540">
@@ -18803,10 +20423,13 @@
         <v>0.1749</v>
       </c>
       <c r="I540" s="1" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="J540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="J540" s="1" t="n">
-        <v>0.1749</v>
+      <c r="K540" s="1" t="n">
+        <v>0.174</v>
       </c>
     </row>
     <row r="541">
@@ -18837,10 +20460,13 @@
         <v>0.1227</v>
       </c>
       <c r="I541" s="1" t="n">
+        <v>0.1226</v>
+      </c>
+      <c r="J541" s="1" t="n">
         <v>0.1239</v>
       </c>
-      <c r="J541" s="1" t="n">
-        <v>0.1227</v>
+      <c r="K541" s="1" t="n">
+        <v>0.1226</v>
       </c>
     </row>
     <row r="542">
@@ -18871,10 +20497,13 @@
         <v>0.02493</v>
       </c>
       <c r="I542" s="1" t="n">
+        <v>0.02481</v>
+      </c>
+      <c r="J542" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="J542" s="1" t="n">
-        <v>0.02489</v>
+      <c r="K542" s="1" t="n">
+        <v>0.02481</v>
       </c>
     </row>
     <row r="543">
@@ -18905,9 +20534,12 @@
         <v>0.0588</v>
       </c>
       <c r="I543" s="1" t="n">
+        <v>0.0586</v>
+      </c>
+      <c r="J543" s="1" t="n">
         <v>0.059</v>
       </c>
-      <c r="J543" s="1" t="n">
+      <c r="K543" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K543"/>
+  <dimension ref="A1:L543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -428,8 +428,9 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,10 +481,15 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>price_02:00</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -520,10 +526,13 @@
         <v>71185.89999999999</v>
       </c>
       <c r="J2" s="1" t="n">
+        <v>70995.10000000001</v>
+      </c>
+      <c r="K2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="K2" s="1" t="n">
-        <v>71185.89999999999</v>
+      <c r="L2" s="1" t="n">
+        <v>70995.10000000001</v>
       </c>
     </row>
     <row r="3">
@@ -557,10 +566,13 @@
         <v>2105.84</v>
       </c>
       <c r="J3" s="1" t="n">
+        <v>2102.04</v>
+      </c>
+      <c r="K3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="K3" s="1" t="n">
-        <v>2105.84</v>
+      <c r="L3" s="1" t="n">
+        <v>2102.04</v>
       </c>
     </row>
     <row r="4">
@@ -594,10 +606,13 @@
         <v>88.86</v>
       </c>
       <c r="J4" s="1" t="n">
+        <v>88.81999999999999</v>
+      </c>
+      <c r="K4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="K4" s="1" t="n">
-        <v>88.86</v>
+      <c r="L4" s="1" t="n">
+        <v>88.81999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -631,9 +646,12 @@
         <v>3.845</v>
       </c>
       <c r="J5" s="1" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="L5" s="1" t="n">
         <v>3.77</v>
       </c>
     </row>
@@ -668,10 +686,13 @@
         <v>1.3962</v>
       </c>
       <c r="J6" s="1" t="n">
+        <v>1.3931</v>
+      </c>
+      <c r="K6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="K6" s="1" t="n">
-        <v>1.3962</v>
+      <c r="L6" s="1" t="n">
+        <v>1.3931</v>
       </c>
     </row>
     <row r="7">
@@ -705,10 +726,13 @@
         <v>0.09636</v>
       </c>
       <c r="J7" s="1" t="n">
+        <v>0.09601</v>
+      </c>
+      <c r="K7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="K7" s="1" t="n">
-        <v>0.09636</v>
+      <c r="L7" s="1" t="n">
+        <v>0.09601</v>
       </c>
     </row>
     <row r="8">
@@ -742,9 +766,12 @@
         <v>0.014164</v>
       </c>
       <c r="J8" s="1" t="n">
+        <v>0.014443</v>
+      </c>
+      <c r="K8" s="1" t="n">
         <v>0.014568</v>
       </c>
-      <c r="K8" s="1" t="n">
+      <c r="L8" s="1" t="n">
         <v>0.014064</v>
       </c>
     </row>
@@ -779,10 +806,13 @@
         <v>656.64</v>
       </c>
       <c r="J9" s="1" t="n">
+        <v>655.72</v>
+      </c>
+      <c r="K9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="K9" s="1" t="n">
-        <v>656.64</v>
+      <c r="L9" s="1" t="n">
+        <v>655.72</v>
       </c>
     </row>
     <row r="10">
@@ -816,9 +846,12 @@
         <v>19.544</v>
       </c>
       <c r="J10" s="1" t="n">
+        <v>19.515</v>
+      </c>
+      <c r="K10" s="1" t="n">
         <v>19.544</v>
       </c>
-      <c r="K10" s="1" t="n">
+      <c r="L10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -853,10 +886,13 @@
         <v>0.0034204</v>
       </c>
       <c r="J11" s="1" t="n">
+        <v>0.0034117</v>
+      </c>
+      <c r="K11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="K11" s="1" t="n">
-        <v>0.0034204</v>
+      <c r="L11" s="1" t="n">
+        <v>0.0034117</v>
       </c>
     </row>
     <row r="12">
@@ -890,9 +926,12 @@
         <v>36.561</v>
       </c>
       <c r="J12" s="1" t="n">
-        <v>36.561</v>
+        <v>36.656</v>
       </c>
       <c r="K12" s="1" t="n">
+        <v>36.656</v>
+      </c>
+      <c r="L12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -927,9 +966,12 @@
         <v>212.33</v>
       </c>
       <c r="J13" s="1" t="n">
+        <v>212.77</v>
+      </c>
+      <c r="K13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="K13" s="1" t="n">
+      <c r="L13" s="1" t="n">
         <v>212.33</v>
       </c>
     </row>
@@ -964,10 +1006,13 @@
         <v>0.0011153</v>
       </c>
       <c r="J14" s="1" t="n">
+        <v>0.0011148</v>
+      </c>
+      <c r="K14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="K14" s="1" t="n">
-        <v>0.0011153</v>
+      <c r="L14" s="1" t="n">
+        <v>0.0011148</v>
       </c>
     </row>
     <row r="15">
@@ -1001,9 +1046,12 @@
         <v>0.2907</v>
       </c>
       <c r="J15" s="1" t="n">
+        <v>0.28996</v>
+      </c>
+      <c r="K15" s="1" t="n">
         <v>0.29276</v>
       </c>
-      <c r="K15" s="1" t="n">
+      <c r="L15" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -1038,9 +1086,12 @@
         <v>233.64</v>
       </c>
       <c r="J16" s="1" t="n">
+        <v>234.3</v>
+      </c>
+      <c r="K16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="K16" s="1" t="n">
+      <c r="L16" s="1" t="n">
         <v>230.3</v>
       </c>
     </row>
@@ -1075,9 +1126,12 @@
         <v>0.9963</v>
       </c>
       <c r="J17" s="1" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="K17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="K17" s="1" t="n">
+      <c r="L17" s="1" t="n">
         <v>0.9963</v>
       </c>
     </row>
@@ -1112,10 +1166,13 @@
         <v>0.2681</v>
       </c>
       <c r="J18" s="1" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="K18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="K18" s="1" t="n">
-        <v>0.2681</v>
+      <c r="L18" s="1" t="n">
+        <v>0.2671</v>
       </c>
     </row>
     <row r="19">
@@ -1149,10 +1206,13 @@
         <v>9.773</v>
       </c>
       <c r="J19" s="1" t="n">
+        <v>9.755000000000001</v>
+      </c>
+      <c r="K19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="K19" s="1" t="n">
-        <v>9.773</v>
+      <c r="L19" s="1" t="n">
+        <v>9.755000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -1186,9 +1246,12 @@
         <v>5056.39</v>
       </c>
       <c r="J20" s="1" t="n">
+        <v>5045.1</v>
+      </c>
+      <c r="K20" s="1" t="n">
         <v>5059.14</v>
       </c>
-      <c r="K20" s="1" t="n">
+      <c r="L20" s="1" t="n">
         <v>5033.31</v>
       </c>
     </row>
@@ -1223,10 +1286,13 @@
         <v>462.45</v>
       </c>
       <c r="J21" s="1" t="n">
+        <v>462.36</v>
+      </c>
+      <c r="K21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="K21" s="1" t="n">
-        <v>462.45</v>
+      <c r="L21" s="1" t="n">
+        <v>462.36</v>
       </c>
     </row>
     <row r="22">
@@ -1260,9 +1326,12 @@
         <v>1.4445</v>
       </c>
       <c r="J22" s="1" t="n">
+        <v>1.4452</v>
+      </c>
+      <c r="K22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="K22" s="1" t="n">
+      <c r="L22" s="1" t="n">
         <v>1.4185</v>
       </c>
     </row>
@@ -1297,9 +1366,12 @@
         <v>1.0792</v>
       </c>
       <c r="J23" s="1" t="n">
+        <v>1.0812</v>
+      </c>
+      <c r="K23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="K23" s="1" t="n">
+      <c r="L23" s="1" t="n">
         <v>1.0691</v>
       </c>
     </row>
@@ -1334,10 +1406,13 @@
         <v>1.349</v>
       </c>
       <c r="J24" s="1" t="n">
+        <v>1.346</v>
+      </c>
+      <c r="K24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="K24" s="1" t="n">
-        <v>1.349</v>
+      <c r="L24" s="1" t="n">
+        <v>1.346</v>
       </c>
     </row>
     <row r="25">
@@ -1371,10 +1446,13 @@
         <v>9.153</v>
       </c>
       <c r="J25" s="1" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="K25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="K25" s="1" t="n">
-        <v>9.153</v>
+      <c r="L25" s="1" t="n">
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1408,9 +1486,12 @@
         <v>0.3734</v>
       </c>
       <c r="J26" s="1" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="K26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="K26" s="1" t="n">
+      <c r="L26" s="1" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -1445,10 +1526,13 @@
         <v>0.877</v>
       </c>
       <c r="J27" s="1" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="K27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="K27" s="1" t="n">
-        <v>0.877</v>
+      <c r="L27" s="1" t="n">
+        <v>0.876</v>
       </c>
     </row>
     <row r="28">
@@ -1482,9 +1566,12 @@
         <v>1.796</v>
       </c>
       <c r="J28" s="1" t="n">
+        <v>1.806</v>
+      </c>
+      <c r="K28" s="1" t="n">
         <v>1.823</v>
       </c>
-      <c r="K28" s="1" t="n">
+      <c r="L28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -1519,10 +1606,13 @@
         <v>0.1102</v>
       </c>
       <c r="J29" s="1" t="n">
+        <v>0.1096</v>
+      </c>
+      <c r="K29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="K29" s="1" t="n">
-        <v>0.1102</v>
+      <c r="L29" s="1" t="n">
+        <v>0.1096</v>
       </c>
     </row>
     <row r="30">
@@ -1556,9 +1646,12 @@
         <v>0.002045</v>
       </c>
       <c r="J30" s="1" t="n">
+        <v>0.002046</v>
+      </c>
+      <c r="K30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="K30" s="1" t="n">
+      <c r="L30" s="1" t="n">
         <v>0.002045</v>
       </c>
     </row>
@@ -1593,9 +1686,12 @@
         <v>1.48</v>
       </c>
       <c r="J31" s="1" t="n">
+        <v>1.481</v>
+      </c>
+      <c r="K31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="K31" s="1" t="n">
+      <c r="L31" s="1" t="n">
         <v>1.48</v>
       </c>
     </row>
@@ -1630,9 +1726,12 @@
         <v>0.1739</v>
       </c>
       <c r="J32" s="1" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="K32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="K32" s="1" t="n">
+      <c r="L32" s="1" t="n">
         <v>0.1739</v>
       </c>
     </row>
@@ -1667,10 +1766,13 @@
         <v>0.1042</v>
       </c>
       <c r="J33" s="1" t="n">
+        <v>0.1041</v>
+      </c>
+      <c r="K33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="K33" s="1" t="n">
-        <v>0.1042</v>
+      <c r="L33" s="1" t="n">
+        <v>0.1041</v>
       </c>
     </row>
     <row r="34">
@@ -1704,9 +1806,12 @@
         <v>113.01</v>
       </c>
       <c r="J34" s="1" t="n">
+        <v>113.04</v>
+      </c>
+      <c r="K34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="K34" s="1" t="n">
+      <c r="L34" s="1" t="n">
         <v>113.01</v>
       </c>
     </row>
@@ -1741,10 +1846,13 @@
         <v>6.764</v>
       </c>
       <c r="J35" s="1" t="n">
+        <v>6.711</v>
+      </c>
+      <c r="K35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="K35" s="1" t="n">
-        <v>6.764</v>
+      <c r="L35" s="1" t="n">
+        <v>6.711</v>
       </c>
     </row>
     <row r="36">
@@ -1778,9 +1886,12 @@
         <v>0.016815</v>
       </c>
       <c r="J36" s="1" t="n">
+        <v>0.01709</v>
+      </c>
+      <c r="K36" s="1" t="n">
         <v>0.017421</v>
       </c>
-      <c r="K36" s="1" t="n">
+      <c r="L36" s="1" t="n">
         <v>0.016815</v>
       </c>
     </row>
@@ -1815,9 +1926,12 @@
         <v>0.361</v>
       </c>
       <c r="J37" s="1" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="K37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="K37" s="1" t="n">
+      <c r="L37" s="1" t="n">
         <v>0.361</v>
       </c>
     </row>
@@ -1852,9 +1966,12 @@
         <v>55.32</v>
       </c>
       <c r="J38" s="1" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="K38" s="1" t="n">
         <v>55.79</v>
       </c>
-      <c r="K38" s="1" t="n">
+      <c r="L38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -1889,9 +2006,12 @@
         <v>0.59932</v>
       </c>
       <c r="J39" s="1" t="n">
+        <v>0.59781</v>
+      </c>
+      <c r="K39" s="1" t="n">
         <v>0.59932</v>
       </c>
-      <c r="K39" s="1" t="n">
+      <c r="L39" s="1" t="n">
         <v>0.58131</v>
       </c>
     </row>
@@ -1926,10 +2046,13 @@
         <v>4.038</v>
       </c>
       <c r="J40" s="1" t="n">
+        <v>4.036</v>
+      </c>
+      <c r="K40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="K40" s="1" t="n">
-        <v>4.038</v>
+      <c r="L40" s="1" t="n">
+        <v>4.036</v>
       </c>
     </row>
     <row r="41">
@@ -1963,9 +2086,12 @@
         <v>0.05015</v>
       </c>
       <c r="J41" s="1" t="n">
-        <v>0.05015</v>
+        <v>0.05054</v>
       </c>
       <c r="K41" s="1" t="n">
+        <v>0.05054</v>
+      </c>
+      <c r="L41" s="1" t="n">
         <v>0.04927</v>
       </c>
     </row>
@@ -2000,9 +2126,12 @@
         <v>0.7006</v>
       </c>
       <c r="J42" s="1" t="n">
+        <v>0.7015</v>
+      </c>
+      <c r="K42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="K42" s="1" t="n">
+      <c r="L42" s="1" t="n">
         <v>0.7006</v>
       </c>
     </row>
@@ -2037,10 +2166,13 @@
         <v>0.23214</v>
       </c>
       <c r="J43" s="1" t="n">
+        <v>0.23207</v>
+      </c>
+      <c r="K43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="K43" s="1" t="n">
-        <v>0.23214</v>
+      <c r="L43" s="1" t="n">
+        <v>0.23207</v>
       </c>
     </row>
     <row r="44">
@@ -2074,9 +2206,12 @@
         <v>0.3539</v>
       </c>
       <c r="J44" s="1" t="n">
-        <v>0.35416</v>
+        <v>0.35528</v>
       </c>
       <c r="K44" s="1" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="L44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -2111,9 +2246,12 @@
         <v>0.1699</v>
       </c>
       <c r="J45" s="1" t="n">
+        <v>0.1703</v>
+      </c>
+      <c r="K45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="K45" s="1" t="n">
+      <c r="L45" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -2148,10 +2286,13 @@
         <v>0.0263</v>
       </c>
       <c r="J46" s="1" t="n">
+        <v>0.0261</v>
+      </c>
+      <c r="K46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="K46" s="1" t="n">
-        <v>0.0262</v>
+      <c r="L46" s="1" t="n">
+        <v>0.0261</v>
       </c>
     </row>
     <row r="47">
@@ -2185,10 +2326,13 @@
         <v>0.005968</v>
       </c>
       <c r="J47" s="1" t="n">
+        <v>0.005961</v>
+      </c>
+      <c r="K47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="K47" s="1" t="n">
-        <v>0.005968</v>
+      <c r="L47" s="1" t="n">
+        <v>0.005961</v>
       </c>
     </row>
     <row r="48">
@@ -2222,9 +2366,12 @@
         <v>0.007349</v>
       </c>
       <c r="J48" s="1" t="n">
+        <v>0.00737</v>
+      </c>
+      <c r="K48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="K48" s="1" t="n">
+      <c r="L48" s="1" t="n">
         <v>0.007349</v>
       </c>
     </row>
@@ -2259,10 +2406,13 @@
         <v>0.1078</v>
       </c>
       <c r="J49" s="1" t="n">
+        <v>0.1077</v>
+      </c>
+      <c r="K49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="K49" s="1" t="n">
-        <v>0.1078</v>
+      <c r="L49" s="1" t="n">
+        <v>0.1077</v>
       </c>
     </row>
     <row r="50">
@@ -2296,9 +2446,12 @@
         <v>0.04068</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>0.04068</v>
+        <v>0.04075</v>
       </c>
       <c r="K50" s="1" t="n">
+        <v>0.04075</v>
+      </c>
+      <c r="L50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -2333,9 +2486,12 @@
         <v>0.1617</v>
       </c>
       <c r="J51" s="1" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="K51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="K51" s="1" t="n">
+      <c r="L51" s="1" t="n">
         <v>0.1617</v>
       </c>
     </row>
@@ -2370,10 +2526,13 @@
         <v>0.00351</v>
       </c>
       <c r="J52" s="1" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="K52" s="1" t="n">
         <v>0.00357</v>
       </c>
-      <c r="K52" s="1" t="n">
-        <v>0.00351</v>
+      <c r="L52" s="1" t="n">
+        <v>0.0035</v>
       </c>
     </row>
     <row r="53">
@@ -2407,9 +2566,12 @@
         <v>2.622</v>
       </c>
       <c r="J53" s="1" t="n">
+        <v>2.622</v>
+      </c>
+      <c r="K53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="K53" s="1" t="n">
+      <c r="L53" s="1" t="n">
         <v>2.622</v>
       </c>
     </row>
@@ -2444,10 +2606,13 @@
         <v>0.006191</v>
       </c>
       <c r="J54" s="1" t="n">
+        <v>0.006188</v>
+      </c>
+      <c r="K54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="K54" s="1" t="n">
-        <v>0.006191</v>
+      <c r="L54" s="1" t="n">
+        <v>0.006188</v>
       </c>
     </row>
     <row r="55">
@@ -2481,9 +2646,12 @@
         <v>0.02955</v>
       </c>
       <c r="J55" s="1" t="n">
+        <v>0.03013</v>
+      </c>
+      <c r="K55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="K55" s="1" t="n">
+      <c r="L55" s="1" t="n">
         <v>0.02879</v>
       </c>
     </row>
@@ -2518,9 +2686,12 @@
         <v>0.7352</v>
       </c>
       <c r="J56" s="1" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="K56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="K56" s="1" t="n">
+      <c r="L56" s="1" t="n">
         <v>0.7352</v>
       </c>
     </row>
@@ -2555,9 +2726,12 @@
         <v>0.1034</v>
       </c>
       <c r="J57" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="K57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="K57" s="1" t="n">
+      <c r="L57" s="1" t="n">
         <v>0.1034</v>
       </c>
     </row>
@@ -2592,10 +2766,13 @@
         <v>0.9374</v>
       </c>
       <c r="J58" s="1" t="n">
+        <v>0.9355</v>
+      </c>
+      <c r="K58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="K58" s="1" t="n">
-        <v>0.9374</v>
+      <c r="L58" s="1" t="n">
+        <v>0.9355</v>
       </c>
     </row>
     <row r="59">
@@ -2629,9 +2806,12 @@
         <v>0.08645</v>
       </c>
       <c r="J59" s="1" t="n">
+        <v>0.08598</v>
+      </c>
+      <c r="K59" s="1" t="n">
         <v>0.08704000000000001</v>
       </c>
-      <c r="K59" s="1" t="n">
+      <c r="L59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -2666,9 +2846,12 @@
         <v>0.06929</v>
       </c>
       <c r="J60" s="1" t="n">
-        <v>0.07001</v>
+        <v>0.07003</v>
       </c>
       <c r="K60" s="1" t="n">
+        <v>0.07003</v>
+      </c>
+      <c r="L60" s="1" t="n">
         <v>0.06924</v>
       </c>
     </row>
@@ -2703,9 +2886,12 @@
         <v>0.05445</v>
       </c>
       <c r="J61" s="1" t="n">
+        <v>0.05462</v>
+      </c>
+      <c r="K61" s="1" t="n">
         <v>0.05523</v>
       </c>
-      <c r="K61" s="1" t="n">
+      <c r="L61" s="1" t="n">
         <v>0.05445</v>
       </c>
     </row>
@@ -2740,9 +2926,12 @@
         <v>0.009516999999999999</v>
       </c>
       <c r="J62" s="1" t="n">
+        <v>0.009816</v>
+      </c>
+      <c r="K62" s="1" t="n">
         <v>0.010194</v>
       </c>
-      <c r="K62" s="1" t="n">
+      <c r="L62" s="1" t="n">
         <v>0.009387</v>
       </c>
     </row>
@@ -2777,9 +2966,12 @@
         <v>0.29028</v>
       </c>
       <c r="J63" s="1" t="n">
-        <v>0.29032</v>
+        <v>0.29049</v>
       </c>
       <c r="K63" s="1" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="L63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -2814,9 +3006,12 @@
         <v>0.074</v>
       </c>
       <c r="J64" s="1" t="n">
-        <v>0.07489</v>
+        <v>0.07511</v>
       </c>
       <c r="K64" s="1" t="n">
+        <v>0.07511</v>
+      </c>
+      <c r="L64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -2851,9 +3046,12 @@
         <v>0.3138</v>
       </c>
       <c r="J65" s="1" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="K65" s="1" t="n">
         <v>0.3155</v>
       </c>
-      <c r="K65" s="1" t="n">
+      <c r="L65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -2888,10 +3086,13 @@
         <v>0.16242</v>
       </c>
       <c r="J66" s="1" t="n">
+        <v>0.16235</v>
+      </c>
+      <c r="K66" s="1" t="n">
         <v>0.16461</v>
       </c>
-      <c r="K66" s="1" t="n">
-        <v>0.16242</v>
+      <c r="L66" s="1" t="n">
+        <v>0.16235</v>
       </c>
     </row>
     <row r="67">
@@ -2925,9 +3126,12 @@
         <v>0.11999</v>
       </c>
       <c r="J67" s="1" t="n">
+        <v>0.11951</v>
+      </c>
+      <c r="K67" s="1" t="n">
         <v>0.11999</v>
       </c>
-      <c r="K67" s="1" t="n">
+      <c r="L67" s="1" t="n">
         <v>0.11919</v>
       </c>
     </row>
@@ -2962,9 +3166,12 @@
         <v>0.09548</v>
       </c>
       <c r="J68" s="1" t="n">
+        <v>0.09556000000000001</v>
+      </c>
+      <c r="K68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="K68" s="1" t="n">
+      <c r="L68" s="1" t="n">
         <v>0.09548</v>
       </c>
     </row>
@@ -2999,9 +3206,12 @@
         <v>0.1239</v>
       </c>
       <c r="J69" s="1" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="K69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="K69" s="1" t="n">
+      <c r="L69" s="1" t="n">
         <v>0.1239</v>
       </c>
     </row>
@@ -3036,10 +3246,13 @@
         <v>8.502000000000001</v>
       </c>
       <c r="J70" s="1" t="n">
+        <v>8.494</v>
+      </c>
+      <c r="K70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="K70" s="1" t="n">
-        <v>8.502000000000001</v>
+      <c r="L70" s="1" t="n">
+        <v>8.494</v>
       </c>
     </row>
     <row r="71">
@@ -3073,9 +3286,12 @@
         <v>0.238</v>
       </c>
       <c r="J71" s="1" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="K71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="K71" s="1" t="n">
+      <c r="L71" s="1" t="n">
         <v>0.238</v>
       </c>
     </row>
@@ -3110,10 +3326,13 @@
         <v>0.0504</v>
       </c>
       <c r="J72" s="1" t="n">
+        <v>0.05012</v>
+      </c>
+      <c r="K72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="K72" s="1" t="n">
-        <v>0.0504</v>
+      <c r="L72" s="1" t="n">
+        <v>0.05012</v>
       </c>
     </row>
     <row r="73">
@@ -3147,9 +3366,12 @@
         <v>0.05062</v>
       </c>
       <c r="J73" s="1" t="n">
+        <v>0.05036</v>
+      </c>
+      <c r="K73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="K73" s="1" t="n">
+      <c r="L73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -3184,9 +3406,12 @@
         <v>0.1253</v>
       </c>
       <c r="J74" s="1" t="n">
+        <v>0.1257</v>
+      </c>
+      <c r="K74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="K74" s="1" t="n">
+      <c r="L74" s="1" t="n">
         <v>0.1252</v>
       </c>
     </row>
@@ -3221,9 +3446,12 @@
         <v>0.04621</v>
       </c>
       <c r="J75" s="1" t="n">
+        <v>0.0463</v>
+      </c>
+      <c r="K75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="K75" s="1" t="n">
+      <c r="L75" s="1" t="n">
         <v>0.04621</v>
       </c>
     </row>
@@ -3258,10 +3486,13 @@
         <v>0.06741</v>
       </c>
       <c r="J76" s="1" t="n">
+        <v>0.06691</v>
+      </c>
+      <c r="K76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="K76" s="1" t="n">
-        <v>0.06741</v>
+      <c r="L76" s="1" t="n">
+        <v>0.06691</v>
       </c>
     </row>
     <row r="77">
@@ -3295,9 +3526,12 @@
         <v>0.12654</v>
       </c>
       <c r="J77" s="1" t="n">
+        <v>0.12709</v>
+      </c>
+      <c r="K77" s="1" t="n">
         <v>0.12881</v>
       </c>
-      <c r="K77" s="1" t="n">
+      <c r="L77" s="1" t="n">
         <v>0.12654</v>
       </c>
     </row>
@@ -3332,9 +3566,12 @@
         <v>0.1613</v>
       </c>
       <c r="J78" s="1" t="n">
+        <v>0.1622</v>
+      </c>
+      <c r="K78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="K78" s="1" t="n">
+      <c r="L78" s="1" t="n">
         <v>0.1613</v>
       </c>
     </row>
@@ -3369,10 +3606,13 @@
         <v>0.02719</v>
       </c>
       <c r="J79" s="1" t="n">
+        <v>0.0271</v>
+      </c>
+      <c r="K79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="K79" s="1" t="n">
-        <v>0.02719</v>
+      <c r="L79" s="1" t="n">
+        <v>0.0271</v>
       </c>
     </row>
     <row r="80">
@@ -3406,9 +3646,12 @@
         <v>357.15</v>
       </c>
       <c r="J80" s="1" t="n">
+        <v>356.5</v>
+      </c>
+      <c r="K80" s="1" t="n">
         <v>357.15</v>
       </c>
-      <c r="K80" s="1" t="n">
+      <c r="L80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -3443,9 +3686,12 @@
         <v>7.080999999999999e-05</v>
       </c>
       <c r="J81" s="1" t="n">
+        <v>7.098e-05</v>
+      </c>
+      <c r="K81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="K81" s="1" t="n">
+      <c r="L81" s="1" t="n">
         <v>7.080999999999999e-05</v>
       </c>
     </row>
@@ -3480,9 +3726,12 @@
         <v>0.2645</v>
       </c>
       <c r="J82" s="1" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="K82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="K82" s="1" t="n">
+      <c r="L82" s="1" t="n">
         <v>0.2645</v>
       </c>
     </row>
@@ -3517,9 +3766,12 @@
         <v>1.1379</v>
       </c>
       <c r="J83" s="1" t="n">
+        <v>1.1391</v>
+      </c>
+      <c r="K83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="K83" s="1" t="n">
+      <c r="L83" s="1" t="n">
         <v>1.1379</v>
       </c>
     </row>
@@ -3554,10 +3806,13 @@
         <v>0.3543</v>
       </c>
       <c r="J84" s="1" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="K84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="K84" s="1" t="n">
-        <v>0.3543</v>
+      <c r="L84" s="1" t="n">
+        <v>0.3541</v>
       </c>
     </row>
     <row r="85">
@@ -3591,9 +3846,12 @@
         <v>2.0149</v>
       </c>
       <c r="J85" s="1" t="n">
+        <v>2.0188</v>
+      </c>
+      <c r="K85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="K85" s="1" t="n">
+      <c r="L85" s="1" t="n">
         <v>2.0067</v>
       </c>
     </row>
@@ -3628,9 +3886,12 @@
         <v>1.3126</v>
       </c>
       <c r="J86" s="1" t="n">
+        <v>1.3152</v>
+      </c>
+      <c r="K86" s="1" t="n">
         <v>1.3167</v>
       </c>
-      <c r="K86" s="1" t="n">
+      <c r="L86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -3665,9 +3926,12 @@
         <v>32.73</v>
       </c>
       <c r="J87" s="1" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="K87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="K87" s="1" t="n">
+      <c r="L87" s="1" t="n">
         <v>32.73</v>
       </c>
     </row>
@@ -3702,9 +3966,12 @@
         <v>0.009690000000000001</v>
       </c>
       <c r="J88" s="1" t="n">
+        <v>0.009719999999999999</v>
+      </c>
+      <c r="K88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="K88" s="1" t="n">
+      <c r="L88" s="1" t="n">
         <v>0.009690000000000001</v>
       </c>
     </row>
@@ -3739,9 +4006,12 @@
         <v>0.0184</v>
       </c>
       <c r="J89" s="1" t="n">
+        <v>0.01833</v>
+      </c>
+      <c r="K89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="K89" s="1" t="n">
+      <c r="L89" s="1" t="n">
         <v>0.01828</v>
       </c>
     </row>
@@ -3776,9 +4046,12 @@
         <v>0.03548</v>
       </c>
       <c r="J90" s="1" t="n">
+        <v>0.03548</v>
+      </c>
+      <c r="K90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="K90" s="1" t="n">
+      <c r="L90" s="1" t="n">
         <v>0.03548</v>
       </c>
     </row>
@@ -3813,9 +4086,12 @@
         <v>0.0118</v>
       </c>
       <c r="J91" s="1" t="n">
+        <v>0.01186</v>
+      </c>
+      <c r="K91" s="1" t="n">
         <v>0.01202</v>
       </c>
-      <c r="K91" s="1" t="n">
+      <c r="L91" s="1" t="n">
         <v>0.0118</v>
       </c>
     </row>
@@ -3850,10 +4126,13 @@
         <v>3.097</v>
       </c>
       <c r="J92" s="1" t="n">
+        <v>3.095</v>
+      </c>
+      <c r="K92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="K92" s="1" t="n">
-        <v>3.097</v>
+      <c r="L92" s="1" t="n">
+        <v>3.095</v>
       </c>
     </row>
     <row r="93">
@@ -3887,9 +4166,12 @@
         <v>0.005596</v>
       </c>
       <c r="J93" s="1" t="n">
+        <v>0.005605</v>
+      </c>
+      <c r="K93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="K93" s="1" t="n">
+      <c r="L93" s="1" t="n">
         <v>0.005596</v>
       </c>
     </row>
@@ -3924,10 +4206,13 @@
         <v>0.093</v>
       </c>
       <c r="J94" s="1" t="n">
+        <v>0.0925</v>
+      </c>
+      <c r="K94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="K94" s="1" t="n">
-        <v>0.093</v>
+      <c r="L94" s="1" t="n">
+        <v>0.0925</v>
       </c>
     </row>
     <row r="95">
@@ -3961,9 +4246,12 @@
         <v>0.6054</v>
       </c>
       <c r="J95" s="1" t="n">
-        <v>0.6058</v>
+        <v>0.6063</v>
       </c>
       <c r="K95" s="1" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="L95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -3998,10 +4286,13 @@
         <v>1.28e-05</v>
       </c>
       <c r="J96" s="1" t="n">
+        <v>1.27e-05</v>
+      </c>
+      <c r="K96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="K96" s="1" t="n">
-        <v>1.28e-05</v>
+      <c r="L96" s="1" t="n">
+        <v>1.27e-05</v>
       </c>
     </row>
     <row r="97">
@@ -4035,10 +4326,13 @@
         <v>1.132</v>
       </c>
       <c r="J97" s="1" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="K97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="K97" s="1" t="n">
-        <v>1.132</v>
+      <c r="L97" s="1" t="n">
+        <v>1.125</v>
       </c>
     </row>
     <row r="98">
@@ -4072,9 +4366,12 @@
         <v>0.2523</v>
       </c>
       <c r="J98" s="1" t="n">
+        <v>0.25663</v>
+      </c>
+      <c r="K98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="K98" s="1" t="n">
+      <c r="L98" s="1" t="n">
         <v>0.2523</v>
       </c>
     </row>
@@ -4109,10 +4406,13 @@
         <v>1.147</v>
       </c>
       <c r="J99" s="1" t="n">
+        <v>1.144</v>
+      </c>
+      <c r="K99" s="1" t="n">
         <v>1.156</v>
       </c>
-      <c r="K99" s="1" t="n">
-        <v>1.146</v>
+      <c r="L99" s="1" t="n">
+        <v>1.144</v>
       </c>
     </row>
     <row r="100">
@@ -4146,9 +4446,12 @@
         <v>1.852</v>
       </c>
       <c r="J100" s="1" t="n">
+        <v>1.853</v>
+      </c>
+      <c r="K100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="K100" s="1" t="n">
+      <c r="L100" s="1" t="n">
         <v>1.852</v>
       </c>
     </row>
@@ -4183,10 +4486,13 @@
         <v>0.01587</v>
       </c>
       <c r="J101" s="1" t="n">
+        <v>0.01579</v>
+      </c>
+      <c r="K101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="K101" s="1" t="n">
-        <v>0.01587</v>
+      <c r="L101" s="1" t="n">
+        <v>0.01579</v>
       </c>
     </row>
     <row r="102">
@@ -4220,9 +4526,12 @@
         <v>0.10392</v>
       </c>
       <c r="J102" s="1" t="n">
+        <v>0.10374</v>
+      </c>
+      <c r="K102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="K102" s="1" t="n">
+      <c r="L102" s="1" t="n">
         <v>0.10353</v>
       </c>
     </row>
@@ -4257,10 +4566,13 @@
         <v>0.0005972</v>
       </c>
       <c r="J103" s="1" t="n">
+        <v>0.0005967</v>
+      </c>
+      <c r="K103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="K103" s="1" t="n">
-        <v>0.0005972</v>
+      <c r="L103" s="1" t="n">
+        <v>0.0005967</v>
       </c>
     </row>
     <row r="104">
@@ -4294,9 +4606,12 @@
         <v>0.0005734</v>
       </c>
       <c r="J104" s="1" t="n">
+        <v>0.0005724</v>
+      </c>
+      <c r="K104" s="1" t="n">
         <v>0.0005776000000000001</v>
       </c>
-      <c r="K104" s="1" t="n">
+      <c r="L104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -4331,9 +4646,12 @@
         <v>0.003244</v>
       </c>
       <c r="J105" s="1" t="n">
-        <v>0.003257</v>
+        <v>0.003259</v>
       </c>
       <c r="K105" s="1" t="n">
+        <v>0.003259</v>
+      </c>
+      <c r="L105" s="1" t="n">
         <v>0.003229</v>
       </c>
     </row>
@@ -4368,9 +4686,12 @@
         <v>2.587</v>
       </c>
       <c r="J106" s="1" t="n">
+        <v>2.588</v>
+      </c>
+      <c r="K106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="K106" s="1" t="n">
+      <c r="L106" s="1" t="n">
         <v>2.587</v>
       </c>
     </row>
@@ -4405,10 +4726,13 @@
         <v>0.1654</v>
       </c>
       <c r="J107" s="1" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="K107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="K107" s="1" t="n">
-        <v>0.1654</v>
+      <c r="L107" s="1" t="n">
+        <v>0.165</v>
       </c>
     </row>
     <row r="108">
@@ -4442,9 +4766,12 @@
         <v>0.0955</v>
       </c>
       <c r="J108" s="1" t="n">
+        <v>0.09607</v>
+      </c>
+      <c r="K108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="K108" s="1" t="n">
+      <c r="L108" s="1" t="n">
         <v>0.0955</v>
       </c>
     </row>
@@ -4479,9 +4806,12 @@
         <v>0.02204</v>
       </c>
       <c r="J109" s="1" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="K109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="K109" s="1" t="n">
+      <c r="L109" s="1" t="n">
         <v>0.02204</v>
       </c>
     </row>
@@ -4516,10 +4846,13 @@
         <v>0.2915</v>
       </c>
       <c r="J110" s="1" t="n">
+        <v>0.2912</v>
+      </c>
+      <c r="K110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="K110" s="1" t="n">
-        <v>0.2913</v>
+      <c r="L110" s="1" t="n">
+        <v>0.2912</v>
       </c>
     </row>
     <row r="111">
@@ -4553,9 +4886,12 @@
         <v>0.05665</v>
       </c>
       <c r="J111" s="1" t="n">
+        <v>0.05672</v>
+      </c>
+      <c r="K111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="K111" s="1" t="n">
+      <c r="L111" s="1" t="n">
         <v>0.05665</v>
       </c>
     </row>
@@ -4590,9 +4926,12 @@
         <v>0.3002</v>
       </c>
       <c r="J112" s="1" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="K112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="K112" s="1" t="n">
+      <c r="L112" s="1" t="n">
         <v>0.3002</v>
       </c>
     </row>
@@ -4627,9 +4966,12 @@
         <v>18.6</v>
       </c>
       <c r="J113" s="1" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="K113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="K113" s="1" t="n">
+      <c r="L113" s="1" t="n">
         <v>18.6</v>
       </c>
     </row>
@@ -4664,10 +5006,13 @@
         <v>0.13035</v>
       </c>
       <c r="J114" s="1" t="n">
+        <v>0.12871</v>
+      </c>
+      <c r="K114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="K114" s="1" t="n">
-        <v>0.13035</v>
+      <c r="L114" s="1" t="n">
+        <v>0.12871</v>
       </c>
     </row>
     <row r="115">
@@ -4701,9 +5046,12 @@
         <v>0.01557</v>
       </c>
       <c r="J115" s="1" t="n">
+        <v>0.01553</v>
+      </c>
+      <c r="K115" s="1" t="n">
         <v>0.01583</v>
       </c>
-      <c r="K115" s="1" t="n">
+      <c r="L115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -4738,10 +5086,13 @@
         <v>0.08472</v>
       </c>
       <c r="J116" s="1" t="n">
+        <v>0.08470999999999999</v>
+      </c>
+      <c r="K116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="K116" s="1" t="n">
-        <v>0.08472</v>
+      <c r="L116" s="1" t="n">
+        <v>0.08470999999999999</v>
       </c>
     </row>
     <row r="117">
@@ -4775,9 +5126,12 @@
         <v>0.048525</v>
       </c>
       <c r="J117" s="1" t="n">
+        <v>0.04817</v>
+      </c>
+      <c r="K117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="K117" s="1" t="n">
+      <c r="L117" s="1" t="n">
         <v>0.047711</v>
       </c>
     </row>
@@ -4812,10 +5166,13 @@
         <v>0.04737</v>
       </c>
       <c r="J118" s="1" t="n">
+        <v>0.04733</v>
+      </c>
+      <c r="K118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="K118" s="1" t="n">
-        <v>0.04737</v>
+      <c r="L118" s="1" t="n">
+        <v>0.04733</v>
       </c>
     </row>
     <row r="119">
@@ -4849,9 +5206,12 @@
         <v>0.04175</v>
       </c>
       <c r="J119" s="1" t="n">
+        <v>0.04146</v>
+      </c>
+      <c r="K119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="K119" s="1" t="n">
+      <c r="L119" s="1" t="n">
         <v>0.04109</v>
       </c>
     </row>
@@ -4886,10 +5246,13 @@
         <v>0.14531</v>
       </c>
       <c r="J120" s="1" t="n">
+        <v>0.14463</v>
+      </c>
+      <c r="K120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="K120" s="1" t="n">
-        <v>0.14499</v>
+      <c r="L120" s="1" t="n">
+        <v>0.14463</v>
       </c>
     </row>
     <row r="121">
@@ -4923,9 +5286,12 @@
         <v>0.1274</v>
       </c>
       <c r="J121" s="1" t="n">
+        <v>0.1274</v>
+      </c>
+      <c r="K121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="K121" s="1" t="n">
+      <c r="L121" s="1" t="n">
         <v>0.1272</v>
       </c>
     </row>
@@ -4960,10 +5326,13 @@
         <v>1.873</v>
       </c>
       <c r="J122" s="1" t="n">
+        <v>1.867</v>
+      </c>
+      <c r="K122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="K122" s="1" t="n">
-        <v>1.873</v>
+      <c r="L122" s="1" t="n">
+        <v>1.867</v>
       </c>
     </row>
     <row r="123">
@@ -4997,10 +5366,13 @@
         <v>0.03013</v>
       </c>
       <c r="J123" s="1" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="K123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="K123" s="1" t="n">
-        <v>0.03013</v>
+      <c r="L123" s="1" t="n">
+        <v>0.0301</v>
       </c>
     </row>
     <row r="124">
@@ -5034,9 +5406,12 @@
         <v>0.13211</v>
       </c>
       <c r="J124" s="1" t="n">
+        <v>0.13228</v>
+      </c>
+      <c r="K124" s="1" t="n">
         <v>0.13401</v>
       </c>
-      <c r="K124" s="1" t="n">
+      <c r="L124" s="1" t="n">
         <v>0.13211</v>
       </c>
     </row>
@@ -5071,9 +5446,12 @@
         <v>0.04095</v>
       </c>
       <c r="J125" s="1" t="n">
+        <v>0.04107</v>
+      </c>
+      <c r="K125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="K125" s="1" t="n">
+      <c r="L125" s="1" t="n">
         <v>0.04095</v>
       </c>
     </row>
@@ -5108,10 +5486,13 @@
         <v>0.1151</v>
       </c>
       <c r="J126" s="1" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="K126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="K126" s="1" t="n">
-        <v>0.1151</v>
+      <c r="L126" s="1" t="n">
+        <v>0.1148</v>
       </c>
     </row>
     <row r="127">
@@ -5145,9 +5526,12 @@
         <v>0.5017</v>
       </c>
       <c r="J127" s="1" t="n">
+        <v>0.5034999999999999</v>
+      </c>
+      <c r="K127" s="1" t="n">
         <v>0.5046</v>
       </c>
-      <c r="K127" s="1" t="n">
+      <c r="L127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -5182,9 +5566,12 @@
         <v>0.03792</v>
       </c>
       <c r="J128" s="1" t="n">
+        <v>0.0379</v>
+      </c>
+      <c r="K128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="K128" s="1" t="n">
+      <c r="L128" s="1" t="n">
         <v>0.03787</v>
       </c>
     </row>
@@ -5219,9 +5606,12 @@
         <v>0.792</v>
       </c>
       <c r="J129" s="1" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="K129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="K129" s="1" t="n">
+      <c r="L129" s="1" t="n">
         <v>0.792</v>
       </c>
     </row>
@@ -5256,9 +5646,12 @@
         <v>0.03423</v>
       </c>
       <c r="J130" s="1" t="n">
+        <v>0.03428</v>
+      </c>
+      <c r="K130" s="1" t="n">
         <v>0.03458</v>
       </c>
-      <c r="K130" s="1" t="n">
+      <c r="L130" s="1" t="n">
         <v>0.03422</v>
       </c>
     </row>
@@ -5293,9 +5686,12 @@
         <v>0.418</v>
       </c>
       <c r="J131" s="1" t="n">
+        <v>0.4191</v>
+      </c>
+      <c r="K131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="K131" s="1" t="n">
+      <c r="L131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -5330,9 +5726,12 @@
         <v>0.04354</v>
       </c>
       <c r="J132" s="1" t="n">
+        <v>0.04378</v>
+      </c>
+      <c r="K132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="K132" s="1" t="n">
+      <c r="L132" s="1" t="n">
         <v>0.04354</v>
       </c>
     </row>
@@ -5367,9 +5766,12 @@
         <v>1.282</v>
       </c>
       <c r="J133" s="1" t="n">
+        <v>1.2851</v>
+      </c>
+      <c r="K133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="K133" s="1" t="n">
+      <c r="L133" s="1" t="n">
         <v>1.282</v>
       </c>
     </row>
@@ -5404,9 +5806,12 @@
         <v>0.02184</v>
       </c>
       <c r="J134" s="1" t="n">
+        <v>0.02191</v>
+      </c>
+      <c r="K134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="K134" s="1" t="n">
+      <c r="L134" s="1" t="n">
         <v>0.02184</v>
       </c>
     </row>
@@ -5441,9 +5846,12 @@
         <v>0.0004592</v>
       </c>
       <c r="J135" s="1" t="n">
+        <v>0.0004597</v>
+      </c>
+      <c r="K135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="K135" s="1" t="n">
+      <c r="L135" s="1" t="n">
         <v>0.0004592</v>
       </c>
     </row>
@@ -5478,10 +5886,13 @@
         <v>0.001908</v>
       </c>
       <c r="J136" s="1" t="n">
+        <v>0.001896</v>
+      </c>
+      <c r="K136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="K136" s="1" t="n">
-        <v>0.001908</v>
+      <c r="L136" s="1" t="n">
+        <v>0.001896</v>
       </c>
     </row>
     <row r="137">
@@ -5515,10 +5926,13 @@
         <v>0.3177</v>
       </c>
       <c r="J137" s="1" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="K137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="K137" s="1" t="n">
-        <v>0.3177</v>
+      <c r="L137" s="1" t="n">
+        <v>0.317</v>
       </c>
     </row>
     <row r="138">
@@ -5552,10 +5966,13 @@
         <v>0.5703</v>
       </c>
       <c r="J138" s="1" t="n">
+        <v>0.5698</v>
+      </c>
+      <c r="K138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="K138" s="1" t="n">
-        <v>0.5703</v>
+      <c r="L138" s="1" t="n">
+        <v>0.5698</v>
       </c>
     </row>
     <row r="139">
@@ -5589,10 +6006,13 @@
         <v>0.02136</v>
       </c>
       <c r="J139" s="1" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="K139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="K139" s="1" t="n">
-        <v>0.02136</v>
+      <c r="L139" s="1" t="n">
+        <v>0.02125</v>
       </c>
     </row>
     <row r="140">
@@ -5626,10 +6046,13 @@
         <v>0.0805</v>
       </c>
       <c r="J140" s="1" t="n">
+        <v>0.08036</v>
+      </c>
+      <c r="K140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="K140" s="1" t="n">
-        <v>0.0805</v>
+      <c r="L140" s="1" t="n">
+        <v>0.08036</v>
       </c>
     </row>
     <row r="141">
@@ -5663,9 +6086,12 @@
         <v>0.001672</v>
       </c>
       <c r="J141" s="1" t="n">
+        <v>0.001668</v>
+      </c>
+      <c r="K141" s="1" t="n">
         <v>0.001672</v>
       </c>
-      <c r="K141" s="1" t="n">
+      <c r="L141" s="1" t="n">
         <v>0.001616</v>
       </c>
     </row>
@@ -5700,9 +6126,12 @@
         <v>0.4289</v>
       </c>
       <c r="J142" s="1" t="n">
-        <v>0.4289</v>
+        <v>0.4387</v>
       </c>
       <c r="K142" s="1" t="n">
+        <v>0.4387</v>
+      </c>
+      <c r="L142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -5737,9 +6166,12 @@
         <v>0.030208</v>
       </c>
       <c r="J143" s="1" t="n">
+        <v>0.030392</v>
+      </c>
+      <c r="K143" s="1" t="n">
         <v>0.030681</v>
       </c>
-      <c r="K143" s="1" t="n">
+      <c r="L143" s="1" t="n">
         <v>0.030021</v>
       </c>
     </row>
@@ -5774,9 +6206,12 @@
         <v>0.000225</v>
       </c>
       <c r="J144" s="1" t="n">
+        <v>0.000225</v>
+      </c>
+      <c r="K144" s="1" t="n">
         <v>0.000226</v>
       </c>
-      <c r="K144" s="1" t="n">
+      <c r="L144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -5811,9 +6246,12 @@
         <v>0.03696</v>
       </c>
       <c r="J145" s="1" t="n">
+        <v>0.03586</v>
+      </c>
+      <c r="K145" s="1" t="n">
         <v>0.03696</v>
       </c>
-      <c r="K145" s="1" t="n">
+      <c r="L145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -5848,9 +6286,12 @@
         <v>0.11531</v>
       </c>
       <c r="J146" s="1" t="n">
+        <v>0.11578</v>
+      </c>
+      <c r="K146" s="1" t="n">
         <v>0.116</v>
       </c>
-      <c r="K146" s="1" t="n">
+      <c r="L146" s="1" t="n">
         <v>0.11518</v>
       </c>
     </row>
@@ -5885,9 +6326,12 @@
         <v>0.02175</v>
       </c>
       <c r="J147" s="1" t="n">
+        <v>0.02183</v>
+      </c>
+      <c r="K147" s="1" t="n">
         <v>0.02198</v>
       </c>
-      <c r="K147" s="1" t="n">
+      <c r="L147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -5922,10 +6366,13 @@
         <v>1.4092</v>
       </c>
       <c r="J148" s="1" t="n">
+        <v>1.4084</v>
+      </c>
+      <c r="K148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="K148" s="1" t="n">
-        <v>1.4092</v>
+      <c r="L148" s="1" t="n">
+        <v>1.4084</v>
       </c>
     </row>
     <row r="149">
@@ -5959,9 +6406,12 @@
         <v>1.8656</v>
       </c>
       <c r="J149" s="1" t="n">
+        <v>1.8622</v>
+      </c>
+      <c r="K149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="K149" s="1" t="n">
+      <c r="L149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -5996,9 +6446,12 @@
         <v>0.097</v>
       </c>
       <c r="J150" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="K150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="K150" s="1" t="n">
+      <c r="L150" s="1" t="n">
         <v>0.097</v>
       </c>
     </row>
@@ -6033,9 +6486,12 @@
         <v>4.612</v>
       </c>
       <c r="J151" s="1" t="n">
-        <v>4.623</v>
+        <v>4.64</v>
       </c>
       <c r="K151" s="1" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="L151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -6070,10 +6526,13 @@
         <v>5.527</v>
       </c>
       <c r="J152" s="1" t="n">
+        <v>5.522</v>
+      </c>
+      <c r="K152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="K152" s="1" t="n">
-        <v>5.527</v>
+      <c r="L152" s="1" t="n">
+        <v>5.522</v>
       </c>
     </row>
     <row r="153">
@@ -6107,9 +6566,12 @@
         <v>0.3175</v>
       </c>
       <c r="J153" s="1" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="K153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="K153" s="1" t="n">
+      <c r="L153" s="1" t="n">
         <v>0.3175</v>
       </c>
     </row>
@@ -6144,10 +6606,13 @@
         <v>0.5877</v>
       </c>
       <c r="J154" s="1" t="n">
+        <v>0.5867</v>
+      </c>
+      <c r="K154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="K154" s="1" t="n">
-        <v>0.5877</v>
+      <c r="L154" s="1" t="n">
+        <v>0.5867</v>
       </c>
     </row>
     <row r="155">
@@ -6181,9 +6646,12 @@
         <v>0.01287</v>
       </c>
       <c r="J155" s="1" t="n">
+        <v>0.01281</v>
+      </c>
+      <c r="K155" s="1" t="n">
         <v>0.01292</v>
       </c>
-      <c r="K155" s="1" t="n">
+      <c r="L155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -6218,10 +6686,13 @@
         <v>0.0987</v>
       </c>
       <c r="J156" s="1" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="K156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="K156" s="1" t="n">
-        <v>0.0987</v>
+      <c r="L156" s="1" t="n">
+        <v>0.09859999999999999</v>
       </c>
     </row>
     <row r="157">
@@ -6255,10 +6726,13 @@
         <v>16.538</v>
       </c>
       <c r="J157" s="1" t="n">
+        <v>16.525</v>
+      </c>
+      <c r="K157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="K157" s="1" t="n">
-        <v>16.538</v>
+      <c r="L157" s="1" t="n">
+        <v>16.525</v>
       </c>
     </row>
     <row r="158">
@@ -6292,9 +6766,12 @@
         <v>0.05542</v>
       </c>
       <c r="J158" s="1" t="n">
+        <v>0.05564</v>
+      </c>
+      <c r="K158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="K158" s="1" t="n">
+      <c r="L158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -6329,9 +6806,12 @@
         <v>28.93</v>
       </c>
       <c r="J159" s="1" t="n">
+        <v>28.96</v>
+      </c>
+      <c r="K159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="K159" s="1" t="n">
+      <c r="L159" s="1" t="n">
         <v>28.87</v>
       </c>
     </row>
@@ -6366,10 +6846,13 @@
         <v>0.02117</v>
       </c>
       <c r="J160" s="1" t="n">
+        <v>0.02115</v>
+      </c>
+      <c r="K160" s="1" t="n">
         <v>0.02141</v>
       </c>
-      <c r="K160" s="1" t="n">
-        <v>0.02117</v>
+      <c r="L160" s="1" t="n">
+        <v>0.02115</v>
       </c>
     </row>
     <row r="161">
@@ -6403,9 +6886,12 @@
         <v>0.0006507</v>
       </c>
       <c r="J161" s="1" t="n">
+        <v>0.0006532</v>
+      </c>
+      <c r="K161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="K161" s="1" t="n">
+      <c r="L161" s="1" t="n">
         <v>0.0006507</v>
       </c>
     </row>
@@ -6440,10 +6926,13 @@
         <v>0.3922</v>
       </c>
       <c r="J162" s="1" t="n">
+        <v>0.3879</v>
+      </c>
+      <c r="K162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="K162" s="1" t="n">
-        <v>0.3922</v>
+      <c r="L162" s="1" t="n">
+        <v>0.3879</v>
       </c>
     </row>
     <row r="163">
@@ -6477,9 +6966,12 @@
         <v>0.1925</v>
       </c>
       <c r="J163" s="1" t="n">
+        <v>0.1925</v>
+      </c>
+      <c r="K163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="K163" s="1" t="n">
+      <c r="L163" s="1" t="n">
         <v>0.1925</v>
       </c>
     </row>
@@ -6514,10 +7006,13 @@
         <v>0.317</v>
       </c>
       <c r="J164" s="1" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="K164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="K164" s="1" t="n">
-        <v>0.317</v>
+      <c r="L164" s="1" t="n">
+        <v>0.315</v>
       </c>
     </row>
     <row r="165">
@@ -6551,9 +7046,12 @@
         <v>0.372</v>
       </c>
       <c r="J165" s="1" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="K165" s="1" t="n">
         <v>0.377</v>
       </c>
-      <c r="K165" s="1" t="n">
+      <c r="L165" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -6588,9 +7086,12 @@
         <v>0.02258</v>
       </c>
       <c r="J166" s="1" t="n">
+        <v>0.02258</v>
+      </c>
+      <c r="K166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="K166" s="1" t="n">
+      <c r="L166" s="1" t="n">
         <v>0.02258</v>
       </c>
     </row>
@@ -6625,10 +7126,13 @@
         <v>0.007303</v>
       </c>
       <c r="J167" s="1" t="n">
+        <v>0.007295</v>
+      </c>
+      <c r="K167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="K167" s="1" t="n">
-        <v>0.007303</v>
+      <c r="L167" s="1" t="n">
+        <v>0.007295</v>
       </c>
     </row>
     <row r="168">
@@ -6662,10 +7166,13 @@
         <v>0.01362</v>
       </c>
       <c r="J168" s="1" t="n">
+        <v>0.01355</v>
+      </c>
+      <c r="K168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="K168" s="1" t="n">
-        <v>0.01362</v>
+      <c r="L168" s="1" t="n">
+        <v>0.01355</v>
       </c>
     </row>
     <row r="169">
@@ -6699,9 +7206,12 @@
         <v>0.25175</v>
       </c>
       <c r="J169" s="1" t="n">
+        <v>0.25199</v>
+      </c>
+      <c r="K169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="K169" s="1" t="n">
+      <c r="L169" s="1" t="n">
         <v>0.25175</v>
       </c>
     </row>
@@ -6736,9 +7246,12 @@
         <v>0.02174</v>
       </c>
       <c r="J170" s="1" t="n">
+        <v>0.02179</v>
+      </c>
+      <c r="K170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="K170" s="1" t="n">
+      <c r="L170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -6773,9 +7286,12 @@
         <v>0.1718</v>
       </c>
       <c r="J171" s="1" t="n">
+        <v>0.1724</v>
+      </c>
+      <c r="K171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="K171" s="1" t="n">
+      <c r="L171" s="1" t="n">
         <v>0.1718</v>
       </c>
     </row>
@@ -6810,9 +7326,12 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="J172" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="K172" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="K172" s="1" t="n">
+      <c r="L172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -6847,9 +7366,12 @@
         <v>0.004682</v>
       </c>
       <c r="J173" s="1" t="n">
+        <v>0.004691</v>
+      </c>
+      <c r="K173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="K173" s="1" t="n">
+      <c r="L173" s="1" t="n">
         <v>0.004682</v>
       </c>
     </row>
@@ -6884,10 +7406,13 @@
         <v>0.437</v>
       </c>
       <c r="J174" s="1" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="K174" s="1" t="n">
         <v>0.4423</v>
       </c>
-      <c r="K174" s="1" t="n">
-        <v>0.4368</v>
+      <c r="L174" s="1" t="n">
+        <v>0.4364</v>
       </c>
     </row>
     <row r="175">
@@ -6921,9 +7446,12 @@
         <v>0.08935999999999999</v>
       </c>
       <c r="J175" s="1" t="n">
+        <v>0.09017</v>
+      </c>
+      <c r="K175" s="1" t="n">
         <v>0.09021999999999999</v>
       </c>
-      <c r="K175" s="1" t="n">
+      <c r="L175" s="1" t="n">
         <v>0.08935999999999999</v>
       </c>
     </row>
@@ -6958,9 +7486,12 @@
         <v>0.246</v>
       </c>
       <c r="J176" s="1" t="n">
+        <v>0.2473</v>
+      </c>
+      <c r="K176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="K176" s="1" t="n">
+      <c r="L176" s="1" t="n">
         <v>0.2453</v>
       </c>
     </row>
@@ -6995,9 +7526,12 @@
         <v>0.01909</v>
       </c>
       <c r="J177" s="1" t="n">
+        <v>0.01913</v>
+      </c>
+      <c r="K177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="K177" s="1" t="n">
+      <c r="L177" s="1" t="n">
         <v>0.01909</v>
       </c>
     </row>
@@ -7032,9 +7566,12 @@
         <v>6.138</v>
       </c>
       <c r="J178" s="1" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="K178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="K178" s="1" t="n">
+      <c r="L178" s="1" t="n">
         <v>6.138</v>
       </c>
     </row>
@@ -7069,9 +7606,12 @@
         <v>0.1362</v>
       </c>
       <c r="J179" s="1" t="n">
+        <v>0.1368</v>
+      </c>
+      <c r="K179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="K179" s="1" t="n">
+      <c r="L179" s="1" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -7106,9 +7646,12 @@
         <v>0.005154</v>
       </c>
       <c r="J180" s="1" t="n">
+        <v>0.005113</v>
+      </c>
+      <c r="K180" s="1" t="n">
         <v>0.005154</v>
       </c>
-      <c r="K180" s="1" t="n">
+      <c r="L180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -7143,9 +7686,12 @@
         <v>0.01193</v>
       </c>
       <c r="J181" s="1" t="n">
+        <v>0.01195</v>
+      </c>
+      <c r="K181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="K181" s="1" t="n">
+      <c r="L181" s="1" t="n">
         <v>0.01189</v>
       </c>
     </row>
@@ -7180,9 +7726,12 @@
         <v>0.007353</v>
       </c>
       <c r="J182" s="1" t="n">
+        <v>0.007352</v>
+      </c>
+      <c r="K182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="K182" s="1" t="n">
+      <c r="L182" s="1" t="n">
         <v>0.007295</v>
       </c>
     </row>
@@ -7217,9 +7766,12 @@
         <v>0.12975</v>
       </c>
       <c r="J183" s="1" t="n">
+        <v>0.13194</v>
+      </c>
+      <c r="K183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="K183" s="1" t="n">
+      <c r="L183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -7254,9 +7806,12 @@
         <v>0.09649000000000001</v>
       </c>
       <c r="J184" s="1" t="n">
+        <v>0.09676</v>
+      </c>
+      <c r="K184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="K184" s="1" t="n">
+      <c r="L184" s="1" t="n">
         <v>0.09587</v>
       </c>
     </row>
@@ -7291,10 +7846,13 @@
         <v>0.00755</v>
       </c>
       <c r="J185" s="1" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="K185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="K185" s="1" t="n">
-        <v>0.00755</v>
+      <c r="L185" s="1" t="n">
+        <v>0.00754</v>
       </c>
     </row>
     <row r="186">
@@ -7328,9 +7886,12 @@
         <v>0.0486</v>
       </c>
       <c r="J186" s="1" t="n">
+        <v>0.04866</v>
+      </c>
+      <c r="K186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="K186" s="1" t="n">
+      <c r="L186" s="1" t="n">
         <v>0.0486</v>
       </c>
     </row>
@@ -7365,9 +7926,12 @@
         <v>0.02674</v>
       </c>
       <c r="J187" s="1" t="n">
+        <v>0.02677</v>
+      </c>
+      <c r="K187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="K187" s="1" t="n">
+      <c r="L187" s="1" t="n">
         <v>0.02674</v>
       </c>
     </row>
@@ -7402,9 +7966,12 @@
         <v>0.003303</v>
       </c>
       <c r="J188" s="1" t="n">
+        <v>0.003306</v>
+      </c>
+      <c r="K188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="K188" s="1" t="n">
+      <c r="L188" s="1" t="n">
         <v>0.003303</v>
       </c>
     </row>
@@ -7439,9 +8006,12 @@
         <v>0.286</v>
       </c>
       <c r="J189" s="1" t="n">
+        <v>0.2862</v>
+      </c>
+      <c r="K189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="K189" s="1" t="n">
+      <c r="L189" s="1" t="n">
         <v>0.286</v>
       </c>
     </row>
@@ -7476,10 +8046,13 @@
         <v>0.01805</v>
       </c>
       <c r="J190" s="1" t="n">
+        <v>0.01797</v>
+      </c>
+      <c r="K190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="K190" s="1" t="n">
-        <v>0.01805</v>
+      <c r="L190" s="1" t="n">
+        <v>0.01797</v>
       </c>
     </row>
     <row r="191">
@@ -7513,9 +8086,12 @@
         <v>0.2574</v>
       </c>
       <c r="J191" s="1" t="n">
+        <v>0.2574</v>
+      </c>
+      <c r="K191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="K191" s="1" t="n">
+      <c r="L191" s="1" t="n">
         <v>0.2574</v>
       </c>
     </row>
@@ -7550,10 +8126,13 @@
         <v>0.03844</v>
       </c>
       <c r="J192" s="1" t="n">
+        <v>0.03801</v>
+      </c>
+      <c r="K192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="K192" s="1" t="n">
-        <v>0.03844</v>
+      <c r="L192" s="1" t="n">
+        <v>0.03801</v>
       </c>
     </row>
     <row r="193">
@@ -7587,9 +8166,12 @@
         <v>0.0002226</v>
       </c>
       <c r="J193" s="1" t="n">
-        <v>0.0002234</v>
+        <v>0.0002235</v>
       </c>
       <c r="K193" s="1" t="n">
+        <v>0.0002235</v>
+      </c>
+      <c r="L193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -7624,9 +8206,12 @@
         <v>4.091</v>
       </c>
       <c r="J194" s="1" t="n">
+        <v>4.108</v>
+      </c>
+      <c r="K194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="K194" s="1" t="n">
+      <c r="L194" s="1" t="n">
         <v>4.091</v>
       </c>
     </row>
@@ -7661,9 +8246,12 @@
         <v>0.9994</v>
       </c>
       <c r="J195" s="1" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="K195" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="K195" s="1" t="n">
+      <c r="L195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -7698,9 +8286,12 @@
         <v>4.276</v>
       </c>
       <c r="J196" s="1" t="n">
+        <v>4.304</v>
+      </c>
+      <c r="K196" s="1" t="n">
         <v>4.347</v>
       </c>
-      <c r="K196" s="1" t="n">
+      <c r="L196" s="1" t="n">
         <v>4.276</v>
       </c>
     </row>
@@ -7735,9 +8326,12 @@
         <v>0.15151</v>
       </c>
       <c r="J197" s="1" t="n">
-        <v>0.15151</v>
+        <v>0.15176</v>
       </c>
       <c r="K197" s="1" t="n">
+        <v>0.15176</v>
+      </c>
+      <c r="L197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -7772,9 +8366,12 @@
         <v>0.007514</v>
       </c>
       <c r="J198" s="1" t="n">
+        <v>0.007479</v>
+      </c>
+      <c r="K198" s="1" t="n">
         <v>0.0077</v>
       </c>
-      <c r="K198" s="1" t="n">
+      <c r="L198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -7809,10 +8406,13 @@
         <v>0.4483</v>
       </c>
       <c r="J199" s="1" t="n">
+        <v>0.4482</v>
+      </c>
+      <c r="K199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="K199" s="1" t="n">
-        <v>0.4483</v>
+      <c r="L199" s="1" t="n">
+        <v>0.4482</v>
       </c>
     </row>
     <row r="200">
@@ -7846,9 +8446,12 @@
         <v>0.5784</v>
       </c>
       <c r="J200" s="1" t="n">
+        <v>0.5813</v>
+      </c>
+      <c r="K200" s="1" t="n">
         <v>0.5857</v>
       </c>
-      <c r="K200" s="1" t="n">
+      <c r="L200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -7883,9 +8486,12 @@
         <v>0.0931</v>
       </c>
       <c r="J201" s="1" t="n">
+        <v>0.09320000000000001</v>
+      </c>
+      <c r="K201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="K201" s="1" t="n">
+      <c r="L201" s="1" t="n">
         <v>0.0931</v>
       </c>
     </row>
@@ -7920,9 +8526,12 @@
         <v>0.06044</v>
       </c>
       <c r="J202" s="1" t="n">
+        <v>0.06044</v>
+      </c>
+      <c r="K202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="K202" s="1" t="n">
+      <c r="L202" s="1" t="n">
         <v>0.06044</v>
       </c>
     </row>
@@ -7957,9 +8566,12 @@
         <v>0.00817</v>
       </c>
       <c r="J203" s="1" t="n">
+        <v>0.008330000000000001</v>
+      </c>
+      <c r="K203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="K203" s="1" t="n">
+      <c r="L203" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -7994,9 +8606,12 @@
         <v>0.00418</v>
       </c>
       <c r="J204" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="K204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="K204" s="1" t="n">
+      <c r="L204" s="1" t="n">
         <v>0.00418</v>
       </c>
     </row>
@@ -8031,10 +8646,13 @@
         <v>0.009136</v>
       </c>
       <c r="J205" s="1" t="n">
+        <v>0.00912</v>
+      </c>
+      <c r="K205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="K205" s="1" t="n">
-        <v>0.009136</v>
+      <c r="L205" s="1" t="n">
+        <v>0.00912</v>
       </c>
     </row>
     <row r="206">
@@ -8068,9 +8686,12 @@
         <v>0.2399</v>
       </c>
       <c r="J206" s="1" t="n">
+        <v>0.2396</v>
+      </c>
+      <c r="K206" s="1" t="n">
         <v>0.2413</v>
       </c>
-      <c r="K206" s="1" t="n">
+      <c r="L206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -8105,10 +8726,13 @@
         <v>0.02092</v>
       </c>
       <c r="J207" s="1" t="n">
+        <v>0.02077</v>
+      </c>
+      <c r="K207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="K207" s="1" t="n">
-        <v>0.02092</v>
+      <c r="L207" s="1" t="n">
+        <v>0.02077</v>
       </c>
     </row>
     <row r="208">
@@ -8142,10 +8766,13 @@
         <v>0.2368</v>
       </c>
       <c r="J208" s="1" t="n">
+        <v>0.2364</v>
+      </c>
+      <c r="K208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="K208" s="1" t="n">
-        <v>0.2366</v>
+      <c r="L208" s="1" t="n">
+        <v>0.2364</v>
       </c>
     </row>
     <row r="209">
@@ -8179,9 +8806,12 @@
         <v>0.3587</v>
       </c>
       <c r="J209" s="1" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="K209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="K209" s="1" t="n">
+      <c r="L209" s="1" t="n">
         <v>0.3587</v>
       </c>
     </row>
@@ -8216,10 +8846,13 @@
         <v>0.04249</v>
       </c>
       <c r="J210" s="1" t="n">
+        <v>0.04236</v>
+      </c>
+      <c r="K210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="K210" s="1" t="n">
-        <v>0.04249</v>
+      <c r="L210" s="1" t="n">
+        <v>0.04236</v>
       </c>
     </row>
     <row r="211">
@@ -8253,9 +8886,12 @@
         <v>0.0004256</v>
       </c>
       <c r="J211" s="1" t="n">
+        <v>0.0004257</v>
+      </c>
+      <c r="K211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="K211" s="1" t="n">
+      <c r="L211" s="1" t="n">
         <v>0.0004256</v>
       </c>
     </row>
@@ -8290,9 +8926,12 @@
         <v>0.02151</v>
       </c>
       <c r="J212" s="1" t="n">
+        <v>0.02152</v>
+      </c>
+      <c r="K212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="K212" s="1" t="n">
+      <c r="L212" s="1" t="n">
         <v>0.02151</v>
       </c>
     </row>
@@ -8327,9 +8966,12 @@
         <v>0.1137</v>
       </c>
       <c r="J213" s="1" t="n">
+        <v>0.1142</v>
+      </c>
+      <c r="K213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="K213" s="1" t="n">
+      <c r="L213" s="1" t="n">
         <v>0.1137</v>
       </c>
     </row>
@@ -8364,9 +9006,12 @@
         <v>0.04174</v>
       </c>
       <c r="J214" s="1" t="n">
+        <v>0.04175</v>
+      </c>
+      <c r="K214" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="K214" s="1" t="n">
+      <c r="L214" s="1" t="n">
         <v>0.04174</v>
       </c>
     </row>
@@ -8401,9 +9046,12 @@
         <v>0.009991</v>
       </c>
       <c r="J215" s="1" t="n">
+        <v>0.009933000000000001</v>
+      </c>
+      <c r="K215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="K215" s="1" t="n">
+      <c r="L215" s="1" t="n">
         <v>0.009896</v>
       </c>
     </row>
@@ -8438,9 +9086,12 @@
         <v>0.0639</v>
       </c>
       <c r="J216" s="1" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="K216" s="1" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="K216" s="1" t="n">
+      <c r="L216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -8475,9 +9126,12 @@
         <v>0.004183</v>
       </c>
       <c r="J217" s="1" t="n">
+        <v>0.004199</v>
+      </c>
+      <c r="K217" s="1" t="n">
         <v>0.004231</v>
       </c>
-      <c r="K217" s="1" t="n">
+      <c r="L217" s="1" t="n">
         <v>0.004177</v>
       </c>
     </row>
@@ -8512,9 +9166,12 @@
         <v>0.01013</v>
       </c>
       <c r="J218" s="1" t="n">
+        <v>0.009990000000000001</v>
+      </c>
+      <c r="K218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="K218" s="1" t="n">
+      <c r="L218" s="1" t="n">
         <v>0.009820000000000001</v>
       </c>
     </row>
@@ -8549,9 +9206,12 @@
         <v>0.03001</v>
       </c>
       <c r="J219" s="1" t="n">
+        <v>0.0307</v>
+      </c>
+      <c r="K219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="K219" s="1" t="n">
+      <c r="L219" s="1" t="n">
         <v>0.02958</v>
       </c>
     </row>
@@ -8586,10 +9246,13 @@
         <v>2.292</v>
       </c>
       <c r="J220" s="1" t="n">
+        <v>2.291</v>
+      </c>
+      <c r="K220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="K220" s="1" t="n">
-        <v>2.292</v>
+      <c r="L220" s="1" t="n">
+        <v>2.291</v>
       </c>
     </row>
     <row r="221">
@@ -8623,10 +9286,13 @@
         <v>0.022886</v>
       </c>
       <c r="J221" s="1" t="n">
+        <v>0.022878</v>
+      </c>
+      <c r="K221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="K221" s="1" t="n">
-        <v>0.022886</v>
+      <c r="L221" s="1" t="n">
+        <v>0.022878</v>
       </c>
     </row>
     <row r="222">
@@ -8660,9 +9326,12 @@
         <v>0.0369</v>
       </c>
       <c r="J222" s="1" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="K222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="K222" s="1" t="n">
+      <c r="L222" s="1" t="n">
         <v>0.0369</v>
       </c>
     </row>
@@ -8697,9 +9366,12 @@
         <v>0.2918</v>
       </c>
       <c r="J223" s="1" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="K223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="K223" s="1" t="n">
+      <c r="L223" s="1" t="n">
         <v>0.2918</v>
       </c>
     </row>
@@ -8734,9 +9406,12 @@
         <v>0.01552</v>
       </c>
       <c r="J224" s="1" t="n">
+        <v>0.01556</v>
+      </c>
+      <c r="K224" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="K224" s="1" t="n">
+      <c r="L224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -8771,9 +9446,12 @@
         <v>0.0004069</v>
       </c>
       <c r="J225" s="1" t="n">
+        <v>0.0004076</v>
+      </c>
+      <c r="K225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="K225" s="1" t="n">
+      <c r="L225" s="1" t="n">
         <v>0.0004069</v>
       </c>
     </row>
@@ -8808,9 +9486,12 @@
         <v>0.08654000000000001</v>
       </c>
       <c r="J226" s="1" t="n">
+        <v>0.0868</v>
+      </c>
+      <c r="K226" s="1" t="n">
         <v>0.08815000000000001</v>
       </c>
-      <c r="K226" s="1" t="n">
+      <c r="L226" s="1" t="n">
         <v>0.08654000000000001</v>
       </c>
     </row>
@@ -8845,9 +9526,12 @@
         <v>0.946</v>
       </c>
       <c r="J227" s="1" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="K227" s="1" t="n">
         <v>0.959</v>
       </c>
-      <c r="K227" s="1" t="n">
+      <c r="L227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -8882,10 +9566,13 @@
         <v>0.05581</v>
       </c>
       <c r="J228" s="1" t="n">
+        <v>0.05555</v>
+      </c>
+      <c r="K228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="K228" s="1" t="n">
-        <v>0.0558</v>
+      <c r="L228" s="1" t="n">
+        <v>0.05555</v>
       </c>
     </row>
     <row r="229">
@@ -8919,9 +9606,12 @@
         <v>0.002003</v>
       </c>
       <c r="J229" s="1" t="n">
+        <v>0.002006</v>
+      </c>
+      <c r="K229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="K229" s="1" t="n">
+      <c r="L229" s="1" t="n">
         <v>0.002003</v>
       </c>
     </row>
@@ -8956,9 +9646,12 @@
         <v>0.023091</v>
       </c>
       <c r="J230" s="1" t="n">
+        <v>0.022928</v>
+      </c>
+      <c r="K230" s="1" t="n">
         <v>0.023091</v>
       </c>
-      <c r="K230" s="1" t="n">
+      <c r="L230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -8993,9 +9686,12 @@
         <v>0.0535</v>
       </c>
       <c r="J231" s="1" t="n">
+        <v>0.0535</v>
+      </c>
+      <c r="K231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="K231" s="1" t="n">
+      <c r="L231" s="1" t="n">
         <v>0.0535</v>
       </c>
     </row>
@@ -9030,10 +9726,13 @@
         <v>0.0588</v>
       </c>
       <c r="J232" s="1" t="n">
+        <v>0.0587</v>
+      </c>
+      <c r="K232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="K232" s="1" t="n">
-        <v>0.0588</v>
+      <c r="L232" s="1" t="n">
+        <v>0.0587</v>
       </c>
     </row>
     <row r="233">
@@ -9067,9 +9766,12 @@
         <v>0.001679</v>
       </c>
       <c r="J233" s="1" t="n">
+        <v>0.001682</v>
+      </c>
+      <c r="K233" s="1" t="n">
         <v>0.001701</v>
       </c>
-      <c r="K233" s="1" t="n">
+      <c r="L233" s="1" t="n">
         <v>0.001678</v>
       </c>
     </row>
@@ -9104,10 +9806,13 @@
         <v>0.005769</v>
       </c>
       <c r="J234" s="1" t="n">
+        <v>0.00575</v>
+      </c>
+      <c r="K234" s="1" t="n">
         <v>0.005854</v>
       </c>
-      <c r="K234" s="1" t="n">
-        <v>0.005769</v>
+      <c r="L234" s="1" t="n">
+        <v>0.00575</v>
       </c>
     </row>
     <row r="235">
@@ -9141,9 +9846,12 @@
         <v>0.12492</v>
       </c>
       <c r="J235" s="1" t="n">
+        <v>0.12551</v>
+      </c>
+      <c r="K235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="K235" s="1" t="n">
+      <c r="L235" s="1" t="n">
         <v>0.12453</v>
       </c>
     </row>
@@ -9178,9 +9886,12 @@
         <v>64.73</v>
       </c>
       <c r="J236" s="1" t="n">
+        <v>64.73</v>
+      </c>
+      <c r="K236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="K236" s="1" t="n">
+      <c r="L236" s="1" t="n">
         <v>64.73</v>
       </c>
     </row>
@@ -9215,10 +9926,13 @@
         <v>0.1017</v>
       </c>
       <c r="J237" s="1" t="n">
+        <v>0.1016</v>
+      </c>
+      <c r="K237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="K237" s="1" t="n">
-        <v>0.1017</v>
+      <c r="L237" s="1" t="n">
+        <v>0.1016</v>
       </c>
     </row>
     <row r="238">
@@ -9252,9 +9966,12 @@
         <v>0.003952</v>
       </c>
       <c r="J238" s="1" t="n">
+        <v>0.003949</v>
+      </c>
+      <c r="K238" s="1" t="n">
         <v>0.003993</v>
       </c>
-      <c r="K238" s="1" t="n">
+      <c r="L238" s="1" t="n">
         <v>0.003925</v>
       </c>
     </row>
@@ -9289,9 +10006,12 @@
         <v>0.01551</v>
       </c>
       <c r="J239" s="1" t="n">
+        <v>0.01556</v>
+      </c>
+      <c r="K239" s="1" t="n">
         <v>0.01562</v>
       </c>
-      <c r="K239" s="1" t="n">
+      <c r="L239" s="1" t="n">
         <v>0.01532</v>
       </c>
     </row>
@@ -9326,9 +10046,12 @@
         <v>0.05598</v>
       </c>
       <c r="J240" s="1" t="n">
+        <v>0.05609</v>
+      </c>
+      <c r="K240" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="K240" s="1" t="n">
+      <c r="L240" s="1" t="n">
         <v>0.05598</v>
       </c>
     </row>
@@ -9363,9 +10086,12 @@
         <v>0.0113</v>
       </c>
       <c r="J241" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="K241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="K241" s="1" t="n">
+      <c r="L241" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -9400,9 +10126,12 @@
         <v>0.3334</v>
       </c>
       <c r="J242" s="1" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="K242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="K242" s="1" t="n">
+      <c r="L242" s="1" t="n">
         <v>0.3334</v>
       </c>
     </row>
@@ -9437,9 +10166,12 @@
         <v>0.01229</v>
       </c>
       <c r="J243" s="1" t="n">
+        <v>0.01232</v>
+      </c>
+      <c r="K243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="K243" s="1" t="n">
+      <c r="L243" s="1" t="n">
         <v>0.01229</v>
       </c>
     </row>
@@ -9474,9 +10206,12 @@
         <v>0.08006000000000001</v>
       </c>
       <c r="J244" s="1" t="n">
+        <v>0.08053</v>
+      </c>
+      <c r="K244" s="1" t="n">
         <v>0.08067000000000001</v>
       </c>
-      <c r="K244" s="1" t="n">
+      <c r="L244" s="1" t="n">
         <v>0.07997</v>
       </c>
     </row>
@@ -9511,9 +10246,12 @@
         <v>0.007769</v>
       </c>
       <c r="J245" s="1" t="n">
+        <v>0.007771</v>
+      </c>
+      <c r="K245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="K245" s="1" t="n">
+      <c r="L245" s="1" t="n">
         <v>0.007769</v>
       </c>
     </row>
@@ -9548,10 +10286,13 @@
         <v>0.03029</v>
       </c>
       <c r="J246" s="1" t="n">
+        <v>0.03025</v>
+      </c>
+      <c r="K246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="K246" s="1" t="n">
-        <v>0.03029</v>
+      <c r="L246" s="1" t="n">
+        <v>0.03025</v>
       </c>
     </row>
     <row r="247">
@@ -9585,9 +10326,12 @@
         <v>0.1801</v>
       </c>
       <c r="J247" s="1" t="n">
+        <v>0.1803</v>
+      </c>
+      <c r="K247" s="1" t="n">
         <v>0.1827</v>
       </c>
-      <c r="K247" s="1" t="n">
+      <c r="L247" s="1" t="n">
         <v>0.1801</v>
       </c>
     </row>
@@ -9622,10 +10366,13 @@
         <v>0.05886</v>
       </c>
       <c r="J248" s="1" t="n">
+        <v>0.05884</v>
+      </c>
+      <c r="K248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="K248" s="1" t="n">
-        <v>0.05886</v>
+      <c r="L248" s="1" t="n">
+        <v>0.05884</v>
       </c>
     </row>
     <row r="249">
@@ -9659,10 +10406,13 @@
         <v>0.1664</v>
       </c>
       <c r="J249" s="1" t="n">
+        <v>0.1663</v>
+      </c>
+      <c r="K249" s="1" t="n">
         <v>0.1684</v>
       </c>
-      <c r="K249" s="1" t="n">
-        <v>0.1664</v>
+      <c r="L249" s="1" t="n">
+        <v>0.1663</v>
       </c>
     </row>
     <row r="250">
@@ -9696,10 +10446,13 @@
         <v>0.01916</v>
       </c>
       <c r="J250" s="1" t="n">
+        <v>0.01906</v>
+      </c>
+      <c r="K250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="K250" s="1" t="n">
-        <v>0.01916</v>
+      <c r="L250" s="1" t="n">
+        <v>0.01906</v>
       </c>
     </row>
     <row r="251">
@@ -9733,9 +10486,12 @@
         <v>0.02295</v>
       </c>
       <c r="J251" s="1" t="n">
+        <v>0.02308</v>
+      </c>
+      <c r="K251" s="1" t="n">
         <v>0.02318</v>
       </c>
-      <c r="K251" s="1" t="n">
+      <c r="L251" s="1" t="n">
         <v>0.02295</v>
       </c>
     </row>
@@ -9770,9 +10526,12 @@
         <v>0.30831</v>
       </c>
       <c r="J252" s="1" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="K252" s="1" t="n">
         <v>0.31227</v>
       </c>
-      <c r="K252" s="1" t="n">
+      <c r="L252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -9807,9 +10566,12 @@
         <v>0.005971</v>
       </c>
       <c r="J253" s="1" t="n">
+        <v>0.006013</v>
+      </c>
+      <c r="K253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="K253" s="1" t="n">
+      <c r="L253" s="1" t="n">
         <v>0.005971</v>
       </c>
     </row>
@@ -9844,9 +10606,12 @@
         <v>0.6116</v>
       </c>
       <c r="J254" s="1" t="n">
+        <v>0.6126</v>
+      </c>
+      <c r="K254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="K254" s="1" t="n">
+      <c r="L254" s="1" t="n">
         <v>0.6116</v>
       </c>
     </row>
@@ -9881,9 +10646,12 @@
         <v>0.10612</v>
       </c>
       <c r="J255" s="1" t="n">
+        <v>0.10628</v>
+      </c>
+      <c r="K255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="K255" s="1" t="n">
+      <c r="L255" s="1" t="n">
         <v>0.10612</v>
       </c>
     </row>
@@ -9918,9 +10686,12 @@
         <v>0.0902</v>
       </c>
       <c r="J256" s="1" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="K256" s="1" t="n">
         <v>0.0911</v>
       </c>
-      <c r="K256" s="1" t="n">
+      <c r="L256" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -9955,9 +10726,12 @@
         <v>0.01421</v>
       </c>
       <c r="J257" s="1" t="n">
+        <v>0.01428</v>
+      </c>
+      <c r="K257" s="1" t="n">
         <v>0.01454</v>
       </c>
-      <c r="K257" s="1" t="n">
+      <c r="L257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -9992,9 +10766,12 @@
         <v>0.05125</v>
       </c>
       <c r="J258" s="1" t="n">
+        <v>0.05115</v>
+      </c>
+      <c r="K258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="K258" s="1" t="n">
+      <c r="L258" s="1" t="n">
         <v>0.0511</v>
       </c>
     </row>
@@ -10029,9 +10806,12 @@
         <v>0.008109999999999999</v>
       </c>
       <c r="J259" s="1" t="n">
+        <v>0.00814</v>
+      </c>
+      <c r="K259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="K259" s="1" t="n">
+      <c r="L259" s="1" t="n">
         <v>0.008109999999999999</v>
       </c>
     </row>
@@ -10066,9 +10846,12 @@
         <v>0.1894</v>
       </c>
       <c r="J260" s="1" t="n">
+        <v>0.1901</v>
+      </c>
+      <c r="K260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="K260" s="1" t="n">
+      <c r="L260" s="1" t="n">
         <v>0.1894</v>
       </c>
     </row>
@@ -10103,10 +10886,13 @@
         <v>0.0983</v>
       </c>
       <c r="J261" s="1" t="n">
+        <v>0.0982</v>
+      </c>
+      <c r="K261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="K261" s="1" t="n">
-        <v>0.0983</v>
+      <c r="L261" s="1" t="n">
+        <v>0.0982</v>
       </c>
     </row>
     <row r="262">
@@ -10140,9 +10926,12 @@
         <v>0.2113</v>
       </c>
       <c r="J262" s="1" t="n">
+        <v>0.2114</v>
+      </c>
+      <c r="K262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="K262" s="1" t="n">
+      <c r="L262" s="1" t="n">
         <v>0.2113</v>
       </c>
     </row>
@@ -10177,9 +10966,12 @@
         <v>0.008465</v>
       </c>
       <c r="J263" s="1" t="n">
+        <v>0.008496999999999999</v>
+      </c>
+      <c r="K263" s="1" t="n">
         <v>0.008522999999999999</v>
       </c>
-      <c r="K263" s="1" t="n">
+      <c r="L263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -10214,9 +11006,12 @@
         <v>2.632</v>
       </c>
       <c r="J264" s="1" t="n">
+        <v>2.632</v>
+      </c>
+      <c r="K264" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="K264" s="1" t="n">
+      <c r="L264" s="1" t="n">
         <v>2.632</v>
       </c>
     </row>
@@ -10251,9 +11046,12 @@
         <v>0.01855</v>
       </c>
       <c r="J265" s="1" t="n">
+        <v>0.01856</v>
+      </c>
+      <c r="K265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="K265" s="1" t="n">
+      <c r="L265" s="1" t="n">
         <v>0.01847</v>
       </c>
     </row>
@@ -10288,9 +11086,12 @@
         <v>0.3592</v>
       </c>
       <c r="J266" s="1" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="K266" s="1" t="n">
         <v>0.3604</v>
       </c>
-      <c r="K266" s="1" t="n">
+      <c r="L266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -10325,9 +11126,12 @@
         <v>0.03408</v>
       </c>
       <c r="J267" s="1" t="n">
+        <v>0.03442</v>
+      </c>
+      <c r="K267" s="1" t="n">
         <v>0.03464</v>
       </c>
-      <c r="K267" s="1" t="n">
+      <c r="L267" s="1" t="n">
         <v>0.03408</v>
       </c>
     </row>
@@ -10362,9 +11166,12 @@
         <v>0.118</v>
       </c>
       <c r="J268" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="K268" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="K268" s="1" t="n">
+      <c r="L268" s="1" t="n">
         <v>0.118</v>
       </c>
     </row>
@@ -10399,9 +11206,12 @@
         <v>0.07973</v>
       </c>
       <c r="J269" s="1" t="n">
+        <v>0.08005</v>
+      </c>
+      <c r="K269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="K269" s="1" t="n">
+      <c r="L269" s="1" t="n">
         <v>0.07973</v>
       </c>
     </row>
@@ -10436,9 +11246,12 @@
         <v>0.01382</v>
       </c>
       <c r="J270" s="1" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="K270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="K270" s="1" t="n">
+      <c r="L270" s="1" t="n">
         <v>0.01382</v>
       </c>
     </row>
@@ -10473,9 +11286,12 @@
         <v>0.007558</v>
       </c>
       <c r="J271" s="1" t="n">
+        <v>0.007568</v>
+      </c>
+      <c r="K271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="K271" s="1" t="n">
+      <c r="L271" s="1" t="n">
         <v>0.007558</v>
       </c>
     </row>
@@ -10510,9 +11326,12 @@
         <v>0.0741</v>
       </c>
       <c r="J272" s="1" t="n">
+        <v>0.07421999999999999</v>
+      </c>
+      <c r="K272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="K272" s="1" t="n">
+      <c r="L272" s="1" t="n">
         <v>0.0741</v>
       </c>
     </row>
@@ -10547,9 +11366,12 @@
         <v>3.16e-05</v>
       </c>
       <c r="J273" s="1" t="n">
+        <v>3.14e-05</v>
+      </c>
+      <c r="K273" s="1" t="n">
         <v>3.16e-05</v>
       </c>
-      <c r="K273" s="1" t="n">
+      <c r="L273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -10584,9 +11406,12 @@
         <v>0.005469</v>
       </c>
       <c r="J274" s="1" t="n">
+        <v>0.00548</v>
+      </c>
+      <c r="K274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="K274" s="1" t="n">
+      <c r="L274" s="1" t="n">
         <v>0.005469</v>
       </c>
     </row>
@@ -10621,9 +11446,12 @@
         <v>0.1813</v>
       </c>
       <c r="J275" s="1" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="K275" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="K275" s="1" t="n">
+      <c r="L275" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -10658,10 +11486,13 @@
         <v>0.006844</v>
       </c>
       <c r="J276" s="1" t="n">
+        <v>0.006843</v>
+      </c>
+      <c r="K276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="K276" s="1" t="n">
-        <v>0.006844</v>
+      <c r="L276" s="1" t="n">
+        <v>0.006843</v>
       </c>
     </row>
     <row r="277">
@@ -10695,9 +11526,12 @@
         <v>0.1303</v>
       </c>
       <c r="J277" s="1" t="n">
+        <v>0.1306</v>
+      </c>
+      <c r="K277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="K277" s="1" t="n">
+      <c r="L277" s="1" t="n">
         <v>0.1303</v>
       </c>
     </row>
@@ -10732,9 +11566,12 @@
         <v>0.02308</v>
       </c>
       <c r="J278" s="1" t="n">
+        <v>0.02323</v>
+      </c>
+      <c r="K278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="K278" s="1" t="n">
+      <c r="L278" s="1" t="n">
         <v>0.02308</v>
       </c>
     </row>
@@ -10769,9 +11606,12 @@
         <v>0.01812</v>
       </c>
       <c r="J279" s="1" t="n">
+        <v>0.01814</v>
+      </c>
+      <c r="K279" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="K279" s="1" t="n">
+      <c r="L279" s="1" t="n">
         <v>0.01812</v>
       </c>
     </row>
@@ -10806,10 +11646,13 @@
         <v>0.03723</v>
       </c>
       <c r="J280" s="1" t="n">
+        <v>0.03715</v>
+      </c>
+      <c r="K280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="K280" s="1" t="n">
-        <v>0.03723</v>
+      <c r="L280" s="1" t="n">
+        <v>0.03715</v>
       </c>
     </row>
     <row r="281">
@@ -10843,9 +11686,12 @@
         <v>0.03953</v>
       </c>
       <c r="J281" s="1" t="n">
+        <v>0.03961</v>
+      </c>
+      <c r="K281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="K281" s="1" t="n">
+      <c r="L281" s="1" t="n">
         <v>0.03953</v>
       </c>
     </row>
@@ -10880,10 +11726,13 @@
         <v>0.3007</v>
       </c>
       <c r="J282" s="1" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="K282" s="1" t="n">
         <v>0.3059</v>
       </c>
-      <c r="K282" s="1" t="n">
-        <v>0.3007</v>
+      <c r="L282" s="1" t="n">
+        <v>0.3001</v>
       </c>
     </row>
     <row r="283">
@@ -10917,10 +11766,13 @@
         <v>0.0112</v>
       </c>
       <c r="J283" s="1" t="n">
+        <v>0.01119</v>
+      </c>
+      <c r="K283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="K283" s="1" t="n">
-        <v>0.0112</v>
+      <c r="L283" s="1" t="n">
+        <v>0.01119</v>
       </c>
     </row>
     <row r="284">
@@ -10954,9 +11806,12 @@
         <v>9.500000000000001e-06</v>
       </c>
       <c r="J284" s="1" t="n">
+        <v>9.500000000000001e-06</v>
+      </c>
+      <c r="K284" s="1" t="n">
         <v>9.7e-06</v>
       </c>
-      <c r="K284" s="1" t="n">
+      <c r="L284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -10991,9 +11846,12 @@
         <v>0.1141</v>
       </c>
       <c r="J285" s="1" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="K285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="K285" s="1" t="n">
+      <c r="L285" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -11028,9 +11886,12 @@
         <v>0.003422</v>
       </c>
       <c r="J286" s="1" t="n">
+        <v>0.003424</v>
+      </c>
+      <c r="K286" s="1" t="n">
         <v>0.003485</v>
       </c>
-      <c r="K286" s="1" t="n">
+      <c r="L286" s="1" t="n">
         <v>0.003422</v>
       </c>
     </row>
@@ -11065,9 +11926,12 @@
         <v>0.08486</v>
       </c>
       <c r="J287" s="1" t="n">
+        <v>0.08513999999999999</v>
+      </c>
+      <c r="K287" s="1" t="n">
         <v>0.08573</v>
       </c>
-      <c r="K287" s="1" t="n">
+      <c r="L287" s="1" t="n">
         <v>0.08486</v>
       </c>
     </row>
@@ -11102,9 +11966,12 @@
         <v>0.09869</v>
       </c>
       <c r="J288" s="1" t="n">
+        <v>0.09938</v>
+      </c>
+      <c r="K288" s="1" t="n">
         <v>0.1001</v>
       </c>
-      <c r="K288" s="1" t="n">
+      <c r="L288" s="1" t="n">
         <v>0.09869</v>
       </c>
     </row>
@@ -11139,9 +12006,12 @@
         <v>0.4334</v>
       </c>
       <c r="J289" s="1" t="n">
+        <v>0.4335</v>
+      </c>
+      <c r="K289" s="1" t="n">
         <v>0.4359</v>
       </c>
-      <c r="K289" s="1" t="n">
+      <c r="L289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -11176,9 +12046,12 @@
         <v>0.03878</v>
       </c>
       <c r="J290" s="1" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="K290" s="1" t="n">
         <v>0.03966</v>
       </c>
-      <c r="K290" s="1" t="n">
+      <c r="L290" s="1" t="n">
         <v>0.03878</v>
       </c>
     </row>
@@ -11213,10 +12086,13 @@
         <v>0.2392</v>
       </c>
       <c r="J291" s="1" t="n">
+        <v>0.2376</v>
+      </c>
+      <c r="K291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="K291" s="1" t="n">
-        <v>0.2392</v>
+      <c r="L291" s="1" t="n">
+        <v>0.2376</v>
       </c>
     </row>
     <row r="292">
@@ -11250,9 +12126,12 @@
         <v>0.28331</v>
       </c>
       <c r="J292" s="1" t="n">
+        <v>0.28303</v>
+      </c>
+      <c r="K292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="K292" s="1" t="n">
+      <c r="L292" s="1" t="n">
         <v>0.28275</v>
       </c>
     </row>
@@ -11287,9 +12166,12 @@
         <v>0.1489</v>
       </c>
       <c r="J293" s="1" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="K293" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="K293" s="1" t="n">
+      <c r="L293" s="1" t="n">
         <v>0.1489</v>
       </c>
     </row>
@@ -11324,10 +12206,13 @@
         <v>4.207</v>
       </c>
       <c r="J294" s="1" t="n">
+        <v>4.205</v>
+      </c>
+      <c r="K294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="K294" s="1" t="n">
-        <v>4.207</v>
+      <c r="L294" s="1" t="n">
+        <v>4.205</v>
       </c>
     </row>
     <row r="295">
@@ -11361,9 +12246,12 @@
         <v>0.03339</v>
       </c>
       <c r="J295" s="1" t="n">
+        <v>0.03271</v>
+      </c>
+      <c r="K295" s="1" t="n">
         <v>0.03339</v>
       </c>
-      <c r="K295" s="1" t="n">
+      <c r="L295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -11398,10 +12286,13 @@
         <v>0.000975</v>
       </c>
       <c r="J296" s="1" t="n">
+        <v>0.000973</v>
+      </c>
+      <c r="K296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="K296" s="1" t="n">
-        <v>0.000975</v>
+      <c r="L296" s="1" t="n">
+        <v>0.000973</v>
       </c>
     </row>
     <row r="297">
@@ -11435,9 +12326,12 @@
         <v>0.08154</v>
       </c>
       <c r="J297" s="1" t="n">
+        <v>0.08180999999999999</v>
+      </c>
+      <c r="K297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="K297" s="1" t="n">
+      <c r="L297" s="1" t="n">
         <v>0.08154</v>
       </c>
     </row>
@@ -11472,9 +12366,12 @@
         <v>0.05745</v>
       </c>
       <c r="J298" s="1" t="n">
+        <v>0.0577</v>
+      </c>
+      <c r="K298" s="1" t="n">
         <v>0.05821</v>
       </c>
-      <c r="K298" s="1" t="n">
+      <c r="L298" s="1" t="n">
         <v>0.05745</v>
       </c>
     </row>
@@ -11509,9 +12406,12 @@
         <v>0.091</v>
       </c>
       <c r="J299" s="1" t="n">
+        <v>0.09080000000000001</v>
+      </c>
+      <c r="K299" s="1" t="n">
         <v>0.0917</v>
       </c>
-      <c r="K299" s="1" t="n">
+      <c r="L299" s="1" t="n">
         <v>0.09066</v>
       </c>
     </row>
@@ -11546,9 +12446,12 @@
         <v>0.0274</v>
       </c>
       <c r="J300" s="1" t="n">
+        <v>0.02754</v>
+      </c>
+      <c r="K300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="K300" s="1" t="n">
+      <c r="L300" s="1" t="n">
         <v>0.0274</v>
       </c>
     </row>
@@ -11583,9 +12486,12 @@
         <v>0.06557</v>
       </c>
       <c r="J301" s="1" t="n">
+        <v>0.06571</v>
+      </c>
+      <c r="K301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="K301" s="1" t="n">
+      <c r="L301" s="1" t="n">
         <v>0.06557</v>
       </c>
     </row>
@@ -11620,9 +12526,12 @@
         <v>0.052936</v>
       </c>
       <c r="J302" s="1" t="n">
-        <v>0.052936</v>
+        <v>0.052985</v>
       </c>
       <c r="K302" s="1" t="n">
+        <v>0.052985</v>
+      </c>
+      <c r="L302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -11657,9 +12566,12 @@
         <v>5169.3</v>
       </c>
       <c r="J303" s="1" t="n">
+        <v>5168.8</v>
+      </c>
+      <c r="K303" s="1" t="n">
         <v>5177.6</v>
       </c>
-      <c r="K303" s="1" t="n">
+      <c r="L303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -11694,9 +12606,12 @@
         <v>14.9</v>
       </c>
       <c r="J304" s="1" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="K304" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="K304" s="1" t="n">
+      <c r="L304" s="1" t="n">
         <v>14.9</v>
       </c>
     </row>
@@ -11731,9 +12646,12 @@
         <v>0.003695</v>
       </c>
       <c r="J305" s="1" t="n">
+        <v>0.003696</v>
+      </c>
+      <c r="K305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="K305" s="1" t="n">
+      <c r="L305" s="1" t="n">
         <v>0.003695</v>
       </c>
     </row>
@@ -11768,10 +12686,13 @@
         <v>0.4568</v>
       </c>
       <c r="J306" s="1" t="n">
+        <v>0.4558</v>
+      </c>
+      <c r="K306" s="1" t="n">
         <v>0.4608</v>
       </c>
-      <c r="K306" s="1" t="n">
-        <v>0.4568</v>
+      <c r="L306" s="1" t="n">
+        <v>0.4558</v>
       </c>
     </row>
     <row r="307">
@@ -11805,9 +12726,12 @@
         <v>0.04696</v>
       </c>
       <c r="J307" s="1" t="n">
+        <v>0.04703</v>
+      </c>
+      <c r="K307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="K307" s="1" t="n">
+      <c r="L307" s="1" t="n">
         <v>0.04696</v>
       </c>
     </row>
@@ -11842,9 +12766,12 @@
         <v>1.4876</v>
       </c>
       <c r="J308" s="1" t="n">
+        <v>1.4886</v>
+      </c>
+      <c r="K308" s="1" t="n">
         <v>1.4891</v>
       </c>
-      <c r="K308" s="1" t="n">
+      <c r="L308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -11879,9 +12806,12 @@
         <v>0.0007937</v>
       </c>
       <c r="J309" s="1" t="n">
+        <v>0.0007986</v>
+      </c>
+      <c r="K309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="K309" s="1" t="n">
+      <c r="L309" s="1" t="n">
         <v>0.0007937</v>
       </c>
     </row>
@@ -11916,10 +12846,13 @@
         <v>4.617</v>
       </c>
       <c r="J310" s="1" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="K310" s="1" t="n">
-        <v>4.617</v>
+      <c r="L310" s="1" t="n">
+        <v>4.6</v>
       </c>
     </row>
     <row r="311">
@@ -11953,10 +12886,13 @@
         <v>4.761</v>
       </c>
       <c r="J311" s="1" t="n">
+        <v>4.743</v>
+      </c>
+      <c r="K311" s="1" t="n">
         <v>4.805</v>
       </c>
-      <c r="K311" s="1" t="n">
-        <v>4.761</v>
+      <c r="L311" s="1" t="n">
+        <v>4.743</v>
       </c>
     </row>
     <row r="312">
@@ -11990,9 +12926,12 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="J312" s="1" t="n">
+        <v>0.08125</v>
+      </c>
+      <c r="K312" s="1" t="n">
         <v>0.08212</v>
       </c>
-      <c r="K312" s="1" t="n">
+      <c r="L312" s="1" t="n">
         <v>0.08098</v>
       </c>
     </row>
@@ -12027,9 +12966,12 @@
         <v>2.012</v>
       </c>
       <c r="J313" s="1" t="n">
+        <v>2.021</v>
+      </c>
+      <c r="K313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="K313" s="1" t="n">
+      <c r="L313" s="1" t="n">
         <v>2.012</v>
       </c>
     </row>
@@ -12064,9 +13006,12 @@
         <v>0.07053</v>
       </c>
       <c r="J314" s="1" t="n">
-        <v>0.07123</v>
+        <v>0.07154000000000001</v>
       </c>
       <c r="K314" s="1" t="n">
+        <v>0.07154000000000001</v>
+      </c>
+      <c r="L314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -12101,9 +13046,12 @@
         <v>0.946</v>
       </c>
       <c r="J315" s="1" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="K315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="K315" s="1" t="n">
+      <c r="L315" s="1" t="n">
         <v>0.946</v>
       </c>
     </row>
@@ -12138,9 +13086,12 @@
         <v>0.1299</v>
       </c>
       <c r="J316" s="1" t="n">
+        <v>0.1299</v>
+      </c>
+      <c r="K316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="K316" s="1" t="n">
+      <c r="L316" s="1" t="n">
         <v>0.1299</v>
       </c>
     </row>
@@ -12175,9 +13126,12 @@
         <v>0.1811</v>
       </c>
       <c r="J317" s="1" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="K317" s="1" t="n">
         <v>0.186</v>
       </c>
-      <c r="K317" s="1" t="n">
+      <c r="L317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -12212,10 +13166,13 @@
         <v>0.01626</v>
       </c>
       <c r="J318" s="1" t="n">
+        <v>0.01615</v>
+      </c>
+      <c r="K318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="K318" s="1" t="n">
-        <v>0.01626</v>
+      <c r="L318" s="1" t="n">
+        <v>0.01615</v>
       </c>
     </row>
     <row r="319">
@@ -12249,10 +13206,13 @@
         <v>0.08369</v>
       </c>
       <c r="J319" s="1" t="n">
+        <v>0.08348999999999999</v>
+      </c>
+      <c r="K319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="K319" s="1" t="n">
-        <v>0.08369</v>
+      <c r="L319" s="1" t="n">
+        <v>0.08348999999999999</v>
       </c>
     </row>
     <row r="320">
@@ -12286,9 +13246,12 @@
         <v>0.007571</v>
       </c>
       <c r="J320" s="1" t="n">
+        <v>0.007584</v>
+      </c>
+      <c r="K320" s="1" t="n">
         <v>0.007667</v>
       </c>
-      <c r="K320" s="1" t="n">
+      <c r="L320" s="1" t="n">
         <v>0.007571</v>
       </c>
     </row>
@@ -12323,9 +13286,12 @@
         <v>0.05406</v>
       </c>
       <c r="J321" s="1" t="n">
+        <v>0.0541</v>
+      </c>
+      <c r="K321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="K321" s="1" t="n">
+      <c r="L321" s="1" t="n">
         <v>0.05406</v>
       </c>
     </row>
@@ -12360,9 +13326,12 @@
         <v>0.5476</v>
       </c>
       <c r="J322" s="1" t="n">
+        <v>0.5498</v>
+      </c>
+      <c r="K322" s="1" t="n">
         <v>0.5514</v>
       </c>
-      <c r="K322" s="1" t="n">
+      <c r="L322" s="1" t="n">
         <v>0.5476</v>
       </c>
     </row>
@@ -12397,9 +13366,12 @@
         <v>0.07557</v>
       </c>
       <c r="J323" s="1" t="n">
+        <v>0.07607999999999999</v>
+      </c>
+      <c r="K323" s="1" t="n">
         <v>0.07611999999999999</v>
       </c>
-      <c r="K323" s="1" t="n">
+      <c r="L323" s="1" t="n">
         <v>0.07525</v>
       </c>
     </row>
@@ -12434,9 +13406,12 @@
         <v>0.012909</v>
       </c>
       <c r="J324" s="1" t="n">
+        <v>0.012917</v>
+      </c>
+      <c r="K324" s="1" t="n">
         <v>0.013001</v>
       </c>
-      <c r="K324" s="1" t="n">
+      <c r="L324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -12471,9 +13446,12 @@
         <v>0.0989</v>
       </c>
       <c r="J325" s="1" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="K325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="K325" s="1" t="n">
+      <c r="L325" s="1" t="n">
         <v>0.0989</v>
       </c>
     </row>
@@ -12508,10 +13486,13 @@
         <v>0.01735</v>
       </c>
       <c r="J326" s="1" t="n">
+        <v>0.01732</v>
+      </c>
+      <c r="K326" s="1" t="n">
         <v>0.01765</v>
       </c>
-      <c r="K326" s="1" t="n">
-        <v>0.01735</v>
+      <c r="L326" s="1" t="n">
+        <v>0.01732</v>
       </c>
     </row>
     <row r="327">
@@ -12545,9 +13526,12 @@
         <v>0.06382</v>
       </c>
       <c r="J327" s="1" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="K327" s="1" t="n">
         <v>0.06435</v>
       </c>
-      <c r="K327" s="1" t="n">
+      <c r="L327" s="1" t="n">
         <v>0.06382</v>
       </c>
     </row>
@@ -12582,9 +13566,12 @@
         <v>0.2627</v>
       </c>
       <c r="J328" s="1" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="K328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="K328" s="1" t="n">
+      <c r="L328" s="1" t="n">
         <v>0.2627</v>
       </c>
     </row>
@@ -12619,9 +13606,12 @@
         <v>0.17234</v>
       </c>
       <c r="J329" s="1" t="n">
+        <v>0.17212</v>
+      </c>
+      <c r="K329" s="1" t="n">
         <v>0.17297</v>
       </c>
-      <c r="K329" s="1" t="n">
+      <c r="L329" s="1" t="n">
         <v>0.17145</v>
       </c>
     </row>
@@ -12656,9 +13646,12 @@
         <v>2.053</v>
       </c>
       <c r="J330" s="1" t="n">
+        <v>2.055</v>
+      </c>
+      <c r="K330" s="1" t="n">
         <v>2.088</v>
       </c>
-      <c r="K330" s="1" t="n">
+      <c r="L330" s="1" t="n">
         <v>2.043</v>
       </c>
     </row>
@@ -12693,9 +13686,12 @@
         <v>0.0283</v>
       </c>
       <c r="J331" s="1" t="n">
-        <v>0.0283</v>
+        <v>0.0285</v>
       </c>
       <c r="K331" s="1" t="n">
+        <v>0.0285</v>
+      </c>
+      <c r="L331" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -12730,9 +13726,12 @@
         <v>0.006026</v>
       </c>
       <c r="J332" s="1" t="n">
+        <v>0.006006</v>
+      </c>
+      <c r="K332" s="1" t="n">
         <v>0.006031</v>
       </c>
-      <c r="K332" s="1" t="n">
+      <c r="L332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -12767,9 +13766,12 @@
         <v>0.003497</v>
       </c>
       <c r="J333" s="1" t="n">
+        <v>0.003522</v>
+      </c>
+      <c r="K333" s="1" t="n">
         <v>0.003579</v>
       </c>
-      <c r="K333" s="1" t="n">
+      <c r="L333" s="1" t="n">
         <v>0.003497</v>
       </c>
     </row>
@@ -12804,10 +13806,13 @@
         <v>0.01395</v>
       </c>
       <c r="J334" s="1" t="n">
+        <v>0.01394</v>
+      </c>
+      <c r="K334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="K334" s="1" t="n">
-        <v>0.01395</v>
+      <c r="L334" s="1" t="n">
+        <v>0.01394</v>
       </c>
     </row>
     <row r="335">
@@ -12841,9 +13846,12 @@
         <v>1.123</v>
       </c>
       <c r="J335" s="1" t="n">
-        <v>1.13</v>
+        <v>1.132</v>
       </c>
       <c r="K335" s="1" t="n">
+        <v>1.132</v>
+      </c>
+      <c r="L335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -12878,10 +13886,13 @@
         <v>0.011297</v>
       </c>
       <c r="J336" s="1" t="n">
+        <v>0.011238</v>
+      </c>
+      <c r="K336" s="1" t="n">
         <v>0.011326</v>
       </c>
-      <c r="K336" s="1" t="n">
-        <v>0.011253</v>
+      <c r="L336" s="1" t="n">
+        <v>0.011238</v>
       </c>
     </row>
     <row r="337">
@@ -12915,9 +13926,12 @@
         <v>2.965</v>
       </c>
       <c r="J337" s="1" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="K337" s="1" t="n">
         <v>3.043</v>
       </c>
-      <c r="K337" s="1" t="n">
+      <c r="L337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -12952,9 +13966,12 @@
         <v>0.01858</v>
       </c>
       <c r="J338" s="1" t="n">
+        <v>0.01859</v>
+      </c>
+      <c r="K338" s="1" t="n">
         <v>0.01885</v>
       </c>
-      <c r="K338" s="1" t="n">
+      <c r="L338" s="1" t="n">
         <v>0.01858</v>
       </c>
     </row>
@@ -12989,9 +14006,12 @@
         <v>0.07708</v>
       </c>
       <c r="J339" s="1" t="n">
+        <v>0.07726</v>
+      </c>
+      <c r="K339" s="1" t="n">
         <v>0.07790999999999999</v>
       </c>
-      <c r="K339" s="1" t="n">
+      <c r="L339" s="1" t="n">
         <v>0.07689</v>
       </c>
     </row>
@@ -13026,9 +14046,12 @@
         <v>0.075</v>
       </c>
       <c r="J340" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="K340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="K340" s="1" t="n">
+      <c r="L340" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -13063,9 +14086,12 @@
         <v>0.03591</v>
       </c>
       <c r="J341" s="1" t="n">
+        <v>0.03591</v>
+      </c>
+      <c r="K341" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="K341" s="1" t="n">
+      <c r="L341" s="1" t="n">
         <v>0.03591</v>
       </c>
     </row>
@@ -13100,10 +14126,13 @@
         <v>2607</v>
       </c>
       <c r="J342" s="1" t="n">
+        <v>2606</v>
+      </c>
+      <c r="K342" s="1" t="n">
         <v>2647</v>
       </c>
-      <c r="K342" s="1" t="n">
-        <v>2607</v>
+      <c r="L342" s="1" t="n">
+        <v>2606</v>
       </c>
     </row>
     <row r="343">
@@ -13137,9 +14166,12 @@
         <v>0.0001962</v>
       </c>
       <c r="J343" s="1" t="n">
+        <v>0.0001972</v>
+      </c>
+      <c r="K343" s="1" t="n">
         <v>0.000198</v>
       </c>
-      <c r="K343" s="1" t="n">
+      <c r="L343" s="1" t="n">
         <v>0.0001959</v>
       </c>
     </row>
@@ -13174,9 +14206,12 @@
         <v>0.07925</v>
       </c>
       <c r="J344" s="1" t="n">
+        <v>0.07948</v>
+      </c>
+      <c r="K344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="K344" s="1" t="n">
+      <c r="L344" s="1" t="n">
         <v>0.07925</v>
       </c>
     </row>
@@ -13211,9 +14246,12 @@
         <v>0.0163</v>
       </c>
       <c r="J345" s="1" t="n">
+        <v>0.01653</v>
+      </c>
+      <c r="K345" s="1" t="n">
         <v>0.01656</v>
       </c>
-      <c r="K345" s="1" t="n">
+      <c r="L345" s="1" t="n">
         <v>0.0163</v>
       </c>
     </row>
@@ -13248,9 +14286,12 @@
         <v>2.746</v>
       </c>
       <c r="J346" s="1" t="n">
+        <v>2.757</v>
+      </c>
+      <c r="K346" s="1" t="n">
         <v>2.799</v>
       </c>
-      <c r="K346" s="1" t="n">
+      <c r="L346" s="1" t="n">
         <v>2.746</v>
       </c>
     </row>
@@ -13285,9 +14326,12 @@
         <v>0.01631</v>
       </c>
       <c r="J347" s="1" t="n">
+        <v>0.01633</v>
+      </c>
+      <c r="K347" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="K347" s="1" t="n">
+      <c r="L347" s="1" t="n">
         <v>0.01631</v>
       </c>
     </row>
@@ -13322,9 +14366,12 @@
         <v>0.03863</v>
       </c>
       <c r="J348" s="1" t="n">
+        <v>0.03867</v>
+      </c>
+      <c r="K348" s="1" t="n">
         <v>0.03897</v>
       </c>
-      <c r="K348" s="1" t="n">
+      <c r="L348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -13359,9 +14406,12 @@
         <v>0.3029</v>
       </c>
       <c r="J349" s="1" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="K349" s="1" t="n">
         <v>0.3065</v>
       </c>
-      <c r="K349" s="1" t="n">
+      <c r="L349" s="1" t="n">
         <v>0.3029</v>
       </c>
     </row>
@@ -13396,9 +14446,12 @@
         <v>0.005076</v>
       </c>
       <c r="J350" s="1" t="n">
+        <v>0.005091</v>
+      </c>
+      <c r="K350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="K350" s="1" t="n">
+      <c r="L350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -13433,9 +14486,12 @@
         <v>0.005065</v>
       </c>
       <c r="J351" s="1" t="n">
+        <v>0.005103</v>
+      </c>
+      <c r="K351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="K351" s="1" t="n">
+      <c r="L351" s="1" t="n">
         <v>0.005065</v>
       </c>
     </row>
@@ -13470,9 +14526,12 @@
         <v>0.004384</v>
       </c>
       <c r="J352" s="1" t="n">
+        <v>0.004388</v>
+      </c>
+      <c r="K352" s="1" t="n">
         <v>0.004419</v>
       </c>
-      <c r="K352" s="1" t="n">
+      <c r="L352" s="1" t="n">
         <v>0.004384</v>
       </c>
     </row>
@@ -13507,9 +14566,12 @@
         <v>0.08062999999999999</v>
       </c>
       <c r="J353" s="1" t="n">
+        <v>0.08101999999999999</v>
+      </c>
+      <c r="K353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="K353" s="1" t="n">
+      <c r="L353" s="1" t="n">
         <v>0.08062999999999999</v>
       </c>
     </row>
@@ -13544,9 +14606,12 @@
         <v>1.293</v>
       </c>
       <c r="J354" s="1" t="n">
+        <v>1.286</v>
+      </c>
+      <c r="K354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="K354" s="1" t="n">
+      <c r="L354" s="1" t="n">
         <v>1.283</v>
       </c>
     </row>
@@ -13581,9 +14646,12 @@
         <v>7.707</v>
       </c>
       <c r="J355" s="1" t="n">
+        <v>7.708</v>
+      </c>
+      <c r="K355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="K355" s="1" t="n">
+      <c r="L355" s="1" t="n">
         <v>7.707</v>
       </c>
     </row>
@@ -13618,9 +14686,12 @@
         <v>0.00778</v>
       </c>
       <c r="J356" s="1" t="n">
+        <v>0.007849999999999999</v>
+      </c>
+      <c r="K356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="K356" s="1" t="n">
+      <c r="L356" s="1" t="n">
         <v>0.00778</v>
       </c>
     </row>
@@ -13655,10 +14726,13 @@
         <v>0.005707</v>
       </c>
       <c r="J357" s="1" t="n">
+        <v>0.005632</v>
+      </c>
+      <c r="K357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="K357" s="1" t="n">
-        <v>0.005696</v>
+      <c r="L357" s="1" t="n">
+        <v>0.005632</v>
       </c>
     </row>
     <row r="358">
@@ -13692,9 +14766,12 @@
         <v>0.01551</v>
       </c>
       <c r="J358" s="1" t="n">
+        <v>0.01555</v>
+      </c>
+      <c r="K358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="K358" s="1" t="n">
+      <c r="L358" s="1" t="n">
         <v>0.01551</v>
       </c>
     </row>
@@ -13729,9 +14806,12 @@
         <v>3.636</v>
       </c>
       <c r="J359" s="1" t="n">
+        <v>3.637</v>
+      </c>
+      <c r="K359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="K359" s="1" t="n">
+      <c r="L359" s="1" t="n">
         <v>3.636</v>
       </c>
     </row>
@@ -13766,10 +14846,13 @@
         <v>0.1502</v>
       </c>
       <c r="J360" s="1" t="n">
+        <v>0.1497</v>
+      </c>
+      <c r="K360" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="K360" s="1" t="n">
-        <v>0.1499</v>
+      <c r="L360" s="1" t="n">
+        <v>0.1497</v>
       </c>
     </row>
     <row r="361">
@@ -13803,9 +14886,12 @@
         <v>0.07019</v>
       </c>
       <c r="J361" s="1" t="n">
+        <v>0.07035</v>
+      </c>
+      <c r="K361" s="1" t="n">
         <v>0.07104000000000001</v>
       </c>
-      <c r="K361" s="1" t="n">
+      <c r="L361" s="1" t="n">
         <v>0.07019</v>
       </c>
     </row>
@@ -13840,9 +14926,12 @@
         <v>0.01761</v>
       </c>
       <c r="J362" s="1" t="n">
+        <v>0.01764</v>
+      </c>
+      <c r="K362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="K362" s="1" t="n">
+      <c r="L362" s="1" t="n">
         <v>0.01761</v>
       </c>
     </row>
@@ -13877,9 +14966,12 @@
         <v>0.02234</v>
       </c>
       <c r="J363" s="1" t="n">
+        <v>0.02238</v>
+      </c>
+      <c r="K363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="K363" s="1" t="n">
+      <c r="L363" s="1" t="n">
         <v>0.02234</v>
       </c>
     </row>
@@ -13914,9 +15006,12 @@
         <v>0.01249</v>
       </c>
       <c r="J364" s="1" t="n">
+        <v>0.01256</v>
+      </c>
+      <c r="K364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="K364" s="1" t="n">
+      <c r="L364" s="1" t="n">
         <v>0.01249</v>
       </c>
     </row>
@@ -13951,10 +15046,13 @@
         <v>0.0916</v>
       </c>
       <c r="J365" s="1" t="n">
+        <v>0.0915</v>
+      </c>
+      <c r="K365" s="1" t="n">
         <v>0.0926</v>
       </c>
-      <c r="K365" s="1" t="n">
-        <v>0.0916</v>
+      <c r="L365" s="1" t="n">
+        <v>0.0915</v>
       </c>
     </row>
     <row r="366">
@@ -13988,9 +15086,12 @@
         <v>0.04224</v>
       </c>
       <c r="J366" s="1" t="n">
+        <v>0.04227</v>
+      </c>
+      <c r="K366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="K366" s="1" t="n">
+      <c r="L366" s="1" t="n">
         <v>0.04224</v>
       </c>
     </row>
@@ -14025,9 +15126,12 @@
         <v>0.03141</v>
       </c>
       <c r="J367" s="1" t="n">
-        <v>0.03164</v>
+        <v>0.03174</v>
       </c>
       <c r="K367" s="1" t="n">
+        <v>0.03174</v>
+      </c>
+      <c r="L367" s="1" t="n">
         <v>0.03141</v>
       </c>
     </row>
@@ -14062,9 +15166,12 @@
         <v>0.02335</v>
       </c>
       <c r="J368" s="1" t="n">
+        <v>0.02342</v>
+      </c>
+      <c r="K368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="K368" s="1" t="n">
+      <c r="L368" s="1" t="n">
         <v>0.02335</v>
       </c>
     </row>
@@ -14099,9 +15206,12 @@
         <v>0.03089</v>
       </c>
       <c r="J369" s="1" t="n">
+        <v>0.03099</v>
+      </c>
+      <c r="K369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="K369" s="1" t="n">
+      <c r="L369" s="1" t="n">
         <v>0.03089</v>
       </c>
     </row>
@@ -14136,9 +15246,12 @@
         <v>0.07924</v>
       </c>
       <c r="J370" s="1" t="n">
+        <v>0.07905</v>
+      </c>
+      <c r="K370" s="1" t="n">
         <v>0.07932</v>
       </c>
-      <c r="K370" s="1" t="n">
+      <c r="L370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -14173,9 +15286,12 @@
         <v>0.1077</v>
       </c>
       <c r="J371" s="1" t="n">
+        <v>0.1075</v>
+      </c>
+      <c r="K371" s="1" t="n">
         <v>0.1089</v>
       </c>
-      <c r="K371" s="1" t="n">
+      <c r="L371" s="1" t="n">
         <v>0.1074</v>
       </c>
     </row>
@@ -14210,9 +15326,12 @@
         <v>0.007045</v>
       </c>
       <c r="J372" s="1" t="n">
+        <v>0.007062</v>
+      </c>
+      <c r="K372" s="1" t="n">
         <v>0.007209</v>
       </c>
-      <c r="K372" s="1" t="n">
+      <c r="L372" s="1" t="n">
         <v>0.007045</v>
       </c>
     </row>
@@ -14247,9 +15366,12 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="J373" s="1" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="K373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="K373" s="1" t="n">
+      <c r="L373" s="1" t="n">
         <v>0.09619999999999999</v>
       </c>
     </row>
@@ -14284,9 +15406,12 @@
         <v>0.05804</v>
       </c>
       <c r="J374" s="1" t="n">
+        <v>0.05805</v>
+      </c>
+      <c r="K374" s="1" t="n">
         <v>0.05881</v>
       </c>
-      <c r="K374" s="1" t="n">
+      <c r="L374" s="1" t="n">
         <v>0.05804</v>
       </c>
     </row>
@@ -14321,9 +15446,12 @@
         <v>0.3205</v>
       </c>
       <c r="J375" s="1" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="K375" s="1" t="n">
         <v>0.3238</v>
       </c>
-      <c r="K375" s="1" t="n">
+      <c r="L375" s="1" t="n">
         <v>0.3193</v>
       </c>
     </row>
@@ -14358,9 +15486,12 @@
         <v>0.01958</v>
       </c>
       <c r="J376" s="1" t="n">
+        <v>0.01962</v>
+      </c>
+      <c r="K376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="K376" s="1" t="n">
+      <c r="L376" s="1" t="n">
         <v>0.01958</v>
       </c>
     </row>
@@ -14395,9 +15526,12 @@
         <v>0.06852999999999999</v>
       </c>
       <c r="J377" s="1" t="n">
+        <v>0.06868</v>
+      </c>
+      <c r="K377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="K377" s="1" t="n">
+      <c r="L377" s="1" t="n">
         <v>0.06852999999999999</v>
       </c>
     </row>
@@ -14432,9 +15566,12 @@
         <v>0.1581</v>
       </c>
       <c r="J378" s="1" t="n">
+        <v>0.15542</v>
+      </c>
+      <c r="K378" s="1" t="n">
         <v>0.1581</v>
       </c>
-      <c r="K378" s="1" t="n">
+      <c r="L378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -14469,9 +15606,12 @@
         <v>0.0005965</v>
       </c>
       <c r="J379" s="1" t="n">
+        <v>0.0005983</v>
+      </c>
+      <c r="K379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="K379" s="1" t="n">
+      <c r="L379" s="1" t="n">
         <v>0.0005965</v>
       </c>
     </row>
@@ -14506,9 +15646,12 @@
         <v>0.01015</v>
       </c>
       <c r="J380" s="1" t="n">
+        <v>0.01017</v>
+      </c>
+      <c r="K380" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="K380" s="1" t="n">
+      <c r="L380" s="1" t="n">
         <v>0.01015</v>
       </c>
     </row>
@@ -14543,9 +15686,12 @@
         <v>0.02547</v>
       </c>
       <c r="J381" s="1" t="n">
+        <v>0.02548</v>
+      </c>
+      <c r="K381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="K381" s="1" t="n">
+      <c r="L381" s="1" t="n">
         <v>0.02547</v>
       </c>
     </row>
@@ -14580,9 +15726,12 @@
         <v>0.19219</v>
       </c>
       <c r="J382" s="1" t="n">
+        <v>0.19254</v>
+      </c>
+      <c r="K382" s="1" t="n">
         <v>0.19263</v>
       </c>
-      <c r="K382" s="1" t="n">
+      <c r="L382" s="1" t="n">
         <v>0.18936</v>
       </c>
     </row>
@@ -14617,9 +15766,12 @@
         <v>0.09236</v>
       </c>
       <c r="J383" s="1" t="n">
+        <v>0.09236</v>
+      </c>
+      <c r="K383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="K383" s="1" t="n">
+      <c r="L383" s="1" t="n">
         <v>0.09236</v>
       </c>
     </row>
@@ -14654,9 +15806,12 @@
         <v>0.03179</v>
       </c>
       <c r="J384" s="1" t="n">
+        <v>0.0319</v>
+      </c>
+      <c r="K384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="K384" s="1" t="n">
+      <c r="L384" s="1" t="n">
         <v>0.03176</v>
       </c>
     </row>
@@ -14691,10 +15846,13 @@
         <v>0.011</v>
       </c>
       <c r="J385" s="1" t="n">
+        <v>0.01099</v>
+      </c>
+      <c r="K385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="K385" s="1" t="n">
-        <v>0.011</v>
+      <c r="L385" s="1" t="n">
+        <v>0.01099</v>
       </c>
     </row>
     <row r="386">
@@ -14728,9 +15886,12 @@
         <v>0.05224</v>
       </c>
       <c r="J386" s="1" t="n">
+        <v>0.05188</v>
+      </c>
+      <c r="K386" s="1" t="n">
         <v>0.05224</v>
       </c>
-      <c r="K386" s="1" t="n">
+      <c r="L386" s="1" t="n">
         <v>0.05087</v>
       </c>
     </row>
@@ -14765,9 +15926,12 @@
         <v>0.0252</v>
       </c>
       <c r="J387" s="1" t="n">
+        <v>0.02513</v>
+      </c>
+      <c r="K387" s="1" t="n">
         <v>0.02541</v>
       </c>
-      <c r="K387" s="1" t="n">
+      <c r="L387" s="1" t="n">
         <v>0.02483</v>
       </c>
     </row>
@@ -14802,9 +15966,12 @@
         <v>0.007267</v>
       </c>
       <c r="J388" s="1" t="n">
+        <v>0.007301</v>
+      </c>
+      <c r="K388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="K388" s="1" t="n">
+      <c r="L388" s="1" t="n">
         <v>0.007267</v>
       </c>
     </row>
@@ -14839,9 +16006,12 @@
         <v>0.01011</v>
       </c>
       <c r="J389" s="1" t="n">
+        <v>0.01013</v>
+      </c>
+      <c r="K389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="K389" s="1" t="n">
+      <c r="L389" s="1" t="n">
         <v>0.01011</v>
       </c>
     </row>
@@ -14876,9 +16046,12 @@
         <v>0.08233</v>
       </c>
       <c r="J390" s="1" t="n">
+        <v>0.08251</v>
+      </c>
+      <c r="K390" s="1" t="n">
         <v>0.0839</v>
       </c>
-      <c r="K390" s="1" t="n">
+      <c r="L390" s="1" t="n">
         <v>0.08233</v>
       </c>
     </row>
@@ -14913,10 +16086,13 @@
         <v>0.5021</v>
       </c>
       <c r="J391" s="1" t="n">
+        <v>0.5014</v>
+      </c>
+      <c r="K391" s="1" t="n">
         <v>0.5061</v>
       </c>
-      <c r="K391" s="1" t="n">
-        <v>0.5017</v>
+      <c r="L391" s="1" t="n">
+        <v>0.5014</v>
       </c>
     </row>
     <row r="392">
@@ -14950,10 +16126,13 @@
         <v>0.1171</v>
       </c>
       <c r="J392" s="1" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="K392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="K392" s="1" t="n">
-        <v>0.1171</v>
+      <c r="L392" s="1" t="n">
+        <v>0.117</v>
       </c>
     </row>
     <row r="393">
@@ -14987,9 +16166,12 @@
         <v>0.00246</v>
       </c>
       <c r="J393" s="1" t="n">
+        <v>0.00247</v>
+      </c>
+      <c r="K393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="K393" s="1" t="n">
+      <c r="L393" s="1" t="n">
         <v>0.00246</v>
       </c>
     </row>
@@ -15024,9 +16206,12 @@
         <v>0.02125</v>
       </c>
       <c r="J394" s="1" t="n">
+        <v>0.02129</v>
+      </c>
+      <c r="K394" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="K394" s="1" t="n">
+      <c r="L394" s="1" t="n">
         <v>0.02121</v>
       </c>
     </row>
@@ -15061,10 +16246,13 @@
         <v>0.0162</v>
       </c>
       <c r="J395" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="K395" s="1" t="n">
         <v>0.0163</v>
       </c>
-      <c r="K395" s="1" t="n">
-        <v>0.0161</v>
+      <c r="L395" s="1" t="n">
+        <v>0.0159</v>
       </c>
     </row>
     <row r="396">
@@ -15098,9 +16286,12 @@
         <v>0.1356</v>
       </c>
       <c r="J396" s="1" t="n">
+        <v>0.1358</v>
+      </c>
+      <c r="K396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="K396" s="1" t="n">
+      <c r="L396" s="1" t="n">
         <v>0.1356</v>
       </c>
     </row>
@@ -15135,10 +16326,13 @@
         <v>0.01458</v>
       </c>
       <c r="J397" s="1" t="n">
+        <v>0.01453</v>
+      </c>
+      <c r="K397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="K397" s="1" t="n">
-        <v>0.01458</v>
+      <c r="L397" s="1" t="n">
+        <v>0.01453</v>
       </c>
     </row>
     <row r="398">
@@ -15172,9 +16366,12 @@
         <v>6.813</v>
       </c>
       <c r="J398" s="1" t="n">
+        <v>6.782</v>
+      </c>
+      <c r="K398" s="1" t="n">
         <v>6.955</v>
       </c>
-      <c r="K398" s="1" t="n">
+      <c r="L398" s="1" t="n">
         <v>6.725</v>
       </c>
     </row>
@@ -15209,9 +16406,12 @@
         <v>0.009471</v>
       </c>
       <c r="J399" s="1" t="n">
+        <v>0.009455</v>
+      </c>
+      <c r="K399" s="1" t="n">
         <v>0.009509999999999999</v>
       </c>
-      <c r="K399" s="1" t="n">
+      <c r="L399" s="1" t="n">
         <v>0.009448</v>
       </c>
     </row>
@@ -15246,9 +16446,12 @@
         <v>0.001256</v>
       </c>
       <c r="J400" s="1" t="n">
+        <v>0.001263</v>
+      </c>
+      <c r="K400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="K400" s="1" t="n">
+      <c r="L400" s="1" t="n">
         <v>0.001256</v>
       </c>
     </row>
@@ -15283,9 +16486,12 @@
         <v>0.01846</v>
       </c>
       <c r="J401" s="1" t="n">
+        <v>0.01846</v>
+      </c>
+      <c r="K401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="K401" s="1" t="n">
+      <c r="L401" s="1" t="n">
         <v>0.01841</v>
       </c>
     </row>
@@ -15320,9 +16526,12 @@
         <v>0.08488999999999999</v>
       </c>
       <c r="J402" s="1" t="n">
+        <v>0.08506</v>
+      </c>
+      <c r="K402" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="K402" s="1" t="n">
+      <c r="L402" s="1" t="n">
         <v>0.08488999999999999</v>
       </c>
     </row>
@@ -15357,9 +16566,12 @@
         <v>0.00552</v>
       </c>
       <c r="J403" s="1" t="n">
+        <v>0.00552</v>
+      </c>
+      <c r="K403" s="1" t="n">
         <v>0.00556</v>
       </c>
-      <c r="K403" s="1" t="n">
+      <c r="L403" s="1" t="n">
         <v>0.00552</v>
       </c>
     </row>
@@ -15394,10 +16606,13 @@
         <v>0.04302</v>
       </c>
       <c r="J404" s="1" t="n">
+        <v>0.04278</v>
+      </c>
+      <c r="K404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="K404" s="1" t="n">
-        <v>0.04302</v>
+      <c r="L404" s="1" t="n">
+        <v>0.04278</v>
       </c>
     </row>
     <row r="405">
@@ -15431,9 +16646,12 @@
         <v>0.05838</v>
       </c>
       <c r="J405" s="1" t="n">
+        <v>0.05855</v>
+      </c>
+      <c r="K405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="K405" s="1" t="n">
+      <c r="L405" s="1" t="n">
         <v>0.05838</v>
       </c>
     </row>
@@ -15468,9 +16686,12 @@
         <v>0.01647</v>
       </c>
       <c r="J406" s="1" t="n">
+        <v>0.01649</v>
+      </c>
+      <c r="K406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="K406" s="1" t="n">
+      <c r="L406" s="1" t="n">
         <v>0.01647</v>
       </c>
     </row>
@@ -15505,9 +16726,12 @@
         <v>0.0423</v>
       </c>
       <c r="J407" s="1" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="K407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="K407" s="1" t="n">
+      <c r="L407" s="1" t="n">
         <v>0.0423</v>
       </c>
     </row>
@@ -15542,9 +16766,12 @@
         <v>0.01927</v>
       </c>
       <c r="J408" s="1" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="K408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="K408" s="1" t="n">
+      <c r="L408" s="1" t="n">
         <v>0.01927</v>
       </c>
     </row>
@@ -15579,9 +16806,12 @@
         <v>0.4441</v>
       </c>
       <c r="J409" s="1" t="n">
+        <v>0.4443</v>
+      </c>
+      <c r="K409" s="1" t="n">
         <v>0.4484</v>
       </c>
-      <c r="K409" s="1" t="n">
+      <c r="L409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -15616,9 +16846,12 @@
         <v>0.04419</v>
       </c>
       <c r="J410" s="1" t="n">
+        <v>0.04438</v>
+      </c>
+      <c r="K410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="K410" s="1" t="n">
+      <c r="L410" s="1" t="n">
         <v>0.04418</v>
       </c>
     </row>
@@ -15653,9 +16886,12 @@
         <v>27.45</v>
       </c>
       <c r="J411" s="1" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="K411" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="K411" s="1" t="n">
+      <c r="L411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -15690,9 +16926,12 @@
         <v>0.0351</v>
       </c>
       <c r="J412" s="1" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="K412" s="1" t="n">
         <v>0.03564</v>
       </c>
-      <c r="K412" s="1" t="n">
+      <c r="L412" s="1" t="n">
         <v>0.0351</v>
       </c>
     </row>
@@ -15727,10 +16966,13 @@
         <v>0.00341</v>
       </c>
       <c r="J413" s="1" t="n">
+        <v>0.003405</v>
+      </c>
+      <c r="K413" s="1" t="n">
         <v>0.003432</v>
       </c>
-      <c r="K413" s="1" t="n">
-        <v>0.00341</v>
+      <c r="L413" s="1" t="n">
+        <v>0.003405</v>
       </c>
     </row>
     <row r="414">
@@ -15764,9 +17006,12 @@
         <v>0.1526</v>
       </c>
       <c r="J414" s="1" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="K414" s="1" t="n">
         <v>0.1538</v>
       </c>
-      <c r="K414" s="1" t="n">
+      <c r="L414" s="1" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -15801,9 +17046,12 @@
         <v>0.0525</v>
       </c>
       <c r="J415" s="1" t="n">
+        <v>0.05263</v>
+      </c>
+      <c r="K415" s="1" t="n">
         <v>0.05288</v>
       </c>
-      <c r="K415" s="1" t="n">
+      <c r="L415" s="1" t="n">
         <v>0.0525</v>
       </c>
     </row>
@@ -15838,10 +17086,13 @@
         <v>0.0066</v>
       </c>
       <c r="J416" s="1" t="n">
+        <v>0.00658</v>
+      </c>
+      <c r="K416" s="1" t="n">
         <v>0.00669</v>
       </c>
-      <c r="K416" s="1" t="n">
-        <v>0.0066</v>
+      <c r="L416" s="1" t="n">
+        <v>0.00658</v>
       </c>
     </row>
     <row r="417">
@@ -15875,10 +17126,13 @@
         <v>0.06053</v>
       </c>
       <c r="J417" s="1" t="n">
+        <v>0.06052</v>
+      </c>
+      <c r="K417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="K417" s="1" t="n">
-        <v>0.06053</v>
+      <c r="L417" s="1" t="n">
+        <v>0.06052</v>
       </c>
     </row>
     <row r="418">
@@ -15912,10 +17166,13 @@
         <v>0.008047</v>
       </c>
       <c r="J418" s="1" t="n">
+        <v>0.008043</v>
+      </c>
+      <c r="K418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="K418" s="1" t="n">
-        <v>0.008047</v>
+      <c r="L418" s="1" t="n">
+        <v>0.008043</v>
       </c>
     </row>
     <row r="419">
@@ -15949,10 +17206,13 @@
         <v>0.07474</v>
       </c>
       <c r="J419" s="1" t="n">
+        <v>0.07435</v>
+      </c>
+      <c r="K419" s="1" t="n">
         <v>0.07524</v>
       </c>
-      <c r="K419" s="1" t="n">
-        <v>0.07459</v>
+      <c r="L419" s="1" t="n">
+        <v>0.07435</v>
       </c>
     </row>
     <row r="420">
@@ -15986,9 +17246,12 @@
         <v>0.02105</v>
       </c>
       <c r="J420" s="1" t="n">
+        <v>0.02123</v>
+      </c>
+      <c r="K420" s="1" t="n">
         <v>0.02146</v>
       </c>
-      <c r="K420" s="1" t="n">
+      <c r="L420" s="1" t="n">
         <v>0.02105</v>
       </c>
     </row>
@@ -16023,9 +17286,12 @@
         <v>0.06977999999999999</v>
       </c>
       <c r="J421" s="1" t="n">
+        <v>0.06987</v>
+      </c>
+      <c r="K421" s="1" t="n">
         <v>0.07038999999999999</v>
       </c>
-      <c r="K421" s="1" t="n">
+      <c r="L421" s="1" t="n">
         <v>0.06938999999999999</v>
       </c>
     </row>
@@ -16060,10 +17326,13 @@
         <v>0.01493</v>
       </c>
       <c r="J422" s="1" t="n">
+        <v>0.01487</v>
+      </c>
+      <c r="K422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="K422" s="1" t="n">
-        <v>0.01493</v>
+      <c r="L422" s="1" t="n">
+        <v>0.01487</v>
       </c>
     </row>
     <row r="423">
@@ -16097,9 +17366,12 @@
         <v>0.006648</v>
       </c>
       <c r="J423" s="1" t="n">
+        <v>0.006654</v>
+      </c>
+      <c r="K423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="K423" s="1" t="n">
+      <c r="L423" s="1" t="n">
         <v>0.006648</v>
       </c>
     </row>
@@ -16134,9 +17406,12 @@
         <v>0.912</v>
       </c>
       <c r="J424" s="1" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="K424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="K424" s="1" t="n">
+      <c r="L424" s="1" t="n">
         <v>0.912</v>
       </c>
     </row>
@@ -16171,9 +17446,12 @@
         <v>0.03546</v>
       </c>
       <c r="J425" s="1" t="n">
+        <v>0.03555</v>
+      </c>
+      <c r="K425" s="1" t="n">
         <v>0.03596</v>
       </c>
-      <c r="K425" s="1" t="n">
+      <c r="L425" s="1" t="n">
         <v>0.03546</v>
       </c>
     </row>
@@ -16208,9 +17486,12 @@
         <v>1.781</v>
       </c>
       <c r="J426" s="1" t="n">
+        <v>1.803</v>
+      </c>
+      <c r="K426" s="1" t="n">
         <v>1.81</v>
       </c>
-      <c r="K426" s="1" t="n">
+      <c r="L426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -16245,9 +17526,12 @@
         <v>0.12736</v>
       </c>
       <c r="J427" s="1" t="n">
+        <v>0.12775</v>
+      </c>
+      <c r="K427" s="1" t="n">
         <v>0.12835</v>
       </c>
-      <c r="K427" s="1" t="n">
+      <c r="L427" s="1" t="n">
         <v>0.12736</v>
       </c>
     </row>
@@ -16282,9 +17566,12 @@
         <v>0.05297</v>
       </c>
       <c r="J428" s="1" t="n">
+        <v>0.05336</v>
+      </c>
+      <c r="K428" s="1" t="n">
         <v>0.05362</v>
       </c>
-      <c r="K428" s="1" t="n">
+      <c r="L428" s="1" t="n">
         <v>0.05297</v>
       </c>
     </row>
@@ -16319,9 +17606,12 @@
         <v>1.289</v>
       </c>
       <c r="J429" s="1" t="n">
+        <v>1.293</v>
+      </c>
+      <c r="K429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="K429" s="1" t="n">
+      <c r="L429" s="1" t="n">
         <v>1.289</v>
       </c>
     </row>
@@ -16356,9 +17646,12 @@
         <v>0.07482</v>
       </c>
       <c r="J430" s="1" t="n">
+        <v>0.07506</v>
+      </c>
+      <c r="K430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="K430" s="1" t="n">
+      <c r="L430" s="1" t="n">
         <v>0.07482</v>
       </c>
     </row>
@@ -16393,10 +17686,13 @@
         <v>0.1588</v>
       </c>
       <c r="J431" s="1" t="n">
+        <v>0.1585</v>
+      </c>
+      <c r="K431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="K431" s="1" t="n">
-        <v>0.1588</v>
+      <c r="L431" s="1" t="n">
+        <v>0.1585</v>
       </c>
     </row>
     <row r="432">
@@ -16430,9 +17726,12 @@
         <v>1.445</v>
       </c>
       <c r="J432" s="1" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="K432" s="1" t="n">
         <v>1.461</v>
       </c>
-      <c r="K432" s="1" t="n">
+      <c r="L432" s="1" t="n">
         <v>1.445</v>
       </c>
     </row>
@@ -16467,9 +17766,12 @@
         <v>3.266</v>
       </c>
       <c r="J433" s="1" t="n">
+        <v>3.272</v>
+      </c>
+      <c r="K433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="K433" s="1" t="n">
+      <c r="L433" s="1" t="n">
         <v>3.266</v>
       </c>
     </row>
@@ -16504,9 +17806,12 @@
         <v>0.1783</v>
       </c>
       <c r="J434" s="1" t="n">
+        <v>0.1787</v>
+      </c>
+      <c r="K434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="K434" s="1" t="n">
+      <c r="L434" s="1" t="n">
         <v>0.1783</v>
       </c>
     </row>
@@ -16541,9 +17846,12 @@
         <v>0.008580000000000001</v>
       </c>
       <c r="J435" s="1" t="n">
+        <v>0.008595999999999999</v>
+      </c>
+      <c r="K435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="K435" s="1" t="n">
+      <c r="L435" s="1" t="n">
         <v>0.008580000000000001</v>
       </c>
     </row>
@@ -16578,10 +17886,13 @@
         <v>0.2826</v>
       </c>
       <c r="J436" s="1" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="K436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="K436" s="1" t="n">
-        <v>0.2826</v>
+      <c r="L436" s="1" t="n">
+        <v>0.2818</v>
       </c>
     </row>
     <row r="437">
@@ -16615,9 +17926,12 @@
         <v>0.03906</v>
       </c>
       <c r="J437" s="1" t="n">
+        <v>0.03881</v>
+      </c>
+      <c r="K437" s="1" t="n">
         <v>0.03906</v>
       </c>
-      <c r="K437" s="1" t="n">
+      <c r="L437" s="1" t="n">
         <v>0.03814</v>
       </c>
     </row>
@@ -16652,9 +17966,12 @@
         <v>0.0242</v>
       </c>
       <c r="J438" s="1" t="n">
+        <v>0.02422</v>
+      </c>
+      <c r="K438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="K438" s="1" t="n">
+      <c r="L438" s="1" t="n">
         <v>0.0242</v>
       </c>
     </row>
@@ -16689,9 +18006,12 @@
         <v>0.04413</v>
       </c>
       <c r="J439" s="1" t="n">
+        <v>0.04406</v>
+      </c>
+      <c r="K439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="K439" s="1" t="n">
+      <c r="L439" s="1" t="n">
         <v>0.04405</v>
       </c>
     </row>
@@ -16726,10 +18046,13 @@
         <v>0.0005192</v>
       </c>
       <c r="J440" s="1" t="n">
+        <v>0.0005188</v>
+      </c>
+      <c r="K440" s="1" t="n">
         <v>0.0005258</v>
       </c>
-      <c r="K440" s="1" t="n">
-        <v>0.0005192</v>
+      <c r="L440" s="1" t="n">
+        <v>0.0005188</v>
       </c>
     </row>
     <row r="441">
@@ -16763,9 +18086,12 @@
         <v>0.04451</v>
       </c>
       <c r="J441" s="1" t="n">
-        <v>0.04451</v>
+        <v>0.04489</v>
       </c>
       <c r="K441" s="1" t="n">
+        <v>0.04489</v>
+      </c>
+      <c r="L441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -16800,9 +18126,12 @@
         <v>0.00041</v>
       </c>
       <c r="J442" s="1" t="n">
+        <v>0.000411</v>
+      </c>
+      <c r="K442" s="1" t="n">
         <v>0.000416</v>
       </c>
-      <c r="K442" s="1" t="n">
+      <c r="L442" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -16837,10 +18166,13 @@
         <v>0.09528</v>
       </c>
       <c r="J443" s="1" t="n">
+        <v>0.09513000000000001</v>
+      </c>
+      <c r="K443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="K443" s="1" t="n">
-        <v>0.09528</v>
+      <c r="L443" s="1" t="n">
+        <v>0.09513000000000001</v>
       </c>
     </row>
     <row r="444">
@@ -16874,9 +18206,12 @@
         <v>2.29</v>
       </c>
       <c r="J444" s="1" t="n">
+        <v>2.298</v>
+      </c>
+      <c r="K444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="K444" s="1" t="n">
+      <c r="L444" s="1" t="n">
         <v>2.289</v>
       </c>
     </row>
@@ -16911,9 +18246,12 @@
         <v>0.2715</v>
       </c>
       <c r="J445" s="1" t="n">
+        <v>0.2686</v>
+      </c>
+      <c r="K445" s="1" t="n">
         <v>0.2741</v>
       </c>
-      <c r="K445" s="1" t="n">
+      <c r="L445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -16948,10 +18286,13 @@
         <v>0.0007423</v>
       </c>
       <c r="J446" s="1" t="n">
+        <v>0.0007415</v>
+      </c>
+      <c r="K446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="K446" s="1" t="n">
-        <v>0.0007423</v>
+      <c r="L446" s="1" t="n">
+        <v>0.0007415</v>
       </c>
     </row>
     <row r="447">
@@ -16985,10 +18326,13 @@
         <v>0.03824</v>
       </c>
       <c r="J447" s="1" t="n">
+        <v>0.03821</v>
+      </c>
+      <c r="K447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="K447" s="1" t="n">
-        <v>0.03824</v>
+      <c r="L447" s="1" t="n">
+        <v>0.03821</v>
       </c>
     </row>
     <row r="448">
@@ -17022,9 +18366,12 @@
         <v>0.1769</v>
       </c>
       <c r="J448" s="1" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="K448" s="1" t="n">
         <v>0.1773</v>
       </c>
-      <c r="K448" s="1" t="n">
+      <c r="L448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -17059,9 +18406,12 @@
         <v>0.0426</v>
       </c>
       <c r="J449" s="1" t="n">
+        <v>0.04263</v>
+      </c>
+      <c r="K449" s="1" t="n">
         <v>0.04301</v>
       </c>
-      <c r="K449" s="1" t="n">
+      <c r="L449" s="1" t="n">
         <v>0.0426</v>
       </c>
     </row>
@@ -17096,9 +18446,12 @@
         <v>0.0001632</v>
       </c>
       <c r="J450" s="1" t="n">
+        <v>0.0001635</v>
+      </c>
+      <c r="K450" s="1" t="n">
         <v>0.0001654</v>
       </c>
-      <c r="K450" s="1" t="n">
+      <c r="L450" s="1" t="n">
         <v>0.0001632</v>
       </c>
     </row>
@@ -17133,9 +18486,12 @@
         <v>0.03745</v>
       </c>
       <c r="J451" s="1" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="K451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="K451" s="1" t="n">
+      <c r="L451" s="1" t="n">
         <v>0.03745</v>
       </c>
     </row>
@@ -17170,9 +18526,12 @@
         <v>0.00976</v>
       </c>
       <c r="J452" s="1" t="n">
+        <v>0.00978</v>
+      </c>
+      <c r="K452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="K452" s="1" t="n">
+      <c r="L452" s="1" t="n">
         <v>0.00976</v>
       </c>
     </row>
@@ -17207,9 +18566,12 @@
         <v>0.06782000000000001</v>
       </c>
       <c r="J453" s="1" t="n">
+        <v>0.06794</v>
+      </c>
+      <c r="K453" s="1" t="n">
         <v>0.06816</v>
       </c>
-      <c r="K453" s="1" t="n">
+      <c r="L453" s="1" t="n">
         <v>0.06782000000000001</v>
       </c>
     </row>
@@ -17244,10 +18606,13 @@
         <v>0.007496</v>
       </c>
       <c r="J454" s="1" t="n">
+        <v>0.007494</v>
+      </c>
+      <c r="K454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="K454" s="1" t="n">
-        <v>0.007496</v>
+      <c r="L454" s="1" t="n">
+        <v>0.007494</v>
       </c>
     </row>
     <row r="455">
@@ -17281,10 +18646,13 @@
         <v>0.003314</v>
       </c>
       <c r="J455" s="1" t="n">
+        <v>0.003307</v>
+      </c>
+      <c r="K455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="K455" s="1" t="n">
-        <v>0.003314</v>
+      <c r="L455" s="1" t="n">
+        <v>0.003307</v>
       </c>
     </row>
     <row r="456">
@@ -17318,9 +18686,12 @@
         <v>0.001842</v>
       </c>
       <c r="J456" s="1" t="n">
+        <v>0.001842</v>
+      </c>
+      <c r="K456" s="1" t="n">
         <v>0.001875</v>
       </c>
-      <c r="K456" s="1" t="n">
+      <c r="L456" s="1" t="n">
         <v>0.001842</v>
       </c>
     </row>
@@ -17355,9 +18726,12 @@
         <v>0.0001745</v>
       </c>
       <c r="J457" s="1" t="n">
+        <v>0.000175</v>
+      </c>
+      <c r="K457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="K457" s="1" t="n">
+      <c r="L457" s="1" t="n">
         <v>0.0001745</v>
       </c>
     </row>
@@ -17392,9 +18766,12 @@
         <v>0.0003889</v>
       </c>
       <c r="J458" s="1" t="n">
+        <v>0.0003879</v>
+      </c>
+      <c r="K458" s="1" t="n">
         <v>0.0003916</v>
       </c>
-      <c r="K458" s="1" t="n">
+      <c r="L458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -17429,9 +18806,12 @@
         <v>0.01403</v>
       </c>
       <c r="J459" s="1" t="n">
+        <v>0.01401</v>
+      </c>
+      <c r="K459" s="1" t="n">
         <v>0.01413</v>
       </c>
-      <c r="K459" s="1" t="n">
+      <c r="L459" s="1" t="n">
         <v>0.01391</v>
       </c>
     </row>
@@ -17466,9 +18846,12 @@
         <v>0.04523</v>
       </c>
       <c r="J460" s="1" t="n">
+        <v>0.04538</v>
+      </c>
+      <c r="K460" s="1" t="n">
         <v>0.04559</v>
       </c>
-      <c r="K460" s="1" t="n">
+      <c r="L460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -17503,9 +18886,12 @@
         <v>0.2809</v>
       </c>
       <c r="J461" s="1" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="K461" s="1" t="n">
         <v>0.2839</v>
       </c>
-      <c r="K461" s="1" t="n">
+      <c r="L461" s="1" t="n">
         <v>0.2809</v>
       </c>
     </row>
@@ -17540,9 +18926,12 @@
         <v>0.006267</v>
       </c>
       <c r="J462" s="1" t="n">
+        <v>0.006236</v>
+      </c>
+      <c r="K462" s="1" t="n">
         <v>0.006312</v>
       </c>
-      <c r="K462" s="1" t="n">
+      <c r="L462" s="1" t="n">
         <v>0.00622</v>
       </c>
     </row>
@@ -17577,9 +18966,12 @@
         <v>0.007032</v>
       </c>
       <c r="J463" s="1" t="n">
+        <v>0.007036</v>
+      </c>
+      <c r="K463" s="1" t="n">
         <v>0.007088</v>
       </c>
-      <c r="K463" s="1" t="n">
+      <c r="L463" s="1" t="n">
         <v>0.007032</v>
       </c>
     </row>
@@ -17614,9 +19006,12 @@
         <v>0.2876</v>
       </c>
       <c r="J464" s="1" t="n">
+        <v>0.2877</v>
+      </c>
+      <c r="K464" s="1" t="n">
         <v>0.288</v>
       </c>
-      <c r="K464" s="1" t="n">
+      <c r="L464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -17651,9 +19046,12 @@
         <v>0.08076</v>
       </c>
       <c r="J465" s="1" t="n">
+        <v>0.08076999999999999</v>
+      </c>
+      <c r="K465" s="1" t="n">
         <v>0.08183</v>
       </c>
-      <c r="K465" s="1" t="n">
+      <c r="L465" s="1" t="n">
         <v>0.08076</v>
       </c>
     </row>
@@ -17688,9 +19086,12 @@
         <v>0.6321</v>
       </c>
       <c r="J466" s="1" t="n">
+        <v>0.6343</v>
+      </c>
+      <c r="K466" s="1" t="n">
         <v>0.6368</v>
       </c>
-      <c r="K466" s="1" t="n">
+      <c r="L466" s="1" t="n">
         <v>0.6318</v>
       </c>
     </row>
@@ -17725,9 +19126,12 @@
         <v>0.01481</v>
       </c>
       <c r="J467" s="1" t="n">
+        <v>0.01478</v>
+      </c>
+      <c r="K467" s="1" t="n">
         <v>0.01499</v>
       </c>
-      <c r="K467" s="1" t="n">
+      <c r="L467" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -17762,10 +19166,13 @@
         <v>0.03437</v>
       </c>
       <c r="J468" s="1" t="n">
+        <v>0.03434</v>
+      </c>
+      <c r="K468" s="1" t="n">
         <v>0.03468</v>
       </c>
-      <c r="K468" s="1" t="n">
-        <v>0.03437</v>
+      <c r="L468" s="1" t="n">
+        <v>0.03434</v>
       </c>
     </row>
     <row r="469">
@@ -17799,9 +19206,12 @@
         <v>0.1624</v>
       </c>
       <c r="J469" s="1" t="n">
+        <v>0.1626</v>
+      </c>
+      <c r="K469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="K469" s="1" t="n">
+      <c r="L469" s="1" t="n">
         <v>0.1624</v>
       </c>
     </row>
@@ -17836,10 +19246,13 @@
         <v>0.4091</v>
       </c>
       <c r="J470" s="1" t="n">
+        <v>0.4085</v>
+      </c>
+      <c r="K470" s="1" t="n">
         <v>0.4151</v>
       </c>
-      <c r="K470" s="1" t="n">
-        <v>0.4091</v>
+      <c r="L470" s="1" t="n">
+        <v>0.4085</v>
       </c>
     </row>
     <row r="471">
@@ -17873,10 +19286,13 @@
         <v>0.06947</v>
       </c>
       <c r="J471" s="1" t="n">
+        <v>0.06934999999999999</v>
+      </c>
+      <c r="K471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="K471" s="1" t="n">
-        <v>0.06947</v>
+      <c r="L471" s="1" t="n">
+        <v>0.06934999999999999</v>
       </c>
     </row>
     <row r="472">
@@ -17910,10 +19326,13 @@
         <v>0.06641</v>
       </c>
       <c r="J472" s="1" t="n">
+        <v>0.06623999999999999</v>
+      </c>
+      <c r="K472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="K472" s="1" t="n">
-        <v>0.06641</v>
+      <c r="L472" s="1" t="n">
+        <v>0.06623999999999999</v>
       </c>
     </row>
     <row r="473">
@@ -17947,9 +19366,12 @@
         <v>0.01621</v>
       </c>
       <c r="J473" s="1" t="n">
+        <v>0.01621</v>
+      </c>
+      <c r="K473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="K473" s="1" t="n">
+      <c r="L473" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -17984,9 +19406,12 @@
         <v>0.2066</v>
       </c>
       <c r="J474" s="1" t="n">
+        <v>0.2069</v>
+      </c>
+      <c r="K474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="K474" s="1" t="n">
+      <c r="L474" s="1" t="n">
         <v>0.2066</v>
       </c>
     </row>
@@ -18021,10 +19446,13 @@
         <v>0.04222</v>
       </c>
       <c r="J475" s="1" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="K475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="K475" s="1" t="n">
-        <v>0.04202</v>
+      <c r="L475" s="1" t="n">
+        <v>0.042</v>
       </c>
     </row>
     <row r="476">
@@ -18058,10 +19486,13 @@
         <v>1.563</v>
       </c>
       <c r="J476" s="1" t="n">
+        <v>1.561</v>
+      </c>
+      <c r="K476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="K476" s="1" t="n">
-        <v>1.563</v>
+      <c r="L476" s="1" t="n">
+        <v>1.561</v>
       </c>
     </row>
     <row r="477">
@@ -18095,10 +19526,13 @@
         <v>0.1004</v>
       </c>
       <c r="J477" s="1" t="n">
+        <v>0.1003</v>
+      </c>
+      <c r="K477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="K477" s="1" t="n">
-        <v>0.1004</v>
+      <c r="L477" s="1" t="n">
+        <v>0.1003</v>
       </c>
     </row>
     <row r="478">
@@ -18132,9 +19566,12 @@
         <v>0.00115</v>
       </c>
       <c r="J478" s="1" t="n">
+        <v>0.001152</v>
+      </c>
+      <c r="K478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="K478" s="1" t="n">
+      <c r="L478" s="1" t="n">
         <v>0.00115</v>
       </c>
     </row>
@@ -18169,10 +19606,13 @@
         <v>0.1473</v>
       </c>
       <c r="J479" s="1" t="n">
+        <v>0.1457</v>
+      </c>
+      <c r="K479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="K479" s="1" t="n">
-        <v>0.1462</v>
+      <c r="L479" s="1" t="n">
+        <v>0.1457</v>
       </c>
     </row>
     <row r="480">
@@ -18206,9 +19646,12 @@
         <v>0.001719</v>
       </c>
       <c r="J480" s="1" t="n">
+        <v>0.001722</v>
+      </c>
+      <c r="K480" s="1" t="n">
         <v>0.001734</v>
       </c>
-      <c r="K480" s="1" t="n">
+      <c r="L480" s="1" t="n">
         <v>0.001719</v>
       </c>
     </row>
@@ -18243,10 +19686,13 @@
         <v>0.909</v>
       </c>
       <c r="J481" s="1" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="K481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="K481" s="1" t="n">
-        <v>0.909</v>
+      <c r="L481" s="1" t="n">
+        <v>0.908</v>
       </c>
     </row>
     <row r="482">
@@ -18280,9 +19726,12 @@
         <v>0.13336</v>
       </c>
       <c r="J482" s="1" t="n">
+        <v>0.13374</v>
+      </c>
+      <c r="K482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="K482" s="1" t="n">
+      <c r="L482" s="1" t="n">
         <v>0.13336</v>
       </c>
     </row>
@@ -18317,10 +19766,13 @@
         <v>0.04024</v>
       </c>
       <c r="J483" s="1" t="n">
+        <v>0.04023</v>
+      </c>
+      <c r="K483" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="K483" s="1" t="n">
-        <v>0.04024</v>
+      <c r="L483" s="1" t="n">
+        <v>0.04023</v>
       </c>
     </row>
     <row r="484">
@@ -18354,9 +19806,12 @@
         <v>0.3021</v>
       </c>
       <c r="J484" s="1" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="K484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="K484" s="1" t="n">
+      <c r="L484" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -18391,10 +19846,13 @@
         <v>0.05646</v>
       </c>
       <c r="J485" s="1" t="n">
+        <v>0.05603</v>
+      </c>
+      <c r="K485" s="1" t="n">
         <v>0.05709</v>
       </c>
-      <c r="K485" s="1" t="n">
-        <v>0.05633</v>
+      <c r="L485" s="1" t="n">
+        <v>0.05603</v>
       </c>
     </row>
     <row r="486">
@@ -18428,9 +19886,12 @@
         <v>0.001564</v>
       </c>
       <c r="J486" s="1" t="n">
+        <v>0.001568</v>
+      </c>
+      <c r="K486" s="1" t="n">
         <v>0.001579</v>
       </c>
-      <c r="K486" s="1" t="n">
+      <c r="L486" s="1" t="n">
         <v>0.001564</v>
       </c>
     </row>
@@ -18465,10 +19926,13 @@
         <v>0.06705999999999999</v>
       </c>
       <c r="J487" s="1" t="n">
+        <v>0.06702</v>
+      </c>
+      <c r="K487" s="1" t="n">
         <v>0.06766999999999999</v>
       </c>
-      <c r="K487" s="1" t="n">
-        <v>0.06705999999999999</v>
+      <c r="L487" s="1" t="n">
+        <v>0.06702</v>
       </c>
     </row>
     <row r="488">
@@ -18502,9 +19966,12 @@
         <v>0.1929</v>
       </c>
       <c r="J488" s="1" t="n">
+        <v>0.1932</v>
+      </c>
+      <c r="K488" s="1" t="n">
         <v>0.1953</v>
       </c>
-      <c r="K488" s="1" t="n">
+      <c r="L488" s="1" t="n">
         <v>0.1929</v>
       </c>
     </row>
@@ -18539,9 +20006,12 @@
         <v>0.04779</v>
       </c>
       <c r="J489" s="1" t="n">
+        <v>0.04797</v>
+      </c>
+      <c r="K489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="K489" s="1" t="n">
+      <c r="L489" s="1" t="n">
         <v>0.04779</v>
       </c>
     </row>
@@ -18576,9 +20046,12 @@
         <v>0.1389</v>
       </c>
       <c r="J490" s="1" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="K490" s="1" t="n">
         <v>0.1401</v>
       </c>
-      <c r="K490" s="1" t="n">
+      <c r="L490" s="1" t="n">
         <v>0.1389</v>
       </c>
     </row>
@@ -18613,9 +20086,12 @@
         <v>0.02245</v>
       </c>
       <c r="J491" s="1" t="n">
+        <v>0.02252</v>
+      </c>
+      <c r="K491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="K491" s="1" t="n">
+      <c r="L491" s="1" t="n">
         <v>0.02243</v>
       </c>
     </row>
@@ -18650,10 +20126,13 @@
         <v>0.007761</v>
       </c>
       <c r="J492" s="1" t="n">
+        <v>0.007746</v>
+      </c>
+      <c r="K492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="K492" s="1" t="n">
-        <v>0.007761</v>
+      <c r="L492" s="1" t="n">
+        <v>0.007746</v>
       </c>
     </row>
     <row r="493">
@@ -18687,9 +20166,12 @@
         <v>0.0005932</v>
       </c>
       <c r="J493" s="1" t="n">
+        <v>0.0005947</v>
+      </c>
+      <c r="K493" s="1" t="n">
         <v>0.0005992</v>
       </c>
-      <c r="K493" s="1" t="n">
+      <c r="L493" s="1" t="n">
         <v>0.0005932</v>
       </c>
     </row>
@@ -18724,9 +20206,12 @@
         <v>3.014</v>
       </c>
       <c r="J494" s="1" t="n">
+        <v>3.017</v>
+      </c>
+      <c r="K494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="K494" s="1" t="n">
+      <c r="L494" s="1" t="n">
         <v>2.999</v>
       </c>
     </row>
@@ -18761,9 +20246,12 @@
         <v>0.05042</v>
       </c>
       <c r="J495" s="1" t="n">
+        <v>0.05056</v>
+      </c>
+      <c r="K495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="K495" s="1" t="n">
+      <c r="L495" s="1" t="n">
         <v>0.05042</v>
       </c>
     </row>
@@ -18798,10 +20286,13 @@
         <v>0.00677</v>
       </c>
       <c r="J496" s="1" t="n">
+        <v>0.006742</v>
+      </c>
+      <c r="K496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="K496" s="1" t="n">
-        <v>0.00677</v>
+      <c r="L496" s="1" t="n">
+        <v>0.006742</v>
       </c>
     </row>
     <row r="497">
@@ -18835,9 +20326,12 @@
         <v>1.3</v>
       </c>
       <c r="J497" s="1" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="K497" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="K497" s="1" t="n">
+      <c r="L497" s="1" t="n">
         <v>1.299</v>
       </c>
     </row>
@@ -18872,10 +20366,13 @@
         <v>0.03957</v>
       </c>
       <c r="J498" s="1" t="n">
+        <v>0.03892</v>
+      </c>
+      <c r="K498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="K498" s="1" t="n">
-        <v>0.03957</v>
+      <c r="L498" s="1" t="n">
+        <v>0.03892</v>
       </c>
     </row>
     <row r="499">
@@ -18909,10 +20406,13 @@
         <v>0.04145</v>
       </c>
       <c r="J499" s="1" t="n">
+        <v>0.04101</v>
+      </c>
+      <c r="K499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="K499" s="1" t="n">
-        <v>0.04145</v>
+      <c r="L499" s="1" t="n">
+        <v>0.04101</v>
       </c>
     </row>
     <row r="500">
@@ -18946,9 +20446,12 @@
         <v>0.00544</v>
       </c>
       <c r="J500" s="1" t="n">
+        <v>0.00545</v>
+      </c>
+      <c r="K500" s="1" t="n">
         <v>0.00549</v>
       </c>
-      <c r="K500" s="1" t="n">
+      <c r="L500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -18983,10 +20486,13 @@
         <v>0.03572</v>
       </c>
       <c r="J501" s="1" t="n">
+        <v>0.03571</v>
+      </c>
+      <c r="K501" s="1" t="n">
         <v>0.0364</v>
       </c>
-      <c r="K501" s="1" t="n">
-        <v>0.03572</v>
+      <c r="L501" s="1" t="n">
+        <v>0.03571</v>
       </c>
     </row>
     <row r="502">
@@ -19020,10 +20526,13 @@
         <v>0.07288</v>
       </c>
       <c r="J502" s="1" t="n">
+        <v>0.07244</v>
+      </c>
+      <c r="K502" s="1" t="n">
         <v>0.07342</v>
       </c>
-      <c r="K502" s="1" t="n">
-        <v>0.07288</v>
+      <c r="L502" s="1" t="n">
+        <v>0.07244</v>
       </c>
     </row>
     <row r="503">
@@ -19057,9 +20566,12 @@
         <v>0.0007422</v>
       </c>
       <c r="J503" s="1" t="n">
+        <v>0.0007432</v>
+      </c>
+      <c r="K503" s="1" t="n">
         <v>0.000755</v>
       </c>
-      <c r="K503" s="1" t="n">
+      <c r="L503" s="1" t="n">
         <v>0.0007422</v>
       </c>
     </row>
@@ -19094,9 +20606,12 @@
         <v>0.015968</v>
       </c>
       <c r="J504" s="1" t="n">
+        <v>0.015962</v>
+      </c>
+      <c r="K504" s="1" t="n">
         <v>0.016003</v>
       </c>
-      <c r="K504" s="1" t="n">
+      <c r="L504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -19131,9 +20646,12 @@
         <v>0.00703</v>
       </c>
       <c r="J505" s="1" t="n">
+        <v>0.00703</v>
+      </c>
+      <c r="K505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="K505" s="1" t="n">
+      <c r="L505" s="1" t="n">
         <v>0.00703</v>
       </c>
     </row>
@@ -19168,9 +20686,12 @@
         <v>0.0255</v>
       </c>
       <c r="J506" s="1" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="K506" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="K506" s="1" t="n">
+      <c r="L506" s="1" t="n">
         <v>0.0255</v>
       </c>
     </row>
@@ -19205,9 +20726,12 @@
         <v>0.001351</v>
       </c>
       <c r="J507" s="1" t="n">
-        <v>0.001358</v>
+        <v>0.001359</v>
       </c>
       <c r="K507" s="1" t="n">
+        <v>0.001359</v>
+      </c>
+      <c r="L507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -19242,9 +20766,12 @@
         <v>0.2805</v>
       </c>
       <c r="J508" s="1" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="K508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="K508" s="1" t="n">
+      <c r="L508" s="1" t="n">
         <v>0.2805</v>
       </c>
     </row>
@@ -19279,9 +20806,12 @@
         <v>0.1317</v>
       </c>
       <c r="J509" s="1" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="K509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="K509" s="1" t="n">
+      <c r="L509" s="1" t="n">
         <v>0.1317</v>
       </c>
     </row>
@@ -19316,9 +20846,12 @@
         <v>0.04896</v>
       </c>
       <c r="J510" s="1" t="n">
+        <v>0.04903</v>
+      </c>
+      <c r="K510" s="1" t="n">
         <v>0.04972</v>
       </c>
-      <c r="K510" s="1" t="n">
+      <c r="L510" s="1" t="n">
         <v>0.04896</v>
       </c>
     </row>
@@ -19353,10 +20886,13 @@
         <v>0.00274</v>
       </c>
       <c r="J511" s="1" t="n">
+        <v>0.00273</v>
+      </c>
+      <c r="K511" s="1" t="n">
         <v>0.00278</v>
       </c>
-      <c r="K511" s="1" t="n">
-        <v>0.00274</v>
+      <c r="L511" s="1" t="n">
+        <v>0.00273</v>
       </c>
     </row>
     <row r="512">
@@ -19390,9 +20926,12 @@
         <v>0.015285</v>
       </c>
       <c r="J512" s="1" t="n">
+        <v>0.015293</v>
+      </c>
+      <c r="K512" s="1" t="n">
         <v>0.015454</v>
       </c>
-      <c r="K512" s="1" t="n">
+      <c r="L512" s="1" t="n">
         <v>0.015285</v>
       </c>
     </row>
@@ -19427,10 +20966,13 @@
         <v>0.6918</v>
       </c>
       <c r="J513" s="1" t="n">
+        <v>0.6899</v>
+      </c>
+      <c r="K513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="K513" s="1" t="n">
-        <v>0.6918</v>
+      <c r="L513" s="1" t="n">
+        <v>0.6899</v>
       </c>
     </row>
     <row r="514">
@@ -19464,10 +21006,13 @@
         <v>0.004538</v>
       </c>
       <c r="J514" s="1" t="n">
+        <v>0.004517</v>
+      </c>
+      <c r="K514" s="1" t="n">
         <v>0.004589</v>
       </c>
-      <c r="K514" s="1" t="n">
-        <v>0.004534</v>
+      <c r="L514" s="1" t="n">
+        <v>0.004517</v>
       </c>
     </row>
     <row r="515">
@@ -19501,9 +21046,12 @@
         <v>0.005008</v>
       </c>
       <c r="J515" s="1" t="n">
+        <v>0.005016</v>
+      </c>
+      <c r="K515" s="1" t="n">
         <v>0.005066</v>
       </c>
-      <c r="K515" s="1" t="n">
+      <c r="L515" s="1" t="n">
         <v>0.005008</v>
       </c>
     </row>
@@ -19538,10 +21086,13 @@
         <v>0.06321</v>
       </c>
       <c r="J516" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="K516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="K516" s="1" t="n">
-        <v>0.06321</v>
+      <c r="L516" s="1" t="n">
+        <v>0.06320000000000001</v>
       </c>
     </row>
     <row r="517">
@@ -19575,9 +21126,12 @@
         <v>0.06458</v>
       </c>
       <c r="J517" s="1" t="n">
+        <v>0.06485</v>
+      </c>
+      <c r="K517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="K517" s="1" t="n">
+      <c r="L517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -19612,9 +21166,12 @@
         <v>0.01199</v>
       </c>
       <c r="J518" s="1" t="n">
+        <v>0.01202</v>
+      </c>
+      <c r="K518" s="1" t="n">
         <v>0.01219</v>
       </c>
-      <c r="K518" s="1" t="n">
+      <c r="L518" s="1" t="n">
         <v>0.01199</v>
       </c>
     </row>
@@ -19649,9 +21206,12 @@
         <v>0.04749</v>
       </c>
       <c r="J519" s="1" t="n">
+        <v>0.04759</v>
+      </c>
+      <c r="K519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="K519" s="1" t="n">
+      <c r="L519" s="1" t="n">
         <v>0.04743</v>
       </c>
     </row>
@@ -19686,9 +21246,12 @@
         <v>0.04349</v>
       </c>
       <c r="J520" s="1" t="n">
+        <v>0.04365</v>
+      </c>
+      <c r="K520" s="1" t="n">
         <v>0.04411</v>
       </c>
-      <c r="K520" s="1" t="n">
+      <c r="L520" s="1" t="n">
         <v>0.04349</v>
       </c>
     </row>
@@ -19723,10 +21286,13 @@
         <v>0.008461</v>
       </c>
       <c r="J521" s="1" t="n">
+        <v>0.008411999999999999</v>
+      </c>
+      <c r="K521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="K521" s="1" t="n">
-        <v>0.008461</v>
+      <c r="L521" s="1" t="n">
+        <v>0.008411999999999999</v>
       </c>
     </row>
     <row r="522">
@@ -19760,10 +21326,13 @@
         <v>0.08908000000000001</v>
       </c>
       <c r="J522" s="1" t="n">
+        <v>0.08819</v>
+      </c>
+      <c r="K522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="K522" s="1" t="n">
-        <v>0.08906</v>
+      <c r="L522" s="1" t="n">
+        <v>0.08819</v>
       </c>
     </row>
     <row r="523">
@@ -19797,9 +21366,12 @@
         <v>0.006433</v>
       </c>
       <c r="J523" s="1" t="n">
+        <v>0.006439</v>
+      </c>
+      <c r="K523" s="1" t="n">
         <v>0.006492</v>
       </c>
-      <c r="K523" s="1" t="n">
+      <c r="L523" s="1" t="n">
         <v>0.006433</v>
       </c>
     </row>
@@ -19834,10 +21406,13 @@
         <v>0.01646</v>
       </c>
       <c r="J524" s="1" t="n">
+        <v>0.01644</v>
+      </c>
+      <c r="K524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="K524" s="1" t="n">
-        <v>0.01646</v>
+      <c r="L524" s="1" t="n">
+        <v>0.01644</v>
       </c>
     </row>
     <row r="525">
@@ -19871,10 +21446,13 @@
         <v>0.01787</v>
       </c>
       <c r="J525" s="1" t="n">
+        <v>0.01779</v>
+      </c>
+      <c r="K525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="K525" s="1" t="n">
-        <v>0.01787</v>
+      <c r="L525" s="1" t="n">
+        <v>0.01779</v>
       </c>
     </row>
     <row r="526">
@@ -19908,9 +21486,12 @@
         <v>0.07883</v>
       </c>
       <c r="J526" s="1" t="n">
+        <v>0.07919</v>
+      </c>
+      <c r="K526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="K526" s="1" t="n">
+      <c r="L526" s="1" t="n">
         <v>0.07883</v>
       </c>
     </row>
@@ -19945,10 +21526,13 @@
         <v>0.01611</v>
       </c>
       <c r="J527" s="1" t="n">
+        <v>0.01606</v>
+      </c>
+      <c r="K527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="K527" s="1" t="n">
-        <v>0.01611</v>
+      <c r="L527" s="1" t="n">
+        <v>0.01606</v>
       </c>
     </row>
     <row r="528">
@@ -19982,9 +21566,12 @@
         <v>0.004183</v>
       </c>
       <c r="J528" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="K528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="K528" s="1" t="n">
+      <c r="L528" s="1" t="n">
         <v>0.004164</v>
       </c>
     </row>
@@ -20019,10 +21606,13 @@
         <v>0.003694</v>
       </c>
       <c r="J529" s="1" t="n">
+        <v>0.00369</v>
+      </c>
+      <c r="K529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="K529" s="1" t="n">
-        <v>0.003694</v>
+      <c r="L529" s="1" t="n">
+        <v>0.00369</v>
       </c>
     </row>
     <row r="530">
@@ -20056,9 +21646,12 @@
         <v>1.316</v>
       </c>
       <c r="J530" s="1" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="K530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="K530" s="1" t="n">
+      <c r="L530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -20093,10 +21686,13 @@
         <v>0.4896</v>
       </c>
       <c r="J531" s="1" t="n">
+        <v>0.4893</v>
+      </c>
+      <c r="K531" s="1" t="n">
         <v>0.494</v>
       </c>
-      <c r="K531" s="1" t="n">
-        <v>0.4896</v>
+      <c r="L531" s="1" t="n">
+        <v>0.4893</v>
       </c>
     </row>
     <row r="532">
@@ -20130,9 +21726,12 @@
         <v>0.03065</v>
       </c>
       <c r="J532" s="1" t="n">
+        <v>0.03065</v>
+      </c>
+      <c r="K532" s="1" t="n">
         <v>0.03091</v>
       </c>
-      <c r="K532" s="1" t="n">
+      <c r="L532" s="1" t="n">
         <v>0.03058</v>
       </c>
     </row>
@@ -20167,9 +21766,12 @@
         <v>0.153</v>
       </c>
       <c r="J533" s="1" t="n">
+        <v>0.1531</v>
+      </c>
+      <c r="K533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="K533" s="1" t="n">
+      <c r="L533" s="1" t="n">
         <v>0.153</v>
       </c>
     </row>
@@ -20204,10 +21806,13 @@
         <v>0.05393</v>
       </c>
       <c r="J534" s="1" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="K534" s="1" t="n">
         <v>0.05424</v>
       </c>
-      <c r="K534" s="1" t="n">
-        <v>0.05388</v>
+      <c r="L534" s="1" t="n">
+        <v>0.0536</v>
       </c>
     </row>
     <row r="535">
@@ -20241,9 +21846,12 @@
         <v>0.01498</v>
       </c>
       <c r="J535" s="1" t="n">
+        <v>0.01501</v>
+      </c>
+      <c r="K535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="K535" s="1" t="n">
+      <c r="L535" s="1" t="n">
         <v>0.01498</v>
       </c>
     </row>
@@ -20278,9 +21886,12 @@
         <v>0.05832</v>
       </c>
       <c r="J536" s="1" t="n">
+        <v>0.05823</v>
+      </c>
+      <c r="K536" s="1" t="n">
         <v>0.05879</v>
       </c>
-      <c r="K536" s="1" t="n">
+      <c r="L536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -20315,9 +21926,12 @@
         <v>0.05481</v>
       </c>
       <c r="J537" s="1" t="n">
+        <v>0.05487</v>
+      </c>
+      <c r="K537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="K537" s="1" t="n">
+      <c r="L537" s="1" t="n">
         <v>0.05481</v>
       </c>
     </row>
@@ -20352,9 +21966,12 @@
         <v>0.1059</v>
       </c>
       <c r="J538" s="1" t="n">
+        <v>0.1059</v>
+      </c>
+      <c r="K538" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="K538" s="1" t="n">
+      <c r="L538" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -20389,9 +22006,12 @@
         <v>0.01278</v>
       </c>
       <c r="J539" s="1" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="K539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="K539" s="1" t="n">
+      <c r="L539" s="1" t="n">
         <v>0.01278</v>
       </c>
     </row>
@@ -20426,9 +22046,12 @@
         <v>0.174</v>
       </c>
       <c r="J540" s="1" t="n">
+        <v>0.1742</v>
+      </c>
+      <c r="K540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="K540" s="1" t="n">
+      <c r="L540" s="1" t="n">
         <v>0.174</v>
       </c>
     </row>
@@ -20463,9 +22086,12 @@
         <v>0.1226</v>
       </c>
       <c r="J541" s="1" t="n">
+        <v>0.1227</v>
+      </c>
+      <c r="K541" s="1" t="n">
         <v>0.1239</v>
       </c>
-      <c r="K541" s="1" t="n">
+      <c r="L541" s="1" t="n">
         <v>0.1226</v>
       </c>
     </row>
@@ -20500,9 +22126,12 @@
         <v>0.02481</v>
       </c>
       <c r="J542" s="1" t="n">
+        <v>0.02485</v>
+      </c>
+      <c r="K542" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="K542" s="1" t="n">
+      <c r="L542" s="1" t="n">
         <v>0.02481</v>
       </c>
     </row>
@@ -20537,9 +22166,12 @@
         <v>0.0586</v>
       </c>
       <c r="J543" s="1" t="n">
+        <v>0.05862</v>
+      </c>
+      <c r="K543" s="1" t="n">
         <v>0.059</v>
       </c>
-      <c r="K543" s="1" t="n">
+      <c r="L543" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L543"/>
+  <dimension ref="A1:M543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -429,8 +429,9 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,10 +487,15 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>price_02:15</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -529,9 +535,12 @@
         <v>70995.10000000001</v>
       </c>
       <c r="K2" s="1" t="n">
+        <v>71180.10000000001</v>
+      </c>
+      <c r="L2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="L2" s="1" t="n">
+      <c r="M2" s="1" t="n">
         <v>70995.10000000001</v>
       </c>
     </row>
@@ -569,9 +578,12 @@
         <v>2102.04</v>
       </c>
       <c r="K3" s="1" t="n">
+        <v>2103.84</v>
+      </c>
+      <c r="L3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="L3" s="1" t="n">
+      <c r="M3" s="1" t="n">
         <v>2102.04</v>
       </c>
     </row>
@@ -609,9 +621,12 @@
         <v>88.81999999999999</v>
       </c>
       <c r="K4" s="1" t="n">
+        <v>88.92</v>
+      </c>
+      <c r="L4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="L4" s="1" t="n">
+      <c r="M4" s="1" t="n">
         <v>88.81999999999999</v>
       </c>
     </row>
@@ -649,9 +664,12 @@
         <v>3.85</v>
       </c>
       <c r="K5" s="1" t="n">
+        <v>3.799</v>
+      </c>
+      <c r="L5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="L5" s="1" t="n">
+      <c r="M5" s="1" t="n">
         <v>3.77</v>
       </c>
     </row>
@@ -689,9 +707,12 @@
         <v>1.3931</v>
       </c>
       <c r="K6" s="1" t="n">
+        <v>1.3964</v>
+      </c>
+      <c r="L6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="L6" s="1" t="n">
+      <c r="M6" s="1" t="n">
         <v>1.3931</v>
       </c>
     </row>
@@ -729,9 +750,12 @@
         <v>0.09601</v>
       </c>
       <c r="K7" s="1" t="n">
+        <v>0.09629</v>
+      </c>
+      <c r="L7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.09601</v>
       </c>
     </row>
@@ -769,9 +793,12 @@
         <v>0.014443</v>
       </c>
       <c r="K8" s="1" t="n">
-        <v>0.014568</v>
+        <v>0.014819</v>
       </c>
       <c r="L8" s="1" t="n">
+        <v>0.014819</v>
+      </c>
+      <c r="M8" s="1" t="n">
         <v>0.014064</v>
       </c>
     </row>
@@ -809,9 +836,12 @@
         <v>655.72</v>
       </c>
       <c r="K9" s="1" t="n">
+        <v>657.25</v>
+      </c>
+      <c r="L9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="L9" s="1" t="n">
+      <c r="M9" s="1" t="n">
         <v>655.72</v>
       </c>
     </row>
@@ -849,9 +879,12 @@
         <v>19.515</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>19.544</v>
+        <v>19.633</v>
       </c>
       <c r="L10" s="1" t="n">
+        <v>19.633</v>
+      </c>
+      <c r="M10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -889,9 +922,12 @@
         <v>0.0034117</v>
       </c>
       <c r="K11" s="1" t="n">
+        <v>0.003424</v>
+      </c>
+      <c r="L11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="L11" s="1" t="n">
+      <c r="M11" s="1" t="n">
         <v>0.0034117</v>
       </c>
     </row>
@@ -929,9 +965,12 @@
         <v>36.656</v>
       </c>
       <c r="K12" s="1" t="n">
-        <v>36.656</v>
+        <v>36.658</v>
       </c>
       <c r="L12" s="1" t="n">
+        <v>36.658</v>
+      </c>
+      <c r="M12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -969,9 +1008,12 @@
         <v>212.77</v>
       </c>
       <c r="K13" s="1" t="n">
+        <v>213.84</v>
+      </c>
+      <c r="L13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="L13" s="1" t="n">
+      <c r="M13" s="1" t="n">
         <v>212.33</v>
       </c>
     </row>
@@ -1009,10 +1051,13 @@
         <v>0.0011148</v>
       </c>
       <c r="K14" s="1" t="n">
+        <v>0.0011136</v>
+      </c>
+      <c r="L14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="L14" s="1" t="n">
-        <v>0.0011148</v>
+      <c r="M14" s="1" t="n">
+        <v>0.0011136</v>
       </c>
     </row>
     <row r="15">
@@ -1049,9 +1094,12 @@
         <v>0.28996</v>
       </c>
       <c r="K15" s="1" t="n">
-        <v>0.29276</v>
+        <v>0.29413</v>
       </c>
       <c r="L15" s="1" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="M15" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -1089,9 +1137,12 @@
         <v>234.3</v>
       </c>
       <c r="K16" s="1" t="n">
+        <v>232.4</v>
+      </c>
+      <c r="L16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="L16" s="1" t="n">
+      <c r="M16" s="1" t="n">
         <v>230.3</v>
       </c>
     </row>
@@ -1129,9 +1180,12 @@
         <v>0.9999</v>
       </c>
       <c r="K17" s="1" t="n">
+        <v>1.0034</v>
+      </c>
+      <c r="L17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="L17" s="1" t="n">
+      <c r="M17" s="1" t="n">
         <v>0.9963</v>
       </c>
     </row>
@@ -1169,9 +1223,12 @@
         <v>0.2671</v>
       </c>
       <c r="K18" s="1" t="n">
+        <v>0.2678</v>
+      </c>
+      <c r="L18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="L18" s="1" t="n">
+      <c r="M18" s="1" t="n">
         <v>0.2671</v>
       </c>
     </row>
@@ -1209,9 +1266,12 @@
         <v>9.755000000000001</v>
       </c>
       <c r="K19" s="1" t="n">
+        <v>9.776</v>
+      </c>
+      <c r="L19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="L19" s="1" t="n">
+      <c r="M19" s="1" t="n">
         <v>9.755000000000001</v>
       </c>
     </row>
@@ -1249,9 +1309,12 @@
         <v>5045.1</v>
       </c>
       <c r="K20" s="1" t="n">
+        <v>5042.34</v>
+      </c>
+      <c r="L20" s="1" t="n">
         <v>5059.14</v>
       </c>
-      <c r="L20" s="1" t="n">
+      <c r="M20" s="1" t="n">
         <v>5033.31</v>
       </c>
     </row>
@@ -1289,9 +1352,12 @@
         <v>462.36</v>
       </c>
       <c r="K21" s="1" t="n">
+        <v>464.17</v>
+      </c>
+      <c r="L21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="L21" s="1" t="n">
+      <c r="M21" s="1" t="n">
         <v>462.36</v>
       </c>
     </row>
@@ -1329,9 +1395,12 @@
         <v>1.4452</v>
       </c>
       <c r="K22" s="1" t="n">
+        <v>1.4327</v>
+      </c>
+      <c r="L22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="L22" s="1" t="n">
+      <c r="M22" s="1" t="n">
         <v>1.4185</v>
       </c>
     </row>
@@ -1369,10 +1438,13 @@
         <v>1.0812</v>
       </c>
       <c r="K23" s="1" t="n">
+        <v>1.0679</v>
+      </c>
+      <c r="L23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="L23" s="1" t="n">
-        <v>1.0691</v>
+      <c r="M23" s="1" t="n">
+        <v>1.0679</v>
       </c>
     </row>
     <row r="24">
@@ -1409,9 +1481,12 @@
         <v>1.346</v>
       </c>
       <c r="K24" s="1" t="n">
+        <v>1.349</v>
+      </c>
+      <c r="L24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="L24" s="1" t="n">
+      <c r="M24" s="1" t="n">
         <v>1.346</v>
       </c>
     </row>
@@ -1449,9 +1524,12 @@
         <v>9.140000000000001</v>
       </c>
       <c r="K25" s="1" t="n">
+        <v>9.166</v>
+      </c>
+      <c r="L25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="L25" s="1" t="n">
+      <c r="M25" s="1" t="n">
         <v>9.140000000000001</v>
       </c>
     </row>
@@ -1489,9 +1567,12 @@
         <v>0.3695</v>
       </c>
       <c r="K26" s="1" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="L26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="L26" s="1" t="n">
+      <c r="M26" s="1" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -1529,9 +1610,12 @@
         <v>0.876</v>
       </c>
       <c r="K27" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="L27" s="1" t="n">
+      <c r="M27" s="1" t="n">
         <v>0.876</v>
       </c>
     </row>
@@ -1569,9 +1653,12 @@
         <v>1.806</v>
       </c>
       <c r="K28" s="1" t="n">
+        <v>1.808</v>
+      </c>
+      <c r="L28" s="1" t="n">
         <v>1.823</v>
       </c>
-      <c r="L28" s="1" t="n">
+      <c r="M28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -1609,9 +1696,12 @@
         <v>0.1096</v>
       </c>
       <c r="K29" s="1" t="n">
+        <v>0.1096</v>
+      </c>
+      <c r="L29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="L29" s="1" t="n">
+      <c r="M29" s="1" t="n">
         <v>0.1096</v>
       </c>
     </row>
@@ -1649,9 +1739,12 @@
         <v>0.002046</v>
       </c>
       <c r="K30" s="1" t="n">
+        <v>0.00205</v>
+      </c>
+      <c r="L30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="L30" s="1" t="n">
+      <c r="M30" s="1" t="n">
         <v>0.002045</v>
       </c>
     </row>
@@ -1689,9 +1782,12 @@
         <v>1.481</v>
       </c>
       <c r="K31" s="1" t="n">
+        <v>1.482</v>
+      </c>
+      <c r="L31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="L31" s="1" t="n">
+      <c r="M31" s="1" t="n">
         <v>1.48</v>
       </c>
     </row>
@@ -1729,9 +1825,12 @@
         <v>0.174</v>
       </c>
       <c r="K32" s="1" t="n">
+        <v>0.1751</v>
+      </c>
+      <c r="L32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="L32" s="1" t="n">
+      <c r="M32" s="1" t="n">
         <v>0.1739</v>
       </c>
     </row>
@@ -1769,10 +1868,13 @@
         <v>0.1041</v>
       </c>
       <c r="K33" s="1" t="n">
+        <v>0.1038</v>
+      </c>
+      <c r="L33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="L33" s="1" t="n">
-        <v>0.1041</v>
+      <c r="M33" s="1" t="n">
+        <v>0.1038</v>
       </c>
     </row>
     <row r="34">
@@ -1809,9 +1911,12 @@
         <v>113.04</v>
       </c>
       <c r="K34" s="1" t="n">
+        <v>113.11</v>
+      </c>
+      <c r="L34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="L34" s="1" t="n">
+      <c r="M34" s="1" t="n">
         <v>113.01</v>
       </c>
     </row>
@@ -1849,10 +1954,13 @@
         <v>6.711</v>
       </c>
       <c r="K35" s="1" t="n">
+        <v>6.659</v>
+      </c>
+      <c r="L35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="L35" s="1" t="n">
-        <v>6.711</v>
+      <c r="M35" s="1" t="n">
+        <v>6.659</v>
       </c>
     </row>
     <row r="36">
@@ -1889,9 +1997,12 @@
         <v>0.01709</v>
       </c>
       <c r="K36" s="1" t="n">
+        <v>0.016993</v>
+      </c>
+      <c r="L36" s="1" t="n">
         <v>0.017421</v>
       </c>
-      <c r="L36" s="1" t="n">
+      <c r="M36" s="1" t="n">
         <v>0.016815</v>
       </c>
     </row>
@@ -1929,9 +2040,12 @@
         <v>0.3612</v>
       </c>
       <c r="K37" s="1" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="L37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="L37" s="1" t="n">
+      <c r="M37" s="1" t="n">
         <v>0.361</v>
       </c>
     </row>
@@ -1969,9 +2083,12 @@
         <v>55.3</v>
       </c>
       <c r="K38" s="1" t="n">
+        <v>55.49</v>
+      </c>
+      <c r="L38" s="1" t="n">
         <v>55.79</v>
       </c>
-      <c r="L38" s="1" t="n">
+      <c r="M38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -2009,9 +2126,12 @@
         <v>0.59781</v>
       </c>
       <c r="K39" s="1" t="n">
-        <v>0.59932</v>
+        <v>0.60089</v>
       </c>
       <c r="L39" s="1" t="n">
+        <v>0.60089</v>
+      </c>
+      <c r="M39" s="1" t="n">
         <v>0.58131</v>
       </c>
     </row>
@@ -2049,9 +2169,12 @@
         <v>4.036</v>
       </c>
       <c r="K40" s="1" t="n">
+        <v>4.041</v>
+      </c>
+      <c r="L40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="L40" s="1" t="n">
+      <c r="M40" s="1" t="n">
         <v>4.036</v>
       </c>
     </row>
@@ -2089,9 +2212,12 @@
         <v>0.05054</v>
       </c>
       <c r="K41" s="1" t="n">
-        <v>0.05054</v>
+        <v>0.0512</v>
       </c>
       <c r="L41" s="1" t="n">
+        <v>0.0512</v>
+      </c>
+      <c r="M41" s="1" t="n">
         <v>0.04927</v>
       </c>
     </row>
@@ -2129,9 +2255,12 @@
         <v>0.7015</v>
       </c>
       <c r="K42" s="1" t="n">
+        <v>0.7032</v>
+      </c>
+      <c r="L42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="L42" s="1" t="n">
+      <c r="M42" s="1" t="n">
         <v>0.7006</v>
       </c>
     </row>
@@ -2169,10 +2298,13 @@
         <v>0.23207</v>
       </c>
       <c r="K43" s="1" t="n">
+        <v>0.22894</v>
+      </c>
+      <c r="L43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="L43" s="1" t="n">
-        <v>0.23207</v>
+      <c r="M43" s="1" t="n">
+        <v>0.22894</v>
       </c>
     </row>
     <row r="44">
@@ -2209,9 +2341,12 @@
         <v>0.35528</v>
       </c>
       <c r="K44" s="1" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="L44" s="1" t="n">
         <v>0.35528</v>
       </c>
-      <c r="L44" s="1" t="n">
+      <c r="M44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -2249,9 +2384,12 @@
         <v>0.1703</v>
       </c>
       <c r="K45" s="1" t="n">
+        <v>0.1706</v>
+      </c>
+      <c r="L45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="L45" s="1" t="n">
+      <c r="M45" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -2289,10 +2427,13 @@
         <v>0.0261</v>
       </c>
       <c r="K46" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="L46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="L46" s="1" t="n">
-        <v>0.0261</v>
+      <c r="M46" s="1" t="n">
+        <v>0.026</v>
       </c>
     </row>
     <row r="47">
@@ -2329,9 +2470,12 @@
         <v>0.005961</v>
       </c>
       <c r="K47" s="1" t="n">
+        <v>0.005975</v>
+      </c>
+      <c r="L47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="L47" s="1" t="n">
+      <c r="M47" s="1" t="n">
         <v>0.005961</v>
       </c>
     </row>
@@ -2369,9 +2513,12 @@
         <v>0.00737</v>
       </c>
       <c r="K48" s="1" t="n">
+        <v>0.007387</v>
+      </c>
+      <c r="L48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="L48" s="1" t="n">
+      <c r="M48" s="1" t="n">
         <v>0.007349</v>
       </c>
     </row>
@@ -2409,9 +2556,12 @@
         <v>0.1077</v>
       </c>
       <c r="K49" s="1" t="n">
+        <v>0.1082</v>
+      </c>
+      <c r="L49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="L49" s="1" t="n">
+      <c r="M49" s="1" t="n">
         <v>0.1077</v>
       </c>
     </row>
@@ -2449,9 +2599,12 @@
         <v>0.04075</v>
       </c>
       <c r="K50" s="1" t="n">
-        <v>0.04075</v>
+        <v>0.04119</v>
       </c>
       <c r="L50" s="1" t="n">
+        <v>0.04119</v>
+      </c>
+      <c r="M50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -2489,9 +2642,12 @@
         <v>0.1625</v>
       </c>
       <c r="K51" s="1" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="L51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="L51" s="1" t="n">
+      <c r="M51" s="1" t="n">
         <v>0.1617</v>
       </c>
     </row>
@@ -2529,9 +2685,12 @@
         <v>0.0035</v>
       </c>
       <c r="K52" s="1" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="L52" s="1" t="n">
         <v>0.00357</v>
       </c>
-      <c r="L52" s="1" t="n">
+      <c r="M52" s="1" t="n">
         <v>0.0035</v>
       </c>
     </row>
@@ -2569,9 +2728,12 @@
         <v>2.622</v>
       </c>
       <c r="K53" s="1" t="n">
+        <v>2.634</v>
+      </c>
+      <c r="L53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="L53" s="1" t="n">
+      <c r="M53" s="1" t="n">
         <v>2.622</v>
       </c>
     </row>
@@ -2609,9 +2771,12 @@
         <v>0.006188</v>
       </c>
       <c r="K54" s="1" t="n">
+        <v>0.006202</v>
+      </c>
+      <c r="L54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="L54" s="1" t="n">
+      <c r="M54" s="1" t="n">
         <v>0.006188</v>
       </c>
     </row>
@@ -2649,9 +2814,12 @@
         <v>0.03013</v>
       </c>
       <c r="K55" s="1" t="n">
+        <v>0.02958</v>
+      </c>
+      <c r="L55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="L55" s="1" t="n">
+      <c r="M55" s="1" t="n">
         <v>0.02879</v>
       </c>
     </row>
@@ -2689,9 +2857,12 @@
         <v>0.736</v>
       </c>
       <c r="K56" s="1" t="n">
+        <v>0.7377</v>
+      </c>
+      <c r="L56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="L56" s="1" t="n">
+      <c r="M56" s="1" t="n">
         <v>0.7352</v>
       </c>
     </row>
@@ -2729,9 +2900,12 @@
         <v>0.1034</v>
       </c>
       <c r="K57" s="1" t="n">
+        <v>0.1037</v>
+      </c>
+      <c r="L57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="L57" s="1" t="n">
+      <c r="M57" s="1" t="n">
         <v>0.1034</v>
       </c>
     </row>
@@ -2769,9 +2943,12 @@
         <v>0.9355</v>
       </c>
       <c r="K58" s="1" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="L58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="L58" s="1" t="n">
+      <c r="M58" s="1" t="n">
         <v>0.9355</v>
       </c>
     </row>
@@ -2809,9 +2986,12 @@
         <v>0.08598</v>
       </c>
       <c r="K59" s="1" t="n">
-        <v>0.08704000000000001</v>
+        <v>0.08826000000000001</v>
       </c>
       <c r="L59" s="1" t="n">
+        <v>0.08826000000000001</v>
+      </c>
+      <c r="M59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -2849,9 +3029,12 @@
         <v>0.07003</v>
       </c>
       <c r="K60" s="1" t="n">
-        <v>0.07003</v>
+        <v>0.0703</v>
       </c>
       <c r="L60" s="1" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="M60" s="1" t="n">
         <v>0.06924</v>
       </c>
     </row>
@@ -2889,9 +3072,12 @@
         <v>0.05462</v>
       </c>
       <c r="K61" s="1" t="n">
+        <v>0.05467</v>
+      </c>
+      <c r="L61" s="1" t="n">
         <v>0.05523</v>
       </c>
-      <c r="L61" s="1" t="n">
+      <c r="M61" s="1" t="n">
         <v>0.05445</v>
       </c>
     </row>
@@ -2929,9 +3115,12 @@
         <v>0.009816</v>
       </c>
       <c r="K62" s="1" t="n">
+        <v>0.009982</v>
+      </c>
+      <c r="L62" s="1" t="n">
         <v>0.010194</v>
       </c>
-      <c r="L62" s="1" t="n">
+      <c r="M62" s="1" t="n">
         <v>0.009387</v>
       </c>
     </row>
@@ -2969,9 +3158,12 @@
         <v>0.29049</v>
       </c>
       <c r="K63" s="1" t="n">
-        <v>0.29049</v>
+        <v>0.29088</v>
       </c>
       <c r="L63" s="1" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="M63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -3009,9 +3201,12 @@
         <v>0.07511</v>
       </c>
       <c r="K64" s="1" t="n">
-        <v>0.07511</v>
+        <v>0.07581</v>
       </c>
       <c r="L64" s="1" t="n">
+        <v>0.07581</v>
+      </c>
+      <c r="M64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -3049,9 +3244,12 @@
         <v>0.314</v>
       </c>
       <c r="K65" s="1" t="n">
-        <v>0.3155</v>
+        <v>0.3169</v>
       </c>
       <c r="L65" s="1" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="M65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -3089,9 +3287,12 @@
         <v>0.16235</v>
       </c>
       <c r="K66" s="1" t="n">
+        <v>0.16309</v>
+      </c>
+      <c r="L66" s="1" t="n">
         <v>0.16461</v>
       </c>
-      <c r="L66" s="1" t="n">
+      <c r="M66" s="1" t="n">
         <v>0.16235</v>
       </c>
     </row>
@@ -3129,9 +3330,12 @@
         <v>0.11951</v>
       </c>
       <c r="K67" s="1" t="n">
+        <v>0.11981</v>
+      </c>
+      <c r="L67" s="1" t="n">
         <v>0.11999</v>
       </c>
-      <c r="L67" s="1" t="n">
+      <c r="M67" s="1" t="n">
         <v>0.11919</v>
       </c>
     </row>
@@ -3169,9 +3373,12 @@
         <v>0.09556000000000001</v>
       </c>
       <c r="K68" s="1" t="n">
+        <v>0.09566</v>
+      </c>
+      <c r="L68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="L68" s="1" t="n">
+      <c r="M68" s="1" t="n">
         <v>0.09548</v>
       </c>
     </row>
@@ -3209,9 +3416,12 @@
         <v>0.124</v>
       </c>
       <c r="K69" s="1" t="n">
+        <v>0.1242</v>
+      </c>
+      <c r="L69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="L69" s="1" t="n">
+      <c r="M69" s="1" t="n">
         <v>0.1239</v>
       </c>
     </row>
@@ -3249,9 +3459,12 @@
         <v>8.494</v>
       </c>
       <c r="K70" s="1" t="n">
+        <v>8.528</v>
+      </c>
+      <c r="L70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="L70" s="1" t="n">
+      <c r="M70" s="1" t="n">
         <v>8.494</v>
       </c>
     </row>
@@ -3289,9 +3502,12 @@
         <v>0.239</v>
       </c>
       <c r="K71" s="1" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="L71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="L71" s="1" t="n">
+      <c r="M71" s="1" t="n">
         <v>0.238</v>
       </c>
     </row>
@@ -3329,10 +3545,13 @@
         <v>0.05012</v>
       </c>
       <c r="K72" s="1" t="n">
+        <v>0.05001</v>
+      </c>
+      <c r="L72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="L72" s="1" t="n">
-        <v>0.05012</v>
+      <c r="M72" s="1" t="n">
+        <v>0.05001</v>
       </c>
     </row>
     <row r="73">
@@ -3369,9 +3588,12 @@
         <v>0.05036</v>
       </c>
       <c r="K73" s="1" t="n">
+        <v>0.0507</v>
+      </c>
+      <c r="L73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="L73" s="1" t="n">
+      <c r="M73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -3409,9 +3631,12 @@
         <v>0.1257</v>
       </c>
       <c r="K74" s="1" t="n">
+        <v>0.1254</v>
+      </c>
+      <c r="L74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="L74" s="1" t="n">
+      <c r="M74" s="1" t="n">
         <v>0.1252</v>
       </c>
     </row>
@@ -3449,9 +3674,12 @@
         <v>0.0463</v>
       </c>
       <c r="K75" s="1" t="n">
+        <v>0.04627</v>
+      </c>
+      <c r="L75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="L75" s="1" t="n">
+      <c r="M75" s="1" t="n">
         <v>0.04621</v>
       </c>
     </row>
@@ -3489,9 +3717,12 @@
         <v>0.06691</v>
       </c>
       <c r="K76" s="1" t="n">
+        <v>0.06734</v>
+      </c>
+      <c r="L76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="L76" s="1" t="n">
+      <c r="M76" s="1" t="n">
         <v>0.06691</v>
       </c>
     </row>
@@ -3529,9 +3760,12 @@
         <v>0.12709</v>
       </c>
       <c r="K77" s="1" t="n">
+        <v>0.12738</v>
+      </c>
+      <c r="L77" s="1" t="n">
         <v>0.12881</v>
       </c>
-      <c r="L77" s="1" t="n">
+      <c r="M77" s="1" t="n">
         <v>0.12654</v>
       </c>
     </row>
@@ -3569,9 +3803,12 @@
         <v>0.1622</v>
       </c>
       <c r="K78" s="1" t="n">
+        <v>0.1623</v>
+      </c>
+      <c r="L78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="L78" s="1" t="n">
+      <c r="M78" s="1" t="n">
         <v>0.1613</v>
       </c>
     </row>
@@ -3609,9 +3846,12 @@
         <v>0.0271</v>
       </c>
       <c r="K79" s="1" t="n">
+        <v>0.02716</v>
+      </c>
+      <c r="L79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="L79" s="1" t="n">
+      <c r="M79" s="1" t="n">
         <v>0.0271</v>
       </c>
     </row>
@@ -3649,9 +3889,12 @@
         <v>356.5</v>
       </c>
       <c r="K80" s="1" t="n">
-        <v>357.15</v>
+        <v>357.41</v>
       </c>
       <c r="L80" s="1" t="n">
+        <v>357.41</v>
+      </c>
+      <c r="M80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -3689,9 +3932,12 @@
         <v>7.098e-05</v>
       </c>
       <c r="K81" s="1" t="n">
+        <v>7.118000000000001e-05</v>
+      </c>
+      <c r="L81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="L81" s="1" t="n">
+      <c r="M81" s="1" t="n">
         <v>7.080999999999999e-05</v>
       </c>
     </row>
@@ -3729,9 +3975,12 @@
         <v>0.2645</v>
       </c>
       <c r="K82" s="1" t="n">
+        <v>0.2653</v>
+      </c>
+      <c r="L82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="L82" s="1" t="n">
+      <c r="M82" s="1" t="n">
         <v>0.2645</v>
       </c>
     </row>
@@ -3769,9 +4018,12 @@
         <v>1.1391</v>
       </c>
       <c r="K83" s="1" t="n">
+        <v>1.1392</v>
+      </c>
+      <c r="L83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="L83" s="1" t="n">
+      <c r="M83" s="1" t="n">
         <v>1.1379</v>
       </c>
     </row>
@@ -3809,9 +4061,12 @@
         <v>0.3541</v>
       </c>
       <c r="K84" s="1" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="L84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="L84" s="1" t="n">
+      <c r="M84" s="1" t="n">
         <v>0.3541</v>
       </c>
     </row>
@@ -3849,9 +4104,12 @@
         <v>2.0188</v>
       </c>
       <c r="K85" s="1" t="n">
+        <v>2.0106</v>
+      </c>
+      <c r="L85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="L85" s="1" t="n">
+      <c r="M85" s="1" t="n">
         <v>2.0067</v>
       </c>
     </row>
@@ -3889,9 +4147,12 @@
         <v>1.3152</v>
       </c>
       <c r="K86" s="1" t="n">
-        <v>1.3167</v>
+        <v>1.317</v>
       </c>
       <c r="L86" s="1" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="M86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -3929,9 +4190,12 @@
         <v>32.73</v>
       </c>
       <c r="K87" s="1" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="L87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="L87" s="1" t="n">
+      <c r="M87" s="1" t="n">
         <v>32.73</v>
       </c>
     </row>
@@ -3969,10 +4233,13 @@
         <v>0.009719999999999999</v>
       </c>
       <c r="K88" s="1" t="n">
+        <v>0.00954</v>
+      </c>
+      <c r="L88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="L88" s="1" t="n">
-        <v>0.009690000000000001</v>
+      <c r="M88" s="1" t="n">
+        <v>0.00954</v>
       </c>
     </row>
     <row r="89">
@@ -4009,9 +4276,12 @@
         <v>0.01833</v>
       </c>
       <c r="K89" s="1" t="n">
+        <v>0.01833</v>
+      </c>
+      <c r="L89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="L89" s="1" t="n">
+      <c r="M89" s="1" t="n">
         <v>0.01828</v>
       </c>
     </row>
@@ -4049,10 +4319,13 @@
         <v>0.03548</v>
       </c>
       <c r="K90" s="1" t="n">
+        <v>0.03539</v>
+      </c>
+      <c r="L90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="L90" s="1" t="n">
-        <v>0.03548</v>
+      <c r="M90" s="1" t="n">
+        <v>0.03539</v>
       </c>
     </row>
     <row r="91">
@@ -4089,9 +4362,12 @@
         <v>0.01186</v>
       </c>
       <c r="K91" s="1" t="n">
-        <v>0.01202</v>
+        <v>0.01203</v>
       </c>
       <c r="L91" s="1" t="n">
+        <v>0.01203</v>
+      </c>
+      <c r="M91" s="1" t="n">
         <v>0.0118</v>
       </c>
     </row>
@@ -4129,9 +4405,12 @@
         <v>3.095</v>
       </c>
       <c r="K92" s="1" t="n">
+        <v>3.103</v>
+      </c>
+      <c r="L92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="L92" s="1" t="n">
+      <c r="M92" s="1" t="n">
         <v>3.095</v>
       </c>
     </row>
@@ -4169,9 +4448,12 @@
         <v>0.005605</v>
       </c>
       <c r="K93" s="1" t="n">
+        <v>0.005625</v>
+      </c>
+      <c r="L93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="L93" s="1" t="n">
+      <c r="M93" s="1" t="n">
         <v>0.005596</v>
       </c>
     </row>
@@ -4209,9 +4491,12 @@
         <v>0.0925</v>
       </c>
       <c r="K94" s="1" t="n">
+        <v>0.0929</v>
+      </c>
+      <c r="L94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="L94" s="1" t="n">
+      <c r="M94" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -4249,9 +4534,12 @@
         <v>0.6063</v>
       </c>
       <c r="K95" s="1" t="n">
-        <v>0.6063</v>
+        <v>0.6098</v>
       </c>
       <c r="L95" s="1" t="n">
+        <v>0.6098</v>
+      </c>
+      <c r="M95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -4289,9 +4577,12 @@
         <v>1.27e-05</v>
       </c>
       <c r="K96" s="1" t="n">
+        <v>1.28e-05</v>
+      </c>
+      <c r="L96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="L96" s="1" t="n">
+      <c r="M96" s="1" t="n">
         <v>1.27e-05</v>
       </c>
     </row>
@@ -4329,9 +4620,12 @@
         <v>1.125</v>
       </c>
       <c r="K97" s="1" t="n">
+        <v>1.126</v>
+      </c>
+      <c r="L97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="L97" s="1" t="n">
+      <c r="M97" s="1" t="n">
         <v>1.125</v>
       </c>
     </row>
@@ -4369,9 +4663,12 @@
         <v>0.25663</v>
       </c>
       <c r="K98" s="1" t="n">
+        <v>0.25499</v>
+      </c>
+      <c r="L98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="L98" s="1" t="n">
+      <c r="M98" s="1" t="n">
         <v>0.2523</v>
       </c>
     </row>
@@ -4409,9 +4706,12 @@
         <v>1.144</v>
       </c>
       <c r="K99" s="1" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="L99" s="1" t="n">
         <v>1.156</v>
       </c>
-      <c r="L99" s="1" t="n">
+      <c r="M99" s="1" t="n">
         <v>1.144</v>
       </c>
     </row>
@@ -4449,9 +4749,12 @@
         <v>1.853</v>
       </c>
       <c r="K100" s="1" t="n">
+        <v>1.859</v>
+      </c>
+      <c r="L100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="L100" s="1" t="n">
+      <c r="M100" s="1" t="n">
         <v>1.852</v>
       </c>
     </row>
@@ -4489,9 +4792,12 @@
         <v>0.01579</v>
       </c>
       <c r="K101" s="1" t="n">
+        <v>0.01584</v>
+      </c>
+      <c r="L101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="L101" s="1" t="n">
+      <c r="M101" s="1" t="n">
         <v>0.01579</v>
       </c>
     </row>
@@ -4529,10 +4835,13 @@
         <v>0.10374</v>
       </c>
       <c r="K102" s="1" t="n">
+        <v>0.10316</v>
+      </c>
+      <c r="L102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="L102" s="1" t="n">
-        <v>0.10353</v>
+      <c r="M102" s="1" t="n">
+        <v>0.10316</v>
       </c>
     </row>
     <row r="103">
@@ -4569,9 +4878,12 @@
         <v>0.0005967</v>
       </c>
       <c r="K103" s="1" t="n">
+        <v>0.0005981</v>
+      </c>
+      <c r="L103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="L103" s="1" t="n">
+      <c r="M103" s="1" t="n">
         <v>0.0005967</v>
       </c>
     </row>
@@ -4609,9 +4921,12 @@
         <v>0.0005724</v>
       </c>
       <c r="K104" s="1" t="n">
+        <v>0.0005726</v>
+      </c>
+      <c r="L104" s="1" t="n">
         <v>0.0005776000000000001</v>
       </c>
-      <c r="L104" s="1" t="n">
+      <c r="M104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -4649,9 +4964,12 @@
         <v>0.003259</v>
       </c>
       <c r="K105" s="1" t="n">
-        <v>0.003259</v>
+        <v>0.003264</v>
       </c>
       <c r="L105" s="1" t="n">
+        <v>0.003264</v>
+      </c>
+      <c r="M105" s="1" t="n">
         <v>0.003229</v>
       </c>
     </row>
@@ -4689,9 +5007,12 @@
         <v>2.588</v>
       </c>
       <c r="K106" s="1" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="L106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="L106" s="1" t="n">
+      <c r="M106" s="1" t="n">
         <v>2.587</v>
       </c>
     </row>
@@ -4729,9 +5050,12 @@
         <v>0.165</v>
       </c>
       <c r="K107" s="1" t="n">
+        <v>0.1655</v>
+      </c>
+      <c r="L107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="L107" s="1" t="n">
+      <c r="M107" s="1" t="n">
         <v>0.165</v>
       </c>
     </row>
@@ -4769,9 +5093,12 @@
         <v>0.09607</v>
       </c>
       <c r="K108" s="1" t="n">
+        <v>0.09616</v>
+      </c>
+      <c r="L108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="L108" s="1" t="n">
+      <c r="M108" s="1" t="n">
         <v>0.0955</v>
       </c>
     </row>
@@ -4809,9 +5136,12 @@
         <v>0.0222</v>
       </c>
       <c r="K109" s="1" t="n">
+        <v>0.02222</v>
+      </c>
+      <c r="L109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="L109" s="1" t="n">
+      <c r="M109" s="1" t="n">
         <v>0.02204</v>
       </c>
     </row>
@@ -4849,9 +5179,12 @@
         <v>0.2912</v>
       </c>
       <c r="K110" s="1" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="L110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="L110" s="1" t="n">
+      <c r="M110" s="1" t="n">
         <v>0.2912</v>
       </c>
     </row>
@@ -4889,9 +5222,12 @@
         <v>0.05672</v>
       </c>
       <c r="K111" s="1" t="n">
+        <v>0.05672</v>
+      </c>
+      <c r="L111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="L111" s="1" t="n">
+      <c r="M111" s="1" t="n">
         <v>0.05665</v>
       </c>
     </row>
@@ -4929,9 +5265,12 @@
         <v>0.3008</v>
       </c>
       <c r="K112" s="1" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="L112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="L112" s="1" t="n">
+      <c r="M112" s="1" t="n">
         <v>0.3002</v>
       </c>
     </row>
@@ -4969,9 +5308,12 @@
         <v>18.68</v>
       </c>
       <c r="K113" s="1" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="L113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="L113" s="1" t="n">
+      <c r="M113" s="1" t="n">
         <v>18.6</v>
       </c>
     </row>
@@ -5009,10 +5351,13 @@
         <v>0.12871</v>
       </c>
       <c r="K114" s="1" t="n">
+        <v>0.12837</v>
+      </c>
+      <c r="L114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="L114" s="1" t="n">
-        <v>0.12871</v>
+      <c r="M114" s="1" t="n">
+        <v>0.12837</v>
       </c>
     </row>
     <row r="115">
@@ -5049,9 +5394,12 @@
         <v>0.01553</v>
       </c>
       <c r="K115" s="1" t="n">
+        <v>0.01562</v>
+      </c>
+      <c r="L115" s="1" t="n">
         <v>0.01583</v>
       </c>
-      <c r="L115" s="1" t="n">
+      <c r="M115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -5089,9 +5437,12 @@
         <v>0.08470999999999999</v>
       </c>
       <c r="K116" s="1" t="n">
+        <v>0.08479</v>
+      </c>
+      <c r="L116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="L116" s="1" t="n">
+      <c r="M116" s="1" t="n">
         <v>0.08470999999999999</v>
       </c>
     </row>
@@ -5129,10 +5480,13 @@
         <v>0.04817</v>
       </c>
       <c r="K117" s="1" t="n">
+        <v>0.047554</v>
+      </c>
+      <c r="L117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="L117" s="1" t="n">
-        <v>0.047711</v>
+      <c r="M117" s="1" t="n">
+        <v>0.047554</v>
       </c>
     </row>
     <row r="118">
@@ -5169,9 +5523,12 @@
         <v>0.04733</v>
       </c>
       <c r="K118" s="1" t="n">
+        <v>0.04743</v>
+      </c>
+      <c r="L118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="L118" s="1" t="n">
+      <c r="M118" s="1" t="n">
         <v>0.04733</v>
       </c>
     </row>
@@ -5209,10 +5566,13 @@
         <v>0.04146</v>
       </c>
       <c r="K119" s="1" t="n">
+        <v>0.0405</v>
+      </c>
+      <c r="L119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="L119" s="1" t="n">
-        <v>0.04109</v>
+      <c r="M119" s="1" t="n">
+        <v>0.0405</v>
       </c>
     </row>
     <row r="120">
@@ -5249,9 +5609,12 @@
         <v>0.14463</v>
       </c>
       <c r="K120" s="1" t="n">
+        <v>0.14501</v>
+      </c>
+      <c r="L120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="L120" s="1" t="n">
+      <c r="M120" s="1" t="n">
         <v>0.14463</v>
       </c>
     </row>
@@ -5289,9 +5652,12 @@
         <v>0.1274</v>
       </c>
       <c r="K121" s="1" t="n">
+        <v>0.1279</v>
+      </c>
+      <c r="L121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="L121" s="1" t="n">
+      <c r="M121" s="1" t="n">
         <v>0.1272</v>
       </c>
     </row>
@@ -5329,9 +5695,12 @@
         <v>1.867</v>
       </c>
       <c r="K122" s="1" t="n">
+        <v>1.874</v>
+      </c>
+      <c r="L122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="L122" s="1" t="n">
+      <c r="M122" s="1" t="n">
         <v>1.867</v>
       </c>
     </row>
@@ -5369,9 +5738,12 @@
         <v>0.0301</v>
       </c>
       <c r="K123" s="1" t="n">
+        <v>0.03018</v>
+      </c>
+      <c r="L123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="L123" s="1" t="n">
+      <c r="M123" s="1" t="n">
         <v>0.0301</v>
       </c>
     </row>
@@ -5409,10 +5781,13 @@
         <v>0.13228</v>
       </c>
       <c r="K124" s="1" t="n">
+        <v>0.13159</v>
+      </c>
+      <c r="L124" s="1" t="n">
         <v>0.13401</v>
       </c>
-      <c r="L124" s="1" t="n">
-        <v>0.13211</v>
+      <c r="M124" s="1" t="n">
+        <v>0.13159</v>
       </c>
     </row>
     <row r="125">
@@ -5449,9 +5824,12 @@
         <v>0.04107</v>
       </c>
       <c r="K125" s="1" t="n">
+        <v>0.04108</v>
+      </c>
+      <c r="L125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="L125" s="1" t="n">
+      <c r="M125" s="1" t="n">
         <v>0.04095</v>
       </c>
     </row>
@@ -5489,9 +5867,12 @@
         <v>0.1148</v>
       </c>
       <c r="K126" s="1" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="L126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="L126" s="1" t="n">
+      <c r="M126" s="1" t="n">
         <v>0.1148</v>
       </c>
     </row>
@@ -5529,9 +5910,12 @@
         <v>0.5034999999999999</v>
       </c>
       <c r="K127" s="1" t="n">
-        <v>0.5046</v>
+        <v>0.5077</v>
       </c>
       <c r="L127" s="1" t="n">
+        <v>0.5077</v>
+      </c>
+      <c r="M127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -5569,9 +5953,12 @@
         <v>0.0379</v>
       </c>
       <c r="K128" s="1" t="n">
+        <v>0.03808</v>
+      </c>
+      <c r="L128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="L128" s="1" t="n">
+      <c r="M128" s="1" t="n">
         <v>0.03787</v>
       </c>
     </row>
@@ -5609,9 +5996,12 @@
         <v>0.792</v>
       </c>
       <c r="K129" s="1" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="L129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="L129" s="1" t="n">
+      <c r="M129" s="1" t="n">
         <v>0.792</v>
       </c>
     </row>
@@ -5649,9 +6039,12 @@
         <v>0.03428</v>
       </c>
       <c r="K130" s="1" t="n">
+        <v>0.03435</v>
+      </c>
+      <c r="L130" s="1" t="n">
         <v>0.03458</v>
       </c>
-      <c r="L130" s="1" t="n">
+      <c r="M130" s="1" t="n">
         <v>0.03422</v>
       </c>
     </row>
@@ -5689,9 +6082,12 @@
         <v>0.4191</v>
       </c>
       <c r="K131" s="1" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="L131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="L131" s="1" t="n">
+      <c r="M131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -5729,9 +6125,12 @@
         <v>0.04378</v>
       </c>
       <c r="K132" s="1" t="n">
+        <v>0.04406</v>
+      </c>
+      <c r="L132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="L132" s="1" t="n">
+      <c r="M132" s="1" t="n">
         <v>0.04354</v>
       </c>
     </row>
@@ -5769,9 +6168,12 @@
         <v>1.2851</v>
       </c>
       <c r="K133" s="1" t="n">
+        <v>1.2891</v>
+      </c>
+      <c r="L133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="L133" s="1" t="n">
+      <c r="M133" s="1" t="n">
         <v>1.282</v>
       </c>
     </row>
@@ -5809,9 +6211,12 @@
         <v>0.02191</v>
       </c>
       <c r="K134" s="1" t="n">
+        <v>0.02198</v>
+      </c>
+      <c r="L134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="L134" s="1" t="n">
+      <c r="M134" s="1" t="n">
         <v>0.02184</v>
       </c>
     </row>
@@ -5849,9 +6254,12 @@
         <v>0.0004597</v>
       </c>
       <c r="K135" s="1" t="n">
+        <v>0.0004604</v>
+      </c>
+      <c r="L135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="L135" s="1" t="n">
+      <c r="M135" s="1" t="n">
         <v>0.0004592</v>
       </c>
     </row>
@@ -5889,10 +6297,13 @@
         <v>0.001896</v>
       </c>
       <c r="K136" s="1" t="n">
+        <v>0.001881</v>
+      </c>
+      <c r="L136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="L136" s="1" t="n">
-        <v>0.001896</v>
+      <c r="M136" s="1" t="n">
+        <v>0.001881</v>
       </c>
     </row>
     <row r="137">
@@ -5929,9 +6340,12 @@
         <v>0.317</v>
       </c>
       <c r="K137" s="1" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="L137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="L137" s="1" t="n">
+      <c r="M137" s="1" t="n">
         <v>0.317</v>
       </c>
     </row>
@@ -5969,9 +6383,12 @@
         <v>0.5698</v>
       </c>
       <c r="K138" s="1" t="n">
+        <v>0.5713</v>
+      </c>
+      <c r="L138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="L138" s="1" t="n">
+      <c r="M138" s="1" t="n">
         <v>0.5698</v>
       </c>
     </row>
@@ -6009,9 +6426,12 @@
         <v>0.02125</v>
       </c>
       <c r="K139" s="1" t="n">
+        <v>0.02129</v>
+      </c>
+      <c r="L139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="L139" s="1" t="n">
+      <c r="M139" s="1" t="n">
         <v>0.02125</v>
       </c>
     </row>
@@ -6049,9 +6469,12 @@
         <v>0.08036</v>
       </c>
       <c r="K140" s="1" t="n">
+        <v>0.08044999999999999</v>
+      </c>
+      <c r="L140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="L140" s="1" t="n">
+      <c r="M140" s="1" t="n">
         <v>0.08036</v>
       </c>
     </row>
@@ -6089,9 +6512,12 @@
         <v>0.001668</v>
       </c>
       <c r="K141" s="1" t="n">
+        <v>0.001663</v>
+      </c>
+      <c r="L141" s="1" t="n">
         <v>0.001672</v>
       </c>
-      <c r="L141" s="1" t="n">
+      <c r="M141" s="1" t="n">
         <v>0.001616</v>
       </c>
     </row>
@@ -6129,9 +6555,12 @@
         <v>0.4387</v>
       </c>
       <c r="K142" s="1" t="n">
+        <v>0.4378</v>
+      </c>
+      <c r="L142" s="1" t="n">
         <v>0.4387</v>
       </c>
-      <c r="L142" s="1" t="n">
+      <c r="M142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -6169,9 +6598,12 @@
         <v>0.030392</v>
       </c>
       <c r="K143" s="1" t="n">
+        <v>0.030645</v>
+      </c>
+      <c r="L143" s="1" t="n">
         <v>0.030681</v>
       </c>
-      <c r="L143" s="1" t="n">
+      <c r="M143" s="1" t="n">
         <v>0.030021</v>
       </c>
     </row>
@@ -6209,9 +6641,12 @@
         <v>0.000225</v>
       </c>
       <c r="K144" s="1" t="n">
+        <v>0.000225</v>
+      </c>
+      <c r="L144" s="1" t="n">
         <v>0.000226</v>
       </c>
-      <c r="L144" s="1" t="n">
+      <c r="M144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -6249,9 +6684,12 @@
         <v>0.03586</v>
       </c>
       <c r="K145" s="1" t="n">
+        <v>0.03542</v>
+      </c>
+      <c r="L145" s="1" t="n">
         <v>0.03696</v>
       </c>
-      <c r="L145" s="1" t="n">
+      <c r="M145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -6289,9 +6727,12 @@
         <v>0.11578</v>
       </c>
       <c r="K146" s="1" t="n">
+        <v>0.11536</v>
+      </c>
+      <c r="L146" s="1" t="n">
         <v>0.116</v>
       </c>
-      <c r="L146" s="1" t="n">
+      <c r="M146" s="1" t="n">
         <v>0.11518</v>
       </c>
     </row>
@@ -6329,9 +6770,12 @@
         <v>0.02183</v>
       </c>
       <c r="K147" s="1" t="n">
+        <v>0.02182</v>
+      </c>
+      <c r="L147" s="1" t="n">
         <v>0.02198</v>
       </c>
-      <c r="L147" s="1" t="n">
+      <c r="M147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -6369,9 +6813,12 @@
         <v>1.4084</v>
       </c>
       <c r="K148" s="1" t="n">
+        <v>1.412</v>
+      </c>
+      <c r="L148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="L148" s="1" t="n">
+      <c r="M148" s="1" t="n">
         <v>1.4084</v>
       </c>
     </row>
@@ -6409,9 +6856,12 @@
         <v>1.8622</v>
       </c>
       <c r="K149" s="1" t="n">
+        <v>1.8684</v>
+      </c>
+      <c r="L149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="L149" s="1" t="n">
+      <c r="M149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -6449,9 +6899,12 @@
         <v>0.097</v>
       </c>
       <c r="K150" s="1" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="L150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="L150" s="1" t="n">
+      <c r="M150" s="1" t="n">
         <v>0.097</v>
       </c>
     </row>
@@ -6489,9 +6942,12 @@
         <v>4.64</v>
       </c>
       <c r="K151" s="1" t="n">
+        <v>4.598</v>
+      </c>
+      <c r="L151" s="1" t="n">
         <v>4.64</v>
       </c>
-      <c r="L151" s="1" t="n">
+      <c r="M151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -6529,9 +6985,12 @@
         <v>5.522</v>
       </c>
       <c r="K152" s="1" t="n">
+        <v>5.539</v>
+      </c>
+      <c r="L152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="L152" s="1" t="n">
+      <c r="M152" s="1" t="n">
         <v>5.522</v>
       </c>
     </row>
@@ -6569,9 +7028,12 @@
         <v>0.3206</v>
       </c>
       <c r="K153" s="1" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="L153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="L153" s="1" t="n">
+      <c r="M153" s="1" t="n">
         <v>0.3175</v>
       </c>
     </row>
@@ -6609,9 +7071,12 @@
         <v>0.5867</v>
       </c>
       <c r="K154" s="1" t="n">
+        <v>0.5878</v>
+      </c>
+      <c r="L154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="L154" s="1" t="n">
+      <c r="M154" s="1" t="n">
         <v>0.5867</v>
       </c>
     </row>
@@ -6649,9 +7114,12 @@
         <v>0.01281</v>
       </c>
       <c r="K155" s="1" t="n">
+        <v>0.01291</v>
+      </c>
+      <c r="L155" s="1" t="n">
         <v>0.01292</v>
       </c>
-      <c r="L155" s="1" t="n">
+      <c r="M155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -6689,9 +7157,12 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="K156" s="1" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="L156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="L156" s="1" t="n">
+      <c r="M156" s="1" t="n">
         <v>0.09859999999999999</v>
       </c>
     </row>
@@ -6729,9 +7200,12 @@
         <v>16.525</v>
       </c>
       <c r="K157" s="1" t="n">
+        <v>16.558</v>
+      </c>
+      <c r="L157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="L157" s="1" t="n">
+      <c r="M157" s="1" t="n">
         <v>16.525</v>
       </c>
     </row>
@@ -6769,9 +7243,12 @@
         <v>0.05564</v>
       </c>
       <c r="K158" s="1" t="n">
+        <v>0.05554</v>
+      </c>
+      <c r="L158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="L158" s="1" t="n">
+      <c r="M158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -6809,9 +7286,12 @@
         <v>28.96</v>
       </c>
       <c r="K159" s="1" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="L159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="L159" s="1" t="n">
+      <c r="M159" s="1" t="n">
         <v>28.87</v>
       </c>
     </row>
@@ -6849,10 +7329,13 @@
         <v>0.02115</v>
       </c>
       <c r="K160" s="1" t="n">
+        <v>0.02112</v>
+      </c>
+      <c r="L160" s="1" t="n">
         <v>0.02141</v>
       </c>
-      <c r="L160" s="1" t="n">
-        <v>0.02115</v>
+      <c r="M160" s="1" t="n">
+        <v>0.02112</v>
       </c>
     </row>
     <row r="161">
@@ -6889,9 +7372,12 @@
         <v>0.0006532</v>
       </c>
       <c r="K161" s="1" t="n">
+        <v>0.0006541</v>
+      </c>
+      <c r="L161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="L161" s="1" t="n">
+      <c r="M161" s="1" t="n">
         <v>0.0006507</v>
       </c>
     </row>
@@ -6929,10 +7415,13 @@
         <v>0.3879</v>
       </c>
       <c r="K162" s="1" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="L162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="L162" s="1" t="n">
-        <v>0.3879</v>
+      <c r="M162" s="1" t="n">
+        <v>0.3871</v>
       </c>
     </row>
     <row r="163">
@@ -6969,9 +7458,12 @@
         <v>0.1925</v>
       </c>
       <c r="K163" s="1" t="n">
+        <v>0.1926</v>
+      </c>
+      <c r="L163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="L163" s="1" t="n">
+      <c r="M163" s="1" t="n">
         <v>0.1925</v>
       </c>
     </row>
@@ -7009,9 +7501,12 @@
         <v>0.315</v>
       </c>
       <c r="K164" s="1" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="L164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="L164" s="1" t="n">
+      <c r="M164" s="1" t="n">
         <v>0.315</v>
       </c>
     </row>
@@ -7049,9 +7544,12 @@
         <v>0.373</v>
       </c>
       <c r="K165" s="1" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="L165" s="1" t="n">
         <v>0.377</v>
       </c>
-      <c r="L165" s="1" t="n">
+      <c r="M165" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -7089,9 +7587,12 @@
         <v>0.02258</v>
       </c>
       <c r="K166" s="1" t="n">
+        <v>0.02259</v>
+      </c>
+      <c r="L166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="L166" s="1" t="n">
+      <c r="M166" s="1" t="n">
         <v>0.02258</v>
       </c>
     </row>
@@ -7129,9 +7630,12 @@
         <v>0.007295</v>
       </c>
       <c r="K167" s="1" t="n">
+        <v>0.007313</v>
+      </c>
+      <c r="L167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="L167" s="1" t="n">
+      <c r="M167" s="1" t="n">
         <v>0.007295</v>
       </c>
     </row>
@@ -7169,9 +7673,12 @@
         <v>0.01355</v>
       </c>
       <c r="K168" s="1" t="n">
+        <v>0.01359</v>
+      </c>
+      <c r="L168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="L168" s="1" t="n">
+      <c r="M168" s="1" t="n">
         <v>0.01355</v>
       </c>
     </row>
@@ -7209,10 +7716,13 @@
         <v>0.25199</v>
       </c>
       <c r="K169" s="1" t="n">
+        <v>0.25151</v>
+      </c>
+      <c r="L169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="L169" s="1" t="n">
-        <v>0.25175</v>
+      <c r="M169" s="1" t="n">
+        <v>0.25151</v>
       </c>
     </row>
     <row r="170">
@@ -7249,9 +7759,12 @@
         <v>0.02179</v>
       </c>
       <c r="K170" s="1" t="n">
+        <v>0.02184</v>
+      </c>
+      <c r="L170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="L170" s="1" t="n">
+      <c r="M170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -7289,10 +7802,13 @@
         <v>0.1724</v>
       </c>
       <c r="K171" s="1" t="n">
+        <v>0.1715</v>
+      </c>
+      <c r="L171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="L171" s="1" t="n">
-        <v>0.1718</v>
+      <c r="M171" s="1" t="n">
+        <v>0.1715</v>
       </c>
     </row>
     <row r="172">
@@ -7329,9 +7845,12 @@
         <v>0.089</v>
       </c>
       <c r="K172" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="L172" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="L172" s="1" t="n">
+      <c r="M172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -7369,9 +7888,12 @@
         <v>0.004691</v>
       </c>
       <c r="K173" s="1" t="n">
+        <v>0.004689</v>
+      </c>
+      <c r="L173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="L173" s="1" t="n">
+      <c r="M173" s="1" t="n">
         <v>0.004682</v>
       </c>
     </row>
@@ -7409,9 +7931,12 @@
         <v>0.4364</v>
       </c>
       <c r="K174" s="1" t="n">
+        <v>0.4373</v>
+      </c>
+      <c r="L174" s="1" t="n">
         <v>0.4423</v>
       </c>
-      <c r="L174" s="1" t="n">
+      <c r="M174" s="1" t="n">
         <v>0.4364</v>
       </c>
     </row>
@@ -7449,9 +7974,12 @@
         <v>0.09017</v>
       </c>
       <c r="K175" s="1" t="n">
-        <v>0.09021999999999999</v>
+        <v>0.09042</v>
       </c>
       <c r="L175" s="1" t="n">
+        <v>0.09042</v>
+      </c>
+      <c r="M175" s="1" t="n">
         <v>0.08935999999999999</v>
       </c>
     </row>
@@ -7489,9 +8017,12 @@
         <v>0.2473</v>
       </c>
       <c r="K176" s="1" t="n">
+        <v>0.2473</v>
+      </c>
+      <c r="L176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="L176" s="1" t="n">
+      <c r="M176" s="1" t="n">
         <v>0.2453</v>
       </c>
     </row>
@@ -7529,9 +8060,12 @@
         <v>0.01913</v>
       </c>
       <c r="K177" s="1" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="L177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="L177" s="1" t="n">
+      <c r="M177" s="1" t="n">
         <v>0.01909</v>
       </c>
     </row>
@@ -7569,9 +8103,12 @@
         <v>6.14</v>
       </c>
       <c r="K178" s="1" t="n">
+        <v>6.151</v>
+      </c>
+      <c r="L178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="L178" s="1" t="n">
+      <c r="M178" s="1" t="n">
         <v>6.138</v>
       </c>
     </row>
@@ -7609,9 +8146,12 @@
         <v>0.1368</v>
       </c>
       <c r="K179" s="1" t="n">
+        <v>0.1377</v>
+      </c>
+      <c r="L179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="L179" s="1" t="n">
+      <c r="M179" s="1" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -7649,9 +8189,12 @@
         <v>0.005113</v>
       </c>
       <c r="K180" s="1" t="n">
+        <v>0.005083</v>
+      </c>
+      <c r="L180" s="1" t="n">
         <v>0.005154</v>
       </c>
-      <c r="L180" s="1" t="n">
+      <c r="M180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -7689,9 +8232,12 @@
         <v>0.01195</v>
       </c>
       <c r="K181" s="1" t="n">
+        <v>0.01202</v>
+      </c>
+      <c r="L181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="L181" s="1" t="n">
+      <c r="M181" s="1" t="n">
         <v>0.01189</v>
       </c>
     </row>
@@ -7729,9 +8275,12 @@
         <v>0.007352</v>
       </c>
       <c r="K182" s="1" t="n">
+        <v>0.007344</v>
+      </c>
+      <c r="L182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="L182" s="1" t="n">
+      <c r="M182" s="1" t="n">
         <v>0.007295</v>
       </c>
     </row>
@@ -7769,9 +8318,12 @@
         <v>0.13194</v>
       </c>
       <c r="K183" s="1" t="n">
+        <v>0.13203</v>
+      </c>
+      <c r="L183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="L183" s="1" t="n">
+      <c r="M183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -7809,9 +8361,12 @@
         <v>0.09676</v>
       </c>
       <c r="K184" s="1" t="n">
+        <v>0.09712</v>
+      </c>
+      <c r="L184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="L184" s="1" t="n">
+      <c r="M184" s="1" t="n">
         <v>0.09587</v>
       </c>
     </row>
@@ -7849,9 +8404,12 @@
         <v>0.00754</v>
       </c>
       <c r="K185" s="1" t="n">
+        <v>0.00757</v>
+      </c>
+      <c r="L185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="L185" s="1" t="n">
+      <c r="M185" s="1" t="n">
         <v>0.00754</v>
       </c>
     </row>
@@ -7889,9 +8447,12 @@
         <v>0.04866</v>
       </c>
       <c r="K186" s="1" t="n">
+        <v>0.04879</v>
+      </c>
+      <c r="L186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="L186" s="1" t="n">
+      <c r="M186" s="1" t="n">
         <v>0.0486</v>
       </c>
     </row>
@@ -7929,9 +8490,12 @@
         <v>0.02677</v>
       </c>
       <c r="K187" s="1" t="n">
+        <v>0.02686</v>
+      </c>
+      <c r="L187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="L187" s="1" t="n">
+      <c r="M187" s="1" t="n">
         <v>0.02674</v>
       </c>
     </row>
@@ -7969,9 +8533,12 @@
         <v>0.003306</v>
       </c>
       <c r="K188" s="1" t="n">
+        <v>0.003315</v>
+      </c>
+      <c r="L188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="L188" s="1" t="n">
+      <c r="M188" s="1" t="n">
         <v>0.003303</v>
       </c>
     </row>
@@ -8009,9 +8576,12 @@
         <v>0.2862</v>
       </c>
       <c r="K189" s="1" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="L189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="L189" s="1" t="n">
+      <c r="M189" s="1" t="n">
         <v>0.286</v>
       </c>
     </row>
@@ -8049,9 +8619,12 @@
         <v>0.01797</v>
       </c>
       <c r="K190" s="1" t="n">
+        <v>0.01797</v>
+      </c>
+      <c r="L190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="L190" s="1" t="n">
+      <c r="M190" s="1" t="n">
         <v>0.01797</v>
       </c>
     </row>
@@ -8089,9 +8662,12 @@
         <v>0.2574</v>
       </c>
       <c r="K191" s="1" t="n">
+        <v>0.2578</v>
+      </c>
+      <c r="L191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="L191" s="1" t="n">
+      <c r="M191" s="1" t="n">
         <v>0.2574</v>
       </c>
     </row>
@@ -8129,10 +8705,13 @@
         <v>0.03801</v>
       </c>
       <c r="K192" s="1" t="n">
+        <v>0.03799</v>
+      </c>
+      <c r="L192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="L192" s="1" t="n">
-        <v>0.03801</v>
+      <c r="M192" s="1" t="n">
+        <v>0.03799</v>
       </c>
     </row>
     <row r="193">
@@ -8169,9 +8748,12 @@
         <v>0.0002235</v>
       </c>
       <c r="K193" s="1" t="n">
-        <v>0.0002235</v>
+        <v>0.000224</v>
       </c>
       <c r="L193" s="1" t="n">
+        <v>0.000224</v>
+      </c>
+      <c r="M193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -8209,9 +8791,12 @@
         <v>4.108</v>
       </c>
       <c r="K194" s="1" t="n">
+        <v>4.116</v>
+      </c>
+      <c r="L194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="L194" s="1" t="n">
+      <c r="M194" s="1" t="n">
         <v>4.091</v>
       </c>
     </row>
@@ -8249,9 +8834,12 @@
         <v>0.9994</v>
       </c>
       <c r="K195" s="1" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="L195" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="L195" s="1" t="n">
+      <c r="M195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -8289,9 +8877,12 @@
         <v>4.304</v>
       </c>
       <c r="K196" s="1" t="n">
+        <v>4.315</v>
+      </c>
+      <c r="L196" s="1" t="n">
         <v>4.347</v>
       </c>
-      <c r="L196" s="1" t="n">
+      <c r="M196" s="1" t="n">
         <v>4.276</v>
       </c>
     </row>
@@ -8329,9 +8920,12 @@
         <v>0.15176</v>
       </c>
       <c r="K197" s="1" t="n">
-        <v>0.15176</v>
+        <v>0.15232</v>
       </c>
       <c r="L197" s="1" t="n">
+        <v>0.15232</v>
+      </c>
+      <c r="M197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -8369,9 +8963,12 @@
         <v>0.007479</v>
       </c>
       <c r="K198" s="1" t="n">
-        <v>0.0077</v>
+        <v>0.007899</v>
       </c>
       <c r="L198" s="1" t="n">
+        <v>0.007899</v>
+      </c>
+      <c r="M198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -8409,9 +9006,12 @@
         <v>0.4482</v>
       </c>
       <c r="K199" s="1" t="n">
+        <v>0.4492</v>
+      </c>
+      <c r="L199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="L199" s="1" t="n">
+      <c r="M199" s="1" t="n">
         <v>0.4482</v>
       </c>
     </row>
@@ -8449,9 +9049,12 @@
         <v>0.5813</v>
       </c>
       <c r="K200" s="1" t="n">
-        <v>0.5857</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="L200" s="1" t="n">
+        <v>0.5911999999999999</v>
+      </c>
+      <c r="M200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -8489,9 +9092,12 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="K201" s="1" t="n">
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="L201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="L201" s="1" t="n">
+      <c r="M201" s="1" t="n">
         <v>0.0931</v>
       </c>
     </row>
@@ -8529,9 +9135,12 @@
         <v>0.06044</v>
       </c>
       <c r="K202" s="1" t="n">
+        <v>0.06055</v>
+      </c>
+      <c r="L202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="L202" s="1" t="n">
+      <c r="M202" s="1" t="n">
         <v>0.06044</v>
       </c>
     </row>
@@ -8569,9 +9178,12 @@
         <v>0.008330000000000001</v>
       </c>
       <c r="K203" s="1" t="n">
+        <v>0.00831</v>
+      </c>
+      <c r="L203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="L203" s="1" t="n">
+      <c r="M203" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -8609,9 +9221,12 @@
         <v>0.00419</v>
       </c>
       <c r="K204" s="1" t="n">
+        <v>0.00419</v>
+      </c>
+      <c r="L204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="L204" s="1" t="n">
+      <c r="M204" s="1" t="n">
         <v>0.00418</v>
       </c>
     </row>
@@ -8649,10 +9264,13 @@
         <v>0.00912</v>
       </c>
       <c r="K205" s="1" t="n">
+        <v>0.009103</v>
+      </c>
+      <c r="L205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="L205" s="1" t="n">
-        <v>0.00912</v>
+      <c r="M205" s="1" t="n">
+        <v>0.009103</v>
       </c>
     </row>
     <row r="206">
@@ -8689,9 +9307,12 @@
         <v>0.2396</v>
       </c>
       <c r="K206" s="1" t="n">
-        <v>0.2413</v>
+        <v>0.2418</v>
       </c>
       <c r="L206" s="1" t="n">
+        <v>0.2418</v>
+      </c>
+      <c r="M206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -8729,9 +9350,12 @@
         <v>0.02077</v>
       </c>
       <c r="K207" s="1" t="n">
+        <v>0.02098</v>
+      </c>
+      <c r="L207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="L207" s="1" t="n">
+      <c r="M207" s="1" t="n">
         <v>0.02077</v>
       </c>
     </row>
@@ -8769,9 +9393,12 @@
         <v>0.2364</v>
       </c>
       <c r="K208" s="1" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="L208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="L208" s="1" t="n">
+      <c r="M208" s="1" t="n">
         <v>0.2364</v>
       </c>
     </row>
@@ -8809,10 +9436,13 @@
         <v>0.3597</v>
       </c>
       <c r="K209" s="1" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="L209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="L209" s="1" t="n">
-        <v>0.3587</v>
+      <c r="M209" s="1" t="n">
+        <v>0.3586</v>
       </c>
     </row>
     <row r="210">
@@ -8849,9 +9479,12 @@
         <v>0.04236</v>
       </c>
       <c r="K210" s="1" t="n">
+        <v>0.04247</v>
+      </c>
+      <c r="L210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="L210" s="1" t="n">
+      <c r="M210" s="1" t="n">
         <v>0.04236</v>
       </c>
     </row>
@@ -8889,9 +9522,12 @@
         <v>0.0004257</v>
       </c>
       <c r="K211" s="1" t="n">
+        <v>0.0004278</v>
+      </c>
+      <c r="L211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="L211" s="1" t="n">
+      <c r="M211" s="1" t="n">
         <v>0.0004256</v>
       </c>
     </row>
@@ -8929,9 +9565,12 @@
         <v>0.02152</v>
       </c>
       <c r="K212" s="1" t="n">
+        <v>0.02156</v>
+      </c>
+      <c r="L212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="L212" s="1" t="n">
+      <c r="M212" s="1" t="n">
         <v>0.02151</v>
       </c>
     </row>
@@ -8969,9 +9608,12 @@
         <v>0.1142</v>
       </c>
       <c r="K213" s="1" t="n">
+        <v>0.1146</v>
+      </c>
+      <c r="L213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="L213" s="1" t="n">
+      <c r="M213" s="1" t="n">
         <v>0.1137</v>
       </c>
     </row>
@@ -9009,9 +9651,12 @@
         <v>0.04175</v>
       </c>
       <c r="K214" s="1" t="n">
+        <v>0.04183</v>
+      </c>
+      <c r="L214" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="L214" s="1" t="n">
+      <c r="M214" s="1" t="n">
         <v>0.04174</v>
       </c>
     </row>
@@ -9049,9 +9694,12 @@
         <v>0.009933000000000001</v>
       </c>
       <c r="K215" s="1" t="n">
+        <v>0.009896</v>
+      </c>
+      <c r="L215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="L215" s="1" t="n">
+      <c r="M215" s="1" t="n">
         <v>0.009896</v>
       </c>
     </row>
@@ -9089,9 +9737,12 @@
         <v>0.0641</v>
       </c>
       <c r="K216" s="1" t="n">
+        <v>0.06419999999999999</v>
+      </c>
+      <c r="L216" s="1" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="L216" s="1" t="n">
+      <c r="M216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -9129,9 +9780,12 @@
         <v>0.004199</v>
       </c>
       <c r="K217" s="1" t="n">
-        <v>0.004231</v>
+        <v>0.004248</v>
       </c>
       <c r="L217" s="1" t="n">
+        <v>0.004248</v>
+      </c>
+      <c r="M217" s="1" t="n">
         <v>0.004177</v>
       </c>
     </row>
@@ -9169,9 +9823,12 @@
         <v>0.009990000000000001</v>
       </c>
       <c r="K218" s="1" t="n">
+        <v>0.01008</v>
+      </c>
+      <c r="L218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="L218" s="1" t="n">
+      <c r="M218" s="1" t="n">
         <v>0.009820000000000001</v>
       </c>
     </row>
@@ -9209,9 +9866,12 @@
         <v>0.0307</v>
       </c>
       <c r="K219" s="1" t="n">
+        <v>0.03003</v>
+      </c>
+      <c r="L219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="L219" s="1" t="n">
+      <c r="M219" s="1" t="n">
         <v>0.02958</v>
       </c>
     </row>
@@ -9249,9 +9909,12 @@
         <v>2.291</v>
       </c>
       <c r="K220" s="1" t="n">
+        <v>2.298</v>
+      </c>
+      <c r="L220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="L220" s="1" t="n">
+      <c r="M220" s="1" t="n">
         <v>2.291</v>
       </c>
     </row>
@@ -9289,10 +9952,13 @@
         <v>0.022878</v>
       </c>
       <c r="K221" s="1" t="n">
+        <v>0.022861</v>
+      </c>
+      <c r="L221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="L221" s="1" t="n">
-        <v>0.022878</v>
+      <c r="M221" s="1" t="n">
+        <v>0.022861</v>
       </c>
     </row>
     <row r="222">
@@ -9329,9 +9995,12 @@
         <v>0.0369</v>
       </c>
       <c r="K222" s="1" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="L222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="L222" s="1" t="n">
+      <c r="M222" s="1" t="n">
         <v>0.0369</v>
       </c>
     </row>
@@ -9369,9 +10038,12 @@
         <v>0.293</v>
       </c>
       <c r="K223" s="1" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="L223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="L223" s="1" t="n">
+      <c r="M223" s="1" t="n">
         <v>0.2918</v>
       </c>
     </row>
@@ -9409,9 +10081,12 @@
         <v>0.01556</v>
       </c>
       <c r="K224" s="1" t="n">
+        <v>0.01561</v>
+      </c>
+      <c r="L224" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="L224" s="1" t="n">
+      <c r="M224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -9449,9 +10124,12 @@
         <v>0.0004076</v>
       </c>
       <c r="K225" s="1" t="n">
+        <v>0.0004069</v>
+      </c>
+      <c r="L225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="L225" s="1" t="n">
+      <c r="M225" s="1" t="n">
         <v>0.0004069</v>
       </c>
     </row>
@@ -9489,10 +10167,13 @@
         <v>0.0868</v>
       </c>
       <c r="K226" s="1" t="n">
+        <v>0.0863</v>
+      </c>
+      <c r="L226" s="1" t="n">
         <v>0.08815000000000001</v>
       </c>
-      <c r="L226" s="1" t="n">
-        <v>0.08654000000000001</v>
+      <c r="M226" s="1" t="n">
+        <v>0.0863</v>
       </c>
     </row>
     <row r="227">
@@ -9529,9 +10210,12 @@
         <v>0.947</v>
       </c>
       <c r="K227" s="1" t="n">
+        <v>0.953</v>
+      </c>
+      <c r="L227" s="1" t="n">
         <v>0.959</v>
       </c>
-      <c r="L227" s="1" t="n">
+      <c r="M227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -9569,10 +10253,13 @@
         <v>0.05555</v>
       </c>
       <c r="K228" s="1" t="n">
+        <v>0.05546</v>
+      </c>
+      <c r="L228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="L228" s="1" t="n">
-        <v>0.05555</v>
+      <c r="M228" s="1" t="n">
+        <v>0.05546</v>
       </c>
     </row>
     <row r="229">
@@ -9609,9 +10296,12 @@
         <v>0.002006</v>
       </c>
       <c r="K229" s="1" t="n">
+        <v>0.002011</v>
+      </c>
+      <c r="L229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="L229" s="1" t="n">
+      <c r="M229" s="1" t="n">
         <v>0.002003</v>
       </c>
     </row>
@@ -9649,9 +10339,12 @@
         <v>0.022928</v>
       </c>
       <c r="K230" s="1" t="n">
-        <v>0.023091</v>
+        <v>0.023101</v>
       </c>
       <c r="L230" s="1" t="n">
+        <v>0.023101</v>
+      </c>
+      <c r="M230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -9689,9 +10382,12 @@
         <v>0.0535</v>
       </c>
       <c r="K231" s="1" t="n">
+        <v>0.05364</v>
+      </c>
+      <c r="L231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="L231" s="1" t="n">
+      <c r="M231" s="1" t="n">
         <v>0.0535</v>
       </c>
     </row>
@@ -9729,9 +10425,12 @@
         <v>0.0587</v>
       </c>
       <c r="K232" s="1" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="L232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="L232" s="1" t="n">
+      <c r="M232" s="1" t="n">
         <v>0.0587</v>
       </c>
     </row>
@@ -9769,9 +10468,12 @@
         <v>0.001682</v>
       </c>
       <c r="K233" s="1" t="n">
+        <v>0.001679</v>
+      </c>
+      <c r="L233" s="1" t="n">
         <v>0.001701</v>
       </c>
-      <c r="L233" s="1" t="n">
+      <c r="M233" s="1" t="n">
         <v>0.001678</v>
       </c>
     </row>
@@ -9809,10 +10511,13 @@
         <v>0.00575</v>
       </c>
       <c r="K234" s="1" t="n">
+        <v>0.005747</v>
+      </c>
+      <c r="L234" s="1" t="n">
         <v>0.005854</v>
       </c>
-      <c r="L234" s="1" t="n">
-        <v>0.00575</v>
+      <c r="M234" s="1" t="n">
+        <v>0.005747</v>
       </c>
     </row>
     <row r="235">
@@ -9849,9 +10554,12 @@
         <v>0.12551</v>
       </c>
       <c r="K235" s="1" t="n">
+        <v>0.12485</v>
+      </c>
+      <c r="L235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="L235" s="1" t="n">
+      <c r="M235" s="1" t="n">
         <v>0.12453</v>
       </c>
     </row>
@@ -9889,9 +10597,12 @@
         <v>64.73</v>
       </c>
       <c r="K236" s="1" t="n">
+        <v>64.79000000000001</v>
+      </c>
+      <c r="L236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="L236" s="1" t="n">
+      <c r="M236" s="1" t="n">
         <v>64.73</v>
       </c>
     </row>
@@ -9929,9 +10640,12 @@
         <v>0.1016</v>
       </c>
       <c r="K237" s="1" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="L237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="L237" s="1" t="n">
+      <c r="M237" s="1" t="n">
         <v>0.1016</v>
       </c>
     </row>
@@ -9969,9 +10683,12 @@
         <v>0.003949</v>
       </c>
       <c r="K238" s="1" t="n">
-        <v>0.003993</v>
+        <v>0.004006</v>
       </c>
       <c r="L238" s="1" t="n">
+        <v>0.004006</v>
+      </c>
+      <c r="M238" s="1" t="n">
         <v>0.003925</v>
       </c>
     </row>
@@ -10009,9 +10726,12 @@
         <v>0.01556</v>
       </c>
       <c r="K239" s="1" t="n">
+        <v>0.01543</v>
+      </c>
+      <c r="L239" s="1" t="n">
         <v>0.01562</v>
       </c>
-      <c r="L239" s="1" t="n">
+      <c r="M239" s="1" t="n">
         <v>0.01532</v>
       </c>
     </row>
@@ -10049,9 +10769,12 @@
         <v>0.05609</v>
       </c>
       <c r="K240" s="1" t="n">
+        <v>0.05622</v>
+      </c>
+      <c r="L240" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="L240" s="1" t="n">
+      <c r="M240" s="1" t="n">
         <v>0.05598</v>
       </c>
     </row>
@@ -10089,9 +10812,12 @@
         <v>0.0114</v>
       </c>
       <c r="K241" s="1" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="L241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="L241" s="1" t="n">
+      <c r="M241" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -10129,9 +10855,12 @@
         <v>0.3346</v>
       </c>
       <c r="K242" s="1" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="L242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="L242" s="1" t="n">
+      <c r="M242" s="1" t="n">
         <v>0.3334</v>
       </c>
     </row>
@@ -10169,9 +10898,12 @@
         <v>0.01232</v>
       </c>
       <c r="K243" s="1" t="n">
+        <v>0.01231</v>
+      </c>
+      <c r="L243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="L243" s="1" t="n">
+      <c r="M243" s="1" t="n">
         <v>0.01229</v>
       </c>
     </row>
@@ -10209,9 +10941,12 @@
         <v>0.08053</v>
       </c>
       <c r="K244" s="1" t="n">
-        <v>0.08067000000000001</v>
+        <v>0.08083</v>
       </c>
       <c r="L244" s="1" t="n">
+        <v>0.08083</v>
+      </c>
+      <c r="M244" s="1" t="n">
         <v>0.07997</v>
       </c>
     </row>
@@ -10249,9 +10984,12 @@
         <v>0.007771</v>
       </c>
       <c r="K245" s="1" t="n">
+        <v>0.00783</v>
+      </c>
+      <c r="L245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="L245" s="1" t="n">
+      <c r="M245" s="1" t="n">
         <v>0.007769</v>
       </c>
     </row>
@@ -10289,9 +11027,12 @@
         <v>0.03025</v>
       </c>
       <c r="K246" s="1" t="n">
+        <v>0.03032</v>
+      </c>
+      <c r="L246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="L246" s="1" t="n">
+      <c r="M246" s="1" t="n">
         <v>0.03025</v>
       </c>
     </row>
@@ -10329,9 +11070,12 @@
         <v>0.1803</v>
       </c>
       <c r="K247" s="1" t="n">
+        <v>0.1806</v>
+      </c>
+      <c r="L247" s="1" t="n">
         <v>0.1827</v>
       </c>
-      <c r="L247" s="1" t="n">
+      <c r="M247" s="1" t="n">
         <v>0.1801</v>
       </c>
     </row>
@@ -10369,9 +11113,12 @@
         <v>0.05884</v>
       </c>
       <c r="K248" s="1" t="n">
+        <v>0.05889</v>
+      </c>
+      <c r="L248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="L248" s="1" t="n">
+      <c r="M248" s="1" t="n">
         <v>0.05884</v>
       </c>
     </row>
@@ -10409,10 +11156,13 @@
         <v>0.1663</v>
       </c>
       <c r="K249" s="1" t="n">
+        <v>0.1662</v>
+      </c>
+      <c r="L249" s="1" t="n">
         <v>0.1684</v>
       </c>
-      <c r="L249" s="1" t="n">
-        <v>0.1663</v>
+      <c r="M249" s="1" t="n">
+        <v>0.1662</v>
       </c>
     </row>
     <row r="250">
@@ -10449,9 +11199,12 @@
         <v>0.01906</v>
       </c>
       <c r="K250" s="1" t="n">
+        <v>0.01921</v>
+      </c>
+      <c r="L250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="L250" s="1" t="n">
+      <c r="M250" s="1" t="n">
         <v>0.01906</v>
       </c>
     </row>
@@ -10489,9 +11242,12 @@
         <v>0.02308</v>
       </c>
       <c r="K251" s="1" t="n">
+        <v>0.02307</v>
+      </c>
+      <c r="L251" s="1" t="n">
         <v>0.02318</v>
       </c>
-      <c r="L251" s="1" t="n">
+      <c r="M251" s="1" t="n">
         <v>0.02295</v>
       </c>
     </row>
@@ -10529,9 +11285,12 @@
         <v>0.30579</v>
       </c>
       <c r="K252" s="1" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="L252" s="1" t="n">
         <v>0.31227</v>
       </c>
-      <c r="L252" s="1" t="n">
+      <c r="M252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -10569,9 +11328,12 @@
         <v>0.006013</v>
       </c>
       <c r="K253" s="1" t="n">
+        <v>0.006064</v>
+      </c>
+      <c r="L253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="L253" s="1" t="n">
+      <c r="M253" s="1" t="n">
         <v>0.005971</v>
       </c>
     </row>
@@ -10609,9 +11371,12 @@
         <v>0.6126</v>
       </c>
       <c r="K254" s="1" t="n">
+        <v>0.6137</v>
+      </c>
+      <c r="L254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="L254" s="1" t="n">
+      <c r="M254" s="1" t="n">
         <v>0.6116</v>
       </c>
     </row>
@@ -10649,9 +11414,12 @@
         <v>0.10628</v>
       </c>
       <c r="K255" s="1" t="n">
+        <v>0.10655</v>
+      </c>
+      <c r="L255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="L255" s="1" t="n">
+      <c r="M255" s="1" t="n">
         <v>0.10612</v>
       </c>
     </row>
@@ -10689,9 +11457,12 @@
         <v>0.091</v>
       </c>
       <c r="K256" s="1" t="n">
-        <v>0.0911</v>
+        <v>0.0916</v>
       </c>
       <c r="L256" s="1" t="n">
+        <v>0.0916</v>
+      </c>
+      <c r="M256" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -10729,9 +11500,12 @@
         <v>0.01428</v>
       </c>
       <c r="K257" s="1" t="n">
-        <v>0.01454</v>
+        <v>0.01468</v>
       </c>
       <c r="L257" s="1" t="n">
+        <v>0.01468</v>
+      </c>
+      <c r="M257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -10769,10 +11543,13 @@
         <v>0.05115</v>
       </c>
       <c r="K258" s="1" t="n">
+        <v>0.05083</v>
+      </c>
+      <c r="L258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="L258" s="1" t="n">
-        <v>0.0511</v>
+      <c r="M258" s="1" t="n">
+        <v>0.05083</v>
       </c>
     </row>
     <row r="259">
@@ -10809,9 +11586,12 @@
         <v>0.00814</v>
       </c>
       <c r="K259" s="1" t="n">
+        <v>0.00814</v>
+      </c>
+      <c r="L259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="L259" s="1" t="n">
+      <c r="M259" s="1" t="n">
         <v>0.008109999999999999</v>
       </c>
     </row>
@@ -10849,9 +11629,12 @@
         <v>0.1901</v>
       </c>
       <c r="K260" s="1" t="n">
+        <v>0.1906</v>
+      </c>
+      <c r="L260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="L260" s="1" t="n">
+      <c r="M260" s="1" t="n">
         <v>0.1894</v>
       </c>
     </row>
@@ -10889,9 +11672,12 @@
         <v>0.0982</v>
       </c>
       <c r="K261" s="1" t="n">
+        <v>0.0982</v>
+      </c>
+      <c r="L261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="L261" s="1" t="n">
+      <c r="M261" s="1" t="n">
         <v>0.0982</v>
       </c>
     </row>
@@ -10929,9 +11715,12 @@
         <v>0.2114</v>
       </c>
       <c r="K262" s="1" t="n">
+        <v>0.2118</v>
+      </c>
+      <c r="L262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="L262" s="1" t="n">
+      <c r="M262" s="1" t="n">
         <v>0.2113</v>
       </c>
     </row>
@@ -10969,9 +11758,12 @@
         <v>0.008496999999999999</v>
       </c>
       <c r="K263" s="1" t="n">
-        <v>0.008522999999999999</v>
+        <v>0.008560999999999999</v>
       </c>
       <c r="L263" s="1" t="n">
+        <v>0.008560999999999999</v>
+      </c>
+      <c r="M263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -11009,9 +11801,12 @@
         <v>2.632</v>
       </c>
       <c r="K264" s="1" t="n">
+        <v>2.634</v>
+      </c>
+      <c r="L264" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="L264" s="1" t="n">
+      <c r="M264" s="1" t="n">
         <v>2.632</v>
       </c>
     </row>
@@ -11049,9 +11844,12 @@
         <v>0.01856</v>
       </c>
       <c r="K265" s="1" t="n">
+        <v>0.01862</v>
+      </c>
+      <c r="L265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="L265" s="1" t="n">
+      <c r="M265" s="1" t="n">
         <v>0.01847</v>
       </c>
     </row>
@@ -11089,9 +11887,12 @@
         <v>0.3601</v>
       </c>
       <c r="K266" s="1" t="n">
-        <v>0.3604</v>
+        <v>0.3607</v>
       </c>
       <c r="L266" s="1" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="M266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -11129,9 +11930,12 @@
         <v>0.03442</v>
       </c>
       <c r="K267" s="1" t="n">
+        <v>0.03446</v>
+      </c>
+      <c r="L267" s="1" t="n">
         <v>0.03464</v>
       </c>
-      <c r="L267" s="1" t="n">
+      <c r="M267" s="1" t="n">
         <v>0.03408</v>
       </c>
     </row>
@@ -11169,9 +11973,12 @@
         <v>0.119</v>
       </c>
       <c r="K268" s="1" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="L268" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="L268" s="1" t="n">
+      <c r="M268" s="1" t="n">
         <v>0.118</v>
       </c>
     </row>
@@ -11209,9 +12016,12 @@
         <v>0.08005</v>
       </c>
       <c r="K269" s="1" t="n">
+        <v>0.08011</v>
+      </c>
+      <c r="L269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="L269" s="1" t="n">
+      <c r="M269" s="1" t="n">
         <v>0.07973</v>
       </c>
     </row>
@@ -11249,9 +12059,12 @@
         <v>0.01384</v>
       </c>
       <c r="K270" s="1" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="L270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="L270" s="1" t="n">
+      <c r="M270" s="1" t="n">
         <v>0.01382</v>
       </c>
     </row>
@@ -11289,9 +12102,12 @@
         <v>0.007568</v>
       </c>
       <c r="K271" s="1" t="n">
+        <v>0.007594</v>
+      </c>
+      <c r="L271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="L271" s="1" t="n">
+      <c r="M271" s="1" t="n">
         <v>0.007558</v>
       </c>
     </row>
@@ -11329,9 +12145,12 @@
         <v>0.07421999999999999</v>
       </c>
       <c r="K272" s="1" t="n">
+        <v>0.07444000000000001</v>
+      </c>
+      <c r="L272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="L272" s="1" t="n">
+      <c r="M272" s="1" t="n">
         <v>0.0741</v>
       </c>
     </row>
@@ -11369,9 +12188,12 @@
         <v>3.14e-05</v>
       </c>
       <c r="K273" s="1" t="n">
+        <v>3.15e-05</v>
+      </c>
+      <c r="L273" s="1" t="n">
         <v>3.16e-05</v>
       </c>
-      <c r="L273" s="1" t="n">
+      <c r="M273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -11409,9 +12231,12 @@
         <v>0.00548</v>
       </c>
       <c r="K274" s="1" t="n">
+        <v>0.005506</v>
+      </c>
+      <c r="L274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="L274" s="1" t="n">
+      <c r="M274" s="1" t="n">
         <v>0.005469</v>
       </c>
     </row>
@@ -11449,9 +12274,12 @@
         <v>0.181</v>
       </c>
       <c r="K275" s="1" t="n">
+        <v>0.1809</v>
+      </c>
+      <c r="L275" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="L275" s="1" t="n">
+      <c r="M275" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -11489,9 +12317,12 @@
         <v>0.006843</v>
       </c>
       <c r="K276" s="1" t="n">
+        <v>0.006843</v>
+      </c>
+      <c r="L276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="L276" s="1" t="n">
+      <c r="M276" s="1" t="n">
         <v>0.006843</v>
       </c>
     </row>
@@ -11529,9 +12360,12 @@
         <v>0.1306</v>
       </c>
       <c r="K277" s="1" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="L277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="L277" s="1" t="n">
+      <c r="M277" s="1" t="n">
         <v>0.1303</v>
       </c>
     </row>
@@ -11569,9 +12403,12 @@
         <v>0.02323</v>
       </c>
       <c r="K278" s="1" t="n">
+        <v>0.02334</v>
+      </c>
+      <c r="L278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="L278" s="1" t="n">
+      <c r="M278" s="1" t="n">
         <v>0.02308</v>
       </c>
     </row>
@@ -11609,9 +12446,12 @@
         <v>0.01814</v>
       </c>
       <c r="K279" s="1" t="n">
+        <v>0.01814</v>
+      </c>
+      <c r="L279" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="L279" s="1" t="n">
+      <c r="M279" s="1" t="n">
         <v>0.01812</v>
       </c>
     </row>
@@ -11649,9 +12489,12 @@
         <v>0.03715</v>
       </c>
       <c r="K280" s="1" t="n">
+        <v>0.03728</v>
+      </c>
+      <c r="L280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="L280" s="1" t="n">
+      <c r="M280" s="1" t="n">
         <v>0.03715</v>
       </c>
     </row>
@@ -11689,9 +12532,12 @@
         <v>0.03961</v>
       </c>
       <c r="K281" s="1" t="n">
+        <v>0.0399</v>
+      </c>
+      <c r="L281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="L281" s="1" t="n">
+      <c r="M281" s="1" t="n">
         <v>0.03953</v>
       </c>
     </row>
@@ -11729,9 +12575,12 @@
         <v>0.3001</v>
       </c>
       <c r="K282" s="1" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="L282" s="1" t="n">
         <v>0.3059</v>
       </c>
-      <c r="L282" s="1" t="n">
+      <c r="M282" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -11769,9 +12618,12 @@
         <v>0.01119</v>
       </c>
       <c r="K283" s="1" t="n">
+        <v>0.01124</v>
+      </c>
+      <c r="L283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="L283" s="1" t="n">
+      <c r="M283" s="1" t="n">
         <v>0.01119</v>
       </c>
     </row>
@@ -11809,9 +12661,12 @@
         <v>9.500000000000001e-06</v>
       </c>
       <c r="K284" s="1" t="n">
-        <v>9.7e-06</v>
+        <v>9.799999999999999e-06</v>
       </c>
       <c r="L284" s="1" t="n">
+        <v>9.799999999999999e-06</v>
+      </c>
+      <c r="M284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -11849,9 +12704,12 @@
         <v>0.1144</v>
       </c>
       <c r="K285" s="1" t="n">
+        <v>0.1151</v>
+      </c>
+      <c r="L285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="L285" s="1" t="n">
+      <c r="M285" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -11889,9 +12747,12 @@
         <v>0.003424</v>
       </c>
       <c r="K286" s="1" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="L286" s="1" t="n">
         <v>0.003485</v>
       </c>
-      <c r="L286" s="1" t="n">
+      <c r="M286" s="1" t="n">
         <v>0.003422</v>
       </c>
     </row>
@@ -11929,9 +12790,12 @@
         <v>0.08513999999999999</v>
       </c>
       <c r="K287" s="1" t="n">
-        <v>0.08573</v>
+        <v>0.08577</v>
       </c>
       <c r="L287" s="1" t="n">
+        <v>0.08577</v>
+      </c>
+      <c r="M287" s="1" t="n">
         <v>0.08486</v>
       </c>
     </row>
@@ -11969,9 +12833,12 @@
         <v>0.09938</v>
       </c>
       <c r="K288" s="1" t="n">
+        <v>0.10008</v>
+      </c>
+      <c r="L288" s="1" t="n">
         <v>0.1001</v>
       </c>
-      <c r="L288" s="1" t="n">
+      <c r="M288" s="1" t="n">
         <v>0.09869</v>
       </c>
     </row>
@@ -12009,9 +12876,12 @@
         <v>0.4335</v>
       </c>
       <c r="K289" s="1" t="n">
+        <v>0.4334</v>
+      </c>
+      <c r="L289" s="1" t="n">
         <v>0.4359</v>
       </c>
-      <c r="L289" s="1" t="n">
+      <c r="M289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -12049,9 +12919,12 @@
         <v>0.039</v>
       </c>
       <c r="K290" s="1" t="n">
+        <v>0.03911</v>
+      </c>
+      <c r="L290" s="1" t="n">
         <v>0.03966</v>
       </c>
-      <c r="L290" s="1" t="n">
+      <c r="M290" s="1" t="n">
         <v>0.03878</v>
       </c>
     </row>
@@ -12089,9 +12962,12 @@
         <v>0.2376</v>
       </c>
       <c r="K291" s="1" t="n">
+        <v>0.2377</v>
+      </c>
+      <c r="L291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="L291" s="1" t="n">
+      <c r="M291" s="1" t="n">
         <v>0.2376</v>
       </c>
     </row>
@@ -12129,10 +13005,13 @@
         <v>0.28303</v>
       </c>
       <c r="K292" s="1" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="L292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="L292" s="1" t="n">
-        <v>0.28275</v>
+      <c r="M292" s="1" t="n">
+        <v>0.2826</v>
       </c>
     </row>
     <row r="293">
@@ -12169,9 +13048,12 @@
         <v>0.149</v>
       </c>
       <c r="K293" s="1" t="n">
+        <v>0.1499</v>
+      </c>
+      <c r="L293" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="L293" s="1" t="n">
+      <c r="M293" s="1" t="n">
         <v>0.1489</v>
       </c>
     </row>
@@ -12209,9 +13091,12 @@
         <v>4.205</v>
       </c>
       <c r="K294" s="1" t="n">
+        <v>4.212</v>
+      </c>
+      <c r="L294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="L294" s="1" t="n">
+      <c r="M294" s="1" t="n">
         <v>4.205</v>
       </c>
     </row>
@@ -12249,9 +13134,12 @@
         <v>0.03271</v>
       </c>
       <c r="K295" s="1" t="n">
+        <v>0.03294</v>
+      </c>
+      <c r="L295" s="1" t="n">
         <v>0.03339</v>
       </c>
-      <c r="L295" s="1" t="n">
+      <c r="M295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -12289,10 +13177,13 @@
         <v>0.000973</v>
       </c>
       <c r="K296" s="1" t="n">
+        <v>0.000969</v>
+      </c>
+      <c r="L296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="L296" s="1" t="n">
-        <v>0.000973</v>
+      <c r="M296" s="1" t="n">
+        <v>0.000969</v>
       </c>
     </row>
     <row r="297">
@@ -12329,9 +13220,12 @@
         <v>0.08180999999999999</v>
       </c>
       <c r="K297" s="1" t="n">
+        <v>0.08183</v>
+      </c>
+      <c r="L297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="L297" s="1" t="n">
+      <c r="M297" s="1" t="n">
         <v>0.08154</v>
       </c>
     </row>
@@ -12369,9 +13263,12 @@
         <v>0.0577</v>
       </c>
       <c r="K298" s="1" t="n">
+        <v>0.05798</v>
+      </c>
+      <c r="L298" s="1" t="n">
         <v>0.05821</v>
       </c>
-      <c r="L298" s="1" t="n">
+      <c r="M298" s="1" t="n">
         <v>0.05745</v>
       </c>
     </row>
@@ -12409,9 +13306,12 @@
         <v>0.09080000000000001</v>
       </c>
       <c r="K299" s="1" t="n">
+        <v>0.09154</v>
+      </c>
+      <c r="L299" s="1" t="n">
         <v>0.0917</v>
       </c>
-      <c r="L299" s="1" t="n">
+      <c r="M299" s="1" t="n">
         <v>0.09066</v>
       </c>
     </row>
@@ -12449,9 +13349,12 @@
         <v>0.02754</v>
       </c>
       <c r="K300" s="1" t="n">
+        <v>0.02759</v>
+      </c>
+      <c r="L300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="L300" s="1" t="n">
+      <c r="M300" s="1" t="n">
         <v>0.0274</v>
       </c>
     </row>
@@ -12489,9 +13392,12 @@
         <v>0.06571</v>
       </c>
       <c r="K301" s="1" t="n">
+        <v>0.06594</v>
+      </c>
+      <c r="L301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="L301" s="1" t="n">
+      <c r="M301" s="1" t="n">
         <v>0.06557</v>
       </c>
     </row>
@@ -12529,9 +13435,12 @@
         <v>0.052985</v>
       </c>
       <c r="K302" s="1" t="n">
-        <v>0.052985</v>
+        <v>0.053267</v>
       </c>
       <c r="L302" s="1" t="n">
+        <v>0.053267</v>
+      </c>
+      <c r="M302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -12569,9 +13478,12 @@
         <v>5168.8</v>
       </c>
       <c r="K303" s="1" t="n">
+        <v>5172</v>
+      </c>
+      <c r="L303" s="1" t="n">
         <v>5177.6</v>
       </c>
-      <c r="L303" s="1" t="n">
+      <c r="M303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -12609,9 +13521,12 @@
         <v>14.9</v>
       </c>
       <c r="K304" s="1" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="L304" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="L304" s="1" t="n">
+      <c r="M304" s="1" t="n">
         <v>14.9</v>
       </c>
     </row>
@@ -12649,9 +13564,12 @@
         <v>0.003696</v>
       </c>
       <c r="K305" s="1" t="n">
+        <v>0.003714</v>
+      </c>
+      <c r="L305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="L305" s="1" t="n">
+      <c r="M305" s="1" t="n">
         <v>0.003695</v>
       </c>
     </row>
@@ -12689,9 +13607,12 @@
         <v>0.4558</v>
       </c>
       <c r="K306" s="1" t="n">
+        <v>0.4572</v>
+      </c>
+      <c r="L306" s="1" t="n">
         <v>0.4608</v>
       </c>
-      <c r="L306" s="1" t="n">
+      <c r="M306" s="1" t="n">
         <v>0.4558</v>
       </c>
     </row>
@@ -12729,9 +13650,12 @@
         <v>0.04703</v>
       </c>
       <c r="K307" s="1" t="n">
+        <v>0.04707</v>
+      </c>
+      <c r="L307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="L307" s="1" t="n">
+      <c r="M307" s="1" t="n">
         <v>0.04696</v>
       </c>
     </row>
@@ -12769,9 +13693,12 @@
         <v>1.4886</v>
       </c>
       <c r="K308" s="1" t="n">
-        <v>1.4891</v>
+        <v>1.4902</v>
       </c>
       <c r="L308" s="1" t="n">
+        <v>1.4902</v>
+      </c>
+      <c r="M308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -12809,9 +13736,12 @@
         <v>0.0007986</v>
       </c>
       <c r="K309" s="1" t="n">
+        <v>0.0007974</v>
+      </c>
+      <c r="L309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="L309" s="1" t="n">
+      <c r="M309" s="1" t="n">
         <v>0.0007937</v>
       </c>
     </row>
@@ -12849,10 +13779,13 @@
         <v>4.6</v>
       </c>
       <c r="K310" s="1" t="n">
+        <v>4.599</v>
+      </c>
+      <c r="L310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="L310" s="1" t="n">
-        <v>4.6</v>
+      <c r="M310" s="1" t="n">
+        <v>4.599</v>
       </c>
     </row>
     <row r="311">
@@ -12889,9 +13822,12 @@
         <v>4.743</v>
       </c>
       <c r="K311" s="1" t="n">
+        <v>4.762</v>
+      </c>
+      <c r="L311" s="1" t="n">
         <v>4.805</v>
       </c>
-      <c r="L311" s="1" t="n">
+      <c r="M311" s="1" t="n">
         <v>4.743</v>
       </c>
     </row>
@@ -12929,9 +13865,12 @@
         <v>0.08125</v>
       </c>
       <c r="K312" s="1" t="n">
+        <v>0.08139</v>
+      </c>
+      <c r="L312" s="1" t="n">
         <v>0.08212</v>
       </c>
-      <c r="L312" s="1" t="n">
+      <c r="M312" s="1" t="n">
         <v>0.08098</v>
       </c>
     </row>
@@ -12969,9 +13908,12 @@
         <v>2.021</v>
       </c>
       <c r="K313" s="1" t="n">
+        <v>2.032</v>
+      </c>
+      <c r="L313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="L313" s="1" t="n">
+      <c r="M313" s="1" t="n">
         <v>2.012</v>
       </c>
     </row>
@@ -13009,9 +13951,12 @@
         <v>0.07154000000000001</v>
       </c>
       <c r="K314" s="1" t="n">
-        <v>0.07154000000000001</v>
+        <v>0.07260999999999999</v>
       </c>
       <c r="L314" s="1" t="n">
+        <v>0.07260999999999999</v>
+      </c>
+      <c r="M314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -13049,9 +13994,12 @@
         <v>0.949</v>
       </c>
       <c r="K315" s="1" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="L315" s="1" t="n">
+      <c r="M315" s="1" t="n">
         <v>0.946</v>
       </c>
     </row>
@@ -13089,9 +14037,12 @@
         <v>0.1299</v>
       </c>
       <c r="K316" s="1" t="n">
+        <v>0.131</v>
+      </c>
+      <c r="L316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="L316" s="1" t="n">
+      <c r="M316" s="1" t="n">
         <v>0.1299</v>
       </c>
     </row>
@@ -13129,9 +14080,12 @@
         <v>0.1824</v>
       </c>
       <c r="K317" s="1" t="n">
+        <v>0.1839</v>
+      </c>
+      <c r="L317" s="1" t="n">
         <v>0.186</v>
       </c>
-      <c r="L317" s="1" t="n">
+      <c r="M317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -13169,9 +14123,12 @@
         <v>0.01615</v>
       </c>
       <c r="K318" s="1" t="n">
+        <v>0.01621</v>
+      </c>
+      <c r="L318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="L318" s="1" t="n">
+      <c r="M318" s="1" t="n">
         <v>0.01615</v>
       </c>
     </row>
@@ -13209,9 +14166,12 @@
         <v>0.08348999999999999</v>
       </c>
       <c r="K319" s="1" t="n">
+        <v>0.08352</v>
+      </c>
+      <c r="L319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="L319" s="1" t="n">
+      <c r="M319" s="1" t="n">
         <v>0.08348999999999999</v>
       </c>
     </row>
@@ -13249,9 +14209,12 @@
         <v>0.007584</v>
       </c>
       <c r="K320" s="1" t="n">
+        <v>0.007641</v>
+      </c>
+      <c r="L320" s="1" t="n">
         <v>0.007667</v>
       </c>
-      <c r="L320" s="1" t="n">
+      <c r="M320" s="1" t="n">
         <v>0.007571</v>
       </c>
     </row>
@@ -13289,9 +14252,12 @@
         <v>0.0541</v>
       </c>
       <c r="K321" s="1" t="n">
+        <v>0.05444</v>
+      </c>
+      <c r="L321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="L321" s="1" t="n">
+      <c r="M321" s="1" t="n">
         <v>0.05406</v>
       </c>
     </row>
@@ -13329,9 +14295,12 @@
         <v>0.5498</v>
       </c>
       <c r="K322" s="1" t="n">
-        <v>0.5514</v>
+        <v>0.5515</v>
       </c>
       <c r="L322" s="1" t="n">
+        <v>0.5515</v>
+      </c>
+      <c r="M322" s="1" t="n">
         <v>0.5476</v>
       </c>
     </row>
@@ -13369,9 +14338,12 @@
         <v>0.07607999999999999</v>
       </c>
       <c r="K323" s="1" t="n">
-        <v>0.07611999999999999</v>
+        <v>0.07625</v>
       </c>
       <c r="L323" s="1" t="n">
+        <v>0.07625</v>
+      </c>
+      <c r="M323" s="1" t="n">
         <v>0.07525</v>
       </c>
     </row>
@@ -13409,9 +14381,12 @@
         <v>0.012917</v>
       </c>
       <c r="K324" s="1" t="n">
+        <v>0.01296</v>
+      </c>
+      <c r="L324" s="1" t="n">
         <v>0.013001</v>
       </c>
-      <c r="L324" s="1" t="n">
+      <c r="M324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -13449,9 +14424,12 @@
         <v>0.099</v>
       </c>
       <c r="K325" s="1" t="n">
+        <v>0.09909999999999999</v>
+      </c>
+      <c r="L325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="L325" s="1" t="n">
+      <c r="M325" s="1" t="n">
         <v>0.0989</v>
       </c>
     </row>
@@ -13489,10 +14467,13 @@
         <v>0.01732</v>
       </c>
       <c r="K326" s="1" t="n">
+        <v>0.01731</v>
+      </c>
+      <c r="L326" s="1" t="n">
         <v>0.01765</v>
       </c>
-      <c r="L326" s="1" t="n">
-        <v>0.01732</v>
+      <c r="M326" s="1" t="n">
+        <v>0.01731</v>
       </c>
     </row>
     <row r="327">
@@ -13529,9 +14510,12 @@
         <v>0.064</v>
       </c>
       <c r="K327" s="1" t="n">
+        <v>0.0641</v>
+      </c>
+      <c r="L327" s="1" t="n">
         <v>0.06435</v>
       </c>
-      <c r="L327" s="1" t="n">
+      <c r="M327" s="1" t="n">
         <v>0.06382</v>
       </c>
     </row>
@@ -13569,9 +14553,12 @@
         <v>0.263</v>
       </c>
       <c r="K328" s="1" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="L328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="L328" s="1" t="n">
+      <c r="M328" s="1" t="n">
         <v>0.2627</v>
       </c>
     </row>
@@ -13609,9 +14596,12 @@
         <v>0.17212</v>
       </c>
       <c r="K329" s="1" t="n">
-        <v>0.17297</v>
+        <v>0.17328</v>
       </c>
       <c r="L329" s="1" t="n">
+        <v>0.17328</v>
+      </c>
+      <c r="M329" s="1" t="n">
         <v>0.17145</v>
       </c>
     </row>
@@ -13649,9 +14639,12 @@
         <v>2.055</v>
       </c>
       <c r="K330" s="1" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L330" s="1" t="n">
         <v>2.088</v>
       </c>
-      <c r="L330" s="1" t="n">
+      <c r="M330" s="1" t="n">
         <v>2.043</v>
       </c>
     </row>
@@ -13689,9 +14682,12 @@
         <v>0.0285</v>
       </c>
       <c r="K331" s="1" t="n">
-        <v>0.0285</v>
+        <v>0.0286</v>
       </c>
       <c r="L331" s="1" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="M331" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -13729,9 +14725,12 @@
         <v>0.006006</v>
       </c>
       <c r="K332" s="1" t="n">
+        <v>0.006022</v>
+      </c>
+      <c r="L332" s="1" t="n">
         <v>0.006031</v>
       </c>
-      <c r="L332" s="1" t="n">
+      <c r="M332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -13769,9 +14768,12 @@
         <v>0.003522</v>
       </c>
       <c r="K333" s="1" t="n">
+        <v>0.003539</v>
+      </c>
+      <c r="L333" s="1" t="n">
         <v>0.003579</v>
       </c>
-      <c r="L333" s="1" t="n">
+      <c r="M333" s="1" t="n">
         <v>0.003497</v>
       </c>
     </row>
@@ -13809,9 +14811,12 @@
         <v>0.01394</v>
       </c>
       <c r="K334" s="1" t="n">
+        <v>0.01407</v>
+      </c>
+      <c r="L334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="L334" s="1" t="n">
+      <c r="M334" s="1" t="n">
         <v>0.01394</v>
       </c>
     </row>
@@ -13849,9 +14854,12 @@
         <v>1.132</v>
       </c>
       <c r="K335" s="1" t="n">
-        <v>1.132</v>
+        <v>1.134</v>
       </c>
       <c r="L335" s="1" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="M335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -13889,9 +14897,12 @@
         <v>0.011238</v>
       </c>
       <c r="K336" s="1" t="n">
+        <v>0.011258</v>
+      </c>
+      <c r="L336" s="1" t="n">
         <v>0.011326</v>
       </c>
-      <c r="L336" s="1" t="n">
+      <c r="M336" s="1" t="n">
         <v>0.011238</v>
       </c>
     </row>
@@ -13929,9 +14940,12 @@
         <v>2.975</v>
       </c>
       <c r="K337" s="1" t="n">
+        <v>2.982</v>
+      </c>
+      <c r="L337" s="1" t="n">
         <v>3.043</v>
       </c>
-      <c r="L337" s="1" t="n">
+      <c r="M337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -13969,9 +14983,12 @@
         <v>0.01859</v>
       </c>
       <c r="K338" s="1" t="n">
+        <v>0.01863</v>
+      </c>
+      <c r="L338" s="1" t="n">
         <v>0.01885</v>
       </c>
-      <c r="L338" s="1" t="n">
+      <c r="M338" s="1" t="n">
         <v>0.01858</v>
       </c>
     </row>
@@ -14009,9 +15026,12 @@
         <v>0.07726</v>
       </c>
       <c r="K339" s="1" t="n">
+        <v>0.07747999999999999</v>
+      </c>
+      <c r="L339" s="1" t="n">
         <v>0.07790999999999999</v>
       </c>
-      <c r="L339" s="1" t="n">
+      <c r="M339" s="1" t="n">
         <v>0.07689</v>
       </c>
     </row>
@@ -14049,9 +15069,12 @@
         <v>0.075</v>
       </c>
       <c r="K340" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="L340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="L340" s="1" t="n">
+      <c r="M340" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -14089,9 +15112,12 @@
         <v>0.03591</v>
       </c>
       <c r="K341" s="1" t="n">
+        <v>0.03601</v>
+      </c>
+      <c r="L341" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="L341" s="1" t="n">
+      <c r="M341" s="1" t="n">
         <v>0.03591</v>
       </c>
     </row>
@@ -14129,9 +15155,12 @@
         <v>2606</v>
       </c>
       <c r="K342" s="1" t="n">
+        <v>2613</v>
+      </c>
+      <c r="L342" s="1" t="n">
         <v>2647</v>
       </c>
-      <c r="L342" s="1" t="n">
+      <c r="M342" s="1" t="n">
         <v>2606</v>
       </c>
     </row>
@@ -14169,9 +15198,12 @@
         <v>0.0001972</v>
       </c>
       <c r="K343" s="1" t="n">
+        <v>0.0001975</v>
+      </c>
+      <c r="L343" s="1" t="n">
         <v>0.000198</v>
       </c>
-      <c r="L343" s="1" t="n">
+      <c r="M343" s="1" t="n">
         <v>0.0001959</v>
       </c>
     </row>
@@ -14209,9 +15241,12 @@
         <v>0.07948</v>
       </c>
       <c r="K344" s="1" t="n">
+        <v>0.07955</v>
+      </c>
+      <c r="L344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="L344" s="1" t="n">
+      <c r="M344" s="1" t="n">
         <v>0.07925</v>
       </c>
     </row>
@@ -14249,9 +15284,12 @@
         <v>0.01653</v>
       </c>
       <c r="K345" s="1" t="n">
-        <v>0.01656</v>
+        <v>0.0168</v>
       </c>
       <c r="L345" s="1" t="n">
+        <v>0.0168</v>
+      </c>
+      <c r="M345" s="1" t="n">
         <v>0.0163</v>
       </c>
     </row>
@@ -14289,9 +15327,12 @@
         <v>2.757</v>
       </c>
       <c r="K346" s="1" t="n">
+        <v>2.757</v>
+      </c>
+      <c r="L346" s="1" t="n">
         <v>2.799</v>
       </c>
-      <c r="L346" s="1" t="n">
+      <c r="M346" s="1" t="n">
         <v>2.746</v>
       </c>
     </row>
@@ -14329,9 +15370,12 @@
         <v>0.01633</v>
       </c>
       <c r="K347" s="1" t="n">
+        <v>0.01638</v>
+      </c>
+      <c r="L347" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="L347" s="1" t="n">
+      <c r="M347" s="1" t="n">
         <v>0.01631</v>
       </c>
     </row>
@@ -14369,9 +15413,12 @@
         <v>0.03867</v>
       </c>
       <c r="K348" s="1" t="n">
+        <v>0.03884</v>
+      </c>
+      <c r="L348" s="1" t="n">
         <v>0.03897</v>
       </c>
-      <c r="L348" s="1" t="n">
+      <c r="M348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -14409,9 +15456,12 @@
         <v>0.3035</v>
       </c>
       <c r="K349" s="1" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="L349" s="1" t="n">
         <v>0.3065</v>
       </c>
-      <c r="L349" s="1" t="n">
+      <c r="M349" s="1" t="n">
         <v>0.3029</v>
       </c>
     </row>
@@ -14449,9 +15499,12 @@
         <v>0.005091</v>
       </c>
       <c r="K350" s="1" t="n">
+        <v>0.005114</v>
+      </c>
+      <c r="L350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="L350" s="1" t="n">
+      <c r="M350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -14489,9 +15542,12 @@
         <v>0.005103</v>
       </c>
       <c r="K351" s="1" t="n">
+        <v>0.005113</v>
+      </c>
+      <c r="L351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="L351" s="1" t="n">
+      <c r="M351" s="1" t="n">
         <v>0.005065</v>
       </c>
     </row>
@@ -14529,9 +15585,12 @@
         <v>0.004388</v>
       </c>
       <c r="K352" s="1" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="L352" s="1" t="n">
         <v>0.004419</v>
       </c>
-      <c r="L352" s="1" t="n">
+      <c r="M352" s="1" t="n">
         <v>0.004384</v>
       </c>
     </row>
@@ -14569,9 +15628,12 @@
         <v>0.08101999999999999</v>
       </c>
       <c r="K353" s="1" t="n">
+        <v>0.08109</v>
+      </c>
+      <c r="L353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="L353" s="1" t="n">
+      <c r="M353" s="1" t="n">
         <v>0.08062999999999999</v>
       </c>
     </row>
@@ -14609,10 +15671,13 @@
         <v>1.286</v>
       </c>
       <c r="K354" s="1" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="L354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="L354" s="1" t="n">
-        <v>1.283</v>
+      <c r="M354" s="1" t="n">
+        <v>1.277</v>
       </c>
     </row>
     <row r="355">
@@ -14649,9 +15714,12 @@
         <v>7.708</v>
       </c>
       <c r="K355" s="1" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="L355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="L355" s="1" t="n">
+      <c r="M355" s="1" t="n">
         <v>7.707</v>
       </c>
     </row>
@@ -14689,9 +15757,12 @@
         <v>0.007849999999999999</v>
       </c>
       <c r="K356" s="1" t="n">
+        <v>0.007860000000000001</v>
+      </c>
+      <c r="L356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="L356" s="1" t="n">
+      <c r="M356" s="1" t="n">
         <v>0.00778</v>
       </c>
     </row>
@@ -14729,9 +15800,12 @@
         <v>0.005632</v>
       </c>
       <c r="K357" s="1" t="n">
+        <v>0.005644</v>
+      </c>
+      <c r="L357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="L357" s="1" t="n">
+      <c r="M357" s="1" t="n">
         <v>0.005632</v>
       </c>
     </row>
@@ -14769,9 +15843,12 @@
         <v>0.01555</v>
       </c>
       <c r="K358" s="1" t="n">
+        <v>0.01556</v>
+      </c>
+      <c r="L358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="L358" s="1" t="n">
+      <c r="M358" s="1" t="n">
         <v>0.01551</v>
       </c>
     </row>
@@ -14809,9 +15886,12 @@
         <v>3.637</v>
       </c>
       <c r="K359" s="1" t="n">
+        <v>3.644</v>
+      </c>
+      <c r="L359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="L359" s="1" t="n">
+      <c r="M359" s="1" t="n">
         <v>3.636</v>
       </c>
     </row>
@@ -14849,9 +15929,12 @@
         <v>0.1497</v>
       </c>
       <c r="K360" s="1" t="n">
+        <v>0.1501</v>
+      </c>
+      <c r="L360" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="L360" s="1" t="n">
+      <c r="M360" s="1" t="n">
         <v>0.1497</v>
       </c>
     </row>
@@ -14889,9 +15972,12 @@
         <v>0.07035</v>
       </c>
       <c r="K361" s="1" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="L361" s="1" t="n">
         <v>0.07104000000000001</v>
       </c>
-      <c r="L361" s="1" t="n">
+      <c r="M361" s="1" t="n">
         <v>0.07019</v>
       </c>
     </row>
@@ -14929,9 +16015,12 @@
         <v>0.01764</v>
       </c>
       <c r="K362" s="1" t="n">
+        <v>0.01771</v>
+      </c>
+      <c r="L362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="L362" s="1" t="n">
+      <c r="M362" s="1" t="n">
         <v>0.01761</v>
       </c>
     </row>
@@ -14969,9 +16058,12 @@
         <v>0.02238</v>
       </c>
       <c r="K363" s="1" t="n">
+        <v>0.02244</v>
+      </c>
+      <c r="L363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="L363" s="1" t="n">
+      <c r="M363" s="1" t="n">
         <v>0.02234</v>
       </c>
     </row>
@@ -15009,9 +16101,12 @@
         <v>0.01256</v>
       </c>
       <c r="K364" s="1" t="n">
+        <v>0.01259</v>
+      </c>
+      <c r="L364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="L364" s="1" t="n">
+      <c r="M364" s="1" t="n">
         <v>0.01249</v>
       </c>
     </row>
@@ -15049,9 +16144,12 @@
         <v>0.0915</v>
       </c>
       <c r="K365" s="1" t="n">
+        <v>0.0917</v>
+      </c>
+      <c r="L365" s="1" t="n">
         <v>0.0926</v>
       </c>
-      <c r="L365" s="1" t="n">
+      <c r="M365" s="1" t="n">
         <v>0.0915</v>
       </c>
     </row>
@@ -15089,9 +16187,12 @@
         <v>0.04227</v>
       </c>
       <c r="K366" s="1" t="n">
+        <v>0.04239</v>
+      </c>
+      <c r="L366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="L366" s="1" t="n">
+      <c r="M366" s="1" t="n">
         <v>0.04224</v>
       </c>
     </row>
@@ -15129,9 +16230,12 @@
         <v>0.03174</v>
       </c>
       <c r="K367" s="1" t="n">
+        <v>0.03173</v>
+      </c>
+      <c r="L367" s="1" t="n">
         <v>0.03174</v>
       </c>
-      <c r="L367" s="1" t="n">
+      <c r="M367" s="1" t="n">
         <v>0.03141</v>
       </c>
     </row>
@@ -15169,10 +16273,13 @@
         <v>0.02342</v>
       </c>
       <c r="K368" s="1" t="n">
+        <v>0.02334</v>
+      </c>
+      <c r="L368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="L368" s="1" t="n">
-        <v>0.02335</v>
+      <c r="M368" s="1" t="n">
+        <v>0.02334</v>
       </c>
     </row>
     <row r="369">
@@ -15209,9 +16316,12 @@
         <v>0.03099</v>
       </c>
       <c r="K369" s="1" t="n">
+        <v>0.03101</v>
+      </c>
+      <c r="L369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="L369" s="1" t="n">
+      <c r="M369" s="1" t="n">
         <v>0.03089</v>
       </c>
     </row>
@@ -15249,9 +16359,12 @@
         <v>0.07905</v>
       </c>
       <c r="K370" s="1" t="n">
+        <v>0.0793</v>
+      </c>
+      <c r="L370" s="1" t="n">
         <v>0.07932</v>
       </c>
-      <c r="L370" s="1" t="n">
+      <c r="M370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -15289,9 +16402,12 @@
         <v>0.1075</v>
       </c>
       <c r="K371" s="1" t="n">
+        <v>0.1079</v>
+      </c>
+      <c r="L371" s="1" t="n">
         <v>0.1089</v>
       </c>
-      <c r="L371" s="1" t="n">
+      <c r="M371" s="1" t="n">
         <v>0.1074</v>
       </c>
     </row>
@@ -15329,9 +16445,12 @@
         <v>0.007062</v>
       </c>
       <c r="K372" s="1" t="n">
+        <v>0.007081</v>
+      </c>
+      <c r="L372" s="1" t="n">
         <v>0.007209</v>
       </c>
-      <c r="L372" s="1" t="n">
+      <c r="M372" s="1" t="n">
         <v>0.007045</v>
       </c>
     </row>
@@ -15369,9 +16488,12 @@
         <v>0.0963</v>
       </c>
       <c r="K373" s="1" t="n">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="L373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="L373" s="1" t="n">
+      <c r="M373" s="1" t="n">
         <v>0.09619999999999999</v>
       </c>
     </row>
@@ -15409,9 +16531,12 @@
         <v>0.05805</v>
       </c>
       <c r="K374" s="1" t="n">
+        <v>0.05824</v>
+      </c>
+      <c r="L374" s="1" t="n">
         <v>0.05881</v>
       </c>
-      <c r="L374" s="1" t="n">
+      <c r="M374" s="1" t="n">
         <v>0.05804</v>
       </c>
     </row>
@@ -15449,9 +16574,12 @@
         <v>0.3204</v>
       </c>
       <c r="K375" s="1" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="L375" s="1" t="n">
         <v>0.3238</v>
       </c>
-      <c r="L375" s="1" t="n">
+      <c r="M375" s="1" t="n">
         <v>0.3193</v>
       </c>
     </row>
@@ -15489,9 +16617,12 @@
         <v>0.01962</v>
       </c>
       <c r="K376" s="1" t="n">
+        <v>0.01962</v>
+      </c>
+      <c r="L376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="L376" s="1" t="n">
+      <c r="M376" s="1" t="n">
         <v>0.01958</v>
       </c>
     </row>
@@ -15529,9 +16660,12 @@
         <v>0.06868</v>
       </c>
       <c r="K377" s="1" t="n">
+        <v>0.06852999999999999</v>
+      </c>
+      <c r="L377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="L377" s="1" t="n">
+      <c r="M377" s="1" t="n">
         <v>0.06852999999999999</v>
       </c>
     </row>
@@ -15569,9 +16703,12 @@
         <v>0.15542</v>
       </c>
       <c r="K378" s="1" t="n">
+        <v>0.15528</v>
+      </c>
+      <c r="L378" s="1" t="n">
         <v>0.1581</v>
       </c>
-      <c r="L378" s="1" t="n">
+      <c r="M378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -15609,9 +16746,12 @@
         <v>0.0005983</v>
       </c>
       <c r="K379" s="1" t="n">
+        <v>0.000599</v>
+      </c>
+      <c r="L379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="L379" s="1" t="n">
+      <c r="M379" s="1" t="n">
         <v>0.0005965</v>
       </c>
     </row>
@@ -15649,9 +16789,12 @@
         <v>0.01017</v>
       </c>
       <c r="K380" s="1" t="n">
+        <v>0.01017</v>
+      </c>
+      <c r="L380" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="L380" s="1" t="n">
+      <c r="M380" s="1" t="n">
         <v>0.01015</v>
       </c>
     </row>
@@ -15689,9 +16832,12 @@
         <v>0.02548</v>
       </c>
       <c r="K381" s="1" t="n">
+        <v>0.02556</v>
+      </c>
+      <c r="L381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="L381" s="1" t="n">
+      <c r="M381" s="1" t="n">
         <v>0.02547</v>
       </c>
     </row>
@@ -15729,9 +16875,12 @@
         <v>0.19254</v>
       </c>
       <c r="K382" s="1" t="n">
-        <v>0.19263</v>
+        <v>0.19348</v>
       </c>
       <c r="L382" s="1" t="n">
+        <v>0.19348</v>
+      </c>
+      <c r="M382" s="1" t="n">
         <v>0.18936</v>
       </c>
     </row>
@@ -15769,9 +16918,12 @@
         <v>0.09236</v>
       </c>
       <c r="K383" s="1" t="n">
+        <v>0.09308</v>
+      </c>
+      <c r="L383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="L383" s="1" t="n">
+      <c r="M383" s="1" t="n">
         <v>0.09236</v>
       </c>
     </row>
@@ -15809,10 +16961,13 @@
         <v>0.0319</v>
       </c>
       <c r="K384" s="1" t="n">
+        <v>0.03169</v>
+      </c>
+      <c r="L384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="L384" s="1" t="n">
-        <v>0.03176</v>
+      <c r="M384" s="1" t="n">
+        <v>0.03169</v>
       </c>
     </row>
     <row r="385">
@@ -15849,10 +17004,13 @@
         <v>0.01099</v>
       </c>
       <c r="K385" s="1" t="n">
+        <v>0.01094</v>
+      </c>
+      <c r="L385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="L385" s="1" t="n">
-        <v>0.01099</v>
+      <c r="M385" s="1" t="n">
+        <v>0.01094</v>
       </c>
     </row>
     <row r="386">
@@ -15889,9 +17047,12 @@
         <v>0.05188</v>
       </c>
       <c r="K386" s="1" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="L386" s="1" t="n">
         <v>0.05224</v>
       </c>
-      <c r="L386" s="1" t="n">
+      <c r="M386" s="1" t="n">
         <v>0.05087</v>
       </c>
     </row>
@@ -15929,9 +17090,12 @@
         <v>0.02513</v>
       </c>
       <c r="K387" s="1" t="n">
+        <v>0.02508</v>
+      </c>
+      <c r="L387" s="1" t="n">
         <v>0.02541</v>
       </c>
-      <c r="L387" s="1" t="n">
+      <c r="M387" s="1" t="n">
         <v>0.02483</v>
       </c>
     </row>
@@ -15969,9 +17133,12 @@
         <v>0.007301</v>
       </c>
       <c r="K388" s="1" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="L388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="L388" s="1" t="n">
+      <c r="M388" s="1" t="n">
         <v>0.007267</v>
       </c>
     </row>
@@ -16009,9 +17176,12 @@
         <v>0.01013</v>
       </c>
       <c r="K389" s="1" t="n">
+        <v>0.01016</v>
+      </c>
+      <c r="L389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="L389" s="1" t="n">
+      <c r="M389" s="1" t="n">
         <v>0.01011</v>
       </c>
     </row>
@@ -16049,9 +17219,12 @@
         <v>0.08251</v>
       </c>
       <c r="K390" s="1" t="n">
+        <v>0.08255</v>
+      </c>
+      <c r="L390" s="1" t="n">
         <v>0.0839</v>
       </c>
-      <c r="L390" s="1" t="n">
+      <c r="M390" s="1" t="n">
         <v>0.08233</v>
       </c>
     </row>
@@ -16089,9 +17262,12 @@
         <v>0.5014</v>
       </c>
       <c r="K391" s="1" t="n">
+        <v>0.5047</v>
+      </c>
+      <c r="L391" s="1" t="n">
         <v>0.5061</v>
       </c>
-      <c r="L391" s="1" t="n">
+      <c r="M391" s="1" t="n">
         <v>0.5014</v>
       </c>
     </row>
@@ -16129,10 +17305,13 @@
         <v>0.117</v>
       </c>
       <c r="K392" s="1" t="n">
+        <v>0.1168</v>
+      </c>
+      <c r="L392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="L392" s="1" t="n">
-        <v>0.117</v>
+      <c r="M392" s="1" t="n">
+        <v>0.1168</v>
       </c>
     </row>
     <row r="393">
@@ -16169,9 +17348,12 @@
         <v>0.00247</v>
       </c>
       <c r="K393" s="1" t="n">
+        <v>0.00247</v>
+      </c>
+      <c r="L393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="L393" s="1" t="n">
+      <c r="M393" s="1" t="n">
         <v>0.00246</v>
       </c>
     </row>
@@ -16209,9 +17391,12 @@
         <v>0.02129</v>
       </c>
       <c r="K394" s="1" t="n">
+        <v>0.02133</v>
+      </c>
+      <c r="L394" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="L394" s="1" t="n">
+      <c r="M394" s="1" t="n">
         <v>0.02121</v>
       </c>
     </row>
@@ -16249,9 +17434,12 @@
         <v>0.0159</v>
       </c>
       <c r="K395" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="L395" s="1" t="n">
         <v>0.0163</v>
       </c>
-      <c r="L395" s="1" t="n">
+      <c r="M395" s="1" t="n">
         <v>0.0159</v>
       </c>
     </row>
@@ -16289,10 +17477,13 @@
         <v>0.1358</v>
       </c>
       <c r="K396" s="1" t="n">
+        <v>0.1355</v>
+      </c>
+      <c r="L396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="L396" s="1" t="n">
-        <v>0.1356</v>
+      <c r="M396" s="1" t="n">
+        <v>0.1355</v>
       </c>
     </row>
     <row r="397">
@@ -16329,10 +17520,13 @@
         <v>0.01453</v>
       </c>
       <c r="K397" s="1" t="n">
+        <v>0.01452</v>
+      </c>
+      <c r="L397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="L397" s="1" t="n">
-        <v>0.01453</v>
+      <c r="M397" s="1" t="n">
+        <v>0.01452</v>
       </c>
     </row>
     <row r="398">
@@ -16369,9 +17563,12 @@
         <v>6.782</v>
       </c>
       <c r="K398" s="1" t="n">
+        <v>6.749</v>
+      </c>
+      <c r="L398" s="1" t="n">
         <v>6.955</v>
       </c>
-      <c r="L398" s="1" t="n">
+      <c r="M398" s="1" t="n">
         <v>6.725</v>
       </c>
     </row>
@@ -16409,10 +17606,13 @@
         <v>0.009455</v>
       </c>
       <c r="K399" s="1" t="n">
+        <v>0.009434</v>
+      </c>
+      <c r="L399" s="1" t="n">
         <v>0.009509999999999999</v>
       </c>
-      <c r="L399" s="1" t="n">
-        <v>0.009448</v>
+      <c r="M399" s="1" t="n">
+        <v>0.009434</v>
       </c>
     </row>
     <row r="400">
@@ -16449,9 +17649,12 @@
         <v>0.001263</v>
       </c>
       <c r="K400" s="1" t="n">
+        <v>0.001266</v>
+      </c>
+      <c r="L400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="L400" s="1" t="n">
+      <c r="M400" s="1" t="n">
         <v>0.001256</v>
       </c>
     </row>
@@ -16489,9 +17692,12 @@
         <v>0.01846</v>
       </c>
       <c r="K401" s="1" t="n">
+        <v>0.01851</v>
+      </c>
+      <c r="L401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="L401" s="1" t="n">
+      <c r="M401" s="1" t="n">
         <v>0.01841</v>
       </c>
     </row>
@@ -16529,9 +17735,12 @@
         <v>0.08506</v>
       </c>
       <c r="K402" s="1" t="n">
+        <v>0.08515</v>
+      </c>
+      <c r="L402" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="L402" s="1" t="n">
+      <c r="M402" s="1" t="n">
         <v>0.08488999999999999</v>
       </c>
     </row>
@@ -16569,9 +17778,12 @@
         <v>0.00552</v>
       </c>
       <c r="K403" s="1" t="n">
+        <v>0.00552</v>
+      </c>
+      <c r="L403" s="1" t="n">
         <v>0.00556</v>
       </c>
-      <c r="L403" s="1" t="n">
+      <c r="M403" s="1" t="n">
         <v>0.00552</v>
       </c>
     </row>
@@ -16609,9 +17821,12 @@
         <v>0.04278</v>
       </c>
       <c r="K404" s="1" t="n">
+        <v>0.04287</v>
+      </c>
+      <c r="L404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="L404" s="1" t="n">
+      <c r="M404" s="1" t="n">
         <v>0.04278</v>
       </c>
     </row>
@@ -16649,9 +17864,12 @@
         <v>0.05855</v>
       </c>
       <c r="K405" s="1" t="n">
+        <v>0.0587</v>
+      </c>
+      <c r="L405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="L405" s="1" t="n">
+      <c r="M405" s="1" t="n">
         <v>0.05838</v>
       </c>
     </row>
@@ -16689,9 +17907,12 @@
         <v>0.01649</v>
       </c>
       <c r="K406" s="1" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="L406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="L406" s="1" t="n">
+      <c r="M406" s="1" t="n">
         <v>0.01647</v>
       </c>
     </row>
@@ -16729,9 +17950,12 @@
         <v>0.0424</v>
       </c>
       <c r="K407" s="1" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="L407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="L407" s="1" t="n">
+      <c r="M407" s="1" t="n">
         <v>0.0423</v>
       </c>
     </row>
@@ -16769,9 +17993,12 @@
         <v>0.0193</v>
       </c>
       <c r="K408" s="1" t="n">
+        <v>0.01932</v>
+      </c>
+      <c r="L408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="L408" s="1" t="n">
+      <c r="M408" s="1" t="n">
         <v>0.01927</v>
       </c>
     </row>
@@ -16809,9 +18036,12 @@
         <v>0.4443</v>
       </c>
       <c r="K409" s="1" t="n">
+        <v>0.4459</v>
+      </c>
+      <c r="L409" s="1" t="n">
         <v>0.4484</v>
       </c>
-      <c r="L409" s="1" t="n">
+      <c r="M409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -16849,9 +18079,12 @@
         <v>0.04438</v>
       </c>
       <c r="K410" s="1" t="n">
+        <v>0.04421</v>
+      </c>
+      <c r="L410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="L410" s="1" t="n">
+      <c r="M410" s="1" t="n">
         <v>0.04418</v>
       </c>
     </row>
@@ -16889,9 +18122,12 @@
         <v>27.25</v>
       </c>
       <c r="K411" s="1" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="L411" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="L411" s="1" t="n">
+      <c r="M411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -16929,9 +18165,12 @@
         <v>0.0351</v>
       </c>
       <c r="K412" s="1" t="n">
+        <v>0.03512</v>
+      </c>
+      <c r="L412" s="1" t="n">
         <v>0.03564</v>
       </c>
-      <c r="L412" s="1" t="n">
+      <c r="M412" s="1" t="n">
         <v>0.0351</v>
       </c>
     </row>
@@ -16969,10 +18208,13 @@
         <v>0.003405</v>
       </c>
       <c r="K413" s="1" t="n">
+        <v>0.003404</v>
+      </c>
+      <c r="L413" s="1" t="n">
         <v>0.003432</v>
       </c>
-      <c r="L413" s="1" t="n">
-        <v>0.003405</v>
+      <c r="M413" s="1" t="n">
+        <v>0.003404</v>
       </c>
     </row>
     <row r="414">
@@ -17009,9 +18251,12 @@
         <v>0.153</v>
       </c>
       <c r="K414" s="1" t="n">
+        <v>0.1533</v>
+      </c>
+      <c r="L414" s="1" t="n">
         <v>0.1538</v>
       </c>
-      <c r="L414" s="1" t="n">
+      <c r="M414" s="1" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -17049,9 +18294,12 @@
         <v>0.05263</v>
       </c>
       <c r="K415" s="1" t="n">
+        <v>0.0527</v>
+      </c>
+      <c r="L415" s="1" t="n">
         <v>0.05288</v>
       </c>
-      <c r="L415" s="1" t="n">
+      <c r="M415" s="1" t="n">
         <v>0.0525</v>
       </c>
     </row>
@@ -17089,9 +18337,12 @@
         <v>0.00658</v>
       </c>
       <c r="K416" s="1" t="n">
+        <v>0.00658</v>
+      </c>
+      <c r="L416" s="1" t="n">
         <v>0.00669</v>
       </c>
-      <c r="L416" s="1" t="n">
+      <c r="M416" s="1" t="n">
         <v>0.00658</v>
       </c>
     </row>
@@ -17129,10 +18380,13 @@
         <v>0.06052</v>
       </c>
       <c r="K417" s="1" t="n">
+        <v>0.06051</v>
+      </c>
+      <c r="L417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="L417" s="1" t="n">
-        <v>0.06052</v>
+      <c r="M417" s="1" t="n">
+        <v>0.06051</v>
       </c>
     </row>
     <row r="418">
@@ -17169,9 +18423,12 @@
         <v>0.008043</v>
       </c>
       <c r="K418" s="1" t="n">
+        <v>0.008054</v>
+      </c>
+      <c r="L418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="L418" s="1" t="n">
+      <c r="M418" s="1" t="n">
         <v>0.008043</v>
       </c>
     </row>
@@ -17209,9 +18466,12 @@
         <v>0.07435</v>
       </c>
       <c r="K419" s="1" t="n">
+        <v>0.07446</v>
+      </c>
+      <c r="L419" s="1" t="n">
         <v>0.07524</v>
       </c>
-      <c r="L419" s="1" t="n">
+      <c r="M419" s="1" t="n">
         <v>0.07435</v>
       </c>
     </row>
@@ -17249,9 +18509,12 @@
         <v>0.02123</v>
       </c>
       <c r="K420" s="1" t="n">
+        <v>0.02123</v>
+      </c>
+      <c r="L420" s="1" t="n">
         <v>0.02146</v>
       </c>
-      <c r="L420" s="1" t="n">
+      <c r="M420" s="1" t="n">
         <v>0.02105</v>
       </c>
     </row>
@@ -17289,9 +18552,12 @@
         <v>0.06987</v>
       </c>
       <c r="K421" s="1" t="n">
+        <v>0.06972</v>
+      </c>
+      <c r="L421" s="1" t="n">
         <v>0.07038999999999999</v>
       </c>
-      <c r="L421" s="1" t="n">
+      <c r="M421" s="1" t="n">
         <v>0.06938999999999999</v>
       </c>
     </row>
@@ -17329,9 +18595,12 @@
         <v>0.01487</v>
       </c>
       <c r="K422" s="1" t="n">
+        <v>0.01491</v>
+      </c>
+      <c r="L422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="L422" s="1" t="n">
+      <c r="M422" s="1" t="n">
         <v>0.01487</v>
       </c>
     </row>
@@ -17369,9 +18638,12 @@
         <v>0.006654</v>
       </c>
       <c r="K423" s="1" t="n">
+        <v>0.00666</v>
+      </c>
+      <c r="L423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="L423" s="1" t="n">
+      <c r="M423" s="1" t="n">
         <v>0.006648</v>
       </c>
     </row>
@@ -17409,9 +18681,12 @@
         <v>0.912</v>
       </c>
       <c r="K424" s="1" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="L424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="L424" s="1" t="n">
+      <c r="M424" s="1" t="n">
         <v>0.912</v>
       </c>
     </row>
@@ -17449,9 +18724,12 @@
         <v>0.03555</v>
       </c>
       <c r="K425" s="1" t="n">
+        <v>0.03565</v>
+      </c>
+      <c r="L425" s="1" t="n">
         <v>0.03596</v>
       </c>
-      <c r="L425" s="1" t="n">
+      <c r="M425" s="1" t="n">
         <v>0.03546</v>
       </c>
     </row>
@@ -17489,9 +18767,12 @@
         <v>1.803</v>
       </c>
       <c r="K426" s="1" t="n">
+        <v>1.801</v>
+      </c>
+      <c r="L426" s="1" t="n">
         <v>1.81</v>
       </c>
-      <c r="L426" s="1" t="n">
+      <c r="M426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -17529,9 +18810,12 @@
         <v>0.12775</v>
       </c>
       <c r="K427" s="1" t="n">
+        <v>0.12807</v>
+      </c>
+      <c r="L427" s="1" t="n">
         <v>0.12835</v>
       </c>
-      <c r="L427" s="1" t="n">
+      <c r="M427" s="1" t="n">
         <v>0.12736</v>
       </c>
     </row>
@@ -17569,9 +18853,12 @@
         <v>0.05336</v>
       </c>
       <c r="K428" s="1" t="n">
+        <v>0.05334</v>
+      </c>
+      <c r="L428" s="1" t="n">
         <v>0.05362</v>
       </c>
-      <c r="L428" s="1" t="n">
+      <c r="M428" s="1" t="n">
         <v>0.05297</v>
       </c>
     </row>
@@ -17609,9 +18896,12 @@
         <v>1.293</v>
       </c>
       <c r="K429" s="1" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="L429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="L429" s="1" t="n">
+      <c r="M429" s="1" t="n">
         <v>1.289</v>
       </c>
     </row>
@@ -17649,9 +18939,12 @@
         <v>0.07506</v>
       </c>
       <c r="K430" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="L430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="L430" s="1" t="n">
+      <c r="M430" s="1" t="n">
         <v>0.07482</v>
       </c>
     </row>
@@ -17689,10 +18982,13 @@
         <v>0.1585</v>
       </c>
       <c r="K431" s="1" t="n">
+        <v>0.1583</v>
+      </c>
+      <c r="L431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="L431" s="1" t="n">
-        <v>0.1585</v>
+      <c r="M431" s="1" t="n">
+        <v>0.1583</v>
       </c>
     </row>
     <row r="432">
@@ -17729,9 +19025,12 @@
         <v>1.45</v>
       </c>
       <c r="K432" s="1" t="n">
+        <v>1.452</v>
+      </c>
+      <c r="L432" s="1" t="n">
         <v>1.461</v>
       </c>
-      <c r="L432" s="1" t="n">
+      <c r="M432" s="1" t="n">
         <v>1.445</v>
       </c>
     </row>
@@ -17769,9 +19068,12 @@
         <v>3.272</v>
       </c>
       <c r="K433" s="1" t="n">
+        <v>3.284</v>
+      </c>
+      <c r="L433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="L433" s="1" t="n">
+      <c r="M433" s="1" t="n">
         <v>3.266</v>
       </c>
     </row>
@@ -17809,9 +19111,12 @@
         <v>0.1787</v>
       </c>
       <c r="K434" s="1" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="L434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="L434" s="1" t="n">
+      <c r="M434" s="1" t="n">
         <v>0.1783</v>
       </c>
     </row>
@@ -17849,9 +19154,12 @@
         <v>0.008595999999999999</v>
       </c>
       <c r="K435" s="1" t="n">
+        <v>0.008607</v>
+      </c>
+      <c r="L435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="L435" s="1" t="n">
+      <c r="M435" s="1" t="n">
         <v>0.008580000000000001</v>
       </c>
     </row>
@@ -17889,9 +19197,12 @@
         <v>0.2818</v>
       </c>
       <c r="K436" s="1" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="L436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="L436" s="1" t="n">
+      <c r="M436" s="1" t="n">
         <v>0.2818</v>
       </c>
     </row>
@@ -17929,9 +19240,12 @@
         <v>0.03881</v>
       </c>
       <c r="K437" s="1" t="n">
-        <v>0.03906</v>
+        <v>0.03957</v>
       </c>
       <c r="L437" s="1" t="n">
+        <v>0.03957</v>
+      </c>
+      <c r="M437" s="1" t="n">
         <v>0.03814</v>
       </c>
     </row>
@@ -17969,9 +19283,12 @@
         <v>0.02422</v>
       </c>
       <c r="K438" s="1" t="n">
+        <v>0.02431</v>
+      </c>
+      <c r="L438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="L438" s="1" t="n">
+      <c r="M438" s="1" t="n">
         <v>0.0242</v>
       </c>
     </row>
@@ -18009,9 +19326,12 @@
         <v>0.04406</v>
       </c>
       <c r="K439" s="1" t="n">
+        <v>0.04413</v>
+      </c>
+      <c r="L439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="L439" s="1" t="n">
+      <c r="M439" s="1" t="n">
         <v>0.04405</v>
       </c>
     </row>
@@ -18049,9 +19369,12 @@
         <v>0.0005188</v>
       </c>
       <c r="K440" s="1" t="n">
+        <v>0.0005212</v>
+      </c>
+      <c r="L440" s="1" t="n">
         <v>0.0005258</v>
       </c>
-      <c r="L440" s="1" t="n">
+      <c r="M440" s="1" t="n">
         <v>0.0005188</v>
       </c>
     </row>
@@ -18089,9 +19412,12 @@
         <v>0.04489</v>
       </c>
       <c r="K441" s="1" t="n">
+        <v>0.04449</v>
+      </c>
+      <c r="L441" s="1" t="n">
         <v>0.04489</v>
       </c>
-      <c r="L441" s="1" t="n">
+      <c r="M441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -18129,9 +19455,12 @@
         <v>0.000411</v>
       </c>
       <c r="K442" s="1" t="n">
+        <v>0.000413</v>
+      </c>
+      <c r="L442" s="1" t="n">
         <v>0.000416</v>
       </c>
-      <c r="L442" s="1" t="n">
+      <c r="M442" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -18169,10 +19498,13 @@
         <v>0.09513000000000001</v>
       </c>
       <c r="K443" s="1" t="n">
+        <v>0.0949</v>
+      </c>
+      <c r="L443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="L443" s="1" t="n">
-        <v>0.09513000000000001</v>
+      <c r="M443" s="1" t="n">
+        <v>0.0949</v>
       </c>
     </row>
     <row r="444">
@@ -18209,9 +19541,12 @@
         <v>2.298</v>
       </c>
       <c r="K444" s="1" t="n">
+        <v>2.302</v>
+      </c>
+      <c r="L444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="L444" s="1" t="n">
+      <c r="M444" s="1" t="n">
         <v>2.289</v>
       </c>
     </row>
@@ -18249,9 +19584,12 @@
         <v>0.2686</v>
       </c>
       <c r="K445" s="1" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="L445" s="1" t="n">
         <v>0.2741</v>
       </c>
-      <c r="L445" s="1" t="n">
+      <c r="M445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -18289,9 +19627,12 @@
         <v>0.0007415</v>
       </c>
       <c r="K446" s="1" t="n">
+        <v>0.0007457</v>
+      </c>
+      <c r="L446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="L446" s="1" t="n">
+      <c r="M446" s="1" t="n">
         <v>0.0007415</v>
       </c>
     </row>
@@ -18329,9 +19670,12 @@
         <v>0.03821</v>
       </c>
       <c r="K447" s="1" t="n">
+        <v>0.03835</v>
+      </c>
+      <c r="L447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="L447" s="1" t="n">
+      <c r="M447" s="1" t="n">
         <v>0.03821</v>
       </c>
     </row>
@@ -18369,9 +19713,12 @@
         <v>0.177</v>
       </c>
       <c r="K448" s="1" t="n">
-        <v>0.1773</v>
+        <v>0.1782</v>
       </c>
       <c r="L448" s="1" t="n">
+        <v>0.1782</v>
+      </c>
+      <c r="M448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -18409,9 +19756,12 @@
         <v>0.04263</v>
       </c>
       <c r="K449" s="1" t="n">
+        <v>0.04275</v>
+      </c>
+      <c r="L449" s="1" t="n">
         <v>0.04301</v>
       </c>
-      <c r="L449" s="1" t="n">
+      <c r="M449" s="1" t="n">
         <v>0.0426</v>
       </c>
     </row>
@@ -18449,9 +19799,12 @@
         <v>0.0001635</v>
       </c>
       <c r="K450" s="1" t="n">
+        <v>0.0001643</v>
+      </c>
+      <c r="L450" s="1" t="n">
         <v>0.0001654</v>
       </c>
-      <c r="L450" s="1" t="n">
+      <c r="M450" s="1" t="n">
         <v>0.0001632</v>
       </c>
     </row>
@@ -18489,9 +19842,12 @@
         <v>0.0375</v>
       </c>
       <c r="K451" s="1" t="n">
+        <v>0.03747</v>
+      </c>
+      <c r="L451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="L451" s="1" t="n">
+      <c r="M451" s="1" t="n">
         <v>0.03745</v>
       </c>
     </row>
@@ -18529,9 +19885,12 @@
         <v>0.00978</v>
       </c>
       <c r="K452" s="1" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="L452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="L452" s="1" t="n">
+      <c r="M452" s="1" t="n">
         <v>0.00976</v>
       </c>
     </row>
@@ -18569,9 +19928,12 @@
         <v>0.06794</v>
       </c>
       <c r="K453" s="1" t="n">
+        <v>0.06798</v>
+      </c>
+      <c r="L453" s="1" t="n">
         <v>0.06816</v>
       </c>
-      <c r="L453" s="1" t="n">
+      <c r="M453" s="1" t="n">
         <v>0.06782000000000001</v>
       </c>
     </row>
@@ -18609,9 +19971,12 @@
         <v>0.007494</v>
       </c>
       <c r="K454" s="1" t="n">
+        <v>0.007515</v>
+      </c>
+      <c r="L454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="L454" s="1" t="n">
+      <c r="M454" s="1" t="n">
         <v>0.007494</v>
       </c>
     </row>
@@ -18649,10 +20014,13 @@
         <v>0.003307</v>
       </c>
       <c r="K455" s="1" t="n">
+        <v>0.003302</v>
+      </c>
+      <c r="L455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="L455" s="1" t="n">
-        <v>0.003307</v>
+      <c r="M455" s="1" t="n">
+        <v>0.003302</v>
       </c>
     </row>
     <row r="456">
@@ -18689,9 +20057,12 @@
         <v>0.001842</v>
       </c>
       <c r="K456" s="1" t="n">
+        <v>0.001849</v>
+      </c>
+      <c r="L456" s="1" t="n">
         <v>0.001875</v>
       </c>
-      <c r="L456" s="1" t="n">
+      <c r="M456" s="1" t="n">
         <v>0.001842</v>
       </c>
     </row>
@@ -18729,9 +20100,12 @@
         <v>0.000175</v>
       </c>
       <c r="K457" s="1" t="n">
+        <v>0.0001756</v>
+      </c>
+      <c r="L457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="L457" s="1" t="n">
+      <c r="M457" s="1" t="n">
         <v>0.0001745</v>
       </c>
     </row>
@@ -18769,9 +20143,12 @@
         <v>0.0003879</v>
       </c>
       <c r="K458" s="1" t="n">
+        <v>0.0003906</v>
+      </c>
+      <c r="L458" s="1" t="n">
         <v>0.0003916</v>
       </c>
-      <c r="L458" s="1" t="n">
+      <c r="M458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -18809,9 +20186,12 @@
         <v>0.01401</v>
       </c>
       <c r="K459" s="1" t="n">
+        <v>0.01393</v>
+      </c>
+      <c r="L459" s="1" t="n">
         <v>0.01413</v>
       </c>
-      <c r="L459" s="1" t="n">
+      <c r="M459" s="1" t="n">
         <v>0.01391</v>
       </c>
     </row>
@@ -18849,9 +20229,12 @@
         <v>0.04538</v>
       </c>
       <c r="K460" s="1" t="n">
-        <v>0.04559</v>
+        <v>0.04578</v>
       </c>
       <c r="L460" s="1" t="n">
+        <v>0.04578</v>
+      </c>
+      <c r="M460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -18889,9 +20272,12 @@
         <v>0.2812</v>
       </c>
       <c r="K461" s="1" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="L461" s="1" t="n">
         <v>0.2839</v>
       </c>
-      <c r="L461" s="1" t="n">
+      <c r="M461" s="1" t="n">
         <v>0.2809</v>
       </c>
     </row>
@@ -18929,9 +20315,12 @@
         <v>0.006236</v>
       </c>
       <c r="K462" s="1" t="n">
+        <v>0.006272</v>
+      </c>
+      <c r="L462" s="1" t="n">
         <v>0.006312</v>
       </c>
-      <c r="L462" s="1" t="n">
+      <c r="M462" s="1" t="n">
         <v>0.00622</v>
       </c>
     </row>
@@ -18969,9 +20358,12 @@
         <v>0.007036</v>
       </c>
       <c r="K463" s="1" t="n">
+        <v>0.007061</v>
+      </c>
+      <c r="L463" s="1" t="n">
         <v>0.007088</v>
       </c>
-      <c r="L463" s="1" t="n">
+      <c r="M463" s="1" t="n">
         <v>0.007032</v>
       </c>
     </row>
@@ -19009,9 +20401,12 @@
         <v>0.2877</v>
       </c>
       <c r="K464" s="1" t="n">
-        <v>0.288</v>
+        <v>0.2884</v>
       </c>
       <c r="L464" s="1" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="M464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -19049,9 +20444,12 @@
         <v>0.08076999999999999</v>
       </c>
       <c r="K465" s="1" t="n">
+        <v>0.08096</v>
+      </c>
+      <c r="L465" s="1" t="n">
         <v>0.08183</v>
       </c>
-      <c r="L465" s="1" t="n">
+      <c r="M465" s="1" t="n">
         <v>0.08076</v>
       </c>
     </row>
@@ -19089,9 +20487,12 @@
         <v>0.6343</v>
       </c>
       <c r="K466" s="1" t="n">
+        <v>0.6363</v>
+      </c>
+      <c r="L466" s="1" t="n">
         <v>0.6368</v>
       </c>
-      <c r="L466" s="1" t="n">
+      <c r="M466" s="1" t="n">
         <v>0.6318</v>
       </c>
     </row>
@@ -19129,9 +20530,12 @@
         <v>0.01478</v>
       </c>
       <c r="K467" s="1" t="n">
+        <v>0.01483</v>
+      </c>
+      <c r="L467" s="1" t="n">
         <v>0.01499</v>
       </c>
-      <c r="L467" s="1" t="n">
+      <c r="M467" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -19169,9 +20573,12 @@
         <v>0.03434</v>
       </c>
       <c r="K468" s="1" t="n">
+        <v>0.03442</v>
+      </c>
+      <c r="L468" s="1" t="n">
         <v>0.03468</v>
       </c>
-      <c r="L468" s="1" t="n">
+      <c r="M468" s="1" t="n">
         <v>0.03434</v>
       </c>
     </row>
@@ -19209,9 +20616,12 @@
         <v>0.1626</v>
       </c>
       <c r="K469" s="1" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="L469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="L469" s="1" t="n">
+      <c r="M469" s="1" t="n">
         <v>0.1624</v>
       </c>
     </row>
@@ -19249,9 +20659,12 @@
         <v>0.4085</v>
       </c>
       <c r="K470" s="1" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L470" s="1" t="n">
         <v>0.4151</v>
       </c>
-      <c r="L470" s="1" t="n">
+      <c r="M470" s="1" t="n">
         <v>0.4085</v>
       </c>
     </row>
@@ -19289,9 +20702,12 @@
         <v>0.06934999999999999</v>
       </c>
       <c r="K471" s="1" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="L471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="L471" s="1" t="n">
+      <c r="M471" s="1" t="n">
         <v>0.06934999999999999</v>
       </c>
     </row>
@@ -19329,9 +20745,12 @@
         <v>0.06623999999999999</v>
       </c>
       <c r="K472" s="1" t="n">
+        <v>0.06653000000000001</v>
+      </c>
+      <c r="L472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="L472" s="1" t="n">
+      <c r="M472" s="1" t="n">
         <v>0.06623999999999999</v>
       </c>
     </row>
@@ -19369,9 +20788,12 @@
         <v>0.01621</v>
       </c>
       <c r="K473" s="1" t="n">
+        <v>0.01624</v>
+      </c>
+      <c r="L473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="L473" s="1" t="n">
+      <c r="M473" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -19409,10 +20831,13 @@
         <v>0.2069</v>
       </c>
       <c r="K474" s="1" t="n">
+        <v>0.2061</v>
+      </c>
+      <c r="L474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="L474" s="1" t="n">
-        <v>0.2066</v>
+      <c r="M474" s="1" t="n">
+        <v>0.2061</v>
       </c>
     </row>
     <row r="475">
@@ -19449,9 +20874,12 @@
         <v>0.042</v>
       </c>
       <c r="K475" s="1" t="n">
+        <v>0.04222</v>
+      </c>
+      <c r="L475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="L475" s="1" t="n">
+      <c r="M475" s="1" t="n">
         <v>0.042</v>
       </c>
     </row>
@@ -19489,9 +20917,12 @@
         <v>1.561</v>
       </c>
       <c r="K476" s="1" t="n">
+        <v>1.563</v>
+      </c>
+      <c r="L476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="L476" s="1" t="n">
+      <c r="M476" s="1" t="n">
         <v>1.561</v>
       </c>
     </row>
@@ -19529,9 +20960,12 @@
         <v>0.1003</v>
       </c>
       <c r="K477" s="1" t="n">
+        <v>0.1007</v>
+      </c>
+      <c r="L477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="L477" s="1" t="n">
+      <c r="M477" s="1" t="n">
         <v>0.1003</v>
       </c>
     </row>
@@ -19569,9 +21003,12 @@
         <v>0.001152</v>
       </c>
       <c r="K478" s="1" t="n">
+        <v>0.001154</v>
+      </c>
+      <c r="L478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="L478" s="1" t="n">
+      <c r="M478" s="1" t="n">
         <v>0.00115</v>
       </c>
     </row>
@@ -19609,10 +21046,13 @@
         <v>0.1457</v>
       </c>
       <c r="K479" s="1" t="n">
+        <v>0.1447</v>
+      </c>
+      <c r="L479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="L479" s="1" t="n">
-        <v>0.1457</v>
+      <c r="M479" s="1" t="n">
+        <v>0.1447</v>
       </c>
     </row>
     <row r="480">
@@ -19649,9 +21089,12 @@
         <v>0.001722</v>
       </c>
       <c r="K480" s="1" t="n">
+        <v>0.001732</v>
+      </c>
+      <c r="L480" s="1" t="n">
         <v>0.001734</v>
       </c>
-      <c r="L480" s="1" t="n">
+      <c r="M480" s="1" t="n">
         <v>0.001719</v>
       </c>
     </row>
@@ -19689,9 +21132,12 @@
         <v>0.908</v>
       </c>
       <c r="K481" s="1" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="L481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="L481" s="1" t="n">
+      <c r="M481" s="1" t="n">
         <v>0.908</v>
       </c>
     </row>
@@ -19729,9 +21175,12 @@
         <v>0.13374</v>
       </c>
       <c r="K482" s="1" t="n">
+        <v>0.13342</v>
+      </c>
+      <c r="L482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="L482" s="1" t="n">
+      <c r="M482" s="1" t="n">
         <v>0.13336</v>
       </c>
     </row>
@@ -19769,9 +21218,12 @@
         <v>0.04023</v>
       </c>
       <c r="K483" s="1" t="n">
+        <v>0.04031</v>
+      </c>
+      <c r="L483" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="L483" s="1" t="n">
+      <c r="M483" s="1" t="n">
         <v>0.04023</v>
       </c>
     </row>
@@ -19809,9 +21261,12 @@
         <v>0.301</v>
       </c>
       <c r="K484" s="1" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="L484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="L484" s="1" t="n">
+      <c r="M484" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -19849,9 +21304,12 @@
         <v>0.05603</v>
       </c>
       <c r="K485" s="1" t="n">
+        <v>0.05637</v>
+      </c>
+      <c r="L485" s="1" t="n">
         <v>0.05709</v>
       </c>
-      <c r="L485" s="1" t="n">
+      <c r="M485" s="1" t="n">
         <v>0.05603</v>
       </c>
     </row>
@@ -19889,9 +21347,12 @@
         <v>0.001568</v>
       </c>
       <c r="K486" s="1" t="n">
+        <v>0.001569</v>
+      </c>
+      <c r="L486" s="1" t="n">
         <v>0.001579</v>
       </c>
-      <c r="L486" s="1" t="n">
+      <c r="M486" s="1" t="n">
         <v>0.001564</v>
       </c>
     </row>
@@ -19929,9 +21390,12 @@
         <v>0.06702</v>
       </c>
       <c r="K487" s="1" t="n">
+        <v>0.06723999999999999</v>
+      </c>
+      <c r="L487" s="1" t="n">
         <v>0.06766999999999999</v>
       </c>
-      <c r="L487" s="1" t="n">
+      <c r="M487" s="1" t="n">
         <v>0.06702</v>
       </c>
     </row>
@@ -19969,9 +21433,12 @@
         <v>0.1932</v>
       </c>
       <c r="K488" s="1" t="n">
+        <v>0.1935</v>
+      </c>
+      <c r="L488" s="1" t="n">
         <v>0.1953</v>
       </c>
-      <c r="L488" s="1" t="n">
+      <c r="M488" s="1" t="n">
         <v>0.1929</v>
       </c>
     </row>
@@ -20009,9 +21476,12 @@
         <v>0.04797</v>
       </c>
       <c r="K489" s="1" t="n">
+        <v>0.04803</v>
+      </c>
+      <c r="L489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="L489" s="1" t="n">
+      <c r="M489" s="1" t="n">
         <v>0.04779</v>
       </c>
     </row>
@@ -20049,9 +21519,12 @@
         <v>0.1393</v>
       </c>
       <c r="K490" s="1" t="n">
+        <v>0.1396</v>
+      </c>
+      <c r="L490" s="1" t="n">
         <v>0.1401</v>
       </c>
-      <c r="L490" s="1" t="n">
+      <c r="M490" s="1" t="n">
         <v>0.1389</v>
       </c>
     </row>
@@ -20089,9 +21562,12 @@
         <v>0.02252</v>
       </c>
       <c r="K491" s="1" t="n">
+        <v>0.02253</v>
+      </c>
+      <c r="L491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="L491" s="1" t="n">
+      <c r="M491" s="1" t="n">
         <v>0.02243</v>
       </c>
     </row>
@@ -20129,9 +21605,12 @@
         <v>0.007746</v>
       </c>
       <c r="K492" s="1" t="n">
+        <v>0.007776</v>
+      </c>
+      <c r="L492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="L492" s="1" t="n">
+      <c r="M492" s="1" t="n">
         <v>0.007746</v>
       </c>
     </row>
@@ -20169,10 +21648,13 @@
         <v>0.0005947</v>
       </c>
       <c r="K493" s="1" t="n">
+        <v>0.000593</v>
+      </c>
+      <c r="L493" s="1" t="n">
         <v>0.0005992</v>
       </c>
-      <c r="L493" s="1" t="n">
-        <v>0.0005932</v>
+      <c r="M493" s="1" t="n">
+        <v>0.000593</v>
       </c>
     </row>
     <row r="494">
@@ -20209,9 +21691,12 @@
         <v>3.017</v>
       </c>
       <c r="K494" s="1" t="n">
+        <v>3.026</v>
+      </c>
+      <c r="L494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="L494" s="1" t="n">
+      <c r="M494" s="1" t="n">
         <v>2.999</v>
       </c>
     </row>
@@ -20249,9 +21734,12 @@
         <v>0.05056</v>
       </c>
       <c r="K495" s="1" t="n">
+        <v>0.0507</v>
+      </c>
+      <c r="L495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="L495" s="1" t="n">
+      <c r="M495" s="1" t="n">
         <v>0.05042</v>
       </c>
     </row>
@@ -20289,9 +21777,12 @@
         <v>0.006742</v>
       </c>
       <c r="K496" s="1" t="n">
+        <v>0.006772</v>
+      </c>
+      <c r="L496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="L496" s="1" t="n">
+      <c r="M496" s="1" t="n">
         <v>0.006742</v>
       </c>
     </row>
@@ -20329,9 +21820,12 @@
         <v>1.301</v>
       </c>
       <c r="K497" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L497" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="L497" s="1" t="n">
+      <c r="M497" s="1" t="n">
         <v>1.299</v>
       </c>
     </row>
@@ -20369,9 +21863,12 @@
         <v>0.03892</v>
       </c>
       <c r="K498" s="1" t="n">
+        <v>0.03948</v>
+      </c>
+      <c r="L498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="L498" s="1" t="n">
+      <c r="M498" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -20409,9 +21906,12 @@
         <v>0.04101</v>
       </c>
       <c r="K499" s="1" t="n">
+        <v>0.04138</v>
+      </c>
+      <c r="L499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="L499" s="1" t="n">
+      <c r="M499" s="1" t="n">
         <v>0.04101</v>
       </c>
     </row>
@@ -20449,9 +21949,12 @@
         <v>0.00545</v>
       </c>
       <c r="K500" s="1" t="n">
+        <v>0.00545</v>
+      </c>
+      <c r="L500" s="1" t="n">
         <v>0.00549</v>
       </c>
-      <c r="L500" s="1" t="n">
+      <c r="M500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -20489,9 +21992,12 @@
         <v>0.03571</v>
       </c>
       <c r="K501" s="1" t="n">
+        <v>0.03575</v>
+      </c>
+      <c r="L501" s="1" t="n">
         <v>0.0364</v>
       </c>
-      <c r="L501" s="1" t="n">
+      <c r="M501" s="1" t="n">
         <v>0.03571</v>
       </c>
     </row>
@@ -20529,10 +22035,13 @@
         <v>0.07244</v>
       </c>
       <c r="K502" s="1" t="n">
+        <v>0.07240000000000001</v>
+      </c>
+      <c r="L502" s="1" t="n">
         <v>0.07342</v>
       </c>
-      <c r="L502" s="1" t="n">
-        <v>0.07244</v>
+      <c r="M502" s="1" t="n">
+        <v>0.07240000000000001</v>
       </c>
     </row>
     <row r="503">
@@ -20569,9 +22078,12 @@
         <v>0.0007432</v>
       </c>
       <c r="K503" s="1" t="n">
+        <v>0.0007496</v>
+      </c>
+      <c r="L503" s="1" t="n">
         <v>0.000755</v>
       </c>
-      <c r="L503" s="1" t="n">
+      <c r="M503" s="1" t="n">
         <v>0.0007422</v>
       </c>
     </row>
@@ -20609,9 +22121,12 @@
         <v>0.015962</v>
       </c>
       <c r="K504" s="1" t="n">
+        <v>0.015986</v>
+      </c>
+      <c r="L504" s="1" t="n">
         <v>0.016003</v>
       </c>
-      <c r="L504" s="1" t="n">
+      <c r="M504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -20649,9 +22164,12 @@
         <v>0.00703</v>
       </c>
       <c r="K505" s="1" t="n">
+        <v>0.00704</v>
+      </c>
+      <c r="L505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="L505" s="1" t="n">
+      <c r="M505" s="1" t="n">
         <v>0.00703</v>
       </c>
     </row>
@@ -20689,9 +22207,12 @@
         <v>0.0255</v>
       </c>
       <c r="K506" s="1" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="L506" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="L506" s="1" t="n">
+      <c r="M506" s="1" t="n">
         <v>0.0255</v>
       </c>
     </row>
@@ -20729,9 +22250,12 @@
         <v>0.001359</v>
       </c>
       <c r="K507" s="1" t="n">
-        <v>0.001359</v>
+        <v>0.00136</v>
       </c>
       <c r="L507" s="1" t="n">
+        <v>0.00136</v>
+      </c>
+      <c r="M507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -20769,9 +22293,12 @@
         <v>0.2806</v>
       </c>
       <c r="K508" s="1" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="L508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="L508" s="1" t="n">
+      <c r="M508" s="1" t="n">
         <v>0.2805</v>
       </c>
     </row>
@@ -20809,9 +22336,12 @@
         <v>0.1319</v>
       </c>
       <c r="K509" s="1" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="L509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="L509" s="1" t="n">
+      <c r="M509" s="1" t="n">
         <v>0.1317</v>
       </c>
     </row>
@@ -20849,9 +22379,12 @@
         <v>0.04903</v>
       </c>
       <c r="K510" s="1" t="n">
+        <v>0.04927</v>
+      </c>
+      <c r="L510" s="1" t="n">
         <v>0.04972</v>
       </c>
-      <c r="L510" s="1" t="n">
+      <c r="M510" s="1" t="n">
         <v>0.04896</v>
       </c>
     </row>
@@ -20889,9 +22422,12 @@
         <v>0.00273</v>
       </c>
       <c r="K511" s="1" t="n">
+        <v>0.00273</v>
+      </c>
+      <c r="L511" s="1" t="n">
         <v>0.00278</v>
       </c>
-      <c r="L511" s="1" t="n">
+      <c r="M511" s="1" t="n">
         <v>0.00273</v>
       </c>
     </row>
@@ -20929,9 +22465,12 @@
         <v>0.015293</v>
       </c>
       <c r="K512" s="1" t="n">
+        <v>0.015301</v>
+      </c>
+      <c r="L512" s="1" t="n">
         <v>0.015454</v>
       </c>
-      <c r="L512" s="1" t="n">
+      <c r="M512" s="1" t="n">
         <v>0.015285</v>
       </c>
     </row>
@@ -20969,9 +22508,12 @@
         <v>0.6899</v>
       </c>
       <c r="K513" s="1" t="n">
+        <v>0.6927</v>
+      </c>
+      <c r="L513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="L513" s="1" t="n">
+      <c r="M513" s="1" t="n">
         <v>0.6899</v>
       </c>
     </row>
@@ -21009,9 +22551,12 @@
         <v>0.004517</v>
       </c>
       <c r="K514" s="1" t="n">
+        <v>0.00452</v>
+      </c>
+      <c r="L514" s="1" t="n">
         <v>0.004589</v>
       </c>
-      <c r="L514" s="1" t="n">
+      <c r="M514" s="1" t="n">
         <v>0.004517</v>
       </c>
     </row>
@@ -21049,9 +22594,12 @@
         <v>0.005016</v>
       </c>
       <c r="K515" s="1" t="n">
+        <v>0.00503</v>
+      </c>
+      <c r="L515" s="1" t="n">
         <v>0.005066</v>
       </c>
-      <c r="L515" s="1" t="n">
+      <c r="M515" s="1" t="n">
         <v>0.005008</v>
       </c>
     </row>
@@ -21089,9 +22637,12 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="K516" s="1" t="n">
+        <v>0.06338000000000001</v>
+      </c>
+      <c r="L516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="L516" s="1" t="n">
+      <c r="M516" s="1" t="n">
         <v>0.06320000000000001</v>
       </c>
     </row>
@@ -21129,9 +22680,12 @@
         <v>0.06485</v>
       </c>
       <c r="K517" s="1" t="n">
+        <v>0.06533</v>
+      </c>
+      <c r="L517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="L517" s="1" t="n">
+      <c r="M517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -21169,9 +22723,12 @@
         <v>0.01202</v>
       </c>
       <c r="K518" s="1" t="n">
+        <v>0.01207</v>
+      </c>
+      <c r="L518" s="1" t="n">
         <v>0.01219</v>
       </c>
-      <c r="L518" s="1" t="n">
+      <c r="M518" s="1" t="n">
         <v>0.01199</v>
       </c>
     </row>
@@ -21209,9 +22766,12 @@
         <v>0.04759</v>
       </c>
       <c r="K519" s="1" t="n">
+        <v>0.04779</v>
+      </c>
+      <c r="L519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="L519" s="1" t="n">
+      <c r="M519" s="1" t="n">
         <v>0.04743</v>
       </c>
     </row>
@@ -21249,9 +22809,12 @@
         <v>0.04365</v>
       </c>
       <c r="K520" s="1" t="n">
+        <v>0.04365</v>
+      </c>
+      <c r="L520" s="1" t="n">
         <v>0.04411</v>
       </c>
-      <c r="L520" s="1" t="n">
+      <c r="M520" s="1" t="n">
         <v>0.04349</v>
       </c>
     </row>
@@ -21289,9 +22852,12 @@
         <v>0.008411999999999999</v>
       </c>
       <c r="K521" s="1" t="n">
+        <v>0.008448000000000001</v>
+      </c>
+      <c r="L521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="L521" s="1" t="n">
+      <c r="M521" s="1" t="n">
         <v>0.008411999999999999</v>
       </c>
     </row>
@@ -21329,10 +22895,13 @@
         <v>0.08819</v>
       </c>
       <c r="K522" s="1" t="n">
+        <v>0.08791</v>
+      </c>
+      <c r="L522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="L522" s="1" t="n">
-        <v>0.08819</v>
+      <c r="M522" s="1" t="n">
+        <v>0.08791</v>
       </c>
     </row>
     <row r="523">
@@ -21369,9 +22938,12 @@
         <v>0.006439</v>
       </c>
       <c r="K523" s="1" t="n">
+        <v>0.006451</v>
+      </c>
+      <c r="L523" s="1" t="n">
         <v>0.006492</v>
       </c>
-      <c r="L523" s="1" t="n">
+      <c r="M523" s="1" t="n">
         <v>0.006433</v>
       </c>
     </row>
@@ -21409,9 +22981,12 @@
         <v>0.01644</v>
       </c>
       <c r="K524" s="1" t="n">
+        <v>0.01646</v>
+      </c>
+      <c r="L524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="L524" s="1" t="n">
+      <c r="M524" s="1" t="n">
         <v>0.01644</v>
       </c>
     </row>
@@ -21449,9 +23024,12 @@
         <v>0.01779</v>
       </c>
       <c r="K525" s="1" t="n">
+        <v>0.01786</v>
+      </c>
+      <c r="L525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="L525" s="1" t="n">
+      <c r="M525" s="1" t="n">
         <v>0.01779</v>
       </c>
     </row>
@@ -21489,9 +23067,12 @@
         <v>0.07919</v>
       </c>
       <c r="K526" s="1" t="n">
+        <v>0.07951</v>
+      </c>
+      <c r="L526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="L526" s="1" t="n">
+      <c r="M526" s="1" t="n">
         <v>0.07883</v>
       </c>
     </row>
@@ -21529,9 +23110,12 @@
         <v>0.01606</v>
       </c>
       <c r="K527" s="1" t="n">
+        <v>0.01612</v>
+      </c>
+      <c r="L527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="L527" s="1" t="n">
+      <c r="M527" s="1" t="n">
         <v>0.01606</v>
       </c>
     </row>
@@ -21569,9 +23153,12 @@
         <v>0.00419</v>
       </c>
       <c r="K528" s="1" t="n">
+        <v>0.00417</v>
+      </c>
+      <c r="L528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="L528" s="1" t="n">
+      <c r="M528" s="1" t="n">
         <v>0.004164</v>
       </c>
     </row>
@@ -21609,9 +23196,12 @@
         <v>0.00369</v>
       </c>
       <c r="K529" s="1" t="n">
+        <v>0.003714</v>
+      </c>
+      <c r="L529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="L529" s="1" t="n">
+      <c r="M529" s="1" t="n">
         <v>0.00369</v>
       </c>
     </row>
@@ -21649,9 +23239,12 @@
         <v>1.316</v>
       </c>
       <c r="K530" s="1" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="L530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="L530" s="1" t="n">
+      <c r="M530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -21689,9 +23282,12 @@
         <v>0.4893</v>
       </c>
       <c r="K531" s="1" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="L531" s="1" t="n">
         <v>0.494</v>
       </c>
-      <c r="L531" s="1" t="n">
+      <c r="M531" s="1" t="n">
         <v>0.4893</v>
       </c>
     </row>
@@ -21729,9 +23325,12 @@
         <v>0.03065</v>
       </c>
       <c r="K532" s="1" t="n">
+        <v>0.03069</v>
+      </c>
+      <c r="L532" s="1" t="n">
         <v>0.03091</v>
       </c>
-      <c r="L532" s="1" t="n">
+      <c r="M532" s="1" t="n">
         <v>0.03058</v>
       </c>
     </row>
@@ -21769,9 +23368,12 @@
         <v>0.1531</v>
       </c>
       <c r="K533" s="1" t="n">
+        <v>0.1533</v>
+      </c>
+      <c r="L533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="L533" s="1" t="n">
+      <c r="M533" s="1" t="n">
         <v>0.153</v>
       </c>
     </row>
@@ -21809,9 +23411,12 @@
         <v>0.0536</v>
       </c>
       <c r="K534" s="1" t="n">
+        <v>0.05405</v>
+      </c>
+      <c r="L534" s="1" t="n">
         <v>0.05424</v>
       </c>
-      <c r="L534" s="1" t="n">
+      <c r="M534" s="1" t="n">
         <v>0.0536</v>
       </c>
     </row>
@@ -21849,10 +23454,13 @@
         <v>0.01501</v>
       </c>
       <c r="K535" s="1" t="n">
+        <v>0.01494</v>
+      </c>
+      <c r="L535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="L535" s="1" t="n">
-        <v>0.01498</v>
+      <c r="M535" s="1" t="n">
+        <v>0.01494</v>
       </c>
     </row>
     <row r="536">
@@ -21889,9 +23497,12 @@
         <v>0.05823</v>
       </c>
       <c r="K536" s="1" t="n">
-        <v>0.05879</v>
+        <v>0.05893</v>
       </c>
       <c r="L536" s="1" t="n">
+        <v>0.05893</v>
+      </c>
+      <c r="M536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -21929,9 +23540,12 @@
         <v>0.05487</v>
       </c>
       <c r="K537" s="1" t="n">
+        <v>0.05496</v>
+      </c>
+      <c r="L537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="L537" s="1" t="n">
+      <c r="M537" s="1" t="n">
         <v>0.05481</v>
       </c>
     </row>
@@ -21969,9 +23583,12 @@
         <v>0.1059</v>
       </c>
       <c r="K538" s="1" t="n">
+        <v>0.1062</v>
+      </c>
+      <c r="L538" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="L538" s="1" t="n">
+      <c r="M538" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -22009,9 +23626,12 @@
         <v>0.0128</v>
       </c>
       <c r="K539" s="1" t="n">
+        <v>0.01278</v>
+      </c>
+      <c r="L539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="L539" s="1" t="n">
+      <c r="M539" s="1" t="n">
         <v>0.01278</v>
       </c>
     </row>
@@ -22049,9 +23669,12 @@
         <v>0.1742</v>
       </c>
       <c r="K540" s="1" t="n">
+        <v>0.1746</v>
+      </c>
+      <c r="L540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="L540" s="1" t="n">
+      <c r="M540" s="1" t="n">
         <v>0.174</v>
       </c>
     </row>
@@ -22089,9 +23712,12 @@
         <v>0.1227</v>
       </c>
       <c r="K541" s="1" t="n">
+        <v>0.1228</v>
+      </c>
+      <c r="L541" s="1" t="n">
         <v>0.1239</v>
       </c>
-      <c r="L541" s="1" t="n">
+      <c r="M541" s="1" t="n">
         <v>0.1226</v>
       </c>
     </row>
@@ -22129,9 +23755,12 @@
         <v>0.02485</v>
       </c>
       <c r="K542" s="1" t="n">
+        <v>0.02489</v>
+      </c>
+      <c r="L542" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="L542" s="1" t="n">
+      <c r="M542" s="1" t="n">
         <v>0.02481</v>
       </c>
     </row>
@@ -22169,9 +23798,12 @@
         <v>0.05862</v>
       </c>
       <c r="K543" s="1" t="n">
+        <v>0.05877</v>
+      </c>
+      <c r="L543" s="1" t="n">
         <v>0.059</v>
       </c>
-      <c r="L543" s="1" t="n">
+      <c r="M543" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M543"/>
+  <dimension ref="A1:N543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -430,8 +430,9 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -492,10 +493,15 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>price_02:30</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -538,9 +544,12 @@
         <v>71180.10000000001</v>
       </c>
       <c r="L2" s="1" t="n">
+        <v>71177.5</v>
+      </c>
+      <c r="M2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="M2" s="1" t="n">
+      <c r="N2" s="1" t="n">
         <v>70995.10000000001</v>
       </c>
     </row>
@@ -581,9 +590,12 @@
         <v>2103.84</v>
       </c>
       <c r="L3" s="1" t="n">
+        <v>2104.28</v>
+      </c>
+      <c r="M3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="M3" s="1" t="n">
+      <c r="N3" s="1" t="n">
         <v>2102.04</v>
       </c>
     </row>
@@ -624,9 +636,12 @@
         <v>88.92</v>
       </c>
       <c r="L4" s="1" t="n">
+        <v>88.86</v>
+      </c>
+      <c r="M4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="N4" s="1" t="n">
         <v>88.81999999999999</v>
       </c>
     </row>
@@ -667,9 +682,12 @@
         <v>3.799</v>
       </c>
       <c r="L5" s="1" t="n">
+        <v>3.792</v>
+      </c>
+      <c r="M5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="N5" s="1" t="n">
         <v>3.77</v>
       </c>
     </row>
@@ -710,9 +728,12 @@
         <v>1.3964</v>
       </c>
       <c r="L6" s="1" t="n">
+        <v>1.3962</v>
+      </c>
+      <c r="M6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="N6" s="1" t="n">
         <v>1.3931</v>
       </c>
     </row>
@@ -753,9 +774,12 @@
         <v>0.09629</v>
       </c>
       <c r="L7" s="1" t="n">
+        <v>0.09623</v>
+      </c>
+      <c r="M7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.09601</v>
       </c>
     </row>
@@ -796,9 +820,12 @@
         <v>0.014819</v>
       </c>
       <c r="L8" s="1" t="n">
+        <v>0.014636</v>
+      </c>
+      <c r="M8" s="1" t="n">
         <v>0.014819</v>
       </c>
-      <c r="M8" s="1" t="n">
+      <c r="N8" s="1" t="n">
         <v>0.014064</v>
       </c>
     </row>
@@ -839,9 +866,12 @@
         <v>657.25</v>
       </c>
       <c r="L9" s="1" t="n">
+        <v>657.14</v>
+      </c>
+      <c r="M9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="M9" s="1" t="n">
+      <c r="N9" s="1" t="n">
         <v>655.72</v>
       </c>
     </row>
@@ -882,9 +912,12 @@
         <v>19.633</v>
       </c>
       <c r="L10" s="1" t="n">
-        <v>19.633</v>
+        <v>20.23</v>
       </c>
       <c r="M10" s="1" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="N10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -925,9 +958,12 @@
         <v>0.003424</v>
       </c>
       <c r="L11" s="1" t="n">
+        <v>0.0034139</v>
+      </c>
+      <c r="M11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="M11" s="1" t="n">
+      <c r="N11" s="1" t="n">
         <v>0.0034117</v>
       </c>
     </row>
@@ -968,9 +1004,12 @@
         <v>36.658</v>
       </c>
       <c r="L12" s="1" t="n">
-        <v>36.658</v>
+        <v>36.704</v>
       </c>
       <c r="M12" s="1" t="n">
+        <v>36.704</v>
+      </c>
+      <c r="N12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -1011,9 +1050,12 @@
         <v>213.84</v>
       </c>
       <c r="L13" s="1" t="n">
+        <v>213.8</v>
+      </c>
+      <c r="M13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="M13" s="1" t="n">
+      <c r="N13" s="1" t="n">
         <v>212.33</v>
       </c>
     </row>
@@ -1054,9 +1096,12 @@
         <v>0.0011136</v>
       </c>
       <c r="L14" s="1" t="n">
+        <v>0.0011147</v>
+      </c>
+      <c r="M14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="M14" s="1" t="n">
+      <c r="N14" s="1" t="n">
         <v>0.0011136</v>
       </c>
     </row>
@@ -1097,9 +1142,12 @@
         <v>0.29413</v>
       </c>
       <c r="L15" s="1" t="n">
-        <v>0.29413</v>
+        <v>0.30062</v>
       </c>
       <c r="M15" s="1" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="N15" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -1140,9 +1188,12 @@
         <v>232.4</v>
       </c>
       <c r="L16" s="1" t="n">
+        <v>232.27</v>
+      </c>
+      <c r="M16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="M16" s="1" t="n">
+      <c r="N16" s="1" t="n">
         <v>230.3</v>
       </c>
     </row>
@@ -1183,9 +1234,12 @@
         <v>1.0034</v>
       </c>
       <c r="L17" s="1" t="n">
+        <v>1.0014</v>
+      </c>
+      <c r="M17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="M17" s="1" t="n">
+      <c r="N17" s="1" t="n">
         <v>0.9963</v>
       </c>
     </row>
@@ -1226,9 +1280,12 @@
         <v>0.2678</v>
       </c>
       <c r="L18" s="1" t="n">
+        <v>0.2673</v>
+      </c>
+      <c r="M18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="M18" s="1" t="n">
+      <c r="N18" s="1" t="n">
         <v>0.2671</v>
       </c>
     </row>
@@ -1269,9 +1326,12 @@
         <v>9.776</v>
       </c>
       <c r="L19" s="1" t="n">
+        <v>9.776</v>
+      </c>
+      <c r="M19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="M19" s="1" t="n">
+      <c r="N19" s="1" t="n">
         <v>9.755000000000001</v>
       </c>
     </row>
@@ -1312,9 +1372,12 @@
         <v>5042.34</v>
       </c>
       <c r="L20" s="1" t="n">
+        <v>5041.65</v>
+      </c>
+      <c r="M20" s="1" t="n">
         <v>5059.14</v>
       </c>
-      <c r="M20" s="1" t="n">
+      <c r="N20" s="1" t="n">
         <v>5033.31</v>
       </c>
     </row>
@@ -1355,9 +1418,12 @@
         <v>464.17</v>
       </c>
       <c r="L21" s="1" t="n">
+        <v>463.92</v>
+      </c>
+      <c r="M21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="M21" s="1" t="n">
+      <c r="N21" s="1" t="n">
         <v>462.36</v>
       </c>
     </row>
@@ -1398,9 +1464,12 @@
         <v>1.4327</v>
       </c>
       <c r="L22" s="1" t="n">
+        <v>1.4211</v>
+      </c>
+      <c r="M22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="M22" s="1" t="n">
+      <c r="N22" s="1" t="n">
         <v>1.4185</v>
       </c>
     </row>
@@ -1441,10 +1510,13 @@
         <v>1.0679</v>
       </c>
       <c r="L23" s="1" t="n">
+        <v>1.0303</v>
+      </c>
+      <c r="M23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="M23" s="1" t="n">
-        <v>1.0679</v>
+      <c r="N23" s="1" t="n">
+        <v>1.0303</v>
       </c>
     </row>
     <row r="24">
@@ -1484,10 +1556,13 @@
         <v>1.349</v>
       </c>
       <c r="L24" s="1" t="n">
+        <v>1.344</v>
+      </c>
+      <c r="M24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="M24" s="1" t="n">
-        <v>1.346</v>
+      <c r="N24" s="1" t="n">
+        <v>1.344</v>
       </c>
     </row>
     <row r="25">
@@ -1527,9 +1602,12 @@
         <v>9.166</v>
       </c>
       <c r="L25" s="1" t="n">
+        <v>9.153</v>
+      </c>
+      <c r="M25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="M25" s="1" t="n">
+      <c r="N25" s="1" t="n">
         <v>9.140000000000001</v>
       </c>
     </row>
@@ -1570,9 +1648,12 @@
         <v>0.3724</v>
       </c>
       <c r="L26" s="1" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="M26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="M26" s="1" t="n">
+      <c r="N26" s="1" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -1613,9 +1694,12 @@
         <v>0.88</v>
       </c>
       <c r="L27" s="1" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="M27" s="1" t="n">
+      <c r="N27" s="1" t="n">
         <v>0.876</v>
       </c>
     </row>
@@ -1656,9 +1740,12 @@
         <v>1.808</v>
       </c>
       <c r="L28" s="1" t="n">
-        <v>1.823</v>
+        <v>1.826</v>
       </c>
       <c r="M28" s="1" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="N28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -1699,9 +1786,12 @@
         <v>0.1096</v>
       </c>
       <c r="L29" s="1" t="n">
+        <v>0.1097</v>
+      </c>
+      <c r="M29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="M29" s="1" t="n">
+      <c r="N29" s="1" t="n">
         <v>0.1096</v>
       </c>
     </row>
@@ -1742,9 +1832,12 @@
         <v>0.00205</v>
       </c>
       <c r="L30" s="1" t="n">
+        <v>0.002047</v>
+      </c>
+      <c r="M30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="M30" s="1" t="n">
+      <c r="N30" s="1" t="n">
         <v>0.002045</v>
       </c>
     </row>
@@ -1785,10 +1878,13 @@
         <v>1.482</v>
       </c>
       <c r="L31" s="1" t="n">
+        <v>1.475</v>
+      </c>
+      <c r="M31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="M31" s="1" t="n">
-        <v>1.48</v>
+      <c r="N31" s="1" t="n">
+        <v>1.475</v>
       </c>
     </row>
     <row r="32">
@@ -1828,9 +1924,12 @@
         <v>0.1751</v>
       </c>
       <c r="L32" s="1" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="M32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="M32" s="1" t="n">
+      <c r="N32" s="1" t="n">
         <v>0.1739</v>
       </c>
     </row>
@@ -1871,9 +1970,12 @@
         <v>0.1038</v>
       </c>
       <c r="L33" s="1" t="n">
+        <v>0.1038</v>
+      </c>
+      <c r="M33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="M33" s="1" t="n">
+      <c r="N33" s="1" t="n">
         <v>0.1038</v>
       </c>
     </row>
@@ -1914,10 +2016,13 @@
         <v>113.11</v>
       </c>
       <c r="L34" s="1" t="n">
+        <v>112.91</v>
+      </c>
+      <c r="M34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="M34" s="1" t="n">
-        <v>113.01</v>
+      <c r="N34" s="1" t="n">
+        <v>112.91</v>
       </c>
     </row>
     <row r="35">
@@ -1957,9 +2062,12 @@
         <v>6.659</v>
       </c>
       <c r="L35" s="1" t="n">
+        <v>6.715</v>
+      </c>
+      <c r="M35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="M35" s="1" t="n">
+      <c r="N35" s="1" t="n">
         <v>6.659</v>
       </c>
     </row>
@@ -2000,9 +2108,12 @@
         <v>0.016993</v>
       </c>
       <c r="L36" s="1" t="n">
+        <v>0.017135</v>
+      </c>
+      <c r="M36" s="1" t="n">
         <v>0.017421</v>
       </c>
-      <c r="M36" s="1" t="n">
+      <c r="N36" s="1" t="n">
         <v>0.016815</v>
       </c>
     </row>
@@ -2043,10 +2154,13 @@
         <v>0.3617</v>
       </c>
       <c r="L37" s="1" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="M37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="M37" s="1" t="n">
-        <v>0.361</v>
+      <c r="N37" s="1" t="n">
+        <v>0.3606</v>
       </c>
     </row>
     <row r="38">
@@ -2086,9 +2200,12 @@
         <v>55.49</v>
       </c>
       <c r="L38" s="1" t="n">
+        <v>55.41</v>
+      </c>
+      <c r="M38" s="1" t="n">
         <v>55.79</v>
       </c>
-      <c r="M38" s="1" t="n">
+      <c r="N38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -2129,9 +2246,12 @@
         <v>0.60089</v>
       </c>
       <c r="L39" s="1" t="n">
+        <v>0.59628</v>
+      </c>
+      <c r="M39" s="1" t="n">
         <v>0.60089</v>
       </c>
-      <c r="M39" s="1" t="n">
+      <c r="N39" s="1" t="n">
         <v>0.58131</v>
       </c>
     </row>
@@ -2172,10 +2292,13 @@
         <v>4.041</v>
       </c>
       <c r="L40" s="1" t="n">
+        <v>4.028</v>
+      </c>
+      <c r="M40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="M40" s="1" t="n">
-        <v>4.036</v>
+      <c r="N40" s="1" t="n">
+        <v>4.028</v>
       </c>
     </row>
     <row r="41">
@@ -2215,9 +2338,12 @@
         <v>0.0512</v>
       </c>
       <c r="L41" s="1" t="n">
-        <v>0.0512</v>
+        <v>0.0513</v>
       </c>
       <c r="M41" s="1" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="N41" s="1" t="n">
         <v>0.04927</v>
       </c>
     </row>
@@ -2258,9 +2384,12 @@
         <v>0.7032</v>
       </c>
       <c r="L42" s="1" t="n">
+        <v>0.7033</v>
+      </c>
+      <c r="M42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="M42" s="1" t="n">
+      <c r="N42" s="1" t="n">
         <v>0.7006</v>
       </c>
     </row>
@@ -2301,10 +2430,13 @@
         <v>0.22894</v>
       </c>
       <c r="L43" s="1" t="n">
+        <v>0.22842</v>
+      </c>
+      <c r="M43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="M43" s="1" t="n">
-        <v>0.22894</v>
+      <c r="N43" s="1" t="n">
+        <v>0.22842</v>
       </c>
     </row>
     <row r="44">
@@ -2344,9 +2476,12 @@
         <v>0.35427</v>
       </c>
       <c r="L44" s="1" t="n">
-        <v>0.35528</v>
+        <v>0.35655</v>
       </c>
       <c r="M44" s="1" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="N44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -2387,9 +2522,12 @@
         <v>0.1706</v>
       </c>
       <c r="L45" s="1" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="M45" s="1" t="n">
+      <c r="N45" s="1" t="n">
         <v>0.1699</v>
       </c>
     </row>
@@ -2430,9 +2568,12 @@
         <v>0.026</v>
       </c>
       <c r="L46" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="M46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="M46" s="1" t="n">
+      <c r="N46" s="1" t="n">
         <v>0.026</v>
       </c>
     </row>
@@ -2473,10 +2614,13 @@
         <v>0.005975</v>
       </c>
       <c r="L47" s="1" t="n">
+        <v>0.005958</v>
+      </c>
+      <c r="M47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="M47" s="1" t="n">
-        <v>0.005961</v>
+      <c r="N47" s="1" t="n">
+        <v>0.005958</v>
       </c>
     </row>
     <row r="48">
@@ -2516,9 +2660,12 @@
         <v>0.007387</v>
       </c>
       <c r="L48" s="1" t="n">
+        <v>0.007379</v>
+      </c>
+      <c r="M48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="M48" s="1" t="n">
+      <c r="N48" s="1" t="n">
         <v>0.007349</v>
       </c>
     </row>
@@ -2559,9 +2706,12 @@
         <v>0.1082</v>
       </c>
       <c r="L49" s="1" t="n">
+        <v>0.1083</v>
+      </c>
+      <c r="M49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="M49" s="1" t="n">
+      <c r="N49" s="1" t="n">
         <v>0.1077</v>
       </c>
     </row>
@@ -2602,9 +2752,12 @@
         <v>0.04119</v>
       </c>
       <c r="L50" s="1" t="n">
+        <v>0.0411</v>
+      </c>
+      <c r="M50" s="1" t="n">
         <v>0.04119</v>
       </c>
-      <c r="M50" s="1" t="n">
+      <c r="N50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -2645,9 +2798,12 @@
         <v>0.1627</v>
       </c>
       <c r="L51" s="1" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="M51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="M51" s="1" t="n">
+      <c r="N51" s="1" t="n">
         <v>0.1617</v>
       </c>
     </row>
@@ -2688,9 +2844,12 @@
         <v>0.0035</v>
       </c>
       <c r="L52" s="1" t="n">
+        <v>0.00351</v>
+      </c>
+      <c r="M52" s="1" t="n">
         <v>0.00357</v>
       </c>
-      <c r="M52" s="1" t="n">
+      <c r="N52" s="1" t="n">
         <v>0.0035</v>
       </c>
     </row>
@@ -2731,9 +2890,12 @@
         <v>2.634</v>
       </c>
       <c r="L53" s="1" t="n">
+        <v>2.634</v>
+      </c>
+      <c r="M53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="M53" s="1" t="n">
+      <c r="N53" s="1" t="n">
         <v>2.622</v>
       </c>
     </row>
@@ -2774,9 +2936,12 @@
         <v>0.006202</v>
       </c>
       <c r="L54" s="1" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="M54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="M54" s="1" t="n">
+      <c r="N54" s="1" t="n">
         <v>0.006188</v>
       </c>
     </row>
@@ -2817,9 +2982,12 @@
         <v>0.02958</v>
       </c>
       <c r="L55" s="1" t="n">
+        <v>0.02967</v>
+      </c>
+      <c r="M55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="M55" s="1" t="n">
+      <c r="N55" s="1" t="n">
         <v>0.02879</v>
       </c>
     </row>
@@ -2860,9 +3028,12 @@
         <v>0.7377</v>
       </c>
       <c r="L56" s="1" t="n">
+        <v>0.7363</v>
+      </c>
+      <c r="M56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="M56" s="1" t="n">
+      <c r="N56" s="1" t="n">
         <v>0.7352</v>
       </c>
     </row>
@@ -2903,9 +3074,12 @@
         <v>0.1037</v>
       </c>
       <c r="L57" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="M57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="M57" s="1" t="n">
+      <c r="N57" s="1" t="n">
         <v>0.1034</v>
       </c>
     </row>
@@ -2946,9 +3120,12 @@
         <v>0.944</v>
       </c>
       <c r="L58" s="1" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="M58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="M58" s="1" t="n">
+      <c r="N58" s="1" t="n">
         <v>0.9355</v>
       </c>
     </row>
@@ -2989,9 +3166,12 @@
         <v>0.08826000000000001</v>
       </c>
       <c r="L59" s="1" t="n">
+        <v>0.08744</v>
+      </c>
+      <c r="M59" s="1" t="n">
         <v>0.08826000000000001</v>
       </c>
-      <c r="M59" s="1" t="n">
+      <c r="N59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -3032,9 +3212,12 @@
         <v>0.0703</v>
       </c>
       <c r="L60" s="1" t="n">
+        <v>0.07003</v>
+      </c>
+      <c r="M60" s="1" t="n">
         <v>0.0703</v>
       </c>
-      <c r="M60" s="1" t="n">
+      <c r="N60" s="1" t="n">
         <v>0.06924</v>
       </c>
     </row>
@@ -3075,9 +3258,12 @@
         <v>0.05467</v>
       </c>
       <c r="L61" s="1" t="n">
+        <v>0.05466</v>
+      </c>
+      <c r="M61" s="1" t="n">
         <v>0.05523</v>
       </c>
-      <c r="M61" s="1" t="n">
+      <c r="N61" s="1" t="n">
         <v>0.05445</v>
       </c>
     </row>
@@ -3118,9 +3304,12 @@
         <v>0.009982</v>
       </c>
       <c r="L62" s="1" t="n">
+        <v>0.009974999999999999</v>
+      </c>
+      <c r="M62" s="1" t="n">
         <v>0.010194</v>
       </c>
-      <c r="M62" s="1" t="n">
+      <c r="N62" s="1" t="n">
         <v>0.009387</v>
       </c>
     </row>
@@ -3161,9 +3350,12 @@
         <v>0.29088</v>
       </c>
       <c r="L63" s="1" t="n">
-        <v>0.29088</v>
+        <v>0.2912</v>
       </c>
       <c r="M63" s="1" t="n">
+        <v>0.2912</v>
+      </c>
+      <c r="N63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -3204,9 +3396,12 @@
         <v>0.07581</v>
       </c>
       <c r="L64" s="1" t="n">
-        <v>0.07581</v>
+        <v>0.07591000000000001</v>
       </c>
       <c r="M64" s="1" t="n">
+        <v>0.07591000000000001</v>
+      </c>
+      <c r="N64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -3247,9 +3442,12 @@
         <v>0.3169</v>
       </c>
       <c r="L65" s="1" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="M65" s="1" t="n">
         <v>0.3169</v>
       </c>
-      <c r="M65" s="1" t="n">
+      <c r="N65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -3290,9 +3488,12 @@
         <v>0.16309</v>
       </c>
       <c r="L66" s="1" t="n">
+        <v>0.16271</v>
+      </c>
+      <c r="M66" s="1" t="n">
         <v>0.16461</v>
       </c>
-      <c r="M66" s="1" t="n">
+      <c r="N66" s="1" t="n">
         <v>0.16235</v>
       </c>
     </row>
@@ -3333,9 +3534,12 @@
         <v>0.11981</v>
       </c>
       <c r="L67" s="1" t="n">
+        <v>0.11957</v>
+      </c>
+      <c r="M67" s="1" t="n">
         <v>0.11999</v>
       </c>
-      <c r="M67" s="1" t="n">
+      <c r="N67" s="1" t="n">
         <v>0.11919</v>
       </c>
     </row>
@@ -3376,9 +3580,12 @@
         <v>0.09566</v>
       </c>
       <c r="L68" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="M68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="M68" s="1" t="n">
+      <c r="N68" s="1" t="n">
         <v>0.09548</v>
       </c>
     </row>
@@ -3419,9 +3626,12 @@
         <v>0.1242</v>
       </c>
       <c r="L69" s="1" t="n">
+        <v>0.1242</v>
+      </c>
+      <c r="M69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="M69" s="1" t="n">
+      <c r="N69" s="1" t="n">
         <v>0.1239</v>
       </c>
     </row>
@@ -3462,9 +3672,12 @@
         <v>8.528</v>
       </c>
       <c r="L70" s="1" t="n">
+        <v>8.523999999999999</v>
+      </c>
+      <c r="M70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="M70" s="1" t="n">
+      <c r="N70" s="1" t="n">
         <v>8.494</v>
       </c>
     </row>
@@ -3505,9 +3718,12 @@
         <v>0.239</v>
       </c>
       <c r="L71" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="M71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="M71" s="1" t="n">
+      <c r="N71" s="1" t="n">
         <v>0.238</v>
       </c>
     </row>
@@ -3548,10 +3764,13 @@
         <v>0.05001</v>
       </c>
       <c r="L72" s="1" t="n">
+        <v>0.04992</v>
+      </c>
+      <c r="M72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="M72" s="1" t="n">
-        <v>0.05001</v>
+      <c r="N72" s="1" t="n">
+        <v>0.04992</v>
       </c>
     </row>
     <row r="73">
@@ -3591,9 +3810,12 @@
         <v>0.0507</v>
       </c>
       <c r="L73" s="1" t="n">
+        <v>0.05038</v>
+      </c>
+      <c r="M73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="M73" s="1" t="n">
+      <c r="N73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -3634,9 +3856,12 @@
         <v>0.1254</v>
       </c>
       <c r="L74" s="1" t="n">
+        <v>0.1255</v>
+      </c>
+      <c r="M74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="M74" s="1" t="n">
+      <c r="N74" s="1" t="n">
         <v>0.1252</v>
       </c>
     </row>
@@ -3677,9 +3902,12 @@
         <v>0.04627</v>
       </c>
       <c r="L75" s="1" t="n">
+        <v>0.04621</v>
+      </c>
+      <c r="M75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="M75" s="1" t="n">
+      <c r="N75" s="1" t="n">
         <v>0.04621</v>
       </c>
     </row>
@@ -3720,9 +3948,12 @@
         <v>0.06734</v>
       </c>
       <c r="L76" s="1" t="n">
+        <v>0.06698</v>
+      </c>
+      <c r="M76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="M76" s="1" t="n">
+      <c r="N76" s="1" t="n">
         <v>0.06691</v>
       </c>
     </row>
@@ -3763,9 +3994,12 @@
         <v>0.12738</v>
       </c>
       <c r="L77" s="1" t="n">
+        <v>0.12696</v>
+      </c>
+      <c r="M77" s="1" t="n">
         <v>0.12881</v>
       </c>
-      <c r="M77" s="1" t="n">
+      <c r="N77" s="1" t="n">
         <v>0.12654</v>
       </c>
     </row>
@@ -3806,9 +4040,12 @@
         <v>0.1623</v>
       </c>
       <c r="L78" s="1" t="n">
+        <v>0.1621</v>
+      </c>
+      <c r="M78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="M78" s="1" t="n">
+      <c r="N78" s="1" t="n">
         <v>0.1613</v>
       </c>
     </row>
@@ -3849,10 +4086,13 @@
         <v>0.02716</v>
       </c>
       <c r="L79" s="1" t="n">
+        <v>0.02705</v>
+      </c>
+      <c r="M79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="M79" s="1" t="n">
-        <v>0.0271</v>
+      <c r="N79" s="1" t="n">
+        <v>0.02705</v>
       </c>
     </row>
     <row r="80">
@@ -3892,9 +4132,12 @@
         <v>357.41</v>
       </c>
       <c r="L80" s="1" t="n">
-        <v>357.41</v>
+        <v>358.61</v>
       </c>
       <c r="M80" s="1" t="n">
+        <v>358.61</v>
+      </c>
+      <c r="N80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -3935,9 +4178,12 @@
         <v>7.118000000000001e-05</v>
       </c>
       <c r="L81" s="1" t="n">
+        <v>7.103e-05</v>
+      </c>
+      <c r="M81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="M81" s="1" t="n">
+      <c r="N81" s="1" t="n">
         <v>7.080999999999999e-05</v>
       </c>
     </row>
@@ -3978,9 +4224,12 @@
         <v>0.2653</v>
       </c>
       <c r="L82" s="1" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="M82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="M82" s="1" t="n">
+      <c r="N82" s="1" t="n">
         <v>0.2645</v>
       </c>
     </row>
@@ -4021,10 +4270,13 @@
         <v>1.1392</v>
       </c>
       <c r="L83" s="1" t="n">
+        <v>1.1341</v>
+      </c>
+      <c r="M83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="M83" s="1" t="n">
-        <v>1.1379</v>
+      <c r="N83" s="1" t="n">
+        <v>1.1341</v>
       </c>
     </row>
     <row r="84">
@@ -4064,10 +4316,13 @@
         <v>0.3563</v>
       </c>
       <c r="L84" s="1" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="M84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="M84" s="1" t="n">
-        <v>0.3541</v>
+      <c r="N84" s="1" t="n">
+        <v>0.3539</v>
       </c>
     </row>
     <row r="85">
@@ -4107,9 +4362,12 @@
         <v>2.0106</v>
       </c>
       <c r="L85" s="1" t="n">
+        <v>2.0174</v>
+      </c>
+      <c r="M85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="M85" s="1" t="n">
+      <c r="N85" s="1" t="n">
         <v>2.0067</v>
       </c>
     </row>
@@ -4150,9 +4408,12 @@
         <v>1.317</v>
       </c>
       <c r="L86" s="1" t="n">
-        <v>1.317</v>
+        <v>1.3205</v>
       </c>
       <c r="M86" s="1" t="n">
+        <v>1.3205</v>
+      </c>
+      <c r="N86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -4193,10 +4454,13 @@
         <v>32.75</v>
       </c>
       <c r="L87" s="1" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="M87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="M87" s="1" t="n">
-        <v>32.73</v>
+      <c r="N87" s="1" t="n">
+        <v>32.68</v>
       </c>
     </row>
     <row r="88">
@@ -4236,10 +4500,13 @@
         <v>0.00954</v>
       </c>
       <c r="L88" s="1" t="n">
+        <v>0.00941</v>
+      </c>
+      <c r="M88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="M88" s="1" t="n">
-        <v>0.00954</v>
+      <c r="N88" s="1" t="n">
+        <v>0.00941</v>
       </c>
     </row>
     <row r="89">
@@ -4279,10 +4546,13 @@
         <v>0.01833</v>
       </c>
       <c r="L89" s="1" t="n">
+        <v>0.01823</v>
+      </c>
+      <c r="M89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="M89" s="1" t="n">
-        <v>0.01828</v>
+      <c r="N89" s="1" t="n">
+        <v>0.01823</v>
       </c>
     </row>
     <row r="90">
@@ -4322,10 +4592,13 @@
         <v>0.03539</v>
       </c>
       <c r="L90" s="1" t="n">
+        <v>0.03497</v>
+      </c>
+      <c r="M90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="M90" s="1" t="n">
-        <v>0.03539</v>
+      <c r="N90" s="1" t="n">
+        <v>0.03497</v>
       </c>
     </row>
     <row r="91">
@@ -4365,9 +4638,12 @@
         <v>0.01203</v>
       </c>
       <c r="L91" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="M91" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="M91" s="1" t="n">
+      <c r="N91" s="1" t="n">
         <v>0.0118</v>
       </c>
     </row>
@@ -4408,9 +4684,12 @@
         <v>3.103</v>
       </c>
       <c r="L92" s="1" t="n">
+        <v>3.098</v>
+      </c>
+      <c r="M92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="M92" s="1" t="n">
+      <c r="N92" s="1" t="n">
         <v>3.095</v>
       </c>
     </row>
@@ -4451,9 +4730,12 @@
         <v>0.005625</v>
       </c>
       <c r="L93" s="1" t="n">
+        <v>0.005614</v>
+      </c>
+      <c r="M93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="M93" s="1" t="n">
+      <c r="N93" s="1" t="n">
         <v>0.005596</v>
       </c>
     </row>
@@ -4494,9 +4776,12 @@
         <v>0.0929</v>
       </c>
       <c r="L94" s="1" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="M94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="M94" s="1" t="n">
+      <c r="N94" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -4537,9 +4822,12 @@
         <v>0.6098</v>
       </c>
       <c r="L95" s="1" t="n">
+        <v>0.6064000000000001</v>
+      </c>
+      <c r="M95" s="1" t="n">
         <v>0.6098</v>
       </c>
-      <c r="M95" s="1" t="n">
+      <c r="N95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -4580,9 +4868,12 @@
         <v>1.28e-05</v>
       </c>
       <c r="L96" s="1" t="n">
+        <v>1.27e-05</v>
+      </c>
+      <c r="M96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="M96" s="1" t="n">
+      <c r="N96" s="1" t="n">
         <v>1.27e-05</v>
       </c>
     </row>
@@ -4623,9 +4914,12 @@
         <v>1.126</v>
       </c>
       <c r="L97" s="1" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="M97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="M97" s="1" t="n">
+      <c r="N97" s="1" t="n">
         <v>1.125</v>
       </c>
     </row>
@@ -4666,9 +4960,12 @@
         <v>0.25499</v>
       </c>
       <c r="L98" s="1" t="n">
+        <v>0.25558</v>
+      </c>
+      <c r="M98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="M98" s="1" t="n">
+      <c r="N98" s="1" t="n">
         <v>0.2523</v>
       </c>
     </row>
@@ -4709,9 +5006,12 @@
         <v>1.147</v>
       </c>
       <c r="L99" s="1" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="M99" s="1" t="n">
         <v>1.156</v>
       </c>
-      <c r="M99" s="1" t="n">
+      <c r="N99" s="1" t="n">
         <v>1.144</v>
       </c>
     </row>
@@ -4752,9 +5052,12 @@
         <v>1.859</v>
       </c>
       <c r="L100" s="1" t="n">
+        <v>1.859</v>
+      </c>
+      <c r="M100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="M100" s="1" t="n">
+      <c r="N100" s="1" t="n">
         <v>1.852</v>
       </c>
     </row>
@@ -4795,9 +5098,12 @@
         <v>0.01584</v>
       </c>
       <c r="L101" s="1" t="n">
+        <v>0.01585</v>
+      </c>
+      <c r="M101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="M101" s="1" t="n">
+      <c r="N101" s="1" t="n">
         <v>0.01579</v>
       </c>
     </row>
@@ -4838,9 +5144,12 @@
         <v>0.10316</v>
       </c>
       <c r="L102" s="1" t="n">
+        <v>0.10332</v>
+      </c>
+      <c r="M102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="M102" s="1" t="n">
+      <c r="N102" s="1" t="n">
         <v>0.10316</v>
       </c>
     </row>
@@ -4881,9 +5190,12 @@
         <v>0.0005981</v>
       </c>
       <c r="L103" s="1" t="n">
+        <v>0.0005974</v>
+      </c>
+      <c r="M103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="M103" s="1" t="n">
+      <c r="N103" s="1" t="n">
         <v>0.0005967</v>
       </c>
     </row>
@@ -4924,9 +5236,12 @@
         <v>0.0005726</v>
       </c>
       <c r="L104" s="1" t="n">
+        <v>0.0005773</v>
+      </c>
+      <c r="M104" s="1" t="n">
         <v>0.0005776000000000001</v>
       </c>
-      <c r="M104" s="1" t="n">
+      <c r="N104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -4967,9 +5282,12 @@
         <v>0.003264</v>
       </c>
       <c r="L105" s="1" t="n">
-        <v>0.003264</v>
+        <v>0.003266</v>
       </c>
       <c r="M105" s="1" t="n">
+        <v>0.003266</v>
+      </c>
+      <c r="N105" s="1" t="n">
         <v>0.003229</v>
       </c>
     </row>
@@ -5010,9 +5328,12 @@
         <v>2.595</v>
       </c>
       <c r="L106" s="1" t="n">
+        <v>2.591</v>
+      </c>
+      <c r="M106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="M106" s="1" t="n">
+      <c r="N106" s="1" t="n">
         <v>2.587</v>
       </c>
     </row>
@@ -5053,9 +5374,12 @@
         <v>0.1655</v>
       </c>
       <c r="L107" s="1" t="n">
+        <v>0.1653</v>
+      </c>
+      <c r="M107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="M107" s="1" t="n">
+      <c r="N107" s="1" t="n">
         <v>0.165</v>
       </c>
     </row>
@@ -5096,9 +5420,12 @@
         <v>0.09616</v>
       </c>
       <c r="L108" s="1" t="n">
+        <v>0.09614</v>
+      </c>
+      <c r="M108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="M108" s="1" t="n">
+      <c r="N108" s="1" t="n">
         <v>0.0955</v>
       </c>
     </row>
@@ -5139,9 +5466,12 @@
         <v>0.02222</v>
       </c>
       <c r="L109" s="1" t="n">
+        <v>0.02217</v>
+      </c>
+      <c r="M109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="M109" s="1" t="n">
+      <c r="N109" s="1" t="n">
         <v>0.02204</v>
       </c>
     </row>
@@ -5182,9 +5512,12 @@
         <v>0.2933</v>
       </c>
       <c r="L110" s="1" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="M110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="M110" s="1" t="n">
+      <c r="N110" s="1" t="n">
         <v>0.2912</v>
       </c>
     </row>
@@ -5225,10 +5558,13 @@
         <v>0.05672</v>
       </c>
       <c r="L111" s="1" t="n">
+        <v>0.05659</v>
+      </c>
+      <c r="M111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="M111" s="1" t="n">
-        <v>0.05665</v>
+      <c r="N111" s="1" t="n">
+        <v>0.05659</v>
       </c>
     </row>
     <row r="112">
@@ -5268,9 +5604,12 @@
         <v>0.3019</v>
       </c>
       <c r="L112" s="1" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="M112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="M112" s="1" t="n">
+      <c r="N112" s="1" t="n">
         <v>0.3002</v>
       </c>
     </row>
@@ -5311,9 +5650,12 @@
         <v>18.7</v>
       </c>
       <c r="L113" s="1" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="M113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="M113" s="1" t="n">
+      <c r="N113" s="1" t="n">
         <v>18.6</v>
       </c>
     </row>
@@ -5354,9 +5696,12 @@
         <v>0.12837</v>
       </c>
       <c r="L114" s="1" t="n">
+        <v>0.12876</v>
+      </c>
+      <c r="M114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="M114" s="1" t="n">
+      <c r="N114" s="1" t="n">
         <v>0.12837</v>
       </c>
     </row>
@@ -5397,9 +5742,12 @@
         <v>0.01562</v>
       </c>
       <c r="L115" s="1" t="n">
+        <v>0.01572</v>
+      </c>
+      <c r="M115" s="1" t="n">
         <v>0.01583</v>
       </c>
-      <c r="M115" s="1" t="n">
+      <c r="N115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -5440,9 +5788,12 @@
         <v>0.08479</v>
       </c>
       <c r="L116" s="1" t="n">
+        <v>0.08473</v>
+      </c>
+      <c r="M116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="M116" s="1" t="n">
+      <c r="N116" s="1" t="n">
         <v>0.08470999999999999</v>
       </c>
     </row>
@@ -5483,10 +5834,13 @@
         <v>0.047554</v>
       </c>
       <c r="L117" s="1" t="n">
+        <v>0.047288</v>
+      </c>
+      <c r="M117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="M117" s="1" t="n">
-        <v>0.047554</v>
+      <c r="N117" s="1" t="n">
+        <v>0.047288</v>
       </c>
     </row>
     <row r="118">
@@ -5526,10 +5880,13 @@
         <v>0.04743</v>
       </c>
       <c r="L118" s="1" t="n">
+        <v>0.04732</v>
+      </c>
+      <c r="M118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="M118" s="1" t="n">
-        <v>0.04733</v>
+      <c r="N118" s="1" t="n">
+        <v>0.04732</v>
       </c>
     </row>
     <row r="119">
@@ -5569,10 +5926,13 @@
         <v>0.0405</v>
       </c>
       <c r="L119" s="1" t="n">
+        <v>0.03999</v>
+      </c>
+      <c r="M119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="M119" s="1" t="n">
-        <v>0.0405</v>
+      <c r="N119" s="1" t="n">
+        <v>0.03999</v>
       </c>
     </row>
     <row r="120">
@@ -5612,9 +5972,12 @@
         <v>0.14501</v>
       </c>
       <c r="L120" s="1" t="n">
+        <v>0.14471</v>
+      </c>
+      <c r="M120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="M120" s="1" t="n">
+      <c r="N120" s="1" t="n">
         <v>0.14463</v>
       </c>
     </row>
@@ -5655,9 +6018,12 @@
         <v>0.1279</v>
       </c>
       <c r="L121" s="1" t="n">
+        <v>0.1275</v>
+      </c>
+      <c r="M121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="M121" s="1" t="n">
+      <c r="N121" s="1" t="n">
         <v>0.1272</v>
       </c>
     </row>
@@ -5698,9 +6064,12 @@
         <v>1.874</v>
       </c>
       <c r="L122" s="1" t="n">
+        <v>1.868</v>
+      </c>
+      <c r="M122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="M122" s="1" t="n">
+      <c r="N122" s="1" t="n">
         <v>1.867</v>
       </c>
     </row>
@@ -5741,9 +6110,12 @@
         <v>0.03018</v>
       </c>
       <c r="L123" s="1" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="M123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="M123" s="1" t="n">
+      <c r="N123" s="1" t="n">
         <v>0.0301</v>
       </c>
     </row>
@@ -5784,9 +6156,12 @@
         <v>0.13159</v>
       </c>
       <c r="L124" s="1" t="n">
+        <v>0.13161</v>
+      </c>
+      <c r="M124" s="1" t="n">
         <v>0.13401</v>
       </c>
-      <c r="M124" s="1" t="n">
+      <c r="N124" s="1" t="n">
         <v>0.13159</v>
       </c>
     </row>
@@ -5827,9 +6202,12 @@
         <v>0.04108</v>
       </c>
       <c r="L125" s="1" t="n">
+        <v>0.04104</v>
+      </c>
+      <c r="M125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="M125" s="1" t="n">
+      <c r="N125" s="1" t="n">
         <v>0.04095</v>
       </c>
     </row>
@@ -5870,10 +6248,13 @@
         <v>0.115</v>
       </c>
       <c r="L126" s="1" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="M126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="M126" s="1" t="n">
-        <v>0.1148</v>
+      <c r="N126" s="1" t="n">
+        <v>0.1147</v>
       </c>
     </row>
     <row r="127">
@@ -5913,9 +6294,12 @@
         <v>0.5077</v>
       </c>
       <c r="L127" s="1" t="n">
-        <v>0.5077</v>
+        <v>0.5108</v>
       </c>
       <c r="M127" s="1" t="n">
+        <v>0.5108</v>
+      </c>
+      <c r="N127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -5956,9 +6340,12 @@
         <v>0.03808</v>
       </c>
       <c r="L128" s="1" t="n">
+        <v>0.03802</v>
+      </c>
+      <c r="M128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="M128" s="1" t="n">
+      <c r="N128" s="1" t="n">
         <v>0.03787</v>
       </c>
     </row>
@@ -5999,10 +6386,13 @@
         <v>0.794</v>
       </c>
       <c r="L129" s="1" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="M129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="M129" s="1" t="n">
-        <v>0.792</v>
+      <c r="N129" s="1" t="n">
+        <v>0.791</v>
       </c>
     </row>
     <row r="130">
@@ -6042,9 +6432,12 @@
         <v>0.03435</v>
       </c>
       <c r="L130" s="1" t="n">
+        <v>0.03441</v>
+      </c>
+      <c r="M130" s="1" t="n">
         <v>0.03458</v>
       </c>
-      <c r="M130" s="1" t="n">
+      <c r="N130" s="1" t="n">
         <v>0.03422</v>
       </c>
     </row>
@@ -6085,9 +6478,12 @@
         <v>0.4237</v>
       </c>
       <c r="L131" s="1" t="n">
+        <v>0.4251</v>
+      </c>
+      <c r="M131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="M131" s="1" t="n">
+      <c r="N131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -6128,9 +6524,12 @@
         <v>0.04406</v>
       </c>
       <c r="L132" s="1" t="n">
+        <v>0.04376</v>
+      </c>
+      <c r="M132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="M132" s="1" t="n">
+      <c r="N132" s="1" t="n">
         <v>0.04354</v>
       </c>
     </row>
@@ -6171,9 +6570,12 @@
         <v>1.2891</v>
       </c>
       <c r="L133" s="1" t="n">
+        <v>1.2878</v>
+      </c>
+      <c r="M133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="M133" s="1" t="n">
+      <c r="N133" s="1" t="n">
         <v>1.282</v>
       </c>
     </row>
@@ -6214,9 +6616,12 @@
         <v>0.02198</v>
       </c>
       <c r="L134" s="1" t="n">
+        <v>0.02191</v>
+      </c>
+      <c r="M134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="M134" s="1" t="n">
+      <c r="N134" s="1" t="n">
         <v>0.02184</v>
       </c>
     </row>
@@ -6257,9 +6662,12 @@
         <v>0.0004604</v>
       </c>
       <c r="L135" s="1" t="n">
+        <v>0.0004597</v>
+      </c>
+      <c r="M135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="M135" s="1" t="n">
+      <c r="N135" s="1" t="n">
         <v>0.0004592</v>
       </c>
     </row>
@@ -6300,9 +6708,12 @@
         <v>0.001881</v>
       </c>
       <c r="L136" s="1" t="n">
+        <v>0.001899</v>
+      </c>
+      <c r="M136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="M136" s="1" t="n">
+      <c r="N136" s="1" t="n">
         <v>0.001881</v>
       </c>
     </row>
@@ -6343,10 +6754,13 @@
         <v>0.3178</v>
       </c>
       <c r="L137" s="1" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="M137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="M137" s="1" t="n">
-        <v>0.317</v>
+      <c r="N137" s="1" t="n">
+        <v>0.3164</v>
       </c>
     </row>
     <row r="138">
@@ -6386,9 +6800,12 @@
         <v>0.5713</v>
       </c>
       <c r="L138" s="1" t="n">
+        <v>0.5705</v>
+      </c>
+      <c r="M138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="M138" s="1" t="n">
+      <c r="N138" s="1" t="n">
         <v>0.5698</v>
       </c>
     </row>
@@ -6429,9 +6846,12 @@
         <v>0.02129</v>
       </c>
       <c r="L139" s="1" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="M139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="M139" s="1" t="n">
+      <c r="N139" s="1" t="n">
         <v>0.02125</v>
       </c>
     </row>
@@ -6472,9 +6892,12 @@
         <v>0.08044999999999999</v>
       </c>
       <c r="L140" s="1" t="n">
+        <v>0.08039</v>
+      </c>
+      <c r="M140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="M140" s="1" t="n">
+      <c r="N140" s="1" t="n">
         <v>0.08036</v>
       </c>
     </row>
@@ -6515,10 +6938,13 @@
         <v>0.001663</v>
       </c>
       <c r="L141" s="1" t="n">
+        <v>0.001523</v>
+      </c>
+      <c r="M141" s="1" t="n">
         <v>0.001672</v>
       </c>
-      <c r="M141" s="1" t="n">
-        <v>0.001616</v>
+      <c r="N141" s="1" t="n">
+        <v>0.001523</v>
       </c>
     </row>
     <row r="142">
@@ -6558,9 +6984,12 @@
         <v>0.4378</v>
       </c>
       <c r="L142" s="1" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="M142" s="1" t="n">
         <v>0.4387</v>
       </c>
-      <c r="M142" s="1" t="n">
+      <c r="N142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -6601,9 +7030,12 @@
         <v>0.030645</v>
       </c>
       <c r="L143" s="1" t="n">
-        <v>0.030681</v>
+        <v>0.030859</v>
       </c>
       <c r="M143" s="1" t="n">
+        <v>0.030859</v>
+      </c>
+      <c r="N143" s="1" t="n">
         <v>0.030021</v>
       </c>
     </row>
@@ -6647,6 +7079,9 @@
         <v>0.000226</v>
       </c>
       <c r="M144" s="1" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="N144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -6687,9 +7122,12 @@
         <v>0.03542</v>
       </c>
       <c r="L145" s="1" t="n">
+        <v>0.03487</v>
+      </c>
+      <c r="M145" s="1" t="n">
         <v>0.03696</v>
       </c>
-      <c r="M145" s="1" t="n">
+      <c r="N145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -6730,9 +7168,12 @@
         <v>0.11536</v>
       </c>
       <c r="L146" s="1" t="n">
+        <v>0.11554</v>
+      </c>
+      <c r="M146" s="1" t="n">
         <v>0.116</v>
       </c>
-      <c r="M146" s="1" t="n">
+      <c r="N146" s="1" t="n">
         <v>0.11518</v>
       </c>
     </row>
@@ -6773,9 +7214,12 @@
         <v>0.02182</v>
       </c>
       <c r="L147" s="1" t="n">
+        <v>0.02197</v>
+      </c>
+      <c r="M147" s="1" t="n">
         <v>0.02198</v>
       </c>
-      <c r="M147" s="1" t="n">
+      <c r="N147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -6816,9 +7260,12 @@
         <v>1.412</v>
       </c>
       <c r="L148" s="1" t="n">
+        <v>1.4122</v>
+      </c>
+      <c r="M148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="M148" s="1" t="n">
+      <c r="N148" s="1" t="n">
         <v>1.4084</v>
       </c>
     </row>
@@ -6859,9 +7306,12 @@
         <v>1.8684</v>
       </c>
       <c r="L149" s="1" t="n">
+        <v>1.8741</v>
+      </c>
+      <c r="M149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="M149" s="1" t="n">
+      <c r="N149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -6902,10 +7352,13 @@
         <v>0.097</v>
       </c>
       <c r="L150" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="M150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="M150" s="1" t="n">
-        <v>0.097</v>
+      <c r="N150" s="1" t="n">
+        <v>0.096</v>
       </c>
     </row>
     <row r="151">
@@ -6945,9 +7398,12 @@
         <v>4.598</v>
       </c>
       <c r="L151" s="1" t="n">
+        <v>4.607</v>
+      </c>
+      <c r="M151" s="1" t="n">
         <v>4.64</v>
       </c>
-      <c r="M151" s="1" t="n">
+      <c r="N151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -6988,9 +7444,12 @@
         <v>5.539</v>
       </c>
       <c r="L152" s="1" t="n">
+        <v>5.534</v>
+      </c>
+      <c r="M152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="M152" s="1" t="n">
+      <c r="N152" s="1" t="n">
         <v>5.522</v>
       </c>
     </row>
@@ -7031,9 +7490,12 @@
         <v>0.3213</v>
       </c>
       <c r="L153" s="1" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="M153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="M153" s="1" t="n">
+      <c r="N153" s="1" t="n">
         <v>0.3175</v>
       </c>
     </row>
@@ -7074,9 +7536,12 @@
         <v>0.5878</v>
       </c>
       <c r="L154" s="1" t="n">
+        <v>0.5869</v>
+      </c>
+      <c r="M154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="M154" s="1" t="n">
+      <c r="N154" s="1" t="n">
         <v>0.5867</v>
       </c>
     </row>
@@ -7117,9 +7582,12 @@
         <v>0.01291</v>
       </c>
       <c r="L155" s="1" t="n">
-        <v>0.01292</v>
+        <v>0.01299</v>
       </c>
       <c r="M155" s="1" t="n">
+        <v>0.01299</v>
+      </c>
+      <c r="N155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -7160,10 +7628,13 @@
         <v>0.09859999999999999</v>
       </c>
       <c r="L156" s="1" t="n">
+        <v>0.0985</v>
+      </c>
+      <c r="M156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="M156" s="1" t="n">
-        <v>0.09859999999999999</v>
+      <c r="N156" s="1" t="n">
+        <v>0.0985</v>
       </c>
     </row>
     <row r="157">
@@ -7203,9 +7674,12 @@
         <v>16.558</v>
       </c>
       <c r="L157" s="1" t="n">
+        <v>16.553</v>
+      </c>
+      <c r="M157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="M157" s="1" t="n">
+      <c r="N157" s="1" t="n">
         <v>16.525</v>
       </c>
     </row>
@@ -7246,9 +7720,12 @@
         <v>0.05554</v>
       </c>
       <c r="L158" s="1" t="n">
+        <v>0.05564</v>
+      </c>
+      <c r="M158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="M158" s="1" t="n">
+      <c r="N158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -7289,9 +7766,12 @@
         <v>29.04</v>
       </c>
       <c r="L159" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="M159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="M159" s="1" t="n">
+      <c r="N159" s="1" t="n">
         <v>28.87</v>
       </c>
     </row>
@@ -7332,10 +7812,13 @@
         <v>0.02112</v>
       </c>
       <c r="L160" s="1" t="n">
+        <v>0.02107</v>
+      </c>
+      <c r="M160" s="1" t="n">
         <v>0.02141</v>
       </c>
-      <c r="M160" s="1" t="n">
-        <v>0.02112</v>
+      <c r="N160" s="1" t="n">
+        <v>0.02107</v>
       </c>
     </row>
     <row r="161">
@@ -7375,9 +7858,12 @@
         <v>0.0006541</v>
       </c>
       <c r="L161" s="1" t="n">
+        <v>0.0006543</v>
+      </c>
+      <c r="M161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="M161" s="1" t="n">
+      <c r="N161" s="1" t="n">
         <v>0.0006507</v>
       </c>
     </row>
@@ -7418,10 +7904,13 @@
         <v>0.3871</v>
       </c>
       <c r="L162" s="1" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="M162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="M162" s="1" t="n">
-        <v>0.3871</v>
+      <c r="N162" s="1" t="n">
+        <v>0.3808</v>
       </c>
     </row>
     <row r="163">
@@ -7461,10 +7950,13 @@
         <v>0.1926</v>
       </c>
       <c r="L163" s="1" t="n">
+        <v>0.1922</v>
+      </c>
+      <c r="M163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="M163" s="1" t="n">
-        <v>0.1925</v>
+      <c r="N163" s="1" t="n">
+        <v>0.1922</v>
       </c>
     </row>
     <row r="164">
@@ -7504,9 +7996,12 @@
         <v>0.316</v>
       </c>
       <c r="L164" s="1" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="M164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="M164" s="1" t="n">
+      <c r="N164" s="1" t="n">
         <v>0.315</v>
       </c>
     </row>
@@ -7547,9 +8042,12 @@
         <v>0.373</v>
       </c>
       <c r="L165" s="1" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="M165" s="1" t="n">
         <v>0.377</v>
       </c>
-      <c r="M165" s="1" t="n">
+      <c r="N165" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -7590,9 +8088,12 @@
         <v>0.02259</v>
       </c>
       <c r="L166" s="1" t="n">
+        <v>0.02259</v>
+      </c>
+      <c r="M166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="M166" s="1" t="n">
+      <c r="N166" s="1" t="n">
         <v>0.02258</v>
       </c>
     </row>
@@ -7633,10 +8134,13 @@
         <v>0.007313</v>
       </c>
       <c r="L167" s="1" t="n">
+        <v>0.007284</v>
+      </c>
+      <c r="M167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="M167" s="1" t="n">
-        <v>0.007295</v>
+      <c r="N167" s="1" t="n">
+        <v>0.007284</v>
       </c>
     </row>
     <row r="168">
@@ -7676,9 +8180,12 @@
         <v>0.01359</v>
       </c>
       <c r="L168" s="1" t="n">
+        <v>0.01355</v>
+      </c>
+      <c r="M168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="M168" s="1" t="n">
+      <c r="N168" s="1" t="n">
         <v>0.01355</v>
       </c>
     </row>
@@ -7719,9 +8226,12 @@
         <v>0.25151</v>
       </c>
       <c r="L169" s="1" t="n">
+        <v>0.25206</v>
+      </c>
+      <c r="M169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="M169" s="1" t="n">
+      <c r="N169" s="1" t="n">
         <v>0.25151</v>
       </c>
     </row>
@@ -7762,9 +8272,12 @@
         <v>0.02184</v>
       </c>
       <c r="L170" s="1" t="n">
+        <v>0.02172</v>
+      </c>
+      <c r="M170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="M170" s="1" t="n">
+      <c r="N170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -7805,10 +8318,13 @@
         <v>0.1715</v>
       </c>
       <c r="L171" s="1" t="n">
+        <v>0.1713</v>
+      </c>
+      <c r="M171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="M171" s="1" t="n">
-        <v>0.1715</v>
+      <c r="N171" s="1" t="n">
+        <v>0.1713</v>
       </c>
     </row>
     <row r="172">
@@ -7848,9 +8364,12 @@
         <v>0.089</v>
       </c>
       <c r="L172" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="M172" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="M172" s="1" t="n">
+      <c r="N172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -7891,10 +8410,13 @@
         <v>0.004689</v>
       </c>
       <c r="L173" s="1" t="n">
+        <v>0.004676</v>
+      </c>
+      <c r="M173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="M173" s="1" t="n">
-        <v>0.004682</v>
+      <c r="N173" s="1" t="n">
+        <v>0.004676</v>
       </c>
     </row>
     <row r="174">
@@ -7934,9 +8456,12 @@
         <v>0.4373</v>
       </c>
       <c r="L174" s="1" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="M174" s="1" t="n">
         <v>0.4423</v>
       </c>
-      <c r="M174" s="1" t="n">
+      <c r="N174" s="1" t="n">
         <v>0.4364</v>
       </c>
     </row>
@@ -7977,9 +8502,12 @@
         <v>0.09042</v>
       </c>
       <c r="L175" s="1" t="n">
+        <v>0.09032999999999999</v>
+      </c>
+      <c r="M175" s="1" t="n">
         <v>0.09042</v>
       </c>
-      <c r="M175" s="1" t="n">
+      <c r="N175" s="1" t="n">
         <v>0.08935999999999999</v>
       </c>
     </row>
@@ -8020,9 +8548,12 @@
         <v>0.2473</v>
       </c>
       <c r="L176" s="1" t="n">
+        <v>0.2471</v>
+      </c>
+      <c r="M176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="M176" s="1" t="n">
+      <c r="N176" s="1" t="n">
         <v>0.2453</v>
       </c>
     </row>
@@ -8063,9 +8594,12 @@
         <v>0.0192</v>
       </c>
       <c r="L177" s="1" t="n">
+        <v>0.01921</v>
+      </c>
+      <c r="M177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="M177" s="1" t="n">
+      <c r="N177" s="1" t="n">
         <v>0.01909</v>
       </c>
     </row>
@@ -8106,9 +8640,12 @@
         <v>6.151</v>
       </c>
       <c r="L178" s="1" t="n">
+        <v>6.138</v>
+      </c>
+      <c r="M178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="M178" s="1" t="n">
+      <c r="N178" s="1" t="n">
         <v>6.138</v>
       </c>
     </row>
@@ -8149,9 +8686,12 @@
         <v>0.1377</v>
       </c>
       <c r="L179" s="1" t="n">
+        <v>0.1363</v>
+      </c>
+      <c r="M179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="M179" s="1" t="n">
+      <c r="N179" s="1" t="n">
         <v>0.136</v>
       </c>
     </row>
@@ -8192,9 +8732,12 @@
         <v>0.005083</v>
       </c>
       <c r="L180" s="1" t="n">
+        <v>0.005054</v>
+      </c>
+      <c r="M180" s="1" t="n">
         <v>0.005154</v>
       </c>
-      <c r="M180" s="1" t="n">
+      <c r="N180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -8235,9 +8778,12 @@
         <v>0.01202</v>
       </c>
       <c r="L181" s="1" t="n">
+        <v>0.01198</v>
+      </c>
+      <c r="M181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="M181" s="1" t="n">
+      <c r="N181" s="1" t="n">
         <v>0.01189</v>
       </c>
     </row>
@@ -8278,9 +8824,12 @@
         <v>0.007344</v>
       </c>
       <c r="L182" s="1" t="n">
+        <v>0.007389</v>
+      </c>
+      <c r="M182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="M182" s="1" t="n">
+      <c r="N182" s="1" t="n">
         <v>0.007295</v>
       </c>
     </row>
@@ -8321,9 +8870,12 @@
         <v>0.13203</v>
       </c>
       <c r="L183" s="1" t="n">
+        <v>0.1305</v>
+      </c>
+      <c r="M183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="M183" s="1" t="n">
+      <c r="N183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -8364,9 +8916,12 @@
         <v>0.09712</v>
       </c>
       <c r="L184" s="1" t="n">
+        <v>0.09696</v>
+      </c>
+      <c r="M184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="M184" s="1" t="n">
+      <c r="N184" s="1" t="n">
         <v>0.09587</v>
       </c>
     </row>
@@ -8407,10 +8962,13 @@
         <v>0.00757</v>
       </c>
       <c r="L185" s="1" t="n">
+        <v>0.00753</v>
+      </c>
+      <c r="M185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="M185" s="1" t="n">
-        <v>0.00754</v>
+      <c r="N185" s="1" t="n">
+        <v>0.00753</v>
       </c>
     </row>
     <row r="186">
@@ -8450,9 +9008,12 @@
         <v>0.04879</v>
       </c>
       <c r="L186" s="1" t="n">
+        <v>0.04874</v>
+      </c>
+      <c r="M186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="M186" s="1" t="n">
+      <c r="N186" s="1" t="n">
         <v>0.0486</v>
       </c>
     </row>
@@ -8493,9 +9054,12 @@
         <v>0.02686</v>
       </c>
       <c r="L187" s="1" t="n">
+        <v>0.02679</v>
+      </c>
+      <c r="M187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="M187" s="1" t="n">
+      <c r="N187" s="1" t="n">
         <v>0.02674</v>
       </c>
     </row>
@@ -8536,9 +9100,12 @@
         <v>0.003315</v>
       </c>
       <c r="L188" s="1" t="n">
+        <v>0.003308</v>
+      </c>
+      <c r="M188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="M188" s="1" t="n">
+      <c r="N188" s="1" t="n">
         <v>0.003303</v>
       </c>
     </row>
@@ -8579,10 +9146,13 @@
         <v>0.2866</v>
       </c>
       <c r="L189" s="1" t="n">
+        <v>0.2859</v>
+      </c>
+      <c r="M189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="M189" s="1" t="n">
-        <v>0.286</v>
+      <c r="N189" s="1" t="n">
+        <v>0.2859</v>
       </c>
     </row>
     <row r="190">
@@ -8622,10 +9192,13 @@
         <v>0.01797</v>
       </c>
       <c r="L190" s="1" t="n">
+        <v>0.0179</v>
+      </c>
+      <c r="M190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="M190" s="1" t="n">
-        <v>0.01797</v>
+      <c r="N190" s="1" t="n">
+        <v>0.0179</v>
       </c>
     </row>
     <row r="191">
@@ -8665,9 +9238,12 @@
         <v>0.2578</v>
       </c>
       <c r="L191" s="1" t="n">
+        <v>0.2576</v>
+      </c>
+      <c r="M191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="M191" s="1" t="n">
+      <c r="N191" s="1" t="n">
         <v>0.2574</v>
       </c>
     </row>
@@ -8708,10 +9284,13 @@
         <v>0.03799</v>
       </c>
       <c r="L192" s="1" t="n">
+        <v>0.03766</v>
+      </c>
+      <c r="M192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="M192" s="1" t="n">
-        <v>0.03799</v>
+      <c r="N192" s="1" t="n">
+        <v>0.03766</v>
       </c>
     </row>
     <row r="193">
@@ -8751,9 +9330,12 @@
         <v>0.000224</v>
       </c>
       <c r="L193" s="1" t="n">
-        <v>0.000224</v>
+        <v>0.0002243</v>
       </c>
       <c r="M193" s="1" t="n">
+        <v>0.0002243</v>
+      </c>
+      <c r="N193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -8794,9 +9376,12 @@
         <v>4.116</v>
       </c>
       <c r="L194" s="1" t="n">
+        <v>4.106</v>
+      </c>
+      <c r="M194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="M194" s="1" t="n">
+      <c r="N194" s="1" t="n">
         <v>4.091</v>
       </c>
     </row>
@@ -8840,6 +9425,9 @@
         <v>0.999401</v>
       </c>
       <c r="M195" s="1" t="n">
+        <v>0.999401</v>
+      </c>
+      <c r="N195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -8880,9 +9468,12 @@
         <v>4.315</v>
       </c>
       <c r="L196" s="1" t="n">
+        <v>4.295</v>
+      </c>
+      <c r="M196" s="1" t="n">
         <v>4.347</v>
       </c>
-      <c r="M196" s="1" t="n">
+      <c r="N196" s="1" t="n">
         <v>4.276</v>
       </c>
     </row>
@@ -8923,9 +9514,12 @@
         <v>0.15232</v>
       </c>
       <c r="L197" s="1" t="n">
+        <v>0.15185</v>
+      </c>
+      <c r="M197" s="1" t="n">
         <v>0.15232</v>
       </c>
-      <c r="M197" s="1" t="n">
+      <c r="N197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -8966,9 +9560,12 @@
         <v>0.007899</v>
       </c>
       <c r="L198" s="1" t="n">
+        <v>0.007766</v>
+      </c>
+      <c r="M198" s="1" t="n">
         <v>0.007899</v>
       </c>
-      <c r="M198" s="1" t="n">
+      <c r="N198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -9009,9 +9606,12 @@
         <v>0.4492</v>
       </c>
       <c r="L199" s="1" t="n">
+        <v>0.4492</v>
+      </c>
+      <c r="M199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="M199" s="1" t="n">
+      <c r="N199" s="1" t="n">
         <v>0.4482</v>
       </c>
     </row>
@@ -9052,9 +9652,12 @@
         <v>0.5911999999999999</v>
       </c>
       <c r="L200" s="1" t="n">
+        <v>0.5895</v>
+      </c>
+      <c r="M200" s="1" t="n">
         <v>0.5911999999999999</v>
       </c>
-      <c r="M200" s="1" t="n">
+      <c r="N200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -9095,9 +9698,12 @@
         <v>0.09329999999999999</v>
       </c>
       <c r="L201" s="1" t="n">
+        <v>0.09320000000000001</v>
+      </c>
+      <c r="M201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="M201" s="1" t="n">
+      <c r="N201" s="1" t="n">
         <v>0.0931</v>
       </c>
     </row>
@@ -9138,10 +9744,13 @@
         <v>0.06055</v>
       </c>
       <c r="L202" s="1" t="n">
+        <v>0.06041</v>
+      </c>
+      <c r="M202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="M202" s="1" t="n">
-        <v>0.06044</v>
+      <c r="N202" s="1" t="n">
+        <v>0.06041</v>
       </c>
     </row>
     <row r="203">
@@ -9181,9 +9790,12 @@
         <v>0.00831</v>
       </c>
       <c r="L203" s="1" t="n">
+        <v>0.00843</v>
+      </c>
+      <c r="M203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="M203" s="1" t="n">
+      <c r="N203" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -9224,9 +9836,12 @@
         <v>0.00419</v>
       </c>
       <c r="L204" s="1" t="n">
+        <v>0.00418</v>
+      </c>
+      <c r="M204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="M204" s="1" t="n">
+      <c r="N204" s="1" t="n">
         <v>0.00418</v>
       </c>
     </row>
@@ -9267,10 +9882,13 @@
         <v>0.009103</v>
       </c>
       <c r="L205" s="1" t="n">
+        <v>0.009070999999999999</v>
+      </c>
+      <c r="M205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="M205" s="1" t="n">
-        <v>0.009103</v>
+      <c r="N205" s="1" t="n">
+        <v>0.009070999999999999</v>
       </c>
     </row>
     <row r="206">
@@ -9310,9 +9928,12 @@
         <v>0.2418</v>
       </c>
       <c r="L206" s="1" t="n">
+        <v>0.2395</v>
+      </c>
+      <c r="M206" s="1" t="n">
         <v>0.2418</v>
       </c>
-      <c r="M206" s="1" t="n">
+      <c r="N206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -9353,10 +9974,13 @@
         <v>0.02098</v>
       </c>
       <c r="L207" s="1" t="n">
+        <v>0.02053</v>
+      </c>
+      <c r="M207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="M207" s="1" t="n">
-        <v>0.02077</v>
+      <c r="N207" s="1" t="n">
+        <v>0.02053</v>
       </c>
     </row>
     <row r="208">
@@ -9396,9 +10020,12 @@
         <v>0.237</v>
       </c>
       <c r="L208" s="1" t="n">
+        <v>0.2365</v>
+      </c>
+      <c r="M208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="M208" s="1" t="n">
+      <c r="N208" s="1" t="n">
         <v>0.2364</v>
       </c>
     </row>
@@ -9439,9 +10066,12 @@
         <v>0.3586</v>
       </c>
       <c r="L209" s="1" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="M209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="M209" s="1" t="n">
+      <c r="N209" s="1" t="n">
         <v>0.3586</v>
       </c>
     </row>
@@ -9482,9 +10112,12 @@
         <v>0.04247</v>
       </c>
       <c r="L210" s="1" t="n">
+        <v>0.04241</v>
+      </c>
+      <c r="M210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="M210" s="1" t="n">
+      <c r="N210" s="1" t="n">
         <v>0.04236</v>
       </c>
     </row>
@@ -9525,9 +10158,12 @@
         <v>0.0004278</v>
       </c>
       <c r="L211" s="1" t="n">
+        <v>0.0004274</v>
+      </c>
+      <c r="M211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="M211" s="1" t="n">
+      <c r="N211" s="1" t="n">
         <v>0.0004256</v>
       </c>
     </row>
@@ -9568,10 +10204,13 @@
         <v>0.02156</v>
       </c>
       <c r="L212" s="1" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="M212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="M212" s="1" t="n">
-        <v>0.02151</v>
+      <c r="N212" s="1" t="n">
+        <v>0.0215</v>
       </c>
     </row>
     <row r="213">
@@ -9611,9 +10250,12 @@
         <v>0.1146</v>
       </c>
       <c r="L213" s="1" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="M213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="M213" s="1" t="n">
+      <c r="N213" s="1" t="n">
         <v>0.1137</v>
       </c>
     </row>
@@ -9654,9 +10296,12 @@
         <v>0.04183</v>
       </c>
       <c r="L214" s="1" t="n">
+        <v>0.04187</v>
+      </c>
+      <c r="M214" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="M214" s="1" t="n">
+      <c r="N214" s="1" t="n">
         <v>0.04174</v>
       </c>
     </row>
@@ -9697,10 +10342,13 @@
         <v>0.009896</v>
       </c>
       <c r="L215" s="1" t="n">
+        <v>0.009887</v>
+      </c>
+      <c r="M215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="M215" s="1" t="n">
-        <v>0.009896</v>
+      <c r="N215" s="1" t="n">
+        <v>0.009887</v>
       </c>
     </row>
     <row r="216">
@@ -9740,9 +10388,12 @@
         <v>0.06419999999999999</v>
       </c>
       <c r="L216" s="1" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="M216" s="1" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="M216" s="1" t="n">
+      <c r="N216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -9783,9 +10434,12 @@
         <v>0.004248</v>
       </c>
       <c r="L217" s="1" t="n">
-        <v>0.004248</v>
+        <v>0.004258</v>
       </c>
       <c r="M217" s="1" t="n">
+        <v>0.004258</v>
+      </c>
+      <c r="N217" s="1" t="n">
         <v>0.004177</v>
       </c>
     </row>
@@ -9826,9 +10480,12 @@
         <v>0.01008</v>
       </c>
       <c r="L218" s="1" t="n">
+        <v>0.01003</v>
+      </c>
+      <c r="M218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="M218" s="1" t="n">
+      <c r="N218" s="1" t="n">
         <v>0.009820000000000001</v>
       </c>
     </row>
@@ -9869,9 +10526,12 @@
         <v>0.03003</v>
       </c>
       <c r="L219" s="1" t="n">
+        <v>0.03011</v>
+      </c>
+      <c r="M219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="M219" s="1" t="n">
+      <c r="N219" s="1" t="n">
         <v>0.02958</v>
       </c>
     </row>
@@ -9912,9 +10572,12 @@
         <v>2.298</v>
       </c>
       <c r="L220" s="1" t="n">
+        <v>2.292</v>
+      </c>
+      <c r="M220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="M220" s="1" t="n">
+      <c r="N220" s="1" t="n">
         <v>2.291</v>
       </c>
     </row>
@@ -9955,9 +10618,12 @@
         <v>0.022861</v>
       </c>
       <c r="L221" s="1" t="n">
+        <v>0.022886</v>
+      </c>
+      <c r="M221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="M221" s="1" t="n">
+      <c r="N221" s="1" t="n">
         <v>0.022861</v>
       </c>
     </row>
@@ -9998,9 +10664,12 @@
         <v>0.037</v>
       </c>
       <c r="L222" s="1" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="M222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="M222" s="1" t="n">
+      <c r="N222" s="1" t="n">
         <v>0.0369</v>
       </c>
     </row>
@@ -10041,9 +10710,12 @@
         <v>0.2934</v>
       </c>
       <c r="L223" s="1" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="M223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="M223" s="1" t="n">
+      <c r="N223" s="1" t="n">
         <v>0.2918</v>
       </c>
     </row>
@@ -10084,9 +10756,12 @@
         <v>0.01561</v>
       </c>
       <c r="L224" s="1" t="n">
+        <v>0.01558</v>
+      </c>
+      <c r="M224" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="M224" s="1" t="n">
+      <c r="N224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -10127,9 +10802,12 @@
         <v>0.0004069</v>
       </c>
       <c r="L225" s="1" t="n">
+        <v>0.0004074</v>
+      </c>
+      <c r="M225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="M225" s="1" t="n">
+      <c r="N225" s="1" t="n">
         <v>0.0004069</v>
       </c>
     </row>
@@ -10170,10 +10848,13 @@
         <v>0.0863</v>
       </c>
       <c r="L226" s="1" t="n">
+        <v>0.08623</v>
+      </c>
+      <c r="M226" s="1" t="n">
         <v>0.08815000000000001</v>
       </c>
-      <c r="M226" s="1" t="n">
-        <v>0.0863</v>
+      <c r="N226" s="1" t="n">
+        <v>0.08623</v>
       </c>
     </row>
     <row r="227">
@@ -10213,9 +10894,12 @@
         <v>0.953</v>
       </c>
       <c r="L227" s="1" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="M227" s="1" t="n">
         <v>0.959</v>
       </c>
-      <c r="M227" s="1" t="n">
+      <c r="N227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -10256,9 +10940,12 @@
         <v>0.05546</v>
       </c>
       <c r="L228" s="1" t="n">
+        <v>0.0557</v>
+      </c>
+      <c r="M228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="M228" s="1" t="n">
+      <c r="N228" s="1" t="n">
         <v>0.05546</v>
       </c>
     </row>
@@ -10299,9 +10986,12 @@
         <v>0.002011</v>
       </c>
       <c r="L229" s="1" t="n">
+        <v>0.002009</v>
+      </c>
+      <c r="M229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="M229" s="1" t="n">
+      <c r="N229" s="1" t="n">
         <v>0.002003</v>
       </c>
     </row>
@@ -10342,9 +11032,12 @@
         <v>0.023101</v>
       </c>
       <c r="L230" s="1" t="n">
+        <v>0.02285</v>
+      </c>
+      <c r="M230" s="1" t="n">
         <v>0.023101</v>
       </c>
-      <c r="M230" s="1" t="n">
+      <c r="N230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -10385,9 +11078,12 @@
         <v>0.05364</v>
       </c>
       <c r="L231" s="1" t="n">
+        <v>0.05358</v>
+      </c>
+      <c r="M231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="M231" s="1" t="n">
+      <c r="N231" s="1" t="n">
         <v>0.0535</v>
       </c>
     </row>
@@ -10428,9 +11124,12 @@
         <v>0.059</v>
       </c>
       <c r="L232" s="1" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="M232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="M232" s="1" t="n">
+      <c r="N232" s="1" t="n">
         <v>0.0587</v>
       </c>
     </row>
@@ -10471,9 +11170,12 @@
         <v>0.001679</v>
       </c>
       <c r="L233" s="1" t="n">
+        <v>0.001681</v>
+      </c>
+      <c r="M233" s="1" t="n">
         <v>0.001701</v>
       </c>
-      <c r="M233" s="1" t="n">
+      <c r="N233" s="1" t="n">
         <v>0.001678</v>
       </c>
     </row>
@@ -10514,10 +11216,13 @@
         <v>0.005747</v>
       </c>
       <c r="L234" s="1" t="n">
+        <v>0.005728</v>
+      </c>
+      <c r="M234" s="1" t="n">
         <v>0.005854</v>
       </c>
-      <c r="M234" s="1" t="n">
-        <v>0.005747</v>
+      <c r="N234" s="1" t="n">
+        <v>0.005728</v>
       </c>
     </row>
     <row r="235">
@@ -10557,10 +11262,13 @@
         <v>0.12485</v>
       </c>
       <c r="L235" s="1" t="n">
+        <v>0.12449</v>
+      </c>
+      <c r="M235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="M235" s="1" t="n">
-        <v>0.12453</v>
+      <c r="N235" s="1" t="n">
+        <v>0.12449</v>
       </c>
     </row>
     <row r="236">
@@ -10600,9 +11308,12 @@
         <v>64.79000000000001</v>
       </c>
       <c r="L236" s="1" t="n">
+        <v>64.77</v>
+      </c>
+      <c r="M236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="M236" s="1" t="n">
+      <c r="N236" s="1" t="n">
         <v>64.73</v>
       </c>
     </row>
@@ -10643,10 +11354,13 @@
         <v>0.102</v>
       </c>
       <c r="L237" s="1" t="n">
+        <v>0.1015</v>
+      </c>
+      <c r="M237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="M237" s="1" t="n">
-        <v>0.1016</v>
+      <c r="N237" s="1" t="n">
+        <v>0.1015</v>
       </c>
     </row>
     <row r="238">
@@ -10686,9 +11400,12 @@
         <v>0.004006</v>
       </c>
       <c r="L238" s="1" t="n">
-        <v>0.004006</v>
+        <v>0.004035</v>
       </c>
       <c r="M238" s="1" t="n">
+        <v>0.004035</v>
+      </c>
+      <c r="N238" s="1" t="n">
         <v>0.003925</v>
       </c>
     </row>
@@ -10729,9 +11446,12 @@
         <v>0.01543</v>
       </c>
       <c r="L239" s="1" t="n">
+        <v>0.01555</v>
+      </c>
+      <c r="M239" s="1" t="n">
         <v>0.01562</v>
       </c>
-      <c r="M239" s="1" t="n">
+      <c r="N239" s="1" t="n">
         <v>0.01532</v>
       </c>
     </row>
@@ -10772,9 +11492,12 @@
         <v>0.05622</v>
       </c>
       <c r="L240" s="1" t="n">
+        <v>0.05604</v>
+      </c>
+      <c r="M240" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="M240" s="1" t="n">
+      <c r="N240" s="1" t="n">
         <v>0.05598</v>
       </c>
     </row>
@@ -10815,9 +11538,12 @@
         <v>0.0114</v>
       </c>
       <c r="L241" s="1" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="M241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="M241" s="1" t="n">
+      <c r="N241" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -10858,10 +11584,13 @@
         <v>0.3353</v>
       </c>
       <c r="L242" s="1" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="M242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="M242" s="1" t="n">
-        <v>0.3334</v>
+      <c r="N242" s="1" t="n">
+        <v>0.3333</v>
       </c>
     </row>
     <row r="243">
@@ -10901,10 +11630,13 @@
         <v>0.01231</v>
       </c>
       <c r="L243" s="1" t="n">
+        <v>0.01227</v>
+      </c>
+      <c r="M243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="M243" s="1" t="n">
-        <v>0.01229</v>
+      <c r="N243" s="1" t="n">
+        <v>0.01227</v>
       </c>
     </row>
     <row r="244">
@@ -10944,9 +11676,12 @@
         <v>0.08083</v>
       </c>
       <c r="L244" s="1" t="n">
-        <v>0.08083</v>
+        <v>0.08087</v>
       </c>
       <c r="M244" s="1" t="n">
+        <v>0.08087</v>
+      </c>
+      <c r="N244" s="1" t="n">
         <v>0.07997</v>
       </c>
     </row>
@@ -10987,9 +11722,12 @@
         <v>0.00783</v>
       </c>
       <c r="L245" s="1" t="n">
+        <v>0.007815000000000001</v>
+      </c>
+      <c r="M245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="M245" s="1" t="n">
+      <c r="N245" s="1" t="n">
         <v>0.007769</v>
       </c>
     </row>
@@ -11030,9 +11768,12 @@
         <v>0.03032</v>
       </c>
       <c r="L246" s="1" t="n">
+        <v>0.03033</v>
+      </c>
+      <c r="M246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="M246" s="1" t="n">
+      <c r="N246" s="1" t="n">
         <v>0.03025</v>
       </c>
     </row>
@@ -11073,10 +11814,13 @@
         <v>0.1806</v>
       </c>
       <c r="L247" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M247" s="1" t="n">
         <v>0.1827</v>
       </c>
-      <c r="M247" s="1" t="n">
-        <v>0.1801</v>
+      <c r="N247" s="1" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="248">
@@ -11116,10 +11860,13 @@
         <v>0.05889</v>
       </c>
       <c r="L248" s="1" t="n">
+        <v>0.05875</v>
+      </c>
+      <c r="M248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="M248" s="1" t="n">
-        <v>0.05884</v>
+      <c r="N248" s="1" t="n">
+        <v>0.05875</v>
       </c>
     </row>
     <row r="249">
@@ -11159,10 +11906,13 @@
         <v>0.1662</v>
       </c>
       <c r="L249" s="1" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="M249" s="1" t="n">
         <v>0.1684</v>
       </c>
-      <c r="M249" s="1" t="n">
-        <v>0.1662</v>
+      <c r="N249" s="1" t="n">
+        <v>0.166</v>
       </c>
     </row>
     <row r="250">
@@ -11202,9 +11952,12 @@
         <v>0.01921</v>
       </c>
       <c r="L250" s="1" t="n">
+        <v>0.01913</v>
+      </c>
+      <c r="M250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="M250" s="1" t="n">
+      <c r="N250" s="1" t="n">
         <v>0.01906</v>
       </c>
     </row>
@@ -11245,9 +11998,12 @@
         <v>0.02307</v>
       </c>
       <c r="L251" s="1" t="n">
-        <v>0.02318</v>
+        <v>0.02322</v>
       </c>
       <c r="M251" s="1" t="n">
+        <v>0.02322</v>
+      </c>
+      <c r="N251" s="1" t="n">
         <v>0.02295</v>
       </c>
     </row>
@@ -11288,9 +12044,12 @@
         <v>0.30521</v>
       </c>
       <c r="L252" s="1" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="M252" s="1" t="n">
         <v>0.31227</v>
       </c>
-      <c r="M252" s="1" t="n">
+      <c r="N252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -11331,9 +12090,12 @@
         <v>0.006064</v>
       </c>
       <c r="L253" s="1" t="n">
+        <v>0.006041</v>
+      </c>
+      <c r="M253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="M253" s="1" t="n">
+      <c r="N253" s="1" t="n">
         <v>0.005971</v>
       </c>
     </row>
@@ -11374,9 +12136,12 @@
         <v>0.6137</v>
       </c>
       <c r="L254" s="1" t="n">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="M254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="M254" s="1" t="n">
+      <c r="N254" s="1" t="n">
         <v>0.6116</v>
       </c>
     </row>
@@ -11417,9 +12182,12 @@
         <v>0.10655</v>
       </c>
       <c r="L255" s="1" t="n">
+        <v>0.10643</v>
+      </c>
+      <c r="M255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="M255" s="1" t="n">
+      <c r="N255" s="1" t="n">
         <v>0.10612</v>
       </c>
     </row>
@@ -11463,6 +12231,9 @@
         <v>0.0916</v>
       </c>
       <c r="M256" s="1" t="n">
+        <v>0.0916</v>
+      </c>
+      <c r="N256" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -11503,9 +12274,12 @@
         <v>0.01468</v>
       </c>
       <c r="L257" s="1" t="n">
+        <v>0.01446</v>
+      </c>
+      <c r="M257" s="1" t="n">
         <v>0.01468</v>
       </c>
-      <c r="M257" s="1" t="n">
+      <c r="N257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -11546,10 +12320,13 @@
         <v>0.05083</v>
       </c>
       <c r="L258" s="1" t="n">
+        <v>0.05051</v>
+      </c>
+      <c r="M258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="M258" s="1" t="n">
-        <v>0.05083</v>
+      <c r="N258" s="1" t="n">
+        <v>0.05051</v>
       </c>
     </row>
     <row r="259">
@@ -11589,10 +12366,13 @@
         <v>0.00814</v>
       </c>
       <c r="L259" s="1" t="n">
+        <v>0.00809</v>
+      </c>
+      <c r="M259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="M259" s="1" t="n">
-        <v>0.008109999999999999</v>
+      <c r="N259" s="1" t="n">
+        <v>0.00809</v>
       </c>
     </row>
     <row r="260">
@@ -11632,9 +12412,12 @@
         <v>0.1906</v>
       </c>
       <c r="L260" s="1" t="n">
+        <v>0.1903</v>
+      </c>
+      <c r="M260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="M260" s="1" t="n">
+      <c r="N260" s="1" t="n">
         <v>0.1894</v>
       </c>
     </row>
@@ -11675,10 +12458,13 @@
         <v>0.0982</v>
       </c>
       <c r="L261" s="1" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="M261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="M261" s="1" t="n">
-        <v>0.0982</v>
+      <c r="N261" s="1" t="n">
+        <v>0.09810000000000001</v>
       </c>
     </row>
     <row r="262">
@@ -11718,9 +12504,12 @@
         <v>0.2118</v>
       </c>
       <c r="L262" s="1" t="n">
+        <v>0.2113</v>
+      </c>
+      <c r="M262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="M262" s="1" t="n">
+      <c r="N262" s="1" t="n">
         <v>0.2113</v>
       </c>
     </row>
@@ -11761,9 +12550,12 @@
         <v>0.008560999999999999</v>
       </c>
       <c r="L263" s="1" t="n">
+        <v>0.008525</v>
+      </c>
+      <c r="M263" s="1" t="n">
         <v>0.008560999999999999</v>
       </c>
-      <c r="M263" s="1" t="n">
+      <c r="N263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -11804,9 +12596,12 @@
         <v>2.634</v>
       </c>
       <c r="L264" s="1" t="n">
+        <v>2.634</v>
+      </c>
+      <c r="M264" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="M264" s="1" t="n">
+      <c r="N264" s="1" t="n">
         <v>2.632</v>
       </c>
     </row>
@@ -11847,9 +12642,12 @@
         <v>0.01862</v>
       </c>
       <c r="L265" s="1" t="n">
+        <v>0.01862</v>
+      </c>
+      <c r="M265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="M265" s="1" t="n">
+      <c r="N265" s="1" t="n">
         <v>0.01847</v>
       </c>
     </row>
@@ -11893,6 +12691,9 @@
         <v>0.3607</v>
       </c>
       <c r="M266" s="1" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="N266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -11933,9 +12734,12 @@
         <v>0.03446</v>
       </c>
       <c r="L267" s="1" t="n">
+        <v>0.03434</v>
+      </c>
+      <c r="M267" s="1" t="n">
         <v>0.03464</v>
       </c>
-      <c r="M267" s="1" t="n">
+      <c r="N267" s="1" t="n">
         <v>0.03408</v>
       </c>
     </row>
@@ -11976,9 +12780,12 @@
         <v>0.119</v>
       </c>
       <c r="L268" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="M268" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="M268" s="1" t="n">
+      <c r="N268" s="1" t="n">
         <v>0.118</v>
       </c>
     </row>
@@ -12019,9 +12826,12 @@
         <v>0.08011</v>
       </c>
       <c r="L269" s="1" t="n">
+        <v>0.07996</v>
+      </c>
+      <c r="M269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="M269" s="1" t="n">
+      <c r="N269" s="1" t="n">
         <v>0.07973</v>
       </c>
     </row>
@@ -12062,9 +12872,12 @@
         <v>0.01384</v>
       </c>
       <c r="L270" s="1" t="n">
+        <v>0.01382</v>
+      </c>
+      <c r="M270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="M270" s="1" t="n">
+      <c r="N270" s="1" t="n">
         <v>0.01382</v>
       </c>
     </row>
@@ -12105,9 +12918,12 @@
         <v>0.007594</v>
       </c>
       <c r="L271" s="1" t="n">
+        <v>0.007568</v>
+      </c>
+      <c r="M271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="M271" s="1" t="n">
+      <c r="N271" s="1" t="n">
         <v>0.007558</v>
       </c>
     </row>
@@ -12148,9 +12964,12 @@
         <v>0.07444000000000001</v>
       </c>
       <c r="L272" s="1" t="n">
+        <v>0.07423</v>
+      </c>
+      <c r="M272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="M272" s="1" t="n">
+      <c r="N272" s="1" t="n">
         <v>0.0741</v>
       </c>
     </row>
@@ -12191,9 +13010,12 @@
         <v>3.15e-05</v>
       </c>
       <c r="L273" s="1" t="n">
+        <v>3.15e-05</v>
+      </c>
+      <c r="M273" s="1" t="n">
         <v>3.16e-05</v>
       </c>
-      <c r="M273" s="1" t="n">
+      <c r="N273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -12234,9 +13056,12 @@
         <v>0.005506</v>
       </c>
       <c r="L274" s="1" t="n">
+        <v>0.00548</v>
+      </c>
+      <c r="M274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="M274" s="1" t="n">
+      <c r="N274" s="1" t="n">
         <v>0.005469</v>
       </c>
     </row>
@@ -12277,9 +13102,12 @@
         <v>0.1809</v>
       </c>
       <c r="L275" s="1" t="n">
+        <v>0.1812</v>
+      </c>
+      <c r="M275" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="M275" s="1" t="n">
+      <c r="N275" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -12320,10 +13148,13 @@
         <v>0.006843</v>
       </c>
       <c r="L276" s="1" t="n">
+        <v>0.006827</v>
+      </c>
+      <c r="M276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="M276" s="1" t="n">
-        <v>0.006843</v>
+      <c r="N276" s="1" t="n">
+        <v>0.006827</v>
       </c>
     </row>
     <row r="277">
@@ -12363,9 +13194,12 @@
         <v>0.131</v>
       </c>
       <c r="L277" s="1" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="M277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="M277" s="1" t="n">
+      <c r="N277" s="1" t="n">
         <v>0.1303</v>
       </c>
     </row>
@@ -12406,9 +13240,12 @@
         <v>0.02334</v>
       </c>
       <c r="L278" s="1" t="n">
+        <v>0.02327</v>
+      </c>
+      <c r="M278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="M278" s="1" t="n">
+      <c r="N278" s="1" t="n">
         <v>0.02308</v>
       </c>
     </row>
@@ -12449,9 +13286,12 @@
         <v>0.01814</v>
       </c>
       <c r="L279" s="1" t="n">
+        <v>0.01822</v>
+      </c>
+      <c r="M279" s="1" t="n">
         <v>0.01827</v>
       </c>
-      <c r="M279" s="1" t="n">
+      <c r="N279" s="1" t="n">
         <v>0.01812</v>
       </c>
     </row>
@@ -12492,10 +13332,13 @@
         <v>0.03728</v>
       </c>
       <c r="L280" s="1" t="n">
+        <v>0.03704</v>
+      </c>
+      <c r="M280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="M280" s="1" t="n">
-        <v>0.03715</v>
+      <c r="N280" s="1" t="n">
+        <v>0.03704</v>
       </c>
     </row>
     <row r="281">
@@ -12535,9 +13378,12 @@
         <v>0.0399</v>
       </c>
       <c r="L281" s="1" t="n">
+        <v>0.03984</v>
+      </c>
+      <c r="M281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="M281" s="1" t="n">
+      <c r="N281" s="1" t="n">
         <v>0.03953</v>
       </c>
     </row>
@@ -12578,9 +13424,12 @@
         <v>0.3012</v>
       </c>
       <c r="L282" s="1" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="M282" s="1" t="n">
         <v>0.3059</v>
       </c>
-      <c r="M282" s="1" t="n">
+      <c r="N282" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -12621,9 +13470,12 @@
         <v>0.01124</v>
       </c>
       <c r="L283" s="1" t="n">
+        <v>0.01121</v>
+      </c>
+      <c r="M283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="M283" s="1" t="n">
+      <c r="N283" s="1" t="n">
         <v>0.01119</v>
       </c>
     </row>
@@ -12664,9 +13516,12 @@
         <v>9.799999999999999e-06</v>
       </c>
       <c r="L284" s="1" t="n">
+        <v>9.7e-06</v>
+      </c>
+      <c r="M284" s="1" t="n">
         <v>9.799999999999999e-06</v>
       </c>
-      <c r="M284" s="1" t="n">
+      <c r="N284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -12707,9 +13562,12 @@
         <v>0.1151</v>
       </c>
       <c r="L285" s="1" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="M285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="M285" s="1" t="n">
+      <c r="N285" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -12750,9 +13608,12 @@
         <v>0.00343</v>
       </c>
       <c r="L286" s="1" t="n">
+        <v>0.00343</v>
+      </c>
+      <c r="M286" s="1" t="n">
         <v>0.003485</v>
       </c>
-      <c r="M286" s="1" t="n">
+      <c r="N286" s="1" t="n">
         <v>0.003422</v>
       </c>
     </row>
@@ -12793,9 +13654,12 @@
         <v>0.08577</v>
       </c>
       <c r="L287" s="1" t="n">
+        <v>0.08562</v>
+      </c>
+      <c r="M287" s="1" t="n">
         <v>0.08577</v>
       </c>
-      <c r="M287" s="1" t="n">
+      <c r="N287" s="1" t="n">
         <v>0.08486</v>
       </c>
     </row>
@@ -12836,9 +13700,12 @@
         <v>0.10008</v>
       </c>
       <c r="L288" s="1" t="n">
-        <v>0.1001</v>
+        <v>0.10076</v>
       </c>
       <c r="M288" s="1" t="n">
+        <v>0.10076</v>
+      </c>
+      <c r="N288" s="1" t="n">
         <v>0.09869</v>
       </c>
     </row>
@@ -12879,9 +13746,12 @@
         <v>0.4334</v>
       </c>
       <c r="L289" s="1" t="n">
+        <v>0.4326</v>
+      </c>
+      <c r="M289" s="1" t="n">
         <v>0.4359</v>
       </c>
-      <c r="M289" s="1" t="n">
+      <c r="N289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -12922,9 +13792,12 @@
         <v>0.03911</v>
       </c>
       <c r="L290" s="1" t="n">
+        <v>0.03915</v>
+      </c>
+      <c r="M290" s="1" t="n">
         <v>0.03966</v>
       </c>
-      <c r="M290" s="1" t="n">
+      <c r="N290" s="1" t="n">
         <v>0.03878</v>
       </c>
     </row>
@@ -12965,10 +13838,13 @@
         <v>0.2377</v>
       </c>
       <c r="L291" s="1" t="n">
+        <v>0.2374</v>
+      </c>
+      <c r="M291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="M291" s="1" t="n">
-        <v>0.2376</v>
+      <c r="N291" s="1" t="n">
+        <v>0.2374</v>
       </c>
     </row>
     <row r="292">
@@ -13008,10 +13884,13 @@
         <v>0.2826</v>
       </c>
       <c r="L292" s="1" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="M292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="M292" s="1" t="n">
-        <v>0.2826</v>
+      <c r="N292" s="1" t="n">
+        <v>0.28254</v>
       </c>
     </row>
     <row r="293">
@@ -13051,9 +13930,12 @@
         <v>0.1499</v>
       </c>
       <c r="L293" s="1" t="n">
+        <v>0.1498</v>
+      </c>
+      <c r="M293" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="M293" s="1" t="n">
+      <c r="N293" s="1" t="n">
         <v>0.1489</v>
       </c>
     </row>
@@ -13094,10 +13976,13 @@
         <v>4.212</v>
       </c>
       <c r="L294" s="1" t="n">
+        <v>4.204</v>
+      </c>
+      <c r="M294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="M294" s="1" t="n">
-        <v>4.205</v>
+      <c r="N294" s="1" t="n">
+        <v>4.204</v>
       </c>
     </row>
     <row r="295">
@@ -13137,9 +14022,12 @@
         <v>0.03294</v>
       </c>
       <c r="L295" s="1" t="n">
+        <v>0.03302</v>
+      </c>
+      <c r="M295" s="1" t="n">
         <v>0.03339</v>
       </c>
-      <c r="M295" s="1" t="n">
+      <c r="N295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -13180,10 +14068,13 @@
         <v>0.000969</v>
       </c>
       <c r="L296" s="1" t="n">
+        <v>0.000965</v>
+      </c>
+      <c r="M296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="M296" s="1" t="n">
-        <v>0.000969</v>
+      <c r="N296" s="1" t="n">
+        <v>0.000965</v>
       </c>
     </row>
     <row r="297">
@@ -13223,9 +14114,12 @@
         <v>0.08183</v>
       </c>
       <c r="L297" s="1" t="n">
+        <v>0.08172</v>
+      </c>
+      <c r="M297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="M297" s="1" t="n">
+      <c r="N297" s="1" t="n">
         <v>0.08154</v>
       </c>
     </row>
@@ -13266,9 +14160,12 @@
         <v>0.05798</v>
       </c>
       <c r="L298" s="1" t="n">
+        <v>0.05812</v>
+      </c>
+      <c r="M298" s="1" t="n">
         <v>0.05821</v>
       </c>
-      <c r="M298" s="1" t="n">
+      <c r="N298" s="1" t="n">
         <v>0.05745</v>
       </c>
     </row>
@@ -13309,9 +14206,12 @@
         <v>0.09154</v>
       </c>
       <c r="L299" s="1" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="M299" s="1" t="n">
         <v>0.0917</v>
       </c>
-      <c r="M299" s="1" t="n">
+      <c r="N299" s="1" t="n">
         <v>0.09066</v>
       </c>
     </row>
@@ -13352,9 +14252,12 @@
         <v>0.02759</v>
       </c>
       <c r="L300" s="1" t="n">
+        <v>0.02752</v>
+      </c>
+      <c r="M300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="M300" s="1" t="n">
+      <c r="N300" s="1" t="n">
         <v>0.0274</v>
       </c>
     </row>
@@ -13395,9 +14298,12 @@
         <v>0.06594</v>
       </c>
       <c r="L301" s="1" t="n">
+        <v>0.06568</v>
+      </c>
+      <c r="M301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="M301" s="1" t="n">
+      <c r="N301" s="1" t="n">
         <v>0.06557</v>
       </c>
     </row>
@@ -13438,9 +14344,12 @@
         <v>0.053267</v>
       </c>
       <c r="L302" s="1" t="n">
-        <v>0.053267</v>
+        <v>0.0535</v>
       </c>
       <c r="M302" s="1" t="n">
+        <v>0.0535</v>
+      </c>
+      <c r="N302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -13481,9 +14390,12 @@
         <v>5172</v>
       </c>
       <c r="L303" s="1" t="n">
+        <v>5171.5</v>
+      </c>
+      <c r="M303" s="1" t="n">
         <v>5177.6</v>
       </c>
-      <c r="M303" s="1" t="n">
+      <c r="N303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -13524,10 +14436,13 @@
         <v>14.9</v>
       </c>
       <c r="L304" s="1" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="M304" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="M304" s="1" t="n">
-        <v>14.9</v>
+      <c r="N304" s="1" t="n">
+        <v>14.88</v>
       </c>
     </row>
     <row r="305">
@@ -13567,9 +14482,12 @@
         <v>0.003714</v>
       </c>
       <c r="L305" s="1" t="n">
+        <v>0.003711</v>
+      </c>
+      <c r="M305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="M305" s="1" t="n">
+      <c r="N305" s="1" t="n">
         <v>0.003695</v>
       </c>
     </row>
@@ -13610,9 +14528,12 @@
         <v>0.4572</v>
       </c>
       <c r="L306" s="1" t="n">
+        <v>0.4562</v>
+      </c>
+      <c r="M306" s="1" t="n">
         <v>0.4608</v>
       </c>
-      <c r="M306" s="1" t="n">
+      <c r="N306" s="1" t="n">
         <v>0.4558</v>
       </c>
     </row>
@@ -13653,9 +14574,12 @@
         <v>0.04707</v>
       </c>
       <c r="L307" s="1" t="n">
+        <v>0.04698</v>
+      </c>
+      <c r="M307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="M307" s="1" t="n">
+      <c r="N307" s="1" t="n">
         <v>0.04696</v>
       </c>
     </row>
@@ -13696,9 +14620,12 @@
         <v>1.4902</v>
       </c>
       <c r="L308" s="1" t="n">
-        <v>1.4902</v>
+        <v>1.4918</v>
       </c>
       <c r="M308" s="1" t="n">
+        <v>1.4918</v>
+      </c>
+      <c r="N308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -13739,10 +14666,13 @@
         <v>0.0007974</v>
       </c>
       <c r="L309" s="1" t="n">
+        <v>0.0007892</v>
+      </c>
+      <c r="M309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="M309" s="1" t="n">
-        <v>0.0007937</v>
+      <c r="N309" s="1" t="n">
+        <v>0.0007892</v>
       </c>
     </row>
     <row r="310">
@@ -13782,10 +14712,13 @@
         <v>4.599</v>
       </c>
       <c r="L310" s="1" t="n">
+        <v>4.579</v>
+      </c>
+      <c r="M310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="M310" s="1" t="n">
-        <v>4.599</v>
+      <c r="N310" s="1" t="n">
+        <v>4.579</v>
       </c>
     </row>
     <row r="311">
@@ -13825,9 +14758,12 @@
         <v>4.762</v>
       </c>
       <c r="L311" s="1" t="n">
+        <v>4.756</v>
+      </c>
+      <c r="M311" s="1" t="n">
         <v>4.805</v>
       </c>
-      <c r="M311" s="1" t="n">
+      <c r="N311" s="1" t="n">
         <v>4.743</v>
       </c>
     </row>
@@ -13868,9 +14804,12 @@
         <v>0.08139</v>
       </c>
       <c r="L312" s="1" t="n">
+        <v>0.08141</v>
+      </c>
+      <c r="M312" s="1" t="n">
         <v>0.08212</v>
       </c>
-      <c r="M312" s="1" t="n">
+      <c r="N312" s="1" t="n">
         <v>0.08098</v>
       </c>
     </row>
@@ -13911,9 +14850,12 @@
         <v>2.032</v>
       </c>
       <c r="L313" s="1" t="n">
+        <v>2.012</v>
+      </c>
+      <c r="M313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="M313" s="1" t="n">
+      <c r="N313" s="1" t="n">
         <v>2.012</v>
       </c>
     </row>
@@ -13957,6 +14899,9 @@
         <v>0.07260999999999999</v>
       </c>
       <c r="M314" s="1" t="n">
+        <v>0.07260999999999999</v>
+      </c>
+      <c r="N314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -13997,10 +14942,13 @@
         <v>0.95</v>
       </c>
       <c r="L315" s="1" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="M315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="M315" s="1" t="n">
-        <v>0.946</v>
+      <c r="N315" s="1" t="n">
+        <v>0.945</v>
       </c>
     </row>
     <row r="316">
@@ -14040,9 +14988,12 @@
         <v>0.131</v>
       </c>
       <c r="L316" s="1" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="M316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="M316" s="1" t="n">
+      <c r="N316" s="1" t="n">
         <v>0.1299</v>
       </c>
     </row>
@@ -14083,9 +15034,12 @@
         <v>0.1839</v>
       </c>
       <c r="L317" s="1" t="n">
+        <v>0.1828</v>
+      </c>
+      <c r="M317" s="1" t="n">
         <v>0.186</v>
       </c>
-      <c r="M317" s="1" t="n">
+      <c r="N317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -14126,9 +15080,12 @@
         <v>0.01621</v>
       </c>
       <c r="L318" s="1" t="n">
+        <v>0.01622</v>
+      </c>
+      <c r="M318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="M318" s="1" t="n">
+      <c r="N318" s="1" t="n">
         <v>0.01615</v>
       </c>
     </row>
@@ -14169,10 +15126,13 @@
         <v>0.08352</v>
       </c>
       <c r="L319" s="1" t="n">
+        <v>0.08343</v>
+      </c>
+      <c r="M319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="M319" s="1" t="n">
-        <v>0.08348999999999999</v>
+      <c r="N319" s="1" t="n">
+        <v>0.08343</v>
       </c>
     </row>
     <row r="320">
@@ -14212,9 +15172,12 @@
         <v>0.007641</v>
       </c>
       <c r="L320" s="1" t="n">
+        <v>0.00763</v>
+      </c>
+      <c r="M320" s="1" t="n">
         <v>0.007667</v>
       </c>
-      <c r="M320" s="1" t="n">
+      <c r="N320" s="1" t="n">
         <v>0.007571</v>
       </c>
     </row>
@@ -14255,9 +15218,12 @@
         <v>0.05444</v>
       </c>
       <c r="L321" s="1" t="n">
+        <v>0.0544</v>
+      </c>
+      <c r="M321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="M321" s="1" t="n">
+      <c r="N321" s="1" t="n">
         <v>0.05406</v>
       </c>
     </row>
@@ -14298,9 +15264,12 @@
         <v>0.5515</v>
       </c>
       <c r="L322" s="1" t="n">
+        <v>0.5505</v>
+      </c>
+      <c r="M322" s="1" t="n">
         <v>0.5515</v>
       </c>
-      <c r="M322" s="1" t="n">
+      <c r="N322" s="1" t="n">
         <v>0.5476</v>
       </c>
     </row>
@@ -14341,9 +15310,12 @@
         <v>0.07625</v>
       </c>
       <c r="L323" s="1" t="n">
-        <v>0.07625</v>
+        <v>0.07636999999999999</v>
       </c>
       <c r="M323" s="1" t="n">
+        <v>0.07636999999999999</v>
+      </c>
+      <c r="N323" s="1" t="n">
         <v>0.07525</v>
       </c>
     </row>
@@ -14384,9 +15356,12 @@
         <v>0.01296</v>
       </c>
       <c r="L324" s="1" t="n">
+        <v>0.012936</v>
+      </c>
+      <c r="M324" s="1" t="n">
         <v>0.013001</v>
       </c>
-      <c r="M324" s="1" t="n">
+      <c r="N324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -14427,9 +15402,12 @@
         <v>0.09909999999999999</v>
       </c>
       <c r="L325" s="1" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="M325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="M325" s="1" t="n">
+      <c r="N325" s="1" t="n">
         <v>0.0989</v>
       </c>
     </row>
@@ -14470,9 +15448,12 @@
         <v>0.01731</v>
       </c>
       <c r="L326" s="1" t="n">
+        <v>0.01739</v>
+      </c>
+      <c r="M326" s="1" t="n">
         <v>0.01765</v>
       </c>
-      <c r="M326" s="1" t="n">
+      <c r="N326" s="1" t="n">
         <v>0.01731</v>
       </c>
     </row>
@@ -14513,9 +15494,12 @@
         <v>0.0641</v>
       </c>
       <c r="L327" s="1" t="n">
+        <v>0.06394</v>
+      </c>
+      <c r="M327" s="1" t="n">
         <v>0.06435</v>
       </c>
-      <c r="M327" s="1" t="n">
+      <c r="N327" s="1" t="n">
         <v>0.06382</v>
       </c>
     </row>
@@ -14556,10 +15540,13 @@
         <v>0.2631</v>
       </c>
       <c r="L328" s="1" t="n">
+        <v>0.2622</v>
+      </c>
+      <c r="M328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="M328" s="1" t="n">
-        <v>0.2627</v>
+      <c r="N328" s="1" t="n">
+        <v>0.2622</v>
       </c>
     </row>
     <row r="329">
@@ -14599,9 +15586,12 @@
         <v>0.17328</v>
       </c>
       <c r="L329" s="1" t="n">
-        <v>0.17328</v>
+        <v>0.17341</v>
       </c>
       <c r="M329" s="1" t="n">
+        <v>0.17341</v>
+      </c>
+      <c r="N329" s="1" t="n">
         <v>0.17145</v>
       </c>
     </row>
@@ -14642,9 +15632,12 @@
         <v>2.06</v>
       </c>
       <c r="L330" s="1" t="n">
+        <v>2.047</v>
+      </c>
+      <c r="M330" s="1" t="n">
         <v>2.088</v>
       </c>
-      <c r="M330" s="1" t="n">
+      <c r="N330" s="1" t="n">
         <v>2.043</v>
       </c>
     </row>
@@ -14685,9 +15678,12 @@
         <v>0.0286</v>
       </c>
       <c r="L331" s="1" t="n">
-        <v>0.0286</v>
+        <v>0.0288</v>
       </c>
       <c r="M331" s="1" t="n">
+        <v>0.0288</v>
+      </c>
+      <c r="N331" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -14728,9 +15724,12 @@
         <v>0.006022</v>
       </c>
       <c r="L332" s="1" t="n">
-        <v>0.006031</v>
+        <v>0.006032</v>
       </c>
       <c r="M332" s="1" t="n">
+        <v>0.006032</v>
+      </c>
+      <c r="N332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -14771,9 +15770,12 @@
         <v>0.003539</v>
       </c>
       <c r="L333" s="1" t="n">
+        <v>0.003534</v>
+      </c>
+      <c r="M333" s="1" t="n">
         <v>0.003579</v>
       </c>
-      <c r="M333" s="1" t="n">
+      <c r="N333" s="1" t="n">
         <v>0.003497</v>
       </c>
     </row>
@@ -14814,9 +15816,12 @@
         <v>0.01407</v>
       </c>
       <c r="L334" s="1" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="M334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="M334" s="1" t="n">
+      <c r="N334" s="1" t="n">
         <v>0.01394</v>
       </c>
     </row>
@@ -14857,9 +15862,12 @@
         <v>1.134</v>
       </c>
       <c r="L335" s="1" t="n">
-        <v>1.134</v>
+        <v>1.136</v>
       </c>
       <c r="M335" s="1" t="n">
+        <v>1.136</v>
+      </c>
+      <c r="N335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -14900,9 +15908,12 @@
         <v>0.011258</v>
       </c>
       <c r="L336" s="1" t="n">
+        <v>0.011259</v>
+      </c>
+      <c r="M336" s="1" t="n">
         <v>0.011326</v>
       </c>
-      <c r="M336" s="1" t="n">
+      <c r="N336" s="1" t="n">
         <v>0.011238</v>
       </c>
     </row>
@@ -14943,9 +15954,12 @@
         <v>2.982</v>
       </c>
       <c r="L337" s="1" t="n">
+        <v>2.975</v>
+      </c>
+      <c r="M337" s="1" t="n">
         <v>3.043</v>
       </c>
-      <c r="M337" s="1" t="n">
+      <c r="N337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -14986,9 +16000,12 @@
         <v>0.01863</v>
       </c>
       <c r="L338" s="1" t="n">
+        <v>0.01862</v>
+      </c>
+      <c r="M338" s="1" t="n">
         <v>0.01885</v>
       </c>
-      <c r="M338" s="1" t="n">
+      <c r="N338" s="1" t="n">
         <v>0.01858</v>
       </c>
     </row>
@@ -15029,9 +16046,12 @@
         <v>0.07747999999999999</v>
       </c>
       <c r="L339" s="1" t="n">
+        <v>0.07731</v>
+      </c>
+      <c r="M339" s="1" t="n">
         <v>0.07790999999999999</v>
       </c>
-      <c r="M339" s="1" t="n">
+      <c r="N339" s="1" t="n">
         <v>0.07689</v>
       </c>
     </row>
@@ -15072,9 +16092,12 @@
         <v>0.076</v>
       </c>
       <c r="L340" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="M340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="M340" s="1" t="n">
+      <c r="N340" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -15115,10 +16138,13 @@
         <v>0.03601</v>
       </c>
       <c r="L341" s="1" t="n">
+        <v>0.03585</v>
+      </c>
+      <c r="M341" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="M341" s="1" t="n">
-        <v>0.03591</v>
+      <c r="N341" s="1" t="n">
+        <v>0.03585</v>
       </c>
     </row>
     <row r="342">
@@ -15158,9 +16184,12 @@
         <v>2613</v>
       </c>
       <c r="L342" s="1" t="n">
+        <v>2610</v>
+      </c>
+      <c r="M342" s="1" t="n">
         <v>2647</v>
       </c>
-      <c r="M342" s="1" t="n">
+      <c r="N342" s="1" t="n">
         <v>2606</v>
       </c>
     </row>
@@ -15201,9 +16230,12 @@
         <v>0.0001975</v>
       </c>
       <c r="L343" s="1" t="n">
+        <v>0.0001974</v>
+      </c>
+      <c r="M343" s="1" t="n">
         <v>0.000198</v>
       </c>
-      <c r="M343" s="1" t="n">
+      <c r="N343" s="1" t="n">
         <v>0.0001959</v>
       </c>
     </row>
@@ -15244,9 +16276,12 @@
         <v>0.07955</v>
       </c>
       <c r="L344" s="1" t="n">
+        <v>0.07944</v>
+      </c>
+      <c r="M344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="M344" s="1" t="n">
+      <c r="N344" s="1" t="n">
         <v>0.07925</v>
       </c>
     </row>
@@ -15287,9 +16322,12 @@
         <v>0.0168</v>
       </c>
       <c r="L345" s="1" t="n">
+        <v>0.01669</v>
+      </c>
+      <c r="M345" s="1" t="n">
         <v>0.0168</v>
       </c>
-      <c r="M345" s="1" t="n">
+      <c r="N345" s="1" t="n">
         <v>0.0163</v>
       </c>
     </row>
@@ -15330,9 +16368,12 @@
         <v>2.757</v>
       </c>
       <c r="L346" s="1" t="n">
+        <v>2.752</v>
+      </c>
+      <c r="M346" s="1" t="n">
         <v>2.799</v>
       </c>
-      <c r="M346" s="1" t="n">
+      <c r="N346" s="1" t="n">
         <v>2.746</v>
       </c>
     </row>
@@ -15373,9 +16414,12 @@
         <v>0.01638</v>
       </c>
       <c r="L347" s="1" t="n">
+        <v>0.01634</v>
+      </c>
+      <c r="M347" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="M347" s="1" t="n">
+      <c r="N347" s="1" t="n">
         <v>0.01631</v>
       </c>
     </row>
@@ -15416,9 +16460,12 @@
         <v>0.03884</v>
       </c>
       <c r="L348" s="1" t="n">
-        <v>0.03897</v>
+        <v>0.03929</v>
       </c>
       <c r="M348" s="1" t="n">
+        <v>0.03929</v>
+      </c>
+      <c r="N348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -15459,10 +16506,13 @@
         <v>0.3033</v>
       </c>
       <c r="L349" s="1" t="n">
+        <v>0.3028</v>
+      </c>
+      <c r="M349" s="1" t="n">
         <v>0.3065</v>
       </c>
-      <c r="M349" s="1" t="n">
-        <v>0.3029</v>
+      <c r="N349" s="1" t="n">
+        <v>0.3028</v>
       </c>
     </row>
     <row r="350">
@@ -15502,9 +16552,12 @@
         <v>0.005114</v>
       </c>
       <c r="L350" s="1" t="n">
+        <v>0.005105</v>
+      </c>
+      <c r="M350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="M350" s="1" t="n">
+      <c r="N350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -15545,9 +16598,12 @@
         <v>0.005113</v>
       </c>
       <c r="L351" s="1" t="n">
+        <v>0.005104</v>
+      </c>
+      <c r="M351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="M351" s="1" t="n">
+      <c r="N351" s="1" t="n">
         <v>0.005065</v>
       </c>
     </row>
@@ -15588,9 +16644,12 @@
         <v>0.0044</v>
       </c>
       <c r="L352" s="1" t="n">
+        <v>0.004397</v>
+      </c>
+      <c r="M352" s="1" t="n">
         <v>0.004419</v>
       </c>
-      <c r="M352" s="1" t="n">
+      <c r="N352" s="1" t="n">
         <v>0.004384</v>
       </c>
     </row>
@@ -15631,9 +16690,12 @@
         <v>0.08109</v>
       </c>
       <c r="L353" s="1" t="n">
+        <v>0.08093</v>
+      </c>
+      <c r="M353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="M353" s="1" t="n">
+      <c r="N353" s="1" t="n">
         <v>0.08062999999999999</v>
       </c>
     </row>
@@ -15674,9 +16736,12 @@
         <v>1.277</v>
       </c>
       <c r="L354" s="1" t="n">
+        <v>1.279</v>
+      </c>
+      <c r="M354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="M354" s="1" t="n">
+      <c r="N354" s="1" t="n">
         <v>1.277</v>
       </c>
     </row>
@@ -15717,10 +16782,13 @@
         <v>7.73</v>
       </c>
       <c r="L355" s="1" t="n">
+        <v>7.705</v>
+      </c>
+      <c r="M355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="M355" s="1" t="n">
-        <v>7.707</v>
+      <c r="N355" s="1" t="n">
+        <v>7.705</v>
       </c>
     </row>
     <row r="356">
@@ -15760,9 +16828,12 @@
         <v>0.007860000000000001</v>
       </c>
       <c r="L356" s="1" t="n">
+        <v>0.007820000000000001</v>
+      </c>
+      <c r="M356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="M356" s="1" t="n">
+      <c r="N356" s="1" t="n">
         <v>0.00778</v>
       </c>
     </row>
@@ -15803,9 +16874,12 @@
         <v>0.005644</v>
       </c>
       <c r="L357" s="1" t="n">
+        <v>0.005637</v>
+      </c>
+      <c r="M357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="M357" s="1" t="n">
+      <c r="N357" s="1" t="n">
         <v>0.005632</v>
       </c>
     </row>
@@ -15846,9 +16920,12 @@
         <v>0.01556</v>
       </c>
       <c r="L358" s="1" t="n">
+        <v>0.01555</v>
+      </c>
+      <c r="M358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="M358" s="1" t="n">
+      <c r="N358" s="1" t="n">
         <v>0.01551</v>
       </c>
     </row>
@@ -15889,10 +16966,13 @@
         <v>3.644</v>
       </c>
       <c r="L359" s="1" t="n">
+        <v>3.635</v>
+      </c>
+      <c r="M359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="M359" s="1" t="n">
-        <v>3.636</v>
+      <c r="N359" s="1" t="n">
+        <v>3.635</v>
       </c>
     </row>
     <row r="360">
@@ -15932,9 +17012,12 @@
         <v>0.1501</v>
       </c>
       <c r="L360" s="1" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M360" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="M360" s="1" t="n">
+      <c r="N360" s="1" t="n">
         <v>0.1497</v>
       </c>
     </row>
@@ -15975,9 +17058,12 @@
         <v>0.0703</v>
       </c>
       <c r="L361" s="1" t="n">
+        <v>0.07047</v>
+      </c>
+      <c r="M361" s="1" t="n">
         <v>0.07104000000000001</v>
       </c>
-      <c r="M361" s="1" t="n">
+      <c r="N361" s="1" t="n">
         <v>0.07019</v>
       </c>
     </row>
@@ -16018,9 +17104,12 @@
         <v>0.01771</v>
       </c>
       <c r="L362" s="1" t="n">
+        <v>0.01765</v>
+      </c>
+      <c r="M362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="M362" s="1" t="n">
+      <c r="N362" s="1" t="n">
         <v>0.01761</v>
       </c>
     </row>
@@ -16061,9 +17150,12 @@
         <v>0.02244</v>
       </c>
       <c r="L363" s="1" t="n">
+        <v>0.02241</v>
+      </c>
+      <c r="M363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="M363" s="1" t="n">
+      <c r="N363" s="1" t="n">
         <v>0.02234</v>
       </c>
     </row>
@@ -16104,9 +17196,12 @@
         <v>0.01259</v>
       </c>
       <c r="L364" s="1" t="n">
+        <v>0.01259</v>
+      </c>
+      <c r="M364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="M364" s="1" t="n">
+      <c r="N364" s="1" t="n">
         <v>0.01249</v>
       </c>
     </row>
@@ -16147,10 +17242,13 @@
         <v>0.0917</v>
       </c>
       <c r="L365" s="1" t="n">
+        <v>0.0914</v>
+      </c>
+      <c r="M365" s="1" t="n">
         <v>0.0926</v>
       </c>
-      <c r="M365" s="1" t="n">
-        <v>0.0915</v>
+      <c r="N365" s="1" t="n">
+        <v>0.0914</v>
       </c>
     </row>
     <row r="366">
@@ -16190,9 +17288,12 @@
         <v>0.04239</v>
       </c>
       <c r="L366" s="1" t="n">
+        <v>0.04232</v>
+      </c>
+      <c r="M366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="M366" s="1" t="n">
+      <c r="N366" s="1" t="n">
         <v>0.04224</v>
       </c>
     </row>
@@ -16233,9 +17334,12 @@
         <v>0.03173</v>
       </c>
       <c r="L367" s="1" t="n">
-        <v>0.03174</v>
+        <v>0.03188</v>
       </c>
       <c r="M367" s="1" t="n">
+        <v>0.03188</v>
+      </c>
+      <c r="N367" s="1" t="n">
         <v>0.03141</v>
       </c>
     </row>
@@ -16276,10 +17380,13 @@
         <v>0.02334</v>
       </c>
       <c r="L368" s="1" t="n">
+        <v>0.02331</v>
+      </c>
+      <c r="M368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="M368" s="1" t="n">
-        <v>0.02334</v>
+      <c r="N368" s="1" t="n">
+        <v>0.02331</v>
       </c>
     </row>
     <row r="369">
@@ -16319,9 +17426,12 @@
         <v>0.03101</v>
       </c>
       <c r="L369" s="1" t="n">
+        <v>0.03099</v>
+      </c>
+      <c r="M369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="M369" s="1" t="n">
+      <c r="N369" s="1" t="n">
         <v>0.03089</v>
       </c>
     </row>
@@ -16362,9 +17472,12 @@
         <v>0.0793</v>
       </c>
       <c r="L370" s="1" t="n">
-        <v>0.07932</v>
+        <v>0.0794</v>
       </c>
       <c r="M370" s="1" t="n">
+        <v>0.0794</v>
+      </c>
+      <c r="N370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -16405,9 +17518,12 @@
         <v>0.1079</v>
       </c>
       <c r="L371" s="1" t="n">
+        <v>0.1076</v>
+      </c>
+      <c r="M371" s="1" t="n">
         <v>0.1089</v>
       </c>
-      <c r="M371" s="1" t="n">
+      <c r="N371" s="1" t="n">
         <v>0.1074</v>
       </c>
     </row>
@@ -16448,10 +17564,13 @@
         <v>0.007081</v>
       </c>
       <c r="L372" s="1" t="n">
+        <v>0.007024</v>
+      </c>
+      <c r="M372" s="1" t="n">
         <v>0.007209</v>
       </c>
-      <c r="M372" s="1" t="n">
-        <v>0.007045</v>
+      <c r="N372" s="1" t="n">
+        <v>0.007024</v>
       </c>
     </row>
     <row r="373">
@@ -16491,10 +17610,13 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="L373" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="M373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="M373" s="1" t="n">
-        <v>0.09619999999999999</v>
+      <c r="N373" s="1" t="n">
+        <v>0.096</v>
       </c>
     </row>
     <row r="374">
@@ -16534,10 +17656,13 @@
         <v>0.05824</v>
       </c>
       <c r="L374" s="1" t="n">
+        <v>0.05771</v>
+      </c>
+      <c r="M374" s="1" t="n">
         <v>0.05881</v>
       </c>
-      <c r="M374" s="1" t="n">
-        <v>0.05804</v>
+      <c r="N374" s="1" t="n">
+        <v>0.05771</v>
       </c>
     </row>
     <row r="375">
@@ -16577,9 +17702,12 @@
         <v>0.3221</v>
       </c>
       <c r="L375" s="1" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="M375" s="1" t="n">
         <v>0.3238</v>
       </c>
-      <c r="M375" s="1" t="n">
+      <c r="N375" s="1" t="n">
         <v>0.3193</v>
       </c>
     </row>
@@ -16620,10 +17748,13 @@
         <v>0.01962</v>
       </c>
       <c r="L376" s="1" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="M376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="M376" s="1" t="n">
-        <v>0.01958</v>
+      <c r="N376" s="1" t="n">
+        <v>0.0195</v>
       </c>
     </row>
     <row r="377">
@@ -16663,10 +17794,13 @@
         <v>0.06852999999999999</v>
       </c>
       <c r="L377" s="1" t="n">
+        <v>0.0684</v>
+      </c>
+      <c r="M377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="M377" s="1" t="n">
-        <v>0.06852999999999999</v>
+      <c r="N377" s="1" t="n">
+        <v>0.0684</v>
       </c>
     </row>
     <row r="378">
@@ -16706,9 +17840,12 @@
         <v>0.15528</v>
       </c>
       <c r="L378" s="1" t="n">
+        <v>0.15577</v>
+      </c>
+      <c r="M378" s="1" t="n">
         <v>0.1581</v>
       </c>
-      <c r="M378" s="1" t="n">
+      <c r="N378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -16749,9 +17886,12 @@
         <v>0.000599</v>
       </c>
       <c r="L379" s="1" t="n">
+        <v>0.0005982</v>
+      </c>
+      <c r="M379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="M379" s="1" t="n">
+      <c r="N379" s="1" t="n">
         <v>0.0005965</v>
       </c>
     </row>
@@ -16792,9 +17932,12 @@
         <v>0.01017</v>
       </c>
       <c r="L380" s="1" t="n">
+        <v>0.01015</v>
+      </c>
+      <c r="M380" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="M380" s="1" t="n">
+      <c r="N380" s="1" t="n">
         <v>0.01015</v>
       </c>
     </row>
@@ -16835,9 +17978,12 @@
         <v>0.02556</v>
       </c>
       <c r="L381" s="1" t="n">
+        <v>0.02553</v>
+      </c>
+      <c r="M381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="M381" s="1" t="n">
+      <c r="N381" s="1" t="n">
         <v>0.02547</v>
       </c>
     </row>
@@ -16878,9 +18024,12 @@
         <v>0.19348</v>
       </c>
       <c r="L382" s="1" t="n">
+        <v>0.19163</v>
+      </c>
+      <c r="M382" s="1" t="n">
         <v>0.19348</v>
       </c>
-      <c r="M382" s="1" t="n">
+      <c r="N382" s="1" t="n">
         <v>0.18936</v>
       </c>
     </row>
@@ -16921,9 +18070,12 @@
         <v>0.09308</v>
       </c>
       <c r="L383" s="1" t="n">
+        <v>0.09242</v>
+      </c>
+      <c r="M383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="M383" s="1" t="n">
+      <c r="N383" s="1" t="n">
         <v>0.09236</v>
       </c>
     </row>
@@ -16964,10 +18116,13 @@
         <v>0.03169</v>
       </c>
       <c r="L384" s="1" t="n">
+        <v>0.03166</v>
+      </c>
+      <c r="M384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="M384" s="1" t="n">
-        <v>0.03169</v>
+      <c r="N384" s="1" t="n">
+        <v>0.03166</v>
       </c>
     </row>
     <row r="385">
@@ -17007,10 +18162,13 @@
         <v>0.01094</v>
       </c>
       <c r="L385" s="1" t="n">
+        <v>0.01093</v>
+      </c>
+      <c r="M385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="M385" s="1" t="n">
-        <v>0.01094</v>
+      <c r="N385" s="1" t="n">
+        <v>0.01093</v>
       </c>
     </row>
     <row r="386">
@@ -17050,9 +18208,12 @@
         <v>0.0515</v>
       </c>
       <c r="L386" s="1" t="n">
+        <v>0.05123</v>
+      </c>
+      <c r="M386" s="1" t="n">
         <v>0.05224</v>
       </c>
-      <c r="M386" s="1" t="n">
+      <c r="N386" s="1" t="n">
         <v>0.05087</v>
       </c>
     </row>
@@ -17093,9 +18254,12 @@
         <v>0.02508</v>
       </c>
       <c r="L387" s="1" t="n">
+        <v>0.02513</v>
+      </c>
+      <c r="M387" s="1" t="n">
         <v>0.02541</v>
       </c>
-      <c r="M387" s="1" t="n">
+      <c r="N387" s="1" t="n">
         <v>0.02483</v>
       </c>
     </row>
@@ -17136,9 +18300,12 @@
         <v>0.0073</v>
       </c>
       <c r="L388" s="1" t="n">
+        <v>0.007302</v>
+      </c>
+      <c r="M388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="M388" s="1" t="n">
+      <c r="N388" s="1" t="n">
         <v>0.007267</v>
       </c>
     </row>
@@ -17179,10 +18346,13 @@
         <v>0.01016</v>
       </c>
       <c r="L389" s="1" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="M389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="M389" s="1" t="n">
-        <v>0.01011</v>
+      <c r="N389" s="1" t="n">
+        <v>0.0101</v>
       </c>
     </row>
     <row r="390">
@@ -17222,9 +18392,12 @@
         <v>0.08255</v>
       </c>
       <c r="L390" s="1" t="n">
+        <v>0.08260000000000001</v>
+      </c>
+      <c r="M390" s="1" t="n">
         <v>0.0839</v>
       </c>
-      <c r="M390" s="1" t="n">
+      <c r="N390" s="1" t="n">
         <v>0.08233</v>
       </c>
     </row>
@@ -17265,9 +18438,12 @@
         <v>0.5047</v>
       </c>
       <c r="L391" s="1" t="n">
+        <v>0.5047</v>
+      </c>
+      <c r="M391" s="1" t="n">
         <v>0.5061</v>
       </c>
-      <c r="M391" s="1" t="n">
+      <c r="N391" s="1" t="n">
         <v>0.5014</v>
       </c>
     </row>
@@ -17308,10 +18484,13 @@
         <v>0.1168</v>
       </c>
       <c r="L392" s="1" t="n">
+        <v>0.1165</v>
+      </c>
+      <c r="M392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="M392" s="1" t="n">
-        <v>0.1168</v>
+      <c r="N392" s="1" t="n">
+        <v>0.1165</v>
       </c>
     </row>
     <row r="393">
@@ -17351,10 +18530,13 @@
         <v>0.00247</v>
       </c>
       <c r="L393" s="1" t="n">
+        <v>0.00245</v>
+      </c>
+      <c r="M393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="M393" s="1" t="n">
-        <v>0.00246</v>
+      <c r="N393" s="1" t="n">
+        <v>0.00245</v>
       </c>
     </row>
     <row r="394">
@@ -17394,9 +18576,12 @@
         <v>0.02133</v>
       </c>
       <c r="L394" s="1" t="n">
+        <v>0.02126</v>
+      </c>
+      <c r="M394" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="M394" s="1" t="n">
+      <c r="N394" s="1" t="n">
         <v>0.02121</v>
       </c>
     </row>
@@ -17437,9 +18622,12 @@
         <v>0.016</v>
       </c>
       <c r="L395" s="1" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="M395" s="1" t="n">
         <v>0.0163</v>
       </c>
-      <c r="M395" s="1" t="n">
+      <c r="N395" s="1" t="n">
         <v>0.0159</v>
       </c>
     </row>
@@ -17480,10 +18668,13 @@
         <v>0.1355</v>
       </c>
       <c r="L396" s="1" t="n">
+        <v>0.1354</v>
+      </c>
+      <c r="M396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="M396" s="1" t="n">
-        <v>0.1355</v>
+      <c r="N396" s="1" t="n">
+        <v>0.1354</v>
       </c>
     </row>
     <row r="397">
@@ -17523,9 +18714,12 @@
         <v>0.01452</v>
       </c>
       <c r="L397" s="1" t="n">
+        <v>0.01458</v>
+      </c>
+      <c r="M397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="M397" s="1" t="n">
+      <c r="N397" s="1" t="n">
         <v>0.01452</v>
       </c>
     </row>
@@ -17566,10 +18760,13 @@
         <v>6.749</v>
       </c>
       <c r="L398" s="1" t="n">
+        <v>6.708</v>
+      </c>
+      <c r="M398" s="1" t="n">
         <v>6.955</v>
       </c>
-      <c r="M398" s="1" t="n">
-        <v>6.725</v>
+      <c r="N398" s="1" t="n">
+        <v>6.708</v>
       </c>
     </row>
     <row r="399">
@@ -17609,10 +18806,13 @@
         <v>0.009434</v>
       </c>
       <c r="L399" s="1" t="n">
+        <v>0.009414</v>
+      </c>
+      <c r="M399" s="1" t="n">
         <v>0.009509999999999999</v>
       </c>
-      <c r="M399" s="1" t="n">
-        <v>0.009434</v>
+      <c r="N399" s="1" t="n">
+        <v>0.009414</v>
       </c>
     </row>
     <row r="400">
@@ -17652,9 +18852,12 @@
         <v>0.001266</v>
       </c>
       <c r="L400" s="1" t="n">
+        <v>0.001265</v>
+      </c>
+      <c r="M400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="M400" s="1" t="n">
+      <c r="N400" s="1" t="n">
         <v>0.001256</v>
       </c>
     </row>
@@ -17695,9 +18898,12 @@
         <v>0.01851</v>
       </c>
       <c r="L401" s="1" t="n">
+        <v>0.01849</v>
+      </c>
+      <c r="M401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="M401" s="1" t="n">
+      <c r="N401" s="1" t="n">
         <v>0.01841</v>
       </c>
     </row>
@@ -17738,9 +18944,12 @@
         <v>0.08515</v>
       </c>
       <c r="L402" s="1" t="n">
+        <v>0.08498</v>
+      </c>
+      <c r="M402" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="M402" s="1" t="n">
+      <c r="N402" s="1" t="n">
         <v>0.08488999999999999</v>
       </c>
     </row>
@@ -17781,10 +18990,13 @@
         <v>0.00552</v>
       </c>
       <c r="L403" s="1" t="n">
+        <v>0.00551</v>
+      </c>
+      <c r="M403" s="1" t="n">
         <v>0.00556</v>
       </c>
-      <c r="M403" s="1" t="n">
-        <v>0.00552</v>
+      <c r="N403" s="1" t="n">
+        <v>0.00551</v>
       </c>
     </row>
     <row r="404">
@@ -17824,10 +19036,13 @@
         <v>0.04287</v>
       </c>
       <c r="L404" s="1" t="n">
+        <v>0.04271</v>
+      </c>
+      <c r="M404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="M404" s="1" t="n">
-        <v>0.04278</v>
+      <c r="N404" s="1" t="n">
+        <v>0.04271</v>
       </c>
     </row>
     <row r="405">
@@ -17867,9 +19082,12 @@
         <v>0.0587</v>
       </c>
       <c r="L405" s="1" t="n">
+        <v>0.05842</v>
+      </c>
+      <c r="M405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="M405" s="1" t="n">
+      <c r="N405" s="1" t="n">
         <v>0.05838</v>
       </c>
     </row>
@@ -17910,9 +19128,12 @@
         <v>0.0166</v>
       </c>
       <c r="L406" s="1" t="n">
+        <v>0.01658</v>
+      </c>
+      <c r="M406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="M406" s="1" t="n">
+      <c r="N406" s="1" t="n">
         <v>0.01647</v>
       </c>
     </row>
@@ -17953,9 +19174,12 @@
         <v>0.0425</v>
       </c>
       <c r="L407" s="1" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="M407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="M407" s="1" t="n">
+      <c r="N407" s="1" t="n">
         <v>0.0423</v>
       </c>
     </row>
@@ -17996,9 +19220,12 @@
         <v>0.01932</v>
       </c>
       <c r="L408" s="1" t="n">
+        <v>0.01928</v>
+      </c>
+      <c r="M408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="M408" s="1" t="n">
+      <c r="N408" s="1" t="n">
         <v>0.01927</v>
       </c>
     </row>
@@ -18039,9 +19266,12 @@
         <v>0.4459</v>
       </c>
       <c r="L409" s="1" t="n">
+        <v>0.4458</v>
+      </c>
+      <c r="M409" s="1" t="n">
         <v>0.4484</v>
       </c>
-      <c r="M409" s="1" t="n">
+      <c r="N409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -18082,10 +19312,13 @@
         <v>0.04421</v>
       </c>
       <c r="L410" s="1" t="n">
+        <v>0.04408</v>
+      </c>
+      <c r="M410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="M410" s="1" t="n">
-        <v>0.04418</v>
+      <c r="N410" s="1" t="n">
+        <v>0.04408</v>
       </c>
     </row>
     <row r="411">
@@ -18125,9 +19358,12 @@
         <v>27.41</v>
       </c>
       <c r="L411" s="1" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="M411" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="M411" s="1" t="n">
+      <c r="N411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -18168,10 +19404,13 @@
         <v>0.03512</v>
       </c>
       <c r="L412" s="1" t="n">
+        <v>0.03508</v>
+      </c>
+      <c r="M412" s="1" t="n">
         <v>0.03564</v>
       </c>
-      <c r="M412" s="1" t="n">
-        <v>0.0351</v>
+      <c r="N412" s="1" t="n">
+        <v>0.03508</v>
       </c>
     </row>
     <row r="413">
@@ -18211,10 +19450,13 @@
         <v>0.003404</v>
       </c>
       <c r="L413" s="1" t="n">
+        <v>0.003397</v>
+      </c>
+      <c r="M413" s="1" t="n">
         <v>0.003432</v>
       </c>
-      <c r="M413" s="1" t="n">
-        <v>0.003404</v>
+      <c r="N413" s="1" t="n">
+        <v>0.003397</v>
       </c>
     </row>
     <row r="414">
@@ -18254,9 +19496,12 @@
         <v>0.1533</v>
       </c>
       <c r="L414" s="1" t="n">
+        <v>0.1531</v>
+      </c>
+      <c r="M414" s="1" t="n">
         <v>0.1538</v>
       </c>
-      <c r="M414" s="1" t="n">
+      <c r="N414" s="1" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -18297,9 +19542,12 @@
         <v>0.0527</v>
       </c>
       <c r="L415" s="1" t="n">
+        <v>0.05272</v>
+      </c>
+      <c r="M415" s="1" t="n">
         <v>0.05288</v>
       </c>
-      <c r="M415" s="1" t="n">
+      <c r="N415" s="1" t="n">
         <v>0.0525</v>
       </c>
     </row>
@@ -18340,9 +19588,12 @@
         <v>0.00658</v>
       </c>
       <c r="L416" s="1" t="n">
+        <v>0.00659</v>
+      </c>
+      <c r="M416" s="1" t="n">
         <v>0.00669</v>
       </c>
-      <c r="M416" s="1" t="n">
+      <c r="N416" s="1" t="n">
         <v>0.00658</v>
       </c>
     </row>
@@ -18383,10 +19634,13 @@
         <v>0.06051</v>
       </c>
       <c r="L417" s="1" t="n">
+        <v>0.06045</v>
+      </c>
+      <c r="M417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="M417" s="1" t="n">
-        <v>0.06051</v>
+      <c r="N417" s="1" t="n">
+        <v>0.06045</v>
       </c>
     </row>
     <row r="418">
@@ -18426,10 +19680,13 @@
         <v>0.008054</v>
       </c>
       <c r="L418" s="1" t="n">
+        <v>0.007979</v>
+      </c>
+      <c r="M418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="M418" s="1" t="n">
-        <v>0.008043</v>
+      <c r="N418" s="1" t="n">
+        <v>0.007979</v>
       </c>
     </row>
     <row r="419">
@@ -18469,9 +19726,12 @@
         <v>0.07446</v>
       </c>
       <c r="L419" s="1" t="n">
+        <v>0.07444000000000001</v>
+      </c>
+      <c r="M419" s="1" t="n">
         <v>0.07524</v>
       </c>
-      <c r="M419" s="1" t="n">
+      <c r="N419" s="1" t="n">
         <v>0.07435</v>
       </c>
     </row>
@@ -18512,9 +19772,12 @@
         <v>0.02123</v>
       </c>
       <c r="L420" s="1" t="n">
+        <v>0.02117</v>
+      </c>
+      <c r="M420" s="1" t="n">
         <v>0.02146</v>
       </c>
-      <c r="M420" s="1" t="n">
+      <c r="N420" s="1" t="n">
         <v>0.02105</v>
       </c>
     </row>
@@ -18555,9 +19818,12 @@
         <v>0.06972</v>
       </c>
       <c r="L421" s="1" t="n">
+        <v>0.06959</v>
+      </c>
+      <c r="M421" s="1" t="n">
         <v>0.07038999999999999</v>
       </c>
-      <c r="M421" s="1" t="n">
+      <c r="N421" s="1" t="n">
         <v>0.06938999999999999</v>
       </c>
     </row>
@@ -18598,9 +19864,12 @@
         <v>0.01491</v>
       </c>
       <c r="L422" s="1" t="n">
+        <v>0.01487</v>
+      </c>
+      <c r="M422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="M422" s="1" t="n">
+      <c r="N422" s="1" t="n">
         <v>0.01487</v>
       </c>
     </row>
@@ -18641,9 +19910,12 @@
         <v>0.00666</v>
       </c>
       <c r="L423" s="1" t="n">
+        <v>0.006652</v>
+      </c>
+      <c r="M423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="M423" s="1" t="n">
+      <c r="N423" s="1" t="n">
         <v>0.006648</v>
       </c>
     </row>
@@ -18684,10 +19956,13 @@
         <v>0.912</v>
       </c>
       <c r="L424" s="1" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="M424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="M424" s="1" t="n">
-        <v>0.912</v>
+      <c r="N424" s="1" t="n">
+        <v>0.909</v>
       </c>
     </row>
     <row r="425">
@@ -18727,9 +20002,12 @@
         <v>0.03565</v>
       </c>
       <c r="L425" s="1" t="n">
+        <v>0.03572</v>
+      </c>
+      <c r="M425" s="1" t="n">
         <v>0.03596</v>
       </c>
-      <c r="M425" s="1" t="n">
+      <c r="N425" s="1" t="n">
         <v>0.03546</v>
       </c>
     </row>
@@ -18770,9 +20048,12 @@
         <v>1.801</v>
       </c>
       <c r="L426" s="1" t="n">
+        <v>1.778</v>
+      </c>
+      <c r="M426" s="1" t="n">
         <v>1.81</v>
       </c>
-      <c r="M426" s="1" t="n">
+      <c r="N426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -18813,9 +20094,12 @@
         <v>0.12807</v>
       </c>
       <c r="L427" s="1" t="n">
+        <v>0.12805</v>
+      </c>
+      <c r="M427" s="1" t="n">
         <v>0.12835</v>
       </c>
-      <c r="M427" s="1" t="n">
+      <c r="N427" s="1" t="n">
         <v>0.12736</v>
       </c>
     </row>
@@ -18856,9 +20140,12 @@
         <v>0.05334</v>
       </c>
       <c r="L428" s="1" t="n">
+        <v>0.05319</v>
+      </c>
+      <c r="M428" s="1" t="n">
         <v>0.05362</v>
       </c>
-      <c r="M428" s="1" t="n">
+      <c r="N428" s="1" t="n">
         <v>0.05297</v>
       </c>
     </row>
@@ -18899,9 +20186,12 @@
         <v>1.294</v>
       </c>
       <c r="L429" s="1" t="n">
+        <v>1.289</v>
+      </c>
+      <c r="M429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="M429" s="1" t="n">
+      <c r="N429" s="1" t="n">
         <v>1.289</v>
       </c>
     </row>
@@ -18942,9 +20232,12 @@
         <v>0.075</v>
       </c>
       <c r="L430" s="1" t="n">
+        <v>0.07492</v>
+      </c>
+      <c r="M430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="M430" s="1" t="n">
+      <c r="N430" s="1" t="n">
         <v>0.07482</v>
       </c>
     </row>
@@ -18985,10 +20278,13 @@
         <v>0.1583</v>
       </c>
       <c r="L431" s="1" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="M431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="M431" s="1" t="n">
-        <v>0.1583</v>
+      <c r="N431" s="1" t="n">
+        <v>0.157</v>
       </c>
     </row>
     <row r="432">
@@ -19028,9 +20324,12 @@
         <v>1.452</v>
       </c>
       <c r="L432" s="1" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M432" s="1" t="n">
         <v>1.461</v>
       </c>
-      <c r="M432" s="1" t="n">
+      <c r="N432" s="1" t="n">
         <v>1.445</v>
       </c>
     </row>
@@ -19071,9 +20370,12 @@
         <v>3.284</v>
       </c>
       <c r="L433" s="1" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="M433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="M433" s="1" t="n">
+      <c r="N433" s="1" t="n">
         <v>3.266</v>
       </c>
     </row>
@@ -19114,9 +20416,12 @@
         <v>0.179</v>
       </c>
       <c r="L434" s="1" t="n">
+        <v>0.179</v>
+      </c>
+      <c r="M434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="M434" s="1" t="n">
+      <c r="N434" s="1" t="n">
         <v>0.1783</v>
       </c>
     </row>
@@ -19157,9 +20462,12 @@
         <v>0.008607</v>
       </c>
       <c r="L435" s="1" t="n">
+        <v>0.00859</v>
+      </c>
+      <c r="M435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="M435" s="1" t="n">
+      <c r="N435" s="1" t="n">
         <v>0.008580000000000001</v>
       </c>
     </row>
@@ -19200,9 +20508,12 @@
         <v>0.283</v>
       </c>
       <c r="L436" s="1" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="M436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="M436" s="1" t="n">
+      <c r="N436" s="1" t="n">
         <v>0.2818</v>
       </c>
     </row>
@@ -19243,9 +20554,12 @@
         <v>0.03957</v>
       </c>
       <c r="L437" s="1" t="n">
+        <v>0.03896</v>
+      </c>
+      <c r="M437" s="1" t="n">
         <v>0.03957</v>
       </c>
-      <c r="M437" s="1" t="n">
+      <c r="N437" s="1" t="n">
         <v>0.03814</v>
       </c>
     </row>
@@ -19286,9 +20600,12 @@
         <v>0.02431</v>
       </c>
       <c r="L438" s="1" t="n">
+        <v>0.02436</v>
+      </c>
+      <c r="M438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="M438" s="1" t="n">
+      <c r="N438" s="1" t="n">
         <v>0.0242</v>
       </c>
     </row>
@@ -19329,10 +20646,13 @@
         <v>0.04413</v>
       </c>
       <c r="L439" s="1" t="n">
+        <v>0.04403</v>
+      </c>
+      <c r="M439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="M439" s="1" t="n">
-        <v>0.04405</v>
+      <c r="N439" s="1" t="n">
+        <v>0.04403</v>
       </c>
     </row>
     <row r="440">
@@ -19372,9 +20692,12 @@
         <v>0.0005212</v>
       </c>
       <c r="L440" s="1" t="n">
+        <v>0.0005192</v>
+      </c>
+      <c r="M440" s="1" t="n">
         <v>0.0005258</v>
       </c>
-      <c r="M440" s="1" t="n">
+      <c r="N440" s="1" t="n">
         <v>0.0005188</v>
       </c>
     </row>
@@ -19415,9 +20738,12 @@
         <v>0.04449</v>
       </c>
       <c r="L441" s="1" t="n">
+        <v>0.04428</v>
+      </c>
+      <c r="M441" s="1" t="n">
         <v>0.04489</v>
       </c>
-      <c r="M441" s="1" t="n">
+      <c r="N441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -19458,9 +20784,12 @@
         <v>0.000413</v>
       </c>
       <c r="L442" s="1" t="n">
+        <v>0.000412</v>
+      </c>
+      <c r="M442" s="1" t="n">
         <v>0.000416</v>
       </c>
-      <c r="M442" s="1" t="n">
+      <c r="N442" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -19501,9 +20830,12 @@
         <v>0.0949</v>
       </c>
       <c r="L443" s="1" t="n">
+        <v>0.09505</v>
+      </c>
+      <c r="M443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="M443" s="1" t="n">
+      <c r="N443" s="1" t="n">
         <v>0.0949</v>
       </c>
     </row>
@@ -19544,9 +20876,12 @@
         <v>2.302</v>
       </c>
       <c r="L444" s="1" t="n">
+        <v>2.307</v>
+      </c>
+      <c r="M444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="M444" s="1" t="n">
+      <c r="N444" s="1" t="n">
         <v>2.289</v>
       </c>
     </row>
@@ -19587,9 +20922,12 @@
         <v>0.2693</v>
       </c>
       <c r="L445" s="1" t="n">
+        <v>0.2684</v>
+      </c>
+      <c r="M445" s="1" t="n">
         <v>0.2741</v>
       </c>
-      <c r="M445" s="1" t="n">
+      <c r="N445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -19630,9 +20968,12 @@
         <v>0.0007457</v>
       </c>
       <c r="L446" s="1" t="n">
+        <v>0.0007415</v>
+      </c>
+      <c r="M446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="M446" s="1" t="n">
+      <c r="N446" s="1" t="n">
         <v>0.0007415</v>
       </c>
     </row>
@@ -19673,9 +21014,12 @@
         <v>0.03835</v>
       </c>
       <c r="L447" s="1" t="n">
+        <v>0.03833</v>
+      </c>
+      <c r="M447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="M447" s="1" t="n">
+      <c r="N447" s="1" t="n">
         <v>0.03821</v>
       </c>
     </row>
@@ -19716,9 +21060,12 @@
         <v>0.1782</v>
       </c>
       <c r="L448" s="1" t="n">
-        <v>0.1782</v>
+        <v>0.1783</v>
       </c>
       <c r="M448" s="1" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="N448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -19759,9 +21106,12 @@
         <v>0.04275</v>
       </c>
       <c r="L449" s="1" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="M449" s="1" t="n">
         <v>0.04301</v>
       </c>
-      <c r="M449" s="1" t="n">
+      <c r="N449" s="1" t="n">
         <v>0.0426</v>
       </c>
     </row>
@@ -19802,9 +21152,12 @@
         <v>0.0001643</v>
       </c>
       <c r="L450" s="1" t="n">
+        <v>0.000164</v>
+      </c>
+      <c r="M450" s="1" t="n">
         <v>0.0001654</v>
       </c>
-      <c r="M450" s="1" t="n">
+      <c r="N450" s="1" t="n">
         <v>0.0001632</v>
       </c>
     </row>
@@ -19845,9 +21198,12 @@
         <v>0.03747</v>
       </c>
       <c r="L451" s="1" t="n">
+        <v>0.03745</v>
+      </c>
+      <c r="M451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="M451" s="1" t="n">
+      <c r="N451" s="1" t="n">
         <v>0.03745</v>
       </c>
     </row>
@@ -19888,9 +21244,12 @@
         <v>0.0098</v>
       </c>
       <c r="L452" s="1" t="n">
+        <v>0.00976</v>
+      </c>
+      <c r="M452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="M452" s="1" t="n">
+      <c r="N452" s="1" t="n">
         <v>0.00976</v>
       </c>
     </row>
@@ -19931,9 +21290,12 @@
         <v>0.06798</v>
       </c>
       <c r="L453" s="1" t="n">
+        <v>0.06791999999999999</v>
+      </c>
+      <c r="M453" s="1" t="n">
         <v>0.06816</v>
       </c>
-      <c r="M453" s="1" t="n">
+      <c r="N453" s="1" t="n">
         <v>0.06782000000000001</v>
       </c>
     </row>
@@ -19974,9 +21336,12 @@
         <v>0.007515</v>
       </c>
       <c r="L454" s="1" t="n">
+        <v>0.007517</v>
+      </c>
+      <c r="M454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="M454" s="1" t="n">
+      <c r="N454" s="1" t="n">
         <v>0.007494</v>
       </c>
     </row>
@@ -20017,9 +21382,12 @@
         <v>0.003302</v>
       </c>
       <c r="L455" s="1" t="n">
+        <v>0.003303</v>
+      </c>
+      <c r="M455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="M455" s="1" t="n">
+      <c r="N455" s="1" t="n">
         <v>0.003302</v>
       </c>
     </row>
@@ -20060,9 +21428,12 @@
         <v>0.001849</v>
       </c>
       <c r="L456" s="1" t="n">
+        <v>0.00185</v>
+      </c>
+      <c r="M456" s="1" t="n">
         <v>0.001875</v>
       </c>
-      <c r="M456" s="1" t="n">
+      <c r="N456" s="1" t="n">
         <v>0.001842</v>
       </c>
     </row>
@@ -20103,9 +21474,12 @@
         <v>0.0001756</v>
       </c>
       <c r="L457" s="1" t="n">
+        <v>0.0001752</v>
+      </c>
+      <c r="M457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="M457" s="1" t="n">
+      <c r="N457" s="1" t="n">
         <v>0.0001745</v>
       </c>
     </row>
@@ -20146,9 +21520,12 @@
         <v>0.0003906</v>
       </c>
       <c r="L458" s="1" t="n">
+        <v>0.00039</v>
+      </c>
+      <c r="M458" s="1" t="n">
         <v>0.0003916</v>
       </c>
-      <c r="M458" s="1" t="n">
+      <c r="N458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -20189,9 +21566,12 @@
         <v>0.01393</v>
       </c>
       <c r="L459" s="1" t="n">
+        <v>0.01394</v>
+      </c>
+      <c r="M459" s="1" t="n">
         <v>0.01413</v>
       </c>
-      <c r="M459" s="1" t="n">
+      <c r="N459" s="1" t="n">
         <v>0.01391</v>
       </c>
     </row>
@@ -20232,9 +21612,12 @@
         <v>0.04578</v>
       </c>
       <c r="L460" s="1" t="n">
-        <v>0.04578</v>
+        <v>0.04579</v>
       </c>
       <c r="M460" s="1" t="n">
+        <v>0.04579</v>
+      </c>
+      <c r="N460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -20275,9 +21658,12 @@
         <v>0.2824</v>
       </c>
       <c r="L461" s="1" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="M461" s="1" t="n">
         <v>0.2839</v>
       </c>
-      <c r="M461" s="1" t="n">
+      <c r="N461" s="1" t="n">
         <v>0.2809</v>
       </c>
     </row>
@@ -20318,9 +21704,12 @@
         <v>0.006272</v>
       </c>
       <c r="L462" s="1" t="n">
+        <v>0.006284</v>
+      </c>
+      <c r="M462" s="1" t="n">
         <v>0.006312</v>
       </c>
-      <c r="M462" s="1" t="n">
+      <c r="N462" s="1" t="n">
         <v>0.00622</v>
       </c>
     </row>
@@ -20361,9 +21750,12 @@
         <v>0.007061</v>
       </c>
       <c r="L463" s="1" t="n">
+        <v>0.007043</v>
+      </c>
+      <c r="M463" s="1" t="n">
         <v>0.007088</v>
       </c>
-      <c r="M463" s="1" t="n">
+      <c r="N463" s="1" t="n">
         <v>0.007032</v>
       </c>
     </row>
@@ -20404,9 +21796,12 @@
         <v>0.2884</v>
       </c>
       <c r="L464" s="1" t="n">
-        <v>0.2884</v>
+        <v>0.2888</v>
       </c>
       <c r="M464" s="1" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="N464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -20447,10 +21842,13 @@
         <v>0.08096</v>
       </c>
       <c r="L465" s="1" t="n">
+        <v>0.08061</v>
+      </c>
+      <c r="M465" s="1" t="n">
         <v>0.08183</v>
       </c>
-      <c r="M465" s="1" t="n">
-        <v>0.08076</v>
+      <c r="N465" s="1" t="n">
+        <v>0.08061</v>
       </c>
     </row>
     <row r="466">
@@ -20490,9 +21888,12 @@
         <v>0.6363</v>
       </c>
       <c r="L466" s="1" t="n">
-        <v>0.6368</v>
+        <v>0.6369</v>
       </c>
       <c r="M466" s="1" t="n">
+        <v>0.6369</v>
+      </c>
+      <c r="N466" s="1" t="n">
         <v>0.6318</v>
       </c>
     </row>
@@ -20533,9 +21934,12 @@
         <v>0.01483</v>
       </c>
       <c r="L467" s="1" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="M467" s="1" t="n">
         <v>0.01499</v>
       </c>
-      <c r="M467" s="1" t="n">
+      <c r="N467" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -20576,9 +21980,12 @@
         <v>0.03442</v>
       </c>
       <c r="L468" s="1" t="n">
+        <v>0.03451</v>
+      </c>
+      <c r="M468" s="1" t="n">
         <v>0.03468</v>
       </c>
-      <c r="M468" s="1" t="n">
+      <c r="N468" s="1" t="n">
         <v>0.03434</v>
       </c>
     </row>
@@ -20619,9 +22026,12 @@
         <v>0.163</v>
       </c>
       <c r="L469" s="1" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="M469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="M469" s="1" t="n">
+      <c r="N469" s="1" t="n">
         <v>0.1624</v>
       </c>
     </row>
@@ -20662,9 +22072,12 @@
         <v>0.41</v>
       </c>
       <c r="L470" s="1" t="n">
+        <v>0.4099</v>
+      </c>
+      <c r="M470" s="1" t="n">
         <v>0.4151</v>
       </c>
-      <c r="M470" s="1" t="n">
+      <c r="N470" s="1" t="n">
         <v>0.4085</v>
       </c>
     </row>
@@ -20705,9 +22118,12 @@
         <v>0.0696</v>
       </c>
       <c r="L471" s="1" t="n">
+        <v>0.06943000000000001</v>
+      </c>
+      <c r="M471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="M471" s="1" t="n">
+      <c r="N471" s="1" t="n">
         <v>0.06934999999999999</v>
       </c>
     </row>
@@ -20748,10 +22164,13 @@
         <v>0.06653000000000001</v>
       </c>
       <c r="L472" s="1" t="n">
+        <v>0.06619</v>
+      </c>
+      <c r="M472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="M472" s="1" t="n">
-        <v>0.06623999999999999</v>
+      <c r="N472" s="1" t="n">
+        <v>0.06619</v>
       </c>
     </row>
     <row r="473">
@@ -20791,9 +22210,12 @@
         <v>0.01624</v>
       </c>
       <c r="L473" s="1" t="n">
+        <v>0.01624</v>
+      </c>
+      <c r="M473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="M473" s="1" t="n">
+      <c r="N473" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -20834,9 +22256,12 @@
         <v>0.2061</v>
       </c>
       <c r="L474" s="1" t="n">
+        <v>0.2062</v>
+      </c>
+      <c r="M474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="M474" s="1" t="n">
+      <c r="N474" s="1" t="n">
         <v>0.2061</v>
       </c>
     </row>
@@ -20877,9 +22302,12 @@
         <v>0.04222</v>
       </c>
       <c r="L475" s="1" t="n">
+        <v>0.04251</v>
+      </c>
+      <c r="M475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="M475" s="1" t="n">
+      <c r="N475" s="1" t="n">
         <v>0.042</v>
       </c>
     </row>
@@ -20920,9 +22348,12 @@
         <v>1.563</v>
       </c>
       <c r="L476" s="1" t="n">
+        <v>1.561</v>
+      </c>
+      <c r="M476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="M476" s="1" t="n">
+      <c r="N476" s="1" t="n">
         <v>1.561</v>
       </c>
     </row>
@@ -20963,9 +22394,12 @@
         <v>0.1007</v>
       </c>
       <c r="L477" s="1" t="n">
+        <v>0.1008</v>
+      </c>
+      <c r="M477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="M477" s="1" t="n">
+      <c r="N477" s="1" t="n">
         <v>0.1003</v>
       </c>
     </row>
@@ -21006,9 +22440,12 @@
         <v>0.001154</v>
       </c>
       <c r="L478" s="1" t="n">
+        <v>0.001152</v>
+      </c>
+      <c r="M478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="M478" s="1" t="n">
+      <c r="N478" s="1" t="n">
         <v>0.00115</v>
       </c>
     </row>
@@ -21049,10 +22486,13 @@
         <v>0.1447</v>
       </c>
       <c r="L479" s="1" t="n">
+        <v>0.1442</v>
+      </c>
+      <c r="M479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="M479" s="1" t="n">
-        <v>0.1447</v>
+      <c r="N479" s="1" t="n">
+        <v>0.1442</v>
       </c>
     </row>
     <row r="480">
@@ -21092,9 +22532,12 @@
         <v>0.001732</v>
       </c>
       <c r="L480" s="1" t="n">
+        <v>0.001723</v>
+      </c>
+      <c r="M480" s="1" t="n">
         <v>0.001734</v>
       </c>
-      <c r="M480" s="1" t="n">
+      <c r="N480" s="1" t="n">
         <v>0.001719</v>
       </c>
     </row>
@@ -21135,9 +22578,12 @@
         <v>0.911</v>
       </c>
       <c r="L481" s="1" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="M481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="M481" s="1" t="n">
+      <c r="N481" s="1" t="n">
         <v>0.908</v>
       </c>
     </row>
@@ -21178,9 +22624,12 @@
         <v>0.13342</v>
       </c>
       <c r="L482" s="1" t="n">
+        <v>0.13375</v>
+      </c>
+      <c r="M482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="M482" s="1" t="n">
+      <c r="N482" s="1" t="n">
         <v>0.13336</v>
       </c>
     </row>
@@ -21221,9 +22670,12 @@
         <v>0.04031</v>
       </c>
       <c r="L483" s="1" t="n">
+        <v>0.04027</v>
+      </c>
+      <c r="M483" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="M483" s="1" t="n">
+      <c r="N483" s="1" t="n">
         <v>0.04023</v>
       </c>
     </row>
@@ -21264,9 +22716,12 @@
         <v>0.3022</v>
       </c>
       <c r="L484" s="1" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="M484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="M484" s="1" t="n">
+      <c r="N484" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -21307,9 +22762,12 @@
         <v>0.05637</v>
       </c>
       <c r="L485" s="1" t="n">
+        <v>0.05646</v>
+      </c>
+      <c r="M485" s="1" t="n">
         <v>0.05709</v>
       </c>
-      <c r="M485" s="1" t="n">
+      <c r="N485" s="1" t="n">
         <v>0.05603</v>
       </c>
     </row>
@@ -21350,10 +22808,13 @@
         <v>0.001569</v>
       </c>
       <c r="L486" s="1" t="n">
+        <v>0.001563</v>
+      </c>
+      <c r="M486" s="1" t="n">
         <v>0.001579</v>
       </c>
-      <c r="M486" s="1" t="n">
-        <v>0.001564</v>
+      <c r="N486" s="1" t="n">
+        <v>0.001563</v>
       </c>
     </row>
     <row r="487">
@@ -21393,9 +22854,12 @@
         <v>0.06723999999999999</v>
       </c>
       <c r="L487" s="1" t="n">
+        <v>0.06708</v>
+      </c>
+      <c r="M487" s="1" t="n">
         <v>0.06766999999999999</v>
       </c>
-      <c r="M487" s="1" t="n">
+      <c r="N487" s="1" t="n">
         <v>0.06702</v>
       </c>
     </row>
@@ -21436,9 +22900,12 @@
         <v>0.1935</v>
       </c>
       <c r="L488" s="1" t="n">
+        <v>0.1929</v>
+      </c>
+      <c r="M488" s="1" t="n">
         <v>0.1953</v>
       </c>
-      <c r="M488" s="1" t="n">
+      <c r="N488" s="1" t="n">
         <v>0.1929</v>
       </c>
     </row>
@@ -21479,9 +22946,12 @@
         <v>0.04803</v>
       </c>
       <c r="L489" s="1" t="n">
+        <v>0.04797</v>
+      </c>
+      <c r="M489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="M489" s="1" t="n">
+      <c r="N489" s="1" t="n">
         <v>0.04779</v>
       </c>
     </row>
@@ -21522,9 +22992,12 @@
         <v>0.1396</v>
       </c>
       <c r="L490" s="1" t="n">
+        <v>0.1393</v>
+      </c>
+      <c r="M490" s="1" t="n">
         <v>0.1401</v>
       </c>
-      <c r="M490" s="1" t="n">
+      <c r="N490" s="1" t="n">
         <v>0.1389</v>
       </c>
     </row>
@@ -21565,9 +23038,12 @@
         <v>0.02253</v>
       </c>
       <c r="L491" s="1" t="n">
+        <v>0.02244</v>
+      </c>
+      <c r="M491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="M491" s="1" t="n">
+      <c r="N491" s="1" t="n">
         <v>0.02243</v>
       </c>
     </row>
@@ -21608,9 +23084,12 @@
         <v>0.007776</v>
       </c>
       <c r="L492" s="1" t="n">
+        <v>0.007781</v>
+      </c>
+      <c r="M492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="M492" s="1" t="n">
+      <c r="N492" s="1" t="n">
         <v>0.007746</v>
       </c>
     </row>
@@ -21651,10 +23130,13 @@
         <v>0.000593</v>
       </c>
       <c r="L493" s="1" t="n">
+        <v>0.0005926</v>
+      </c>
+      <c r="M493" s="1" t="n">
         <v>0.0005992</v>
       </c>
-      <c r="M493" s="1" t="n">
-        <v>0.000593</v>
+      <c r="N493" s="1" t="n">
+        <v>0.0005926</v>
       </c>
     </row>
     <row r="494">
@@ -21694,9 +23176,12 @@
         <v>3.026</v>
       </c>
       <c r="L494" s="1" t="n">
+        <v>3.021</v>
+      </c>
+      <c r="M494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="M494" s="1" t="n">
+      <c r="N494" s="1" t="n">
         <v>2.999</v>
       </c>
     </row>
@@ -21737,9 +23222,12 @@
         <v>0.0507</v>
       </c>
       <c r="L495" s="1" t="n">
+        <v>0.05063</v>
+      </c>
+      <c r="M495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="M495" s="1" t="n">
+      <c r="N495" s="1" t="n">
         <v>0.05042</v>
       </c>
     </row>
@@ -21780,9 +23268,12 @@
         <v>0.006772</v>
       </c>
       <c r="L496" s="1" t="n">
+        <v>0.006775</v>
+      </c>
+      <c r="M496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="M496" s="1" t="n">
+      <c r="N496" s="1" t="n">
         <v>0.006742</v>
       </c>
     </row>
@@ -21823,9 +23314,12 @@
         <v>1.3</v>
       </c>
       <c r="L497" s="1" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="M497" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="M497" s="1" t="n">
+      <c r="N497" s="1" t="n">
         <v>1.299</v>
       </c>
     </row>
@@ -21866,9 +23360,12 @@
         <v>0.03948</v>
       </c>
       <c r="L498" s="1" t="n">
+        <v>0.03941</v>
+      </c>
+      <c r="M498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="M498" s="1" t="n">
+      <c r="N498" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -21909,9 +23406,12 @@
         <v>0.04138</v>
       </c>
       <c r="L499" s="1" t="n">
+        <v>0.04128</v>
+      </c>
+      <c r="M499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="M499" s="1" t="n">
+      <c r="N499" s="1" t="n">
         <v>0.04101</v>
       </c>
     </row>
@@ -21952,9 +23452,12 @@
         <v>0.00545</v>
       </c>
       <c r="L500" s="1" t="n">
+        <v>0.00545</v>
+      </c>
+      <c r="M500" s="1" t="n">
         <v>0.00549</v>
       </c>
-      <c r="M500" s="1" t="n">
+      <c r="N500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -21995,9 +23498,12 @@
         <v>0.03575</v>
       </c>
       <c r="L501" s="1" t="n">
+        <v>0.03576</v>
+      </c>
+      <c r="M501" s="1" t="n">
         <v>0.0364</v>
       </c>
-      <c r="M501" s="1" t="n">
+      <c r="N501" s="1" t="n">
         <v>0.03571</v>
       </c>
     </row>
@@ -22038,10 +23544,13 @@
         <v>0.07240000000000001</v>
       </c>
       <c r="L502" s="1" t="n">
+        <v>0.07232</v>
+      </c>
+      <c r="M502" s="1" t="n">
         <v>0.07342</v>
       </c>
-      <c r="M502" s="1" t="n">
-        <v>0.07240000000000001</v>
+      <c r="N502" s="1" t="n">
+        <v>0.07232</v>
       </c>
     </row>
     <row r="503">
@@ -22081,9 +23590,12 @@
         <v>0.0007496</v>
       </c>
       <c r="L503" s="1" t="n">
+        <v>0.0007467</v>
+      </c>
+      <c r="M503" s="1" t="n">
         <v>0.000755</v>
       </c>
-      <c r="M503" s="1" t="n">
+      <c r="N503" s="1" t="n">
         <v>0.0007422</v>
       </c>
     </row>
@@ -22124,9 +23636,12 @@
         <v>0.015986</v>
       </c>
       <c r="L504" s="1" t="n">
-        <v>0.016003</v>
+        <v>0.016016</v>
       </c>
       <c r="M504" s="1" t="n">
+        <v>0.016016</v>
+      </c>
+      <c r="N504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -22167,9 +23682,12 @@
         <v>0.00704</v>
       </c>
       <c r="L505" s="1" t="n">
+        <v>0.00703</v>
+      </c>
+      <c r="M505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="M505" s="1" t="n">
+      <c r="N505" s="1" t="n">
         <v>0.00703</v>
       </c>
     </row>
@@ -22210,9 +23728,12 @@
         <v>0.0256</v>
       </c>
       <c r="L506" s="1" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="M506" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="M506" s="1" t="n">
+      <c r="N506" s="1" t="n">
         <v>0.0255</v>
       </c>
     </row>
@@ -22253,9 +23774,12 @@
         <v>0.00136</v>
       </c>
       <c r="L507" s="1" t="n">
+        <v>0.001355</v>
+      </c>
+      <c r="M507" s="1" t="n">
         <v>0.00136</v>
       </c>
-      <c r="M507" s="1" t="n">
+      <c r="N507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -22296,9 +23820,12 @@
         <v>0.2815</v>
       </c>
       <c r="L508" s="1" t="n">
+        <v>0.2812</v>
+      </c>
+      <c r="M508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="M508" s="1" t="n">
+      <c r="N508" s="1" t="n">
         <v>0.2805</v>
       </c>
     </row>
@@ -22339,9 +23866,12 @@
         <v>0.132</v>
       </c>
       <c r="L509" s="1" t="n">
+        <v>0.1319</v>
+      </c>
+      <c r="M509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="M509" s="1" t="n">
+      <c r="N509" s="1" t="n">
         <v>0.1317</v>
       </c>
     </row>
@@ -22382,9 +23912,12 @@
         <v>0.04927</v>
       </c>
       <c r="L510" s="1" t="n">
+        <v>0.04927</v>
+      </c>
+      <c r="M510" s="1" t="n">
         <v>0.04972</v>
       </c>
-      <c r="M510" s="1" t="n">
+      <c r="N510" s="1" t="n">
         <v>0.04896</v>
       </c>
     </row>
@@ -22425,10 +23958,13 @@
         <v>0.00273</v>
       </c>
       <c r="L511" s="1" t="n">
+        <v>0.00272</v>
+      </c>
+      <c r="M511" s="1" t="n">
         <v>0.00278</v>
       </c>
-      <c r="M511" s="1" t="n">
-        <v>0.00273</v>
+      <c r="N511" s="1" t="n">
+        <v>0.00272</v>
       </c>
     </row>
     <row r="512">
@@ -22468,10 +24004,13 @@
         <v>0.015301</v>
       </c>
       <c r="L512" s="1" t="n">
+        <v>0.015017</v>
+      </c>
+      <c r="M512" s="1" t="n">
         <v>0.015454</v>
       </c>
-      <c r="M512" s="1" t="n">
-        <v>0.015285</v>
+      <c r="N512" s="1" t="n">
+        <v>0.015017</v>
       </c>
     </row>
     <row r="513">
@@ -22511,9 +24050,12 @@
         <v>0.6927</v>
       </c>
       <c r="L513" s="1" t="n">
+        <v>0.6916</v>
+      </c>
+      <c r="M513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="M513" s="1" t="n">
+      <c r="N513" s="1" t="n">
         <v>0.6899</v>
       </c>
     </row>
@@ -22554,9 +24096,12 @@
         <v>0.00452</v>
       </c>
       <c r="L514" s="1" t="n">
+        <v>0.004535</v>
+      </c>
+      <c r="M514" s="1" t="n">
         <v>0.004589</v>
       </c>
-      <c r="M514" s="1" t="n">
+      <c r="N514" s="1" t="n">
         <v>0.004517</v>
       </c>
     </row>
@@ -22597,9 +24142,12 @@
         <v>0.00503</v>
       </c>
       <c r="L515" s="1" t="n">
+        <v>0.005018</v>
+      </c>
+      <c r="M515" s="1" t="n">
         <v>0.005066</v>
       </c>
-      <c r="M515" s="1" t="n">
+      <c r="N515" s="1" t="n">
         <v>0.005008</v>
       </c>
     </row>
@@ -22640,9 +24188,12 @@
         <v>0.06338000000000001</v>
       </c>
       <c r="L516" s="1" t="n">
+        <v>0.06331000000000001</v>
+      </c>
+      <c r="M516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="M516" s="1" t="n">
+      <c r="N516" s="1" t="n">
         <v>0.06320000000000001</v>
       </c>
     </row>
@@ -22683,9 +24234,12 @@
         <v>0.06533</v>
       </c>
       <c r="L517" s="1" t="n">
+        <v>0.06514</v>
+      </c>
+      <c r="M517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="M517" s="1" t="n">
+      <c r="N517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -22726,9 +24280,12 @@
         <v>0.01207</v>
       </c>
       <c r="L518" s="1" t="n">
+        <v>0.01204</v>
+      </c>
+      <c r="M518" s="1" t="n">
         <v>0.01219</v>
       </c>
-      <c r="M518" s="1" t="n">
+      <c r="N518" s="1" t="n">
         <v>0.01199</v>
       </c>
     </row>
@@ -22769,9 +24326,12 @@
         <v>0.04779</v>
       </c>
       <c r="L519" s="1" t="n">
+        <v>0.04763</v>
+      </c>
+      <c r="M519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="M519" s="1" t="n">
+      <c r="N519" s="1" t="n">
         <v>0.04743</v>
       </c>
     </row>
@@ -22812,9 +24372,12 @@
         <v>0.04365</v>
       </c>
       <c r="L520" s="1" t="n">
+        <v>0.04371</v>
+      </c>
+      <c r="M520" s="1" t="n">
         <v>0.04411</v>
       </c>
-      <c r="M520" s="1" t="n">
+      <c r="N520" s="1" t="n">
         <v>0.04349</v>
       </c>
     </row>
@@ -22855,9 +24418,12 @@
         <v>0.008448000000000001</v>
       </c>
       <c r="L521" s="1" t="n">
+        <v>0.00844</v>
+      </c>
+      <c r="M521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="M521" s="1" t="n">
+      <c r="N521" s="1" t="n">
         <v>0.008411999999999999</v>
       </c>
     </row>
@@ -22898,10 +24464,13 @@
         <v>0.08791</v>
       </c>
       <c r="L522" s="1" t="n">
+        <v>0.08787</v>
+      </c>
+      <c r="M522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="M522" s="1" t="n">
-        <v>0.08791</v>
+      <c r="N522" s="1" t="n">
+        <v>0.08787</v>
       </c>
     </row>
     <row r="523">
@@ -22941,9 +24510,12 @@
         <v>0.006451</v>
       </c>
       <c r="L523" s="1" t="n">
+        <v>0.006443</v>
+      </c>
+      <c r="M523" s="1" t="n">
         <v>0.006492</v>
       </c>
-      <c r="M523" s="1" t="n">
+      <c r="N523" s="1" t="n">
         <v>0.006433</v>
       </c>
     </row>
@@ -22984,10 +24556,13 @@
         <v>0.01646</v>
       </c>
       <c r="L524" s="1" t="n">
+        <v>0.01641</v>
+      </c>
+      <c r="M524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="M524" s="1" t="n">
-        <v>0.01644</v>
+      <c r="N524" s="1" t="n">
+        <v>0.01641</v>
       </c>
     </row>
     <row r="525">
@@ -23027,9 +24602,12 @@
         <v>0.01786</v>
       </c>
       <c r="L525" s="1" t="n">
+        <v>0.01784</v>
+      </c>
+      <c r="M525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="M525" s="1" t="n">
+      <c r="N525" s="1" t="n">
         <v>0.01779</v>
       </c>
     </row>
@@ -23070,9 +24648,12 @@
         <v>0.07951</v>
       </c>
       <c r="L526" s="1" t="n">
+        <v>0.0793</v>
+      </c>
+      <c r="M526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="M526" s="1" t="n">
+      <c r="N526" s="1" t="n">
         <v>0.07883</v>
       </c>
     </row>
@@ -23113,10 +24694,13 @@
         <v>0.01612</v>
       </c>
       <c r="L527" s="1" t="n">
+        <v>0.01603</v>
+      </c>
+      <c r="M527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="M527" s="1" t="n">
-        <v>0.01606</v>
+      <c r="N527" s="1" t="n">
+        <v>0.01603</v>
       </c>
     </row>
     <row r="528">
@@ -23156,9 +24740,12 @@
         <v>0.00417</v>
       </c>
       <c r="L528" s="1" t="n">
+        <v>0.004192</v>
+      </c>
+      <c r="M528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="M528" s="1" t="n">
+      <c r="N528" s="1" t="n">
         <v>0.004164</v>
       </c>
     </row>
@@ -23199,9 +24786,12 @@
         <v>0.003714</v>
       </c>
       <c r="L529" s="1" t="n">
+        <v>0.003699</v>
+      </c>
+      <c r="M529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="M529" s="1" t="n">
+      <c r="N529" s="1" t="n">
         <v>0.00369</v>
       </c>
     </row>
@@ -23242,9 +24832,12 @@
         <v>1.321</v>
       </c>
       <c r="L530" s="1" t="n">
+        <v>1.324</v>
+      </c>
+      <c r="M530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="M530" s="1" t="n">
+      <c r="N530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -23285,9 +24878,12 @@
         <v>0.49</v>
       </c>
       <c r="L531" s="1" t="n">
+        <v>0.4898</v>
+      </c>
+      <c r="M531" s="1" t="n">
         <v>0.494</v>
       </c>
-      <c r="M531" s="1" t="n">
+      <c r="N531" s="1" t="n">
         <v>0.4893</v>
       </c>
     </row>
@@ -23328,9 +24924,12 @@
         <v>0.03069</v>
       </c>
       <c r="L532" s="1" t="n">
+        <v>0.0306</v>
+      </c>
+      <c r="M532" s="1" t="n">
         <v>0.03091</v>
       </c>
-      <c r="M532" s="1" t="n">
+      <c r="N532" s="1" t="n">
         <v>0.03058</v>
       </c>
     </row>
@@ -23371,9 +24970,12 @@
         <v>0.1533</v>
       </c>
       <c r="L533" s="1" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="M533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="M533" s="1" t="n">
+      <c r="N533" s="1" t="n">
         <v>0.153</v>
       </c>
     </row>
@@ -23414,9 +25016,12 @@
         <v>0.05405</v>
       </c>
       <c r="L534" s="1" t="n">
+        <v>0.05382</v>
+      </c>
+      <c r="M534" s="1" t="n">
         <v>0.05424</v>
       </c>
-      <c r="M534" s="1" t="n">
+      <c r="N534" s="1" t="n">
         <v>0.0536</v>
       </c>
     </row>
@@ -23457,10 +25062,13 @@
         <v>0.01494</v>
       </c>
       <c r="L535" s="1" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="M535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="M535" s="1" t="n">
-        <v>0.01494</v>
+      <c r="N535" s="1" t="n">
+        <v>0.0149</v>
       </c>
     </row>
     <row r="536">
@@ -23500,9 +25108,12 @@
         <v>0.05893</v>
       </c>
       <c r="L536" s="1" t="n">
-        <v>0.05893</v>
+        <v>0.05909</v>
       </c>
       <c r="M536" s="1" t="n">
+        <v>0.05909</v>
+      </c>
+      <c r="N536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -23543,9 +25154,12 @@
         <v>0.05496</v>
       </c>
       <c r="L537" s="1" t="n">
+        <v>0.05498</v>
+      </c>
+      <c r="M537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="M537" s="1" t="n">
+      <c r="N537" s="1" t="n">
         <v>0.05481</v>
       </c>
     </row>
@@ -23586,9 +25200,12 @@
         <v>0.1062</v>
       </c>
       <c r="L538" s="1" t="n">
+        <v>0.1061</v>
+      </c>
+      <c r="M538" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="M538" s="1" t="n">
+      <c r="N538" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -23629,10 +25246,13 @@
         <v>0.01278</v>
       </c>
       <c r="L539" s="1" t="n">
+        <v>0.01273</v>
+      </c>
+      <c r="M539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="M539" s="1" t="n">
-        <v>0.01278</v>
+      <c r="N539" s="1" t="n">
+        <v>0.01273</v>
       </c>
     </row>
     <row r="540">
@@ -23672,9 +25292,12 @@
         <v>0.1746</v>
       </c>
       <c r="L540" s="1" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="M540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="M540" s="1" t="n">
+      <c r="N540" s="1" t="n">
         <v>0.174</v>
       </c>
     </row>
@@ -23715,9 +25338,12 @@
         <v>0.1228</v>
       </c>
       <c r="L541" s="1" t="n">
+        <v>0.1228</v>
+      </c>
+      <c r="M541" s="1" t="n">
         <v>0.1239</v>
       </c>
-      <c r="M541" s="1" t="n">
+      <c r="N541" s="1" t="n">
         <v>0.1226</v>
       </c>
     </row>
@@ -23758,9 +25384,12 @@
         <v>0.02489</v>
       </c>
       <c r="L542" s="1" t="n">
+        <v>0.02488</v>
+      </c>
+      <c r="M542" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="M542" s="1" t="n">
+      <c r="N542" s="1" t="n">
         <v>0.02481</v>
       </c>
     </row>
@@ -23801,9 +25430,12 @@
         <v>0.05877</v>
       </c>
       <c r="L543" s="1" t="n">
+        <v>0.05868</v>
+      </c>
+      <c r="M543" s="1" t="n">
         <v>0.059</v>
       </c>
-      <c r="M543" s="1" t="n">
+      <c r="N543" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O543"/>
+  <dimension ref="A1:P543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -432,8 +432,9 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -504,10 +505,15 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>price_03:00</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -556,9 +562,12 @@
         <v>71212.7</v>
       </c>
       <c r="N2" s="1" t="n">
+        <v>71020</v>
+      </c>
+      <c r="O2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="O2" s="1" t="n">
+      <c r="P2" s="1" t="n">
         <v>70995.10000000001</v>
       </c>
     </row>
@@ -605,10 +614,13 @@
         <v>2104.83</v>
       </c>
       <c r="N3" s="1" t="n">
+        <v>2099.88</v>
+      </c>
+      <c r="O3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="O3" s="1" t="n">
-        <v>2102.04</v>
+      <c r="P3" s="1" t="n">
+        <v>2099.88</v>
       </c>
     </row>
     <row r="4">
@@ -654,10 +666,13 @@
         <v>88.98999999999999</v>
       </c>
       <c r="N4" s="1" t="n">
+        <v>88.77</v>
+      </c>
+      <c r="O4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="O4" s="1" t="n">
-        <v>88.81999999999999</v>
+      <c r="P4" s="1" t="n">
+        <v>88.77</v>
       </c>
     </row>
     <row r="5">
@@ -703,10 +718,13 @@
         <v>3.818</v>
       </c>
       <c r="N5" s="1" t="n">
+        <v>3.766</v>
+      </c>
+      <c r="O5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="O5" s="1" t="n">
-        <v>3.77</v>
+      <c r="P5" s="1" t="n">
+        <v>3.766</v>
       </c>
     </row>
     <row r="6">
@@ -752,9 +770,12 @@
         <v>1.3996</v>
       </c>
       <c r="N6" s="1" t="n">
+        <v>1.3965</v>
+      </c>
+      <c r="O6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="O6" s="1" t="n">
+      <c r="P6" s="1" t="n">
         <v>1.3931</v>
       </c>
     </row>
@@ -801,10 +822,13 @@
         <v>0.09612</v>
       </c>
       <c r="N7" s="1" t="n">
+        <v>0.0958</v>
+      </c>
+      <c r="O7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="O7" s="1" t="n">
-        <v>0.09601</v>
+      <c r="P7" s="1" t="n">
+        <v>0.0958</v>
       </c>
     </row>
     <row r="8">
@@ -850,9 +874,12 @@
         <v>0.014471</v>
       </c>
       <c r="N8" s="1" t="n">
+        <v>0.014091</v>
+      </c>
+      <c r="O8" s="1" t="n">
         <v>0.014819</v>
       </c>
-      <c r="O8" s="1" t="n">
+      <c r="P8" s="1" t="n">
         <v>0.014064</v>
       </c>
     </row>
@@ -899,9 +926,12 @@
         <v>657.99</v>
       </c>
       <c r="N9" s="1" t="n">
+        <v>656.88</v>
+      </c>
+      <c r="O9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="O9" s="1" t="n">
+      <c r="P9" s="1" t="n">
         <v>655.72</v>
       </c>
     </row>
@@ -948,9 +978,12 @@
         <v>20.091</v>
       </c>
       <c r="N10" s="1" t="n">
+        <v>19.819</v>
+      </c>
+      <c r="O10" s="1" t="n">
         <v>20.23</v>
       </c>
-      <c r="O10" s="1" t="n">
+      <c r="P10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -997,10 +1030,13 @@
         <v>0.0034123</v>
       </c>
       <c r="N11" s="1" t="n">
+        <v>0.0033976</v>
+      </c>
+      <c r="O11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="O11" s="1" t="n">
-        <v>0.0034117</v>
+      <c r="P11" s="1" t="n">
+        <v>0.0033976</v>
       </c>
     </row>
     <row r="12">
@@ -1046,9 +1082,12 @@
         <v>36.596</v>
       </c>
       <c r="N12" s="1" t="n">
+        <v>36.554</v>
+      </c>
+      <c r="O12" s="1" t="n">
         <v>36.704</v>
       </c>
-      <c r="O12" s="1" t="n">
+      <c r="P12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -1095,9 +1134,12 @@
         <v>214.65</v>
       </c>
       <c r="N13" s="1" t="n">
+        <v>213.88</v>
+      </c>
+      <c r="O13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="O13" s="1" t="n">
+      <c r="P13" s="1" t="n">
         <v>212.33</v>
       </c>
     </row>
@@ -1144,9 +1186,12 @@
         <v>0.0011238</v>
       </c>
       <c r="N14" s="1" t="n">
+        <v>0.0011181</v>
+      </c>
+      <c r="O14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="O14" s="1" t="n">
+      <c r="P14" s="1" t="n">
         <v>0.0011136</v>
       </c>
     </row>
@@ -1193,9 +1238,12 @@
         <v>0.30332</v>
       </c>
       <c r="N15" s="1" t="n">
+        <v>0.29971</v>
+      </c>
+      <c r="O15" s="1" t="n">
         <v>0.30332</v>
       </c>
-      <c r="O15" s="1" t="n">
+      <c r="P15" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -1242,9 +1290,12 @@
         <v>231.81</v>
       </c>
       <c r="N16" s="1" t="n">
+        <v>231.89</v>
+      </c>
+      <c r="O16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="O16" s="1" t="n">
+      <c r="P16" s="1" t="n">
         <v>230.3</v>
       </c>
     </row>
@@ -1291,9 +1342,12 @@
         <v>1.0032</v>
       </c>
       <c r="N17" s="1" t="n">
+        <v>0.9991</v>
+      </c>
+      <c r="O17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="O17" s="1" t="n">
+      <c r="P17" s="1" t="n">
         <v>0.9963</v>
       </c>
     </row>
@@ -1340,10 +1394,13 @@
         <v>0.2673</v>
       </c>
       <c r="N18" s="1" t="n">
+        <v>0.2664</v>
+      </c>
+      <c r="O18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="O18" s="1" t="n">
-        <v>0.2671</v>
+      <c r="P18" s="1" t="n">
+        <v>0.2664</v>
       </c>
     </row>
     <row r="19">
@@ -1389,9 +1446,12 @@
         <v>9.802</v>
       </c>
       <c r="N19" s="1" t="n">
+        <v>9.772</v>
+      </c>
+      <c r="O19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="O19" s="1" t="n">
+      <c r="P19" s="1" t="n">
         <v>9.755000000000001</v>
       </c>
     </row>
@@ -1438,9 +1498,12 @@
         <v>5044.51</v>
       </c>
       <c r="N20" s="1" t="n">
+        <v>5046.6</v>
+      </c>
+      <c r="O20" s="1" t="n">
         <v>5059.14</v>
       </c>
-      <c r="O20" s="1" t="n">
+      <c r="P20" s="1" t="n">
         <v>5033.31</v>
       </c>
     </row>
@@ -1487,9 +1550,12 @@
         <v>464.45</v>
       </c>
       <c r="N21" s="1" t="n">
+        <v>463.97</v>
+      </c>
+      <c r="O21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="O21" s="1" t="n">
+      <c r="P21" s="1" t="n">
         <v>462.36</v>
       </c>
     </row>
@@ -1536,10 +1602,13 @@
         <v>1.404</v>
       </c>
       <c r="N22" s="1" t="n">
+        <v>1.3961</v>
+      </c>
+      <c r="O22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="O22" s="1" t="n">
-        <v>1.404</v>
+      <c r="P22" s="1" t="n">
+        <v>1.3961</v>
       </c>
     </row>
     <row r="23">
@@ -1585,9 +1654,12 @@
         <v>1.0136</v>
       </c>
       <c r="N23" s="1" t="n">
+        <v>1.0422</v>
+      </c>
+      <c r="O23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="O23" s="1" t="n">
+      <c r="P23" s="1" t="n">
         <v>1.0136</v>
       </c>
     </row>
@@ -1634,9 +1706,12 @@
         <v>1.349</v>
       </c>
       <c r="N24" s="1" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="O24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="O24" s="1" t="n">
+      <c r="P24" s="1" t="n">
         <v>1.344</v>
       </c>
     </row>
@@ -1683,10 +1758,13 @@
         <v>9.17</v>
       </c>
       <c r="N25" s="1" t="n">
+        <v>9.124000000000001</v>
+      </c>
+      <c r="O25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="O25" s="1" t="n">
-        <v>9.140000000000001</v>
+      <c r="P25" s="1" t="n">
+        <v>9.124000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1732,9 +1810,12 @@
         <v>0.3716</v>
       </c>
       <c r="N26" s="1" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="O26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="O26" s="1" t="n">
+      <c r="P26" s="1" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -1781,9 +1862,12 @@
         <v>0.88</v>
       </c>
       <c r="N27" s="1" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="O27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="O27" s="1" t="n">
+      <c r="P27" s="1" t="n">
         <v>0.876</v>
       </c>
     </row>
@@ -1830,9 +1914,12 @@
         <v>1.844</v>
       </c>
       <c r="N28" s="1" t="n">
+        <v>1.841</v>
+      </c>
+      <c r="O28" s="1" t="n">
         <v>1.844</v>
       </c>
-      <c r="O28" s="1" t="n">
+      <c r="P28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -1879,10 +1966,13 @@
         <v>0.1098</v>
       </c>
       <c r="N29" s="1" t="n">
+        <v>0.1093</v>
+      </c>
+      <c r="O29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="O29" s="1" t="n">
-        <v>0.1096</v>
+      <c r="P29" s="1" t="n">
+        <v>0.1093</v>
       </c>
     </row>
     <row r="30">
@@ -1928,10 +2018,13 @@
         <v>0.002045</v>
       </c>
       <c r="N30" s="1" t="n">
+        <v>0.002034</v>
+      </c>
+      <c r="O30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="O30" s="1" t="n">
-        <v>0.002045</v>
+      <c r="P30" s="1" t="n">
+        <v>0.002034</v>
       </c>
     </row>
     <row r="31">
@@ -1977,10 +2070,13 @@
         <v>1.477</v>
       </c>
       <c r="N31" s="1" t="n">
+        <v>1.472</v>
+      </c>
+      <c r="O31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="O31" s="1" t="n">
-        <v>1.475</v>
+      <c r="P31" s="1" t="n">
+        <v>1.472</v>
       </c>
     </row>
     <row r="32">
@@ -2026,9 +2122,12 @@
         <v>0.1765</v>
       </c>
       <c r="N32" s="1" t="n">
+        <v>0.1763</v>
+      </c>
+      <c r="O32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="O32" s="1" t="n">
+      <c r="P32" s="1" t="n">
         <v>0.1739</v>
       </c>
     </row>
@@ -2075,10 +2174,13 @@
         <v>0.1037</v>
       </c>
       <c r="N33" s="1" t="n">
+        <v>0.1036</v>
+      </c>
+      <c r="O33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="O33" s="1" t="n">
-        <v>0.1037</v>
+      <c r="P33" s="1" t="n">
+        <v>0.1036</v>
       </c>
     </row>
     <row r="34">
@@ -2124,10 +2226,13 @@
         <v>113.05</v>
       </c>
       <c r="N34" s="1" t="n">
+        <v>112.61</v>
+      </c>
+      <c r="O34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="O34" s="1" t="n">
-        <v>112.91</v>
+      <c r="P34" s="1" t="n">
+        <v>112.61</v>
       </c>
     </row>
     <row r="35">
@@ -2173,10 +2278,13 @@
         <v>6.652</v>
       </c>
       <c r="N35" s="1" t="n">
+        <v>6.587</v>
+      </c>
+      <c r="O35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="O35" s="1" t="n">
-        <v>6.652</v>
+      <c r="P35" s="1" t="n">
+        <v>6.587</v>
       </c>
     </row>
     <row r="36">
@@ -2222,9 +2330,12 @@
         <v>0.017343</v>
       </c>
       <c r="N36" s="1" t="n">
+        <v>0.017342</v>
+      </c>
+      <c r="O36" s="1" t="n">
         <v>0.017421</v>
       </c>
-      <c r="O36" s="1" t="n">
+      <c r="P36" s="1" t="n">
         <v>0.016815</v>
       </c>
     </row>
@@ -2271,10 +2382,13 @@
         <v>0.3616</v>
       </c>
       <c r="N37" s="1" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="O37" s="1" t="n">
-        <v>0.3606</v>
+      <c r="P37" s="1" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="38">
@@ -2320,9 +2434,12 @@
         <v>55.49</v>
       </c>
       <c r="N38" s="1" t="n">
+        <v>55.34</v>
+      </c>
+      <c r="O38" s="1" t="n">
         <v>55.79</v>
       </c>
-      <c r="O38" s="1" t="n">
+      <c r="P38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -2369,9 +2486,12 @@
         <v>0.59515</v>
       </c>
       <c r="N39" s="1" t="n">
+        <v>0.59954</v>
+      </c>
+      <c r="O39" s="1" t="n">
         <v>0.60089</v>
       </c>
-      <c r="O39" s="1" t="n">
+      <c r="P39" s="1" t="n">
         <v>0.58131</v>
       </c>
     </row>
@@ -2418,10 +2538,13 @@
         <v>4.037</v>
       </c>
       <c r="N40" s="1" t="n">
+        <v>4.024</v>
+      </c>
+      <c r="O40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="O40" s="1" t="n">
-        <v>4.028</v>
+      <c r="P40" s="1" t="n">
+        <v>4.024</v>
       </c>
     </row>
     <row r="41">
@@ -2467,9 +2590,12 @@
         <v>0.05077</v>
       </c>
       <c r="N41" s="1" t="n">
+        <v>0.05006</v>
+      </c>
+      <c r="O41" s="1" t="n">
         <v>0.0513</v>
       </c>
-      <c r="O41" s="1" t="n">
+      <c r="P41" s="1" t="n">
         <v>0.04927</v>
       </c>
     </row>
@@ -2516,9 +2642,12 @@
         <v>0.7032</v>
       </c>
       <c r="N42" s="1" t="n">
+        <v>0.7018</v>
+      </c>
+      <c r="O42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="O42" s="1" t="n">
+      <c r="P42" s="1" t="n">
         <v>0.7006</v>
       </c>
     </row>
@@ -2565,10 +2694,13 @@
         <v>0.22831</v>
       </c>
       <c r="N43" s="1" t="n">
+        <v>0.22812</v>
+      </c>
+      <c r="O43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="O43" s="1" t="n">
-        <v>0.22831</v>
+      <c r="P43" s="1" t="n">
+        <v>0.22812</v>
       </c>
     </row>
     <row r="44">
@@ -2614,9 +2746,12 @@
         <v>0.35581</v>
       </c>
       <c r="N44" s="1" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="O44" s="1" t="n">
         <v>0.35655</v>
       </c>
-      <c r="O44" s="1" t="n">
+      <c r="P44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -2663,10 +2798,13 @@
         <v>0.1703</v>
       </c>
       <c r="N45" s="1" t="n">
+        <v>0.1698</v>
+      </c>
+      <c r="O45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="O45" s="1" t="n">
-        <v>0.1699</v>
+      <c r="P45" s="1" t="n">
+        <v>0.1698</v>
       </c>
     </row>
     <row r="46">
@@ -2712,10 +2850,13 @@
         <v>0.0259</v>
       </c>
       <c r="N46" s="1" t="n">
+        <v>0.0258</v>
+      </c>
+      <c r="O46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="O46" s="1" t="n">
-        <v>0.0259</v>
+      <c r="P46" s="1" t="n">
+        <v>0.0258</v>
       </c>
     </row>
     <row r="47">
@@ -2761,10 +2902,13 @@
         <v>0.005964</v>
       </c>
       <c r="N47" s="1" t="n">
+        <v>0.005942</v>
+      </c>
+      <c r="O47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="O47" s="1" t="n">
-        <v>0.005958</v>
+      <c r="P47" s="1" t="n">
+        <v>0.005942</v>
       </c>
     </row>
     <row r="48">
@@ -2810,9 +2954,12 @@
         <v>0.007394</v>
       </c>
       <c r="N48" s="1" t="n">
+        <v>0.007367</v>
+      </c>
+      <c r="O48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="O48" s="1" t="n">
+      <c r="P48" s="1" t="n">
         <v>0.007349</v>
       </c>
     </row>
@@ -2859,9 +3006,12 @@
         <v>0.1084</v>
       </c>
       <c r="N49" s="1" t="n">
+        <v>0.1083</v>
+      </c>
+      <c r="O49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="O49" s="1" t="n">
+      <c r="P49" s="1" t="n">
         <v>0.1077</v>
       </c>
     </row>
@@ -2908,9 +3058,12 @@
         <v>0.04153</v>
       </c>
       <c r="N50" s="1" t="n">
-        <v>0.04153</v>
+        <v>0.04159</v>
       </c>
       <c r="O50" s="1" t="n">
+        <v>0.04159</v>
+      </c>
+      <c r="P50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -2957,9 +3110,12 @@
         <v>0.1633</v>
       </c>
       <c r="N51" s="1" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="O51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="O51" s="1" t="n">
+      <c r="P51" s="1" t="n">
         <v>0.1617</v>
       </c>
     </row>
@@ -3006,9 +3162,12 @@
         <v>0.00352</v>
       </c>
       <c r="N52" s="1" t="n">
+        <v>0.00351</v>
+      </c>
+      <c r="O52" s="1" t="n">
         <v>0.00357</v>
       </c>
-      <c r="O52" s="1" t="n">
+      <c r="P52" s="1" t="n">
         <v>0.0035</v>
       </c>
     </row>
@@ -3055,9 +3214,12 @@
         <v>2.636</v>
       </c>
       <c r="N53" s="1" t="n">
+        <v>2.629</v>
+      </c>
+      <c r="O53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="O53" s="1" t="n">
+      <c r="P53" s="1" t="n">
         <v>2.622</v>
       </c>
     </row>
@@ -3104,10 +3266,13 @@
         <v>0.00621</v>
       </c>
       <c r="N54" s="1" t="n">
+        <v>0.006182</v>
+      </c>
+      <c r="O54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="O54" s="1" t="n">
-        <v>0.006188</v>
+      <c r="P54" s="1" t="n">
+        <v>0.006182</v>
       </c>
     </row>
     <row r="55">
@@ -3153,9 +3318,12 @@
         <v>0.02948</v>
       </c>
       <c r="N55" s="1" t="n">
+        <v>0.02918</v>
+      </c>
+      <c r="O55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="O55" s="1" t="n">
+      <c r="P55" s="1" t="n">
         <v>0.02879</v>
       </c>
     </row>
@@ -3202,10 +3370,13 @@
         <v>0.7371</v>
       </c>
       <c r="N56" s="1" t="n">
+        <v>0.7351</v>
+      </c>
+      <c r="O56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="O56" s="1" t="n">
-        <v>0.7352</v>
+      <c r="P56" s="1" t="n">
+        <v>0.7351</v>
       </c>
     </row>
     <row r="57">
@@ -3251,9 +3422,12 @@
         <v>0.1038</v>
       </c>
       <c r="N57" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="O57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="O57" s="1" t="n">
+      <c r="P57" s="1" t="n">
         <v>0.1034</v>
       </c>
     </row>
@@ -3300,9 +3474,12 @@
         <v>0.9449</v>
       </c>
       <c r="N58" s="1" t="n">
+        <v>0.9383</v>
+      </c>
+      <c r="O58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="O58" s="1" t="n">
+      <c r="P58" s="1" t="n">
         <v>0.9355</v>
       </c>
     </row>
@@ -3349,9 +3526,12 @@
         <v>0.08729000000000001</v>
       </c>
       <c r="N59" s="1" t="n">
+        <v>0.08769</v>
+      </c>
+      <c r="O59" s="1" t="n">
         <v>0.08826000000000001</v>
       </c>
-      <c r="O59" s="1" t="n">
+      <c r="P59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -3398,10 +3578,13 @@
         <v>0.06969</v>
       </c>
       <c r="N60" s="1" t="n">
+        <v>0.06918000000000001</v>
+      </c>
+      <c r="O60" s="1" t="n">
         <v>0.0703</v>
       </c>
-      <c r="O60" s="1" t="n">
-        <v>0.06924</v>
+      <c r="P60" s="1" t="n">
+        <v>0.06918000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -3447,10 +3630,13 @@
         <v>0.05468</v>
       </c>
       <c r="N61" s="1" t="n">
+        <v>0.05439</v>
+      </c>
+      <c r="O61" s="1" t="n">
         <v>0.05523</v>
       </c>
-      <c r="O61" s="1" t="n">
-        <v>0.05445</v>
+      <c r="P61" s="1" t="n">
+        <v>0.05439</v>
       </c>
     </row>
     <row r="62">
@@ -3496,9 +3682,12 @@
         <v>0.010081</v>
       </c>
       <c r="N62" s="1" t="n">
+        <v>0.01007</v>
+      </c>
+      <c r="O62" s="1" t="n">
         <v>0.010194</v>
       </c>
-      <c r="O62" s="1" t="n">
+      <c r="P62" s="1" t="n">
         <v>0.009387</v>
       </c>
     </row>
@@ -3545,9 +3734,12 @@
         <v>0.29107</v>
       </c>
       <c r="N63" s="1" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="O63" s="1" t="n">
         <v>0.2912</v>
       </c>
-      <c r="O63" s="1" t="n">
+      <c r="P63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -3594,9 +3786,12 @@
         <v>0.07581</v>
       </c>
       <c r="N64" s="1" t="n">
-        <v>0.07591000000000001</v>
+        <v>0.07613</v>
       </c>
       <c r="O64" s="1" t="n">
+        <v>0.07613</v>
+      </c>
+      <c r="P64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -3643,9 +3838,12 @@
         <v>0.3184</v>
       </c>
       <c r="N65" s="1" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="O65" s="1" t="n">
         <v>0.3184</v>
       </c>
-      <c r="O65" s="1" t="n">
+      <c r="P65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -3692,10 +3890,13 @@
         <v>0.16279</v>
       </c>
       <c r="N66" s="1" t="n">
+        <v>0.1622</v>
+      </c>
+      <c r="O66" s="1" t="n">
         <v>0.16461</v>
       </c>
-      <c r="O66" s="1" t="n">
-        <v>0.16235</v>
+      <c r="P66" s="1" t="n">
+        <v>0.1622</v>
       </c>
     </row>
     <row r="67">
@@ -3741,9 +3942,12 @@
         <v>0.11957</v>
       </c>
       <c r="N67" s="1" t="n">
-        <v>0.11999</v>
+        <v>0.12014</v>
       </c>
       <c r="O67" s="1" t="n">
+        <v>0.12014</v>
+      </c>
+      <c r="P67" s="1" t="n">
         <v>0.11919</v>
       </c>
     </row>
@@ -3790,10 +3994,13 @@
         <v>0.09568</v>
       </c>
       <c r="N68" s="1" t="n">
+        <v>0.09520000000000001</v>
+      </c>
+      <c r="O68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="O68" s="1" t="n">
-        <v>0.09548</v>
+      <c r="P68" s="1" t="n">
+        <v>0.09520000000000001</v>
       </c>
     </row>
     <row r="69">
@@ -3839,9 +4046,12 @@
         <v>0.1248</v>
       </c>
       <c r="N69" s="1" t="n">
+        <v>0.1241</v>
+      </c>
+      <c r="O69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="O69" s="1" t="n">
+      <c r="P69" s="1" t="n">
         <v>0.1239</v>
       </c>
     </row>
@@ -3888,9 +4098,12 @@
         <v>8.532</v>
       </c>
       <c r="N70" s="1" t="n">
+        <v>8.503</v>
+      </c>
+      <c r="O70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="O70" s="1" t="n">
+      <c r="P70" s="1" t="n">
         <v>8.494</v>
       </c>
     </row>
@@ -3937,9 +4150,12 @@
         <v>0.238</v>
       </c>
       <c r="N71" s="1" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="O71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="O71" s="1" t="n">
+      <c r="P71" s="1" t="n">
         <v>0.238</v>
       </c>
     </row>
@@ -3986,9 +4202,12 @@
         <v>0.05005</v>
       </c>
       <c r="N72" s="1" t="n">
+        <v>0.04994</v>
+      </c>
+      <c r="O72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="O72" s="1" t="n">
+      <c r="P72" s="1" t="n">
         <v>0.04992</v>
       </c>
     </row>
@@ -4035,9 +4254,12 @@
         <v>0.05044</v>
       </c>
       <c r="N73" s="1" t="n">
+        <v>0.05022</v>
+      </c>
+      <c r="O73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="O73" s="1" t="n">
+      <c r="P73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -4084,10 +4306,13 @@
         <v>0.1258</v>
       </c>
       <c r="N74" s="1" t="n">
+        <v>0.1246</v>
+      </c>
+      <c r="O74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="O74" s="1" t="n">
-        <v>0.1252</v>
+      <c r="P74" s="1" t="n">
+        <v>0.1246</v>
       </c>
     </row>
     <row r="75">
@@ -4133,9 +4358,12 @@
         <v>0.04666</v>
       </c>
       <c r="N75" s="1" t="n">
+        <v>0.04656</v>
+      </c>
+      <c r="O75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="O75" s="1" t="n">
+      <c r="P75" s="1" t="n">
         <v>0.04621</v>
       </c>
     </row>
@@ -4182,9 +4410,12 @@
         <v>0.06703000000000001</v>
       </c>
       <c r="N76" s="1" t="n">
+        <v>0.06691999999999999</v>
+      </c>
+      <c r="O76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="O76" s="1" t="n">
+      <c r="P76" s="1" t="n">
         <v>0.06691</v>
       </c>
     </row>
@@ -4231,9 +4462,12 @@
         <v>0.12584</v>
       </c>
       <c r="N77" s="1" t="n">
+        <v>0.12665</v>
+      </c>
+      <c r="O77" s="1" t="n">
         <v>0.12881</v>
       </c>
-      <c r="O77" s="1" t="n">
+      <c r="P77" s="1" t="n">
         <v>0.12584</v>
       </c>
     </row>
@@ -4280,10 +4514,13 @@
         <v>0.1618</v>
       </c>
       <c r="N78" s="1" t="n">
+        <v>0.1611</v>
+      </c>
+      <c r="O78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="O78" s="1" t="n">
-        <v>0.1613</v>
+      <c r="P78" s="1" t="n">
+        <v>0.1611</v>
       </c>
     </row>
     <row r="79">
@@ -4329,9 +4566,12 @@
         <v>0.02714</v>
       </c>
       <c r="N79" s="1" t="n">
+        <v>0.02706</v>
+      </c>
+      <c r="O79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="O79" s="1" t="n">
+      <c r="P79" s="1" t="n">
         <v>0.02705</v>
       </c>
     </row>
@@ -4378,9 +4618,12 @@
         <v>358.2</v>
       </c>
       <c r="N80" s="1" t="n">
+        <v>357.33</v>
+      </c>
+      <c r="O80" s="1" t="n">
         <v>358.61</v>
       </c>
-      <c r="O80" s="1" t="n">
+      <c r="P80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -4427,10 +4670,13 @@
         <v>7.103e-05</v>
       </c>
       <c r="N81" s="1" t="n">
+        <v>7.067999999999999e-05</v>
+      </c>
+      <c r="O81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="O81" s="1" t="n">
-        <v>7.080999999999999e-05</v>
+      <c r="P81" s="1" t="n">
+        <v>7.067999999999999e-05</v>
       </c>
     </row>
     <row r="82">
@@ -4476,9 +4722,12 @@
         <v>0.2659</v>
       </c>
       <c r="N82" s="1" t="n">
+        <v>0.2645</v>
+      </c>
+      <c r="O82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="O82" s="1" t="n">
+      <c r="P82" s="1" t="n">
         <v>0.2645</v>
       </c>
     </row>
@@ -4525,10 +4774,13 @@
         <v>1.1314</v>
       </c>
       <c r="N83" s="1" t="n">
+        <v>1.1287</v>
+      </c>
+      <c r="O83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="O83" s="1" t="n">
-        <v>1.1314</v>
+      <c r="P83" s="1" t="n">
+        <v>1.1287</v>
       </c>
     </row>
     <row r="84">
@@ -4574,10 +4826,13 @@
         <v>0.3565</v>
       </c>
       <c r="N84" s="1" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="O84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="O84" s="1" t="n">
-        <v>0.3539</v>
+      <c r="P84" s="1" t="n">
+        <v>0.3535</v>
       </c>
     </row>
     <row r="85">
@@ -4623,9 +4878,12 @@
         <v>2.0207</v>
       </c>
       <c r="N85" s="1" t="n">
+        <v>2.0155</v>
+      </c>
+      <c r="O85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="O85" s="1" t="n">
+      <c r="P85" s="1" t="n">
         <v>2.0067</v>
       </c>
     </row>
@@ -4672,9 +4930,12 @@
         <v>1.3195</v>
       </c>
       <c r="N86" s="1" t="n">
+        <v>1.3143</v>
+      </c>
+      <c r="O86" s="1" t="n">
         <v>1.3205</v>
       </c>
-      <c r="O86" s="1" t="n">
+      <c r="P86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -4721,10 +4982,13 @@
         <v>32.78</v>
       </c>
       <c r="N87" s="1" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="O87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="O87" s="1" t="n">
-        <v>32.68</v>
+      <c r="P87" s="1" t="n">
+        <v>32.65</v>
       </c>
     </row>
     <row r="88">
@@ -4770,9 +5034,12 @@
         <v>0.009549999999999999</v>
       </c>
       <c r="N88" s="1" t="n">
+        <v>0.00958</v>
+      </c>
+      <c r="O88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="O88" s="1" t="n">
+      <c r="P88" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -4819,10 +5086,13 @@
         <v>0.01823</v>
       </c>
       <c r="N89" s="1" t="n">
+        <v>0.01808</v>
+      </c>
+      <c r="O89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="O89" s="1" t="n">
-        <v>0.01823</v>
+      <c r="P89" s="1" t="n">
+        <v>0.01808</v>
       </c>
     </row>
     <row r="90">
@@ -4868,10 +5138,13 @@
         <v>0.03505</v>
       </c>
       <c r="N90" s="1" t="n">
+        <v>0.03479</v>
+      </c>
+      <c r="O90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="O90" s="1" t="n">
-        <v>0.03497</v>
+      <c r="P90" s="1" t="n">
+        <v>0.03479</v>
       </c>
     </row>
     <row r="91">
@@ -4917,9 +5190,12 @@
         <v>0.01195</v>
       </c>
       <c r="N91" s="1" t="n">
+        <v>0.01181</v>
+      </c>
+      <c r="O91" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="O91" s="1" t="n">
+      <c r="P91" s="1" t="n">
         <v>0.0118</v>
       </c>
     </row>
@@ -4966,10 +5242,13 @@
         <v>3.101</v>
       </c>
       <c r="N92" s="1" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="O92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="O92" s="1" t="n">
-        <v>3.095</v>
+      <c r="P92" s="1" t="n">
+        <v>3.09</v>
       </c>
     </row>
     <row r="93">
@@ -5015,10 +5294,13 @@
         <v>0.005611</v>
       </c>
       <c r="N93" s="1" t="n">
+        <v>0.005592</v>
+      </c>
+      <c r="O93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="O93" s="1" t="n">
-        <v>0.005596</v>
+      <c r="P93" s="1" t="n">
+        <v>0.005592</v>
       </c>
     </row>
     <row r="94">
@@ -5064,9 +5346,12 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="N94" s="1" t="n">
+        <v>0.0931</v>
+      </c>
+      <c r="O94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="O94" s="1" t="n">
+      <c r="P94" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -5113,9 +5398,12 @@
         <v>0.6095</v>
       </c>
       <c r="N95" s="1" t="n">
+        <v>0.6077</v>
+      </c>
+      <c r="O95" s="1" t="n">
         <v>0.6098</v>
       </c>
-      <c r="O95" s="1" t="n">
+      <c r="P95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -5162,9 +5450,12 @@
         <v>1.27e-05</v>
       </c>
       <c r="N96" s="1" t="n">
+        <v>1.27e-05</v>
+      </c>
+      <c r="O96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="O96" s="1" t="n">
+      <c r="P96" s="1" t="n">
         <v>1.27e-05</v>
       </c>
     </row>
@@ -5211,10 +5502,13 @@
         <v>1.121</v>
       </c>
       <c r="N97" s="1" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="O97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="O97" s="1" t="n">
-        <v>1.121</v>
+      <c r="P97" s="1" t="n">
+        <v>1.12</v>
       </c>
     </row>
     <row r="98">
@@ -5260,9 +5554,12 @@
         <v>0.25473</v>
       </c>
       <c r="N98" s="1" t="n">
+        <v>0.25443</v>
+      </c>
+      <c r="O98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="O98" s="1" t="n">
+      <c r="P98" s="1" t="n">
         <v>0.2523</v>
       </c>
     </row>
@@ -5309,10 +5606,13 @@
         <v>1.147</v>
       </c>
       <c r="N99" s="1" t="n">
+        <v>1.143</v>
+      </c>
+      <c r="O99" s="1" t="n">
         <v>1.156</v>
       </c>
-      <c r="O99" s="1" t="n">
-        <v>1.144</v>
+      <c r="P99" s="1" t="n">
+        <v>1.143</v>
       </c>
     </row>
     <row r="100">
@@ -5358,9 +5658,12 @@
         <v>1.858</v>
       </c>
       <c r="N100" s="1" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="O100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="O100" s="1" t="n">
+      <c r="P100" s="1" t="n">
         <v>1.852</v>
       </c>
     </row>
@@ -5407,9 +5710,12 @@
         <v>0.0159</v>
       </c>
       <c r="N101" s="1" t="n">
+        <v>0.01589</v>
+      </c>
+      <c r="O101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="O101" s="1" t="n">
+      <c r="P101" s="1" t="n">
         <v>0.01579</v>
       </c>
     </row>
@@ -5456,9 +5762,12 @@
         <v>0.10279</v>
       </c>
       <c r="N102" s="1" t="n">
+        <v>0.10283</v>
+      </c>
+      <c r="O102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="O102" s="1" t="n">
+      <c r="P102" s="1" t="n">
         <v>0.10279</v>
       </c>
     </row>
@@ -5505,10 +5814,13 @@
         <v>0.0005981</v>
       </c>
       <c r="N103" s="1" t="n">
+        <v>0.0005946</v>
+      </c>
+      <c r="O103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="O103" s="1" t="n">
-        <v>0.0005967</v>
+      <c r="P103" s="1" t="n">
+        <v>0.0005946</v>
       </c>
     </row>
     <row r="104">
@@ -5554,9 +5866,12 @@
         <v>0.0005856</v>
       </c>
       <c r="N104" s="1" t="n">
-        <v>0.0005856</v>
+        <v>0.0005888999999999999</v>
       </c>
       <c r="O104" s="1" t="n">
+        <v>0.0005888999999999999</v>
+      </c>
+      <c r="P104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -5603,9 +5918,12 @@
         <v>0.003269</v>
       </c>
       <c r="N105" s="1" t="n">
+        <v>0.003246</v>
+      </c>
+      <c r="O105" s="1" t="n">
         <v>0.003269</v>
       </c>
-      <c r="O105" s="1" t="n">
+      <c r="P105" s="1" t="n">
         <v>0.003229</v>
       </c>
     </row>
@@ -5652,9 +5970,12 @@
         <v>2.602</v>
       </c>
       <c r="N106" s="1" t="n">
+        <v>2.587</v>
+      </c>
+      <c r="O106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="O106" s="1" t="n">
+      <c r="P106" s="1" t="n">
         <v>2.587</v>
       </c>
     </row>
@@ -5701,9 +6022,12 @@
         <v>0.1657</v>
       </c>
       <c r="N107" s="1" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="O107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="O107" s="1" t="n">
+      <c r="P107" s="1" t="n">
         <v>0.165</v>
       </c>
     </row>
@@ -5750,9 +6074,12 @@
         <v>0.09647</v>
       </c>
       <c r="N108" s="1" t="n">
+        <v>0.09619999999999999</v>
+      </c>
+      <c r="O108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="O108" s="1" t="n">
+      <c r="P108" s="1" t="n">
         <v>0.0955</v>
       </c>
     </row>
@@ -5799,9 +6126,12 @@
         <v>0.02207</v>
       </c>
       <c r="N109" s="1" t="n">
+        <v>0.02208</v>
+      </c>
+      <c r="O109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="O109" s="1" t="n">
+      <c r="P109" s="1" t="n">
         <v>0.02204</v>
       </c>
     </row>
@@ -5848,9 +6178,12 @@
         <v>0.2941</v>
       </c>
       <c r="N110" s="1" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="O110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="O110" s="1" t="n">
+      <c r="P110" s="1" t="n">
         <v>0.2912</v>
       </c>
     </row>
@@ -5897,9 +6230,12 @@
         <v>0.05692</v>
       </c>
       <c r="N111" s="1" t="n">
+        <v>0.05691</v>
+      </c>
+      <c r="O111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="O111" s="1" t="n">
+      <c r="P111" s="1" t="n">
         <v>0.05659</v>
       </c>
     </row>
@@ -5946,9 +6282,12 @@
         <v>0.3016</v>
       </c>
       <c r="N112" s="1" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="O112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="O112" s="1" t="n">
+      <c r="P112" s="1" t="n">
         <v>0.3002</v>
       </c>
     </row>
@@ -5995,9 +6334,12 @@
         <v>18.65</v>
       </c>
       <c r="N113" s="1" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="O113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="O113" s="1" t="n">
+      <c r="P113" s="1" t="n">
         <v>18.6</v>
       </c>
     </row>
@@ -6044,10 +6386,13 @@
         <v>0.12837</v>
       </c>
       <c r="N114" s="1" t="n">
+        <v>0.12826</v>
+      </c>
+      <c r="O114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="O114" s="1" t="n">
-        <v>0.12837</v>
+      <c r="P114" s="1" t="n">
+        <v>0.12826</v>
       </c>
     </row>
     <row r="115">
@@ -6093,9 +6438,12 @@
         <v>0.01584</v>
       </c>
       <c r="N115" s="1" t="n">
+        <v>0.01577</v>
+      </c>
+      <c r="O115" s="1" t="n">
         <v>0.01584</v>
       </c>
-      <c r="O115" s="1" t="n">
+      <c r="P115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -6142,10 +6490,13 @@
         <v>0.08497</v>
       </c>
       <c r="N116" s="1" t="n">
+        <v>0.08454</v>
+      </c>
+      <c r="O116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="O116" s="1" t="n">
-        <v>0.08470999999999999</v>
+      <c r="P116" s="1" t="n">
+        <v>0.08454</v>
       </c>
     </row>
     <row r="117">
@@ -6191,9 +6542,12 @@
         <v>0.047386</v>
       </c>
       <c r="N117" s="1" t="n">
+        <v>0.047376</v>
+      </c>
+      <c r="O117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="O117" s="1" t="n">
+      <c r="P117" s="1" t="n">
         <v>0.047288</v>
       </c>
     </row>
@@ -6240,10 +6594,13 @@
         <v>0.04743</v>
       </c>
       <c r="N118" s="1" t="n">
+        <v>0.04721</v>
+      </c>
+      <c r="O118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="O118" s="1" t="n">
-        <v>0.04732</v>
+      <c r="P118" s="1" t="n">
+        <v>0.04721</v>
       </c>
     </row>
     <row r="119">
@@ -6289,9 +6646,12 @@
         <v>0.04054</v>
       </c>
       <c r="N119" s="1" t="n">
+        <v>0.04053</v>
+      </c>
+      <c r="O119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="O119" s="1" t="n">
+      <c r="P119" s="1" t="n">
         <v>0.03999</v>
       </c>
     </row>
@@ -6338,9 +6698,12 @@
         <v>0.14387</v>
       </c>
       <c r="N120" s="1" t="n">
+        <v>0.14421</v>
+      </c>
+      <c r="O120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="O120" s="1" t="n">
+      <c r="P120" s="1" t="n">
         <v>0.14387</v>
       </c>
     </row>
@@ -6387,10 +6750,13 @@
         <v>0.1273</v>
       </c>
       <c r="N121" s="1" t="n">
+        <v>0.1268</v>
+      </c>
+      <c r="O121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="O121" s="1" t="n">
-        <v>0.1272</v>
+      <c r="P121" s="1" t="n">
+        <v>0.1268</v>
       </c>
     </row>
     <row r="122">
@@ -6436,10 +6802,13 @@
         <v>1.864</v>
       </c>
       <c r="N122" s="1" t="n">
+        <v>1.859</v>
+      </c>
+      <c r="O122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="O122" s="1" t="n">
-        <v>1.864</v>
+      <c r="P122" s="1" t="n">
+        <v>1.859</v>
       </c>
     </row>
     <row r="123">
@@ -6485,10 +6854,13 @@
         <v>0.03026</v>
       </c>
       <c r="N123" s="1" t="n">
+        <v>0.03009</v>
+      </c>
+      <c r="O123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="O123" s="1" t="n">
-        <v>0.0301</v>
+      <c r="P123" s="1" t="n">
+        <v>0.03009</v>
       </c>
     </row>
     <row r="124">
@@ -6534,10 +6906,13 @@
         <v>0.13153</v>
       </c>
       <c r="N124" s="1" t="n">
+        <v>0.13138</v>
+      </c>
+      <c r="O124" s="1" t="n">
         <v>0.13401</v>
       </c>
-      <c r="O124" s="1" t="n">
-        <v>0.13153</v>
+      <c r="P124" s="1" t="n">
+        <v>0.13138</v>
       </c>
     </row>
     <row r="125">
@@ -6583,9 +6958,12 @@
         <v>0.04103</v>
       </c>
       <c r="N125" s="1" t="n">
+        <v>0.04097</v>
+      </c>
+      <c r="O125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="O125" s="1" t="n">
+      <c r="P125" s="1" t="n">
         <v>0.04095</v>
       </c>
     </row>
@@ -6632,10 +7010,13 @@
         <v>0.1152</v>
       </c>
       <c r="N126" s="1" t="n">
+        <v>0.1145</v>
+      </c>
+      <c r="O126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="O126" s="1" t="n">
-        <v>0.1147</v>
+      <c r="P126" s="1" t="n">
+        <v>0.1145</v>
       </c>
     </row>
     <row r="127">
@@ -6681,9 +7062,12 @@
         <v>0.5164</v>
       </c>
       <c r="N127" s="1" t="n">
-        <v>0.5164</v>
+        <v>0.5196</v>
       </c>
       <c r="O127" s="1" t="n">
+        <v>0.5196</v>
+      </c>
+      <c r="P127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -6730,9 +7114,12 @@
         <v>0.03787</v>
       </c>
       <c r="N128" s="1" t="n">
+        <v>0.03787</v>
+      </c>
+      <c r="O128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="O128" s="1" t="n">
+      <c r="P128" s="1" t="n">
         <v>0.03787</v>
       </c>
     </row>
@@ -6779,9 +7166,12 @@
         <v>0.792</v>
       </c>
       <c r="N129" s="1" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="O129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="O129" s="1" t="n">
+      <c r="P129" s="1" t="n">
         <v>0.791</v>
       </c>
     </row>
@@ -6828,9 +7218,12 @@
         <v>0.03449</v>
       </c>
       <c r="N130" s="1" t="n">
+        <v>0.03431</v>
+      </c>
+      <c r="O130" s="1" t="n">
         <v>0.03458</v>
       </c>
-      <c r="O130" s="1" t="n">
+      <c r="P130" s="1" t="n">
         <v>0.03422</v>
       </c>
     </row>
@@ -6877,9 +7270,12 @@
         <v>0.4246</v>
       </c>
       <c r="N131" s="1" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="O131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="O131" s="1" t="n">
+      <c r="P131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -6926,10 +7322,13 @@
         <v>0.04382</v>
       </c>
       <c r="N132" s="1" t="n">
+        <v>0.04309</v>
+      </c>
+      <c r="O132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="O132" s="1" t="n">
-        <v>0.04354</v>
+      <c r="P132" s="1" t="n">
+        <v>0.04309</v>
       </c>
     </row>
     <row r="133">
@@ -6975,9 +7374,12 @@
         <v>1.2899</v>
       </c>
       <c r="N133" s="1" t="n">
+        <v>1.2845</v>
+      </c>
+      <c r="O133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="O133" s="1" t="n">
+      <c r="P133" s="1" t="n">
         <v>1.282</v>
       </c>
     </row>
@@ -7024,9 +7426,12 @@
         <v>0.02189</v>
       </c>
       <c r="N134" s="1" t="n">
+        <v>0.02186</v>
+      </c>
+      <c r="O134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="O134" s="1" t="n">
+      <c r="P134" s="1" t="n">
         <v>0.02184</v>
       </c>
     </row>
@@ -7073,10 +7478,13 @@
         <v>0.0004608</v>
       </c>
       <c r="N135" s="1" t="n">
+        <v>0.0004583</v>
+      </c>
+      <c r="O135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="O135" s="1" t="n">
-        <v>0.0004592</v>
+      <c r="P135" s="1" t="n">
+        <v>0.0004583</v>
       </c>
     </row>
     <row r="136">
@@ -7122,9 +7530,12 @@
         <v>0.001904</v>
       </c>
       <c r="N136" s="1" t="n">
+        <v>0.001907</v>
+      </c>
+      <c r="O136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="O136" s="1" t="n">
+      <c r="P136" s="1" t="n">
         <v>0.001881</v>
       </c>
     </row>
@@ -7171,10 +7582,13 @@
         <v>0.3165</v>
       </c>
       <c r="N137" s="1" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="O137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="O137" s="1" t="n">
-        <v>0.3164</v>
+      <c r="P137" s="1" t="n">
+        <v>0.3143</v>
       </c>
     </row>
     <row r="138">
@@ -7220,10 +7634,13 @@
         <v>0.5706</v>
       </c>
       <c r="N138" s="1" t="n">
+        <v>0.5672</v>
+      </c>
+      <c r="O138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="O138" s="1" t="n">
-        <v>0.5698</v>
+      <c r="P138" s="1" t="n">
+        <v>0.5672</v>
       </c>
     </row>
     <row r="139">
@@ -7269,9 +7686,12 @@
         <v>0.02134</v>
       </c>
       <c r="N139" s="1" t="n">
+        <v>0.02127</v>
+      </c>
+      <c r="O139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="O139" s="1" t="n">
+      <c r="P139" s="1" t="n">
         <v>0.02125</v>
       </c>
     </row>
@@ -7318,10 +7738,13 @@
         <v>0.0804</v>
       </c>
       <c r="N140" s="1" t="n">
+        <v>0.08018</v>
+      </c>
+      <c r="O140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="O140" s="1" t="n">
-        <v>0.08036</v>
+      <c r="P140" s="1" t="n">
+        <v>0.08018</v>
       </c>
     </row>
     <row r="141">
@@ -7367,9 +7790,12 @@
         <v>0.001502</v>
       </c>
       <c r="N141" s="1" t="n">
+        <v>0.001522</v>
+      </c>
+      <c r="O141" s="1" t="n">
         <v>0.001672</v>
       </c>
-      <c r="O141" s="1" t="n">
+      <c r="P141" s="1" t="n">
         <v>0.001502</v>
       </c>
     </row>
@@ -7416,9 +7842,12 @@
         <v>0.4447</v>
       </c>
       <c r="N142" s="1" t="n">
-        <v>0.4447</v>
+        <v>0.4475</v>
       </c>
       <c r="O142" s="1" t="n">
+        <v>0.4475</v>
+      </c>
+      <c r="P142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -7465,9 +7894,12 @@
         <v>0.031368</v>
       </c>
       <c r="N143" s="1" t="n">
+        <v>0.030287</v>
+      </c>
+      <c r="O143" s="1" t="n">
         <v>0.031368</v>
       </c>
-      <c r="O143" s="1" t="n">
+      <c r="P143" s="1" t="n">
         <v>0.030021</v>
       </c>
     </row>
@@ -7514,9 +7946,12 @@
         <v>0.000227</v>
       </c>
       <c r="N144" s="1" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="O144" s="1" t="n">
         <v>0.000227</v>
       </c>
-      <c r="O144" s="1" t="n">
+      <c r="P144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -7563,9 +7998,12 @@
         <v>0.03446</v>
       </c>
       <c r="N145" s="1" t="n">
+        <v>0.03474</v>
+      </c>
+      <c r="O145" s="1" t="n">
         <v>0.03696</v>
       </c>
-      <c r="O145" s="1" t="n">
+      <c r="P145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -7612,10 +8050,13 @@
         <v>0.11548</v>
       </c>
       <c r="N146" s="1" t="n">
+        <v>0.11505</v>
+      </c>
+      <c r="O146" s="1" t="n">
         <v>0.116</v>
       </c>
-      <c r="O146" s="1" t="n">
-        <v>0.11518</v>
+      <c r="P146" s="1" t="n">
+        <v>0.11505</v>
       </c>
     </row>
     <row r="147">
@@ -7661,9 +8102,12 @@
         <v>0.0219</v>
       </c>
       <c r="N147" s="1" t="n">
+        <v>0.02193</v>
+      </c>
+      <c r="O147" s="1" t="n">
         <v>0.02198</v>
       </c>
-      <c r="O147" s="1" t="n">
+      <c r="P147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -7710,9 +8154,12 @@
         <v>1.4145</v>
       </c>
       <c r="N148" s="1" t="n">
+        <v>1.4105</v>
+      </c>
+      <c r="O148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="O148" s="1" t="n">
+      <c r="P148" s="1" t="n">
         <v>1.4084</v>
       </c>
     </row>
@@ -7759,9 +8206,12 @@
         <v>1.8787</v>
       </c>
       <c r="N149" s="1" t="n">
+        <v>1.8738</v>
+      </c>
+      <c r="O149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="O149" s="1" t="n">
+      <c r="P149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -7808,9 +8258,12 @@
         <v>0.097</v>
       </c>
       <c r="N150" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="O150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="O150" s="1" t="n">
+      <c r="P150" s="1" t="n">
         <v>0.096</v>
       </c>
     </row>
@@ -7857,9 +8310,12 @@
         <v>4.614</v>
       </c>
       <c r="N151" s="1" t="n">
+        <v>4.614</v>
+      </c>
+      <c r="O151" s="1" t="n">
         <v>4.64</v>
       </c>
-      <c r="O151" s="1" t="n">
+      <c r="P151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -7906,9 +8362,12 @@
         <v>5.564</v>
       </c>
       <c r="N152" s="1" t="n">
+        <v>5.533</v>
+      </c>
+      <c r="O152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="O152" s="1" t="n">
+      <c r="P152" s="1" t="n">
         <v>5.522</v>
       </c>
     </row>
@@ -7955,10 +8414,13 @@
         <v>0.3172</v>
       </c>
       <c r="N153" s="1" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="O153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="O153" s="1" t="n">
-        <v>0.3172</v>
+      <c r="P153" s="1" t="n">
+        <v>0.3154</v>
       </c>
     </row>
     <row r="154">
@@ -8004,10 +8466,13 @@
         <v>0.5862000000000001</v>
       </c>
       <c r="N154" s="1" t="n">
+        <v>0.5847</v>
+      </c>
+      <c r="O154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="O154" s="1" t="n">
-        <v>0.5862000000000001</v>
+      <c r="P154" s="1" t="n">
+        <v>0.5847</v>
       </c>
     </row>
     <row r="155">
@@ -8053,9 +8518,12 @@
         <v>0.01292</v>
       </c>
       <c r="N155" s="1" t="n">
+        <v>0.01285</v>
+      </c>
+      <c r="O155" s="1" t="n">
         <v>0.01299</v>
       </c>
-      <c r="O155" s="1" t="n">
+      <c r="P155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -8102,10 +8570,13 @@
         <v>0.0989</v>
       </c>
       <c r="N156" s="1" t="n">
+        <v>0.0982</v>
+      </c>
+      <c r="O156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="O156" s="1" t="n">
-        <v>0.0985</v>
+      <c r="P156" s="1" t="n">
+        <v>0.0982</v>
       </c>
     </row>
     <row r="157">
@@ -8151,10 +8622,13 @@
         <v>16.578</v>
       </c>
       <c r="N157" s="1" t="n">
+        <v>16.504</v>
+      </c>
+      <c r="O157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="O157" s="1" t="n">
-        <v>16.525</v>
+      <c r="P157" s="1" t="n">
+        <v>16.504</v>
       </c>
     </row>
     <row r="158">
@@ -8200,9 +8674,12 @@
         <v>0.05572</v>
       </c>
       <c r="N158" s="1" t="n">
+        <v>0.05537</v>
+      </c>
+      <c r="O158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="O158" s="1" t="n">
+      <c r="P158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -8249,10 +8726,13 @@
         <v>28.88</v>
       </c>
       <c r="N159" s="1" t="n">
+        <v>28.83</v>
+      </c>
+      <c r="O159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="O159" s="1" t="n">
-        <v>28.87</v>
+      <c r="P159" s="1" t="n">
+        <v>28.83</v>
       </c>
     </row>
     <row r="160">
@@ -8298,10 +8778,13 @@
         <v>0.02113</v>
       </c>
       <c r="N160" s="1" t="n">
+        <v>0.02103</v>
+      </c>
+      <c r="O160" s="1" t="n">
         <v>0.02141</v>
       </c>
-      <c r="O160" s="1" t="n">
-        <v>0.02107</v>
+      <c r="P160" s="1" t="n">
+        <v>0.02103</v>
       </c>
     </row>
     <row r="161">
@@ -8347,9 +8830,12 @@
         <v>0.0006555</v>
       </c>
       <c r="N161" s="1" t="n">
+        <v>0.0006535999999999999</v>
+      </c>
+      <c r="O161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="O161" s="1" t="n">
+      <c r="P161" s="1" t="n">
         <v>0.0006507</v>
       </c>
     </row>
@@ -8396,9 +8882,12 @@
         <v>0.3831</v>
       </c>
       <c r="N162" s="1" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="O162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="O162" s="1" t="n">
+      <c r="P162" s="1" t="n">
         <v>0.3808</v>
       </c>
     </row>
@@ -8445,10 +8934,13 @@
         <v>0.1924</v>
       </c>
       <c r="N163" s="1" t="n">
+        <v>0.1915</v>
+      </c>
+      <c r="O163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="O163" s="1" t="n">
-        <v>0.1922</v>
+      <c r="P163" s="1" t="n">
+        <v>0.1915</v>
       </c>
     </row>
     <row r="164">
@@ -8494,9 +8986,12 @@
         <v>0.317</v>
       </c>
       <c r="N164" s="1" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="O164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="O164" s="1" t="n">
+      <c r="P164" s="1" t="n">
         <v>0.315</v>
       </c>
     </row>
@@ -8543,9 +9038,12 @@
         <v>0.373</v>
       </c>
       <c r="N165" s="1" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="O165" s="1" t="n">
         <v>0.377</v>
       </c>
-      <c r="O165" s="1" t="n">
+      <c r="P165" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -8592,10 +9090,13 @@
         <v>0.02256</v>
       </c>
       <c r="N166" s="1" t="n">
+        <v>0.02238</v>
+      </c>
+      <c r="O166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="O166" s="1" t="n">
-        <v>0.02256</v>
+      <c r="P166" s="1" t="n">
+        <v>0.02238</v>
       </c>
     </row>
     <row r="167">
@@ -8641,10 +9142,13 @@
         <v>0.007291</v>
       </c>
       <c r="N167" s="1" t="n">
+        <v>0.007269</v>
+      </c>
+      <c r="O167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="O167" s="1" t="n">
-        <v>0.007284</v>
+      <c r="P167" s="1" t="n">
+        <v>0.007269</v>
       </c>
     </row>
     <row r="168">
@@ -8690,10 +9194,13 @@
         <v>0.01357</v>
       </c>
       <c r="N168" s="1" t="n">
+        <v>0.01344</v>
+      </c>
+      <c r="O168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="O168" s="1" t="n">
-        <v>0.01355</v>
+      <c r="P168" s="1" t="n">
+        <v>0.01344</v>
       </c>
     </row>
     <row r="169">
@@ -8739,9 +9246,12 @@
         <v>0.25348</v>
       </c>
       <c r="N169" s="1" t="n">
+        <v>0.25363</v>
+      </c>
+      <c r="O169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="O169" s="1" t="n">
+      <c r="P169" s="1" t="n">
         <v>0.25151</v>
       </c>
     </row>
@@ -8788,9 +9298,12 @@
         <v>0.02172</v>
       </c>
       <c r="N170" s="1" t="n">
+        <v>0.02159</v>
+      </c>
+      <c r="O170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="O170" s="1" t="n">
+      <c r="P170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -8837,9 +9350,12 @@
         <v>0.1711</v>
       </c>
       <c r="N171" s="1" t="n">
+        <v>0.1717</v>
+      </c>
+      <c r="O171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="O171" s="1" t="n">
+      <c r="P171" s="1" t="n">
         <v>0.1711</v>
       </c>
     </row>
@@ -8886,9 +9402,12 @@
         <v>0.089</v>
       </c>
       <c r="N172" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="O172" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="O172" s="1" t="n">
+      <c r="P172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -8935,10 +9454,13 @@
         <v>0.004679</v>
       </c>
       <c r="N173" s="1" t="n">
+        <v>0.004669</v>
+      </c>
+      <c r="O173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="O173" s="1" t="n">
-        <v>0.004676</v>
+      <c r="P173" s="1" t="n">
+        <v>0.004669</v>
       </c>
     </row>
     <row r="174">
@@ -8984,10 +9506,13 @@
         <v>0.4376</v>
       </c>
       <c r="N174" s="1" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="O174" s="1" t="n">
         <v>0.4423</v>
       </c>
-      <c r="O174" s="1" t="n">
-        <v>0.4364</v>
+      <c r="P174" s="1" t="n">
+        <v>0.4361</v>
       </c>
     </row>
     <row r="175">
@@ -9033,9 +9558,12 @@
         <v>0.09016</v>
       </c>
       <c r="N175" s="1" t="n">
+        <v>0.09019000000000001</v>
+      </c>
+      <c r="O175" s="1" t="n">
         <v>0.09042</v>
       </c>
-      <c r="O175" s="1" t="n">
+      <c r="P175" s="1" t="n">
         <v>0.08935999999999999</v>
       </c>
     </row>
@@ -9082,9 +9610,12 @@
         <v>0.2474</v>
       </c>
       <c r="N176" s="1" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="O176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="O176" s="1" t="n">
+      <c r="P176" s="1" t="n">
         <v>0.2453</v>
       </c>
     </row>
@@ -9131,9 +9662,12 @@
         <v>0.01922</v>
       </c>
       <c r="N177" s="1" t="n">
+        <v>0.01915</v>
+      </c>
+      <c r="O177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="O177" s="1" t="n">
+      <c r="P177" s="1" t="n">
         <v>0.01909</v>
       </c>
     </row>
@@ -9180,10 +9714,13 @@
         <v>6.149</v>
       </c>
       <c r="N178" s="1" t="n">
+        <v>6.122</v>
+      </c>
+      <c r="O178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="O178" s="1" t="n">
-        <v>6.138</v>
+      <c r="P178" s="1" t="n">
+        <v>6.122</v>
       </c>
     </row>
     <row r="179">
@@ -9229,10 +9766,13 @@
         <v>0.136</v>
       </c>
       <c r="N179" s="1" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="O179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="O179" s="1" t="n">
-        <v>0.136</v>
+      <c r="P179" s="1" t="n">
+        <v>0.135</v>
       </c>
     </row>
     <row r="180">
@@ -9278,9 +9818,12 @@
         <v>0.005062</v>
       </c>
       <c r="N180" s="1" t="n">
+        <v>0.005062</v>
+      </c>
+      <c r="O180" s="1" t="n">
         <v>0.005154</v>
       </c>
-      <c r="O180" s="1" t="n">
+      <c r="P180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -9327,9 +9870,12 @@
         <v>0.01197</v>
       </c>
       <c r="N181" s="1" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="O181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="O181" s="1" t="n">
+      <c r="P181" s="1" t="n">
         <v>0.01189</v>
       </c>
     </row>
@@ -9376,10 +9922,13 @@
         <v>0.007314</v>
       </c>
       <c r="N182" s="1" t="n">
+        <v>0.007224</v>
+      </c>
+      <c r="O182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="O182" s="1" t="n">
-        <v>0.007295</v>
+      <c r="P182" s="1" t="n">
+        <v>0.007224</v>
       </c>
     </row>
     <row r="183">
@@ -9425,9 +9974,12 @@
         <v>0.13152</v>
       </c>
       <c r="N183" s="1" t="n">
+        <v>0.13179</v>
+      </c>
+      <c r="O183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="O183" s="1" t="n">
+      <c r="P183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -9474,9 +10026,12 @@
         <v>0.09686</v>
       </c>
       <c r="N184" s="1" t="n">
+        <v>0.09604</v>
+      </c>
+      <c r="O184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="O184" s="1" t="n">
+      <c r="P184" s="1" t="n">
         <v>0.09587</v>
       </c>
     </row>
@@ -9523,10 +10078,13 @@
         <v>0.00757</v>
       </c>
       <c r="N185" s="1" t="n">
+        <v>0.00752</v>
+      </c>
+      <c r="O185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="O185" s="1" t="n">
-        <v>0.00753</v>
+      <c r="P185" s="1" t="n">
+        <v>0.00752</v>
       </c>
     </row>
     <row r="186">
@@ -9572,9 +10130,12 @@
         <v>0.04879</v>
       </c>
       <c r="N186" s="1" t="n">
+        <v>0.04861</v>
+      </c>
+      <c r="O186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="O186" s="1" t="n">
+      <c r="P186" s="1" t="n">
         <v>0.0486</v>
       </c>
     </row>
@@ -9621,10 +10182,13 @@
         <v>0.02677</v>
       </c>
       <c r="N187" s="1" t="n">
+        <v>0.02667</v>
+      </c>
+      <c r="O187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="O187" s="1" t="n">
-        <v>0.02674</v>
+      <c r="P187" s="1" t="n">
+        <v>0.02667</v>
       </c>
     </row>
     <row r="188">
@@ -9670,10 +10234,13 @@
         <v>0.003315</v>
       </c>
       <c r="N188" s="1" t="n">
+        <v>0.003302</v>
+      </c>
+      <c r="O188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="O188" s="1" t="n">
-        <v>0.003303</v>
+      <c r="P188" s="1" t="n">
+        <v>0.003302</v>
       </c>
     </row>
     <row r="189">
@@ -9719,10 +10286,13 @@
         <v>0.2862</v>
       </c>
       <c r="N189" s="1" t="n">
+        <v>0.2854</v>
+      </c>
+      <c r="O189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="O189" s="1" t="n">
-        <v>0.2859</v>
+      <c r="P189" s="1" t="n">
+        <v>0.2854</v>
       </c>
     </row>
     <row r="190">
@@ -9768,10 +10338,13 @@
         <v>0.01793</v>
       </c>
       <c r="N190" s="1" t="n">
+        <v>0.01785</v>
+      </c>
+      <c r="O190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="O190" s="1" t="n">
-        <v>0.0179</v>
+      <c r="P190" s="1" t="n">
+        <v>0.01785</v>
       </c>
     </row>
     <row r="191">
@@ -9817,10 +10390,13 @@
         <v>0.2584</v>
       </c>
       <c r="N191" s="1" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="O191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="O191" s="1" t="n">
-        <v>0.2574</v>
+      <c r="P191" s="1" t="n">
+        <v>0.257</v>
       </c>
     </row>
     <row r="192">
@@ -9866,9 +10442,12 @@
         <v>0.03791</v>
       </c>
       <c r="N192" s="1" t="n">
+        <v>0.03786</v>
+      </c>
+      <c r="O192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="O192" s="1" t="n">
+      <c r="P192" s="1" t="n">
         <v>0.03766</v>
       </c>
     </row>
@@ -9915,9 +10494,12 @@
         <v>0.0002237</v>
       </c>
       <c r="N193" s="1" t="n">
+        <v>0.000222</v>
+      </c>
+      <c r="O193" s="1" t="n">
         <v>0.0002243</v>
       </c>
-      <c r="O193" s="1" t="n">
+      <c r="P193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -9964,10 +10546,13 @@
         <v>4.101</v>
       </c>
       <c r="N194" s="1" t="n">
+        <v>4.066</v>
+      </c>
+      <c r="O194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="O194" s="1" t="n">
-        <v>4.091</v>
+      <c r="P194" s="1" t="n">
+        <v>4.066</v>
       </c>
     </row>
     <row r="195">
@@ -10013,9 +10598,12 @@
         <v>0.9994</v>
       </c>
       <c r="N195" s="1" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="O195" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="O195" s="1" t="n">
+      <c r="P195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -10062,9 +10650,12 @@
         <v>4.31</v>
       </c>
       <c r="N196" s="1" t="n">
+        <v>4.304</v>
+      </c>
+      <c r="O196" s="1" t="n">
         <v>4.347</v>
       </c>
-      <c r="O196" s="1" t="n">
+      <c r="P196" s="1" t="n">
         <v>4.276</v>
       </c>
     </row>
@@ -10111,9 +10702,12 @@
         <v>0.15143</v>
       </c>
       <c r="N197" s="1" t="n">
+        <v>0.15181</v>
+      </c>
+      <c r="O197" s="1" t="n">
         <v>0.15232</v>
       </c>
-      <c r="O197" s="1" t="n">
+      <c r="P197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -10160,9 +10754,12 @@
         <v>0.007704</v>
       </c>
       <c r="N198" s="1" t="n">
+        <v>0.007664</v>
+      </c>
+      <c r="O198" s="1" t="n">
         <v>0.007899</v>
       </c>
-      <c r="O198" s="1" t="n">
+      <c r="P198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -10209,9 +10806,12 @@
         <v>0.4493</v>
       </c>
       <c r="N199" s="1" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="O199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="O199" s="1" t="n">
+      <c r="P199" s="1" t="n">
         <v>0.4482</v>
       </c>
     </row>
@@ -10258,9 +10858,12 @@
         <v>0.5877</v>
       </c>
       <c r="N200" s="1" t="n">
+        <v>0.5824</v>
+      </c>
+      <c r="O200" s="1" t="n">
         <v>0.5911999999999999</v>
       </c>
-      <c r="O200" s="1" t="n">
+      <c r="P200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -10307,10 +10910,13 @@
         <v>0.0931</v>
       </c>
       <c r="N201" s="1" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="O201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="O201" s="1" t="n">
-        <v>0.0931</v>
+      <c r="P201" s="1" t="n">
+        <v>0.09279999999999999</v>
       </c>
     </row>
     <row r="202">
@@ -10356,10 +10962,13 @@
         <v>0.06025</v>
       </c>
       <c r="N202" s="1" t="n">
+        <v>0.06001</v>
+      </c>
+      <c r="O202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="O202" s="1" t="n">
-        <v>0.06025</v>
+      <c r="P202" s="1" t="n">
+        <v>0.06001</v>
       </c>
     </row>
     <row r="203">
@@ -10405,9 +11014,12 @@
         <v>0.008500000000000001</v>
       </c>
       <c r="N203" s="1" t="n">
+        <v>0.008200000000000001</v>
+      </c>
+      <c r="O203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="O203" s="1" t="n">
+      <c r="P203" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -10454,10 +11066,13 @@
         <v>0.00418</v>
       </c>
       <c r="N204" s="1" t="n">
+        <v>0.00417</v>
+      </c>
+      <c r="O204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="O204" s="1" t="n">
-        <v>0.00418</v>
+      <c r="P204" s="1" t="n">
+        <v>0.00417</v>
       </c>
     </row>
     <row r="205">
@@ -10503,9 +11118,12 @@
         <v>0.009128000000000001</v>
       </c>
       <c r="N205" s="1" t="n">
+        <v>0.009127</v>
+      </c>
+      <c r="O205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="O205" s="1" t="n">
+      <c r="P205" s="1" t="n">
         <v>0.009070999999999999</v>
       </c>
     </row>
@@ -10552,9 +11170,12 @@
         <v>0.2395</v>
       </c>
       <c r="N206" s="1" t="n">
+        <v>0.2397</v>
+      </c>
+      <c r="O206" s="1" t="n">
         <v>0.2418</v>
       </c>
-      <c r="O206" s="1" t="n">
+      <c r="P206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -10601,9 +11222,12 @@
         <v>0.02065</v>
       </c>
       <c r="N207" s="1" t="n">
+        <v>0.0206</v>
+      </c>
+      <c r="O207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="O207" s="1" t="n">
+      <c r="P207" s="1" t="n">
         <v>0.02053</v>
       </c>
     </row>
@@ -10650,9 +11274,12 @@
         <v>0.2373</v>
       </c>
       <c r="N208" s="1" t="n">
+        <v>0.2366</v>
+      </c>
+      <c r="O208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="O208" s="1" t="n">
+      <c r="P208" s="1" t="n">
         <v>0.2364</v>
       </c>
     </row>
@@ -10699,9 +11326,12 @@
         <v>0.3601</v>
       </c>
       <c r="N209" s="1" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="O209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="O209" s="1" t="n">
+      <c r="P209" s="1" t="n">
         <v>0.3586</v>
       </c>
     </row>
@@ -10748,10 +11378,13 @@
         <v>0.04253</v>
       </c>
       <c r="N210" s="1" t="n">
+        <v>0.04232</v>
+      </c>
+      <c r="O210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="O210" s="1" t="n">
-        <v>0.04236</v>
+      <c r="P210" s="1" t="n">
+        <v>0.04232</v>
       </c>
     </row>
     <row r="211">
@@ -10797,9 +11430,12 @@
         <v>0.0004285</v>
       </c>
       <c r="N211" s="1" t="n">
+        <v>0.0004268</v>
+      </c>
+      <c r="O211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="O211" s="1" t="n">
+      <c r="P211" s="1" t="n">
         <v>0.0004256</v>
       </c>
     </row>
@@ -10846,10 +11482,13 @@
         <v>0.02148</v>
       </c>
       <c r="N212" s="1" t="n">
+        <v>0.02136</v>
+      </c>
+      <c r="O212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="O212" s="1" t="n">
-        <v>0.02148</v>
+      <c r="P212" s="1" t="n">
+        <v>0.02136</v>
       </c>
     </row>
     <row r="213">
@@ -10895,9 +11534,12 @@
         <v>0.1145</v>
       </c>
       <c r="N213" s="1" t="n">
+        <v>0.1142</v>
+      </c>
+      <c r="O213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="O213" s="1" t="n">
+      <c r="P213" s="1" t="n">
         <v>0.1137</v>
       </c>
     </row>
@@ -10944,9 +11586,12 @@
         <v>0.0419</v>
       </c>
       <c r="N214" s="1" t="n">
+        <v>0.04174</v>
+      </c>
+      <c r="O214" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="O214" s="1" t="n">
+      <c r="P214" s="1" t="n">
         <v>0.04174</v>
       </c>
     </row>
@@ -10993,10 +11638,13 @@
         <v>0.009875999999999999</v>
       </c>
       <c r="N215" s="1" t="n">
+        <v>0.009841000000000001</v>
+      </c>
+      <c r="O215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="O215" s="1" t="n">
-        <v>0.009875999999999999</v>
+      <c r="P215" s="1" t="n">
+        <v>0.009841000000000001</v>
       </c>
     </row>
     <row r="216">
@@ -11042,9 +11690,12 @@
         <v>0.0641</v>
       </c>
       <c r="N216" s="1" t="n">
+        <v>0.0639</v>
+      </c>
+      <c r="O216" s="1" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="O216" s="1" t="n">
+      <c r="P216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -11091,9 +11742,12 @@
         <v>0.004266</v>
       </c>
       <c r="N217" s="1" t="n">
+        <v>0.004225</v>
+      </c>
+      <c r="O217" s="1" t="n">
         <v>0.004266</v>
       </c>
-      <c r="O217" s="1" t="n">
+      <c r="P217" s="1" t="n">
         <v>0.004177</v>
       </c>
     </row>
@@ -11140,9 +11794,12 @@
         <v>0.01005</v>
       </c>
       <c r="N218" s="1" t="n">
+        <v>0.00996</v>
+      </c>
+      <c r="O218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="O218" s="1" t="n">
+      <c r="P218" s="1" t="n">
         <v>0.009820000000000001</v>
       </c>
     </row>
@@ -11189,10 +11846,13 @@
         <v>0.0297</v>
       </c>
       <c r="N219" s="1" t="n">
+        <v>0.02941</v>
+      </c>
+      <c r="O219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="O219" s="1" t="n">
-        <v>0.02958</v>
+      <c r="P219" s="1" t="n">
+        <v>0.02941</v>
       </c>
     </row>
     <row r="220">
@@ -11238,10 +11898,13 @@
         <v>2.298</v>
       </c>
       <c r="N220" s="1" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="O220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="O220" s="1" t="n">
-        <v>2.291</v>
+      <c r="P220" s="1" t="n">
+        <v>2.29</v>
       </c>
     </row>
     <row r="221">
@@ -11287,10 +11950,13 @@
         <v>0.022819</v>
       </c>
       <c r="N221" s="1" t="n">
+        <v>0.022737</v>
+      </c>
+      <c r="O221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="O221" s="1" t="n">
-        <v>0.022819</v>
+      <c r="P221" s="1" t="n">
+        <v>0.022737</v>
       </c>
     </row>
     <row r="222">
@@ -11336,9 +12002,12 @@
         <v>0.0371</v>
       </c>
       <c r="N222" s="1" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="O222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="O222" s="1" t="n">
+      <c r="P222" s="1" t="n">
         <v>0.0369</v>
       </c>
     </row>
@@ -11385,9 +12054,12 @@
         <v>0.2929</v>
       </c>
       <c r="N223" s="1" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="O223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="O223" s="1" t="n">
+      <c r="P223" s="1" t="n">
         <v>0.2918</v>
       </c>
     </row>
@@ -11434,9 +12106,12 @@
         <v>0.01565</v>
       </c>
       <c r="N224" s="1" t="n">
+        <v>0.01554</v>
+      </c>
+      <c r="O224" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="O224" s="1" t="n">
+      <c r="P224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -11483,10 +12158,13 @@
         <v>0.0004076</v>
       </c>
       <c r="N225" s="1" t="n">
+        <v>0.0004061</v>
+      </c>
+      <c r="O225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="O225" s="1" t="n">
-        <v>0.0004069</v>
+      <c r="P225" s="1" t="n">
+        <v>0.0004061</v>
       </c>
     </row>
     <row r="226">
@@ -11532,9 +12210,12 @@
         <v>0.08659</v>
       </c>
       <c r="N226" s="1" t="n">
+        <v>0.08656</v>
+      </c>
+      <c r="O226" s="1" t="n">
         <v>0.08815000000000001</v>
       </c>
-      <c r="O226" s="1" t="n">
+      <c r="P226" s="1" t="n">
         <v>0.08623</v>
       </c>
     </row>
@@ -11581,9 +12262,12 @@
         <v>0.95</v>
       </c>
       <c r="N227" s="1" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="O227" s="1" t="n">
         <v>0.959</v>
       </c>
-      <c r="O227" s="1" t="n">
+      <c r="P227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -11630,10 +12314,13 @@
         <v>0.05534</v>
       </c>
       <c r="N228" s="1" t="n">
+        <v>0.05523</v>
+      </c>
+      <c r="O228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="O228" s="1" t="n">
-        <v>0.05534</v>
+      <c r="P228" s="1" t="n">
+        <v>0.05523</v>
       </c>
     </row>
     <row r="229">
@@ -11679,10 +12366,13 @@
         <v>0.002008</v>
       </c>
       <c r="N229" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="O229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="O229" s="1" t="n">
-        <v>0.002003</v>
+      <c r="P229" s="1" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="230">
@@ -11728,9 +12418,12 @@
         <v>0.022782</v>
       </c>
       <c r="N230" s="1" t="n">
+        <v>0.022778</v>
+      </c>
+      <c r="O230" s="1" t="n">
         <v>0.023101</v>
       </c>
-      <c r="O230" s="1" t="n">
+      <c r="P230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -11777,9 +12470,12 @@
         <v>0.05373</v>
       </c>
       <c r="N231" s="1" t="n">
+        <v>0.0535</v>
+      </c>
+      <c r="O231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="O231" s="1" t="n">
+      <c r="P231" s="1" t="n">
         <v>0.0535</v>
       </c>
     </row>
@@ -11826,9 +12522,12 @@
         <v>0.0588</v>
       </c>
       <c r="N232" s="1" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="O232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="O232" s="1" t="n">
+      <c r="P232" s="1" t="n">
         <v>0.0587</v>
       </c>
     </row>
@@ -11875,10 +12574,13 @@
         <v>0.001684</v>
       </c>
       <c r="N233" s="1" t="n">
+        <v>0.001676</v>
+      </c>
+      <c r="O233" s="1" t="n">
         <v>0.001701</v>
       </c>
-      <c r="O233" s="1" t="n">
-        <v>0.001678</v>
+      <c r="P233" s="1" t="n">
+        <v>0.001676</v>
       </c>
     </row>
     <row r="234">
@@ -11924,9 +12626,12 @@
         <v>0.00576</v>
       </c>
       <c r="N234" s="1" t="n">
+        <v>0.005738</v>
+      </c>
+      <c r="O234" s="1" t="n">
         <v>0.005854</v>
       </c>
-      <c r="O234" s="1" t="n">
+      <c r="P234" s="1" t="n">
         <v>0.005728</v>
       </c>
     </row>
@@ -11973,10 +12678,13 @@
         <v>0.12437</v>
       </c>
       <c r="N235" s="1" t="n">
+        <v>0.12365</v>
+      </c>
+      <c r="O235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="O235" s="1" t="n">
-        <v>0.12437</v>
+      <c r="P235" s="1" t="n">
+        <v>0.12365</v>
       </c>
     </row>
     <row r="236">
@@ -12022,10 +12730,13 @@
         <v>64.5</v>
       </c>
       <c r="N236" s="1" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="O236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="O236" s="1" t="n">
-        <v>64.5</v>
+      <c r="P236" s="1" t="n">
+        <v>64.25</v>
       </c>
     </row>
     <row r="237">
@@ -12071,10 +12782,13 @@
         <v>0.1015</v>
       </c>
       <c r="N237" s="1" t="n">
+        <v>0.1014</v>
+      </c>
+      <c r="O237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="O237" s="1" t="n">
-        <v>0.1015</v>
+      <c r="P237" s="1" t="n">
+        <v>0.1014</v>
       </c>
     </row>
     <row r="238">
@@ -12120,9 +12834,12 @@
         <v>0.004053</v>
       </c>
       <c r="N238" s="1" t="n">
-        <v>0.004053</v>
+        <v>0.004063</v>
       </c>
       <c r="O238" s="1" t="n">
+        <v>0.004063</v>
+      </c>
+      <c r="P238" s="1" t="n">
         <v>0.003925</v>
       </c>
     </row>
@@ -12169,9 +12886,12 @@
         <v>0.01554</v>
       </c>
       <c r="N239" s="1" t="n">
+        <v>0.01538</v>
+      </c>
+      <c r="O239" s="1" t="n">
         <v>0.01562</v>
       </c>
-      <c r="O239" s="1" t="n">
+      <c r="P239" s="1" t="n">
         <v>0.01532</v>
       </c>
     </row>
@@ -12218,10 +12938,13 @@
         <v>0.05605</v>
       </c>
       <c r="N240" s="1" t="n">
+        <v>0.05594</v>
+      </c>
+      <c r="O240" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="O240" s="1" t="n">
-        <v>0.05598</v>
+      <c r="P240" s="1" t="n">
+        <v>0.05594</v>
       </c>
     </row>
     <row r="241">
@@ -12267,9 +12990,12 @@
         <v>0.0113</v>
       </c>
       <c r="N241" s="1" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="O241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="O241" s="1" t="n">
+      <c r="P241" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -12316,10 +13042,13 @@
         <v>0.3333</v>
       </c>
       <c r="N242" s="1" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="O242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="O242" s="1" t="n">
-        <v>0.3333</v>
+      <c r="P242" s="1" t="n">
+        <v>0.3332</v>
       </c>
     </row>
     <row r="243">
@@ -12365,10 +13094,13 @@
         <v>0.01228</v>
       </c>
       <c r="N243" s="1" t="n">
+        <v>0.01223</v>
+      </c>
+      <c r="O243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="O243" s="1" t="n">
-        <v>0.01227</v>
+      <c r="P243" s="1" t="n">
+        <v>0.01223</v>
       </c>
     </row>
     <row r="244">
@@ -12414,9 +13146,12 @@
         <v>0.08121</v>
       </c>
       <c r="N244" s="1" t="n">
+        <v>0.08116</v>
+      </c>
+      <c r="O244" s="1" t="n">
         <v>0.08121</v>
       </c>
-      <c r="O244" s="1" t="n">
+      <c r="P244" s="1" t="n">
         <v>0.07997</v>
       </c>
     </row>
@@ -12463,9 +13198,12 @@
         <v>0.007835</v>
       </c>
       <c r="N245" s="1" t="n">
+        <v>0.007777</v>
+      </c>
+      <c r="O245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="O245" s="1" t="n">
+      <c r="P245" s="1" t="n">
         <v>0.007769</v>
       </c>
     </row>
@@ -12512,9 +13250,12 @@
         <v>0.03036</v>
       </c>
       <c r="N246" s="1" t="n">
+        <v>0.03025</v>
+      </c>
+      <c r="O246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="O246" s="1" t="n">
+      <c r="P246" s="1" t="n">
         <v>0.03025</v>
       </c>
     </row>
@@ -12561,9 +13302,12 @@
         <v>0.1807</v>
       </c>
       <c r="N247" s="1" t="n">
+        <v>0.1802</v>
+      </c>
+      <c r="O247" s="1" t="n">
         <v>0.1827</v>
       </c>
-      <c r="O247" s="1" t="n">
+      <c r="P247" s="1" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -12610,10 +13354,13 @@
         <v>0.05876</v>
       </c>
       <c r="N248" s="1" t="n">
+        <v>0.05867</v>
+      </c>
+      <c r="O248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="O248" s="1" t="n">
-        <v>0.05875</v>
+      <c r="P248" s="1" t="n">
+        <v>0.05867</v>
       </c>
     </row>
     <row r="249">
@@ -12659,10 +13406,13 @@
         <v>0.166</v>
       </c>
       <c r="N249" s="1" t="n">
+        <v>0.1656</v>
+      </c>
+      <c r="O249" s="1" t="n">
         <v>0.1684</v>
       </c>
-      <c r="O249" s="1" t="n">
-        <v>0.166</v>
+      <c r="P249" s="1" t="n">
+        <v>0.1656</v>
       </c>
     </row>
     <row r="250">
@@ -12708,10 +13458,13 @@
         <v>0.01916</v>
       </c>
       <c r="N250" s="1" t="n">
+        <v>0.01904</v>
+      </c>
+      <c r="O250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="O250" s="1" t="n">
-        <v>0.01906</v>
+      <c r="P250" s="1" t="n">
+        <v>0.01904</v>
       </c>
     </row>
     <row r="251">
@@ -12757,9 +13510,12 @@
         <v>0.02317</v>
       </c>
       <c r="N251" s="1" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="O251" s="1" t="n">
         <v>0.02322</v>
       </c>
-      <c r="O251" s="1" t="n">
+      <c r="P251" s="1" t="n">
         <v>0.02295</v>
       </c>
     </row>
@@ -12806,9 +13562,12 @@
         <v>0.30622</v>
       </c>
       <c r="N252" s="1" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="O252" s="1" t="n">
         <v>0.31227</v>
       </c>
-      <c r="O252" s="1" t="n">
+      <c r="P252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -12855,9 +13614,12 @@
         <v>0.006013</v>
       </c>
       <c r="N253" s="1" t="n">
+        <v>0.005992</v>
+      </c>
+      <c r="O253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="O253" s="1" t="n">
+      <c r="P253" s="1" t="n">
         <v>0.005971</v>
       </c>
     </row>
@@ -12904,9 +13666,12 @@
         <v>0.6139</v>
       </c>
       <c r="N254" s="1" t="n">
+        <v>0.6123</v>
+      </c>
+      <c r="O254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="O254" s="1" t="n">
+      <c r="P254" s="1" t="n">
         <v>0.6116</v>
       </c>
     </row>
@@ -12953,10 +13718,13 @@
         <v>0.10635</v>
       </c>
       <c r="N255" s="1" t="n">
+        <v>0.10601</v>
+      </c>
+      <c r="O255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="O255" s="1" t="n">
-        <v>0.10612</v>
+      <c r="P255" s="1" t="n">
+        <v>0.10601</v>
       </c>
     </row>
     <row r="256">
@@ -13002,9 +13770,12 @@
         <v>0.0912</v>
       </c>
       <c r="N256" s="1" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="O256" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="O256" s="1" t="n">
+      <c r="P256" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -13051,9 +13822,12 @@
         <v>0.01444</v>
       </c>
       <c r="N257" s="1" t="n">
+        <v>0.01451</v>
+      </c>
+      <c r="O257" s="1" t="n">
         <v>0.01468</v>
       </c>
-      <c r="O257" s="1" t="n">
+      <c r="P257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -13100,10 +13874,13 @@
         <v>0.05025</v>
       </c>
       <c r="N258" s="1" t="n">
+        <v>0.05013</v>
+      </c>
+      <c r="O258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="O258" s="1" t="n">
-        <v>0.05025</v>
+      <c r="P258" s="1" t="n">
+        <v>0.05013</v>
       </c>
     </row>
     <row r="259">
@@ -13149,10 +13926,13 @@
         <v>0.0081</v>
       </c>
       <c r="N259" s="1" t="n">
+        <v>0.008070000000000001</v>
+      </c>
+      <c r="O259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="O259" s="1" t="n">
-        <v>0.00809</v>
+      <c r="P259" s="1" t="n">
+        <v>0.008070000000000001</v>
       </c>
     </row>
     <row r="260">
@@ -13198,9 +13978,12 @@
         <v>0.19</v>
       </c>
       <c r="N260" s="1" t="n">
+        <v>0.1898</v>
+      </c>
+      <c r="O260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="O260" s="1" t="n">
+      <c r="P260" s="1" t="n">
         <v>0.1894</v>
       </c>
     </row>
@@ -13247,10 +14030,13 @@
         <v>0.0983</v>
       </c>
       <c r="N261" s="1" t="n">
+        <v>0.0979</v>
+      </c>
+      <c r="O261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="O261" s="1" t="n">
-        <v>0.09810000000000001</v>
+      <c r="P261" s="1" t="n">
+        <v>0.0979</v>
       </c>
     </row>
     <row r="262">
@@ -13296,10 +14082,13 @@
         <v>0.2116</v>
       </c>
       <c r="N262" s="1" t="n">
+        <v>0.2107</v>
+      </c>
+      <c r="O262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="O262" s="1" t="n">
-        <v>0.2113</v>
+      <c r="P262" s="1" t="n">
+        <v>0.2107</v>
       </c>
     </row>
     <row r="263">
@@ -13345,9 +14134,12 @@
         <v>0.008503999999999999</v>
       </c>
       <c r="N263" s="1" t="n">
+        <v>0.008529999999999999</v>
+      </c>
+      <c r="O263" s="1" t="n">
         <v>0.008560999999999999</v>
       </c>
-      <c r="O263" s="1" t="n">
+      <c r="P263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -13394,10 +14186,13 @@
         <v>2.637</v>
       </c>
       <c r="N264" s="1" t="n">
+        <v>2.629</v>
+      </c>
+      <c r="O264" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="O264" s="1" t="n">
-        <v>2.632</v>
+      <c r="P264" s="1" t="n">
+        <v>2.629</v>
       </c>
     </row>
     <row r="265">
@@ -13443,9 +14238,12 @@
         <v>0.0188</v>
       </c>
       <c r="N265" s="1" t="n">
+        <v>0.01869</v>
+      </c>
+      <c r="O265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="O265" s="1" t="n">
+      <c r="P265" s="1" t="n">
         <v>0.01847</v>
       </c>
     </row>
@@ -13492,9 +14290,12 @@
         <v>0.3594</v>
       </c>
       <c r="N266" s="1" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="O266" s="1" t="n">
         <v>0.3607</v>
       </c>
-      <c r="O266" s="1" t="n">
+      <c r="P266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -13541,10 +14342,13 @@
         <v>0.03427</v>
       </c>
       <c r="N267" s="1" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="O267" s="1" t="n">
         <v>0.03464</v>
       </c>
-      <c r="O267" s="1" t="n">
-        <v>0.03408</v>
+      <c r="P267" s="1" t="n">
+        <v>0.034</v>
       </c>
     </row>
     <row r="268">
@@ -13590,9 +14394,12 @@
         <v>0.117</v>
       </c>
       <c r="N268" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="O268" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="O268" s="1" t="n">
+      <c r="P268" s="1" t="n">
         <v>0.117</v>
       </c>
     </row>
@@ -13639,9 +14446,12 @@
         <v>0.08024000000000001</v>
       </c>
       <c r="N269" s="1" t="n">
+        <v>0.07997</v>
+      </c>
+      <c r="O269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="O269" s="1" t="n">
+      <c r="P269" s="1" t="n">
         <v>0.07973</v>
       </c>
     </row>
@@ -13688,10 +14498,13 @@
         <v>0.01384</v>
       </c>
       <c r="N270" s="1" t="n">
+        <v>0.0138</v>
+      </c>
+      <c r="O270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="O270" s="1" t="n">
-        <v>0.01382</v>
+      <c r="P270" s="1" t="n">
+        <v>0.0138</v>
       </c>
     </row>
     <row r="271">
@@ -13737,10 +14550,13 @@
         <v>0.007578</v>
       </c>
       <c r="N271" s="1" t="n">
+        <v>0.007538</v>
+      </c>
+      <c r="O271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="O271" s="1" t="n">
-        <v>0.007558</v>
+      <c r="P271" s="1" t="n">
+        <v>0.007538</v>
       </c>
     </row>
     <row r="272">
@@ -13786,10 +14602,13 @@
         <v>0.0742</v>
       </c>
       <c r="N272" s="1" t="n">
+        <v>0.07405</v>
+      </c>
+      <c r="O272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="O272" s="1" t="n">
-        <v>0.0741</v>
+      <c r="P272" s="1" t="n">
+        <v>0.07405</v>
       </c>
     </row>
     <row r="273">
@@ -13835,9 +14654,12 @@
         <v>3.15e-05</v>
       </c>
       <c r="N273" s="1" t="n">
+        <v>3.14e-05</v>
+      </c>
+      <c r="O273" s="1" t="n">
         <v>3.16e-05</v>
       </c>
-      <c r="O273" s="1" t="n">
+      <c r="P273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -13884,10 +14706,13 @@
         <v>0.005445</v>
       </c>
       <c r="N274" s="1" t="n">
+        <v>0.005434</v>
+      </c>
+      <c r="O274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="O274" s="1" t="n">
-        <v>0.005445</v>
+      <c r="P274" s="1" t="n">
+        <v>0.005434</v>
       </c>
     </row>
     <row r="275">
@@ -13933,9 +14758,12 @@
         <v>0.1816</v>
       </c>
       <c r="N275" s="1" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="O275" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="O275" s="1" t="n">
+      <c r="P275" s="1" t="n">
         <v>0.1802</v>
       </c>
     </row>
@@ -13982,10 +14810,13 @@
         <v>0.006836</v>
       </c>
       <c r="N276" s="1" t="n">
+        <v>0.00682</v>
+      </c>
+      <c r="O276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="O276" s="1" t="n">
-        <v>0.006827</v>
+      <c r="P276" s="1" t="n">
+        <v>0.00682</v>
       </c>
     </row>
     <row r="277">
@@ -14031,9 +14862,12 @@
         <v>0.1309</v>
       </c>
       <c r="N277" s="1" t="n">
+        <v>0.1303</v>
+      </c>
+      <c r="O277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="O277" s="1" t="n">
+      <c r="P277" s="1" t="n">
         <v>0.1303</v>
       </c>
     </row>
@@ -14080,9 +14914,12 @@
         <v>0.02332</v>
       </c>
       <c r="N278" s="1" t="n">
+        <v>0.02317</v>
+      </c>
+      <c r="O278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="O278" s="1" t="n">
+      <c r="P278" s="1" t="n">
         <v>0.02308</v>
       </c>
     </row>
@@ -14129,9 +14966,12 @@
         <v>0.01823</v>
       </c>
       <c r="N279" s="1" t="n">
-        <v>0.01827</v>
+        <v>0.01837</v>
       </c>
       <c r="O279" s="1" t="n">
+        <v>0.01837</v>
+      </c>
+      <c r="P279" s="1" t="n">
         <v>0.01812</v>
       </c>
     </row>
@@ -14178,10 +15018,13 @@
         <v>0.03717</v>
       </c>
       <c r="N280" s="1" t="n">
+        <v>0.03697</v>
+      </c>
+      <c r="O280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="O280" s="1" t="n">
-        <v>0.03704</v>
+      <c r="P280" s="1" t="n">
+        <v>0.03697</v>
       </c>
     </row>
     <row r="281">
@@ -14227,9 +15070,12 @@
         <v>0.03985</v>
       </c>
       <c r="N281" s="1" t="n">
+        <v>0.03976</v>
+      </c>
+      <c r="O281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="O281" s="1" t="n">
+      <c r="P281" s="1" t="n">
         <v>0.03953</v>
       </c>
     </row>
@@ -14276,9 +15122,12 @@
         <v>0.3017</v>
       </c>
       <c r="N282" s="1" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="O282" s="1" t="n">
         <v>0.3059</v>
       </c>
-      <c r="O282" s="1" t="n">
+      <c r="P282" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -14325,9 +15174,12 @@
         <v>0.01122</v>
       </c>
       <c r="N283" s="1" t="n">
+        <v>0.01119</v>
+      </c>
+      <c r="O283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="O283" s="1" t="n">
+      <c r="P283" s="1" t="n">
         <v>0.01119</v>
       </c>
     </row>
@@ -14374,9 +15226,12 @@
         <v>9.799999999999999e-06</v>
       </c>
       <c r="N284" s="1" t="n">
+        <v>9.6e-06</v>
+      </c>
+      <c r="O284" s="1" t="n">
         <v>9.799999999999999e-06</v>
       </c>
-      <c r="O284" s="1" t="n">
+      <c r="P284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -14423,9 +15278,12 @@
         <v>0.1147</v>
       </c>
       <c r="N285" s="1" t="n">
+        <v>0.1145</v>
+      </c>
+      <c r="O285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="O285" s="1" t="n">
+      <c r="P285" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -14472,9 +15330,12 @@
         <v>0.003439</v>
       </c>
       <c r="N286" s="1" t="n">
+        <v>0.003432</v>
+      </c>
+      <c r="O286" s="1" t="n">
         <v>0.003485</v>
       </c>
-      <c r="O286" s="1" t="n">
+      <c r="P286" s="1" t="n">
         <v>0.003422</v>
       </c>
     </row>
@@ -14521,9 +15382,12 @@
         <v>0.08512</v>
       </c>
       <c r="N287" s="1" t="n">
+        <v>0.08499</v>
+      </c>
+      <c r="O287" s="1" t="n">
         <v>0.08577</v>
       </c>
-      <c r="O287" s="1" t="n">
+      <c r="P287" s="1" t="n">
         <v>0.08486</v>
       </c>
     </row>
@@ -14570,9 +15434,12 @@
         <v>0.10055</v>
       </c>
       <c r="N288" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O288" s="1" t="n">
         <v>0.10076</v>
       </c>
-      <c r="O288" s="1" t="n">
+      <c r="P288" s="1" t="n">
         <v>0.09869</v>
       </c>
     </row>
@@ -14619,9 +15486,12 @@
         <v>0.4337</v>
       </c>
       <c r="N289" s="1" t="n">
-        <v>0.4359</v>
+        <v>0.4367</v>
       </c>
       <c r="O289" s="1" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="P289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -14668,9 +15538,12 @@
         <v>0.03898</v>
       </c>
       <c r="N290" s="1" t="n">
+        <v>0.03929</v>
+      </c>
+      <c r="O290" s="1" t="n">
         <v>0.03966</v>
       </c>
-      <c r="O290" s="1" t="n">
+      <c r="P290" s="1" t="n">
         <v>0.03878</v>
       </c>
     </row>
@@ -14717,10 +15590,13 @@
         <v>0.2373</v>
       </c>
       <c r="N291" s="1" t="n">
+        <v>0.2357</v>
+      </c>
+      <c r="O291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="O291" s="1" t="n">
-        <v>0.2373</v>
+      <c r="P291" s="1" t="n">
+        <v>0.2357</v>
       </c>
     </row>
     <row r="292">
@@ -14766,9 +15642,12 @@
         <v>0.28126</v>
       </c>
       <c r="N292" s="1" t="n">
+        <v>0.28237</v>
+      </c>
+      <c r="O292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="O292" s="1" t="n">
+      <c r="P292" s="1" t="n">
         <v>0.28126</v>
       </c>
     </row>
@@ -14815,9 +15694,12 @@
         <v>0.15</v>
       </c>
       <c r="N293" s="1" t="n">
+        <v>0.1496</v>
+      </c>
+      <c r="O293" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="O293" s="1" t="n">
+      <c r="P293" s="1" t="n">
         <v>0.1489</v>
       </c>
     </row>
@@ -14864,10 +15746,13 @@
         <v>4.203</v>
       </c>
       <c r="N294" s="1" t="n">
+        <v>4.182</v>
+      </c>
+      <c r="O294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="O294" s="1" t="n">
-        <v>4.203</v>
+      <c r="P294" s="1" t="n">
+        <v>4.182</v>
       </c>
     </row>
     <row r="295">
@@ -14913,9 +15798,12 @@
         <v>0.03341</v>
       </c>
       <c r="N295" s="1" t="n">
-        <v>0.03341</v>
+        <v>0.0338</v>
       </c>
       <c r="O295" s="1" t="n">
+        <v>0.0338</v>
+      </c>
+      <c r="P295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -14962,9 +15850,12 @@
         <v>0.000972</v>
       </c>
       <c r="N296" s="1" t="n">
+        <v>0.000969</v>
+      </c>
+      <c r="O296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="O296" s="1" t="n">
+      <c r="P296" s="1" t="n">
         <v>0.000965</v>
       </c>
     </row>
@@ -15011,9 +15902,12 @@
         <v>0.08176</v>
       </c>
       <c r="N297" s="1" t="n">
+        <v>0.08155</v>
+      </c>
+      <c r="O297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="O297" s="1" t="n">
+      <c r="P297" s="1" t="n">
         <v>0.08154</v>
       </c>
     </row>
@@ -15060,9 +15954,12 @@
         <v>0.05845</v>
       </c>
       <c r="N298" s="1" t="n">
+        <v>0.05807</v>
+      </c>
+      <c r="O298" s="1" t="n">
         <v>0.05845</v>
       </c>
-      <c r="O298" s="1" t="n">
+      <c r="P298" s="1" t="n">
         <v>0.05745</v>
       </c>
     </row>
@@ -15109,10 +16006,13 @@
         <v>0.09096</v>
       </c>
       <c r="N299" s="1" t="n">
+        <v>0.0906</v>
+      </c>
+      <c r="O299" s="1" t="n">
         <v>0.0917</v>
       </c>
-      <c r="O299" s="1" t="n">
-        <v>0.09066</v>
+      <c r="P299" s="1" t="n">
+        <v>0.0906</v>
       </c>
     </row>
     <row r="300">
@@ -15158,10 +16058,13 @@
         <v>0.02744</v>
       </c>
       <c r="N300" s="1" t="n">
+        <v>0.02734</v>
+      </c>
+      <c r="O300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="O300" s="1" t="n">
-        <v>0.0274</v>
+      <c r="P300" s="1" t="n">
+        <v>0.02734</v>
       </c>
     </row>
     <row r="301">
@@ -15207,10 +16110,13 @@
         <v>0.06568</v>
       </c>
       <c r="N301" s="1" t="n">
+        <v>0.0654</v>
+      </c>
+      <c r="O301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="O301" s="1" t="n">
-        <v>0.06557</v>
+      <c r="P301" s="1" t="n">
+        <v>0.0654</v>
       </c>
     </row>
     <row r="302">
@@ -15256,9 +16162,12 @@
         <v>0.053585</v>
       </c>
       <c r="N302" s="1" t="n">
+        <v>0.053535</v>
+      </c>
+      <c r="O302" s="1" t="n">
         <v>0.053585</v>
       </c>
-      <c r="O302" s="1" t="n">
+      <c r="P302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -15305,9 +16214,12 @@
         <v>5170</v>
       </c>
       <c r="N303" s="1" t="n">
+        <v>5166.4</v>
+      </c>
+      <c r="O303" s="1" t="n">
         <v>5177.6</v>
       </c>
-      <c r="O303" s="1" t="n">
+      <c r="P303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -15354,10 +16266,13 @@
         <v>14.9</v>
       </c>
       <c r="N304" s="1" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="O304" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="O304" s="1" t="n">
-        <v>14.88</v>
+      <c r="P304" s="1" t="n">
+        <v>14.85</v>
       </c>
     </row>
     <row r="305">
@@ -15403,9 +16318,12 @@
         <v>0.003713</v>
       </c>
       <c r="N305" s="1" t="n">
+        <v>0.003706</v>
+      </c>
+      <c r="O305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="O305" s="1" t="n">
+      <c r="P305" s="1" t="n">
         <v>0.003695</v>
       </c>
     </row>
@@ -15452,10 +16370,13 @@
         <v>0.456</v>
       </c>
       <c r="N306" s="1" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="O306" s="1" t="n">
         <v>0.4608</v>
       </c>
-      <c r="O306" s="1" t="n">
-        <v>0.4558</v>
+      <c r="P306" s="1" t="n">
+        <v>0.4531</v>
       </c>
     </row>
     <row r="307">
@@ -15501,10 +16422,13 @@
         <v>0.04682</v>
       </c>
       <c r="N307" s="1" t="n">
+        <v>0.04666</v>
+      </c>
+      <c r="O307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="O307" s="1" t="n">
-        <v>0.04682</v>
+      <c r="P307" s="1" t="n">
+        <v>0.04666</v>
       </c>
     </row>
     <row r="308">
@@ -15550,9 +16474,12 @@
         <v>1.4939</v>
       </c>
       <c r="N308" s="1" t="n">
-        <v>1.4939</v>
+        <v>1.4978</v>
       </c>
       <c r="O308" s="1" t="n">
+        <v>1.4978</v>
+      </c>
+      <c r="P308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -15599,9 +16526,12 @@
         <v>0.0008085</v>
       </c>
       <c r="N309" s="1" t="n">
+        <v>0.000803</v>
+      </c>
+      <c r="O309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="O309" s="1" t="n">
+      <c r="P309" s="1" t="n">
         <v>0.0007892</v>
       </c>
     </row>
@@ -15648,10 +16578,13 @@
         <v>4.596</v>
       </c>
       <c r="N310" s="1" t="n">
+        <v>4.577</v>
+      </c>
+      <c r="O310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="O310" s="1" t="n">
-        <v>4.579</v>
+      <c r="P310" s="1" t="n">
+        <v>4.577</v>
       </c>
     </row>
     <row r="311">
@@ -15697,9 +16630,12 @@
         <v>4.771</v>
       </c>
       <c r="N311" s="1" t="n">
+        <v>4.756</v>
+      </c>
+      <c r="O311" s="1" t="n">
         <v>4.805</v>
       </c>
-      <c r="O311" s="1" t="n">
+      <c r="P311" s="1" t="n">
         <v>4.743</v>
       </c>
     </row>
@@ -15746,9 +16682,12 @@
         <v>0.08159</v>
       </c>
       <c r="N312" s="1" t="n">
+        <v>0.08126</v>
+      </c>
+      <c r="O312" s="1" t="n">
         <v>0.08212</v>
       </c>
-      <c r="O312" s="1" t="n">
+      <c r="P312" s="1" t="n">
         <v>0.08098</v>
       </c>
     </row>
@@ -15795,9 +16734,12 @@
         <v>2.016</v>
       </c>
       <c r="N313" s="1" t="n">
+        <v>2.012</v>
+      </c>
+      <c r="O313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="O313" s="1" t="n">
+      <c r="P313" s="1" t="n">
         <v>2.012</v>
       </c>
     </row>
@@ -15844,9 +16786,12 @@
         <v>0.07482999999999999</v>
       </c>
       <c r="N314" s="1" t="n">
+        <v>0.07343</v>
+      </c>
+      <c r="O314" s="1" t="n">
         <v>0.07482999999999999</v>
       </c>
-      <c r="O314" s="1" t="n">
+      <c r="P314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -15893,10 +16838,13 @@
         <v>0.9429999999999999</v>
       </c>
       <c r="N315" s="1" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="O315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="O315" s="1" t="n">
-        <v>0.9429999999999999</v>
+      <c r="P315" s="1" t="n">
+        <v>0.9350000000000001</v>
       </c>
     </row>
     <row r="316">
@@ -15942,9 +16890,12 @@
         <v>0.131</v>
       </c>
       <c r="N316" s="1" t="n">
+        <v>0.1305</v>
+      </c>
+      <c r="O316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="O316" s="1" t="n">
+      <c r="P316" s="1" t="n">
         <v>0.1299</v>
       </c>
     </row>
@@ -15991,9 +16942,12 @@
         <v>0.1855</v>
       </c>
       <c r="N317" s="1" t="n">
+        <v>0.1849</v>
+      </c>
+      <c r="O317" s="1" t="n">
         <v>0.186</v>
       </c>
-      <c r="O317" s="1" t="n">
+      <c r="P317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -16040,10 +16994,13 @@
         <v>0.01621</v>
       </c>
       <c r="N318" s="1" t="n">
+        <v>0.01607</v>
+      </c>
+      <c r="O318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="O318" s="1" t="n">
-        <v>0.01615</v>
+      <c r="P318" s="1" t="n">
+        <v>0.01607</v>
       </c>
     </row>
     <row r="319">
@@ -16089,10 +17046,13 @@
         <v>0.08357000000000001</v>
       </c>
       <c r="N319" s="1" t="n">
+        <v>0.08325</v>
+      </c>
+      <c r="O319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="O319" s="1" t="n">
-        <v>0.08343</v>
+      <c r="P319" s="1" t="n">
+        <v>0.08325</v>
       </c>
     </row>
     <row r="320">
@@ -16138,10 +17098,13 @@
         <v>0.007617</v>
       </c>
       <c r="N320" s="1" t="n">
+        <v>0.00754</v>
+      </c>
+      <c r="O320" s="1" t="n">
         <v>0.007667</v>
       </c>
-      <c r="O320" s="1" t="n">
-        <v>0.007571</v>
+      <c r="P320" s="1" t="n">
+        <v>0.00754</v>
       </c>
     </row>
     <row r="321">
@@ -16187,9 +17150,12 @@
         <v>0.05432</v>
       </c>
       <c r="N321" s="1" t="n">
+        <v>0.05422</v>
+      </c>
+      <c r="O321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="O321" s="1" t="n">
+      <c r="P321" s="1" t="n">
         <v>0.05406</v>
       </c>
     </row>
@@ -16236,9 +17202,12 @@
         <v>0.5507</v>
       </c>
       <c r="N322" s="1" t="n">
+        <v>0.5483</v>
+      </c>
+      <c r="O322" s="1" t="n">
         <v>0.5515</v>
       </c>
-      <c r="O322" s="1" t="n">
+      <c r="P322" s="1" t="n">
         <v>0.5476</v>
       </c>
     </row>
@@ -16285,9 +17254,12 @@
         <v>0.07609</v>
       </c>
       <c r="N323" s="1" t="n">
+        <v>0.07588</v>
+      </c>
+      <c r="O323" s="1" t="n">
         <v>0.07636999999999999</v>
       </c>
-      <c r="O323" s="1" t="n">
+      <c r="P323" s="1" t="n">
         <v>0.07525</v>
       </c>
     </row>
@@ -16334,9 +17306,12 @@
         <v>0.012985</v>
       </c>
       <c r="N324" s="1" t="n">
+        <v>0.01291</v>
+      </c>
+      <c r="O324" s="1" t="n">
         <v>0.013001</v>
       </c>
-      <c r="O324" s="1" t="n">
+      <c r="P324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -16383,9 +17358,12 @@
         <v>0.09909999999999999</v>
       </c>
       <c r="N325" s="1" t="n">
+        <v>0.0989</v>
+      </c>
+      <c r="O325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="O325" s="1" t="n">
+      <c r="P325" s="1" t="n">
         <v>0.0989</v>
       </c>
     </row>
@@ -16432,9 +17410,12 @@
         <v>0.01741</v>
       </c>
       <c r="N326" s="1" t="n">
+        <v>0.01736</v>
+      </c>
+      <c r="O326" s="1" t="n">
         <v>0.01765</v>
       </c>
-      <c r="O326" s="1" t="n">
+      <c r="P326" s="1" t="n">
         <v>0.01731</v>
       </c>
     </row>
@@ -16481,9 +17462,12 @@
         <v>0.06401999999999999</v>
       </c>
       <c r="N327" s="1" t="n">
+        <v>0.06386</v>
+      </c>
+      <c r="O327" s="1" t="n">
         <v>0.06435</v>
       </c>
-      <c r="O327" s="1" t="n">
+      <c r="P327" s="1" t="n">
         <v>0.06382</v>
       </c>
     </row>
@@ -16530,10 +17514,13 @@
         <v>0.2625</v>
       </c>
       <c r="N328" s="1" t="n">
+        <v>0.2616</v>
+      </c>
+      <c r="O328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="O328" s="1" t="n">
-        <v>0.2622</v>
+      <c r="P328" s="1" t="n">
+        <v>0.2616</v>
       </c>
     </row>
     <row r="329">
@@ -16579,9 +17566,12 @@
         <v>0.17301</v>
       </c>
       <c r="N329" s="1" t="n">
+        <v>0.17337</v>
+      </c>
+      <c r="O329" s="1" t="n">
         <v>0.17341</v>
       </c>
-      <c r="O329" s="1" t="n">
+      <c r="P329" s="1" t="n">
         <v>0.17145</v>
       </c>
     </row>
@@ -16628,9 +17618,12 @@
         <v>2.063</v>
       </c>
       <c r="N330" s="1" t="n">
+        <v>2.061</v>
+      </c>
+      <c r="O330" s="1" t="n">
         <v>2.088</v>
       </c>
-      <c r="O330" s="1" t="n">
+      <c r="P330" s="1" t="n">
         <v>2.043</v>
       </c>
     </row>
@@ -16677,9 +17670,12 @@
         <v>0.0286</v>
       </c>
       <c r="N331" s="1" t="n">
+        <v>0.0283</v>
+      </c>
+      <c r="O331" s="1" t="n">
         <v>0.0288</v>
       </c>
-      <c r="O331" s="1" t="n">
+      <c r="P331" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -16726,9 +17722,12 @@
         <v>0.006003</v>
       </c>
       <c r="N332" s="1" t="n">
-        <v>0.006032</v>
+        <v>0.006063</v>
       </c>
       <c r="O332" s="1" t="n">
+        <v>0.006063</v>
+      </c>
+      <c r="P332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -16775,9 +17774,12 @@
         <v>0.003532</v>
       </c>
       <c r="N333" s="1" t="n">
+        <v>0.003519</v>
+      </c>
+      <c r="O333" s="1" t="n">
         <v>0.003579</v>
       </c>
-      <c r="O333" s="1" t="n">
+      <c r="P333" s="1" t="n">
         <v>0.003497</v>
       </c>
     </row>
@@ -16824,9 +17826,12 @@
         <v>0.01403</v>
       </c>
       <c r="N334" s="1" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="O334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="O334" s="1" t="n">
+      <c r="P334" s="1" t="n">
         <v>0.01394</v>
       </c>
     </row>
@@ -16873,9 +17878,12 @@
         <v>1.136</v>
       </c>
       <c r="N335" s="1" t="n">
+        <v>1.132</v>
+      </c>
+      <c r="O335" s="1" t="n">
         <v>1.136</v>
       </c>
-      <c r="O335" s="1" t="n">
+      <c r="P335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -16922,9 +17930,12 @@
         <v>0.011312</v>
       </c>
       <c r="N336" s="1" t="n">
-        <v>0.011326</v>
+        <v>0.011344</v>
       </c>
       <c r="O336" s="1" t="n">
+        <v>0.011344</v>
+      </c>
+      <c r="P336" s="1" t="n">
         <v>0.011238</v>
       </c>
     </row>
@@ -16971,9 +17982,12 @@
         <v>2.951</v>
       </c>
       <c r="N337" s="1" t="n">
+        <v>2.945</v>
+      </c>
+      <c r="O337" s="1" t="n">
         <v>3.043</v>
       </c>
-      <c r="O337" s="1" t="n">
+      <c r="P337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -17020,10 +18034,13 @@
         <v>0.01863</v>
       </c>
       <c r="N338" s="1" t="n">
+        <v>0.01854</v>
+      </c>
+      <c r="O338" s="1" t="n">
         <v>0.01885</v>
       </c>
-      <c r="O338" s="1" t="n">
-        <v>0.01858</v>
+      <c r="P338" s="1" t="n">
+        <v>0.01854</v>
       </c>
     </row>
     <row r="339">
@@ -17069,9 +18086,12 @@
         <v>0.07756</v>
       </c>
       <c r="N339" s="1" t="n">
+        <v>0.07721</v>
+      </c>
+      <c r="O339" s="1" t="n">
         <v>0.07790999999999999</v>
       </c>
-      <c r="O339" s="1" t="n">
+      <c r="P339" s="1" t="n">
         <v>0.07689</v>
       </c>
     </row>
@@ -17118,9 +18138,12 @@
         <v>0.075</v>
       </c>
       <c r="N340" s="1" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="O340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="O340" s="1" t="n">
+      <c r="P340" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -17167,10 +18190,13 @@
         <v>0.03592</v>
       </c>
       <c r="N341" s="1" t="n">
+        <v>0.03581</v>
+      </c>
+      <c r="O341" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="O341" s="1" t="n">
-        <v>0.03585</v>
+      <c r="P341" s="1" t="n">
+        <v>0.03581</v>
       </c>
     </row>
     <row r="342">
@@ -17216,10 +18242,13 @@
         <v>2607</v>
       </c>
       <c r="N342" s="1" t="n">
+        <v>2599</v>
+      </c>
+      <c r="O342" s="1" t="n">
         <v>2647</v>
       </c>
-      <c r="O342" s="1" t="n">
-        <v>2606</v>
+      <c r="P342" s="1" t="n">
+        <v>2599</v>
       </c>
     </row>
     <row r="343">
@@ -17268,6 +18297,9 @@
         <v>0.0002003</v>
       </c>
       <c r="O343" s="1" t="n">
+        <v>0.0002003</v>
+      </c>
+      <c r="P343" s="1" t="n">
         <v>0.0001959</v>
       </c>
     </row>
@@ -17314,9 +18346,12 @@
         <v>0.07961</v>
       </c>
       <c r="N344" s="1" t="n">
+        <v>0.0794</v>
+      </c>
+      <c r="O344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="O344" s="1" t="n">
+      <c r="P344" s="1" t="n">
         <v>0.07925</v>
       </c>
     </row>
@@ -17363,9 +18398,12 @@
         <v>0.01661</v>
       </c>
       <c r="N345" s="1" t="n">
+        <v>0.01639</v>
+      </c>
+      <c r="O345" s="1" t="n">
         <v>0.0168</v>
       </c>
-      <c r="O345" s="1" t="n">
+      <c r="P345" s="1" t="n">
         <v>0.0163</v>
       </c>
     </row>
@@ -17412,10 +18450,13 @@
         <v>2.751</v>
       </c>
       <c r="N346" s="1" t="n">
+        <v>2.735</v>
+      </c>
+      <c r="O346" s="1" t="n">
         <v>2.799</v>
       </c>
-      <c r="O346" s="1" t="n">
-        <v>2.746</v>
+      <c r="P346" s="1" t="n">
+        <v>2.735</v>
       </c>
     </row>
     <row r="347">
@@ -17461,10 +18502,13 @@
         <v>0.01634</v>
       </c>
       <c r="N347" s="1" t="n">
+        <v>0.01626</v>
+      </c>
+      <c r="O347" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="O347" s="1" t="n">
-        <v>0.01631</v>
+      <c r="P347" s="1" t="n">
+        <v>0.01626</v>
       </c>
     </row>
     <row r="348">
@@ -17510,9 +18554,12 @@
         <v>0.03928</v>
       </c>
       <c r="N348" s="1" t="n">
-        <v>0.03929</v>
+        <v>0.03968</v>
       </c>
       <c r="O348" s="1" t="n">
+        <v>0.03968</v>
+      </c>
+      <c r="P348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -17559,9 +18606,12 @@
         <v>0.3044</v>
       </c>
       <c r="N349" s="1" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="O349" s="1" t="n">
         <v>0.3065</v>
       </c>
-      <c r="O349" s="1" t="n">
+      <c r="P349" s="1" t="n">
         <v>0.3028</v>
       </c>
     </row>
@@ -17608,9 +18658,12 @@
         <v>0.005113</v>
       </c>
       <c r="N350" s="1" t="n">
+        <v>0.005096</v>
+      </c>
+      <c r="O350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="O350" s="1" t="n">
+      <c r="P350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -17657,9 +18710,12 @@
         <v>0.005093</v>
       </c>
       <c r="N351" s="1" t="n">
+        <v>0.005071</v>
+      </c>
+      <c r="O351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="O351" s="1" t="n">
+      <c r="P351" s="1" t="n">
         <v>0.005065</v>
       </c>
     </row>
@@ -17706,10 +18762,13 @@
         <v>0.0044</v>
       </c>
       <c r="N352" s="1" t="n">
+        <v>0.004383</v>
+      </c>
+      <c r="O352" s="1" t="n">
         <v>0.004419</v>
       </c>
-      <c r="O352" s="1" t="n">
-        <v>0.004384</v>
+      <c r="P352" s="1" t="n">
+        <v>0.004383</v>
       </c>
     </row>
     <row r="353">
@@ -17755,10 +18814,13 @@
         <v>0.08083</v>
       </c>
       <c r="N353" s="1" t="n">
+        <v>0.0803</v>
+      </c>
+      <c r="O353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="O353" s="1" t="n">
-        <v>0.08062999999999999</v>
+      <c r="P353" s="1" t="n">
+        <v>0.0803</v>
       </c>
     </row>
     <row r="354">
@@ -17804,10 +18866,13 @@
         <v>1.281</v>
       </c>
       <c r="N354" s="1" t="n">
+        <v>1.271</v>
+      </c>
+      <c r="O354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="O354" s="1" t="n">
-        <v>1.277</v>
+      <c r="P354" s="1" t="n">
+        <v>1.271</v>
       </c>
     </row>
     <row r="355">
@@ -17853,10 +18918,13 @@
         <v>7.7</v>
       </c>
       <c r="N355" s="1" t="n">
+        <v>7.684</v>
+      </c>
+      <c r="O355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="O355" s="1" t="n">
-        <v>7.7</v>
+      <c r="P355" s="1" t="n">
+        <v>7.684</v>
       </c>
     </row>
     <row r="356">
@@ -17902,9 +18970,12 @@
         <v>0.007820000000000001</v>
       </c>
       <c r="N356" s="1" t="n">
+        <v>0.0078</v>
+      </c>
+      <c r="O356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="O356" s="1" t="n">
+      <c r="P356" s="1" t="n">
         <v>0.00778</v>
       </c>
     </row>
@@ -17951,10 +19022,13 @@
         <v>0.00563</v>
       </c>
       <c r="N357" s="1" t="n">
+        <v>0.005608</v>
+      </c>
+      <c r="O357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="O357" s="1" t="n">
-        <v>0.00563</v>
+      <c r="P357" s="1" t="n">
+        <v>0.005608</v>
       </c>
     </row>
     <row r="358">
@@ -18000,10 +19074,13 @@
         <v>0.01549</v>
       </c>
       <c r="N358" s="1" t="n">
+        <v>0.01546</v>
+      </c>
+      <c r="O358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="O358" s="1" t="n">
-        <v>0.01549</v>
+      <c r="P358" s="1" t="n">
+        <v>0.01546</v>
       </c>
     </row>
     <row r="359">
@@ -18049,10 +19126,13 @@
         <v>3.636</v>
       </c>
       <c r="N359" s="1" t="n">
+        <v>3.617</v>
+      </c>
+      <c r="O359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="O359" s="1" t="n">
-        <v>3.635</v>
+      <c r="P359" s="1" t="n">
+        <v>3.617</v>
       </c>
     </row>
     <row r="360">
@@ -18098,9 +19178,12 @@
         <v>0.1503</v>
       </c>
       <c r="N360" s="1" t="n">
+        <v>0.1499</v>
+      </c>
+      <c r="O360" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="O360" s="1" t="n">
+      <c r="P360" s="1" t="n">
         <v>0.1497</v>
       </c>
     </row>
@@ -18147,9 +19230,12 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="N361" s="1" t="n">
+        <v>0.07038</v>
+      </c>
+      <c r="O361" s="1" t="n">
         <v>0.07104000000000001</v>
       </c>
-      <c r="O361" s="1" t="n">
+      <c r="P361" s="1" t="n">
         <v>0.07019</v>
       </c>
     </row>
@@ -18196,10 +19282,13 @@
         <v>0.01766</v>
       </c>
       <c r="N362" s="1" t="n">
+        <v>0.0176</v>
+      </c>
+      <c r="O362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="O362" s="1" t="n">
-        <v>0.01761</v>
+      <c r="P362" s="1" t="n">
+        <v>0.0176</v>
       </c>
     </row>
     <row r="363">
@@ -18245,9 +19334,12 @@
         <v>0.0224</v>
       </c>
       <c r="N363" s="1" t="n">
+        <v>0.02238</v>
+      </c>
+      <c r="O363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="O363" s="1" t="n">
+      <c r="P363" s="1" t="n">
         <v>0.02234</v>
       </c>
     </row>
@@ -18294,9 +19386,12 @@
         <v>0.0126</v>
       </c>
       <c r="N364" s="1" t="n">
+        <v>0.01254</v>
+      </c>
+      <c r="O364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="O364" s="1" t="n">
+      <c r="P364" s="1" t="n">
         <v>0.01249</v>
       </c>
     </row>
@@ -18343,10 +19438,13 @@
         <v>0.0916</v>
       </c>
       <c r="N365" s="1" t="n">
+        <v>0.0912</v>
+      </c>
+      <c r="O365" s="1" t="n">
         <v>0.0926</v>
       </c>
-      <c r="O365" s="1" t="n">
-        <v>0.0914</v>
+      <c r="P365" s="1" t="n">
+        <v>0.0912</v>
       </c>
     </row>
     <row r="366">
@@ -18392,9 +19490,12 @@
         <v>0.04239</v>
       </c>
       <c r="N366" s="1" t="n">
+        <v>0.04227</v>
+      </c>
+      <c r="O366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="O366" s="1" t="n">
+      <c r="P366" s="1" t="n">
         <v>0.04224</v>
       </c>
     </row>
@@ -18441,9 +19542,12 @@
         <v>0.03151</v>
       </c>
       <c r="N367" s="1" t="n">
+        <v>0.03144</v>
+      </c>
+      <c r="O367" s="1" t="n">
         <v>0.03188</v>
       </c>
-      <c r="O367" s="1" t="n">
+      <c r="P367" s="1" t="n">
         <v>0.03141</v>
       </c>
     </row>
@@ -18490,9 +19594,12 @@
         <v>0.02345</v>
       </c>
       <c r="N368" s="1" t="n">
+        <v>0.02331</v>
+      </c>
+      <c r="O368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="O368" s="1" t="n">
+      <c r="P368" s="1" t="n">
         <v>0.02331</v>
       </c>
     </row>
@@ -18539,10 +19646,13 @@
         <v>0.03096</v>
       </c>
       <c r="N369" s="1" t="n">
+        <v>0.03088</v>
+      </c>
+      <c r="O369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="O369" s="1" t="n">
-        <v>0.03089</v>
+      <c r="P369" s="1" t="n">
+        <v>0.03088</v>
       </c>
     </row>
     <row r="370">
@@ -18588,9 +19698,12 @@
         <v>0.07990999999999999</v>
       </c>
       <c r="N370" s="1" t="n">
+        <v>0.07932</v>
+      </c>
+      <c r="O370" s="1" t="n">
         <v>0.07990999999999999</v>
       </c>
-      <c r="O370" s="1" t="n">
+      <c r="P370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -18637,10 +19750,13 @@
         <v>0.1077</v>
       </c>
       <c r="N371" s="1" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="O371" s="1" t="n">
         <v>0.1089</v>
       </c>
-      <c r="O371" s="1" t="n">
-        <v>0.1074</v>
+      <c r="P371" s="1" t="n">
+        <v>0.1073</v>
       </c>
     </row>
     <row r="372">
@@ -18686,10 +19802,13 @@
         <v>0.007051</v>
       </c>
       <c r="N372" s="1" t="n">
+        <v>0.007001</v>
+      </c>
+      <c r="O372" s="1" t="n">
         <v>0.007209</v>
       </c>
-      <c r="O372" s="1" t="n">
-        <v>0.007024</v>
+      <c r="P372" s="1" t="n">
+        <v>0.007001</v>
       </c>
     </row>
     <row r="373">
@@ -18735,10 +19854,13 @@
         <v>0.0963</v>
       </c>
       <c r="N373" s="1" t="n">
+        <v>0.0956</v>
+      </c>
+      <c r="O373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="O373" s="1" t="n">
-        <v>0.096</v>
+      <c r="P373" s="1" t="n">
+        <v>0.0956</v>
       </c>
     </row>
     <row r="374">
@@ -18784,10 +19906,13 @@
         <v>0.05778</v>
       </c>
       <c r="N374" s="1" t="n">
+        <v>0.05735</v>
+      </c>
+      <c r="O374" s="1" t="n">
         <v>0.05881</v>
       </c>
-      <c r="O374" s="1" t="n">
-        <v>0.05771</v>
+      <c r="P374" s="1" t="n">
+        <v>0.05735</v>
       </c>
     </row>
     <row r="375">
@@ -18833,10 +19958,13 @@
         <v>0.3222</v>
       </c>
       <c r="N375" s="1" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="O375" s="1" t="n">
         <v>0.3238</v>
       </c>
-      <c r="O375" s="1" t="n">
-        <v>0.3193</v>
+      <c r="P375" s="1" t="n">
+        <v>0.3192</v>
       </c>
     </row>
     <row r="376">
@@ -18882,10 +20010,13 @@
         <v>0.01953</v>
       </c>
       <c r="N376" s="1" t="n">
+        <v>0.01942</v>
+      </c>
+      <c r="O376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="O376" s="1" t="n">
-        <v>0.0195</v>
+      <c r="P376" s="1" t="n">
+        <v>0.01942</v>
       </c>
     </row>
     <row r="377">
@@ -18931,10 +20062,13 @@
         <v>0.06854</v>
       </c>
       <c r="N377" s="1" t="n">
+        <v>0.06827999999999999</v>
+      </c>
+      <c r="O377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="O377" s="1" t="n">
-        <v>0.0684</v>
+      <c r="P377" s="1" t="n">
+        <v>0.06827999999999999</v>
       </c>
     </row>
     <row r="378">
@@ -18980,9 +20114,12 @@
         <v>0.15664</v>
       </c>
       <c r="N378" s="1" t="n">
+        <v>0.15697</v>
+      </c>
+      <c r="O378" s="1" t="n">
         <v>0.1581</v>
       </c>
-      <c r="O378" s="1" t="n">
+      <c r="P378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -19029,10 +20166,13 @@
         <v>0.0005977000000000001</v>
       </c>
       <c r="N379" s="1" t="n">
+        <v>0.000595</v>
+      </c>
+      <c r="O379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="O379" s="1" t="n">
-        <v>0.0005965</v>
+      <c r="P379" s="1" t="n">
+        <v>0.000595</v>
       </c>
     </row>
     <row r="380">
@@ -19078,9 +20218,12 @@
         <v>0.01018</v>
       </c>
       <c r="N380" s="1" t="n">
+        <v>0.01016</v>
+      </c>
+      <c r="O380" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="O380" s="1" t="n">
+      <c r="P380" s="1" t="n">
         <v>0.01015</v>
       </c>
     </row>
@@ -19127,10 +20270,13 @@
         <v>0.02548</v>
       </c>
       <c r="N381" s="1" t="n">
+        <v>0.02538</v>
+      </c>
+      <c r="O381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="O381" s="1" t="n">
-        <v>0.02547</v>
+      <c r="P381" s="1" t="n">
+        <v>0.02538</v>
       </c>
     </row>
     <row r="382">
@@ -19176,9 +20322,12 @@
         <v>0.19134</v>
       </c>
       <c r="N382" s="1" t="n">
+        <v>0.19144</v>
+      </c>
+      <c r="O382" s="1" t="n">
         <v>0.19348</v>
       </c>
-      <c r="O382" s="1" t="n">
+      <c r="P382" s="1" t="n">
         <v>0.18936</v>
       </c>
     </row>
@@ -19225,9 +20374,12 @@
         <v>0.09329</v>
       </c>
       <c r="N383" s="1" t="n">
+        <v>0.09282</v>
+      </c>
+      <c r="O383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="O383" s="1" t="n">
+      <c r="P383" s="1" t="n">
         <v>0.09236</v>
       </c>
     </row>
@@ -19274,10 +20426,13 @@
         <v>0.03167</v>
       </c>
       <c r="N384" s="1" t="n">
+        <v>0.03163</v>
+      </c>
+      <c r="O384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="O384" s="1" t="n">
-        <v>0.03166</v>
+      <c r="P384" s="1" t="n">
+        <v>0.03163</v>
       </c>
     </row>
     <row r="385">
@@ -19323,10 +20478,13 @@
         <v>0.01098</v>
       </c>
       <c r="N385" s="1" t="n">
+        <v>0.01092</v>
+      </c>
+      <c r="O385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="O385" s="1" t="n">
-        <v>0.01093</v>
+      <c r="P385" s="1" t="n">
+        <v>0.01092</v>
       </c>
     </row>
     <row r="386">
@@ -19372,9 +20530,12 @@
         <v>0.05131</v>
       </c>
       <c r="N386" s="1" t="n">
+        <v>0.05105</v>
+      </c>
+      <c r="O386" s="1" t="n">
         <v>0.05224</v>
       </c>
-      <c r="O386" s="1" t="n">
+      <c r="P386" s="1" t="n">
         <v>0.05087</v>
       </c>
     </row>
@@ -19421,9 +20582,12 @@
         <v>0.02514</v>
       </c>
       <c r="N387" s="1" t="n">
+        <v>0.02498</v>
+      </c>
+      <c r="O387" s="1" t="n">
         <v>0.02541</v>
       </c>
-      <c r="O387" s="1" t="n">
+      <c r="P387" s="1" t="n">
         <v>0.02483</v>
       </c>
     </row>
@@ -19470,9 +20634,12 @@
         <v>0.00728</v>
       </c>
       <c r="N388" s="1" t="n">
+        <v>0.007292</v>
+      </c>
+      <c r="O388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="O388" s="1" t="n">
+      <c r="P388" s="1" t="n">
         <v>0.007267</v>
       </c>
     </row>
@@ -19519,10 +20686,13 @@
         <v>0.01014</v>
       </c>
       <c r="N389" s="1" t="n">
+        <v>0.01009</v>
+      </c>
+      <c r="O389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="O389" s="1" t="n">
-        <v>0.0101</v>
+      <c r="P389" s="1" t="n">
+        <v>0.01009</v>
       </c>
     </row>
     <row r="390">
@@ -19568,10 +20738,13 @@
         <v>0.08266</v>
       </c>
       <c r="N390" s="1" t="n">
+        <v>0.0823</v>
+      </c>
+      <c r="O390" s="1" t="n">
         <v>0.0839</v>
       </c>
-      <c r="O390" s="1" t="n">
-        <v>0.08233</v>
+      <c r="P390" s="1" t="n">
+        <v>0.0823</v>
       </c>
     </row>
     <row r="391">
@@ -19617,9 +20790,12 @@
         <v>0.5056</v>
       </c>
       <c r="N391" s="1" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="O391" s="1" t="n">
         <v>0.5061</v>
       </c>
-      <c r="O391" s="1" t="n">
+      <c r="P391" s="1" t="n">
         <v>0.5014</v>
       </c>
     </row>
@@ -19666,10 +20842,13 @@
         <v>0.1166</v>
       </c>
       <c r="N392" s="1" t="n">
+        <v>0.1162</v>
+      </c>
+      <c r="O392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="O392" s="1" t="n">
-        <v>0.1165</v>
+      <c r="P392" s="1" t="n">
+        <v>0.1162</v>
       </c>
     </row>
     <row r="393">
@@ -19715,10 +20894,13 @@
         <v>0.00245</v>
       </c>
       <c r="N393" s="1" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="O393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="O393" s="1" t="n">
-        <v>0.00245</v>
+      <c r="P393" s="1" t="n">
+        <v>0.00244</v>
       </c>
     </row>
     <row r="394">
@@ -19764,9 +20946,12 @@
         <v>0.0213</v>
       </c>
       <c r="N394" s="1" t="n">
+        <v>0.02122</v>
+      </c>
+      <c r="O394" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="O394" s="1" t="n">
+      <c r="P394" s="1" t="n">
         <v>0.02121</v>
       </c>
     </row>
@@ -19813,10 +20998,13 @@
         <v>0.016</v>
       </c>
       <c r="N395" s="1" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="O395" s="1" t="n">
         <v>0.0163</v>
       </c>
-      <c r="O395" s="1" t="n">
-        <v>0.0159</v>
+      <c r="P395" s="1" t="n">
+        <v>0.0158</v>
       </c>
     </row>
     <row r="396">
@@ -19862,10 +21050,13 @@
         <v>0.1353</v>
       </c>
       <c r="N396" s="1" t="n">
+        <v>0.1349</v>
+      </c>
+      <c r="O396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="O396" s="1" t="n">
-        <v>0.1353</v>
+      <c r="P396" s="1" t="n">
+        <v>0.1349</v>
       </c>
     </row>
     <row r="397">
@@ -19911,10 +21102,13 @@
         <v>0.01453</v>
       </c>
       <c r="N397" s="1" t="n">
+        <v>0.01446</v>
+      </c>
+      <c r="O397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="O397" s="1" t="n">
-        <v>0.01452</v>
+      <c r="P397" s="1" t="n">
+        <v>0.01446</v>
       </c>
     </row>
     <row r="398">
@@ -19960,10 +21154,13 @@
         <v>6.797</v>
       </c>
       <c r="N398" s="1" t="n">
+        <v>6.701</v>
+      </c>
+      <c r="O398" s="1" t="n">
         <v>6.955</v>
       </c>
-      <c r="O398" s="1" t="n">
-        <v>6.708</v>
+      <c r="P398" s="1" t="n">
+        <v>6.701</v>
       </c>
     </row>
     <row r="399">
@@ -20009,10 +21206,13 @@
         <v>0.009396</v>
       </c>
       <c r="N399" s="1" t="n">
+        <v>0.009384999999999999</v>
+      </c>
+      <c r="O399" s="1" t="n">
         <v>0.009509999999999999</v>
       </c>
-      <c r="O399" s="1" t="n">
-        <v>0.009396</v>
+      <c r="P399" s="1" t="n">
+        <v>0.009384999999999999</v>
       </c>
     </row>
     <row r="400">
@@ -20058,9 +21258,12 @@
         <v>0.00127</v>
       </c>
       <c r="N400" s="1" t="n">
+        <v>0.001264</v>
+      </c>
+      <c r="O400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="O400" s="1" t="n">
+      <c r="P400" s="1" t="n">
         <v>0.001256</v>
       </c>
     </row>
@@ -20107,9 +21310,12 @@
         <v>0.01852</v>
       </c>
       <c r="N401" s="1" t="n">
+        <v>0.01846</v>
+      </c>
+      <c r="O401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="O401" s="1" t="n">
+      <c r="P401" s="1" t="n">
         <v>0.01841</v>
       </c>
     </row>
@@ -20156,10 +21362,13 @@
         <v>0.08507000000000001</v>
       </c>
       <c r="N402" s="1" t="n">
+        <v>0.08484999999999999</v>
+      </c>
+      <c r="O402" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="O402" s="1" t="n">
-        <v>0.08488999999999999</v>
+      <c r="P402" s="1" t="n">
+        <v>0.08484999999999999</v>
       </c>
     </row>
     <row r="403">
@@ -20205,10 +21414,13 @@
         <v>0.00553</v>
       </c>
       <c r="N403" s="1" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="O403" s="1" t="n">
         <v>0.00556</v>
       </c>
-      <c r="O403" s="1" t="n">
-        <v>0.00551</v>
+      <c r="P403" s="1" t="n">
+        <v>0.0055</v>
       </c>
     </row>
     <row r="404">
@@ -20254,10 +21466,13 @@
         <v>0.04272</v>
       </c>
       <c r="N404" s="1" t="n">
+        <v>0.04238</v>
+      </c>
+      <c r="O404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="O404" s="1" t="n">
-        <v>0.04271</v>
+      <c r="P404" s="1" t="n">
+        <v>0.04238</v>
       </c>
     </row>
     <row r="405">
@@ -20303,10 +21518,13 @@
         <v>0.05836</v>
       </c>
       <c r="N405" s="1" t="n">
+        <v>0.05833</v>
+      </c>
+      <c r="O405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="O405" s="1" t="n">
-        <v>0.05836</v>
+      <c r="P405" s="1" t="n">
+        <v>0.05833</v>
       </c>
     </row>
     <row r="406">
@@ -20352,9 +21570,12 @@
         <v>0.01663</v>
       </c>
       <c r="N406" s="1" t="n">
+        <v>0.01653</v>
+      </c>
+      <c r="O406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="O406" s="1" t="n">
+      <c r="P406" s="1" t="n">
         <v>0.01647</v>
       </c>
     </row>
@@ -20401,9 +21622,12 @@
         <v>0.0425</v>
       </c>
       <c r="N407" s="1" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="O407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="O407" s="1" t="n">
+      <c r="P407" s="1" t="n">
         <v>0.0423</v>
       </c>
     </row>
@@ -20450,10 +21674,13 @@
         <v>0.01929</v>
       </c>
       <c r="N408" s="1" t="n">
+        <v>0.01922</v>
+      </c>
+      <c r="O408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="O408" s="1" t="n">
-        <v>0.01927</v>
+      <c r="P408" s="1" t="n">
+        <v>0.01922</v>
       </c>
     </row>
     <row r="409">
@@ -20499,9 +21726,12 @@
         <v>0.4452</v>
       </c>
       <c r="N409" s="1" t="n">
+        <v>0.4447</v>
+      </c>
+      <c r="O409" s="1" t="n">
         <v>0.4484</v>
       </c>
-      <c r="O409" s="1" t="n">
+      <c r="P409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -20548,10 +21778,13 @@
         <v>0.04412</v>
       </c>
       <c r="N410" s="1" t="n">
+        <v>0.04399</v>
+      </c>
+      <c r="O410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="O410" s="1" t="n">
-        <v>0.04408</v>
+      <c r="P410" s="1" t="n">
+        <v>0.04399</v>
       </c>
     </row>
     <row r="411">
@@ -20597,9 +21830,12 @@
         <v>27.35</v>
       </c>
       <c r="N411" s="1" t="n">
+        <v>27.41</v>
+      </c>
+      <c r="O411" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="O411" s="1" t="n">
+      <c r="P411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -20646,10 +21882,13 @@
         <v>0.03522</v>
       </c>
       <c r="N412" s="1" t="n">
+        <v>0.03503</v>
+      </c>
+      <c r="O412" s="1" t="n">
         <v>0.03564</v>
       </c>
-      <c r="O412" s="1" t="n">
-        <v>0.03508</v>
+      <c r="P412" s="1" t="n">
+        <v>0.03503</v>
       </c>
     </row>
     <row r="413">
@@ -20695,10 +21934,13 @@
         <v>0.003401</v>
       </c>
       <c r="N413" s="1" t="n">
+        <v>0.003396</v>
+      </c>
+      <c r="O413" s="1" t="n">
         <v>0.003432</v>
       </c>
-      <c r="O413" s="1" t="n">
-        <v>0.003397</v>
+      <c r="P413" s="1" t="n">
+        <v>0.003396</v>
       </c>
     </row>
     <row r="414">
@@ -20744,9 +21986,12 @@
         <v>0.1531</v>
       </c>
       <c r="N414" s="1" t="n">
+        <v>0.1528</v>
+      </c>
+      <c r="O414" s="1" t="n">
         <v>0.1538</v>
       </c>
-      <c r="O414" s="1" t="n">
+      <c r="P414" s="1" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -20793,9 +22038,12 @@
         <v>0.05273</v>
       </c>
       <c r="N415" s="1" t="n">
+        <v>0.05269</v>
+      </c>
+      <c r="O415" s="1" t="n">
         <v>0.05288</v>
       </c>
-      <c r="O415" s="1" t="n">
+      <c r="P415" s="1" t="n">
         <v>0.0525</v>
       </c>
     </row>
@@ -20842,10 +22090,13 @@
         <v>0.00661</v>
       </c>
       <c r="N416" s="1" t="n">
+        <v>0.00656</v>
+      </c>
+      <c r="O416" s="1" t="n">
         <v>0.00669</v>
       </c>
-      <c r="O416" s="1" t="n">
-        <v>0.00658</v>
+      <c r="P416" s="1" t="n">
+        <v>0.00656</v>
       </c>
     </row>
     <row r="417">
@@ -20891,10 +22142,13 @@
         <v>0.06052</v>
       </c>
       <c r="N417" s="1" t="n">
+        <v>0.06034</v>
+      </c>
+      <c r="O417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="O417" s="1" t="n">
-        <v>0.06045</v>
+      <c r="P417" s="1" t="n">
+        <v>0.06034</v>
       </c>
     </row>
     <row r="418">
@@ -20940,9 +22194,12 @@
         <v>0.008036</v>
       </c>
       <c r="N418" s="1" t="n">
+        <v>0.008009</v>
+      </c>
+      <c r="O418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="O418" s="1" t="n">
+      <c r="P418" s="1" t="n">
         <v>0.007979</v>
       </c>
     </row>
@@ -20989,10 +22246,13 @@
         <v>0.07464999999999999</v>
       </c>
       <c r="N419" s="1" t="n">
+        <v>0.07432</v>
+      </c>
+      <c r="O419" s="1" t="n">
         <v>0.07524</v>
       </c>
-      <c r="O419" s="1" t="n">
-        <v>0.07435</v>
+      <c r="P419" s="1" t="n">
+        <v>0.07432</v>
       </c>
     </row>
     <row r="420">
@@ -21038,9 +22298,12 @@
         <v>0.02128</v>
       </c>
       <c r="N420" s="1" t="n">
+        <v>0.02121</v>
+      </c>
+      <c r="O420" s="1" t="n">
         <v>0.02146</v>
       </c>
-      <c r="O420" s="1" t="n">
+      <c r="P420" s="1" t="n">
         <v>0.02105</v>
       </c>
     </row>
@@ -21087,10 +22350,13 @@
         <v>0.06962</v>
       </c>
       <c r="N421" s="1" t="n">
+        <v>0.06933</v>
+      </c>
+      <c r="O421" s="1" t="n">
         <v>0.07038999999999999</v>
       </c>
-      <c r="O421" s="1" t="n">
-        <v>0.06938999999999999</v>
+      <c r="P421" s="1" t="n">
+        <v>0.06933</v>
       </c>
     </row>
     <row r="422">
@@ -21136,10 +22402,13 @@
         <v>0.0149</v>
       </c>
       <c r="N422" s="1" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="O422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="O422" s="1" t="n">
-        <v>0.01487</v>
+      <c r="P422" s="1" t="n">
+        <v>0.0148</v>
       </c>
     </row>
     <row r="423">
@@ -21185,10 +22454,13 @@
         <v>0.006638</v>
       </c>
       <c r="N423" s="1" t="n">
+        <v>0.006615</v>
+      </c>
+      <c r="O423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="O423" s="1" t="n">
-        <v>0.006638</v>
+      <c r="P423" s="1" t="n">
+        <v>0.006615</v>
       </c>
     </row>
     <row r="424">
@@ -21234,10 +22506,13 @@
         <v>0.912</v>
       </c>
       <c r="N424" s="1" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="O424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="O424" s="1" t="n">
-        <v>0.909</v>
+      <c r="P424" s="1" t="n">
+        <v>0.908</v>
       </c>
     </row>
     <row r="425">
@@ -21283,9 +22558,12 @@
         <v>0.03567</v>
       </c>
       <c r="N425" s="1" t="n">
+        <v>0.03559</v>
+      </c>
+      <c r="O425" s="1" t="n">
         <v>0.03596</v>
       </c>
-      <c r="O425" s="1" t="n">
+      <c r="P425" s="1" t="n">
         <v>0.03546</v>
       </c>
     </row>
@@ -21332,9 +22610,12 @@
         <v>1.792</v>
       </c>
       <c r="N426" s="1" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="O426" s="1" t="n">
         <v>1.81</v>
       </c>
-      <c r="O426" s="1" t="n">
+      <c r="P426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -21381,9 +22662,12 @@
         <v>0.12825</v>
       </c>
       <c r="N427" s="1" t="n">
+        <v>0.12791</v>
+      </c>
+      <c r="O427" s="1" t="n">
         <v>0.12835</v>
       </c>
-      <c r="O427" s="1" t="n">
+      <c r="P427" s="1" t="n">
         <v>0.12736</v>
       </c>
     </row>
@@ -21430,10 +22714,13 @@
         <v>0.05307</v>
       </c>
       <c r="N428" s="1" t="n">
+        <v>0.05285</v>
+      </c>
+      <c r="O428" s="1" t="n">
         <v>0.05362</v>
       </c>
-      <c r="O428" s="1" t="n">
-        <v>0.05297</v>
+      <c r="P428" s="1" t="n">
+        <v>0.05285</v>
       </c>
     </row>
     <row r="429">
@@ -21479,10 +22766,13 @@
         <v>1.292</v>
       </c>
       <c r="N429" s="1" t="n">
+        <v>1.287</v>
+      </c>
+      <c r="O429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="O429" s="1" t="n">
-        <v>1.289</v>
+      <c r="P429" s="1" t="n">
+        <v>1.287</v>
       </c>
     </row>
     <row r="430">
@@ -21528,10 +22818,13 @@
         <v>0.07488</v>
       </c>
       <c r="N430" s="1" t="n">
+        <v>0.07463</v>
+      </c>
+      <c r="O430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="O430" s="1" t="n">
-        <v>0.07482</v>
+      <c r="P430" s="1" t="n">
+        <v>0.07463</v>
       </c>
     </row>
     <row r="431">
@@ -21577,9 +22870,12 @@
         <v>0.1573</v>
       </c>
       <c r="N431" s="1" t="n">
+        <v>0.1576</v>
+      </c>
+      <c r="O431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="O431" s="1" t="n">
+      <c r="P431" s="1" t="n">
         <v>0.157</v>
       </c>
     </row>
@@ -21626,10 +22922,13 @@
         <v>1.446</v>
       </c>
       <c r="N432" s="1" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="O432" s="1" t="n">
         <v>1.461</v>
       </c>
-      <c r="O432" s="1" t="n">
-        <v>1.445</v>
+      <c r="P432" s="1" t="n">
+        <v>1.438</v>
       </c>
     </row>
     <row r="433">
@@ -21675,10 +22974,13 @@
         <v>3.268</v>
       </c>
       <c r="N433" s="1" t="n">
+        <v>3.257</v>
+      </c>
+      <c r="O433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="O433" s="1" t="n">
-        <v>3.266</v>
+      <c r="P433" s="1" t="n">
+        <v>3.257</v>
       </c>
     </row>
     <row r="434">
@@ -21724,9 +23026,12 @@
         <v>0.1791</v>
       </c>
       <c r="N434" s="1" t="n">
+        <v>0.1786</v>
+      </c>
+      <c r="O434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="O434" s="1" t="n">
+      <c r="P434" s="1" t="n">
         <v>0.1783</v>
       </c>
     </row>
@@ -21773,10 +23078,13 @@
         <v>0.008598</v>
       </c>
       <c r="N435" s="1" t="n">
+        <v>0.008572</v>
+      </c>
+      <c r="O435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="O435" s="1" t="n">
-        <v>0.008580000000000001</v>
+      <c r="P435" s="1" t="n">
+        <v>0.008572</v>
       </c>
     </row>
     <row r="436">
@@ -21822,9 +23130,12 @@
         <v>0.2833</v>
       </c>
       <c r="N436" s="1" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="O436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="O436" s="1" t="n">
+      <c r="P436" s="1" t="n">
         <v>0.2818</v>
       </c>
     </row>
@@ -21871,9 +23182,12 @@
         <v>0.03898</v>
       </c>
       <c r="N437" s="1" t="n">
+        <v>0.03899</v>
+      </c>
+      <c r="O437" s="1" t="n">
         <v>0.03957</v>
       </c>
-      <c r="O437" s="1" t="n">
+      <c r="P437" s="1" t="n">
         <v>0.03814</v>
       </c>
     </row>
@@ -21920,9 +23234,12 @@
         <v>0.02435</v>
       </c>
       <c r="N438" s="1" t="n">
+        <v>0.02435</v>
+      </c>
+      <c r="O438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="O438" s="1" t="n">
+      <c r="P438" s="1" t="n">
         <v>0.0242</v>
       </c>
     </row>
@@ -21969,10 +23286,13 @@
         <v>0.04404</v>
       </c>
       <c r="N439" s="1" t="n">
+        <v>0.04401</v>
+      </c>
+      <c r="O439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="O439" s="1" t="n">
-        <v>0.04403</v>
+      <c r="P439" s="1" t="n">
+        <v>0.04401</v>
       </c>
     </row>
     <row r="440">
@@ -22018,10 +23338,13 @@
         <v>0.0005195</v>
       </c>
       <c r="N440" s="1" t="n">
+        <v>0.000518</v>
+      </c>
+      <c r="O440" s="1" t="n">
         <v>0.0005258</v>
       </c>
-      <c r="O440" s="1" t="n">
-        <v>0.0005188</v>
+      <c r="P440" s="1" t="n">
+        <v>0.000518</v>
       </c>
     </row>
     <row r="441">
@@ -22067,9 +23390,12 @@
         <v>0.04467</v>
       </c>
       <c r="N441" s="1" t="n">
-        <v>0.04489</v>
+        <v>0.04546</v>
       </c>
       <c r="O441" s="1" t="n">
+        <v>0.04546</v>
+      </c>
+      <c r="P441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -22116,9 +23442,12 @@
         <v>0.000413</v>
       </c>
       <c r="N442" s="1" t="n">
+        <v>0.000414</v>
+      </c>
+      <c r="O442" s="1" t="n">
         <v>0.000416</v>
       </c>
-      <c r="O442" s="1" t="n">
+      <c r="P442" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -22165,10 +23494,13 @@
         <v>0.09467</v>
       </c>
       <c r="N443" s="1" t="n">
+        <v>0.09419</v>
+      </c>
+      <c r="O443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="O443" s="1" t="n">
-        <v>0.09467</v>
+      <c r="P443" s="1" t="n">
+        <v>0.09419</v>
       </c>
     </row>
     <row r="444">
@@ -22214,9 +23546,12 @@
         <v>2.303</v>
       </c>
       <c r="N444" s="1" t="n">
+        <v>2.299</v>
+      </c>
+      <c r="O444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="O444" s="1" t="n">
+      <c r="P444" s="1" t="n">
         <v>2.289</v>
       </c>
     </row>
@@ -22263,9 +23598,12 @@
         <v>0.2685</v>
       </c>
       <c r="N445" s="1" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="O445" s="1" t="n">
         <v>0.2741</v>
       </c>
-      <c r="O445" s="1" t="n">
+      <c r="P445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -22312,10 +23650,13 @@
         <v>0.0007434</v>
       </c>
       <c r="N446" s="1" t="n">
+        <v>0.000741</v>
+      </c>
+      <c r="O446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="O446" s="1" t="n">
-        <v>0.0007415</v>
+      <c r="P446" s="1" t="n">
+        <v>0.000741</v>
       </c>
     </row>
     <row r="447">
@@ -22361,10 +23702,13 @@
         <v>0.03812</v>
       </c>
       <c r="N447" s="1" t="n">
+        <v>0.03807</v>
+      </c>
+      <c r="O447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="O447" s="1" t="n">
-        <v>0.03812</v>
+      <c r="P447" s="1" t="n">
+        <v>0.03807</v>
       </c>
     </row>
     <row r="448">
@@ -22410,9 +23754,12 @@
         <v>0.1778</v>
       </c>
       <c r="N448" s="1" t="n">
+        <v>0.1766</v>
+      </c>
+      <c r="O448" s="1" t="n">
         <v>0.1783</v>
       </c>
-      <c r="O448" s="1" t="n">
+      <c r="P448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -22459,9 +23806,12 @@
         <v>0.04288</v>
       </c>
       <c r="N449" s="1" t="n">
+        <v>0.04278</v>
+      </c>
+      <c r="O449" s="1" t="n">
         <v>0.04301</v>
       </c>
-      <c r="O449" s="1" t="n">
+      <c r="P449" s="1" t="n">
         <v>0.0426</v>
       </c>
     </row>
@@ -22508,9 +23858,12 @@
         <v>0.0001643</v>
       </c>
       <c r="N450" s="1" t="n">
+        <v>0.0001641</v>
+      </c>
+      <c r="O450" s="1" t="n">
         <v>0.0001654</v>
       </c>
-      <c r="O450" s="1" t="n">
+      <c r="P450" s="1" t="n">
         <v>0.0001632</v>
       </c>
     </row>
@@ -22557,10 +23910,13 @@
         <v>0.03734</v>
       </c>
       <c r="N451" s="1" t="n">
+        <v>0.03708</v>
+      </c>
+      <c r="O451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="O451" s="1" t="n">
-        <v>0.03734</v>
+      <c r="P451" s="1" t="n">
+        <v>0.03708</v>
       </c>
     </row>
     <row r="452">
@@ -22606,10 +23962,13 @@
         <v>0.00976</v>
       </c>
       <c r="N452" s="1" t="n">
+        <v>0.009730000000000001</v>
+      </c>
+      <c r="O452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="O452" s="1" t="n">
-        <v>0.00976</v>
+      <c r="P452" s="1" t="n">
+        <v>0.009730000000000001</v>
       </c>
     </row>
     <row r="453">
@@ -22655,9 +24014,12 @@
         <v>0.06789000000000001</v>
       </c>
       <c r="N453" s="1" t="n">
+        <v>0.06797</v>
+      </c>
+      <c r="O453" s="1" t="n">
         <v>0.06816</v>
       </c>
-      <c r="O453" s="1" t="n">
+      <c r="P453" s="1" t="n">
         <v>0.06782000000000001</v>
       </c>
     </row>
@@ -22704,10 +24066,13 @@
         <v>0.007524</v>
       </c>
       <c r="N454" s="1" t="n">
+        <v>0.00749</v>
+      </c>
+      <c r="O454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="O454" s="1" t="n">
-        <v>0.007494</v>
+      <c r="P454" s="1" t="n">
+        <v>0.00749</v>
       </c>
     </row>
     <row r="455">
@@ -22753,10 +24118,13 @@
         <v>0.003298</v>
       </c>
       <c r="N455" s="1" t="n">
+        <v>0.003278</v>
+      </c>
+      <c r="O455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="O455" s="1" t="n">
-        <v>0.003298</v>
+      <c r="P455" s="1" t="n">
+        <v>0.003278</v>
       </c>
     </row>
     <row r="456">
@@ -22802,9 +24170,12 @@
         <v>0.001848</v>
       </c>
       <c r="N456" s="1" t="n">
+        <v>0.001842</v>
+      </c>
+      <c r="O456" s="1" t="n">
         <v>0.001875</v>
       </c>
-      <c r="O456" s="1" t="n">
+      <c r="P456" s="1" t="n">
         <v>0.001842</v>
       </c>
     </row>
@@ -22851,9 +24222,12 @@
         <v>0.0001752</v>
       </c>
       <c r="N457" s="1" t="n">
+        <v>0.0001746</v>
+      </c>
+      <c r="O457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="O457" s="1" t="n">
+      <c r="P457" s="1" t="n">
         <v>0.0001745</v>
       </c>
     </row>
@@ -22900,9 +24274,12 @@
         <v>0.00039</v>
       </c>
       <c r="N458" s="1" t="n">
+        <v>0.0003891</v>
+      </c>
+      <c r="O458" s="1" t="n">
         <v>0.0003916</v>
       </c>
-      <c r="O458" s="1" t="n">
+      <c r="P458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -22949,9 +24326,12 @@
         <v>0.01398</v>
       </c>
       <c r="N459" s="1" t="n">
+        <v>0.01392</v>
+      </c>
+      <c r="O459" s="1" t="n">
         <v>0.01413</v>
       </c>
-      <c r="O459" s="1" t="n">
+      <c r="P459" s="1" t="n">
         <v>0.01391</v>
       </c>
     </row>
@@ -22998,9 +24378,12 @@
         <v>0.04586</v>
       </c>
       <c r="N460" s="1" t="n">
+        <v>0.04576</v>
+      </c>
+      <c r="O460" s="1" t="n">
         <v>0.04586</v>
       </c>
-      <c r="O460" s="1" t="n">
+      <c r="P460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -23047,9 +24430,12 @@
         <v>0.2821</v>
       </c>
       <c r="N461" s="1" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="O461" s="1" t="n">
         <v>0.2839</v>
       </c>
-      <c r="O461" s="1" t="n">
+      <c r="P461" s="1" t="n">
         <v>0.2809</v>
       </c>
     </row>
@@ -23096,9 +24482,12 @@
         <v>0.006261</v>
       </c>
       <c r="N462" s="1" t="n">
+        <v>0.006254</v>
+      </c>
+      <c r="O462" s="1" t="n">
         <v>0.006312</v>
       </c>
-      <c r="O462" s="1" t="n">
+      <c r="P462" s="1" t="n">
         <v>0.00622</v>
       </c>
     </row>
@@ -23145,10 +24534,13 @@
         <v>0.007045</v>
       </c>
       <c r="N463" s="1" t="n">
+        <v>0.007024</v>
+      </c>
+      <c r="O463" s="1" t="n">
         <v>0.007088</v>
       </c>
-      <c r="O463" s="1" t="n">
-        <v>0.007032</v>
+      <c r="P463" s="1" t="n">
+        <v>0.007024</v>
       </c>
     </row>
     <row r="464">
@@ -23194,9 +24586,12 @@
         <v>0.2886</v>
       </c>
       <c r="N464" s="1" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="O464" s="1" t="n">
         <v>0.2888</v>
       </c>
-      <c r="O464" s="1" t="n">
+      <c r="P464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -23243,9 +24638,12 @@
         <v>0.08053</v>
       </c>
       <c r="N465" s="1" t="n">
+        <v>0.08058</v>
+      </c>
+      <c r="O465" s="1" t="n">
         <v>0.08183</v>
       </c>
-      <c r="O465" s="1" t="n">
+      <c r="P465" s="1" t="n">
         <v>0.08053</v>
       </c>
     </row>
@@ -23292,9 +24690,12 @@
         <v>0.6368</v>
       </c>
       <c r="N466" s="1" t="n">
-        <v>0.6369</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="O466" s="1" t="n">
+        <v>0.6375999999999999</v>
+      </c>
+      <c r="P466" s="1" t="n">
         <v>0.6318</v>
       </c>
     </row>
@@ -23341,9 +24742,12 @@
         <v>0.01476</v>
       </c>
       <c r="N467" s="1" t="n">
+        <v>0.01472</v>
+      </c>
+      <c r="O467" s="1" t="n">
         <v>0.01499</v>
       </c>
-      <c r="O467" s="1" t="n">
+      <c r="P467" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -23390,9 +24794,12 @@
         <v>0.03458</v>
       </c>
       <c r="N468" s="1" t="n">
+        <v>0.03452</v>
+      </c>
+      <c r="O468" s="1" t="n">
         <v>0.03468</v>
       </c>
-      <c r="O468" s="1" t="n">
+      <c r="P468" s="1" t="n">
         <v>0.03434</v>
       </c>
     </row>
@@ -23439,10 +24846,13 @@
         <v>0.1627</v>
       </c>
       <c r="N469" s="1" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="O469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="O469" s="1" t="n">
-        <v>0.1624</v>
+      <c r="P469" s="1" t="n">
+        <v>0.1619</v>
       </c>
     </row>
     <row r="470">
@@ -23488,9 +24898,12 @@
         <v>0.4105</v>
       </c>
       <c r="N470" s="1" t="n">
+        <v>0.4087</v>
+      </c>
+      <c r="O470" s="1" t="n">
         <v>0.4151</v>
       </c>
-      <c r="O470" s="1" t="n">
+      <c r="P470" s="1" t="n">
         <v>0.4085</v>
       </c>
     </row>
@@ -23537,10 +24950,13 @@
         <v>0.06884</v>
       </c>
       <c r="N471" s="1" t="n">
+        <v>0.06874</v>
+      </c>
+      <c r="O471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="O471" s="1" t="n">
-        <v>0.06884</v>
+      <c r="P471" s="1" t="n">
+        <v>0.06874</v>
       </c>
     </row>
     <row r="472">
@@ -23586,10 +25002,13 @@
         <v>0.06643</v>
       </c>
       <c r="N472" s="1" t="n">
+        <v>0.06612999999999999</v>
+      </c>
+      <c r="O472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="O472" s="1" t="n">
-        <v>0.06619</v>
+      <c r="P472" s="1" t="n">
+        <v>0.06612999999999999</v>
       </c>
     </row>
     <row r="473">
@@ -23635,9 +25054,12 @@
         <v>0.01624</v>
       </c>
       <c r="N473" s="1" t="n">
+        <v>0.01623</v>
+      </c>
+      <c r="O473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="O473" s="1" t="n">
+      <c r="P473" s="1" t="n">
         <v>0.01621</v>
       </c>
     </row>
@@ -23684,9 +25106,12 @@
         <v>0.2068</v>
       </c>
       <c r="N474" s="1" t="n">
+        <v>0.2061</v>
+      </c>
+      <c r="O474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="O474" s="1" t="n">
+      <c r="P474" s="1" t="n">
         <v>0.2061</v>
       </c>
     </row>
@@ -23733,9 +25158,12 @@
         <v>0.04246</v>
       </c>
       <c r="N475" s="1" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="O475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="O475" s="1" t="n">
+      <c r="P475" s="1" t="n">
         <v>0.042</v>
       </c>
     </row>
@@ -23782,10 +25210,13 @@
         <v>1.564</v>
       </c>
       <c r="N476" s="1" t="n">
+        <v>1.559</v>
+      </c>
+      <c r="O476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="O476" s="1" t="n">
-        <v>1.561</v>
+      <c r="P476" s="1" t="n">
+        <v>1.559</v>
       </c>
     </row>
     <row r="477">
@@ -23831,10 +25262,13 @@
         <v>0.1008</v>
       </c>
       <c r="N477" s="1" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="O477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="O477" s="1" t="n">
-        <v>0.1003</v>
+      <c r="P477" s="1" t="n">
+        <v>0.1002</v>
       </c>
     </row>
     <row r="478">
@@ -23880,9 +25314,12 @@
         <v>0.001155</v>
       </c>
       <c r="N478" s="1" t="n">
+        <v>0.001152</v>
+      </c>
+      <c r="O478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="O478" s="1" t="n">
+      <c r="P478" s="1" t="n">
         <v>0.00115</v>
       </c>
     </row>
@@ -23929,10 +25366,13 @@
         <v>0.1445</v>
       </c>
       <c r="N479" s="1" t="n">
+        <v>0.1439</v>
+      </c>
+      <c r="O479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="O479" s="1" t="n">
-        <v>0.1442</v>
+      <c r="P479" s="1" t="n">
+        <v>0.1439</v>
       </c>
     </row>
     <row r="480">
@@ -23978,9 +25418,12 @@
         <v>0.001724</v>
       </c>
       <c r="N480" s="1" t="n">
+        <v>0.001722</v>
+      </c>
+      <c r="O480" s="1" t="n">
         <v>0.001734</v>
       </c>
-      <c r="O480" s="1" t="n">
+      <c r="P480" s="1" t="n">
         <v>0.001719</v>
       </c>
     </row>
@@ -24027,9 +25470,12 @@
         <v>0.912</v>
       </c>
       <c r="N481" s="1" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="O481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="O481" s="1" t="n">
+      <c r="P481" s="1" t="n">
         <v>0.908</v>
       </c>
     </row>
@@ -24076,10 +25522,13 @@
         <v>0.13375</v>
       </c>
       <c r="N482" s="1" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="O482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="O482" s="1" t="n">
-        <v>0.13336</v>
+      <c r="P482" s="1" t="n">
+        <v>0.1333</v>
       </c>
     </row>
     <row r="483">
@@ -24125,10 +25574,13 @@
         <v>0.04027</v>
       </c>
       <c r="N483" s="1" t="n">
+        <v>0.04013</v>
+      </c>
+      <c r="O483" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="O483" s="1" t="n">
-        <v>0.04023</v>
+      <c r="P483" s="1" t="n">
+        <v>0.04013</v>
       </c>
     </row>
     <row r="484">
@@ -24174,9 +25626,12 @@
         <v>0.3021</v>
       </c>
       <c r="N484" s="1" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="O484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="O484" s="1" t="n">
+      <c r="P484" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -24223,9 +25678,12 @@
         <v>0.05658</v>
       </c>
       <c r="N485" s="1" t="n">
+        <v>0.05661</v>
+      </c>
+      <c r="O485" s="1" t="n">
         <v>0.05709</v>
       </c>
-      <c r="O485" s="1" t="n">
+      <c r="P485" s="1" t="n">
         <v>0.05603</v>
       </c>
     </row>
@@ -24272,9 +25730,12 @@
         <v>0.001566</v>
       </c>
       <c r="N486" s="1" t="n">
+        <v>0.001563</v>
+      </c>
+      <c r="O486" s="1" t="n">
         <v>0.001579</v>
       </c>
-      <c r="O486" s="1" t="n">
+      <c r="P486" s="1" t="n">
         <v>0.001563</v>
       </c>
     </row>
@@ -24321,10 +25782,13 @@
         <v>0.06705999999999999</v>
       </c>
       <c r="N487" s="1" t="n">
+        <v>0.06686</v>
+      </c>
+      <c r="O487" s="1" t="n">
         <v>0.06766999999999999</v>
       </c>
-      <c r="O487" s="1" t="n">
-        <v>0.06702</v>
+      <c r="P487" s="1" t="n">
+        <v>0.06686</v>
       </c>
     </row>
     <row r="488">
@@ -24370,10 +25834,13 @@
         <v>0.1924</v>
       </c>
       <c r="N488" s="1" t="n">
+        <v>0.1914</v>
+      </c>
+      <c r="O488" s="1" t="n">
         <v>0.1953</v>
       </c>
-      <c r="O488" s="1" t="n">
-        <v>0.1924</v>
+      <c r="P488" s="1" t="n">
+        <v>0.1914</v>
       </c>
     </row>
     <row r="489">
@@ -24419,9 +25886,12 @@
         <v>0.04798</v>
       </c>
       <c r="N489" s="1" t="n">
+        <v>0.04779</v>
+      </c>
+      <c r="O489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="O489" s="1" t="n">
+      <c r="P489" s="1" t="n">
         <v>0.04779</v>
       </c>
     </row>
@@ -24468,9 +25938,12 @@
         <v>0.1395</v>
       </c>
       <c r="N490" s="1" t="n">
+        <v>0.1391</v>
+      </c>
+      <c r="O490" s="1" t="n">
         <v>0.1401</v>
       </c>
-      <c r="O490" s="1" t="n">
+      <c r="P490" s="1" t="n">
         <v>0.1389</v>
       </c>
     </row>
@@ -24517,10 +25990,13 @@
         <v>0.02245</v>
       </c>
       <c r="N491" s="1" t="n">
+        <v>0.02235</v>
+      </c>
+      <c r="O491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="O491" s="1" t="n">
-        <v>0.02243</v>
+      <c r="P491" s="1" t="n">
+        <v>0.02235</v>
       </c>
     </row>
     <row r="492">
@@ -24566,9 +26042,12 @@
         <v>0.007795</v>
       </c>
       <c r="N492" s="1" t="n">
+        <v>0.007757</v>
+      </c>
+      <c r="O492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="O492" s="1" t="n">
+      <c r="P492" s="1" t="n">
         <v>0.007746</v>
       </c>
     </row>
@@ -24615,10 +26094,13 @@
         <v>0.0005938</v>
       </c>
       <c r="N493" s="1" t="n">
+        <v>0.0005918</v>
+      </c>
+      <c r="O493" s="1" t="n">
         <v>0.0005992</v>
       </c>
-      <c r="O493" s="1" t="n">
-        <v>0.0005926</v>
+      <c r="P493" s="1" t="n">
+        <v>0.0005918</v>
       </c>
     </row>
     <row r="494">
@@ -24664,9 +26146,12 @@
         <v>3.027</v>
       </c>
       <c r="N494" s="1" t="n">
+        <v>3.026</v>
+      </c>
+      <c r="O494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="O494" s="1" t="n">
+      <c r="P494" s="1" t="n">
         <v>2.999</v>
       </c>
     </row>
@@ -24713,9 +26198,12 @@
         <v>0.05082</v>
       </c>
       <c r="N495" s="1" t="n">
+        <v>0.05061</v>
+      </c>
+      <c r="O495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="O495" s="1" t="n">
+      <c r="P495" s="1" t="n">
         <v>0.05042</v>
       </c>
     </row>
@@ -24762,9 +26250,12 @@
         <v>0.006824</v>
       </c>
       <c r="N496" s="1" t="n">
+        <v>0.006797</v>
+      </c>
+      <c r="O496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="O496" s="1" t="n">
+      <c r="P496" s="1" t="n">
         <v>0.006742</v>
       </c>
     </row>
@@ -24811,9 +26302,12 @@
         <v>1.303</v>
       </c>
       <c r="N497" s="1" t="n">
+        <v>1.303</v>
+      </c>
+      <c r="O497" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="O497" s="1" t="n">
+      <c r="P497" s="1" t="n">
         <v>1.299</v>
       </c>
     </row>
@@ -24860,9 +26354,12 @@
         <v>0.03949</v>
       </c>
       <c r="N498" s="1" t="n">
+        <v>0.03936</v>
+      </c>
+      <c r="O498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="O498" s="1" t="n">
+      <c r="P498" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -24909,9 +26406,12 @@
         <v>0.04133</v>
       </c>
       <c r="N499" s="1" t="n">
+        <v>0.0411</v>
+      </c>
+      <c r="O499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="O499" s="1" t="n">
+      <c r="P499" s="1" t="n">
         <v>0.04101</v>
       </c>
     </row>
@@ -24958,9 +26458,12 @@
         <v>0.00546</v>
       </c>
       <c r="N500" s="1" t="n">
+        <v>0.00547</v>
+      </c>
+      <c r="O500" s="1" t="n">
         <v>0.00549</v>
       </c>
-      <c r="O500" s="1" t="n">
+      <c r="P500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -25007,10 +26510,13 @@
         <v>0.03579</v>
       </c>
       <c r="N501" s="1" t="n">
+        <v>0.03566</v>
+      </c>
+      <c r="O501" s="1" t="n">
         <v>0.0364</v>
       </c>
-      <c r="O501" s="1" t="n">
-        <v>0.03571</v>
+      <c r="P501" s="1" t="n">
+        <v>0.03566</v>
       </c>
     </row>
     <row r="502">
@@ -25056,9 +26562,12 @@
         <v>0.07227</v>
       </c>
       <c r="N502" s="1" t="n">
+        <v>0.07232</v>
+      </c>
+      <c r="O502" s="1" t="n">
         <v>0.07342</v>
       </c>
-      <c r="O502" s="1" t="n">
+      <c r="P502" s="1" t="n">
         <v>0.07227</v>
       </c>
     </row>
@@ -25105,10 +26614,13 @@
         <v>0.0007439</v>
       </c>
       <c r="N503" s="1" t="n">
+        <v>0.0007412</v>
+      </c>
+      <c r="O503" s="1" t="n">
         <v>0.000755</v>
       </c>
-      <c r="O503" s="1" t="n">
-        <v>0.0007422</v>
+      <c r="P503" s="1" t="n">
+        <v>0.0007412</v>
       </c>
     </row>
     <row r="504">
@@ -25154,9 +26666,12 @@
         <v>0.016002</v>
       </c>
       <c r="N504" s="1" t="n">
+        <v>0.015988</v>
+      </c>
+      <c r="O504" s="1" t="n">
         <v>0.016016</v>
       </c>
-      <c r="O504" s="1" t="n">
+      <c r="P504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -25203,9 +26718,12 @@
         <v>0.00704</v>
       </c>
       <c r="N505" s="1" t="n">
+        <v>0.00703</v>
+      </c>
+      <c r="O505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="O505" s="1" t="n">
+      <c r="P505" s="1" t="n">
         <v>0.00703</v>
       </c>
     </row>
@@ -25252,9 +26770,12 @@
         <v>0.0255</v>
       </c>
       <c r="N506" s="1" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="O506" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="O506" s="1" t="n">
+      <c r="P506" s="1" t="n">
         <v>0.0255</v>
       </c>
     </row>
@@ -25301,9 +26822,12 @@
         <v>0.001354</v>
       </c>
       <c r="N507" s="1" t="n">
+        <v>0.001345</v>
+      </c>
+      <c r="O507" s="1" t="n">
         <v>0.00136</v>
       </c>
-      <c r="O507" s="1" t="n">
+      <c r="P507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -25350,9 +26874,12 @@
         <v>0.2816</v>
       </c>
       <c r="N508" s="1" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="O508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="O508" s="1" t="n">
+      <c r="P508" s="1" t="n">
         <v>0.2805</v>
       </c>
     </row>
@@ -25399,10 +26926,13 @@
         <v>0.1319</v>
       </c>
       <c r="N509" s="1" t="n">
+        <v>0.1314</v>
+      </c>
+      <c r="O509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="O509" s="1" t="n">
-        <v>0.1317</v>
+      <c r="P509" s="1" t="n">
+        <v>0.1314</v>
       </c>
     </row>
     <row r="510">
@@ -25448,9 +26978,12 @@
         <v>0.04927</v>
       </c>
       <c r="N510" s="1" t="n">
+        <v>0.04896</v>
+      </c>
+      <c r="O510" s="1" t="n">
         <v>0.04972</v>
       </c>
-      <c r="O510" s="1" t="n">
+      <c r="P510" s="1" t="n">
         <v>0.04896</v>
       </c>
     </row>
@@ -25497,9 +27030,12 @@
         <v>0.00273</v>
       </c>
       <c r="N511" s="1" t="n">
+        <v>0.00272</v>
+      </c>
+      <c r="O511" s="1" t="n">
         <v>0.00278</v>
       </c>
-      <c r="O511" s="1" t="n">
+      <c r="P511" s="1" t="n">
         <v>0.00272</v>
       </c>
     </row>
@@ -25546,9 +27082,12 @@
         <v>0.015206</v>
       </c>
       <c r="N512" s="1" t="n">
+        <v>0.015171</v>
+      </c>
+      <c r="O512" s="1" t="n">
         <v>0.015454</v>
       </c>
-      <c r="O512" s="1" t="n">
+      <c r="P512" s="1" t="n">
         <v>0.015017</v>
       </c>
     </row>
@@ -25595,9 +27134,12 @@
         <v>0.6918</v>
       </c>
       <c r="N513" s="1" t="n">
+        <v>0.6925</v>
+      </c>
+      <c r="O513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="O513" s="1" t="n">
+      <c r="P513" s="1" t="n">
         <v>0.6899</v>
       </c>
     </row>
@@ -25644,10 +27186,13 @@
         <v>0.004528</v>
       </c>
       <c r="N514" s="1" t="n">
+        <v>0.004515</v>
+      </c>
+      <c r="O514" s="1" t="n">
         <v>0.004589</v>
       </c>
-      <c r="O514" s="1" t="n">
-        <v>0.004517</v>
+      <c r="P514" s="1" t="n">
+        <v>0.004515</v>
       </c>
     </row>
     <row r="515">
@@ -25693,9 +27238,12 @@
         <v>0.005019</v>
       </c>
       <c r="N515" s="1" t="n">
+        <v>0.005009</v>
+      </c>
+      <c r="O515" s="1" t="n">
         <v>0.005066</v>
       </c>
-      <c r="O515" s="1" t="n">
+      <c r="P515" s="1" t="n">
         <v>0.005008</v>
       </c>
     </row>
@@ -25742,9 +27290,12 @@
         <v>0.06343</v>
       </c>
       <c r="N516" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="O516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="O516" s="1" t="n">
+      <c r="P516" s="1" t="n">
         <v>0.06320000000000001</v>
       </c>
     </row>
@@ -25791,9 +27342,12 @@
         <v>0.06489</v>
       </c>
       <c r="N517" s="1" t="n">
+        <v>0.06476999999999999</v>
+      </c>
+      <c r="O517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="O517" s="1" t="n">
+      <c r="P517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -25840,9 +27394,12 @@
         <v>0.01203</v>
       </c>
       <c r="N518" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="O518" s="1" t="n">
         <v>0.01219</v>
       </c>
-      <c r="O518" s="1" t="n">
+      <c r="P518" s="1" t="n">
         <v>0.01199</v>
       </c>
     </row>
@@ -25889,9 +27446,12 @@
         <v>0.04767</v>
       </c>
       <c r="N519" s="1" t="n">
+        <v>0.04753</v>
+      </c>
+      <c r="O519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="O519" s="1" t="n">
+      <c r="P519" s="1" t="n">
         <v>0.04743</v>
       </c>
     </row>
@@ -25938,9 +27498,12 @@
         <v>0.04381</v>
       </c>
       <c r="N520" s="1" t="n">
+        <v>0.04365</v>
+      </c>
+      <c r="O520" s="1" t="n">
         <v>0.04411</v>
       </c>
-      <c r="O520" s="1" t="n">
+      <c r="P520" s="1" t="n">
         <v>0.04349</v>
       </c>
     </row>
@@ -25987,9 +27550,12 @@
         <v>0.008469000000000001</v>
       </c>
       <c r="N521" s="1" t="n">
+        <v>0.00844</v>
+      </c>
+      <c r="O521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="O521" s="1" t="n">
+      <c r="P521" s="1" t="n">
         <v>0.008411999999999999</v>
       </c>
     </row>
@@ -26036,9 +27602,12 @@
         <v>0.08817</v>
       </c>
       <c r="N522" s="1" t="n">
+        <v>0.0881</v>
+      </c>
+      <c r="O522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="O522" s="1" t="n">
+      <c r="P522" s="1" t="n">
         <v>0.08787</v>
       </c>
     </row>
@@ -26085,9 +27654,12 @@
         <v>0.006451</v>
       </c>
       <c r="N523" s="1" t="n">
+        <v>0.006435</v>
+      </c>
+      <c r="O523" s="1" t="n">
         <v>0.006492</v>
       </c>
-      <c r="O523" s="1" t="n">
+      <c r="P523" s="1" t="n">
         <v>0.006433</v>
       </c>
     </row>
@@ -26134,10 +27706,13 @@
         <v>0.01644</v>
       </c>
       <c r="N524" s="1" t="n">
+        <v>0.01635</v>
+      </c>
+      <c r="O524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="O524" s="1" t="n">
-        <v>0.01641</v>
+      <c r="P524" s="1" t="n">
+        <v>0.01635</v>
       </c>
     </row>
     <row r="525">
@@ -26183,9 +27758,12 @@
         <v>0.01786</v>
       </c>
       <c r="N525" s="1" t="n">
+        <v>0.01781</v>
+      </c>
+      <c r="O525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="O525" s="1" t="n">
+      <c r="P525" s="1" t="n">
         <v>0.01779</v>
       </c>
     </row>
@@ -26232,9 +27810,12 @@
         <v>0.07922</v>
       </c>
       <c r="N526" s="1" t="n">
+        <v>0.07892</v>
+      </c>
+      <c r="O526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="O526" s="1" t="n">
+      <c r="P526" s="1" t="n">
         <v>0.07883</v>
       </c>
     </row>
@@ -26281,10 +27862,13 @@
         <v>0.01604</v>
       </c>
       <c r="N527" s="1" t="n">
+        <v>0.01594</v>
+      </c>
+      <c r="O527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="O527" s="1" t="n">
-        <v>0.01603</v>
+      <c r="P527" s="1" t="n">
+        <v>0.01594</v>
       </c>
     </row>
     <row r="528">
@@ -26330,9 +27914,12 @@
         <v>0.004182</v>
       </c>
       <c r="N528" s="1" t="n">
+        <v>0.004164</v>
+      </c>
+      <c r="O528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="O528" s="1" t="n">
+      <c r="P528" s="1" t="n">
         <v>0.004164</v>
       </c>
     </row>
@@ -26379,9 +27966,12 @@
         <v>0.003712</v>
       </c>
       <c r="N529" s="1" t="n">
+        <v>0.003706</v>
+      </c>
+      <c r="O529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="O529" s="1" t="n">
+      <c r="P529" s="1" t="n">
         <v>0.00369</v>
       </c>
     </row>
@@ -26428,9 +28018,12 @@
         <v>1.329</v>
       </c>
       <c r="N530" s="1" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="O530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="O530" s="1" t="n">
+      <c r="P530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -26477,10 +28070,13 @@
         <v>0.4899</v>
       </c>
       <c r="N531" s="1" t="n">
+        <v>0.4882</v>
+      </c>
+      <c r="O531" s="1" t="n">
         <v>0.494</v>
       </c>
-      <c r="O531" s="1" t="n">
-        <v>0.4893</v>
+      <c r="P531" s="1" t="n">
+        <v>0.4882</v>
       </c>
     </row>
     <row r="532">
@@ -26526,9 +28122,12 @@
         <v>0.03064</v>
       </c>
       <c r="N532" s="1" t="n">
+        <v>0.03061</v>
+      </c>
+      <c r="O532" s="1" t="n">
         <v>0.03091</v>
       </c>
-      <c r="O532" s="1" t="n">
+      <c r="P532" s="1" t="n">
         <v>0.03058</v>
       </c>
     </row>
@@ -26575,10 +28174,13 @@
         <v>0.1531</v>
       </c>
       <c r="N533" s="1" t="n">
+        <v>0.1524</v>
+      </c>
+      <c r="O533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="O533" s="1" t="n">
-        <v>0.153</v>
+      <c r="P533" s="1" t="n">
+        <v>0.1524</v>
       </c>
     </row>
     <row r="534">
@@ -26624,9 +28226,12 @@
         <v>0.0538</v>
       </c>
       <c r="N534" s="1" t="n">
+        <v>0.05374</v>
+      </c>
+      <c r="O534" s="1" t="n">
         <v>0.05424</v>
       </c>
-      <c r="O534" s="1" t="n">
+      <c r="P534" s="1" t="n">
         <v>0.0536</v>
       </c>
     </row>
@@ -26673,10 +28278,13 @@
         <v>0.01494</v>
       </c>
       <c r="N535" s="1" t="n">
+        <v>0.01489</v>
+      </c>
+      <c r="O535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="O535" s="1" t="n">
-        <v>0.0149</v>
+      <c r="P535" s="1" t="n">
+        <v>0.01489</v>
       </c>
     </row>
     <row r="536">
@@ -26722,9 +28330,12 @@
         <v>0.05899</v>
       </c>
       <c r="N536" s="1" t="n">
+        <v>0.0589</v>
+      </c>
+      <c r="O536" s="1" t="n">
         <v>0.05909</v>
       </c>
-      <c r="O536" s="1" t="n">
+      <c r="P536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -26771,9 +28382,12 @@
         <v>0.05487</v>
       </c>
       <c r="N537" s="1" t="n">
+        <v>0.05484</v>
+      </c>
+      <c r="O537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="O537" s="1" t="n">
+      <c r="P537" s="1" t="n">
         <v>0.05481</v>
       </c>
     </row>
@@ -26820,9 +28434,12 @@
         <v>0.1061</v>
       </c>
       <c r="N538" s="1" t="n">
+        <v>0.1058</v>
+      </c>
+      <c r="O538" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="O538" s="1" t="n">
+      <c r="P538" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -26869,9 +28486,12 @@
         <v>0.01278</v>
       </c>
       <c r="N539" s="1" t="n">
+        <v>0.01274</v>
+      </c>
+      <c r="O539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="O539" s="1" t="n">
+      <c r="P539" s="1" t="n">
         <v>0.01273</v>
       </c>
     </row>
@@ -26918,10 +28538,13 @@
         <v>0.1741</v>
       </c>
       <c r="N540" s="1" t="n">
+        <v>0.1736</v>
+      </c>
+      <c r="O540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="O540" s="1" t="n">
-        <v>0.174</v>
+      <c r="P540" s="1" t="n">
+        <v>0.1736</v>
       </c>
     </row>
     <row r="541">
@@ -26967,10 +28590,13 @@
         <v>0.1226</v>
       </c>
       <c r="N541" s="1" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="O541" s="1" t="n">
         <v>0.1239</v>
       </c>
-      <c r="O541" s="1" t="n">
-        <v>0.1226</v>
+      <c r="P541" s="1" t="n">
+        <v>0.1225</v>
       </c>
     </row>
     <row r="542">
@@ -27016,9 +28642,12 @@
         <v>0.02485</v>
       </c>
       <c r="N542" s="1" t="n">
+        <v>0.02485</v>
+      </c>
+      <c r="O542" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="O542" s="1" t="n">
+      <c r="P542" s="1" t="n">
         <v>0.02481</v>
       </c>
     </row>
@@ -27065,9 +28694,12 @@
         <v>0.05872</v>
       </c>
       <c r="N543" s="1" t="n">
+        <v>0.05869</v>
+      </c>
+      <c r="O543" s="1" t="n">
         <v>0.059</v>
       </c>
-      <c r="O543" s="1" t="n">
+      <c r="P543" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P543"/>
+  <dimension ref="A1:Q543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -433,8 +433,9 @@
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
     <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -510,10 +511,15 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>price_03:15</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -565,9 +571,12 @@
         <v>71020</v>
       </c>
       <c r="O2" s="1" t="n">
+        <v>71187.10000000001</v>
+      </c>
+      <c r="P2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="P2" s="1" t="n">
+      <c r="Q2" s="1" t="n">
         <v>70995.10000000001</v>
       </c>
     </row>
@@ -617,9 +626,12 @@
         <v>2099.88</v>
       </c>
       <c r="O3" s="1" t="n">
+        <v>2103.06</v>
+      </c>
+      <c r="P3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="P3" s="1" t="n">
+      <c r="Q3" s="1" t="n">
         <v>2099.88</v>
       </c>
     </row>
@@ -669,10 +681,13 @@
         <v>88.77</v>
       </c>
       <c r="O4" s="1" t="n">
+        <v>88.70999999999999</v>
+      </c>
+      <c r="P4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="P4" s="1" t="n">
-        <v>88.77</v>
+      <c r="Q4" s="1" t="n">
+        <v>88.70999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -721,9 +736,12 @@
         <v>3.766</v>
       </c>
       <c r="O5" s="1" t="n">
+        <v>3.803</v>
+      </c>
+      <c r="P5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="P5" s="1" t="n">
+      <c r="Q5" s="1" t="n">
         <v>3.766</v>
       </c>
     </row>
@@ -773,9 +791,12 @@
         <v>1.3965</v>
       </c>
       <c r="O6" s="1" t="n">
+        <v>1.3989</v>
+      </c>
+      <c r="P6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="P6" s="1" t="n">
+      <c r="Q6" s="1" t="n">
         <v>1.3931</v>
       </c>
     </row>
@@ -825,9 +846,12 @@
         <v>0.0958</v>
       </c>
       <c r="O7" s="1" t="n">
+        <v>0.09588000000000001</v>
+      </c>
+      <c r="P7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="P7" s="1" t="n">
+      <c r="Q7" s="1" t="n">
         <v>0.0958</v>
       </c>
     </row>
@@ -877,9 +901,12 @@
         <v>0.014091</v>
       </c>
       <c r="O8" s="1" t="n">
+        <v>0.014259</v>
+      </c>
+      <c r="P8" s="1" t="n">
         <v>0.014819</v>
       </c>
-      <c r="P8" s="1" t="n">
+      <c r="Q8" s="1" t="n">
         <v>0.014064</v>
       </c>
     </row>
@@ -929,9 +956,12 @@
         <v>656.88</v>
       </c>
       <c r="O9" s="1" t="n">
+        <v>657.67</v>
+      </c>
+      <c r="P9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="P9" s="1" t="n">
+      <c r="Q9" s="1" t="n">
         <v>655.72</v>
       </c>
     </row>
@@ -981,9 +1011,12 @@
         <v>19.819</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>20.23</v>
+        <v>20.288</v>
       </c>
       <c r="P10" s="1" t="n">
+        <v>20.288</v>
+      </c>
+      <c r="Q10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -1033,10 +1066,13 @@
         <v>0.0033976</v>
       </c>
       <c r="O11" s="1" t="n">
+        <v>0.003395</v>
+      </c>
+      <c r="P11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="P11" s="1" t="n">
-        <v>0.0033976</v>
+      <c r="Q11" s="1" t="n">
+        <v>0.003395</v>
       </c>
     </row>
     <row r="12">
@@ -1085,9 +1121,12 @@
         <v>36.554</v>
       </c>
       <c r="O12" s="1" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="P12" s="1" t="n">
         <v>36.704</v>
       </c>
-      <c r="P12" s="1" t="n">
+      <c r="Q12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -1137,9 +1176,12 @@
         <v>213.88</v>
       </c>
       <c r="O13" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="P13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="P13" s="1" t="n">
+      <c r="Q13" s="1" t="n">
         <v>212.33</v>
       </c>
     </row>
@@ -1189,9 +1231,12 @@
         <v>0.0011181</v>
       </c>
       <c r="O14" s="1" t="n">
+        <v>0.0011196</v>
+      </c>
+      <c r="P14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="P14" s="1" t="n">
+      <c r="Q14" s="1" t="n">
         <v>0.0011136</v>
       </c>
     </row>
@@ -1241,9 +1286,12 @@
         <v>0.29971</v>
       </c>
       <c r="O15" s="1" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="P15" s="1" t="n">
         <v>0.30332</v>
       </c>
-      <c r="P15" s="1" t="n">
+      <c r="Q15" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -1293,9 +1341,12 @@
         <v>231.89</v>
       </c>
       <c r="O16" s="1" t="n">
+        <v>231.75</v>
+      </c>
+      <c r="P16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="P16" s="1" t="n">
+      <c r="Q16" s="1" t="n">
         <v>230.3</v>
       </c>
     </row>
@@ -1345,9 +1396,12 @@
         <v>0.9991</v>
       </c>
       <c r="O17" s="1" t="n">
+        <v>0.9995000000000001</v>
+      </c>
+      <c r="P17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="P17" s="1" t="n">
+      <c r="Q17" s="1" t="n">
         <v>0.9963</v>
       </c>
     </row>
@@ -1397,9 +1451,12 @@
         <v>0.2664</v>
       </c>
       <c r="O18" s="1" t="n">
+        <v>0.2669</v>
+      </c>
+      <c r="P18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="P18" s="1" t="n">
+      <c r="Q18" s="1" t="n">
         <v>0.2664</v>
       </c>
     </row>
@@ -1449,9 +1506,12 @@
         <v>9.772</v>
       </c>
       <c r="O19" s="1" t="n">
+        <v>9.766999999999999</v>
+      </c>
+      <c r="P19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="P19" s="1" t="n">
+      <c r="Q19" s="1" t="n">
         <v>9.755000000000001</v>
       </c>
     </row>
@@ -1501,9 +1561,12 @@
         <v>5046.6</v>
       </c>
       <c r="O20" s="1" t="n">
+        <v>5040.86</v>
+      </c>
+      <c r="P20" s="1" t="n">
         <v>5059.14</v>
       </c>
-      <c r="P20" s="1" t="n">
+      <c r="Q20" s="1" t="n">
         <v>5033.31</v>
       </c>
     </row>
@@ -1553,9 +1616,12 @@
         <v>463.97</v>
       </c>
       <c r="O21" s="1" t="n">
+        <v>464.29</v>
+      </c>
+      <c r="P21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="P21" s="1" t="n">
+      <c r="Q21" s="1" t="n">
         <v>462.36</v>
       </c>
     </row>
@@ -1605,10 +1671,13 @@
         <v>1.3961</v>
       </c>
       <c r="O22" s="1" t="n">
+        <v>1.3736</v>
+      </c>
+      <c r="P22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="P22" s="1" t="n">
-        <v>1.3961</v>
+      <c r="Q22" s="1" t="n">
+        <v>1.3736</v>
       </c>
     </row>
     <row r="23">
@@ -1657,9 +1726,12 @@
         <v>1.0422</v>
       </c>
       <c r="O23" s="1" t="n">
+        <v>1.0347</v>
+      </c>
+      <c r="P23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="P23" s="1" t="n">
+      <c r="Q23" s="1" t="n">
         <v>1.0136</v>
       </c>
     </row>
@@ -1709,9 +1781,12 @@
         <v>1.345</v>
       </c>
       <c r="O24" s="1" t="n">
+        <v>1.348</v>
+      </c>
+      <c r="P24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="P24" s="1" t="n">
+      <c r="Q24" s="1" t="n">
         <v>1.344</v>
       </c>
     </row>
@@ -1761,9 +1836,12 @@
         <v>9.124000000000001</v>
       </c>
       <c r="O25" s="1" t="n">
+        <v>9.128</v>
+      </c>
+      <c r="P25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="P25" s="1" t="n">
+      <c r="Q25" s="1" t="n">
         <v>9.124000000000001</v>
       </c>
     </row>
@@ -1813,9 +1891,12 @@
         <v>0.3695</v>
       </c>
       <c r="O26" s="1" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="P26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="P26" s="1" t="n">
+      <c r="Q26" s="1" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -1865,9 +1946,12 @@
         <v>0.877</v>
       </c>
       <c r="O27" s="1" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="P27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="P27" s="1" t="n">
+      <c r="Q27" s="1" t="n">
         <v>0.876</v>
       </c>
     </row>
@@ -1917,9 +2001,12 @@
         <v>1.841</v>
       </c>
       <c r="O28" s="1" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="P28" s="1" t="n">
         <v>1.844</v>
       </c>
-      <c r="P28" s="1" t="n">
+      <c r="Q28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -1969,10 +2056,13 @@
         <v>0.1093</v>
       </c>
       <c r="O29" s="1" t="n">
+        <v>0.1092</v>
+      </c>
+      <c r="P29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="P29" s="1" t="n">
-        <v>0.1093</v>
+      <c r="Q29" s="1" t="n">
+        <v>0.1092</v>
       </c>
     </row>
     <row r="30">
@@ -2021,9 +2111,12 @@
         <v>0.002034</v>
       </c>
       <c r="O30" s="1" t="n">
+        <v>0.002036</v>
+      </c>
+      <c r="P30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="P30" s="1" t="n">
+      <c r="Q30" s="1" t="n">
         <v>0.002034</v>
       </c>
     </row>
@@ -2073,9 +2166,12 @@
         <v>1.472</v>
       </c>
       <c r="O31" s="1" t="n">
+        <v>1.474</v>
+      </c>
+      <c r="P31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="P31" s="1" t="n">
+      <c r="Q31" s="1" t="n">
         <v>1.472</v>
       </c>
     </row>
@@ -2125,9 +2221,12 @@
         <v>0.1763</v>
       </c>
       <c r="O32" s="1" t="n">
+        <v>0.1768</v>
+      </c>
+      <c r="P32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="P32" s="1" t="n">
+      <c r="Q32" s="1" t="n">
         <v>0.1739</v>
       </c>
     </row>
@@ -2177,9 +2276,12 @@
         <v>0.1036</v>
       </c>
       <c r="O33" s="1" t="n">
+        <v>0.1036</v>
+      </c>
+      <c r="P33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="P33" s="1" t="n">
+      <c r="Q33" s="1" t="n">
         <v>0.1036</v>
       </c>
     </row>
@@ -2229,9 +2331,12 @@
         <v>112.61</v>
       </c>
       <c r="O34" s="1" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="P34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="P34" s="1" t="n">
+      <c r="Q34" s="1" t="n">
         <v>112.61</v>
       </c>
     </row>
@@ -2281,9 +2386,12 @@
         <v>6.587</v>
       </c>
       <c r="O35" s="1" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="P35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="P35" s="1" t="n">
+      <c r="Q35" s="1" t="n">
         <v>6.587</v>
       </c>
     </row>
@@ -2333,9 +2441,12 @@
         <v>0.017342</v>
       </c>
       <c r="O36" s="1" t="n">
-        <v>0.017421</v>
+        <v>0.017561</v>
       </c>
       <c r="P36" s="1" t="n">
+        <v>0.017561</v>
+      </c>
+      <c r="Q36" s="1" t="n">
         <v>0.016815</v>
       </c>
     </row>
@@ -2385,9 +2496,12 @@
         <v>0.36</v>
       </c>
       <c r="O37" s="1" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="P37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="P37" s="1" t="n">
+      <c r="Q37" s="1" t="n">
         <v>0.36</v>
       </c>
     </row>
@@ -2437,9 +2551,12 @@
         <v>55.34</v>
       </c>
       <c r="O38" s="1" t="n">
+        <v>55.48</v>
+      </c>
+      <c r="P38" s="1" t="n">
         <v>55.79</v>
       </c>
-      <c r="P38" s="1" t="n">
+      <c r="Q38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -2489,9 +2606,12 @@
         <v>0.59954</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>0.60089</v>
+        <v>0.61761</v>
       </c>
       <c r="P39" s="1" t="n">
+        <v>0.61761</v>
+      </c>
+      <c r="Q39" s="1" t="n">
         <v>0.58131</v>
       </c>
     </row>
@@ -2541,9 +2661,12 @@
         <v>4.024</v>
       </c>
       <c r="O40" s="1" t="n">
+        <v>4.027</v>
+      </c>
+      <c r="P40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="P40" s="1" t="n">
+      <c r="Q40" s="1" t="n">
         <v>4.024</v>
       </c>
     </row>
@@ -2593,9 +2716,12 @@
         <v>0.05006</v>
       </c>
       <c r="O41" s="1" t="n">
+        <v>0.04978</v>
+      </c>
+      <c r="P41" s="1" t="n">
         <v>0.0513</v>
       </c>
-      <c r="P41" s="1" t="n">
+      <c r="Q41" s="1" t="n">
         <v>0.04927</v>
       </c>
     </row>
@@ -2645,9 +2771,12 @@
         <v>0.7018</v>
       </c>
       <c r="O42" s="1" t="n">
+        <v>0.7009</v>
+      </c>
+      <c r="P42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="P42" s="1" t="n">
+      <c r="Q42" s="1" t="n">
         <v>0.7006</v>
       </c>
     </row>
@@ -2697,9 +2826,12 @@
         <v>0.22812</v>
       </c>
       <c r="O43" s="1" t="n">
+        <v>0.2284</v>
+      </c>
+      <c r="P43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="P43" s="1" t="n">
+      <c r="Q43" s="1" t="n">
         <v>0.22812</v>
       </c>
     </row>
@@ -2749,9 +2881,12 @@
         <v>0.35544</v>
       </c>
       <c r="O44" s="1" t="n">
-        <v>0.35655</v>
+        <v>0.3581</v>
       </c>
       <c r="P44" s="1" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="Q44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -2801,10 +2936,13 @@
         <v>0.1698</v>
       </c>
       <c r="O45" s="1" t="n">
+        <v>0.1694</v>
+      </c>
+      <c r="P45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="P45" s="1" t="n">
-        <v>0.1698</v>
+      <c r="Q45" s="1" t="n">
+        <v>0.1694</v>
       </c>
     </row>
     <row r="46">
@@ -2853,9 +2991,12 @@
         <v>0.0258</v>
       </c>
       <c r="O46" s="1" t="n">
+        <v>0.0261</v>
+      </c>
+      <c r="P46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="P46" s="1" t="n">
+      <c r="Q46" s="1" t="n">
         <v>0.0258</v>
       </c>
     </row>
@@ -2905,9 +3046,12 @@
         <v>0.005942</v>
       </c>
       <c r="O47" s="1" t="n">
+        <v>0.005949</v>
+      </c>
+      <c r="P47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="P47" s="1" t="n">
+      <c r="Q47" s="1" t="n">
         <v>0.005942</v>
       </c>
     </row>
@@ -2957,9 +3101,12 @@
         <v>0.007367</v>
       </c>
       <c r="O48" s="1" t="n">
+        <v>0.00736</v>
+      </c>
+      <c r="P48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="P48" s="1" t="n">
+      <c r="Q48" s="1" t="n">
         <v>0.007349</v>
       </c>
     </row>
@@ -3009,9 +3156,12 @@
         <v>0.1083</v>
       </c>
       <c r="O49" s="1" t="n">
+        <v>0.1088</v>
+      </c>
+      <c r="P49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="P49" s="1" t="n">
+      <c r="Q49" s="1" t="n">
         <v>0.1077</v>
       </c>
     </row>
@@ -3061,9 +3211,12 @@
         <v>0.04159</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>0.04159</v>
+        <v>0.04182</v>
       </c>
       <c r="P50" s="1" t="n">
+        <v>0.04182</v>
+      </c>
+      <c r="Q50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -3113,10 +3266,13 @@
         <v>0.1619</v>
       </c>
       <c r="O51" s="1" t="n">
+        <v>0.1616</v>
+      </c>
+      <c r="P51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="P51" s="1" t="n">
-        <v>0.1617</v>
+      <c r="Q51" s="1" t="n">
+        <v>0.1616</v>
       </c>
     </row>
     <row r="52">
@@ -3165,9 +3321,12 @@
         <v>0.00351</v>
       </c>
       <c r="O52" s="1" t="n">
+        <v>0.00351</v>
+      </c>
+      <c r="P52" s="1" t="n">
         <v>0.00357</v>
       </c>
-      <c r="P52" s="1" t="n">
+      <c r="Q52" s="1" t="n">
         <v>0.0035</v>
       </c>
     </row>
@@ -3217,10 +3376,13 @@
         <v>2.629</v>
       </c>
       <c r="O53" s="1" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="P53" s="1" t="n">
-        <v>2.622</v>
+      <c r="Q53" s="1" t="n">
+        <v>2.62</v>
       </c>
     </row>
     <row r="54">
@@ -3269,10 +3431,13 @@
         <v>0.006182</v>
       </c>
       <c r="O54" s="1" t="n">
+        <v>0.006174</v>
+      </c>
+      <c r="P54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="P54" s="1" t="n">
-        <v>0.006182</v>
+      <c r="Q54" s="1" t="n">
+        <v>0.006174</v>
       </c>
     </row>
     <row r="55">
@@ -3321,9 +3486,12 @@
         <v>0.02918</v>
       </c>
       <c r="O55" s="1" t="n">
+        <v>0.02927</v>
+      </c>
+      <c r="P55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="P55" s="1" t="n">
+      <c r="Q55" s="1" t="n">
         <v>0.02879</v>
       </c>
     </row>
@@ -3373,9 +3541,12 @@
         <v>0.7351</v>
       </c>
       <c r="O56" s="1" t="n">
+        <v>0.7352</v>
+      </c>
+      <c r="P56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="P56" s="1" t="n">
+      <c r="Q56" s="1" t="n">
         <v>0.7351</v>
       </c>
     </row>
@@ -3425,9 +3596,12 @@
         <v>0.1034</v>
       </c>
       <c r="O57" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="P57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="P57" s="1" t="n">
+      <c r="Q57" s="1" t="n">
         <v>0.1034</v>
       </c>
     </row>
@@ -3477,9 +3651,12 @@
         <v>0.9383</v>
       </c>
       <c r="O58" s="1" t="n">
+        <v>0.9388</v>
+      </c>
+      <c r="P58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="P58" s="1" t="n">
+      <c r="Q58" s="1" t="n">
         <v>0.9355</v>
       </c>
     </row>
@@ -3529,9 +3706,12 @@
         <v>0.08769</v>
       </c>
       <c r="O59" s="1" t="n">
+        <v>0.0873</v>
+      </c>
+      <c r="P59" s="1" t="n">
         <v>0.08826000000000001</v>
       </c>
-      <c r="P59" s="1" t="n">
+      <c r="Q59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -3581,9 +3761,12 @@
         <v>0.06918000000000001</v>
       </c>
       <c r="O60" s="1" t="n">
+        <v>0.06936</v>
+      </c>
+      <c r="P60" s="1" t="n">
         <v>0.0703</v>
       </c>
-      <c r="P60" s="1" t="n">
+      <c r="Q60" s="1" t="n">
         <v>0.06918000000000001</v>
       </c>
     </row>
@@ -3633,9 +3816,12 @@
         <v>0.05439</v>
       </c>
       <c r="O61" s="1" t="n">
+        <v>0.05446</v>
+      </c>
+      <c r="P61" s="1" t="n">
         <v>0.05523</v>
       </c>
-      <c r="P61" s="1" t="n">
+      <c r="Q61" s="1" t="n">
         <v>0.05439</v>
       </c>
     </row>
@@ -3685,9 +3871,12 @@
         <v>0.01007</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>0.010194</v>
+        <v>0.010259</v>
       </c>
       <c r="P62" s="1" t="n">
+        <v>0.010259</v>
+      </c>
+      <c r="Q62" s="1" t="n">
         <v>0.009387</v>
       </c>
     </row>
@@ -3737,9 +3926,12 @@
         <v>0.29065</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>0.2912</v>
+        <v>0.29156</v>
       </c>
       <c r="P63" s="1" t="n">
+        <v>0.29156</v>
+      </c>
+      <c r="Q63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -3789,9 +3981,12 @@
         <v>0.07613</v>
       </c>
       <c r="O64" s="1" t="n">
+        <v>0.07549</v>
+      </c>
+      <c r="P64" s="1" t="n">
         <v>0.07613</v>
       </c>
-      <c r="P64" s="1" t="n">
+      <c r="Q64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -3841,9 +4036,12 @@
         <v>0.3173</v>
       </c>
       <c r="O65" s="1" t="n">
-        <v>0.3184</v>
+        <v>0.3186</v>
       </c>
       <c r="P65" s="1" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="Q65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -3893,9 +4091,12 @@
         <v>0.1622</v>
       </c>
       <c r="O66" s="1" t="n">
+        <v>0.16253</v>
+      </c>
+      <c r="P66" s="1" t="n">
         <v>0.16461</v>
       </c>
-      <c r="P66" s="1" t="n">
+      <c r="Q66" s="1" t="n">
         <v>0.1622</v>
       </c>
     </row>
@@ -3945,9 +4146,12 @@
         <v>0.12014</v>
       </c>
       <c r="O67" s="1" t="n">
+        <v>0.12012</v>
+      </c>
+      <c r="P67" s="1" t="n">
         <v>0.12014</v>
       </c>
-      <c r="P67" s="1" t="n">
+      <c r="Q67" s="1" t="n">
         <v>0.11919</v>
       </c>
     </row>
@@ -3997,10 +4201,13 @@
         <v>0.09520000000000001</v>
       </c>
       <c r="O68" s="1" t="n">
+        <v>0.09512</v>
+      </c>
+      <c r="P68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="P68" s="1" t="n">
-        <v>0.09520000000000001</v>
+      <c r="Q68" s="1" t="n">
+        <v>0.09512</v>
       </c>
     </row>
     <row r="69">
@@ -4049,9 +4256,12 @@
         <v>0.1241</v>
       </c>
       <c r="O69" s="1" t="n">
+        <v>0.1243</v>
+      </c>
+      <c r="P69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="P69" s="1" t="n">
+      <c r="Q69" s="1" t="n">
         <v>0.1239</v>
       </c>
     </row>
@@ -4101,9 +4311,12 @@
         <v>8.503</v>
       </c>
       <c r="O70" s="1" t="n">
+        <v>8.510999999999999</v>
+      </c>
+      <c r="P70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="P70" s="1" t="n">
+      <c r="Q70" s="1" t="n">
         <v>8.494</v>
       </c>
     </row>
@@ -4153,9 +4366,12 @@
         <v>0.239</v>
       </c>
       <c r="O71" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="P71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="P71" s="1" t="n">
+      <c r="Q71" s="1" t="n">
         <v>0.238</v>
       </c>
     </row>
@@ -4205,9 +4421,12 @@
         <v>0.04994</v>
       </c>
       <c r="O72" s="1" t="n">
+        <v>0.04999</v>
+      </c>
+      <c r="P72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="P72" s="1" t="n">
+      <c r="Q72" s="1" t="n">
         <v>0.04992</v>
       </c>
     </row>
@@ -4257,9 +4476,12 @@
         <v>0.05022</v>
       </c>
       <c r="O73" s="1" t="n">
+        <v>0.05037</v>
+      </c>
+      <c r="P73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="P73" s="1" t="n">
+      <c r="Q73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -4309,9 +4531,12 @@
         <v>0.1246</v>
       </c>
       <c r="O74" s="1" t="n">
+        <v>0.1252</v>
+      </c>
+      <c r="P74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="P74" s="1" t="n">
+      <c r="Q74" s="1" t="n">
         <v>0.1246</v>
       </c>
     </row>
@@ -4361,10 +4586,13 @@
         <v>0.04656</v>
       </c>
       <c r="O75" s="1" t="n">
+        <v>0.04619</v>
+      </c>
+      <c r="P75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="P75" s="1" t="n">
-        <v>0.04621</v>
+      <c r="Q75" s="1" t="n">
+        <v>0.04619</v>
       </c>
     </row>
     <row r="76">
@@ -4413,9 +4641,12 @@
         <v>0.06691999999999999</v>
       </c>
       <c r="O76" s="1" t="n">
+        <v>0.06725</v>
+      </c>
+      <c r="P76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="P76" s="1" t="n">
+      <c r="Q76" s="1" t="n">
         <v>0.06691</v>
       </c>
     </row>
@@ -4465,9 +4696,12 @@
         <v>0.12665</v>
       </c>
       <c r="O77" s="1" t="n">
+        <v>0.12835</v>
+      </c>
+      <c r="P77" s="1" t="n">
         <v>0.12881</v>
       </c>
-      <c r="P77" s="1" t="n">
+      <c r="Q77" s="1" t="n">
         <v>0.12584</v>
       </c>
     </row>
@@ -4517,9 +4751,12 @@
         <v>0.1611</v>
       </c>
       <c r="O78" s="1" t="n">
+        <v>0.1611</v>
+      </c>
+      <c r="P78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="P78" s="1" t="n">
+      <c r="Q78" s="1" t="n">
         <v>0.1611</v>
       </c>
     </row>
@@ -4569,10 +4806,13 @@
         <v>0.02706</v>
       </c>
       <c r="O79" s="1" t="n">
+        <v>0.02696</v>
+      </c>
+      <c r="P79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="P79" s="1" t="n">
-        <v>0.02705</v>
+      <c r="Q79" s="1" t="n">
+        <v>0.02696</v>
       </c>
     </row>
     <row r="80">
@@ -4621,9 +4861,12 @@
         <v>357.33</v>
       </c>
       <c r="O80" s="1" t="n">
-        <v>358.61</v>
+        <v>358.62</v>
       </c>
       <c r="P80" s="1" t="n">
+        <v>358.62</v>
+      </c>
+      <c r="Q80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -4673,10 +4916,13 @@
         <v>7.067999999999999e-05</v>
       </c>
       <c r="O81" s="1" t="n">
+        <v>7.053e-05</v>
+      </c>
+      <c r="P81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="P81" s="1" t="n">
-        <v>7.067999999999999e-05</v>
+      <c r="Q81" s="1" t="n">
+        <v>7.053e-05</v>
       </c>
     </row>
     <row r="82">
@@ -4725,9 +4971,12 @@
         <v>0.2645</v>
       </c>
       <c r="O82" s="1" t="n">
+        <v>0.2655</v>
+      </c>
+      <c r="P82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="P82" s="1" t="n">
+      <c r="Q82" s="1" t="n">
         <v>0.2645</v>
       </c>
     </row>
@@ -4777,10 +5026,13 @@
         <v>1.1287</v>
       </c>
       <c r="O83" s="1" t="n">
+        <v>1.1222</v>
+      </c>
+      <c r="P83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="P83" s="1" t="n">
-        <v>1.1287</v>
+      <c r="Q83" s="1" t="n">
+        <v>1.1222</v>
       </c>
     </row>
     <row r="84">
@@ -4829,9 +5081,12 @@
         <v>0.3535</v>
       </c>
       <c r="O84" s="1" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="P84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="P84" s="1" t="n">
+      <c r="Q84" s="1" t="n">
         <v>0.3535</v>
       </c>
     </row>
@@ -4881,10 +5136,13 @@
         <v>2.0155</v>
       </c>
       <c r="O85" s="1" t="n">
+        <v>2.0058</v>
+      </c>
+      <c r="P85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="P85" s="1" t="n">
-        <v>2.0067</v>
+      <c r="Q85" s="1" t="n">
+        <v>2.0058</v>
       </c>
     </row>
     <row r="86">
@@ -4933,9 +5191,12 @@
         <v>1.3143</v>
       </c>
       <c r="O86" s="1" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="P86" s="1" t="n">
         <v>1.3205</v>
       </c>
-      <c r="P86" s="1" t="n">
+      <c r="Q86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -4985,10 +5246,13 @@
         <v>32.65</v>
       </c>
       <c r="O87" s="1" t="n">
+        <v>32.64</v>
+      </c>
+      <c r="P87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="P87" s="1" t="n">
-        <v>32.65</v>
+      <c r="Q87" s="1" t="n">
+        <v>32.64</v>
       </c>
     </row>
     <row r="88">
@@ -5037,9 +5301,12 @@
         <v>0.00958</v>
       </c>
       <c r="O88" s="1" t="n">
+        <v>0.00957</v>
+      </c>
+      <c r="P88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="P88" s="1" t="n">
+      <c r="Q88" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -5089,9 +5356,12 @@
         <v>0.01808</v>
       </c>
       <c r="O89" s="1" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="P89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="P89" s="1" t="n">
+      <c r="Q89" s="1" t="n">
         <v>0.01808</v>
       </c>
     </row>
@@ -5141,9 +5411,12 @@
         <v>0.03479</v>
       </c>
       <c r="O90" s="1" t="n">
+        <v>0.03483</v>
+      </c>
+      <c r="P90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="P90" s="1" t="n">
+      <c r="Q90" s="1" t="n">
         <v>0.03479</v>
       </c>
     </row>
@@ -5193,10 +5466,13 @@
         <v>0.01181</v>
       </c>
       <c r="O91" s="1" t="n">
+        <v>0.01179</v>
+      </c>
+      <c r="P91" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="P91" s="1" t="n">
-        <v>0.0118</v>
+      <c r="Q91" s="1" t="n">
+        <v>0.01179</v>
       </c>
     </row>
     <row r="92">
@@ -5245,9 +5521,12 @@
         <v>3.09</v>
       </c>
       <c r="O92" s="1" t="n">
+        <v>3.098</v>
+      </c>
+      <c r="P92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="P92" s="1" t="n">
+      <c r="Q92" s="1" t="n">
         <v>3.09</v>
       </c>
     </row>
@@ -5297,10 +5576,13 @@
         <v>0.005592</v>
       </c>
       <c r="O93" s="1" t="n">
+        <v>0.005585</v>
+      </c>
+      <c r="P93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="P93" s="1" t="n">
-        <v>0.005592</v>
+      <c r="Q93" s="1" t="n">
+        <v>0.005585</v>
       </c>
     </row>
     <row r="94">
@@ -5349,9 +5631,12 @@
         <v>0.0931</v>
       </c>
       <c r="O94" s="1" t="n">
+        <v>0.09370000000000001</v>
+      </c>
+      <c r="P94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="P94" s="1" t="n">
+      <c r="Q94" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -5401,9 +5686,12 @@
         <v>0.6077</v>
       </c>
       <c r="O95" s="1" t="n">
+        <v>0.6063</v>
+      </c>
+      <c r="P95" s="1" t="n">
         <v>0.6098</v>
       </c>
-      <c r="P95" s="1" t="n">
+      <c r="Q95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -5453,9 +5741,12 @@
         <v>1.27e-05</v>
       </c>
       <c r="O96" s="1" t="n">
+        <v>1.28e-05</v>
+      </c>
+      <c r="P96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="P96" s="1" t="n">
+      <c r="Q96" s="1" t="n">
         <v>1.27e-05</v>
       </c>
     </row>
@@ -5505,10 +5796,13 @@
         <v>1.12</v>
       </c>
       <c r="O97" s="1" t="n">
+        <v>1.103</v>
+      </c>
+      <c r="P97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="P97" s="1" t="n">
-        <v>1.12</v>
+      <c r="Q97" s="1" t="n">
+        <v>1.103</v>
       </c>
     </row>
     <row r="98">
@@ -5557,9 +5851,12 @@
         <v>0.25443</v>
       </c>
       <c r="O98" s="1" t="n">
+        <v>0.25615</v>
+      </c>
+      <c r="P98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="P98" s="1" t="n">
+      <c r="Q98" s="1" t="n">
         <v>0.2523</v>
       </c>
     </row>
@@ -5609,10 +5906,13 @@
         <v>1.143</v>
       </c>
       <c r="O99" s="1" t="n">
+        <v>1.142</v>
+      </c>
+      <c r="P99" s="1" t="n">
         <v>1.156</v>
       </c>
-      <c r="P99" s="1" t="n">
-        <v>1.143</v>
+      <c r="Q99" s="1" t="n">
+        <v>1.142</v>
       </c>
     </row>
     <row r="100">
@@ -5661,9 +5961,12 @@
         <v>1.854</v>
       </c>
       <c r="O100" s="1" t="n">
+        <v>1.858</v>
+      </c>
+      <c r="P100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="P100" s="1" t="n">
+      <c r="Q100" s="1" t="n">
         <v>1.852</v>
       </c>
     </row>
@@ -5713,10 +6016,13 @@
         <v>0.01589</v>
       </c>
       <c r="O101" s="1" t="n">
+        <v>0.01575</v>
+      </c>
+      <c r="P101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="P101" s="1" t="n">
-        <v>0.01579</v>
+      <c r="Q101" s="1" t="n">
+        <v>0.01575</v>
       </c>
     </row>
     <row r="102">
@@ -5765,10 +6071,13 @@
         <v>0.10283</v>
       </c>
       <c r="O102" s="1" t="n">
+        <v>0.10225</v>
+      </c>
+      <c r="P102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="P102" s="1" t="n">
-        <v>0.10279</v>
+      <c r="Q102" s="1" t="n">
+        <v>0.10225</v>
       </c>
     </row>
     <row r="103">
@@ -5817,10 +6126,13 @@
         <v>0.0005946</v>
       </c>
       <c r="O103" s="1" t="n">
+        <v>0.0005941</v>
+      </c>
+      <c r="P103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="P103" s="1" t="n">
-        <v>0.0005946</v>
+      <c r="Q103" s="1" t="n">
+        <v>0.0005941</v>
       </c>
     </row>
     <row r="104">
@@ -5869,9 +6181,12 @@
         <v>0.0005888999999999999</v>
       </c>
       <c r="O104" s="1" t="n">
-        <v>0.0005888999999999999</v>
+        <v>0.0005917</v>
       </c>
       <c r="P104" s="1" t="n">
+        <v>0.0005917</v>
+      </c>
+      <c r="Q104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -5921,9 +6236,12 @@
         <v>0.003246</v>
       </c>
       <c r="O105" s="1" t="n">
+        <v>0.003268</v>
+      </c>
+      <c r="P105" s="1" t="n">
         <v>0.003269</v>
       </c>
-      <c r="P105" s="1" t="n">
+      <c r="Q105" s="1" t="n">
         <v>0.003229</v>
       </c>
     </row>
@@ -5973,10 +6291,13 @@
         <v>2.587</v>
       </c>
       <c r="O106" s="1" t="n">
+        <v>2.582</v>
+      </c>
+      <c r="P106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="P106" s="1" t="n">
-        <v>2.587</v>
+      <c r="Q106" s="1" t="n">
+        <v>2.582</v>
       </c>
     </row>
     <row r="107">
@@ -6025,9 +6346,12 @@
         <v>0.165</v>
       </c>
       <c r="O107" s="1" t="n">
+        <v>0.1653</v>
+      </c>
+      <c r="P107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="P107" s="1" t="n">
+      <c r="Q107" s="1" t="n">
         <v>0.165</v>
       </c>
     </row>
@@ -6077,9 +6401,12 @@
         <v>0.09619999999999999</v>
       </c>
       <c r="O108" s="1" t="n">
+        <v>0.09623</v>
+      </c>
+      <c r="P108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="P108" s="1" t="n">
+      <c r="Q108" s="1" t="n">
         <v>0.0955</v>
       </c>
     </row>
@@ -6129,9 +6456,12 @@
         <v>0.02208</v>
       </c>
       <c r="O109" s="1" t="n">
+        <v>0.02209</v>
+      </c>
+      <c r="P109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="P109" s="1" t="n">
+      <c r="Q109" s="1" t="n">
         <v>0.02204</v>
       </c>
     </row>
@@ -6181,10 +6511,13 @@
         <v>0.2928</v>
       </c>
       <c r="O110" s="1" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="P110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="P110" s="1" t="n">
-        <v>0.2912</v>
+      <c r="Q110" s="1" t="n">
+        <v>0.2901</v>
       </c>
     </row>
     <row r="111">
@@ -6233,9 +6566,12 @@
         <v>0.05691</v>
       </c>
       <c r="O111" s="1" t="n">
+        <v>0.05675</v>
+      </c>
+      <c r="P111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="P111" s="1" t="n">
+      <c r="Q111" s="1" t="n">
         <v>0.05659</v>
       </c>
     </row>
@@ -6285,9 +6621,12 @@
         <v>0.3006</v>
       </c>
       <c r="O112" s="1" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="P112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="P112" s="1" t="n">
+      <c r="Q112" s="1" t="n">
         <v>0.3002</v>
       </c>
     </row>
@@ -6337,10 +6676,13 @@
         <v>18.61</v>
       </c>
       <c r="O113" s="1" t="n">
+        <v>18.58</v>
+      </c>
+      <c r="P113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="P113" s="1" t="n">
-        <v>18.6</v>
+      <c r="Q113" s="1" t="n">
+        <v>18.58</v>
       </c>
     </row>
     <row r="114">
@@ -6389,10 +6731,13 @@
         <v>0.12826</v>
       </c>
       <c r="O114" s="1" t="n">
+        <v>0.12729</v>
+      </c>
+      <c r="P114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="P114" s="1" t="n">
-        <v>0.12826</v>
+      <c r="Q114" s="1" t="n">
+        <v>0.12729</v>
       </c>
     </row>
     <row r="115">
@@ -6441,9 +6786,12 @@
         <v>0.01577</v>
       </c>
       <c r="O115" s="1" t="n">
-        <v>0.01584</v>
+        <v>0.01661</v>
       </c>
       <c r="P115" s="1" t="n">
+        <v>0.01661</v>
+      </c>
+      <c r="Q115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -6493,9 +6841,12 @@
         <v>0.08454</v>
       </c>
       <c r="O116" s="1" t="n">
+        <v>0.08465</v>
+      </c>
+      <c r="P116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="P116" s="1" t="n">
+      <c r="Q116" s="1" t="n">
         <v>0.08454</v>
       </c>
     </row>
@@ -6545,10 +6896,13 @@
         <v>0.047376</v>
       </c>
       <c r="O117" s="1" t="n">
+        <v>0.04726</v>
+      </c>
+      <c r="P117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="P117" s="1" t="n">
-        <v>0.047288</v>
+      <c r="Q117" s="1" t="n">
+        <v>0.04726</v>
       </c>
     </row>
     <row r="118">
@@ -6597,10 +6951,13 @@
         <v>0.04721</v>
       </c>
       <c r="O118" s="1" t="n">
+        <v>0.04717</v>
+      </c>
+      <c r="P118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="P118" s="1" t="n">
-        <v>0.04721</v>
+      <c r="Q118" s="1" t="n">
+        <v>0.04717</v>
       </c>
     </row>
     <row r="119">
@@ -6649,9 +7006,12 @@
         <v>0.04053</v>
       </c>
       <c r="O119" s="1" t="n">
+        <v>0.04046</v>
+      </c>
+      <c r="P119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="P119" s="1" t="n">
+      <c r="Q119" s="1" t="n">
         <v>0.03999</v>
       </c>
     </row>
@@ -6701,9 +7061,12 @@
         <v>0.14421</v>
       </c>
       <c r="O120" s="1" t="n">
+        <v>0.14508</v>
+      </c>
+      <c r="P120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="P120" s="1" t="n">
+      <c r="Q120" s="1" t="n">
         <v>0.14387</v>
       </c>
     </row>
@@ -6753,10 +7116,13 @@
         <v>0.1268</v>
       </c>
       <c r="O121" s="1" t="n">
+        <v>0.1266</v>
+      </c>
+      <c r="P121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="P121" s="1" t="n">
-        <v>0.1268</v>
+      <c r="Q121" s="1" t="n">
+        <v>0.1266</v>
       </c>
     </row>
     <row r="122">
@@ -6805,10 +7171,13 @@
         <v>1.859</v>
       </c>
       <c r="O122" s="1" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="P122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="P122" s="1" t="n">
-        <v>1.859</v>
+      <c r="Q122" s="1" t="n">
+        <v>1.854</v>
       </c>
     </row>
     <row r="123">
@@ -6857,9 +7226,12 @@
         <v>0.03009</v>
       </c>
       <c r="O123" s="1" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="P123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="P123" s="1" t="n">
+      <c r="Q123" s="1" t="n">
         <v>0.03009</v>
       </c>
     </row>
@@ -6909,9 +7281,12 @@
         <v>0.13138</v>
       </c>
       <c r="O124" s="1" t="n">
+        <v>0.13218</v>
+      </c>
+      <c r="P124" s="1" t="n">
         <v>0.13401</v>
       </c>
-      <c r="P124" s="1" t="n">
+      <c r="Q124" s="1" t="n">
         <v>0.13138</v>
       </c>
     </row>
@@ -6961,10 +7336,13 @@
         <v>0.04097</v>
       </c>
       <c r="O125" s="1" t="n">
+        <v>0.04084</v>
+      </c>
+      <c r="P125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="P125" s="1" t="n">
-        <v>0.04095</v>
+      <c r="Q125" s="1" t="n">
+        <v>0.04084</v>
       </c>
     </row>
     <row r="126">
@@ -7013,10 +7391,13 @@
         <v>0.1145</v>
       </c>
       <c r="O126" s="1" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="P126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="P126" s="1" t="n">
-        <v>0.1145</v>
+      <c r="Q126" s="1" t="n">
+        <v>0.1144</v>
       </c>
     </row>
     <row r="127">
@@ -7065,9 +7446,12 @@
         <v>0.5196</v>
       </c>
       <c r="O127" s="1" t="n">
-        <v>0.5196</v>
+        <v>0.5213</v>
       </c>
       <c r="P127" s="1" t="n">
+        <v>0.5213</v>
+      </c>
+      <c r="Q127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -7117,10 +7501,13 @@
         <v>0.03787</v>
       </c>
       <c r="O128" s="1" t="n">
+        <v>0.0378</v>
+      </c>
+      <c r="P128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="P128" s="1" t="n">
-        <v>0.03787</v>
+      <c r="Q128" s="1" t="n">
+        <v>0.0378</v>
       </c>
     </row>
     <row r="129">
@@ -7169,9 +7556,12 @@
         <v>0.791</v>
       </c>
       <c r="O129" s="1" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="P129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="P129" s="1" t="n">
+      <c r="Q129" s="1" t="n">
         <v>0.791</v>
       </c>
     </row>
@@ -7221,9 +7611,12 @@
         <v>0.03431</v>
       </c>
       <c r="O130" s="1" t="n">
+        <v>0.03437</v>
+      </c>
+      <c r="P130" s="1" t="n">
         <v>0.03458</v>
       </c>
-      <c r="P130" s="1" t="n">
+      <c r="Q130" s="1" t="n">
         <v>0.03422</v>
       </c>
     </row>
@@ -7273,9 +7666,12 @@
         <v>0.4274</v>
       </c>
       <c r="O131" s="1" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="P131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="P131" s="1" t="n">
+      <c r="Q131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -7325,9 +7721,12 @@
         <v>0.04309</v>
       </c>
       <c r="O132" s="1" t="n">
+        <v>0.04319</v>
+      </c>
+      <c r="P132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="P132" s="1" t="n">
+      <c r="Q132" s="1" t="n">
         <v>0.04309</v>
       </c>
     </row>
@@ -7377,9 +7776,12 @@
         <v>1.2845</v>
       </c>
       <c r="O133" s="1" t="n">
+        <v>1.2835</v>
+      </c>
+      <c r="P133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="P133" s="1" t="n">
+      <c r="Q133" s="1" t="n">
         <v>1.282</v>
       </c>
     </row>
@@ -7429,9 +7831,12 @@
         <v>0.02186</v>
       </c>
       <c r="O134" s="1" t="n">
+        <v>0.02188</v>
+      </c>
+      <c r="P134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="P134" s="1" t="n">
+      <c r="Q134" s="1" t="n">
         <v>0.02184</v>
       </c>
     </row>
@@ -7481,10 +7886,13 @@
         <v>0.0004583</v>
       </c>
       <c r="O135" s="1" t="n">
+        <v>0.0004575</v>
+      </c>
+      <c r="P135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="P135" s="1" t="n">
-        <v>0.0004583</v>
+      <c r="Q135" s="1" t="n">
+        <v>0.0004575</v>
       </c>
     </row>
     <row r="136">
@@ -7533,9 +7941,12 @@
         <v>0.001907</v>
       </c>
       <c r="O136" s="1" t="n">
+        <v>0.001907</v>
+      </c>
+      <c r="P136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="P136" s="1" t="n">
+      <c r="Q136" s="1" t="n">
         <v>0.001881</v>
       </c>
     </row>
@@ -7585,9 +7996,12 @@
         <v>0.3143</v>
       </c>
       <c r="O137" s="1" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="P137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="P137" s="1" t="n">
+      <c r="Q137" s="1" t="n">
         <v>0.3143</v>
       </c>
     </row>
@@ -7637,10 +8051,13 @@
         <v>0.5672</v>
       </c>
       <c r="O138" s="1" t="n">
+        <v>0.5645</v>
+      </c>
+      <c r="P138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="P138" s="1" t="n">
-        <v>0.5672</v>
+      <c r="Q138" s="1" t="n">
+        <v>0.5645</v>
       </c>
     </row>
     <row r="139">
@@ -7689,10 +8106,13 @@
         <v>0.02127</v>
       </c>
       <c r="O139" s="1" t="n">
+        <v>0.02121</v>
+      </c>
+      <c r="P139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="P139" s="1" t="n">
-        <v>0.02125</v>
+      <c r="Q139" s="1" t="n">
+        <v>0.02121</v>
       </c>
     </row>
     <row r="140">
@@ -7741,10 +8161,13 @@
         <v>0.08018</v>
       </c>
       <c r="O140" s="1" t="n">
+        <v>0.08007</v>
+      </c>
+      <c r="P140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="P140" s="1" t="n">
-        <v>0.08018</v>
+      <c r="Q140" s="1" t="n">
+        <v>0.08007</v>
       </c>
     </row>
     <row r="141">
@@ -7793,9 +8216,12 @@
         <v>0.001522</v>
       </c>
       <c r="O141" s="1" t="n">
+        <v>0.001525</v>
+      </c>
+      <c r="P141" s="1" t="n">
         <v>0.001672</v>
       </c>
-      <c r="P141" s="1" t="n">
+      <c r="Q141" s="1" t="n">
         <v>0.001502</v>
       </c>
     </row>
@@ -7845,9 +8271,12 @@
         <v>0.4475</v>
       </c>
       <c r="O142" s="1" t="n">
-        <v>0.4475</v>
+        <v>0.4489</v>
       </c>
       <c r="P142" s="1" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="Q142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -7897,9 +8326,12 @@
         <v>0.030287</v>
       </c>
       <c r="O143" s="1" t="n">
+        <v>0.030318</v>
+      </c>
+      <c r="P143" s="1" t="n">
         <v>0.031368</v>
       </c>
-      <c r="P143" s="1" t="n">
+      <c r="Q143" s="1" t="n">
         <v>0.030021</v>
       </c>
     </row>
@@ -7952,6 +8384,9 @@
         <v>0.000227</v>
       </c>
       <c r="P144" s="1" t="n">
+        <v>0.000227</v>
+      </c>
+      <c r="Q144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -8001,9 +8436,12 @@
         <v>0.03474</v>
       </c>
       <c r="O145" s="1" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="P145" s="1" t="n">
         <v>0.03696</v>
       </c>
-      <c r="P145" s="1" t="n">
+      <c r="Q145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -8053,9 +8491,12 @@
         <v>0.11505</v>
       </c>
       <c r="O146" s="1" t="n">
+        <v>0.11554</v>
+      </c>
+      <c r="P146" s="1" t="n">
         <v>0.116</v>
       </c>
-      <c r="P146" s="1" t="n">
+      <c r="Q146" s="1" t="n">
         <v>0.11505</v>
       </c>
     </row>
@@ -8105,9 +8546,12 @@
         <v>0.02193</v>
       </c>
       <c r="O147" s="1" t="n">
+        <v>0.02188</v>
+      </c>
+      <c r="P147" s="1" t="n">
         <v>0.02198</v>
       </c>
-      <c r="P147" s="1" t="n">
+      <c r="Q147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -8157,9 +8601,12 @@
         <v>1.4105</v>
       </c>
       <c r="O148" s="1" t="n">
+        <v>1.4116</v>
+      </c>
+      <c r="P148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="P148" s="1" t="n">
+      <c r="Q148" s="1" t="n">
         <v>1.4084</v>
       </c>
     </row>
@@ -8209,9 +8656,12 @@
         <v>1.8738</v>
       </c>
       <c r="O149" s="1" t="n">
+        <v>1.8671</v>
+      </c>
+      <c r="P149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="P149" s="1" t="n">
+      <c r="Q149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -8261,10 +8711,13 @@
         <v>0.096</v>
       </c>
       <c r="O150" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="P150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="P150" s="1" t="n">
-        <v>0.096</v>
+      <c r="Q150" s="1" t="n">
+        <v>0.095</v>
       </c>
     </row>
     <row r="151">
@@ -8313,9 +8766,12 @@
         <v>4.614</v>
       </c>
       <c r="O151" s="1" t="n">
+        <v>4.614</v>
+      </c>
+      <c r="P151" s="1" t="n">
         <v>4.64</v>
       </c>
-      <c r="P151" s="1" t="n">
+      <c r="Q151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -8365,9 +8821,12 @@
         <v>5.533</v>
       </c>
       <c r="O152" s="1" t="n">
+        <v>5.528</v>
+      </c>
+      <c r="P152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="P152" s="1" t="n">
+      <c r="Q152" s="1" t="n">
         <v>5.522</v>
       </c>
     </row>
@@ -8417,9 +8876,12 @@
         <v>0.3154</v>
       </c>
       <c r="O153" s="1" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="P153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="P153" s="1" t="n">
+      <c r="Q153" s="1" t="n">
         <v>0.3154</v>
       </c>
     </row>
@@ -8469,10 +8931,13 @@
         <v>0.5847</v>
       </c>
       <c r="O154" s="1" t="n">
+        <v>0.5838</v>
+      </c>
+      <c r="P154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="P154" s="1" t="n">
-        <v>0.5847</v>
+      <c r="Q154" s="1" t="n">
+        <v>0.5838</v>
       </c>
     </row>
     <row r="155">
@@ -8521,9 +8986,12 @@
         <v>0.01285</v>
       </c>
       <c r="O155" s="1" t="n">
+        <v>0.01283</v>
+      </c>
+      <c r="P155" s="1" t="n">
         <v>0.01299</v>
       </c>
-      <c r="P155" s="1" t="n">
+      <c r="Q155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -8573,10 +9041,13 @@
         <v>0.0982</v>
       </c>
       <c r="O156" s="1" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+      <c r="P156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="P156" s="1" t="n">
-        <v>0.0982</v>
+      <c r="Q156" s="1" t="n">
+        <v>0.09810000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -8625,10 +9096,13 @@
         <v>16.504</v>
       </c>
       <c r="O157" s="1" t="n">
+        <v>16.386</v>
+      </c>
+      <c r="P157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="P157" s="1" t="n">
-        <v>16.504</v>
+      <c r="Q157" s="1" t="n">
+        <v>16.386</v>
       </c>
     </row>
     <row r="158">
@@ -8677,9 +9151,12 @@
         <v>0.05537</v>
       </c>
       <c r="O158" s="1" t="n">
+        <v>0.05516</v>
+      </c>
+      <c r="P158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="P158" s="1" t="n">
+      <c r="Q158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -8729,10 +9206,13 @@
         <v>28.83</v>
       </c>
       <c r="O159" s="1" t="n">
+        <v>28.76</v>
+      </c>
+      <c r="P159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="P159" s="1" t="n">
-        <v>28.83</v>
+      <c r="Q159" s="1" t="n">
+        <v>28.76</v>
       </c>
     </row>
     <row r="160">
@@ -8781,10 +9261,13 @@
         <v>0.02103</v>
       </c>
       <c r="O160" s="1" t="n">
+        <v>0.02087</v>
+      </c>
+      <c r="P160" s="1" t="n">
         <v>0.02141</v>
       </c>
-      <c r="P160" s="1" t="n">
-        <v>0.02103</v>
+      <c r="Q160" s="1" t="n">
+        <v>0.02087</v>
       </c>
     </row>
     <row r="161">
@@ -8833,9 +9316,12 @@
         <v>0.0006535999999999999</v>
       </c>
       <c r="O161" s="1" t="n">
+        <v>0.0006546</v>
+      </c>
+      <c r="P161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="P161" s="1" t="n">
+      <c r="Q161" s="1" t="n">
         <v>0.0006507</v>
       </c>
     </row>
@@ -8885,9 +9371,12 @@
         <v>0.3809</v>
       </c>
       <c r="O162" s="1" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="P162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="P162" s="1" t="n">
+      <c r="Q162" s="1" t="n">
         <v>0.3808</v>
       </c>
     </row>
@@ -8937,9 +9426,12 @@
         <v>0.1915</v>
       </c>
       <c r="O163" s="1" t="n">
+        <v>0.1917</v>
+      </c>
+      <c r="P163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="P163" s="1" t="n">
+      <c r="Q163" s="1" t="n">
         <v>0.1915</v>
       </c>
     </row>
@@ -8989,9 +9481,12 @@
         <v>0.317</v>
       </c>
       <c r="O164" s="1" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="P164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="P164" s="1" t="n">
+      <c r="Q164" s="1" t="n">
         <v>0.315</v>
       </c>
     </row>
@@ -9041,9 +9536,12 @@
         <v>0.372</v>
       </c>
       <c r="O165" s="1" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="P165" s="1" t="n">
         <v>0.377</v>
       </c>
-      <c r="P165" s="1" t="n">
+      <c r="Q165" s="1" t="n">
         <v>0.372</v>
       </c>
     </row>
@@ -9093,9 +9591,12 @@
         <v>0.02238</v>
       </c>
       <c r="O166" s="1" t="n">
+        <v>0.02239</v>
+      </c>
+      <c r="P166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="P166" s="1" t="n">
+      <c r="Q166" s="1" t="n">
         <v>0.02238</v>
       </c>
     </row>
@@ -9145,9 +9646,12 @@
         <v>0.007269</v>
       </c>
       <c r="O167" s="1" t="n">
+        <v>0.007278</v>
+      </c>
+      <c r="P167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="P167" s="1" t="n">
+      <c r="Q167" s="1" t="n">
         <v>0.007269</v>
       </c>
     </row>
@@ -9197,10 +9701,13 @@
         <v>0.01344</v>
       </c>
       <c r="O168" s="1" t="n">
+        <v>0.01341</v>
+      </c>
+      <c r="P168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="P168" s="1" t="n">
-        <v>0.01344</v>
+      <c r="Q168" s="1" t="n">
+        <v>0.01341</v>
       </c>
     </row>
     <row r="169">
@@ -9249,9 +9756,12 @@
         <v>0.25363</v>
       </c>
       <c r="O169" s="1" t="n">
+        <v>0.25338</v>
+      </c>
+      <c r="P169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="P169" s="1" t="n">
+      <c r="Q169" s="1" t="n">
         <v>0.25151</v>
       </c>
     </row>
@@ -9301,9 +9811,12 @@
         <v>0.02159</v>
       </c>
       <c r="O170" s="1" t="n">
+        <v>0.02151</v>
+      </c>
+      <c r="P170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="P170" s="1" t="n">
+      <c r="Q170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -9353,9 +9866,12 @@
         <v>0.1717</v>
       </c>
       <c r="O171" s="1" t="n">
+        <v>0.1714</v>
+      </c>
+      <c r="P171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="P171" s="1" t="n">
+      <c r="Q171" s="1" t="n">
         <v>0.1711</v>
       </c>
     </row>
@@ -9405,9 +9921,12 @@
         <v>0.089</v>
       </c>
       <c r="O172" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="P172" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="P172" s="1" t="n">
+      <c r="Q172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -9457,9 +9976,12 @@
         <v>0.004669</v>
       </c>
       <c r="O173" s="1" t="n">
+        <v>0.00467</v>
+      </c>
+      <c r="P173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="P173" s="1" t="n">
+      <c r="Q173" s="1" t="n">
         <v>0.004669</v>
       </c>
     </row>
@@ -9509,9 +10031,12 @@
         <v>0.4361</v>
       </c>
       <c r="O174" s="1" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="P174" s="1" t="n">
         <v>0.4423</v>
       </c>
-      <c r="P174" s="1" t="n">
+      <c r="Q174" s="1" t="n">
         <v>0.4361</v>
       </c>
     </row>
@@ -9561,9 +10086,12 @@
         <v>0.09019000000000001</v>
       </c>
       <c r="O175" s="1" t="n">
+        <v>0.09029</v>
+      </c>
+      <c r="P175" s="1" t="n">
         <v>0.09042</v>
       </c>
-      <c r="P175" s="1" t="n">
+      <c r="Q175" s="1" t="n">
         <v>0.08935999999999999</v>
       </c>
     </row>
@@ -9613,9 +10141,12 @@
         <v>0.246</v>
       </c>
       <c r="O176" s="1" t="n">
+        <v>0.2464</v>
+      </c>
+      <c r="P176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="P176" s="1" t="n">
+      <c r="Q176" s="1" t="n">
         <v>0.2453</v>
       </c>
     </row>
@@ -9665,9 +10196,12 @@
         <v>0.01915</v>
       </c>
       <c r="O177" s="1" t="n">
+        <v>0.01916</v>
+      </c>
+      <c r="P177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="P177" s="1" t="n">
+      <c r="Q177" s="1" t="n">
         <v>0.01909</v>
       </c>
     </row>
@@ -9717,9 +10251,12 @@
         <v>6.122</v>
       </c>
       <c r="O178" s="1" t="n">
+        <v>6.126</v>
+      </c>
+      <c r="P178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="P178" s="1" t="n">
+      <c r="Q178" s="1" t="n">
         <v>6.122</v>
       </c>
     </row>
@@ -9769,10 +10306,13 @@
         <v>0.135</v>
       </c>
       <c r="O179" s="1" t="n">
+        <v>0.1349</v>
+      </c>
+      <c r="P179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="P179" s="1" t="n">
-        <v>0.135</v>
+      <c r="Q179" s="1" t="n">
+        <v>0.1349</v>
       </c>
     </row>
     <row r="180">
@@ -9821,9 +10361,12 @@
         <v>0.005062</v>
       </c>
       <c r="O180" s="1" t="n">
+        <v>0.005031</v>
+      </c>
+      <c r="P180" s="1" t="n">
         <v>0.005154</v>
       </c>
-      <c r="P180" s="1" t="n">
+      <c r="Q180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -9873,10 +10416,13 @@
         <v>0.0119</v>
       </c>
       <c r="O181" s="1" t="n">
+        <v>0.01183</v>
+      </c>
+      <c r="P181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="P181" s="1" t="n">
-        <v>0.01189</v>
+      <c r="Q181" s="1" t="n">
+        <v>0.01183</v>
       </c>
     </row>
     <row r="182">
@@ -9925,9 +10471,12 @@
         <v>0.007224</v>
       </c>
       <c r="O182" s="1" t="n">
+        <v>0.007285</v>
+      </c>
+      <c r="P182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="P182" s="1" t="n">
+      <c r="Q182" s="1" t="n">
         <v>0.007224</v>
       </c>
     </row>
@@ -9977,9 +10526,12 @@
         <v>0.13179</v>
       </c>
       <c r="O183" s="1" t="n">
+        <v>0.13152</v>
+      </c>
+      <c r="P183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="P183" s="1" t="n">
+      <c r="Q183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -10029,9 +10581,12 @@
         <v>0.09604</v>
       </c>
       <c r="O184" s="1" t="n">
+        <v>0.09587</v>
+      </c>
+      <c r="P184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="P184" s="1" t="n">
+      <c r="Q184" s="1" t="n">
         <v>0.09587</v>
       </c>
     </row>
@@ -10081,9 +10636,12 @@
         <v>0.00752</v>
       </c>
       <c r="O185" s="1" t="n">
+        <v>0.00752</v>
+      </c>
+      <c r="P185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="P185" s="1" t="n">
+      <c r="Q185" s="1" t="n">
         <v>0.00752</v>
       </c>
     </row>
@@ -10133,9 +10691,12 @@
         <v>0.04861</v>
       </c>
       <c r="O186" s="1" t="n">
+        <v>0.04869</v>
+      </c>
+      <c r="P186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="P186" s="1" t="n">
+      <c r="Q186" s="1" t="n">
         <v>0.0486</v>
       </c>
     </row>
@@ -10185,10 +10746,13 @@
         <v>0.02667</v>
       </c>
       <c r="O187" s="1" t="n">
+        <v>0.02666</v>
+      </c>
+      <c r="P187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="P187" s="1" t="n">
-        <v>0.02667</v>
+      <c r="Q187" s="1" t="n">
+        <v>0.02666</v>
       </c>
     </row>
     <row r="188">
@@ -10237,10 +10801,13 @@
         <v>0.003302</v>
       </c>
       <c r="O188" s="1" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="P188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="P188" s="1" t="n">
-        <v>0.003302</v>
+      <c r="Q188" s="1" t="n">
+        <v>0.0033</v>
       </c>
     </row>
     <row r="189">
@@ -10289,9 +10856,12 @@
         <v>0.2854</v>
       </c>
       <c r="O189" s="1" t="n">
+        <v>0.2862</v>
+      </c>
+      <c r="P189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="P189" s="1" t="n">
+      <c r="Q189" s="1" t="n">
         <v>0.2854</v>
       </c>
     </row>
@@ -10341,9 +10911,12 @@
         <v>0.01785</v>
       </c>
       <c r="O190" s="1" t="n">
+        <v>0.01787</v>
+      </c>
+      <c r="P190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="P190" s="1" t="n">
+      <c r="Q190" s="1" t="n">
         <v>0.01785</v>
       </c>
     </row>
@@ -10393,10 +10966,13 @@
         <v>0.257</v>
       </c>
       <c r="O191" s="1" t="n">
+        <v>0.2568</v>
+      </c>
+      <c r="P191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="P191" s="1" t="n">
-        <v>0.257</v>
+      <c r="Q191" s="1" t="n">
+        <v>0.2568</v>
       </c>
     </row>
     <row r="192">
@@ -10445,9 +11021,12 @@
         <v>0.03786</v>
       </c>
       <c r="O192" s="1" t="n">
+        <v>0.03817</v>
+      </c>
+      <c r="P192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="P192" s="1" t="n">
+      <c r="Q192" s="1" t="n">
         <v>0.03766</v>
       </c>
     </row>
@@ -10497,9 +11076,12 @@
         <v>0.000222</v>
       </c>
       <c r="O193" s="1" t="n">
+        <v>0.0002214</v>
+      </c>
+      <c r="P193" s="1" t="n">
         <v>0.0002243</v>
       </c>
-      <c r="P193" s="1" t="n">
+      <c r="Q193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -10549,10 +11131,13 @@
         <v>4.066</v>
       </c>
       <c r="O194" s="1" t="n">
+        <v>4.056</v>
+      </c>
+      <c r="P194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="P194" s="1" t="n">
-        <v>4.066</v>
+      <c r="Q194" s="1" t="n">
+        <v>4.056</v>
       </c>
     </row>
     <row r="195">
@@ -10604,6 +11189,9 @@
         <v>0.999401</v>
       </c>
       <c r="P195" s="1" t="n">
+        <v>0.999401</v>
+      </c>
+      <c r="Q195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -10653,9 +11241,12 @@
         <v>4.304</v>
       </c>
       <c r="O196" s="1" t="n">
+        <v>4.287</v>
+      </c>
+      <c r="P196" s="1" t="n">
         <v>4.347</v>
       </c>
-      <c r="P196" s="1" t="n">
+      <c r="Q196" s="1" t="n">
         <v>4.276</v>
       </c>
     </row>
@@ -10705,9 +11296,12 @@
         <v>0.15181</v>
       </c>
       <c r="O197" s="1" t="n">
+        <v>0.15208</v>
+      </c>
+      <c r="P197" s="1" t="n">
         <v>0.15232</v>
       </c>
-      <c r="P197" s="1" t="n">
+      <c r="Q197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -10757,9 +11351,12 @@
         <v>0.007664</v>
       </c>
       <c r="O198" s="1" t="n">
+        <v>0.007702</v>
+      </c>
+      <c r="P198" s="1" t="n">
         <v>0.007899</v>
       </c>
-      <c r="P198" s="1" t="n">
+      <c r="Q198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -10809,9 +11406,12 @@
         <v>0.4484</v>
       </c>
       <c r="O199" s="1" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="P199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="P199" s="1" t="n">
+      <c r="Q199" s="1" t="n">
         <v>0.4482</v>
       </c>
     </row>
@@ -10861,9 +11461,12 @@
         <v>0.5824</v>
       </c>
       <c r="O200" s="1" t="n">
+        <v>0.5841</v>
+      </c>
+      <c r="P200" s="1" t="n">
         <v>0.5911999999999999</v>
       </c>
-      <c r="P200" s="1" t="n">
+      <c r="Q200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -10913,9 +11516,12 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="O201" s="1" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="P201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="P201" s="1" t="n">
+      <c r="Q201" s="1" t="n">
         <v>0.09279999999999999</v>
       </c>
     </row>
@@ -10965,10 +11571,13 @@
         <v>0.06001</v>
       </c>
       <c r="O202" s="1" t="n">
+        <v>0.05999</v>
+      </c>
+      <c r="P202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="P202" s="1" t="n">
-        <v>0.06001</v>
+      <c r="Q202" s="1" t="n">
+        <v>0.05999</v>
       </c>
     </row>
     <row r="203">
@@ -11017,9 +11626,12 @@
         <v>0.008200000000000001</v>
       </c>
       <c r="O203" s="1" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="P203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="P203" s="1" t="n">
+      <c r="Q203" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -11069,10 +11681,13 @@
         <v>0.00417</v>
       </c>
       <c r="O204" s="1" t="n">
+        <v>0.00415</v>
+      </c>
+      <c r="P204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="P204" s="1" t="n">
-        <v>0.00417</v>
+      <c r="Q204" s="1" t="n">
+        <v>0.00415</v>
       </c>
     </row>
     <row r="205">
@@ -11121,9 +11736,12 @@
         <v>0.009127</v>
       </c>
       <c r="O205" s="1" t="n">
+        <v>0.009131</v>
+      </c>
+      <c r="P205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="P205" s="1" t="n">
+      <c r="Q205" s="1" t="n">
         <v>0.009070999999999999</v>
       </c>
     </row>
@@ -11173,9 +11791,12 @@
         <v>0.2397</v>
       </c>
       <c r="O206" s="1" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="P206" s="1" t="n">
         <v>0.2418</v>
       </c>
-      <c r="P206" s="1" t="n">
+      <c r="Q206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -11225,9 +11846,12 @@
         <v>0.0206</v>
       </c>
       <c r="O207" s="1" t="n">
+        <v>0.02057</v>
+      </c>
+      <c r="P207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="P207" s="1" t="n">
+      <c r="Q207" s="1" t="n">
         <v>0.02053</v>
       </c>
     </row>
@@ -11277,10 +11901,13 @@
         <v>0.2366</v>
       </c>
       <c r="O208" s="1" t="n">
+        <v>0.2363</v>
+      </c>
+      <c r="P208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="P208" s="1" t="n">
-        <v>0.2364</v>
+      <c r="Q208" s="1" t="n">
+        <v>0.2363</v>
       </c>
     </row>
     <row r="209">
@@ -11329,9 +11956,12 @@
         <v>0.3596</v>
       </c>
       <c r="O209" s="1" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="P209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="P209" s="1" t="n">
+      <c r="Q209" s="1" t="n">
         <v>0.3586</v>
       </c>
     </row>
@@ -11381,9 +12011,12 @@
         <v>0.04232</v>
       </c>
       <c r="O210" s="1" t="n">
+        <v>0.04248</v>
+      </c>
+      <c r="P210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="P210" s="1" t="n">
+      <c r="Q210" s="1" t="n">
         <v>0.04232</v>
       </c>
     </row>
@@ -11433,10 +12066,13 @@
         <v>0.0004268</v>
       </c>
       <c r="O211" s="1" t="n">
+        <v>0.000425</v>
+      </c>
+      <c r="P211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="P211" s="1" t="n">
-        <v>0.0004256</v>
+      <c r="Q211" s="1" t="n">
+        <v>0.000425</v>
       </c>
     </row>
     <row r="212">
@@ -11485,10 +12121,13 @@
         <v>0.02136</v>
       </c>
       <c r="O212" s="1" t="n">
+        <v>0.02135</v>
+      </c>
+      <c r="P212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="P212" s="1" t="n">
-        <v>0.02136</v>
+      <c r="Q212" s="1" t="n">
+        <v>0.02135</v>
       </c>
     </row>
     <row r="213">
@@ -11537,9 +12176,12 @@
         <v>0.1142</v>
       </c>
       <c r="O213" s="1" t="n">
+        <v>0.1139</v>
+      </c>
+      <c r="P213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="P213" s="1" t="n">
+      <c r="Q213" s="1" t="n">
         <v>0.1137</v>
       </c>
     </row>
@@ -11589,9 +12231,12 @@
         <v>0.04174</v>
       </c>
       <c r="O214" s="1" t="n">
+        <v>0.04179</v>
+      </c>
+      <c r="P214" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="P214" s="1" t="n">
+      <c r="Q214" s="1" t="n">
         <v>0.04174</v>
       </c>
     </row>
@@ -11641,10 +12286,13 @@
         <v>0.009841000000000001</v>
       </c>
       <c r="O215" s="1" t="n">
+        <v>0.009839000000000001</v>
+      </c>
+      <c r="P215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="P215" s="1" t="n">
-        <v>0.009841000000000001</v>
+      <c r="Q215" s="1" t="n">
+        <v>0.009839000000000001</v>
       </c>
     </row>
     <row r="216">
@@ -11693,9 +12341,12 @@
         <v>0.0639</v>
       </c>
       <c r="O216" s="1" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="P216" s="1" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="P216" s="1" t="n">
+      <c r="Q216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -11745,9 +12396,12 @@
         <v>0.004225</v>
       </c>
       <c r="O217" s="1" t="n">
+        <v>0.004207</v>
+      </c>
+      <c r="P217" s="1" t="n">
         <v>0.004266</v>
       </c>
-      <c r="P217" s="1" t="n">
+      <c r="Q217" s="1" t="n">
         <v>0.004177</v>
       </c>
     </row>
@@ -11797,9 +12451,12 @@
         <v>0.00996</v>
       </c>
       <c r="O218" s="1" t="n">
+        <v>0.00996</v>
+      </c>
+      <c r="P218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="P218" s="1" t="n">
+      <c r="Q218" s="1" t="n">
         <v>0.009820000000000001</v>
       </c>
     </row>
@@ -11849,9 +12506,12 @@
         <v>0.02941</v>
       </c>
       <c r="O219" s="1" t="n">
+        <v>0.02962</v>
+      </c>
+      <c r="P219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="P219" s="1" t="n">
+      <c r="Q219" s="1" t="n">
         <v>0.02941</v>
       </c>
     </row>
@@ -11901,10 +12561,13 @@
         <v>2.29</v>
       </c>
       <c r="O220" s="1" t="n">
+        <v>2.288</v>
+      </c>
+      <c r="P220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="P220" s="1" t="n">
-        <v>2.29</v>
+      <c r="Q220" s="1" t="n">
+        <v>2.288</v>
       </c>
     </row>
     <row r="221">
@@ -11953,9 +12616,12 @@
         <v>0.022737</v>
       </c>
       <c r="O221" s="1" t="n">
+        <v>0.02276</v>
+      </c>
+      <c r="P221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="P221" s="1" t="n">
+      <c r="Q221" s="1" t="n">
         <v>0.022737</v>
       </c>
     </row>
@@ -12005,9 +12671,12 @@
         <v>0.0369</v>
       </c>
       <c r="O222" s="1" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="P222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="P222" s="1" t="n">
+      <c r="Q222" s="1" t="n">
         <v>0.0369</v>
       </c>
     </row>
@@ -12057,10 +12726,13 @@
         <v>0.2921</v>
       </c>
       <c r="O223" s="1" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="P223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="P223" s="1" t="n">
-        <v>0.2918</v>
+      <c r="Q223" s="1" t="n">
+        <v>0.2915</v>
       </c>
     </row>
     <row r="224">
@@ -12109,9 +12781,12 @@
         <v>0.01554</v>
       </c>
       <c r="O224" s="1" t="n">
+        <v>0.01548</v>
+      </c>
+      <c r="P224" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="P224" s="1" t="n">
+      <c r="Q224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -12161,10 +12836,13 @@
         <v>0.0004061</v>
       </c>
       <c r="O225" s="1" t="n">
+        <v>0.0004046</v>
+      </c>
+      <c r="P225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="P225" s="1" t="n">
-        <v>0.0004061</v>
+      <c r="Q225" s="1" t="n">
+        <v>0.0004046</v>
       </c>
     </row>
     <row r="226">
@@ -12213,10 +12891,13 @@
         <v>0.08656</v>
       </c>
       <c r="O226" s="1" t="n">
+        <v>0.08595</v>
+      </c>
+      <c r="P226" s="1" t="n">
         <v>0.08815000000000001</v>
       </c>
-      <c r="P226" s="1" t="n">
-        <v>0.08623</v>
+      <c r="Q226" s="1" t="n">
+        <v>0.08595</v>
       </c>
     </row>
     <row r="227">
@@ -12265,9 +12946,12 @@
         <v>0.947</v>
       </c>
       <c r="O227" s="1" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="P227" s="1" t="n">
         <v>0.959</v>
       </c>
-      <c r="P227" s="1" t="n">
+      <c r="Q227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -12317,10 +13001,13 @@
         <v>0.05523</v>
       </c>
       <c r="O228" s="1" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="P228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="P228" s="1" t="n">
-        <v>0.05523</v>
+      <c r="Q228" s="1" t="n">
+        <v>0.055</v>
       </c>
     </row>
     <row r="229">
@@ -12369,10 +13056,13 @@
         <v>0.002</v>
       </c>
       <c r="O229" s="1" t="n">
+        <v>0.001999</v>
+      </c>
+      <c r="P229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="P229" s="1" t="n">
-        <v>0.002</v>
+      <c r="Q229" s="1" t="n">
+        <v>0.001999</v>
       </c>
     </row>
     <row r="230">
@@ -12421,9 +13111,12 @@
         <v>0.022778</v>
       </c>
       <c r="O230" s="1" t="n">
+        <v>0.022824</v>
+      </c>
+      <c r="P230" s="1" t="n">
         <v>0.023101</v>
       </c>
-      <c r="P230" s="1" t="n">
+      <c r="Q230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -12473,10 +13166,13 @@
         <v>0.0535</v>
       </c>
       <c r="O231" s="1" t="n">
+        <v>0.05342</v>
+      </c>
+      <c r="P231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="P231" s="1" t="n">
-        <v>0.0535</v>
+      <c r="Q231" s="1" t="n">
+        <v>0.05342</v>
       </c>
     </row>
     <row r="232">
@@ -12525,10 +13221,13 @@
         <v>0.0588</v>
       </c>
       <c r="O232" s="1" t="n">
+        <v>0.0586</v>
+      </c>
+      <c r="P232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="P232" s="1" t="n">
-        <v>0.0587</v>
+      <c r="Q232" s="1" t="n">
+        <v>0.0586</v>
       </c>
     </row>
     <row r="233">
@@ -12577,9 +13276,12 @@
         <v>0.001676</v>
       </c>
       <c r="O233" s="1" t="n">
+        <v>0.001676</v>
+      </c>
+      <c r="P233" s="1" t="n">
         <v>0.001701</v>
       </c>
-      <c r="P233" s="1" t="n">
+      <c r="Q233" s="1" t="n">
         <v>0.001676</v>
       </c>
     </row>
@@ -12629,9 +13331,12 @@
         <v>0.005738</v>
       </c>
       <c r="O234" s="1" t="n">
+        <v>0.005748</v>
+      </c>
+      <c r="P234" s="1" t="n">
         <v>0.005854</v>
       </c>
-      <c r="P234" s="1" t="n">
+      <c r="Q234" s="1" t="n">
         <v>0.005728</v>
       </c>
     </row>
@@ -12681,10 +13386,13 @@
         <v>0.12365</v>
       </c>
       <c r="O235" s="1" t="n">
+        <v>0.12267</v>
+      </c>
+      <c r="P235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="P235" s="1" t="n">
-        <v>0.12365</v>
+      <c r="Q235" s="1" t="n">
+        <v>0.12267</v>
       </c>
     </row>
     <row r="236">
@@ -12733,9 +13441,12 @@
         <v>64.25</v>
       </c>
       <c r="O236" s="1" t="n">
+        <v>64.36</v>
+      </c>
+      <c r="P236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="P236" s="1" t="n">
+      <c r="Q236" s="1" t="n">
         <v>64.25</v>
       </c>
     </row>
@@ -12785,10 +13496,13 @@
         <v>0.1014</v>
       </c>
       <c r="O237" s="1" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="P237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="P237" s="1" t="n">
-        <v>0.1014</v>
+      <c r="Q237" s="1" t="n">
+        <v>0.1012</v>
       </c>
     </row>
     <row r="238">
@@ -12837,9 +13551,12 @@
         <v>0.004063</v>
       </c>
       <c r="O238" s="1" t="n">
-        <v>0.004063</v>
+        <v>0.004066</v>
       </c>
       <c r="P238" s="1" t="n">
+        <v>0.004066</v>
+      </c>
+      <c r="Q238" s="1" t="n">
         <v>0.003925</v>
       </c>
     </row>
@@ -12889,9 +13606,12 @@
         <v>0.01538</v>
       </c>
       <c r="O239" s="1" t="n">
+        <v>0.01538</v>
+      </c>
+      <c r="P239" s="1" t="n">
         <v>0.01562</v>
       </c>
-      <c r="P239" s="1" t="n">
+      <c r="Q239" s="1" t="n">
         <v>0.01532</v>
       </c>
     </row>
@@ -12941,10 +13661,13 @@
         <v>0.05594</v>
       </c>
       <c r="O240" s="1" t="n">
+        <v>0.05584</v>
+      </c>
+      <c r="P240" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="P240" s="1" t="n">
-        <v>0.05594</v>
+      <c r="Q240" s="1" t="n">
+        <v>0.05584</v>
       </c>
     </row>
     <row r="241">
@@ -12993,9 +13716,12 @@
         <v>0.0113</v>
       </c>
       <c r="O241" s="1" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="P241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="P241" s="1" t="n">
+      <c r="Q241" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -13045,9 +13771,12 @@
         <v>0.3332</v>
       </c>
       <c r="O242" s="1" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="P242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="P242" s="1" t="n">
+      <c r="Q242" s="1" t="n">
         <v>0.3332</v>
       </c>
     </row>
@@ -13097,9 +13826,12 @@
         <v>0.01223</v>
       </c>
       <c r="O243" s="1" t="n">
+        <v>0.01226</v>
+      </c>
+      <c r="P243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="P243" s="1" t="n">
+      <c r="Q243" s="1" t="n">
         <v>0.01223</v>
       </c>
     </row>
@@ -13149,9 +13881,12 @@
         <v>0.08116</v>
       </c>
       <c r="O244" s="1" t="n">
+        <v>0.08044</v>
+      </c>
+      <c r="P244" s="1" t="n">
         <v>0.08121</v>
       </c>
-      <c r="P244" s="1" t="n">
+      <c r="Q244" s="1" t="n">
         <v>0.07997</v>
       </c>
     </row>
@@ -13201,9 +13936,12 @@
         <v>0.007777</v>
       </c>
       <c r="O245" s="1" t="n">
+        <v>0.007808</v>
+      </c>
+      <c r="P245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="P245" s="1" t="n">
+      <c r="Q245" s="1" t="n">
         <v>0.007769</v>
       </c>
     </row>
@@ -13253,9 +13991,12 @@
         <v>0.03025</v>
       </c>
       <c r="O246" s="1" t="n">
+        <v>0.03027</v>
+      </c>
+      <c r="P246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="P246" s="1" t="n">
+      <c r="Q246" s="1" t="n">
         <v>0.03025</v>
       </c>
     </row>
@@ -13305,9 +14046,12 @@
         <v>0.1802</v>
       </c>
       <c r="O247" s="1" t="n">
+        <v>0.1803</v>
+      </c>
+      <c r="P247" s="1" t="n">
         <v>0.1827</v>
       </c>
-      <c r="P247" s="1" t="n">
+      <c r="Q247" s="1" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -13357,10 +14101,13 @@
         <v>0.05867</v>
       </c>
       <c r="O248" s="1" t="n">
+        <v>0.0586</v>
+      </c>
+      <c r="P248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="P248" s="1" t="n">
-        <v>0.05867</v>
+      <c r="Q248" s="1" t="n">
+        <v>0.0586</v>
       </c>
     </row>
     <row r="249">
@@ -13409,9 +14156,12 @@
         <v>0.1656</v>
       </c>
       <c r="O249" s="1" t="n">
+        <v>0.1663</v>
+      </c>
+      <c r="P249" s="1" t="n">
         <v>0.1684</v>
       </c>
-      <c r="P249" s="1" t="n">
+      <c r="Q249" s="1" t="n">
         <v>0.1656</v>
       </c>
     </row>
@@ -13461,10 +14211,13 @@
         <v>0.01904</v>
       </c>
       <c r="O250" s="1" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="P250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="P250" s="1" t="n">
-        <v>0.01904</v>
+      <c r="Q250" s="1" t="n">
+        <v>0.019</v>
       </c>
     </row>
     <row r="251">
@@ -13513,9 +14266,12 @@
         <v>0.0232</v>
       </c>
       <c r="O251" s="1" t="n">
+        <v>0.02308</v>
+      </c>
+      <c r="P251" s="1" t="n">
         <v>0.02322</v>
       </c>
-      <c r="P251" s="1" t="n">
+      <c r="Q251" s="1" t="n">
         <v>0.02295</v>
       </c>
     </row>
@@ -13565,9 +14321,12 @@
         <v>0.30436</v>
       </c>
       <c r="O252" s="1" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="P252" s="1" t="n">
         <v>0.31227</v>
       </c>
-      <c r="P252" s="1" t="n">
+      <c r="Q252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -13617,9 +14376,12 @@
         <v>0.005992</v>
       </c>
       <c r="O253" s="1" t="n">
+        <v>0.005979</v>
+      </c>
+      <c r="P253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="P253" s="1" t="n">
+      <c r="Q253" s="1" t="n">
         <v>0.005971</v>
       </c>
     </row>
@@ -13669,9 +14431,12 @@
         <v>0.6123</v>
       </c>
       <c r="O254" s="1" t="n">
+        <v>0.6123</v>
+      </c>
+      <c r="P254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="P254" s="1" t="n">
+      <c r="Q254" s="1" t="n">
         <v>0.6116</v>
       </c>
     </row>
@@ -13721,9 +14486,12 @@
         <v>0.10601</v>
       </c>
       <c r="O255" s="1" t="n">
+        <v>0.10619</v>
+      </c>
+      <c r="P255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="P255" s="1" t="n">
+      <c r="Q255" s="1" t="n">
         <v>0.10601</v>
       </c>
     </row>
@@ -13773,9 +14541,12 @@
         <v>0.0902</v>
       </c>
       <c r="O256" s="1" t="n">
+        <v>0.09030000000000001</v>
+      </c>
+      <c r="P256" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="P256" s="1" t="n">
+      <c r="Q256" s="1" t="n">
         <v>0.0901</v>
       </c>
     </row>
@@ -13825,9 +14596,12 @@
         <v>0.01451</v>
       </c>
       <c r="O257" s="1" t="n">
+        <v>0.01456</v>
+      </c>
+      <c r="P257" s="1" t="n">
         <v>0.01468</v>
       </c>
-      <c r="P257" s="1" t="n">
+      <c r="Q257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -13877,10 +14651,13 @@
         <v>0.05013</v>
       </c>
       <c r="O258" s="1" t="n">
+        <v>0.0499</v>
+      </c>
+      <c r="P258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="P258" s="1" t="n">
-        <v>0.05013</v>
+      <c r="Q258" s="1" t="n">
+        <v>0.0499</v>
       </c>
     </row>
     <row r="259">
@@ -13929,10 +14706,13 @@
         <v>0.008070000000000001</v>
       </c>
       <c r="O259" s="1" t="n">
+        <v>0.00804</v>
+      </c>
+      <c r="P259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="P259" s="1" t="n">
-        <v>0.008070000000000001</v>
+      <c r="Q259" s="1" t="n">
+        <v>0.00804</v>
       </c>
     </row>
     <row r="260">
@@ -13981,9 +14761,12 @@
         <v>0.1898</v>
       </c>
       <c r="O260" s="1" t="n">
+        <v>0.1897</v>
+      </c>
+      <c r="P260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="P260" s="1" t="n">
+      <c r="Q260" s="1" t="n">
         <v>0.1894</v>
       </c>
     </row>
@@ -14033,9 +14816,12 @@
         <v>0.0979</v>
       </c>
       <c r="O261" s="1" t="n">
+        <v>0.0979</v>
+      </c>
+      <c r="P261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="P261" s="1" t="n">
+      <c r="Q261" s="1" t="n">
         <v>0.0979</v>
       </c>
     </row>
@@ -14085,9 +14871,12 @@
         <v>0.2107</v>
       </c>
       <c r="O262" s="1" t="n">
+        <v>0.2109</v>
+      </c>
+      <c r="P262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="P262" s="1" t="n">
+      <c r="Q262" s="1" t="n">
         <v>0.2107</v>
       </c>
     </row>
@@ -14137,9 +14926,12 @@
         <v>0.008529999999999999</v>
       </c>
       <c r="O263" s="1" t="n">
+        <v>0.008489</v>
+      </c>
+      <c r="P263" s="1" t="n">
         <v>0.008560999999999999</v>
       </c>
-      <c r="P263" s="1" t="n">
+      <c r="Q263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -14189,9 +14981,12 @@
         <v>2.629</v>
       </c>
       <c r="O264" s="1" t="n">
+        <v>2.636</v>
+      </c>
+      <c r="P264" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="P264" s="1" t="n">
+      <c r="Q264" s="1" t="n">
         <v>2.629</v>
       </c>
     </row>
@@ -14241,9 +15036,12 @@
         <v>0.01869</v>
       </c>
       <c r="O265" s="1" t="n">
+        <v>0.0186</v>
+      </c>
+      <c r="P265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="P265" s="1" t="n">
+      <c r="Q265" s="1" t="n">
         <v>0.01847</v>
       </c>
     </row>
@@ -14293,9 +15091,12 @@
         <v>0.3595</v>
       </c>
       <c r="O266" s="1" t="n">
-        <v>0.3607</v>
+        <v>0.3612</v>
       </c>
       <c r="P266" s="1" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="Q266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -14345,9 +15146,12 @@
         <v>0.034</v>
       </c>
       <c r="O267" s="1" t="n">
+        <v>0.03408</v>
+      </c>
+      <c r="P267" s="1" t="n">
         <v>0.03464</v>
       </c>
-      <c r="P267" s="1" t="n">
+      <c r="Q267" s="1" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -14397,9 +15201,12 @@
         <v>0.118</v>
       </c>
       <c r="O268" s="1" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="P268" s="1" t="n">
         <v>0.121</v>
       </c>
-      <c r="P268" s="1" t="n">
+      <c r="Q268" s="1" t="n">
         <v>0.117</v>
       </c>
     </row>
@@ -14449,9 +15256,12 @@
         <v>0.07997</v>
       </c>
       <c r="O269" s="1" t="n">
+        <v>0.08014</v>
+      </c>
+      <c r="P269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="P269" s="1" t="n">
+      <c r="Q269" s="1" t="n">
         <v>0.07973</v>
       </c>
     </row>
@@ -14501,10 +15311,13 @@
         <v>0.0138</v>
       </c>
       <c r="O270" s="1" t="n">
+        <v>0.01377</v>
+      </c>
+      <c r="P270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="P270" s="1" t="n">
-        <v>0.0138</v>
+      <c r="Q270" s="1" t="n">
+        <v>0.01377</v>
       </c>
     </row>
     <row r="271">
@@ -14553,10 +15366,13 @@
         <v>0.007538</v>
       </c>
       <c r="O271" s="1" t="n">
+        <v>0.007526</v>
+      </c>
+      <c r="P271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="P271" s="1" t="n">
-        <v>0.007538</v>
+      <c r="Q271" s="1" t="n">
+        <v>0.007526</v>
       </c>
     </row>
     <row r="272">
@@ -14605,9 +15421,12 @@
         <v>0.07405</v>
       </c>
       <c r="O272" s="1" t="n">
+        <v>0.07413</v>
+      </c>
+      <c r="P272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="P272" s="1" t="n">
+      <c r="Q272" s="1" t="n">
         <v>0.07405</v>
       </c>
     </row>
@@ -14657,9 +15476,12 @@
         <v>3.14e-05</v>
       </c>
       <c r="O273" s="1" t="n">
+        <v>3.14e-05</v>
+      </c>
+      <c r="P273" s="1" t="n">
         <v>3.16e-05</v>
       </c>
-      <c r="P273" s="1" t="n">
+      <c r="Q273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -14709,10 +15531,13 @@
         <v>0.005434</v>
       </c>
       <c r="O274" s="1" t="n">
+        <v>0.005414</v>
+      </c>
+      <c r="P274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="P274" s="1" t="n">
-        <v>0.005434</v>
+      <c r="Q274" s="1" t="n">
+        <v>0.005414</v>
       </c>
     </row>
     <row r="275">
@@ -14761,10 +15586,13 @@
         <v>0.181</v>
       </c>
       <c r="O275" s="1" t="n">
+        <v>0.1801</v>
+      </c>
+      <c r="P275" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="P275" s="1" t="n">
-        <v>0.1802</v>
+      <c r="Q275" s="1" t="n">
+        <v>0.1801</v>
       </c>
     </row>
     <row r="276">
@@ -14813,9 +15641,12 @@
         <v>0.00682</v>
       </c>
       <c r="O276" s="1" t="n">
+        <v>0.00683</v>
+      </c>
+      <c r="P276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="P276" s="1" t="n">
+      <c r="Q276" s="1" t="n">
         <v>0.00682</v>
       </c>
     </row>
@@ -14865,9 +15696,12 @@
         <v>0.1303</v>
       </c>
       <c r="O277" s="1" t="n">
+        <v>0.1306</v>
+      </c>
+      <c r="P277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="P277" s="1" t="n">
+      <c r="Q277" s="1" t="n">
         <v>0.1303</v>
       </c>
     </row>
@@ -14917,9 +15751,12 @@
         <v>0.02317</v>
       </c>
       <c r="O278" s="1" t="n">
+        <v>0.02313</v>
+      </c>
+      <c r="P278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="P278" s="1" t="n">
+      <c r="Q278" s="1" t="n">
         <v>0.02308</v>
       </c>
     </row>
@@ -14969,9 +15806,12 @@
         <v>0.01837</v>
       </c>
       <c r="O279" s="1" t="n">
+        <v>0.01815</v>
+      </c>
+      <c r="P279" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="P279" s="1" t="n">
+      <c r="Q279" s="1" t="n">
         <v>0.01812</v>
       </c>
     </row>
@@ -15021,10 +15861,13 @@
         <v>0.03697</v>
       </c>
       <c r="O280" s="1" t="n">
+        <v>0.03681</v>
+      </c>
+      <c r="P280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="P280" s="1" t="n">
-        <v>0.03697</v>
+      <c r="Q280" s="1" t="n">
+        <v>0.03681</v>
       </c>
     </row>
     <row r="281">
@@ -15073,9 +15916,12 @@
         <v>0.03976</v>
       </c>
       <c r="O281" s="1" t="n">
+        <v>0.0396</v>
+      </c>
+      <c r="P281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="P281" s="1" t="n">
+      <c r="Q281" s="1" t="n">
         <v>0.03953</v>
       </c>
     </row>
@@ -15125,9 +15971,12 @@
         <v>0.3013</v>
       </c>
       <c r="O282" s="1" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="P282" s="1" t="n">
         <v>0.3059</v>
       </c>
-      <c r="P282" s="1" t="n">
+      <c r="Q282" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -15177,9 +16026,12 @@
         <v>0.01119</v>
       </c>
       <c r="O283" s="1" t="n">
+        <v>0.01119</v>
+      </c>
+      <c r="P283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="P283" s="1" t="n">
+      <c r="Q283" s="1" t="n">
         <v>0.01119</v>
       </c>
     </row>
@@ -15229,9 +16081,12 @@
         <v>9.6e-06</v>
       </c>
       <c r="O284" s="1" t="n">
+        <v>9.7e-06</v>
+      </c>
+      <c r="P284" s="1" t="n">
         <v>9.799999999999999e-06</v>
       </c>
-      <c r="P284" s="1" t="n">
+      <c r="Q284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -15281,9 +16136,12 @@
         <v>0.1145</v>
       </c>
       <c r="O285" s="1" t="n">
+        <v>0.1145</v>
+      </c>
+      <c r="P285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="P285" s="1" t="n">
+      <c r="Q285" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -15333,9 +16191,12 @@
         <v>0.003432</v>
       </c>
       <c r="O286" s="1" t="n">
+        <v>0.003428</v>
+      </c>
+      <c r="P286" s="1" t="n">
         <v>0.003485</v>
       </c>
-      <c r="P286" s="1" t="n">
+      <c r="Q286" s="1" t="n">
         <v>0.003422</v>
       </c>
     </row>
@@ -15385,9 +16246,12 @@
         <v>0.08499</v>
       </c>
       <c r="O287" s="1" t="n">
+        <v>0.08497</v>
+      </c>
+      <c r="P287" s="1" t="n">
         <v>0.08577</v>
       </c>
-      <c r="P287" s="1" t="n">
+      <c r="Q287" s="1" t="n">
         <v>0.08486</v>
       </c>
     </row>
@@ -15437,9 +16301,12 @@
         <v>0.1</v>
       </c>
       <c r="O288" s="1" t="n">
+        <v>0.09934</v>
+      </c>
+      <c r="P288" s="1" t="n">
         <v>0.10076</v>
       </c>
-      <c r="P288" s="1" t="n">
+      <c r="Q288" s="1" t="n">
         <v>0.09869</v>
       </c>
     </row>
@@ -15489,9 +16356,12 @@
         <v>0.4367</v>
       </c>
       <c r="O289" s="1" t="n">
+        <v>0.4338</v>
+      </c>
+      <c r="P289" s="1" t="n">
         <v>0.4367</v>
       </c>
-      <c r="P289" s="1" t="n">
+      <c r="Q289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -15541,9 +16411,12 @@
         <v>0.03929</v>
       </c>
       <c r="O290" s="1" t="n">
+        <v>0.03914</v>
+      </c>
+      <c r="P290" s="1" t="n">
         <v>0.03966</v>
       </c>
-      <c r="P290" s="1" t="n">
+      <c r="Q290" s="1" t="n">
         <v>0.03878</v>
       </c>
     </row>
@@ -15593,10 +16466,13 @@
         <v>0.2357</v>
       </c>
       <c r="O291" s="1" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="P291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="P291" s="1" t="n">
-        <v>0.2357</v>
+      <c r="Q291" s="1" t="n">
+        <v>0.235</v>
       </c>
     </row>
     <row r="292">
@@ -15645,9 +16521,12 @@
         <v>0.28237</v>
       </c>
       <c r="O292" s="1" t="n">
+        <v>0.28304</v>
+      </c>
+      <c r="P292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="P292" s="1" t="n">
+      <c r="Q292" s="1" t="n">
         <v>0.28126</v>
       </c>
     </row>
@@ -15697,9 +16576,12 @@
         <v>0.1496</v>
       </c>
       <c r="O293" s="1" t="n">
+        <v>0.1494</v>
+      </c>
+      <c r="P293" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="P293" s="1" t="n">
+      <c r="Q293" s="1" t="n">
         <v>0.1489</v>
       </c>
     </row>
@@ -15749,10 +16631,13 @@
         <v>4.182</v>
       </c>
       <c r="O294" s="1" t="n">
+        <v>4.181</v>
+      </c>
+      <c r="P294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="P294" s="1" t="n">
-        <v>4.182</v>
+      <c r="Q294" s="1" t="n">
+        <v>4.181</v>
       </c>
     </row>
     <row r="295">
@@ -15801,9 +16686,12 @@
         <v>0.0338</v>
       </c>
       <c r="O295" s="1" t="n">
-        <v>0.0338</v>
+        <v>0.03406</v>
       </c>
       <c r="P295" s="1" t="n">
+        <v>0.03406</v>
+      </c>
+      <c r="Q295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -15853,9 +16741,12 @@
         <v>0.000969</v>
       </c>
       <c r="O296" s="1" t="n">
+        <v>0.000966</v>
+      </c>
+      <c r="P296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="P296" s="1" t="n">
+      <c r="Q296" s="1" t="n">
         <v>0.000965</v>
       </c>
     </row>
@@ -15905,9 +16796,12 @@
         <v>0.08155</v>
       </c>
       <c r="O297" s="1" t="n">
+        <v>0.08161</v>
+      </c>
+      <c r="P297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="P297" s="1" t="n">
+      <c r="Q297" s="1" t="n">
         <v>0.08154</v>
       </c>
     </row>
@@ -15957,9 +16851,12 @@
         <v>0.05807</v>
       </c>
       <c r="O298" s="1" t="n">
+        <v>0.05789</v>
+      </c>
+      <c r="P298" s="1" t="n">
         <v>0.05845</v>
       </c>
-      <c r="P298" s="1" t="n">
+      <c r="Q298" s="1" t="n">
         <v>0.05745</v>
       </c>
     </row>
@@ -16009,10 +16906,13 @@
         <v>0.0906</v>
       </c>
       <c r="O299" s="1" t="n">
+        <v>0.09039</v>
+      </c>
+      <c r="P299" s="1" t="n">
         <v>0.0917</v>
       </c>
-      <c r="P299" s="1" t="n">
-        <v>0.0906</v>
+      <c r="Q299" s="1" t="n">
+        <v>0.09039</v>
       </c>
     </row>
     <row r="300">
@@ -16061,10 +16961,13 @@
         <v>0.02734</v>
       </c>
       <c r="O300" s="1" t="n">
+        <v>0.02724</v>
+      </c>
+      <c r="P300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="P300" s="1" t="n">
-        <v>0.02734</v>
+      <c r="Q300" s="1" t="n">
+        <v>0.02724</v>
       </c>
     </row>
     <row r="301">
@@ -16113,10 +17016,13 @@
         <v>0.0654</v>
       </c>
       <c r="O301" s="1" t="n">
+        <v>0.06526999999999999</v>
+      </c>
+      <c r="P301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="P301" s="1" t="n">
-        <v>0.0654</v>
+      <c r="Q301" s="1" t="n">
+        <v>0.06526999999999999</v>
       </c>
     </row>
     <row r="302">
@@ -16165,9 +17071,12 @@
         <v>0.053535</v>
       </c>
       <c r="O302" s="1" t="n">
+        <v>0.053559</v>
+      </c>
+      <c r="P302" s="1" t="n">
         <v>0.053585</v>
       </c>
-      <c r="P302" s="1" t="n">
+      <c r="Q302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -16217,9 +17126,12 @@
         <v>5166.4</v>
       </c>
       <c r="O303" s="1" t="n">
+        <v>5173.5</v>
+      </c>
+      <c r="P303" s="1" t="n">
         <v>5177.6</v>
       </c>
-      <c r="P303" s="1" t="n">
+      <c r="Q303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -16269,10 +17181,13 @@
         <v>14.85</v>
       </c>
       <c r="O304" s="1" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="P304" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="P304" s="1" t="n">
-        <v>14.85</v>
+      <c r="Q304" s="1" t="n">
+        <v>14.82</v>
       </c>
     </row>
     <row r="305">
@@ -16321,9 +17236,12 @@
         <v>0.003706</v>
       </c>
       <c r="O305" s="1" t="n">
+        <v>0.003698</v>
+      </c>
+      <c r="P305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="P305" s="1" t="n">
+      <c r="Q305" s="1" t="n">
         <v>0.003695</v>
       </c>
     </row>
@@ -16373,9 +17291,12 @@
         <v>0.4531</v>
       </c>
       <c r="O306" s="1" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="P306" s="1" t="n">
         <v>0.4608</v>
       </c>
-      <c r="P306" s="1" t="n">
+      <c r="Q306" s="1" t="n">
         <v>0.4531</v>
       </c>
     </row>
@@ -16425,9 +17346,12 @@
         <v>0.04666</v>
       </c>
       <c r="O307" s="1" t="n">
+        <v>0.04666</v>
+      </c>
+      <c r="P307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="P307" s="1" t="n">
+      <c r="Q307" s="1" t="n">
         <v>0.04666</v>
       </c>
     </row>
@@ -16477,9 +17401,12 @@
         <v>1.4978</v>
       </c>
       <c r="O308" s="1" t="n">
-        <v>1.4978</v>
+        <v>1.4997</v>
       </c>
       <c r="P308" s="1" t="n">
+        <v>1.4997</v>
+      </c>
+      <c r="Q308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -16529,9 +17456,12 @@
         <v>0.000803</v>
       </c>
       <c r="O309" s="1" t="n">
+        <v>0.0007989</v>
+      </c>
+      <c r="P309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="P309" s="1" t="n">
+      <c r="Q309" s="1" t="n">
         <v>0.0007892</v>
       </c>
     </row>
@@ -16581,10 +17511,13 @@
         <v>4.577</v>
       </c>
       <c r="O310" s="1" t="n">
+        <v>4.553</v>
+      </c>
+      <c r="P310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="P310" s="1" t="n">
-        <v>4.577</v>
+      <c r="Q310" s="1" t="n">
+        <v>4.553</v>
       </c>
     </row>
     <row r="311">
@@ -16633,9 +17566,12 @@
         <v>4.756</v>
       </c>
       <c r="O311" s="1" t="n">
+        <v>4.768</v>
+      </c>
+      <c r="P311" s="1" t="n">
         <v>4.805</v>
       </c>
-      <c r="P311" s="1" t="n">
+      <c r="Q311" s="1" t="n">
         <v>4.743</v>
       </c>
     </row>
@@ -16685,9 +17621,12 @@
         <v>0.08126</v>
       </c>
       <c r="O312" s="1" t="n">
+        <v>0.08173</v>
+      </c>
+      <c r="P312" s="1" t="n">
         <v>0.08212</v>
       </c>
-      <c r="P312" s="1" t="n">
+      <c r="Q312" s="1" t="n">
         <v>0.08098</v>
       </c>
     </row>
@@ -16737,10 +17676,13 @@
         <v>2.012</v>
       </c>
       <c r="O313" s="1" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="P313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="P313" s="1" t="n">
-        <v>2.012</v>
+      <c r="Q313" s="1" t="n">
+        <v>2.01</v>
       </c>
     </row>
     <row r="314">
@@ -16789,9 +17731,12 @@
         <v>0.07343</v>
       </c>
       <c r="O314" s="1" t="n">
+        <v>0.07239</v>
+      </c>
+      <c r="P314" s="1" t="n">
         <v>0.07482999999999999</v>
       </c>
-      <c r="P314" s="1" t="n">
+      <c r="Q314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -16841,9 +17786,12 @@
         <v>0.9350000000000001</v>
       </c>
       <c r="O315" s="1" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="P315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="P315" s="1" t="n">
+      <c r="Q315" s="1" t="n">
         <v>0.9350000000000001</v>
       </c>
     </row>
@@ -16893,9 +17841,12 @@
         <v>0.1305</v>
       </c>
       <c r="O316" s="1" t="n">
+        <v>0.1304</v>
+      </c>
+      <c r="P316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="P316" s="1" t="n">
+      <c r="Q316" s="1" t="n">
         <v>0.1299</v>
       </c>
     </row>
@@ -16945,9 +17896,12 @@
         <v>0.1849</v>
       </c>
       <c r="O317" s="1" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="P317" s="1" t="n">
         <v>0.186</v>
       </c>
-      <c r="P317" s="1" t="n">
+      <c r="Q317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -16997,9 +17951,12 @@
         <v>0.01607</v>
       </c>
       <c r="O318" s="1" t="n">
+        <v>0.01607</v>
+      </c>
+      <c r="P318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="P318" s="1" t="n">
+      <c r="Q318" s="1" t="n">
         <v>0.01607</v>
       </c>
     </row>
@@ -17049,9 +18006,12 @@
         <v>0.08325</v>
       </c>
       <c r="O319" s="1" t="n">
+        <v>0.08327</v>
+      </c>
+      <c r="P319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="P319" s="1" t="n">
+      <c r="Q319" s="1" t="n">
         <v>0.08325</v>
       </c>
     </row>
@@ -17101,10 +18061,13 @@
         <v>0.00754</v>
       </c>
       <c r="O320" s="1" t="n">
+        <v>0.007514</v>
+      </c>
+      <c r="P320" s="1" t="n">
         <v>0.007667</v>
       </c>
-      <c r="P320" s="1" t="n">
-        <v>0.00754</v>
+      <c r="Q320" s="1" t="n">
+        <v>0.007514</v>
       </c>
     </row>
     <row r="321">
@@ -17153,9 +18116,12 @@
         <v>0.05422</v>
       </c>
       <c r="O321" s="1" t="n">
+        <v>0.05425</v>
+      </c>
+      <c r="P321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="P321" s="1" t="n">
+      <c r="Q321" s="1" t="n">
         <v>0.05406</v>
       </c>
     </row>
@@ -17205,9 +18171,12 @@
         <v>0.5483</v>
       </c>
       <c r="O322" s="1" t="n">
+        <v>0.5495</v>
+      </c>
+      <c r="P322" s="1" t="n">
         <v>0.5515</v>
       </c>
-      <c r="P322" s="1" t="n">
+      <c r="Q322" s="1" t="n">
         <v>0.5476</v>
       </c>
     </row>
@@ -17257,9 +18226,12 @@
         <v>0.07588</v>
       </c>
       <c r="O323" s="1" t="n">
+        <v>0.07584</v>
+      </c>
+      <c r="P323" s="1" t="n">
         <v>0.07636999999999999</v>
       </c>
-      <c r="P323" s="1" t="n">
+      <c r="Q323" s="1" t="n">
         <v>0.07525</v>
       </c>
     </row>
@@ -17309,9 +18281,12 @@
         <v>0.01291</v>
       </c>
       <c r="O324" s="1" t="n">
+        <v>0.012989</v>
+      </c>
+      <c r="P324" s="1" t="n">
         <v>0.013001</v>
       </c>
-      <c r="P324" s="1" t="n">
+      <c r="Q324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -17361,10 +18336,13 @@
         <v>0.0989</v>
       </c>
       <c r="O325" s="1" t="n">
+        <v>0.0988</v>
+      </c>
+      <c r="P325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="P325" s="1" t="n">
-        <v>0.0989</v>
+      <c r="Q325" s="1" t="n">
+        <v>0.0988</v>
       </c>
     </row>
     <row r="326">
@@ -17413,9 +18391,12 @@
         <v>0.01736</v>
       </c>
       <c r="O326" s="1" t="n">
+        <v>0.01734</v>
+      </c>
+      <c r="P326" s="1" t="n">
         <v>0.01765</v>
       </c>
-      <c r="P326" s="1" t="n">
+      <c r="Q326" s="1" t="n">
         <v>0.01731</v>
       </c>
     </row>
@@ -17465,10 +18446,13 @@
         <v>0.06386</v>
       </c>
       <c r="O327" s="1" t="n">
+        <v>0.0638</v>
+      </c>
+      <c r="P327" s="1" t="n">
         <v>0.06435</v>
       </c>
-      <c r="P327" s="1" t="n">
-        <v>0.06382</v>
+      <c r="Q327" s="1" t="n">
+        <v>0.0638</v>
       </c>
     </row>
     <row r="328">
@@ -17517,10 +18501,13 @@
         <v>0.2616</v>
       </c>
       <c r="O328" s="1" t="n">
+        <v>0.2614</v>
+      </c>
+      <c r="P328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="P328" s="1" t="n">
-        <v>0.2616</v>
+      <c r="Q328" s="1" t="n">
+        <v>0.2614</v>
       </c>
     </row>
     <row r="329">
@@ -17569,9 +18556,12 @@
         <v>0.17337</v>
       </c>
       <c r="O329" s="1" t="n">
-        <v>0.17341</v>
+        <v>0.17406</v>
       </c>
       <c r="P329" s="1" t="n">
+        <v>0.17406</v>
+      </c>
+      <c r="Q329" s="1" t="n">
         <v>0.17145</v>
       </c>
     </row>
@@ -17621,9 +18611,12 @@
         <v>2.061</v>
       </c>
       <c r="O330" s="1" t="n">
+        <v>2.046</v>
+      </c>
+      <c r="P330" s="1" t="n">
         <v>2.088</v>
       </c>
-      <c r="P330" s="1" t="n">
+      <c r="Q330" s="1" t="n">
         <v>2.043</v>
       </c>
     </row>
@@ -17673,9 +18666,12 @@
         <v>0.0283</v>
       </c>
       <c r="O331" s="1" t="n">
+        <v>0.0284</v>
+      </c>
+      <c r="P331" s="1" t="n">
         <v>0.0288</v>
       </c>
-      <c r="P331" s="1" t="n">
+      <c r="Q331" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -17725,9 +18721,12 @@
         <v>0.006063</v>
       </c>
       <c r="O332" s="1" t="n">
+        <v>0.006006</v>
+      </c>
+      <c r="P332" s="1" t="n">
         <v>0.006063</v>
       </c>
-      <c r="P332" s="1" t="n">
+      <c r="Q332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -17777,9 +18776,12 @@
         <v>0.003519</v>
       </c>
       <c r="O333" s="1" t="n">
+        <v>0.003513</v>
+      </c>
+      <c r="P333" s="1" t="n">
         <v>0.003579</v>
       </c>
-      <c r="P333" s="1" t="n">
+      <c r="Q333" s="1" t="n">
         <v>0.003497</v>
       </c>
     </row>
@@ -17829,9 +18831,12 @@
         <v>0.01397</v>
       </c>
       <c r="O334" s="1" t="n">
+        <v>0.01401</v>
+      </c>
+      <c r="P334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="P334" s="1" t="n">
+      <c r="Q334" s="1" t="n">
         <v>0.01394</v>
       </c>
     </row>
@@ -17881,9 +18886,12 @@
         <v>1.132</v>
       </c>
       <c r="O335" s="1" t="n">
-        <v>1.136</v>
+        <v>1.14</v>
       </c>
       <c r="P335" s="1" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Q335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -17933,9 +18941,12 @@
         <v>0.011344</v>
       </c>
       <c r="O336" s="1" t="n">
+        <v>0.011289</v>
+      </c>
+      <c r="P336" s="1" t="n">
         <v>0.011344</v>
       </c>
-      <c r="P336" s="1" t="n">
+      <c r="Q336" s="1" t="n">
         <v>0.011238</v>
       </c>
     </row>
@@ -17985,9 +18996,12 @@
         <v>2.945</v>
       </c>
       <c r="O337" s="1" t="n">
+        <v>2.952</v>
+      </c>
+      <c r="P337" s="1" t="n">
         <v>3.043</v>
       </c>
-      <c r="P337" s="1" t="n">
+      <c r="Q337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -18037,10 +19051,13 @@
         <v>0.01854</v>
       </c>
       <c r="O338" s="1" t="n">
+        <v>0.01851</v>
+      </c>
+      <c r="P338" s="1" t="n">
         <v>0.01885</v>
       </c>
-      <c r="P338" s="1" t="n">
-        <v>0.01854</v>
+      <c r="Q338" s="1" t="n">
+        <v>0.01851</v>
       </c>
     </row>
     <row r="339">
@@ -18089,9 +19106,12 @@
         <v>0.07721</v>
       </c>
       <c r="O339" s="1" t="n">
+        <v>0.07725</v>
+      </c>
+      <c r="P339" s="1" t="n">
         <v>0.07790999999999999</v>
       </c>
-      <c r="P339" s="1" t="n">
+      <c r="Q339" s="1" t="n">
         <v>0.07689</v>
       </c>
     </row>
@@ -18141,9 +19161,12 @@
         <v>0.075</v>
       </c>
       <c r="O340" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="P340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="P340" s="1" t="n">
+      <c r="Q340" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -18193,9 +19216,12 @@
         <v>0.03581</v>
       </c>
       <c r="O341" s="1" t="n">
+        <v>0.03585</v>
+      </c>
+      <c r="P341" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="P341" s="1" t="n">
+      <c r="Q341" s="1" t="n">
         <v>0.03581</v>
       </c>
     </row>
@@ -18245,9 +19271,12 @@
         <v>2599</v>
       </c>
       <c r="O342" s="1" t="n">
+        <v>2602</v>
+      </c>
+      <c r="P342" s="1" t="n">
         <v>2647</v>
       </c>
-      <c r="P342" s="1" t="n">
+      <c r="Q342" s="1" t="n">
         <v>2599</v>
       </c>
     </row>
@@ -18297,9 +19326,12 @@
         <v>0.0002003</v>
       </c>
       <c r="O343" s="1" t="n">
+        <v>0.0001995</v>
+      </c>
+      <c r="P343" s="1" t="n">
         <v>0.0002003</v>
       </c>
-      <c r="P343" s="1" t="n">
+      <c r="Q343" s="1" t="n">
         <v>0.0001959</v>
       </c>
     </row>
@@ -18349,9 +19381,12 @@
         <v>0.0794</v>
       </c>
       <c r="O344" s="1" t="n">
+        <v>0.07929</v>
+      </c>
+      <c r="P344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="P344" s="1" t="n">
+      <c r="Q344" s="1" t="n">
         <v>0.07925</v>
       </c>
     </row>
@@ -18401,9 +19436,12 @@
         <v>0.01639</v>
       </c>
       <c r="O345" s="1" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="P345" s="1" t="n">
         <v>0.0168</v>
       </c>
-      <c r="P345" s="1" t="n">
+      <c r="Q345" s="1" t="n">
         <v>0.0163</v>
       </c>
     </row>
@@ -18453,10 +19491,13 @@
         <v>2.735</v>
       </c>
       <c r="O346" s="1" t="n">
+        <v>2.734</v>
+      </c>
+      <c r="P346" s="1" t="n">
         <v>2.799</v>
       </c>
-      <c r="P346" s="1" t="n">
-        <v>2.735</v>
+      <c r="Q346" s="1" t="n">
+        <v>2.734</v>
       </c>
     </row>
     <row r="347">
@@ -18505,9 +19546,12 @@
         <v>0.01626</v>
       </c>
       <c r="O347" s="1" t="n">
+        <v>0.01626</v>
+      </c>
+      <c r="P347" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="P347" s="1" t="n">
+      <c r="Q347" s="1" t="n">
         <v>0.01626</v>
       </c>
     </row>
@@ -18557,9 +19601,12 @@
         <v>0.03968</v>
       </c>
       <c r="O348" s="1" t="n">
+        <v>0.03951</v>
+      </c>
+      <c r="P348" s="1" t="n">
         <v>0.03968</v>
       </c>
-      <c r="P348" s="1" t="n">
+      <c r="Q348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -18609,9 +19656,12 @@
         <v>0.3033</v>
       </c>
       <c r="O349" s="1" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="P349" s="1" t="n">
         <v>0.3065</v>
       </c>
-      <c r="P349" s="1" t="n">
+      <c r="Q349" s="1" t="n">
         <v>0.3028</v>
       </c>
     </row>
@@ -18661,9 +19711,12 @@
         <v>0.005096</v>
       </c>
       <c r="O350" s="1" t="n">
+        <v>0.005096</v>
+      </c>
+      <c r="P350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="P350" s="1" t="n">
+      <c r="Q350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -18713,9 +19766,12 @@
         <v>0.005071</v>
       </c>
       <c r="O351" s="1" t="n">
+        <v>0.005072</v>
+      </c>
+      <c r="P351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="P351" s="1" t="n">
+      <c r="Q351" s="1" t="n">
         <v>0.005065</v>
       </c>
     </row>
@@ -18765,10 +19821,13 @@
         <v>0.004383</v>
       </c>
       <c r="O352" s="1" t="n">
+        <v>0.004379</v>
+      </c>
+      <c r="P352" s="1" t="n">
         <v>0.004419</v>
       </c>
-      <c r="P352" s="1" t="n">
-        <v>0.004383</v>
+      <c r="Q352" s="1" t="n">
+        <v>0.004379</v>
       </c>
     </row>
     <row r="353">
@@ -18817,9 +19876,12 @@
         <v>0.0803</v>
       </c>
       <c r="O353" s="1" t="n">
+        <v>0.08041</v>
+      </c>
+      <c r="P353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="P353" s="1" t="n">
+      <c r="Q353" s="1" t="n">
         <v>0.0803</v>
       </c>
     </row>
@@ -18869,10 +19931,13 @@
         <v>1.271</v>
       </c>
       <c r="O354" s="1" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="P354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="P354" s="1" t="n">
-        <v>1.271</v>
+      <c r="Q354" s="1" t="n">
+        <v>1.265</v>
       </c>
     </row>
     <row r="355">
@@ -18921,10 +19986,13 @@
         <v>7.684</v>
       </c>
       <c r="O355" s="1" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="P355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="P355" s="1" t="n">
-        <v>7.684</v>
+      <c r="Q355" s="1" t="n">
+        <v>7.68</v>
       </c>
     </row>
     <row r="356">
@@ -18973,10 +20041,13 @@
         <v>0.0078</v>
       </c>
       <c r="O356" s="1" t="n">
+        <v>0.00777</v>
+      </c>
+      <c r="P356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="P356" s="1" t="n">
-        <v>0.00778</v>
+      <c r="Q356" s="1" t="n">
+        <v>0.00777</v>
       </c>
     </row>
     <row r="357">
@@ -19025,9 +20096,12 @@
         <v>0.005608</v>
       </c>
       <c r="O357" s="1" t="n">
+        <v>0.005643</v>
+      </c>
+      <c r="P357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="P357" s="1" t="n">
+      <c r="Q357" s="1" t="n">
         <v>0.005608</v>
       </c>
     </row>
@@ -19077,10 +20151,13 @@
         <v>0.01546</v>
       </c>
       <c r="O358" s="1" t="n">
+        <v>0.01543</v>
+      </c>
+      <c r="P358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="P358" s="1" t="n">
-        <v>0.01546</v>
+      <c r="Q358" s="1" t="n">
+        <v>0.01543</v>
       </c>
     </row>
     <row r="359">
@@ -19129,10 +20206,13 @@
         <v>3.617</v>
       </c>
       <c r="O359" s="1" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="P359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="P359" s="1" t="n">
-        <v>3.617</v>
+      <c r="Q359" s="1" t="n">
+        <v>3.615</v>
       </c>
     </row>
     <row r="360">
@@ -19181,9 +20261,12 @@
         <v>0.1499</v>
       </c>
       <c r="O360" s="1" t="n">
+        <v>0.1503</v>
+      </c>
+      <c r="P360" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="P360" s="1" t="n">
+      <c r="Q360" s="1" t="n">
         <v>0.1497</v>
       </c>
     </row>
@@ -19233,9 +20316,12 @@
         <v>0.07038</v>
       </c>
       <c r="O361" s="1" t="n">
+        <v>0.07038999999999999</v>
+      </c>
+      <c r="P361" s="1" t="n">
         <v>0.07104000000000001</v>
       </c>
-      <c r="P361" s="1" t="n">
+      <c r="Q361" s="1" t="n">
         <v>0.07019</v>
       </c>
     </row>
@@ -19285,9 +20371,12 @@
         <v>0.0176</v>
       </c>
       <c r="O362" s="1" t="n">
+        <v>0.01761</v>
+      </c>
+      <c r="P362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="P362" s="1" t="n">
+      <c r="Q362" s="1" t="n">
         <v>0.0176</v>
       </c>
     </row>
@@ -19337,9 +20426,12 @@
         <v>0.02238</v>
       </c>
       <c r="O363" s="1" t="n">
+        <v>0.02235</v>
+      </c>
+      <c r="P363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="P363" s="1" t="n">
+      <c r="Q363" s="1" t="n">
         <v>0.02234</v>
       </c>
     </row>
@@ -19389,9 +20481,12 @@
         <v>0.01254</v>
       </c>
       <c r="O364" s="1" t="n">
+        <v>0.01251</v>
+      </c>
+      <c r="P364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="P364" s="1" t="n">
+      <c r="Q364" s="1" t="n">
         <v>0.01249</v>
       </c>
     </row>
@@ -19441,10 +20536,13 @@
         <v>0.0912</v>
       </c>
       <c r="O365" s="1" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="P365" s="1" t="n">
         <v>0.0926</v>
       </c>
-      <c r="P365" s="1" t="n">
-        <v>0.0912</v>
+      <c r="Q365" s="1" t="n">
+        <v>0.091</v>
       </c>
     </row>
     <row r="366">
@@ -19493,10 +20591,13 @@
         <v>0.04227</v>
       </c>
       <c r="O366" s="1" t="n">
+        <v>0.04223</v>
+      </c>
+      <c r="P366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="P366" s="1" t="n">
-        <v>0.04224</v>
+      <c r="Q366" s="1" t="n">
+        <v>0.04223</v>
       </c>
     </row>
     <row r="367">
@@ -19545,10 +20646,13 @@
         <v>0.03144</v>
       </c>
       <c r="O367" s="1" t="n">
+        <v>0.03128</v>
+      </c>
+      <c r="P367" s="1" t="n">
         <v>0.03188</v>
       </c>
-      <c r="P367" s="1" t="n">
-        <v>0.03141</v>
+      <c r="Q367" s="1" t="n">
+        <v>0.03128</v>
       </c>
     </row>
     <row r="368">
@@ -19597,9 +20701,12 @@
         <v>0.02331</v>
       </c>
       <c r="O368" s="1" t="n">
+        <v>0.02336</v>
+      </c>
+      <c r="P368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="P368" s="1" t="n">
+      <c r="Q368" s="1" t="n">
         <v>0.02331</v>
       </c>
     </row>
@@ -19649,10 +20756,13 @@
         <v>0.03088</v>
       </c>
       <c r="O369" s="1" t="n">
+        <v>0.03087</v>
+      </c>
+      <c r="P369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="P369" s="1" t="n">
-        <v>0.03088</v>
+      <c r="Q369" s="1" t="n">
+        <v>0.03087</v>
       </c>
     </row>
     <row r="370">
@@ -19701,9 +20811,12 @@
         <v>0.07932</v>
       </c>
       <c r="O370" s="1" t="n">
+        <v>0.07935</v>
+      </c>
+      <c r="P370" s="1" t="n">
         <v>0.07990999999999999</v>
       </c>
-      <c r="P370" s="1" t="n">
+      <c r="Q370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -19753,9 +20866,12 @@
         <v>0.1073</v>
       </c>
       <c r="O371" s="1" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="P371" s="1" t="n">
         <v>0.1089</v>
       </c>
-      <c r="P371" s="1" t="n">
+      <c r="Q371" s="1" t="n">
         <v>0.1073</v>
       </c>
     </row>
@@ -19805,10 +20921,13 @@
         <v>0.007001</v>
       </c>
       <c r="O372" s="1" t="n">
+        <v>0.006965</v>
+      </c>
+      <c r="P372" s="1" t="n">
         <v>0.007209</v>
       </c>
-      <c r="P372" s="1" t="n">
-        <v>0.007001</v>
+      <c r="Q372" s="1" t="n">
+        <v>0.006965</v>
       </c>
     </row>
     <row r="373">
@@ -19857,9 +20976,12 @@
         <v>0.0956</v>
       </c>
       <c r="O373" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="P373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="P373" s="1" t="n">
+      <c r="Q373" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -19909,10 +21031,13 @@
         <v>0.05735</v>
       </c>
       <c r="O374" s="1" t="n">
+        <v>0.0573</v>
+      </c>
+      <c r="P374" s="1" t="n">
         <v>0.05881</v>
       </c>
-      <c r="P374" s="1" t="n">
-        <v>0.05735</v>
+      <c r="Q374" s="1" t="n">
+        <v>0.0573</v>
       </c>
     </row>
     <row r="375">
@@ -19961,10 +21086,13 @@
         <v>0.3192</v>
       </c>
       <c r="O375" s="1" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="P375" s="1" t="n">
         <v>0.3238</v>
       </c>
-      <c r="P375" s="1" t="n">
-        <v>0.3192</v>
+      <c r="Q375" s="1" t="n">
+        <v>0.3175</v>
       </c>
     </row>
     <row r="376">
@@ -20013,9 +21141,12 @@
         <v>0.01942</v>
       </c>
       <c r="O376" s="1" t="n">
+        <v>0.01942</v>
+      </c>
+      <c r="P376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="P376" s="1" t="n">
+      <c r="Q376" s="1" t="n">
         <v>0.01942</v>
       </c>
     </row>
@@ -20065,9 +21196,12 @@
         <v>0.06827999999999999</v>
       </c>
       <c r="O377" s="1" t="n">
+        <v>0.0683</v>
+      </c>
+      <c r="P377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="P377" s="1" t="n">
+      <c r="Q377" s="1" t="n">
         <v>0.06827999999999999</v>
       </c>
     </row>
@@ -20117,9 +21251,12 @@
         <v>0.15697</v>
       </c>
       <c r="O378" s="1" t="n">
+        <v>0.15781</v>
+      </c>
+      <c r="P378" s="1" t="n">
         <v>0.1581</v>
       </c>
-      <c r="P378" s="1" t="n">
+      <c r="Q378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -20169,10 +21306,13 @@
         <v>0.000595</v>
       </c>
       <c r="O379" s="1" t="n">
+        <v>0.0005941</v>
+      </c>
+      <c r="P379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="P379" s="1" t="n">
-        <v>0.000595</v>
+      <c r="Q379" s="1" t="n">
+        <v>0.0005941</v>
       </c>
     </row>
     <row r="380">
@@ -20221,9 +21361,12 @@
         <v>0.01016</v>
       </c>
       <c r="O380" s="1" t="n">
+        <v>0.01015</v>
+      </c>
+      <c r="P380" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="P380" s="1" t="n">
+      <c r="Q380" s="1" t="n">
         <v>0.01015</v>
       </c>
     </row>
@@ -20273,9 +21416,12 @@
         <v>0.02538</v>
       </c>
       <c r="O381" s="1" t="n">
+        <v>0.02548</v>
+      </c>
+      <c r="P381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="P381" s="1" t="n">
+      <c r="Q381" s="1" t="n">
         <v>0.02538</v>
       </c>
     </row>
@@ -20325,9 +21471,12 @@
         <v>0.19144</v>
       </c>
       <c r="O382" s="1" t="n">
+        <v>0.19005</v>
+      </c>
+      <c r="P382" s="1" t="n">
         <v>0.19348</v>
       </c>
-      <c r="P382" s="1" t="n">
+      <c r="Q382" s="1" t="n">
         <v>0.18936</v>
       </c>
     </row>
@@ -20377,9 +21526,12 @@
         <v>0.09282</v>
       </c>
       <c r="O383" s="1" t="n">
+        <v>0.09253</v>
+      </c>
+      <c r="P383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="P383" s="1" t="n">
+      <c r="Q383" s="1" t="n">
         <v>0.09236</v>
       </c>
     </row>
@@ -20429,9 +21581,12 @@
         <v>0.03163</v>
       </c>
       <c r="O384" s="1" t="n">
+        <v>0.03167</v>
+      </c>
+      <c r="P384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="P384" s="1" t="n">
+      <c r="Q384" s="1" t="n">
         <v>0.03163</v>
       </c>
     </row>
@@ -20481,10 +21636,13 @@
         <v>0.01092</v>
       </c>
       <c r="O385" s="1" t="n">
+        <v>0.0109</v>
+      </c>
+      <c r="P385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="P385" s="1" t="n">
-        <v>0.01092</v>
+      <c r="Q385" s="1" t="n">
+        <v>0.0109</v>
       </c>
     </row>
     <row r="386">
@@ -20533,10 +21691,13 @@
         <v>0.05105</v>
       </c>
       <c r="O386" s="1" t="n">
+        <v>0.05073</v>
+      </c>
+      <c r="P386" s="1" t="n">
         <v>0.05224</v>
       </c>
-      <c r="P386" s="1" t="n">
-        <v>0.05087</v>
+      <c r="Q386" s="1" t="n">
+        <v>0.05073</v>
       </c>
     </row>
     <row r="387">
@@ -20585,9 +21746,12 @@
         <v>0.02498</v>
       </c>
       <c r="O387" s="1" t="n">
+        <v>0.02501</v>
+      </c>
+      <c r="P387" s="1" t="n">
         <v>0.02541</v>
       </c>
-      <c r="P387" s="1" t="n">
+      <c r="Q387" s="1" t="n">
         <v>0.02483</v>
       </c>
     </row>
@@ -20637,10 +21801,13 @@
         <v>0.007292</v>
       </c>
       <c r="O388" s="1" t="n">
+        <v>0.007258</v>
+      </c>
+      <c r="P388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="P388" s="1" t="n">
-        <v>0.007267</v>
+      <c r="Q388" s="1" t="n">
+        <v>0.007258</v>
       </c>
     </row>
     <row r="389">
@@ -20689,9 +21856,12 @@
         <v>0.01009</v>
       </c>
       <c r="O389" s="1" t="n">
+        <v>0.01013</v>
+      </c>
+      <c r="P389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="P389" s="1" t="n">
+      <c r="Q389" s="1" t="n">
         <v>0.01009</v>
       </c>
     </row>
@@ -20741,9 +21911,12 @@
         <v>0.0823</v>
       </c>
       <c r="O390" s="1" t="n">
+        <v>0.08237999999999999</v>
+      </c>
+      <c r="P390" s="1" t="n">
         <v>0.0839</v>
       </c>
-      <c r="P390" s="1" t="n">
+      <c r="Q390" s="1" t="n">
         <v>0.0823</v>
       </c>
     </row>
@@ -20793,9 +21966,12 @@
         <v>0.503</v>
       </c>
       <c r="O391" s="1" t="n">
+        <v>0.5039</v>
+      </c>
+      <c r="P391" s="1" t="n">
         <v>0.5061</v>
       </c>
-      <c r="P391" s="1" t="n">
+      <c r="Q391" s="1" t="n">
         <v>0.5014</v>
       </c>
     </row>
@@ -20845,9 +22021,12 @@
         <v>0.1162</v>
       </c>
       <c r="O392" s="1" t="n">
+        <v>0.1162</v>
+      </c>
+      <c r="P392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="P392" s="1" t="n">
+      <c r="Q392" s="1" t="n">
         <v>0.1162</v>
       </c>
     </row>
@@ -20897,9 +22076,12 @@
         <v>0.00244</v>
       </c>
       <c r="O393" s="1" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="P393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="P393" s="1" t="n">
+      <c r="Q393" s="1" t="n">
         <v>0.00244</v>
       </c>
     </row>
@@ -20949,9 +22131,12 @@
         <v>0.02122</v>
       </c>
       <c r="O394" s="1" t="n">
+        <v>0.02127</v>
+      </c>
+      <c r="P394" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="P394" s="1" t="n">
+      <c r="Q394" s="1" t="n">
         <v>0.02121</v>
       </c>
     </row>
@@ -21001,9 +22186,12 @@
         <v>0.0158</v>
       </c>
       <c r="O395" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="P395" s="1" t="n">
         <v>0.0163</v>
       </c>
-      <c r="P395" s="1" t="n">
+      <c r="Q395" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -21053,9 +22241,12 @@
         <v>0.1349</v>
       </c>
       <c r="O396" s="1" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="P396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="P396" s="1" t="n">
+      <c r="Q396" s="1" t="n">
         <v>0.1349</v>
       </c>
     </row>
@@ -21105,10 +22296,13 @@
         <v>0.01446</v>
       </c>
       <c r="O397" s="1" t="n">
+        <v>0.01442</v>
+      </c>
+      <c r="P397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="P397" s="1" t="n">
-        <v>0.01446</v>
+      <c r="Q397" s="1" t="n">
+        <v>0.01442</v>
       </c>
     </row>
     <row r="398">
@@ -21157,9 +22351,12 @@
         <v>6.701</v>
       </c>
       <c r="O398" s="1" t="n">
+        <v>6.731</v>
+      </c>
+      <c r="P398" s="1" t="n">
         <v>6.955</v>
       </c>
-      <c r="P398" s="1" t="n">
+      <c r="Q398" s="1" t="n">
         <v>6.701</v>
       </c>
     </row>
@@ -21209,9 +22406,12 @@
         <v>0.009384999999999999</v>
       </c>
       <c r="O399" s="1" t="n">
+        <v>0.009391</v>
+      </c>
+      <c r="P399" s="1" t="n">
         <v>0.009509999999999999</v>
       </c>
-      <c r="P399" s="1" t="n">
+      <c r="Q399" s="1" t="n">
         <v>0.009384999999999999</v>
       </c>
     </row>
@@ -21261,9 +22461,12 @@
         <v>0.001264</v>
       </c>
       <c r="O400" s="1" t="n">
+        <v>0.001259</v>
+      </c>
+      <c r="P400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="P400" s="1" t="n">
+      <c r="Q400" s="1" t="n">
         <v>0.001256</v>
       </c>
     </row>
@@ -21313,9 +22516,12 @@
         <v>0.01846</v>
       </c>
       <c r="O401" s="1" t="n">
+        <v>0.01849</v>
+      </c>
+      <c r="P401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="P401" s="1" t="n">
+      <c r="Q401" s="1" t="n">
         <v>0.01841</v>
       </c>
     </row>
@@ -21365,10 +22571,13 @@
         <v>0.08484999999999999</v>
       </c>
       <c r="O402" s="1" t="n">
+        <v>0.08470999999999999</v>
+      </c>
+      <c r="P402" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="P402" s="1" t="n">
-        <v>0.08484999999999999</v>
+      <c r="Q402" s="1" t="n">
+        <v>0.08470999999999999</v>
       </c>
     </row>
     <row r="403">
@@ -21417,9 +22626,12 @@
         <v>0.0055</v>
       </c>
       <c r="O403" s="1" t="n">
+        <v>0.00552</v>
+      </c>
+      <c r="P403" s="1" t="n">
         <v>0.00556</v>
       </c>
-      <c r="P403" s="1" t="n">
+      <c r="Q403" s="1" t="n">
         <v>0.0055</v>
       </c>
     </row>
@@ -21469,9 +22681,12 @@
         <v>0.04238</v>
       </c>
       <c r="O404" s="1" t="n">
+        <v>0.0427</v>
+      </c>
+      <c r="P404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="P404" s="1" t="n">
+      <c r="Q404" s="1" t="n">
         <v>0.04238</v>
       </c>
     </row>
@@ -21521,10 +22736,13 @@
         <v>0.05833</v>
       </c>
       <c r="O405" s="1" t="n">
+        <v>0.05831</v>
+      </c>
+      <c r="P405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="P405" s="1" t="n">
-        <v>0.05833</v>
+      <c r="Q405" s="1" t="n">
+        <v>0.05831</v>
       </c>
     </row>
     <row r="406">
@@ -21573,9 +22791,12 @@
         <v>0.01653</v>
       </c>
       <c r="O406" s="1" t="n">
+        <v>0.01652</v>
+      </c>
+      <c r="P406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="P406" s="1" t="n">
+      <c r="Q406" s="1" t="n">
         <v>0.01647</v>
       </c>
     </row>
@@ -21625,9 +22846,12 @@
         <v>0.0424</v>
       </c>
       <c r="O407" s="1" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="P407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="P407" s="1" t="n">
+      <c r="Q407" s="1" t="n">
         <v>0.0423</v>
       </c>
     </row>
@@ -21677,9 +22901,12 @@
         <v>0.01922</v>
       </c>
       <c r="O408" s="1" t="n">
+        <v>0.01924</v>
+      </c>
+      <c r="P408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="P408" s="1" t="n">
+      <c r="Q408" s="1" t="n">
         <v>0.01922</v>
       </c>
     </row>
@@ -21729,9 +22956,12 @@
         <v>0.4447</v>
       </c>
       <c r="O409" s="1" t="n">
+        <v>0.4443</v>
+      </c>
+      <c r="P409" s="1" t="n">
         <v>0.4484</v>
       </c>
-      <c r="P409" s="1" t="n">
+      <c r="Q409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -21781,10 +23011,13 @@
         <v>0.04399</v>
       </c>
       <c r="O410" s="1" t="n">
+        <v>0.04394</v>
+      </c>
+      <c r="P410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="P410" s="1" t="n">
-        <v>0.04399</v>
+      <c r="Q410" s="1" t="n">
+        <v>0.04394</v>
       </c>
     </row>
     <row r="411">
@@ -21833,9 +23066,12 @@
         <v>27.41</v>
       </c>
       <c r="O411" s="1" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="P411" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="P411" s="1" t="n">
+      <c r="Q411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -21885,10 +23121,13 @@
         <v>0.03503</v>
       </c>
       <c r="O412" s="1" t="n">
+        <v>0.03498</v>
+      </c>
+      <c r="P412" s="1" t="n">
         <v>0.03564</v>
       </c>
-      <c r="P412" s="1" t="n">
-        <v>0.03503</v>
+      <c r="Q412" s="1" t="n">
+        <v>0.03498</v>
       </c>
     </row>
     <row r="413">
@@ -21937,10 +23176,13 @@
         <v>0.003396</v>
       </c>
       <c r="O413" s="1" t="n">
+        <v>0.003392</v>
+      </c>
+      <c r="P413" s="1" t="n">
         <v>0.003432</v>
       </c>
-      <c r="P413" s="1" t="n">
-        <v>0.003396</v>
+      <c r="Q413" s="1" t="n">
+        <v>0.003392</v>
       </c>
     </row>
     <row r="414">
@@ -21989,9 +23231,12 @@
         <v>0.1528</v>
       </c>
       <c r="O414" s="1" t="n">
+        <v>0.1528</v>
+      </c>
+      <c r="P414" s="1" t="n">
         <v>0.1538</v>
       </c>
-      <c r="P414" s="1" t="n">
+      <c r="Q414" s="1" t="n">
         <v>0.1526</v>
       </c>
     </row>
@@ -22041,9 +23286,12 @@
         <v>0.05269</v>
       </c>
       <c r="O415" s="1" t="n">
+        <v>0.05258</v>
+      </c>
+      <c r="P415" s="1" t="n">
         <v>0.05288</v>
       </c>
-      <c r="P415" s="1" t="n">
+      <c r="Q415" s="1" t="n">
         <v>0.0525</v>
       </c>
     </row>
@@ -22093,10 +23341,13 @@
         <v>0.00656</v>
       </c>
       <c r="O416" s="1" t="n">
+        <v>0.00654</v>
+      </c>
+      <c r="P416" s="1" t="n">
         <v>0.00669</v>
       </c>
-      <c r="P416" s="1" t="n">
-        <v>0.00656</v>
+      <c r="Q416" s="1" t="n">
+        <v>0.00654</v>
       </c>
     </row>
     <row r="417">
@@ -22145,10 +23396,13 @@
         <v>0.06034</v>
       </c>
       <c r="O417" s="1" t="n">
+        <v>0.06026</v>
+      </c>
+      <c r="P417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="P417" s="1" t="n">
-        <v>0.06034</v>
+      <c r="Q417" s="1" t="n">
+        <v>0.06026</v>
       </c>
     </row>
     <row r="418">
@@ -22197,9 +23451,12 @@
         <v>0.008009</v>
       </c>
       <c r="O418" s="1" t="n">
+        <v>0.008004000000000001</v>
+      </c>
+      <c r="P418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="P418" s="1" t="n">
+      <c r="Q418" s="1" t="n">
         <v>0.007979</v>
       </c>
     </row>
@@ -22249,10 +23506,13 @@
         <v>0.07432</v>
       </c>
       <c r="O419" s="1" t="n">
+        <v>0.07425</v>
+      </c>
+      <c r="P419" s="1" t="n">
         <v>0.07524</v>
       </c>
-      <c r="P419" s="1" t="n">
-        <v>0.07432</v>
+      <c r="Q419" s="1" t="n">
+        <v>0.07425</v>
       </c>
     </row>
     <row r="420">
@@ -22301,9 +23561,12 @@
         <v>0.02121</v>
       </c>
       <c r="O420" s="1" t="n">
+        <v>0.02116</v>
+      </c>
+      <c r="P420" s="1" t="n">
         <v>0.02146</v>
       </c>
-      <c r="P420" s="1" t="n">
+      <c r="Q420" s="1" t="n">
         <v>0.02105</v>
       </c>
     </row>
@@ -22353,10 +23616,13 @@
         <v>0.06933</v>
       </c>
       <c r="O421" s="1" t="n">
+        <v>0.06909</v>
+      </c>
+      <c r="P421" s="1" t="n">
         <v>0.07038999999999999</v>
       </c>
-      <c r="P421" s="1" t="n">
-        <v>0.06933</v>
+      <c r="Q421" s="1" t="n">
+        <v>0.06909</v>
       </c>
     </row>
     <row r="422">
@@ -22405,10 +23671,13 @@
         <v>0.0148</v>
       </c>
       <c r="O422" s="1" t="n">
+        <v>0.01473</v>
+      </c>
+      <c r="P422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="P422" s="1" t="n">
-        <v>0.0148</v>
+      <c r="Q422" s="1" t="n">
+        <v>0.01473</v>
       </c>
     </row>
     <row r="423">
@@ -22457,10 +23726,13 @@
         <v>0.006615</v>
       </c>
       <c r="O423" s="1" t="n">
+        <v>0.006603</v>
+      </c>
+      <c r="P423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="P423" s="1" t="n">
-        <v>0.006615</v>
+      <c r="Q423" s="1" t="n">
+        <v>0.006603</v>
       </c>
     </row>
     <row r="424">
@@ -22509,9 +23781,12 @@
         <v>0.908</v>
       </c>
       <c r="O424" s="1" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="P424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="P424" s="1" t="n">
+      <c r="Q424" s="1" t="n">
         <v>0.908</v>
       </c>
     </row>
@@ -22561,10 +23836,13 @@
         <v>0.03559</v>
       </c>
       <c r="O425" s="1" t="n">
+        <v>0.03524</v>
+      </c>
+      <c r="P425" s="1" t="n">
         <v>0.03596</v>
       </c>
-      <c r="P425" s="1" t="n">
-        <v>0.03546</v>
+      <c r="Q425" s="1" t="n">
+        <v>0.03524</v>
       </c>
     </row>
     <row r="426">
@@ -22613,9 +23891,12 @@
         <v>1.79</v>
       </c>
       <c r="O426" s="1" t="n">
+        <v>1.802</v>
+      </c>
+      <c r="P426" s="1" t="n">
         <v>1.81</v>
       </c>
-      <c r="P426" s="1" t="n">
+      <c r="Q426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -22665,9 +23946,12 @@
         <v>0.12791</v>
       </c>
       <c r="O427" s="1" t="n">
+        <v>0.12821</v>
+      </c>
+      <c r="P427" s="1" t="n">
         <v>0.12835</v>
       </c>
-      <c r="P427" s="1" t="n">
+      <c r="Q427" s="1" t="n">
         <v>0.12736</v>
       </c>
     </row>
@@ -22717,10 +24001,13 @@
         <v>0.05285</v>
       </c>
       <c r="O428" s="1" t="n">
+        <v>0.05269</v>
+      </c>
+      <c r="P428" s="1" t="n">
         <v>0.05362</v>
       </c>
-      <c r="P428" s="1" t="n">
-        <v>0.05285</v>
+      <c r="Q428" s="1" t="n">
+        <v>0.05269</v>
       </c>
     </row>
     <row r="429">
@@ -22769,10 +24056,13 @@
         <v>1.287</v>
       </c>
       <c r="O429" s="1" t="n">
+        <v>1.284</v>
+      </c>
+      <c r="P429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="P429" s="1" t="n">
-        <v>1.287</v>
+      <c r="Q429" s="1" t="n">
+        <v>1.284</v>
       </c>
     </row>
     <row r="430">
@@ -22821,9 +24111,12 @@
         <v>0.07463</v>
       </c>
       <c r="O430" s="1" t="n">
+        <v>0.07474</v>
+      </c>
+      <c r="P430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="P430" s="1" t="n">
+      <c r="Q430" s="1" t="n">
         <v>0.07463</v>
       </c>
     </row>
@@ -22873,10 +24166,13 @@
         <v>0.1576</v>
       </c>
       <c r="O431" s="1" t="n">
+        <v>0.1567</v>
+      </c>
+      <c r="P431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="P431" s="1" t="n">
-        <v>0.157</v>
+      <c r="Q431" s="1" t="n">
+        <v>0.1567</v>
       </c>
     </row>
     <row r="432">
@@ -22925,9 +24221,12 @@
         <v>1.438</v>
       </c>
       <c r="O432" s="1" t="n">
+        <v>1.441</v>
+      </c>
+      <c r="P432" s="1" t="n">
         <v>1.461</v>
       </c>
-      <c r="P432" s="1" t="n">
+      <c r="Q432" s="1" t="n">
         <v>1.438</v>
       </c>
     </row>
@@ -22977,10 +24276,13 @@
         <v>3.257</v>
       </c>
       <c r="O433" s="1" t="n">
+        <v>3.248</v>
+      </c>
+      <c r="P433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="P433" s="1" t="n">
-        <v>3.257</v>
+      <c r="Q433" s="1" t="n">
+        <v>3.248</v>
       </c>
     </row>
     <row r="434">
@@ -23029,9 +24331,12 @@
         <v>0.1786</v>
       </c>
       <c r="O434" s="1" t="n">
+        <v>0.1788</v>
+      </c>
+      <c r="P434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="P434" s="1" t="n">
+      <c r="Q434" s="1" t="n">
         <v>0.1783</v>
       </c>
     </row>
@@ -23081,10 +24386,13 @@
         <v>0.008572</v>
       </c>
       <c r="O435" s="1" t="n">
+        <v>0.008562</v>
+      </c>
+      <c r="P435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="P435" s="1" t="n">
-        <v>0.008572</v>
+      <c r="Q435" s="1" t="n">
+        <v>0.008562</v>
       </c>
     </row>
     <row r="436">
@@ -23133,9 +24441,12 @@
         <v>0.2828</v>
       </c>
       <c r="O436" s="1" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="P436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="P436" s="1" t="n">
+      <c r="Q436" s="1" t="n">
         <v>0.2818</v>
       </c>
     </row>
@@ -23185,9 +24496,12 @@
         <v>0.03899</v>
       </c>
       <c r="O437" s="1" t="n">
+        <v>0.03876</v>
+      </c>
+      <c r="P437" s="1" t="n">
         <v>0.03957</v>
       </c>
-      <c r="P437" s="1" t="n">
+      <c r="Q437" s="1" t="n">
         <v>0.03814</v>
       </c>
     </row>
@@ -23237,9 +24551,12 @@
         <v>0.02435</v>
       </c>
       <c r="O438" s="1" t="n">
+        <v>0.02434</v>
+      </c>
+      <c r="P438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="P438" s="1" t="n">
+      <c r="Q438" s="1" t="n">
         <v>0.0242</v>
       </c>
     </row>
@@ -23289,9 +24606,12 @@
         <v>0.04401</v>
       </c>
       <c r="O439" s="1" t="n">
+        <v>0.04405</v>
+      </c>
+      <c r="P439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="P439" s="1" t="n">
+      <c r="Q439" s="1" t="n">
         <v>0.04401</v>
       </c>
     </row>
@@ -23341,10 +24661,13 @@
         <v>0.000518</v>
       </c>
       <c r="O440" s="1" t="n">
+        <v>0.0005174999999999999</v>
+      </c>
+      <c r="P440" s="1" t="n">
         <v>0.0005258</v>
       </c>
-      <c r="P440" s="1" t="n">
-        <v>0.000518</v>
+      <c r="Q440" s="1" t="n">
+        <v>0.0005174999999999999</v>
       </c>
     </row>
     <row r="441">
@@ -23393,9 +24716,12 @@
         <v>0.04546</v>
       </c>
       <c r="O441" s="1" t="n">
+        <v>0.04439</v>
+      </c>
+      <c r="P441" s="1" t="n">
         <v>0.04546</v>
       </c>
-      <c r="P441" s="1" t="n">
+      <c r="Q441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -23445,9 +24771,12 @@
         <v>0.000414</v>
       </c>
       <c r="O442" s="1" t="n">
+        <v>0.000412</v>
+      </c>
+      <c r="P442" s="1" t="n">
         <v>0.000416</v>
       </c>
-      <c r="P442" s="1" t="n">
+      <c r="Q442" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -23497,9 +24826,12 @@
         <v>0.09419</v>
       </c>
       <c r="O443" s="1" t="n">
+        <v>0.09426</v>
+      </c>
+      <c r="P443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="P443" s="1" t="n">
+      <c r="Q443" s="1" t="n">
         <v>0.09419</v>
       </c>
     </row>
@@ -23549,9 +24881,12 @@
         <v>2.299</v>
       </c>
       <c r="O444" s="1" t="n">
+        <v>2.299</v>
+      </c>
+      <c r="P444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="P444" s="1" t="n">
+      <c r="Q444" s="1" t="n">
         <v>2.289</v>
       </c>
     </row>
@@ -23601,9 +24936,12 @@
         <v>0.2671</v>
       </c>
       <c r="O445" s="1" t="n">
+        <v>0.2678</v>
+      </c>
+      <c r="P445" s="1" t="n">
         <v>0.2741</v>
       </c>
-      <c r="P445" s="1" t="n">
+      <c r="Q445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -23653,9 +24991,12 @@
         <v>0.000741</v>
       </c>
       <c r="O446" s="1" t="n">
+        <v>0.0007412</v>
+      </c>
+      <c r="P446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="P446" s="1" t="n">
+      <c r="Q446" s="1" t="n">
         <v>0.000741</v>
       </c>
     </row>
@@ -23705,9 +25046,12 @@
         <v>0.03807</v>
       </c>
       <c r="O447" s="1" t="n">
+        <v>0.03867</v>
+      </c>
+      <c r="P447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="P447" s="1" t="n">
+      <c r="Q447" s="1" t="n">
         <v>0.03807</v>
       </c>
     </row>
@@ -23757,9 +25101,12 @@
         <v>0.1766</v>
       </c>
       <c r="O448" s="1" t="n">
+        <v>0.1765</v>
+      </c>
+      <c r="P448" s="1" t="n">
         <v>0.1783</v>
       </c>
-      <c r="P448" s="1" t="n">
+      <c r="Q448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -23809,9 +25156,12 @@
         <v>0.04278</v>
       </c>
       <c r="O449" s="1" t="n">
+        <v>0.04275</v>
+      </c>
+      <c r="P449" s="1" t="n">
         <v>0.04301</v>
       </c>
-      <c r="P449" s="1" t="n">
+      <c r="Q449" s="1" t="n">
         <v>0.0426</v>
       </c>
     </row>
@@ -23861,9 +25211,12 @@
         <v>0.0001641</v>
       </c>
       <c r="O450" s="1" t="n">
+        <v>0.0001642</v>
+      </c>
+      <c r="P450" s="1" t="n">
         <v>0.0001654</v>
       </c>
-      <c r="P450" s="1" t="n">
+      <c r="Q450" s="1" t="n">
         <v>0.0001632</v>
       </c>
     </row>
@@ -23913,9 +25266,12 @@
         <v>0.03708</v>
       </c>
       <c r="O451" s="1" t="n">
+        <v>0.03712</v>
+      </c>
+      <c r="P451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="P451" s="1" t="n">
+      <c r="Q451" s="1" t="n">
         <v>0.03708</v>
       </c>
     </row>
@@ -23965,10 +25321,13 @@
         <v>0.009730000000000001</v>
       </c>
       <c r="O452" s="1" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="P452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="P452" s="1" t="n">
-        <v>0.009730000000000001</v>
+      <c r="Q452" s="1" t="n">
+        <v>0.0097</v>
       </c>
     </row>
     <row r="453">
@@ -24017,9 +25376,12 @@
         <v>0.06797</v>
       </c>
       <c r="O453" s="1" t="n">
+        <v>0.06794</v>
+      </c>
+      <c r="P453" s="1" t="n">
         <v>0.06816</v>
       </c>
-      <c r="P453" s="1" t="n">
+      <c r="Q453" s="1" t="n">
         <v>0.06782000000000001</v>
       </c>
     </row>
@@ -24069,9 +25431,12 @@
         <v>0.00749</v>
       </c>
       <c r="O454" s="1" t="n">
+        <v>0.007496</v>
+      </c>
+      <c r="P454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="P454" s="1" t="n">
+      <c r="Q454" s="1" t="n">
         <v>0.00749</v>
       </c>
     </row>
@@ -24121,9 +25486,12 @@
         <v>0.003278</v>
       </c>
       <c r="O455" s="1" t="n">
+        <v>0.003282</v>
+      </c>
+      <c r="P455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="P455" s="1" t="n">
+      <c r="Q455" s="1" t="n">
         <v>0.003278</v>
       </c>
     </row>
@@ -24173,10 +25541,13 @@
         <v>0.001842</v>
       </c>
       <c r="O456" s="1" t="n">
+        <v>0.00184</v>
+      </c>
+      <c r="P456" s="1" t="n">
         <v>0.001875</v>
       </c>
-      <c r="P456" s="1" t="n">
-        <v>0.001842</v>
+      <c r="Q456" s="1" t="n">
+        <v>0.00184</v>
       </c>
     </row>
     <row r="457">
@@ -24225,9 +25596,12 @@
         <v>0.0001746</v>
       </c>
       <c r="O457" s="1" t="n">
+        <v>0.0001749</v>
+      </c>
+      <c r="P457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="P457" s="1" t="n">
+      <c r="Q457" s="1" t="n">
         <v>0.0001745</v>
       </c>
     </row>
@@ -24277,9 +25651,12 @@
         <v>0.0003891</v>
       </c>
       <c r="O458" s="1" t="n">
+        <v>0.0003895</v>
+      </c>
+      <c r="P458" s="1" t="n">
         <v>0.0003916</v>
       </c>
-      <c r="P458" s="1" t="n">
+      <c r="Q458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -24329,9 +25706,12 @@
         <v>0.01392</v>
       </c>
       <c r="O459" s="1" t="n">
+        <v>0.01393</v>
+      </c>
+      <c r="P459" s="1" t="n">
         <v>0.01413</v>
       </c>
-      <c r="P459" s="1" t="n">
+      <c r="Q459" s="1" t="n">
         <v>0.01391</v>
       </c>
     </row>
@@ -24381,9 +25761,12 @@
         <v>0.04576</v>
       </c>
       <c r="O460" s="1" t="n">
+        <v>0.04568</v>
+      </c>
+      <c r="P460" s="1" t="n">
         <v>0.04586</v>
       </c>
-      <c r="P460" s="1" t="n">
+      <c r="Q460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -24433,9 +25816,12 @@
         <v>0.2818</v>
       </c>
       <c r="O461" s="1" t="n">
+        <v>0.2819</v>
+      </c>
+      <c r="P461" s="1" t="n">
         <v>0.2839</v>
       </c>
-      <c r="P461" s="1" t="n">
+      <c r="Q461" s="1" t="n">
         <v>0.2809</v>
       </c>
     </row>
@@ -24485,9 +25871,12 @@
         <v>0.006254</v>
       </c>
       <c r="O462" s="1" t="n">
+        <v>0.006255</v>
+      </c>
+      <c r="P462" s="1" t="n">
         <v>0.006312</v>
       </c>
-      <c r="P462" s="1" t="n">
+      <c r="Q462" s="1" t="n">
         <v>0.00622</v>
       </c>
     </row>
@@ -24537,10 +25926,13 @@
         <v>0.007024</v>
       </c>
       <c r="O463" s="1" t="n">
+        <v>0.006999</v>
+      </c>
+      <c r="P463" s="1" t="n">
         <v>0.007088</v>
       </c>
-      <c r="P463" s="1" t="n">
-        <v>0.007024</v>
+      <c r="Q463" s="1" t="n">
+        <v>0.006999</v>
       </c>
     </row>
     <row r="464">
@@ -24589,9 +25981,12 @@
         <v>0.287</v>
       </c>
       <c r="O464" s="1" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="P464" s="1" t="n">
         <v>0.2888</v>
       </c>
-      <c r="P464" s="1" t="n">
+      <c r="Q464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -24641,10 +26036,13 @@
         <v>0.08058</v>
       </c>
       <c r="O465" s="1" t="n">
+        <v>0.08047</v>
+      </c>
+      <c r="P465" s="1" t="n">
         <v>0.08183</v>
       </c>
-      <c r="P465" s="1" t="n">
-        <v>0.08053</v>
+      <c r="Q465" s="1" t="n">
+        <v>0.08047</v>
       </c>
     </row>
     <row r="466">
@@ -24693,9 +26091,12 @@
         <v>0.6375999999999999</v>
       </c>
       <c r="O466" s="1" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6392</v>
       </c>
       <c r="P466" s="1" t="n">
+        <v>0.6392</v>
+      </c>
+      <c r="Q466" s="1" t="n">
         <v>0.6318</v>
       </c>
     </row>
@@ -24745,9 +26146,12 @@
         <v>0.01472</v>
       </c>
       <c r="O467" s="1" t="n">
+        <v>0.01471</v>
+      </c>
+      <c r="P467" s="1" t="n">
         <v>0.01499</v>
       </c>
-      <c r="P467" s="1" t="n">
+      <c r="Q467" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -24797,10 +26201,13 @@
         <v>0.03452</v>
       </c>
       <c r="O468" s="1" t="n">
+        <v>0.03426</v>
+      </c>
+      <c r="P468" s="1" t="n">
         <v>0.03468</v>
       </c>
-      <c r="P468" s="1" t="n">
-        <v>0.03434</v>
+      <c r="Q468" s="1" t="n">
+        <v>0.03426</v>
       </c>
     </row>
     <row r="469">
@@ -24849,10 +26256,13 @@
         <v>0.1619</v>
       </c>
       <c r="O469" s="1" t="n">
+        <v>0.1617</v>
+      </c>
+      <c r="P469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="P469" s="1" t="n">
-        <v>0.1619</v>
+      <c r="Q469" s="1" t="n">
+        <v>0.1617</v>
       </c>
     </row>
     <row r="470">
@@ -24901,10 +26311,13 @@
         <v>0.4087</v>
       </c>
       <c r="O470" s="1" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="P470" s="1" t="n">
         <v>0.4151</v>
       </c>
-      <c r="P470" s="1" t="n">
-        <v>0.4085</v>
+      <c r="Q470" s="1" t="n">
+        <v>0.408</v>
       </c>
     </row>
     <row r="471">
@@ -24953,10 +26366,13 @@
         <v>0.06874</v>
       </c>
       <c r="O471" s="1" t="n">
+        <v>0.06866</v>
+      </c>
+      <c r="P471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="P471" s="1" t="n">
-        <v>0.06874</v>
+      <c r="Q471" s="1" t="n">
+        <v>0.06866</v>
       </c>
     </row>
     <row r="472">
@@ -25005,10 +26421,13 @@
         <v>0.06612999999999999</v>
       </c>
       <c r="O472" s="1" t="n">
+        <v>0.06605999999999999</v>
+      </c>
+      <c r="P472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="P472" s="1" t="n">
-        <v>0.06612999999999999</v>
+      <c r="Q472" s="1" t="n">
+        <v>0.06605999999999999</v>
       </c>
     </row>
     <row r="473">
@@ -25057,10 +26476,13 @@
         <v>0.01623</v>
       </c>
       <c r="O473" s="1" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="P473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="P473" s="1" t="n">
-        <v>0.01621</v>
+      <c r="Q473" s="1" t="n">
+        <v>0.0162</v>
       </c>
     </row>
     <row r="474">
@@ -25109,9 +26531,12 @@
         <v>0.2061</v>
       </c>
       <c r="O474" s="1" t="n">
+        <v>0.2067</v>
+      </c>
+      <c r="P474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="P474" s="1" t="n">
+      <c r="Q474" s="1" t="n">
         <v>0.2061</v>
       </c>
     </row>
@@ -25161,9 +26586,12 @@
         <v>0.042</v>
       </c>
       <c r="O475" s="1" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="P475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="P475" s="1" t="n">
+      <c r="Q475" s="1" t="n">
         <v>0.042</v>
       </c>
     </row>
@@ -25213,10 +26641,13 @@
         <v>1.559</v>
       </c>
       <c r="O476" s="1" t="n">
+        <v>1.557</v>
+      </c>
+      <c r="P476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="P476" s="1" t="n">
-        <v>1.559</v>
+      <c r="Q476" s="1" t="n">
+        <v>1.557</v>
       </c>
     </row>
     <row r="477">
@@ -25265,9 +26696,12 @@
         <v>0.1002</v>
       </c>
       <c r="O477" s="1" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="P477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="P477" s="1" t="n">
+      <c r="Q477" s="1" t="n">
         <v>0.1002</v>
       </c>
     </row>
@@ -25317,9 +26751,12 @@
         <v>0.001152</v>
       </c>
       <c r="O478" s="1" t="n">
+        <v>0.001154</v>
+      </c>
+      <c r="P478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="P478" s="1" t="n">
+      <c r="Q478" s="1" t="n">
         <v>0.00115</v>
       </c>
     </row>
@@ -25369,10 +26806,13 @@
         <v>0.1439</v>
       </c>
       <c r="O479" s="1" t="n">
+        <v>0.1435</v>
+      </c>
+      <c r="P479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="P479" s="1" t="n">
-        <v>0.1439</v>
+      <c r="Q479" s="1" t="n">
+        <v>0.1435</v>
       </c>
     </row>
     <row r="480">
@@ -25421,9 +26861,12 @@
         <v>0.001722</v>
       </c>
       <c r="O480" s="1" t="n">
+        <v>0.001722</v>
+      </c>
+      <c r="P480" s="1" t="n">
         <v>0.001734</v>
       </c>
-      <c r="P480" s="1" t="n">
+      <c r="Q480" s="1" t="n">
         <v>0.001719</v>
       </c>
     </row>
@@ -25473,9 +26916,12 @@
         <v>0.908</v>
       </c>
       <c r="O481" s="1" t="n">
+        <v>0.908</v>
+      </c>
+      <c r="P481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="P481" s="1" t="n">
+      <c r="Q481" s="1" t="n">
         <v>0.908</v>
       </c>
     </row>
@@ -25525,10 +26971,13 @@
         <v>0.1333</v>
       </c>
       <c r="O482" s="1" t="n">
+        <v>0.13303</v>
+      </c>
+      <c r="P482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="P482" s="1" t="n">
-        <v>0.1333</v>
+      <c r="Q482" s="1" t="n">
+        <v>0.13303</v>
       </c>
     </row>
     <row r="483">
@@ -25577,10 +27026,13 @@
         <v>0.04013</v>
       </c>
       <c r="O483" s="1" t="n">
+        <v>0.04011</v>
+      </c>
+      <c r="P483" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="P483" s="1" t="n">
-        <v>0.04013</v>
+      <c r="Q483" s="1" t="n">
+        <v>0.04011</v>
       </c>
     </row>
     <row r="484">
@@ -25629,9 +27081,12 @@
         <v>0.3006</v>
       </c>
       <c r="O484" s="1" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="P484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="P484" s="1" t="n">
+      <c r="Q484" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -25681,9 +27136,12 @@
         <v>0.05661</v>
       </c>
       <c r="O485" s="1" t="n">
+        <v>0.05667</v>
+      </c>
+      <c r="P485" s="1" t="n">
         <v>0.05709</v>
       </c>
-      <c r="P485" s="1" t="n">
+      <c r="Q485" s="1" t="n">
         <v>0.05603</v>
       </c>
     </row>
@@ -25733,10 +27191,13 @@
         <v>0.001563</v>
       </c>
       <c r="O486" s="1" t="n">
+        <v>0.001559</v>
+      </c>
+      <c r="P486" s="1" t="n">
         <v>0.001579</v>
       </c>
-      <c r="P486" s="1" t="n">
-        <v>0.001563</v>
+      <c r="Q486" s="1" t="n">
+        <v>0.001559</v>
       </c>
     </row>
     <row r="487">
@@ -25785,10 +27246,13 @@
         <v>0.06686</v>
       </c>
       <c r="O487" s="1" t="n">
+        <v>0.06676</v>
+      </c>
+      <c r="P487" s="1" t="n">
         <v>0.06766999999999999</v>
       </c>
-      <c r="P487" s="1" t="n">
-        <v>0.06686</v>
+      <c r="Q487" s="1" t="n">
+        <v>0.06676</v>
       </c>
     </row>
     <row r="488">
@@ -25837,10 +27301,13 @@
         <v>0.1914</v>
       </c>
       <c r="O488" s="1" t="n">
+        <v>0.1913</v>
+      </c>
+      <c r="P488" s="1" t="n">
         <v>0.1953</v>
       </c>
-      <c r="P488" s="1" t="n">
-        <v>0.1914</v>
+      <c r="Q488" s="1" t="n">
+        <v>0.1913</v>
       </c>
     </row>
     <row r="489">
@@ -25889,10 +27356,13 @@
         <v>0.04779</v>
       </c>
       <c r="O489" s="1" t="n">
+        <v>0.04776</v>
+      </c>
+      <c r="P489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="P489" s="1" t="n">
-        <v>0.04779</v>
+      <c r="Q489" s="1" t="n">
+        <v>0.04776</v>
       </c>
     </row>
     <row r="490">
@@ -25941,9 +27411,12 @@
         <v>0.1391</v>
       </c>
       <c r="O490" s="1" t="n">
+        <v>0.1394</v>
+      </c>
+      <c r="P490" s="1" t="n">
         <v>0.1401</v>
       </c>
-      <c r="P490" s="1" t="n">
+      <c r="Q490" s="1" t="n">
         <v>0.1389</v>
       </c>
     </row>
@@ -25993,9 +27466,12 @@
         <v>0.02235</v>
       </c>
       <c r="O491" s="1" t="n">
+        <v>0.02235</v>
+      </c>
+      <c r="P491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="P491" s="1" t="n">
+      <c r="Q491" s="1" t="n">
         <v>0.02235</v>
       </c>
     </row>
@@ -26045,10 +27521,13 @@
         <v>0.007757</v>
       </c>
       <c r="O492" s="1" t="n">
+        <v>0.007735</v>
+      </c>
+      <c r="P492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="P492" s="1" t="n">
-        <v>0.007746</v>
+      <c r="Q492" s="1" t="n">
+        <v>0.007735</v>
       </c>
     </row>
     <row r="493">
@@ -26097,9 +27576,12 @@
         <v>0.0005918</v>
       </c>
       <c r="O493" s="1" t="n">
+        <v>0.0005919</v>
+      </c>
+      <c r="P493" s="1" t="n">
         <v>0.0005992</v>
       </c>
-      <c r="P493" s="1" t="n">
+      <c r="Q493" s="1" t="n">
         <v>0.0005918</v>
       </c>
     </row>
@@ -26149,9 +27631,12 @@
         <v>3.026</v>
       </c>
       <c r="O494" s="1" t="n">
+        <v>3.027</v>
+      </c>
+      <c r="P494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="P494" s="1" t="n">
+      <c r="Q494" s="1" t="n">
         <v>2.999</v>
       </c>
     </row>
@@ -26201,9 +27686,12 @@
         <v>0.05061</v>
       </c>
       <c r="O495" s="1" t="n">
+        <v>0.05064</v>
+      </c>
+      <c r="P495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="P495" s="1" t="n">
+      <c r="Q495" s="1" t="n">
         <v>0.05042</v>
       </c>
     </row>
@@ -26253,9 +27741,12 @@
         <v>0.006797</v>
       </c>
       <c r="O496" s="1" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="P496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="P496" s="1" t="n">
+      <c r="Q496" s="1" t="n">
         <v>0.006742</v>
       </c>
     </row>
@@ -26305,9 +27796,12 @@
         <v>1.303</v>
       </c>
       <c r="O497" s="1" t="n">
+        <v>1.301</v>
+      </c>
+      <c r="P497" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="P497" s="1" t="n">
+      <c r="Q497" s="1" t="n">
         <v>1.299</v>
       </c>
     </row>
@@ -26357,9 +27851,12 @@
         <v>0.03936</v>
       </c>
       <c r="O498" s="1" t="n">
+        <v>0.03926</v>
+      </c>
+      <c r="P498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="P498" s="1" t="n">
+      <c r="Q498" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -26409,10 +27906,13 @@
         <v>0.0411</v>
       </c>
       <c r="O499" s="1" t="n">
+        <v>0.04092</v>
+      </c>
+      <c r="P499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="P499" s="1" t="n">
-        <v>0.04101</v>
+      <c r="Q499" s="1" t="n">
+        <v>0.04092</v>
       </c>
     </row>
     <row r="500">
@@ -26461,9 +27961,12 @@
         <v>0.00547</v>
       </c>
       <c r="O500" s="1" t="n">
+        <v>0.00546</v>
+      </c>
+      <c r="P500" s="1" t="n">
         <v>0.00549</v>
       </c>
-      <c r="P500" s="1" t="n">
+      <c r="Q500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -26513,10 +28016,13 @@
         <v>0.03566</v>
       </c>
       <c r="O501" s="1" t="n">
+        <v>0.03565</v>
+      </c>
+      <c r="P501" s="1" t="n">
         <v>0.0364</v>
       </c>
-      <c r="P501" s="1" t="n">
-        <v>0.03566</v>
+      <c r="Q501" s="1" t="n">
+        <v>0.03565</v>
       </c>
     </row>
     <row r="502">
@@ -26565,10 +28071,13 @@
         <v>0.07232</v>
       </c>
       <c r="O502" s="1" t="n">
+        <v>0.07209</v>
+      </c>
+      <c r="P502" s="1" t="n">
         <v>0.07342</v>
       </c>
-      <c r="P502" s="1" t="n">
-        <v>0.07227</v>
+      <c r="Q502" s="1" t="n">
+        <v>0.07209</v>
       </c>
     </row>
     <row r="503">
@@ -26617,9 +28126,12 @@
         <v>0.0007412</v>
       </c>
       <c r="O503" s="1" t="n">
+        <v>0.0007418</v>
+      </c>
+      <c r="P503" s="1" t="n">
         <v>0.000755</v>
       </c>
-      <c r="P503" s="1" t="n">
+      <c r="Q503" s="1" t="n">
         <v>0.0007412</v>
       </c>
     </row>
@@ -26669,9 +28181,12 @@
         <v>0.015988</v>
       </c>
       <c r="O504" s="1" t="n">
-        <v>0.016016</v>
+        <v>0.016034</v>
       </c>
       <c r="P504" s="1" t="n">
+        <v>0.016034</v>
+      </c>
+      <c r="Q504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -26721,9 +28236,12 @@
         <v>0.00703</v>
       </c>
       <c r="O505" s="1" t="n">
+        <v>0.00703</v>
+      </c>
+      <c r="P505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="P505" s="1" t="n">
+      <c r="Q505" s="1" t="n">
         <v>0.00703</v>
       </c>
     </row>
@@ -26773,10 +28291,13 @@
         <v>0.0255</v>
       </c>
       <c r="O506" s="1" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="P506" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="P506" s="1" t="n">
-        <v>0.0255</v>
+      <c r="Q506" s="1" t="n">
+        <v>0.0253</v>
       </c>
     </row>
     <row r="507">
@@ -26825,9 +28346,12 @@
         <v>0.001345</v>
       </c>
       <c r="O507" s="1" t="n">
+        <v>0.001348</v>
+      </c>
+      <c r="P507" s="1" t="n">
         <v>0.00136</v>
       </c>
-      <c r="P507" s="1" t="n">
+      <c r="Q507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -26877,9 +28401,12 @@
         <v>0.281</v>
       </c>
       <c r="O508" s="1" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="P508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="P508" s="1" t="n">
+      <c r="Q508" s="1" t="n">
         <v>0.2805</v>
       </c>
     </row>
@@ -26929,9 +28456,12 @@
         <v>0.1314</v>
       </c>
       <c r="O509" s="1" t="n">
+        <v>0.1316</v>
+      </c>
+      <c r="P509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="P509" s="1" t="n">
+      <c r="Q509" s="1" t="n">
         <v>0.1314</v>
       </c>
     </row>
@@ -26981,9 +28511,12 @@
         <v>0.04896</v>
       </c>
       <c r="O510" s="1" t="n">
+        <v>0.04897</v>
+      </c>
+      <c r="P510" s="1" t="n">
         <v>0.04972</v>
       </c>
-      <c r="P510" s="1" t="n">
+      <c r="Q510" s="1" t="n">
         <v>0.04896</v>
       </c>
     </row>
@@ -27033,10 +28566,13 @@
         <v>0.00272</v>
       </c>
       <c r="O511" s="1" t="n">
+        <v>0.00271</v>
+      </c>
+      <c r="P511" s="1" t="n">
         <v>0.00278</v>
       </c>
-      <c r="P511" s="1" t="n">
-        <v>0.00272</v>
+      <c r="Q511" s="1" t="n">
+        <v>0.00271</v>
       </c>
     </row>
     <row r="512">
@@ -27085,9 +28621,12 @@
         <v>0.015171</v>
       </c>
       <c r="O512" s="1" t="n">
+        <v>0.015066</v>
+      </c>
+      <c r="P512" s="1" t="n">
         <v>0.015454</v>
       </c>
-      <c r="P512" s="1" t="n">
+      <c r="Q512" s="1" t="n">
         <v>0.015017</v>
       </c>
     </row>
@@ -27137,9 +28676,12 @@
         <v>0.6925</v>
       </c>
       <c r="O513" s="1" t="n">
+        <v>0.6918</v>
+      </c>
+      <c r="P513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="P513" s="1" t="n">
+      <c r="Q513" s="1" t="n">
         <v>0.6899</v>
       </c>
     </row>
@@ -27189,10 +28731,13 @@
         <v>0.004515</v>
       </c>
       <c r="O514" s="1" t="n">
+        <v>0.004508</v>
+      </c>
+      <c r="P514" s="1" t="n">
         <v>0.004589</v>
       </c>
-      <c r="P514" s="1" t="n">
-        <v>0.004515</v>
+      <c r="Q514" s="1" t="n">
+        <v>0.004508</v>
       </c>
     </row>
     <row r="515">
@@ -27241,9 +28786,12 @@
         <v>0.005009</v>
       </c>
       <c r="O515" s="1" t="n">
+        <v>0.005012</v>
+      </c>
+      <c r="P515" s="1" t="n">
         <v>0.005066</v>
       </c>
-      <c r="P515" s="1" t="n">
+      <c r="Q515" s="1" t="n">
         <v>0.005008</v>
       </c>
     </row>
@@ -27293,9 +28841,12 @@
         <v>0.06320000000000001</v>
       </c>
       <c r="O516" s="1" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="P516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="P516" s="1" t="n">
+      <c r="Q516" s="1" t="n">
         <v>0.06320000000000001</v>
       </c>
     </row>
@@ -27345,9 +28896,12 @@
         <v>0.06476999999999999</v>
       </c>
       <c r="O517" s="1" t="n">
+        <v>0.06536</v>
+      </c>
+      <c r="P517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="P517" s="1" t="n">
+      <c r="Q517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -27397,9 +28951,12 @@
         <v>0.012</v>
       </c>
       <c r="O518" s="1" t="n">
+        <v>0.01201</v>
+      </c>
+      <c r="P518" s="1" t="n">
         <v>0.01219</v>
       </c>
-      <c r="P518" s="1" t="n">
+      <c r="Q518" s="1" t="n">
         <v>0.01199</v>
       </c>
     </row>
@@ -27449,10 +29006,13 @@
         <v>0.04753</v>
       </c>
       <c r="O519" s="1" t="n">
+        <v>0.04741</v>
+      </c>
+      <c r="P519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="P519" s="1" t="n">
-        <v>0.04743</v>
+      <c r="Q519" s="1" t="n">
+        <v>0.04741</v>
       </c>
     </row>
     <row r="520">
@@ -27501,9 +29061,12 @@
         <v>0.04365</v>
       </c>
       <c r="O520" s="1" t="n">
+        <v>0.04362</v>
+      </c>
+      <c r="P520" s="1" t="n">
         <v>0.04411</v>
       </c>
-      <c r="P520" s="1" t="n">
+      <c r="Q520" s="1" t="n">
         <v>0.04349</v>
       </c>
     </row>
@@ -27553,9 +29116,12 @@
         <v>0.00844</v>
       </c>
       <c r="O521" s="1" t="n">
+        <v>0.008448000000000001</v>
+      </c>
+      <c r="P521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="P521" s="1" t="n">
+      <c r="Q521" s="1" t="n">
         <v>0.008411999999999999</v>
       </c>
     </row>
@@ -27605,9 +29171,12 @@
         <v>0.0881</v>
       </c>
       <c r="O522" s="1" t="n">
+        <v>0.08801</v>
+      </c>
+      <c r="P522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="P522" s="1" t="n">
+      <c r="Q522" s="1" t="n">
         <v>0.08787</v>
       </c>
     </row>
@@ -27657,10 +29226,13 @@
         <v>0.006435</v>
       </c>
       <c r="O523" s="1" t="n">
+        <v>0.006424</v>
+      </c>
+      <c r="P523" s="1" t="n">
         <v>0.006492</v>
       </c>
-      <c r="P523" s="1" t="n">
-        <v>0.006433</v>
+      <c r="Q523" s="1" t="n">
+        <v>0.006424</v>
       </c>
     </row>
     <row r="524">
@@ -27709,9 +29281,12 @@
         <v>0.01635</v>
       </c>
       <c r="O524" s="1" t="n">
+        <v>0.01637</v>
+      </c>
+      <c r="P524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="P524" s="1" t="n">
+      <c r="Q524" s="1" t="n">
         <v>0.01635</v>
       </c>
     </row>
@@ -27761,10 +29336,13 @@
         <v>0.01781</v>
       </c>
       <c r="O525" s="1" t="n">
+        <v>0.01777</v>
+      </c>
+      <c r="P525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="P525" s="1" t="n">
-        <v>0.01779</v>
+      <c r="Q525" s="1" t="n">
+        <v>0.01777</v>
       </c>
     </row>
     <row r="526">
@@ -27813,10 +29391,13 @@
         <v>0.07892</v>
       </c>
       <c r="O526" s="1" t="n">
+        <v>0.07865999999999999</v>
+      </c>
+      <c r="P526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="P526" s="1" t="n">
-        <v>0.07883</v>
+      <c r="Q526" s="1" t="n">
+        <v>0.07865999999999999</v>
       </c>
     </row>
     <row r="527">
@@ -27865,9 +29446,12 @@
         <v>0.01594</v>
       </c>
       <c r="O527" s="1" t="n">
+        <v>0.01599</v>
+      </c>
+      <c r="P527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="P527" s="1" t="n">
+      <c r="Q527" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -27917,9 +29501,12 @@
         <v>0.004164</v>
       </c>
       <c r="O528" s="1" t="n">
+        <v>0.004175</v>
+      </c>
+      <c r="P528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="P528" s="1" t="n">
+      <c r="Q528" s="1" t="n">
         <v>0.004164</v>
       </c>
     </row>
@@ -27969,9 +29556,12 @@
         <v>0.003706</v>
       </c>
       <c r="O529" s="1" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="P529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="P529" s="1" t="n">
+      <c r="Q529" s="1" t="n">
         <v>0.00369</v>
       </c>
     </row>
@@ -28021,9 +29611,12 @@
         <v>1.32</v>
       </c>
       <c r="O530" s="1" t="n">
+        <v>1.326</v>
+      </c>
+      <c r="P530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="P530" s="1" t="n">
+      <c r="Q530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -28073,9 +29666,12 @@
         <v>0.4882</v>
       </c>
       <c r="O531" s="1" t="n">
+        <v>0.4885</v>
+      </c>
+      <c r="P531" s="1" t="n">
         <v>0.494</v>
       </c>
-      <c r="P531" s="1" t="n">
+      <c r="Q531" s="1" t="n">
         <v>0.4882</v>
       </c>
     </row>
@@ -28125,9 +29721,12 @@
         <v>0.03061</v>
       </c>
       <c r="O532" s="1" t="n">
+        <v>0.03062</v>
+      </c>
+      <c r="P532" s="1" t="n">
         <v>0.03091</v>
       </c>
-      <c r="P532" s="1" t="n">
+      <c r="Q532" s="1" t="n">
         <v>0.03058</v>
       </c>
     </row>
@@ -28177,9 +29776,12 @@
         <v>0.1524</v>
       </c>
       <c r="O533" s="1" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="P533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="P533" s="1" t="n">
+      <c r="Q533" s="1" t="n">
         <v>0.1524</v>
       </c>
     </row>
@@ -28229,10 +29831,13 @@
         <v>0.05374</v>
       </c>
       <c r="O534" s="1" t="n">
+        <v>0.05344</v>
+      </c>
+      <c r="P534" s="1" t="n">
         <v>0.05424</v>
       </c>
-      <c r="P534" s="1" t="n">
-        <v>0.0536</v>
+      <c r="Q534" s="1" t="n">
+        <v>0.05344</v>
       </c>
     </row>
     <row r="535">
@@ -28281,10 +29886,13 @@
         <v>0.01489</v>
       </c>
       <c r="O535" s="1" t="n">
+        <v>0.01479</v>
+      </c>
+      <c r="P535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="P535" s="1" t="n">
-        <v>0.01489</v>
+      <c r="Q535" s="1" t="n">
+        <v>0.01479</v>
       </c>
     </row>
     <row r="536">
@@ -28333,9 +29941,12 @@
         <v>0.0589</v>
       </c>
       <c r="O536" s="1" t="n">
+        <v>0.05866</v>
+      </c>
+      <c r="P536" s="1" t="n">
         <v>0.05909</v>
       </c>
-      <c r="P536" s="1" t="n">
+      <c r="Q536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -28385,10 +29996,13 @@
         <v>0.05484</v>
       </c>
       <c r="O537" s="1" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="P537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="P537" s="1" t="n">
-        <v>0.05481</v>
+      <c r="Q537" s="1" t="n">
+        <v>0.0548</v>
       </c>
     </row>
     <row r="538">
@@ -28437,9 +30051,12 @@
         <v>0.1058</v>
       </c>
       <c r="O538" s="1" t="n">
+        <v>0.1059</v>
+      </c>
+      <c r="P538" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="P538" s="1" t="n">
+      <c r="Q538" s="1" t="n">
         <v>0.1058</v>
       </c>
     </row>
@@ -28489,9 +30106,12 @@
         <v>0.01274</v>
       </c>
       <c r="O539" s="1" t="n">
+        <v>0.01273</v>
+      </c>
+      <c r="P539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="P539" s="1" t="n">
+      <c r="Q539" s="1" t="n">
         <v>0.01273</v>
       </c>
     </row>
@@ -28541,10 +30161,13 @@
         <v>0.1736</v>
       </c>
       <c r="O540" s="1" t="n">
+        <v>0.1728</v>
+      </c>
+      <c r="P540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="P540" s="1" t="n">
-        <v>0.1736</v>
+      <c r="Q540" s="1" t="n">
+        <v>0.1728</v>
       </c>
     </row>
     <row r="541">
@@ -28593,9 +30216,12 @@
         <v>0.1225</v>
       </c>
       <c r="O541" s="1" t="n">
+        <v>0.1228</v>
+      </c>
+      <c r="P541" s="1" t="n">
         <v>0.1239</v>
       </c>
-      <c r="P541" s="1" t="n">
+      <c r="Q541" s="1" t="n">
         <v>0.1225</v>
       </c>
     </row>
@@ -28645,10 +30271,13 @@
         <v>0.02485</v>
       </c>
       <c r="O542" s="1" t="n">
+        <v>0.02478</v>
+      </c>
+      <c r="P542" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="P542" s="1" t="n">
-        <v>0.02481</v>
+      <c r="Q542" s="1" t="n">
+        <v>0.02478</v>
       </c>
     </row>
     <row r="543">
@@ -28697,9 +30326,12 @@
         <v>0.05869</v>
       </c>
       <c r="O543" s="1" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="P543" s="1" t="n">
         <v>0.059</v>
       </c>
-      <c r="P543" s="1" t="n">
+      <c r="Q543" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T543"/>
+  <dimension ref="A1:U543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -437,8 +437,9 @@
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -534,10 +535,15 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>price_04:15</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -601,9 +607,12 @@
         <v>71128.7</v>
       </c>
       <c r="S2" s="1" t="n">
+        <v>71313</v>
+      </c>
+      <c r="T2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="T2" s="1" t="n">
+      <c r="U2" s="1" t="n">
         <v>70995.10000000001</v>
       </c>
     </row>
@@ -665,9 +674,12 @@
         <v>2101</v>
       </c>
       <c r="S3" s="1" t="n">
+        <v>2108.32</v>
+      </c>
+      <c r="T3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="T3" s="1" t="n">
+      <c r="U3" s="1" t="n">
         <v>2098.64</v>
       </c>
     </row>
@@ -729,9 +741,12 @@
         <v>88.84</v>
       </c>
       <c r="S4" s="1" t="n">
+        <v>88.83</v>
+      </c>
+      <c r="T4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="T4" s="1" t="n">
+      <c r="U4" s="1" t="n">
         <v>88.7</v>
       </c>
     </row>
@@ -793,9 +808,12 @@
         <v>3.834</v>
       </c>
       <c r="S5" s="1" t="n">
+        <v>3.846</v>
+      </c>
+      <c r="T5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="T5" s="1" t="n">
+      <c r="U5" s="1" t="n">
         <v>3.766</v>
       </c>
     </row>
@@ -857,9 +875,12 @@
         <v>1.4</v>
       </c>
       <c r="S6" s="1" t="n">
+        <v>1.4007</v>
+      </c>
+      <c r="T6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="T6" s="1" t="n">
+      <c r="U6" s="1" t="n">
         <v>1.3931</v>
       </c>
     </row>
@@ -921,9 +942,12 @@
         <v>0.09596</v>
       </c>
       <c r="S7" s="1" t="n">
+        <v>0.0964</v>
+      </c>
+      <c r="T7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="T7" s="1" t="n">
+      <c r="U7" s="1" t="n">
         <v>0.09572</v>
       </c>
     </row>
@@ -985,9 +1009,12 @@
         <v>0.014425</v>
       </c>
       <c r="S8" s="1" t="n">
+        <v>0.014261</v>
+      </c>
+      <c r="T8" s="1" t="n">
         <v>0.014819</v>
       </c>
-      <c r="T8" s="1" t="n">
+      <c r="U8" s="1" t="n">
         <v>0.014064</v>
       </c>
     </row>
@@ -1049,9 +1076,12 @@
         <v>657.2</v>
       </c>
       <c r="S9" s="1" t="n">
+        <v>658.15</v>
+      </c>
+      <c r="T9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="T9" s="1" t="n">
+      <c r="U9" s="1" t="n">
         <v>655.72</v>
       </c>
     </row>
@@ -1113,9 +1143,12 @@
         <v>20.308</v>
       </c>
       <c r="S10" s="1" t="n">
-        <v>20.308</v>
+        <v>20.4</v>
       </c>
       <c r="T10" s="1" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="U10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -1177,9 +1210,12 @@
         <v>0.0033886</v>
       </c>
       <c r="S11" s="1" t="n">
+        <v>0.0033967</v>
+      </c>
+      <c r="T11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="T11" s="1" t="n">
+      <c r="U11" s="1" t="n">
         <v>0.0033816</v>
       </c>
     </row>
@@ -1241,9 +1277,12 @@
         <v>36.735</v>
       </c>
       <c r="S12" s="1" t="n">
+        <v>36.721</v>
+      </c>
+      <c r="T12" s="1" t="n">
         <v>36.735</v>
       </c>
-      <c r="T12" s="1" t="n">
+      <c r="U12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -1305,10 +1344,13 @@
         <v>212.45</v>
       </c>
       <c r="S13" s="1" t="n">
+        <v>211.82</v>
+      </c>
+      <c r="T13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="T13" s="1" t="n">
-        <v>212.33</v>
+      <c r="U13" s="1" t="n">
+        <v>211.82</v>
       </c>
     </row>
     <row r="14">
@@ -1369,9 +1411,12 @@
         <v>0.0011213</v>
       </c>
       <c r="S14" s="1" t="n">
+        <v>0.0011252</v>
+      </c>
+      <c r="T14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="T14" s="1" t="n">
+      <c r="U14" s="1" t="n">
         <v>0.0011136</v>
       </c>
     </row>
@@ -1433,9 +1478,12 @@
         <v>0.31973</v>
       </c>
       <c r="S15" s="1" t="n">
-        <v>0.31973</v>
+        <v>0.34247</v>
       </c>
       <c r="T15" s="1" t="n">
+        <v>0.34247</v>
+      </c>
+      <c r="U15" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -1497,9 +1545,12 @@
         <v>229.42</v>
       </c>
       <c r="S16" s="1" t="n">
+        <v>231.28</v>
+      </c>
+      <c r="T16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="T16" s="1" t="n">
+      <c r="U16" s="1" t="n">
         <v>229.42</v>
       </c>
     </row>
@@ -1561,9 +1612,12 @@
         <v>1.0008</v>
       </c>
       <c r="S17" s="1" t="n">
+        <v>1.0018</v>
+      </c>
+      <c r="T17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="T17" s="1" t="n">
+      <c r="U17" s="1" t="n">
         <v>0.9963</v>
       </c>
     </row>
@@ -1625,9 +1679,12 @@
         <v>0.2671</v>
       </c>
       <c r="S18" s="1" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="T18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="T18" s="1" t="n">
+      <c r="U18" s="1" t="n">
         <v>0.2664</v>
       </c>
     </row>
@@ -1689,9 +1746,12 @@
         <v>9.766999999999999</v>
       </c>
       <c r="S19" s="1" t="n">
+        <v>9.784000000000001</v>
+      </c>
+      <c r="T19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="T19" s="1" t="n">
+      <c r="U19" s="1" t="n">
         <v>9.747999999999999</v>
       </c>
     </row>
@@ -1753,10 +1813,13 @@
         <v>5019.17</v>
       </c>
       <c r="S20" s="1" t="n">
+        <v>5018.76</v>
+      </c>
+      <c r="T20" s="1" t="n">
         <v>5059.14</v>
       </c>
-      <c r="T20" s="1" t="n">
-        <v>5019.17</v>
+      <c r="U20" s="1" t="n">
+        <v>5018.76</v>
       </c>
     </row>
     <row r="21">
@@ -1817,9 +1880,12 @@
         <v>462.96</v>
       </c>
       <c r="S21" s="1" t="n">
+        <v>463.74</v>
+      </c>
+      <c r="T21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="T21" s="1" t="n">
+      <c r="U21" s="1" t="n">
         <v>462.36</v>
       </c>
     </row>
@@ -1881,10 +1947,13 @@
         <v>1.3823</v>
       </c>
       <c r="S22" s="1" t="n">
+        <v>1.3733</v>
+      </c>
+      <c r="T22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="T22" s="1" t="n">
-        <v>1.3736</v>
+      <c r="U22" s="1" t="n">
+        <v>1.3733</v>
       </c>
     </row>
     <row r="23">
@@ -1945,9 +2014,12 @@
         <v>1.0666</v>
       </c>
       <c r="S23" s="1" t="n">
+        <v>1.0662</v>
+      </c>
+      <c r="T23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="T23" s="1" t="n">
+      <c r="U23" s="1" t="n">
         <v>1.0136</v>
       </c>
     </row>
@@ -2009,10 +2081,13 @@
         <v>1.344</v>
       </c>
       <c r="S24" s="1" t="n">
+        <v>1.342</v>
+      </c>
+      <c r="T24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="T24" s="1" t="n">
-        <v>1.343</v>
+      <c r="U24" s="1" t="n">
+        <v>1.342</v>
       </c>
     </row>
     <row r="25">
@@ -2073,9 +2148,12 @@
         <v>9.140000000000001</v>
       </c>
       <c r="S25" s="1" t="n">
+        <v>9.157</v>
+      </c>
+      <c r="T25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="T25" s="1" t="n">
+      <c r="U25" s="1" t="n">
         <v>9.113</v>
       </c>
     </row>
@@ -2137,9 +2215,12 @@
         <v>0.3717</v>
       </c>
       <c r="S26" s="1" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="T26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="T26" s="1" t="n">
+      <c r="U26" s="1" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -2201,9 +2282,12 @@
         <v>0.872</v>
       </c>
       <c r="S27" s="1" t="n">
+        <v>0.872</v>
+      </c>
+      <c r="T27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="T27" s="1" t="n">
+      <c r="U27" s="1" t="n">
         <v>0.872</v>
       </c>
     </row>
@@ -2265,9 +2349,12 @@
         <v>1.835</v>
       </c>
       <c r="S28" s="1" t="n">
+        <v>1.839</v>
+      </c>
+      <c r="T28" s="1" t="n">
         <v>1.844</v>
       </c>
-      <c r="T28" s="1" t="n">
+      <c r="U28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -2329,9 +2416,12 @@
         <v>0.109</v>
       </c>
       <c r="S29" s="1" t="n">
+        <v>0.1092</v>
+      </c>
+      <c r="T29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="T29" s="1" t="n">
+      <c r="U29" s="1" t="n">
         <v>0.1089</v>
       </c>
     </row>
@@ -2393,9 +2483,12 @@
         <v>0.002015</v>
       </c>
       <c r="S30" s="1" t="n">
+        <v>0.002017</v>
+      </c>
+      <c r="T30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="T30" s="1" t="n">
+      <c r="U30" s="1" t="n">
         <v>0.002011</v>
       </c>
     </row>
@@ -2457,10 +2550,13 @@
         <v>1.467</v>
       </c>
       <c r="S31" s="1" t="n">
+        <v>1.461</v>
+      </c>
+      <c r="T31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="T31" s="1" t="n">
-        <v>1.466</v>
+      <c r="U31" s="1" t="n">
+        <v>1.461</v>
       </c>
     </row>
     <row r="32">
@@ -2521,9 +2617,12 @@
         <v>0.1771</v>
       </c>
       <c r="S32" s="1" t="n">
+        <v>0.1776</v>
+      </c>
+      <c r="T32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="T32" s="1" t="n">
+      <c r="U32" s="1" t="n">
         <v>0.1739</v>
       </c>
     </row>
@@ -2585,9 +2684,12 @@
         <v>0.1036</v>
       </c>
       <c r="S33" s="1" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="T33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="T33" s="1" t="n">
+      <c r="U33" s="1" t="n">
         <v>0.1035</v>
       </c>
     </row>
@@ -2649,9 +2751,12 @@
         <v>112.81</v>
       </c>
       <c r="S34" s="1" t="n">
+        <v>113.21</v>
+      </c>
+      <c r="T34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="T34" s="1" t="n">
+      <c r="U34" s="1" t="n">
         <v>112.49</v>
       </c>
     </row>
@@ -2713,9 +2818,12 @@
         <v>6.645</v>
       </c>
       <c r="S35" s="1" t="n">
+        <v>6.759</v>
+      </c>
+      <c r="T35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="T35" s="1" t="n">
+      <c r="U35" s="1" t="n">
         <v>6.587</v>
       </c>
     </row>
@@ -2777,9 +2885,12 @@
         <v>0.017641</v>
       </c>
       <c r="S36" s="1" t="n">
+        <v>0.017591</v>
+      </c>
+      <c r="T36" s="1" t="n">
         <v>0.017668</v>
       </c>
-      <c r="T36" s="1" t="n">
+      <c r="U36" s="1" t="n">
         <v>0.016815</v>
       </c>
     </row>
@@ -2841,9 +2952,12 @@
         <v>0.3605</v>
       </c>
       <c r="S37" s="1" t="n">
+        <v>0.3606</v>
+      </c>
+      <c r="T37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="T37" s="1" t="n">
+      <c r="U37" s="1" t="n">
         <v>0.3595</v>
       </c>
     </row>
@@ -2905,9 +3019,12 @@
         <v>55.58</v>
       </c>
       <c r="S38" s="1" t="n">
+        <v>55.65</v>
+      </c>
+      <c r="T38" s="1" t="n">
         <v>55.79</v>
       </c>
-      <c r="T38" s="1" t="n">
+      <c r="U38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -2969,10 +3086,13 @@
         <v>0.61856</v>
       </c>
       <c r="S39" s="1" t="n">
+        <v>0.5732</v>
+      </c>
+      <c r="T39" s="1" t="n">
         <v>0.61856</v>
       </c>
-      <c r="T39" s="1" t="n">
-        <v>0.58131</v>
+      <c r="U39" s="1" t="n">
+        <v>0.5732</v>
       </c>
     </row>
     <row r="40">
@@ -3033,9 +3153,12 @@
         <v>4.027</v>
       </c>
       <c r="S40" s="1" t="n">
+        <v>4.028</v>
+      </c>
+      <c r="T40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="T40" s="1" t="n">
+      <c r="U40" s="1" t="n">
         <v>4.017</v>
       </c>
     </row>
@@ -3097,10 +3220,13 @@
         <v>0.04921</v>
       </c>
       <c r="S41" s="1" t="n">
+        <v>0.04892</v>
+      </c>
+      <c r="T41" s="1" t="n">
         <v>0.0513</v>
       </c>
-      <c r="T41" s="1" t="n">
-        <v>0.04921</v>
+      <c r="U41" s="1" t="n">
+        <v>0.04892</v>
       </c>
     </row>
     <row r="42">
@@ -3161,9 +3287,12 @@
         <v>0.6995</v>
       </c>
       <c r="S42" s="1" t="n">
+        <v>0.7005</v>
+      </c>
+      <c r="T42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="T42" s="1" t="n">
+      <c r="U42" s="1" t="n">
         <v>0.6995</v>
       </c>
     </row>
@@ -3225,9 +3354,12 @@
         <v>0.22809</v>
       </c>
       <c r="S43" s="1" t="n">
+        <v>0.2279</v>
+      </c>
+      <c r="T43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="T43" s="1" t="n">
+      <c r="U43" s="1" t="n">
         <v>0.22771</v>
       </c>
     </row>
@@ -3289,9 +3421,12 @@
         <v>0.35918</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>0.35918</v>
+        <v>0.35992</v>
       </c>
       <c r="T44" s="1" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="U44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -3353,9 +3488,12 @@
         <v>0.1686</v>
       </c>
       <c r="S45" s="1" t="n">
+        <v>0.1687</v>
+      </c>
+      <c r="T45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="T45" s="1" t="n">
+      <c r="U45" s="1" t="n">
         <v>0.1682</v>
       </c>
     </row>
@@ -3417,9 +3555,12 @@
         <v>0.026</v>
       </c>
       <c r="S46" s="1" t="n">
+        <v>0.0261</v>
+      </c>
+      <c r="T46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="T46" s="1" t="n">
+      <c r="U46" s="1" t="n">
         <v>0.0258</v>
       </c>
     </row>
@@ -3481,9 +3622,12 @@
         <v>0.005953</v>
       </c>
       <c r="S47" s="1" t="n">
+        <v>0.005965</v>
+      </c>
+      <c r="T47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="T47" s="1" t="n">
+      <c r="U47" s="1" t="n">
         <v>0.00594</v>
       </c>
     </row>
@@ -3545,9 +3689,12 @@
         <v>0.007372</v>
       </c>
       <c r="S48" s="1" t="n">
+        <v>0.007383</v>
+      </c>
+      <c r="T48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="T48" s="1" t="n">
+      <c r="U48" s="1" t="n">
         <v>0.007343</v>
       </c>
     </row>
@@ -3609,9 +3756,12 @@
         <v>0.1094</v>
       </c>
       <c r="S49" s="1" t="n">
+        <v>0.1097</v>
+      </c>
+      <c r="T49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="T49" s="1" t="n">
+      <c r="U49" s="1" t="n">
         <v>0.1077</v>
       </c>
     </row>
@@ -3673,9 +3823,12 @@
         <v>0.04215</v>
       </c>
       <c r="S50" s="1" t="n">
+        <v>0.04211</v>
+      </c>
+      <c r="T50" s="1" t="n">
         <v>0.04215</v>
       </c>
-      <c r="T50" s="1" t="n">
+      <c r="U50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -3737,9 +3890,12 @@
         <v>0.1621</v>
       </c>
       <c r="S51" s="1" t="n">
+        <v>0.1624</v>
+      </c>
+      <c r="T51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="T51" s="1" t="n">
+      <c r="U51" s="1" t="n">
         <v>0.1614</v>
       </c>
     </row>
@@ -3801,9 +3957,12 @@
         <v>0.00353</v>
       </c>
       <c r="S52" s="1" t="n">
+        <v>0.00354</v>
+      </c>
+      <c r="T52" s="1" t="n">
         <v>0.00357</v>
       </c>
-      <c r="T52" s="1" t="n">
+      <c r="U52" s="1" t="n">
         <v>0.0035</v>
       </c>
     </row>
@@ -3865,9 +4024,12 @@
         <v>2.613</v>
       </c>
       <c r="S53" s="1" t="n">
+        <v>2.618</v>
+      </c>
+      <c r="T53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="T53" s="1" t="n">
+      <c r="U53" s="1" t="n">
         <v>2.613</v>
       </c>
     </row>
@@ -3929,9 +4091,12 @@
         <v>0.006187</v>
       </c>
       <c r="S54" s="1" t="n">
+        <v>0.006195</v>
+      </c>
+      <c r="T54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="T54" s="1" t="n">
+      <c r="U54" s="1" t="n">
         <v>0.006157</v>
       </c>
     </row>
@@ -3993,10 +4158,13 @@
         <v>0.02875</v>
       </c>
       <c r="S55" s="1" t="n">
+        <v>0.02867</v>
+      </c>
+      <c r="T55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="T55" s="1" t="n">
-        <v>0.02875</v>
+      <c r="U55" s="1" t="n">
+        <v>0.02867</v>
       </c>
     </row>
     <row r="56">
@@ -4057,9 +4225,12 @@
         <v>0.7344000000000001</v>
       </c>
       <c r="S56" s="1" t="n">
+        <v>0.7362</v>
+      </c>
+      <c r="T56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="T56" s="1" t="n">
+      <c r="U56" s="1" t="n">
         <v>0.7322</v>
       </c>
     </row>
@@ -4121,9 +4292,12 @@
         <v>0.1034</v>
       </c>
       <c r="S57" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="T57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="T57" s="1" t="n">
+      <c r="U57" s="1" t="n">
         <v>0.103</v>
       </c>
     </row>
@@ -4185,9 +4359,12 @@
         <v>0.9383</v>
       </c>
       <c r="S58" s="1" t="n">
+        <v>0.9383</v>
+      </c>
+      <c r="T58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="T58" s="1" t="n">
+      <c r="U58" s="1" t="n">
         <v>0.9355</v>
       </c>
     </row>
@@ -4249,9 +4426,12 @@
         <v>0.08767</v>
       </c>
       <c r="S59" s="1" t="n">
+        <v>0.08697000000000001</v>
+      </c>
+      <c r="T59" s="1" t="n">
         <v>0.08826000000000001</v>
       </c>
-      <c r="T59" s="1" t="n">
+      <c r="U59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -4313,9 +4493,12 @@
         <v>0.06909</v>
       </c>
       <c r="S60" s="1" t="n">
+        <v>0.06909999999999999</v>
+      </c>
+      <c r="T60" s="1" t="n">
         <v>0.0703</v>
       </c>
-      <c r="T60" s="1" t="n">
+      <c r="U60" s="1" t="n">
         <v>0.06900000000000001</v>
       </c>
     </row>
@@ -4377,9 +4560,12 @@
         <v>0.05457</v>
       </c>
       <c r="S61" s="1" t="n">
+        <v>0.05467</v>
+      </c>
+      <c r="T61" s="1" t="n">
         <v>0.05523</v>
       </c>
-      <c r="T61" s="1" t="n">
+      <c r="U61" s="1" t="n">
         <v>0.05439</v>
       </c>
     </row>
@@ -4441,9 +4627,12 @@
         <v>0.010478</v>
       </c>
       <c r="S62" s="1" t="n">
-        <v>0.010478</v>
+        <v>0.010624</v>
       </c>
       <c r="T62" s="1" t="n">
+        <v>0.010624</v>
+      </c>
+      <c r="U62" s="1" t="n">
         <v>0.009387</v>
       </c>
     </row>
@@ -4505,9 +4694,12 @@
         <v>0.29164</v>
       </c>
       <c r="S63" s="1" t="n">
-        <v>0.29164</v>
+        <v>0.29207</v>
       </c>
       <c r="T63" s="1" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="U63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -4569,9 +4761,12 @@
         <v>0.07548000000000001</v>
       </c>
       <c r="S64" s="1" t="n">
+        <v>0.07523000000000001</v>
+      </c>
+      <c r="T64" s="1" t="n">
         <v>0.07613</v>
       </c>
-      <c r="T64" s="1" t="n">
+      <c r="U64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -4633,9 +4828,12 @@
         <v>0.3166</v>
       </c>
       <c r="S65" s="1" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="T65" s="1" t="n">
         <v>0.3186</v>
       </c>
-      <c r="T65" s="1" t="n">
+      <c r="U65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -4697,9 +4895,12 @@
         <v>0.16269</v>
       </c>
       <c r="S66" s="1" t="n">
+        <v>0.16294</v>
+      </c>
+      <c r="T66" s="1" t="n">
         <v>0.16461</v>
       </c>
-      <c r="T66" s="1" t="n">
+      <c r="U66" s="1" t="n">
         <v>0.1622</v>
       </c>
     </row>
@@ -4761,9 +4962,12 @@
         <v>0.1203</v>
       </c>
       <c r="S67" s="1" t="n">
+        <v>0.12026</v>
+      </c>
+      <c r="T67" s="1" t="n">
         <v>0.1203</v>
       </c>
-      <c r="T67" s="1" t="n">
+      <c r="U67" s="1" t="n">
         <v>0.11919</v>
       </c>
     </row>
@@ -4825,9 +5029,12 @@
         <v>0.09501999999999999</v>
       </c>
       <c r="S68" s="1" t="n">
+        <v>0.09487</v>
+      </c>
+      <c r="T68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="T68" s="1" t="n">
+      <c r="U68" s="1" t="n">
         <v>0.09487</v>
       </c>
     </row>
@@ -4889,9 +5096,12 @@
         <v>0.1242</v>
       </c>
       <c r="S69" s="1" t="n">
+        <v>0.1242</v>
+      </c>
+      <c r="T69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="T69" s="1" t="n">
+      <c r="U69" s="1" t="n">
         <v>0.1239</v>
       </c>
     </row>
@@ -4953,9 +5163,12 @@
         <v>8.509</v>
       </c>
       <c r="S70" s="1" t="n">
+        <v>8.513999999999999</v>
+      </c>
+      <c r="T70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="T70" s="1" t="n">
+      <c r="U70" s="1" t="n">
         <v>8.491</v>
       </c>
     </row>
@@ -5017,9 +5230,12 @@
         <v>0.239</v>
       </c>
       <c r="S71" s="1" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="T71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="T71" s="1" t="n">
+      <c r="U71" s="1" t="n">
         <v>0.238</v>
       </c>
     </row>
@@ -5081,10 +5297,13 @@
         <v>0.0499</v>
       </c>
       <c r="S72" s="1" t="n">
+        <v>0.04969</v>
+      </c>
+      <c r="T72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="T72" s="1" t="n">
-        <v>0.04983</v>
+      <c r="U72" s="1" t="n">
+        <v>0.04969</v>
       </c>
     </row>
     <row r="73">
@@ -5145,9 +5364,12 @@
         <v>0.05026</v>
       </c>
       <c r="S73" s="1" t="n">
+        <v>0.05046</v>
+      </c>
+      <c r="T73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="T73" s="1" t="n">
+      <c r="U73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -5209,9 +5431,12 @@
         <v>0.124</v>
       </c>
       <c r="S74" s="1" t="n">
+        <v>0.1243</v>
+      </c>
+      <c r="T74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="T74" s="1" t="n">
+      <c r="U74" s="1" t="n">
         <v>0.124</v>
       </c>
     </row>
@@ -5273,9 +5498,12 @@
         <v>0.04669</v>
       </c>
       <c r="S75" s="1" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="T75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="T75" s="1" t="n">
+      <c r="U75" s="1" t="n">
         <v>0.04619</v>
       </c>
     </row>
@@ -5337,10 +5565,13 @@
         <v>0.06679</v>
       </c>
       <c r="S76" s="1" t="n">
+        <v>0.06678000000000001</v>
+      </c>
+      <c r="T76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="T76" s="1" t="n">
-        <v>0.06679</v>
+      <c r="U76" s="1" t="n">
+        <v>0.06678000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -5401,9 +5632,12 @@
         <v>0.13048</v>
       </c>
       <c r="S77" s="1" t="n">
-        <v>0.13048</v>
+        <v>0.13357</v>
       </c>
       <c r="T77" s="1" t="n">
+        <v>0.13357</v>
+      </c>
+      <c r="U77" s="1" t="n">
         <v>0.12584</v>
       </c>
     </row>
@@ -5465,9 +5699,12 @@
         <v>0.1615</v>
       </c>
       <c r="S78" s="1" t="n">
+        <v>0.1616</v>
+      </c>
+      <c r="T78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="T78" s="1" t="n">
+      <c r="U78" s="1" t="n">
         <v>0.1607</v>
       </c>
     </row>
@@ -5529,9 +5766,12 @@
         <v>0.02699</v>
       </c>
       <c r="S79" s="1" t="n">
+        <v>0.02697</v>
+      </c>
+      <c r="T79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="T79" s="1" t="n">
+      <c r="U79" s="1" t="n">
         <v>0.02693</v>
       </c>
     </row>
@@ -5593,9 +5833,12 @@
         <v>358.27</v>
       </c>
       <c r="S80" s="1" t="n">
-        <v>358.62</v>
+        <v>359.36</v>
       </c>
       <c r="T80" s="1" t="n">
+        <v>359.36</v>
+      </c>
+      <c r="U80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -5657,9 +5900,12 @@
         <v>7.054999999999999e-05</v>
       </c>
       <c r="S81" s="1" t="n">
+        <v>7.062e-05</v>
+      </c>
+      <c r="T81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="T81" s="1" t="n">
+      <c r="U81" s="1" t="n">
         <v>7.029000000000001e-05</v>
       </c>
     </row>
@@ -5721,9 +5967,12 @@
         <v>0.2655</v>
       </c>
       <c r="S82" s="1" t="n">
+        <v>0.2658</v>
+      </c>
+      <c r="T82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="T82" s="1" t="n">
+      <c r="U82" s="1" t="n">
         <v>0.2645</v>
       </c>
     </row>
@@ -5785,9 +6034,12 @@
         <v>1.1056</v>
       </c>
       <c r="S83" s="1" t="n">
+        <v>1.1136</v>
+      </c>
+      <c r="T83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="T83" s="1" t="n">
+      <c r="U83" s="1" t="n">
         <v>1.1054</v>
       </c>
     </row>
@@ -5849,9 +6101,12 @@
         <v>0.3505</v>
       </c>
       <c r="S84" s="1" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="T84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="T84" s="1" t="n">
+      <c r="U84" s="1" t="n">
         <v>0.3496</v>
       </c>
     </row>
@@ -5913,9 +6168,12 @@
         <v>1.9854</v>
       </c>
       <c r="S85" s="1" t="n">
+        <v>1.9822</v>
+      </c>
+      <c r="T85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="T85" s="1" t="n">
+      <c r="U85" s="1" t="n">
         <v>1.9784</v>
       </c>
     </row>
@@ -5977,9 +6235,12 @@
         <v>1.3189</v>
       </c>
       <c r="S86" s="1" t="n">
+        <v>1.3165</v>
+      </c>
+      <c r="T86" s="1" t="n">
         <v>1.3205</v>
       </c>
-      <c r="T86" s="1" t="n">
+      <c r="U86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -6041,9 +6302,12 @@
         <v>32.53</v>
       </c>
       <c r="S87" s="1" t="n">
+        <v>32.59</v>
+      </c>
+      <c r="T87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="T87" s="1" t="n">
+      <c r="U87" s="1" t="n">
         <v>32.52</v>
       </c>
     </row>
@@ -6105,9 +6369,12 @@
         <v>0.00942</v>
       </c>
       <c r="S88" s="1" t="n">
+        <v>0.009509999999999999</v>
+      </c>
+      <c r="T88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="T88" s="1" t="n">
+      <c r="U88" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -6169,9 +6436,12 @@
         <v>0.01798</v>
       </c>
       <c r="S89" s="1" t="n">
+        <v>0.01802</v>
+      </c>
+      <c r="T89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="T89" s="1" t="n">
+      <c r="U89" s="1" t="n">
         <v>0.01798</v>
       </c>
     </row>
@@ -6233,9 +6503,12 @@
         <v>0.03468</v>
       </c>
       <c r="S90" s="1" t="n">
+        <v>0.03478</v>
+      </c>
+      <c r="T90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="T90" s="1" t="n">
+      <c r="U90" s="1" t="n">
         <v>0.03468</v>
       </c>
     </row>
@@ -6297,10 +6570,13 @@
         <v>0.01178</v>
       </c>
       <c r="S91" s="1" t="n">
+        <v>0.01172</v>
+      </c>
+      <c r="T91" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="T91" s="1" t="n">
-        <v>0.01178</v>
+      <c r="U91" s="1" t="n">
+        <v>0.01172</v>
       </c>
     </row>
     <row r="92">
@@ -6361,9 +6637,12 @@
         <v>3.095</v>
       </c>
       <c r="S92" s="1" t="n">
+        <v>3.096</v>
+      </c>
+      <c r="T92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="T92" s="1" t="n">
+      <c r="U92" s="1" t="n">
         <v>3.09</v>
       </c>
     </row>
@@ -6425,9 +6704,12 @@
         <v>0.005571</v>
       </c>
       <c r="S93" s="1" t="n">
+        <v>0.005579</v>
+      </c>
+      <c r="T93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="T93" s="1" t="n">
+      <c r="U93" s="1" t="n">
         <v>0.00557</v>
       </c>
     </row>
@@ -6489,9 +6771,12 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="S94" s="1" t="n">
+        <v>0.09320000000000001</v>
+      </c>
+      <c r="T94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="T94" s="1" t="n">
+      <c r="U94" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -6553,9 +6838,12 @@
         <v>0.6098</v>
       </c>
       <c r="S95" s="1" t="n">
-        <v>0.6098</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="T95" s="1" t="n">
+        <v>0.6124000000000001</v>
+      </c>
+      <c r="U95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -6617,9 +6905,12 @@
         <v>1.28e-05</v>
       </c>
       <c r="S96" s="1" t="n">
+        <v>1.28e-05</v>
+      </c>
+      <c r="T96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="T96" s="1" t="n">
+      <c r="U96" s="1" t="n">
         <v>1.27e-05</v>
       </c>
     </row>
@@ -6681,9 +6972,12 @@
         <v>1.102</v>
       </c>
       <c r="S97" s="1" t="n">
+        <v>1.107</v>
+      </c>
+      <c r="T97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="T97" s="1" t="n">
+      <c r="U97" s="1" t="n">
         <v>1.102</v>
       </c>
     </row>
@@ -6745,9 +7039,12 @@
         <v>0.2542</v>
       </c>
       <c r="S98" s="1" t="n">
+        <v>0.25299</v>
+      </c>
+      <c r="T98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="T98" s="1" t="n">
+      <c r="U98" s="1" t="n">
         <v>0.2523</v>
       </c>
     </row>
@@ -6809,9 +7106,12 @@
         <v>1.145</v>
       </c>
       <c r="S99" s="1" t="n">
+        <v>1.149</v>
+      </c>
+      <c r="T99" s="1" t="n">
         <v>1.156</v>
       </c>
-      <c r="T99" s="1" t="n">
+      <c r="U99" s="1" t="n">
         <v>1.14</v>
       </c>
     </row>
@@ -6873,9 +7173,12 @@
         <v>1.853</v>
       </c>
       <c r="S100" s="1" t="n">
+        <v>1.852</v>
+      </c>
+      <c r="T100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="T100" s="1" t="n">
+      <c r="U100" s="1" t="n">
         <v>1.852</v>
       </c>
     </row>
@@ -6937,9 +7240,12 @@
         <v>0.01577</v>
       </c>
       <c r="S101" s="1" t="n">
+        <v>0.01578</v>
+      </c>
+      <c r="T101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="T101" s="1" t="n">
+      <c r="U101" s="1" t="n">
         <v>0.01575</v>
       </c>
     </row>
@@ -7001,10 +7307,13 @@
         <v>0.10155</v>
       </c>
       <c r="S102" s="1" t="n">
+        <v>0.10145</v>
+      </c>
+      <c r="T102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="T102" s="1" t="n">
-        <v>0.10155</v>
+      <c r="U102" s="1" t="n">
+        <v>0.10145</v>
       </c>
     </row>
     <row r="103">
@@ -7065,9 +7374,12 @@
         <v>0.0005957</v>
       </c>
       <c r="S103" s="1" t="n">
+        <v>0.0005962</v>
+      </c>
+      <c r="T103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="T103" s="1" t="n">
+      <c r="U103" s="1" t="n">
         <v>0.0005941</v>
       </c>
     </row>
@@ -7129,9 +7441,12 @@
         <v>0.0005932</v>
       </c>
       <c r="S104" s="1" t="n">
+        <v>0.0005917</v>
+      </c>
+      <c r="T104" s="1" t="n">
         <v>0.0005932</v>
       </c>
-      <c r="T104" s="1" t="n">
+      <c r="U104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -7193,9 +7508,12 @@
         <v>0.003216</v>
       </c>
       <c r="S105" s="1" t="n">
+        <v>0.003224</v>
+      </c>
+      <c r="T105" s="1" t="n">
         <v>0.003269</v>
       </c>
-      <c r="T105" s="1" t="n">
+      <c r="U105" s="1" t="n">
         <v>0.003216</v>
       </c>
     </row>
@@ -7257,9 +7575,12 @@
         <v>2.575</v>
       </c>
       <c r="S106" s="1" t="n">
+        <v>2.574</v>
+      </c>
+      <c r="T106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="T106" s="1" t="n">
+      <c r="U106" s="1" t="n">
         <v>2.572</v>
       </c>
     </row>
@@ -7321,9 +7642,12 @@
         <v>0.1654</v>
       </c>
       <c r="S107" s="1" t="n">
+        <v>0.1658</v>
+      </c>
+      <c r="T107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="T107" s="1" t="n">
+      <c r="U107" s="1" t="n">
         <v>0.165</v>
       </c>
     </row>
@@ -7385,9 +7709,12 @@
         <v>0.09617000000000001</v>
       </c>
       <c r="S108" s="1" t="n">
+        <v>0.09597</v>
+      </c>
+      <c r="T108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="T108" s="1" t="n">
+      <c r="U108" s="1" t="n">
         <v>0.0955</v>
       </c>
     </row>
@@ -7449,9 +7776,12 @@
         <v>0.02208</v>
       </c>
       <c r="S109" s="1" t="n">
+        <v>0.0221</v>
+      </c>
+      <c r="T109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="T109" s="1" t="n">
+      <c r="U109" s="1" t="n">
         <v>0.02202</v>
       </c>
     </row>
@@ -7513,9 +7843,12 @@
         <v>0.2911</v>
       </c>
       <c r="S110" s="1" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="T110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="T110" s="1" t="n">
+      <c r="U110" s="1" t="n">
         <v>0.2894</v>
       </c>
     </row>
@@ -7577,9 +7910,12 @@
         <v>0.05688</v>
       </c>
       <c r="S111" s="1" t="n">
+        <v>0.05706</v>
+      </c>
+      <c r="T111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="T111" s="1" t="n">
+      <c r="U111" s="1" t="n">
         <v>0.05651</v>
       </c>
     </row>
@@ -7641,9 +7977,12 @@
         <v>0.3008</v>
       </c>
       <c r="S112" s="1" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="T112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="T112" s="1" t="n">
+      <c r="U112" s="1" t="n">
         <v>0.3002</v>
       </c>
     </row>
@@ -7705,9 +8044,12 @@
         <v>18.55</v>
       </c>
       <c r="S113" s="1" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="T113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="T113" s="1" t="n">
+      <c r="U113" s="1" t="n">
         <v>18.53</v>
       </c>
     </row>
@@ -7769,9 +8111,12 @@
         <v>0.12665</v>
       </c>
       <c r="S114" s="1" t="n">
+        <v>0.12639</v>
+      </c>
+      <c r="T114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="T114" s="1" t="n">
+      <c r="U114" s="1" t="n">
         <v>0.12566</v>
       </c>
     </row>
@@ -7833,9 +8178,12 @@
         <v>0.01569</v>
       </c>
       <c r="S115" s="1" t="n">
+        <v>0.0156</v>
+      </c>
+      <c r="T115" s="1" t="n">
         <v>0.01661</v>
       </c>
-      <c r="T115" s="1" t="n">
+      <c r="U115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -7897,9 +8245,12 @@
         <v>0.08461</v>
       </c>
       <c r="S116" s="1" t="n">
+        <v>0.0847</v>
+      </c>
+      <c r="T116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="T116" s="1" t="n">
+      <c r="U116" s="1" t="n">
         <v>0.08442</v>
       </c>
     </row>
@@ -7961,9 +8312,12 @@
         <v>0.046858</v>
       </c>
       <c r="S117" s="1" t="n">
+        <v>0.0473</v>
+      </c>
+      <c r="T117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="T117" s="1" t="n">
+      <c r="U117" s="1" t="n">
         <v>0.046846</v>
       </c>
     </row>
@@ -8025,9 +8379,12 @@
         <v>0.04711</v>
       </c>
       <c r="S118" s="1" t="n">
+        <v>0.04716</v>
+      </c>
+      <c r="T118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="T118" s="1" t="n">
+      <c r="U118" s="1" t="n">
         <v>0.04701</v>
       </c>
     </row>
@@ -8089,9 +8446,12 @@
         <v>0.0403</v>
       </c>
       <c r="S119" s="1" t="n">
+        <v>0.04022</v>
+      </c>
+      <c r="T119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="T119" s="1" t="n">
+      <c r="U119" s="1" t="n">
         <v>0.03999</v>
       </c>
     </row>
@@ -8153,9 +8513,12 @@
         <v>0.14435</v>
       </c>
       <c r="S120" s="1" t="n">
+        <v>0.14406</v>
+      </c>
+      <c r="T120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="T120" s="1" t="n">
+      <c r="U120" s="1" t="n">
         <v>0.14387</v>
       </c>
     </row>
@@ -8217,9 +8580,12 @@
         <v>0.1252</v>
       </c>
       <c r="S121" s="1" t="n">
+        <v>0.1255</v>
+      </c>
+      <c r="T121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="T121" s="1" t="n">
+      <c r="U121" s="1" t="n">
         <v>0.1252</v>
       </c>
     </row>
@@ -8281,10 +8647,13 @@
         <v>1.854</v>
       </c>
       <c r="S122" s="1" t="n">
+        <v>1.845</v>
+      </c>
+      <c r="T122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="T122" s="1" t="n">
-        <v>1.851</v>
+      <c r="U122" s="1" t="n">
+        <v>1.845</v>
       </c>
     </row>
     <row r="123">
@@ -8345,9 +8714,12 @@
         <v>0.03006</v>
       </c>
       <c r="S123" s="1" t="n">
+        <v>0.03005</v>
+      </c>
+      <c r="T123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="T123" s="1" t="n">
+      <c r="U123" s="1" t="n">
         <v>0.03001</v>
       </c>
     </row>
@@ -8409,9 +8781,12 @@
         <v>0.13289</v>
       </c>
       <c r="S124" s="1" t="n">
-        <v>0.13401</v>
+        <v>0.13475</v>
       </c>
       <c r="T124" s="1" t="n">
+        <v>0.13475</v>
+      </c>
+      <c r="U124" s="1" t="n">
         <v>0.13138</v>
       </c>
     </row>
@@ -8473,9 +8848,12 @@
         <v>0.04075</v>
       </c>
       <c r="S125" s="1" t="n">
+        <v>0.04095</v>
+      </c>
+      <c r="T125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="T125" s="1" t="n">
+      <c r="U125" s="1" t="n">
         <v>0.04075</v>
       </c>
     </row>
@@ -8537,9 +8915,12 @@
         <v>0.1144</v>
       </c>
       <c r="S126" s="1" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="T126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="T126" s="1" t="n">
+      <c r="U126" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -8601,9 +8982,12 @@
         <v>0.5286</v>
       </c>
       <c r="S127" s="1" t="n">
-        <v>0.5286</v>
+        <v>0.53</v>
       </c>
       <c r="T127" s="1" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="U127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -8665,9 +9049,12 @@
         <v>0.03796</v>
       </c>
       <c r="S128" s="1" t="n">
+        <v>0.03819</v>
+      </c>
+      <c r="T128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="T128" s="1" t="n">
+      <c r="U128" s="1" t="n">
         <v>0.0378</v>
       </c>
     </row>
@@ -8729,9 +9116,12 @@
         <v>0.793</v>
       </c>
       <c r="S129" s="1" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="T129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="T129" s="1" t="n">
+      <c r="U129" s="1" t="n">
         <v>0.791</v>
       </c>
     </row>
@@ -8793,9 +9183,12 @@
         <v>0.03453</v>
       </c>
       <c r="S130" s="1" t="n">
+        <v>0.03441</v>
+      </c>
+      <c r="T130" s="1" t="n">
         <v>0.03458</v>
       </c>
-      <c r="T130" s="1" t="n">
+      <c r="U130" s="1" t="n">
         <v>0.03422</v>
       </c>
     </row>
@@ -8857,9 +9250,12 @@
         <v>0.4223</v>
       </c>
       <c r="S131" s="1" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="T131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="T131" s="1" t="n">
+      <c r="U131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -8921,9 +9317,12 @@
         <v>0.04328</v>
       </c>
       <c r="S132" s="1" t="n">
+        <v>0.04314</v>
+      </c>
+      <c r="T132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="T132" s="1" t="n">
+      <c r="U132" s="1" t="n">
         <v>0.04309</v>
       </c>
     </row>
@@ -8985,9 +9384,12 @@
         <v>1.2805</v>
       </c>
       <c r="S133" s="1" t="n">
+        <v>1.2816</v>
+      </c>
+      <c r="T133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="T133" s="1" t="n">
+      <c r="U133" s="1" t="n">
         <v>1.2805</v>
       </c>
     </row>
@@ -9049,9 +9451,12 @@
         <v>0.02179</v>
       </c>
       <c r="S134" s="1" t="n">
+        <v>0.02192</v>
+      </c>
+      <c r="T134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="T134" s="1" t="n">
+      <c r="U134" s="1" t="n">
         <v>0.02178</v>
       </c>
     </row>
@@ -9113,9 +9518,12 @@
         <v>0.0004567</v>
       </c>
       <c r="S135" s="1" t="n">
+        <v>0.0004566</v>
+      </c>
+      <c r="T135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="T135" s="1" t="n">
+      <c r="U135" s="1" t="n">
         <v>0.0004561</v>
       </c>
     </row>
@@ -9177,9 +9585,12 @@
         <v>0.001899</v>
       </c>
       <c r="S136" s="1" t="n">
+        <v>0.001912</v>
+      </c>
+      <c r="T136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="T136" s="1" t="n">
+      <c r="U136" s="1" t="n">
         <v>0.001881</v>
       </c>
     </row>
@@ -9241,9 +9652,12 @@
         <v>0.314</v>
       </c>
       <c r="S137" s="1" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="T137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="T137" s="1" t="n">
+      <c r="U137" s="1" t="n">
         <v>0.3136</v>
       </c>
     </row>
@@ -9305,10 +9719,13 @@
         <v>0.5632</v>
       </c>
       <c r="S138" s="1" t="n">
+        <v>0.5599</v>
+      </c>
+      <c r="T138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="T138" s="1" t="n">
-        <v>0.5629999999999999</v>
+      <c r="U138" s="1" t="n">
+        <v>0.5599</v>
       </c>
     </row>
     <row r="139">
@@ -9369,9 +9786,12 @@
         <v>0.02132</v>
       </c>
       <c r="S139" s="1" t="n">
+        <v>0.02134</v>
+      </c>
+      <c r="T139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="T139" s="1" t="n">
+      <c r="U139" s="1" t="n">
         <v>0.02121</v>
       </c>
     </row>
@@ -9433,9 +9853,12 @@
         <v>0.0796</v>
       </c>
       <c r="S140" s="1" t="n">
+        <v>0.07972</v>
+      </c>
+      <c r="T140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="T140" s="1" t="n">
+      <c r="U140" s="1" t="n">
         <v>0.0796</v>
       </c>
     </row>
@@ -9497,9 +9920,12 @@
         <v>0.001516</v>
       </c>
       <c r="S141" s="1" t="n">
+        <v>0.001527</v>
+      </c>
+      <c r="T141" s="1" t="n">
         <v>0.001672</v>
       </c>
-      <c r="T141" s="1" t="n">
+      <c r="U141" s="1" t="n">
         <v>0.001502</v>
       </c>
     </row>
@@ -9561,9 +9987,12 @@
         <v>0.447</v>
       </c>
       <c r="S142" s="1" t="n">
-        <v>0.4489</v>
+        <v>0.4514</v>
       </c>
       <c r="T142" s="1" t="n">
+        <v>0.4514</v>
+      </c>
+      <c r="U142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -9625,10 +10054,13 @@
         <v>0.029994</v>
       </c>
       <c r="S143" s="1" t="n">
+        <v>0.029881</v>
+      </c>
+      <c r="T143" s="1" t="n">
         <v>0.031368</v>
       </c>
-      <c r="T143" s="1" t="n">
-        <v>0.029913</v>
+      <c r="U143" s="1" t="n">
+        <v>0.029881</v>
       </c>
     </row>
     <row r="144">
@@ -9689,9 +10121,12 @@
         <v>0.000226</v>
       </c>
       <c r="S144" s="1" t="n">
+        <v>0.000226</v>
+      </c>
+      <c r="T144" s="1" t="n">
         <v>0.000227</v>
       </c>
-      <c r="T144" s="1" t="n">
+      <c r="U144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -9753,9 +10188,12 @@
         <v>0.03541</v>
       </c>
       <c r="S145" s="1" t="n">
+        <v>0.03476</v>
+      </c>
+      <c r="T145" s="1" t="n">
         <v>0.03696</v>
       </c>
-      <c r="T145" s="1" t="n">
+      <c r="U145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -9817,9 +10255,12 @@
         <v>0.11631</v>
       </c>
       <c r="S146" s="1" t="n">
+        <v>0.11648</v>
+      </c>
+      <c r="T146" s="1" t="n">
         <v>0.11649</v>
       </c>
-      <c r="T146" s="1" t="n">
+      <c r="U146" s="1" t="n">
         <v>0.11505</v>
       </c>
     </row>
@@ -9881,9 +10322,12 @@
         <v>0.02231</v>
       </c>
       <c r="S147" s="1" t="n">
-        <v>0.02231</v>
+        <v>0.0224</v>
       </c>
       <c r="T147" s="1" t="n">
+        <v>0.0224</v>
+      </c>
+      <c r="U147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -9945,9 +10389,12 @@
         <v>1.4122</v>
       </c>
       <c r="S148" s="1" t="n">
+        <v>1.4151</v>
+      </c>
+      <c r="T148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="T148" s="1" t="n">
+      <c r="U148" s="1" t="n">
         <v>1.4084</v>
       </c>
     </row>
@@ -10009,9 +10456,12 @@
         <v>1.864</v>
       </c>
       <c r="S149" s="1" t="n">
+        <v>1.8735</v>
+      </c>
+      <c r="T149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="T149" s="1" t="n">
+      <c r="U149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -10073,9 +10523,12 @@
         <v>0.094</v>
       </c>
       <c r="S150" s="1" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="T150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="T150" s="1" t="n">
+      <c r="U150" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -10137,9 +10590,12 @@
         <v>4.653</v>
       </c>
       <c r="S151" s="1" t="n">
+        <v>4.652</v>
+      </c>
+      <c r="T151" s="1" t="n">
         <v>4.653</v>
       </c>
-      <c r="T151" s="1" t="n">
+      <c r="U151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -10201,9 +10657,12 @@
         <v>5.516</v>
       </c>
       <c r="S152" s="1" t="n">
+        <v>5.532</v>
+      </c>
+      <c r="T152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="T152" s="1" t="n">
+      <c r="U152" s="1" t="n">
         <v>5.511</v>
       </c>
     </row>
@@ -10265,9 +10724,12 @@
         <v>0.3175</v>
       </c>
       <c r="S153" s="1" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="T153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="T153" s="1" t="n">
+      <c r="U153" s="1" t="n">
         <v>0.3154</v>
       </c>
     </row>
@@ -10329,9 +10791,12 @@
         <v>0.583</v>
       </c>
       <c r="S154" s="1" t="n">
+        <v>0.5841</v>
+      </c>
+      <c r="T154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="T154" s="1" t="n">
+      <c r="U154" s="1" t="n">
         <v>0.5825</v>
       </c>
     </row>
@@ -10393,9 +10858,12 @@
         <v>0.01268</v>
       </c>
       <c r="S155" s="1" t="n">
+        <v>0.01273</v>
+      </c>
+      <c r="T155" s="1" t="n">
         <v>0.01299</v>
       </c>
-      <c r="T155" s="1" t="n">
+      <c r="U155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -10457,10 +10925,13 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="S156" s="1" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+      <c r="T156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="T156" s="1" t="n">
-        <v>0.0974</v>
+      <c r="U156" s="1" t="n">
+        <v>0.09710000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -10521,9 +10992,12 @@
         <v>16.409</v>
       </c>
       <c r="S157" s="1" t="n">
+        <v>16.412</v>
+      </c>
+      <c r="T157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="T157" s="1" t="n">
+      <c r="U157" s="1" t="n">
         <v>16.341</v>
       </c>
     </row>
@@ -10585,9 +11059,12 @@
         <v>0.05552</v>
       </c>
       <c r="S158" s="1" t="n">
+        <v>0.0556</v>
+      </c>
+      <c r="T158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="T158" s="1" t="n">
+      <c r="U158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -10649,9 +11126,12 @@
         <v>28.71</v>
       </c>
       <c r="S159" s="1" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="T159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="T159" s="1" t="n">
+      <c r="U159" s="1" t="n">
         <v>28.65</v>
       </c>
     </row>
@@ -10713,9 +11193,12 @@
         <v>0.02123</v>
       </c>
       <c r="S160" s="1" t="n">
+        <v>0.02135</v>
+      </c>
+      <c r="T160" s="1" t="n">
         <v>0.02141</v>
       </c>
-      <c r="T160" s="1" t="n">
+      <c r="U160" s="1" t="n">
         <v>0.02087</v>
       </c>
     </row>
@@ -10777,9 +11260,12 @@
         <v>0.0006511000000000001</v>
       </c>
       <c r="S161" s="1" t="n">
+        <v>0.0006521</v>
+      </c>
+      <c r="T161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="T161" s="1" t="n">
+      <c r="U161" s="1" t="n">
         <v>0.0006503</v>
       </c>
     </row>
@@ -10841,9 +11327,12 @@
         <v>0.3806</v>
       </c>
       <c r="S162" s="1" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="T162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="T162" s="1" t="n">
+      <c r="U162" s="1" t="n">
         <v>0.3785</v>
       </c>
     </row>
@@ -10905,9 +11394,12 @@
         <v>0.1911</v>
       </c>
       <c r="S163" s="1" t="n">
+        <v>0.1915</v>
+      </c>
+      <c r="T163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="T163" s="1" t="n">
+      <c r="U163" s="1" t="n">
         <v>0.1908</v>
       </c>
     </row>
@@ -10969,9 +11461,12 @@
         <v>0.315</v>
       </c>
       <c r="S164" s="1" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="T164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="T164" s="1" t="n">
+      <c r="U164" s="1" t="n">
         <v>0.315</v>
       </c>
     </row>
@@ -11033,9 +11528,12 @@
         <v>0.374</v>
       </c>
       <c r="S165" s="1" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="T165" s="1" t="n">
         <v>0.377</v>
       </c>
-      <c r="T165" s="1" t="n">
+      <c r="U165" s="1" t="n">
         <v>0.371</v>
       </c>
     </row>
@@ -11097,9 +11595,12 @@
         <v>0.02238</v>
       </c>
       <c r="S166" s="1" t="n">
+        <v>0.02253</v>
+      </c>
+      <c r="T166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="T166" s="1" t="n">
+      <c r="U166" s="1" t="n">
         <v>0.02233</v>
       </c>
     </row>
@@ -11161,9 +11662,12 @@
         <v>0.007267</v>
       </c>
       <c r="S167" s="1" t="n">
+        <v>0.00727</v>
+      </c>
+      <c r="T167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="T167" s="1" t="n">
+      <c r="U167" s="1" t="n">
         <v>0.007256</v>
       </c>
     </row>
@@ -11225,9 +11729,12 @@
         <v>0.01332</v>
       </c>
       <c r="S168" s="1" t="n">
+        <v>0.01338</v>
+      </c>
+      <c r="T168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="T168" s="1" t="n">
+      <c r="U168" s="1" t="n">
         <v>0.01332</v>
       </c>
     </row>
@@ -11289,9 +11796,12 @@
         <v>0.25398</v>
       </c>
       <c r="S169" s="1" t="n">
+        <v>0.25504</v>
+      </c>
+      <c r="T169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="T169" s="1" t="n">
+      <c r="U169" s="1" t="n">
         <v>0.25151</v>
       </c>
     </row>
@@ -11353,9 +11863,12 @@
         <v>0.02159</v>
       </c>
       <c r="S170" s="1" t="n">
+        <v>0.02178</v>
+      </c>
+      <c r="T170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="T170" s="1" t="n">
+      <c r="U170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -11417,9 +11930,12 @@
         <v>0.1714</v>
       </c>
       <c r="S171" s="1" t="n">
+        <v>0.1724</v>
+      </c>
+      <c r="T171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="T171" s="1" t="n">
+      <c r="U171" s="1" t="n">
         <v>0.171</v>
       </c>
     </row>
@@ -11481,9 +11997,12 @@
         <v>0.089</v>
       </c>
       <c r="S172" s="1" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="T172" s="1" t="n">
         <v>0.09</v>
       </c>
-      <c r="T172" s="1" t="n">
+      <c r="U172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -11545,9 +12064,12 @@
         <v>0.00467</v>
       </c>
       <c r="S173" s="1" t="n">
+        <v>0.004674</v>
+      </c>
+      <c r="T173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="T173" s="1" t="n">
+      <c r="U173" s="1" t="n">
         <v>0.004662</v>
       </c>
     </row>
@@ -11609,9 +12131,12 @@
         <v>0.4361</v>
       </c>
       <c r="S174" s="1" t="n">
+        <v>0.4374</v>
+      </c>
+      <c r="T174" s="1" t="n">
         <v>0.4423</v>
       </c>
-      <c r="T174" s="1" t="n">
+      <c r="U174" s="1" t="n">
         <v>0.4343</v>
       </c>
     </row>
@@ -11673,9 +12198,12 @@
         <v>0.09013</v>
       </c>
       <c r="S175" s="1" t="n">
-        <v>0.09042</v>
+        <v>0.09057</v>
       </c>
       <c r="T175" s="1" t="n">
+        <v>0.09057</v>
+      </c>
+      <c r="U175" s="1" t="n">
         <v>0.08935999999999999</v>
       </c>
     </row>
@@ -11737,9 +12265,12 @@
         <v>0.2458</v>
       </c>
       <c r="S176" s="1" t="n">
+        <v>0.2459</v>
+      </c>
+      <c r="T176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="T176" s="1" t="n">
+      <c r="U176" s="1" t="n">
         <v>0.2453</v>
       </c>
     </row>
@@ -11801,9 +12332,12 @@
         <v>0.01909</v>
       </c>
       <c r="S177" s="1" t="n">
+        <v>0.01916</v>
+      </c>
+      <c r="T177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="T177" s="1" t="n">
+      <c r="U177" s="1" t="n">
         <v>0.01908</v>
       </c>
     </row>
@@ -11865,9 +12399,12 @@
         <v>6.114</v>
       </c>
       <c r="S178" s="1" t="n">
+        <v>6.115</v>
+      </c>
+      <c r="T178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="T178" s="1" t="n">
+      <c r="U178" s="1" t="n">
         <v>6.108</v>
       </c>
     </row>
@@ -11929,9 +12466,12 @@
         <v>0.1379</v>
       </c>
       <c r="S179" s="1" t="n">
+        <v>0.1378</v>
+      </c>
+      <c r="T179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="T179" s="1" t="n">
+      <c r="U179" s="1" t="n">
         <v>0.1349</v>
       </c>
     </row>
@@ -11993,9 +12533,12 @@
         <v>0.004989</v>
       </c>
       <c r="S180" s="1" t="n">
+        <v>0.005008</v>
+      </c>
+      <c r="T180" s="1" t="n">
         <v>0.005154</v>
       </c>
-      <c r="T180" s="1" t="n">
+      <c r="U180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -12057,9 +12600,12 @@
         <v>0.01192</v>
       </c>
       <c r="S181" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="T181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="T181" s="1" t="n">
+      <c r="U181" s="1" t="n">
         <v>0.01182</v>
       </c>
     </row>
@@ -12121,9 +12667,12 @@
         <v>0.007376</v>
       </c>
       <c r="S182" s="1" t="n">
+        <v>0.007374</v>
+      </c>
+      <c r="T182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="T182" s="1" t="n">
+      <c r="U182" s="1" t="n">
         <v>0.007224</v>
       </c>
     </row>
@@ -12185,9 +12734,12 @@
         <v>0.13039</v>
       </c>
       <c r="S183" s="1" t="n">
+        <v>0.13128</v>
+      </c>
+      <c r="T183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="T183" s="1" t="n">
+      <c r="U183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -12249,9 +12801,12 @@
         <v>0.09585</v>
       </c>
       <c r="S184" s="1" t="n">
+        <v>0.09593</v>
+      </c>
+      <c r="T184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="T184" s="1" t="n">
+      <c r="U184" s="1" t="n">
         <v>0.09513000000000001</v>
       </c>
     </row>
@@ -12313,9 +12868,12 @@
         <v>0.00751</v>
       </c>
       <c r="S185" s="1" t="n">
+        <v>0.00752</v>
+      </c>
+      <c r="T185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="T185" s="1" t="n">
+      <c r="U185" s="1" t="n">
         <v>0.0075</v>
       </c>
     </row>
@@ -12377,9 +12935,12 @@
         <v>0.04864</v>
       </c>
       <c r="S186" s="1" t="n">
+        <v>0.0486</v>
+      </c>
+      <c r="T186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="T186" s="1" t="n">
+      <c r="U186" s="1" t="n">
         <v>0.04851</v>
       </c>
     </row>
@@ -12441,9 +13002,12 @@
         <v>0.02673</v>
       </c>
       <c r="S187" s="1" t="n">
+        <v>0.02687</v>
+      </c>
+      <c r="T187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="T187" s="1" t="n">
+      <c r="U187" s="1" t="n">
         <v>0.02652</v>
       </c>
     </row>
@@ -12505,9 +13069,12 @@
         <v>0.003283</v>
       </c>
       <c r="S188" s="1" t="n">
+        <v>0.003285</v>
+      </c>
+      <c r="T188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="T188" s="1" t="n">
+      <c r="U188" s="1" t="n">
         <v>0.003282</v>
       </c>
     </row>
@@ -12569,9 +13136,12 @@
         <v>0.285</v>
       </c>
       <c r="S189" s="1" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="T189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="T189" s="1" t="n">
+      <c r="U189" s="1" t="n">
         <v>0.2847</v>
       </c>
     </row>
@@ -12633,9 +13203,12 @@
         <v>0.01783</v>
       </c>
       <c r="S190" s="1" t="n">
+        <v>0.01784</v>
+      </c>
+      <c r="T190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="T190" s="1" t="n">
+      <c r="U190" s="1" t="n">
         <v>0.01783</v>
       </c>
     </row>
@@ -12697,9 +13270,12 @@
         <v>0.2564</v>
       </c>
       <c r="S191" s="1" t="n">
+        <v>0.2565</v>
+      </c>
+      <c r="T191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="T191" s="1" t="n">
+      <c r="U191" s="1" t="n">
         <v>0.2562</v>
       </c>
     </row>
@@ -12761,9 +13337,12 @@
         <v>0.0381</v>
       </c>
       <c r="S192" s="1" t="n">
+        <v>0.03821</v>
+      </c>
+      <c r="T192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="T192" s="1" t="n">
+      <c r="U192" s="1" t="n">
         <v>0.03766</v>
       </c>
     </row>
@@ -12825,9 +13404,12 @@
         <v>0.0002207</v>
       </c>
       <c r="S193" s="1" t="n">
+        <v>0.0002219</v>
+      </c>
+      <c r="T193" s="1" t="n">
         <v>0.0002243</v>
       </c>
-      <c r="T193" s="1" t="n">
+      <c r="U193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -12889,9 +13471,12 @@
         <v>4.081</v>
       </c>
       <c r="S194" s="1" t="n">
+        <v>4.085</v>
+      </c>
+      <c r="T194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="T194" s="1" t="n">
+      <c r="U194" s="1" t="n">
         <v>4.056</v>
       </c>
     </row>
@@ -12953,9 +13538,12 @@
         <v>0.9994</v>
       </c>
       <c r="S195" s="1" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="T195" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="T195" s="1" t="n">
+      <c r="U195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -13017,9 +13605,12 @@
         <v>4.3</v>
       </c>
       <c r="S196" s="1" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="T196" s="1" t="n">
         <v>4.347</v>
       </c>
-      <c r="T196" s="1" t="n">
+      <c r="U196" s="1" t="n">
         <v>4.276</v>
       </c>
     </row>
@@ -13081,9 +13672,12 @@
         <v>0.15078</v>
       </c>
       <c r="S197" s="1" t="n">
+        <v>0.15121</v>
+      </c>
+      <c r="T197" s="1" t="n">
         <v>0.15232</v>
       </c>
-      <c r="T197" s="1" t="n">
+      <c r="U197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -13145,9 +13739,12 @@
         <v>0.0077</v>
       </c>
       <c r="S198" s="1" t="n">
+        <v>0.007718</v>
+      </c>
+      <c r="T198" s="1" t="n">
         <v>0.007899</v>
       </c>
-      <c r="T198" s="1" t="n">
+      <c r="U198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -13209,9 +13806,12 @@
         <v>0.4491</v>
       </c>
       <c r="S199" s="1" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="T199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="T199" s="1" t="n">
+      <c r="U199" s="1" t="n">
         <v>0.4482</v>
       </c>
     </row>
@@ -13273,9 +13873,12 @@
         <v>0.5851</v>
       </c>
       <c r="S200" s="1" t="n">
-        <v>0.5911999999999999</v>
+        <v>0.5923</v>
       </c>
       <c r="T200" s="1" t="n">
+        <v>0.5923</v>
+      </c>
+      <c r="U200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -13337,9 +13940,12 @@
         <v>0.0926</v>
       </c>
       <c r="S201" s="1" t="n">
+        <v>0.0927</v>
+      </c>
+      <c r="T201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="T201" s="1" t="n">
+      <c r="U201" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -13401,9 +14007,12 @@
         <v>0.06008</v>
       </c>
       <c r="S202" s="1" t="n">
+        <v>0.0603</v>
+      </c>
+      <c r="T202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="T202" s="1" t="n">
+      <c r="U202" s="1" t="n">
         <v>0.05994</v>
       </c>
     </row>
@@ -13465,9 +14074,12 @@
         <v>0.008240000000000001</v>
       </c>
       <c r="S203" s="1" t="n">
+        <v>0.00826</v>
+      </c>
+      <c r="T203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="T203" s="1" t="n">
+      <c r="U203" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -13529,9 +14141,12 @@
         <v>0.00413</v>
       </c>
       <c r="S204" s="1" t="n">
+        <v>0.00412</v>
+      </c>
+      <c r="T204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="T204" s="1" t="n">
+      <c r="U204" s="1" t="n">
         <v>0.00412</v>
       </c>
     </row>
@@ -13593,10 +14208,13 @@
         <v>0.009122</v>
       </c>
       <c r="S205" s="1" t="n">
+        <v>0.009068</v>
+      </c>
+      <c r="T205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="T205" s="1" t="n">
-        <v>0.009070999999999999</v>
+      <c r="U205" s="1" t="n">
+        <v>0.009068</v>
       </c>
     </row>
     <row r="206">
@@ -13657,9 +14275,12 @@
         <v>0.237</v>
       </c>
       <c r="S206" s="1" t="n">
+        <v>0.2371</v>
+      </c>
+      <c r="T206" s="1" t="n">
         <v>0.2418</v>
       </c>
-      <c r="T206" s="1" t="n">
+      <c r="U206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -13721,9 +14342,12 @@
         <v>0.02066</v>
       </c>
       <c r="S207" s="1" t="n">
+        <v>0.02106</v>
+      </c>
+      <c r="T207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="T207" s="1" t="n">
+      <c r="U207" s="1" t="n">
         <v>0.02052</v>
       </c>
     </row>
@@ -13785,9 +14409,12 @@
         <v>0.236</v>
       </c>
       <c r="S208" s="1" t="n">
+        <v>0.2369</v>
+      </c>
+      <c r="T208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="T208" s="1" t="n">
+      <c r="U208" s="1" t="n">
         <v>0.2357</v>
       </c>
     </row>
@@ -13849,9 +14476,12 @@
         <v>0.3589</v>
       </c>
       <c r="S209" s="1" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="T209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="T209" s="1" t="n">
+      <c r="U209" s="1" t="n">
         <v>0.3584</v>
       </c>
     </row>
@@ -13913,9 +14543,12 @@
         <v>0.04254</v>
       </c>
       <c r="S210" s="1" t="n">
+        <v>0.04272</v>
+      </c>
+      <c r="T210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="T210" s="1" t="n">
+      <c r="U210" s="1" t="n">
         <v>0.04232</v>
       </c>
     </row>
@@ -13977,9 +14610,12 @@
         <v>0.0004241</v>
       </c>
       <c r="S211" s="1" t="n">
+        <v>0.0004246</v>
+      </c>
+      <c r="T211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="T211" s="1" t="n">
+      <c r="U211" s="1" t="n">
         <v>0.0004237</v>
       </c>
     </row>
@@ -14041,9 +14677,12 @@
         <v>0.02125</v>
       </c>
       <c r="S212" s="1" t="n">
+        <v>0.02127</v>
+      </c>
+      <c r="T212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="T212" s="1" t="n">
+      <c r="U212" s="1" t="n">
         <v>0.02125</v>
       </c>
     </row>
@@ -14105,9 +14744,12 @@
         <v>0.1138</v>
       </c>
       <c r="S213" s="1" t="n">
+        <v>0.1136</v>
+      </c>
+      <c r="T213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="T213" s="1" t="n">
+      <c r="U213" s="1" t="n">
         <v>0.1135</v>
       </c>
     </row>
@@ -14169,9 +14811,12 @@
         <v>0.04186</v>
       </c>
       <c r="S214" s="1" t="n">
+        <v>0.04197</v>
+      </c>
+      <c r="T214" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="T214" s="1" t="n">
+      <c r="U214" s="1" t="n">
         <v>0.04173</v>
       </c>
     </row>
@@ -14233,9 +14878,12 @@
         <v>0.009846000000000001</v>
       </c>
       <c r="S215" s="1" t="n">
+        <v>0.009868999999999999</v>
+      </c>
+      <c r="T215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="T215" s="1" t="n">
+      <c r="U215" s="1" t="n">
         <v>0.009839000000000001</v>
       </c>
     </row>
@@ -14297,9 +14945,12 @@
         <v>0.0636</v>
       </c>
       <c r="S216" s="1" t="n">
+        <v>0.06370000000000001</v>
+      </c>
+      <c r="T216" s="1" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="T216" s="1" t="n">
+      <c r="U216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -14361,9 +15012,12 @@
         <v>0.004287</v>
       </c>
       <c r="S217" s="1" t="n">
+        <v>0.004249</v>
+      </c>
+      <c r="T217" s="1" t="n">
         <v>0.004287</v>
       </c>
-      <c r="T217" s="1" t="n">
+      <c r="U217" s="1" t="n">
         <v>0.004177</v>
       </c>
     </row>
@@ -14425,9 +15079,12 @@
         <v>0.01</v>
       </c>
       <c r="S218" s="1" t="n">
+        <v>0.00997</v>
+      </c>
+      <c r="T218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="T218" s="1" t="n">
+      <c r="U218" s="1" t="n">
         <v>0.009820000000000001</v>
       </c>
     </row>
@@ -14489,9 +15146,12 @@
         <v>0.02954</v>
       </c>
       <c r="S219" s="1" t="n">
+        <v>0.02947</v>
+      </c>
+      <c r="T219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="T219" s="1" t="n">
+      <c r="U219" s="1" t="n">
         <v>0.02941</v>
       </c>
     </row>
@@ -14553,9 +15213,12 @@
         <v>2.283</v>
       </c>
       <c r="S220" s="1" t="n">
+        <v>2.289</v>
+      </c>
+      <c r="T220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="T220" s="1" t="n">
+      <c r="U220" s="1" t="n">
         <v>2.281</v>
       </c>
     </row>
@@ -14617,9 +15280,12 @@
         <v>0.022618</v>
       </c>
       <c r="S221" s="1" t="n">
+        <v>0.022748</v>
+      </c>
+      <c r="T221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="T221" s="1" t="n">
+      <c r="U221" s="1" t="n">
         <v>0.022529</v>
       </c>
     </row>
@@ -14681,9 +15347,12 @@
         <v>0.0368</v>
       </c>
       <c r="S222" s="1" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="T222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="T222" s="1" t="n">
+      <c r="U222" s="1" t="n">
         <v>0.0368</v>
       </c>
     </row>
@@ -14745,9 +15414,12 @@
         <v>0.293</v>
       </c>
       <c r="S223" s="1" t="n">
+        <v>0.2933</v>
+      </c>
+      <c r="T223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="T223" s="1" t="n">
+      <c r="U223" s="1" t="n">
         <v>0.2915</v>
       </c>
     </row>
@@ -14809,9 +15481,12 @@
         <v>0.01548</v>
       </c>
       <c r="S224" s="1" t="n">
+        <v>0.01553</v>
+      </c>
+      <c r="T224" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="T224" s="1" t="n">
+      <c r="U224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -14873,9 +15548,12 @@
         <v>0.0004035</v>
       </c>
       <c r="S225" s="1" t="n">
+        <v>0.0004035</v>
+      </c>
+      <c r="T225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="T225" s="1" t="n">
+      <c r="U225" s="1" t="n">
         <v>0.0004032</v>
       </c>
     </row>
@@ -14937,9 +15615,12 @@
         <v>0.08535</v>
       </c>
       <c r="S226" s="1" t="n">
+        <v>0.08556</v>
+      </c>
+      <c r="T226" s="1" t="n">
         <v>0.08815000000000001</v>
       </c>
-      <c r="T226" s="1" t="n">
+      <c r="U226" s="1" t="n">
         <v>0.08522</v>
       </c>
     </row>
@@ -15001,9 +15682,12 @@
         <v>0.947</v>
       </c>
       <c r="S227" s="1" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="T227" s="1" t="n">
         <v>0.959</v>
       </c>
-      <c r="T227" s="1" t="n">
+      <c r="U227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -15065,9 +15749,12 @@
         <v>0.05463</v>
       </c>
       <c r="S228" s="1" t="n">
+        <v>0.05524</v>
+      </c>
+      <c r="T228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="T228" s="1" t="n">
+      <c r="U228" s="1" t="n">
         <v>0.05439</v>
       </c>
     </row>
@@ -15129,9 +15816,12 @@
         <v>0.002003</v>
       </c>
       <c r="S229" s="1" t="n">
+        <v>0.002013</v>
+      </c>
+      <c r="T229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="T229" s="1" t="n">
+      <c r="U229" s="1" t="n">
         <v>0.001997</v>
       </c>
     </row>
@@ -15193,9 +15883,12 @@
         <v>0.02281</v>
       </c>
       <c r="S230" s="1" t="n">
+        <v>0.02287</v>
+      </c>
+      <c r="T230" s="1" t="n">
         <v>0.023101</v>
       </c>
-      <c r="T230" s="1" t="n">
+      <c r="U230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -15257,9 +15950,12 @@
         <v>0.05348</v>
       </c>
       <c r="S231" s="1" t="n">
+        <v>0.05351</v>
+      </c>
+      <c r="T231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="T231" s="1" t="n">
+      <c r="U231" s="1" t="n">
         <v>0.05338</v>
       </c>
     </row>
@@ -15321,9 +16017,12 @@
         <v>0.0584</v>
       </c>
       <c r="S232" s="1" t="n">
+        <v>0.0585</v>
+      </c>
+      <c r="T232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="T232" s="1" t="n">
+      <c r="U232" s="1" t="n">
         <v>0.0583</v>
       </c>
     </row>
@@ -15385,9 +16084,12 @@
         <v>0.001686</v>
       </c>
       <c r="S233" s="1" t="n">
+        <v>0.001695</v>
+      </c>
+      <c r="T233" s="1" t="n">
         <v>0.001701</v>
       </c>
-      <c r="T233" s="1" t="n">
+      <c r="U233" s="1" t="n">
         <v>0.001676</v>
       </c>
     </row>
@@ -15449,9 +16151,12 @@
         <v>0.005737</v>
       </c>
       <c r="S234" s="1" t="n">
+        <v>0.005735</v>
+      </c>
+      <c r="T234" s="1" t="n">
         <v>0.005854</v>
       </c>
-      <c r="T234" s="1" t="n">
+      <c r="U234" s="1" t="n">
         <v>0.005728</v>
       </c>
     </row>
@@ -15513,9 +16218,12 @@
         <v>0.12265</v>
       </c>
       <c r="S235" s="1" t="n">
+        <v>0.12304</v>
+      </c>
+      <c r="T235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="T235" s="1" t="n">
+      <c r="U235" s="1" t="n">
         <v>0.12245</v>
       </c>
     </row>
@@ -15577,9 +16285,12 @@
         <v>64.58</v>
       </c>
       <c r="S236" s="1" t="n">
+        <v>64.87</v>
+      </c>
+      <c r="T236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="T236" s="1" t="n">
+      <c r="U236" s="1" t="n">
         <v>64.25</v>
       </c>
     </row>
@@ -15641,9 +16352,12 @@
         <v>0.1009</v>
       </c>
       <c r="S237" s="1" t="n">
+        <v>0.1014</v>
+      </c>
+      <c r="T237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="T237" s="1" t="n">
+      <c r="U237" s="1" t="n">
         <v>0.1008</v>
       </c>
     </row>
@@ -15705,9 +16419,12 @@
         <v>0.004011</v>
       </c>
       <c r="S238" s="1" t="n">
+        <v>0.004024</v>
+      </c>
+      <c r="T238" s="1" t="n">
         <v>0.004066</v>
       </c>
-      <c r="T238" s="1" t="n">
+      <c r="U238" s="1" t="n">
         <v>0.003925</v>
       </c>
     </row>
@@ -15769,9 +16486,12 @@
         <v>0.01492</v>
       </c>
       <c r="S239" s="1" t="n">
+        <v>0.01505</v>
+      </c>
+      <c r="T239" s="1" t="n">
         <v>0.01562</v>
       </c>
-      <c r="T239" s="1" t="n">
+      <c r="U239" s="1" t="n">
         <v>0.01492</v>
       </c>
     </row>
@@ -15833,9 +16553,12 @@
         <v>0.05586</v>
       </c>
       <c r="S240" s="1" t="n">
+        <v>0.05594</v>
+      </c>
+      <c r="T240" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="T240" s="1" t="n">
+      <c r="U240" s="1" t="n">
         <v>0.05575</v>
       </c>
     </row>
@@ -15897,9 +16620,12 @@
         <v>0.0113</v>
       </c>
       <c r="S241" s="1" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="T241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="T241" s="1" t="n">
+      <c r="U241" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -15961,9 +16687,12 @@
         <v>0.3321</v>
       </c>
       <c r="S242" s="1" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="T242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="T242" s="1" t="n">
+      <c r="U242" s="1" t="n">
         <v>0.3321</v>
       </c>
     </row>
@@ -16025,9 +16754,12 @@
         <v>0.01229</v>
       </c>
       <c r="S243" s="1" t="n">
+        <v>0.01232</v>
+      </c>
+      <c r="T243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="T243" s="1" t="n">
+      <c r="U243" s="1" t="n">
         <v>0.01222</v>
       </c>
     </row>
@@ -16089,9 +16821,12 @@
         <v>0.08006000000000001</v>
       </c>
       <c r="S244" s="1" t="n">
+        <v>0.08069</v>
+      </c>
+      <c r="T244" s="1" t="n">
         <v>0.08121</v>
       </c>
-      <c r="T244" s="1" t="n">
+      <c r="U244" s="1" t="n">
         <v>0.07973</v>
       </c>
     </row>
@@ -16153,9 +16888,12 @@
         <v>0.007861</v>
       </c>
       <c r="S245" s="1" t="n">
+        <v>0.007854</v>
+      </c>
+      <c r="T245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="T245" s="1" t="n">
+      <c r="U245" s="1" t="n">
         <v>0.007769</v>
       </c>
     </row>
@@ -16217,9 +16955,12 @@
         <v>0.03024</v>
       </c>
       <c r="S246" s="1" t="n">
+        <v>0.03025</v>
+      </c>
+      <c r="T246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="T246" s="1" t="n">
+      <c r="U246" s="1" t="n">
         <v>0.0302</v>
       </c>
     </row>
@@ -16281,9 +17022,12 @@
         <v>0.18</v>
       </c>
       <c r="S247" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="T247" s="1" t="n">
         <v>0.1827</v>
       </c>
-      <c r="T247" s="1" t="n">
+      <c r="U247" s="1" t="n">
         <v>0.1796</v>
       </c>
     </row>
@@ -16345,9 +17089,12 @@
         <v>0.05873</v>
       </c>
       <c r="S248" s="1" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="T248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="T248" s="1" t="n">
+      <c r="U248" s="1" t="n">
         <v>0.05856</v>
       </c>
     </row>
@@ -16409,9 +17156,12 @@
         <v>0.1659</v>
       </c>
       <c r="S249" s="1" t="n">
+        <v>0.1659</v>
+      </c>
+      <c r="T249" s="1" t="n">
         <v>0.1684</v>
       </c>
-      <c r="T249" s="1" t="n">
+      <c r="U249" s="1" t="n">
         <v>0.1656</v>
       </c>
     </row>
@@ -16473,9 +17223,12 @@
         <v>0.01903</v>
       </c>
       <c r="S250" s="1" t="n">
+        <v>0.01901</v>
+      </c>
+      <c r="T250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="T250" s="1" t="n">
+      <c r="U250" s="1" t="n">
         <v>0.01898</v>
       </c>
     </row>
@@ -16537,9 +17290,12 @@
         <v>0.02298</v>
       </c>
       <c r="S251" s="1" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="T251" s="1" t="n">
         <v>0.02322</v>
       </c>
-      <c r="T251" s="1" t="n">
+      <c r="U251" s="1" t="n">
         <v>0.02295</v>
       </c>
     </row>
@@ -16601,9 +17357,12 @@
         <v>0.3058</v>
       </c>
       <c r="S252" s="1" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="T252" s="1" t="n">
         <v>0.31227</v>
       </c>
-      <c r="T252" s="1" t="n">
+      <c r="U252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -16665,9 +17424,12 @@
         <v>0.00598</v>
       </c>
       <c r="S253" s="1" t="n">
+        <v>0.00599</v>
+      </c>
+      <c r="T253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="T253" s="1" t="n">
+      <c r="U253" s="1" t="n">
         <v>0.005956</v>
       </c>
     </row>
@@ -16729,9 +17491,12 @@
         <v>0.6125</v>
       </c>
       <c r="S254" s="1" t="n">
+        <v>0.6125</v>
+      </c>
+      <c r="T254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="T254" s="1" t="n">
+      <c r="U254" s="1" t="n">
         <v>0.6116</v>
       </c>
     </row>
@@ -16793,10 +17558,13 @@
         <v>0.10579</v>
       </c>
       <c r="S255" s="1" t="n">
+        <v>0.10569</v>
+      </c>
+      <c r="T255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="T255" s="1" t="n">
-        <v>0.10579</v>
+      <c r="U255" s="1" t="n">
+        <v>0.10569</v>
       </c>
     </row>
     <row r="256">
@@ -16857,10 +17625,13 @@
         <v>0.09</v>
       </c>
       <c r="S256" s="1" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="T256" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="T256" s="1" t="n">
-        <v>0.08989999999999999</v>
+      <c r="U256" s="1" t="n">
+        <v>0.0898</v>
       </c>
     </row>
     <row r="257">
@@ -16921,9 +17692,12 @@
         <v>0.01448</v>
       </c>
       <c r="S257" s="1" t="n">
-        <v>0.01468</v>
+        <v>0.0147</v>
       </c>
       <c r="T257" s="1" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="U257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -16985,9 +17759,12 @@
         <v>0.04998</v>
       </c>
       <c r="S258" s="1" t="n">
+        <v>0.04993</v>
+      </c>
+      <c r="T258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="T258" s="1" t="n">
+      <c r="U258" s="1" t="n">
         <v>0.04965</v>
       </c>
     </row>
@@ -17049,9 +17826,12 @@
         <v>0.008059999999999999</v>
       </c>
       <c r="S259" s="1" t="n">
+        <v>0.008059999999999999</v>
+      </c>
+      <c r="T259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="T259" s="1" t="n">
+      <c r="U259" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -17113,9 +17893,12 @@
         <v>0.1894</v>
       </c>
       <c r="S260" s="1" t="n">
+        <v>0.1898</v>
+      </c>
+      <c r="T260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="T260" s="1" t="n">
+      <c r="U260" s="1" t="n">
         <v>0.1892</v>
       </c>
     </row>
@@ -17177,9 +17960,12 @@
         <v>0.0978</v>
       </c>
       <c r="S261" s="1" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="T261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="T261" s="1" t="n">
+      <c r="U261" s="1" t="n">
         <v>0.09760000000000001</v>
       </c>
     </row>
@@ -17241,9 +18027,12 @@
         <v>0.2107</v>
       </c>
       <c r="S262" s="1" t="n">
+        <v>0.2107</v>
+      </c>
+      <c r="T262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="T262" s="1" t="n">
+      <c r="U262" s="1" t="n">
         <v>0.2103</v>
       </c>
     </row>
@@ -17305,9 +18094,12 @@
         <v>0.008499</v>
       </c>
       <c r="S263" s="1" t="n">
+        <v>0.008479</v>
+      </c>
+      <c r="T263" s="1" t="n">
         <v>0.008560999999999999</v>
       </c>
-      <c r="T263" s="1" t="n">
+      <c r="U263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -17369,9 +18161,12 @@
         <v>2.632</v>
       </c>
       <c r="S264" s="1" t="n">
+        <v>2.633</v>
+      </c>
+      <c r="T264" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="T264" s="1" t="n">
+      <c r="U264" s="1" t="n">
         <v>2.629</v>
       </c>
     </row>
@@ -17433,9 +18228,12 @@
         <v>0.01867</v>
       </c>
       <c r="S265" s="1" t="n">
+        <v>0.01863</v>
+      </c>
+      <c r="T265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="T265" s="1" t="n">
+      <c r="U265" s="1" t="n">
         <v>0.01847</v>
       </c>
     </row>
@@ -17497,9 +18295,12 @@
         <v>0.3596</v>
       </c>
       <c r="S266" s="1" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T266" s="1" t="n">
         <v>0.3612</v>
       </c>
-      <c r="T266" s="1" t="n">
+      <c r="U266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -17561,9 +18362,12 @@
         <v>0.03441</v>
       </c>
       <c r="S267" s="1" t="n">
+        <v>0.03442</v>
+      </c>
+      <c r="T267" s="1" t="n">
         <v>0.03464</v>
       </c>
-      <c r="T267" s="1" t="n">
+      <c r="U267" s="1" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -17625,9 +18429,12 @@
         <v>0.119</v>
       </c>
       <c r="S268" s="1" t="n">
-        <v>0.121</v>
+        <v>0.123</v>
       </c>
       <c r="T268" s="1" t="n">
+        <v>0.123</v>
+      </c>
+      <c r="U268" s="1" t="n">
         <v>0.117</v>
       </c>
     </row>
@@ -17689,10 +18496,13 @@
         <v>0.07937</v>
       </c>
       <c r="S269" s="1" t="n">
+        <v>0.07933</v>
+      </c>
+      <c r="T269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="T269" s="1" t="n">
-        <v>0.07937</v>
+      <c r="U269" s="1" t="n">
+        <v>0.07933</v>
       </c>
     </row>
     <row r="270">
@@ -17753,9 +18563,12 @@
         <v>0.01375</v>
       </c>
       <c r="S270" s="1" t="n">
+        <v>0.01377</v>
+      </c>
+      <c r="T270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="T270" s="1" t="n">
+      <c r="U270" s="1" t="n">
         <v>0.01374</v>
       </c>
     </row>
@@ -17817,9 +18630,12 @@
         <v>0.007508</v>
       </c>
       <c r="S271" s="1" t="n">
+        <v>0.007512</v>
+      </c>
+      <c r="T271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="T271" s="1" t="n">
+      <c r="U271" s="1" t="n">
         <v>0.007504</v>
       </c>
     </row>
@@ -17881,9 +18697,12 @@
         <v>0.07417</v>
       </c>
       <c r="S272" s="1" t="n">
+        <v>0.07428999999999999</v>
+      </c>
+      <c r="T272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="T272" s="1" t="n">
+      <c r="U272" s="1" t="n">
         <v>0.07396</v>
       </c>
     </row>
@@ -17945,9 +18764,12 @@
         <v>3.14e-05</v>
       </c>
       <c r="S273" s="1" t="n">
+        <v>3.15e-05</v>
+      </c>
+      <c r="T273" s="1" t="n">
         <v>3.16e-05</v>
       </c>
-      <c r="T273" s="1" t="n">
+      <c r="U273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -18009,9 +18831,12 @@
         <v>0.005422</v>
       </c>
       <c r="S274" s="1" t="n">
+        <v>0.005445</v>
+      </c>
+      <c r="T274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="T274" s="1" t="n">
+      <c r="U274" s="1" t="n">
         <v>0.005409</v>
       </c>
     </row>
@@ -18073,9 +18898,12 @@
         <v>0.1791</v>
       </c>
       <c r="S275" s="1" t="n">
+        <v>0.1788</v>
+      </c>
+      <c r="T275" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="T275" s="1" t="n">
+      <c r="U275" s="1" t="n">
         <v>0.1784</v>
       </c>
     </row>
@@ -18137,9 +18965,12 @@
         <v>0.00682</v>
       </c>
       <c r="S276" s="1" t="n">
+        <v>0.006819</v>
+      </c>
+      <c r="T276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="T276" s="1" t="n">
+      <c r="U276" s="1" t="n">
         <v>0.006809</v>
       </c>
     </row>
@@ -18201,9 +19032,12 @@
         <v>0.1302</v>
       </c>
       <c r="S277" s="1" t="n">
+        <v>0.1309</v>
+      </c>
+      <c r="T277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="T277" s="1" t="n">
+      <c r="U277" s="1" t="n">
         <v>0.1302</v>
       </c>
     </row>
@@ -18265,9 +19099,12 @@
         <v>0.02315</v>
       </c>
       <c r="S278" s="1" t="n">
+        <v>0.02319</v>
+      </c>
+      <c r="T278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="T278" s="1" t="n">
+      <c r="U278" s="1" t="n">
         <v>0.02306</v>
       </c>
     </row>
@@ -18329,10 +19166,13 @@
         <v>0.01812</v>
       </c>
       <c r="S279" s="1" t="n">
+        <v>0.01811</v>
+      </c>
+      <c r="T279" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="T279" s="1" t="n">
-        <v>0.01812</v>
+      <c r="U279" s="1" t="n">
+        <v>0.01811</v>
       </c>
     </row>
     <row r="280">
@@ -18393,9 +19233,12 @@
         <v>0.03667</v>
       </c>
       <c r="S280" s="1" t="n">
+        <v>0.03678</v>
+      </c>
+      <c r="T280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="T280" s="1" t="n">
+      <c r="U280" s="1" t="n">
         <v>0.03666</v>
       </c>
     </row>
@@ -18457,9 +19300,12 @@
         <v>0.03968</v>
       </c>
       <c r="S281" s="1" t="n">
+        <v>0.03978</v>
+      </c>
+      <c r="T281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="T281" s="1" t="n">
+      <c r="U281" s="1" t="n">
         <v>0.03953</v>
       </c>
     </row>
@@ -18521,9 +19367,12 @@
         <v>0.3043</v>
       </c>
       <c r="S282" s="1" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="T282" s="1" t="n">
         <v>0.3059</v>
       </c>
-      <c r="T282" s="1" t="n">
+      <c r="U282" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -18585,9 +19434,12 @@
         <v>0.01117</v>
       </c>
       <c r="S283" s="1" t="n">
+        <v>0.01118</v>
+      </c>
+      <c r="T283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="T283" s="1" t="n">
+      <c r="U283" s="1" t="n">
         <v>0.01115</v>
       </c>
     </row>
@@ -18649,9 +19501,12 @@
         <v>9.6e-06</v>
       </c>
       <c r="S284" s="1" t="n">
+        <v>9.6e-06</v>
+      </c>
+      <c r="T284" s="1" t="n">
         <v>9.799999999999999e-06</v>
       </c>
-      <c r="T284" s="1" t="n">
+      <c r="U284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -18713,9 +19568,12 @@
         <v>0.1143</v>
       </c>
       <c r="S285" s="1" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="T285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="T285" s="1" t="n">
+      <c r="U285" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -18777,9 +19635,12 @@
         <v>0.003425</v>
       </c>
       <c r="S286" s="1" t="n">
+        <v>0.003441</v>
+      </c>
+      <c r="T286" s="1" t="n">
         <v>0.003485</v>
       </c>
-      <c r="T286" s="1" t="n">
+      <c r="U286" s="1" t="n">
         <v>0.003422</v>
       </c>
     </row>
@@ -18841,9 +19702,12 @@
         <v>0.08477</v>
       </c>
       <c r="S287" s="1" t="n">
+        <v>0.08491</v>
+      </c>
+      <c r="T287" s="1" t="n">
         <v>0.08577</v>
       </c>
-      <c r="T287" s="1" t="n">
+      <c r="U287" s="1" t="n">
         <v>0.08465</v>
       </c>
     </row>
@@ -18905,9 +19769,12 @@
         <v>0.09970999999999999</v>
       </c>
       <c r="S288" s="1" t="n">
+        <v>0.09994</v>
+      </c>
+      <c r="T288" s="1" t="n">
         <v>0.10076</v>
       </c>
-      <c r="T288" s="1" t="n">
+      <c r="U288" s="1" t="n">
         <v>0.09869</v>
       </c>
     </row>
@@ -18969,9 +19836,12 @@
         <v>0.4346</v>
       </c>
       <c r="S289" s="1" t="n">
+        <v>0.4334</v>
+      </c>
+      <c r="T289" s="1" t="n">
         <v>0.4367</v>
       </c>
-      <c r="T289" s="1" t="n">
+      <c r="U289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -19033,9 +19903,12 @@
         <v>0.03959</v>
       </c>
       <c r="S290" s="1" t="n">
+        <v>0.03964</v>
+      </c>
+      <c r="T290" s="1" t="n">
         <v>0.03966</v>
       </c>
-      <c r="T290" s="1" t="n">
+      <c r="U290" s="1" t="n">
         <v>0.03878</v>
       </c>
     </row>
@@ -19097,9 +19970,12 @@
         <v>0.235</v>
       </c>
       <c r="S291" s="1" t="n">
+        <v>0.2351</v>
+      </c>
+      <c r="T291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="T291" s="1" t="n">
+      <c r="U291" s="1" t="n">
         <v>0.2344</v>
       </c>
     </row>
@@ -19161,9 +20037,12 @@
         <v>0.28345</v>
       </c>
       <c r="S292" s="1" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="T292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="T292" s="1" t="n">
+      <c r="U292" s="1" t="n">
         <v>0.28126</v>
       </c>
     </row>
@@ -19225,9 +20104,12 @@
         <v>0.1496</v>
       </c>
       <c r="S293" s="1" t="n">
+        <v>0.1504</v>
+      </c>
+      <c r="T293" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="T293" s="1" t="n">
+      <c r="U293" s="1" t="n">
         <v>0.1487</v>
       </c>
     </row>
@@ -19289,9 +20171,12 @@
         <v>4.172</v>
       </c>
       <c r="S294" s="1" t="n">
+        <v>4.174</v>
+      </c>
+      <c r="T294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="T294" s="1" t="n">
+      <c r="U294" s="1" t="n">
         <v>4.171</v>
       </c>
     </row>
@@ -19353,9 +20238,12 @@
         <v>0.03445</v>
       </c>
       <c r="S295" s="1" t="n">
+        <v>0.03397</v>
+      </c>
+      <c r="T295" s="1" t="n">
         <v>0.03509</v>
       </c>
-      <c r="T295" s="1" t="n">
+      <c r="U295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -19417,9 +20305,12 @@
         <v>0.000967</v>
       </c>
       <c r="S296" s="1" t="n">
+        <v>0.000969</v>
+      </c>
+      <c r="T296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="T296" s="1" t="n">
+      <c r="U296" s="1" t="n">
         <v>0.000964</v>
       </c>
     </row>
@@ -19481,9 +20372,12 @@
         <v>0.08143</v>
       </c>
       <c r="S297" s="1" t="n">
+        <v>0.08153000000000001</v>
+      </c>
+      <c r="T297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="T297" s="1" t="n">
+      <c r="U297" s="1" t="n">
         <v>0.08135000000000001</v>
       </c>
     </row>
@@ -19545,9 +20439,12 @@
         <v>0.05813</v>
       </c>
       <c r="S298" s="1" t="n">
+        <v>0.05839</v>
+      </c>
+      <c r="T298" s="1" t="n">
         <v>0.05845</v>
       </c>
-      <c r="T298" s="1" t="n">
+      <c r="U298" s="1" t="n">
         <v>0.05745</v>
       </c>
     </row>
@@ -19609,9 +20506,12 @@
         <v>0.09079</v>
       </c>
       <c r="S299" s="1" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="T299" s="1" t="n">
         <v>0.0917</v>
       </c>
-      <c r="T299" s="1" t="n">
+      <c r="U299" s="1" t="n">
         <v>0.09028</v>
       </c>
     </row>
@@ -19673,9 +20573,12 @@
         <v>0.02723</v>
       </c>
       <c r="S300" s="1" t="n">
+        <v>0.02725</v>
+      </c>
+      <c r="T300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="T300" s="1" t="n">
+      <c r="U300" s="1" t="n">
         <v>0.02723</v>
       </c>
     </row>
@@ -19737,9 +20640,12 @@
         <v>0.06539</v>
       </c>
       <c r="S301" s="1" t="n">
+        <v>0.06551999999999999</v>
+      </c>
+      <c r="T301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="T301" s="1" t="n">
+      <c r="U301" s="1" t="n">
         <v>0.06525</v>
       </c>
     </row>
@@ -19801,9 +20707,12 @@
         <v>0.053376</v>
       </c>
       <c r="S302" s="1" t="n">
+        <v>0.053462</v>
+      </c>
+      <c r="T302" s="1" t="n">
         <v>0.053585</v>
       </c>
-      <c r="T302" s="1" t="n">
+      <c r="U302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -19865,9 +20774,12 @@
         <v>5171.3</v>
       </c>
       <c r="S303" s="1" t="n">
+        <v>5172</v>
+      </c>
+      <c r="T303" s="1" t="n">
         <v>5177.6</v>
       </c>
-      <c r="T303" s="1" t="n">
+      <c r="U303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -19929,9 +20841,12 @@
         <v>14.83</v>
       </c>
       <c r="S304" s="1" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="T304" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="T304" s="1" t="n">
+      <c r="U304" s="1" t="n">
         <v>14.8</v>
       </c>
     </row>
@@ -19993,9 +20908,12 @@
         <v>0.003706</v>
       </c>
       <c r="S305" s="1" t="n">
+        <v>0.003707</v>
+      </c>
+      <c r="T305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="T305" s="1" t="n">
+      <c r="U305" s="1" t="n">
         <v>0.003688</v>
       </c>
     </row>
@@ -20057,9 +20975,12 @@
         <v>0.4559</v>
       </c>
       <c r="S306" s="1" t="n">
+        <v>0.4552</v>
+      </c>
+      <c r="T306" s="1" t="n">
         <v>0.4608</v>
       </c>
-      <c r="T306" s="1" t="n">
+      <c r="U306" s="1" t="n">
         <v>0.4531</v>
       </c>
     </row>
@@ -20121,9 +21042,12 @@
         <v>0.0466</v>
       </c>
       <c r="S307" s="1" t="n">
+        <v>0.04671</v>
+      </c>
+      <c r="T307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="T307" s="1" t="n">
+      <c r="U307" s="1" t="n">
         <v>0.04651</v>
       </c>
     </row>
@@ -20185,9 +21109,12 @@
         <v>1.5053</v>
       </c>
       <c r="S308" s="1" t="n">
+        <v>1.505</v>
+      </c>
+      <c r="T308" s="1" t="n">
         <v>1.5096</v>
       </c>
-      <c r="T308" s="1" t="n">
+      <c r="U308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -20249,9 +21176,12 @@
         <v>0.0007881</v>
       </c>
       <c r="S309" s="1" t="n">
+        <v>0.0007878</v>
+      </c>
+      <c r="T309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="T309" s="1" t="n">
+      <c r="U309" s="1" t="n">
         <v>0.0007861</v>
       </c>
     </row>
@@ -20313,9 +21243,12 @@
         <v>4.551</v>
       </c>
       <c r="S310" s="1" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="T310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="T310" s="1" t="n">
+      <c r="U310" s="1" t="n">
         <v>4.549</v>
       </c>
     </row>
@@ -20377,9 +21310,12 @@
         <v>4.759</v>
       </c>
       <c r="S311" s="1" t="n">
+        <v>4.761</v>
+      </c>
+      <c r="T311" s="1" t="n">
         <v>4.805</v>
       </c>
-      <c r="T311" s="1" t="n">
+      <c r="U311" s="1" t="n">
         <v>4.743</v>
       </c>
     </row>
@@ -20441,10 +21377,13 @@
         <v>0.08058999999999999</v>
       </c>
       <c r="S312" s="1" t="n">
+        <v>0.08043</v>
+      </c>
+      <c r="T312" s="1" t="n">
         <v>0.08212</v>
       </c>
-      <c r="T312" s="1" t="n">
-        <v>0.08057</v>
+      <c r="U312" s="1" t="n">
+        <v>0.08043</v>
       </c>
     </row>
     <row r="313">
@@ -20505,9 +21444,12 @@
         <v>2.014</v>
       </c>
       <c r="S313" s="1" t="n">
+        <v>2.021</v>
+      </c>
+      <c r="T313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="T313" s="1" t="n">
+      <c r="U313" s="1" t="n">
         <v>2.005</v>
       </c>
     </row>
@@ -20569,9 +21511,12 @@
         <v>0.07189</v>
       </c>
       <c r="S314" s="1" t="n">
+        <v>0.07213</v>
+      </c>
+      <c r="T314" s="1" t="n">
         <v>0.07482999999999999</v>
       </c>
-      <c r="T314" s="1" t="n">
+      <c r="U314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -20633,9 +21578,12 @@
         <v>0.9370000000000001</v>
       </c>
       <c r="S315" s="1" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="T315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="T315" s="1" t="n">
+      <c r="U315" s="1" t="n">
         <v>0.9350000000000001</v>
       </c>
     </row>
@@ -20697,9 +21645,12 @@
         <v>0.1302</v>
       </c>
       <c r="S316" s="1" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="T316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="T316" s="1" t="n">
+      <c r="U316" s="1" t="n">
         <v>0.1299</v>
       </c>
     </row>
@@ -20761,9 +21712,12 @@
         <v>0.1854</v>
       </c>
       <c r="S317" s="1" t="n">
-        <v>0.186</v>
+        <v>0.1867</v>
       </c>
       <c r="T317" s="1" t="n">
+        <v>0.1867</v>
+      </c>
+      <c r="U317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -20825,9 +21779,12 @@
         <v>0.01609</v>
       </c>
       <c r="S318" s="1" t="n">
+        <v>0.01607</v>
+      </c>
+      <c r="T318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="T318" s="1" t="n">
+      <c r="U318" s="1" t="n">
         <v>0.01607</v>
       </c>
     </row>
@@ -20889,9 +21846,12 @@
         <v>0.08326</v>
       </c>
       <c r="S319" s="1" t="n">
+        <v>0.08339000000000001</v>
+      </c>
+      <c r="T319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="T319" s="1" t="n">
+      <c r="U319" s="1" t="n">
         <v>0.08318</v>
       </c>
     </row>
@@ -20953,9 +21913,12 @@
         <v>0.007516</v>
       </c>
       <c r="S320" s="1" t="n">
+        <v>0.007506</v>
+      </c>
+      <c r="T320" s="1" t="n">
         <v>0.007667</v>
       </c>
-      <c r="T320" s="1" t="n">
+      <c r="U320" s="1" t="n">
         <v>0.007463</v>
       </c>
     </row>
@@ -21017,9 +21980,12 @@
         <v>0.05432</v>
       </c>
       <c r="S321" s="1" t="n">
+        <v>0.05434</v>
+      </c>
+      <c r="T321" s="1" t="n">
         <v>0.05505</v>
       </c>
-      <c r="T321" s="1" t="n">
+      <c r="U321" s="1" t="n">
         <v>0.05406</v>
       </c>
     </row>
@@ -21081,9 +22047,12 @@
         <v>0.5499000000000001</v>
       </c>
       <c r="S322" s="1" t="n">
+        <v>0.5501</v>
+      </c>
+      <c r="T322" s="1" t="n">
         <v>0.5515</v>
       </c>
-      <c r="T322" s="1" t="n">
+      <c r="U322" s="1" t="n">
         <v>0.5476</v>
       </c>
     </row>
@@ -21145,9 +22114,12 @@
         <v>0.07564</v>
       </c>
       <c r="S323" s="1" t="n">
+        <v>0.07578</v>
+      </c>
+      <c r="T323" s="1" t="n">
         <v>0.07636999999999999</v>
       </c>
-      <c r="T323" s="1" t="n">
+      <c r="U323" s="1" t="n">
         <v>0.07525</v>
       </c>
     </row>
@@ -21209,9 +22181,12 @@
         <v>0.013004</v>
       </c>
       <c r="S324" s="1" t="n">
+        <v>0.012985</v>
+      </c>
+      <c r="T324" s="1" t="n">
         <v>0.013004</v>
       </c>
-      <c r="T324" s="1" t="n">
+      <c r="U324" s="1" t="n">
         <v>0.012745</v>
       </c>
     </row>
@@ -21273,9 +22248,12 @@
         <v>0.0987</v>
       </c>
       <c r="S325" s="1" t="n">
+        <v>0.0987</v>
+      </c>
+      <c r="T325" s="1" t="n">
         <v>0.0999</v>
       </c>
-      <c r="T325" s="1" t="n">
+      <c r="U325" s="1" t="n">
         <v>0.0985</v>
       </c>
     </row>
@@ -21337,9 +22315,12 @@
         <v>0.01733</v>
       </c>
       <c r="S326" s="1" t="n">
+        <v>0.01736</v>
+      </c>
+      <c r="T326" s="1" t="n">
         <v>0.01765</v>
       </c>
-      <c r="T326" s="1" t="n">
+      <c r="U326" s="1" t="n">
         <v>0.01729</v>
       </c>
     </row>
@@ -21401,9 +22382,12 @@
         <v>0.06395000000000001</v>
       </c>
       <c r="S327" s="1" t="n">
+        <v>0.06403</v>
+      </c>
+      <c r="T327" s="1" t="n">
         <v>0.06435</v>
       </c>
-      <c r="T327" s="1" t="n">
+      <c r="U327" s="1" t="n">
         <v>0.06370000000000001</v>
       </c>
     </row>
@@ -21465,9 +22449,12 @@
         <v>0.263</v>
       </c>
       <c r="S328" s="1" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="T328" s="1" t="n">
         <v>0.2696</v>
       </c>
-      <c r="T328" s="1" t="n">
+      <c r="U328" s="1" t="n">
         <v>0.2612</v>
       </c>
     </row>
@@ -21529,9 +22516,12 @@
         <v>0.17356</v>
       </c>
       <c r="S329" s="1" t="n">
+        <v>0.17347</v>
+      </c>
+      <c r="T329" s="1" t="n">
         <v>0.17476</v>
       </c>
-      <c r="T329" s="1" t="n">
+      <c r="U329" s="1" t="n">
         <v>0.17145</v>
       </c>
     </row>
@@ -21593,10 +22583,13 @@
         <v>2.035</v>
       </c>
       <c r="S330" s="1" t="n">
+        <v>2.034</v>
+      </c>
+      <c r="T330" s="1" t="n">
         <v>2.088</v>
       </c>
-      <c r="T330" s="1" t="n">
-        <v>2.035</v>
+      <c r="U330" s="1" t="n">
+        <v>2.034</v>
       </c>
     </row>
     <row r="331">
@@ -21657,9 +22650,12 @@
         <v>0.0284</v>
       </c>
       <c r="S331" s="1" t="n">
+        <v>0.0287</v>
+      </c>
+      <c r="T331" s="1" t="n">
         <v>0.0288</v>
       </c>
-      <c r="T331" s="1" t="n">
+      <c r="U331" s="1" t="n">
         <v>0.0277</v>
       </c>
     </row>
@@ -21721,9 +22717,12 @@
         <v>0.006015</v>
       </c>
       <c r="S332" s="1" t="n">
+        <v>0.006046</v>
+      </c>
+      <c r="T332" s="1" t="n">
         <v>0.006063</v>
       </c>
-      <c r="T332" s="1" t="n">
+      <c r="U332" s="1" t="n">
         <v>0.005927</v>
       </c>
     </row>
@@ -21785,9 +22784,12 @@
         <v>0.003534</v>
       </c>
       <c r="S333" s="1" t="n">
+        <v>0.003535</v>
+      </c>
+      <c r="T333" s="1" t="n">
         <v>0.003579</v>
       </c>
-      <c r="T333" s="1" t="n">
+      <c r="U333" s="1" t="n">
         <v>0.003497</v>
       </c>
     </row>
@@ -21849,9 +22851,12 @@
         <v>0.014</v>
       </c>
       <c r="S334" s="1" t="n">
+        <v>0.01397</v>
+      </c>
+      <c r="T334" s="1" t="n">
         <v>0.01417</v>
       </c>
-      <c r="T334" s="1" t="n">
+      <c r="U334" s="1" t="n">
         <v>0.01394</v>
       </c>
     </row>
@@ -21913,9 +22918,12 @@
         <v>1.145</v>
       </c>
       <c r="S335" s="1" t="n">
-        <v>1.145</v>
+        <v>1.158</v>
       </c>
       <c r="T335" s="1" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="U335" s="1" t="n">
         <v>1.12</v>
       </c>
     </row>
@@ -21977,9 +22985,12 @@
         <v>0.011332</v>
       </c>
       <c r="S336" s="1" t="n">
-        <v>0.011344</v>
+        <v>0.011365</v>
       </c>
       <c r="T336" s="1" t="n">
+        <v>0.011365</v>
+      </c>
+      <c r="U336" s="1" t="n">
         <v>0.011238</v>
       </c>
     </row>
@@ -22041,9 +23052,12 @@
         <v>2.959</v>
       </c>
       <c r="S337" s="1" t="n">
+        <v>2.967</v>
+      </c>
+      <c r="T337" s="1" t="n">
         <v>3.043</v>
       </c>
-      <c r="T337" s="1" t="n">
+      <c r="U337" s="1" t="n">
         <v>2.913</v>
       </c>
     </row>
@@ -22105,9 +23119,12 @@
         <v>0.0185</v>
       </c>
       <c r="S338" s="1" t="n">
+        <v>0.01849</v>
+      </c>
+      <c r="T338" s="1" t="n">
         <v>0.01885</v>
       </c>
-      <c r="T338" s="1" t="n">
+      <c r="U338" s="1" t="n">
         <v>0.01844</v>
       </c>
     </row>
@@ -22169,9 +23186,12 @@
         <v>0.07704</v>
       </c>
       <c r="S339" s="1" t="n">
+        <v>0.07728</v>
+      </c>
+      <c r="T339" s="1" t="n">
         <v>0.07790999999999999</v>
       </c>
-      <c r="T339" s="1" t="n">
+      <c r="U339" s="1" t="n">
         <v>0.07689</v>
       </c>
     </row>
@@ -22233,9 +23253,12 @@
         <v>0.076</v>
       </c>
       <c r="S340" s="1" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="T340" s="1" t="n">
         <v>0.077</v>
       </c>
-      <c r="T340" s="1" t="n">
+      <c r="U340" s="1" t="n">
         <v>0.075</v>
       </c>
     </row>
@@ -22297,9 +23320,12 @@
         <v>0.03585</v>
       </c>
       <c r="S341" s="1" t="n">
+        <v>0.03586</v>
+      </c>
+      <c r="T341" s="1" t="n">
         <v>0.03638</v>
       </c>
-      <c r="T341" s="1" t="n">
+      <c r="U341" s="1" t="n">
         <v>0.03578</v>
       </c>
     </row>
@@ -22361,9 +23387,12 @@
         <v>2581</v>
       </c>
       <c r="S342" s="1" t="n">
+        <v>2585</v>
+      </c>
+      <c r="T342" s="1" t="n">
         <v>2647</v>
       </c>
-      <c r="T342" s="1" t="n">
+      <c r="U342" s="1" t="n">
         <v>2581</v>
       </c>
     </row>
@@ -22425,9 +23454,12 @@
         <v>0.0002046</v>
       </c>
       <c r="S343" s="1" t="n">
+        <v>0.000204</v>
+      </c>
+      <c r="T343" s="1" t="n">
         <v>0.0002046</v>
       </c>
-      <c r="T343" s="1" t="n">
+      <c r="U343" s="1" t="n">
         <v>0.0001959</v>
       </c>
     </row>
@@ -22489,9 +23521,12 @@
         <v>0.07940999999999999</v>
       </c>
       <c r="S344" s="1" t="n">
+        <v>0.07956000000000001</v>
+      </c>
+      <c r="T344" s="1" t="n">
         <v>0.08032</v>
       </c>
-      <c r="T344" s="1" t="n">
+      <c r="U344" s="1" t="n">
         <v>0.07915</v>
       </c>
     </row>
@@ -22553,9 +23588,12 @@
         <v>0.01628</v>
       </c>
       <c r="S345" s="1" t="n">
+        <v>0.01627</v>
+      </c>
+      <c r="T345" s="1" t="n">
         <v>0.0168</v>
       </c>
-      <c r="T345" s="1" t="n">
+      <c r="U345" s="1" t="n">
         <v>0.01622</v>
       </c>
     </row>
@@ -22617,9 +23655,12 @@
         <v>2.736</v>
       </c>
       <c r="S346" s="1" t="n">
+        <v>2.744</v>
+      </c>
+      <c r="T346" s="1" t="n">
         <v>2.799</v>
       </c>
-      <c r="T346" s="1" t="n">
+      <c r="U346" s="1" t="n">
         <v>2.731</v>
       </c>
     </row>
@@ -22681,9 +23722,12 @@
         <v>0.01636</v>
       </c>
       <c r="S347" s="1" t="n">
+        <v>0.01635</v>
+      </c>
+      <c r="T347" s="1" t="n">
         <v>0.0165</v>
       </c>
-      <c r="T347" s="1" t="n">
+      <c r="U347" s="1" t="n">
         <v>0.01625</v>
       </c>
     </row>
@@ -22745,9 +23789,12 @@
         <v>0.03972</v>
       </c>
       <c r="S348" s="1" t="n">
+        <v>0.03929</v>
+      </c>
+      <c r="T348" s="1" t="n">
         <v>0.04</v>
       </c>
-      <c r="T348" s="1" t="n">
+      <c r="U348" s="1" t="n">
         <v>0.03812</v>
       </c>
     </row>
@@ -22809,9 +23856,12 @@
         <v>0.3076</v>
       </c>
       <c r="S349" s="1" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="T349" s="1" t="n">
         <v>0.3076</v>
       </c>
-      <c r="T349" s="1" t="n">
+      <c r="U349" s="1" t="n">
         <v>0.3028</v>
       </c>
     </row>
@@ -22873,9 +23923,12 @@
         <v>0.005077</v>
       </c>
       <c r="S350" s="1" t="n">
+        <v>0.005095</v>
+      </c>
+      <c r="T350" s="1" t="n">
         <v>0.005155</v>
       </c>
-      <c r="T350" s="1" t="n">
+      <c r="U350" s="1" t="n">
         <v>0.005039</v>
       </c>
     </row>
@@ -22937,9 +23990,12 @@
         <v>0.005084</v>
       </c>
       <c r="S351" s="1" t="n">
+        <v>0.005093</v>
+      </c>
+      <c r="T351" s="1" t="n">
         <v>0.005171</v>
       </c>
-      <c r="T351" s="1" t="n">
+      <c r="U351" s="1" t="n">
         <v>0.005054</v>
       </c>
     </row>
@@ -23001,9 +24057,12 @@
         <v>0.00439</v>
       </c>
       <c r="S352" s="1" t="n">
+        <v>0.00439</v>
+      </c>
+      <c r="T352" s="1" t="n">
         <v>0.004419</v>
       </c>
-      <c r="T352" s="1" t="n">
+      <c r="U352" s="1" t="n">
         <v>0.004379</v>
       </c>
     </row>
@@ -23065,9 +24124,12 @@
         <v>0.08031000000000001</v>
       </c>
       <c r="S353" s="1" t="n">
+        <v>0.08044999999999999</v>
+      </c>
+      <c r="T353" s="1" t="n">
         <v>0.08214</v>
       </c>
-      <c r="T353" s="1" t="n">
+      <c r="U353" s="1" t="n">
         <v>0.08008</v>
       </c>
     </row>
@@ -23129,9 +24191,12 @@
         <v>1.265</v>
       </c>
       <c r="S354" s="1" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="T354" s="1" t="n">
         <v>1.312</v>
       </c>
-      <c r="T354" s="1" t="n">
+      <c r="U354" s="1" t="n">
         <v>1.258</v>
       </c>
     </row>
@@ -23193,9 +24258,12 @@
         <v>7.668</v>
       </c>
       <c r="S355" s="1" t="n">
+        <v>7.664</v>
+      </c>
+      <c r="T355" s="1" t="n">
         <v>7.775</v>
       </c>
-      <c r="T355" s="1" t="n">
+      <c r="U355" s="1" t="n">
         <v>7.651</v>
       </c>
     </row>
@@ -23257,9 +24325,12 @@
         <v>0.00784</v>
       </c>
       <c r="S356" s="1" t="n">
+        <v>0.00787</v>
+      </c>
+      <c r="T356" s="1" t="n">
         <v>0.007990000000000001</v>
       </c>
-      <c r="T356" s="1" t="n">
+      <c r="U356" s="1" t="n">
         <v>0.00777</v>
       </c>
     </row>
@@ -23321,9 +24392,12 @@
         <v>0.005637</v>
       </c>
       <c r="S357" s="1" t="n">
+        <v>0.00563</v>
+      </c>
+      <c r="T357" s="1" t="n">
         <v>0.005738</v>
       </c>
-      <c r="T357" s="1" t="n">
+      <c r="U357" s="1" t="n">
         <v>0.005608</v>
       </c>
     </row>
@@ -23385,9 +24459,12 @@
         <v>0.01545</v>
       </c>
       <c r="S358" s="1" t="n">
+        <v>0.01548</v>
+      </c>
+      <c r="T358" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="T358" s="1" t="n">
+      <c r="U358" s="1" t="n">
         <v>0.01533</v>
       </c>
     </row>
@@ -23449,9 +24526,12 @@
         <v>3.609</v>
       </c>
       <c r="S359" s="1" t="n">
+        <v>3.609</v>
+      </c>
+      <c r="T359" s="1" t="n">
         <v>3.67</v>
       </c>
-      <c r="T359" s="1" t="n">
+      <c r="U359" s="1" t="n">
         <v>3.605</v>
       </c>
     </row>
@@ -23513,9 +24593,12 @@
         <v>0.1498</v>
       </c>
       <c r="S360" s="1" t="n">
+        <v>0.1502</v>
+      </c>
+      <c r="T360" s="1" t="n">
         <v>0.1515</v>
       </c>
-      <c r="T360" s="1" t="n">
+      <c r="U360" s="1" t="n">
         <v>0.1497</v>
       </c>
     </row>
@@ -23577,9 +24660,12 @@
         <v>0.07044</v>
       </c>
       <c r="S361" s="1" t="n">
+        <v>0.07031</v>
+      </c>
+      <c r="T361" s="1" t="n">
         <v>0.07104000000000001</v>
       </c>
-      <c r="T361" s="1" t="n">
+      <c r="U361" s="1" t="n">
         <v>0.07019</v>
       </c>
     </row>
@@ -23641,9 +24727,12 @@
         <v>0.01768</v>
       </c>
       <c r="S362" s="1" t="n">
+        <v>0.01774</v>
+      </c>
+      <c r="T362" s="1" t="n">
         <v>0.01796</v>
       </c>
-      <c r="T362" s="1" t="n">
+      <c r="U362" s="1" t="n">
         <v>0.0176</v>
       </c>
     </row>
@@ -23705,9 +24794,12 @@
         <v>0.02232</v>
       </c>
       <c r="S363" s="1" t="n">
+        <v>0.02231</v>
+      </c>
+      <c r="T363" s="1" t="n">
         <v>0.02278</v>
       </c>
-      <c r="T363" s="1" t="n">
+      <c r="U363" s="1" t="n">
         <v>0.02229</v>
       </c>
     </row>
@@ -23769,9 +24861,12 @@
         <v>0.01251</v>
       </c>
       <c r="S364" s="1" t="n">
+        <v>0.01252</v>
+      </c>
+      <c r="T364" s="1" t="n">
         <v>0.01283</v>
       </c>
-      <c r="T364" s="1" t="n">
+      <c r="U364" s="1" t="n">
         <v>0.01249</v>
       </c>
     </row>
@@ -23833,9 +24928,12 @@
         <v>0.09089999999999999</v>
       </c>
       <c r="S365" s="1" t="n">
+        <v>0.09089999999999999</v>
+      </c>
+      <c r="T365" s="1" t="n">
         <v>0.0926</v>
       </c>
-      <c r="T365" s="1" t="n">
+      <c r="U365" s="1" t="n">
         <v>0.09080000000000001</v>
       </c>
     </row>
@@ -23897,9 +24995,12 @@
         <v>0.04227</v>
       </c>
       <c r="S366" s="1" t="n">
+        <v>0.04233</v>
+      </c>
+      <c r="T366" s="1" t="n">
         <v>0.04261</v>
       </c>
-      <c r="T366" s="1" t="n">
+      <c r="U366" s="1" t="n">
         <v>0.04214</v>
       </c>
     </row>
@@ -23961,9 +25062,12 @@
         <v>0.0314</v>
       </c>
       <c r="S367" s="1" t="n">
+        <v>0.03148</v>
+      </c>
+      <c r="T367" s="1" t="n">
         <v>0.03188</v>
       </c>
-      <c r="T367" s="1" t="n">
+      <c r="U367" s="1" t="n">
         <v>0.03124</v>
       </c>
     </row>
@@ -24025,10 +25129,13 @@
         <v>0.02331</v>
       </c>
       <c r="S368" s="1" t="n">
+        <v>0.02322</v>
+      </c>
+      <c r="T368" s="1" t="n">
         <v>0.02405</v>
       </c>
-      <c r="T368" s="1" t="n">
-        <v>0.0233</v>
+      <c r="U368" s="1" t="n">
+        <v>0.02322</v>
       </c>
     </row>
     <row r="369">
@@ -24089,9 +25196,12 @@
         <v>0.03095</v>
       </c>
       <c r="S369" s="1" t="n">
+        <v>0.03091</v>
+      </c>
+      <c r="T369" s="1" t="n">
         <v>0.0313</v>
       </c>
-      <c r="T369" s="1" t="n">
+      <c r="U369" s="1" t="n">
         <v>0.0308</v>
       </c>
     </row>
@@ -24153,9 +25263,12 @@
         <v>0.07963000000000001</v>
       </c>
       <c r="S370" s="1" t="n">
-        <v>0.07998</v>
+        <v>0.08017000000000001</v>
       </c>
       <c r="T370" s="1" t="n">
+        <v>0.08017000000000001</v>
+      </c>
+      <c r="U370" s="1" t="n">
         <v>0.07741000000000001</v>
       </c>
     </row>
@@ -24217,9 +25330,12 @@
         <v>0.1073</v>
       </c>
       <c r="S371" s="1" t="n">
+        <v>0.1073</v>
+      </c>
+      <c r="T371" s="1" t="n">
         <v>0.1089</v>
       </c>
-      <c r="T371" s="1" t="n">
+      <c r="U371" s="1" t="n">
         <v>0.1072</v>
       </c>
     </row>
@@ -24281,9 +25397,12 @@
         <v>0.006964</v>
       </c>
       <c r="S372" s="1" t="n">
+        <v>0.007009</v>
+      </c>
+      <c r="T372" s="1" t="n">
         <v>0.007209</v>
       </c>
-      <c r="T372" s="1" t="n">
+      <c r="U372" s="1" t="n">
         <v>0.00694</v>
       </c>
     </row>
@@ -24345,9 +25464,12 @@
         <v>0.096</v>
       </c>
       <c r="S373" s="1" t="n">
+        <v>0.0959</v>
+      </c>
+      <c r="T373" s="1" t="n">
         <v>0.09719999999999999</v>
       </c>
-      <c r="T373" s="1" t="n">
+      <c r="U373" s="1" t="n">
         <v>0.0956</v>
       </c>
     </row>
@@ -24409,9 +25531,12 @@
         <v>0.05776</v>
       </c>
       <c r="S374" s="1" t="n">
+        <v>0.0578</v>
+      </c>
+      <c r="T374" s="1" t="n">
         <v>0.05881</v>
       </c>
-      <c r="T374" s="1" t="n">
+      <c r="U374" s="1" t="n">
         <v>0.0573</v>
       </c>
     </row>
@@ -24473,9 +25598,12 @@
         <v>0.3169</v>
       </c>
       <c r="S375" s="1" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="T375" s="1" t="n">
         <v>0.3238</v>
       </c>
-      <c r="T375" s="1" t="n">
+      <c r="U375" s="1" t="n">
         <v>0.3169</v>
       </c>
     </row>
@@ -24537,9 +25665,12 @@
         <v>0.0194</v>
       </c>
       <c r="S376" s="1" t="n">
+        <v>0.01944</v>
+      </c>
+      <c r="T376" s="1" t="n">
         <v>0.02004</v>
       </c>
-      <c r="T376" s="1" t="n">
+      <c r="U376" s="1" t="n">
         <v>0.01938</v>
       </c>
     </row>
@@ -24601,9 +25732,12 @@
         <v>0.06834999999999999</v>
       </c>
       <c r="S377" s="1" t="n">
+        <v>0.06850000000000001</v>
+      </c>
+      <c r="T377" s="1" t="n">
         <v>0.06926</v>
       </c>
-      <c r="T377" s="1" t="n">
+      <c r="U377" s="1" t="n">
         <v>0.06818</v>
       </c>
     </row>
@@ -24665,9 +25799,12 @@
         <v>0.15872</v>
       </c>
       <c r="S378" s="1" t="n">
+        <v>0.15839</v>
+      </c>
+      <c r="T378" s="1" t="n">
         <v>0.15872</v>
       </c>
-      <c r="T378" s="1" t="n">
+      <c r="U378" s="1" t="n">
         <v>0.15347</v>
       </c>
     </row>
@@ -24729,9 +25866,12 @@
         <v>0.0005932999999999999</v>
       </c>
       <c r="S379" s="1" t="n">
+        <v>0.000595</v>
+      </c>
+      <c r="T379" s="1" t="n">
         <v>0.0006091</v>
       </c>
-      <c r="T379" s="1" t="n">
+      <c r="U379" s="1" t="n">
         <v>0.0005922</v>
       </c>
     </row>
@@ -24793,9 +25933,12 @@
         <v>0.01012</v>
       </c>
       <c r="S380" s="1" t="n">
+        <v>0.01017</v>
+      </c>
+      <c r="T380" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="T380" s="1" t="n">
+      <c r="U380" s="1" t="n">
         <v>0.01012</v>
       </c>
     </row>
@@ -24857,9 +26000,12 @@
         <v>0.02562</v>
       </c>
       <c r="S381" s="1" t="n">
+        <v>0.02561</v>
+      </c>
+      <c r="T381" s="1" t="n">
         <v>0.0259</v>
       </c>
-      <c r="T381" s="1" t="n">
+      <c r="U381" s="1" t="n">
         <v>0.02538</v>
       </c>
     </row>
@@ -24921,10 +26067,13 @@
         <v>0.18964</v>
       </c>
       <c r="S382" s="1" t="n">
+        <v>0.18893</v>
+      </c>
+      <c r="T382" s="1" t="n">
         <v>0.19348</v>
       </c>
-      <c r="T382" s="1" t="n">
-        <v>0.18936</v>
+      <c r="U382" s="1" t="n">
+        <v>0.18893</v>
       </c>
     </row>
     <row r="383">
@@ -24985,9 +26134,12 @@
         <v>0.09222</v>
       </c>
       <c r="S383" s="1" t="n">
+        <v>0.09225999999999999</v>
+      </c>
+      <c r="T383" s="1" t="n">
         <v>0.09479</v>
       </c>
-      <c r="T383" s="1" t="n">
+      <c r="U383" s="1" t="n">
         <v>0.09214</v>
       </c>
     </row>
@@ -25049,9 +26201,12 @@
         <v>0.0316</v>
       </c>
       <c r="S384" s="1" t="n">
+        <v>0.0316</v>
+      </c>
+      <c r="T384" s="1" t="n">
         <v>0.03208</v>
       </c>
-      <c r="T384" s="1" t="n">
+      <c r="U384" s="1" t="n">
         <v>0.0316</v>
       </c>
     </row>
@@ -25113,9 +26268,12 @@
         <v>0.01089</v>
       </c>
       <c r="S385" s="1" t="n">
+        <v>0.01087</v>
+      </c>
+      <c r="T385" s="1" t="n">
         <v>0.01126</v>
       </c>
-      <c r="T385" s="1" t="n">
+      <c r="U385" s="1" t="n">
         <v>0.01086</v>
       </c>
     </row>
@@ -25177,9 +26335,12 @@
         <v>0.05043</v>
       </c>
       <c r="S386" s="1" t="n">
+        <v>0.0505</v>
+      </c>
+      <c r="T386" s="1" t="n">
         <v>0.05224</v>
       </c>
-      <c r="T386" s="1" t="n">
+      <c r="U386" s="1" t="n">
         <v>0.05043</v>
       </c>
     </row>
@@ -25241,9 +26402,12 @@
         <v>0.02431</v>
       </c>
       <c r="S387" s="1" t="n">
+        <v>0.02433</v>
+      </c>
+      <c r="T387" s="1" t="n">
         <v>0.02541</v>
       </c>
-      <c r="T387" s="1" t="n">
+      <c r="U387" s="1" t="n">
         <v>0.02405</v>
       </c>
     </row>
@@ -25305,9 +26469,12 @@
         <v>0.007267</v>
       </c>
       <c r="S388" s="1" t="n">
+        <v>0.007269</v>
+      </c>
+      <c r="T388" s="1" t="n">
         <v>0.007381</v>
       </c>
-      <c r="T388" s="1" t="n">
+      <c r="U388" s="1" t="n">
         <v>0.007214</v>
       </c>
     </row>
@@ -25369,9 +26536,12 @@
         <v>0.01013</v>
       </c>
       <c r="S389" s="1" t="n">
+        <v>0.01014</v>
+      </c>
+      <c r="T389" s="1" t="n">
         <v>0.01024</v>
       </c>
-      <c r="T389" s="1" t="n">
+      <c r="U389" s="1" t="n">
         <v>0.01009</v>
       </c>
     </row>
@@ -25433,9 +26603,12 @@
         <v>0.0823</v>
       </c>
       <c r="S390" s="1" t="n">
+        <v>0.08230999999999999</v>
+      </c>
+      <c r="T390" s="1" t="n">
         <v>0.0839</v>
       </c>
-      <c r="T390" s="1" t="n">
+      <c r="U390" s="1" t="n">
         <v>0.08214</v>
       </c>
     </row>
@@ -25497,9 +26670,12 @@
         <v>0.5049</v>
       </c>
       <c r="S391" s="1" t="n">
+        <v>0.5046</v>
+      </c>
+      <c r="T391" s="1" t="n">
         <v>0.5061</v>
       </c>
-      <c r="T391" s="1" t="n">
+      <c r="U391" s="1" t="n">
         <v>0.5014</v>
       </c>
     </row>
@@ -25561,9 +26737,12 @@
         <v>0.1162</v>
       </c>
       <c r="S392" s="1" t="n">
+        <v>0.1164</v>
+      </c>
+      <c r="T392" s="1" t="n">
         <v>0.118</v>
       </c>
-      <c r="T392" s="1" t="n">
+      <c r="U392" s="1" t="n">
         <v>0.1157</v>
       </c>
     </row>
@@ -25625,9 +26804,12 @@
         <v>0.00246</v>
       </c>
       <c r="S393" s="1" t="n">
+        <v>0.00245</v>
+      </c>
+      <c r="T393" s="1" t="n">
         <v>0.00254</v>
       </c>
-      <c r="T393" s="1" t="n">
+      <c r="U393" s="1" t="n">
         <v>0.00244</v>
       </c>
     </row>
@@ -25689,9 +26871,12 @@
         <v>0.02131</v>
       </c>
       <c r="S394" s="1" t="n">
+        <v>0.02139</v>
+      </c>
+      <c r="T394" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="T394" s="1" t="n">
+      <c r="U394" s="1" t="n">
         <v>0.02108</v>
       </c>
     </row>
@@ -25753,9 +26938,12 @@
         <v>0.0158</v>
       </c>
       <c r="S395" s="1" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="T395" s="1" t="n">
         <v>0.0163</v>
       </c>
-      <c r="T395" s="1" t="n">
+      <c r="U395" s="1" t="n">
         <v>0.0158</v>
       </c>
     </row>
@@ -25817,9 +27005,12 @@
         <v>0.1352</v>
       </c>
       <c r="S396" s="1" t="n">
+        <v>0.1351</v>
+      </c>
+      <c r="T396" s="1" t="n">
         <v>0.1364</v>
       </c>
-      <c r="T396" s="1" t="n">
+      <c r="U396" s="1" t="n">
         <v>0.1349</v>
       </c>
     </row>
@@ -25881,9 +27072,12 @@
         <v>0.01443</v>
       </c>
       <c r="S397" s="1" t="n">
+        <v>0.01447</v>
+      </c>
+      <c r="T397" s="1" t="n">
         <v>0.01486</v>
       </c>
-      <c r="T397" s="1" t="n">
+      <c r="U397" s="1" t="n">
         <v>0.0144</v>
       </c>
     </row>
@@ -25945,9 +27139,12 @@
         <v>6.718</v>
       </c>
       <c r="S398" s="1" t="n">
+        <v>6.772</v>
+      </c>
+      <c r="T398" s="1" t="n">
         <v>6.955</v>
       </c>
-      <c r="T398" s="1" t="n">
+      <c r="U398" s="1" t="n">
         <v>6.679</v>
       </c>
     </row>
@@ -26009,9 +27206,12 @@
         <v>0.009379</v>
       </c>
       <c r="S399" s="1" t="n">
+        <v>0.009473000000000001</v>
+      </c>
+      <c r="T399" s="1" t="n">
         <v>0.009509999999999999</v>
       </c>
-      <c r="T399" s="1" t="n">
+      <c r="U399" s="1" t="n">
         <v>0.009363</v>
       </c>
     </row>
@@ -26073,9 +27273,12 @@
         <v>0.001241</v>
       </c>
       <c r="S400" s="1" t="n">
+        <v>0.001246</v>
+      </c>
+      <c r="T400" s="1" t="n">
         <v>0.001291</v>
       </c>
-      <c r="T400" s="1" t="n">
+      <c r="U400" s="1" t="n">
         <v>0.001241</v>
       </c>
     </row>
@@ -26137,9 +27340,12 @@
         <v>0.01846</v>
       </c>
       <c r="S401" s="1" t="n">
+        <v>0.01845</v>
+      </c>
+      <c r="T401" s="1" t="n">
         <v>0.01861</v>
       </c>
-      <c r="T401" s="1" t="n">
+      <c r="U401" s="1" t="n">
         <v>0.0184</v>
       </c>
     </row>
@@ -26201,9 +27407,12 @@
         <v>0.08459999999999999</v>
       </c>
       <c r="S402" s="1" t="n">
+        <v>0.0849</v>
+      </c>
+      <c r="T402" s="1" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="T402" s="1" t="n">
+      <c r="U402" s="1" t="n">
         <v>0.08447</v>
       </c>
     </row>
@@ -26265,9 +27474,12 @@
         <v>0.00549</v>
       </c>
       <c r="S403" s="1" t="n">
+        <v>0.00549</v>
+      </c>
+      <c r="T403" s="1" t="n">
         <v>0.00556</v>
       </c>
-      <c r="T403" s="1" t="n">
+      <c r="U403" s="1" t="n">
         <v>0.00548</v>
       </c>
     </row>
@@ -26329,9 +27541,12 @@
         <v>0.04271</v>
       </c>
       <c r="S404" s="1" t="n">
+        <v>0.04277</v>
+      </c>
+      <c r="T404" s="1" t="n">
         <v>0.04381</v>
       </c>
-      <c r="T404" s="1" t="n">
+      <c r="U404" s="1" t="n">
         <v>0.04238</v>
       </c>
     </row>
@@ -26393,9 +27608,12 @@
         <v>0.05832</v>
       </c>
       <c r="S405" s="1" t="n">
+        <v>0.05838</v>
+      </c>
+      <c r="T405" s="1" t="n">
         <v>0.05915</v>
       </c>
-      <c r="T405" s="1" t="n">
+      <c r="U405" s="1" t="n">
         <v>0.05827</v>
       </c>
     </row>
@@ -26457,9 +27675,12 @@
         <v>0.01689</v>
       </c>
       <c r="S406" s="1" t="n">
+        <v>0.01657</v>
+      </c>
+      <c r="T406" s="1" t="n">
         <v>0.01689</v>
       </c>
-      <c r="T406" s="1" t="n">
+      <c r="U406" s="1" t="n">
         <v>0.01647</v>
       </c>
     </row>
@@ -26521,9 +27742,12 @@
         <v>0.0423</v>
       </c>
       <c r="S407" s="1" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="T407" s="1" t="n">
         <v>0.0428</v>
       </c>
-      <c r="T407" s="1" t="n">
+      <c r="U407" s="1" t="n">
         <v>0.0423</v>
       </c>
     </row>
@@ -26585,9 +27809,12 @@
         <v>0.01925</v>
       </c>
       <c r="S408" s="1" t="n">
+        <v>0.01928</v>
+      </c>
+      <c r="T408" s="1" t="n">
         <v>0.01951</v>
       </c>
-      <c r="T408" s="1" t="n">
+      <c r="U408" s="1" t="n">
         <v>0.01921</v>
       </c>
     </row>
@@ -26649,9 +27876,12 @@
         <v>0.4446</v>
       </c>
       <c r="S409" s="1" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="T409" s="1" t="n">
         <v>0.4484</v>
       </c>
-      <c r="T409" s="1" t="n">
+      <c r="U409" s="1" t="n">
         <v>0.4427</v>
       </c>
     </row>
@@ -26713,9 +27943,12 @@
         <v>0.04379</v>
       </c>
       <c r="S410" s="1" t="n">
+        <v>0.04383</v>
+      </c>
+      <c r="T410" s="1" t="n">
         <v>0.04454</v>
       </c>
-      <c r="T410" s="1" t="n">
+      <c r="U410" s="1" t="n">
         <v>0.04379</v>
       </c>
     </row>
@@ -26777,9 +28010,12 @@
         <v>27.22</v>
       </c>
       <c r="S411" s="1" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="T411" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="T411" s="1" t="n">
+      <c r="U411" s="1" t="n">
         <v>26.78</v>
       </c>
     </row>
@@ -26841,9 +28077,12 @@
         <v>0.03527</v>
       </c>
       <c r="S412" s="1" t="n">
+        <v>0.03521</v>
+      </c>
+      <c r="T412" s="1" t="n">
         <v>0.03564</v>
       </c>
-      <c r="T412" s="1" t="n">
+      <c r="U412" s="1" t="n">
         <v>0.03493</v>
       </c>
     </row>
@@ -26905,9 +28144,12 @@
         <v>0.003398</v>
       </c>
       <c r="S413" s="1" t="n">
+        <v>0.003398</v>
+      </c>
+      <c r="T413" s="1" t="n">
         <v>0.003432</v>
       </c>
-      <c r="T413" s="1" t="n">
+      <c r="U413" s="1" t="n">
         <v>0.003388</v>
       </c>
     </row>
@@ -26969,9 +28211,12 @@
         <v>0.1523</v>
       </c>
       <c r="S414" s="1" t="n">
+        <v>0.1523</v>
+      </c>
+      <c r="T414" s="1" t="n">
         <v>0.1538</v>
       </c>
-      <c r="T414" s="1" t="n">
+      <c r="U414" s="1" t="n">
         <v>0.1523</v>
       </c>
     </row>
@@ -27033,9 +28278,12 @@
         <v>0.05228</v>
       </c>
       <c r="S415" s="1" t="n">
+        <v>0.05236</v>
+      </c>
+      <c r="T415" s="1" t="n">
         <v>0.05288</v>
       </c>
-      <c r="T415" s="1" t="n">
+      <c r="U415" s="1" t="n">
         <v>0.05228</v>
       </c>
     </row>
@@ -27097,9 +28345,12 @@
         <v>0.00655</v>
       </c>
       <c r="S416" s="1" t="n">
+        <v>0.00656</v>
+      </c>
+      <c r="T416" s="1" t="n">
         <v>0.00669</v>
       </c>
-      <c r="T416" s="1" t="n">
+      <c r="U416" s="1" t="n">
         <v>0.00654</v>
       </c>
     </row>
@@ -27161,9 +28412,12 @@
         <v>0.06027</v>
       </c>
       <c r="S417" s="1" t="n">
+        <v>0.06027</v>
+      </c>
+      <c r="T417" s="1" t="n">
         <v>0.06101</v>
       </c>
-      <c r="T417" s="1" t="n">
+      <c r="U417" s="1" t="n">
         <v>0.06025</v>
       </c>
     </row>
@@ -27225,9 +28479,12 @@
         <v>0.008036</v>
       </c>
       <c r="S418" s="1" t="n">
+        <v>0.008061</v>
+      </c>
+      <c r="T418" s="1" t="n">
         <v>0.008241</v>
       </c>
-      <c r="T418" s="1" t="n">
+      <c r="U418" s="1" t="n">
         <v>0.007979</v>
       </c>
     </row>
@@ -27289,9 +28546,12 @@
         <v>0.07428</v>
       </c>
       <c r="S419" s="1" t="n">
+        <v>0.07424</v>
+      </c>
+      <c r="T419" s="1" t="n">
         <v>0.07524</v>
       </c>
-      <c r="T419" s="1" t="n">
+      <c r="U419" s="1" t="n">
         <v>0.07414999999999999</v>
       </c>
     </row>
@@ -27353,9 +28613,12 @@
         <v>0.02133</v>
       </c>
       <c r="S420" s="1" t="n">
+        <v>0.02126</v>
+      </c>
+      <c r="T420" s="1" t="n">
         <v>0.02146</v>
       </c>
-      <c r="T420" s="1" t="n">
+      <c r="U420" s="1" t="n">
         <v>0.02105</v>
       </c>
     </row>
@@ -27417,10 +28680,13 @@
         <v>0.06894</v>
       </c>
       <c r="S421" s="1" t="n">
+        <v>0.0689</v>
+      </c>
+      <c r="T421" s="1" t="n">
         <v>0.07038999999999999</v>
       </c>
-      <c r="T421" s="1" t="n">
-        <v>0.06894</v>
+      <c r="U421" s="1" t="n">
+        <v>0.0689</v>
       </c>
     </row>
     <row r="422">
@@ -27481,9 +28747,12 @@
         <v>0.01478</v>
       </c>
       <c r="S422" s="1" t="n">
+        <v>0.01483</v>
+      </c>
+      <c r="T422" s="1" t="n">
         <v>0.01528</v>
       </c>
-      <c r="T422" s="1" t="n">
+      <c r="U422" s="1" t="n">
         <v>0.01473</v>
       </c>
     </row>
@@ -27545,9 +28814,12 @@
         <v>0.006581</v>
       </c>
       <c r="S423" s="1" t="n">
+        <v>0.006594</v>
+      </c>
+      <c r="T423" s="1" t="n">
         <v>0.006699</v>
       </c>
-      <c r="T423" s="1" t="n">
+      <c r="U423" s="1" t="n">
         <v>0.00658</v>
       </c>
     </row>
@@ -27609,9 +28881,12 @@
         <v>0.909</v>
       </c>
       <c r="S424" s="1" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="T424" s="1" t="n">
         <v>0.921</v>
       </c>
-      <c r="T424" s="1" t="n">
+      <c r="U424" s="1" t="n">
         <v>0.907</v>
       </c>
     </row>
@@ -27673,9 +28948,12 @@
         <v>0.03546</v>
       </c>
       <c r="S425" s="1" t="n">
+        <v>0.03542</v>
+      </c>
+      <c r="T425" s="1" t="n">
         <v>0.03596</v>
       </c>
-      <c r="T425" s="1" t="n">
+      <c r="U425" s="1" t="n">
         <v>0.03519</v>
       </c>
     </row>
@@ -27737,9 +29015,12 @@
         <v>1.801</v>
       </c>
       <c r="S426" s="1" t="n">
+        <v>1.798</v>
+      </c>
+      <c r="T426" s="1" t="n">
         <v>1.81</v>
       </c>
-      <c r="T426" s="1" t="n">
+      <c r="U426" s="1" t="n">
         <v>1.778</v>
       </c>
     </row>
@@ -27801,9 +29082,12 @@
         <v>0.12837</v>
       </c>
       <c r="S427" s="1" t="n">
-        <v>0.12837</v>
+        <v>0.12875</v>
       </c>
       <c r="T427" s="1" t="n">
+        <v>0.12875</v>
+      </c>
+      <c r="U427" s="1" t="n">
         <v>0.12736</v>
       </c>
     </row>
@@ -27865,9 +29149,12 @@
         <v>0.05292</v>
       </c>
       <c r="S428" s="1" t="n">
+        <v>0.05293</v>
+      </c>
+      <c r="T428" s="1" t="n">
         <v>0.05362</v>
       </c>
-      <c r="T428" s="1" t="n">
+      <c r="U428" s="1" t="n">
         <v>0.05269</v>
       </c>
     </row>
@@ -27929,9 +29216,12 @@
         <v>1.289</v>
       </c>
       <c r="S429" s="1" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="T429" s="1" t="n">
         <v>1.333</v>
       </c>
-      <c r="T429" s="1" t="n">
+      <c r="U429" s="1" t="n">
         <v>1.282</v>
       </c>
     </row>
@@ -27993,9 +29283,12 @@
         <v>0.07461</v>
       </c>
       <c r="S430" s="1" t="n">
+        <v>0.07464999999999999</v>
+      </c>
+      <c r="T430" s="1" t="n">
         <v>0.07618</v>
       </c>
-      <c r="T430" s="1" t="n">
+      <c r="U430" s="1" t="n">
         <v>0.07456</v>
       </c>
     </row>
@@ -28057,9 +29350,12 @@
         <v>0.1565</v>
       </c>
       <c r="S431" s="1" t="n">
+        <v>0.1564</v>
+      </c>
+      <c r="T431" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="T431" s="1" t="n">
+      <c r="U431" s="1" t="n">
         <v>0.156</v>
       </c>
     </row>
@@ -28121,9 +29417,12 @@
         <v>1.44</v>
       </c>
       <c r="S432" s="1" t="n">
+        <v>1.443</v>
+      </c>
+      <c r="T432" s="1" t="n">
         <v>1.461</v>
       </c>
-      <c r="T432" s="1" t="n">
+      <c r="U432" s="1" t="n">
         <v>1.438</v>
       </c>
     </row>
@@ -28185,9 +29484,12 @@
         <v>3.255</v>
       </c>
       <c r="S433" s="1" t="n">
+        <v>3.257</v>
+      </c>
+      <c r="T433" s="1" t="n">
         <v>3.324</v>
       </c>
-      <c r="T433" s="1" t="n">
+      <c r="U433" s="1" t="n">
         <v>3.239</v>
       </c>
     </row>
@@ -28249,9 +29551,12 @@
         <v>0.1785</v>
       </c>
       <c r="S434" s="1" t="n">
+        <v>0.1785</v>
+      </c>
+      <c r="T434" s="1" t="n">
         <v>0.1803</v>
       </c>
-      <c r="T434" s="1" t="n">
+      <c r="U434" s="1" t="n">
         <v>0.1783</v>
       </c>
     </row>
@@ -28313,9 +29618,12 @@
         <v>0.008557</v>
       </c>
       <c r="S435" s="1" t="n">
+        <v>0.008562999999999999</v>
+      </c>
+      <c r="T435" s="1" t="n">
         <v>0.008717000000000001</v>
       </c>
-      <c r="T435" s="1" t="n">
+      <c r="U435" s="1" t="n">
         <v>0.008548</v>
       </c>
     </row>
@@ -28377,9 +29685,12 @@
         <v>0.2835</v>
       </c>
       <c r="S436" s="1" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="T436" s="1" t="n">
         <v>0.2881</v>
       </c>
-      <c r="T436" s="1" t="n">
+      <c r="U436" s="1" t="n">
         <v>0.2818</v>
       </c>
     </row>
@@ -28441,9 +29752,12 @@
         <v>0.03884</v>
       </c>
       <c r="S437" s="1" t="n">
+        <v>0.03867</v>
+      </c>
+      <c r="T437" s="1" t="n">
         <v>0.03957</v>
       </c>
-      <c r="T437" s="1" t="n">
+      <c r="U437" s="1" t="n">
         <v>0.03814</v>
       </c>
     </row>
@@ -28505,9 +29819,12 @@
         <v>0.02405</v>
       </c>
       <c r="S438" s="1" t="n">
+        <v>0.02407</v>
+      </c>
+      <c r="T438" s="1" t="n">
         <v>0.02474</v>
       </c>
-      <c r="T438" s="1" t="n">
+      <c r="U438" s="1" t="n">
         <v>0.02405</v>
       </c>
     </row>
@@ -28569,9 +29886,12 @@
         <v>0.04403</v>
       </c>
       <c r="S439" s="1" t="n">
+        <v>0.04404</v>
+      </c>
+      <c r="T439" s="1" t="n">
         <v>0.04418</v>
       </c>
-      <c r="T439" s="1" t="n">
+      <c r="U439" s="1" t="n">
         <v>0.04401</v>
       </c>
     </row>
@@ -28633,9 +29953,12 @@
         <v>0.0005207</v>
       </c>
       <c r="S440" s="1" t="n">
+        <v>0.0005195</v>
+      </c>
+      <c r="T440" s="1" t="n">
         <v>0.0005258</v>
       </c>
-      <c r="T440" s="1" t="n">
+      <c r="U440" s="1" t="n">
         <v>0.0005171</v>
       </c>
     </row>
@@ -28697,9 +30020,12 @@
         <v>0.04511</v>
       </c>
       <c r="S441" s="1" t="n">
-        <v>0.04546</v>
+        <v>0.04581</v>
       </c>
       <c r="T441" s="1" t="n">
+        <v>0.04581</v>
+      </c>
+      <c r="U441" s="1" t="n">
         <v>0.04394</v>
       </c>
     </row>
@@ -28761,9 +30087,12 @@
         <v>0.000415</v>
       </c>
       <c r="S442" s="1" t="n">
+        <v>0.000415</v>
+      </c>
+      <c r="T442" s="1" t="n">
         <v>0.000416</v>
       </c>
-      <c r="T442" s="1" t="n">
+      <c r="U442" s="1" t="n">
         <v>0.00041</v>
       </c>
     </row>
@@ -28825,9 +30154,12 @@
         <v>0.09392</v>
       </c>
       <c r="S443" s="1" t="n">
+        <v>0.09428</v>
+      </c>
+      <c r="T443" s="1" t="n">
         <v>0.09826</v>
       </c>
-      <c r="T443" s="1" t="n">
+      <c r="U443" s="1" t="n">
         <v>0.09392</v>
       </c>
     </row>
@@ -28889,9 +30221,12 @@
         <v>2.286</v>
       </c>
       <c r="S444" s="1" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T444" s="1" t="n">
         <v>2.321</v>
       </c>
-      <c r="T444" s="1" t="n">
+      <c r="U444" s="1" t="n">
         <v>2.286</v>
       </c>
     </row>
@@ -28953,9 +30288,12 @@
         <v>0.2695</v>
       </c>
       <c r="S445" s="1" t="n">
+        <v>0.2705</v>
+      </c>
+      <c r="T445" s="1" t="n">
         <v>0.2741</v>
       </c>
-      <c r="T445" s="1" t="n">
+      <c r="U445" s="1" t="n">
         <v>0.2661</v>
       </c>
     </row>
@@ -29017,9 +30355,12 @@
         <v>0.0007378</v>
       </c>
       <c r="S446" s="1" t="n">
+        <v>0.000739</v>
+      </c>
+      <c r="T446" s="1" t="n">
         <v>0.0007577</v>
       </c>
-      <c r="T446" s="1" t="n">
+      <c r="U446" s="1" t="n">
         <v>0.0007376</v>
       </c>
     </row>
@@ -29081,9 +30422,12 @@
         <v>0.03861</v>
       </c>
       <c r="S447" s="1" t="n">
+        <v>0.03845</v>
+      </c>
+      <c r="T447" s="1" t="n">
         <v>0.03904</v>
       </c>
-      <c r="T447" s="1" t="n">
+      <c r="U447" s="1" t="n">
         <v>0.03807</v>
       </c>
     </row>
@@ -29145,9 +30489,12 @@
         <v>0.1771</v>
       </c>
       <c r="S448" s="1" t="n">
+        <v>0.1772</v>
+      </c>
+      <c r="T448" s="1" t="n">
         <v>0.1783</v>
       </c>
-      <c r="T448" s="1" t="n">
+      <c r="U448" s="1" t="n">
         <v>0.1755</v>
       </c>
     </row>
@@ -29209,9 +30556,12 @@
         <v>0.0429</v>
       </c>
       <c r="S449" s="1" t="n">
+        <v>0.04282</v>
+      </c>
+      <c r="T449" s="1" t="n">
         <v>0.04301</v>
       </c>
-      <c r="T449" s="1" t="n">
+      <c r="U449" s="1" t="n">
         <v>0.0426</v>
       </c>
     </row>
@@ -29273,9 +30623,12 @@
         <v>0.0001649</v>
       </c>
       <c r="S450" s="1" t="n">
+        <v>0.0001646</v>
+      </c>
+      <c r="T450" s="1" t="n">
         <v>0.0001654</v>
       </c>
-      <c r="T450" s="1" t="n">
+      <c r="U450" s="1" t="n">
         <v>0.0001632</v>
       </c>
     </row>
@@ -29337,9 +30690,12 @@
         <v>0.03697</v>
       </c>
       <c r="S451" s="1" t="n">
+        <v>0.03704</v>
+      </c>
+      <c r="T451" s="1" t="n">
         <v>0.03784</v>
       </c>
-      <c r="T451" s="1" t="n">
+      <c r="U451" s="1" t="n">
         <v>0.03697</v>
       </c>
     </row>
@@ -29401,9 +30757,12 @@
         <v>0.009679999999999999</v>
       </c>
       <c r="S452" s="1" t="n">
+        <v>0.00967</v>
+      </c>
+      <c r="T452" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="T452" s="1" t="n">
+      <c r="U452" s="1" t="n">
         <v>0.00966</v>
       </c>
     </row>
@@ -29465,10 +30824,13 @@
         <v>0.0679</v>
       </c>
       <c r="S453" s="1" t="n">
+        <v>0.06776</v>
+      </c>
+      <c r="T453" s="1" t="n">
         <v>0.06816</v>
       </c>
-      <c r="T453" s="1" t="n">
-        <v>0.06782000000000001</v>
+      <c r="U453" s="1" t="n">
+        <v>0.06776</v>
       </c>
     </row>
     <row r="454">
@@ -29529,9 +30891,12 @@
         <v>0.007494</v>
       </c>
       <c r="S454" s="1" t="n">
+        <v>0.007503</v>
+      </c>
+      <c r="T454" s="1" t="n">
         <v>0.007613</v>
       </c>
-      <c r="T454" s="1" t="n">
+      <c r="U454" s="1" t="n">
         <v>0.007478</v>
       </c>
     </row>
@@ -29593,10 +30958,13 @@
         <v>0.003273</v>
       </c>
       <c r="S455" s="1" t="n">
+        <v>0.003267</v>
+      </c>
+      <c r="T455" s="1" t="n">
         <v>0.003377</v>
       </c>
-      <c r="T455" s="1" t="n">
-        <v>0.003269</v>
+      <c r="U455" s="1" t="n">
+        <v>0.003267</v>
       </c>
     </row>
     <row r="456">
@@ -29657,9 +31025,12 @@
         <v>0.001846</v>
       </c>
       <c r="S456" s="1" t="n">
+        <v>0.001843</v>
+      </c>
+      <c r="T456" s="1" t="n">
         <v>0.001875</v>
       </c>
-      <c r="T456" s="1" t="n">
+      <c r="U456" s="1" t="n">
         <v>0.00184</v>
       </c>
     </row>
@@ -29721,9 +31092,12 @@
         <v>0.000175</v>
       </c>
       <c r="S457" s="1" t="n">
+        <v>0.0001752</v>
+      </c>
+      <c r="T457" s="1" t="n">
         <v>0.0001767</v>
       </c>
-      <c r="T457" s="1" t="n">
+      <c r="U457" s="1" t="n">
         <v>0.0001745</v>
       </c>
     </row>
@@ -29785,9 +31159,12 @@
         <v>0.0003889</v>
       </c>
       <c r="S458" s="1" t="n">
+        <v>0.0003878</v>
+      </c>
+      <c r="T458" s="1" t="n">
         <v>0.0003916</v>
       </c>
-      <c r="T458" s="1" t="n">
+      <c r="U458" s="1" t="n">
         <v>0.0003873</v>
       </c>
     </row>
@@ -29849,9 +31226,12 @@
         <v>0.01393</v>
       </c>
       <c r="S459" s="1" t="n">
+        <v>0.01393</v>
+      </c>
+      <c r="T459" s="1" t="n">
         <v>0.01413</v>
       </c>
-      <c r="T459" s="1" t="n">
+      <c r="U459" s="1" t="n">
         <v>0.01391</v>
       </c>
     </row>
@@ -29913,9 +31293,12 @@
         <v>0.04578</v>
       </c>
       <c r="S460" s="1" t="n">
+        <v>0.0458</v>
+      </c>
+      <c r="T460" s="1" t="n">
         <v>0.04586</v>
       </c>
-      <c r="T460" s="1" t="n">
+      <c r="U460" s="1" t="n">
         <v>0.04518</v>
       </c>
     </row>
@@ -29977,9 +31360,12 @@
         <v>0.2837</v>
       </c>
       <c r="S461" s="1" t="n">
-        <v>0.2839</v>
+        <v>0.2842</v>
       </c>
       <c r="T461" s="1" t="n">
+        <v>0.2842</v>
+      </c>
+      <c r="U461" s="1" t="n">
         <v>0.2809</v>
       </c>
     </row>
@@ -30041,9 +31427,12 @@
         <v>0.006224</v>
       </c>
       <c r="S462" s="1" t="n">
+        <v>0.006225</v>
+      </c>
+      <c r="T462" s="1" t="n">
         <v>0.006312</v>
       </c>
-      <c r="T462" s="1" t="n">
+      <c r="U462" s="1" t="n">
         <v>0.00622</v>
       </c>
     </row>
@@ -30105,9 +31494,12 @@
         <v>0.007075</v>
       </c>
       <c r="S463" s="1" t="n">
+        <v>0.00706</v>
+      </c>
+      <c r="T463" s="1" t="n">
         <v>0.007088</v>
       </c>
-      <c r="T463" s="1" t="n">
+      <c r="U463" s="1" t="n">
         <v>0.006999</v>
       </c>
     </row>
@@ -30172,6 +31564,9 @@
         <v>0.289</v>
       </c>
       <c r="T464" s="1" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="U464" s="1" t="n">
         <v>0.2853</v>
       </c>
     </row>
@@ -30233,9 +31628,12 @@
         <v>0.08051999999999999</v>
       </c>
       <c r="S465" s="1" t="n">
+        <v>0.08101</v>
+      </c>
+      <c r="T465" s="1" t="n">
         <v>0.08183</v>
       </c>
-      <c r="T465" s="1" t="n">
+      <c r="U465" s="1" t="n">
         <v>0.08047</v>
       </c>
     </row>
@@ -30297,9 +31695,12 @@
         <v>0.6362</v>
       </c>
       <c r="S466" s="1" t="n">
+        <v>0.6385</v>
+      </c>
+      <c r="T466" s="1" t="n">
         <v>0.6392</v>
       </c>
-      <c r="T466" s="1" t="n">
+      <c r="U466" s="1" t="n">
         <v>0.6318</v>
       </c>
     </row>
@@ -30361,9 +31762,12 @@
         <v>0.01474</v>
       </c>
       <c r="S467" s="1" t="n">
+        <v>0.01474</v>
+      </c>
+      <c r="T467" s="1" t="n">
         <v>0.01499</v>
       </c>
-      <c r="T467" s="1" t="n">
+      <c r="U467" s="1" t="n">
         <v>0.0147</v>
       </c>
     </row>
@@ -30425,9 +31829,12 @@
         <v>0.034</v>
       </c>
       <c r="S468" s="1" t="n">
+        <v>0.03425</v>
+      </c>
+      <c r="T468" s="1" t="n">
         <v>0.03468</v>
       </c>
-      <c r="T468" s="1" t="n">
+      <c r="U468" s="1" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -30489,9 +31896,12 @@
         <v>0.1618</v>
       </c>
       <c r="S469" s="1" t="n">
+        <v>0.1618</v>
+      </c>
+      <c r="T469" s="1" t="n">
         <v>0.1652</v>
       </c>
-      <c r="T469" s="1" t="n">
+      <c r="U469" s="1" t="n">
         <v>0.1613</v>
       </c>
     </row>
@@ -30553,9 +31963,12 @@
         <v>0.409</v>
       </c>
       <c r="S470" s="1" t="n">
+        <v>0.4096</v>
+      </c>
+      <c r="T470" s="1" t="n">
         <v>0.4151</v>
       </c>
-      <c r="T470" s="1" t="n">
+      <c r="U470" s="1" t="n">
         <v>0.408</v>
       </c>
     </row>
@@ -30617,9 +32030,12 @@
         <v>0.06876</v>
       </c>
       <c r="S471" s="1" t="n">
+        <v>0.06877999999999999</v>
+      </c>
+      <c r="T471" s="1" t="n">
         <v>0.07015</v>
       </c>
-      <c r="T471" s="1" t="n">
+      <c r="U471" s="1" t="n">
         <v>0.06854</v>
       </c>
     </row>
@@ -30681,9 +32097,12 @@
         <v>0.06549000000000001</v>
       </c>
       <c r="S472" s="1" t="n">
+        <v>0.06553</v>
+      </c>
+      <c r="T472" s="1" t="n">
         <v>0.06773999999999999</v>
       </c>
-      <c r="T472" s="1" t="n">
+      <c r="U472" s="1" t="n">
         <v>0.06541</v>
       </c>
     </row>
@@ -30745,9 +32164,12 @@
         <v>0.0162</v>
       </c>
       <c r="S473" s="1" t="n">
+        <v>0.01624</v>
+      </c>
+      <c r="T473" s="1" t="n">
         <v>0.01647</v>
       </c>
-      <c r="T473" s="1" t="n">
+      <c r="U473" s="1" t="n">
         <v>0.0162</v>
       </c>
     </row>
@@ -30809,9 +32231,12 @@
         <v>0.2067</v>
       </c>
       <c r="S474" s="1" t="n">
+        <v>0.2072</v>
+      </c>
+      <c r="T474" s="1" t="n">
         <v>0.2124</v>
       </c>
-      <c r="T474" s="1" t="n">
+      <c r="U474" s="1" t="n">
         <v>0.2061</v>
       </c>
     </row>
@@ -30873,9 +32298,12 @@
         <v>0.04183</v>
       </c>
       <c r="S475" s="1" t="n">
+        <v>0.04209</v>
+      </c>
+      <c r="T475" s="1" t="n">
         <v>0.04289</v>
       </c>
-      <c r="T475" s="1" t="n">
+      <c r="U475" s="1" t="n">
         <v>0.04183</v>
       </c>
     </row>
@@ -30937,9 +32365,12 @@
         <v>1.56</v>
       </c>
       <c r="S476" s="1" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="T476" s="1" t="n">
         <v>1.578</v>
       </c>
-      <c r="T476" s="1" t="n">
+      <c r="U476" s="1" t="n">
         <v>1.557</v>
       </c>
     </row>
@@ -31001,9 +32432,12 @@
         <v>0.1005</v>
       </c>
       <c r="S477" s="1" t="n">
+        <v>0.1005</v>
+      </c>
+      <c r="T477" s="1" t="n">
         <v>0.1019</v>
       </c>
-      <c r="T477" s="1" t="n">
+      <c r="U477" s="1" t="n">
         <v>0.1002</v>
       </c>
     </row>
@@ -31065,9 +32499,12 @@
         <v>0.001155</v>
       </c>
       <c r="S478" s="1" t="n">
+        <v>0.001157</v>
+      </c>
+      <c r="T478" s="1" t="n">
         <v>0.001162</v>
       </c>
-      <c r="T478" s="1" t="n">
+      <c r="U478" s="1" t="n">
         <v>0.00115</v>
       </c>
     </row>
@@ -31129,9 +32566,12 @@
         <v>0.1439</v>
       </c>
       <c r="S479" s="1" t="n">
+        <v>0.1437</v>
+      </c>
+      <c r="T479" s="1" t="n">
         <v>0.148</v>
       </c>
-      <c r="T479" s="1" t="n">
+      <c r="U479" s="1" t="n">
         <v>0.1433</v>
       </c>
     </row>
@@ -31193,9 +32633,12 @@
         <v>0.001842</v>
       </c>
       <c r="S480" s="1" t="n">
-        <v>0.001842</v>
+        <v>0.001861</v>
       </c>
       <c r="T480" s="1" t="n">
+        <v>0.001861</v>
+      </c>
+      <c r="U480" s="1" t="n">
         <v>0.001719</v>
       </c>
     </row>
@@ -31257,9 +32700,12 @@
         <v>0.905</v>
       </c>
       <c r="S481" s="1" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="T481" s="1" t="n">
         <v>0.925</v>
       </c>
-      <c r="T481" s="1" t="n">
+      <c r="U481" s="1" t="n">
         <v>0.904</v>
       </c>
     </row>
@@ -31321,9 +32767,12 @@
         <v>0.13233</v>
       </c>
       <c r="S482" s="1" t="n">
+        <v>0.1326</v>
+      </c>
+      <c r="T482" s="1" t="n">
         <v>0.13673</v>
       </c>
-      <c r="T482" s="1" t="n">
+      <c r="U482" s="1" t="n">
         <v>0.13233</v>
       </c>
     </row>
@@ -31385,9 +32834,12 @@
         <v>0.04015</v>
       </c>
       <c r="S483" s="1" t="n">
+        <v>0.04015</v>
+      </c>
+      <c r="T483" s="1" t="n">
         <v>0.04063</v>
       </c>
-      <c r="T483" s="1" t="n">
+      <c r="U483" s="1" t="n">
         <v>0.04005</v>
       </c>
     </row>
@@ -31449,9 +32901,12 @@
         <v>0.3002</v>
       </c>
       <c r="S484" s="1" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="T484" s="1" t="n">
         <v>0.3137</v>
       </c>
-      <c r="T484" s="1" t="n">
+      <c r="U484" s="1" t="n">
         <v>0.2999</v>
       </c>
     </row>
@@ -31513,9 +32968,12 @@
         <v>0.05654</v>
       </c>
       <c r="S485" s="1" t="n">
+        <v>0.05653</v>
+      </c>
+      <c r="T485" s="1" t="n">
         <v>0.05709</v>
       </c>
-      <c r="T485" s="1" t="n">
+      <c r="U485" s="1" t="n">
         <v>0.05603</v>
       </c>
     </row>
@@ -31577,9 +33035,12 @@
         <v>0.00156</v>
       </c>
       <c r="S486" s="1" t="n">
+        <v>0.001561</v>
+      </c>
+      <c r="T486" s="1" t="n">
         <v>0.001579</v>
       </c>
-      <c r="T486" s="1" t="n">
+      <c r="U486" s="1" t="n">
         <v>0.001558</v>
       </c>
     </row>
@@ -31641,9 +33102,12 @@
         <v>0.06676</v>
       </c>
       <c r="S487" s="1" t="n">
+        <v>0.06691999999999999</v>
+      </c>
+      <c r="T487" s="1" t="n">
         <v>0.06766999999999999</v>
       </c>
-      <c r="T487" s="1" t="n">
+      <c r="U487" s="1" t="n">
         <v>0.06662</v>
       </c>
     </row>
@@ -31705,9 +33169,12 @@
         <v>0.1912</v>
       </c>
       <c r="S488" s="1" t="n">
+        <v>0.1914</v>
+      </c>
+      <c r="T488" s="1" t="n">
         <v>0.1953</v>
       </c>
-      <c r="T488" s="1" t="n">
+      <c r="U488" s="1" t="n">
         <v>0.1911</v>
       </c>
     </row>
@@ -31769,9 +33236,12 @@
         <v>0.04772</v>
       </c>
       <c r="S489" s="1" t="n">
+        <v>0.04782</v>
+      </c>
+      <c r="T489" s="1" t="n">
         <v>0.04837</v>
       </c>
-      <c r="T489" s="1" t="n">
+      <c r="U489" s="1" t="n">
         <v>0.04768</v>
       </c>
     </row>
@@ -31833,9 +33303,12 @@
         <v>0.1395</v>
       </c>
       <c r="S490" s="1" t="n">
+        <v>0.1399</v>
+      </c>
+      <c r="T490" s="1" t="n">
         <v>0.1401</v>
       </c>
-      <c r="T490" s="1" t="n">
+      <c r="U490" s="1" t="n">
         <v>0.1389</v>
       </c>
     </row>
@@ -31897,9 +33370,12 @@
         <v>0.02236</v>
       </c>
       <c r="S491" s="1" t="n">
+        <v>0.0224</v>
+      </c>
+      <c r="T491" s="1" t="n">
         <v>0.02281</v>
       </c>
-      <c r="T491" s="1" t="n">
+      <c r="U491" s="1" t="n">
         <v>0.02227</v>
       </c>
     </row>
@@ -31961,9 +33437,12 @@
         <v>0.007734</v>
       </c>
       <c r="S492" s="1" t="n">
+        <v>0.007771</v>
+      </c>
+      <c r="T492" s="1" t="n">
         <v>0.007929</v>
       </c>
-      <c r="T492" s="1" t="n">
+      <c r="U492" s="1" t="n">
         <v>0.007706</v>
       </c>
     </row>
@@ -32025,9 +33504,12 @@
         <v>0.0005932</v>
       </c>
       <c r="S493" s="1" t="n">
+        <v>0.0005932999999999999</v>
+      </c>
+      <c r="T493" s="1" t="n">
         <v>0.0005992</v>
       </c>
-      <c r="T493" s="1" t="n">
+      <c r="U493" s="1" t="n">
         <v>0.0005918</v>
       </c>
     </row>
@@ -32089,9 +33571,12 @@
         <v>3.026</v>
       </c>
       <c r="S494" s="1" t="n">
+        <v>3.027</v>
+      </c>
+      <c r="T494" s="1" t="n">
         <v>3.038</v>
       </c>
-      <c r="T494" s="1" t="n">
+      <c r="U494" s="1" t="n">
         <v>2.999</v>
       </c>
     </row>
@@ -32153,9 +33638,12 @@
         <v>0.05054</v>
       </c>
       <c r="S495" s="1" t="n">
+        <v>0.05061</v>
+      </c>
+      <c r="T495" s="1" t="n">
         <v>0.05131</v>
       </c>
-      <c r="T495" s="1" t="n">
+      <c r="U495" s="1" t="n">
         <v>0.05042</v>
       </c>
     </row>
@@ -32217,9 +33705,12 @@
         <v>0.006847</v>
       </c>
       <c r="S496" s="1" t="n">
+        <v>0.006851</v>
+      </c>
+      <c r="T496" s="1" t="n">
         <v>0.006886</v>
       </c>
-      <c r="T496" s="1" t="n">
+      <c r="U496" s="1" t="n">
         <v>0.006742</v>
       </c>
     </row>
@@ -32281,9 +33772,12 @@
         <v>1.306</v>
       </c>
       <c r="S497" s="1" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="T497" s="1" t="n">
         <v>1.31</v>
       </c>
-      <c r="T497" s="1" t="n">
+      <c r="U497" s="1" t="n">
         <v>1.299</v>
       </c>
     </row>
@@ -32345,9 +33839,12 @@
         <v>0.03912</v>
       </c>
       <c r="S498" s="1" t="n">
+        <v>0.03918</v>
+      </c>
+      <c r="T498" s="1" t="n">
         <v>0.04018</v>
       </c>
-      <c r="T498" s="1" t="n">
+      <c r="U498" s="1" t="n">
         <v>0.03892</v>
       </c>
     </row>
@@ -32409,9 +33906,12 @@
         <v>0.04096</v>
       </c>
       <c r="S499" s="1" t="n">
+        <v>0.04095</v>
+      </c>
+      <c r="T499" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="T499" s="1" t="n">
+      <c r="U499" s="1" t="n">
         <v>0.04085</v>
       </c>
     </row>
@@ -32473,9 +33973,12 @@
         <v>0.00543</v>
       </c>
       <c r="S500" s="1" t="n">
+        <v>0.00545</v>
+      </c>
+      <c r="T500" s="1" t="n">
         <v>0.00549</v>
       </c>
-      <c r="T500" s="1" t="n">
+      <c r="U500" s="1" t="n">
         <v>0.00536</v>
       </c>
     </row>
@@ -32537,9 +34040,12 @@
         <v>0.03549</v>
       </c>
       <c r="S501" s="1" t="n">
+        <v>0.03559</v>
+      </c>
+      <c r="T501" s="1" t="n">
         <v>0.0364</v>
       </c>
-      <c r="T501" s="1" t="n">
+      <c r="U501" s="1" t="n">
         <v>0.03548</v>
       </c>
     </row>
@@ -32601,9 +34107,12 @@
         <v>0.07216</v>
       </c>
       <c r="S502" s="1" t="n">
+        <v>0.07226</v>
+      </c>
+      <c r="T502" s="1" t="n">
         <v>0.07342</v>
       </c>
-      <c r="T502" s="1" t="n">
+      <c r="U502" s="1" t="n">
         <v>0.07205</v>
       </c>
     </row>
@@ -32665,9 +34174,12 @@
         <v>0.0007427999999999999</v>
       </c>
       <c r="S503" s="1" t="n">
+        <v>0.0007441</v>
+      </c>
+      <c r="T503" s="1" t="n">
         <v>0.000755</v>
       </c>
-      <c r="T503" s="1" t="n">
+      <c r="U503" s="1" t="n">
         <v>0.0007412</v>
       </c>
     </row>
@@ -32732,6 +34244,9 @@
         <v>0.016034</v>
       </c>
       <c r="T504" s="1" t="n">
+        <v>0.016034</v>
+      </c>
+      <c r="U504" s="1" t="n">
         <v>0.015945</v>
       </c>
     </row>
@@ -32793,10 +34308,13 @@
         <v>0.00702</v>
       </c>
       <c r="S505" s="1" t="n">
+        <v>0.00701</v>
+      </c>
+      <c r="T505" s="1" t="n">
         <v>0.00713</v>
       </c>
-      <c r="T505" s="1" t="n">
-        <v>0.00702</v>
+      <c r="U505" s="1" t="n">
+        <v>0.00701</v>
       </c>
     </row>
     <row r="506">
@@ -32857,9 +34375,12 @@
         <v>0.0253</v>
       </c>
       <c r="S506" s="1" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="T506" s="1" t="n">
         <v>0.0257</v>
       </c>
-      <c r="T506" s="1" t="n">
+      <c r="U506" s="1" t="n">
         <v>0.0252</v>
       </c>
     </row>
@@ -32921,9 +34442,12 @@
         <v>0.001346</v>
       </c>
       <c r="S507" s="1" t="n">
+        <v>0.001353</v>
+      </c>
+      <c r="T507" s="1" t="n">
         <v>0.00136</v>
       </c>
-      <c r="T507" s="1" t="n">
+      <c r="U507" s="1" t="n">
         <v>0.001343</v>
       </c>
     </row>
@@ -32985,9 +34509,12 @@
         <v>0.2812</v>
       </c>
       <c r="S508" s="1" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="T508" s="1" t="n">
         <v>0.2837</v>
       </c>
-      <c r="T508" s="1" t="n">
+      <c r="U508" s="1" t="n">
         <v>0.2805</v>
       </c>
     </row>
@@ -33049,9 +34576,12 @@
         <v>0.1317</v>
       </c>
       <c r="S509" s="1" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="T509" s="1" t="n">
         <v>0.133</v>
       </c>
-      <c r="T509" s="1" t="n">
+      <c r="U509" s="1" t="n">
         <v>0.1314</v>
       </c>
     </row>
@@ -33113,9 +34643,12 @@
         <v>0.04904</v>
       </c>
       <c r="S510" s="1" t="n">
+        <v>0.04917</v>
+      </c>
+      <c r="T510" s="1" t="n">
         <v>0.04972</v>
       </c>
-      <c r="T510" s="1" t="n">
+      <c r="U510" s="1" t="n">
         <v>0.04883</v>
       </c>
     </row>
@@ -33177,10 +34710,13 @@
         <v>0.00271</v>
       </c>
       <c r="S511" s="1" t="n">
+        <v>0.0027</v>
+      </c>
+      <c r="T511" s="1" t="n">
         <v>0.00278</v>
       </c>
-      <c r="T511" s="1" t="n">
-        <v>0.00271</v>
+      <c r="U511" s="1" t="n">
+        <v>0.0027</v>
       </c>
     </row>
     <row r="512">
@@ -33241,9 +34777,12 @@
         <v>0.015051</v>
       </c>
       <c r="S512" s="1" t="n">
+        <v>0.015093</v>
+      </c>
+      <c r="T512" s="1" t="n">
         <v>0.015454</v>
       </c>
-      <c r="T512" s="1" t="n">
+      <c r="U512" s="1" t="n">
         <v>0.014989</v>
       </c>
     </row>
@@ -33305,9 +34844,12 @@
         <v>0.6919</v>
       </c>
       <c r="S513" s="1" t="n">
+        <v>0.6906</v>
+      </c>
+      <c r="T513" s="1" t="n">
         <v>0.6948</v>
       </c>
-      <c r="T513" s="1" t="n">
+      <c r="U513" s="1" t="n">
         <v>0.6899</v>
       </c>
     </row>
@@ -33369,9 +34911,12 @@
         <v>0.004496</v>
       </c>
       <c r="S514" s="1" t="n">
+        <v>0.004498</v>
+      </c>
+      <c r="T514" s="1" t="n">
         <v>0.004589</v>
       </c>
-      <c r="T514" s="1" t="n">
+      <c r="U514" s="1" t="n">
         <v>0.004471</v>
       </c>
     </row>
@@ -33433,9 +34978,12 @@
         <v>0.005026</v>
       </c>
       <c r="S515" s="1" t="n">
+        <v>0.005024</v>
+      </c>
+      <c r="T515" s="1" t="n">
         <v>0.005066</v>
       </c>
-      <c r="T515" s="1" t="n">
+      <c r="U515" s="1" t="n">
         <v>0.005008</v>
       </c>
     </row>
@@ -33497,9 +35045,12 @@
         <v>0.06335</v>
       </c>
       <c r="S516" s="1" t="n">
+        <v>0.06320000000000001</v>
+      </c>
+      <c r="T516" s="1" t="n">
         <v>0.06394</v>
       </c>
-      <c r="T516" s="1" t="n">
+      <c r="U516" s="1" t="n">
         <v>0.06320000000000001</v>
       </c>
     </row>
@@ -33561,9 +35112,12 @@
         <v>0.06551999999999999</v>
       </c>
       <c r="S517" s="1" t="n">
+        <v>0.06515</v>
+      </c>
+      <c r="T517" s="1" t="n">
         <v>0.06566</v>
       </c>
-      <c r="T517" s="1" t="n">
+      <c r="U517" s="1" t="n">
         <v>0.06401</v>
       </c>
     </row>
@@ -33625,9 +35179,12 @@
         <v>0.012</v>
       </c>
       <c r="S518" s="1" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="T518" s="1" t="n">
         <v>0.01219</v>
       </c>
-      <c r="T518" s="1" t="n">
+      <c r="U518" s="1" t="n">
         <v>0.01198</v>
       </c>
     </row>
@@ -33689,9 +35246,12 @@
         <v>0.0475</v>
       </c>
       <c r="S519" s="1" t="n">
+        <v>0.04742</v>
+      </c>
+      <c r="T519" s="1" t="n">
         <v>0.04795</v>
       </c>
-      <c r="T519" s="1" t="n">
+      <c r="U519" s="1" t="n">
         <v>0.04733</v>
       </c>
     </row>
@@ -33753,9 +35313,12 @@
         <v>0.04364</v>
       </c>
       <c r="S520" s="1" t="n">
+        <v>0.04369</v>
+      </c>
+      <c r="T520" s="1" t="n">
         <v>0.04411</v>
       </c>
-      <c r="T520" s="1" t="n">
+      <c r="U520" s="1" t="n">
         <v>0.04349</v>
       </c>
     </row>
@@ -33817,9 +35380,12 @@
         <v>0.008425999999999999</v>
       </c>
       <c r="S521" s="1" t="n">
+        <v>0.008404</v>
+      </c>
+      <c r="T521" s="1" t="n">
         <v>0.008609</v>
       </c>
-      <c r="T521" s="1" t="n">
+      <c r="U521" s="1" t="n">
         <v>0.008402</v>
       </c>
     </row>
@@ -33881,9 +35447,12 @@
         <v>0.08772000000000001</v>
       </c>
       <c r="S522" s="1" t="n">
+        <v>0.08779000000000001</v>
+      </c>
+      <c r="T522" s="1" t="n">
         <v>0.08992</v>
       </c>
-      <c r="T522" s="1" t="n">
+      <c r="U522" s="1" t="n">
         <v>0.08762</v>
       </c>
     </row>
@@ -33945,9 +35514,12 @@
         <v>0.00647</v>
       </c>
       <c r="S523" s="1" t="n">
+        <v>0.006467</v>
+      </c>
+      <c r="T523" s="1" t="n">
         <v>0.006492</v>
       </c>
-      <c r="T523" s="1" t="n">
+      <c r="U523" s="1" t="n">
         <v>0.006407</v>
       </c>
     </row>
@@ -34009,9 +35581,12 @@
         <v>0.01636</v>
       </c>
       <c r="S524" s="1" t="n">
+        <v>0.01636</v>
+      </c>
+      <c r="T524" s="1" t="n">
         <v>0.01671</v>
       </c>
-      <c r="T524" s="1" t="n">
+      <c r="U524" s="1" t="n">
         <v>0.01628</v>
       </c>
     </row>
@@ -34073,9 +35648,12 @@
         <v>0.01773</v>
       </c>
       <c r="S525" s="1" t="n">
+        <v>0.01776</v>
+      </c>
+      <c r="T525" s="1" t="n">
         <v>0.0181</v>
       </c>
-      <c r="T525" s="1" t="n">
+      <c r="U525" s="1" t="n">
         <v>0.01762</v>
       </c>
     </row>
@@ -34137,9 +35715,12 @@
         <v>0.07897999999999999</v>
       </c>
       <c r="S526" s="1" t="n">
+        <v>0.07883</v>
+      </c>
+      <c r="T526" s="1" t="n">
         <v>0.07968</v>
       </c>
-      <c r="T526" s="1" t="n">
+      <c r="U526" s="1" t="n">
         <v>0.07862</v>
       </c>
     </row>
@@ -34201,9 +35782,12 @@
         <v>0.01606</v>
       </c>
       <c r="S527" s="1" t="n">
+        <v>0.01606</v>
+      </c>
+      <c r="T527" s="1" t="n">
         <v>0.01652</v>
       </c>
-      <c r="T527" s="1" t="n">
+      <c r="U527" s="1" t="n">
         <v>0.01594</v>
       </c>
     </row>
@@ -34265,10 +35849,13 @@
         <v>0.004151</v>
       </c>
       <c r="S528" s="1" t="n">
+        <v>0.004126</v>
+      </c>
+      <c r="T528" s="1" t="n">
         <v>0.004198</v>
       </c>
-      <c r="T528" s="1" t="n">
-        <v>0.004151</v>
+      <c r="U528" s="1" t="n">
+        <v>0.004126</v>
       </c>
     </row>
     <row r="529">
@@ -34329,9 +35916,12 @@
         <v>0.003678</v>
       </c>
       <c r="S529" s="1" t="n">
+        <v>0.003676</v>
+      </c>
+      <c r="T529" s="1" t="n">
         <v>0.003753</v>
       </c>
-      <c r="T529" s="1" t="n">
+      <c r="U529" s="1" t="n">
         <v>0.003672</v>
       </c>
     </row>
@@ -34393,9 +35983,12 @@
         <v>1.328</v>
       </c>
       <c r="S530" s="1" t="n">
+        <v>1.326</v>
+      </c>
+      <c r="T530" s="1" t="n">
         <v>1.332</v>
       </c>
-      <c r="T530" s="1" t="n">
+      <c r="U530" s="1" t="n">
         <v>1.316</v>
       </c>
     </row>
@@ -34457,9 +36050,12 @@
         <v>0.4877</v>
       </c>
       <c r="S531" s="1" t="n">
+        <v>0.4879</v>
+      </c>
+      <c r="T531" s="1" t="n">
         <v>0.494</v>
       </c>
-      <c r="T531" s="1" t="n">
+      <c r="U531" s="1" t="n">
         <v>0.487</v>
       </c>
     </row>
@@ -34521,9 +36117,12 @@
         <v>0.03061</v>
       </c>
       <c r="S532" s="1" t="n">
+        <v>0.03058</v>
+      </c>
+      <c r="T532" s="1" t="n">
         <v>0.03091</v>
       </c>
-      <c r="T532" s="1" t="n">
+      <c r="U532" s="1" t="n">
         <v>0.03058</v>
       </c>
     </row>
@@ -34585,9 +36184,12 @@
         <v>0.1526</v>
       </c>
       <c r="S533" s="1" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="T533" s="1" t="n">
         <v>0.154</v>
       </c>
-      <c r="T533" s="1" t="n">
+      <c r="U533" s="1" t="n">
         <v>0.1524</v>
       </c>
     </row>
@@ -34649,9 +36251,12 @@
         <v>0.05359</v>
       </c>
       <c r="S534" s="1" t="n">
+        <v>0.0536</v>
+      </c>
+      <c r="T534" s="1" t="n">
         <v>0.05424</v>
       </c>
-      <c r="T534" s="1" t="n">
+      <c r="U534" s="1" t="n">
         <v>0.05344</v>
       </c>
     </row>
@@ -34713,9 +36318,12 @@
         <v>0.01486</v>
       </c>
       <c r="S535" s="1" t="n">
+        <v>0.01476</v>
+      </c>
+      <c r="T535" s="1" t="n">
         <v>0.01516</v>
       </c>
-      <c r="T535" s="1" t="n">
+      <c r="U535" s="1" t="n">
         <v>0.01476</v>
       </c>
     </row>
@@ -34777,9 +36385,12 @@
         <v>0.05863</v>
       </c>
       <c r="S536" s="1" t="n">
+        <v>0.05868</v>
+      </c>
+      <c r="T536" s="1" t="n">
         <v>0.05909</v>
       </c>
-      <c r="T536" s="1" t="n">
+      <c r="U536" s="1" t="n">
         <v>0.0581</v>
       </c>
     </row>
@@ -34841,9 +36452,12 @@
         <v>0.05484</v>
       </c>
       <c r="S537" s="1" t="n">
+        <v>0.05478</v>
+      </c>
+      <c r="T537" s="1" t="n">
         <v>0.05508</v>
       </c>
-      <c r="T537" s="1" t="n">
+      <c r="U537" s="1" t="n">
         <v>0.05476</v>
       </c>
     </row>
@@ -34905,9 +36519,12 @@
         <v>0.1058</v>
       </c>
       <c r="S538" s="1" t="n">
+        <v>0.1059</v>
+      </c>
+      <c r="T538" s="1" t="n">
         <v>0.1076</v>
       </c>
-      <c r="T538" s="1" t="n">
+      <c r="U538" s="1" t="n">
         <v>0.1057</v>
       </c>
     </row>
@@ -34969,9 +36586,12 @@
         <v>0.01265</v>
       </c>
       <c r="S539" s="1" t="n">
+        <v>0.01269</v>
+      </c>
+      <c r="T539" s="1" t="n">
         <v>0.01296</v>
       </c>
-      <c r="T539" s="1" t="n">
+      <c r="U539" s="1" t="n">
         <v>0.01265</v>
       </c>
     </row>
@@ -35033,9 +36653,12 @@
         <v>0.1723</v>
       </c>
       <c r="S540" s="1" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="T540" s="1" t="n">
         <v>0.1765</v>
       </c>
-      <c r="T540" s="1" t="n">
+      <c r="U540" s="1" t="n">
         <v>0.1723</v>
       </c>
     </row>
@@ -35097,9 +36720,12 @@
         <v>0.123</v>
       </c>
       <c r="S541" s="1" t="n">
+        <v>0.1231</v>
+      </c>
+      <c r="T541" s="1" t="n">
         <v>0.1239</v>
       </c>
-      <c r="T541" s="1" t="n">
+      <c r="U541" s="1" t="n">
         <v>0.1225</v>
       </c>
     </row>
@@ -35161,9 +36787,12 @@
         <v>0.02484</v>
       </c>
       <c r="S542" s="1" t="n">
+        <v>0.02485</v>
+      </c>
+      <c r="T542" s="1" t="n">
         <v>0.0251</v>
       </c>
-      <c r="T542" s="1" t="n">
+      <c r="U542" s="1" t="n">
         <v>0.02478</v>
       </c>
     </row>
@@ -35225,9 +36854,12 @@
         <v>0.05858</v>
       </c>
       <c r="S543" s="1" t="n">
+        <v>0.05862</v>
+      </c>
+      <c r="T543" s="1" t="n">
         <v>0.059</v>
       </c>
-      <c r="T543" s="1" t="n">
+      <c r="U543" s="1" t="n">
         <v>0.05852</v>
       </c>
     </row>

--- a/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
+++ b/records/weeks/2026-03-09_2026-03-15/2026-03-14.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U543"/>
+  <dimension ref="A1:V543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -438,8 +438,9 @@
     <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,10 +541,15 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
+          <t>price_04:30</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
           <t>day_high</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>day_low</t>
         </is>
@@ -610,9 +616,12 @@
         <v>71313</v>
       </c>
       <c r="T2" s="1" t="n">
+        <v>71260.7</v>
+      </c>
+      <c r="U2" s="1" t="n">
         <v>72052.5</v>
       </c>
-      <c r="U2" s="1" t="n">
+      <c r="V2" s="1" t="n">
         <v>70995.10000000001</v>
       </c>
     </row>
@@ -677,9 +686,12 @@
         <v>2108.32</v>
       </c>
       <c r="T3" s="1" t="n">
+        <v>2109.27</v>
+      </c>
+      <c r="U3" s="1" t="n">
         <v>2135.64</v>
       </c>
-      <c r="U3" s="1" t="n">
+      <c r="V3" s="1" t="n">
         <v>2098.64</v>
       </c>
     </row>
@@ -744,9 +756,12 @@
         <v>88.83</v>
       </c>
       <c r="T4" s="1" t="n">
+        <v>88.84999999999999</v>
+      </c>
+      <c r="U4" s="1" t="n">
         <v>89.84</v>
       </c>
-      <c r="U4" s="1" t="n">
+      <c r="V4" s="1" t="n">
         <v>88.7</v>
       </c>
     </row>
@@ -811,9 +826,12 @@
         <v>3.846</v>
       </c>
       <c r="T5" s="1" t="n">
+        <v>3.877</v>
+      </c>
+      <c r="U5" s="1" t="n">
         <v>3.888</v>
       </c>
-      <c r="U5" s="1" t="n">
+      <c r="V5" s="1" t="n">
         <v>3.766</v>
       </c>
     </row>
@@ -878,9 +896,12 @@
         <v>1.4007</v>
       </c>
       <c r="T6" s="1" t="n">
+        <v>1.403</v>
+      </c>
+      <c r="U6" s="1" t="n">
         <v>1.4097</v>
       </c>
-      <c r="U6" s="1" t="n">
+      <c r="V6" s="1" t="n">
         <v>1.3931</v>
       </c>
     </row>
@@ -945,9 +966,12 @@
         <v>0.0964</v>
       </c>
       <c r="T7" s="1" t="n">
+        <v>0.09626999999999999</v>
+      </c>
+      <c r="U7" s="1" t="n">
         <v>0.09828000000000001</v>
       </c>
-      <c r="U7" s="1" t="n">
+      <c r="V7" s="1" t="n">
         <v>0.09572</v>
       </c>
     </row>
@@ -1012,9 +1036,12 @@
         <v>0.014261</v>
       </c>
       <c r="T8" s="1" t="n">
+        <v>0.014167</v>
+      </c>
+      <c r="U8" s="1" t="n">
         <v>0.014819</v>
       </c>
-      <c r="U8" s="1" t="n">
+      <c r="V8" s="1" t="n">
         <v>0.014064</v>
       </c>
     </row>
@@ -1079,9 +1106,12 @@
         <v>658.15</v>
       </c>
       <c r="T9" s="1" t="n">
+        <v>657.42</v>
+      </c>
+      <c r="U9" s="1" t="n">
         <v>663.25</v>
       </c>
-      <c r="U9" s="1" t="n">
+      <c r="V9" s="1" t="n">
         <v>655.72</v>
       </c>
     </row>
@@ -1146,9 +1176,12 @@
         <v>20.4</v>
       </c>
       <c r="T10" s="1" t="n">
-        <v>20.4</v>
+        <v>20.464</v>
       </c>
       <c r="U10" s="1" t="n">
+        <v>20.464</v>
+      </c>
+      <c r="V10" s="1" t="n">
         <v>18.938</v>
       </c>
     </row>
@@ -1213,9 +1246,12 @@
         <v>0.0033967</v>
       </c>
       <c r="T11" s="1" t="n">
+        <v>0.0033968</v>
+      </c>
+      <c r="U11" s="1" t="n">
         <v>0.0034884</v>
       </c>
-      <c r="U11" s="1" t="n">
+      <c r="V11" s="1" t="n">
         <v>0.0033816</v>
       </c>
     </row>
@@ -1280,9 +1316,12 @@
         <v>36.721</v>
       </c>
       <c r="T12" s="1" t="n">
-        <v>36.735</v>
+        <v>36.869</v>
       </c>
       <c r="U12" s="1" t="n">
+        <v>36.869</v>
+      </c>
+      <c r="V12" s="1" t="n">
         <v>36.163</v>
       </c>
     </row>
@@ -1347,10 +1386,13 @@
         <v>211.82</v>
       </c>
       <c r="T13" s="1" t="n">
+        <v>211.7</v>
+      </c>
+      <c r="U13" s="1" t="n">
         <v>214.83</v>
       </c>
-      <c r="U13" s="1" t="n">
-        <v>211.82</v>
+      <c r="V13" s="1" t="n">
+        <v>211.7</v>
       </c>
     </row>
     <row r="14">
@@ -1414,9 +1456,12 @@
         <v>0.0011252</v>
       </c>
       <c r="T14" s="1" t="n">
+        <v>0.0011316</v>
+      </c>
+      <c r="U14" s="1" t="n">
         <v>0.0011389</v>
       </c>
-      <c r="U14" s="1" t="n">
+      <c r="V14" s="1" t="n">
         <v>0.0011136</v>
       </c>
     </row>
@@ -1481,9 +1526,12 @@
         <v>0.34247</v>
       </c>
       <c r="T15" s="1" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="U15" s="1" t="n">
         <v>0.34247</v>
       </c>
-      <c r="U15" s="1" t="n">
+      <c r="V15" s="1" t="n">
         <v>0.28497</v>
       </c>
     </row>
@@ -1548,9 +1596,12 @@
         <v>231.28</v>
       </c>
       <c r="T16" s="1" t="n">
+        <v>231.42</v>
+      </c>
+      <c r="U16" s="1" t="n">
         <v>237.1</v>
       </c>
-      <c r="U16" s="1" t="n">
+      <c r="V16" s="1" t="n">
         <v>229.42</v>
       </c>
     </row>
@@ -1615,9 +1666,12 @@
         <v>1.0018</v>
       </c>
       <c r="T17" s="1" t="n">
+        <v>1.0017</v>
+      </c>
+      <c r="U17" s="1" t="n">
         <v>1.0151</v>
       </c>
-      <c r="U17" s="1" t="n">
+      <c r="V17" s="1" t="n">
         <v>0.9963</v>
       </c>
     </row>
@@ -1682,9 +1736,12 @@
         <v>0.2671</v>
       </c>
       <c r="T18" s="1" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="U18" s="1" t="n">
         <v>0.2725</v>
       </c>
-      <c r="U18" s="1" t="n">
+      <c r="V18" s="1" t="n">
         <v>0.2664</v>
       </c>
     </row>
@@ -1749,9 +1806,12 @@
         <v>9.784000000000001</v>
       </c>
       <c r="T19" s="1" t="n">
+        <v>9.776</v>
+      </c>
+      <c r="U19" s="1" t="n">
         <v>9.906000000000001</v>
       </c>
-      <c r="U19" s="1" t="n">
+      <c r="V19" s="1" t="n">
         <v>9.747999999999999</v>
       </c>
     </row>
@@ -1816,10 +1876,13 @@
         <v>5018.76</v>
       </c>
       <c r="T20" s="1" t="n">
+        <v>5015.33</v>
+      </c>
+      <c r="U20" s="1" t="n">
         <v>5059.14</v>
       </c>
-      <c r="U20" s="1" t="n">
-        <v>5018.76</v>
+      <c r="V20" s="1" t="n">
+        <v>5015.33</v>
       </c>
     </row>
     <row r="21">
@@ -1883,9 +1946,12 @@
         <v>463.74</v>
       </c>
       <c r="T21" s="1" t="n">
+        <v>463.07</v>
+      </c>
+      <c r="U21" s="1" t="n">
         <v>464.66</v>
       </c>
-      <c r="U21" s="1" t="n">
+      <c r="V21" s="1" t="n">
         <v>462.36</v>
       </c>
     </row>
@@ -1950,10 +2016,13 @@
         <v>1.3733</v>
       </c>
       <c r="T22" s="1" t="n">
+        <v>1.3686</v>
+      </c>
+      <c r="U22" s="1" t="n">
         <v>1.4544</v>
       </c>
-      <c r="U22" s="1" t="n">
-        <v>1.3733</v>
+      <c r="V22" s="1" t="n">
+        <v>1.3686</v>
       </c>
     </row>
     <row r="23">
@@ -2017,9 +2086,12 @@
         <v>1.0662</v>
       </c>
       <c r="T23" s="1" t="n">
+        <v>1.0649</v>
+      </c>
+      <c r="U23" s="1" t="n">
         <v>1.1445</v>
       </c>
-      <c r="U23" s="1" t="n">
+      <c r="V23" s="1" t="n">
         <v>1.0136</v>
       </c>
     </row>
@@ -2084,9 +2156,12 @@
         <v>1.342</v>
       </c>
       <c r="T24" s="1" t="n">
+        <v>1.342</v>
+      </c>
+      <c r="U24" s="1" t="n">
         <v>1.37</v>
       </c>
-      <c r="U24" s="1" t="n">
+      <c r="V24" s="1" t="n">
         <v>1.342</v>
       </c>
     </row>
@@ -2151,9 +2226,12 @@
         <v>9.157</v>
       </c>
       <c r="T25" s="1" t="n">
+        <v>9.159000000000001</v>
+      </c>
+      <c r="U25" s="1" t="n">
         <v>9.297000000000001</v>
       </c>
-      <c r="U25" s="1" t="n">
+      <c r="V25" s="1" t="n">
         <v>9.113</v>
       </c>
     </row>
@@ -2218,9 +2296,12 @@
         <v>0.3704</v>
       </c>
       <c r="T26" s="1" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="U26" s="1" t="n">
         <v>0.3776</v>
       </c>
-      <c r="U26" s="1" t="n">
+      <c r="V26" s="1" t="n">
         <v>0.368</v>
       </c>
     </row>
@@ -2285,10 +2366,13 @@
         <v>0.872</v>
       </c>
       <c r="T27" s="1" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="U27" s="1" t="n">
         <v>0.897</v>
       </c>
-      <c r="U27" s="1" t="n">
-        <v>0.872</v>
+      <c r="V27" s="1" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="28">
@@ -2352,9 +2436,12 @@
         <v>1.839</v>
       </c>
       <c r="T28" s="1" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="U28" s="1" t="n">
         <v>1.844</v>
       </c>
-      <c r="U28" s="1" t="n">
+      <c r="V28" s="1" t="n">
         <v>1.787</v>
       </c>
     </row>
@@ -2419,9 +2506,12 @@
         <v>0.1092</v>
       </c>
       <c r="T29" s="1" t="n">
+        <v>0.1095</v>
+      </c>
+      <c r="U29" s="1" t="n">
         <v>0.1121</v>
       </c>
-      <c r="U29" s="1" t="n">
+      <c r="V29" s="1" t="n">
         <v>0.1089</v>
       </c>
     </row>
@@ -2486,9 +2576,12 @@
         <v>0.002017</v>
       </c>
       <c r="T30" s="1" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="U30" s="1" t="n">
         <v>0.002065</v>
       </c>
-      <c r="U30" s="1" t="n">
+      <c r="V30" s="1" t="n">
         <v>0.002011</v>
       </c>
     </row>
@@ -2553,10 +2646,13 @@
         <v>1.461</v>
       </c>
       <c r="T31" s="1" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U31" s="1" t="n">
         <v>1.511</v>
       </c>
-      <c r="U31" s="1" t="n">
-        <v>1.461</v>
+      <c r="V31" s="1" t="n">
+        <v>1.46</v>
       </c>
     </row>
     <row r="32">
@@ -2620,9 +2716,12 @@
         <v>0.1776</v>
       </c>
       <c r="T32" s="1" t="n">
+        <v>0.1774</v>
+      </c>
+      <c r="U32" s="1" t="n">
         <v>0.1792</v>
       </c>
-      <c r="U32" s="1" t="n">
+      <c r="V32" s="1" t="n">
         <v>0.1739</v>
       </c>
     </row>
@@ -2687,9 +2786,12 @@
         <v>0.1035</v>
       </c>
       <c r="T33" s="1" t="n">
+        <v>0.1038</v>
+      </c>
+      <c r="U33" s="1" t="n">
         <v>0.1058</v>
       </c>
-      <c r="U33" s="1" t="n">
+      <c r="V33" s="1" t="n">
         <v>0.1035</v>
       </c>
     </row>
@@ -2754,9 +2856,12 @@
         <v>113.21</v>
       </c>
       <c r="T34" s="1" t="n">
+        <v>113.28</v>
+      </c>
+      <c r="U34" s="1" t="n">
         <v>114.6</v>
       </c>
-      <c r="U34" s="1" t="n">
+      <c r="V34" s="1" t="n">
         <v>112.49</v>
       </c>
     </row>
@@ -2821,9 +2926,12 @@
         <v>6.759</v>
       </c>
       <c r="T35" s="1" t="n">
+        <v>6.812</v>
+      </c>
+      <c r="U35" s="1" t="n">
         <v>6.936</v>
       </c>
-      <c r="U35" s="1" t="n">
+      <c r="V35" s="1" t="n">
         <v>6.587</v>
       </c>
     </row>
@@ -2888,9 +2996,12 @@
         <v>0.017591</v>
       </c>
       <c r="T36" s="1" t="n">
+        <v>0.017562</v>
+      </c>
+      <c r="U36" s="1" t="n">
         <v>0.017668</v>
       </c>
-      <c r="U36" s="1" t="n">
+      <c r="V36" s="1" t="n">
         <v>0.016815</v>
       </c>
     </row>
@@ -2955,9 +3066,12 @@
         <v>0.3606</v>
       </c>
       <c r="T37" s="1" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="U37" s="1" t="n">
         <v>0.3687</v>
       </c>
-      <c r="U37" s="1" t="n">
+      <c r="V37" s="1" t="n">
         <v>0.3595</v>
       </c>
     </row>
@@ -3022,9 +3136,12 @@
         <v>55.65</v>
       </c>
       <c r="T38" s="1" t="n">
+        <v>55.65</v>
+      </c>
+      <c r="U38" s="1" t="n">
         <v>55.79</v>
       </c>
-      <c r="U38" s="1" t="n">
+      <c r="V38" s="1" t="n">
         <v>55.3</v>
       </c>
     </row>
@@ -3089,10 +3206,13 @@
         <v>0.5732</v>
       </c>
       <c r="T39" s="1" t="n">
+        <v>0.5717</v>
+      </c>
+      <c r="U39" s="1" t="n">
         <v>0.61856</v>
       </c>
-      <c r="U39" s="1" t="n">
-        <v>0.5732</v>
+      <c r="V39" s="1" t="n">
+        <v>0.5717</v>
       </c>
     </row>
     <row r="40">
@@ -3156,9 +3276,12 @@
         <v>4.028</v>
       </c>
       <c r="T40" s="1" t="n">
+        <v>4.023</v>
+      </c>
+      <c r="U40" s="1" t="n">
         <v>4.096</v>
       </c>
-      <c r="U40" s="1" t="n">
+      <c r="V40" s="1" t="n">
         <v>4.017</v>
       </c>
     </row>
@@ -3223,9 +3346,12 @@
         <v>0.04892</v>
       </c>
       <c r="T41" s="1" t="n">
+        <v>0.04892</v>
+      </c>
+      <c r="U41" s="1" t="n">
         <v>0.0513</v>
       </c>
-      <c r="U41" s="1" t="n">
+      <c r="V41" s="1" t="n">
         <v>0.04892</v>
       </c>
     </row>
@@ -3290,9 +3416,12 @@
         <v>0.7005</v>
       </c>
       <c r="T42" s="1" t="n">
+        <v>0.7022</v>
+      </c>
+      <c r="U42" s="1" t="n">
         <v>0.7066</v>
       </c>
-      <c r="U42" s="1" t="n">
+      <c r="V42" s="1" t="n">
         <v>0.6995</v>
       </c>
     </row>
@@ -3357,10 +3486,13 @@
         <v>0.2279</v>
       </c>
       <c r="T43" s="1" t="n">
+        <v>0.22713</v>
+      </c>
+      <c r="U43" s="1" t="n">
         <v>0.2383</v>
       </c>
-      <c r="U43" s="1" t="n">
-        <v>0.22771</v>
+      <c r="V43" s="1" t="n">
+        <v>0.22713</v>
       </c>
     </row>
     <row r="44">
@@ -3424,9 +3556,12 @@
         <v>0.35992</v>
       </c>
       <c r="T44" s="1" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="U44" s="1" t="n">
         <v>0.35992</v>
       </c>
-      <c r="U44" s="1" t="n">
+      <c r="V44" s="1" t="n">
         <v>0.35261</v>
       </c>
     </row>
@@ -3491,9 +3626,12 @@
         <v>0.1687</v>
       </c>
       <c r="T45" s="1" t="n">
+        <v>0.1688</v>
+      </c>
+      <c r="U45" s="1" t="n">
         <v>0.1734</v>
       </c>
-      <c r="U45" s="1" t="n">
+      <c r="V45" s="1" t="n">
         <v>0.1682</v>
       </c>
     </row>
@@ -3558,9 +3696,12 @@
         <v>0.0261</v>
       </c>
       <c r="T46" s="1" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="U46" s="1" t="n">
         <v>0.0266</v>
       </c>
-      <c r="U46" s="1" t="n">
+      <c r="V46" s="1" t="n">
         <v>0.0258</v>
       </c>
     </row>
@@ -3625,9 +3766,12 @@
         <v>0.005965</v>
       </c>
       <c r="T47" s="1" t="n">
+        <v>0.005967</v>
+      </c>
+      <c r="U47" s="1" t="n">
         <v>0.006059</v>
       </c>
-      <c r="U47" s="1" t="n">
+      <c r="V47" s="1" t="n">
         <v>0.00594</v>
       </c>
     </row>
@@ -3692,9 +3836,12 @@
         <v>0.007383</v>
       </c>
       <c r="T48" s="1" t="n">
+        <v>0.007391</v>
+      </c>
+      <c r="U48" s="1" t="n">
         <v>0.007521</v>
       </c>
-      <c r="U48" s="1" t="n">
+      <c r="V48" s="1" t="n">
         <v>0.007343</v>
       </c>
     </row>
@@ -3759,9 +3906,12 @@
         <v>0.1097</v>
       </c>
       <c r="T49" s="1" t="n">
+        <v>0.1099</v>
+      </c>
+      <c r="U49" s="1" t="n">
         <v>0.1115</v>
       </c>
-      <c r="U49" s="1" t="n">
+      <c r="V49" s="1" t="n">
         <v>0.1077</v>
       </c>
     </row>
@@ -3826,9 +3976,12 @@
         <v>0.04211</v>
       </c>
       <c r="T50" s="1" t="n">
-        <v>0.04215</v>
+        <v>0.04222</v>
       </c>
       <c r="U50" s="1" t="n">
+        <v>0.04222</v>
+      </c>
+      <c r="V50" s="1" t="n">
         <v>0.04017</v>
       </c>
     </row>
@@ -3893,9 +4046,12 @@
         <v>0.1624</v>
       </c>
       <c r="T51" s="1" t="n">
+        <v>0.1614</v>
+      </c>
+      <c r="U51" s="1" t="n">
         <v>0.1671</v>
       </c>
-      <c r="U51" s="1" t="n">
+      <c r="V51" s="1" t="n">
         <v>0.1614</v>
       </c>
     </row>
@@ -3960,9 +4116,12 @@
         <v>0.00354</v>
       </c>
       <c r="T52" s="1" t="n">
+        <v>0.00354</v>
+      </c>
+      <c r="U52" s="1" t="n">
         <v>0.00357</v>
       </c>
-      <c r="U52" s="1" t="n">
+      <c r="V52" s="1" t="n">
         <v>0.0035</v>
       </c>
     </row>
@@ -4027,9 +4186,12 @@
         <v>2.618</v>
       </c>
       <c r="T53" s="1" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U53" s="1" t="n">
         <v>2.665</v>
       </c>
-      <c r="U53" s="1" t="n">
+      <c r="V53" s="1" t="n">
         <v>2.613</v>
       </c>
     </row>
@@ -4094,9 +4256,12 @@
         <v>0.006195</v>
       </c>
       <c r="T54" s="1" t="n">
+        <v>0.006193</v>
+      </c>
+      <c r="U54" s="1" t="n">
         <v>0.006309</v>
       </c>
-      <c r="U54" s="1" t="n">
+      <c r="V54" s="1" t="n">
         <v>0.006157</v>
       </c>
     </row>
@@ -4161,10 +4326,13 @@
         <v>0.02867</v>
       </c>
       <c r="T55" s="1" t="n">
+        <v>0.0283</v>
+      </c>
+      <c r="U55" s="1" t="n">
         <v>0.03019</v>
       </c>
-      <c r="U55" s="1" t="n">
-        <v>0.02867</v>
+      <c r="V55" s="1" t="n">
+        <v>0.0283</v>
       </c>
     </row>
     <row r="56">
@@ -4228,9 +4396,12 @@
         <v>0.7362</v>
       </c>
       <c r="T56" s="1" t="n">
+        <v>0.7342</v>
+      </c>
+      <c r="U56" s="1" t="n">
         <v>0.7513</v>
       </c>
-      <c r="U56" s="1" t="n">
+      <c r="V56" s="1" t="n">
         <v>0.7322</v>
       </c>
     </row>
@@ -4295,9 +4466,12 @@
         <v>0.1034</v>
       </c>
       <c r="T57" s="1" t="n">
+        <v>0.1034</v>
+      </c>
+      <c r="U57" s="1" t="n">
         <v>0.105</v>
       </c>
-      <c r="U57" s="1" t="n">
+      <c r="V57" s="1" t="n">
         <v>0.103</v>
       </c>
     </row>
@@ -4362,9 +4536,12 @@
         <v>0.9383</v>
       </c>
       <c r="T58" s="1" t="n">
+        <v>0.9369</v>
+      </c>
+      <c r="U58" s="1" t="n">
         <v>0.9622000000000001</v>
       </c>
-      <c r="U58" s="1" t="n">
+      <c r="V58" s="1" t="n">
         <v>0.9355</v>
       </c>
     </row>
@@ -4429,9 +4606,12 @@
         <v>0.08697000000000001</v>
       </c>
       <c r="T59" s="1" t="n">
+        <v>0.08691</v>
+      </c>
+      <c r="U59" s="1" t="n">
         <v>0.08826000000000001</v>
       </c>
-      <c r="U59" s="1" t="n">
+      <c r="V59" s="1" t="n">
         <v>0.08381</v>
       </c>
     </row>
@@ -4496,9 +4676,12 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="T60" s="1" t="n">
+        <v>0.07027</v>
+      </c>
+      <c r="U60" s="1" t="n">
         <v>0.0703</v>
       </c>
-      <c r="U60" s="1" t="n">
+      <c r="V60" s="1" t="n">
         <v>0.06900000000000001</v>
       </c>
     </row>
@@ -4563,9 +4746,12 @@
         <v>0.05467</v>
       </c>
       <c r="T61" s="1" t="n">
+        <v>0.05472</v>
+      </c>
+      <c r="U61" s="1" t="n">
         <v>0.05523</v>
       </c>
-      <c r="U61" s="1" t="n">
+      <c r="V61" s="1" t="n">
         <v>0.05439</v>
       </c>
     </row>
@@ -4630,9 +4816,12 @@
         <v>0.010624</v>
       </c>
       <c r="T62" s="1" t="n">
+        <v>0.010598</v>
+      </c>
+      <c r="U62" s="1" t="n">
         <v>0.010624</v>
       </c>
-      <c r="U62" s="1" t="n">
+      <c r="V62" s="1" t="n">
         <v>0.009387</v>
       </c>
     </row>
@@ -4700,6 +4889,9 @@
         <v>0.29207</v>
       </c>
       <c r="U63" s="1" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="V63" s="1" t="n">
         <v>0.28945</v>
       </c>
     </row>
@@ -4764,9 +4956,12 @@
         <v>0.07523000000000001</v>
       </c>
       <c r="T64" s="1" t="n">
+        <v>0.07452</v>
+      </c>
+      <c r="U64" s="1" t="n">
         <v>0.07613</v>
       </c>
-      <c r="U64" s="1" t="n">
+      <c r="V64" s="1" t="n">
         <v>0.06894</v>
       </c>
     </row>
@@ -4831,9 +5026,12 @@
         <v>0.3175</v>
       </c>
       <c r="T65" s="1" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="U65" s="1" t="n">
         <v>0.3186</v>
       </c>
-      <c r="U65" s="1" t="n">
+      <c r="V65" s="1" t="n">
         <v>0.3068</v>
       </c>
     </row>
@@ -4898,9 +5096,12 @@
         <v>0.16294</v>
       </c>
       <c r="T66" s="1" t="n">
+        <v>0.16283</v>
+      </c>
+      <c r="U66" s="1" t="n">
         <v>0.16461</v>
       </c>
-      <c r="U66" s="1" t="n">
+      <c r="V66" s="1" t="n">
         <v>0.1622</v>
       </c>
     </row>
@@ -4965,9 +5166,12 @@
         <v>0.12026</v>
       </c>
       <c r="T67" s="1" t="n">
+        <v>0.12022</v>
+      </c>
+      <c r="U67" s="1" t="n">
         <v>0.1203</v>
       </c>
-      <c r="U67" s="1" t="n">
+      <c r="V67" s="1" t="n">
         <v>0.11919</v>
       </c>
     </row>
@@ -5032,10 +5236,13 @@
         <v>0.09487</v>
       </c>
       <c r="T68" s="1" t="n">
+        <v>0.09474</v>
+      </c>
+      <c r="U68" s="1" t="n">
         <v>0.09734</v>
       </c>
-      <c r="U68" s="1" t="n">
-        <v>0.09487</v>
+      <c r="V68" s="1" t="n">
+        <v>0.09474</v>
       </c>
     </row>
     <row r="69">
@@ -5099,9 +5306,12 @@
         <v>0.1242</v>
       </c>
       <c r="T69" s="1" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="U69" s="1" t="n">
         <v>0.1262</v>
       </c>
-      <c r="U69" s="1" t="n">
+      <c r="V69" s="1" t="n">
         <v>0.1239</v>
       </c>
     </row>
@@ -5166,9 +5376,12 @@
         <v>8.513999999999999</v>
       </c>
       <c r="T70" s="1" t="n">
+        <v>8.52</v>
+      </c>
+      <c r="U70" s="1" t="n">
         <v>8.621</v>
       </c>
-      <c r="U70" s="1" t="n">
+      <c r="V70" s="1" t="n">
         <v>8.491</v>
       </c>
     </row>
@@ -5233,9 +5446,12 @@
         <v>0.238</v>
       </c>
       <c r="T71" s="1" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="U71" s="1" t="n">
         <v>0.241</v>
       </c>
-      <c r="U71" s="1" t="n">
+      <c r="V71" s="1" t="n">
         <v>0.238</v>
       </c>
     </row>
@@ -5300,9 +5516,12 @@
         <v>0.04969</v>
       </c>
       <c r="T72" s="1" t="n">
+        <v>0.04984</v>
+      </c>
+      <c r="U72" s="1" t="n">
         <v>0.05179</v>
       </c>
-      <c r="U72" s="1" t="n">
+      <c r="V72" s="1" t="n">
         <v>0.04969</v>
       </c>
     </row>
@@ -5367,9 +5586,12 @@
         <v>0.05046</v>
       </c>
       <c r="T73" s="1" t="n">
+        <v>0.05073</v>
+      </c>
+      <c r="U73" s="1" t="n">
         <v>0.05109</v>
       </c>
-      <c r="U73" s="1" t="n">
+      <c r="V73" s="1" t="n">
         <v>0.05013</v>
       </c>
     </row>
@@ -5434,9 +5656,12 @@
         <v>0.1243</v>
       </c>
       <c r="T74" s="1" t="n">
+        <v>0.1253</v>
+      </c>
+      <c r="U74" s="1" t="n">
         <v>0.1266</v>
       </c>
-      <c r="U74" s="1" t="n">
+      <c r="V74" s="1" t="n">
         <v>0.124</v>
       </c>
     </row>
@@ -5501,9 +5726,12 @@
         <v>0.04697</v>
       </c>
       <c r="T75" s="1" t="n">
+        <v>0.04668</v>
+      </c>
+      <c r="U75" s="1" t="n">
         <v>0.04726</v>
       </c>
-      <c r="U75" s="1" t="n">
+      <c r="V75" s="1" t="n">
         <v>0.04619</v>
       </c>
     </row>
@@ -5568,10 +5796,13 @@
         <v>0.06678000000000001</v>
       </c>
       <c r="T76" s="1" t="n">
+        <v>0.06668</v>
+      </c>
+      <c r="U76" s="1" t="n">
         <v>0.06786</v>
       </c>
-      <c r="U76" s="1" t="n">
-        <v>0.06678000000000001</v>
+      <c r="V76" s="1" t="n">
+        <v>0.06668</v>
       </c>
     </row>
     <row r="77">
@@ -5635,9 +5866,12 @@
         <v>0.13357</v>
       </c>
       <c r="T77" s="1" t="n">
+        <v>0.13299</v>
+      </c>
+      <c r="U77" s="1" t="n">
         <v>0.13357</v>
       </c>
-      <c r="U77" s="1" t="n">
+      <c r="V77" s="1" t="n">
         <v>0.12584</v>
       </c>
     </row>
@@ -5702,9 +5936,12 @@
         <v>0.1616</v>
       </c>
       <c r="T78" s="1" t="n">
+        <v>0.1617</v>
+      </c>
+      <c r="U78" s="1" t="n">
         <v>0.1653</v>
       </c>
-      <c r="U78" s="1" t="n">
+      <c r="V78" s="1" t="n">
         <v>0.1607</v>
       </c>
     </row>
@@ -5769,9 +6006,12 @@
         <v>0.02697</v>
       </c>
       <c r="T79" s="1" t="n">
+        <v>0.02695</v>
+      </c>
+      <c r="U79" s="1" t="n">
         <v>0.0276</v>
       </c>
-      <c r="U79" s="1" t="n">
+      <c r="V79" s="1" t="n">
         <v>0.02693</v>
       </c>
     </row>
@@ -5836,9 +6076,12 @@
         <v>359.36</v>
       </c>
       <c r="T80" s="1" t="n">
+        <v>358.73</v>
+      </c>
+      <c r="U80" s="1" t="n">
         <v>359.36</v>
       </c>
-      <c r="U80" s="1" t="n">
+      <c r="V80" s="1" t="n">
         <v>354.1</v>
       </c>
     </row>
@@ -5903,9 +6146,12 @@
         <v>7.062e-05</v>
       </c>
       <c r="T81" s="1" t="n">
+        <v>7.071000000000001e-05</v>
+      </c>
+      <c r="U81" s="1" t="n">
         <v>7.249000000000001e-05</v>
       </c>
-      <c r="U81" s="1" t="n">
+      <c r="V81" s="1" t="n">
         <v>7.029000000000001e-05</v>
       </c>
     </row>
@@ -5970,9 +6216,12 @@
         <v>0.2658</v>
       </c>
       <c r="T82" s="1" t="n">
+        <v>0.2653</v>
+      </c>
+      <c r="U82" s="1" t="n">
         <v>0.2688</v>
       </c>
-      <c r="U82" s="1" t="n">
+      <c r="V82" s="1" t="n">
         <v>0.2645</v>
       </c>
     </row>
@@ -6037,9 +6286,12 @@
         <v>1.1136</v>
       </c>
       <c r="T83" s="1" t="n">
+        <v>1.1147</v>
+      </c>
+      <c r="U83" s="1" t="n">
         <v>1.1483</v>
       </c>
-      <c r="U83" s="1" t="n">
+      <c r="V83" s="1" t="n">
         <v>1.1054</v>
       </c>
     </row>
@@ -6104,9 +6356,12 @@
         <v>0.3521</v>
       </c>
       <c r="T84" s="1" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="U84" s="1" t="n">
         <v>0.363</v>
       </c>
-      <c r="U84" s="1" t="n">
+      <c r="V84" s="1" t="n">
         <v>0.3496</v>
       </c>
     </row>
@@ -6171,10 +6426,13 @@
         <v>1.9822</v>
       </c>
       <c r="T85" s="1" t="n">
+        <v>1.9568</v>
+      </c>
+      <c r="U85" s="1" t="n">
         <v>2.0327</v>
       </c>
-      <c r="U85" s="1" t="n">
-        <v>1.9784</v>
+      <c r="V85" s="1" t="n">
+        <v>1.9568</v>
       </c>
     </row>
     <row r="86">
@@ -6238,9 +6496,12 @@
         <v>1.3165</v>
       </c>
       <c r="T86" s="1" t="n">
+        <v>1.3164</v>
+      </c>
+      <c r="U86" s="1" t="n">
         <v>1.3205</v>
       </c>
-      <c r="U86" s="1" t="n">
+      <c r="V86" s="1" t="n">
         <v>1.3103</v>
       </c>
     </row>
@@ -6305,9 +6566,12 @@
         <v>32.59</v>
       </c>
       <c r="T87" s="1" t="n">
+        <v>32.56</v>
+      </c>
+      <c r="U87" s="1" t="n">
         <v>33.17</v>
       </c>
-      <c r="U87" s="1" t="n">
+      <c r="V87" s="1" t="n">
         <v>32.52</v>
       </c>
     </row>
@@ -6372,9 +6636,12 @@
         <v>0.009509999999999999</v>
       </c>
       <c r="T88" s="1" t="n">
+        <v>0.00949</v>
+      </c>
+      <c r="U88" s="1" t="n">
         <v>0.01147</v>
       </c>
-      <c r="U88" s="1" t="n">
+      <c r="V88" s="1" t="n">
         <v>0.00941</v>
       </c>
     </row>
@@ -6439,9 +6706,12 @@
         <v>0.01802</v>
       </c>
       <c r="T89" s="1" t="n">
+        <v>0.01803</v>
+      </c>
+      <c r="U89" s="1" t="n">
         <v>0.01843</v>
       </c>
-      <c r="U89" s="1" t="n">
+      <c r="V89" s="1" t="n">
         <v>0.01798</v>
       </c>
     </row>
@@ -6506,9 +6776,12 @@
         <v>0.03478</v>
       </c>
       <c r="T90" s="1" t="n">
+        <v>0.03502</v>
+      </c>
+      <c r="U90" s="1" t="n">
         <v>0.03619</v>
       </c>
-      <c r="U90" s="1" t="n">
+      <c r="V90" s="1" t="n">
         <v>0.03468</v>
       </c>
     </row>
@@ -6573,9 +6846,12 @@
         <v>0.01172</v>
       </c>
       <c r="T91" s="1" t="n">
+        <v>0.01174</v>
+      </c>
+      <c r="U91" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="U91" s="1" t="n">
+      <c r="V91" s="1" t="n">
         <v>0.01172</v>
       </c>
     </row>
@@ -6640,9 +6916,12 @@
         <v>3.096</v>
       </c>
       <c r="T92" s="1" t="n">
+        <v>3.095</v>
+      </c>
+      <c r="U92" s="1" t="n">
         <v>3.136</v>
       </c>
-      <c r="U92" s="1" t="n">
+      <c r="V92" s="1" t="n">
         <v>3.09</v>
       </c>
     </row>
@@ -6707,10 +6986,13 @@
         <v>0.005579</v>
       </c>
       <c r="T93" s="1" t="n">
+        <v>0.005565</v>
+      </c>
+      <c r="U93" s="1" t="n">
         <v>0.005656</v>
       </c>
-      <c r="U93" s="1" t="n">
-        <v>0.00557</v>
+      <c r="V93" s="1" t="n">
+        <v>0.005565</v>
       </c>
     </row>
     <row r="94">
@@ -6774,9 +7056,12 @@
         <v>0.09320000000000001</v>
       </c>
       <c r="T94" s="1" t="n">
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="U94" s="1" t="n">
         <v>0.0946</v>
       </c>
-      <c r="U94" s="1" t="n">
+      <c r="V94" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -6841,9 +7126,12 @@
         <v>0.6124000000000001</v>
       </c>
       <c r="T95" s="1" t="n">
-        <v>0.6124000000000001</v>
+        <v>0.619</v>
       </c>
       <c r="U95" s="1" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="V95" s="1" t="n">
         <v>0.6006</v>
       </c>
     </row>
@@ -6908,9 +7196,12 @@
         <v>1.28e-05</v>
       </c>
       <c r="T96" s="1" t="n">
+        <v>1.27e-05</v>
+      </c>
+      <c r="U96" s="1" t="n">
         <v>1.3e-05</v>
       </c>
-      <c r="U96" s="1" t="n">
+      <c r="V96" s="1" t="n">
         <v>1.27e-05</v>
       </c>
     </row>
@@ -6975,10 +7266,13 @@
         <v>1.107</v>
       </c>
       <c r="T97" s="1" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="U97" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="U97" s="1" t="n">
-        <v>1.102</v>
+      <c r="V97" s="1" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="98">
@@ -7042,9 +7336,12 @@
         <v>0.25299</v>
       </c>
       <c r="T98" s="1" t="n">
+        <v>0.25252</v>
+      </c>
+      <c r="U98" s="1" t="n">
         <v>0.26116</v>
       </c>
-      <c r="U98" s="1" t="n">
+      <c r="V98" s="1" t="n">
         <v>0.2523</v>
       </c>
     </row>
@@ -7109,9 +7406,12 @@
         <v>1.149</v>
       </c>
       <c r="T99" s="1" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="U99" s="1" t="n">
         <v>1.156</v>
       </c>
-      <c r="U99" s="1" t="n">
+      <c r="V99" s="1" t="n">
         <v>1.14</v>
       </c>
     </row>
@@ -7176,9 +7476,12 @@
         <v>1.852</v>
       </c>
       <c r="T100" s="1" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="U100" s="1" t="n">
         <v>1.873</v>
       </c>
-      <c r="U100" s="1" t="n">
+      <c r="V100" s="1" t="n">
         <v>1.852</v>
       </c>
     </row>
@@ -7243,10 +7546,13 @@
         <v>0.01578</v>
       </c>
       <c r="T101" s="1" t="n">
+        <v>0.01573</v>
+      </c>
+      <c r="U101" s="1" t="n">
         <v>0.01601</v>
       </c>
-      <c r="U101" s="1" t="n">
-        <v>0.01575</v>
+      <c r="V101" s="1" t="n">
+        <v>0.01573</v>
       </c>
     </row>
     <row r="102">
@@ -7310,10 +7616,13 @@
         <v>0.10145</v>
       </c>
       <c r="T102" s="1" t="n">
+        <v>0.10062</v>
+      </c>
+      <c r="U102" s="1" t="n">
         <v>0.10431</v>
       </c>
-      <c r="U102" s="1" t="n">
-        <v>0.10145</v>
+      <c r="V102" s="1" t="n">
+        <v>0.10062</v>
       </c>
     </row>
     <row r="103">
@@ -7377,9 +7686,12 @@
         <v>0.0005962</v>
       </c>
       <c r="T103" s="1" t="n">
+        <v>0.0005965</v>
+      </c>
+      <c r="U103" s="1" t="n">
         <v>0.0006089</v>
       </c>
-      <c r="U103" s="1" t="n">
+      <c r="V103" s="1" t="n">
         <v>0.0005941</v>
       </c>
     </row>
@@ -7444,9 +7756,12 @@
         <v>0.0005917</v>
       </c>
       <c r="T104" s="1" t="n">
+        <v>0.0005808</v>
+      </c>
+      <c r="U104" s="1" t="n">
         <v>0.0005932</v>
       </c>
-      <c r="U104" s="1" t="n">
+      <c r="V104" s="1" t="n">
         <v>0.0005566</v>
       </c>
     </row>
@@ -7511,9 +7826,12 @@
         <v>0.003224</v>
       </c>
       <c r="T105" s="1" t="n">
+        <v>0.003231</v>
+      </c>
+      <c r="U105" s="1" t="n">
         <v>0.003269</v>
       </c>
-      <c r="U105" s="1" t="n">
+      <c r="V105" s="1" t="n">
         <v>0.003216</v>
       </c>
     </row>
@@ -7578,9 +7896,12 @@
         <v>2.574</v>
       </c>
       <c r="T106" s="1" t="n">
+        <v>2.572</v>
+      </c>
+      <c r="U106" s="1" t="n">
         <v>2.647</v>
       </c>
-      <c r="U106" s="1" t="n">
+      <c r="V106" s="1" t="n">
         <v>2.572</v>
       </c>
     </row>
@@ -7645,9 +7966,12 @@
         <v>0.1658</v>
       </c>
       <c r="T107" s="1" t="n">
+        <v>0.1658</v>
+      </c>
+      <c r="U107" s="1" t="n">
         <v>0.1681</v>
       </c>
-      <c r="U107" s="1" t="n">
+      <c r="V107" s="1" t="n">
         <v>0.165</v>
       </c>
     </row>
@@ -7712,9 +8036,12 @@
         <v>0.09597</v>
       </c>
       <c r="T108" s="1" t="n">
+        <v>0.09605</v>
+      </c>
+      <c r="U108" s="1" t="n">
         <v>0.09814000000000001</v>
       </c>
-      <c r="U108" s="1" t="n">
+      <c r="V108" s="1" t="n">
         <v>0.0955</v>
       </c>
     </row>
@@ -7779,9 +8106,12 @@
         <v>0.0221</v>
       </c>
       <c r="T109" s="1" t="n">
+        <v>0.02207</v>
+      </c>
+      <c r="U109" s="1" t="n">
         <v>0.02242</v>
       </c>
-      <c r="U109" s="1" t="n">
+      <c r="V109" s="1" t="n">
         <v>0.02202</v>
       </c>
     </row>
@@ -7846,9 +8176,12 @@
         <v>0.291</v>
       </c>
       <c r="T110" s="1" t="n">
+        <v>0.2916</v>
+      </c>
+      <c r="U110" s="1" t="n">
         <v>0.2971</v>
       </c>
-      <c r="U110" s="1" t="n">
+      <c r="V110" s="1" t="n">
         <v>0.2894</v>
       </c>
     </row>
@@ -7913,9 +8246,12 @@
         <v>0.05706</v>
       </c>
       <c r="T111" s="1" t="n">
+        <v>0.05712</v>
+      </c>
+      <c r="U111" s="1" t="n">
         <v>0.05736</v>
       </c>
-      <c r="U111" s="1" t="n">
+      <c r="V111" s="1" t="n">
         <v>0.05651</v>
       </c>
     </row>
@@ -7980,9 +8316,12 @@
         <v>0.3008</v>
       </c>
       <c r="T112" s="1" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="U112" s="1" t="n">
         <v>0.3064</v>
       </c>
-      <c r="U112" s="1" t="n">
+      <c r="V112" s="1" t="n">
         <v>0.3002</v>
       </c>
     </row>
@@ -8047,9 +8386,12 @@
         <v>18.61</v>
       </c>
       <c r="T113" s="1" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="U113" s="1" t="n">
         <v>18.73</v>
       </c>
-      <c r="U113" s="1" t="n">
+      <c r="V113" s="1" t="n">
         <v>18.53</v>
       </c>
     </row>
@@ -8114,9 +8456,12 @@
         <v>0.12639</v>
       </c>
       <c r="T114" s="1" t="n">
+        <v>0.12753</v>
+      </c>
+      <c r="U114" s="1" t="n">
         <v>0.13604</v>
       </c>
-      <c r="U114" s="1" t="n">
+      <c r="V114" s="1" t="n">
         <v>0.12566</v>
       </c>
     </row>
@@ -8181,9 +8526,12 @@
         <v>0.0156</v>
       </c>
       <c r="T115" s="1" t="n">
+        <v>0.01557</v>
+      </c>
+      <c r="U115" s="1" t="n">
         <v>0.01661</v>
       </c>
-      <c r="U115" s="1" t="n">
+      <c r="V115" s="1" t="n">
         <v>0.01538</v>
       </c>
     </row>
@@ -8248,9 +8596,12 @@
         <v>0.0847</v>
       </c>
       <c r="T116" s="1" t="n">
+        <v>0.08451</v>
+      </c>
+      <c r="U116" s="1" t="n">
         <v>0.08609</v>
       </c>
-      <c r="U116" s="1" t="n">
+      <c r="V116" s="1" t="n">
         <v>0.08442</v>
       </c>
     </row>
@@ -8315,9 +8666,12 @@
         <v>0.0473</v>
       </c>
       <c r="T117" s="1" t="n">
+        <v>0.04704</v>
+      </c>
+      <c r="U117" s="1" t="n">
         <v>0.04998</v>
       </c>
-      <c r="U117" s="1" t="n">
+      <c r="V117" s="1" t="n">
         <v>0.046846</v>
       </c>
     </row>
@@ -8382,9 +8736,12 @@
         <v>0.04716</v>
       </c>
       <c r="T118" s="1" t="n">
+        <v>0.04713</v>
+      </c>
+      <c r="U118" s="1" t="n">
         <v>0.04849</v>
       </c>
-      <c r="U118" s="1" t="n">
+      <c r="V118" s="1" t="n">
         <v>0.04701</v>
       </c>
     </row>
@@ -8449,9 +8806,12 @@
         <v>0.04022</v>
       </c>
       <c r="T119" s="1" t="n">
+        <v>0.04016</v>
+      </c>
+      <c r="U119" s="1" t="n">
         <v>0.04271</v>
       </c>
-      <c r="U119" s="1" t="n">
+      <c r="V119" s="1" t="n">
         <v>0.03999</v>
       </c>
     </row>
@@ -8516,9 +8876,12 @@
         <v>0.14406</v>
       </c>
       <c r="T120" s="1" t="n">
+        <v>0.14451</v>
+      </c>
+      <c r="U120" s="1" t="n">
         <v>0.14662</v>
       </c>
-      <c r="U120" s="1" t="n">
+      <c r="V120" s="1" t="n">
         <v>0.14387</v>
       </c>
     </row>
@@ -8583,9 +8946,12 @@
         <v>0.1255</v>
       </c>
       <c r="T121" s="1" t="n">
+        <v>0.1254</v>
+      </c>
+      <c r="U121" s="1" t="n">
         <v>0.1287</v>
       </c>
-      <c r="U121" s="1" t="n">
+      <c r="V121" s="1" t="n">
         <v>0.1252</v>
       </c>
     </row>
@@ -8650,10 +9016,13 @@
         <v>1.845</v>
       </c>
       <c r="T122" s="1" t="n">
+        <v>1.842</v>
+      </c>
+      <c r="U122" s="1" t="n">
         <v>1.903</v>
       </c>
-      <c r="U122" s="1" t="n">
-        <v>1.845</v>
+      <c r="V122" s="1" t="n">
+        <v>1.842</v>
       </c>
     </row>
     <row r="123">
@@ -8717,9 +9086,12 @@
         <v>0.03005</v>
       </c>
       <c r="T123" s="1" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="U123" s="1" t="n">
         <v>0.03064</v>
       </c>
-      <c r="U123" s="1" t="n">
+      <c r="V123" s="1" t="n">
         <v>0.03001</v>
       </c>
     </row>
@@ -8784,9 +9156,12 @@
         <v>0.13475</v>
       </c>
       <c r="T124" s="1" t="n">
+        <v>0.13454</v>
+      </c>
+      <c r="U124" s="1" t="n">
         <v>0.13475</v>
       </c>
-      <c r="U124" s="1" t="n">
+      <c r="V124" s="1" t="n">
         <v>0.13138</v>
       </c>
     </row>
@@ -8851,9 +9226,12 @@
         <v>0.04095</v>
       </c>
       <c r="T125" s="1" t="n">
+        <v>0.04096</v>
+      </c>
+      <c r="U125" s="1" t="n">
         <v>0.04187</v>
       </c>
-      <c r="U125" s="1" t="n">
+      <c r="V125" s="1" t="n">
         <v>0.04075</v>
       </c>
     </row>
@@ -8918,9 +9296,12 @@
         <v>0.1144</v>
       </c>
       <c r="T126" s="1" t="n">
+        <v>0.1145</v>
+      </c>
+      <c r="U126" s="1" t="n">
         <v>0.1166</v>
       </c>
-      <c r="U126" s="1" t="n">
+      <c r="V126" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -8985,9 +9366,12 @@
         <v>0.53</v>
       </c>
       <c r="T127" s="1" t="n">
-        <v>0.53</v>
+        <v>0.5322</v>
       </c>
       <c r="U127" s="1" t="n">
+        <v>0.5322</v>
+      </c>
+      <c r="V127" s="1" t="n">
         <v>0.4957</v>
       </c>
     </row>
@@ -9052,9 +9436,12 @@
         <v>0.03819</v>
       </c>
       <c r="T128" s="1" t="n">
+        <v>0.03819</v>
+      </c>
+      <c r="U128" s="1" t="n">
         <v>0.03838</v>
       </c>
-      <c r="U128" s="1" t="n">
+      <c r="V128" s="1" t="n">
         <v>0.0378</v>
       </c>
     </row>
@@ -9119,9 +9506,12 @@
         <v>0.794</v>
       </c>
       <c r="T129" s="1" t="n">
+        <v>0.794</v>
+      </c>
+      <c r="U129" s="1" t="n">
         <v>0.798</v>
       </c>
-      <c r="U129" s="1" t="n">
+      <c r="V129" s="1" t="n">
         <v>0.791</v>
       </c>
     </row>
@@ -9186,9 +9576,12 @@
         <v>0.03441</v>
       </c>
       <c r="T130" s="1" t="n">
+        <v>0.03428</v>
+      </c>
+      <c r="U130" s="1" t="n">
         <v>0.03458</v>
       </c>
-      <c r="U130" s="1" t="n">
+      <c r="V130" s="1" t="n">
         <v>0.03422</v>
       </c>
     </row>
@@ -9253,9 +9646,12 @@
         <v>0.4234</v>
       </c>
       <c r="T131" s="1" t="n">
+        <v>0.4219</v>
+      </c>
+      <c r="U131" s="1" t="n">
         <v>0.4316</v>
       </c>
-      <c r="U131" s="1" t="n">
+      <c r="V131" s="1" t="n">
         <v>0.4149</v>
       </c>
     </row>
@@ -9320,10 +9716,13 @@
         <v>0.04314</v>
       </c>
       <c r="T132" s="1" t="n">
+        <v>0.04303</v>
+      </c>
+      <c r="U132" s="1" t="n">
         <v>0.04409</v>
       </c>
-      <c r="U132" s="1" t="n">
-        <v>0.04309</v>
+      <c r="V132" s="1" t="n">
+        <v>0.04303</v>
       </c>
     </row>
     <row r="133">
@@ -9387,9 +9786,12 @@
         <v>1.2816</v>
       </c>
       <c r="T133" s="1" t="n">
+        <v>1.2806</v>
+      </c>
+      <c r="U133" s="1" t="n">
         <v>1.3057</v>
       </c>
-      <c r="U133" s="1" t="n">
+      <c r="V133" s="1" t="n">
         <v>1.2805</v>
       </c>
     </row>
@@ -9454,9 +9856,12 @@
         <v>0.02192</v>
       </c>
       <c r="T134" s="1" t="n">
+        <v>0.02191</v>
+      </c>
+      <c r="U134" s="1" t="n">
         <v>0.0222</v>
       </c>
-      <c r="U134" s="1" t="n">
+      <c r="V134" s="1" t="n">
         <v>0.02178</v>
       </c>
     </row>
@@ -9521,9 +9926,12 @@
         <v>0.0004566</v>
       </c>
       <c r="T135" s="1" t="n">
+        <v>0.0004565</v>
+      </c>
+      <c r="U135" s="1" t="n">
         <v>0.0004731</v>
       </c>
-      <c r="U135" s="1" t="n">
+      <c r="V135" s="1" t="n">
         <v>0.0004561</v>
       </c>
     </row>
@@ -9588,9 +9996,12 @@
         <v>0.001912</v>
       </c>
       <c r="T136" s="1" t="n">
+        <v>0.001928</v>
+      </c>
+      <c r="U136" s="1" t="n">
         <v>0.001976</v>
       </c>
-      <c r="U136" s="1" t="n">
+      <c r="V136" s="1" t="n">
         <v>0.001881</v>
       </c>
     </row>
@@ -9655,9 +10066,12 @@
         <v>0.3148</v>
       </c>
       <c r="T137" s="1" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="U137" s="1" t="n">
         <v>0.3239</v>
       </c>
-      <c r="U137" s="1" t="n">
+      <c r="V137" s="1" t="n">
         <v>0.3136</v>
       </c>
     </row>
@@ -9722,9 +10136,12 @@
         <v>0.5599</v>
       </c>
       <c r="T138" s="1" t="n">
+        <v>0.5603</v>
+      </c>
+      <c r="U138" s="1" t="n">
         <v>0.5759</v>
       </c>
-      <c r="U138" s="1" t="n">
+      <c r="V138" s="1" t="n">
         <v>0.5599</v>
       </c>
     </row>
@@ -9789,9 +10206,12 @@
         <v>0.02134</v>
       </c>
       <c r="T139" s="1" t="n">
+        <v>0.02135</v>
+      </c>
+      <c r="U139" s="1" t="n">
         <v>0.02161</v>
       </c>
-      <c r="U139" s="1" t="n">
+      <c r="V139" s="1" t="n">
         <v>0.02121</v>
       </c>
     </row>
@@ -9856,9 +10276,12 @@
         <v>0.07972</v>
       </c>
       <c r="T140" s="1" t="n">
+        <v>0.07994</v>
+      </c>
+      <c r="U140" s="1" t="n">
         <v>0.08103</v>
       </c>
-      <c r="U140" s="1" t="n">
+      <c r="V140" s="1" t="n">
         <v>0.0796</v>
       </c>
     </row>
@@ -9923,9 +10346,12 @@
         <v>0.001527</v>
       </c>
       <c r="T141" s="1" t="n">
+        <v>0.00153</v>
+      </c>
+      <c r="U141" s="1" t="n">
         <v>0.001672</v>
       </c>
-      <c r="U141" s="1" t="n">
+      <c r="V141" s="1" t="n">
         <v>0.001502</v>
       </c>
     </row>
@@ -9990,9 +10416,12 @@
         <v>0.4514</v>
       </c>
       <c r="T142" s="1" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="U142" s="1" t="n">
         <v>0.4514</v>
       </c>
-      <c r="U142" s="1" t="n">
+      <c r="V142" s="1" t="n">
         <v>0.4218</v>
       </c>
     </row>
@@ -10057,9 +10486,12 @@
         <v>0.029881</v>
       </c>
       <c r="T143" s="1" t="n">
+        <v>0.030224</v>
+      </c>
+      <c r="U143" s="1" t="n">
         <v>0.031368</v>
       </c>
-      <c r="U143" s="1" t="n">
+      <c r="V143" s="1" t="n">
         <v>0.029881</v>
       </c>
     </row>
@@ -10124,9 +10556,12 @@
         <v>0.000226</v>
       </c>
       <c r="T144" s="1" t="n">
+        <v>0.000225</v>
+      </c>
+      <c r="U144" s="1" t="n">
         <v>0.000227</v>
       </c>
-      <c r="U144" s="1" t="n">
+      <c r="V144" s="1" t="n">
         <v>0.000223</v>
       </c>
     </row>
@@ -10191,9 +10626,12 @@
         <v>0.03476</v>
       </c>
       <c r="T145" s="1" t="n">
+        <v>0.03498</v>
+      </c>
+      <c r="U145" s="1" t="n">
         <v>0.03696</v>
       </c>
-      <c r="U145" s="1" t="n">
+      <c r="V145" s="1" t="n">
         <v>0.03178</v>
       </c>
     </row>
@@ -10258,9 +10696,12 @@
         <v>0.11648</v>
       </c>
       <c r="T146" s="1" t="n">
-        <v>0.11649</v>
+        <v>0.11676</v>
       </c>
       <c r="U146" s="1" t="n">
+        <v>0.11676</v>
+      </c>
+      <c r="V146" s="1" t="n">
         <v>0.11505</v>
       </c>
     </row>
@@ -10325,9 +10766,12 @@
         <v>0.0224</v>
       </c>
       <c r="T147" s="1" t="n">
-        <v>0.0224</v>
+        <v>0.02254</v>
       </c>
       <c r="U147" s="1" t="n">
+        <v>0.02254</v>
+      </c>
+      <c r="V147" s="1" t="n">
         <v>0.02164</v>
       </c>
     </row>
@@ -10392,9 +10836,12 @@
         <v>1.4151</v>
       </c>
       <c r="T148" s="1" t="n">
+        <v>1.4143</v>
+      </c>
+      <c r="U148" s="1" t="n">
         <v>1.4256</v>
       </c>
-      <c r="U148" s="1" t="n">
+      <c r="V148" s="1" t="n">
         <v>1.4084</v>
       </c>
     </row>
@@ -10459,9 +10906,12 @@
         <v>1.8735</v>
       </c>
       <c r="T149" s="1" t="n">
+        <v>1.8691</v>
+      </c>
+      <c r="U149" s="1" t="n">
         <v>1.8868</v>
       </c>
-      <c r="U149" s="1" t="n">
+      <c r="V149" s="1" t="n">
         <v>1.8594</v>
       </c>
     </row>
@@ -10526,9 +10976,12 @@
         <v>0.096</v>
       </c>
       <c r="T150" s="1" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="U150" s="1" t="n">
         <v>0.101</v>
       </c>
-      <c r="U150" s="1" t="n">
+      <c r="V150" s="1" t="n">
         <v>0.094</v>
       </c>
     </row>
@@ -10593,9 +11046,12 @@
         <v>4.652</v>
       </c>
       <c r="T151" s="1" t="n">
-        <v>4.653</v>
+        <v>4.697</v>
       </c>
       <c r="U151" s="1" t="n">
+        <v>4.697</v>
+      </c>
+      <c r="V151" s="1" t="n">
         <v>4.488</v>
       </c>
     </row>
@@ -10660,9 +11116,12 @@
         <v>5.532</v>
       </c>
       <c r="T152" s="1" t="n">
+        <v>5.534</v>
+      </c>
+      <c r="U152" s="1" t="n">
         <v>5.593</v>
       </c>
-      <c r="U152" s="1" t="n">
+      <c r="V152" s="1" t="n">
         <v>5.511</v>
       </c>
     </row>
@@ -10727,9 +11186,12 @@
         <v>0.321</v>
       </c>
       <c r="T153" s="1" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="U153" s="1" t="n">
         <v>0.3263</v>
       </c>
-      <c r="U153" s="1" t="n">
+      <c r="V153" s="1" t="n">
         <v>0.3154</v>
       </c>
     </row>
@@ -10794,9 +11256,12 @@
         <v>0.5841</v>
       </c>
       <c r="T154" s="1" t="n">
+        <v>0.5838</v>
+      </c>
+      <c r="U154" s="1" t="n">
         <v>0.5921999999999999</v>
       </c>
-      <c r="U154" s="1" t="n">
+      <c r="V154" s="1" t="n">
         <v>0.5825</v>
       </c>
     </row>
@@ -10861,9 +11326,12 @@
         <v>0.01273</v>
       </c>
       <c r="T155" s="1" t="n">
+        <v>0.01274</v>
+      </c>
+      <c r="U155" s="1" t="n">
         <v>0.01299</v>
       </c>
-      <c r="U155" s="1" t="n">
+      <c r="V155" s="1" t="n">
         <v>0.01267</v>
       </c>
     </row>
@@ -10928,9 +11396,12 @@
         <v>0.09710000000000001</v>
       </c>
       <c r="T156" s="1" t="n">
+        <v>0.0973</v>
+      </c>
+      <c r="U156" s="1" t="n">
         <v>0.1005</v>
       </c>
-      <c r="U156" s="1" t="n">
+      <c r="V156" s="1" t="n">
         <v>0.09710000000000001</v>
       </c>
     </row>
@@ -10995,9 +11466,12 @@
         <v>16.412</v>
       </c>
       <c r="T157" s="1" t="n">
+        <v>16.395</v>
+      </c>
+      <c r="U157" s="1" t="n">
         <v>16.755</v>
       </c>
-      <c r="U157" s="1" t="n">
+      <c r="V157" s="1" t="n">
         <v>16.341</v>
       </c>
     </row>
@@ -11062,9 +11536,12 @@
         <v>0.0556</v>
       </c>
       <c r="T158" s="1" t="n">
+        <v>0.0555</v>
+      </c>
+      <c r="U158" s="1" t="n">
         <v>0.05615</v>
       </c>
-      <c r="U158" s="1" t="n">
+      <c r="V158" s="1" t="n">
         <v>0.05477</v>
       </c>
     </row>
@@ -11129,9 +11606,12 @@
         <v>28.75</v>
       </c>
       <c r="T159" s="1" t="n">
+        <v>28.77</v>
+      </c>
+      <c r="U159" s="1" t="n">
         <v>29.22</v>
       </c>
-      <c r="U159" s="1" t="n">
+      <c r="V159" s="1" t="n">
         <v>28.65</v>
       </c>
     </row>
@@ -11196,9 +11676,12 @@
         <v>0.02135</v>
       </c>
       <c r="T160" s="1" t="n">
+        <v>0.02133</v>
+      </c>
+      <c r="U160" s="1" t="n">
         <v>0.02141</v>
       </c>
-      <c r="U160" s="1" t="n">
+      <c r="V160" s="1" t="n">
         <v>0.02087</v>
       </c>
     </row>
@@ -11263,9 +11746,12 @@
         <v>0.0006521</v>
       </c>
       <c r="T161" s="1" t="n">
+        <v>0.0006539</v>
+      </c>
+      <c r="U161" s="1" t="n">
         <v>0.0006655</v>
       </c>
-      <c r="U161" s="1" t="n">
+      <c r="V161" s="1" t="n">
         <v>0.0006503</v>
       </c>
     </row>
@@ -11330,9 +11816,12 @@
         <v>0.3801</v>
       </c>
       <c r="T162" s="1" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="U162" s="1" t="n">
         <v>0.4068</v>
       </c>
-      <c r="U162" s="1" t="n">
+      <c r="V162" s="1" t="n">
         <v>0.3785</v>
       </c>
     </row>
@@ -11397,9 +11886,12 @@
         <v>0.1915</v>
       </c>
       <c r="T163" s="1" t="n">
+        <v>0.1911</v>
+      </c>
+      <c r="U163" s="1" t="n">
         <v>0.1952</v>
       </c>
-      <c r="U163" s="1" t="n">
+      <c r="V163" s="1" t="n">
         <v>0.1908</v>
       </c>
     </row>
@@ -11464,9 +11956,12 @@
         <v>0.316</v>
       </c>
       <c r="T164" s="1" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="U164" s="1" t="n">
         <v>0.322</v>
       </c>
-      <c r="U164" s="1" t="n">
+      <c r="V164" s="1" t="n">
         <v>0.315</v>
       </c>
     </row>
@@ -11531,9 +12026,12 @@
         <v>0.374</v>
       </c>
       <c r="T165" s="1" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="U165" s="1" t="n">
         <v>0.377</v>
       </c>
-      <c r="U165" s="1" t="n">
+      <c r="V165" s="1" t="n">
         <v>0.371</v>
       </c>
     </row>
@@ -11598,9 +12096,12 @@
         <v>0.02253</v>
       </c>
       <c r="T166" s="1" t="n">
+        <v>0.02245</v>
+      </c>
+      <c r="U166" s="1" t="n">
         <v>0.02286</v>
       </c>
-      <c r="U166" s="1" t="n">
+      <c r="V166" s="1" t="n">
         <v>0.02233</v>
       </c>
     </row>
@@ -11665,9 +12166,12 @@
         <v>0.00727</v>
       </c>
       <c r="T167" s="1" t="n">
+        <v>0.007268</v>
+      </c>
+      <c r="U167" s="1" t="n">
         <v>0.0074</v>
       </c>
-      <c r="U167" s="1" t="n">
+      <c r="V167" s="1" t="n">
         <v>0.007256</v>
       </c>
     </row>
@@ -11732,9 +12236,12 @@
         <v>0.01338</v>
       </c>
       <c r="T168" s="1" t="n">
+        <v>0.01341</v>
+      </c>
+      <c r="U168" s="1" t="n">
         <v>0.01397</v>
       </c>
-      <c r="U168" s="1" t="n">
+      <c r="V168" s="1" t="n">
         <v>0.01332</v>
       </c>
     </row>
@@ -11799,9 +12306,12 @@
         <v>0.25504</v>
       </c>
       <c r="T169" s="1" t="n">
+        <v>0.25566</v>
+      </c>
+      <c r="U169" s="1" t="n">
         <v>0.26035</v>
       </c>
-      <c r="U169" s="1" t="n">
+      <c r="V169" s="1" t="n">
         <v>0.25151</v>
       </c>
     </row>
@@ -11866,9 +12376,12 @@
         <v>0.02178</v>
       </c>
       <c r="T170" s="1" t="n">
+        <v>0.0218</v>
+      </c>
+      <c r="U170" s="1" t="n">
         <v>0.02193</v>
       </c>
-      <c r="U170" s="1" t="n">
+      <c r="V170" s="1" t="n">
         <v>0.02143</v>
       </c>
     </row>
@@ -11933,9 +12446,12 @@
         <v>0.1724</v>
       </c>
       <c r="T171" s="1" t="n">
+        <v>0.1722</v>
+      </c>
+      <c r="U171" s="1" t="n">
         <v>0.177</v>
       </c>
-      <c r="U171" s="1" t="n">
+      <c r="V171" s="1" t="n">
         <v>0.171</v>
       </c>
     </row>
@@ -12003,6 +12519,9 @@
         <v>0.09</v>
       </c>
       <c r="U172" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="V172" s="1" t="n">
         <v>0.08799999999999999</v>
       </c>
     </row>
@@ -12067,9 +12586,12 @@
         <v>0.004674</v>
       </c>
       <c r="T173" s="1" t="n">
+        <v>0.004673</v>
+      </c>
+      <c r="U173" s="1" t="n">
         <v>0.004732</v>
       </c>
-      <c r="U173" s="1" t="n">
+      <c r="V173" s="1" t="n">
         <v>0.004662</v>
       </c>
     </row>
@@ -12134,9 +12656,12 @@
         <v>0.4374</v>
       </c>
       <c r="T174" s="1" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="U174" s="1" t="n">
         <v>0.4423</v>
       </c>
-      <c r="U174" s="1" t="n">
+      <c r="V174" s="1" t="n">
         <v>0.4343</v>
       </c>
     </row>
@@ -12201,9 +12726,12 @@
         <v>0.09057</v>
       </c>
       <c r="T175" s="1" t="n">
+        <v>0.09053</v>
+      </c>
+      <c r="U175" s="1" t="n">
         <v>0.09057</v>
       </c>
-      <c r="U175" s="1" t="n">
+      <c r="V175" s="1" t="n">
         <v>0.08935999999999999</v>
       </c>
     </row>
@@ -12268,9 +12796,12 @@
         <v>0.2459</v>
       </c>
       <c r="T176" s="1" t="n">
+        <v>0.2458</v>
+      </c>
+      <c r="U176" s="1" t="n">
         <v>0.2476</v>
       </c>
-      <c r="U176" s="1" t="n">
+      <c r="V176" s="1" t="n">
         <v>0.2453</v>
       </c>
     </row>
@@ -12335,9 +12866,12 @@
         <v>0.01916</v>
       </c>
       <c r="T177" s="1" t="n">
+        <v>0.01919</v>
+      </c>
+      <c r="U177" s="1" t="n">
         <v>0.01935</v>
       </c>
-      <c r="U177" s="1" t="n">
+      <c r="V177" s="1" t="n">
         <v>0.01908</v>
       </c>
     </row>
@@ -12402,10 +12936,13 @@
         <v>6.115</v>
       </c>
       <c r="T178" s="1" t="n">
+        <v>6.106</v>
+      </c>
+      <c r="U178" s="1" t="n">
         <v>6.24</v>
       </c>
-      <c r="U178" s="1" t="n">
-        <v>6.108</v>
+      <c r="V178" s="1" t="n">
+        <v>6.106</v>
       </c>
     </row>
     <row r="179">
@@ -12469,9 +13006,12 @@
         <v>0.1378</v>
       </c>
       <c r="T179" s="1" t="n">
+        <v>0.1372</v>
+      </c>
+      <c r="U179" s="1" t="n">
         <v>0.1383</v>
       </c>
-      <c r="U179" s="1" t="n">
+      <c r="V179" s="1" t="n">
         <v>0.1349</v>
       </c>
     </row>
@@ -12536,9 +13076,12 @@
         <v>0.005008</v>
       </c>
       <c r="T180" s="1" t="n">
+        <v>0.005006</v>
+      </c>
+      <c r="U180" s="1" t="n">
         <v>0.005154</v>
       </c>
-      <c r="U180" s="1" t="n">
+      <c r="V180" s="1" t="n">
         <v>0.004848</v>
       </c>
     </row>
@@ -12603,9 +13146,12 @@
         <v>0.012</v>
       </c>
       <c r="T181" s="1" t="n">
+        <v>0.01195</v>
+      </c>
+      <c r="U181" s="1" t="n">
         <v>0.01203</v>
       </c>
-      <c r="U181" s="1" t="n">
+      <c r="V181" s="1" t="n">
         <v>0.01182</v>
       </c>
     </row>
@@ -12670,9 +13216,12 @@
         <v>0.007374</v>
       </c>
       <c r="T182" s="1" t="n">
+        <v>0.007395</v>
+      </c>
+      <c r="U182" s="1" t="n">
         <v>0.007538</v>
       </c>
-      <c r="U182" s="1" t="n">
+      <c r="V182" s="1" t="n">
         <v>0.007224</v>
       </c>
     </row>
@@ -12737,9 +13286,12 @@
         <v>0.13128</v>
       </c>
       <c r="T183" s="1" t="n">
+        <v>0.13047</v>
+      </c>
+      <c r="U183" s="1" t="n">
         <v>0.13206</v>
       </c>
-      <c r="U183" s="1" t="n">
+      <c r="V183" s="1" t="n">
         <v>0.12964</v>
       </c>
     </row>
@@ -12804,9 +13356,12 @@
         <v>0.09593</v>
       </c>
       <c r="T184" s="1" t="n">
+        <v>0.09587</v>
+      </c>
+      <c r="U184" s="1" t="n">
         <v>0.09733</v>
       </c>
-      <c r="U184" s="1" t="n">
+      <c r="V184" s="1" t="n">
         <v>0.09513000000000001</v>
       </c>
     </row>
@@ -12871,9 +13426,12 @@
         <v>0.00752</v>
       </c>
       <c r="T185" s="1" t="n">
+        <v>0.00752</v>
+      </c>
+      <c r="U185" s="1" t="n">
         <v>0.00764</v>
       </c>
-      <c r="U185" s="1" t="n">
+      <c r="V185" s="1" t="n">
         <v>0.0075</v>
       </c>
     </row>
@@ -12938,9 +13496,12 @@
         <v>0.0486</v>
       </c>
       <c r="T186" s="1" t="n">
+        <v>0.04862</v>
+      </c>
+      <c r="U186" s="1" t="n">
         <v>0.04951</v>
       </c>
-      <c r="U186" s="1" t="n">
+      <c r="V186" s="1" t="n">
         <v>0.04851</v>
       </c>
     </row>
@@ -13005,9 +13566,12 @@
         <v>0.02687</v>
       </c>
       <c r="T187" s="1" t="n">
+        <v>0.02685</v>
+      </c>
+      <c r="U187" s="1" t="n">
         <v>0.02725</v>
       </c>
-      <c r="U187" s="1" t="n">
+      <c r="V187" s="1" t="n">
         <v>0.02652</v>
       </c>
     </row>
@@ -13072,9 +13636,12 @@
         <v>0.003285</v>
       </c>
       <c r="T188" s="1" t="n">
+        <v>0.003283</v>
+      </c>
+      <c r="U188" s="1" t="n">
         <v>0.003351</v>
       </c>
-      <c r="U188" s="1" t="n">
+      <c r="V188" s="1" t="n">
         <v>0.003282</v>
       </c>
     </row>
@@ -13139,9 +13706,12 @@
         <v>0.2856</v>
       </c>
       <c r="T189" s="1" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="U189" s="1" t="n">
         <v>0.29</v>
       </c>
-      <c r="U189" s="1" t="n">
+      <c r="V189" s="1" t="n">
         <v>0.2847</v>
       </c>
     </row>
@@ -13206,9 +13776,12 @@
         <v>0.01784</v>
       </c>
       <c r="T190" s="1" t="n">
+        <v>0.01783</v>
+      </c>
+      <c r="U190" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="U190" s="1" t="n">
+      <c r="V190" s="1" t="n">
         <v>0.01783</v>
       </c>
     </row>
@@ -13273,9 +13846,12 @@
         <v>0.2565</v>
       </c>
       <c r="T191" s="1" t="n">
+        <v>0.2566</v>
+      </c>
+      <c r="U191" s="1" t="n">
         <v>0.262</v>
       </c>
-      <c r="U191" s="1" t="n">
+      <c r="V191" s="1" t="n">
         <v>0.2562</v>
       </c>
     </row>
@@ -13340,9 +13916,12 @@
         <v>0.03821</v>
       </c>
       <c r="T192" s="1" t="n">
+        <v>0.03805</v>
+      </c>
+      <c r="U192" s="1" t="n">
         <v>0.03981</v>
       </c>
-      <c r="U192" s="1" t="n">
+      <c r="V192" s="1" t="n">
         <v>0.03766</v>
       </c>
     </row>
@@ -13407,9 +13986,12 @@
         <v>0.0002219</v>
       </c>
       <c r="T193" s="1" t="n">
+        <v>0.000221</v>
+      </c>
+      <c r="U193" s="1" t="n">
         <v>0.0002243</v>
       </c>
-      <c r="U193" s="1" t="n">
+      <c r="V193" s="1" t="n">
         <v>0.0002205</v>
       </c>
     </row>
@@ -13474,9 +14056,12 @@
         <v>4.085</v>
       </c>
       <c r="T194" s="1" t="n">
+        <v>4.078</v>
+      </c>
+      <c r="U194" s="1" t="n">
         <v>4.196</v>
       </c>
-      <c r="U194" s="1" t="n">
+      <c r="V194" s="1" t="n">
         <v>4.056</v>
       </c>
     </row>
@@ -13541,9 +14126,12 @@
         <v>0.9994</v>
       </c>
       <c r="T195" s="1" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="U195" s="1" t="n">
         <v>0.999401</v>
       </c>
-      <c r="U195" s="1" t="n">
+      <c r="V195" s="1" t="n">
         <v>0.99934</v>
       </c>
     </row>
@@ -13608,9 +14196,12 @@
         <v>4.32</v>
       </c>
       <c r="T196" s="1" t="n">
+        <v>4.324</v>
+      </c>
+      <c r="U196" s="1" t="n">
         <v>4.347</v>
       </c>
-      <c r="U196" s="1" t="n">
+      <c r="V196" s="1" t="n">
         <v>4.276</v>
       </c>
     </row>
@@ -13675,9 +14266,12 @@
         <v>0.15121</v>
       </c>
       <c r="T197" s="1" t="n">
+        <v>0.15195</v>
+      </c>
+      <c r="U197" s="1" t="n">
         <v>0.15232</v>
       </c>
-      <c r="U197" s="1" t="n">
+      <c r="V197" s="1" t="n">
         <v>0.14981</v>
       </c>
     </row>
@@ -13742,9 +14336,12 @@
         <v>0.007718</v>
       </c>
       <c r="T198" s="1" t="n">
-        <v>0.007899</v>
+        <v>0.00792</v>
       </c>
       <c r="U198" s="1" t="n">
+        <v>0.00792</v>
+      </c>
+      <c r="V198" s="1" t="n">
         <v>0.007413</v>
       </c>
     </row>
@@ -13809,9 +14406,12 @@
         <v>0.45</v>
       </c>
       <c r="T199" s="1" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="U199" s="1" t="n">
         <v>0.4533</v>
       </c>
-      <c r="U199" s="1" t="n">
+      <c r="V199" s="1" t="n">
         <v>0.4482</v>
       </c>
     </row>
@@ -13876,9 +14476,12 @@
         <v>0.5923</v>
       </c>
       <c r="T200" s="1" t="n">
+        <v>0.5872000000000001</v>
+      </c>
+      <c r="U200" s="1" t="n">
         <v>0.5923</v>
       </c>
-      <c r="U200" s="1" t="n">
+      <c r="V200" s="1" t="n">
         <v>0.5715</v>
       </c>
     </row>
@@ -13943,9 +14546,12 @@
         <v>0.0927</v>
       </c>
       <c r="T201" s="1" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="U201" s="1" t="n">
         <v>0.09429999999999999</v>
       </c>
-      <c r="U201" s="1" t="n">
+      <c r="V201" s="1" t="n">
         <v>0.0925</v>
       </c>
     </row>
@@ -14010,9 +14616,12 @@
         <v>0.0603</v>
       </c>
       <c r="T202" s="1" t="n">
+        <v>0.06041</v>
+      </c>
+      <c r="U202" s="1" t="n">
         <v>0.0612</v>
       </c>
-      <c r="U202" s="1" t="n">
+      <c r="V202" s="1" t="n">
         <v>0.05994</v>
       </c>
     </row>
@@ -14077,9 +14686,12 @@
         <v>0.00826</v>
       </c>
       <c r="T203" s="1" t="n">
+        <v>0.008319999999999999</v>
+      </c>
+      <c r="U203" s="1" t="n">
         <v>0.008619999999999999</v>
       </c>
-      <c r="U203" s="1" t="n">
+      <c r="V203" s="1" t="n">
         <v>0.00804</v>
       </c>
     </row>
@@ -14144,9 +14756,12 @@
         <v>0.00412</v>
       </c>
       <c r="T204" s="1" t="n">
+        <v>0.00412</v>
+      </c>
+      <c r="U204" s="1" t="n">
         <v>0.00423</v>
       </c>
-      <c r="U204" s="1" t="n">
+      <c r="V204" s="1" t="n">
         <v>0.00412</v>
       </c>
     </row>
@@ -14211,10 +14826,13 @@
         <v>0.009068</v>
       </c>
       <c r="T205" s="1" t="n">
+        <v>0.009067</v>
+      </c>
+      <c r="U205" s="1" t="n">
         <v>0.009318</v>
       </c>
-      <c r="U205" s="1" t="n">
-        <v>0.009068</v>
+      <c r="V205" s="1" t="n">
+        <v>0.009067</v>
       </c>
     </row>
     <row r="206">
@@ -14278,9 +14896,12 @@
         <v>0.2371</v>
       </c>
       <c r="T206" s="1" t="n">
+        <v>0.2371</v>
+      </c>
+      <c r="U206" s="1" t="n">
         <v>0.2418</v>
       </c>
-      <c r="U206" s="1" t="n">
+      <c r="V206" s="1" t="n">
         <v>0.2356</v>
       </c>
     </row>
@@ -14345,9 +14966,12 @@
         <v>0.02106</v>
       </c>
       <c r="T207" s="1" t="n">
+        <v>0.02109</v>
+      </c>
+      <c r="U207" s="1" t="n">
         <v>0.02163</v>
       </c>
-      <c r="U207" s="1" t="n">
+      <c r="V207" s="1" t="n">
         <v>0.02052</v>
       </c>
     </row>
@@ -14412,9 +15036,12 @@
         <v>0.2369</v>
       </c>
       <c r="T208" s="1" t="n">
+        <v>0.2373</v>
+      </c>
+      <c r="U208" s="1" t="n">
         <v>0.2392</v>
       </c>
-      <c r="U208" s="1" t="n">
+      <c r="V208" s="1" t="n">
         <v>0.2357</v>
       </c>
     </row>
@@ -14479,9 +15106,12 @@
         <v>0.3598</v>
       </c>
       <c r="T209" s="1" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="U209" s="1" t="n">
         <v>0.3638</v>
       </c>
-      <c r="U209" s="1" t="n">
+      <c r="V209" s="1" t="n">
         <v>0.3584</v>
       </c>
     </row>
@@ -14546,9 +15176,12 @@
         <v>0.04272</v>
       </c>
       <c r="T210" s="1" t="n">
+        <v>0.04294</v>
+      </c>
+      <c r="U210" s="1" t="n">
         <v>0.04318</v>
       </c>
-      <c r="U210" s="1" t="n">
+      <c r="V210" s="1" t="n">
         <v>0.04232</v>
       </c>
     </row>
@@ -14613,10 +15246,13 @@
         <v>0.0004246</v>
       </c>
       <c r="T211" s="1" t="n">
+        <v>0.0004235</v>
+      </c>
+      <c r="U211" s="1" t="n">
         <v>0.0004329</v>
       </c>
-      <c r="U211" s="1" t="n">
-        <v>0.0004237</v>
+      <c r="V211" s="1" t="n">
+        <v>0.0004235</v>
       </c>
     </row>
     <row r="212">
@@ -14680,10 +15316,13 @@
         <v>0.02127</v>
       </c>
       <c r="T212" s="1" t="n">
+        <v>0.02123</v>
+      </c>
+      <c r="U212" s="1" t="n">
         <v>0.02179</v>
       </c>
-      <c r="U212" s="1" t="n">
-        <v>0.02125</v>
+      <c r="V212" s="1" t="n">
+        <v>0.02123</v>
       </c>
     </row>
     <row r="213">
@@ -14747,9 +15386,12 @@
         <v>0.1136</v>
       </c>
       <c r="T213" s="1" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="U213" s="1" t="n">
         <v>0.1165</v>
       </c>
-      <c r="U213" s="1" t="n">
+      <c r="V213" s="1" t="n">
         <v>0.1135</v>
       </c>
     </row>
@@ -14814,9 +15456,12 @@
         <v>0.04197</v>
       </c>
       <c r="T214" s="1" t="n">
+        <v>0.04193</v>
+      </c>
+      <c r="U214" s="1" t="n">
         <v>0.04206</v>
       </c>
-      <c r="U214" s="1" t="n">
+      <c r="V214" s="1" t="n">
         <v>0.04173</v>
       </c>
     </row>
@@ -14881,9 +15526,12 @@
         <v>0.009868999999999999</v>
       </c>
       <c r="T215" s="1" t="n">
+        <v>0.009875999999999999</v>
+      </c>
+      <c r="U215" s="1" t="n">
         <v>0.010079</v>
       </c>
-      <c r="U215" s="1" t="n">
+      <c r="V215" s="1" t="n">
         <v>0.009839000000000001</v>
       </c>
     </row>
@@ -14948,9 +15596,12 @@
         <v>0.06370000000000001</v>
       </c>
       <c r="T216" s="1" t="n">
+        <v>0.0636</v>
+      </c>
+      <c r="U216" s="1" t="n">
         <v>0.06469999999999999</v>
       </c>
-      <c r="U216" s="1" t="n">
+      <c r="V216" s="1" t="n">
         <v>0.0634</v>
       </c>
     </row>
@@ -15015,9 +15666,12 @@
         <v>0.004249</v>
       </c>
       <c r="T217" s="1" t="n">
+        <v>0.004224</v>
+      </c>
+      <c r="U217" s="1" t="n">
         <v>0.004287</v>
       </c>
-      <c r="U217" s="1" t="n">
+      <c r="V217" s="1" t="n">
         <v>0.004177</v>
       </c>
     </row>
@@ -15082,9 +15736,12 @@
         <v>0.00997</v>
       </c>
       <c r="T218" s="1" t="n">
+        <v>0.01002</v>
+      </c>
+      <c r="U218" s="1" t="n">
         <v>0.01085</v>
       </c>
-      <c r="U218" s="1" t="n">
+      <c r="V218" s="1" t="n">
         <v>0.009820000000000001</v>
       </c>
     </row>
@@ -15149,9 +15806,12 @@
         <v>0.02947</v>
       </c>
       <c r="T219" s="1" t="n">
+        <v>0.02943</v>
+      </c>
+      <c r="U219" s="1" t="n">
         <v>0.03134</v>
       </c>
-      <c r="U219" s="1" t="n">
+      <c r="V219" s="1" t="n">
         <v>0.02941</v>
       </c>
     </row>
@@ -15216,9 +15876,12 @@
         <v>2.289</v>
       </c>
       <c r="T220" s="1" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U220" s="1" t="n">
         <v>2.315</v>
       </c>
-      <c r="U220" s="1" t="n">
+      <c r="V220" s="1" t="n">
         <v>2.281</v>
       </c>
     </row>
@@ -15283,9 +15946,12 @@
         <v>0.022748</v>
       </c>
       <c r="T221" s="1" t="n">
+        <v>0.022707</v>
+      </c>
+      <c r="U221" s="1" t="n">
         <v>0.023224</v>
       </c>
-      <c r="U221" s="1" t="n">
+      <c r="V221" s="1" t="n">
         <v>0.022529</v>
       </c>
     </row>
@@ -15350,9 +16016,12 @@
         <v>0.0368</v>
       </c>
       <c r="T222" s="1" t="n">
+        <v>0.0368</v>
+      </c>
+      <c r="U222" s="1" t="n">
         <v>0.0372</v>
       </c>
-      <c r="U222" s="1" t="n">
+      <c r="V222" s="1" t="n">
         <v>0.0368</v>
       </c>
     </row>
@@ -15417,9 +16086,12 @@
         <v>0.2933</v>
       </c>
       <c r="T223" s="1" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="U223" s="1" t="n">
         <v>0.295</v>
       </c>
-      <c r="U223" s="1" t="n">
+      <c r="V223" s="1" t="n">
         <v>0.2915</v>
       </c>
     </row>
@@ -15484,9 +16156,12 @@
         <v>0.01553</v>
       </c>
       <c r="T224" s="1" t="n">
+        <v>0.01553</v>
+      </c>
+      <c r="U224" s="1" t="n">
         <v>0.01582</v>
       </c>
-      <c r="U224" s="1" t="n">
+      <c r="V224" s="1" t="n">
         <v>0.01537</v>
       </c>
     </row>
@@ -15551,10 +16226,13 @@
         <v>0.0004035</v>
       </c>
       <c r="T225" s="1" t="n">
+        <v>0.0004031</v>
+      </c>
+      <c r="U225" s="1" t="n">
         <v>0.0004153</v>
       </c>
-      <c r="U225" s="1" t="n">
-        <v>0.0004032</v>
+      <c r="V225" s="1" t="n">
+        <v>0.0004031</v>
       </c>
     </row>
     <row r="226">
@@ -15618,10 +16296,13 @@
         <v>0.08556</v>
       </c>
       <c r="T226" s="1" t="n">
+        <v>0.08519</v>
+      </c>
+      <c r="U226" s="1" t="n">
         <v>0.08815000000000001</v>
       </c>
-      <c r="U226" s="1" t="n">
-        <v>0.08522</v>
+      <c r="V226" s="1" t="n">
+        <v>0.08519</v>
       </c>
     </row>
     <row r="227">
@@ -15685,9 +16366,12 @@
         <v>0.948</v>
       </c>
       <c r="T227" s="1" t="n">
+        <v>0.948</v>
+      </c>
+      <c r="U227" s="1" t="n">
         <v>0.959</v>
       </c>
-      <c r="U227" s="1" t="n">
+      <c r="V227" s="1" t="n">
         <v>0.945</v>
       </c>
     </row>
@@ -15752,9 +16436,12 @@
         <v>0.05524</v>
       </c>
       <c r="T228" s="1" t="n">
+        <v>0.05565</v>
+      </c>
+      <c r="U228" s="1" t="n">
         <v>0.05641</v>
       </c>
-      <c r="U228" s="1" t="n">
+      <c r="V228" s="1" t="n">
         <v>0.05439</v>
       </c>
     </row>
@@ -15819,9 +16506,12 @@
         <v>0.002013</v>
       </c>
       <c r="T229" s="1" t="n">
+        <v>0.002018</v>
+      </c>
+      <c r="U229" s="1" t="n">
         <v>0.002035</v>
       </c>
-      <c r="U229" s="1" t="n">
+      <c r="V229" s="1" t="n">
         <v>0.001997</v>
       </c>
     </row>
@@ -15886,9 +16576,12 @@
         <v>0.02287</v>
       </c>
       <c r="T230" s="1" t="n">
+        <v>0.022858</v>
+      </c>
+      <c r="U230" s="1" t="n">
         <v>0.023101</v>
       </c>
-      <c r="U230" s="1" t="n">
+      <c r="V230" s="1" t="n">
         <v>0.022659</v>
       </c>
     </row>
@@ -15953,9 +16646,12 @@
         <v>0.05351</v>
       </c>
       <c r="T231" s="1" t="n">
+        <v>0.05344</v>
+      </c>
+      <c r="U231" s="1" t="n">
         <v>0.05507</v>
       </c>
-      <c r="U231" s="1" t="n">
+      <c r="V231" s="1" t="n">
         <v>0.05338</v>
       </c>
     </row>
@@ -16020,9 +16716,12 @@
         <v>0.0585</v>
       </c>
       <c r="T232" s="1" t="n">
+        <v>0.0583</v>
+      </c>
+      <c r="U232" s="1" t="n">
         <v>0.0597</v>
       </c>
-      <c r="U232" s="1" t="n">
+      <c r="V232" s="1" t="n">
         <v>0.0583</v>
       </c>
     </row>
@@ -16087,9 +16786,12 @@
         <v>0.001695</v>
       </c>
       <c r="T233" s="1" t="n">
-        <v>0.001701</v>
+        <v>0.001705</v>
       </c>
       <c r="U233" s="1" t="n">
+        <v>0.001705</v>
+      </c>
+      <c r="V233" s="1" t="n">
         <v>0.001676</v>
       </c>
     </row>
@@ -16154,9 +16856,12 @@
         <v>0.005735</v>
       </c>
       <c r="T234" s="1" t="n">
+        <v>0.00573</v>
+      </c>
+      <c r="U234" s="1" t="n">
         <v>0.005854</v>
       </c>
-      <c r="U234" s="1" t="n">
+      <c r="V234" s="1" t="n">
         <v>0.005728</v>
       </c>
     </row>
@@ -16221,9 +16926,12 @@
         <v>0.12304</v>
       </c>
       <c r="T235" s="1" t="n">
+        <v>0.12263</v>
+      </c>
+      <c r="U235" s="1" t="n">
         <v>0.1264</v>
       </c>
-      <c r="U235" s="1" t="n">
+      <c r="V235" s="1" t="n">
         <v>0.12245</v>
       </c>
     </row>
@@ -16288,9 +16996,12 @@
         <v>64.87</v>
       </c>
       <c r="T236" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="U236" s="1" t="n">
         <v>65.36</v>
       </c>
-      <c r="U236" s="1" t="n">
+      <c r="V236" s="1" t="n">
         <v>64.25</v>
       </c>
     </row>
@@ -16355,9 +17066,12 @@
         <v>0.1014</v>
       </c>
       <c r="T237" s="1" t="n">
+        <v>0.1015</v>
+      </c>
+      <c r="U237" s="1" t="n">
         <v>0.1032</v>
       </c>
-      <c r="U237" s="1" t="n">
+      <c r="V237" s="1" t="n">
         <v>0.1008</v>
       </c>
     </row>
@@ -16422,9 +17136,12 @@
         <v>0.004024</v>
       </c>
       <c r="T238" s="1" t="n">
+        <v>0.004039</v>
+      </c>
+      <c r="U238" s="1" t="n">
         <v>0.004066</v>
       </c>
-      <c r="U238" s="1" t="n">
+      <c r="V238" s="1" t="n">
         <v>0.003925</v>
       </c>
     </row>
@@ -16489,9 +17206,12 @@
         <v>0.01505</v>
       </c>
       <c r="T239" s="1" t="n">
+        <v>0.01509</v>
+      </c>
+      <c r="U239" s="1" t="n">
         <v>0.01562</v>
       </c>
-      <c r="U239" s="1" t="n">
+      <c r="V239" s="1" t="n">
         <v>0.01492</v>
       </c>
     </row>
@@ -16556,9 +17276,12 @@
         <v>0.05594</v>
       </c>
       <c r="T240" s="1" t="n">
+        <v>0.05591</v>
+      </c>
+      <c r="U240" s="1" t="n">
         <v>0.0568</v>
       </c>
-      <c r="U240" s="1" t="n">
+      <c r="V240" s="1" t="n">
         <v>0.05575</v>
       </c>
     </row>
@@ -16623,9 +17346,12 @@
         <v>0.0113</v>
       </c>
       <c r="T241" s="1" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="U241" s="1" t="n">
         <v>0.0116</v>
       </c>
-      <c r="U241" s="1" t="n">
+      <c r="V241" s="1" t="n">
         <v>0.0113</v>
       </c>
     </row>
@@ -16690,9 +17416,12 @@
         <v>0.3324</v>
       </c>
       <c r="T242" s="1" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="U242" s="1" t="n">
         <v>0.3388</v>
       </c>
-      <c r="U242" s="1" t="n">
+      <c r="V242" s="1" t="n">
         <v>0.3321</v>
       </c>
     </row>
@@ -16757,9 +17486,12 @@
         <v>0.01232</v>
       </c>
       <c r="T243" s="1" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="U243" s="1" t="n">
         <v>0.01249</v>
       </c>
-      <c r="U243" s="1" t="n">
+      <c r="V243" s="1" t="n">
         <v>0.01222</v>
       </c>
     </row>
@@ -16824,9 +17556,12 @@
         <v>0.08069</v>
       </c>
       <c r="T244" s="1" t="n">
+        <v>0.08111</v>
+      </c>
+      <c r="U244" s="1" t="n">
         <v>0.08121</v>
       </c>
-      <c r="U244" s="1" t="n">
+      <c r="V244" s="1" t="n">
         <v>0.07973</v>
       </c>
     </row>
@@ -16891,9 +17626,12 @@
         <v>0.007854</v>
       </c>
       <c r="T245" s="1" t="n">
+        <v>0.007812</v>
+      </c>
+      <c r="U245" s="1" t="n">
         <v>0.008052</v>
       </c>
-      <c r="U245" s="1" t="n">
+      <c r="V245" s="1" t="n">
         <v>0.007769</v>
       </c>
     </row>
@@ -16958,9 +17696,12 @@
         <v>0.03025</v>
       </c>
       <c r="T246" s="1" t="n">
+        <v>0.03026</v>
+      </c>
+      <c r="U246" s="1" t="n">
         <v>0.03071</v>
       </c>
-      <c r="U246" s="1" t="n">
+      <c r="V246" s="1" t="n">
         <v>0.0302</v>
       </c>
     </row>
@@ -17025,9 +17766,12 @@
         <v>0.18</v>
       </c>
       <c r="T247" s="1" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="U247" s="1" t="n">
         <v>0.1827</v>
       </c>
-      <c r="U247" s="1" t="n">
+      <c r="V247" s="1" t="n">
         <v>0.1796</v>
       </c>
     </row>
@@ -17092,9 +17836,12 @@
         <v>0.0588</v>
       </c>
       <c r="T248" s="1" t="n">
+        <v>0.05867</v>
+      </c>
+      <c r="U248" s="1" t="n">
         <v>0.05956</v>
       </c>
-      <c r="U248" s="1" t="n">
+      <c r="V248" s="1" t="n">
         <v>0.05856</v>
       </c>
     </row>
@@ -17159,9 +17906,12 @@
         <v>0.1659</v>
       </c>
       <c r="T249" s="1" t="n">
+        <v>0.1656</v>
+      </c>
+      <c r="U249" s="1" t="n">
         <v>0.1684</v>
       </c>
-      <c r="U249" s="1" t="n">
+      <c r="V249" s="1" t="n">
         <v>0.1656</v>
       </c>
     </row>
@@ -17226,10 +17976,13 @@
         <v>0.01901</v>
       </c>
       <c r="T250" s="1" t="n">
+        <v>0.01896</v>
+      </c>
+      <c r="U250" s="1" t="n">
         <v>0.01947</v>
       </c>
-      <c r="U250" s="1" t="n">
-        <v>0.01898</v>
+      <c r="V250" s="1" t="n">
+        <v>0.01896</v>
       </c>
     </row>
     <row r="251">
@@ -17293,9 +18046,12 @@
         <v>0.023</v>
       </c>
       <c r="T251" s="1" t="n">
+        <v>0.02301</v>
+      </c>
+      <c r="U251" s="1" t="n">
         <v>0.02322</v>
       </c>
-      <c r="U251" s="1" t="n">
+      <c r="V251" s="1" t="n">
         <v>0.02295</v>
       </c>
     </row>
@@ -17360,9 +18116,12 @@
         <v>0.30498</v>
       </c>
       <c r="T252" s="1" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="U252" s="1" t="n">
         <v>0.31227</v>
       </c>
-      <c r="U252" s="1" t="n">
+      <c r="V252" s="1" t="n">
         <v>0.2993</v>
       </c>
     </row>
@@ -17427,9 +18186,12 @@
         <v>0.00599</v>
       </c>
       <c r="T253" s="1" t="n">
+        <v>0.005981</v>
+      </c>
+      <c r="U253" s="1" t="n">
         <v>0.006143</v>
       </c>
-      <c r="U253" s="1" t="n">
+      <c r="V253" s="1" t="n">
         <v>0.005956</v>
       </c>
     </row>
@@ -17494,9 +18256,12 @@
         <v>0.6125</v>
       </c>
       <c r="T254" s="1" t="n">
+        <v>0.6125</v>
+      </c>
+      <c r="U254" s="1" t="n">
         <v>0.6193</v>
       </c>
-      <c r="U254" s="1" t="n">
+      <c r="V254" s="1" t="n">
         <v>0.6116</v>
       </c>
     </row>
@@ -17561,9 +18326,12 @@
         <v>0.10569</v>
       </c>
       <c r="T255" s="1" t="n">
+        <v>0.10577</v>
+      </c>
+      <c r="U255" s="1" t="n">
         <v>0.10823</v>
       </c>
-      <c r="U255" s="1" t="n">
+      <c r="V255" s="1" t="n">
         <v>0.10569</v>
       </c>
     </row>
@@ -17628,9 +18396,12 @@
         <v>0.0898</v>
       </c>
       <c r="T256" s="1" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="U256" s="1" t="n">
         <v>0.0916</v>
       </c>
-      <c r="U256" s="1" t="n">
+      <c r="V256" s="1" t="n">
         <v>0.0898</v>
       </c>
     </row>
@@ -17695,9 +18466,12 @@
         <v>0.0147</v>
       </c>
       <c r="T257" s="1" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="U257" s="1" t="n">
         <v>0.0147</v>
       </c>
-      <c r="U257" s="1" t="n">
+      <c r="V257" s="1" t="n">
         <v>0.01417</v>
       </c>
     </row>
@@ -17762,9 +18536,12 @@
         <v>0.04993</v>
       </c>
       <c r="T258" s="1" t="n">
+        <v>0.04988</v>
+      </c>
+      <c r="U258" s="1" t="n">
         <v>0.05145</v>
       </c>
-      <c r="U258" s="1" t="n">
+      <c r="V258" s="1" t="n">
         <v>0.04965</v>
       </c>
     </row>
@@ -17829,10 +18606,13 @@
         <v>0.008059999999999999</v>
       </c>
       <c r="T259" s="1" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="U259" s="1" t="n">
         <v>0.008319999999999999</v>
       </c>
-      <c r="U259" s="1" t="n">
-        <v>0.00804</v>
+      <c r="V259" s="1" t="n">
+        <v>0.008</v>
       </c>
     </row>
     <row r="260">
@@ -17896,9 +18676,12 @@
         <v>0.1898</v>
       </c>
       <c r="T260" s="1" t="n">
+        <v>0.1895</v>
+      </c>
+      <c r="U260" s="1" t="n">
         <v>0.1915</v>
       </c>
-      <c r="U260" s="1" t="n">
+      <c r="V260" s="1" t="n">
         <v>0.1892</v>
       </c>
     </row>
@@ -17963,9 +18746,12 @@
         <v>0.098</v>
       </c>
       <c r="T261" s="1" t="n">
+        <v>0.0977</v>
+      </c>
+      <c r="U261" s="1" t="n">
         <v>0.0993</v>
       </c>
-      <c r="U261" s="1" t="n">
+      <c r="V261" s="1" t="n">
         <v>0.09760000000000001</v>
       </c>
     </row>
@@ -18030,9 +18816,12 @@
         <v>0.2107</v>
       </c>
       <c r="T262" s="1" t="n">
+        <v>0.2105</v>
+      </c>
+      <c r="U262" s="1" t="n">
         <v>0.2144</v>
       </c>
-      <c r="U262" s="1" t="n">
+      <c r="V262" s="1" t="n">
         <v>0.2103</v>
       </c>
     </row>
@@ -18097,9 +18886,12 @@
         <v>0.008479</v>
       </c>
       <c r="T263" s="1" t="n">
+        <v>0.008486</v>
+      </c>
+      <c r="U263" s="1" t="n">
         <v>0.008560999999999999</v>
       </c>
-      <c r="U263" s="1" t="n">
+      <c r="V263" s="1" t="n">
         <v>0.008366</v>
       </c>
     </row>
@@ -18164,10 +18956,13 @@
         <v>2.633</v>
       </c>
       <c r="T264" s="1" t="n">
+        <v>2.628</v>
+      </c>
+      <c r="U264" s="1" t="n">
         <v>2.659</v>
       </c>
-      <c r="U264" s="1" t="n">
-        <v>2.629</v>
+      <c r="V264" s="1" t="n">
+        <v>2.628</v>
       </c>
     </row>
     <row r="265">
@@ -18231,9 +19026,12 @@
         <v>0.01863</v>
       </c>
       <c r="T265" s="1" t="n">
+        <v>0.01858</v>
+      </c>
+      <c r="U265" s="1" t="n">
         <v>0.01907</v>
       </c>
-      <c r="U265" s="1" t="n">
+      <c r="V265" s="1" t="n">
         <v>0.01847</v>
       </c>
     </row>
@@ -18298,9 +19096,12 @@
         <v>0.3601</v>
       </c>
       <c r="T266" s="1" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="U266" s="1" t="n">
         <v>0.3612</v>
       </c>
-      <c r="U266" s="1" t="n">
+      <c r="V266" s="1" t="n">
         <v>0.359</v>
       </c>
     </row>
@@ -18365,9 +19166,12 @@
         <v>0.03442</v>
       </c>
       <c r="T267" s="1" t="n">
+        <v>0.03438</v>
+      </c>
+      <c r="U267" s="1" t="n">
         <v>0.03464</v>
       </c>
-      <c r="U267" s="1" t="n">
+      <c r="V267" s="1" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -18432,9 +19236,12 @@
         <v>0.123</v>
       </c>
       <c r="T268" s="1" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="U268" s="1" t="n">
         <v>0.123</v>
       </c>
-      <c r="U268" s="1" t="n">
+      <c r="V268" s="1" t="n">
         <v>0.117</v>
       </c>
     </row>
@@ -18499,10 +19306,13 @@
         <v>0.07933</v>
       </c>
       <c r="T269" s="1" t="n">
+        <v>0.07925</v>
+      </c>
+      <c r="U269" s="1" t="n">
         <v>0.08105</v>
       </c>
-      <c r="U269" s="1" t="n">
-        <v>0.07933</v>
+      <c r="V269" s="1" t="n">
+        <v>0.07925</v>
       </c>
     </row>
     <row r="270">
@@ -18566,9 +19376,12 @@
         <v>0.01377</v>
       </c>
       <c r="T270" s="1" t="n">
+        <v>0.01376</v>
+      </c>
+      <c r="U270" s="1" t="n">
         <v>0.01402</v>
       </c>
-      <c r="U270" s="1" t="n">
+      <c r="V270" s="1" t="n">
         <v>0.01374</v>
       </c>
     </row>
@@ -18633,9 +19446,12 @@
         <v>0.007512</v>
       </c>
       <c r="T271" s="1" t="n">
+        <v>0.007513</v>
+      </c>
+      <c r="U271" s="1" t="n">
         <v>0.007707</v>
       </c>
-      <c r="U271" s="1" t="n">
+      <c r="V271" s="1" t="n">
         <v>0.007504</v>
       </c>
     </row>
@@ -18700,9 +19516,12 @@
         <v>0.07428999999999999</v>
       </c>
       <c r="T272" s="1" t="n">
+        <v>0.07425</v>
+      </c>
+      <c r="U272" s="1" t="n">
         <v>0.07452</v>
       </c>
-      <c r="U272" s="1" t="n">
+      <c r="V272" s="1" t="n">
         <v>0.07396</v>
       </c>
     </row>
@@ -18767,9 +19586,12 @@
         <v>3.15e-05</v>
       </c>
       <c r="T273" s="1" t="n">
+        <v>3.15e-05</v>
+      </c>
+      <c r="U273" s="1" t="n">
         <v>3.16e-05</v>
       </c>
-      <c r="U273" s="1" t="n">
+      <c r="V273" s="1" t="n">
         <v>3.11e-05</v>
       </c>
     </row>
@@ -18834,9 +19656,12 @@
         <v>0.005445</v>
       </c>
       <c r="T274" s="1" t="n">
+        <v>0.005432</v>
+      </c>
+      <c r="U274" s="1" t="n">
         <v>0.005646</v>
       </c>
-      <c r="U274" s="1" t="n">
+      <c r="V274" s="1" t="n">
         <v>0.005409</v>
       </c>
     </row>
@@ -18901,10 +19726,13 @@
         <v>0.1788</v>
       </c>
       <c r="T275" s="1" t="n">
+        <v>0.1766</v>
+      </c>
+      <c r="U275" s="1" t="n">
         <v>0.1821</v>
       </c>
-      <c r="U275" s="1" t="n">
-        <v>0.1784</v>
+      <c r="V275" s="1" t="n">
+        <v>0.1766</v>
       </c>
     </row>
     <row r="276">
@@ -18968,9 +19796,12 @@
         <v>0.006819</v>
       </c>
       <c r="T276" s="1" t="n">
+        <v>0.006817</v>
+      </c>
+      <c r="U276" s="1" t="n">
         <v>0.006933</v>
       </c>
-      <c r="U276" s="1" t="n">
+      <c r="V276" s="1" t="n">
         <v>0.006809</v>
       </c>
     </row>
@@ -19035,9 +19866,12 @@
         <v>0.1309</v>
       </c>
       <c r="T277" s="1" t="n">
+        <v>0.1308</v>
+      </c>
+      <c r="U277" s="1" t="n">
         <v>0.1332</v>
       </c>
-      <c r="U277" s="1" t="n">
+      <c r="V277" s="1" t="n">
         <v>0.1302</v>
       </c>
     </row>
@@ -19102,9 +19936,12 @@
         <v>0.02319</v>
       </c>
       <c r="T278" s="1" t="n">
+        <v>0.02315</v>
+      </c>
+      <c r="U278" s="1" t="n">
         <v>0.0237</v>
       </c>
-      <c r="U278" s="1" t="n">
+      <c r="V278" s="1" t="n">
         <v>0.02306</v>
       </c>
     </row>
@@ -19169,10 +20006,13 @@
         <v>0.01811</v>
       </c>
       <c r="T279" s="1" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="U279" s="1" t="n">
         <v>0.01837</v>
       </c>
-      <c r="U279" s="1" t="n">
-        <v>0.01811</v>
+      <c r="V279" s="1" t="n">
+        <v>0.0181</v>
       </c>
     </row>
     <row r="280">
@@ -19236,9 +20076,12 @@
         <v>0.03678</v>
       </c>
       <c r="T280" s="1" t="n">
+        <v>0.03668</v>
+      </c>
+      <c r="U280" s="1" t="n">
         <v>0.03802</v>
       </c>
-      <c r="U280" s="1" t="n">
+      <c r="V280" s="1" t="n">
         <v>0.03666</v>
       </c>
     </row>
@@ -19303,9 +20146,12 @@
         <v>0.03978</v>
       </c>
       <c r="T281" s="1" t="n">
+        <v>0.0397</v>
+      </c>
+      <c r="U281" s="1" t="n">
         <v>0.0401</v>
       </c>
-      <c r="U281" s="1" t="n">
+      <c r="V281" s="1" t="n">
         <v>0.03953</v>
       </c>
     </row>
@@ -19370,9 +20216,12 @@
         <v>0.3055</v>
       </c>
       <c r="T282" s="1" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="U282" s="1" t="n">
         <v>0.3059</v>
       </c>
-      <c r="U282" s="1" t="n">
+      <c r="V282" s="1" t="n">
         <v>0.3001</v>
       </c>
     </row>
@@ -19437,9 +20286,12 @@
         <v>0.01118</v>
       </c>
       <c r="T283" s="1" t="n">
+        <v>0.01119</v>
+      </c>
+      <c r="U283" s="1" t="n">
         <v>0.01133</v>
       </c>
-      <c r="U283" s="1" t="n">
+      <c r="V283" s="1" t="n">
         <v>0.01115</v>
       </c>
     </row>
@@ -19504,9 +20356,12 @@
         <v>9.6e-06</v>
       </c>
       <c r="T284" s="1" t="n">
+        <v>9.7e-06</v>
+      </c>
+      <c r="U284" s="1" t="n">
         <v>9.799999999999999e-06</v>
       </c>
-      <c r="U284" s="1" t="n">
+      <c r="V284" s="1" t="n">
         <v>9.500000000000001e-06</v>
       </c>
     </row>
@@ -19571,9 +20426,12 @@
         <v>0.1144</v>
       </c>
       <c r="T285" s="1" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="U285" s="1" t="n">
         <v>0.1159</v>
       </c>
-      <c r="U285" s="1" t="n">
+      <c r="V285" s="1" t="n">
         <v>0.1141</v>
       </c>
     </row>
@@ -19638,9 +20496,12 @@
         <v>0.003441</v>
       </c>
       <c r="T286" s="1" t="n">
+        <v>0.003439</v>
+      </c>
+      <c r="U286" s="1" t="n">
         <v>0.003485</v>
       </c>
-      <c r="U286" s="1" t="n">
+      <c r="V286" s="1" t="n">
         <v>0.003422</v>
       </c>
     </row>
@@ -19705,9 +20566,12 @@
         <v>0.08491</v>
       </c>
       <c r="T287" s="1" t="n">
+        <v>0.08487</v>
+      </c>
+      <c r="U287" s="1" t="n">
         <v>0.08577</v>
       </c>
-      <c r="U287" s="1" t="n">
+      <c r="V287" s="1" t="n">
         <v>0.08465</v>
       </c>
     </row>
@@ -19772,9 +20636,12 @@
         <v>0.09994</v>
       </c>
       <c r="T288" s="1" t="n">
+        <v>0.09943</v>
+      </c>
+      <c r="U288" s="1" t="n">
         <v>0.10076</v>
       </c>
-      <c r="U288" s="1" t="n">
+      <c r="V288" s="1" t="n">
         <v>0.09869</v>
       </c>
     </row>
@@ -19839,9 +20706,12 @@
         <v>0.4334</v>
       </c>
       <c r="T289" s="1" t="n">
+        <v>0.4353</v>
+      </c>
+      <c r="U289" s="1" t="n">
         <v>0.4367</v>
       </c>
-      <c r="U289" s="1" t="n">
+      <c r="V289" s="1" t="n">
         <v>0.4307</v>
       </c>
     </row>
@@ -19906,9 +20776,12 @@
         <v>0.03964</v>
       </c>
       <c r="T290" s="1" t="n">
+        <v>0.03951</v>
+      </c>
+      <c r="U290" s="1" t="n">
         <v>0.03966</v>
       </c>
-      <c r="U290" s="1" t="n">
+      <c r="V290" s="1" t="n">
         <v>0.03878</v>
       </c>
     </row>
@@ -19973,9 +20846,12 @@
         <v>0.2351</v>
       </c>
       <c r="T291" s="1" t="n">
+        <v>0.2345</v>
+      </c>
+      <c r="U291" s="1" t="n">
         <v>0.2474</v>
       </c>
-      <c r="U291" s="1" t="n">
+      <c r="V291" s="1" t="n">
         <v>0.2344</v>
       </c>
     </row>
@@ -20040,9 +20916,12 @@
         <v>0.28363</v>
       </c>
       <c r="T292" s="1" t="n">
+        <v>0.2832</v>
+      </c>
+      <c r="U292" s="1" t="n">
         <v>0.28533</v>
       </c>
-      <c r="U292" s="1" t="n">
+      <c r="V292" s="1" t="n">
         <v>0.28126</v>
       </c>
     </row>
@@ -20107,9 +20986,12 @@
         <v>0.1504</v>
       </c>
       <c r="T293" s="1" t="n">
-        <v>0.1515</v>
+        <v>0.152</v>
       </c>
       <c r="U293" s="1" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="V293" s="1" t="n">
         <v>0.1487</v>
       </c>
     </row>
@@ -20174,10 +21056,13 @@
         <v>4.174</v>
       </c>
       <c r="T294" s="1" t="n">
+        <v>4.165</v>
+      </c>
+      <c r="U294" s="1" t="n">
         <v>4.269</v>
       </c>
-      <c r="U294" s="1" t="n">
-        <v>4.171</v>
+      <c r="V294" s="1" t="n">
+        <v>4.165</v>
       </c>
     </row>
     <row r="295">
@@ -20241,9 +21126,12 @@
         <v>0.03397</v>
       </c>
       <c r="T295" s="1" t="n">
+        <v>0.03416</v>
+      </c>
+      <c r="U295" s="1" t="n">
         <v>0.03509</v>
       </c>
-      <c r="U295" s="1" t="n">
+      <c r="V295" s="1" t="n">
         <v>0.03212</v>
       </c>
     </row>
@@ -20308,9 +21196,12 @@
         <v>0.000969</v>
       </c>
       <c r="T296" s="1" t="n">
+        <v>0.0009700000000000001</v>
+      </c>
+      <c r="U296" s="1" t="n">
         <v>0.0009909999999999999</v>
       </c>
-      <c r="U296" s="1" t="n">
+      <c r="V296" s="1" t="n">
         <v>0.000964</v>
       </c>
     </row>
@@ -20375,9 +21266,12 @@
         <v>0.08153000000000001</v>
       </c>
       <c r="T297" s="1" t="n">
+        <v>0.0815</v>
+      </c>
+      <c r="U297" s="1" t="n">
         <v>0.08259</v>
       </c>
-      <c r="U297" s="1" t="n">
+      <c r="V297" s="1" t="n">
         <v>0.08135000000000001</v>
       </c>
     </row>
@@ -20442,9 +21336,12 @@
         <v>0.05839</v>
       </c>
       <c r="T298" s="1" t="n">
-        <v>0.05845</v>
+        <v>0.05869</v>
       </c>
       <c r="U298" s="1" t="n">
+        <v>0.05869</v>
+      </c>
+      <c r="V298" s="1" t="n">
         <v>0.05745</v>
       </c>
     </row>
@@ -20509,9 +21406,12 @@
         <v>0.091</v>
       </c>
       <c r="T299" s="1" t="n">
+        <v>0.09103</v>
+      </c>
+      <c r="U299" s="1" t="n">
         <v>0.0917</v>
       </c>
-      <c r="U299" s="1" t="n">
+      <c r="V299" s="1" t="n">
         <v>0.09028</v>
       </c>
     </row>
@@ -20576,9 +21476,12 @@
         <v>0.02725</v>
       </c>
       <c r="T300" s="1" t="n">
+        <v>0.02727</v>
+      </c>
+      <c r="U300" s="1" t="n">
         <v>0.02792</v>
       </c>
-      <c r="U300" s="1" t="n">
+      <c r="V300" s="1" t="n">
         <v>0.02723</v>
       </c>
     </row>
@@ -20643,9 +21546,12 @@
         <v>0.06551999999999999</v>
       </c>
       <c r="T301" s="1" t="n">
+        <v>0.06562</v>
+      </c>
+      <c r="U301" s="1" t="n">
         <v>0.06634</v>
       </c>
-      <c r="U301" s="1" t="n">
+      <c r="V301" s="1" t="n">
         <v>0.06525</v>
       </c>
     </row>
@@ -20710,9 +21616,12 @@
         <v>0.053462</v>
       </c>
       <c r="T302" s="1" t="n">
+        <v>0.053416</v>
+      </c>
+      <c r="U302" s="1" t="n">
         <v>0.053585</v>
       </c>
-      <c r="U302" s="1" t="n">
+      <c r="V302" s="1" t="n">
         <v>0.051794</v>
       </c>
     </row>
@@ -20777,9 +21686,12 @@
         <v>5172</v>
       </c>
       <c r="T303" s="1" t="n">
+        <v>5167.1</v>
+      </c>
+      <c r="U303" s="1" t="n">
         <v>5177.6</v>
       </c>
-      <c r="U303" s="1" t="n">
+      <c r="V303" s="1" t="n">
         <v>5156.4</v>
       </c>
     </row>
@@ -20844,9 +21756,12 @@
         <v>14.88</v>
       </c>
       <c r="T304" s="1" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="U304" s="1" t="n">
         <v>15.1</v>
       </c>
-      <c r="U304" s="1" t="n">
+      <c r="V304" s="1" t="n">
         <v>14.8</v>
       </c>
     </row>
@@ -20911,9 +21826,12 @@
         <v>0.003707</v>
       </c>
       <c r="T305" s="1" t="n">
+        <v>0.003717</v>
+      </c>
+      <c r="U305" s="1" t="n">
         <v>0.00379</v>
       </c>
-      <c r="U305" s="1" t="n">
+      <c r="V305" s="1" t="n">
         <v>0.003688</v>
       </c>
     </row>
@@ -20978,9 +21896,12 @@
         <v>0.4552</v>
       </c>
       <c r="T306" s="1" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="U306" s="1" t="n">
         <v>0.4608</v>
       </c>
-      <c r="U306" s="1" t="n">
+      <c r="V306" s="1" t="n">
         <v>0.4531</v>
       </c>
     </row>
@@ -21045,9 +21966,12 @@
         <v>0.04671</v>
       </c>
       <c r="T307" s="1" t="n">
+        <v>0.04673</v>
+      </c>
+      <c r="U307" s="1" t="n">
         <v>0.04753</v>
       </c>
-      <c r="U307" s="1" t="n">
+      <c r="V307" s="1" t="n">
         <v>0.04651</v>
       </c>
     </row>
@@ -21112,9 +22036,12 @@
         <v>1.505</v>
       </c>
       <c r="T308" s="1" t="n">
+        <v>1.4885</v>
+      </c>
+      <c r="U308" s="1" t="n">
         <v>1.5096</v>
       </c>
-      <c r="U308" s="1" t="n">
+      <c r="V308" s="1" t="n">
         <v>1.4598</v>
       </c>
     </row>
@@ -21179,9 +22106,12 @@
         <v>0.0007878</v>
       </c>
       <c r="T309" s="1" t="n">
+        <v>0.0007911</v>
+      </c>
+      <c r="U309" s="1" t="n">
         <v>0.0008101</v>
       </c>
-      <c r="U309" s="1" t="n">
+      <c r="V309" s="1" t="n">
         <v>0.0007861</v>
       </c>
     </row>
@@ -21246,9 +22176,12 @@
         <v>4.55</v>
       </c>
       <c r="T310" s="1" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="U310" s="1" t="n">
         <v>4.721</v>
       </c>
-      <c r="U310" s="1" t="n">
+      <c r="V310" s="1" t="n">
         <v>4.549</v>
       </c>
     </row>
@@ -21313,9 +22246,12 @@
         <v>4.761</v>
       </c>
       <c r="T311" s="1" t="n">
+        <v>4.777</v>
+      </c>
+      <c r="U311" s="1" t="n">
         <v>4.805</v>
       </c>
-      <c r="U311" s="1" t="n">
+      <c r="V311" s="1" t="n">
         <v>4.743</v>
       </c>
     </row>
@@ -21380,10 +22316,13 @@
         <v>0.08043</v>
       </c>
       <c r="T312" s="1" t="n">
+        <v>0.08033999999999999</v>
+      </c>
+      <c r="U312" s="1" t="n">
         <v>0.08212</v>
       </c>
-      <c r="U312" s="1" t="n">
-        <v>0.08043</v>
+      <c r="V312" s="1" t="n">
+        <v>0.08033999999999999</v>
       </c>
     </row>
     <row r="313">
@@ -21447,9 +22386,12 @@
         <v>2.021</v>
       </c>
       <c r="T313" s="1" t="n">
+        <v>2.022</v>
+      </c>
+      <c r="U313" s="1" t="n">
         <v>2.05</v>
       </c>
-      <c r="U313" s="1" t="n">
+      <c r="V313" s="1" t="n">
         <v>2.005</v>
       </c>
     </row>
@@ -21514,9 +22456,12 @@
         <v>0.07213</v>
       </c>
       <c r="T314" s="1" t="n">
+        <v>0.07196</v>
+      </c>
+      <c r="U314" s="1" t="n">
         <v>0.07482999999999999</v>
       </c>
-      <c r="U314" s="1" t="n">
+      <c r="V314" s="1" t="n">
         <v>0.06802</v>
       </c>
     </row>
@@ -21581,9 +22526,12 @@
         <v>0.9419999999999999</v>
       </c>
       <c r="T315" s="1" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="U315" s="1" t="n">
         <v>0.97</v>
       </c>
-      <c r="U315" s="1" t="n">
+      <c r="V315" s="1" t="n">
         <v>0.9350000000000001</v>
       </c>
     </row>
@@ -21648,10 +22596,13 @@
         <v>0.1301</v>
       </c>
       <c r="T316" s="1" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="U316" s="1" t="n">
         <v>0.1313</v>
       </c>
-      <c r="U316" s="1" t="n">
-        <v>0.1299</v>
+      <c r="V316" s="1" t="n">
+        <v>0.1295</v>
       </c>
     </row>
     <row r="317">
@@ -21715,9 +22666,12 @@
         <v>0.1867</v>
       </c>
       <c r="T317" s="1" t="n">
-        <v>0.1867</v>
+        <v>0.187</v>
       </c>
       <c r="U317" s="1" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="V317" s="1" t="n">
         <v>0.1761</v>
       </c>
     </row>
@@ -21782,9 +22736,12 @@
         <v>0.01607</v>
       </c>
       <c r="T318" s="1" t="n">
+        <v>0.01607</v>
+      </c>
+      <c r="U318" s="1" t="n">
         <v>0.01666</v>
       </c>
-      <c r="U318" s="1" t="n">
+      <c r="V318" s="1" t="n">
         <v>0.01607</v>
       </c>
     </row>
@@ -21849,9 +22806,12 @@
         <v>0.08339000000000001</v>
       </c>
       <c r="T319" s="1" t="n">
+        <v>0.0834</v>
+      </c>
+      <c r="U319" s="1" t="n">
         <v>0.08445999999999999</v>
       </c>
-      <c r="U319" s="1" t="n">
+      <c r="V319" s="1" t="n">
         <v>0.08318</v>
       </c>
     </row>
@@ -21916,9 +22876,12 @@
         <v>0.007506</v>
       </c>
       <c r="T320" s="1" t="n">
+        <v>0.007502</v>
+      </c>
+      <c r="U320" s="1" t="n">
         <v>0.00